--- a/STS_holy_grail_v2.xlsx
+++ b/STS_holy_grail_v2.xlsx
@@ -474,7 +474,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.72</v>
+        <v>-0.96</v>
       </c>
     </row>
     <row r="6">
@@ -537,7 +537,7 @@
         <v>50.88</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.33</v>
+        <v>-1.58</v>
       </c>
     </row>
     <row r="11">
@@ -556,7 +556,7 @@
         <v>34.62</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.75</v>
+        <v>-3.01</v>
       </c>
     </row>
     <row r="12">
@@ -575,7 +575,7 @@
         <v>38.35</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.38</v>
+        <v>-0.62</v>
       </c>
     </row>
     <row r="13">
@@ -594,7 +594,7 @@
         <v>58.06</v>
       </c>
       <c r="E13" t="n">
-        <v>4.08</v>
+        <v>3.85</v>
       </c>
     </row>
     <row r="15">
@@ -647,7 +647,7 @@
         <v>39.78</v>
       </c>
       <c r="E17" t="n">
-        <v>0.11</v>
+        <v>-0.13</v>
       </c>
     </row>
     <row r="18">
@@ -666,7 +666,7 @@
         <v>35</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.52</v>
+        <v>-1.77</v>
       </c>
     </row>
     <row r="19">
@@ -685,7 +685,7 @@
         <v>35.71</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.53</v>
+        <v>-1.77</v>
       </c>
     </row>
     <row r="20">
@@ -704,7 +704,7 @@
         <v>31.58</v>
       </c>
       <c r="E20" t="n">
-        <v>-7.31</v>
+        <v>-7.56</v>
       </c>
     </row>
     <row r="21">
@@ -723,7 +723,7 @@
         <v>54.65</v>
       </c>
       <c r="E21" t="n">
-        <v>2.07</v>
+        <v>1.83</v>
       </c>
     </row>
     <row r="23">
@@ -776,7 +776,7 @@
         <v>60</v>
       </c>
       <c r="E25" t="n">
-        <v>7.22</v>
+        <v>6.97</v>
       </c>
     </row>
     <row r="26">
@@ -795,7 +795,7 @@
         <v>40</v>
       </c>
       <c r="E26" t="n">
-        <v>-5.33</v>
+        <v>-5.59</v>
       </c>
     </row>
     <row r="27">
@@ -814,7 +814,7 @@
         <v>33.33</v>
       </c>
       <c r="E27" t="n">
-        <v>-1.45</v>
+        <v>-1.7</v>
       </c>
     </row>
     <row r="29">
@@ -867,7 +867,7 @@
         <v>39.77</v>
       </c>
       <c r="E31" t="n">
-        <v>0.68</v>
+        <v>0.43</v>
       </c>
     </row>
     <row r="32">
@@ -886,7 +886,7 @@
         <v>44.53</v>
       </c>
       <c r="E32" t="n">
-        <v>-2.59</v>
+        <v>-2.83</v>
       </c>
     </row>
   </sheetData>
@@ -1063,7 +1063,7 @@
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="n">
-        <v>-2.01</v>
+        <v>-2</v>
       </c>
       <c r="M3" t="n">
         <v>-0.06</v>
@@ -1110,7 +1110,7 @@
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="n">
-        <v>-0.73</v>
+        <v>-0.76</v>
       </c>
       <c r="M4" t="n">
         <v>-0.3</v>
@@ -1251,7 +1251,7 @@
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="n">
-        <v>-1.36</v>
+        <v>-1.45</v>
       </c>
       <c r="M7" t="n">
         <v>-0.28</v>
@@ -1301,7 +1301,7 @@
         <v>-0.97</v>
       </c>
       <c r="M8" t="n">
-        <v>3.8</v>
+        <v>3.55</v>
       </c>
       <c r="N8" t="b">
         <v>0</v>
@@ -1348,7 +1348,7 @@
         <v>-1.79</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.08</v>
+        <v>-0.33</v>
       </c>
       <c r="N9" t="b">
         <v>0</v>
@@ -1399,7 +1399,7 @@
         <v>-1.23</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.64</v>
+        <v>-0.88</v>
       </c>
       <c r="N10" t="b">
         <v>0</v>
@@ -1446,7 +1446,7 @@
         <v>-1.92</v>
       </c>
       <c r="M11" t="n">
-        <v>1.06</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="N11" t="b">
         <v>0</v>
@@ -1493,7 +1493,7 @@
         <v>-4.62</v>
       </c>
       <c r="M12" t="n">
-        <v>-4.24</v>
+        <v>-4.49</v>
       </c>
       <c r="N12" t="b">
         <v>0</v>
@@ -1540,7 +1540,7 @@
         <v>-4.08</v>
       </c>
       <c r="M13" t="n">
-        <v>-4.19</v>
+        <v>-4.44</v>
       </c>
       <c r="N13" t="b">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         <v>-0.7</v>
       </c>
       <c r="M14" t="n">
-        <v>1.67</v>
+        <v>1.42</v>
       </c>
       <c r="N14" t="b">
         <v>0</v>
@@ -1634,7 +1634,7 @@
         <v>-1.07</v>
       </c>
       <c r="M15" t="n">
-        <v>1.78</v>
+        <v>1.53</v>
       </c>
       <c r="N15" t="b">
         <v>1</v>
@@ -1681,7 +1681,7 @@
         <v>-2.44</v>
       </c>
       <c r="M16" t="n">
-        <v>3.78</v>
+        <v>3.53</v>
       </c>
       <c r="N16" t="b">
         <v>1</v>
@@ -1728,7 +1728,7 @@
         <v>-1.2</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.41</v>
+        <v>-1.66</v>
       </c>
       <c r="N17" t="b">
         <v>1</v>
@@ -1775,7 +1775,7 @@
         <v>-3.95</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.43</v>
+        <v>-0.68</v>
       </c>
       <c r="N18" t="b">
         <v>1</v>
@@ -1822,7 +1822,7 @@
         <v>-22.27</v>
       </c>
       <c r="M19" t="n">
-        <v>-20.24</v>
+        <v>-20.49</v>
       </c>
       <c r="N19" t="b">
         <v>0</v>
@@ -1869,7 +1869,7 @@
         <v>-3.87</v>
       </c>
       <c r="M20" t="n">
-        <v>0.97</v>
+        <v>0.72</v>
       </c>
       <c r="N20" t="b">
         <v>1</v>
@@ -1916,7 +1916,7 @@
         <v>-3.78</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.02</v>
+        <v>-0.27</v>
       </c>
       <c r="N21" t="b">
         <v>1</v>
@@ -1963,7 +1963,7 @@
         <v>-4.85</v>
       </c>
       <c r="M22" t="n">
-        <v>0.84</v>
+        <v>0.6</v>
       </c>
       <c r="N22" t="b">
         <v>1</v>
@@ -2010,7 +2010,7 @@
         <v>-0.4</v>
       </c>
       <c r="M23" t="n">
-        <v>2.65</v>
+        <v>2.4</v>
       </c>
       <c r="N23" t="b">
         <v>0</v>
@@ -2057,7 +2057,7 @@
         <v>-7.96</v>
       </c>
       <c r="M24" t="n">
-        <v>-6.54</v>
+        <v>-6.79</v>
       </c>
       <c r="N24" t="b">
         <v>0</v>
@@ -2104,7 +2104,7 @@
         <v>-5.89</v>
       </c>
       <c r="M25" t="n">
-        <v>0.61</v>
+        <v>0.37</v>
       </c>
       <c r="N25" t="b">
         <v>0</v>
@@ -2151,7 +2151,7 @@
         <v>-9.640000000000001</v>
       </c>
       <c r="M26" t="n">
-        <v>-6.12</v>
+        <v>-6.37</v>
       </c>
       <c r="N26" t="b">
         <v>0</v>
@@ -2198,7 +2198,7 @@
         <v>-4.53</v>
       </c>
       <c r="M27" t="n">
-        <v>3.87</v>
+        <v>3.62</v>
       </c>
       <c r="N27" t="b">
         <v>1</v>
@@ -2245,7 +2245,7 @@
         <v>-9.220000000000001</v>
       </c>
       <c r="M28" t="n">
-        <v>-6.26</v>
+        <v>-6.51</v>
       </c>
       <c r="N28" t="b">
         <v>0</v>
@@ -2289,10 +2289,10 @@
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="n">
-        <v>-11.77</v>
+        <v>-11.81</v>
       </c>
       <c r="M29" t="n">
-        <v>-10.78</v>
+        <v>-11.03</v>
       </c>
       <c r="N29" t="b">
         <v>0</v>
@@ -2339,7 +2339,7 @@
         <v>-18.92</v>
       </c>
       <c r="M30" t="n">
-        <v>-12.44</v>
+        <v>-12.68</v>
       </c>
       <c r="N30" t="b">
         <v>0</v>
@@ -2388,7 +2388,7 @@
         <v>-6.51</v>
       </c>
       <c r="M31" t="n">
-        <v>2.08</v>
+        <v>1.83</v>
       </c>
       <c r="N31" t="b">
         <v>0</v>
@@ -2437,7 +2437,7 @@
         <v>-11.94</v>
       </c>
       <c r="M32" t="n">
-        <v>-9.98</v>
+        <v>-10.22</v>
       </c>
       <c r="N32" t="b">
         <v>0</v>
@@ -2486,7 +2486,7 @@
         <v>-3.07</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.08</v>
+        <v>-0.32</v>
       </c>
       <c r="N33" t="b">
         <v>0</v>
@@ -2535,7 +2535,7 @@
         <v>-7.3</v>
       </c>
       <c r="M34" t="n">
-        <v>-2.53</v>
+        <v>-2.78</v>
       </c>
       <c r="N34" t="b">
         <v>0</v>
@@ -2584,7 +2584,7 @@
         <v>-12.91</v>
       </c>
       <c r="M35" t="n">
-        <v>-9.73</v>
+        <v>-9.970000000000001</v>
       </c>
       <c r="N35" t="b">
         <v>1</v>
@@ -2633,7 +2633,7 @@
         <v>-6.01</v>
       </c>
       <c r="M36" t="n">
-        <v>5.95</v>
+        <v>5.71</v>
       </c>
       <c r="N36" t="b">
         <v>0</v>
@@ -2682,7 +2682,7 @@
         <v>-0.88</v>
       </c>
       <c r="M37" t="n">
-        <v>2.57</v>
+        <v>2.32</v>
       </c>
       <c r="N37" t="b">
         <v>1</v>
@@ -2731,7 +2731,7 @@
         <v>-7.44</v>
       </c>
       <c r="M38" t="n">
-        <v>-0.48</v>
+        <v>-0.73</v>
       </c>
       <c r="N38" t="b">
         <v>0</v>
@@ -2780,7 +2780,7 @@
         <v>-2.64</v>
       </c>
       <c r="M39" t="n">
-        <v>0.42</v>
+        <v>0.17</v>
       </c>
       <c r="N39" t="b">
         <v>1</v>
@@ -2829,7 +2829,7 @@
         <v>-7.05</v>
       </c>
       <c r="M40" t="n">
-        <v>-5.22</v>
+        <v>-5.46</v>
       </c>
       <c r="N40" t="b">
         <v>0</v>
@@ -2878,7 +2878,7 @@
         <v>-5.21</v>
       </c>
       <c r="M41" t="n">
-        <v>10.85</v>
+        <v>10.61</v>
       </c>
       <c r="N41" t="b">
         <v>1</v>
@@ -2927,7 +2927,7 @@
         <v>-16.17</v>
       </c>
       <c r="M42" t="n">
-        <v>-10.53</v>
+        <v>-10.78</v>
       </c>
       <c r="N42" t="b">
         <v>0</v>
@@ -2976,7 +2976,7 @@
         <v>-12.94</v>
       </c>
       <c r="M43" t="n">
-        <v>-8.82</v>
+        <v>-9.07</v>
       </c>
       <c r="N43" t="b">
         <v>0</v>
@@ -3025,7 +3025,7 @@
         <v>-9.02</v>
       </c>
       <c r="M44" t="n">
-        <v>-4.64</v>
+        <v>-4.88</v>
       </c>
       <c r="N44" t="b">
         <v>1</v>
@@ -3074,7 +3074,7 @@
         <v>-0.9</v>
       </c>
       <c r="M45" t="n">
-        <v>17.55</v>
+        <v>17.31</v>
       </c>
       <c r="N45" t="b">
         <v>0</v>
@@ -3123,7 +3123,7 @@
         <v>-10.12</v>
       </c>
       <c r="M46" t="n">
-        <v>-2.98</v>
+        <v>-3.22</v>
       </c>
       <c r="N46" t="b">
         <v>0</v>
@@ -3172,7 +3172,7 @@
         <v>-9.65</v>
       </c>
       <c r="M47" t="n">
-        <v>-5.21</v>
+        <v>-5.46</v>
       </c>
       <c r="N47" t="b">
         <v>0</v>
@@ -3221,7 +3221,7 @@
         <v>-14.61</v>
       </c>
       <c r="M48" t="n">
-        <v>-12.61</v>
+        <v>-12.85</v>
       </c>
       <c r="N48" t="b">
         <v>1</v>
@@ -3267,10 +3267,10 @@
       <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="n">
-        <v>-19.23</v>
+        <v>-19.25</v>
       </c>
       <c r="M49" t="n">
-        <v>-17.07</v>
+        <v>-17.32</v>
       </c>
       <c r="N49" t="b">
         <v>1</v>
@@ -3319,7 +3319,7 @@
         <v>-5.67</v>
       </c>
       <c r="M50" t="n">
-        <v>3.78</v>
+        <v>3.53</v>
       </c>
       <c r="N50" t="b">
         <v>1</v>
@@ -3365,10 +3365,10 @@
       <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="n">
-        <v>-10.79</v>
+        <v>-10.8</v>
       </c>
       <c r="M51" t="n">
-        <v>-9.76</v>
+        <v>-10.01</v>
       </c>
       <c r="N51" t="b">
         <v>1</v>
@@ -3417,7 +3417,7 @@
         <v>-13.32</v>
       </c>
       <c r="M52" t="n">
-        <v>-9.029999999999999</v>
+        <v>-9.279999999999999</v>
       </c>
       <c r="N52" t="b">
         <v>0</v>
@@ -3466,7 +3466,7 @@
         <v>-5.8</v>
       </c>
       <c r="M53" t="n">
-        <v>-4.09</v>
+        <v>-4.33</v>
       </c>
       <c r="N53" t="b">
         <v>0</v>
@@ -3515,7 +3515,7 @@
         <v>-12.98</v>
       </c>
       <c r="M54" t="n">
-        <v>-5.43</v>
+        <v>-5.67</v>
       </c>
       <c r="N54" t="b">
         <v>0</v>
@@ -3568,7 +3568,7 @@
         <v>-4.96</v>
       </c>
       <c r="M55" t="n">
-        <v>-1.41</v>
+        <v>-1.66</v>
       </c>
       <c r="N55" t="b">
         <v>0</v>
@@ -3617,7 +3617,7 @@
         <v>-12.18</v>
       </c>
       <c r="M56" t="n">
-        <v>-9.08</v>
+        <v>-9.33</v>
       </c>
       <c r="N56" t="b">
         <v>0</v>
@@ -3666,7 +3666,7 @@
         <v>-9.449999999999999</v>
       </c>
       <c r="M57" t="n">
-        <v>7.29</v>
+        <v>7.04</v>
       </c>
       <c r="N57" t="b">
         <v>0</v>
@@ -3715,7 +3715,7 @@
         <v>-4.88</v>
       </c>
       <c r="M58" t="n">
-        <v>-3.99</v>
+        <v>-4.24</v>
       </c>
       <c r="N58" t="b">
         <v>0</v>
@@ -3766,7 +3766,7 @@
         <v>-21.29</v>
       </c>
       <c r="M59" t="n">
-        <v>-19.7</v>
+        <v>-19.95</v>
       </c>
       <c r="N59" t="b">
         <v>0</v>
@@ -3817,7 +3817,7 @@
         <v>-4.72</v>
       </c>
       <c r="M60" t="n">
-        <v>-3.13</v>
+        <v>-3.37</v>
       </c>
       <c r="N60" t="b">
         <v>1</v>
@@ -3868,7 +3868,7 @@
         <v>-16.43</v>
       </c>
       <c r="M61" t="n">
-        <v>-15.22</v>
+        <v>-15.46</v>
       </c>
       <c r="N61" t="b">
         <v>1</v>
@@ -3919,7 +3919,7 @@
         <v>-15.23</v>
       </c>
       <c r="M62" t="n">
-        <v>-7.91</v>
+        <v>-8.16</v>
       </c>
       <c r="N62" t="b">
         <v>1</v>
@@ -3970,7 +3970,7 @@
         <v>-10.37</v>
       </c>
       <c r="M63" t="n">
-        <v>-7.51</v>
+        <v>-7.76</v>
       </c>
       <c r="N63" t="b">
         <v>0</v>
@@ -4021,7 +4021,7 @@
         <v>-9.92</v>
       </c>
       <c r="M64" t="n">
-        <v>-7.93</v>
+        <v>-8.17</v>
       </c>
       <c r="N64" t="b">
         <v>0</v>
@@ -4072,7 +4072,7 @@
         <v>-13.26</v>
       </c>
       <c r="M65" t="n">
-        <v>-15.09</v>
+        <v>-15.34</v>
       </c>
       <c r="N65" t="b">
         <v>0</v>
@@ -4123,7 +4123,7 @@
         <v>-13.02</v>
       </c>
       <c r="M66" t="n">
-        <v>-10.98</v>
+        <v>-11.22</v>
       </c>
       <c r="N66" t="b">
         <v>0</v>
@@ -4174,7 +4174,7 @@
         <v>-4.86</v>
       </c>
       <c r="M67" t="n">
-        <v>-6.32</v>
+        <v>-6.57</v>
       </c>
       <c r="N67" t="b">
         <v>1</v>
@@ -4225,7 +4225,7 @@
         <v>-10.74</v>
       </c>
       <c r="M68" t="n">
-        <v>-6.5</v>
+        <v>-6.74</v>
       </c>
       <c r="N68" t="b">
         <v>0</v>
@@ -4276,7 +4276,7 @@
         <v>-9.94</v>
       </c>
       <c r="M69" t="n">
-        <v>9.140000000000001</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="N69" t="b">
         <v>1</v>
@@ -4327,7 +4327,7 @@
         <v>-9.83</v>
       </c>
       <c r="M70" t="n">
-        <v>-7.12</v>
+        <v>-7.37</v>
       </c>
       <c r="N70" t="b">
         <v>1</v>
@@ -4378,7 +4378,7 @@
         <v>-1.82</v>
       </c>
       <c r="M71" t="n">
-        <v>27.32</v>
+        <v>27.07</v>
       </c>
       <c r="N71" t="b">
         <v>0</v>
@@ -4429,7 +4429,7 @@
         <v>-2.31</v>
       </c>
       <c r="M72" t="n">
-        <v>22.68</v>
+        <v>22.44</v>
       </c>
       <c r="N72" t="b">
         <v>0</v>
@@ -4480,7 +4480,7 @@
         <v>-0.41</v>
       </c>
       <c r="M73" t="n">
-        <v>25.05</v>
+        <v>24.81</v>
       </c>
       <c r="N73" t="b">
         <v>0</v>
@@ -4531,7 +4531,7 @@
         <v>-17.51</v>
       </c>
       <c r="M74" t="n">
-        <v>-15.94</v>
+        <v>-16.19</v>
       </c>
       <c r="N74" t="b">
         <v>1</v>
@@ -4582,7 +4582,7 @@
         <v>-5.27</v>
       </c>
       <c r="M75" t="n">
-        <v>-1.31</v>
+        <v>-1.55</v>
       </c>
       <c r="N75" t="b">
         <v>1</v>
@@ -4633,7 +4633,7 @@
         <v>-5.3</v>
       </c>
       <c r="M76" t="n">
-        <v>1.48</v>
+        <v>1.24</v>
       </c>
       <c r="N76" t="b">
         <v>0</v>
@@ -4684,7 +4684,7 @@
         <v>-4.46</v>
       </c>
       <c r="M77" t="n">
-        <v>-3.75</v>
+        <v>-4</v>
       </c>
       <c r="N77" t="b">
         <v>1</v>
@@ -4739,7 +4739,7 @@
         <v>-9</v>
       </c>
       <c r="M78" t="n">
-        <v>9.31</v>
+        <v>9.07</v>
       </c>
       <c r="N78" t="b">
         <v>1</v>
@@ -4790,7 +4790,7 @@
         <v>-0.87</v>
       </c>
       <c r="M79" t="n">
-        <v>1.11</v>
+        <v>0.87</v>
       </c>
       <c r="N79" t="b">
         <v>1</v>
@@ -4841,7 +4841,7 @@
         <v>-8.869999999999999</v>
       </c>
       <c r="M80" t="n">
-        <v>10.92</v>
+        <v>10.68</v>
       </c>
       <c r="N80" t="b">
         <v>0</v>
@@ -4892,7 +4892,7 @@
         <v>-11.86</v>
       </c>
       <c r="M81" t="n">
-        <v>-13.17</v>
+        <v>-13.42</v>
       </c>
       <c r="N81" t="b">
         <v>0</v>
@@ -4943,7 +4943,7 @@
         <v>-1.88</v>
       </c>
       <c r="M82" t="n">
-        <v>-4.21</v>
+        <v>-4.46</v>
       </c>
       <c r="N82" t="b">
         <v>0</v>
@@ -4994,7 +4994,7 @@
         <v>-14.04</v>
       </c>
       <c r="M83" t="n">
-        <v>-6.35</v>
+        <v>-6.59</v>
       </c>
       <c r="N83" t="b">
         <v>0</v>
@@ -5045,7 +5045,7 @@
         <v>-6.11</v>
       </c>
       <c r="M84" t="n">
-        <v>-4.76</v>
+        <v>-5</v>
       </c>
       <c r="N84" t="b">
         <v>0</v>
@@ -5096,7 +5096,7 @@
         <v>-8.43</v>
       </c>
       <c r="M85" t="n">
-        <v>-2.28</v>
+        <v>-2.53</v>
       </c>
       <c r="N85" t="b">
         <v>1</v>
@@ -5147,7 +5147,7 @@
         <v>-2.97</v>
       </c>
       <c r="M86" t="n">
-        <v>2.69</v>
+        <v>2.45</v>
       </c>
       <c r="N86" t="b">
         <v>0</v>
@@ -5198,7 +5198,7 @@
         <v>-0.07000000000000001</v>
       </c>
       <c r="M87" t="n">
-        <v>12.19</v>
+        <v>11.94</v>
       </c>
       <c r="N87" t="b">
         <v>0</v>
@@ -5249,7 +5249,7 @@
         <v>-3.43</v>
       </c>
       <c r="M88" t="n">
-        <v>8.33</v>
+        <v>8.08</v>
       </c>
       <c r="N88" t="b">
         <v>1</v>
@@ -5300,7 +5300,7 @@
         <v>-10.93</v>
       </c>
       <c r="M89" t="n">
-        <v>-8.76</v>
+        <v>-9</v>
       </c>
       <c r="N89" t="b">
         <v>0</v>
@@ -5351,7 +5351,7 @@
         <v>-7.57</v>
       </c>
       <c r="M90" t="n">
-        <v>-1.69</v>
+        <v>-1.94</v>
       </c>
       <c r="N90" t="b">
         <v>1</v>
@@ -5402,7 +5402,7 @@
         <v>-1.92</v>
       </c>
       <c r="M91" t="n">
-        <v>-0.59</v>
+        <v>-0.83</v>
       </c>
       <c r="N91" t="b">
         <v>0</v>
@@ -5453,7 +5453,7 @@
         <v>-15</v>
       </c>
       <c r="M92" t="n">
-        <v>-9.289999999999999</v>
+        <v>-9.539999999999999</v>
       </c>
       <c r="N92" t="b">
         <v>1</v>
@@ -5504,7 +5504,7 @@
         <v>0</v>
       </c>
       <c r="M93" t="n">
-        <v>21.22</v>
+        <v>20.98</v>
       </c>
       <c r="N93" t="b">
         <v>1</v>
@@ -5555,7 +5555,7 @@
         <v>-24.79</v>
       </c>
       <c r="M94" t="n">
-        <v>-30.26</v>
+        <v>-30.5</v>
       </c>
       <c r="N94" t="b">
         <v>1</v>
@@ -5606,7 +5606,7 @@
         <v>-3.94</v>
       </c>
       <c r="M95" t="n">
-        <v>5.56</v>
+        <v>5.32</v>
       </c>
       <c r="N95" t="b">
         <v>1</v>
@@ -5657,7 +5657,7 @@
         <v>-1.59</v>
       </c>
       <c r="M96" t="n">
-        <v>7.25</v>
+        <v>7.01</v>
       </c>
       <c r="N96" t="b">
         <v>0</v>
@@ -5708,7 +5708,7 @@
         <v>-7.84</v>
       </c>
       <c r="M97" t="n">
-        <v>-2.24</v>
+        <v>-2.48</v>
       </c>
       <c r="N97" t="b">
         <v>0</v>
@@ -5759,7 +5759,7 @@
         <v>-22</v>
       </c>
       <c r="M98" t="n">
-        <v>-22.02</v>
+        <v>-22.27</v>
       </c>
       <c r="N98" t="b">
         <v>0</v>
@@ -5810,7 +5810,7 @@
         <v>-3.85</v>
       </c>
       <c r="M99" t="n">
-        <v>20.76</v>
+        <v>20.51</v>
       </c>
       <c r="N99" t="b">
         <v>0</v>
@@ -5865,7 +5865,7 @@
         <v>-2.53</v>
       </c>
       <c r="M100" t="n">
-        <v>22.28</v>
+        <v>22.03</v>
       </c>
       <c r="N100" t="b">
         <v>1</v>
@@ -5916,7 +5916,7 @@
         <v>-6.27</v>
       </c>
       <c r="M101" t="n">
-        <v>-0.86</v>
+        <v>-1.12</v>
       </c>
       <c r="N101" t="b">
         <v>1</v>
@@ -5967,7 +5967,7 @@
         <v>-0.44</v>
       </c>
       <c r="M102" t="n">
-        <v>3.71</v>
+        <v>3.45</v>
       </c>
       <c r="N102" t="b">
         <v>0</v>
@@ -6022,7 +6022,7 @@
         <v>-2.53</v>
       </c>
       <c r="M103" t="n">
-        <v>15.27</v>
+        <v>15.01</v>
       </c>
       <c r="N103" t="b">
         <v>0</v>
@@ -6073,7 +6073,7 @@
         <v>-2.25</v>
       </c>
       <c r="M104" t="n">
-        <v>31.63</v>
+        <v>31.38</v>
       </c>
       <c r="N104" t="b">
         <v>0</v>
@@ -6124,7 +6124,7 @@
         <v>-19.66</v>
       </c>
       <c r="M105" t="n">
-        <v>3.64</v>
+        <v>3.39</v>
       </c>
       <c r="N105" t="b">
         <v>0</v>
@@ -6175,7 +6175,7 @@
         <v>-0.95</v>
       </c>
       <c r="M106" t="n">
-        <v>-4.41</v>
+        <v>-4.67</v>
       </c>
       <c r="N106" t="b">
         <v>0</v>
@@ -6226,7 +6226,7 @@
         <v>-5.11</v>
       </c>
       <c r="M107" t="n">
-        <v>22.35</v>
+        <v>22.09</v>
       </c>
       <c r="N107" t="b">
         <v>1</v>
@@ -6281,7 +6281,7 @@
         <v>-0.9</v>
       </c>
       <c r="M108" t="n">
-        <v>6.84</v>
+        <v>6.59</v>
       </c>
       <c r="N108" t="b">
         <v>0</v>
@@ -6332,7 +6332,7 @@
         <v>-17.98</v>
       </c>
       <c r="M109" t="n">
-        <v>-9.58</v>
+        <v>-9.83</v>
       </c>
       <c r="N109" t="b">
         <v>0</v>
@@ -6383,7 +6383,7 @@
         <v>-23.19</v>
       </c>
       <c r="M110" t="n">
-        <v>-16.85</v>
+        <v>-17.1</v>
       </c>
       <c r="N110" t="b">
         <v>0</v>
@@ -6434,7 +6434,7 @@
         <v>-4.09</v>
       </c>
       <c r="M111" t="n">
-        <v>1.39</v>
+        <v>1.13</v>
       </c>
       <c r="N111" t="b">
         <v>1</v>
@@ -6489,7 +6489,7 @@
         <v>-15.24</v>
       </c>
       <c r="M112" t="n">
-        <v>-25.17</v>
+        <v>-25.43</v>
       </c>
       <c r="N112" t="b">
         <v>0</v>
@@ -6540,7 +6540,7 @@
         <v>-7.35</v>
       </c>
       <c r="M113" t="n">
-        <v>-6.67</v>
+        <v>-6.92</v>
       </c>
       <c r="N113" t="b">
         <v>0</v>
@@ -6591,7 +6591,7 @@
         <v>-2.36</v>
       </c>
       <c r="M114" t="n">
-        <v>31.41</v>
+        <v>31.16</v>
       </c>
       <c r="N114" t="b">
         <v>0</v>
@@ -6642,7 +6642,7 @@
         <v>-1.51</v>
       </c>
       <c r="M115" t="n">
-        <v>-3.07</v>
+        <v>-3.33</v>
       </c>
       <c r="N115" t="b">
         <v>0</v>
@@ -6693,7 +6693,7 @@
         <v>-4.12</v>
       </c>
       <c r="M116" t="n">
-        <v>-9.75</v>
+        <v>-10.01</v>
       </c>
       <c r="N116" t="b">
         <v>0</v>
@@ -6744,7 +6744,7 @@
         <v>-31.28</v>
       </c>
       <c r="M117" t="n">
-        <v>-28.38</v>
+        <v>-28.63</v>
       </c>
       <c r="N117" t="b">
         <v>1</v>
@@ -6795,7 +6795,7 @@
         <v>-3.33</v>
       </c>
       <c r="M118" t="n">
-        <v>-14.36</v>
+        <v>-14.61</v>
       </c>
       <c r="N118" t="b">
         <v>0</v>
@@ -6846,7 +6846,7 @@
         <v>-3.27</v>
       </c>
       <c r="M119" t="n">
-        <v>-4.09</v>
+        <v>-4.35</v>
       </c>
       <c r="N119" t="b">
         <v>0</v>
@@ -6897,7 +6897,7 @@
         <v>-8.890000000000001</v>
       </c>
       <c r="M120" t="n">
-        <v>-3.45</v>
+        <v>-3.7</v>
       </c>
       <c r="N120" t="b">
         <v>0</v>
@@ -6948,7 +6948,7 @@
         <v>-0.54</v>
       </c>
       <c r="M121" t="n">
-        <v>8.82</v>
+        <v>8.56</v>
       </c>
       <c r="N121" t="b">
         <v>1</v>
@@ -6999,7 +6999,7 @@
         <v>-0.49</v>
       </c>
       <c r="M122" t="n">
-        <v>-9.460000000000001</v>
+        <v>-9.710000000000001</v>
       </c>
       <c r="N122" t="b">
         <v>0</v>
@@ -7050,7 +7050,7 @@
         <v>-3.06</v>
       </c>
       <c r="M123" t="n">
-        <v>16.63</v>
+        <v>16.37</v>
       </c>
       <c r="N123" t="b">
         <v>1</v>
@@ -7101,7 +7101,7 @@
         <v>-2.27</v>
       </c>
       <c r="M124" t="n">
-        <v>-3.49</v>
+        <v>-3.74</v>
       </c>
       <c r="N124" t="b">
         <v>0</v>
@@ -7152,7 +7152,7 @@
         <v>-1.63</v>
       </c>
       <c r="M125" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-1.06</v>
       </c>
       <c r="N125" t="b">
         <v>1</v>
@@ -7203,7 +7203,7 @@
         <v>-5.45</v>
       </c>
       <c r="M126" t="n">
-        <v>-10.25</v>
+        <v>-10.5</v>
       </c>
       <c r="N126" t="b">
         <v>1</v>
@@ -7254,7 +7254,7 @@
         <v>-5.7</v>
       </c>
       <c r="M127" t="n">
-        <v>-4.98</v>
+        <v>-5.24</v>
       </c>
       <c r="N127" t="b">
         <v>0</v>
@@ -7309,7 +7309,7 @@
         <v>-0.79</v>
       </c>
       <c r="M128" t="n">
-        <v>-3.21</v>
+        <v>-3.47</v>
       </c>
       <c r="N128" t="b">
         <v>0</v>
@@ -7360,7 +7360,7 @@
         <v>-18.31</v>
       </c>
       <c r="M129" t="n">
-        <v>-20.72</v>
+        <v>-20.97</v>
       </c>
       <c r="N129" t="b">
         <v>1</v>
@@ -7411,7 +7411,7 @@
         <v>-0.31</v>
       </c>
       <c r="M130" t="n">
-        <v>-0.34</v>
+        <v>-0.6</v>
       </c>
       <c r="N130" t="b">
         <v>1</v>
@@ -7462,7 +7462,7 @@
         <v>-27.45</v>
       </c>
       <c r="M131" t="n">
-        <v>-14.39</v>
+        <v>-14.65</v>
       </c>
       <c r="N131" t="b">
         <v>0</v>
@@ -7513,7 +7513,7 @@
         <v>-2.79</v>
       </c>
       <c r="M132" t="n">
-        <v>-5.68</v>
+        <v>-5.94</v>
       </c>
       <c r="N132" t="b">
         <v>0</v>
@@ -7564,7 +7564,7 @@
         <v>-5.87</v>
       </c>
       <c r="M133" t="n">
-        <v>25.32</v>
+        <v>25.06</v>
       </c>
       <c r="N133" t="b">
         <v>0</v>
@@ -7615,7 +7615,7 @@
         <v>-5.46</v>
       </c>
       <c r="M134" t="n">
-        <v>4.95</v>
+        <v>4.69</v>
       </c>
       <c r="N134" t="b">
         <v>0</v>
@@ -7666,7 +7666,7 @@
         <v>-13.7</v>
       </c>
       <c r="M135" t="n">
-        <v>-18.81</v>
+        <v>-19.07</v>
       </c>
       <c r="N135" t="b">
         <v>0</v>
@@ -7717,7 +7717,7 @@
         <v>-11.9</v>
       </c>
       <c r="M136" t="n">
-        <v>-2.6</v>
+        <v>-2.86</v>
       </c>
       <c r="N136" t="b">
         <v>0</v>
@@ -7768,7 +7768,7 @@
         <v>-26.82</v>
       </c>
       <c r="M137" t="n">
-        <v>-28.65</v>
+        <v>-28.91</v>
       </c>
       <c r="N137" t="b">
         <v>1</v>
@@ -7819,7 +7819,7 @@
         <v>-10.3</v>
       </c>
       <c r="M138" t="n">
-        <v>-3.23</v>
+        <v>-3.48</v>
       </c>
       <c r="N138" t="b">
         <v>0</v>
@@ -7870,7 +7870,7 @@
         <v>-8.66</v>
       </c>
       <c r="M139" t="n">
-        <v>27.08</v>
+        <v>26.83</v>
       </c>
       <c r="N139" t="b">
         <v>0</v>
@@ -7925,7 +7925,7 @@
         <v>-7.48</v>
       </c>
       <c r="M140" t="n">
-        <v>35.61</v>
+        <v>35.36</v>
       </c>
       <c r="N140" t="b">
         <v>0</v>
@@ -7976,7 +7976,7 @@
         <v>-5.3</v>
       </c>
       <c r="M141" t="n">
-        <v>0.91</v>
+        <v>0.66</v>
       </c>
       <c r="N141" t="b">
         <v>0</v>
@@ -8027,7 +8027,7 @@
         <v>-13.87</v>
       </c>
       <c r="M142" t="n">
-        <v>22.76</v>
+        <v>22.51</v>
       </c>
       <c r="N142" t="b">
         <v>1</v>
@@ -8078,7 +8078,7 @@
         <v>-6.18</v>
       </c>
       <c r="M143" t="n">
-        <v>9.94</v>
+        <v>9.69</v>
       </c>
       <c r="N143" t="b">
         <v>1</v>
@@ -8129,7 +8129,7 @@
         <v>-16.26</v>
       </c>
       <c r="M144" t="n">
-        <v>-28.26</v>
+        <v>-28.52</v>
       </c>
       <c r="N144" t="b">
         <v>1</v>
@@ -8180,7 +8180,7 @@
         <v>-23.15</v>
       </c>
       <c r="M145" t="n">
-        <v>-5.52</v>
+        <v>-5.77</v>
       </c>
       <c r="N145" t="b">
         <v>1</v>
@@ -8231,7 +8231,7 @@
         <v>-20.75</v>
       </c>
       <c r="M146" t="n">
-        <v>16.76</v>
+        <v>16.5</v>
       </c>
       <c r="N146" t="b">
         <v>0</v>
@@ -8282,7 +8282,7 @@
         <v>-22.94</v>
       </c>
       <c r="M147" t="n">
-        <v>-18.57</v>
+        <v>-18.83</v>
       </c>
       <c r="N147" t="b">
         <v>0</v>
@@ -8333,7 +8333,7 @@
         <v>-33.97</v>
       </c>
       <c r="M148" t="n">
-        <v>16.47</v>
+        <v>16.22</v>
       </c>
       <c r="N148" t="b">
         <v>1</v>
@@ -8384,7 +8384,7 @@
         <v>-20.26</v>
       </c>
       <c r="M149" t="n">
-        <v>7.71</v>
+        <v>7.46</v>
       </c>
       <c r="N149" t="b">
         <v>0</v>
@@ -8435,7 +8435,7 @@
         <v>-5.11</v>
       </c>
       <c r="M150" t="n">
-        <v>31.43</v>
+        <v>31.18</v>
       </c>
       <c r="N150" t="b">
         <v>0</v>
@@ -8486,7 +8486,7 @@
         <v>-24.48</v>
       </c>
       <c r="M151" t="n">
-        <v>13.73</v>
+        <v>13.48</v>
       </c>
       <c r="N151" t="b">
         <v>1</v>
@@ -8537,7 +8537,7 @@
         <v>-25.09</v>
       </c>
       <c r="M152" t="n">
-        <v>-9.199999999999999</v>
+        <v>-9.449999999999999</v>
       </c>
       <c r="N152" t="b">
         <v>1</v>
@@ -8588,7 +8588,7 @@
         <v>-27.91</v>
       </c>
       <c r="M153" t="n">
-        <v>-26.18</v>
+        <v>-26.43</v>
       </c>
       <c r="N153" t="b">
         <v>1</v>
@@ -8639,7 +8639,7 @@
         <v>-29.01</v>
       </c>
       <c r="M154" t="n">
-        <v>-8.81</v>
+        <v>-9.07</v>
       </c>
       <c r="N154" t="b">
         <v>0</v>
@@ -8690,7 +8690,7 @@
         <v>-19.1</v>
       </c>
       <c r="M155" t="n">
-        <v>-2.67</v>
+        <v>-2.92</v>
       </c>
       <c r="N155" t="b">
         <v>0</v>
@@ -8741,7 +8741,7 @@
         <v>-25.46</v>
       </c>
       <c r="M156" t="n">
-        <v>-15.99</v>
+        <v>-16.25</v>
       </c>
       <c r="N156" t="b">
         <v>1</v>
@@ -8792,7 +8792,7 @@
         <v>-15.76</v>
       </c>
       <c r="M157" t="n">
-        <v>1.09</v>
+        <v>0.84</v>
       </c>
       <c r="N157" t="b">
         <v>1</v>
@@ -8843,7 +8843,7 @@
         <v>-23.43</v>
       </c>
       <c r="M158" t="n">
-        <v>-15.86</v>
+        <v>-16.12</v>
       </c>
       <c r="N158" t="b">
         <v>1</v>
@@ -8894,7 +8894,7 @@
         <v>-18.87</v>
       </c>
       <c r="M159" t="n">
-        <v>-0.96</v>
+        <v>-1.21</v>
       </c>
       <c r="N159" t="b">
         <v>1</v>
@@ -8945,7 +8945,7 @@
         <v>-9.029999999999999</v>
       </c>
       <c r="M160" t="n">
-        <v>41.93</v>
+        <v>41.68</v>
       </c>
       <c r="N160" t="b">
         <v>0</v>
@@ -8996,7 +8996,7 @@
         <v>-20.74</v>
       </c>
       <c r="M161" t="n">
-        <v>3.18</v>
+        <v>2.93</v>
       </c>
       <c r="N161" t="b">
         <v>0</v>
@@ -9047,7 +9047,7 @@
         <v>-26.7</v>
       </c>
       <c r="M162" t="n">
-        <v>12.65</v>
+        <v>12.4</v>
       </c>
       <c r="N162" t="b">
         <v>1</v>
@@ -9098,7 +9098,7 @@
         <v>-22.77</v>
       </c>
       <c r="M163" t="n">
-        <v>-23.29</v>
+        <v>-23.54</v>
       </c>
       <c r="N163" t="b">
         <v>0</v>
@@ -9149,7 +9149,7 @@
         <v>-13.77</v>
       </c>
       <c r="M164" t="n">
-        <v>7.17</v>
+        <v>6.91</v>
       </c>
       <c r="N164" t="b">
         <v>0</v>
@@ -9200,7 +9200,7 @@
         <v>-30.04</v>
       </c>
       <c r="M165" t="n">
-        <v>-18.86</v>
+        <v>-19.11</v>
       </c>
       <c r="N165" t="b">
         <v>1</v>
@@ -9251,7 +9251,7 @@
         <v>-20.5</v>
       </c>
       <c r="M166" t="n">
-        <v>-15.37</v>
+        <v>-15.62</v>
       </c>
       <c r="N166" t="b">
         <v>1</v>
@@ -9302,7 +9302,7 @@
         <v>-11.51</v>
       </c>
       <c r="M167" t="n">
-        <v>156.78</v>
+        <v>156.53</v>
       </c>
       <c r="N167" t="b">
         <v>0</v>
@@ -9353,7 +9353,7 @@
         <v>-22.54</v>
       </c>
       <c r="M168" t="n">
-        <v>1.6</v>
+        <v>1.35</v>
       </c>
       <c r="N168" t="b">
         <v>1</v>
@@ -9404,7 +9404,7 @@
         <v>-23.32</v>
       </c>
       <c r="M169" t="n">
-        <v>-7.72</v>
+        <v>-7.97</v>
       </c>
       <c r="N169" t="b">
         <v>0</v>
@@ -9455,7 +9455,7 @@
         <v>-22.54</v>
       </c>
       <c r="M170" t="n">
-        <v>-32.82</v>
+        <v>-33.08</v>
       </c>
       <c r="N170" t="b">
         <v>1</v>
@@ -9506,7 +9506,7 @@
         <v>-25.38</v>
       </c>
       <c r="M171" t="n">
-        <v>8.82</v>
+        <v>8.57</v>
       </c>
       <c r="N171" t="b">
         <v>0</v>
@@ -9557,7 +9557,7 @@
         <v>-40.98</v>
       </c>
       <c r="M172" t="n">
-        <v>-32.7</v>
+        <v>-32.96</v>
       </c>
       <c r="N172" t="b">
         <v>0</v>
@@ -9608,7 +9608,7 @@
         <v>-19.41</v>
       </c>
       <c r="M173" t="n">
-        <v>-2.71</v>
+        <v>-2.96</v>
       </c>
       <c r="N173" t="b">
         <v>0</v>
@@ -9659,7 +9659,7 @@
         <v>-23.78</v>
       </c>
       <c r="M174" t="n">
-        <v>-14.52</v>
+        <v>-14.77</v>
       </c>
       <c r="N174" t="b">
         <v>0</v>
@@ -9710,7 +9710,7 @@
         <v>-18.71</v>
       </c>
       <c r="M175" t="n">
-        <v>-14.36</v>
+        <v>-14.61</v>
       </c>
       <c r="N175" t="b">
         <v>0</v>
@@ -9761,7 +9761,7 @@
         <v>-22.9</v>
       </c>
       <c r="M176" t="n">
-        <v>-21.61</v>
+        <v>-21.87</v>
       </c>
       <c r="N176" t="b">
         <v>0</v>
@@ -9812,7 +9812,7 @@
         <v>-16.62</v>
       </c>
       <c r="M177" t="n">
-        <v>0.88</v>
+        <v>0.62</v>
       </c>
       <c r="N177" t="b">
         <v>1</v>
@@ -9863,7 +9863,7 @@
         <v>-4.65</v>
       </c>
       <c r="M178" t="n">
-        <v>-5.63</v>
+        <v>-5.89</v>
       </c>
       <c r="N178" t="b">
         <v>1</v>
@@ -9914,7 +9914,7 @@
         <v>-28.18</v>
       </c>
       <c r="M179" t="n">
-        <v>1.22</v>
+        <v>0.97</v>
       </c>
       <c r="N179" t="b">
         <v>1</v>
@@ -9965,7 +9965,7 @@
         <v>-26.24</v>
       </c>
       <c r="M180" t="n">
-        <v>-29.41</v>
+        <v>-29.66</v>
       </c>
       <c r="N180" t="b">
         <v>1</v>
@@ -10020,7 +10020,7 @@
         <v>-4.72</v>
       </c>
       <c r="M181" t="n">
-        <v>21.72</v>
+        <v>21.47</v>
       </c>
       <c r="N181" t="b">
         <v>0</v>
@@ -10071,7 +10071,7 @@
         <v>-11.08</v>
       </c>
       <c r="M182" t="n">
-        <v>-11.89</v>
+        <v>-12.15</v>
       </c>
       <c r="N182" t="b">
         <v>0</v>
@@ -10122,7 +10122,7 @@
         <v>-22.36</v>
       </c>
       <c r="M183" t="n">
-        <v>37.24</v>
+        <v>36.99</v>
       </c>
       <c r="N183" t="b">
         <v>1</v>
@@ -10173,7 +10173,7 @@
         <v>-4.9</v>
       </c>
       <c r="M184" t="n">
-        <v>-1.13</v>
+        <v>-1.39</v>
       </c>
       <c r="N184" t="b">
         <v>0</v>
@@ -10224,7 +10224,7 @@
         <v>-15.41</v>
       </c>
       <c r="M185" t="n">
-        <v>-29.57</v>
+        <v>-29.82</v>
       </c>
       <c r="N185" t="b">
         <v>0</v>
@@ -10275,7 +10275,7 @@
         <v>-16.87</v>
       </c>
       <c r="M186" t="n">
-        <v>-25.2</v>
+        <v>-25.46</v>
       </c>
       <c r="N186" t="b">
         <v>0</v>
@@ -10326,7 +10326,7 @@
         <v>-23.66</v>
       </c>
       <c r="M187" t="n">
-        <v>-14.26</v>
+        <v>-14.51</v>
       </c>
       <c r="N187" t="b">
         <v>0</v>
@@ -10377,7 +10377,7 @@
         <v>-11.87</v>
       </c>
       <c r="M188" t="n">
-        <v>-14.74</v>
+        <v>-15</v>
       </c>
       <c r="N188" t="b">
         <v>0</v>
@@ -10428,7 +10428,7 @@
         <v>-0.29</v>
       </c>
       <c r="M189" t="n">
-        <v>58.14</v>
+        <v>57.89</v>
       </c>
       <c r="N189" t="b">
         <v>0</v>
@@ -10479,7 +10479,7 @@
         <v>-9.67</v>
       </c>
       <c r="M190" t="n">
-        <v>-14.83</v>
+        <v>-15.09</v>
       </c>
       <c r="N190" t="b">
         <v>0</v>
@@ -10530,7 +10530,7 @@
         <v>-36.39</v>
       </c>
       <c r="M191" t="n">
-        <v>-26.92</v>
+        <v>-27.17</v>
       </c>
       <c r="N191" t="b">
         <v>1</v>
@@ -10581,7 +10581,7 @@
         <v>-10.68</v>
       </c>
       <c r="M192" t="n">
-        <v>14.94</v>
+        <v>14.69</v>
       </c>
       <c r="N192" t="b">
         <v>0</v>
@@ -10632,7 +10632,7 @@
         <v>-19.39</v>
       </c>
       <c r="M193" t="n">
-        <v>4.37</v>
+        <v>4.11</v>
       </c>
       <c r="N193" t="b">
         <v>0</v>
@@ -10683,7 +10683,7 @@
         <v>-23.85</v>
       </c>
       <c r="M194" t="n">
-        <v>-4.29</v>
+        <v>-4.55</v>
       </c>
       <c r="N194" t="b">
         <v>0</v>
@@ -10734,7 +10734,7 @@
         <v>-12.27</v>
       </c>
       <c r="M195" t="n">
-        <v>-4.73</v>
+        <v>-4.99</v>
       </c>
       <c r="N195" t="b">
         <v>0</v>
@@ -10785,7 +10785,7 @@
         <v>-21.04</v>
       </c>
       <c r="M196" t="n">
-        <v>-27.44</v>
+        <v>-27.69</v>
       </c>
       <c r="N196" t="b">
         <v>0</v>
@@ -10836,7 +10836,7 @@
         <v>-17.57</v>
       </c>
       <c r="M197" t="n">
-        <v>-2.33</v>
+        <v>-2.59</v>
       </c>
       <c r="N197" t="b">
         <v>1</v>
@@ -10887,7 +10887,7 @@
         <v>-2.51</v>
       </c>
       <c r="M198" t="n">
-        <v>7.33</v>
+        <v>7.07</v>
       </c>
       <c r="N198" t="b">
         <v>1</v>
@@ -10938,7 +10938,7 @@
         <v>-2.79</v>
       </c>
       <c r="M199" t="n">
-        <v>-9.5</v>
+        <v>-9.75</v>
       </c>
       <c r="N199" t="b">
         <v>1</v>
@@ -10989,7 +10989,7 @@
         <v>-2.6</v>
       </c>
       <c r="M200" t="n">
-        <v>-14.69</v>
+        <v>-14.94</v>
       </c>
       <c r="N200" t="b">
         <v>1</v>
@@ -11044,7 +11044,7 @@
         <v>-21.72</v>
       </c>
       <c r="M201" t="n">
-        <v>-24.66</v>
+        <v>-24.91</v>
       </c>
       <c r="N201" t="b">
         <v>1</v>
@@ -11095,7 +11095,7 @@
         <v>-14.35</v>
       </c>
       <c r="M202" t="n">
-        <v>103.51</v>
+        <v>103.25</v>
       </c>
       <c r="N202" t="b">
         <v>0</v>
@@ -11146,7 +11146,7 @@
         <v>-35.86</v>
       </c>
       <c r="M203" t="n">
-        <v>-11.53</v>
+        <v>-11.78</v>
       </c>
       <c r="N203" t="b">
         <v>0</v>
@@ -11197,7 +11197,7 @@
         <v>-24.96</v>
       </c>
       <c r="M204" t="n">
-        <v>-14.79</v>
+        <v>-15.05</v>
       </c>
       <c r="N204" t="b">
         <v>0</v>
@@ -11248,7 +11248,7 @@
         <v>-13.87</v>
       </c>
       <c r="M205" t="n">
-        <v>-6.79</v>
+        <v>-7.05</v>
       </c>
       <c r="N205" t="b">
         <v>0</v>
@@ -11299,7 +11299,7 @@
         <v>-6.77</v>
       </c>
       <c r="M206" t="n">
-        <v>18.13</v>
+        <v>17.88</v>
       </c>
       <c r="N206" t="b">
         <v>0</v>
@@ -11350,7 +11350,7 @@
         <v>-19.27</v>
       </c>
       <c r="M207" t="n">
-        <v>6.41</v>
+        <v>6.16</v>
       </c>
       <c r="N207" t="b">
         <v>1</v>
@@ -11401,7 +11401,7 @@
         <v>-3.54</v>
       </c>
       <c r="M208" t="n">
-        <v>-3.31</v>
+        <v>-3.57</v>
       </c>
       <c r="N208" t="b">
         <v>1</v>
@@ -11452,7 +11452,7 @@
         <v>-27.1</v>
       </c>
       <c r="M209" t="n">
-        <v>-19.75</v>
+        <v>-20</v>
       </c>
       <c r="N209" t="b">
         <v>0</v>
@@ -11503,7 +11503,7 @@
         <v>-17.14</v>
       </c>
       <c r="M210" t="n">
-        <v>13.64</v>
+        <v>13.38</v>
       </c>
       <c r="N210" t="b">
         <v>0</v>
@@ -11554,7 +11554,7 @@
         <v>-19.04</v>
       </c>
       <c r="M211" t="n">
-        <v>-0.86</v>
+        <v>-1.12</v>
       </c>
       <c r="N211" t="b">
         <v>0</v>
@@ -11605,7 +11605,7 @@
         <v>-12.62</v>
       </c>
       <c r="M212" t="n">
-        <v>-1.66</v>
+        <v>-1.92</v>
       </c>
       <c r="N212" t="b">
         <v>0</v>
@@ -11656,7 +11656,7 @@
         <v>-2.43</v>
       </c>
       <c r="M213" t="n">
-        <v>-3.84</v>
+        <v>-4.1</v>
       </c>
       <c r="N213" t="b">
         <v>0</v>
@@ -11707,7 +11707,7 @@
         <v>-7.63</v>
       </c>
       <c r="M214" t="n">
-        <v>2.11</v>
+        <v>1.86</v>
       </c>
       <c r="N214" t="b">
         <v>1</v>
@@ -11758,7 +11758,7 @@
         <v>-16.67</v>
       </c>
       <c r="M215" t="n">
-        <v>-30.02</v>
+        <v>-30.27</v>
       </c>
       <c r="N215" t="b">
         <v>1</v>
@@ -11813,7 +11813,7 @@
         <v>-10.75</v>
       </c>
       <c r="M216" t="n">
-        <v>-14.56</v>
+        <v>-14.82</v>
       </c>
       <c r="N216" t="b">
         <v>0</v>
@@ -11864,7 +11864,7 @@
         <v>-12</v>
       </c>
       <c r="M217" t="n">
-        <v>1.89</v>
+        <v>1.64</v>
       </c>
       <c r="N217" t="b">
         <v>0</v>
@@ -11915,7 +11915,7 @@
         <v>-5.66</v>
       </c>
       <c r="M218" t="n">
-        <v>34.03</v>
+        <v>33.78</v>
       </c>
       <c r="N218" t="b">
         <v>1</v>
@@ -11966,7 +11966,7 @@
         <v>-23.05</v>
       </c>
       <c r="M219" t="n">
-        <v>-20.58</v>
+        <v>-20.83</v>
       </c>
       <c r="N219" t="b">
         <v>1</v>
@@ -12017,7 +12017,7 @@
         <v>-7.7</v>
       </c>
       <c r="M220" t="n">
-        <v>5.4</v>
+        <v>5.14</v>
       </c>
       <c r="N220" t="b">
         <v>0</v>
@@ -12068,7 +12068,7 @@
         <v>-24.02</v>
       </c>
       <c r="M221" t="n">
-        <v>-0.96</v>
+        <v>-1.22</v>
       </c>
       <c r="N221" t="b">
         <v>1</v>
@@ -12119,7 +12119,7 @@
         <v>-23.27</v>
       </c>
       <c r="M222" t="n">
-        <v>-1.8</v>
+        <v>-2.05</v>
       </c>
       <c r="N222" t="b">
         <v>1</v>
@@ -12170,7 +12170,7 @@
         <v>-27.18</v>
       </c>
       <c r="M223" t="n">
-        <v>-12.87</v>
+        <v>-13.12</v>
       </c>
       <c r="N223" t="b">
         <v>1</v>
@@ -12221,7 +12221,7 @@
         <v>-22.12</v>
       </c>
       <c r="M224" t="n">
-        <v>-27.26</v>
+        <v>-27.51</v>
       </c>
       <c r="N224" t="b">
         <v>1</v>
@@ -12272,7 +12272,7 @@
         <v>-0.85</v>
       </c>
       <c r="M225" t="n">
-        <v>-0.87</v>
+        <v>-1.12</v>
       </c>
       <c r="N225" t="b">
         <v>1</v>
@@ -12323,7 +12323,7 @@
         <v>-6.39</v>
       </c>
       <c r="M226" t="n">
-        <v>26.49</v>
+        <v>26.24</v>
       </c>
       <c r="N226" t="b">
         <v>1</v>
@@ -12374,7 +12374,7 @@
         <v>-22.5</v>
       </c>
       <c r="M227" t="n">
-        <v>-6.83</v>
+        <v>-7.08</v>
       </c>
       <c r="N227" t="b">
         <v>1</v>
@@ -12425,7 +12425,7 @@
         <v>-9.43</v>
       </c>
       <c r="M228" t="n">
-        <v>-7.11</v>
+        <v>-7.36</v>
       </c>
       <c r="N228" t="b">
         <v>1</v>
@@ -12476,7 +12476,7 @@
         <v>-2.97</v>
       </c>
       <c r="M229" t="n">
-        <v>-3.66</v>
+        <v>-3.91</v>
       </c>
       <c r="N229" t="b">
         <v>0</v>
@@ -12527,7 +12527,7 @@
         <v>-11.7</v>
       </c>
       <c r="M230" t="n">
-        <v>1.98</v>
+        <v>1.73</v>
       </c>
       <c r="N230" t="b">
         <v>0</v>
@@ -12578,7 +12578,7 @@
         <v>-2.79</v>
       </c>
       <c r="M231" t="n">
-        <v>13.28</v>
+        <v>13.02</v>
       </c>
       <c r="N231" t="b">
         <v>0</v>
@@ -12629,7 +12629,7 @@
         <v>-0.96</v>
       </c>
       <c r="M232" t="n">
-        <v>17.85</v>
+        <v>17.59</v>
       </c>
       <c r="N232" t="b">
         <v>0</v>
@@ -12680,7 +12680,7 @@
         <v>-2.79</v>
       </c>
       <c r="M233" t="n">
-        <v>9.800000000000001</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="N233" t="b">
         <v>1</v>
@@ -12731,7 +12731,7 @@
         <v>-10.33</v>
       </c>
       <c r="M234" t="n">
-        <v>-2.67</v>
+        <v>-2.93</v>
       </c>
       <c r="N234" t="b">
         <v>0</v>
@@ -12786,7 +12786,7 @@
         <v>-3.45</v>
       </c>
       <c r="M235" t="n">
-        <v>-18.73</v>
+        <v>-18.98</v>
       </c>
       <c r="N235" t="b">
         <v>0</v>
@@ -12837,7 +12837,7 @@
         <v>-27.15</v>
       </c>
       <c r="M236" t="n">
-        <v>-38.24</v>
+        <v>-38.49</v>
       </c>
       <c r="N236" t="b">
         <v>0</v>
@@ -12888,7 +12888,7 @@
         <v>-10.87</v>
       </c>
       <c r="M237" t="n">
-        <v>-31.85</v>
+        <v>-32.11</v>
       </c>
       <c r="N237" t="b">
         <v>1</v>
@@ -12939,7 +12939,7 @@
         <v>-4.3</v>
       </c>
       <c r="M238" t="n">
-        <v>-1.78</v>
+        <v>-2.03</v>
       </c>
       <c r="N238" t="b">
         <v>0</v>
@@ -12990,7 +12990,7 @@
         <v>-15.02</v>
       </c>
       <c r="M239" t="n">
-        <v>-23.69</v>
+        <v>-23.94</v>
       </c>
       <c r="N239" t="b">
         <v>1</v>
@@ -13041,7 +13041,7 @@
         <v>-9.27</v>
       </c>
       <c r="M240" t="n">
-        <v>-21.06</v>
+        <v>-21.31</v>
       </c>
       <c r="N240" t="b">
         <v>1</v>
@@ -13092,7 +13092,7 @@
         <v>-9.960000000000001</v>
       </c>
       <c r="M241" t="n">
-        <v>31.21</v>
+        <v>30.95</v>
       </c>
       <c r="N241" t="b">
         <v>0</v>
@@ -13143,7 +13143,7 @@
         <v>-26.97</v>
       </c>
       <c r="M242" t="n">
-        <v>-40.05</v>
+        <v>-40.3</v>
       </c>
       <c r="N242" t="b">
         <v>0</v>
@@ -13194,7 +13194,7 @@
         <v>-16.45</v>
       </c>
       <c r="M243" t="n">
-        <v>-9.5</v>
+        <v>-9.75</v>
       </c>
       <c r="N243" t="b">
         <v>1</v>
@@ -13249,7 +13249,7 @@
         <v>-10.68</v>
       </c>
       <c r="M244" t="n">
-        <v>-13.22</v>
+        <v>-13.47</v>
       </c>
       <c r="N244" t="b">
         <v>0</v>
@@ -13300,7 +13300,7 @@
         <v>-8.130000000000001</v>
       </c>
       <c r="M245" t="n">
-        <v>-3.09</v>
+        <v>-3.35</v>
       </c>
       <c r="N245" t="b">
         <v>1</v>
@@ -13351,7 +13351,7 @@
         <v>-8.039999999999999</v>
       </c>
       <c r="M246" t="n">
-        <v>-17.29</v>
+        <v>-17.55</v>
       </c>
       <c r="N246" t="b">
         <v>1</v>
@@ -13402,7 +13402,7 @@
         <v>-12.86</v>
       </c>
       <c r="M247" t="n">
-        <v>-13.12</v>
+        <v>-13.37</v>
       </c>
       <c r="N247" t="b">
         <v>0</v>
@@ -13453,7 +13453,7 @@
         <v>-24.93</v>
       </c>
       <c r="M248" t="n">
-        <v>-23.73</v>
+        <v>-23.98</v>
       </c>
       <c r="N248" t="b">
         <v>0</v>
@@ -13504,7 +13504,7 @@
         <v>-3.68</v>
       </c>
       <c r="M249" t="n">
-        <v>-1</v>
+        <v>-1.25</v>
       </c>
       <c r="N249" t="b">
         <v>1</v>
@@ -13555,7 +13555,7 @@
         <v>-11.4</v>
       </c>
       <c r="M250" t="n">
-        <v>-11.67</v>
+        <v>-11.93</v>
       </c>
       <c r="N250" t="b">
         <v>0</v>
@@ -13606,7 +13606,7 @@
         <v>-22.11</v>
       </c>
       <c r="M251" t="n">
-        <v>-2.9</v>
+        <v>-3.15</v>
       </c>
       <c r="N251" t="b">
         <v>1</v>
@@ -13661,7 +13661,7 @@
         <v>-8.52</v>
       </c>
       <c r="M252" t="n">
-        <v>-6.65</v>
+        <v>-6.9</v>
       </c>
       <c r="N252" t="b">
         <v>1</v>
@@ -13712,7 +13712,7 @@
         <v>-18.58</v>
       </c>
       <c r="M253" t="n">
-        <v>-0.24</v>
+        <v>-0.5</v>
       </c>
       <c r="N253" t="b">
         <v>0</v>
@@ -13763,7 +13763,7 @@
         <v>-9.43</v>
       </c>
       <c r="M254" t="n">
-        <v>-2.42</v>
+        <v>-2.68</v>
       </c>
       <c r="N254" t="b">
         <v>1</v>
@@ -13814,7 +13814,7 @@
         <v>-11.36</v>
       </c>
       <c r="M255" t="n">
-        <v>-12.04</v>
+        <v>-12.29</v>
       </c>
       <c r="N255" t="b">
         <v>1</v>
@@ -13865,7 +13865,7 @@
         <v>-5.79</v>
       </c>
       <c r="M256" t="n">
-        <v>54.02</v>
+        <v>53.77</v>
       </c>
       <c r="N256" t="b">
         <v>0</v>
@@ -13916,7 +13916,7 @@
         <v>-14.35</v>
       </c>
       <c r="M257" t="n">
-        <v>-17.62</v>
+        <v>-17.87</v>
       </c>
       <c r="N257" t="b">
         <v>1</v>
@@ -13967,7 +13967,7 @@
         <v>-6.54</v>
       </c>
       <c r="M258" t="n">
-        <v>-8.83</v>
+        <v>-9.08</v>
       </c>
       <c r="N258" t="b">
         <v>0</v>
@@ -14022,7 +14022,7 @@
         <v>-18.61</v>
       </c>
       <c r="M259" t="n">
-        <v>14.48</v>
+        <v>14.22</v>
       </c>
       <c r="N259" t="b">
         <v>0</v>
@@ -14073,7 +14073,7 @@
         <v>-7.28</v>
       </c>
       <c r="M260" t="n">
-        <v>-4.07</v>
+        <v>-4.33</v>
       </c>
       <c r="N260" t="b">
         <v>0</v>
@@ -14124,7 +14124,7 @@
         <v>-4.05</v>
       </c>
       <c r="M261" t="n">
-        <v>-5.07</v>
+        <v>-5.32</v>
       </c>
       <c r="N261" t="b">
         <v>0</v>
@@ -14175,7 +14175,7 @@
         <v>-3.92</v>
       </c>
       <c r="M262" t="n">
-        <v>9</v>
+        <v>8.75</v>
       </c>
       <c r="N262" t="b">
         <v>1</v>
@@ -14277,7 +14277,7 @@
         <v>-23.7</v>
       </c>
       <c r="M264" t="n">
-        <v>-30</v>
+        <v>-30.25</v>
       </c>
       <c r="N264" t="b">
         <v>1</v>
@@ -14328,7 +14328,7 @@
         <v>-5.89</v>
       </c>
       <c r="M265" t="n">
-        <v>-0.26</v>
+        <v>-0.51</v>
       </c>
       <c r="N265" t="b">
         <v>1</v>
@@ -14379,7 +14379,7 @@
         <v>-0.47</v>
       </c>
       <c r="M266" t="n">
-        <v>4.2</v>
+        <v>3.94</v>
       </c>
       <c r="N266" t="b">
         <v>0</v>
@@ -14430,7 +14430,7 @@
         <v>-14.18</v>
       </c>
       <c r="M267" t="n">
-        <v>-11.59</v>
+        <v>-11.84</v>
       </c>
       <c r="N267" t="b">
         <v>1</v>
@@ -14481,7 +14481,7 @@
         <v>-11.02</v>
       </c>
       <c r="M268" t="n">
-        <v>44.69</v>
+        <v>44.44</v>
       </c>
       <c r="N268" t="b">
         <v>0</v>
@@ -14532,7 +14532,7 @@
         <v>-6.78</v>
       </c>
       <c r="M269" t="n">
-        <v>41.84</v>
+        <v>41.59</v>
       </c>
       <c r="N269" t="b">
         <v>1</v>
@@ -14583,7 +14583,7 @@
         <v>-11.94</v>
       </c>
       <c r="M270" t="n">
-        <v>49.87</v>
+        <v>49.61</v>
       </c>
       <c r="N270" t="b">
         <v>0</v>
@@ -14634,7 +14634,7 @@
         <v>-13.21</v>
       </c>
       <c r="M271" t="n">
-        <v>-2.34</v>
+        <v>-2.59</v>
       </c>
       <c r="N271" t="b">
         <v>0</v>
@@ -14685,7 +14685,7 @@
         <v>-7.7</v>
       </c>
       <c r="M272" t="n">
-        <v>-0.86</v>
+        <v>-1.11</v>
       </c>
       <c r="N272" t="b">
         <v>1</v>
@@ -14736,7 +14736,7 @@
         <v>-6.64</v>
       </c>
       <c r="M273" t="n">
-        <v>11.5</v>
+        <v>11.24</v>
       </c>
       <c r="N273" t="b">
         <v>0</v>
@@ -14787,7 +14787,7 @@
         <v>-13.65</v>
       </c>
       <c r="M274" t="n">
-        <v>-15.86</v>
+        <v>-16.11</v>
       </c>
       <c r="N274" t="b">
         <v>0</v>
@@ -14838,7 +14838,7 @@
         <v>-5.54</v>
       </c>
       <c r="M275" t="n">
-        <v>23.97</v>
+        <v>23.72</v>
       </c>
       <c r="N275" t="b">
         <v>1</v>
@@ -14889,7 +14889,7 @@
         <v>-2.34</v>
       </c>
       <c r="M276" t="n">
-        <v>18.3</v>
+        <v>18.05</v>
       </c>
       <c r="N276" t="b">
         <v>0</v>
@@ -14940,7 +14940,7 @@
         <v>-6.89</v>
       </c>
       <c r="M277" t="n">
-        <v>-7.39</v>
+        <v>-7.64</v>
       </c>
       <c r="N277" t="b">
         <v>1</v>
@@ -14991,7 +14991,7 @@
         <v>-12.56</v>
       </c>
       <c r="M278" t="n">
-        <v>-10.91</v>
+        <v>-11.16</v>
       </c>
       <c r="N278" t="b">
         <v>0</v>
@@ -15042,7 +15042,7 @@
         <v>-0.92</v>
       </c>
       <c r="M279" t="n">
-        <v>48.84</v>
+        <v>48.58</v>
       </c>
       <c r="N279" t="b">
         <v>1</v>
@@ -15093,7 +15093,7 @@
         <v>-1.94</v>
       </c>
       <c r="M280" t="n">
-        <v>26.89</v>
+        <v>26.64</v>
       </c>
       <c r="N280" t="b">
         <v>0</v>
@@ -15144,7 +15144,7 @@
         <v>-9.9</v>
       </c>
       <c r="M281" t="n">
-        <v>0.76</v>
+        <v>0.51</v>
       </c>
       <c r="N281" t="b">
         <v>1</v>
@@ -15199,7 +15199,7 @@
         <v>-21.11</v>
       </c>
       <c r="M282" t="n">
-        <v>3.12</v>
+        <v>2.86</v>
       </c>
       <c r="N282" t="b">
         <v>0</v>
@@ -15250,7 +15250,7 @@
         <v>-7.51</v>
       </c>
       <c r="M283" t="n">
-        <v>0.1</v>
+        <v>-0.16</v>
       </c>
       <c r="N283" t="b">
         <v>0</v>
@@ -15301,7 +15301,7 @@
         <v>-5.43</v>
       </c>
       <c r="M284" t="n">
-        <v>31.94</v>
+        <v>31.69</v>
       </c>
       <c r="N284" t="b">
         <v>0</v>
@@ -15352,7 +15352,7 @@
         <v>-13.18</v>
       </c>
       <c r="M285" t="n">
-        <v>-21.82</v>
+        <v>-22.08</v>
       </c>
       <c r="N285" t="b">
         <v>0</v>
@@ -15403,7 +15403,7 @@
         <v>-17.88</v>
       </c>
       <c r="M286" t="n">
-        <v>-4.4</v>
+        <v>-4.65</v>
       </c>
       <c r="N286" t="b">
         <v>1</v>
@@ -15454,7 +15454,7 @@
         <v>-21.48</v>
       </c>
       <c r="M287" t="n">
-        <v>-26.47</v>
+        <v>-26.73</v>
       </c>
       <c r="N287" t="b">
         <v>1</v>
@@ -15505,7 +15505,7 @@
         <v>-0.93</v>
       </c>
       <c r="M288" t="n">
-        <v>10.78</v>
+        <v>10.52</v>
       </c>
       <c r="N288" t="b">
         <v>0</v>
@@ -15556,7 +15556,7 @@
         <v>-3.83</v>
       </c>
       <c r="M289" t="n">
-        <v>-0.46</v>
+        <v>-0.72</v>
       </c>
       <c r="N289" t="b">
         <v>1</v>
@@ -15607,7 +15607,7 @@
         <v>-13.66</v>
       </c>
       <c r="M290" t="n">
-        <v>-12.44</v>
+        <v>-12.69</v>
       </c>
       <c r="N290" t="b">
         <v>0</v>
@@ -15658,7 +15658,7 @@
         <v>-1.7</v>
       </c>
       <c r="M291" t="n">
-        <v>7.46</v>
+        <v>7.21</v>
       </c>
       <c r="N291" t="b">
         <v>1</v>
@@ -15709,7 +15709,7 @@
         <v>-4.1</v>
       </c>
       <c r="M292" t="n">
-        <v>33.09</v>
+        <v>32.84</v>
       </c>
       <c r="N292" t="b">
         <v>1</v>
@@ -15764,7 +15764,7 @@
         <v>-10.92</v>
       </c>
       <c r="M293" t="n">
-        <v>20.85</v>
+        <v>20.6</v>
       </c>
       <c r="N293" t="b">
         <v>1</v>
@@ -15815,7 +15815,7 @@
         <v>-1.61</v>
       </c>
       <c r="M294" t="n">
-        <v>-12.47</v>
+        <v>-12.72</v>
       </c>
       <c r="N294" t="b">
         <v>1</v>
@@ -15866,7 +15866,7 @@
         <v>-10.43</v>
       </c>
       <c r="M295" t="n">
-        <v>17.68</v>
+        <v>17.43</v>
       </c>
       <c r="N295" t="b">
         <v>1</v>
@@ -15917,7 +15917,7 @@
         <v>-3.3</v>
       </c>
       <c r="M296" t="n">
-        <v>-14.86</v>
+        <v>-15.11</v>
       </c>
       <c r="N296" t="b">
         <v>1</v>
@@ -15968,7 +15968,7 @@
         <v>-3.45</v>
       </c>
       <c r="M297" t="n">
-        <v>-19.17</v>
+        <v>-19.43</v>
       </c>
       <c r="N297" t="b">
         <v>0</v>
@@ -16019,7 +16019,7 @@
         <v>-11.2</v>
       </c>
       <c r="M298" t="n">
-        <v>18.47</v>
+        <v>18.22</v>
       </c>
       <c r="N298" t="b">
         <v>1</v>
@@ -16070,7 +16070,7 @@
         <v>-11.03</v>
       </c>
       <c r="M299" t="n">
-        <v>-6.13</v>
+        <v>-6.38</v>
       </c>
       <c r="N299" t="b">
         <v>1</v>
@@ -16121,7 +16121,7 @@
         <v>-7.81</v>
       </c>
       <c r="M300" t="n">
-        <v>-7.15</v>
+        <v>-7.4</v>
       </c>
       <c r="N300" t="b">
         <v>0</v>
@@ -16306,7 +16306,7 @@
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="n">
-        <v>-2.01</v>
+        <v>-2</v>
       </c>
       <c r="M3" t="n">
         <v>-0.06</v>
@@ -16353,7 +16353,7 @@
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="n">
-        <v>-0.73</v>
+        <v>-0.76</v>
       </c>
       <c r="M4" t="n">
         <v>-0.3</v>
@@ -16447,7 +16447,7 @@
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="n">
-        <v>-1.36</v>
+        <v>-1.45</v>
       </c>
       <c r="M6" t="n">
         <v>-0.28</v>
@@ -16497,7 +16497,7 @@
         <v>-1.07</v>
       </c>
       <c r="M7" t="n">
-        <v>1.78</v>
+        <v>1.53</v>
       </c>
       <c r="N7" t="b">
         <v>1</v>
@@ -16544,7 +16544,7 @@
         <v>-2.44</v>
       </c>
       <c r="M8" t="n">
-        <v>3.78</v>
+        <v>3.53</v>
       </c>
       <c r="N8" t="b">
         <v>1</v>
@@ -16591,7 +16591,7 @@
         <v>-1.2</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.41</v>
+        <v>-1.66</v>
       </c>
       <c r="N9" t="b">
         <v>1</v>
@@ -16638,7 +16638,7 @@
         <v>-3.95</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.43</v>
+        <v>-0.68</v>
       </c>
       <c r="N10" t="b">
         <v>1</v>
@@ -16685,7 +16685,7 @@
         <v>-3.87</v>
       </c>
       <c r="M11" t="n">
-        <v>0.97</v>
+        <v>0.72</v>
       </c>
       <c r="N11" t="b">
         <v>1</v>
@@ -16732,7 +16732,7 @@
         <v>-3.78</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.02</v>
+        <v>-0.27</v>
       </c>
       <c r="N12" t="b">
         <v>1</v>
@@ -16779,7 +16779,7 @@
         <v>-4.85</v>
       </c>
       <c r="M13" t="n">
-        <v>0.84</v>
+        <v>0.6</v>
       </c>
       <c r="N13" t="b">
         <v>1</v>
@@ -16826,7 +16826,7 @@
         <v>-4.53</v>
       </c>
       <c r="M14" t="n">
-        <v>3.87</v>
+        <v>3.62</v>
       </c>
       <c r="N14" t="b">
         <v>1</v>
@@ -16875,7 +16875,7 @@
         <v>-12.91</v>
       </c>
       <c r="M15" t="n">
-        <v>-9.73</v>
+        <v>-9.970000000000001</v>
       </c>
       <c r="N15" t="b">
         <v>1</v>
@@ -16924,7 +16924,7 @@
         <v>-0.88</v>
       </c>
       <c r="M16" t="n">
-        <v>2.57</v>
+        <v>2.32</v>
       </c>
       <c r="N16" t="b">
         <v>1</v>
@@ -16973,7 +16973,7 @@
         <v>-2.64</v>
       </c>
       <c r="M17" t="n">
-        <v>0.42</v>
+        <v>0.17</v>
       </c>
       <c r="N17" t="b">
         <v>1</v>
@@ -17022,7 +17022,7 @@
         <v>-5.21</v>
       </c>
       <c r="M18" t="n">
-        <v>10.85</v>
+        <v>10.61</v>
       </c>
       <c r="N18" t="b">
         <v>1</v>
@@ -17071,7 +17071,7 @@
         <v>-9.02</v>
       </c>
       <c r="M19" t="n">
-        <v>-4.64</v>
+        <v>-4.88</v>
       </c>
       <c r="N19" t="b">
         <v>1</v>
@@ -17120,7 +17120,7 @@
         <v>-14.61</v>
       </c>
       <c r="M20" t="n">
-        <v>-12.61</v>
+        <v>-12.85</v>
       </c>
       <c r="N20" t="b">
         <v>1</v>
@@ -17166,10 +17166,10 @@
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="n">
-        <v>-19.23</v>
+        <v>-19.25</v>
       </c>
       <c r="M21" t="n">
-        <v>-17.07</v>
+        <v>-17.32</v>
       </c>
       <c r="N21" t="b">
         <v>1</v>
@@ -17218,7 +17218,7 @@
         <v>-5.67</v>
       </c>
       <c r="M22" t="n">
-        <v>3.78</v>
+        <v>3.53</v>
       </c>
       <c r="N22" t="b">
         <v>1</v>
@@ -17264,10 +17264,10 @@
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="n">
-        <v>-10.79</v>
+        <v>-10.8</v>
       </c>
       <c r="M23" t="n">
-        <v>-9.76</v>
+        <v>-10.01</v>
       </c>
       <c r="N23" t="b">
         <v>1</v>
@@ -17318,7 +17318,7 @@
         <v>-4.72</v>
       </c>
       <c r="M24" t="n">
-        <v>-3.13</v>
+        <v>-3.37</v>
       </c>
       <c r="N24" t="b">
         <v>1</v>
@@ -17369,7 +17369,7 @@
         <v>-16.43</v>
       </c>
       <c r="M25" t="n">
-        <v>-15.22</v>
+        <v>-15.46</v>
       </c>
       <c r="N25" t="b">
         <v>1</v>
@@ -17420,7 +17420,7 @@
         <v>-15.23</v>
       </c>
       <c r="M26" t="n">
-        <v>-7.91</v>
+        <v>-8.16</v>
       </c>
       <c r="N26" t="b">
         <v>1</v>
@@ -17471,7 +17471,7 @@
         <v>-4.86</v>
       </c>
       <c r="M27" t="n">
-        <v>-6.32</v>
+        <v>-6.57</v>
       </c>
       <c r="N27" t="b">
         <v>1</v>
@@ -17522,7 +17522,7 @@
         <v>-9.94</v>
       </c>
       <c r="M28" t="n">
-        <v>9.140000000000001</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="N28" t="b">
         <v>1</v>
@@ -17573,7 +17573,7 @@
         <v>-9.83</v>
       </c>
       <c r="M29" t="n">
-        <v>-7.12</v>
+        <v>-7.37</v>
       </c>
       <c r="N29" t="b">
         <v>1</v>
@@ -17624,7 +17624,7 @@
         <v>-17.51</v>
       </c>
       <c r="M30" t="n">
-        <v>-15.94</v>
+        <v>-16.19</v>
       </c>
       <c r="N30" t="b">
         <v>1</v>
@@ -17675,7 +17675,7 @@
         <v>-5.27</v>
       </c>
       <c r="M31" t="n">
-        <v>-1.31</v>
+        <v>-1.55</v>
       </c>
       <c r="N31" t="b">
         <v>1</v>
@@ -17726,7 +17726,7 @@
         <v>-4.46</v>
       </c>
       <c r="M32" t="n">
-        <v>-3.75</v>
+        <v>-4</v>
       </c>
       <c r="N32" t="b">
         <v>1</v>
@@ -17781,7 +17781,7 @@
         <v>-9</v>
       </c>
       <c r="M33" t="n">
-        <v>9.31</v>
+        <v>9.07</v>
       </c>
       <c r="N33" t="b">
         <v>1</v>
@@ -17832,7 +17832,7 @@
         <v>-0.87</v>
       </c>
       <c r="M34" t="n">
-        <v>1.11</v>
+        <v>0.87</v>
       </c>
       <c r="N34" t="b">
         <v>1</v>
@@ -17883,7 +17883,7 @@
         <v>-8.43</v>
       </c>
       <c r="M35" t="n">
-        <v>-2.28</v>
+        <v>-2.53</v>
       </c>
       <c r="N35" t="b">
         <v>1</v>
@@ -17934,7 +17934,7 @@
         <v>-3.43</v>
       </c>
       <c r="M36" t="n">
-        <v>8.33</v>
+        <v>8.08</v>
       </c>
       <c r="N36" t="b">
         <v>1</v>
@@ -17985,7 +17985,7 @@
         <v>-7.57</v>
       </c>
       <c r="M37" t="n">
-        <v>-1.69</v>
+        <v>-1.94</v>
       </c>
       <c r="N37" t="b">
         <v>1</v>
@@ -18036,7 +18036,7 @@
         <v>-15</v>
       </c>
       <c r="M38" t="n">
-        <v>-9.289999999999999</v>
+        <v>-9.539999999999999</v>
       </c>
       <c r="N38" t="b">
         <v>1</v>
@@ -18087,7 +18087,7 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>21.22</v>
+        <v>20.98</v>
       </c>
       <c r="N39" t="b">
         <v>1</v>
@@ -18138,7 +18138,7 @@
         <v>-24.79</v>
       </c>
       <c r="M40" t="n">
-        <v>-30.26</v>
+        <v>-30.5</v>
       </c>
       <c r="N40" t="b">
         <v>1</v>
@@ -18189,7 +18189,7 @@
         <v>-3.94</v>
       </c>
       <c r="M41" t="n">
-        <v>5.56</v>
+        <v>5.32</v>
       </c>
       <c r="N41" t="b">
         <v>1</v>
@@ -18244,7 +18244,7 @@
         <v>-2.53</v>
       </c>
       <c r="M42" t="n">
-        <v>22.28</v>
+        <v>22.03</v>
       </c>
       <c r="N42" t="b">
         <v>1</v>
@@ -18295,7 +18295,7 @@
         <v>-6.27</v>
       </c>
       <c r="M43" t="n">
-        <v>-0.86</v>
+        <v>-1.12</v>
       </c>
       <c r="N43" t="b">
         <v>1</v>
@@ -18346,7 +18346,7 @@
         <v>-5.11</v>
       </c>
       <c r="M44" t="n">
-        <v>22.35</v>
+        <v>22.09</v>
       </c>
       <c r="N44" t="b">
         <v>1</v>
@@ -18397,7 +18397,7 @@
         <v>-4.09</v>
       </c>
       <c r="M45" t="n">
-        <v>1.39</v>
+        <v>1.13</v>
       </c>
       <c r="N45" t="b">
         <v>1</v>
@@ -18448,7 +18448,7 @@
         <v>-31.28</v>
       </c>
       <c r="M46" t="n">
-        <v>-28.38</v>
+        <v>-28.63</v>
       </c>
       <c r="N46" t="b">
         <v>1</v>
@@ -18499,7 +18499,7 @@
         <v>-0.54</v>
       </c>
       <c r="M47" t="n">
-        <v>8.82</v>
+        <v>8.56</v>
       </c>
       <c r="N47" t="b">
         <v>1</v>
@@ -18550,7 +18550,7 @@
         <v>-3.06</v>
       </c>
       <c r="M48" t="n">
-        <v>16.63</v>
+        <v>16.37</v>
       </c>
       <c r="N48" t="b">
         <v>1</v>
@@ -18601,7 +18601,7 @@
         <v>-1.63</v>
       </c>
       <c r="M49" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-1.06</v>
       </c>
       <c r="N49" t="b">
         <v>1</v>
@@ -18652,7 +18652,7 @@
         <v>-5.45</v>
       </c>
       <c r="M50" t="n">
-        <v>-10.25</v>
+        <v>-10.5</v>
       </c>
       <c r="N50" t="b">
         <v>1</v>
@@ -18703,7 +18703,7 @@
         <v>-18.31</v>
       </c>
       <c r="M51" t="n">
-        <v>-20.72</v>
+        <v>-20.97</v>
       </c>
       <c r="N51" t="b">
         <v>1</v>
@@ -18754,7 +18754,7 @@
         <v>-0.31</v>
       </c>
       <c r="M52" t="n">
-        <v>-0.34</v>
+        <v>-0.6</v>
       </c>
       <c r="N52" t="b">
         <v>1</v>
@@ -18805,7 +18805,7 @@
         <v>-26.82</v>
       </c>
       <c r="M53" t="n">
-        <v>-28.65</v>
+        <v>-28.91</v>
       </c>
       <c r="N53" t="b">
         <v>1</v>
@@ -18856,7 +18856,7 @@
         <v>-13.87</v>
       </c>
       <c r="M54" t="n">
-        <v>22.76</v>
+        <v>22.51</v>
       </c>
       <c r="N54" t="b">
         <v>1</v>
@@ -18907,7 +18907,7 @@
         <v>-6.18</v>
       </c>
       <c r="M55" t="n">
-        <v>9.94</v>
+        <v>9.69</v>
       </c>
       <c r="N55" t="b">
         <v>1</v>
@@ -18958,7 +18958,7 @@
         <v>-16.26</v>
       </c>
       <c r="M56" t="n">
-        <v>-28.26</v>
+        <v>-28.52</v>
       </c>
       <c r="N56" t="b">
         <v>1</v>
@@ -19009,7 +19009,7 @@
         <v>-23.15</v>
       </c>
       <c r="M57" t="n">
-        <v>-5.52</v>
+        <v>-5.77</v>
       </c>
       <c r="N57" t="b">
         <v>1</v>
@@ -19060,7 +19060,7 @@
         <v>-33.97</v>
       </c>
       <c r="M58" t="n">
-        <v>16.47</v>
+        <v>16.22</v>
       </c>
       <c r="N58" t="b">
         <v>1</v>
@@ -19111,7 +19111,7 @@
         <v>-24.48</v>
       </c>
       <c r="M59" t="n">
-        <v>13.73</v>
+        <v>13.48</v>
       </c>
       <c r="N59" t="b">
         <v>1</v>
@@ -19162,7 +19162,7 @@
         <v>-25.09</v>
       </c>
       <c r="M60" t="n">
-        <v>-9.199999999999999</v>
+        <v>-9.449999999999999</v>
       </c>
       <c r="N60" t="b">
         <v>1</v>
@@ -19213,7 +19213,7 @@
         <v>-27.91</v>
       </c>
       <c r="M61" t="n">
-        <v>-26.18</v>
+        <v>-26.43</v>
       </c>
       <c r="N61" t="b">
         <v>1</v>
@@ -19264,7 +19264,7 @@
         <v>-25.46</v>
       </c>
       <c r="M62" t="n">
-        <v>-15.99</v>
+        <v>-16.25</v>
       </c>
       <c r="N62" t="b">
         <v>1</v>
@@ -19315,7 +19315,7 @@
         <v>-15.76</v>
       </c>
       <c r="M63" t="n">
-        <v>1.09</v>
+        <v>0.84</v>
       </c>
       <c r="N63" t="b">
         <v>1</v>
@@ -19366,7 +19366,7 @@
         <v>-23.43</v>
       </c>
       <c r="M64" t="n">
-        <v>-15.86</v>
+        <v>-16.12</v>
       </c>
       <c r="N64" t="b">
         <v>1</v>
@@ -19417,7 +19417,7 @@
         <v>-18.87</v>
       </c>
       <c r="M65" t="n">
-        <v>-0.96</v>
+        <v>-1.21</v>
       </c>
       <c r="N65" t="b">
         <v>1</v>
@@ -19468,7 +19468,7 @@
         <v>-26.7</v>
       </c>
       <c r="M66" t="n">
-        <v>12.65</v>
+        <v>12.4</v>
       </c>
       <c r="N66" t="b">
         <v>1</v>
@@ -19519,7 +19519,7 @@
         <v>-30.04</v>
       </c>
       <c r="M67" t="n">
-        <v>-18.86</v>
+        <v>-19.11</v>
       </c>
       <c r="N67" t="b">
         <v>1</v>
@@ -19570,7 +19570,7 @@
         <v>-20.5</v>
       </c>
       <c r="M68" t="n">
-        <v>-15.37</v>
+        <v>-15.62</v>
       </c>
       <c r="N68" t="b">
         <v>1</v>
@@ -19621,7 +19621,7 @@
         <v>-22.54</v>
       </c>
       <c r="M69" t="n">
-        <v>1.6</v>
+        <v>1.35</v>
       </c>
       <c r="N69" t="b">
         <v>1</v>
@@ -19672,7 +19672,7 @@
         <v>-22.54</v>
       </c>
       <c r="M70" t="n">
-        <v>-32.82</v>
+        <v>-33.08</v>
       </c>
       <c r="N70" t="b">
         <v>1</v>
@@ -19723,7 +19723,7 @@
         <v>-16.62</v>
       </c>
       <c r="M71" t="n">
-        <v>0.88</v>
+        <v>0.62</v>
       </c>
       <c r="N71" t="b">
         <v>1</v>
@@ -19774,7 +19774,7 @@
         <v>-4.65</v>
       </c>
       <c r="M72" t="n">
-        <v>-5.63</v>
+        <v>-5.89</v>
       </c>
       <c r="N72" t="b">
         <v>1</v>
@@ -19825,7 +19825,7 @@
         <v>-28.18</v>
       </c>
       <c r="M73" t="n">
-        <v>1.22</v>
+        <v>0.97</v>
       </c>
       <c r="N73" t="b">
         <v>1</v>
@@ -19876,7 +19876,7 @@
         <v>-26.24</v>
       </c>
       <c r="M74" t="n">
-        <v>-29.41</v>
+        <v>-29.66</v>
       </c>
       <c r="N74" t="b">
         <v>1</v>
@@ -19927,7 +19927,7 @@
         <v>-22.36</v>
       </c>
       <c r="M75" t="n">
-        <v>37.24</v>
+        <v>36.99</v>
       </c>
       <c r="N75" t="b">
         <v>1</v>
@@ -19978,7 +19978,7 @@
         <v>-36.39</v>
       </c>
       <c r="M76" t="n">
-        <v>-26.92</v>
+        <v>-27.17</v>
       </c>
       <c r="N76" t="b">
         <v>1</v>
@@ -20029,7 +20029,7 @@
         <v>-17.57</v>
       </c>
       <c r="M77" t="n">
-        <v>-2.33</v>
+        <v>-2.59</v>
       </c>
       <c r="N77" t="b">
         <v>1</v>
@@ -20080,7 +20080,7 @@
         <v>-2.51</v>
       </c>
       <c r="M78" t="n">
-        <v>7.33</v>
+        <v>7.07</v>
       </c>
       <c r="N78" t="b">
         <v>1</v>
@@ -20131,7 +20131,7 @@
         <v>-2.79</v>
       </c>
       <c r="M79" t="n">
-        <v>-9.5</v>
+        <v>-9.75</v>
       </c>
       <c r="N79" t="b">
         <v>1</v>
@@ -20182,7 +20182,7 @@
         <v>-2.6</v>
       </c>
       <c r="M80" t="n">
-        <v>-14.69</v>
+        <v>-14.94</v>
       </c>
       <c r="N80" t="b">
         <v>1</v>
@@ -20237,7 +20237,7 @@
         <v>-21.72</v>
       </c>
       <c r="M81" t="n">
-        <v>-24.66</v>
+        <v>-24.91</v>
       </c>
       <c r="N81" t="b">
         <v>1</v>
@@ -20288,7 +20288,7 @@
         <v>-19.27</v>
       </c>
       <c r="M82" t="n">
-        <v>6.41</v>
+        <v>6.16</v>
       </c>
       <c r="N82" t="b">
         <v>1</v>
@@ -20339,7 +20339,7 @@
         <v>-3.54</v>
       </c>
       <c r="M83" t="n">
-        <v>-3.31</v>
+        <v>-3.57</v>
       </c>
       <c r="N83" t="b">
         <v>1</v>
@@ -20390,7 +20390,7 @@
         <v>-7.63</v>
       </c>
       <c r="M84" t="n">
-        <v>2.11</v>
+        <v>1.86</v>
       </c>
       <c r="N84" t="b">
         <v>1</v>
@@ -20441,7 +20441,7 @@
         <v>-16.67</v>
       </c>
       <c r="M85" t="n">
-        <v>-30.02</v>
+        <v>-30.27</v>
       </c>
       <c r="N85" t="b">
         <v>1</v>
@@ -20492,7 +20492,7 @@
         <v>-5.66</v>
       </c>
       <c r="M86" t="n">
-        <v>34.03</v>
+        <v>33.78</v>
       </c>
       <c r="N86" t="b">
         <v>1</v>
@@ -20543,7 +20543,7 @@
         <v>-23.05</v>
       </c>
       <c r="M87" t="n">
-        <v>-20.58</v>
+        <v>-20.83</v>
       </c>
       <c r="N87" t="b">
         <v>1</v>
@@ -20594,7 +20594,7 @@
         <v>-24.02</v>
       </c>
       <c r="M88" t="n">
-        <v>-0.96</v>
+        <v>-1.22</v>
       </c>
       <c r="N88" t="b">
         <v>1</v>
@@ -20645,7 +20645,7 @@
         <v>-23.27</v>
       </c>
       <c r="M89" t="n">
-        <v>-1.8</v>
+        <v>-2.05</v>
       </c>
       <c r="N89" t="b">
         <v>1</v>
@@ -20696,7 +20696,7 @@
         <v>-27.18</v>
       </c>
       <c r="M90" t="n">
-        <v>-12.87</v>
+        <v>-13.12</v>
       </c>
       <c r="N90" t="b">
         <v>1</v>
@@ -20747,7 +20747,7 @@
         <v>-22.12</v>
       </c>
       <c r="M91" t="n">
-        <v>-27.26</v>
+        <v>-27.51</v>
       </c>
       <c r="N91" t="b">
         <v>1</v>
@@ -20798,7 +20798,7 @@
         <v>-0.85</v>
       </c>
       <c r="M92" t="n">
-        <v>-0.87</v>
+        <v>-1.12</v>
       </c>
       <c r="N92" t="b">
         <v>1</v>
@@ -20849,7 +20849,7 @@
         <v>-6.39</v>
       </c>
       <c r="M93" t="n">
-        <v>26.49</v>
+        <v>26.24</v>
       </c>
       <c r="N93" t="b">
         <v>1</v>
@@ -20900,7 +20900,7 @@
         <v>-22.5</v>
       </c>
       <c r="M94" t="n">
-        <v>-6.83</v>
+        <v>-7.08</v>
       </c>
       <c r="N94" t="b">
         <v>1</v>
@@ -20951,7 +20951,7 @@
         <v>-9.43</v>
       </c>
       <c r="M95" t="n">
-        <v>-7.11</v>
+        <v>-7.36</v>
       </c>
       <c r="N95" t="b">
         <v>1</v>
@@ -21002,7 +21002,7 @@
         <v>-2.79</v>
       </c>
       <c r="M96" t="n">
-        <v>9.800000000000001</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="N96" t="b">
         <v>1</v>
@@ -21053,7 +21053,7 @@
         <v>-10.87</v>
       </c>
       <c r="M97" t="n">
-        <v>-31.85</v>
+        <v>-32.11</v>
       </c>
       <c r="N97" t="b">
         <v>1</v>
@@ -21104,7 +21104,7 @@
         <v>-15.02</v>
       </c>
       <c r="M98" t="n">
-        <v>-23.69</v>
+        <v>-23.94</v>
       </c>
       <c r="N98" t="b">
         <v>1</v>
@@ -21155,7 +21155,7 @@
         <v>-9.27</v>
       </c>
       <c r="M99" t="n">
-        <v>-21.06</v>
+        <v>-21.31</v>
       </c>
       <c r="N99" t="b">
         <v>1</v>
@@ -21206,7 +21206,7 @@
         <v>-16.45</v>
       </c>
       <c r="M100" t="n">
-        <v>-9.5</v>
+        <v>-9.75</v>
       </c>
       <c r="N100" t="b">
         <v>1</v>
@@ -21257,7 +21257,7 @@
         <v>-8.130000000000001</v>
       </c>
       <c r="M101" t="n">
-        <v>-3.09</v>
+        <v>-3.35</v>
       </c>
       <c r="N101" t="b">
         <v>1</v>
@@ -21308,7 +21308,7 @@
         <v>-8.039999999999999</v>
       </c>
       <c r="M102" t="n">
-        <v>-17.29</v>
+        <v>-17.55</v>
       </c>
       <c r="N102" t="b">
         <v>1</v>
@@ -21359,7 +21359,7 @@
         <v>-3.68</v>
       </c>
       <c r="M103" t="n">
-        <v>-1</v>
+        <v>-1.25</v>
       </c>
       <c r="N103" t="b">
         <v>1</v>
@@ -21410,7 +21410,7 @@
         <v>-22.11</v>
       </c>
       <c r="M104" t="n">
-        <v>-2.9</v>
+        <v>-3.15</v>
       </c>
       <c r="N104" t="b">
         <v>1</v>
@@ -21465,7 +21465,7 @@
         <v>-8.52</v>
       </c>
       <c r="M105" t="n">
-        <v>-6.65</v>
+        <v>-6.9</v>
       </c>
       <c r="N105" t="b">
         <v>1</v>
@@ -21516,7 +21516,7 @@
         <v>-9.43</v>
       </c>
       <c r="M106" t="n">
-        <v>-2.42</v>
+        <v>-2.68</v>
       </c>
       <c r="N106" t="b">
         <v>1</v>
@@ -21567,7 +21567,7 @@
         <v>-11.36</v>
       </c>
       <c r="M107" t="n">
-        <v>-12.04</v>
+        <v>-12.29</v>
       </c>
       <c r="N107" t="b">
         <v>1</v>
@@ -21618,7 +21618,7 @@
         <v>-14.35</v>
       </c>
       <c r="M108" t="n">
-        <v>-17.62</v>
+        <v>-17.87</v>
       </c>
       <c r="N108" t="b">
         <v>1</v>
@@ -21669,7 +21669,7 @@
         <v>-3.92</v>
       </c>
       <c r="M109" t="n">
-        <v>9</v>
+        <v>8.75</v>
       </c>
       <c r="N109" t="b">
         <v>1</v>
@@ -21720,7 +21720,7 @@
         <v>-23.7</v>
       </c>
       <c r="M110" t="n">
-        <v>-30</v>
+        <v>-30.25</v>
       </c>
       <c r="N110" t="b">
         <v>1</v>
@@ -21771,7 +21771,7 @@
         <v>-5.89</v>
       </c>
       <c r="M111" t="n">
-        <v>-0.26</v>
+        <v>-0.51</v>
       </c>
       <c r="N111" t="b">
         <v>1</v>
@@ -21822,7 +21822,7 @@
         <v>-14.18</v>
       </c>
       <c r="M112" t="n">
-        <v>-11.59</v>
+        <v>-11.84</v>
       </c>
       <c r="N112" t="b">
         <v>1</v>
@@ -21873,7 +21873,7 @@
         <v>-6.78</v>
       </c>
       <c r="M113" t="n">
-        <v>41.84</v>
+        <v>41.59</v>
       </c>
       <c r="N113" t="b">
         <v>1</v>
@@ -21924,7 +21924,7 @@
         <v>-7.7</v>
       </c>
       <c r="M114" t="n">
-        <v>-0.86</v>
+        <v>-1.11</v>
       </c>
       <c r="N114" t="b">
         <v>1</v>
@@ -21975,7 +21975,7 @@
         <v>-5.54</v>
       </c>
       <c r="M115" t="n">
-        <v>23.97</v>
+        <v>23.72</v>
       </c>
       <c r="N115" t="b">
         <v>1</v>
@@ -22026,7 +22026,7 @@
         <v>-6.89</v>
       </c>
       <c r="M116" t="n">
-        <v>-7.39</v>
+        <v>-7.64</v>
       </c>
       <c r="N116" t="b">
         <v>1</v>
@@ -22077,7 +22077,7 @@
         <v>-0.92</v>
       </c>
       <c r="M117" t="n">
-        <v>48.84</v>
+        <v>48.58</v>
       </c>
       <c r="N117" t="b">
         <v>1</v>
@@ -22128,7 +22128,7 @@
         <v>-9.9</v>
       </c>
       <c r="M118" t="n">
-        <v>0.76</v>
+        <v>0.51</v>
       </c>
       <c r="N118" t="b">
         <v>1</v>
@@ -22179,7 +22179,7 @@
         <v>-17.88</v>
       </c>
       <c r="M119" t="n">
-        <v>-4.4</v>
+        <v>-4.65</v>
       </c>
       <c r="N119" t="b">
         <v>1</v>
@@ -22230,7 +22230,7 @@
         <v>-21.48</v>
       </c>
       <c r="M120" t="n">
-        <v>-26.47</v>
+        <v>-26.73</v>
       </c>
       <c r="N120" t="b">
         <v>1</v>
@@ -22281,7 +22281,7 @@
         <v>-3.83</v>
       </c>
       <c r="M121" t="n">
-        <v>-0.46</v>
+        <v>-0.72</v>
       </c>
       <c r="N121" t="b">
         <v>1</v>
@@ -22332,7 +22332,7 @@
         <v>-1.7</v>
       </c>
       <c r="M122" t="n">
-        <v>7.46</v>
+        <v>7.21</v>
       </c>
       <c r="N122" t="b">
         <v>1</v>
@@ -22383,7 +22383,7 @@
         <v>-4.1</v>
       </c>
       <c r="M123" t="n">
-        <v>33.09</v>
+        <v>32.84</v>
       </c>
       <c r="N123" t="b">
         <v>1</v>
@@ -22438,7 +22438,7 @@
         <v>-10.92</v>
       </c>
       <c r="M124" t="n">
-        <v>20.85</v>
+        <v>20.6</v>
       </c>
       <c r="N124" t="b">
         <v>1</v>
@@ -22489,7 +22489,7 @@
         <v>-1.61</v>
       </c>
       <c r="M125" t="n">
-        <v>-12.47</v>
+        <v>-12.72</v>
       </c>
       <c r="N125" t="b">
         <v>1</v>
@@ -22540,7 +22540,7 @@
         <v>-10.43</v>
       </c>
       <c r="M126" t="n">
-        <v>17.68</v>
+        <v>17.43</v>
       </c>
       <c r="N126" t="b">
         <v>1</v>
@@ -22591,7 +22591,7 @@
         <v>-3.3</v>
       </c>
       <c r="M127" t="n">
-        <v>-14.86</v>
+        <v>-15.11</v>
       </c>
       <c r="N127" t="b">
         <v>1</v>
@@ -22642,7 +22642,7 @@
         <v>-11.2</v>
       </c>
       <c r="M128" t="n">
-        <v>18.47</v>
+        <v>18.22</v>
       </c>
       <c r="N128" t="b">
         <v>1</v>
@@ -22693,7 +22693,7 @@
         <v>-11.03</v>
       </c>
       <c r="M129" t="n">
-        <v>-6.13</v>
+        <v>-6.38</v>
       </c>
       <c r="N129" t="b">
         <v>1</v>

--- a/STS_holy_grail_v2.xlsx
+++ b/STS_holy_grail_v2.xlsx
@@ -464,7 +464,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.52</v>
+        <v>1.53</v>
       </c>
     </row>
     <row r="5">
@@ -474,7 +474,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.41</v>
+        <v>-1.24</v>
       </c>
     </row>
     <row r="6">
@@ -484,7 +484,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>49</v>
+        <v>43.3</v>
       </c>
     </row>
     <row r="8">
@@ -531,13 +531,13 @@
         <v>60</v>
       </c>
       <c r="C10" t="n">
-        <v>1.55</v>
+        <v>1.07</v>
       </c>
       <c r="D10" t="n">
-        <v>51.67</v>
+        <v>45</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.09</v>
+        <v>-1.46</v>
       </c>
     </row>
     <row r="11">
@@ -550,13 +550,13 @@
         <v>78</v>
       </c>
       <c r="C11" t="n">
-        <v>2.51</v>
+        <v>1.33</v>
       </c>
       <c r="D11" t="n">
-        <v>44.87</v>
+        <v>38.46</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.07</v>
+        <v>-2.01</v>
       </c>
     </row>
     <row r="12">
@@ -569,13 +569,13 @@
         <v>141</v>
       </c>
       <c r="C12" t="n">
-        <v>2.71</v>
+        <v>1.34</v>
       </c>
       <c r="D12" t="n">
-        <v>47.52</v>
+        <v>43.26</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.26</v>
+        <v>-1.47</v>
       </c>
     </row>
     <row r="13">
@@ -588,13 +588,13 @@
         <v>33</v>
       </c>
       <c r="C13" t="n">
-        <v>3.56</v>
+        <v>3.65</v>
       </c>
       <c r="D13" t="n">
-        <v>60.61</v>
+        <v>51.52</v>
       </c>
       <c r="E13" t="n">
-        <v>1.81</v>
+        <v>1.93</v>
       </c>
     </row>
     <row r="15">
@@ -641,13 +641,13 @@
         <v>100</v>
       </c>
       <c r="C17" t="n">
-        <v>3.35</v>
+        <v>1.73</v>
       </c>
       <c r="D17" t="n">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="E17" t="n">
-        <v>0.28</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="18">
@@ -660,13 +660,13 @@
         <v>42</v>
       </c>
       <c r="C18" t="n">
-        <v>1.17</v>
+        <v>0.3</v>
       </c>
       <c r="D18" t="n">
-        <v>45.24</v>
+        <v>40.48</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.52</v>
+        <v>-2.28</v>
       </c>
     </row>
     <row r="19">
@@ -679,13 +679,13 @@
         <v>43</v>
       </c>
       <c r="C19" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-1.31</v>
       </c>
       <c r="D19" t="n">
-        <v>39.53</v>
+        <v>32.56</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.97</v>
+        <v>-4.03</v>
       </c>
     </row>
     <row r="20">
@@ -698,13 +698,13 @@
         <v>39</v>
       </c>
       <c r="C20" t="n">
-        <v>-4.33</v>
+        <v>-5.57</v>
       </c>
       <c r="D20" t="n">
-        <v>38.46</v>
+        <v>28.21</v>
       </c>
       <c r="E20" t="n">
-        <v>-7.15</v>
+        <v>-8.279999999999999</v>
       </c>
     </row>
     <row r="21">
@@ -717,13 +717,13 @@
         <v>88</v>
       </c>
       <c r="C21" t="n">
-        <v>6.55</v>
+        <v>6.43</v>
       </c>
       <c r="D21" t="n">
-        <v>60.23</v>
+        <v>55.68</v>
       </c>
       <c r="E21" t="n">
-        <v>3.58</v>
+        <v>3.62</v>
       </c>
     </row>
     <row r="23">
@@ -770,13 +770,13 @@
         <v>10</v>
       </c>
       <c r="C25" t="n">
-        <v>9.119999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="D25" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="E25" t="n">
-        <v>5.75</v>
+        <v>6.17</v>
       </c>
     </row>
     <row r="26">
@@ -789,13 +789,13 @@
         <v>5</v>
       </c>
       <c r="C26" t="n">
-        <v>-3.06</v>
+        <v>-3.08</v>
       </c>
       <c r="D26" t="n">
         <v>40</v>
       </c>
       <c r="E26" t="n">
-        <v>-7.15</v>
+        <v>-7.16</v>
       </c>
     </row>
     <row r="27">
@@ -808,13 +808,13 @@
         <v>3</v>
       </c>
       <c r="C27" t="n">
-        <v>2.72</v>
+        <v>1.7</v>
       </c>
       <c r="D27" t="n">
         <v>33.33</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.33</v>
+        <v>-1.34</v>
       </c>
     </row>
     <row r="29">
@@ -861,13 +861,13 @@
         <v>180</v>
       </c>
       <c r="C31" t="n">
-        <v>4.01</v>
+        <v>2.93</v>
       </c>
       <c r="D31" t="n">
-        <v>47.22</v>
+        <v>41.11</v>
       </c>
       <c r="E31" t="n">
-        <v>1.11</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="32">
@@ -880,13 +880,13 @@
         <v>132</v>
       </c>
       <c r="C32" t="n">
-        <v>0.49</v>
+        <v>-0.38</v>
       </c>
       <c r="D32" t="n">
-        <v>51.52</v>
+        <v>46.21</v>
       </c>
       <c r="E32" t="n">
-        <v>-2.47</v>
+        <v>-3.26</v>
       </c>
     </row>
   </sheetData>
@@ -985,7 +985,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -1010,16 +1010,16 @@
         <v>-17.9</v>
       </c>
       <c r="H2" t="n">
-        <v>-2.87</v>
+        <v>0.23</v>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="n">
-        <v>-3.22</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>-2.79</v>
+        <v>0.87</v>
       </c>
       <c r="N2" t="b">
         <v>0</v>
@@ -1032,7 +1032,7 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -1057,16 +1057,16 @@
         <v>-2.7</v>
       </c>
       <c r="H3" t="n">
-        <v>1.76</v>
+        <v>-2.98</v>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="n">
-        <v>-0.55</v>
+        <v>-2.98</v>
       </c>
       <c r="M3" t="n">
-        <v>1.84</v>
+        <v>-2.34</v>
       </c>
       <c r="N3" t="b">
         <v>1</v>
@@ -1079,7 +1079,7 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -1104,16 +1104,16 @@
         <v>-25.3</v>
       </c>
       <c r="H4" t="n">
-        <v>1.99</v>
+        <v>1.71</v>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="n">
-        <v>-0.25</v>
+        <v>-1.03</v>
       </c>
       <c r="M4" t="n">
-        <v>2.08</v>
+        <v>2.35</v>
       </c>
       <c r="N4" t="b">
         <v>0</v>
@@ -1126,7 +1126,7 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -1151,16 +1151,16 @@
         <v>25.6</v>
       </c>
       <c r="H5" t="n">
-        <v>-2.44</v>
+        <v>-1.91</v>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="n">
-        <v>-3.69</v>
+        <v>-2.24</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.35</v>
+        <v>-1.27</v>
       </c>
       <c r="N5" t="b">
         <v>0</v>
@@ -1173,7 +1173,7 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -1198,16 +1198,16 @@
         <v>26.9</v>
       </c>
       <c r="H6" t="n">
-        <v>3.34</v>
+        <v>-0.99</v>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="n">
-        <v>-0.4</v>
+        <v>-2.51</v>
       </c>
       <c r="M6" t="n">
-        <v>3.42</v>
+        <v>-0.35</v>
       </c>
       <c r="N6" t="b">
         <v>1</v>
@@ -1245,16 +1245,16 @@
         <v>-14.5</v>
       </c>
       <c r="H7" t="n">
-        <v>1.03</v>
+        <v>-3.75</v>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="n">
-        <v>-1.54</v>
+        <v>-3.93</v>
       </c>
       <c r="M7" t="n">
-        <v>0.1</v>
+        <v>-3.96</v>
       </c>
       <c r="N7" t="b">
         <v>0</v>
@@ -1292,16 +1292,16 @@
         <v>17.2</v>
       </c>
       <c r="H8" t="n">
-        <v>-2.85</v>
+        <v>-10.19</v>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="n">
-        <v>-3.51</v>
+        <v>-10.54</v>
       </c>
       <c r="M8" t="n">
-        <v>-3.78</v>
+        <v>-11.13</v>
       </c>
       <c r="N8" t="b">
         <v>0</v>
@@ -1339,7 +1339,7 @@
         <v>-13.2</v>
       </c>
       <c r="H9" t="n">
-        <v>6.03</v>
+        <v>8.18</v>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
@@ -1348,7 +1348,7 @@
         <v>-0.82</v>
       </c>
       <c r="M9" t="n">
-        <v>5.1</v>
+        <v>7.25</v>
       </c>
       <c r="N9" t="b">
         <v>0</v>
@@ -1386,7 +1386,7 @@
         <v>-7.7</v>
       </c>
       <c r="H10" t="n">
-        <v>0.65</v>
+        <v>0.62</v>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
@@ -1395,7 +1395,7 @@
         <v>-0.59</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.28</v>
+        <v>-0.31</v>
       </c>
       <c r="N10" t="b">
         <v>0</v>
@@ -1433,7 +1433,7 @@
         <v>-18.1</v>
       </c>
       <c r="H11" t="n">
-        <v>0.64</v>
+        <v>-0.8</v>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
@@ -1442,7 +1442,7 @@
         <v>-2.05</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.29</v>
+        <v>-1.73</v>
       </c>
       <c r="N11" t="b">
         <v>0</v>
@@ -1480,16 +1480,16 @@
         <v>-18.1</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.04</v>
+        <v>1.07</v>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="n">
-        <v>-2.52</v>
+        <v>-2.69</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.97</v>
+        <v>0.14</v>
       </c>
       <c r="N12" t="b">
         <v>1</v>
@@ -1527,16 +1527,16 @@
         <v>7.7</v>
       </c>
       <c r="H13" t="n">
-        <v>0.5</v>
+        <v>-7.25</v>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="n">
-        <v>-5.77</v>
+        <v>-7.73</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.43</v>
+        <v>-8.18</v>
       </c>
       <c r="N13" t="b">
         <v>0</v>
@@ -1574,7 +1574,7 @@
         <v>-21.5</v>
       </c>
       <c r="H14" t="n">
-        <v>7.91</v>
+        <v>5.73</v>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
@@ -1583,7 +1583,7 @@
         <v>-1.4</v>
       </c>
       <c r="M14" t="n">
-        <v>6.98</v>
+        <v>4.8</v>
       </c>
       <c r="N14" t="b">
         <v>1</v>
@@ -1621,16 +1621,16 @@
         <v>41.6</v>
       </c>
       <c r="H15" t="n">
-        <v>-2.18</v>
+        <v>-3</v>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="n">
-        <v>-3.27</v>
+        <v>-4.38</v>
       </c>
       <c r="M15" t="n">
-        <v>-3.76</v>
+        <v>-4.58</v>
       </c>
       <c r="N15" t="b">
         <v>1</v>
@@ -1668,16 +1668,16 @@
         <v>32.1</v>
       </c>
       <c r="H16" t="n">
-        <v>-2.08</v>
+        <v>-0.52</v>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="n">
-        <v>-4.4</v>
+        <v>-2.19</v>
       </c>
       <c r="M16" t="n">
-        <v>-3.66</v>
+        <v>-2.11</v>
       </c>
       <c r="N16" t="b">
         <v>1</v>
@@ -1715,7 +1715,7 @@
         <v>-14.4</v>
       </c>
       <c r="H17" t="n">
-        <v>1.82</v>
+        <v>-1.19</v>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
@@ -1724,7 +1724,7 @@
         <v>-1.54</v>
       </c>
       <c r="M17" t="n">
-        <v>0.24</v>
+        <v>-2.78</v>
       </c>
       <c r="N17" t="b">
         <v>1</v>
@@ -1751,7 +1751,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Extended</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="E18" t="inlineStr"/>
@@ -1762,7 +1762,7 @@
         <v>-16.8</v>
       </c>
       <c r="H18" t="n">
-        <v>6.15</v>
+        <v>4.18</v>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
@@ -1771,7 +1771,7 @@
         <v>-3.26</v>
       </c>
       <c r="M18" t="n">
-        <v>4.56</v>
+        <v>2.59</v>
       </c>
       <c r="N18" t="b">
         <v>0</v>
@@ -1809,16 +1809,16 @@
         <v>-10</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.82</v>
+        <v>-3.02</v>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="n">
-        <v>-1.8</v>
+        <v>-5.75</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.4</v>
+        <v>-4.6</v>
       </c>
       <c r="N19" t="b">
         <v>1</v>
@@ -1856,7 +1856,7 @@
         <v>6.4</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.6</v>
+        <v>-1.14</v>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
@@ -1865,7 +1865,7 @@
         <v>-1.45</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.18</v>
+        <v>-2.72</v>
       </c>
       <c r="N20" t="b">
         <v>1</v>
@@ -1903,7 +1903,7 @@
         <v>-11</v>
       </c>
       <c r="H21" t="n">
-        <v>6.74</v>
+        <v>7.04</v>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
@@ -1912,7 +1912,7 @@
         <v>-0.97</v>
       </c>
       <c r="M21" t="n">
-        <v>5.15</v>
+        <v>5.45</v>
       </c>
       <c r="N21" t="b">
         <v>0</v>
@@ -1950,7 +1950,7 @@
         <v>-23.9</v>
       </c>
       <c r="H22" t="n">
-        <v>0.15</v>
+        <v>-0.39</v>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
@@ -1959,7 +1959,7 @@
         <v>-1.79</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.45</v>
+        <v>-1.98</v>
       </c>
       <c r="N22" t="b">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>-9.800000000000001</v>
       </c>
       <c r="H23" t="n">
-        <v>0.39</v>
+        <v>-0.74</v>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
@@ -2010,7 +2010,7 @@
         <v>-2.63</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.2</v>
+        <v>-2.33</v>
       </c>
       <c r="N23" t="b">
         <v>0</v>
@@ -2048,7 +2048,7 @@
         <v>-36.1</v>
       </c>
       <c r="H24" t="n">
-        <v>6.7</v>
+        <v>5.2</v>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
@@ -2057,7 +2057,7 @@
         <v>-1.92</v>
       </c>
       <c r="M24" t="n">
-        <v>5.1</v>
+        <v>4.34</v>
       </c>
       <c r="N24" t="b">
         <v>0</v>
@@ -2095,7 +2095,7 @@
         <v>-7.9</v>
       </c>
       <c r="H25" t="n">
-        <v>-6.65</v>
+        <v>-6.05</v>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
@@ -2104,7 +2104,7 @@
         <v>-8.449999999999999</v>
       </c>
       <c r="M25" t="n">
-        <v>-8.24</v>
+        <v>-7.64</v>
       </c>
       <c r="N25" t="b">
         <v>0</v>
@@ -2142,16 +2142,16 @@
         <v>2.6</v>
       </c>
       <c r="H26" t="n">
-        <v>-5.81</v>
+        <v>-5.07</v>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="n">
-        <v>-6.34</v>
+        <v>-6.16</v>
       </c>
       <c r="M26" t="n">
-        <v>-7.89</v>
+        <v>-7.15</v>
       </c>
       <c r="N26" t="b">
         <v>0</v>
@@ -2189,7 +2189,7 @@
         <v>6.3</v>
       </c>
       <c r="H27" t="n">
-        <v>4.89</v>
+        <v>3.78</v>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
@@ -2198,7 +2198,7 @@
         <v>-0.7</v>
       </c>
       <c r="M27" t="n">
-        <v>2.81</v>
+        <v>1.7</v>
       </c>
       <c r="N27" t="b">
         <v>0</v>
@@ -2236,7 +2236,7 @@
         <v>20.2</v>
       </c>
       <c r="H28" t="n">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
@@ -2245,7 +2245,7 @@
         <v>-1.07</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.36</v>
+        <v>-0.25</v>
       </c>
       <c r="N28" t="b">
         <v>1</v>
@@ -2272,7 +2272,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Extended</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="E29" t="inlineStr"/>
@@ -2283,7 +2283,7 @@
         <v>43.7</v>
       </c>
       <c r="H29" t="n">
-        <v>6.46</v>
+        <v>3.98</v>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
@@ -2292,7 +2292,7 @@
         <v>-2.44</v>
       </c>
       <c r="M29" t="n">
-        <v>4.47</v>
+        <v>1.98</v>
       </c>
       <c r="N29" t="b">
         <v>1</v>
@@ -2330,16 +2330,16 @@
         <v>1.9</v>
       </c>
       <c r="H30" t="n">
-        <v>-2.22</v>
+        <v>-3.03</v>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="n">
-        <v>-3.37</v>
+        <v>-3.2</v>
       </c>
       <c r="M30" t="n">
-        <v>-4.21</v>
+        <v>-5.02</v>
       </c>
       <c r="N30" t="b">
         <v>1</v>
@@ -2377,7 +2377,7 @@
         <v>37.5</v>
       </c>
       <c r="H31" t="n">
-        <v>2.46</v>
+        <v>-0.34</v>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
@@ -2386,7 +2386,7 @@
         <v>-3.95</v>
       </c>
       <c r="M31" t="n">
-        <v>0.31</v>
+        <v>-2.49</v>
       </c>
       <c r="N31" t="b">
         <v>1</v>
@@ -2424,7 +2424,7 @@
         <v>15</v>
       </c>
       <c r="H32" t="n">
-        <v>-13.4</v>
+        <v>-19.31</v>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
@@ -2433,7 +2433,7 @@
         <v>-22.27</v>
       </c>
       <c r="M32" t="n">
-        <v>-15.55</v>
+        <v>-21.45</v>
       </c>
       <c r="N32" t="b">
         <v>0</v>
@@ -2471,7 +2471,7 @@
         <v>40.2</v>
       </c>
       <c r="H33" t="n">
-        <v>1.44</v>
+        <v>-0.15</v>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
@@ -2480,7 +2480,7 @@
         <v>-3.87</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.71</v>
+        <v>-2.3</v>
       </c>
       <c r="N33" t="b">
         <v>1</v>
@@ -2518,7 +2518,7 @@
         <v>10.7</v>
       </c>
       <c r="H34" t="n">
-        <v>1.21</v>
+        <v>3.18</v>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
@@ -2527,7 +2527,7 @@
         <v>-3.78</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.9399999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="N34" t="b">
         <v>1</v>
@@ -2565,7 +2565,7 @@
         <v>25.6</v>
       </c>
       <c r="H35" t="n">
-        <v>2.42</v>
+        <v>2.11</v>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
@@ -2574,7 +2574,7 @@
         <v>-4.85</v>
       </c>
       <c r="M35" t="n">
-        <v>1.04</v>
+        <v>0.73</v>
       </c>
       <c r="N35" t="b">
         <v>1</v>
@@ -2612,7 +2612,7 @@
         <v>6.3</v>
       </c>
       <c r="H36" t="n">
-        <v>8.699999999999999</v>
+        <v>5.89</v>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
@@ -2621,7 +2621,7 @@
         <v>-0.4</v>
       </c>
       <c r="M36" t="n">
-        <v>6.43</v>
+        <v>3.62</v>
       </c>
       <c r="N36" t="b">
         <v>0</v>
@@ -2659,16 +2659,16 @@
         <v>2.3</v>
       </c>
       <c r="H37" t="n">
-        <v>-5.36</v>
+        <v>-7.81</v>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="n">
-        <v>-7.96</v>
+        <v>-8.02</v>
       </c>
       <c r="M37" t="n">
-        <v>-7.63</v>
+        <v>-10.09</v>
       </c>
       <c r="N37" t="b">
         <v>0</v>
@@ -2706,7 +2706,7 @@
         <v>-4.3</v>
       </c>
       <c r="H38" t="n">
-        <v>3.79</v>
+        <v>3.39</v>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
@@ -2715,7 +2715,7 @@
         <v>-5.89</v>
       </c>
       <c r="M38" t="n">
-        <v>2.32</v>
+        <v>1.93</v>
       </c>
       <c r="N38" t="b">
         <v>0</v>
@@ -2753,7 +2753,7 @@
         <v>-29.4</v>
       </c>
       <c r="H39" t="n">
-        <v>-3.99</v>
+        <v>-5.75</v>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr"/>
@@ -2762,7 +2762,7 @@
         <v>-9.640000000000001</v>
       </c>
       <c r="M39" t="n">
-        <v>-5.46</v>
+        <v>-7.21</v>
       </c>
       <c r="N39" t="b">
         <v>0</v>
@@ -2800,7 +2800,7 @@
         <v>-6.9</v>
       </c>
       <c r="H40" t="n">
-        <v>7.14</v>
+        <v>6.44</v>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
@@ -2809,7 +2809,7 @@
         <v>-4.53</v>
       </c>
       <c r="M40" t="n">
-        <v>5.68</v>
+        <v>4.97</v>
       </c>
       <c r="N40" t="b">
         <v>1</v>
@@ -2847,16 +2847,16 @@
         <v>4.2</v>
       </c>
       <c r="H41" t="n">
-        <v>-7.28</v>
+        <v>-10.83</v>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="n">
-        <v>-9.220000000000001</v>
+        <v>-11.21</v>
       </c>
       <c r="M41" t="n">
-        <v>-8.75</v>
+        <v>-12.29</v>
       </c>
       <c r="N41" t="b">
         <v>0</v>
@@ -2894,10 +2894,10 @@
         <v>-32.4</v>
       </c>
       <c r="H42" t="n">
-        <v>-2.43</v>
+        <v>-3.58</v>
       </c>
       <c r="I42" t="n">
-        <v>-2.43</v>
+        <v>-3.58</v>
       </c>
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
@@ -2905,7 +2905,7 @@
         <v>-12.47</v>
       </c>
       <c r="M42" t="n">
-        <v>-3.24</v>
+        <v>-4.39</v>
       </c>
       <c r="N42" t="b">
         <v>0</v>
@@ -2992,7 +2992,7 @@
         <v>9.699999999999999</v>
       </c>
       <c r="H44" t="n">
-        <v>12.92</v>
+        <v>13.1</v>
       </c>
       <c r="I44" t="n">
         <v>1.27</v>
@@ -3003,7 +3003,7 @@
         <v>-6.51</v>
       </c>
       <c r="M44" t="n">
-        <v>11.95</v>
+        <v>12.13</v>
       </c>
       <c r="N44" t="b">
         <v>0</v>
@@ -3041,7 +3041,7 @@
         <v>-28.1</v>
       </c>
       <c r="H45" t="n">
-        <v>-7.53</v>
+        <v>-8.15</v>
       </c>
       <c r="I45" t="n">
         <v>-10.79</v>
@@ -3052,7 +3052,7 @@
         <v>-12.06</v>
       </c>
       <c r="M45" t="n">
-        <v>-8.5</v>
+        <v>-9.119999999999999</v>
       </c>
       <c r="N45" t="b">
         <v>0</v>
@@ -3090,7 +3090,7 @@
         <v>-17.7</v>
       </c>
       <c r="H46" t="n">
-        <v>-0.63</v>
+        <v>-4.26</v>
       </c>
       <c r="I46" t="n">
         <v>-0.89</v>
@@ -3098,10 +3098,10 @@
       <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="n">
-        <v>-4.61</v>
+        <v>-4.73</v>
       </c>
       <c r="M46" t="n">
-        <v>-1.59</v>
+        <v>-5.23</v>
       </c>
       <c r="N46" t="b">
         <v>0</v>
@@ -3139,7 +3139,7 @@
         <v>-9.300000000000001</v>
       </c>
       <c r="H47" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-5.34</v>
       </c>
       <c r="I47" t="n">
         <v>-3.34</v>
@@ -3150,7 +3150,7 @@
         <v>-7.3</v>
       </c>
       <c r="M47" t="n">
-        <v>-1.04</v>
+        <v>-6.3</v>
       </c>
       <c r="N47" t="b">
         <v>0</v>
@@ -3188,7 +3188,7 @@
         <v>0.3</v>
       </c>
       <c r="H48" t="n">
-        <v>-11.49</v>
+        <v>-12.25</v>
       </c>
       <c r="I48" t="n">
         <v>-10.53</v>
@@ -3196,10 +3196,10 @@
       <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="n">
-        <v>-13.26</v>
+        <v>-13.04</v>
       </c>
       <c r="M48" t="n">
-        <v>-12.45</v>
+        <v>-13.22</v>
       </c>
       <c r="N48" t="b">
         <v>1</v>
@@ -3237,7 +3237,7 @@
         <v>12.3</v>
       </c>
       <c r="H49" t="n">
-        <v>7.88</v>
+        <v>7.91</v>
       </c>
       <c r="I49" t="n">
         <v>6.51</v>
@@ -3248,7 +3248,7 @@
         <v>-6.01</v>
       </c>
       <c r="M49" t="n">
-        <v>6.19</v>
+        <v>6.23</v>
       </c>
       <c r="N49" t="b">
         <v>0</v>
@@ -3286,7 +3286,7 @@
         <v>2.8</v>
       </c>
       <c r="H50" t="n">
-        <v>2.98</v>
+        <v>1.39</v>
       </c>
       <c r="I50" t="n">
         <v>3.18</v>
@@ -3297,7 +3297,7 @@
         <v>-0.88</v>
       </c>
       <c r="M50" t="n">
-        <v>1.29</v>
+        <v>-0.29</v>
       </c>
       <c r="N50" t="b">
         <v>1</v>
@@ -3335,7 +3335,7 @@
         <v>-1.4</v>
       </c>
       <c r="H51" t="n">
-        <v>12.71</v>
+        <v>10.66</v>
       </c>
       <c r="I51" t="n">
         <v>-4.52</v>
@@ -3346,7 +3346,7 @@
         <v>-7.44</v>
       </c>
       <c r="M51" t="n">
-        <v>11.03</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="N51" t="b">
         <v>0</v>
@@ -3373,7 +3373,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Extended</t>
         </is>
       </c>
       <c r="E52" t="inlineStr"/>
@@ -3384,7 +3384,7 @@
         <v>34.5</v>
       </c>
       <c r="H52" t="n">
-        <v>4.65</v>
+        <v>7.38</v>
       </c>
       <c r="I52" t="n">
         <v>0.66</v>
@@ -3395,7 +3395,7 @@
         <v>-2.64</v>
       </c>
       <c r="M52" t="n">
-        <v>2.97</v>
+        <v>5.69</v>
       </c>
       <c r="N52" t="b">
         <v>1</v>
@@ -3433,7 +3433,7 @@
         <v>-22.7</v>
       </c>
       <c r="H53" t="n">
-        <v>-2.62</v>
+        <v>-5.42</v>
       </c>
       <c r="I53" t="n">
         <v>-6.71</v>
@@ -3444,7 +3444,7 @@
         <v>-7.05</v>
       </c>
       <c r="M53" t="n">
-        <v>-4.37</v>
+        <v>-7.16</v>
       </c>
       <c r="N53" t="b">
         <v>0</v>
@@ -3482,7 +3482,7 @@
         <v>24.3</v>
       </c>
       <c r="H54" t="n">
-        <v>17.26</v>
+        <v>15.95</v>
       </c>
       <c r="I54" t="n">
         <v>2.54</v>
@@ -3493,7 +3493,7 @@
         <v>-5.21</v>
       </c>
       <c r="M54" t="n">
-        <v>16.22</v>
+        <v>14.91</v>
       </c>
       <c r="N54" t="b">
         <v>1</v>
@@ -3531,7 +3531,7 @@
         <v>56.6</v>
       </c>
       <c r="H55" t="n">
-        <v>-8.960000000000001</v>
+        <v>-6.86</v>
       </c>
       <c r="I55" t="n">
         <v>-13.1</v>
@@ -3542,7 +3542,7 @@
         <v>-16.17</v>
       </c>
       <c r="M55" t="n">
-        <v>-10</v>
+        <v>-7.9</v>
       </c>
       <c r="N55" t="b">
         <v>0</v>
@@ -3580,7 +3580,7 @@
         <v>2.9</v>
       </c>
       <c r="H56" t="n">
-        <v>-9.890000000000001</v>
+        <v>-11.02</v>
       </c>
       <c r="I56" t="n">
         <v>-8.470000000000001</v>
@@ -3591,7 +3591,7 @@
         <v>-12.94</v>
       </c>
       <c r="M56" t="n">
-        <v>-10.93</v>
+        <v>-11.33</v>
       </c>
       <c r="N56" t="b">
         <v>0</v>
@@ -3629,7 +3629,7 @@
         <v>-16.9</v>
       </c>
       <c r="H57" t="n">
-        <v>-5.59</v>
+        <v>-7.29</v>
       </c>
       <c r="I57" t="n">
         <v>-6.47</v>
@@ -3640,7 +3640,7 @@
         <v>-9.02</v>
       </c>
       <c r="M57" t="n">
-        <v>-6.63</v>
+        <v>-8.33</v>
       </c>
       <c r="N57" t="b">
         <v>1</v>
@@ -3678,7 +3678,7 @@
         <v>32.8</v>
       </c>
       <c r="H58" t="n">
-        <v>8.27</v>
+        <v>8.68</v>
       </c>
       <c r="I58" t="n">
         <v>14.96</v>
@@ -3689,7 +3689,7 @@
         <v>-0.9</v>
       </c>
       <c r="M58" t="n">
-        <v>7.81</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="N58" t="b">
         <v>0</v>
@@ -3727,7 +3727,7 @@
         <v>0.8</v>
       </c>
       <c r="H59" t="n">
-        <v>-2.25</v>
+        <v>-4.81</v>
       </c>
       <c r="I59" t="n">
         <v>-7.73</v>
@@ -3738,7 +3738,7 @@
         <v>-10.12</v>
       </c>
       <c r="M59" t="n">
-        <v>-2.71</v>
+        <v>-4.54</v>
       </c>
       <c r="N59" t="b">
         <v>0</v>
@@ -3776,7 +3776,7 @@
         <v>-9.6</v>
       </c>
       <c r="H60" t="n">
-        <v>-4.22</v>
+        <v>-8.42</v>
       </c>
       <c r="I60" t="n">
         <v>-1.23</v>
@@ -3787,7 +3787,7 @@
         <v>-9.65</v>
       </c>
       <c r="M60" t="n">
-        <v>-4.68</v>
+        <v>-8.880000000000001</v>
       </c>
       <c r="N60" t="b">
         <v>0</v>
@@ -3825,7 +3825,7 @@
         <v>20.3</v>
       </c>
       <c r="H61" t="n">
-        <v>-14.57</v>
+        <v>-16.02</v>
       </c>
       <c r="I61" t="n">
         <v>-2.07</v>
@@ -3833,10 +3833,10 @@
       <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr"/>
       <c r="L61" t="n">
-        <v>-15.52</v>
+        <v>-16.13</v>
       </c>
       <c r="M61" t="n">
-        <v>-15.46</v>
+        <v>-16.91</v>
       </c>
       <c r="N61" t="b">
         <v>1</v>
@@ -3874,7 +3874,7 @@
         <v>0.3</v>
       </c>
       <c r="H62" t="n">
-        <v>-17.03</v>
+        <v>-18.83</v>
       </c>
       <c r="I62" t="n">
         <v>-9.9</v>
@@ -3885,7 +3885,7 @@
         <v>-21.11</v>
       </c>
       <c r="M62" t="n">
-        <v>-18.41</v>
+        <v>-20.21</v>
       </c>
       <c r="N62" t="b">
         <v>1</v>
@@ -3923,7 +3923,7 @@
         <v>49.4</v>
       </c>
       <c r="H63" t="n">
-        <v>4.49</v>
+        <v>3.93</v>
       </c>
       <c r="I63" t="n">
         <v>2.9</v>
@@ -3934,7 +3934,7 @@
         <v>-5.67</v>
       </c>
       <c r="M63" t="n">
-        <v>3.29</v>
+        <v>2.74</v>
       </c>
       <c r="N63" t="b">
         <v>1</v>
@@ -3972,7 +3972,7 @@
         <v>4.5</v>
       </c>
       <c r="H64" t="n">
-        <v>-10.4</v>
+        <v>-10.17</v>
       </c>
       <c r="I64" t="n">
         <v>-7.61</v>
@@ -3980,10 +3980,10 @@
       <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr"/>
       <c r="L64" t="n">
-        <v>-10.85</v>
+        <v>-10.98</v>
       </c>
       <c r="M64" t="n">
-        <v>-11.6</v>
+        <v>-11.36</v>
       </c>
       <c r="N64" t="b">
         <v>1</v>
@@ -4021,18 +4021,20 @@
         <v>4.2</v>
       </c>
       <c r="H65" t="n">
-        <v>-17.64</v>
+        <v>-20.21</v>
       </c>
       <c r="I65" t="n">
         <v>-6.86</v>
       </c>
-      <c r="J65" t="inlineStr"/>
+      <c r="J65" t="n">
+        <v>-20.21</v>
+      </c>
       <c r="K65" t="inlineStr"/>
       <c r="L65" t="n">
-        <v>-18.26</v>
+        <v>-20.23</v>
       </c>
       <c r="M65" t="n">
-        <v>-18.84</v>
+        <v>-20.68</v>
       </c>
       <c r="N65" t="b">
         <v>0</v>
@@ -4070,7 +4072,7 @@
         <v>15.4</v>
       </c>
       <c r="H66" t="n">
-        <v>-5.67</v>
+        <v>-6.09</v>
       </c>
       <c r="I66" t="n">
         <v>-1.19</v>
@@ -4078,10 +4080,10 @@
       <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr"/>
       <c r="L66" t="n">
-        <v>-5.81</v>
+        <v>-7.43</v>
       </c>
       <c r="M66" t="n">
-        <v>-6.86</v>
+        <v>-7.28</v>
       </c>
       <c r="N66" t="b">
         <v>0</v>
@@ -4119,20 +4121,20 @@
         <v>15.5</v>
       </c>
       <c r="H67" t="n">
-        <v>-9.800000000000001</v>
+        <v>-7.45</v>
       </c>
       <c r="I67" t="n">
         <v>-7.36</v>
       </c>
       <c r="J67" t="n">
-        <v>-9.800000000000001</v>
+        <v>-7.45</v>
       </c>
       <c r="K67" t="inlineStr"/>
       <c r="L67" t="n">
         <v>-12.98</v>
       </c>
       <c r="M67" t="n">
-        <v>-11.18</v>
+        <v>-8.83</v>
       </c>
       <c r="N67" t="b">
         <v>0</v>
@@ -4174,20 +4176,20 @@
         <v>-8.5</v>
       </c>
       <c r="H68" t="n">
-        <v>-0.5</v>
+        <v>-0.61</v>
       </c>
       <c r="I68" t="n">
         <v>-3.04</v>
       </c>
       <c r="J68" t="n">
-        <v>-0.5</v>
+        <v>-0.61</v>
       </c>
       <c r="K68" t="inlineStr"/>
       <c r="L68" t="n">
         <v>-4.96</v>
       </c>
       <c r="M68" t="n">
-        <v>-1.87</v>
+        <v>-1.98</v>
       </c>
       <c r="N68" t="b">
         <v>0</v>
@@ -4225,7 +4227,7 @@
         <v>1.8</v>
       </c>
       <c r="H69" t="n">
-        <v>-13.36</v>
+        <v>-12.48</v>
       </c>
       <c r="I69" t="n">
         <v>-6.45</v>
@@ -4238,7 +4240,7 @@
         <v>-13.57</v>
       </c>
       <c r="M69" t="n">
-        <v>-14.74</v>
+        <v>-13.12</v>
       </c>
       <c r="N69" t="b">
         <v>0</v>
@@ -4276,20 +4278,20 @@
         <v>33.9</v>
       </c>
       <c r="H70" t="n">
-        <v>13.25</v>
+        <v>14.43</v>
       </c>
       <c r="I70" t="n">
         <v>-7.74</v>
       </c>
       <c r="J70" t="n">
-        <v>13.25</v>
+        <v>14.43</v>
       </c>
       <c r="K70" t="inlineStr"/>
       <c r="L70" t="n">
         <v>-9.449999999999999</v>
       </c>
       <c r="M70" t="n">
-        <v>11.87</v>
+        <v>13.06</v>
       </c>
       <c r="N70" t="b">
         <v>0</v>
@@ -4327,7 +4329,7 @@
         <v>-25</v>
       </c>
       <c r="H71" t="n">
-        <v>-4.13</v>
+        <v>-5.39</v>
       </c>
       <c r="I71" t="n">
         <v>2.51</v>
@@ -4340,7 +4342,7 @@
         <v>-4.88</v>
       </c>
       <c r="M71" t="n">
-        <v>-5.33</v>
+        <v>-6.6</v>
       </c>
       <c r="N71" t="b">
         <v>0</v>
@@ -4378,7 +4380,7 @@
         <v>-12.6</v>
       </c>
       <c r="H72" t="n">
-        <v>-22.79</v>
+        <v>-23.45</v>
       </c>
       <c r="I72" t="n">
         <v>-7.89</v>
@@ -4391,7 +4393,7 @@
         <v>-21.29</v>
       </c>
       <c r="M72" t="n">
-        <v>-24.01</v>
+        <v>-24.67</v>
       </c>
       <c r="N72" t="b">
         <v>0</v>
@@ -4429,7 +4431,7 @@
         <v>-17.9</v>
       </c>
       <c r="H73" t="n">
-        <v>-4.99</v>
+        <v>-7.39</v>
       </c>
       <c r="I73" t="n">
         <v>0.6</v>
@@ -4442,7 +4444,7 @@
         <v>-4.72</v>
       </c>
       <c r="M73" t="n">
-        <v>-6.21</v>
+        <v>-8.609999999999999</v>
       </c>
       <c r="N73" t="b">
         <v>1</v>
@@ -4480,7 +4482,7 @@
         <v>2.1</v>
       </c>
       <c r="H74" t="n">
-        <v>-15.29</v>
+        <v>-17.66</v>
       </c>
       <c r="I74" t="n">
         <v>0.25</v>
@@ -4493,7 +4495,7 @@
         <v>-16.43</v>
       </c>
       <c r="M74" t="n">
-        <v>-16.51</v>
+        <v>-18.88</v>
       </c>
       <c r="N74" t="b">
         <v>1</v>
@@ -4531,7 +4533,7 @@
         <v>19.4</v>
       </c>
       <c r="H75" t="n">
-        <v>-12.14</v>
+        <v>-12.47</v>
       </c>
       <c r="I75" t="n">
         <v>-10.01</v>
@@ -4544,7 +4546,7 @@
         <v>-15.23</v>
       </c>
       <c r="M75" t="n">
-        <v>-12.78</v>
+        <v>-13.11</v>
       </c>
       <c r="N75" t="b">
         <v>1</v>
@@ -4582,7 +4584,7 @@
         <v>-30.5</v>
       </c>
       <c r="H76" t="n">
-        <v>-21.36</v>
+        <v>-24.31</v>
       </c>
       <c r="I76" t="n">
         <v>-4.6</v>
@@ -4595,7 +4597,7 @@
         <v>-10.37</v>
       </c>
       <c r="M76" t="n">
-        <v>-22</v>
+        <v>-24.95</v>
       </c>
       <c r="N76" t="b">
         <v>0</v>
@@ -4633,7 +4635,7 @@
         <v>-20.5</v>
       </c>
       <c r="H77" t="n">
-        <v>-9.16</v>
+        <v>-9.43</v>
       </c>
       <c r="I77" t="n">
         <v>-4.62</v>
@@ -4646,7 +4648,7 @@
         <v>-9.92</v>
       </c>
       <c r="M77" t="n">
-        <v>-9.800000000000001</v>
+        <v>-10.07</v>
       </c>
       <c r="N77" t="b">
         <v>0</v>
@@ -4684,7 +4686,7 @@
         <v>-12.3</v>
       </c>
       <c r="H78" t="n">
-        <v>-18.87</v>
+        <v>-24.13</v>
       </c>
       <c r="I78" t="n">
         <v>-4.36</v>
@@ -4697,7 +4699,7 @@
         <v>-13.26</v>
       </c>
       <c r="M78" t="n">
-        <v>-19.73</v>
+        <v>-24.99</v>
       </c>
       <c r="N78" t="b">
         <v>0</v>
@@ -4735,7 +4737,7 @@
         <v>13.7</v>
       </c>
       <c r="H79" t="n">
-        <v>-14.84</v>
+        <v>-16.66</v>
       </c>
       <c r="I79" t="n">
         <v>-12.16</v>
@@ -4748,7 +4750,7 @@
         <v>-13.02</v>
       </c>
       <c r="M79" t="n">
-        <v>-15.7</v>
+        <v>-17.52</v>
       </c>
       <c r="N79" t="b">
         <v>0</v>
@@ -4786,7 +4788,7 @@
         <v>-2.6</v>
       </c>
       <c r="H80" t="n">
-        <v>-7.71</v>
+        <v>-9.19</v>
       </c>
       <c r="I80" t="n">
         <v>-4.27</v>
@@ -4799,7 +4801,7 @@
         <v>-4.86</v>
       </c>
       <c r="M80" t="n">
-        <v>-8.57</v>
+        <v>-10.05</v>
       </c>
       <c r="N80" t="b">
         <v>1</v>
@@ -4837,7 +4839,7 @@
         <v>25.6</v>
       </c>
       <c r="H81" t="n">
-        <v>-4.17</v>
+        <v>-6.01</v>
       </c>
       <c r="I81" t="n">
         <v>4.26</v>
@@ -4850,7 +4852,7 @@
         <v>-10.74</v>
       </c>
       <c r="M81" t="n">
-        <v>-5.03</v>
+        <v>-6.87</v>
       </c>
       <c r="N81" t="b">
         <v>0</v>
@@ -4888,7 +4890,7 @@
         <v>23.8</v>
       </c>
       <c r="H82" t="n">
-        <v>7.04</v>
+        <v>4.35</v>
       </c>
       <c r="I82" t="n">
         <v>1.36</v>
@@ -4901,7 +4903,7 @@
         <v>-9.94</v>
       </c>
       <c r="M82" t="n">
-        <v>7.15</v>
+        <v>4.46</v>
       </c>
       <c r="N82" t="b">
         <v>1</v>
@@ -4939,7 +4941,7 @@
         <v>38.9</v>
       </c>
       <c r="H83" t="n">
-        <v>-8.77</v>
+        <v>-10.09</v>
       </c>
       <c r="I83" t="n">
         <v>-9.220000000000001</v>
@@ -4952,7 +4954,7 @@
         <v>-9.83</v>
       </c>
       <c r="M83" t="n">
-        <v>-8.65</v>
+        <v>-9.970000000000001</v>
       </c>
       <c r="N83" t="b">
         <v>1</v>
@@ -4990,7 +4992,7 @@
         <v>32.1</v>
       </c>
       <c r="H84" t="n">
-        <v>29.55</v>
+        <v>33.7</v>
       </c>
       <c r="I84" t="n">
         <v>11.84</v>
@@ -5003,7 +5005,7 @@
         <v>-1.82</v>
       </c>
       <c r="M84" t="n">
-        <v>29.67</v>
+        <v>33.81</v>
       </c>
       <c r="N84" t="b">
         <v>0</v>
@@ -5041,7 +5043,7 @@
         <v>53.4</v>
       </c>
       <c r="H85" t="n">
-        <v>9.98</v>
+        <v>9.6</v>
       </c>
       <c r="I85" t="n">
         <v>2.75</v>
@@ -5054,7 +5056,7 @@
         <v>-2.31</v>
       </c>
       <c r="M85" t="n">
-        <v>10.4</v>
+        <v>10.02</v>
       </c>
       <c r="N85" t="b">
         <v>0</v>
@@ -5092,7 +5094,7 @@
         <v>54.1</v>
       </c>
       <c r="H86" t="n">
-        <v>13.13</v>
+        <v>12.75</v>
       </c>
       <c r="I86" t="n">
         <v>5.54</v>
@@ -5105,7 +5107,7 @@
         <v>-0.41</v>
       </c>
       <c r="M86" t="n">
-        <v>13.07</v>
+        <v>12.7</v>
       </c>
       <c r="N86" t="b">
         <v>0</v>
@@ -5143,7 +5145,7 @@
         <v>43.2</v>
       </c>
       <c r="H87" t="n">
-        <v>-20.23</v>
+        <v>-20.83</v>
       </c>
       <c r="I87" t="n">
         <v>-3.15</v>
@@ -5156,7 +5158,7 @@
         <v>-17.51</v>
       </c>
       <c r="M87" t="n">
-        <v>-20.29</v>
+        <v>-20.88</v>
       </c>
       <c r="N87" t="b">
         <v>1</v>
@@ -5194,7 +5196,7 @@
         <v>-8.199999999999999</v>
       </c>
       <c r="H88" t="n">
-        <v>-4.93</v>
+        <v>-5.01</v>
       </c>
       <c r="I88" t="n">
         <v>5.34</v>
@@ -5207,7 +5209,7 @@
         <v>-5.27</v>
       </c>
       <c r="M88" t="n">
-        <v>-4.99</v>
+        <v>-5.06</v>
       </c>
       <c r="N88" t="b">
         <v>1</v>
@@ -5245,7 +5247,7 @@
         <v>-1.2</v>
       </c>
       <c r="H89" t="n">
-        <v>-1.77</v>
+        <v>0.01</v>
       </c>
       <c r="I89" t="n">
         <v>8.27</v>
@@ -5258,7 +5260,7 @@
         <v>-5.3</v>
       </c>
       <c r="M89" t="n">
-        <v>-1.87</v>
+        <v>-0.09</v>
       </c>
       <c r="N89" t="b">
         <v>0</v>
@@ -5296,7 +5298,7 @@
         <v>-23.9</v>
       </c>
       <c r="H90" t="n">
-        <v>-6.71</v>
+        <v>-7.28</v>
       </c>
       <c r="I90" t="n">
         <v>3.28</v>
@@ -5309,7 +5311,7 @@
         <v>-4.46</v>
       </c>
       <c r="M90" t="n">
-        <v>-7.06</v>
+        <v>-7.63</v>
       </c>
       <c r="N90" t="b">
         <v>1</v>
@@ -5351,7 +5353,7 @@
         <v>-6.1</v>
       </c>
       <c r="H91" t="n">
-        <v>9</v>
+        <v>7.41</v>
       </c>
       <c r="I91" t="n">
         <v>4.9</v>
@@ -5364,7 +5366,7 @@
         <v>-9</v>
       </c>
       <c r="M91" t="n">
-        <v>8.65</v>
+        <v>7.06</v>
       </c>
       <c r="N91" t="b">
         <v>1</v>
@@ -5402,7 +5404,7 @@
         <v>26.7</v>
       </c>
       <c r="H92" t="n">
-        <v>-0.84</v>
+        <v>-0.87</v>
       </c>
       <c r="I92" t="n">
         <v>-0.05</v>
@@ -5415,7 +5417,7 @@
         <v>-0.87</v>
       </c>
       <c r="M92" t="n">
-        <v>-1.19</v>
+        <v>-1.22</v>
       </c>
       <c r="N92" t="b">
         <v>1</v>
@@ -5453,7 +5455,7 @@
         <v>39.5</v>
       </c>
       <c r="H93" t="n">
-        <v>19.46</v>
+        <v>19.23</v>
       </c>
       <c r="I93" t="n">
         <v>-5.13</v>
@@ -5466,7 +5468,7 @@
         <v>-8.869999999999999</v>
       </c>
       <c r="M93" t="n">
-        <v>19.11</v>
+        <v>18.88</v>
       </c>
       <c r="N93" t="b">
         <v>0</v>
@@ -5504,7 +5506,7 @@
         <v>14.3</v>
       </c>
       <c r="H94" t="n">
-        <v>-1.79</v>
+        <v>-5.38</v>
       </c>
       <c r="I94" t="n">
         <v>-0.43</v>
@@ -5517,7 +5519,7 @@
         <v>-11.86</v>
       </c>
       <c r="M94" t="n">
-        <v>-2.14</v>
+        <v>-5.01</v>
       </c>
       <c r="N94" t="b">
         <v>0</v>
@@ -5555,7 +5557,7 @@
         <v>-11.3</v>
       </c>
       <c r="H95" t="n">
-        <v>-2.38</v>
+        <v>-2.23</v>
       </c>
       <c r="I95" t="n">
         <v>1.31</v>
@@ -5568,7 +5570,7 @@
         <v>-1.88</v>
       </c>
       <c r="M95" t="n">
-        <v>-2.73</v>
+        <v>-2.57</v>
       </c>
       <c r="N95" t="b">
         <v>0</v>
@@ -5606,7 +5608,7 @@
         <v>-23.5</v>
       </c>
       <c r="H96" t="n">
-        <v>-11.18</v>
+        <v>-14.57</v>
       </c>
       <c r="I96" t="n">
         <v>13.29</v>
@@ -5619,7 +5621,7 @@
         <v>-14.04</v>
       </c>
       <c r="M96" t="n">
-        <v>-11.53</v>
+        <v>-14.92</v>
       </c>
       <c r="N96" t="b">
         <v>0</v>
@@ -5657,7 +5659,7 @@
         <v>10.5</v>
       </c>
       <c r="H97" t="n">
-        <v>-7.06</v>
+        <v>-7.99</v>
       </c>
       <c r="I97" t="n">
         <v>-0.86</v>
@@ -5670,7 +5672,7 @@
         <v>-6.11</v>
       </c>
       <c r="M97" t="n">
-        <v>-7.41</v>
+        <v>-8.34</v>
       </c>
       <c r="N97" t="b">
         <v>0</v>
@@ -5708,7 +5710,7 @@
         <v>-3.5</v>
       </c>
       <c r="H98" t="n">
-        <v>0.5600000000000001</v>
+        <v>-0.34</v>
       </c>
       <c r="I98" t="n">
         <v>-4.95</v>
@@ -5721,7 +5723,7 @@
         <v>-8.43</v>
       </c>
       <c r="M98" t="n">
-        <v>0</v>
+        <v>-0.9</v>
       </c>
       <c r="N98" t="b">
         <v>1</v>
@@ -5759,7 +5761,7 @@
         <v>-12.8</v>
       </c>
       <c r="H99" t="n">
-        <v>1.46</v>
+        <v>-0.3</v>
       </c>
       <c r="I99" t="n">
         <v>-1.74</v>
@@ -5772,7 +5774,7 @@
         <v>-2.97</v>
       </c>
       <c r="M99" t="n">
-        <v>0.91</v>
+        <v>-0.13</v>
       </c>
       <c r="N99" t="b">
         <v>0</v>
@@ -5810,7 +5812,7 @@
         <v>2.4</v>
       </c>
       <c r="H100" t="n">
-        <v>15.57</v>
+        <v>19.82</v>
       </c>
       <c r="I100" t="n">
         <v>12.41</v>
@@ -5823,7 +5825,7 @@
         <v>-0.07000000000000001</v>
       </c>
       <c r="M100" t="n">
-        <v>15.01</v>
+        <v>19.99</v>
       </c>
       <c r="N100" t="b">
         <v>0</v>
@@ -5861,7 +5863,7 @@
         <v>-17.9</v>
       </c>
       <c r="H101" t="n">
-        <v>9.41</v>
+        <v>6.27</v>
       </c>
       <c r="I101" t="n">
         <v>-0.5</v>
@@ -5874,7 +5876,7 @@
         <v>-3.43</v>
       </c>
       <c r="M101" t="n">
-        <v>8.85</v>
+        <v>5.71</v>
       </c>
       <c r="N101" t="b">
         <v>1</v>
@@ -5912,7 +5914,7 @@
         <v>11.9</v>
       </c>
       <c r="H102" t="n">
-        <v>-9.039999999999999</v>
+        <v>-9.69</v>
       </c>
       <c r="I102" t="n">
         <v>6.88</v>
@@ -5925,7 +5927,7 @@
         <v>-10.93</v>
       </c>
       <c r="M102" t="n">
-        <v>-9.699999999999999</v>
+        <v>-9.630000000000001</v>
       </c>
       <c r="N102" t="b">
         <v>0</v>
@@ -5963,7 +5965,7 @@
         <v>53.5</v>
       </c>
       <c r="H103" t="n">
-        <v>1.84</v>
+        <v>2.66</v>
       </c>
       <c r="I103" t="n">
         <v>1.23</v>
@@ -5976,7 +5978,7 @@
         <v>-7.57</v>
       </c>
       <c r="M103" t="n">
-        <v>1.18</v>
+        <v>2</v>
       </c>
       <c r="N103" t="b">
         <v>1</v>
@@ -6014,7 +6016,7 @@
         <v>18.1</v>
       </c>
       <c r="H104" t="n">
-        <v>-1.76</v>
+        <v>-1.79</v>
       </c>
       <c r="I104" t="n">
         <v>-1.69</v>
@@ -6027,7 +6029,7 @@
         <v>-1.92</v>
       </c>
       <c r="M104" t="n">
-        <v>-2.42</v>
+        <v>-2.45</v>
       </c>
       <c r="N104" t="b">
         <v>0</v>
@@ -6065,7 +6067,7 @@
         <v>-1</v>
       </c>
       <c r="H105" t="n">
-        <v>-9.75</v>
+        <v>-14.7</v>
       </c>
       <c r="I105" t="n">
         <v>-6.26</v>
@@ -6078,7 +6080,7 @@
         <v>-15</v>
       </c>
       <c r="M105" t="n">
-        <v>-10.41</v>
+        <v>-15.36</v>
       </c>
       <c r="N105" t="b">
         <v>1</v>
@@ -6116,7 +6118,7 @@
         <v>29.7</v>
       </c>
       <c r="H106" t="n">
-        <v>15.43</v>
+        <v>11.21</v>
       </c>
       <c r="I106" t="n">
         <v>11.27</v>
@@ -6129,7 +6131,7 @@
         <v>0</v>
       </c>
       <c r="M106" t="n">
-        <v>14.77</v>
+        <v>10.54</v>
       </c>
       <c r="N106" t="b">
         <v>1</v>
@@ -6167,7 +6169,7 @@
         <v>15.2</v>
       </c>
       <c r="H107" t="n">
-        <v>-29.88</v>
+        <v>-33.13</v>
       </c>
       <c r="I107" t="n">
         <v>-8.77</v>
@@ -6180,7 +6182,7 @@
         <v>-24.79</v>
       </c>
       <c r="M107" t="n">
-        <v>-29.81</v>
+        <v>-33.06</v>
       </c>
       <c r="N107" t="b">
         <v>1</v>
@@ -6218,7 +6220,7 @@
         <v>22.2</v>
       </c>
       <c r="H108" t="n">
-        <v>6.25</v>
+        <v>7.62</v>
       </c>
       <c r="I108" t="n">
         <v>1.01</v>
@@ -6231,7 +6233,7 @@
         <v>-3.94</v>
       </c>
       <c r="M108" t="n">
-        <v>6.32</v>
+        <v>7.69</v>
       </c>
       <c r="N108" t="b">
         <v>1</v>
@@ -6269,7 +6271,7 @@
         <v>10.8</v>
       </c>
       <c r="H109" t="n">
-        <v>0.38</v>
+        <v>-0.57</v>
       </c>
       <c r="I109" t="n">
         <v>5.62</v>
@@ -6282,7 +6284,7 @@
         <v>-1.59</v>
       </c>
       <c r="M109" t="n">
-        <v>0.45</v>
+        <v>-0.5</v>
       </c>
       <c r="N109" t="b">
         <v>0</v>
@@ -6320,7 +6322,7 @@
         <v>-2.1</v>
       </c>
       <c r="H110" t="n">
-        <v>-3.1</v>
+        <v>-3.87</v>
       </c>
       <c r="I110" t="n">
         <v>0.67</v>
@@ -6333,7 +6335,7 @@
         <v>-7.84</v>
       </c>
       <c r="M110" t="n">
-        <v>-3.03</v>
+        <v>-3.08</v>
       </c>
       <c r="N110" t="b">
         <v>0</v>
@@ -6371,7 +6373,7 @@
         <v>16.7</v>
       </c>
       <c r="H111" t="n">
-        <v>-17.96</v>
+        <v>-19.53</v>
       </c>
       <c r="I111" t="n">
         <v>-15.31</v>
@@ -6384,7 +6386,7 @@
         <v>-22</v>
       </c>
       <c r="M111" t="n">
-        <v>-19.89</v>
+        <v>-20.72</v>
       </c>
       <c r="N111" t="b">
         <v>0</v>
@@ -6422,7 +6424,7 @@
         <v>0.3</v>
       </c>
       <c r="H112" t="n">
-        <v>18.31</v>
+        <v>23.14</v>
       </c>
       <c r="I112" t="n">
         <v>6.01</v>
@@ -6435,7 +6437,7 @@
         <v>-3.85</v>
       </c>
       <c r="M112" t="n">
-        <v>14.86</v>
+        <v>19.69</v>
       </c>
       <c r="N112" t="b">
         <v>0</v>
@@ -6477,7 +6479,7 @@
         <v>-0</v>
       </c>
       <c r="H113" t="n">
-        <v>24.25</v>
+        <v>28.93</v>
       </c>
       <c r="I113" t="n">
         <v>13.5</v>
@@ -6490,7 +6492,7 @@
         <v>-2.53</v>
       </c>
       <c r="M113" t="n">
-        <v>20.8</v>
+        <v>25.48</v>
       </c>
       <c r="N113" t="b">
         <v>1</v>
@@ -6528,7 +6530,7 @@
         <v>10.5</v>
       </c>
       <c r="H114" t="n">
-        <v>2.16</v>
+        <v>0.67</v>
       </c>
       <c r="I114" t="n">
         <v>1.99</v>
@@ -6541,7 +6543,7 @@
         <v>-6.27</v>
       </c>
       <c r="M114" t="n">
-        <v>-1.29</v>
+        <v>-2.78</v>
       </c>
       <c r="N114" t="b">
         <v>1</v>
@@ -6579,7 +6581,7 @@
         <v>30.4</v>
       </c>
       <c r="H115" t="n">
-        <v>5.76</v>
+        <v>5.24</v>
       </c>
       <c r="I115" t="n">
         <v>8.539999999999999</v>
@@ -6592,7 +6594,7 @@
         <v>-0.44</v>
       </c>
       <c r="M115" t="n">
-        <v>2.31</v>
+        <v>1.79</v>
       </c>
       <c r="N115" t="b">
         <v>0</v>
@@ -6634,7 +6636,7 @@
         <v>-3.2</v>
       </c>
       <c r="H116" t="n">
-        <v>13.5</v>
+        <v>16</v>
       </c>
       <c r="I116" t="n">
         <v>15.28</v>
@@ -6647,7 +6649,7 @@
         <v>-2.53</v>
       </c>
       <c r="M116" t="n">
-        <v>10.05</v>
+        <v>12.55</v>
       </c>
       <c r="N116" t="b">
         <v>0</v>
@@ -6685,7 +6687,7 @@
         <v>-23.5</v>
       </c>
       <c r="H117" t="n">
-        <v>37.91</v>
+        <v>25.58</v>
       </c>
       <c r="I117" t="n">
         <v>20.48</v>
@@ -6698,7 +6700,7 @@
         <v>-2.25</v>
       </c>
       <c r="M117" t="n">
-        <v>34.46</v>
+        <v>22.13</v>
       </c>
       <c r="N117" t="b">
         <v>0</v>
@@ -6736,7 +6738,7 @@
         <v>-27.3</v>
       </c>
       <c r="H118" t="n">
-        <v>3</v>
+        <v>1.63</v>
       </c>
       <c r="I118" t="n">
         <v>-8.83</v>
@@ -6749,7 +6751,7 @@
         <v>-19.66</v>
       </c>
       <c r="M118" t="n">
-        <v>-0.45</v>
+        <v>-1.82</v>
       </c>
       <c r="N118" t="b">
         <v>0</v>
@@ -6787,7 +6789,7 @@
         <v>-12.5</v>
       </c>
       <c r="H119" t="n">
-        <v>-1.73</v>
+        <v>-4.52</v>
       </c>
       <c r="I119" t="n">
         <v>21.54</v>
@@ -6800,7 +6802,7 @@
         <v>-0.95</v>
       </c>
       <c r="M119" t="n">
-        <v>-5.84</v>
+        <v>-8.630000000000001</v>
       </c>
       <c r="N119" t="b">
         <v>0</v>
@@ -6838,7 +6840,7 @@
         <v>-37</v>
       </c>
       <c r="H120" t="n">
-        <v>26.54</v>
+        <v>26.83</v>
       </c>
       <c r="I120" t="n">
         <v>18.38</v>
@@ -6851,7 +6853,7 @@
         <v>-5.11</v>
       </c>
       <c r="M120" t="n">
-        <v>22.43</v>
+        <v>22.71</v>
       </c>
       <c r="N120" t="b">
         <v>1</v>
@@ -6893,7 +6895,7 @@
         <v>-3.4</v>
       </c>
       <c r="H121" t="n">
-        <v>7.99</v>
+        <v>6.28</v>
       </c>
       <c r="I121" t="n">
         <v>30.48</v>
@@ -6906,7 +6908,7 @@
         <v>-0.9</v>
       </c>
       <c r="M121" t="n">
-        <v>3.88</v>
+        <v>2.91</v>
       </c>
       <c r="N121" t="b">
         <v>0</v>
@@ -6944,7 +6946,7 @@
         <v>-23.4</v>
       </c>
       <c r="H122" t="n">
-        <v>-4.53</v>
+        <v>-3.02</v>
       </c>
       <c r="I122" t="n">
         <v>-3.58</v>
@@ -6957,7 +6959,7 @@
         <v>-17.98</v>
       </c>
       <c r="M122" t="n">
-        <v>-8.640000000000001</v>
+        <v>-7.13</v>
       </c>
       <c r="N122" t="b">
         <v>0</v>
@@ -6995,7 +6997,7 @@
         <v>-28.9</v>
       </c>
       <c r="H123" t="n">
-        <v>-15.31</v>
+        <v>-17.06</v>
       </c>
       <c r="I123" t="n">
         <v>-12.9</v>
@@ -7008,7 +7010,7 @@
         <v>-23.19</v>
       </c>
       <c r="M123" t="n">
-        <v>-19.42</v>
+        <v>-21.17</v>
       </c>
       <c r="N123" t="b">
         <v>0</v>
@@ -7046,7 +7048,7 @@
         <v>-26.8</v>
       </c>
       <c r="H124" t="n">
-        <v>12.75</v>
+        <v>12.92</v>
       </c>
       <c r="I124" t="n">
         <v>4.56</v>
@@ -7059,7 +7061,7 @@
         <v>-4.09</v>
       </c>
       <c r="M124" t="n">
-        <v>8.640000000000001</v>
+        <v>8.81</v>
       </c>
       <c r="N124" t="b">
         <v>1</v>
@@ -7101,7 +7103,7 @@
         <v>-9.800000000000001</v>
       </c>
       <c r="H125" t="n">
-        <v>-23.14</v>
+        <v>-23.78</v>
       </c>
       <c r="I125" t="n">
         <v>-4.09</v>
@@ -7114,7 +7116,7 @@
         <v>-15.24</v>
       </c>
       <c r="M125" t="n">
-        <v>-28.47</v>
+        <v>-29.11</v>
       </c>
       <c r="N125" t="b">
         <v>0</v>
@@ -7152,7 +7154,7 @@
         <v>21</v>
       </c>
       <c r="H126" t="n">
-        <v>-1.45</v>
+        <v>-1.01</v>
       </c>
       <c r="I126" t="n">
         <v>-0.72</v>
@@ -7165,7 +7167,7 @@
         <v>-7.35</v>
       </c>
       <c r="M126" t="n">
-        <v>-6.78</v>
+        <v>-6.35</v>
       </c>
       <c r="N126" t="b">
         <v>0</v>
@@ -7203,7 +7205,7 @@
         <v>13.2</v>
       </c>
       <c r="H127" t="n">
-        <v>35.34</v>
+        <v>31.41</v>
       </c>
       <c r="I127" t="n">
         <v>8.130000000000001</v>
@@ -7216,7 +7218,7 @@
         <v>-2.36</v>
       </c>
       <c r="M127" t="n">
-        <v>30.01</v>
+        <v>26.08</v>
       </c>
       <c r="N127" t="b">
         <v>0</v>
@@ -7254,7 +7256,7 @@
         <v>6.1</v>
       </c>
       <c r="H128" t="n">
-        <v>1.2</v>
+        <v>-3.99</v>
       </c>
       <c r="I128" t="n">
         <v>10.43</v>
@@ -7267,7 +7269,7 @@
         <v>-1.51</v>
       </c>
       <c r="M128" t="n">
-        <v>-4.13</v>
+        <v>-9.32</v>
       </c>
       <c r="N128" t="b">
         <v>0</v>
@@ -7305,7 +7307,7 @@
         <v>6.5</v>
       </c>
       <c r="H129" t="n">
-        <v>-8.5</v>
+        <v>-7.87</v>
       </c>
       <c r="I129" t="n">
         <v>-0.04</v>
@@ -7318,7 +7320,7 @@
         <v>-4.12</v>
       </c>
       <c r="M129" t="n">
-        <v>-13.83</v>
+        <v>-13.2</v>
       </c>
       <c r="N129" t="b">
         <v>0</v>
@@ -7356,7 +7358,7 @@
         <v>-36.5</v>
       </c>
       <c r="H130" t="n">
-        <v>-29.41</v>
+        <v>-32.08</v>
       </c>
       <c r="I130" t="n">
         <v>-27.75</v>
@@ -7369,7 +7371,7 @@
         <v>-31.28</v>
       </c>
       <c r="M130" t="n">
-        <v>-34.18</v>
+        <v>-36.1</v>
       </c>
       <c r="N130" t="b">
         <v>1</v>
@@ -7407,7 +7409,7 @@
         <v>-14.5</v>
       </c>
       <c r="H131" t="n">
-        <v>-11.08</v>
+        <v>-12.13</v>
       </c>
       <c r="I131" t="n">
         <v>4.48</v>
@@ -7420,7 +7422,7 @@
         <v>-3.33</v>
       </c>
       <c r="M131" t="n">
-        <v>-15.86</v>
+        <v>-16.91</v>
       </c>
       <c r="N131" t="b">
         <v>0</v>
@@ -7458,7 +7460,7 @@
         <v>1.7</v>
       </c>
       <c r="H132" t="n">
-        <v>-1.53</v>
+        <v>-3.04</v>
       </c>
       <c r="I132" t="n">
         <v>8.859999999999999</v>
@@ -7471,7 +7473,7 @@
         <v>-3.27</v>
       </c>
       <c r="M132" t="n">
-        <v>-6.31</v>
+        <v>-7.81</v>
       </c>
       <c r="N132" t="b">
         <v>0</v>
@@ -7509,7 +7511,7 @@
         <v>48.1</v>
       </c>
       <c r="H133" t="n">
-        <v>-4.17</v>
+        <v>-3.46</v>
       </c>
       <c r="I133" t="n">
         <v>0.16</v>
@@ -7522,7 +7524,7 @@
         <v>-8.890000000000001</v>
       </c>
       <c r="M133" t="n">
-        <v>-8.949999999999999</v>
+        <v>-8.23</v>
       </c>
       <c r="N133" t="b">
         <v>0</v>
@@ -7560,7 +7562,7 @@
         <v>-38.7</v>
       </c>
       <c r="H134" t="n">
-        <v>10.53</v>
+        <v>8.57</v>
       </c>
       <c r="I134" t="n">
         <v>17.17</v>
@@ -7573,7 +7575,7 @@
         <v>-0.54</v>
       </c>
       <c r="M134" t="n">
-        <v>5.75</v>
+        <v>3.79</v>
       </c>
       <c r="N134" t="b">
         <v>1</v>
@@ -7611,7 +7613,7 @@
         <v>24.9</v>
       </c>
       <c r="H135" t="n">
-        <v>-2.91</v>
+        <v>-3.69</v>
       </c>
       <c r="I135" t="n">
         <v>10.45</v>
@@ -7624,7 +7626,7 @@
         <v>-0.49</v>
       </c>
       <c r="M135" t="n">
-        <v>-7.69</v>
+        <v>-8.470000000000001</v>
       </c>
       <c r="N135" t="b">
         <v>0</v>
@@ -7662,7 +7664,7 @@
         <v>-34.6</v>
       </c>
       <c r="H136" t="n">
-        <v>18.39</v>
+        <v>20.01</v>
       </c>
       <c r="I136" t="n">
         <v>6.67</v>
@@ -7675,7 +7677,7 @@
         <v>-3.06</v>
       </c>
       <c r="M136" t="n">
-        <v>13.61</v>
+        <v>15.23</v>
       </c>
       <c r="N136" t="b">
         <v>1</v>
@@ -7713,7 +7715,7 @@
         <v>-21.4</v>
       </c>
       <c r="H137" t="n">
-        <v>-0.04</v>
+        <v>-1.15</v>
       </c>
       <c r="I137" t="n">
         <v>2.8</v>
@@ -7726,7 +7728,7 @@
         <v>-2.27</v>
       </c>
       <c r="M137" t="n">
-        <v>-4.82</v>
+        <v>-5.17</v>
       </c>
       <c r="N137" t="b">
         <v>0</v>
@@ -7764,7 +7766,7 @@
         <v>-11.8</v>
       </c>
       <c r="H138" t="n">
-        <v>0.24</v>
+        <v>-3.44</v>
       </c>
       <c r="I138" t="n">
         <v>9.76</v>
@@ -7777,7 +7779,7 @@
         <v>-1.63</v>
       </c>
       <c r="M138" t="n">
-        <v>-4.65</v>
+        <v>-8.33</v>
       </c>
       <c r="N138" t="b">
         <v>1</v>
@@ -7815,7 +7817,7 @@
         <v>0.1</v>
       </c>
       <c r="H139" t="n">
-        <v>-11.42</v>
+        <v>-16.65</v>
       </c>
       <c r="I139" t="n">
         <v>-2.83</v>
@@ -7828,7 +7830,7 @@
         <v>-5.45</v>
       </c>
       <c r="M139" t="n">
-        <v>-16.31</v>
+        <v>-21.54</v>
       </c>
       <c r="N139" t="b">
         <v>1</v>
@@ -7866,7 +7868,7 @@
         <v>-13.8</v>
       </c>
       <c r="H140" t="n">
-        <v>4.24</v>
+        <v>5.22</v>
       </c>
       <c r="I140" t="n">
         <v>4.67</v>
@@ -7879,7 +7881,7 @@
         <v>-5.7</v>
       </c>
       <c r="M140" t="n">
-        <v>-0.64</v>
+        <v>0.33</v>
       </c>
       <c r="N140" t="b">
         <v>0</v>
@@ -7921,7 +7923,7 @@
         <v>-8.800000000000001</v>
       </c>
       <c r="H141" t="n">
-        <v>-1.49</v>
+        <v>-2.35</v>
       </c>
       <c r="I141" t="n">
         <v>15.97</v>
@@ -7934,7 +7936,7 @@
         <v>-0.79</v>
       </c>
       <c r="M141" t="n">
-        <v>-6.37</v>
+        <v>-7.23</v>
       </c>
       <c r="N141" t="b">
         <v>0</v>
@@ -7972,7 +7974,7 @@
         <v>24.1</v>
       </c>
       <c r="H142" t="n">
-        <v>-14.5</v>
+        <v>-14.1</v>
       </c>
       <c r="I142" t="n">
         <v>-8.31</v>
@@ -7985,7 +7987,7 @@
         <v>-18.31</v>
       </c>
       <c r="M142" t="n">
-        <v>-18.58</v>
+        <v>-18.18</v>
       </c>
       <c r="N142" t="b">
         <v>1</v>
@@ -8023,7 +8025,7 @@
         <v>-15.9</v>
       </c>
       <c r="H143" t="n">
-        <v>-0.34</v>
+        <v>2.57</v>
       </c>
       <c r="I143" t="n">
         <v>10.45</v>
@@ -8036,7 +8038,7 @@
         <v>-0.31</v>
       </c>
       <c r="M143" t="n">
-        <v>-4.42</v>
+        <v>-1.51</v>
       </c>
       <c r="N143" t="b">
         <v>1</v>
@@ -8074,7 +8076,7 @@
         <v>-23.3</v>
       </c>
       <c r="H144" t="n">
-        <v>-7.71</v>
+        <v>-9.59</v>
       </c>
       <c r="I144" t="n">
         <v>-20.42</v>
@@ -8087,7 +8089,7 @@
         <v>-27.45</v>
       </c>
       <c r="M144" t="n">
-        <v>-11.79</v>
+        <v>-13.67</v>
       </c>
       <c r="N144" t="b">
         <v>0</v>
@@ -8125,7 +8127,7 @@
         <v>28.9</v>
       </c>
       <c r="H145" t="n">
-        <v>-5.28</v>
+        <v>-5.29</v>
       </c>
       <c r="I145" t="n">
         <v>8.06</v>
@@ -8138,7 +8140,7 @@
         <v>-2.79</v>
       </c>
       <c r="M145" t="n">
-        <v>-10.26</v>
+        <v>-9.51</v>
       </c>
       <c r="N145" t="b">
         <v>0</v>
@@ -8176,7 +8178,7 @@
         <v>40.1</v>
       </c>
       <c r="H146" t="n">
-        <v>35.17</v>
+        <v>41.89</v>
       </c>
       <c r="I146" t="n">
         <v>15.9</v>
@@ -8189,7 +8191,7 @@
         <v>-5.87</v>
       </c>
       <c r="M146" t="n">
-        <v>30.19</v>
+        <v>36.9</v>
       </c>
       <c r="N146" t="b">
         <v>0</v>
@@ -8227,7 +8229,7 @@
         <v>-27.3</v>
       </c>
       <c r="H147" t="n">
-        <v>10.19</v>
+        <v>6.02</v>
       </c>
       <c r="I147" t="n">
         <v>0.75</v>
@@ -8240,7 +8242,7 @@
         <v>-5.46</v>
       </c>
       <c r="M147" t="n">
-        <v>5.33</v>
+        <v>1.16</v>
       </c>
       <c r="N147" t="b">
         <v>0</v>
@@ -8278,7 +8280,7 @@
         <v>19.7</v>
       </c>
       <c r="H148" t="n">
-        <v>-4.66</v>
+        <v>-4.58</v>
       </c>
       <c r="I148" t="n">
         <v>-4.49</v>
@@ -8291,7 +8293,7 @@
         <v>-13.7</v>
       </c>
       <c r="M148" t="n">
-        <v>-9.52</v>
+        <v>-9.44</v>
       </c>
       <c r="N148" t="b">
         <v>0</v>
@@ -8329,7 +8331,7 @@
         <v>-21.3</v>
       </c>
       <c r="H149" t="n">
-        <v>1.6</v>
+        <v>-2.01</v>
       </c>
       <c r="I149" t="n">
         <v>7.16</v>
@@ -8342,7 +8344,7 @@
         <v>-11.9</v>
       </c>
       <c r="M149" t="n">
-        <v>-3.26</v>
+        <v>-6.12</v>
       </c>
       <c r="N149" t="b">
         <v>0</v>
@@ -8380,7 +8382,7 @@
         <v>-21.8</v>
       </c>
       <c r="H150" t="n">
-        <v>-20.65</v>
+        <v>-23.9</v>
       </c>
       <c r="I150" t="n">
         <v>-18.97</v>
@@ -8393,7 +8395,7 @@
         <v>-26.82</v>
       </c>
       <c r="M150" t="n">
-        <v>-25.51</v>
+        <v>-28.76</v>
       </c>
       <c r="N150" t="b">
         <v>1</v>
@@ -8431,7 +8433,7 @@
         <v>-37.6</v>
       </c>
       <c r="H151" t="n">
-        <v>-2.23</v>
+        <v>-3.91</v>
       </c>
       <c r="I151" t="n">
         <v>15.2</v>
@@ -8444,7 +8446,7 @@
         <v>-10.3</v>
       </c>
       <c r="M151" t="n">
-        <v>-6.07</v>
+        <v>-7.01</v>
       </c>
       <c r="N151" t="b">
         <v>0</v>
@@ -8482,7 +8484,7 @@
         <v>53.8</v>
       </c>
       <c r="H152" t="n">
-        <v>39.19</v>
+        <v>45.38</v>
       </c>
       <c r="I152" t="n">
         <v>4.09</v>
@@ -8495,7 +8497,7 @@
         <v>-8.66</v>
       </c>
       <c r="M152" t="n">
-        <v>35.35</v>
+        <v>41.54</v>
       </c>
       <c r="N152" t="b">
         <v>0</v>
@@ -8537,7 +8539,7 @@
         <v>-5.7</v>
       </c>
       <c r="H153" t="n">
-        <v>43.32</v>
+        <v>46.61</v>
       </c>
       <c r="I153" t="n">
         <v>17.92</v>
@@ -8550,7 +8552,7 @@
         <v>-7.48</v>
       </c>
       <c r="M153" t="n">
-        <v>39.48</v>
+        <v>42.77</v>
       </c>
       <c r="N153" t="b">
         <v>0</v>
@@ -8588,7 +8590,7 @@
         <v>-39.3</v>
       </c>
       <c r="H154" t="n">
-        <v>-0.75</v>
+        <v>-2.63</v>
       </c>
       <c r="I154" t="n">
         <v>11.34</v>
@@ -8601,7 +8603,7 @@
         <v>-5.3</v>
       </c>
       <c r="M154" t="n">
-        <v>-4.59</v>
+        <v>-6.47</v>
       </c>
       <c r="N154" t="b">
         <v>0</v>
@@ -8639,7 +8641,7 @@
         <v>57</v>
       </c>
       <c r="H155" t="n">
-        <v>14.86</v>
+        <v>14.27</v>
       </c>
       <c r="I155" t="n">
         <v>-11.21</v>
@@ -8652,7 +8654,7 @@
         <v>-13.87</v>
       </c>
       <c r="M155" t="n">
-        <v>11.02</v>
+        <v>10.43</v>
       </c>
       <c r="N155" t="b">
         <v>1</v>
@@ -8690,7 +8692,7 @@
         <v>-21.8</v>
       </c>
       <c r="H156" t="n">
-        <v>9.82</v>
+        <v>10.31</v>
       </c>
       <c r="I156" t="n">
         <v>1.71</v>
@@ -8703,7 +8705,7 @@
         <v>-6.18</v>
       </c>
       <c r="M156" t="n">
-        <v>5.98</v>
+        <v>6.47</v>
       </c>
       <c r="N156" t="b">
         <v>1</v>
@@ -8741,7 +8743,7 @@
         <v>1</v>
       </c>
       <c r="H157" t="n">
-        <v>-32.46</v>
+        <v>-33.75</v>
       </c>
       <c r="I157" t="n">
         <v>-11.52</v>
@@ -8754,7 +8756,7 @@
         <v>-16.26</v>
       </c>
       <c r="M157" t="n">
-        <v>-36.34</v>
+        <v>-37.64</v>
       </c>
       <c r="N157" t="b">
         <v>1</v>
@@ -8792,7 +8794,7 @@
         <v>45.4</v>
       </c>
       <c r="H158" t="n">
-        <v>16.72</v>
+        <v>16.5</v>
       </c>
       <c r="I158" t="n">
         <v>-1.72</v>
@@ -8805,7 +8807,7 @@
         <v>-23.15</v>
       </c>
       <c r="M158" t="n">
-        <v>12.83</v>
+        <v>13.36</v>
       </c>
       <c r="N158" t="b">
         <v>1</v>
@@ -8843,7 +8845,7 @@
         <v>49.6</v>
       </c>
       <c r="H159" t="n">
-        <v>27.63</v>
+        <v>26.92</v>
       </c>
       <c r="I159" t="n">
         <v>6.34</v>
@@ -8856,7 +8858,7 @@
         <v>-20.75</v>
       </c>
       <c r="M159" t="n">
-        <v>23.74</v>
+        <v>23.78</v>
       </c>
       <c r="N159" t="b">
         <v>0</v>
@@ -8894,7 +8896,7 @@
         <v>55.3</v>
       </c>
       <c r="H160" t="n">
-        <v>-12.11</v>
+        <v>-10.39</v>
       </c>
       <c r="I160" t="n">
         <v>3.73</v>
@@ -8907,7 +8909,7 @@
         <v>-22.94</v>
       </c>
       <c r="M160" t="n">
-        <v>-16</v>
+        <v>-13.53</v>
       </c>
       <c r="N160" t="b">
         <v>0</v>
@@ -8945,7 +8947,7 @@
         <v>76.5</v>
       </c>
       <c r="H161" t="n">
-        <v>24.83</v>
+        <v>20.17</v>
       </c>
       <c r="I161" t="n">
         <v>-5.56</v>
@@ -8958,7 +8960,7 @@
         <v>-33.97</v>
       </c>
       <c r="M161" t="n">
-        <v>20.94</v>
+        <v>17.03</v>
       </c>
       <c r="N161" t="b">
         <v>1</v>
@@ -8996,7 +8998,7 @@
         <v>77.90000000000001</v>
       </c>
       <c r="H162" t="n">
-        <v>18.46</v>
+        <v>15.84</v>
       </c>
       <c r="I162" t="n">
         <v>-3.53</v>
@@ -9009,7 +9011,7 @@
         <v>-20.26</v>
       </c>
       <c r="M162" t="n">
-        <v>14.57</v>
+        <v>12.7</v>
       </c>
       <c r="N162" t="b">
         <v>0</v>
@@ -9047,7 +9049,7 @@
         <v>57.6</v>
       </c>
       <c r="H163" t="n">
-        <v>34.09</v>
+        <v>36.94</v>
       </c>
       <c r="I163" t="n">
         <v>14.81</v>
@@ -9060,7 +9062,7 @@
         <v>-5.11</v>
       </c>
       <c r="M163" t="n">
-        <v>30.2</v>
+        <v>33.81</v>
       </c>
       <c r="N163" t="b">
         <v>0</v>
@@ -9098,7 +9100,7 @@
         <v>32.1</v>
       </c>
       <c r="H164" t="n">
-        <v>22.31</v>
+        <v>17.38</v>
       </c>
       <c r="I164" t="n">
         <v>16.93</v>
@@ -9111,7 +9113,7 @@
         <v>-24.48</v>
       </c>
       <c r="M164" t="n">
-        <v>18.42</v>
+        <v>14.25</v>
       </c>
       <c r="N164" t="b">
         <v>1</v>
@@ -9149,7 +9151,7 @@
         <v>51.8</v>
       </c>
       <c r="H165" t="n">
-        <v>11.3</v>
+        <v>10.38</v>
       </c>
       <c r="I165" t="n">
         <v>10.75</v>
@@ -9162,7 +9164,7 @@
         <v>-25.09</v>
       </c>
       <c r="M165" t="n">
-        <v>7.41</v>
+        <v>7.24</v>
       </c>
       <c r="N165" t="b">
         <v>1</v>
@@ -9200,7 +9202,7 @@
         <v>32.3</v>
       </c>
       <c r="H166" t="n">
-        <v>-24.42</v>
+        <v>-25.09</v>
       </c>
       <c r="I166" t="n">
         <v>-20.76</v>
@@ -9213,7 +9215,7 @@
         <v>-27.91</v>
       </c>
       <c r="M166" t="n">
-        <v>-28.31</v>
+        <v>-28.98</v>
       </c>
       <c r="N166" t="b">
         <v>1</v>
@@ -9251,7 +9253,7 @@
         <v>15.7</v>
       </c>
       <c r="H167" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-4.05</v>
       </c>
       <c r="I167" t="n">
         <v>-0.87</v>
@@ -9264,7 +9266,7 @@
         <v>-29.01</v>
       </c>
       <c r="M167" t="n">
-        <v>-4.7</v>
+        <v>-7.19</v>
       </c>
       <c r="N167" t="b">
         <v>0</v>
@@ -9302,7 +9304,7 @@
         <v>63.7</v>
       </c>
       <c r="H168" t="n">
-        <v>6.46</v>
+        <v>6.93</v>
       </c>
       <c r="I168" t="n">
         <v>-2.16</v>
@@ -9315,7 +9317,7 @@
         <v>-19.1</v>
       </c>
       <c r="M168" t="n">
-        <v>2.58</v>
+        <v>3.04</v>
       </c>
       <c r="N168" t="b">
         <v>0</v>
@@ -9353,7 +9355,7 @@
         <v>3.7</v>
       </c>
       <c r="H169" t="n">
-        <v>-6.43</v>
+        <v>-12.7</v>
       </c>
       <c r="I169" t="n">
         <v>-1.11</v>
@@ -9366,7 +9368,7 @@
         <v>-25.46</v>
       </c>
       <c r="M169" t="n">
-        <v>-10.31</v>
+        <v>-15.84</v>
       </c>
       <c r="N169" t="b">
         <v>1</v>
@@ -9404,7 +9406,7 @@
         <v>42.4</v>
       </c>
       <c r="H170" t="n">
-        <v>15.73</v>
+        <v>11.93</v>
       </c>
       <c r="I170" t="n">
         <v>2.16</v>
@@ -9417,7 +9419,7 @@
         <v>-15.76</v>
       </c>
       <c r="M170" t="n">
-        <v>11.84</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="N170" t="b">
         <v>1</v>
@@ -9455,7 +9457,7 @@
         <v>28.2</v>
       </c>
       <c r="H171" t="n">
-        <v>-11.26</v>
+        <v>-11.19</v>
       </c>
       <c r="I171" t="n">
         <v>-1.71</v>
@@ -9468,7 +9470,7 @@
         <v>-23.43</v>
       </c>
       <c r="M171" t="n">
-        <v>-15.15</v>
+        <v>-14.33</v>
       </c>
       <c r="N171" t="b">
         <v>1</v>
@@ -9506,7 +9508,7 @@
         <v>28.6</v>
       </c>
       <c r="H172" t="n">
-        <v>21.82</v>
+        <v>28.55</v>
       </c>
       <c r="I172" t="n">
         <v>2.81</v>
@@ -9519,7 +9521,7 @@
         <v>-18.87</v>
       </c>
       <c r="M172" t="n">
-        <v>17.93</v>
+        <v>24.66</v>
       </c>
       <c r="N172" t="b">
         <v>1</v>
@@ -9557,7 +9559,7 @@
         <v>89.09999999999999</v>
       </c>
       <c r="H173" t="n">
-        <v>39.14</v>
+        <v>39.37</v>
       </c>
       <c r="I173" t="n">
         <v>18.45</v>
@@ -9570,7 +9572,7 @@
         <v>-9.029999999999999</v>
       </c>
       <c r="M173" t="n">
-        <v>35.26</v>
+        <v>36.23</v>
       </c>
       <c r="N173" t="b">
         <v>0</v>
@@ -9608,7 +9610,7 @@
         <v>50.5</v>
       </c>
       <c r="H174" t="n">
-        <v>20.03</v>
+        <v>18.81</v>
       </c>
       <c r="I174" t="n">
         <v>-2.26</v>
@@ -9621,7 +9623,7 @@
         <v>-20.74</v>
       </c>
       <c r="M174" t="n">
-        <v>16.14</v>
+        <v>15.67</v>
       </c>
       <c r="N174" t="b">
         <v>0</v>
@@ -9659,7 +9661,7 @@
         <v>33.1</v>
       </c>
       <c r="H175" t="n">
-        <v>16.53</v>
+        <v>15.47</v>
       </c>
       <c r="I175" t="n">
         <v>4.68</v>
@@ -9672,7 +9674,7 @@
         <v>-26.7</v>
       </c>
       <c r="M175" t="n">
-        <v>12.65</v>
+        <v>12.33</v>
       </c>
       <c r="N175" t="b">
         <v>1</v>
@@ -9710,7 +9712,7 @@
         <v>46.3</v>
       </c>
       <c r="H176" t="n">
-        <v>-16.28</v>
+        <v>-15.94</v>
       </c>
       <c r="I176" t="n">
         <v>-3.24</v>
@@ -9723,7 +9725,7 @@
         <v>-22.77</v>
       </c>
       <c r="M176" t="n">
-        <v>-20.17</v>
+        <v>-19.08</v>
       </c>
       <c r="N176" t="b">
         <v>0</v>
@@ -9761,7 +9763,7 @@
         <v>-13.8</v>
       </c>
       <c r="H177" t="n">
-        <v>13.7</v>
+        <v>12.37</v>
       </c>
       <c r="I177" t="n">
         <v>6.03</v>
@@ -9774,7 +9776,7 @@
         <v>-13.77</v>
       </c>
       <c r="M177" t="n">
-        <v>9.81</v>
+        <v>8.48</v>
       </c>
       <c r="N177" t="b">
         <v>0</v>
@@ -9812,7 +9814,7 @@
         <v>21.8</v>
       </c>
       <c r="H178" t="n">
-        <v>-10.09</v>
+        <v>-11.26</v>
       </c>
       <c r="I178" t="n">
         <v>-6.34</v>
@@ -9825,7 +9827,7 @@
         <v>-30.04</v>
       </c>
       <c r="M178" t="n">
-        <v>-13.98</v>
+        <v>-15.14</v>
       </c>
       <c r="N178" t="b">
         <v>1</v>
@@ -9863,7 +9865,7 @@
         <v>40.3</v>
       </c>
       <c r="H179" t="n">
-        <v>-8.56</v>
+        <v>-10.27</v>
       </c>
       <c r="I179" t="n">
         <v>1.24</v>
@@ -9876,7 +9878,7 @@
         <v>-20.5</v>
       </c>
       <c r="M179" t="n">
-        <v>-12.44</v>
+        <v>-14.16</v>
       </c>
       <c r="N179" t="b">
         <v>1</v>
@@ -9914,7 +9916,7 @@
         <v>36.6</v>
       </c>
       <c r="H180" t="n">
-        <v>206.77</v>
+        <v>206.02</v>
       </c>
       <c r="I180" t="n">
         <v>-4.23</v>
@@ -9965,7 +9967,7 @@
         <v>24.1</v>
       </c>
       <c r="H181" t="n">
-        <v>6.95</v>
+        <v>2.76</v>
       </c>
       <c r="I181" t="n">
         <v>-1.6</v>
@@ -9978,7 +9980,7 @@
         <v>-22.54</v>
       </c>
       <c r="M181" t="n">
-        <v>3.06</v>
+        <v>-1.13</v>
       </c>
       <c r="N181" t="b">
         <v>1</v>
@@ -10016,7 +10018,7 @@
         <v>50.3</v>
       </c>
       <c r="H182" t="n">
-        <v>1.86</v>
+        <v>-2.1</v>
       </c>
       <c r="I182" t="n">
         <v>-3.34</v>
@@ -10029,7 +10031,7 @@
         <v>-23.32</v>
       </c>
       <c r="M182" t="n">
-        <v>-2.02</v>
+        <v>-5.99</v>
       </c>
       <c r="N182" t="b">
         <v>0</v>
@@ -10067,7 +10069,7 @@
         <v>24.5</v>
       </c>
       <c r="H183" t="n">
-        <v>-27.9</v>
+        <v>-28.71</v>
       </c>
       <c r="I183" t="n">
         <v>-12.99</v>
@@ -10080,7 +10082,7 @@
         <v>-22.54</v>
       </c>
       <c r="M183" t="n">
-        <v>-31.79</v>
+        <v>-32.6</v>
       </c>
       <c r="N183" t="b">
         <v>1</v>
@@ -10118,7 +10120,7 @@
         <v>-4</v>
       </c>
       <c r="H184" t="n">
-        <v>14.15</v>
+        <v>11.81</v>
       </c>
       <c r="I184" t="n">
         <v>-1.59</v>
@@ -10131,7 +10133,7 @@
         <v>-25.38</v>
       </c>
       <c r="M184" t="n">
-        <v>10.27</v>
+        <v>8.67</v>
       </c>
       <c r="N184" t="b">
         <v>0</v>
@@ -10169,7 +10171,7 @@
         <v>14.8</v>
       </c>
       <c r="H185" t="n">
-        <v>-27.84</v>
+        <v>-33.3</v>
       </c>
       <c r="I185" t="n">
         <v>-2.48</v>
@@ -10182,7 +10184,7 @@
         <v>-40.98</v>
       </c>
       <c r="M185" t="n">
-        <v>-31.73</v>
+        <v>-37.19</v>
       </c>
       <c r="N185" t="b">
         <v>0</v>
@@ -10220,7 +10222,7 @@
         <v>-27.6</v>
       </c>
       <c r="H186" t="n">
-        <v>15.92</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="I186" t="n">
         <v>-0.36</v>
@@ -10233,7 +10235,7 @@
         <v>-19.41</v>
       </c>
       <c r="M186" t="n">
-        <v>12.03</v>
+        <v>5.64</v>
       </c>
       <c r="N186" t="b">
         <v>0</v>
@@ -10271,7 +10273,7 @@
         <v>9.1</v>
       </c>
       <c r="H187" t="n">
-        <v>-10.81</v>
+        <v>-15.85</v>
       </c>
       <c r="I187" t="n">
         <v>-2.83</v>
@@ -10284,7 +10286,7 @@
         <v>-23.78</v>
       </c>
       <c r="M187" t="n">
-        <v>-14.7</v>
+        <v>-18.99</v>
       </c>
       <c r="N187" t="b">
         <v>0</v>
@@ -10322,7 +10324,7 @@
         <v>11</v>
       </c>
       <c r="H188" t="n">
-        <v>-7.33</v>
+        <v>-10.51</v>
       </c>
       <c r="I188" t="n">
         <v>3.38</v>
@@ -10335,7 +10337,7 @@
         <v>-18.71</v>
       </c>
       <c r="M188" t="n">
-        <v>-11.21</v>
+        <v>-14.4</v>
       </c>
       <c r="N188" t="b">
         <v>0</v>
@@ -10373,7 +10375,7 @@
         <v>31.2</v>
       </c>
       <c r="H189" t="n">
-        <v>-14.4</v>
+        <v>-14.61</v>
       </c>
       <c r="I189" t="n">
         <v>-11.26</v>
@@ -10386,7 +10388,7 @@
         <v>-22.9</v>
       </c>
       <c r="M189" t="n">
-        <v>-18.29</v>
+        <v>-18.5</v>
       </c>
       <c r="N189" t="b">
         <v>0</v>
@@ -10424,7 +10426,7 @@
         <v>19.3</v>
       </c>
       <c r="H190" t="n">
-        <v>10.48</v>
+        <v>7.84</v>
       </c>
       <c r="I190" t="n">
         <v>11.79</v>
@@ -10437,7 +10439,7 @@
         <v>-16.62</v>
       </c>
       <c r="M190" t="n">
-        <v>6.6</v>
+        <v>3.95</v>
       </c>
       <c r="N190" t="b">
         <v>1</v>
@@ -10475,7 +10477,7 @@
         <v>-8.699999999999999</v>
       </c>
       <c r="H191" t="n">
-        <v>-6.44</v>
+        <v>-10</v>
       </c>
       <c r="I191" t="n">
         <v>17.25</v>
@@ -10488,7 +10490,7 @@
         <v>-4.65</v>
       </c>
       <c r="M191" t="n">
-        <v>-10.33</v>
+        <v>-13.89</v>
       </c>
       <c r="N191" t="b">
         <v>1</v>
@@ -10526,7 +10528,7 @@
         <v>15.2</v>
       </c>
       <c r="H192" t="n">
-        <v>1.02</v>
+        <v>-2.17</v>
       </c>
       <c r="I192" t="n">
         <v>5.36</v>
@@ -10539,7 +10541,7 @@
         <v>-28.18</v>
       </c>
       <c r="M192" t="n">
-        <v>-2.87</v>
+        <v>-5.31</v>
       </c>
       <c r="N192" t="b">
         <v>1</v>
@@ -10577,7 +10579,7 @@
         <v>37.2</v>
       </c>
       <c r="H193" t="n">
-        <v>-24.96</v>
+        <v>-24.28</v>
       </c>
       <c r="I193" t="n">
         <v>-7.64</v>
@@ -10590,7 +10592,7 @@
         <v>-26.24</v>
       </c>
       <c r="M193" t="n">
-        <v>-28.84</v>
+        <v>-28.17</v>
       </c>
       <c r="N193" t="b">
         <v>1</v>
@@ -10632,7 +10634,7 @@
         <v>-0.5</v>
       </c>
       <c r="H194" t="n">
-        <v>31.07</v>
+        <v>29.35</v>
       </c>
       <c r="I194" t="n">
         <v>12.75</v>
@@ -10645,7 +10647,7 @@
         <v>-4.72</v>
       </c>
       <c r="M194" t="n">
-        <v>27.19</v>
+        <v>25.47</v>
       </c>
       <c r="N194" t="b">
         <v>0</v>
@@ -10683,7 +10685,7 @@
         <v>-27.9</v>
       </c>
       <c r="H195" t="n">
-        <v>-5.54</v>
+        <v>-11.53</v>
       </c>
       <c r="I195" t="n">
         <v>-5.72</v>
@@ -10696,7 +10698,7 @@
         <v>-11.08</v>
       </c>
       <c r="M195" t="n">
-        <v>-9.43</v>
+        <v>-15.42</v>
       </c>
       <c r="N195" t="b">
         <v>0</v>
@@ -10734,7 +10736,7 @@
         <v>29.8</v>
       </c>
       <c r="H196" t="n">
-        <v>31.27</v>
+        <v>27.51</v>
       </c>
       <c r="I196" t="n">
         <v>-2.74</v>
@@ -10747,7 +10749,7 @@
         <v>-22.36</v>
       </c>
       <c r="M196" t="n">
-        <v>27.39</v>
+        <v>23.62</v>
       </c>
       <c r="N196" t="b">
         <v>1</v>
@@ -10785,7 +10787,7 @@
         <v>60.9</v>
       </c>
       <c r="H197" t="n">
-        <v>4.99</v>
+        <v>4.23</v>
       </c>
       <c r="I197" t="n">
         <v>6.71</v>
@@ -10798,7 +10800,7 @@
         <v>-4.9</v>
       </c>
       <c r="M197" t="n">
-        <v>1.1</v>
+        <v>0.34</v>
       </c>
       <c r="N197" t="b">
         <v>0</v>
@@ -10836,7 +10838,7 @@
         <v>-13.4</v>
       </c>
       <c r="H198" t="n">
-        <v>-25.34</v>
+        <v>-27.68</v>
       </c>
       <c r="I198" t="n">
         <v>0.79</v>
@@ -10849,7 +10851,7 @@
         <v>-15.41</v>
       </c>
       <c r="M198" t="n">
-        <v>-29.23</v>
+        <v>-30.82</v>
       </c>
       <c r="N198" t="b">
         <v>0</v>
@@ -10887,7 +10889,7 @@
         <v>18.2</v>
       </c>
       <c r="H199" t="n">
-        <v>-19.17</v>
+        <v>-18.62</v>
       </c>
       <c r="I199" t="n">
         <v>-11.28</v>
@@ -10900,7 +10902,7 @@
         <v>-16.87</v>
       </c>
       <c r="M199" t="n">
-        <v>-23.05</v>
+        <v>-22.5</v>
       </c>
       <c r="N199" t="b">
         <v>0</v>
@@ -10938,7 +10940,7 @@
         <v>31.2</v>
       </c>
       <c r="H200" t="n">
-        <v>-5.23</v>
+        <v>-6.35</v>
       </c>
       <c r="I200" t="n">
         <v>-3.17</v>
@@ -10951,7 +10953,7 @@
         <v>-23.66</v>
       </c>
       <c r="M200" t="n">
-        <v>-9.119999999999999</v>
+        <v>-9.49</v>
       </c>
       <c r="N200" t="b">
         <v>0</v>
@@ -10989,7 +10991,7 @@
         <v>-1.3</v>
       </c>
       <c r="H201" t="n">
-        <v>-13.23</v>
+        <v>-16.64</v>
       </c>
       <c r="I201" t="n">
         <v>5.29</v>
@@ -11002,7 +11004,7 @@
         <v>-11.87</v>
       </c>
       <c r="M201" t="n">
-        <v>-17.12</v>
+        <v>-19.78</v>
       </c>
       <c r="N201" t="b">
         <v>0</v>
@@ -11040,7 +11042,7 @@
         <v>-29.8</v>
       </c>
       <c r="H202" t="n">
-        <v>70.25</v>
+        <v>69.84</v>
       </c>
       <c r="I202" t="n">
         <v>29.88</v>
@@ -11053,7 +11055,7 @@
         <v>-0.29</v>
       </c>
       <c r="M202" t="n">
-        <v>66.36</v>
+        <v>66.7</v>
       </c>
       <c r="N202" t="b">
         <v>0</v>
@@ -11091,7 +11093,7 @@
         <v>-22.4</v>
       </c>
       <c r="H203" t="n">
-        <v>-9.390000000000001</v>
+        <v>-14.69</v>
       </c>
       <c r="I203" t="n">
         <v>5.79</v>
@@ -11104,7 +11106,7 @@
         <v>-9.67</v>
       </c>
       <c r="M203" t="n">
-        <v>-13.27</v>
+        <v>-18.58</v>
       </c>
       <c r="N203" t="b">
         <v>0</v>
@@ -11142,7 +11144,7 @@
         <v>19.3</v>
       </c>
       <c r="H204" t="n">
-        <v>-18.45</v>
+        <v>-20.34</v>
       </c>
       <c r="I204" t="n">
         <v>-16.69</v>
@@ -11155,7 +11157,7 @@
         <v>-36.39</v>
       </c>
       <c r="M204" t="n">
-        <v>-22.33</v>
+        <v>-24.23</v>
       </c>
       <c r="N204" t="b">
         <v>1</v>
@@ -11193,7 +11195,7 @@
         <v>7.6</v>
       </c>
       <c r="H205" t="n">
-        <v>22.82</v>
+        <v>21.64</v>
       </c>
       <c r="I205" t="n">
         <v>6.22</v>
@@ -11206,7 +11208,7 @@
         <v>-10.68</v>
       </c>
       <c r="M205" t="n">
-        <v>18.93</v>
+        <v>18.5</v>
       </c>
       <c r="N205" t="b">
         <v>0</v>
@@ -11244,7 +11246,7 @@
         <v>68.8</v>
       </c>
       <c r="H206" t="n">
-        <v>18.59</v>
+        <v>16.85</v>
       </c>
       <c r="I206" t="n">
         <v>-1.41</v>
@@ -11257,7 +11259,7 @@
         <v>-19.39</v>
       </c>
       <c r="M206" t="n">
-        <v>14.7</v>
+        <v>13.71</v>
       </c>
       <c r="N206" t="b">
         <v>0</v>
@@ -11295,7 +11297,7 @@
         <v>8.5</v>
       </c>
       <c r="H207" t="n">
-        <v>2.3</v>
+        <v>-2.3</v>
       </c>
       <c r="I207" t="n">
         <v>-4.26</v>
@@ -11308,7 +11310,7 @@
         <v>-23.85</v>
       </c>
       <c r="M207" t="n">
-        <v>-1.59</v>
+        <v>-5.44</v>
       </c>
       <c r="N207" t="b">
         <v>0</v>
@@ -11346,7 +11348,7 @@
         <v>-15.2</v>
       </c>
       <c r="H208" t="n">
-        <v>8.5</v>
+        <v>5.98</v>
       </c>
       <c r="I208" t="n">
         <v>12.27</v>
@@ -11359,7 +11361,7 @@
         <v>-12.27</v>
       </c>
       <c r="M208" t="n">
-        <v>4.61</v>
+        <v>2.85</v>
       </c>
       <c r="N208" t="b">
         <v>0</v>
@@ -11397,7 +11399,7 @@
         <v>-33.1</v>
       </c>
       <c r="H209" t="n">
-        <v>-26.59</v>
+        <v>-29.82</v>
       </c>
       <c r="I209" t="n">
         <v>-13.13</v>
@@ -11410,7 +11412,7 @@
         <v>-21.04</v>
       </c>
       <c r="M209" t="n">
-        <v>-30.48</v>
+        <v>-33.7</v>
       </c>
       <c r="N209" t="b">
         <v>0</v>
@@ -11448,7 +11450,7 @@
         <v>11.8</v>
       </c>
       <c r="H210" t="n">
-        <v>1.11</v>
+        <v>-0.28</v>
       </c>
       <c r="I210" t="n">
         <v>-1.19</v>
@@ -11461,7 +11463,7 @@
         <v>-17.57</v>
       </c>
       <c r="M210" t="n">
-        <v>-2.77</v>
+        <v>-4.17</v>
       </c>
       <c r="N210" t="b">
         <v>1</v>
@@ -11499,7 +11501,7 @@
         <v>27.5</v>
       </c>
       <c r="H211" t="n">
-        <v>16.42</v>
+        <v>18.32</v>
       </c>
       <c r="I211" t="n">
         <v>8.42</v>
@@ -11512,7 +11514,7 @@
         <v>-2.51</v>
       </c>
       <c r="M211" t="n">
-        <v>12.53</v>
+        <v>14.44</v>
       </c>
       <c r="N211" t="b">
         <v>1</v>
@@ -11550,7 +11552,7 @@
         <v>-22.4</v>
       </c>
       <c r="H212" t="n">
-        <v>-9.57</v>
+        <v>-9.869999999999999</v>
       </c>
       <c r="I212" t="n">
         <v>9.42</v>
@@ -11563,7 +11565,7 @@
         <v>-2.79</v>
       </c>
       <c r="M212" t="n">
-        <v>-13.46</v>
+        <v>-13.75</v>
       </c>
       <c r="N212" t="b">
         <v>1</v>
@@ -11601,7 +11603,7 @@
         <v>-14.7</v>
       </c>
       <c r="H213" t="n">
-        <v>-10.19</v>
+        <v>-9.34</v>
       </c>
       <c r="I213" t="n">
         <v>10.3</v>
@@ -11614,7 +11616,7 @@
         <v>-2.6</v>
       </c>
       <c r="M213" t="n">
-        <v>-14.07</v>
+        <v>-13.23</v>
       </c>
       <c r="N213" t="b">
         <v>1</v>
@@ -11656,7 +11658,7 @@
         <v>-9.300000000000001</v>
       </c>
       <c r="H214" t="n">
-        <v>-22.42</v>
+        <v>-23.63</v>
       </c>
       <c r="I214" t="n">
         <v>10.42</v>
@@ -11669,7 +11671,7 @@
         <v>-21.72</v>
       </c>
       <c r="M214" t="n">
-        <v>-26.31</v>
+        <v>-27.52</v>
       </c>
       <c r="N214" t="b">
         <v>1</v>
@@ -11707,7 +11709,7 @@
         <v>-13.5</v>
       </c>
       <c r="H215" t="n">
-        <v>101.96</v>
+        <v>108.85</v>
       </c>
       <c r="I215" t="n">
         <v>18.09</v>
@@ -11720,7 +11722,7 @@
         <v>-14.35</v>
       </c>
       <c r="M215" t="n">
-        <v>98.08</v>
+        <v>104.96</v>
       </c>
       <c r="N215" t="b">
         <v>0</v>
@@ -11758,7 +11760,7 @@
         <v>-27.5</v>
       </c>
       <c r="H216" t="n">
-        <v>-5.59</v>
+        <v>-7.25</v>
       </c>
       <c r="I216" t="n">
         <v>-29.95</v>
@@ -11771,7 +11773,7 @@
         <v>-35.86</v>
       </c>
       <c r="M216" t="n">
-        <v>-9.470000000000001</v>
+        <v>-10.39</v>
       </c>
       <c r="N216" t="b">
         <v>0</v>
@@ -11809,7 +11811,7 @@
         <v>11.9</v>
       </c>
       <c r="H217" t="n">
-        <v>-9.16</v>
+        <v>-12.68</v>
       </c>
       <c r="I217" t="n">
         <v>-3.02</v>
@@ -11822,7 +11824,7 @@
         <v>-24.96</v>
       </c>
       <c r="M217" t="n">
-        <v>-13.05</v>
+        <v>-15.82</v>
       </c>
       <c r="N217" t="b">
         <v>0</v>
@@ -11860,7 +11862,7 @@
         <v>5</v>
       </c>
       <c r="H218" t="n">
-        <v>-5.31</v>
+        <v>-8.41</v>
       </c>
       <c r="I218" t="n">
         <v>0.41</v>
@@ -11873,7 +11875,7 @@
         <v>-13.87</v>
       </c>
       <c r="M218" t="n">
-        <v>-9.199999999999999</v>
+        <v>-12.3</v>
       </c>
       <c r="N218" t="b">
         <v>0</v>
@@ -11911,7 +11913,7 @@
         <v>-35.9</v>
       </c>
       <c r="H219" t="n">
-        <v>21.49</v>
+        <v>17.71</v>
       </c>
       <c r="I219" t="n">
         <v>18.67</v>
@@ -11924,7 +11926,7 @@
         <v>-6.77</v>
       </c>
       <c r="M219" t="n">
-        <v>17.6</v>
+        <v>14.57</v>
       </c>
       <c r="N219" t="b">
         <v>0</v>
@@ -11962,7 +11964,7 @@
         <v>-25.2</v>
       </c>
       <c r="H220" t="n">
-        <v>15.68</v>
+        <v>15.86</v>
       </c>
       <c r="I220" t="n">
         <v>22.53</v>
@@ -11975,7 +11977,7 @@
         <v>-19.27</v>
       </c>
       <c r="M220" t="n">
-        <v>11.79</v>
+        <v>12.72</v>
       </c>
       <c r="N220" t="b">
         <v>1</v>
@@ -12013,7 +12015,7 @@
         <v>5.1</v>
       </c>
       <c r="H221" t="n">
-        <v>2.08</v>
+        <v>0.9</v>
       </c>
       <c r="I221" t="n">
         <v>8.77</v>
@@ -12026,7 +12028,7 @@
         <v>-3.54</v>
       </c>
       <c r="M221" t="n">
-        <v>-1.81</v>
+        <v>-2.99</v>
       </c>
       <c r="N221" t="b">
         <v>1</v>
@@ -12064,7 +12066,7 @@
         <v>20.8</v>
       </c>
       <c r="H222" t="n">
-        <v>-16.34</v>
+        <v>-17.89</v>
       </c>
       <c r="I222" t="n">
         <v>-10.93</v>
@@ -12077,7 +12079,7 @@
         <v>-27.1</v>
       </c>
       <c r="M222" t="n">
-        <v>-20.23</v>
+        <v>-21.78</v>
       </c>
       <c r="N222" t="b">
         <v>0</v>
@@ -12115,7 +12117,7 @@
         <v>-27.7</v>
       </c>
       <c r="H223" t="n">
-        <v>19.76</v>
+        <v>18.01</v>
       </c>
       <c r="I223" t="n">
         <v>-10.22</v>
@@ -12128,7 +12130,7 @@
         <v>-17.14</v>
       </c>
       <c r="M223" t="n">
-        <v>15.88</v>
+        <v>14.87</v>
       </c>
       <c r="N223" t="b">
         <v>0</v>
@@ -12166,7 +12168,7 @@
         <v>-24.7</v>
       </c>
       <c r="H224" t="n">
-        <v>9.289999999999999</v>
+        <v>4.69</v>
       </c>
       <c r="I224" t="n">
         <v>1.65</v>
@@ -12179,7 +12181,7 @@
         <v>-19.04</v>
       </c>
       <c r="M224" t="n">
-        <v>5.41</v>
+        <v>1.55</v>
       </c>
       <c r="N224" t="b">
         <v>0</v>
@@ -12217,7 +12219,7 @@
         <v>-34.9</v>
       </c>
       <c r="H225" t="n">
-        <v>-8.15</v>
+        <v>-8.66</v>
       </c>
       <c r="I225" t="n">
         <v>19.9</v>
@@ -12230,7 +12232,7 @@
         <v>-12.62</v>
       </c>
       <c r="M225" t="n">
-        <v>-12.03</v>
+        <v>-12.54</v>
       </c>
       <c r="N225" t="b">
         <v>0</v>
@@ -12268,7 +12270,7 @@
         <v>-29.5</v>
       </c>
       <c r="H226" t="n">
-        <v>-5.66</v>
+        <v>-5.34</v>
       </c>
       <c r="I226" t="n">
         <v>4.05</v>
@@ -12281,7 +12283,7 @@
         <v>-2.43</v>
       </c>
       <c r="M226" t="n">
-        <v>-9.550000000000001</v>
+        <v>-9.23</v>
       </c>
       <c r="N226" t="b">
         <v>0</v>
@@ -12319,7 +12321,7 @@
         <v>34.2</v>
       </c>
       <c r="H227" t="n">
-        <v>5.37</v>
+        <v>7.74</v>
       </c>
       <c r="I227" t="n">
         <v>8.15</v>
@@ -12332,7 +12334,7 @@
         <v>-7.63</v>
       </c>
       <c r="M227" t="n">
-        <v>1.49</v>
+        <v>3.86</v>
       </c>
       <c r="N227" t="b">
         <v>1</v>
@@ -12370,7 +12372,7 @@
         <v>42</v>
       </c>
       <c r="H228" t="n">
-        <v>-29.39</v>
+        <v>-30.27</v>
       </c>
       <c r="I228" t="n">
         <v>0.6</v>
@@ -12383,7 +12385,7 @@
         <v>-16.67</v>
       </c>
       <c r="M228" t="n">
-        <v>-33.28</v>
+        <v>-34.16</v>
       </c>
       <c r="N228" t="b">
         <v>1</v>
@@ -12425,7 +12427,7 @@
         <v>-0.4</v>
       </c>
       <c r="H229" t="n">
-        <v>-13.61</v>
+        <v>-14.41</v>
       </c>
       <c r="I229" t="n">
         <v>4.83</v>
@@ -12438,7 +12440,7 @@
         <v>-10.75</v>
       </c>
       <c r="M229" t="n">
-        <v>-17.49</v>
+        <v>-18.3</v>
       </c>
       <c r="N229" t="b">
         <v>0</v>
@@ -12476,7 +12478,7 @@
         <v>64.59999999999999</v>
       </c>
       <c r="H230" t="n">
-        <v>6.66</v>
+        <v>9.4</v>
       </c>
       <c r="I230" t="n">
         <v>3.01</v>
@@ -12489,7 +12491,7 @@
         <v>-12</v>
       </c>
       <c r="M230" t="n">
-        <v>2.77</v>
+        <v>5.51</v>
       </c>
       <c r="N230" t="b">
         <v>0</v>
@@ -12527,7 +12529,7 @@
         <v>-25.3</v>
       </c>
       <c r="H231" t="n">
-        <v>30.94</v>
+        <v>30.77</v>
       </c>
       <c r="I231" t="n">
         <v>36.1</v>
@@ -12540,7 +12542,7 @@
         <v>-5.66</v>
       </c>
       <c r="M231" t="n">
-        <v>27.06</v>
+        <v>26.89</v>
       </c>
       <c r="N231" t="b">
         <v>1</v>
@@ -12578,7 +12580,7 @@
         <v>-7.7</v>
       </c>
       <c r="H232" t="n">
-        <v>-2.1</v>
+        <v>-3.75</v>
       </c>
       <c r="I232" t="n">
         <v>-6.47</v>
@@ -12591,7 +12593,7 @@
         <v>-23.05</v>
       </c>
       <c r="M232" t="n">
-        <v>-5.99</v>
+        <v>-7.64</v>
       </c>
       <c r="N232" t="b">
         <v>1</v>
@@ -12629,7 +12631,7 @@
         <v>-2.9</v>
       </c>
       <c r="H233" t="n">
-        <v>8.57</v>
+        <v>4.56</v>
       </c>
       <c r="I233" t="n">
         <v>-1.47</v>
@@ -12642,7 +12644,7 @@
         <v>-7.7</v>
       </c>
       <c r="M233" t="n">
-        <v>4.68</v>
+        <v>0.67</v>
       </c>
       <c r="N233" t="b">
         <v>0</v>
@@ -12680,7 +12682,7 @@
         <v>13.7</v>
       </c>
       <c r="H234" t="n">
-        <v>7.4</v>
+        <v>7.27</v>
       </c>
       <c r="I234" t="n">
         <v>2.74</v>
@@ -12693,7 +12695,7 @@
         <v>-24.02</v>
       </c>
       <c r="M234" t="n">
-        <v>3.51</v>
+        <v>3.38</v>
       </c>
       <c r="N234" t="b">
         <v>1</v>
@@ -12731,7 +12733,7 @@
         <v>21.8</v>
       </c>
       <c r="H235" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.49</v>
       </c>
       <c r="I235" t="n">
         <v>18.32</v>
@@ -12744,7 +12746,7 @@
         <v>-23.27</v>
       </c>
       <c r="M235" t="n">
-        <v>-3.96</v>
+        <v>-4.38</v>
       </c>
       <c r="N235" t="b">
         <v>1</v>
@@ -12782,7 +12784,7 @@
         <v>29.4</v>
       </c>
       <c r="H236" t="n">
-        <v>-3.9</v>
+        <v>-4.41</v>
       </c>
       <c r="I236" t="n">
         <v>-2.62</v>
@@ -12795,7 +12797,7 @@
         <v>-27.18</v>
       </c>
       <c r="M236" t="n">
-        <v>-7.79</v>
+        <v>-8.300000000000001</v>
       </c>
       <c r="N236" t="b">
         <v>1</v>
@@ -12833,7 +12835,7 @@
         <v>-3.7</v>
       </c>
       <c r="H237" t="n">
-        <v>-23.58</v>
+        <v>-24.58</v>
       </c>
       <c r="I237" t="n">
         <v>-8.07</v>
@@ -12846,7 +12848,7 @@
         <v>-22.12</v>
       </c>
       <c r="M237" t="n">
-        <v>-27.47</v>
+        <v>-28.46</v>
       </c>
       <c r="N237" t="b">
         <v>1</v>
@@ -12884,7 +12886,7 @@
         <v>21.3</v>
       </c>
       <c r="H238" t="n">
-        <v>1.87</v>
+        <v>1.54</v>
       </c>
       <c r="I238" t="n">
         <v>0.23</v>
@@ -12897,7 +12899,7 @@
         <v>-0.85</v>
       </c>
       <c r="M238" t="n">
-        <v>-2.01</v>
+        <v>-2.35</v>
       </c>
       <c r="N238" t="b">
         <v>1</v>
@@ -12935,7 +12937,7 @@
         <v>-21.4</v>
       </c>
       <c r="H239" t="n">
-        <v>29.3</v>
+        <v>24.14</v>
       </c>
       <c r="I239" t="n">
         <v>4.55</v>
@@ -12948,7 +12950,7 @@
         <v>-6.39</v>
       </c>
       <c r="M239" t="n">
-        <v>25.42</v>
+        <v>21</v>
       </c>
       <c r="N239" t="b">
         <v>1</v>
@@ -12986,7 +12988,7 @@
         <v>16.3</v>
       </c>
       <c r="H240" t="n">
-        <v>2.97</v>
+        <v>5.89</v>
       </c>
       <c r="I240" t="n">
         <v>-1</v>
@@ -12999,7 +13001,7 @@
         <v>-22.5</v>
       </c>
       <c r="M240" t="n">
-        <v>-0.92</v>
+        <v>2</v>
       </c>
       <c r="N240" t="b">
         <v>1</v>
@@ -13037,7 +13039,7 @@
         <v>11.9</v>
       </c>
       <c r="H241" t="n">
-        <v>-2.06</v>
+        <v>-2.14</v>
       </c>
       <c r="I241" t="n">
         <v>7.74</v>
@@ -13050,7 +13052,7 @@
         <v>-9.43</v>
       </c>
       <c r="M241" t="n">
-        <v>-5.95</v>
+        <v>-6.02</v>
       </c>
       <c r="N241" t="b">
         <v>1</v>
@@ -13088,7 +13090,7 @@
         <v>19.4</v>
       </c>
       <c r="H242" t="n">
-        <v>-2.12</v>
+        <v>-2</v>
       </c>
       <c r="I242" t="n">
         <v>10.89</v>
@@ -13101,7 +13103,7 @@
         <v>-2.97</v>
       </c>
       <c r="M242" t="n">
-        <v>-6.01</v>
+        <v>-5.89</v>
       </c>
       <c r="N242" t="b">
         <v>0</v>
@@ -13139,7 +13141,7 @@
         <v>66.7</v>
       </c>
       <c r="H243" t="n">
-        <v>7.19</v>
+        <v>12.55</v>
       </c>
       <c r="I243" t="n">
         <v>4.84</v>
@@ -13152,7 +13154,7 @@
         <v>-11.7</v>
       </c>
       <c r="M243" t="n">
-        <v>3.3</v>
+        <v>8.66</v>
       </c>
       <c r="N243" t="b">
         <v>0</v>
@@ -13190,7 +13192,7 @@
         <v>3.7</v>
       </c>
       <c r="H244" t="n">
-        <v>12.33</v>
+        <v>13.55</v>
       </c>
       <c r="I244" t="n">
         <v>11.13</v>
@@ -13203,7 +13205,7 @@
         <v>-2.79</v>
       </c>
       <c r="M244" t="n">
-        <v>8.44</v>
+        <v>9.66</v>
       </c>
       <c r="N244" t="b">
         <v>0</v>
@@ -13241,7 +13243,7 @@
         <v>36.8</v>
       </c>
       <c r="H245" t="n">
-        <v>16.95</v>
+        <v>19.02</v>
       </c>
       <c r="I245" t="n">
         <v>15.47</v>
@@ -13254,7 +13256,7 @@
         <v>-0.96</v>
       </c>
       <c r="M245" t="n">
-        <v>13.06</v>
+        <v>15.14</v>
       </c>
       <c r="N245" t="b">
         <v>0</v>
@@ -13292,7 +13294,7 @@
         <v>0.2</v>
       </c>
       <c r="H246" t="n">
-        <v>10.47</v>
+        <v>10.27</v>
       </c>
       <c r="I246" t="n">
         <v>4.35</v>
@@ -13305,7 +13307,7 @@
         <v>-2.79</v>
       </c>
       <c r="M246" t="n">
-        <v>6.58</v>
+        <v>6.38</v>
       </c>
       <c r="N246" t="b">
         <v>1</v>
@@ -13343,7 +13345,7 @@
         <v>-31</v>
       </c>
       <c r="H247" t="n">
-        <v>8.17</v>
+        <v>1.87</v>
       </c>
       <c r="I247" t="n">
         <v>19.41</v>
@@ -13356,7 +13358,7 @@
         <v>-10.33</v>
       </c>
       <c r="M247" t="n">
-        <v>4.28</v>
+        <v>-1.27</v>
       </c>
       <c r="N247" t="b">
         <v>0</v>
@@ -13398,7 +13400,7 @@
         <v>-2</v>
       </c>
       <c r="H248" t="n">
-        <v>-17.61</v>
+        <v>-17.34</v>
       </c>
       <c r="I248" t="n">
         <v>14.61</v>
@@ -13411,7 +13413,7 @@
         <v>-3.45</v>
       </c>
       <c r="M248" t="n">
-        <v>-21.49</v>
+        <v>-21.23</v>
       </c>
       <c r="N248" t="b">
         <v>0</v>
@@ -13449,7 +13451,7 @@
         <v>12.2</v>
       </c>
       <c r="H249" t="n">
-        <v>-38.27</v>
+        <v>-41.95</v>
       </c>
       <c r="I249" t="n">
         <v>3.47</v>
@@ -13462,7 +13464,7 @@
         <v>-27.15</v>
       </c>
       <c r="M249" t="n">
-        <v>-42.15</v>
+        <v>-45.84</v>
       </c>
       <c r="N249" t="b">
         <v>0</v>
@@ -13500,7 +13502,7 @@
         <v>8.4</v>
       </c>
       <c r="H250" t="n">
-        <v>-32.14</v>
+        <v>-32.4</v>
       </c>
       <c r="I250" t="n">
         <v>-0.13</v>
@@ -13513,7 +13515,7 @@
         <v>-10.87</v>
       </c>
       <c r="M250" t="n">
-        <v>-36.03</v>
+        <v>-36.29</v>
       </c>
       <c r="N250" t="b">
         <v>1</v>
@@ -13551,7 +13553,7 @@
         <v>-21.7</v>
       </c>
       <c r="H251" t="n">
-        <v>0.92</v>
+        <v>-0.64</v>
       </c>
       <c r="I251" t="n">
         <v>5.5</v>
@@ -13564,7 +13566,7 @@
         <v>-4.3</v>
       </c>
       <c r="M251" t="n">
-        <v>-2.97</v>
+        <v>-4.53</v>
       </c>
       <c r="N251" t="b">
         <v>0</v>
@@ -13602,7 +13604,7 @@
         <v>-7.3</v>
       </c>
       <c r="H252" t="n">
-        <v>-19.63</v>
+        <v>-20.32</v>
       </c>
       <c r="I252" t="n">
         <v>-4.12</v>
@@ -13615,7 +13617,7 @@
         <v>-15.02</v>
       </c>
       <c r="M252" t="n">
-        <v>-23.51</v>
+        <v>-24.2</v>
       </c>
       <c r="N252" t="b">
         <v>1</v>
@@ -13653,7 +13655,7 @@
         <v>-26.1</v>
       </c>
       <c r="H253" t="n">
-        <v>-15.16</v>
+        <v>-17.55</v>
       </c>
       <c r="I253" t="n">
         <v>5.05</v>
@@ -13666,7 +13668,7 @@
         <v>-9.27</v>
       </c>
       <c r="M253" t="n">
-        <v>-19.05</v>
+        <v>-21.43</v>
       </c>
       <c r="N253" t="b">
         <v>1</v>
@@ -13704,7 +13706,7 @@
         <v>-18.5</v>
       </c>
       <c r="H254" t="n">
-        <v>34.78</v>
+        <v>38.49</v>
       </c>
       <c r="I254" t="n">
         <v>16.22</v>
@@ -13717,7 +13719,7 @@
         <v>-9.960000000000001</v>
       </c>
       <c r="M254" t="n">
-        <v>30.89</v>
+        <v>35.36</v>
       </c>
       <c r="N254" t="b">
         <v>0</v>
@@ -13755,7 +13757,7 @@
         <v>15.3</v>
       </c>
       <c r="H255" t="n">
-        <v>-35.87</v>
+        <v>-37.08</v>
       </c>
       <c r="I255" t="n">
         <v>-21.4</v>
@@ -13768,7 +13770,7 @@
         <v>-26.97</v>
       </c>
       <c r="M255" t="n">
-        <v>-39.76</v>
+        <v>-40.97</v>
       </c>
       <c r="N255" t="b">
         <v>0</v>
@@ -13806,7 +13808,7 @@
         <v>26.1</v>
       </c>
       <c r="H256" t="n">
-        <v>-8.91</v>
+        <v>-8.859999999999999</v>
       </c>
       <c r="I256" t="n">
         <v>-0.51</v>
@@ -13819,7 +13821,7 @@
         <v>-16.45</v>
       </c>
       <c r="M256" t="n">
-        <v>-12.79</v>
+        <v>-12.75</v>
       </c>
       <c r="N256" t="b">
         <v>1</v>
@@ -13861,7 +13863,7 @@
         <v>-8.199999999999999</v>
       </c>
       <c r="H257" t="n">
-        <v>-8.84</v>
+        <v>-8.44</v>
       </c>
       <c r="I257" t="n">
         <v>17.48</v>
@@ -13874,7 +13876,7 @@
         <v>-10.68</v>
       </c>
       <c r="M257" t="n">
-        <v>-12.73</v>
+        <v>-12.32</v>
       </c>
       <c r="N257" t="b">
         <v>0</v>
@@ -13912,7 +13914,7 @@
         <v>17.9</v>
       </c>
       <c r="H258" t="n">
-        <v>1.64</v>
+        <v>2.5</v>
       </c>
       <c r="I258" t="n">
         <v>12.97</v>
@@ -13925,7 +13927,7 @@
         <v>-8.130000000000001</v>
       </c>
       <c r="M258" t="n">
-        <v>-2.25</v>
+        <v>-1.39</v>
       </c>
       <c r="N258" t="b">
         <v>1</v>
@@ -13963,7 +13965,7 @@
         <v>0.7</v>
       </c>
       <c r="H259" t="n">
-        <v>-13.04</v>
+        <v>-14.69</v>
       </c>
       <c r="I259" t="n">
         <v>14.96</v>
@@ -13976,7 +13978,7 @@
         <v>-8.039999999999999</v>
       </c>
       <c r="M259" t="n">
-        <v>-16.93</v>
+        <v>-18.58</v>
       </c>
       <c r="N259" t="b">
         <v>1</v>
@@ -14014,7 +14016,7 @@
         <v>61.6</v>
       </c>
       <c r="H260" t="n">
-        <v>-4.26</v>
+        <v>-2.71</v>
       </c>
       <c r="I260" t="n">
         <v>11.47</v>
@@ -14027,7 +14029,7 @@
         <v>-12.86</v>
       </c>
       <c r="M260" t="n">
-        <v>-8.15</v>
+        <v>-6.6</v>
       </c>
       <c r="N260" t="b">
         <v>0</v>
@@ -14065,7 +14067,7 @@
         <v>54.3</v>
       </c>
       <c r="H261" t="n">
-        <v>-21.72</v>
+        <v>-21.97</v>
       </c>
       <c r="I261" t="n">
         <v>-2.86</v>
@@ -14078,7 +14080,7 @@
         <v>-24.93</v>
       </c>
       <c r="M261" t="n">
-        <v>-25.61</v>
+        <v>-25.86</v>
       </c>
       <c r="N261" t="b">
         <v>0</v>
@@ -14116,7 +14118,7 @@
         <v>14.8</v>
       </c>
       <c r="H262" t="n">
-        <v>-2.46</v>
+        <v>-3.36</v>
       </c>
       <c r="I262" t="n">
         <v>0.35</v>
@@ -14129,7 +14131,7 @@
         <v>-3.68</v>
       </c>
       <c r="M262" t="n">
-        <v>-6.35</v>
+        <v>-7.24</v>
       </c>
       <c r="N262" t="b">
         <v>1</v>
@@ -14167,7 +14169,7 @@
         <v>-13.5</v>
       </c>
       <c r="H263" t="n">
-        <v>-9.4</v>
+        <v>-11.69</v>
       </c>
       <c r="I263" t="n">
         <v>-1.88</v>
@@ -14180,7 +14182,7 @@
         <v>-11.4</v>
       </c>
       <c r="M263" t="n">
-        <v>-13.29</v>
+        <v>-14.83</v>
       </c>
       <c r="N263" t="b">
         <v>0</v>
@@ -14218,7 +14220,7 @@
         <v>25.5</v>
       </c>
       <c r="H264" t="n">
-        <v>0.45</v>
+        <v>2.52</v>
       </c>
       <c r="I264" t="n">
         <v>-9.369999999999999</v>
@@ -14231,7 +14233,7 @@
         <v>-22.11</v>
       </c>
       <c r="M264" t="n">
-        <v>-3.44</v>
+        <v>-1.37</v>
       </c>
       <c r="N264" t="b">
         <v>1</v>
@@ -14273,7 +14275,7 @@
         <v>-7.5</v>
       </c>
       <c r="H265" t="n">
-        <v>-2.82</v>
+        <v>-3.18</v>
       </c>
       <c r="I265" t="n">
         <v>4.46</v>
@@ -14286,7 +14288,7 @@
         <v>-8.52</v>
       </c>
       <c r="M265" t="n">
-        <v>-6.71</v>
+        <v>-7.07</v>
       </c>
       <c r="N265" t="b">
         <v>1</v>
@@ -14324,7 +14326,7 @@
         <v>1.5</v>
       </c>
       <c r="H266" t="n">
-        <v>13.6</v>
+        <v>13.01</v>
       </c>
       <c r="I266" t="n">
         <v>-7.31</v>
@@ -14337,7 +14339,7 @@
         <v>-18.58</v>
       </c>
       <c r="M266" t="n">
-        <v>9.710000000000001</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="N266" t="b">
         <v>0</v>
@@ -14375,7 +14377,7 @@
         <v>-11</v>
       </c>
       <c r="H267" t="n">
-        <v>3.9</v>
+        <v>5.58</v>
       </c>
       <c r="I267" t="n">
         <v>10.7</v>
@@ -14388,7 +14390,7 @@
         <v>-9.43</v>
       </c>
       <c r="M267" t="n">
-        <v>0.01</v>
+        <v>1.69</v>
       </c>
       <c r="N267" t="b">
         <v>1</v>
@@ -14426,7 +14428,7 @@
         <v>-11.4</v>
       </c>
       <c r="H268" t="n">
-        <v>-10.33</v>
+        <v>-10.82</v>
       </c>
       <c r="I268" t="n">
         <v>4.36</v>
@@ -14439,7 +14441,7 @@
         <v>-11.36</v>
       </c>
       <c r="M268" t="n">
-        <v>-14.21</v>
+        <v>-14.71</v>
       </c>
       <c r="N268" t="b">
         <v>1</v>
@@ -14477,7 +14479,7 @@
         <v>2.1</v>
       </c>
       <c r="H269" t="n">
-        <v>54.93</v>
+        <v>52.91</v>
       </c>
       <c r="I269" t="n">
         <v>20.72</v>
@@ -14490,7 +14492,7 @@
         <v>-5.79</v>
       </c>
       <c r="M269" t="n">
-        <v>51.05</v>
+        <v>49.02</v>
       </c>
       <c r="N269" t="b">
         <v>0</v>
@@ -14528,7 +14530,7 @@
         <v>27.1</v>
       </c>
       <c r="H270" t="n">
-        <v>-6.75</v>
+        <v>-7.41</v>
       </c>
       <c r="I270" t="n">
         <v>5.02</v>
@@ -14541,7 +14543,7 @@
         <v>-14.35</v>
       </c>
       <c r="M270" t="n">
-        <v>-10.64</v>
+        <v>-11.3</v>
       </c>
       <c r="N270" t="b">
         <v>1</v>
@@ -14579,7 +14581,7 @@
         <v>-21.6</v>
       </c>
       <c r="H271" t="n">
-        <v>-1.82</v>
+        <v>-4.61</v>
       </c>
       <c r="I271" t="n">
         <v>1.22</v>
@@ -14592,7 +14594,7 @@
         <v>-6.54</v>
       </c>
       <c r="M271" t="n">
-        <v>-5.7</v>
+        <v>-8.5</v>
       </c>
       <c r="N271" t="b">
         <v>0</v>
@@ -14634,7 +14636,7 @@
         <v>-2.2</v>
       </c>
       <c r="H272" t="n">
-        <v>20.85</v>
+        <v>19.34</v>
       </c>
       <c r="I272" t="n">
         <v>-9.050000000000001</v>
@@ -14647,7 +14649,7 @@
         <v>-18.61</v>
       </c>
       <c r="M272" t="n">
-        <v>16.96</v>
+        <v>16.2</v>
       </c>
       <c r="N272" t="b">
         <v>0</v>
@@ -14685,7 +14687,7 @@
         <v>0.7</v>
       </c>
       <c r="H273" t="n">
-        <v>-2.31</v>
+        <v>-1.78</v>
       </c>
       <c r="I273" t="n">
         <v>11.4</v>
@@ -14698,7 +14700,7 @@
         <v>-7.28</v>
       </c>
       <c r="M273" t="n">
-        <v>-6.19</v>
+        <v>-5.67</v>
       </c>
       <c r="N273" t="b">
         <v>0</v>
@@ -14736,7 +14738,7 @@
         <v>-31.7</v>
       </c>
       <c r="H274" t="n">
-        <v>2.67</v>
+        <v>3.34</v>
       </c>
       <c r="I274" t="n">
         <v>17.04</v>
@@ -14749,7 +14751,7 @@
         <v>-4.05</v>
       </c>
       <c r="M274" t="n">
-        <v>-1.22</v>
+        <v>-0.55</v>
       </c>
       <c r="N274" t="b">
         <v>0</v>
@@ -14787,7 +14789,7 @@
         <v>32.2</v>
       </c>
       <c r="H275" t="n">
-        <v>13.53</v>
+        <v>16.88</v>
       </c>
       <c r="I275" t="n">
         <v>6.49</v>
@@ -14800,7 +14802,7 @@
         <v>-3.92</v>
       </c>
       <c r="M275" t="n">
-        <v>9.640000000000001</v>
+        <v>12.99</v>
       </c>
       <c r="N275" t="b">
         <v>1</v>
@@ -14889,7 +14891,7 @@
         <v>3.2</v>
       </c>
       <c r="H277" t="n">
-        <v>-25.58</v>
+        <v>-22.68</v>
       </c>
       <c r="I277" t="n">
         <v>-10.41</v>
@@ -14902,7 +14904,7 @@
         <v>-23.7</v>
       </c>
       <c r="M277" t="n">
-        <v>-29.46</v>
+        <v>-26.56</v>
       </c>
       <c r="N277" t="b">
         <v>1</v>
@@ -14940,7 +14942,7 @@
         <v>7.3</v>
       </c>
       <c r="H278" t="n">
-        <v>-2.62</v>
+        <v>-1.42</v>
       </c>
       <c r="I278" t="n">
         <v>-0.57</v>
@@ -14953,7 +14955,7 @@
         <v>-5.89</v>
       </c>
       <c r="M278" t="n">
-        <v>-6.5</v>
+        <v>-5.3</v>
       </c>
       <c r="N278" t="b">
         <v>1</v>
@@ -14991,7 +14993,7 @@
         <v>24.5</v>
       </c>
       <c r="H279" t="n">
-        <v>5.1</v>
+        <v>5.66</v>
       </c>
       <c r="I279" t="n">
         <v>17.24</v>
@@ -15004,7 +15006,7 @@
         <v>-0.47</v>
       </c>
       <c r="M279" t="n">
-        <v>1.21</v>
+        <v>1.77</v>
       </c>
       <c r="N279" t="b">
         <v>0</v>
@@ -15042,7 +15044,7 @@
         <v>-0.3</v>
       </c>
       <c r="H280" t="n">
-        <v>-5.65</v>
+        <v>-3.58</v>
       </c>
       <c r="I280" t="n">
         <v>17.76</v>
@@ -15055,7 +15057,7 @@
         <v>-14.18</v>
       </c>
       <c r="M280" t="n">
-        <v>-9.539999999999999</v>
+        <v>-7.47</v>
       </c>
       <c r="N280" t="b">
         <v>1</v>
@@ -15093,7 +15095,7 @@
         <v>4</v>
       </c>
       <c r="H281" t="n">
-        <v>45.54</v>
+        <v>46.1</v>
       </c>
       <c r="I281" t="n">
         <v>8.75</v>
@@ -15106,7 +15108,7 @@
         <v>-11.02</v>
       </c>
       <c r="M281" t="n">
-        <v>41.65</v>
+        <v>42.21</v>
       </c>
       <c r="N281" t="b">
         <v>0</v>
@@ -15144,7 +15146,7 @@
         <v>-6.8</v>
       </c>
       <c r="H282" t="n">
-        <v>45.85</v>
+        <v>48.27</v>
       </c>
       <c r="I282" t="n">
         <v>8.279999999999999</v>
@@ -15157,7 +15159,7 @@
         <v>-6.78</v>
       </c>
       <c r="M282" t="n">
-        <v>41.96</v>
+        <v>44.38</v>
       </c>
       <c r="N282" t="b">
         <v>1</v>
@@ -15195,7 +15197,7 @@
         <v>-42</v>
       </c>
       <c r="H283" t="n">
-        <v>65.17</v>
+        <v>60.1</v>
       </c>
       <c r="I283" t="n">
         <v>-3.61</v>
@@ -15208,7 +15210,7 @@
         <v>-11.94</v>
       </c>
       <c r="M283" t="n">
-        <v>61.28</v>
+        <v>56.96</v>
       </c>
       <c r="N283" t="b">
         <v>0</v>
@@ -15246,7 +15248,7 @@
         <v>14.6</v>
       </c>
       <c r="H284" t="n">
-        <v>0.65</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="I284" t="n">
         <v>8.539999999999999</v>
@@ -15259,7 +15261,7 @@
         <v>-13.21</v>
       </c>
       <c r="M284" t="n">
-        <v>-3.24</v>
+        <v>-4.45</v>
       </c>
       <c r="N284" t="b">
         <v>0</v>
@@ -15297,7 +15299,7 @@
         <v>34.6</v>
       </c>
       <c r="H285" t="n">
-        <v>-1.47</v>
+        <v>-2.73</v>
       </c>
       <c r="I285" t="n">
         <v>5.7</v>
@@ -15310,7 +15312,7 @@
         <v>-7.7</v>
       </c>
       <c r="M285" t="n">
-        <v>-5.36</v>
+        <v>-6.62</v>
       </c>
       <c r="N285" t="b">
         <v>1</v>
@@ -15348,7 +15350,7 @@
         <v>-37.2</v>
       </c>
       <c r="H286" t="n">
-        <v>11.71</v>
+        <v>9.92</v>
       </c>
       <c r="I286" t="n">
         <v>21.67</v>
@@ -15361,7 +15363,7 @@
         <v>-6.64</v>
       </c>
       <c r="M286" t="n">
-        <v>7.82</v>
+        <v>6.04</v>
       </c>
       <c r="N286" t="b">
         <v>0</v>
@@ -15399,7 +15401,7 @@
         <v>-31.2</v>
       </c>
       <c r="H287" t="n">
-        <v>-14.7</v>
+        <v>-17.33</v>
       </c>
       <c r="I287" t="n">
         <v>1.03</v>
@@ -15412,7 +15414,7 @@
         <v>-13.65</v>
       </c>
       <c r="M287" t="n">
-        <v>-18.59</v>
+        <v>-21.21</v>
       </c>
       <c r="N287" t="b">
         <v>0</v>
@@ -15450,7 +15452,7 @@
         <v>10.4</v>
       </c>
       <c r="H288" t="n">
-        <v>25.05</v>
+        <v>25.82</v>
       </c>
       <c r="I288" t="n">
         <v>11.05</v>
@@ -15463,7 +15465,7 @@
         <v>-5.54</v>
       </c>
       <c r="M288" t="n">
-        <v>21.16</v>
+        <v>21.93</v>
       </c>
       <c r="N288" t="b">
         <v>1</v>
@@ -15501,7 +15503,7 @@
         <v>-14.7</v>
       </c>
       <c r="H289" t="n">
-        <v>25.62</v>
+        <v>18.66</v>
       </c>
       <c r="I289" t="n">
         <v>12.94</v>
@@ -15514,7 +15516,7 @@
         <v>-2.34</v>
       </c>
       <c r="M289" t="n">
-        <v>21.74</v>
+        <v>14.78</v>
       </c>
       <c r="N289" t="b">
         <v>0</v>
@@ -15552,7 +15554,7 @@
         <v>-21.5</v>
       </c>
       <c r="H290" t="n">
-        <v>-9.73</v>
+        <v>-14.83</v>
       </c>
       <c r="I290" t="n">
         <v>10.65</v>
@@ -15565,7 +15567,7 @@
         <v>-6.89</v>
       </c>
       <c r="M290" t="n">
-        <v>-13.62</v>
+        <v>-17.97</v>
       </c>
       <c r="N290" t="b">
         <v>1</v>
@@ -15603,7 +15605,7 @@
         <v>20.2</v>
       </c>
       <c r="H291" t="n">
-        <v>-8.960000000000001</v>
+        <v>-8.5</v>
       </c>
       <c r="I291" t="n">
         <v>-1.23</v>
@@ -15616,7 +15618,7 @@
         <v>-12.56</v>
       </c>
       <c r="M291" t="n">
-        <v>-12.84</v>
+        <v>-12.39</v>
       </c>
       <c r="N291" t="b">
         <v>0</v>
@@ -15654,7 +15656,7 @@
         <v>3.5</v>
       </c>
       <c r="H292" t="n">
-        <v>45.26</v>
+        <v>43.51</v>
       </c>
       <c r="I292" t="n">
         <v>33.01</v>
@@ -15667,7 +15669,7 @@
         <v>-0.92</v>
       </c>
       <c r="M292" t="n">
-        <v>41.37</v>
+        <v>39.62</v>
       </c>
       <c r="N292" t="b">
         <v>1</v>
@@ -15705,7 +15707,7 @@
         <v>14</v>
       </c>
       <c r="H293" t="n">
-        <v>21.57</v>
+        <v>25.59</v>
       </c>
       <c r="I293" t="n">
         <v>2.89</v>
@@ -15718,7 +15720,7 @@
         <v>-1.94</v>
       </c>
       <c r="M293" t="n">
-        <v>17.68</v>
+        <v>21.71</v>
       </c>
       <c r="N293" t="b">
         <v>0</v>
@@ -15756,7 +15758,7 @@
         <v>19.8</v>
       </c>
       <c r="H294" t="n">
-        <v>6.61</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="I294" t="n">
         <v>4.74</v>
@@ -15769,7 +15771,7 @@
         <v>-9.9</v>
       </c>
       <c r="M294" t="n">
-        <v>2.72</v>
+        <v>4.57</v>
       </c>
       <c r="N294" t="b">
         <v>1</v>
@@ -15811,7 +15813,7 @@
         <v>-7.4</v>
       </c>
       <c r="H295" t="n">
-        <v>6.02</v>
+        <v>4.01</v>
       </c>
       <c r="I295" t="n">
         <v>-3.85</v>
@@ -15824,7 +15826,7 @@
         <v>-21.11</v>
       </c>
       <c r="M295" t="n">
-        <v>2.13</v>
+        <v>0.13</v>
       </c>
       <c r="N295" t="b">
         <v>0</v>
@@ -15862,7 +15864,7 @@
         <v>-10.8</v>
       </c>
       <c r="H296" t="n">
-        <v>6.73</v>
+        <v>9.09</v>
       </c>
       <c r="I296" t="n">
         <v>1.78</v>
@@ -15875,7 +15877,7 @@
         <v>-7.51</v>
       </c>
       <c r="M296" t="n">
-        <v>2.84</v>
+        <v>5.2</v>
       </c>
       <c r="N296" t="b">
         <v>0</v>
@@ -15913,7 +15915,7 @@
         <v>-24</v>
       </c>
       <c r="H297" t="n">
-        <v>42.75</v>
+        <v>45.65</v>
       </c>
       <c r="I297" t="n">
         <v>10.85</v>
@@ -15926,7 +15928,7 @@
         <v>-5.43</v>
       </c>
       <c r="M297" t="n">
-        <v>38.86</v>
+        <v>41.76</v>
       </c>
       <c r="N297" t="b">
         <v>0</v>
@@ -15964,7 +15966,7 @@
         <v>-28.3</v>
       </c>
       <c r="H298" t="n">
-        <v>-20.82</v>
+        <v>-22.25</v>
       </c>
       <c r="I298" t="n">
         <v>-8.949999999999999</v>
@@ -15977,7 +15979,7 @@
         <v>-13.18</v>
       </c>
       <c r="M298" t="n">
-        <v>-24.7</v>
+        <v>-25.39</v>
       </c>
       <c r="N298" t="b">
         <v>0</v>
@@ -16015,7 +16017,7 @@
         <v>-30.5</v>
       </c>
       <c r="H299" t="n">
-        <v>2.42</v>
+        <v>1.71</v>
       </c>
       <c r="I299" t="n">
         <v>2.96</v>
@@ -16028,7 +16030,7 @@
         <v>-17.88</v>
       </c>
       <c r="M299" t="n">
-        <v>-1.46</v>
+        <v>-1.43</v>
       </c>
       <c r="N299" t="b">
         <v>1</v>
@@ -16066,7 +16068,7 @@
         <v>-6</v>
       </c>
       <c r="H300" t="n">
-        <v>-21.44</v>
+        <v>-22.02</v>
       </c>
       <c r="I300" t="n">
         <v>3.31</v>
@@ -16079,7 +16081,7 @@
         <v>-21.48</v>
       </c>
       <c r="M300" t="n">
-        <v>-25.33</v>
+        <v>-25.9</v>
       </c>
       <c r="N300" t="b">
         <v>1</v>
@@ -16117,7 +16119,7 @@
         <v>-42.2</v>
       </c>
       <c r="H301" t="n">
-        <v>10.16</v>
+        <v>10.01</v>
       </c>
       <c r="I301" t="n">
         <v>19.24</v>
@@ -16130,7 +16132,7 @@
         <v>-0.93</v>
       </c>
       <c r="M301" t="n">
-        <v>6.27</v>
+        <v>6.12</v>
       </c>
       <c r="N301" t="b">
         <v>0</v>
@@ -16168,7 +16170,7 @@
         <v>-34.6</v>
       </c>
       <c r="H302" t="n">
-        <v>1.52</v>
+        <v>1.94</v>
       </c>
       <c r="I302" t="n">
         <v>23.65</v>
@@ -16181,7 +16183,7 @@
         <v>-3.83</v>
       </c>
       <c r="M302" t="n">
-        <v>-2.37</v>
+        <v>-1.95</v>
       </c>
       <c r="N302" t="b">
         <v>1</v>
@@ -16219,7 +16221,7 @@
         <v>-48.1</v>
       </c>
       <c r="H303" t="n">
-        <v>-4.6</v>
+        <v>-8.44</v>
       </c>
       <c r="I303" t="n">
         <v>2.19</v>
@@ -16232,7 +16234,7 @@
         <v>-13.66</v>
       </c>
       <c r="M303" t="n">
-        <v>-8.49</v>
+        <v>-11.58</v>
       </c>
       <c r="N303" t="b">
         <v>0</v>
@@ -16270,7 +16272,7 @@
         <v>-16.2</v>
       </c>
       <c r="H304" t="n">
-        <v>11.6</v>
+        <v>12.69</v>
       </c>
       <c r="I304" t="n">
         <v>25.77</v>
@@ -16283,7 +16285,7 @@
         <v>-1.7</v>
       </c>
       <c r="M304" t="n">
-        <v>7.71</v>
+        <v>8.81</v>
       </c>
       <c r="N304" t="b">
         <v>1</v>
@@ -16321,7 +16323,7 @@
         <v>-24.9</v>
       </c>
       <c r="H305" t="n">
-        <v>40.15</v>
+        <v>32.15</v>
       </c>
       <c r="I305" t="n">
         <v>10.88</v>
@@ -16334,7 +16336,7 @@
         <v>-4.1</v>
       </c>
       <c r="M305" t="n">
-        <v>36.26</v>
+        <v>28.26</v>
       </c>
       <c r="N305" t="b">
         <v>1</v>
@@ -16376,7 +16378,7 @@
         <v>-8.1</v>
       </c>
       <c r="H306" t="n">
-        <v>18.13</v>
+        <v>20.27</v>
       </c>
       <c r="I306" t="n">
         <v>14.27</v>
@@ -16389,7 +16391,7 @@
         <v>-10.92</v>
       </c>
       <c r="M306" t="n">
-        <v>14.24</v>
+        <v>16.38</v>
       </c>
       <c r="N306" t="b">
         <v>1</v>
@@ -16427,7 +16429,7 @@
         <v>-10.2</v>
       </c>
       <c r="H307" t="n">
-        <v>-6.97</v>
+        <v>-10.2</v>
       </c>
       <c r="I307" t="n">
         <v>15.03</v>
@@ -16440,7 +16442,7 @@
         <v>-1.61</v>
       </c>
       <c r="M307" t="n">
-        <v>-10.86</v>
+        <v>-14.08</v>
       </c>
       <c r="N307" t="b">
         <v>1</v>
@@ -16478,7 +16480,7 @@
         <v>68.90000000000001</v>
       </c>
       <c r="H308" t="n">
-        <v>10.83</v>
+        <v>9.32</v>
       </c>
       <c r="I308" t="n">
         <v>1.84</v>
@@ -16491,7 +16493,7 @@
         <v>-10.43</v>
       </c>
       <c r="M308" t="n">
-        <v>6.94</v>
+        <v>5.44</v>
       </c>
       <c r="N308" t="b">
         <v>1</v>
@@ -16529,7 +16531,7 @@
         <v>-40.8</v>
       </c>
       <c r="H309" t="n">
-        <v>-8.460000000000001</v>
+        <v>-10.17</v>
       </c>
       <c r="I309" t="n">
         <v>21.71</v>
@@ -16542,7 +16544,7 @@
         <v>-3.3</v>
       </c>
       <c r="M309" t="n">
-        <v>-12.34</v>
+        <v>-14.06</v>
       </c>
       <c r="N309" t="b">
         <v>1</v>
@@ -16580,7 +16582,7 @@
         <v>-10.1</v>
       </c>
       <c r="H310" t="n">
-        <v>-15.47</v>
+        <v>-14.77</v>
       </c>
       <c r="I310" t="n">
         <v>1.83</v>
@@ -16593,7 +16595,7 @@
         <v>-3.45</v>
       </c>
       <c r="M310" t="n">
-        <v>-19.36</v>
+        <v>-18.65</v>
       </c>
       <c r="N310" t="b">
         <v>0</v>
@@ -16631,7 +16633,7 @@
         <v>40.7</v>
       </c>
       <c r="H311" t="n">
-        <v>40.65</v>
+        <v>43.7</v>
       </c>
       <c r="I311" t="n">
         <v>-4.08</v>
@@ -16644,7 +16646,7 @@
         <v>-11.2</v>
       </c>
       <c r="M311" t="n">
-        <v>36.76</v>
+        <v>39.81</v>
       </c>
       <c r="N311" t="b">
         <v>1</v>
@@ -16682,7 +16684,7 @@
         <v>25.7</v>
       </c>
       <c r="H312" t="n">
-        <v>-8.1</v>
+        <v>-9.32</v>
       </c>
       <c r="I312" t="n">
         <v>11.3</v>
@@ -16695,7 +16697,7 @@
         <v>-11.03</v>
       </c>
       <c r="M312" t="n">
-        <v>-11.99</v>
+        <v>-13.21</v>
       </c>
       <c r="N312" t="b">
         <v>1</v>
@@ -16733,7 +16735,7 @@
         <v>2.3</v>
       </c>
       <c r="H313" t="n">
-        <v>-6.83</v>
+        <v>-5.35</v>
       </c>
       <c r="I313" t="n">
         <v>-0.95</v>
@@ -16746,7 +16748,7 @@
         <v>-7.81</v>
       </c>
       <c r="M313" t="n">
-        <v>-10.72</v>
+        <v>-9.24</v>
       </c>
       <c r="N313" t="b">
         <v>0</v>
@@ -16853,7 +16855,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -16878,16 +16880,16 @@
         <v>-2.7</v>
       </c>
       <c r="H2" t="n">
-        <v>1.76</v>
+        <v>-2.98</v>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="n">
-        <v>-0.55</v>
+        <v>-2.98</v>
       </c>
       <c r="M2" t="n">
-        <v>1.84</v>
+        <v>-2.34</v>
       </c>
       <c r="N2" t="b">
         <v>1</v>
@@ -16900,7 +16902,7 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -16925,16 +16927,16 @@
         <v>26.9</v>
       </c>
       <c r="H3" t="n">
-        <v>3.34</v>
+        <v>-0.99</v>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="n">
-        <v>-0.4</v>
+        <v>-2.51</v>
       </c>
       <c r="M3" t="n">
-        <v>3.42</v>
+        <v>-0.35</v>
       </c>
       <c r="N3" t="b">
         <v>1</v>
@@ -16972,16 +16974,16 @@
         <v>-18.1</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.04</v>
+        <v>1.07</v>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="n">
-        <v>-2.52</v>
+        <v>-2.69</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.97</v>
+        <v>0.14</v>
       </c>
       <c r="N4" t="b">
         <v>1</v>
@@ -17019,7 +17021,7 @@
         <v>-21.5</v>
       </c>
       <c r="H5" t="n">
-        <v>7.91</v>
+        <v>5.73</v>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
@@ -17028,7 +17030,7 @@
         <v>-1.4</v>
       </c>
       <c r="M5" t="n">
-        <v>6.98</v>
+        <v>4.8</v>
       </c>
       <c r="N5" t="b">
         <v>1</v>
@@ -17066,16 +17068,16 @@
         <v>41.6</v>
       </c>
       <c r="H6" t="n">
-        <v>-2.18</v>
+        <v>-3</v>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="n">
-        <v>-3.27</v>
+        <v>-4.38</v>
       </c>
       <c r="M6" t="n">
-        <v>-3.76</v>
+        <v>-4.58</v>
       </c>
       <c r="N6" t="b">
         <v>1</v>
@@ -17113,16 +17115,16 @@
         <v>32.1</v>
       </c>
       <c r="H7" t="n">
-        <v>-2.08</v>
+        <v>-0.52</v>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="n">
-        <v>-4.4</v>
+        <v>-2.19</v>
       </c>
       <c r="M7" t="n">
-        <v>-3.66</v>
+        <v>-2.11</v>
       </c>
       <c r="N7" t="b">
         <v>1</v>
@@ -17160,7 +17162,7 @@
         <v>-14.4</v>
       </c>
       <c r="H8" t="n">
-        <v>1.82</v>
+        <v>-1.19</v>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
@@ -17169,7 +17171,7 @@
         <v>-1.54</v>
       </c>
       <c r="M8" t="n">
-        <v>0.24</v>
+        <v>-2.78</v>
       </c>
       <c r="N8" t="b">
         <v>1</v>
@@ -17207,16 +17209,16 @@
         <v>-10</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.82</v>
+        <v>-3.02</v>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="n">
-        <v>-1.8</v>
+        <v>-5.75</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.4</v>
+        <v>-4.6</v>
       </c>
       <c r="N9" t="b">
         <v>1</v>
@@ -17254,7 +17256,7 @@
         <v>6.4</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.6</v>
+        <v>-1.14</v>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
@@ -17263,7 +17265,7 @@
         <v>-1.45</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.18</v>
+        <v>-2.72</v>
       </c>
       <c r="N10" t="b">
         <v>1</v>
@@ -17301,7 +17303,7 @@
         <v>20.2</v>
       </c>
       <c r="H11" t="n">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
@@ -17310,7 +17312,7 @@
         <v>-1.07</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.36</v>
+        <v>-0.25</v>
       </c>
       <c r="N11" t="b">
         <v>1</v>
@@ -17337,7 +17339,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Extended</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="E12" t="inlineStr"/>
@@ -17348,7 +17350,7 @@
         <v>43.7</v>
       </c>
       <c r="H12" t="n">
-        <v>6.46</v>
+        <v>3.98</v>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
@@ -17357,7 +17359,7 @@
         <v>-2.44</v>
       </c>
       <c r="M12" t="n">
-        <v>4.47</v>
+        <v>1.98</v>
       </c>
       <c r="N12" t="b">
         <v>1</v>
@@ -17395,16 +17397,16 @@
         <v>1.9</v>
       </c>
       <c r="H13" t="n">
-        <v>-2.22</v>
+        <v>-3.03</v>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="n">
-        <v>-3.37</v>
+        <v>-3.2</v>
       </c>
       <c r="M13" t="n">
-        <v>-4.21</v>
+        <v>-5.02</v>
       </c>
       <c r="N13" t="b">
         <v>1</v>
@@ -17442,7 +17444,7 @@
         <v>37.5</v>
       </c>
       <c r="H14" t="n">
-        <v>2.46</v>
+        <v>-0.34</v>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
@@ -17451,7 +17453,7 @@
         <v>-3.95</v>
       </c>
       <c r="M14" t="n">
-        <v>0.31</v>
+        <v>-2.49</v>
       </c>
       <c r="N14" t="b">
         <v>1</v>
@@ -17489,7 +17491,7 @@
         <v>40.2</v>
       </c>
       <c r="H15" t="n">
-        <v>1.44</v>
+        <v>-0.15</v>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
@@ -17498,7 +17500,7 @@
         <v>-3.87</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.71</v>
+        <v>-2.3</v>
       </c>
       <c r="N15" t="b">
         <v>1</v>
@@ -17536,7 +17538,7 @@
         <v>10.7</v>
       </c>
       <c r="H16" t="n">
-        <v>1.21</v>
+        <v>3.18</v>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
@@ -17545,7 +17547,7 @@
         <v>-3.78</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.9399999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="N16" t="b">
         <v>1</v>
@@ -17583,7 +17585,7 @@
         <v>25.6</v>
       </c>
       <c r="H17" t="n">
-        <v>2.42</v>
+        <v>2.11</v>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
@@ -17592,7 +17594,7 @@
         <v>-4.85</v>
       </c>
       <c r="M17" t="n">
-        <v>1.04</v>
+        <v>0.73</v>
       </c>
       <c r="N17" t="b">
         <v>1</v>
@@ -17630,7 +17632,7 @@
         <v>-6.9</v>
       </c>
       <c r="H18" t="n">
-        <v>7.14</v>
+        <v>6.44</v>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
@@ -17639,7 +17641,7 @@
         <v>-4.53</v>
       </c>
       <c r="M18" t="n">
-        <v>5.68</v>
+        <v>4.97</v>
       </c>
       <c r="N18" t="b">
         <v>1</v>
@@ -17677,7 +17679,7 @@
         <v>0.3</v>
       </c>
       <c r="H19" t="n">
-        <v>-11.49</v>
+        <v>-12.25</v>
       </c>
       <c r="I19" t="n">
         <v>-10.53</v>
@@ -17685,10 +17687,10 @@
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="n">
-        <v>-13.26</v>
+        <v>-13.04</v>
       </c>
       <c r="M19" t="n">
-        <v>-12.45</v>
+        <v>-13.22</v>
       </c>
       <c r="N19" t="b">
         <v>1</v>
@@ -17726,7 +17728,7 @@
         <v>2.8</v>
       </c>
       <c r="H20" t="n">
-        <v>2.98</v>
+        <v>1.39</v>
       </c>
       <c r="I20" t="n">
         <v>3.18</v>
@@ -17737,7 +17739,7 @@
         <v>-0.88</v>
       </c>
       <c r="M20" t="n">
-        <v>1.29</v>
+        <v>-0.29</v>
       </c>
       <c r="N20" t="b">
         <v>1</v>
@@ -17764,7 +17766,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Extended</t>
         </is>
       </c>
       <c r="E21" t="inlineStr"/>
@@ -17775,7 +17777,7 @@
         <v>34.5</v>
       </c>
       <c r="H21" t="n">
-        <v>4.65</v>
+        <v>7.38</v>
       </c>
       <c r="I21" t="n">
         <v>0.66</v>
@@ -17786,7 +17788,7 @@
         <v>-2.64</v>
       </c>
       <c r="M21" t="n">
-        <v>2.97</v>
+        <v>5.69</v>
       </c>
       <c r="N21" t="b">
         <v>1</v>
@@ -17824,7 +17826,7 @@
         <v>24.3</v>
       </c>
       <c r="H22" t="n">
-        <v>17.26</v>
+        <v>15.95</v>
       </c>
       <c r="I22" t="n">
         <v>2.54</v>
@@ -17835,7 +17837,7 @@
         <v>-5.21</v>
       </c>
       <c r="M22" t="n">
-        <v>16.22</v>
+        <v>14.91</v>
       </c>
       <c r="N22" t="b">
         <v>1</v>
@@ -17873,7 +17875,7 @@
         <v>-16.9</v>
       </c>
       <c r="H23" t="n">
-        <v>-5.59</v>
+        <v>-7.29</v>
       </c>
       <c r="I23" t="n">
         <v>-6.47</v>
@@ -17884,7 +17886,7 @@
         <v>-9.02</v>
       </c>
       <c r="M23" t="n">
-        <v>-6.63</v>
+        <v>-8.33</v>
       </c>
       <c r="N23" t="b">
         <v>1</v>
@@ -17922,7 +17924,7 @@
         <v>20.3</v>
       </c>
       <c r="H24" t="n">
-        <v>-14.57</v>
+        <v>-16.02</v>
       </c>
       <c r="I24" t="n">
         <v>-2.07</v>
@@ -17930,10 +17932,10 @@
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="n">
-        <v>-15.52</v>
+        <v>-16.13</v>
       </c>
       <c r="M24" t="n">
-        <v>-15.46</v>
+        <v>-16.91</v>
       </c>
       <c r="N24" t="b">
         <v>1</v>
@@ -17971,7 +17973,7 @@
         <v>0.3</v>
       </c>
       <c r="H25" t="n">
-        <v>-17.03</v>
+        <v>-18.83</v>
       </c>
       <c r="I25" t="n">
         <v>-9.9</v>
@@ -17982,7 +17984,7 @@
         <v>-21.11</v>
       </c>
       <c r="M25" t="n">
-        <v>-18.41</v>
+        <v>-20.21</v>
       </c>
       <c r="N25" t="b">
         <v>1</v>
@@ -18020,7 +18022,7 @@
         <v>49.4</v>
       </c>
       <c r="H26" t="n">
-        <v>4.49</v>
+        <v>3.93</v>
       </c>
       <c r="I26" t="n">
         <v>2.9</v>
@@ -18031,7 +18033,7 @@
         <v>-5.67</v>
       </c>
       <c r="M26" t="n">
-        <v>3.29</v>
+        <v>2.74</v>
       </c>
       <c r="N26" t="b">
         <v>1</v>
@@ -18069,7 +18071,7 @@
         <v>4.5</v>
       </c>
       <c r="H27" t="n">
-        <v>-10.4</v>
+        <v>-10.17</v>
       </c>
       <c r="I27" t="n">
         <v>-7.61</v>
@@ -18077,10 +18079,10 @@
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="n">
-        <v>-10.85</v>
+        <v>-10.98</v>
       </c>
       <c r="M27" t="n">
-        <v>-11.6</v>
+        <v>-11.36</v>
       </c>
       <c r="N27" t="b">
         <v>1</v>
@@ -18118,7 +18120,7 @@
         <v>-17.9</v>
       </c>
       <c r="H28" t="n">
-        <v>-4.99</v>
+        <v>-7.39</v>
       </c>
       <c r="I28" t="n">
         <v>0.6</v>
@@ -18131,7 +18133,7 @@
         <v>-4.72</v>
       </c>
       <c r="M28" t="n">
-        <v>-6.21</v>
+        <v>-8.609999999999999</v>
       </c>
       <c r="N28" t="b">
         <v>1</v>
@@ -18169,7 +18171,7 @@
         <v>2.1</v>
       </c>
       <c r="H29" t="n">
-        <v>-15.29</v>
+        <v>-17.66</v>
       </c>
       <c r="I29" t="n">
         <v>0.25</v>
@@ -18182,7 +18184,7 @@
         <v>-16.43</v>
       </c>
       <c r="M29" t="n">
-        <v>-16.51</v>
+        <v>-18.88</v>
       </c>
       <c r="N29" t="b">
         <v>1</v>
@@ -18220,7 +18222,7 @@
         <v>19.4</v>
       </c>
       <c r="H30" t="n">
-        <v>-12.14</v>
+        <v>-12.47</v>
       </c>
       <c r="I30" t="n">
         <v>-10.01</v>
@@ -18233,7 +18235,7 @@
         <v>-15.23</v>
       </c>
       <c r="M30" t="n">
-        <v>-12.78</v>
+        <v>-13.11</v>
       </c>
       <c r="N30" t="b">
         <v>1</v>
@@ -18271,7 +18273,7 @@
         <v>-2.6</v>
       </c>
       <c r="H31" t="n">
-        <v>-7.71</v>
+        <v>-9.19</v>
       </c>
       <c r="I31" t="n">
         <v>-4.27</v>
@@ -18284,7 +18286,7 @@
         <v>-4.86</v>
       </c>
       <c r="M31" t="n">
-        <v>-8.57</v>
+        <v>-10.05</v>
       </c>
       <c r="N31" t="b">
         <v>1</v>
@@ -18322,7 +18324,7 @@
         <v>23.8</v>
       </c>
       <c r="H32" t="n">
-        <v>7.04</v>
+        <v>4.35</v>
       </c>
       <c r="I32" t="n">
         <v>1.36</v>
@@ -18335,7 +18337,7 @@
         <v>-9.94</v>
       </c>
       <c r="M32" t="n">
-        <v>7.15</v>
+        <v>4.46</v>
       </c>
       <c r="N32" t="b">
         <v>1</v>
@@ -18373,7 +18375,7 @@
         <v>38.9</v>
       </c>
       <c r="H33" t="n">
-        <v>-8.77</v>
+        <v>-10.09</v>
       </c>
       <c r="I33" t="n">
         <v>-9.220000000000001</v>
@@ -18386,7 +18388,7 @@
         <v>-9.83</v>
       </c>
       <c r="M33" t="n">
-        <v>-8.65</v>
+        <v>-9.970000000000001</v>
       </c>
       <c r="N33" t="b">
         <v>1</v>
@@ -18424,7 +18426,7 @@
         <v>43.2</v>
       </c>
       <c r="H34" t="n">
-        <v>-20.23</v>
+        <v>-20.83</v>
       </c>
       <c r="I34" t="n">
         <v>-3.15</v>
@@ -18437,7 +18439,7 @@
         <v>-17.51</v>
       </c>
       <c r="M34" t="n">
-        <v>-20.29</v>
+        <v>-20.88</v>
       </c>
       <c r="N34" t="b">
         <v>1</v>
@@ -18475,7 +18477,7 @@
         <v>-8.199999999999999</v>
       </c>
       <c r="H35" t="n">
-        <v>-4.93</v>
+        <v>-5.01</v>
       </c>
       <c r="I35" t="n">
         <v>5.34</v>
@@ -18488,7 +18490,7 @@
         <v>-5.27</v>
       </c>
       <c r="M35" t="n">
-        <v>-4.99</v>
+        <v>-5.06</v>
       </c>
       <c r="N35" t="b">
         <v>1</v>
@@ -18526,7 +18528,7 @@
         <v>-23.9</v>
       </c>
       <c r="H36" t="n">
-        <v>-6.71</v>
+        <v>-7.28</v>
       </c>
       <c r="I36" t="n">
         <v>3.28</v>
@@ -18539,7 +18541,7 @@
         <v>-4.46</v>
       </c>
       <c r="M36" t="n">
-        <v>-7.06</v>
+        <v>-7.63</v>
       </c>
       <c r="N36" t="b">
         <v>1</v>
@@ -18581,7 +18583,7 @@
         <v>-6.1</v>
       </c>
       <c r="H37" t="n">
-        <v>9</v>
+        <v>7.41</v>
       </c>
       <c r="I37" t="n">
         <v>4.9</v>
@@ -18594,7 +18596,7 @@
         <v>-9</v>
       </c>
       <c r="M37" t="n">
-        <v>8.65</v>
+        <v>7.06</v>
       </c>
       <c r="N37" t="b">
         <v>1</v>
@@ -18632,7 +18634,7 @@
         <v>26.7</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.84</v>
+        <v>-0.87</v>
       </c>
       <c r="I38" t="n">
         <v>-0.05</v>
@@ -18645,7 +18647,7 @@
         <v>-0.87</v>
       </c>
       <c r="M38" t="n">
-        <v>-1.19</v>
+        <v>-1.22</v>
       </c>
       <c r="N38" t="b">
         <v>1</v>
@@ -18683,7 +18685,7 @@
         <v>-3.5</v>
       </c>
       <c r="H39" t="n">
-        <v>0.5600000000000001</v>
+        <v>-0.34</v>
       </c>
       <c r="I39" t="n">
         <v>-4.95</v>
@@ -18696,7 +18698,7 @@
         <v>-8.43</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>-0.9</v>
       </c>
       <c r="N39" t="b">
         <v>1</v>
@@ -18734,7 +18736,7 @@
         <v>-17.9</v>
       </c>
       <c r="H40" t="n">
-        <v>9.41</v>
+        <v>6.27</v>
       </c>
       <c r="I40" t="n">
         <v>-0.5</v>
@@ -18747,7 +18749,7 @@
         <v>-3.43</v>
       </c>
       <c r="M40" t="n">
-        <v>8.85</v>
+        <v>5.71</v>
       </c>
       <c r="N40" t="b">
         <v>1</v>
@@ -18785,7 +18787,7 @@
         <v>53.5</v>
       </c>
       <c r="H41" t="n">
-        <v>1.84</v>
+        <v>2.66</v>
       </c>
       <c r="I41" t="n">
         <v>1.23</v>
@@ -18798,7 +18800,7 @@
         <v>-7.57</v>
       </c>
       <c r="M41" t="n">
-        <v>1.18</v>
+        <v>2</v>
       </c>
       <c r="N41" t="b">
         <v>1</v>
@@ -18836,7 +18838,7 @@
         <v>-1</v>
       </c>
       <c r="H42" t="n">
-        <v>-9.75</v>
+        <v>-14.7</v>
       </c>
       <c r="I42" t="n">
         <v>-6.26</v>
@@ -18849,7 +18851,7 @@
         <v>-15</v>
       </c>
       <c r="M42" t="n">
-        <v>-10.41</v>
+        <v>-15.36</v>
       </c>
       <c r="N42" t="b">
         <v>1</v>
@@ -18887,7 +18889,7 @@
         <v>29.7</v>
       </c>
       <c r="H43" t="n">
-        <v>15.43</v>
+        <v>11.21</v>
       </c>
       <c r="I43" t="n">
         <v>11.27</v>
@@ -18900,7 +18902,7 @@
         <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>14.77</v>
+        <v>10.54</v>
       </c>
       <c r="N43" t="b">
         <v>1</v>
@@ -18938,7 +18940,7 @@
         <v>15.2</v>
       </c>
       <c r="H44" t="n">
-        <v>-29.88</v>
+        <v>-33.13</v>
       </c>
       <c r="I44" t="n">
         <v>-8.77</v>
@@ -18951,7 +18953,7 @@
         <v>-24.79</v>
       </c>
       <c r="M44" t="n">
-        <v>-29.81</v>
+        <v>-33.06</v>
       </c>
       <c r="N44" t="b">
         <v>1</v>
@@ -18989,7 +18991,7 @@
         <v>22.2</v>
       </c>
       <c r="H45" t="n">
-        <v>6.25</v>
+        <v>7.62</v>
       </c>
       <c r="I45" t="n">
         <v>1.01</v>
@@ -19002,7 +19004,7 @@
         <v>-3.94</v>
       </c>
       <c r="M45" t="n">
-        <v>6.32</v>
+        <v>7.69</v>
       </c>
       <c r="N45" t="b">
         <v>1</v>
@@ -19044,7 +19046,7 @@
         <v>-0</v>
       </c>
       <c r="H46" t="n">
-        <v>24.25</v>
+        <v>28.93</v>
       </c>
       <c r="I46" t="n">
         <v>13.5</v>
@@ -19057,7 +19059,7 @@
         <v>-2.53</v>
       </c>
       <c r="M46" t="n">
-        <v>20.8</v>
+        <v>25.48</v>
       </c>
       <c r="N46" t="b">
         <v>1</v>
@@ -19095,7 +19097,7 @@
         <v>10.5</v>
       </c>
       <c r="H47" t="n">
-        <v>2.16</v>
+        <v>0.67</v>
       </c>
       <c r="I47" t="n">
         <v>1.99</v>
@@ -19108,7 +19110,7 @@
         <v>-6.27</v>
       </c>
       <c r="M47" t="n">
-        <v>-1.29</v>
+        <v>-2.78</v>
       </c>
       <c r="N47" t="b">
         <v>1</v>
@@ -19146,7 +19148,7 @@
         <v>-37</v>
       </c>
       <c r="H48" t="n">
-        <v>26.54</v>
+        <v>26.83</v>
       </c>
       <c r="I48" t="n">
         <v>18.38</v>
@@ -19159,7 +19161,7 @@
         <v>-5.11</v>
       </c>
       <c r="M48" t="n">
-        <v>22.43</v>
+        <v>22.71</v>
       </c>
       <c r="N48" t="b">
         <v>1</v>
@@ -19197,7 +19199,7 @@
         <v>-26.8</v>
       </c>
       <c r="H49" t="n">
-        <v>12.75</v>
+        <v>12.92</v>
       </c>
       <c r="I49" t="n">
         <v>4.56</v>
@@ -19210,7 +19212,7 @@
         <v>-4.09</v>
       </c>
       <c r="M49" t="n">
-        <v>8.640000000000001</v>
+        <v>8.81</v>
       </c>
       <c r="N49" t="b">
         <v>1</v>
@@ -19248,7 +19250,7 @@
         <v>-36.5</v>
       </c>
       <c r="H50" t="n">
-        <v>-29.41</v>
+        <v>-32.08</v>
       </c>
       <c r="I50" t="n">
         <v>-27.75</v>
@@ -19261,7 +19263,7 @@
         <v>-31.28</v>
       </c>
       <c r="M50" t="n">
-        <v>-34.18</v>
+        <v>-36.1</v>
       </c>
       <c r="N50" t="b">
         <v>1</v>
@@ -19299,7 +19301,7 @@
         <v>-38.7</v>
       </c>
       <c r="H51" t="n">
-        <v>10.53</v>
+        <v>8.57</v>
       </c>
       <c r="I51" t="n">
         <v>17.17</v>
@@ -19312,7 +19314,7 @@
         <v>-0.54</v>
       </c>
       <c r="M51" t="n">
-        <v>5.75</v>
+        <v>3.79</v>
       </c>
       <c r="N51" t="b">
         <v>1</v>
@@ -19350,7 +19352,7 @@
         <v>-34.6</v>
       </c>
       <c r="H52" t="n">
-        <v>18.39</v>
+        <v>20.01</v>
       </c>
       <c r="I52" t="n">
         <v>6.67</v>
@@ -19363,7 +19365,7 @@
         <v>-3.06</v>
       </c>
       <c r="M52" t="n">
-        <v>13.61</v>
+        <v>15.23</v>
       </c>
       <c r="N52" t="b">
         <v>1</v>
@@ -19401,7 +19403,7 @@
         <v>-11.8</v>
       </c>
       <c r="H53" t="n">
-        <v>0.24</v>
+        <v>-3.44</v>
       </c>
       <c r="I53" t="n">
         <v>9.76</v>
@@ -19414,7 +19416,7 @@
         <v>-1.63</v>
       </c>
       <c r="M53" t="n">
-        <v>-4.65</v>
+        <v>-8.33</v>
       </c>
       <c r="N53" t="b">
         <v>1</v>
@@ -19452,7 +19454,7 @@
         <v>0.1</v>
       </c>
       <c r="H54" t="n">
-        <v>-11.42</v>
+        <v>-16.65</v>
       </c>
       <c r="I54" t="n">
         <v>-2.83</v>
@@ -19465,7 +19467,7 @@
         <v>-5.45</v>
       </c>
       <c r="M54" t="n">
-        <v>-16.31</v>
+        <v>-21.54</v>
       </c>
       <c r="N54" t="b">
         <v>1</v>
@@ -19503,7 +19505,7 @@
         <v>24.1</v>
       </c>
       <c r="H55" t="n">
-        <v>-14.5</v>
+        <v>-14.1</v>
       </c>
       <c r="I55" t="n">
         <v>-8.31</v>
@@ -19516,7 +19518,7 @@
         <v>-18.31</v>
       </c>
       <c r="M55" t="n">
-        <v>-18.58</v>
+        <v>-18.18</v>
       </c>
       <c r="N55" t="b">
         <v>1</v>
@@ -19554,7 +19556,7 @@
         <v>-15.9</v>
       </c>
       <c r="H56" t="n">
-        <v>-0.34</v>
+        <v>2.57</v>
       </c>
       <c r="I56" t="n">
         <v>10.45</v>
@@ -19567,7 +19569,7 @@
         <v>-0.31</v>
       </c>
       <c r="M56" t="n">
-        <v>-4.42</v>
+        <v>-1.51</v>
       </c>
       <c r="N56" t="b">
         <v>1</v>
@@ -19605,7 +19607,7 @@
         <v>-21.8</v>
       </c>
       <c r="H57" t="n">
-        <v>-20.65</v>
+        <v>-23.9</v>
       </c>
       <c r="I57" t="n">
         <v>-18.97</v>
@@ -19618,7 +19620,7 @@
         <v>-26.82</v>
       </c>
       <c r="M57" t="n">
-        <v>-25.51</v>
+        <v>-28.76</v>
       </c>
       <c r="N57" t="b">
         <v>1</v>
@@ -19656,7 +19658,7 @@
         <v>57</v>
       </c>
       <c r="H58" t="n">
-        <v>14.86</v>
+        <v>14.27</v>
       </c>
       <c r="I58" t="n">
         <v>-11.21</v>
@@ -19669,7 +19671,7 @@
         <v>-13.87</v>
       </c>
       <c r="M58" t="n">
-        <v>11.02</v>
+        <v>10.43</v>
       </c>
       <c r="N58" t="b">
         <v>1</v>
@@ -19707,7 +19709,7 @@
         <v>-21.8</v>
       </c>
       <c r="H59" t="n">
-        <v>9.82</v>
+        <v>10.31</v>
       </c>
       <c r="I59" t="n">
         <v>1.71</v>
@@ -19720,7 +19722,7 @@
         <v>-6.18</v>
       </c>
       <c r="M59" t="n">
-        <v>5.98</v>
+        <v>6.47</v>
       </c>
       <c r="N59" t="b">
         <v>1</v>
@@ -19758,7 +19760,7 @@
         <v>1</v>
       </c>
       <c r="H60" t="n">
-        <v>-32.46</v>
+        <v>-33.75</v>
       </c>
       <c r="I60" t="n">
         <v>-11.52</v>
@@ -19771,7 +19773,7 @@
         <v>-16.26</v>
       </c>
       <c r="M60" t="n">
-        <v>-36.34</v>
+        <v>-37.64</v>
       </c>
       <c r="N60" t="b">
         <v>1</v>
@@ -19809,7 +19811,7 @@
         <v>45.4</v>
       </c>
       <c r="H61" t="n">
-        <v>16.72</v>
+        <v>16.5</v>
       </c>
       <c r="I61" t="n">
         <v>-1.72</v>
@@ -19822,7 +19824,7 @@
         <v>-23.15</v>
       </c>
       <c r="M61" t="n">
-        <v>12.83</v>
+        <v>13.36</v>
       </c>
       <c r="N61" t="b">
         <v>1</v>
@@ -19860,7 +19862,7 @@
         <v>76.5</v>
       </c>
       <c r="H62" t="n">
-        <v>24.83</v>
+        <v>20.17</v>
       </c>
       <c r="I62" t="n">
         <v>-5.56</v>
@@ -19873,7 +19875,7 @@
         <v>-33.97</v>
       </c>
       <c r="M62" t="n">
-        <v>20.94</v>
+        <v>17.03</v>
       </c>
       <c r="N62" t="b">
         <v>1</v>
@@ -19911,7 +19913,7 @@
         <v>32.1</v>
       </c>
       <c r="H63" t="n">
-        <v>22.31</v>
+        <v>17.38</v>
       </c>
       <c r="I63" t="n">
         <v>16.93</v>
@@ -19924,7 +19926,7 @@
         <v>-24.48</v>
       </c>
       <c r="M63" t="n">
-        <v>18.42</v>
+        <v>14.25</v>
       </c>
       <c r="N63" t="b">
         <v>1</v>
@@ -19962,7 +19964,7 @@
         <v>51.8</v>
       </c>
       <c r="H64" t="n">
-        <v>11.3</v>
+        <v>10.38</v>
       </c>
       <c r="I64" t="n">
         <v>10.75</v>
@@ -19975,7 +19977,7 @@
         <v>-25.09</v>
       </c>
       <c r="M64" t="n">
-        <v>7.41</v>
+        <v>7.24</v>
       </c>
       <c r="N64" t="b">
         <v>1</v>
@@ -20013,7 +20015,7 @@
         <v>32.3</v>
       </c>
       <c r="H65" t="n">
-        <v>-24.42</v>
+        <v>-25.09</v>
       </c>
       <c r="I65" t="n">
         <v>-20.76</v>
@@ -20026,7 +20028,7 @@
         <v>-27.91</v>
       </c>
       <c r="M65" t="n">
-        <v>-28.31</v>
+        <v>-28.98</v>
       </c>
       <c r="N65" t="b">
         <v>1</v>
@@ -20064,7 +20066,7 @@
         <v>3.7</v>
       </c>
       <c r="H66" t="n">
-        <v>-6.43</v>
+        <v>-12.7</v>
       </c>
       <c r="I66" t="n">
         <v>-1.11</v>
@@ -20077,7 +20079,7 @@
         <v>-25.46</v>
       </c>
       <c r="M66" t="n">
-        <v>-10.31</v>
+        <v>-15.84</v>
       </c>
       <c r="N66" t="b">
         <v>1</v>
@@ -20115,7 +20117,7 @@
         <v>42.4</v>
       </c>
       <c r="H67" t="n">
-        <v>15.73</v>
+        <v>11.93</v>
       </c>
       <c r="I67" t="n">
         <v>2.16</v>
@@ -20128,7 +20130,7 @@
         <v>-15.76</v>
       </c>
       <c r="M67" t="n">
-        <v>11.84</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="N67" t="b">
         <v>1</v>
@@ -20166,7 +20168,7 @@
         <v>28.2</v>
       </c>
       <c r="H68" t="n">
-        <v>-11.26</v>
+        <v>-11.19</v>
       </c>
       <c r="I68" t="n">
         <v>-1.71</v>
@@ -20179,7 +20181,7 @@
         <v>-23.43</v>
       </c>
       <c r="M68" t="n">
-        <v>-15.15</v>
+        <v>-14.33</v>
       </c>
       <c r="N68" t="b">
         <v>1</v>
@@ -20217,7 +20219,7 @@
         <v>28.6</v>
       </c>
       <c r="H69" t="n">
-        <v>21.82</v>
+        <v>28.55</v>
       </c>
       <c r="I69" t="n">
         <v>2.81</v>
@@ -20230,7 +20232,7 @@
         <v>-18.87</v>
       </c>
       <c r="M69" t="n">
-        <v>17.93</v>
+        <v>24.66</v>
       </c>
       <c r="N69" t="b">
         <v>1</v>
@@ -20268,7 +20270,7 @@
         <v>33.1</v>
       </c>
       <c r="H70" t="n">
-        <v>16.53</v>
+        <v>15.47</v>
       </c>
       <c r="I70" t="n">
         <v>4.68</v>
@@ -20281,7 +20283,7 @@
         <v>-26.7</v>
       </c>
       <c r="M70" t="n">
-        <v>12.65</v>
+        <v>12.33</v>
       </c>
       <c r="N70" t="b">
         <v>1</v>
@@ -20319,7 +20321,7 @@
         <v>21.8</v>
       </c>
       <c r="H71" t="n">
-        <v>-10.09</v>
+        <v>-11.26</v>
       </c>
       <c r="I71" t="n">
         <v>-6.34</v>
@@ -20332,7 +20334,7 @@
         <v>-30.04</v>
       </c>
       <c r="M71" t="n">
-        <v>-13.98</v>
+        <v>-15.14</v>
       </c>
       <c r="N71" t="b">
         <v>1</v>
@@ -20370,7 +20372,7 @@
         <v>40.3</v>
       </c>
       <c r="H72" t="n">
-        <v>-8.56</v>
+        <v>-10.27</v>
       </c>
       <c r="I72" t="n">
         <v>1.24</v>
@@ -20383,7 +20385,7 @@
         <v>-20.5</v>
       </c>
       <c r="M72" t="n">
-        <v>-12.44</v>
+        <v>-14.16</v>
       </c>
       <c r="N72" t="b">
         <v>1</v>
@@ -20421,7 +20423,7 @@
         <v>24.1</v>
       </c>
       <c r="H73" t="n">
-        <v>6.95</v>
+        <v>2.76</v>
       </c>
       <c r="I73" t="n">
         <v>-1.6</v>
@@ -20434,7 +20436,7 @@
         <v>-22.54</v>
       </c>
       <c r="M73" t="n">
-        <v>3.06</v>
+        <v>-1.13</v>
       </c>
       <c r="N73" t="b">
         <v>1</v>
@@ -20472,7 +20474,7 @@
         <v>24.5</v>
       </c>
       <c r="H74" t="n">
-        <v>-27.9</v>
+        <v>-28.71</v>
       </c>
       <c r="I74" t="n">
         <v>-12.99</v>
@@ -20485,7 +20487,7 @@
         <v>-22.54</v>
       </c>
       <c r="M74" t="n">
-        <v>-31.79</v>
+        <v>-32.6</v>
       </c>
       <c r="N74" t="b">
         <v>1</v>
@@ -20523,7 +20525,7 @@
         <v>19.3</v>
       </c>
       <c r="H75" t="n">
-        <v>10.48</v>
+        <v>7.84</v>
       </c>
       <c r="I75" t="n">
         <v>11.79</v>
@@ -20536,7 +20538,7 @@
         <v>-16.62</v>
       </c>
       <c r="M75" t="n">
-        <v>6.6</v>
+        <v>3.95</v>
       </c>
       <c r="N75" t="b">
         <v>1</v>
@@ -20574,7 +20576,7 @@
         <v>-8.699999999999999</v>
       </c>
       <c r="H76" t="n">
-        <v>-6.44</v>
+        <v>-10</v>
       </c>
       <c r="I76" t="n">
         <v>17.25</v>
@@ -20587,7 +20589,7 @@
         <v>-4.65</v>
       </c>
       <c r="M76" t="n">
-        <v>-10.33</v>
+        <v>-13.89</v>
       </c>
       <c r="N76" t="b">
         <v>1</v>
@@ -20625,7 +20627,7 @@
         <v>15.2</v>
       </c>
       <c r="H77" t="n">
-        <v>1.02</v>
+        <v>-2.17</v>
       </c>
       <c r="I77" t="n">
         <v>5.36</v>
@@ -20638,7 +20640,7 @@
         <v>-28.18</v>
       </c>
       <c r="M77" t="n">
-        <v>-2.87</v>
+        <v>-5.31</v>
       </c>
       <c r="N77" t="b">
         <v>1</v>
@@ -20676,7 +20678,7 @@
         <v>37.2</v>
       </c>
       <c r="H78" t="n">
-        <v>-24.96</v>
+        <v>-24.28</v>
       </c>
       <c r="I78" t="n">
         <v>-7.64</v>
@@ -20689,7 +20691,7 @@
         <v>-26.24</v>
       </c>
       <c r="M78" t="n">
-        <v>-28.84</v>
+        <v>-28.17</v>
       </c>
       <c r="N78" t="b">
         <v>1</v>
@@ -20727,7 +20729,7 @@
         <v>29.8</v>
       </c>
       <c r="H79" t="n">
-        <v>31.27</v>
+        <v>27.51</v>
       </c>
       <c r="I79" t="n">
         <v>-2.74</v>
@@ -20740,7 +20742,7 @@
         <v>-22.36</v>
       </c>
       <c r="M79" t="n">
-        <v>27.39</v>
+        <v>23.62</v>
       </c>
       <c r="N79" t="b">
         <v>1</v>
@@ -20778,7 +20780,7 @@
         <v>19.3</v>
       </c>
       <c r="H80" t="n">
-        <v>-18.45</v>
+        <v>-20.34</v>
       </c>
       <c r="I80" t="n">
         <v>-16.69</v>
@@ -20791,7 +20793,7 @@
         <v>-36.39</v>
       </c>
       <c r="M80" t="n">
-        <v>-22.33</v>
+        <v>-24.23</v>
       </c>
       <c r="N80" t="b">
         <v>1</v>
@@ -20829,7 +20831,7 @@
         <v>11.8</v>
       </c>
       <c r="H81" t="n">
-        <v>1.11</v>
+        <v>-0.28</v>
       </c>
       <c r="I81" t="n">
         <v>-1.19</v>
@@ -20842,7 +20844,7 @@
         <v>-17.57</v>
       </c>
       <c r="M81" t="n">
-        <v>-2.77</v>
+        <v>-4.17</v>
       </c>
       <c r="N81" t="b">
         <v>1</v>
@@ -20880,7 +20882,7 @@
         <v>27.5</v>
       </c>
       <c r="H82" t="n">
-        <v>16.42</v>
+        <v>18.32</v>
       </c>
       <c r="I82" t="n">
         <v>8.42</v>
@@ -20893,7 +20895,7 @@
         <v>-2.51</v>
       </c>
       <c r="M82" t="n">
-        <v>12.53</v>
+        <v>14.44</v>
       </c>
       <c r="N82" t="b">
         <v>1</v>
@@ -20931,7 +20933,7 @@
         <v>-22.4</v>
       </c>
       <c r="H83" t="n">
-        <v>-9.57</v>
+        <v>-9.869999999999999</v>
       </c>
       <c r="I83" t="n">
         <v>9.42</v>
@@ -20944,7 +20946,7 @@
         <v>-2.79</v>
       </c>
       <c r="M83" t="n">
-        <v>-13.46</v>
+        <v>-13.75</v>
       </c>
       <c r="N83" t="b">
         <v>1</v>
@@ -20982,7 +20984,7 @@
         <v>-14.7</v>
       </c>
       <c r="H84" t="n">
-        <v>-10.19</v>
+        <v>-9.34</v>
       </c>
       <c r="I84" t="n">
         <v>10.3</v>
@@ -20995,7 +20997,7 @@
         <v>-2.6</v>
       </c>
       <c r="M84" t="n">
-        <v>-14.07</v>
+        <v>-13.23</v>
       </c>
       <c r="N84" t="b">
         <v>1</v>
@@ -21037,7 +21039,7 @@
         <v>-9.300000000000001</v>
       </c>
       <c r="H85" t="n">
-        <v>-22.42</v>
+        <v>-23.63</v>
       </c>
       <c r="I85" t="n">
         <v>10.42</v>
@@ -21050,7 +21052,7 @@
         <v>-21.72</v>
       </c>
       <c r="M85" t="n">
-        <v>-26.31</v>
+        <v>-27.52</v>
       </c>
       <c r="N85" t="b">
         <v>1</v>
@@ -21088,7 +21090,7 @@
         <v>-25.2</v>
       </c>
       <c r="H86" t="n">
-        <v>15.68</v>
+        <v>15.86</v>
       </c>
       <c r="I86" t="n">
         <v>22.53</v>
@@ -21101,7 +21103,7 @@
         <v>-19.27</v>
       </c>
       <c r="M86" t="n">
-        <v>11.79</v>
+        <v>12.72</v>
       </c>
       <c r="N86" t="b">
         <v>1</v>
@@ -21139,7 +21141,7 @@
         <v>5.1</v>
       </c>
       <c r="H87" t="n">
-        <v>2.08</v>
+        <v>0.9</v>
       </c>
       <c r="I87" t="n">
         <v>8.77</v>
@@ -21152,7 +21154,7 @@
         <v>-3.54</v>
       </c>
       <c r="M87" t="n">
-        <v>-1.81</v>
+        <v>-2.99</v>
       </c>
       <c r="N87" t="b">
         <v>1</v>
@@ -21190,7 +21192,7 @@
         <v>34.2</v>
       </c>
       <c r="H88" t="n">
-        <v>5.37</v>
+        <v>7.74</v>
       </c>
       <c r="I88" t="n">
         <v>8.15</v>
@@ -21203,7 +21205,7 @@
         <v>-7.63</v>
       </c>
       <c r="M88" t="n">
-        <v>1.49</v>
+        <v>3.86</v>
       </c>
       <c r="N88" t="b">
         <v>1</v>
@@ -21241,7 +21243,7 @@
         <v>42</v>
       </c>
       <c r="H89" t="n">
-        <v>-29.39</v>
+        <v>-30.27</v>
       </c>
       <c r="I89" t="n">
         <v>0.6</v>
@@ -21254,7 +21256,7 @@
         <v>-16.67</v>
       </c>
       <c r="M89" t="n">
-        <v>-33.28</v>
+        <v>-34.16</v>
       </c>
       <c r="N89" t="b">
         <v>1</v>
@@ -21292,7 +21294,7 @@
         <v>-25.3</v>
       </c>
       <c r="H90" t="n">
-        <v>30.94</v>
+        <v>30.77</v>
       </c>
       <c r="I90" t="n">
         <v>36.1</v>
@@ -21305,7 +21307,7 @@
         <v>-5.66</v>
       </c>
       <c r="M90" t="n">
-        <v>27.06</v>
+        <v>26.89</v>
       </c>
       <c r="N90" t="b">
         <v>1</v>
@@ -21343,7 +21345,7 @@
         <v>-7.7</v>
       </c>
       <c r="H91" t="n">
-        <v>-2.1</v>
+        <v>-3.75</v>
       </c>
       <c r="I91" t="n">
         <v>-6.47</v>
@@ -21356,7 +21358,7 @@
         <v>-23.05</v>
       </c>
       <c r="M91" t="n">
-        <v>-5.99</v>
+        <v>-7.64</v>
       </c>
       <c r="N91" t="b">
         <v>1</v>
@@ -21394,7 +21396,7 @@
         <v>13.7</v>
       </c>
       <c r="H92" t="n">
-        <v>7.4</v>
+        <v>7.27</v>
       </c>
       <c r="I92" t="n">
         <v>2.74</v>
@@ -21407,7 +21409,7 @@
         <v>-24.02</v>
       </c>
       <c r="M92" t="n">
-        <v>3.51</v>
+        <v>3.38</v>
       </c>
       <c r="N92" t="b">
         <v>1</v>
@@ -21445,7 +21447,7 @@
         <v>21.8</v>
       </c>
       <c r="H93" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.49</v>
       </c>
       <c r="I93" t="n">
         <v>18.32</v>
@@ -21458,7 +21460,7 @@
         <v>-23.27</v>
       </c>
       <c r="M93" t="n">
-        <v>-3.96</v>
+        <v>-4.38</v>
       </c>
       <c r="N93" t="b">
         <v>1</v>
@@ -21496,7 +21498,7 @@
         <v>29.4</v>
       </c>
       <c r="H94" t="n">
-        <v>-3.9</v>
+        <v>-4.41</v>
       </c>
       <c r="I94" t="n">
         <v>-2.62</v>
@@ -21509,7 +21511,7 @@
         <v>-27.18</v>
       </c>
       <c r="M94" t="n">
-        <v>-7.79</v>
+        <v>-8.300000000000001</v>
       </c>
       <c r="N94" t="b">
         <v>1</v>
@@ -21547,7 +21549,7 @@
         <v>-3.7</v>
       </c>
       <c r="H95" t="n">
-        <v>-23.58</v>
+        <v>-24.58</v>
       </c>
       <c r="I95" t="n">
         <v>-8.07</v>
@@ -21560,7 +21562,7 @@
         <v>-22.12</v>
       </c>
       <c r="M95" t="n">
-        <v>-27.47</v>
+        <v>-28.46</v>
       </c>
       <c r="N95" t="b">
         <v>1</v>
@@ -21598,7 +21600,7 @@
         <v>21.3</v>
       </c>
       <c r="H96" t="n">
-        <v>1.87</v>
+        <v>1.54</v>
       </c>
       <c r="I96" t="n">
         <v>0.23</v>
@@ -21611,7 +21613,7 @@
         <v>-0.85</v>
       </c>
       <c r="M96" t="n">
-        <v>-2.01</v>
+        <v>-2.35</v>
       </c>
       <c r="N96" t="b">
         <v>1</v>
@@ -21649,7 +21651,7 @@
         <v>-21.4</v>
       </c>
       <c r="H97" t="n">
-        <v>29.3</v>
+        <v>24.14</v>
       </c>
       <c r="I97" t="n">
         <v>4.55</v>
@@ -21662,7 +21664,7 @@
         <v>-6.39</v>
       </c>
       <c r="M97" t="n">
-        <v>25.42</v>
+        <v>21</v>
       </c>
       <c r="N97" t="b">
         <v>1</v>
@@ -21700,7 +21702,7 @@
         <v>16.3</v>
       </c>
       <c r="H98" t="n">
-        <v>2.97</v>
+        <v>5.89</v>
       </c>
       <c r="I98" t="n">
         <v>-1</v>
@@ -21713,7 +21715,7 @@
         <v>-22.5</v>
       </c>
       <c r="M98" t="n">
-        <v>-0.92</v>
+        <v>2</v>
       </c>
       <c r="N98" t="b">
         <v>1</v>
@@ -21751,7 +21753,7 @@
         <v>11.9</v>
       </c>
       <c r="H99" t="n">
-        <v>-2.06</v>
+        <v>-2.14</v>
       </c>
       <c r="I99" t="n">
         <v>7.74</v>
@@ -21764,7 +21766,7 @@
         <v>-9.43</v>
       </c>
       <c r="M99" t="n">
-        <v>-5.95</v>
+        <v>-6.02</v>
       </c>
       <c r="N99" t="b">
         <v>1</v>
@@ -21802,7 +21804,7 @@
         <v>0.2</v>
       </c>
       <c r="H100" t="n">
-        <v>10.47</v>
+        <v>10.27</v>
       </c>
       <c r="I100" t="n">
         <v>4.35</v>
@@ -21815,7 +21817,7 @@
         <v>-2.79</v>
       </c>
       <c r="M100" t="n">
-        <v>6.58</v>
+        <v>6.38</v>
       </c>
       <c r="N100" t="b">
         <v>1</v>
@@ -21853,7 +21855,7 @@
         <v>8.4</v>
       </c>
       <c r="H101" t="n">
-        <v>-32.14</v>
+        <v>-32.4</v>
       </c>
       <c r="I101" t="n">
         <v>-0.13</v>
@@ -21866,7 +21868,7 @@
         <v>-10.87</v>
       </c>
       <c r="M101" t="n">
-        <v>-36.03</v>
+        <v>-36.29</v>
       </c>
       <c r="N101" t="b">
         <v>1</v>
@@ -21904,7 +21906,7 @@
         <v>-7.3</v>
       </c>
       <c r="H102" t="n">
-        <v>-19.63</v>
+        <v>-20.32</v>
       </c>
       <c r="I102" t="n">
         <v>-4.12</v>
@@ -21917,7 +21919,7 @@
         <v>-15.02</v>
       </c>
       <c r="M102" t="n">
-        <v>-23.51</v>
+        <v>-24.2</v>
       </c>
       <c r="N102" t="b">
         <v>1</v>
@@ -21955,7 +21957,7 @@
         <v>-26.1</v>
       </c>
       <c r="H103" t="n">
-        <v>-15.16</v>
+        <v>-17.55</v>
       </c>
       <c r="I103" t="n">
         <v>5.05</v>
@@ -21968,7 +21970,7 @@
         <v>-9.27</v>
       </c>
       <c r="M103" t="n">
-        <v>-19.05</v>
+        <v>-21.43</v>
       </c>
       <c r="N103" t="b">
         <v>1</v>
@@ -22006,7 +22008,7 @@
         <v>26.1</v>
       </c>
       <c r="H104" t="n">
-        <v>-8.91</v>
+        <v>-8.859999999999999</v>
       </c>
       <c r="I104" t="n">
         <v>-0.51</v>
@@ -22019,7 +22021,7 @@
         <v>-16.45</v>
       </c>
       <c r="M104" t="n">
-        <v>-12.79</v>
+        <v>-12.75</v>
       </c>
       <c r="N104" t="b">
         <v>1</v>
@@ -22057,7 +22059,7 @@
         <v>17.9</v>
       </c>
       <c r="H105" t="n">
-        <v>1.64</v>
+        <v>2.5</v>
       </c>
       <c r="I105" t="n">
         <v>12.97</v>
@@ -22070,7 +22072,7 @@
         <v>-8.130000000000001</v>
       </c>
       <c r="M105" t="n">
-        <v>-2.25</v>
+        <v>-1.39</v>
       </c>
       <c r="N105" t="b">
         <v>1</v>
@@ -22108,7 +22110,7 @@
         <v>0.7</v>
       </c>
       <c r="H106" t="n">
-        <v>-13.04</v>
+        <v>-14.69</v>
       </c>
       <c r="I106" t="n">
         <v>14.96</v>
@@ -22121,7 +22123,7 @@
         <v>-8.039999999999999</v>
       </c>
       <c r="M106" t="n">
-        <v>-16.93</v>
+        <v>-18.58</v>
       </c>
       <c r="N106" t="b">
         <v>1</v>
@@ -22159,7 +22161,7 @@
         <v>14.8</v>
       </c>
       <c r="H107" t="n">
-        <v>-2.46</v>
+        <v>-3.36</v>
       </c>
       <c r="I107" t="n">
         <v>0.35</v>
@@ -22172,7 +22174,7 @@
         <v>-3.68</v>
       </c>
       <c r="M107" t="n">
-        <v>-6.35</v>
+        <v>-7.24</v>
       </c>
       <c r="N107" t="b">
         <v>1</v>
@@ -22210,7 +22212,7 @@
         <v>25.5</v>
       </c>
       <c r="H108" t="n">
-        <v>0.45</v>
+        <v>2.52</v>
       </c>
       <c r="I108" t="n">
         <v>-9.369999999999999</v>
@@ -22223,7 +22225,7 @@
         <v>-22.11</v>
       </c>
       <c r="M108" t="n">
-        <v>-3.44</v>
+        <v>-1.37</v>
       </c>
       <c r="N108" t="b">
         <v>1</v>
@@ -22265,7 +22267,7 @@
         <v>-7.5</v>
       </c>
       <c r="H109" t="n">
-        <v>-2.82</v>
+        <v>-3.18</v>
       </c>
       <c r="I109" t="n">
         <v>4.46</v>
@@ -22278,7 +22280,7 @@
         <v>-8.52</v>
       </c>
       <c r="M109" t="n">
-        <v>-6.71</v>
+        <v>-7.07</v>
       </c>
       <c r="N109" t="b">
         <v>1</v>
@@ -22316,7 +22318,7 @@
         <v>-11</v>
       </c>
       <c r="H110" t="n">
-        <v>3.9</v>
+        <v>5.58</v>
       </c>
       <c r="I110" t="n">
         <v>10.7</v>
@@ -22329,7 +22331,7 @@
         <v>-9.43</v>
       </c>
       <c r="M110" t="n">
-        <v>0.01</v>
+        <v>1.69</v>
       </c>
       <c r="N110" t="b">
         <v>1</v>
@@ -22367,7 +22369,7 @@
         <v>-11.4</v>
       </c>
       <c r="H111" t="n">
-        <v>-10.33</v>
+        <v>-10.82</v>
       </c>
       <c r="I111" t="n">
         <v>4.36</v>
@@ -22380,7 +22382,7 @@
         <v>-11.36</v>
       </c>
       <c r="M111" t="n">
-        <v>-14.21</v>
+        <v>-14.71</v>
       </c>
       <c r="N111" t="b">
         <v>1</v>
@@ -22418,7 +22420,7 @@
         <v>27.1</v>
       </c>
       <c r="H112" t="n">
-        <v>-6.75</v>
+        <v>-7.41</v>
       </c>
       <c r="I112" t="n">
         <v>5.02</v>
@@ -22431,7 +22433,7 @@
         <v>-14.35</v>
       </c>
       <c r="M112" t="n">
-        <v>-10.64</v>
+        <v>-11.3</v>
       </c>
       <c r="N112" t="b">
         <v>1</v>
@@ -22469,7 +22471,7 @@
         <v>32.2</v>
       </c>
       <c r="H113" t="n">
-        <v>13.53</v>
+        <v>16.88</v>
       </c>
       <c r="I113" t="n">
         <v>6.49</v>
@@ -22482,7 +22484,7 @@
         <v>-3.92</v>
       </c>
       <c r="M113" t="n">
-        <v>9.640000000000001</v>
+        <v>12.99</v>
       </c>
       <c r="N113" t="b">
         <v>1</v>
@@ -22520,7 +22522,7 @@
         <v>3.2</v>
       </c>
       <c r="H114" t="n">
-        <v>-25.58</v>
+        <v>-22.68</v>
       </c>
       <c r="I114" t="n">
         <v>-10.41</v>
@@ -22533,7 +22535,7 @@
         <v>-23.7</v>
       </c>
       <c r="M114" t="n">
-        <v>-29.46</v>
+        <v>-26.56</v>
       </c>
       <c r="N114" t="b">
         <v>1</v>
@@ -22571,7 +22573,7 @@
         <v>7.3</v>
       </c>
       <c r="H115" t="n">
-        <v>-2.62</v>
+        <v>-1.42</v>
       </c>
       <c r="I115" t="n">
         <v>-0.57</v>
@@ -22584,7 +22586,7 @@
         <v>-5.89</v>
       </c>
       <c r="M115" t="n">
-        <v>-6.5</v>
+        <v>-5.3</v>
       </c>
       <c r="N115" t="b">
         <v>1</v>
@@ -22622,7 +22624,7 @@
         <v>-0.3</v>
       </c>
       <c r="H116" t="n">
-        <v>-5.65</v>
+        <v>-3.58</v>
       </c>
       <c r="I116" t="n">
         <v>17.76</v>
@@ -22635,7 +22637,7 @@
         <v>-14.18</v>
       </c>
       <c r="M116" t="n">
-        <v>-9.539999999999999</v>
+        <v>-7.47</v>
       </c>
       <c r="N116" t="b">
         <v>1</v>
@@ -22673,7 +22675,7 @@
         <v>-6.8</v>
       </c>
       <c r="H117" t="n">
-        <v>45.85</v>
+        <v>48.27</v>
       </c>
       <c r="I117" t="n">
         <v>8.279999999999999</v>
@@ -22686,7 +22688,7 @@
         <v>-6.78</v>
       </c>
       <c r="M117" t="n">
-        <v>41.96</v>
+        <v>44.38</v>
       </c>
       <c r="N117" t="b">
         <v>1</v>
@@ -22724,7 +22726,7 @@
         <v>34.6</v>
       </c>
       <c r="H118" t="n">
-        <v>-1.47</v>
+        <v>-2.73</v>
       </c>
       <c r="I118" t="n">
         <v>5.7</v>
@@ -22737,7 +22739,7 @@
         <v>-7.7</v>
       </c>
       <c r="M118" t="n">
-        <v>-5.36</v>
+        <v>-6.62</v>
       </c>
       <c r="N118" t="b">
         <v>1</v>
@@ -22775,7 +22777,7 @@
         <v>10.4</v>
       </c>
       <c r="H119" t="n">
-        <v>25.05</v>
+        <v>25.82</v>
       </c>
       <c r="I119" t="n">
         <v>11.05</v>
@@ -22788,7 +22790,7 @@
         <v>-5.54</v>
       </c>
       <c r="M119" t="n">
-        <v>21.16</v>
+        <v>21.93</v>
       </c>
       <c r="N119" t="b">
         <v>1</v>
@@ -22826,7 +22828,7 @@
         <v>-21.5</v>
       </c>
       <c r="H120" t="n">
-        <v>-9.73</v>
+        <v>-14.83</v>
       </c>
       <c r="I120" t="n">
         <v>10.65</v>
@@ -22839,7 +22841,7 @@
         <v>-6.89</v>
       </c>
       <c r="M120" t="n">
-        <v>-13.62</v>
+        <v>-17.97</v>
       </c>
       <c r="N120" t="b">
         <v>1</v>
@@ -22877,7 +22879,7 @@
         <v>3.5</v>
       </c>
       <c r="H121" t="n">
-        <v>45.26</v>
+        <v>43.51</v>
       </c>
       <c r="I121" t="n">
         <v>33.01</v>
@@ -22890,7 +22892,7 @@
         <v>-0.92</v>
       </c>
       <c r="M121" t="n">
-        <v>41.37</v>
+        <v>39.62</v>
       </c>
       <c r="N121" t="b">
         <v>1</v>
@@ -22928,7 +22930,7 @@
         <v>19.8</v>
       </c>
       <c r="H122" t="n">
-        <v>6.61</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="I122" t="n">
         <v>4.74</v>
@@ -22941,7 +22943,7 @@
         <v>-9.9</v>
       </c>
       <c r="M122" t="n">
-        <v>2.72</v>
+        <v>4.57</v>
       </c>
       <c r="N122" t="b">
         <v>1</v>
@@ -22979,7 +22981,7 @@
         <v>-30.5</v>
       </c>
       <c r="H123" t="n">
-        <v>2.42</v>
+        <v>1.71</v>
       </c>
       <c r="I123" t="n">
         <v>2.96</v>
@@ -22992,7 +22994,7 @@
         <v>-17.88</v>
       </c>
       <c r="M123" t="n">
-        <v>-1.46</v>
+        <v>-1.43</v>
       </c>
       <c r="N123" t="b">
         <v>1</v>
@@ -23030,7 +23032,7 @@
         <v>-6</v>
       </c>
       <c r="H124" t="n">
-        <v>-21.44</v>
+        <v>-22.02</v>
       </c>
       <c r="I124" t="n">
         <v>3.31</v>
@@ -23043,7 +23045,7 @@
         <v>-21.48</v>
       </c>
       <c r="M124" t="n">
-        <v>-25.33</v>
+        <v>-25.9</v>
       </c>
       <c r="N124" t="b">
         <v>1</v>
@@ -23081,7 +23083,7 @@
         <v>-34.6</v>
       </c>
       <c r="H125" t="n">
-        <v>1.52</v>
+        <v>1.94</v>
       </c>
       <c r="I125" t="n">
         <v>23.65</v>
@@ -23094,7 +23096,7 @@
         <v>-3.83</v>
       </c>
       <c r="M125" t="n">
-        <v>-2.37</v>
+        <v>-1.95</v>
       </c>
       <c r="N125" t="b">
         <v>1</v>
@@ -23132,7 +23134,7 @@
         <v>-16.2</v>
       </c>
       <c r="H126" t="n">
-        <v>11.6</v>
+        <v>12.69</v>
       </c>
       <c r="I126" t="n">
         <v>25.77</v>
@@ -23145,7 +23147,7 @@
         <v>-1.7</v>
       </c>
       <c r="M126" t="n">
-        <v>7.71</v>
+        <v>8.81</v>
       </c>
       <c r="N126" t="b">
         <v>1</v>
@@ -23183,7 +23185,7 @@
         <v>-24.9</v>
       </c>
       <c r="H127" t="n">
-        <v>40.15</v>
+        <v>32.15</v>
       </c>
       <c r="I127" t="n">
         <v>10.88</v>
@@ -23196,7 +23198,7 @@
         <v>-4.1</v>
       </c>
       <c r="M127" t="n">
-        <v>36.26</v>
+        <v>28.26</v>
       </c>
       <c r="N127" t="b">
         <v>1</v>
@@ -23238,7 +23240,7 @@
         <v>-8.1</v>
       </c>
       <c r="H128" t="n">
-        <v>18.13</v>
+        <v>20.27</v>
       </c>
       <c r="I128" t="n">
         <v>14.27</v>
@@ -23251,7 +23253,7 @@
         <v>-10.92</v>
       </c>
       <c r="M128" t="n">
-        <v>14.24</v>
+        <v>16.38</v>
       </c>
       <c r="N128" t="b">
         <v>1</v>
@@ -23289,7 +23291,7 @@
         <v>-10.2</v>
       </c>
       <c r="H129" t="n">
-        <v>-6.97</v>
+        <v>-10.2</v>
       </c>
       <c r="I129" t="n">
         <v>15.03</v>
@@ -23302,7 +23304,7 @@
         <v>-1.61</v>
       </c>
       <c r="M129" t="n">
-        <v>-10.86</v>
+        <v>-14.08</v>
       </c>
       <c r="N129" t="b">
         <v>1</v>
@@ -23340,7 +23342,7 @@
         <v>68.90000000000001</v>
       </c>
       <c r="H130" t="n">
-        <v>10.83</v>
+        <v>9.32</v>
       </c>
       <c r="I130" t="n">
         <v>1.84</v>
@@ -23353,7 +23355,7 @@
         <v>-10.43</v>
       </c>
       <c r="M130" t="n">
-        <v>6.94</v>
+        <v>5.44</v>
       </c>
       <c r="N130" t="b">
         <v>1</v>
@@ -23391,7 +23393,7 @@
         <v>-40.8</v>
       </c>
       <c r="H131" t="n">
-        <v>-8.460000000000001</v>
+        <v>-10.17</v>
       </c>
       <c r="I131" t="n">
         <v>21.71</v>
@@ -23404,7 +23406,7 @@
         <v>-3.3</v>
       </c>
       <c r="M131" t="n">
-        <v>-12.34</v>
+        <v>-14.06</v>
       </c>
       <c r="N131" t="b">
         <v>1</v>
@@ -23442,7 +23444,7 @@
         <v>40.7</v>
       </c>
       <c r="H132" t="n">
-        <v>40.65</v>
+        <v>43.7</v>
       </c>
       <c r="I132" t="n">
         <v>-4.08</v>
@@ -23455,7 +23457,7 @@
         <v>-11.2</v>
       </c>
       <c r="M132" t="n">
-        <v>36.76</v>
+        <v>39.81</v>
       </c>
       <c r="N132" t="b">
         <v>1</v>
@@ -23493,7 +23495,7 @@
         <v>25.7</v>
       </c>
       <c r="H133" t="n">
-        <v>-8.1</v>
+        <v>-9.32</v>
       </c>
       <c r="I133" t="n">
         <v>11.3</v>
@@ -23506,7 +23508,7 @@
         <v>-11.03</v>
       </c>
       <c r="M133" t="n">
-        <v>-11.99</v>
+        <v>-13.21</v>
       </c>
       <c r="N133" t="b">
         <v>1</v>

--- a/STS_holy_grail_v2.xlsx
+++ b/STS_holy_grail_v2.xlsx
@@ -464,7 +464,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.53</v>
+        <v>1.18</v>
       </c>
     </row>
     <row r="5">
@@ -474,7 +474,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-1.24</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="6">
@@ -531,13 +531,13 @@
         <v>60</v>
       </c>
       <c r="C10" t="n">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="D10" t="n">
-        <v>45</v>
+        <v>48.33</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.46</v>
+        <v>-0.78</v>
       </c>
     </row>
     <row r="11">
@@ -550,13 +550,13 @@
         <v>78</v>
       </c>
       <c r="C11" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="D11" t="n">
-        <v>38.46</v>
+        <v>39.74</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.01</v>
+        <v>-1.53</v>
       </c>
     </row>
     <row r="12">
@@ -569,13 +569,13 @@
         <v>141</v>
       </c>
       <c r="C12" t="n">
-        <v>1.34</v>
+        <v>0.39</v>
       </c>
       <c r="D12" t="n">
-        <v>43.26</v>
+        <v>39.01</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.47</v>
+        <v>-1.83</v>
       </c>
     </row>
     <row r="13">
@@ -588,13 +588,13 @@
         <v>33</v>
       </c>
       <c r="C13" t="n">
-        <v>3.65</v>
+        <v>4.44</v>
       </c>
       <c r="D13" t="n">
-        <v>51.52</v>
+        <v>60.61</v>
       </c>
       <c r="E13" t="n">
-        <v>1.93</v>
+        <v>3.42</v>
       </c>
     </row>
     <row r="15">
@@ -641,13 +641,13 @@
         <v>100</v>
       </c>
       <c r="C17" t="n">
-        <v>1.73</v>
+        <v>0.97</v>
       </c>
       <c r="D17" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.13</v>
+        <v>-1.34</v>
       </c>
     </row>
     <row r="18">
@@ -660,13 +660,13 @@
         <v>42</v>
       </c>
       <c r="C18" t="n">
-        <v>0.3</v>
+        <v>-1.09</v>
       </c>
       <c r="D18" t="n">
-        <v>40.48</v>
+        <v>38.1</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.28</v>
+        <v>-3.03</v>
       </c>
     </row>
     <row r="19">
@@ -679,13 +679,13 @@
         <v>43</v>
       </c>
       <c r="C19" t="n">
-        <v>-1.31</v>
+        <v>-1.83</v>
       </c>
       <c r="D19" t="n">
         <v>32.56</v>
       </c>
       <c r="E19" t="n">
-        <v>-4.03</v>
+        <v>-3.96</v>
       </c>
     </row>
     <row r="20">
@@ -698,13 +698,13 @@
         <v>39</v>
       </c>
       <c r="C20" t="n">
-        <v>-5.57</v>
+        <v>-5.8</v>
       </c>
       <c r="D20" t="n">
-        <v>28.21</v>
+        <v>35.9</v>
       </c>
       <c r="E20" t="n">
-        <v>-8.279999999999999</v>
+        <v>-7.86</v>
       </c>
     </row>
     <row r="21">
@@ -717,13 +717,13 @@
         <v>88</v>
       </c>
       <c r="C21" t="n">
-        <v>6.43</v>
+        <v>7.07</v>
       </c>
       <c r="D21" t="n">
-        <v>55.68</v>
+        <v>59.09</v>
       </c>
       <c r="E21" t="n">
-        <v>3.62</v>
+        <v>4.87</v>
       </c>
     </row>
     <row r="23">
@@ -770,13 +770,13 @@
         <v>10</v>
       </c>
       <c r="C25" t="n">
-        <v>9.4</v>
+        <v>7.28</v>
       </c>
       <c r="D25" t="n">
         <v>60</v>
       </c>
       <c r="E25" t="n">
-        <v>6.17</v>
+        <v>4.66</v>
       </c>
     </row>
     <row r="26">
@@ -789,13 +789,13 @@
         <v>5</v>
       </c>
       <c r="C26" t="n">
-        <v>-3.08</v>
+        <v>-2.8</v>
       </c>
       <c r="D26" t="n">
         <v>40</v>
       </c>
       <c r="E26" t="n">
-        <v>-7.16</v>
+        <v>-6.14</v>
       </c>
     </row>
     <row r="27">
@@ -808,13 +808,13 @@
         <v>3</v>
       </c>
       <c r="C27" t="n">
-        <v>1.7</v>
+        <v>0.31</v>
       </c>
       <c r="D27" t="n">
         <v>33.33</v>
       </c>
       <c r="E27" t="n">
-        <v>-1.34</v>
+        <v>-1.99</v>
       </c>
     </row>
     <row r="29">
@@ -861,13 +861,13 @@
         <v>180</v>
       </c>
       <c r="C31" t="n">
-        <v>2.93</v>
+        <v>2.55</v>
       </c>
       <c r="D31" t="n">
         <v>41.11</v>
       </c>
       <c r="E31" t="n">
-        <v>0.24</v>
+        <v>0.41</v>
       </c>
     </row>
     <row r="32">
@@ -880,13 +880,13 @@
         <v>132</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.38</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="D32" t="n">
         <v>46.21</v>
       </c>
       <c r="E32" t="n">
-        <v>-3.26</v>
+        <v>-2.9</v>
       </c>
     </row>
   </sheetData>
@@ -1010,16 +1010,16 @@
         <v>-17.9</v>
       </c>
       <c r="H2" t="n">
-        <v>0.23</v>
+        <v>-1.03</v>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>-2.67</v>
       </c>
       <c r="M2" t="n">
-        <v>0.87</v>
+        <v>-0.3</v>
       </c>
       <c r="N2" t="b">
         <v>0</v>
@@ -1057,16 +1057,16 @@
         <v>-2.7</v>
       </c>
       <c r="H3" t="n">
-        <v>-2.98</v>
+        <v>-4.69</v>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="n">
-        <v>-2.98</v>
+        <v>-5.23</v>
       </c>
       <c r="M3" t="n">
-        <v>-2.34</v>
+        <v>-3.96</v>
       </c>
       <c r="N3" t="b">
         <v>1</v>
@@ -1104,7 +1104,7 @@
         <v>-25.3</v>
       </c>
       <c r="H4" t="n">
-        <v>1.71</v>
+        <v>0.45</v>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
@@ -1113,7 +1113,7 @@
         <v>-1.03</v>
       </c>
       <c r="M4" t="n">
-        <v>2.35</v>
+        <v>1.18</v>
       </c>
       <c r="N4" t="b">
         <v>0</v>
@@ -1151,16 +1151,16 @@
         <v>25.6</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.91</v>
+        <v>-2.16</v>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="n">
-        <v>-2.24</v>
+        <v>-3.22</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.27</v>
+        <v>-1.44</v>
       </c>
       <c r="N5" t="b">
         <v>0</v>
@@ -1198,7 +1198,7 @@
         <v>26.9</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.99</v>
+        <v>2.29</v>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
@@ -1207,7 +1207,7 @@
         <v>-2.51</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.35</v>
+        <v>3.02</v>
       </c>
       <c r="N6" t="b">
         <v>1</v>
@@ -1245,16 +1245,16 @@
         <v>-14.5</v>
       </c>
       <c r="H7" t="n">
-        <v>-3.75</v>
+        <v>-3.9</v>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="n">
-        <v>-3.93</v>
+        <v>-4.33</v>
       </c>
       <c r="M7" t="n">
-        <v>-3.96</v>
+        <v>-4.02</v>
       </c>
       <c r="N7" t="b">
         <v>0</v>
@@ -1292,7 +1292,7 @@
         <v>17.2</v>
       </c>
       <c r="H8" t="n">
-        <v>-10.19</v>
+        <v>-9.109999999999999</v>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
@@ -1301,7 +1301,7 @@
         <v>-10.54</v>
       </c>
       <c r="M8" t="n">
-        <v>-11.13</v>
+        <v>-9.31</v>
       </c>
       <c r="N8" t="b">
         <v>0</v>
@@ -1339,7 +1339,7 @@
         <v>-13.2</v>
       </c>
       <c r="H9" t="n">
-        <v>8.18</v>
+        <v>12.69</v>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
@@ -1348,7 +1348,7 @@
         <v>-0.82</v>
       </c>
       <c r="M9" t="n">
-        <v>7.25</v>
+        <v>12.49</v>
       </c>
       <c r="N9" t="b">
         <v>0</v>
@@ -1386,16 +1386,16 @@
         <v>-7.7</v>
       </c>
       <c r="H10" t="n">
-        <v>0.62</v>
+        <v>-1.69</v>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="n">
-        <v>-0.59</v>
+        <v>-3.04</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.31</v>
+        <v>-1.89</v>
       </c>
       <c r="N10" t="b">
         <v>0</v>
@@ -1433,16 +1433,16 @@
         <v>-18.1</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.8</v>
+        <v>-2.05</v>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="n">
-        <v>-2.05</v>
+        <v>-2.57</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.73</v>
+        <v>-2.26</v>
       </c>
       <c r="N11" t="b">
         <v>0</v>
@@ -1480,7 +1480,7 @@
         <v>-18.1</v>
       </c>
       <c r="H12" t="n">
-        <v>1.07</v>
+        <v>1.33</v>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
@@ -1489,7 +1489,7 @@
         <v>-2.69</v>
       </c>
       <c r="M12" t="n">
-        <v>0.14</v>
+        <v>1.12</v>
       </c>
       <c r="N12" t="b">
         <v>1</v>
@@ -1527,16 +1527,16 @@
         <v>7.7</v>
       </c>
       <c r="H13" t="n">
-        <v>-7.25</v>
+        <v>-6.28</v>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="n">
-        <v>-7.73</v>
+        <v>-8.16</v>
       </c>
       <c r="M13" t="n">
-        <v>-8.18</v>
+        <v>-6.48</v>
       </c>
       <c r="N13" t="b">
         <v>0</v>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Extended</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="E14" t="inlineStr"/>
@@ -1574,7 +1574,7 @@
         <v>-21.5</v>
       </c>
       <c r="H14" t="n">
-        <v>5.73</v>
+        <v>3.71</v>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
@@ -1583,7 +1583,7 @@
         <v>-1.4</v>
       </c>
       <c r="M14" t="n">
-        <v>4.8</v>
+        <v>3.51</v>
       </c>
       <c r="N14" t="b">
         <v>1</v>
@@ -1621,7 +1621,7 @@
         <v>41.6</v>
       </c>
       <c r="H15" t="n">
-        <v>-3</v>
+        <v>2.85</v>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
@@ -1630,7 +1630,7 @@
         <v>-4.38</v>
       </c>
       <c r="M15" t="n">
-        <v>-4.58</v>
+        <v>2</v>
       </c>
       <c r="N15" t="b">
         <v>1</v>
@@ -1668,7 +1668,7 @@
         <v>32.1</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.52</v>
+        <v>-0.87</v>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
@@ -1677,7 +1677,7 @@
         <v>-2.19</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.11</v>
+        <v>-1.73</v>
       </c>
       <c r="N16" t="b">
         <v>1</v>
@@ -1715,16 +1715,16 @@
         <v>-14.4</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.19</v>
+        <v>-3.82</v>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="n">
-        <v>-1.54</v>
+        <v>-4.51</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.78</v>
+        <v>-4.68</v>
       </c>
       <c r="N17" t="b">
         <v>1</v>
@@ -1762,7 +1762,7 @@
         <v>-16.8</v>
       </c>
       <c r="H18" t="n">
-        <v>4.18</v>
+        <v>4.12</v>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
@@ -1771,7 +1771,7 @@
         <v>-3.26</v>
       </c>
       <c r="M18" t="n">
-        <v>2.59</v>
+        <v>3.26</v>
       </c>
       <c r="N18" t="b">
         <v>0</v>
@@ -1809,7 +1809,7 @@
         <v>-10</v>
       </c>
       <c r="H19" t="n">
-        <v>-3.02</v>
+        <v>-2.67</v>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
@@ -1818,7 +1818,7 @@
         <v>-5.75</v>
       </c>
       <c r="M19" t="n">
-        <v>-4.6</v>
+        <v>-3.52</v>
       </c>
       <c r="N19" t="b">
         <v>1</v>
@@ -1856,16 +1856,16 @@
         <v>6.4</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.14</v>
+        <v>-0.2</v>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="n">
-        <v>-1.45</v>
+        <v>-1.7</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.72</v>
+        <v>-1.05</v>
       </c>
       <c r="N20" t="b">
         <v>1</v>
@@ -1892,7 +1892,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Extended</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="E21" t="inlineStr"/>
@@ -1903,7 +1903,7 @@
         <v>-11</v>
       </c>
       <c r="H21" t="n">
-        <v>7.04</v>
+        <v>4.77</v>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
@@ -1912,7 +1912,7 @@
         <v>-0.97</v>
       </c>
       <c r="M21" t="n">
-        <v>5.45</v>
+        <v>3.9</v>
       </c>
       <c r="N21" t="b">
         <v>0</v>
@@ -1950,16 +1950,16 @@
         <v>-23.9</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.39</v>
+        <v>-1.84</v>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="n">
-        <v>-1.79</v>
+        <v>-3.06</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.98</v>
+        <v>-2.7</v>
       </c>
       <c r="N22" t="b">
         <v>0</v>
@@ -2001,16 +2001,16 @@
         <v>-9.800000000000001</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.74</v>
+        <v>-3.39</v>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="n">
-        <v>-2.63</v>
+        <v>-3.55</v>
       </c>
       <c r="M23" t="n">
-        <v>-2.33</v>
+        <v>-4.25</v>
       </c>
       <c r="N23" t="b">
         <v>0</v>
@@ -2037,7 +2037,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Extended</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="E24" t="inlineStr"/>
@@ -2048,7 +2048,7 @@
         <v>-36.1</v>
       </c>
       <c r="H24" t="n">
-        <v>5.2</v>
+        <v>4.55</v>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
@@ -2057,7 +2057,7 @@
         <v>-1.92</v>
       </c>
       <c r="M24" t="n">
-        <v>4.34</v>
+        <v>3.77</v>
       </c>
       <c r="N24" t="b">
         <v>0</v>
@@ -2095,16 +2095,16 @@
         <v>-7.9</v>
       </c>
       <c r="H25" t="n">
-        <v>-6.05</v>
+        <v>-8.31</v>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="n">
-        <v>-8.449999999999999</v>
+        <v>-8.59</v>
       </c>
       <c r="M25" t="n">
-        <v>-7.64</v>
+        <v>-9.17</v>
       </c>
       <c r="N25" t="b">
         <v>0</v>
@@ -2142,16 +2142,16 @@
         <v>2.6</v>
       </c>
       <c r="H26" t="n">
-        <v>-5.07</v>
+        <v>-8.23</v>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="n">
-        <v>-6.16</v>
+        <v>-8.640000000000001</v>
       </c>
       <c r="M26" t="n">
-        <v>-7.15</v>
+        <v>-9.58</v>
       </c>
       <c r="N26" t="b">
         <v>0</v>
@@ -2189,7 +2189,7 @@
         <v>6.3</v>
       </c>
       <c r="H27" t="n">
-        <v>3.78</v>
+        <v>2.74</v>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
@@ -2198,7 +2198,7 @@
         <v>-0.7</v>
       </c>
       <c r="M27" t="n">
-        <v>1.7</v>
+        <v>1.39</v>
       </c>
       <c r="N27" t="b">
         <v>0</v>
@@ -2236,7 +2236,7 @@
         <v>20.2</v>
       </c>
       <c r="H28" t="n">
-        <v>1.75</v>
+        <v>2.15</v>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
@@ -2245,7 +2245,7 @@
         <v>-1.07</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.25</v>
+        <v>0.89</v>
       </c>
       <c r="N28" t="b">
         <v>1</v>
@@ -2272,7 +2272,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Extended</t>
         </is>
       </c>
       <c r="E29" t="inlineStr"/>
@@ -2283,7 +2283,7 @@
         <v>43.7</v>
       </c>
       <c r="H29" t="n">
-        <v>3.98</v>
+        <v>6.55</v>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
@@ -2292,7 +2292,7 @@
         <v>-2.44</v>
       </c>
       <c r="M29" t="n">
-        <v>1.98</v>
+        <v>5.28</v>
       </c>
       <c r="N29" t="b">
         <v>1</v>
@@ -2330,16 +2330,16 @@
         <v>1.9</v>
       </c>
       <c r="H30" t="n">
-        <v>-3.03</v>
+        <v>-5.37</v>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="n">
-        <v>-3.2</v>
+        <v>-5.97</v>
       </c>
       <c r="M30" t="n">
-        <v>-5.02</v>
+        <v>-6.63</v>
       </c>
       <c r="N30" t="b">
         <v>1</v>
@@ -2366,7 +2366,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Extended</t>
         </is>
       </c>
       <c r="E31" t="inlineStr"/>
@@ -2377,7 +2377,7 @@
         <v>37.5</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.34</v>
+        <v>5.81</v>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
@@ -2386,7 +2386,7 @@
         <v>-3.95</v>
       </c>
       <c r="M31" t="n">
-        <v>-2.49</v>
+        <v>4.4</v>
       </c>
       <c r="N31" t="b">
         <v>1</v>
@@ -2424,7 +2424,7 @@
         <v>15</v>
       </c>
       <c r="H32" t="n">
-        <v>-19.31</v>
+        <v>-20.38</v>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
@@ -2433,7 +2433,7 @@
         <v>-22.27</v>
       </c>
       <c r="M32" t="n">
-        <v>-21.45</v>
+        <v>-21.79</v>
       </c>
       <c r="N32" t="b">
         <v>0</v>
@@ -2471,7 +2471,7 @@
         <v>40.2</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.15</v>
+        <v>-0.92</v>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
@@ -2480,7 +2480,7 @@
         <v>-3.87</v>
       </c>
       <c r="M33" t="n">
-        <v>-2.3</v>
+        <v>-2.33</v>
       </c>
       <c r="N33" t="b">
         <v>1</v>
@@ -2507,7 +2507,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Extended</t>
         </is>
       </c>
       <c r="E34" t="inlineStr"/>
@@ -2518,7 +2518,7 @@
         <v>10.7</v>
       </c>
       <c r="H34" t="n">
-        <v>3.18</v>
+        <v>5.32</v>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
@@ -2527,7 +2527,7 @@
         <v>-3.78</v>
       </c>
       <c r="M34" t="n">
-        <v>1.03</v>
+        <v>3.9</v>
       </c>
       <c r="N34" t="b">
         <v>1</v>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Extended</t>
         </is>
       </c>
       <c r="E35" t="inlineStr"/>
@@ -2565,7 +2565,7 @@
         <v>25.6</v>
       </c>
       <c r="H35" t="n">
-        <v>2.11</v>
+        <v>7.23</v>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
@@ -2574,7 +2574,7 @@
         <v>-4.85</v>
       </c>
       <c r="M35" t="n">
-        <v>0.73</v>
+        <v>6.58</v>
       </c>
       <c r="N35" t="b">
         <v>1</v>
@@ -2612,7 +2612,7 @@
         <v>6.3</v>
       </c>
       <c r="H36" t="n">
-        <v>5.89</v>
+        <v>7.2</v>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
@@ -2621,7 +2621,7 @@
         <v>-0.4</v>
       </c>
       <c r="M36" t="n">
-        <v>3.62</v>
+        <v>5.66</v>
       </c>
       <c r="N36" t="b">
         <v>0</v>
@@ -2659,16 +2659,16 @@
         <v>2.3</v>
       </c>
       <c r="H37" t="n">
-        <v>-7.81</v>
+        <v>-8.85</v>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="n">
-        <v>-8.02</v>
+        <v>-11.75</v>
       </c>
       <c r="M37" t="n">
-        <v>-10.09</v>
+        <v>-10.4</v>
       </c>
       <c r="N37" t="b">
         <v>0</v>
@@ -2706,16 +2706,18 @@
         <v>-4.3</v>
       </c>
       <c r="H38" t="n">
-        <v>3.39</v>
-      </c>
-      <c r="I38" t="inlineStr"/>
+        <v>2.25</v>
+      </c>
+      <c r="I38" t="n">
+        <v>2.25</v>
+      </c>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="n">
         <v>-5.89</v>
       </c>
       <c r="M38" t="n">
-        <v>1.93</v>
+        <v>1.51</v>
       </c>
       <c r="N38" t="b">
         <v>0</v>
@@ -2753,16 +2755,18 @@
         <v>-29.4</v>
       </c>
       <c r="H39" t="n">
-        <v>-5.75</v>
-      </c>
-      <c r="I39" t="inlineStr"/>
+        <v>-7</v>
+      </c>
+      <c r="I39" t="n">
+        <v>-7</v>
+      </c>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="n">
         <v>-9.640000000000001</v>
       </c>
       <c r="M39" t="n">
-        <v>-7.21</v>
+        <v>-7.74</v>
       </c>
       <c r="N39" t="b">
         <v>0</v>
@@ -2800,16 +2804,18 @@
         <v>-6.9</v>
       </c>
       <c r="H40" t="n">
-        <v>6.44</v>
-      </c>
-      <c r="I40" t="inlineStr"/>
+        <v>7</v>
+      </c>
+      <c r="I40" t="n">
+        <v>7</v>
+      </c>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="n">
         <v>-4.53</v>
       </c>
       <c r="M40" t="n">
-        <v>4.97</v>
+        <v>6.26</v>
       </c>
       <c r="N40" t="b">
         <v>1</v>
@@ -2847,16 +2853,18 @@
         <v>4.2</v>
       </c>
       <c r="H41" t="n">
-        <v>-10.83</v>
-      </c>
-      <c r="I41" t="inlineStr"/>
+        <v>-12.37</v>
+      </c>
+      <c r="I41" t="n">
+        <v>-12.37</v>
+      </c>
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="n">
-        <v>-11.21</v>
+        <v>-13.81</v>
       </c>
       <c r="M41" t="n">
-        <v>-12.29</v>
+        <v>-13.1</v>
       </c>
       <c r="N41" t="b">
         <v>0</v>
@@ -2894,7 +2902,7 @@
         <v>-32.4</v>
       </c>
       <c r="H42" t="n">
-        <v>-3.58</v>
+        <v>-2.93</v>
       </c>
       <c r="I42" t="n">
         <v>-3.58</v>
@@ -2905,7 +2913,7 @@
         <v>-12.47</v>
       </c>
       <c r="M42" t="n">
-        <v>-4.39</v>
+        <v>-3.01</v>
       </c>
       <c r="N42" t="b">
         <v>0</v>
@@ -2943,7 +2951,7 @@
         <v>-11</v>
       </c>
       <c r="H43" t="n">
-        <v>-8.449999999999999</v>
+        <v>-7.53</v>
       </c>
       <c r="I43" t="n">
         <v>-8.449999999999999</v>
@@ -2954,7 +2962,7 @@
         <v>-18.92</v>
       </c>
       <c r="M43" t="n">
-        <v>-9.26</v>
+        <v>-7.62</v>
       </c>
       <c r="N43" t="b">
         <v>0</v>
@@ -2992,7 +3000,7 @@
         <v>9.699999999999999</v>
       </c>
       <c r="H44" t="n">
-        <v>13.1</v>
+        <v>11.26</v>
       </c>
       <c r="I44" t="n">
         <v>1.27</v>
@@ -3003,7 +3011,7 @@
         <v>-6.51</v>
       </c>
       <c r="M44" t="n">
-        <v>12.13</v>
+        <v>11.02</v>
       </c>
       <c r="N44" t="b">
         <v>0</v>
@@ -3041,7 +3049,7 @@
         <v>-28.1</v>
       </c>
       <c r="H45" t="n">
-        <v>-8.15</v>
+        <v>-8.029999999999999</v>
       </c>
       <c r="I45" t="n">
         <v>-10.79</v>
@@ -3052,7 +3060,7 @@
         <v>-12.06</v>
       </c>
       <c r="M45" t="n">
-        <v>-9.119999999999999</v>
+        <v>-8.26</v>
       </c>
       <c r="N45" t="b">
         <v>0</v>
@@ -3090,7 +3098,7 @@
         <v>-17.7</v>
       </c>
       <c r="H46" t="n">
-        <v>-4.26</v>
+        <v>-3.49</v>
       </c>
       <c r="I46" t="n">
         <v>-0.89</v>
@@ -3098,10 +3106,10 @@
       <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="n">
-        <v>-4.73</v>
+        <v>-5.08</v>
       </c>
       <c r="M46" t="n">
-        <v>-5.23</v>
+        <v>-3.73</v>
       </c>
       <c r="N46" t="b">
         <v>0</v>
@@ -3139,7 +3147,7 @@
         <v>-9.300000000000001</v>
       </c>
       <c r="H47" t="n">
-        <v>-5.34</v>
+        <v>-4.55</v>
       </c>
       <c r="I47" t="n">
         <v>-3.34</v>
@@ -3147,10 +3155,10 @@
       <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="n">
-        <v>-7.3</v>
+        <v>-7.34</v>
       </c>
       <c r="M47" t="n">
-        <v>-6.3</v>
+        <v>-4.79</v>
       </c>
       <c r="N47" t="b">
         <v>0</v>
@@ -3188,7 +3196,7 @@
         <v>0.3</v>
       </c>
       <c r="H48" t="n">
-        <v>-12.25</v>
+        <v>-13.63</v>
       </c>
       <c r="I48" t="n">
         <v>-10.53</v>
@@ -3196,10 +3204,10 @@
       <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="n">
-        <v>-13.04</v>
+        <v>-15.78</v>
       </c>
       <c r="M48" t="n">
-        <v>-13.22</v>
+        <v>-13.87</v>
       </c>
       <c r="N48" t="b">
         <v>1</v>
@@ -3237,7 +3245,7 @@
         <v>12.3</v>
       </c>
       <c r="H49" t="n">
-        <v>7.91</v>
+        <v>6.89</v>
       </c>
       <c r="I49" t="n">
         <v>6.51</v>
@@ -3248,7 +3256,7 @@
         <v>-6.01</v>
       </c>
       <c r="M49" t="n">
-        <v>6.23</v>
+        <v>5.94</v>
       </c>
       <c r="N49" t="b">
         <v>0</v>
@@ -3286,7 +3294,7 @@
         <v>2.8</v>
       </c>
       <c r="H50" t="n">
-        <v>1.39</v>
+        <v>0.29</v>
       </c>
       <c r="I50" t="n">
         <v>3.18</v>
@@ -3297,7 +3305,7 @@
         <v>-0.88</v>
       </c>
       <c r="M50" t="n">
-        <v>-0.29</v>
+        <v>-0.66</v>
       </c>
       <c r="N50" t="b">
         <v>1</v>
@@ -3335,7 +3343,7 @@
         <v>-1.4</v>
       </c>
       <c r="H51" t="n">
-        <v>10.66</v>
+        <v>9.029999999999999</v>
       </c>
       <c r="I51" t="n">
         <v>-4.52</v>
@@ -3346,7 +3354,7 @@
         <v>-7.44</v>
       </c>
       <c r="M51" t="n">
-        <v>8.970000000000001</v>
+        <v>8.08</v>
       </c>
       <c r="N51" t="b">
         <v>0</v>
@@ -3384,7 +3392,7 @@
         <v>34.5</v>
       </c>
       <c r="H52" t="n">
-        <v>7.38</v>
+        <v>5.66</v>
       </c>
       <c r="I52" t="n">
         <v>0.66</v>
@@ -3395,7 +3403,7 @@
         <v>-2.64</v>
       </c>
       <c r="M52" t="n">
-        <v>5.69</v>
+        <v>4.71</v>
       </c>
       <c r="N52" t="b">
         <v>1</v>
@@ -3433,7 +3441,7 @@
         <v>-22.7</v>
       </c>
       <c r="H53" t="n">
-        <v>-5.42</v>
+        <v>-7.21</v>
       </c>
       <c r="I53" t="n">
         <v>-6.71</v>
@@ -3441,10 +3449,10 @@
       <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="n">
-        <v>-7.05</v>
+        <v>-8.67</v>
       </c>
       <c r="M53" t="n">
-        <v>-7.16</v>
+        <v>-8.220000000000001</v>
       </c>
       <c r="N53" t="b">
         <v>0</v>
@@ -3482,7 +3490,7 @@
         <v>24.3</v>
       </c>
       <c r="H54" t="n">
-        <v>15.95</v>
+        <v>28.88</v>
       </c>
       <c r="I54" t="n">
         <v>2.54</v>
@@ -3493,7 +3501,7 @@
         <v>-5.21</v>
       </c>
       <c r="M54" t="n">
-        <v>14.91</v>
+        <v>28.57</v>
       </c>
       <c r="N54" t="b">
         <v>1</v>
@@ -3542,7 +3550,7 @@
         <v>-16.17</v>
       </c>
       <c r="M55" t="n">
-        <v>-7.9</v>
+        <v>-7.17</v>
       </c>
       <c r="N55" t="b">
         <v>0</v>
@@ -3580,7 +3588,7 @@
         <v>2.9</v>
       </c>
       <c r="H56" t="n">
-        <v>-11.02</v>
+        <v>-12.46</v>
       </c>
       <c r="I56" t="n">
         <v>-8.470000000000001</v>
@@ -3588,10 +3596,10 @@
       <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="n">
-        <v>-12.94</v>
+        <v>-13.99</v>
       </c>
       <c r="M56" t="n">
-        <v>-11.33</v>
+        <v>-12.69</v>
       </c>
       <c r="N56" t="b">
         <v>0</v>
@@ -3629,7 +3637,7 @@
         <v>-16.9</v>
       </c>
       <c r="H57" t="n">
-        <v>-7.29</v>
+        <v>-11.25</v>
       </c>
       <c r="I57" t="n">
         <v>-6.47</v>
@@ -3637,10 +3645,10 @@
       <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="n">
-        <v>-9.02</v>
+        <v>-11.5</v>
       </c>
       <c r="M57" t="n">
-        <v>-8.33</v>
+        <v>-11.56</v>
       </c>
       <c r="N57" t="b">
         <v>1</v>
@@ -3678,7 +3686,7 @@
         <v>32.8</v>
       </c>
       <c r="H58" t="n">
-        <v>8.68</v>
+        <v>5.23</v>
       </c>
       <c r="I58" t="n">
         <v>14.96</v>
@@ -3689,7 +3697,7 @@
         <v>-0.9</v>
       </c>
       <c r="M58" t="n">
-        <v>8.220000000000001</v>
+        <v>5.49</v>
       </c>
       <c r="N58" t="b">
         <v>0</v>
@@ -3727,7 +3735,7 @@
         <v>0.8</v>
       </c>
       <c r="H59" t="n">
-        <v>-4.81</v>
+        <v>-6.05</v>
       </c>
       <c r="I59" t="n">
         <v>-7.73</v>
@@ -3738,7 +3746,7 @@
         <v>-10.12</v>
       </c>
       <c r="M59" t="n">
-        <v>-4.54</v>
+        <v>-5.7</v>
       </c>
       <c r="N59" t="b">
         <v>0</v>
@@ -3776,7 +3784,7 @@
         <v>-9.6</v>
       </c>
       <c r="H60" t="n">
-        <v>-8.42</v>
+        <v>-17.87</v>
       </c>
       <c r="I60" t="n">
         <v>-1.23</v>
@@ -3784,10 +3792,10 @@
       <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="n">
-        <v>-9.65</v>
+        <v>-18.52</v>
       </c>
       <c r="M60" t="n">
-        <v>-8.880000000000001</v>
+        <v>-17.61</v>
       </c>
       <c r="N60" t="b">
         <v>0</v>
@@ -3825,7 +3833,7 @@
         <v>20.3</v>
       </c>
       <c r="H61" t="n">
-        <v>-16.02</v>
+        <v>-15.32</v>
       </c>
       <c r="I61" t="n">
         <v>-2.07</v>
@@ -3833,10 +3841,10 @@
       <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr"/>
       <c r="L61" t="n">
-        <v>-16.13</v>
+        <v>-17.35</v>
       </c>
       <c r="M61" t="n">
-        <v>-16.91</v>
+        <v>-15.48</v>
       </c>
       <c r="N61" t="b">
         <v>1</v>
@@ -3863,7 +3871,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Retired</t>
         </is>
       </c>
       <c r="E62" t="inlineStr"/>
@@ -3874,7 +3882,7 @@
         <v>0.3</v>
       </c>
       <c r="H62" t="n">
-        <v>-18.83</v>
+        <v>-19.17</v>
       </c>
       <c r="I62" t="n">
         <v>-9.9</v>
@@ -3882,10 +3890,10 @@
       <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
       <c r="L62" t="n">
-        <v>-21.11</v>
+        <v>-21.72</v>
       </c>
       <c r="M62" t="n">
-        <v>-20.21</v>
+        <v>-19.82</v>
       </c>
       <c r="N62" t="b">
         <v>1</v>
@@ -3923,18 +3931,20 @@
         <v>49.4</v>
       </c>
       <c r="H63" t="n">
-        <v>3.93</v>
+        <v>3.68</v>
       </c>
       <c r="I63" t="n">
         <v>2.9</v>
       </c>
-      <c r="J63" t="inlineStr"/>
+      <c r="J63" t="n">
+        <v>3.68</v>
+      </c>
       <c r="K63" t="inlineStr"/>
       <c r="L63" t="n">
         <v>-5.67</v>
       </c>
       <c r="M63" t="n">
-        <v>2.74</v>
+        <v>3.22</v>
       </c>
       <c r="N63" t="b">
         <v>1</v>
@@ -3972,18 +3982,20 @@
         <v>4.5</v>
       </c>
       <c r="H64" t="n">
-        <v>-10.17</v>
+        <v>-10.6</v>
       </c>
       <c r="I64" t="n">
         <v>-7.61</v>
       </c>
-      <c r="J64" t="inlineStr"/>
+      <c r="J64" t="n">
+        <v>-10.6</v>
+      </c>
       <c r="K64" t="inlineStr"/>
       <c r="L64" t="n">
-        <v>-10.98</v>
+        <v>-11.1</v>
       </c>
       <c r="M64" t="n">
-        <v>-11.36</v>
+        <v>-11.07</v>
       </c>
       <c r="N64" t="b">
         <v>1</v>
@@ -4021,7 +4033,7 @@
         <v>4.2</v>
       </c>
       <c r="H65" t="n">
-        <v>-20.21</v>
+        <v>-19.27</v>
       </c>
       <c r="I65" t="n">
         <v>-6.86</v>
@@ -4034,7 +4046,7 @@
         <v>-20.23</v>
       </c>
       <c r="M65" t="n">
-        <v>-20.68</v>
+        <v>-19.65</v>
       </c>
       <c r="N65" t="b">
         <v>0</v>
@@ -4072,18 +4084,20 @@
         <v>15.4</v>
       </c>
       <c r="H66" t="n">
-        <v>-6.09</v>
+        <v>-5.15</v>
       </c>
       <c r="I66" t="n">
         <v>-1.19</v>
       </c>
-      <c r="J66" t="inlineStr"/>
+      <c r="J66" t="n">
+        <v>-5.15</v>
+      </c>
       <c r="K66" t="inlineStr"/>
       <c r="L66" t="n">
         <v>-7.43</v>
       </c>
       <c r="M66" t="n">
-        <v>-7.28</v>
+        <v>-5.61</v>
       </c>
       <c r="N66" t="b">
         <v>0</v>
@@ -4121,7 +4135,7 @@
         <v>15.5</v>
       </c>
       <c r="H67" t="n">
-        <v>-7.45</v>
+        <v>-9.26</v>
       </c>
       <c r="I67" t="n">
         <v>-7.36</v>
@@ -4134,7 +4148,7 @@
         <v>-12.98</v>
       </c>
       <c r="M67" t="n">
-        <v>-8.83</v>
+        <v>-9.9</v>
       </c>
       <c r="N67" t="b">
         <v>0</v>
@@ -4176,7 +4190,7 @@
         <v>-8.5</v>
       </c>
       <c r="H68" t="n">
-        <v>-0.61</v>
+        <v>-3.92</v>
       </c>
       <c r="I68" t="n">
         <v>-3.04</v>
@@ -4189,7 +4203,7 @@
         <v>-4.96</v>
       </c>
       <c r="M68" t="n">
-        <v>-1.98</v>
+        <v>-4.56</v>
       </c>
       <c r="N68" t="b">
         <v>0</v>
@@ -4227,7 +4241,7 @@
         <v>1.8</v>
       </c>
       <c r="H69" t="n">
-        <v>-12.48</v>
+        <v>-13.12</v>
       </c>
       <c r="I69" t="n">
         <v>-6.45</v>
@@ -4240,7 +4254,7 @@
         <v>-13.57</v>
       </c>
       <c r="M69" t="n">
-        <v>-13.12</v>
+        <v>-13.68</v>
       </c>
       <c r="N69" t="b">
         <v>0</v>
@@ -4278,7 +4292,7 @@
         <v>33.9</v>
       </c>
       <c r="H70" t="n">
-        <v>14.43</v>
+        <v>13.87</v>
       </c>
       <c r="I70" t="n">
         <v>-7.74</v>
@@ -4291,7 +4305,7 @@
         <v>-9.449999999999999</v>
       </c>
       <c r="M70" t="n">
-        <v>13.06</v>
+        <v>13.22</v>
       </c>
       <c r="N70" t="b">
         <v>0</v>
@@ -4329,7 +4343,7 @@
         <v>-25</v>
       </c>
       <c r="H71" t="n">
-        <v>-5.39</v>
+        <v>-9.9</v>
       </c>
       <c r="I71" t="n">
         <v>2.51</v>
@@ -4342,7 +4356,7 @@
         <v>-4.88</v>
       </c>
       <c r="M71" t="n">
-        <v>-6.6</v>
+        <v>-10.38</v>
       </c>
       <c r="N71" t="b">
         <v>0</v>
@@ -4380,7 +4394,7 @@
         <v>-12.6</v>
       </c>
       <c r="H72" t="n">
-        <v>-23.45</v>
+        <v>-23.29</v>
       </c>
       <c r="I72" t="n">
         <v>-7.89</v>
@@ -4393,7 +4407,7 @@
         <v>-21.29</v>
       </c>
       <c r="M72" t="n">
-        <v>-24.67</v>
+        <v>-23.78</v>
       </c>
       <c r="N72" t="b">
         <v>0</v>
@@ -4431,7 +4445,7 @@
         <v>-17.9</v>
       </c>
       <c r="H73" t="n">
-        <v>-7.39</v>
+        <v>-9.4</v>
       </c>
       <c r="I73" t="n">
         <v>0.6</v>
@@ -4444,7 +4458,7 @@
         <v>-4.72</v>
       </c>
       <c r="M73" t="n">
-        <v>-8.609999999999999</v>
+        <v>-9.890000000000001</v>
       </c>
       <c r="N73" t="b">
         <v>1</v>
@@ -4482,7 +4496,7 @@
         <v>2.1</v>
       </c>
       <c r="H74" t="n">
-        <v>-17.66</v>
+        <v>-21.11</v>
       </c>
       <c r="I74" t="n">
         <v>0.25</v>
@@ -4495,7 +4509,7 @@
         <v>-16.43</v>
       </c>
       <c r="M74" t="n">
-        <v>-18.88</v>
+        <v>-21.6</v>
       </c>
       <c r="N74" t="b">
         <v>1</v>
@@ -4533,7 +4547,7 @@
         <v>19.4</v>
       </c>
       <c r="H75" t="n">
-        <v>-12.47</v>
+        <v>-10.22</v>
       </c>
       <c r="I75" t="n">
         <v>-10.01</v>
@@ -4546,7 +4560,7 @@
         <v>-15.23</v>
       </c>
       <c r="M75" t="n">
-        <v>-13.11</v>
+        <v>-10.13</v>
       </c>
       <c r="N75" t="b">
         <v>1</v>
@@ -4584,7 +4598,7 @@
         <v>-30.5</v>
       </c>
       <c r="H76" t="n">
-        <v>-24.31</v>
+        <v>-24.83</v>
       </c>
       <c r="I76" t="n">
         <v>-4.6</v>
@@ -4597,7 +4611,7 @@
         <v>-10.37</v>
       </c>
       <c r="M76" t="n">
-        <v>-24.95</v>
+        <v>-24.75</v>
       </c>
       <c r="N76" t="b">
         <v>0</v>
@@ -4635,7 +4649,7 @@
         <v>-20.5</v>
       </c>
       <c r="H77" t="n">
-        <v>-9.43</v>
+        <v>-12.18</v>
       </c>
       <c r="I77" t="n">
         <v>-4.62</v>
@@ -4648,7 +4662,7 @@
         <v>-9.92</v>
       </c>
       <c r="M77" t="n">
-        <v>-10.07</v>
+        <v>-12.1</v>
       </c>
       <c r="N77" t="b">
         <v>0</v>
@@ -4686,7 +4700,7 @@
         <v>-12.3</v>
       </c>
       <c r="H78" t="n">
-        <v>-24.13</v>
+        <v>-21.39</v>
       </c>
       <c r="I78" t="n">
         <v>-4.36</v>
@@ -4699,7 +4713,7 @@
         <v>-13.26</v>
       </c>
       <c r="M78" t="n">
-        <v>-24.99</v>
+        <v>-21.53</v>
       </c>
       <c r="N78" t="b">
         <v>0</v>
@@ -4737,7 +4751,7 @@
         <v>13.7</v>
       </c>
       <c r="H79" t="n">
-        <v>-16.66</v>
+        <v>-17.03</v>
       </c>
       <c r="I79" t="n">
         <v>-12.16</v>
@@ -4750,7 +4764,7 @@
         <v>-13.02</v>
       </c>
       <c r="M79" t="n">
-        <v>-17.52</v>
+        <v>-17.16</v>
       </c>
       <c r="N79" t="b">
         <v>0</v>
@@ -4788,7 +4802,7 @@
         <v>-2.6</v>
       </c>
       <c r="H80" t="n">
-        <v>-9.19</v>
+        <v>-9.619999999999999</v>
       </c>
       <c r="I80" t="n">
         <v>-4.27</v>
@@ -4801,7 +4815,7 @@
         <v>-4.86</v>
       </c>
       <c r="M80" t="n">
-        <v>-10.05</v>
+        <v>-9.76</v>
       </c>
       <c r="N80" t="b">
         <v>1</v>
@@ -4839,7 +4853,7 @@
         <v>25.6</v>
       </c>
       <c r="H81" t="n">
-        <v>-6.01</v>
+        <v>-12.03</v>
       </c>
       <c r="I81" t="n">
         <v>4.26</v>
@@ -4852,7 +4866,7 @@
         <v>-10.74</v>
       </c>
       <c r="M81" t="n">
-        <v>-6.87</v>
+        <v>-12.16</v>
       </c>
       <c r="N81" t="b">
         <v>0</v>
@@ -4890,7 +4904,7 @@
         <v>23.8</v>
       </c>
       <c r="H82" t="n">
-        <v>4.35</v>
+        <v>11.92</v>
       </c>
       <c r="I82" t="n">
         <v>1.36</v>
@@ -4903,7 +4917,7 @@
         <v>-9.94</v>
       </c>
       <c r="M82" t="n">
-        <v>4.46</v>
+        <v>12.75</v>
       </c>
       <c r="N82" t="b">
         <v>1</v>
@@ -4941,7 +4955,7 @@
         <v>38.9</v>
       </c>
       <c r="H83" t="n">
-        <v>-10.09</v>
+        <v>-12.42</v>
       </c>
       <c r="I83" t="n">
         <v>-9.220000000000001</v>
@@ -4954,7 +4968,7 @@
         <v>-9.83</v>
       </c>
       <c r="M83" t="n">
-        <v>-9.970000000000001</v>
+        <v>-11.59</v>
       </c>
       <c r="N83" t="b">
         <v>1</v>
@@ -4992,7 +5006,7 @@
         <v>32.1</v>
       </c>
       <c r="H84" t="n">
-        <v>33.7</v>
+        <v>43.4</v>
       </c>
       <c r="I84" t="n">
         <v>11.84</v>
@@ -5005,7 +5019,7 @@
         <v>-1.82</v>
       </c>
       <c r="M84" t="n">
-        <v>33.81</v>
+        <v>44.23</v>
       </c>
       <c r="N84" t="b">
         <v>0</v>
@@ -5043,7 +5057,7 @@
         <v>53.4</v>
       </c>
       <c r="H85" t="n">
-        <v>9.6</v>
+        <v>11.65</v>
       </c>
       <c r="I85" t="n">
         <v>2.75</v>
@@ -5056,7 +5070,7 @@
         <v>-2.31</v>
       </c>
       <c r="M85" t="n">
-        <v>10.02</v>
+        <v>12.78</v>
       </c>
       <c r="N85" t="b">
         <v>0</v>
@@ -5094,7 +5108,7 @@
         <v>54.1</v>
       </c>
       <c r="H86" t="n">
-        <v>12.75</v>
+        <v>13.5</v>
       </c>
       <c r="I86" t="n">
         <v>5.54</v>
@@ -5107,7 +5121,7 @@
         <v>-0.41</v>
       </c>
       <c r="M86" t="n">
-        <v>12.7</v>
+        <v>14.16</v>
       </c>
       <c r="N86" t="b">
         <v>0</v>
@@ -5145,7 +5159,7 @@
         <v>43.2</v>
       </c>
       <c r="H87" t="n">
-        <v>-20.83</v>
+        <v>-20.7</v>
       </c>
       <c r="I87" t="n">
         <v>-3.15</v>
@@ -5158,7 +5172,7 @@
         <v>-17.51</v>
       </c>
       <c r="M87" t="n">
-        <v>-20.88</v>
+        <v>-20.03</v>
       </c>
       <c r="N87" t="b">
         <v>1</v>
@@ -5196,7 +5210,7 @@
         <v>-8.199999999999999</v>
       </c>
       <c r="H88" t="n">
-        <v>-5.01</v>
+        <v>-6.75</v>
       </c>
       <c r="I88" t="n">
         <v>5.34</v>
@@ -5209,7 +5223,7 @@
         <v>-5.27</v>
       </c>
       <c r="M88" t="n">
-        <v>-5.06</v>
+        <v>-6.08</v>
       </c>
       <c r="N88" t="b">
         <v>1</v>
@@ -5247,7 +5261,7 @@
         <v>-1.2</v>
       </c>
       <c r="H89" t="n">
-        <v>0.01</v>
+        <v>0.2</v>
       </c>
       <c r="I89" t="n">
         <v>8.27</v>
@@ -5260,7 +5274,7 @@
         <v>-5.3</v>
       </c>
       <c r="M89" t="n">
-        <v>-0.09</v>
+        <v>0.83</v>
       </c>
       <c r="N89" t="b">
         <v>0</v>
@@ -5298,7 +5312,7 @@
         <v>-23.9</v>
       </c>
       <c r="H90" t="n">
-        <v>-7.28</v>
+        <v>-10.2</v>
       </c>
       <c r="I90" t="n">
         <v>3.28</v>
@@ -5311,7 +5325,7 @@
         <v>-4.46</v>
       </c>
       <c r="M90" t="n">
-        <v>-7.63</v>
+        <v>-9.83</v>
       </c>
       <c r="N90" t="b">
         <v>1</v>
@@ -5353,7 +5367,7 @@
         <v>-6.1</v>
       </c>
       <c r="H91" t="n">
-        <v>7.41</v>
+        <v>4.42</v>
       </c>
       <c r="I91" t="n">
         <v>4.9</v>
@@ -5366,7 +5380,7 @@
         <v>-9</v>
       </c>
       <c r="M91" t="n">
-        <v>7.06</v>
+        <v>4.79</v>
       </c>
       <c r="N91" t="b">
         <v>1</v>
@@ -5404,7 +5418,7 @@
         <v>26.7</v>
       </c>
       <c r="H92" t="n">
-        <v>-0.87</v>
+        <v>-1.12</v>
       </c>
       <c r="I92" t="n">
         <v>-0.05</v>
@@ -5417,7 +5431,7 @@
         <v>-0.87</v>
       </c>
       <c r="M92" t="n">
-        <v>-1.22</v>
+        <v>-0.75</v>
       </c>
       <c r="N92" t="b">
         <v>1</v>
@@ -5455,7 +5469,7 @@
         <v>39.5</v>
       </c>
       <c r="H93" t="n">
-        <v>19.23</v>
+        <v>21.43</v>
       </c>
       <c r="I93" t="n">
         <v>-5.13</v>
@@ -5468,7 +5482,7 @@
         <v>-8.869999999999999</v>
       </c>
       <c r="M93" t="n">
-        <v>18.88</v>
+        <v>21.8</v>
       </c>
       <c r="N93" t="b">
         <v>0</v>
@@ -5506,7 +5520,7 @@
         <v>14.3</v>
       </c>
       <c r="H94" t="n">
-        <v>-5.38</v>
+        <v>-3.51</v>
       </c>
       <c r="I94" t="n">
         <v>-0.43</v>
@@ -5519,7 +5533,7 @@
         <v>-11.86</v>
       </c>
       <c r="M94" t="n">
-        <v>-5.01</v>
+        <v>-3.05</v>
       </c>
       <c r="N94" t="b">
         <v>0</v>
@@ -5557,7 +5571,7 @@
         <v>-11.3</v>
       </c>
       <c r="H95" t="n">
-        <v>-2.23</v>
+        <v>-3.06</v>
       </c>
       <c r="I95" t="n">
         <v>1.31</v>
@@ -5570,7 +5584,7 @@
         <v>-1.88</v>
       </c>
       <c r="M95" t="n">
-        <v>-2.57</v>
+        <v>-2.69</v>
       </c>
       <c r="N95" t="b">
         <v>0</v>
@@ -5608,7 +5622,7 @@
         <v>-23.5</v>
       </c>
       <c r="H96" t="n">
-        <v>-14.57</v>
+        <v>-16.81</v>
       </c>
       <c r="I96" t="n">
         <v>13.29</v>
@@ -5621,7 +5635,7 @@
         <v>-14.04</v>
       </c>
       <c r="M96" t="n">
-        <v>-14.92</v>
+        <v>-16.44</v>
       </c>
       <c r="N96" t="b">
         <v>0</v>
@@ -5659,7 +5673,7 @@
         <v>10.5</v>
       </c>
       <c r="H97" t="n">
-        <v>-7.99</v>
+        <v>-8.98</v>
       </c>
       <c r="I97" t="n">
         <v>-0.86</v>
@@ -5672,7 +5686,7 @@
         <v>-6.11</v>
       </c>
       <c r="M97" t="n">
-        <v>-8.34</v>
+        <v>-8.609999999999999</v>
       </c>
       <c r="N97" t="b">
         <v>0</v>
@@ -5710,7 +5724,7 @@
         <v>-3.5</v>
       </c>
       <c r="H98" t="n">
-        <v>-0.34</v>
+        <v>-2.58</v>
       </c>
       <c r="I98" t="n">
         <v>-4.95</v>
@@ -5723,7 +5737,7 @@
         <v>-8.43</v>
       </c>
       <c r="M98" t="n">
-        <v>-0.9</v>
+        <v>-2.41</v>
       </c>
       <c r="N98" t="b">
         <v>1</v>
@@ -5761,7 +5775,7 @@
         <v>-12.8</v>
       </c>
       <c r="H99" t="n">
-        <v>-0.3</v>
+        <v>-0.32</v>
       </c>
       <c r="I99" t="n">
         <v>-1.74</v>
@@ -5774,7 +5788,7 @@
         <v>-2.97</v>
       </c>
       <c r="M99" t="n">
-        <v>-0.13</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="N99" t="b">
         <v>0</v>
@@ -5812,7 +5826,7 @@
         <v>2.4</v>
       </c>
       <c r="H100" t="n">
-        <v>19.82</v>
+        <v>20.32</v>
       </c>
       <c r="I100" t="n">
         <v>12.41</v>
@@ -5825,7 +5839,7 @@
         <v>-0.07000000000000001</v>
       </c>
       <c r="M100" t="n">
-        <v>19.99</v>
+        <v>20.57</v>
       </c>
       <c r="N100" t="b">
         <v>0</v>
@@ -5863,7 +5877,7 @@
         <v>-17.9</v>
       </c>
       <c r="H101" t="n">
-        <v>6.27</v>
+        <v>3.59</v>
       </c>
       <c r="I101" t="n">
         <v>-0.5</v>
@@ -5876,7 +5890,7 @@
         <v>-3.43</v>
       </c>
       <c r="M101" t="n">
-        <v>5.71</v>
+        <v>3.76</v>
       </c>
       <c r="N101" t="b">
         <v>1</v>
@@ -5914,7 +5928,7 @@
         <v>11.9</v>
       </c>
       <c r="H102" t="n">
-        <v>-9.69</v>
+        <v>-9.539999999999999</v>
       </c>
       <c r="I102" t="n">
         <v>6.88</v>
@@ -5927,7 +5941,7 @@
         <v>-10.93</v>
       </c>
       <c r="M102" t="n">
-        <v>-9.630000000000001</v>
+        <v>-9.390000000000001</v>
       </c>
       <c r="N102" t="b">
         <v>0</v>
@@ -5965,7 +5979,7 @@
         <v>53.5</v>
       </c>
       <c r="H103" t="n">
-        <v>2.66</v>
+        <v>1.63</v>
       </c>
       <c r="I103" t="n">
         <v>1.23</v>
@@ -5978,7 +5992,7 @@
         <v>-7.57</v>
       </c>
       <c r="M103" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="N103" t="b">
         <v>1</v>
@@ -6016,7 +6030,7 @@
         <v>18.1</v>
       </c>
       <c r="H104" t="n">
-        <v>-1.79</v>
+        <v>-1.76</v>
       </c>
       <c r="I104" t="n">
         <v>-1.69</v>
@@ -6029,7 +6043,7 @@
         <v>-1.92</v>
       </c>
       <c r="M104" t="n">
-        <v>-2.45</v>
+        <v>-1.69</v>
       </c>
       <c r="N104" t="b">
         <v>0</v>
@@ -6067,7 +6081,7 @@
         <v>-1</v>
       </c>
       <c r="H105" t="n">
-        <v>-14.7</v>
+        <v>-14.06</v>
       </c>
       <c r="I105" t="n">
         <v>-6.26</v>
@@ -6080,7 +6094,7 @@
         <v>-15</v>
       </c>
       <c r="M105" t="n">
-        <v>-15.36</v>
+        <v>-14</v>
       </c>
       <c r="N105" t="b">
         <v>1</v>
@@ -6118,7 +6132,7 @@
         <v>29.7</v>
       </c>
       <c r="H106" t="n">
-        <v>11.21</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="I106" t="n">
         <v>11.27</v>
@@ -6131,7 +6145,7 @@
         <v>0</v>
       </c>
       <c r="M106" t="n">
-        <v>10.54</v>
+        <v>9.19</v>
       </c>
       <c r="N106" t="b">
         <v>1</v>
@@ -6169,7 +6183,7 @@
         <v>15.2</v>
       </c>
       <c r="H107" t="n">
-        <v>-33.13</v>
+        <v>-34.95</v>
       </c>
       <c r="I107" t="n">
         <v>-8.77</v>
@@ -6182,7 +6196,7 @@
         <v>-24.79</v>
       </c>
       <c r="M107" t="n">
-        <v>-33.06</v>
+        <v>-34.16</v>
       </c>
       <c r="N107" t="b">
         <v>1</v>
@@ -6220,7 +6234,7 @@
         <v>22.2</v>
       </c>
       <c r="H108" t="n">
-        <v>7.62</v>
+        <v>6.97</v>
       </c>
       <c r="I108" t="n">
         <v>1.01</v>
@@ -6233,7 +6247,7 @@
         <v>-3.94</v>
       </c>
       <c r="M108" t="n">
-        <v>7.69</v>
+        <v>7.76</v>
       </c>
       <c r="N108" t="b">
         <v>1</v>
@@ -6271,7 +6285,7 @@
         <v>10.8</v>
       </c>
       <c r="H109" t="n">
-        <v>-0.57</v>
+        <v>1.5</v>
       </c>
       <c r="I109" t="n">
         <v>5.62</v>
@@ -6284,7 +6298,7 @@
         <v>-1.59</v>
       </c>
       <c r="M109" t="n">
-        <v>-0.5</v>
+        <v>2.29</v>
       </c>
       <c r="N109" t="b">
         <v>0</v>
@@ -6322,7 +6336,7 @@
         <v>-2.1</v>
       </c>
       <c r="H110" t="n">
-        <v>-3.87</v>
+        <v>-2.14</v>
       </c>
       <c r="I110" t="n">
         <v>0.67</v>
@@ -6335,7 +6349,7 @@
         <v>-7.84</v>
       </c>
       <c r="M110" t="n">
-        <v>-3.08</v>
+        <v>-1.27</v>
       </c>
       <c r="N110" t="b">
         <v>0</v>
@@ -6386,7 +6400,7 @@
         <v>-22</v>
       </c>
       <c r="M111" t="n">
-        <v>-20.72</v>
+        <v>-20.64</v>
       </c>
       <c r="N111" t="b">
         <v>0</v>
@@ -6424,7 +6438,7 @@
         <v>0.3</v>
       </c>
       <c r="H112" t="n">
-        <v>23.14</v>
+        <v>22.26</v>
       </c>
       <c r="I112" t="n">
         <v>6.01</v>
@@ -6437,7 +6451,7 @@
         <v>-3.85</v>
       </c>
       <c r="M112" t="n">
-        <v>19.69</v>
+        <v>19.55</v>
       </c>
       <c r="N112" t="b">
         <v>0</v>
@@ -6479,7 +6493,7 @@
         <v>-0</v>
       </c>
       <c r="H113" t="n">
-        <v>28.93</v>
+        <v>30.88</v>
       </c>
       <c r="I113" t="n">
         <v>13.5</v>
@@ -6492,7 +6506,7 @@
         <v>-2.53</v>
       </c>
       <c r="M113" t="n">
-        <v>25.48</v>
+        <v>28.18</v>
       </c>
       <c r="N113" t="b">
         <v>1</v>
@@ -6530,7 +6544,7 @@
         <v>10.5</v>
       </c>
       <c r="H114" t="n">
-        <v>0.67</v>
+        <v>0.71</v>
       </c>
       <c r="I114" t="n">
         <v>1.99</v>
@@ -6543,7 +6557,7 @@
         <v>-6.27</v>
       </c>
       <c r="M114" t="n">
-        <v>-2.78</v>
+        <v>-2</v>
       </c>
       <c r="N114" t="b">
         <v>1</v>
@@ -6581,7 +6595,7 @@
         <v>30.4</v>
       </c>
       <c r="H115" t="n">
-        <v>5.24</v>
+        <v>5.13</v>
       </c>
       <c r="I115" t="n">
         <v>8.539999999999999</v>
@@ -6594,7 +6608,7 @@
         <v>-0.44</v>
       </c>
       <c r="M115" t="n">
-        <v>1.79</v>
+        <v>2.42</v>
       </c>
       <c r="N115" t="b">
         <v>0</v>
@@ -6636,7 +6650,7 @@
         <v>-3.2</v>
       </c>
       <c r="H116" t="n">
-        <v>16</v>
+        <v>15.17</v>
       </c>
       <c r="I116" t="n">
         <v>15.28</v>
@@ -6649,7 +6663,7 @@
         <v>-2.53</v>
       </c>
       <c r="M116" t="n">
-        <v>12.55</v>
+        <v>12.46</v>
       </c>
       <c r="N116" t="b">
         <v>0</v>
@@ -6687,7 +6701,7 @@
         <v>-23.5</v>
       </c>
       <c r="H117" t="n">
-        <v>25.58</v>
+        <v>21.87</v>
       </c>
       <c r="I117" t="n">
         <v>20.48</v>
@@ -6700,7 +6714,7 @@
         <v>-2.25</v>
       </c>
       <c r="M117" t="n">
-        <v>22.13</v>
+        <v>19.16</v>
       </c>
       <c r="N117" t="b">
         <v>0</v>
@@ -6738,7 +6752,7 @@
         <v>-27.3</v>
       </c>
       <c r="H118" t="n">
-        <v>1.63</v>
+        <v>-1.2</v>
       </c>
       <c r="I118" t="n">
         <v>-8.83</v>
@@ -6751,7 +6765,7 @@
         <v>-19.66</v>
       </c>
       <c r="M118" t="n">
-        <v>-1.82</v>
+        <v>-3.91</v>
       </c>
       <c r="N118" t="b">
         <v>0</v>
@@ -6789,7 +6803,7 @@
         <v>-12.5</v>
       </c>
       <c r="H119" t="n">
-        <v>-4.52</v>
+        <v>-8</v>
       </c>
       <c r="I119" t="n">
         <v>21.54</v>
@@ -6802,7 +6816,7 @@
         <v>-0.95</v>
       </c>
       <c r="M119" t="n">
-        <v>-8.630000000000001</v>
+        <v>-11.36</v>
       </c>
       <c r="N119" t="b">
         <v>0</v>
@@ -6840,7 +6854,7 @@
         <v>-37</v>
       </c>
       <c r="H120" t="n">
-        <v>26.83</v>
+        <v>24.3</v>
       </c>
       <c r="I120" t="n">
         <v>18.38</v>
@@ -6853,7 +6867,7 @@
         <v>-5.11</v>
       </c>
       <c r="M120" t="n">
-        <v>22.71</v>
+        <v>20.93</v>
       </c>
       <c r="N120" t="b">
         <v>1</v>
@@ -6895,7 +6909,7 @@
         <v>-3.4</v>
       </c>
       <c r="H121" t="n">
-        <v>6.28</v>
+        <v>2.69</v>
       </c>
       <c r="I121" t="n">
         <v>30.48</v>
@@ -6908,7 +6922,7 @@
         <v>-0.9</v>
       </c>
       <c r="M121" t="n">
-        <v>2.91</v>
+        <v>-0.59</v>
       </c>
       <c r="N121" t="b">
         <v>0</v>
@@ -6946,7 +6960,7 @@
         <v>-23.4</v>
       </c>
       <c r="H122" t="n">
-        <v>-3.02</v>
+        <v>-4.53</v>
       </c>
       <c r="I122" t="n">
         <v>-3.58</v>
@@ -6959,7 +6973,7 @@
         <v>-17.98</v>
       </c>
       <c r="M122" t="n">
-        <v>-7.13</v>
+        <v>-7.89</v>
       </c>
       <c r="N122" t="b">
         <v>0</v>
@@ -6997,7 +7011,7 @@
         <v>-28.9</v>
       </c>
       <c r="H123" t="n">
-        <v>-17.06</v>
+        <v>-17.49</v>
       </c>
       <c r="I123" t="n">
         <v>-12.9</v>
@@ -7010,7 +7024,7 @@
         <v>-23.19</v>
       </c>
       <c r="M123" t="n">
-        <v>-21.17</v>
+        <v>-20.86</v>
       </c>
       <c r="N123" t="b">
         <v>0</v>
@@ -7048,7 +7062,7 @@
         <v>-26.8</v>
       </c>
       <c r="H124" t="n">
-        <v>12.92</v>
+        <v>15.43</v>
       </c>
       <c r="I124" t="n">
         <v>4.56</v>
@@ -7061,7 +7075,7 @@
         <v>-4.09</v>
       </c>
       <c r="M124" t="n">
-        <v>8.81</v>
+        <v>12.06</v>
       </c>
       <c r="N124" t="b">
         <v>1</v>
@@ -7103,7 +7117,7 @@
         <v>-9.800000000000001</v>
       </c>
       <c r="H125" t="n">
-        <v>-23.78</v>
+        <v>-23.07</v>
       </c>
       <c r="I125" t="n">
         <v>-4.09</v>
@@ -7116,7 +7130,7 @@
         <v>-15.24</v>
       </c>
       <c r="M125" t="n">
-        <v>-29.11</v>
+        <v>-27.65</v>
       </c>
       <c r="N125" t="b">
         <v>0</v>
@@ -7154,7 +7168,7 @@
         <v>21</v>
       </c>
       <c r="H126" t="n">
-        <v>-1.01</v>
+        <v>-1.73</v>
       </c>
       <c r="I126" t="n">
         <v>-0.72</v>
@@ -7167,7 +7181,7 @@
         <v>-7.35</v>
       </c>
       <c r="M126" t="n">
-        <v>-6.35</v>
+        <v>-6.3</v>
       </c>
       <c r="N126" t="b">
         <v>0</v>
@@ -7205,7 +7219,7 @@
         <v>13.2</v>
       </c>
       <c r="H127" t="n">
-        <v>31.41</v>
+        <v>33.45</v>
       </c>
       <c r="I127" t="n">
         <v>8.130000000000001</v>
@@ -7218,7 +7232,7 @@
         <v>-2.36</v>
       </c>
       <c r="M127" t="n">
-        <v>26.08</v>
+        <v>28.87</v>
       </c>
       <c r="N127" t="b">
         <v>0</v>
@@ -7256,7 +7270,7 @@
         <v>6.1</v>
       </c>
       <c r="H128" t="n">
-        <v>-3.99</v>
+        <v>0.92</v>
       </c>
       <c r="I128" t="n">
         <v>10.43</v>
@@ -7269,7 +7283,7 @@
         <v>-1.51</v>
       </c>
       <c r="M128" t="n">
-        <v>-9.32</v>
+        <v>-3.66</v>
       </c>
       <c r="N128" t="b">
         <v>0</v>
@@ -7307,7 +7321,7 @@
         <v>6.5</v>
       </c>
       <c r="H129" t="n">
-        <v>-7.87</v>
+        <v>-8.460000000000001</v>
       </c>
       <c r="I129" t="n">
         <v>-0.04</v>
@@ -7320,7 +7334,7 @@
         <v>-4.12</v>
       </c>
       <c r="M129" t="n">
-        <v>-13.2</v>
+        <v>-13.03</v>
       </c>
       <c r="N129" t="b">
         <v>0</v>
@@ -7358,7 +7372,7 @@
         <v>-36.5</v>
       </c>
       <c r="H130" t="n">
-        <v>-32.08</v>
+        <v>-32.35</v>
       </c>
       <c r="I130" t="n">
         <v>-27.75</v>
@@ -7371,7 +7385,7 @@
         <v>-31.28</v>
       </c>
       <c r="M130" t="n">
-        <v>-36.1</v>
+        <v>-36.29</v>
       </c>
       <c r="N130" t="b">
         <v>1</v>
@@ -7409,7 +7423,7 @@
         <v>-14.5</v>
       </c>
       <c r="H131" t="n">
-        <v>-12.13</v>
+        <v>-14.72</v>
       </c>
       <c r="I131" t="n">
         <v>4.48</v>
@@ -7422,7 +7436,7 @@
         <v>-3.33</v>
       </c>
       <c r="M131" t="n">
-        <v>-16.91</v>
+        <v>-18.74</v>
       </c>
       <c r="N131" t="b">
         <v>0</v>
@@ -7460,7 +7474,7 @@
         <v>1.7</v>
       </c>
       <c r="H132" t="n">
-        <v>-3.04</v>
+        <v>-3.93</v>
       </c>
       <c r="I132" t="n">
         <v>8.859999999999999</v>
@@ -7473,7 +7487,7 @@
         <v>-3.27</v>
       </c>
       <c r="M132" t="n">
-        <v>-7.81</v>
+        <v>-7.95</v>
       </c>
       <c r="N132" t="b">
         <v>0</v>
@@ -7511,7 +7525,7 @@
         <v>48.1</v>
       </c>
       <c r="H133" t="n">
-        <v>-3.46</v>
+        <v>-2.03</v>
       </c>
       <c r="I133" t="n">
         <v>0.16</v>
@@ -7524,7 +7538,7 @@
         <v>-8.890000000000001</v>
       </c>
       <c r="M133" t="n">
-        <v>-8.23</v>
+        <v>-6.05</v>
       </c>
       <c r="N133" t="b">
         <v>0</v>
@@ -7562,7 +7576,7 @@
         <v>-38.7</v>
       </c>
       <c r="H134" t="n">
-        <v>8.57</v>
+        <v>7.01</v>
       </c>
       <c r="I134" t="n">
         <v>17.17</v>
@@ -7575,7 +7589,7 @@
         <v>-0.54</v>
       </c>
       <c r="M134" t="n">
-        <v>3.79</v>
+        <v>2.99</v>
       </c>
       <c r="N134" t="b">
         <v>1</v>
@@ -7613,7 +7627,7 @@
         <v>24.9</v>
       </c>
       <c r="H135" t="n">
-        <v>-3.69</v>
+        <v>-3.73</v>
       </c>
       <c r="I135" t="n">
         <v>10.45</v>
@@ -7626,7 +7640,7 @@
         <v>-0.49</v>
       </c>
       <c r="M135" t="n">
-        <v>-8.470000000000001</v>
+        <v>-7.75</v>
       </c>
       <c r="N135" t="b">
         <v>0</v>
@@ -7664,7 +7678,7 @@
         <v>-34.6</v>
       </c>
       <c r="H136" t="n">
-        <v>20.01</v>
+        <v>16.77</v>
       </c>
       <c r="I136" t="n">
         <v>6.67</v>
@@ -7677,7 +7691,7 @@
         <v>-3.06</v>
       </c>
       <c r="M136" t="n">
-        <v>15.23</v>
+        <v>12.75</v>
       </c>
       <c r="N136" t="b">
         <v>1</v>
@@ -7715,7 +7729,7 @@
         <v>-21.4</v>
       </c>
       <c r="H137" t="n">
-        <v>-1.15</v>
+        <v>-0.65</v>
       </c>
       <c r="I137" t="n">
         <v>2.8</v>
@@ -7728,7 +7742,7 @@
         <v>-2.27</v>
       </c>
       <c r="M137" t="n">
-        <v>-5.17</v>
+        <v>-4.59</v>
       </c>
       <c r="N137" t="b">
         <v>0</v>
@@ -7766,7 +7780,7 @@
         <v>-11.8</v>
       </c>
       <c r="H138" t="n">
-        <v>-3.44</v>
+        <v>-6.36</v>
       </c>
       <c r="I138" t="n">
         <v>9.76</v>
@@ -7779,7 +7793,7 @@
         <v>-1.63</v>
       </c>
       <c r="M138" t="n">
-        <v>-8.33</v>
+        <v>-10.49</v>
       </c>
       <c r="N138" t="b">
         <v>1</v>
@@ -7817,7 +7831,7 @@
         <v>0.1</v>
       </c>
       <c r="H139" t="n">
-        <v>-16.65</v>
+        <v>-15.34</v>
       </c>
       <c r="I139" t="n">
         <v>-2.83</v>
@@ -7830,7 +7844,7 @@
         <v>-5.45</v>
       </c>
       <c r="M139" t="n">
-        <v>-21.54</v>
+        <v>-19.47</v>
       </c>
       <c r="N139" t="b">
         <v>1</v>
@@ -7868,7 +7882,7 @@
         <v>-13.8</v>
       </c>
       <c r="H140" t="n">
-        <v>5.22</v>
+        <v>8.24</v>
       </c>
       <c r="I140" t="n">
         <v>4.67</v>
@@ -7881,7 +7895,7 @@
         <v>-5.7</v>
       </c>
       <c r="M140" t="n">
-        <v>0.33</v>
+        <v>4.11</v>
       </c>
       <c r="N140" t="b">
         <v>0</v>
@@ -7923,7 +7937,7 @@
         <v>-8.800000000000001</v>
       </c>
       <c r="H141" t="n">
-        <v>-2.35</v>
+        <v>-2.48</v>
       </c>
       <c r="I141" t="n">
         <v>15.97</v>
@@ -7936,7 +7950,7 @@
         <v>-0.79</v>
       </c>
       <c r="M141" t="n">
-        <v>-7.23</v>
+        <v>-6.61</v>
       </c>
       <c r="N141" t="b">
         <v>0</v>
@@ -7974,7 +7988,7 @@
         <v>24.1</v>
       </c>
       <c r="H142" t="n">
-        <v>-14.1</v>
+        <v>-15.22</v>
       </c>
       <c r="I142" t="n">
         <v>-8.31</v>
@@ -7987,7 +8001,7 @@
         <v>-18.31</v>
       </c>
       <c r="M142" t="n">
-        <v>-18.18</v>
+        <v>-18.55</v>
       </c>
       <c r="N142" t="b">
         <v>1</v>
@@ -8025,7 +8039,7 @@
         <v>-15.9</v>
       </c>
       <c r="H143" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="I143" t="n">
         <v>10.45</v>
@@ -8038,7 +8052,7 @@
         <v>-0.31</v>
       </c>
       <c r="M143" t="n">
-        <v>-1.51</v>
+        <v>-3.33</v>
       </c>
       <c r="N143" t="b">
         <v>1</v>
@@ -8076,7 +8090,7 @@
         <v>-23.3</v>
       </c>
       <c r="H144" t="n">
-        <v>-9.59</v>
+        <v>-8.460000000000001</v>
       </c>
       <c r="I144" t="n">
         <v>-20.42</v>
@@ -8089,7 +8103,7 @@
         <v>-27.45</v>
       </c>
       <c r="M144" t="n">
-        <v>-13.67</v>
+        <v>-11.79</v>
       </c>
       <c r="N144" t="b">
         <v>0</v>
@@ -8127,7 +8141,7 @@
         <v>28.9</v>
       </c>
       <c r="H145" t="n">
-        <v>-5.29</v>
+        <v>-4.81</v>
       </c>
       <c r="I145" t="n">
         <v>8.06</v>
@@ -8140,7 +8154,7 @@
         <v>-2.79</v>
       </c>
       <c r="M145" t="n">
-        <v>-9.51</v>
+        <v>-8.949999999999999</v>
       </c>
       <c r="N145" t="b">
         <v>0</v>
@@ -8178,7 +8192,7 @@
         <v>40.1</v>
       </c>
       <c r="H146" t="n">
-        <v>41.89</v>
+        <v>40.36</v>
       </c>
       <c r="I146" t="n">
         <v>15.9</v>
@@ -8191,7 +8205,7 @@
         <v>-5.87</v>
       </c>
       <c r="M146" t="n">
-        <v>36.9</v>
+        <v>36.14</v>
       </c>
       <c r="N146" t="b">
         <v>0</v>
@@ -8229,7 +8243,7 @@
         <v>-27.3</v>
       </c>
       <c r="H147" t="n">
-        <v>6.02</v>
+        <v>5.33</v>
       </c>
       <c r="I147" t="n">
         <v>0.75</v>
@@ -8242,7 +8256,7 @@
         <v>-5.46</v>
       </c>
       <c r="M147" t="n">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="N147" t="b">
         <v>0</v>
@@ -8280,7 +8294,7 @@
         <v>19.7</v>
       </c>
       <c r="H148" t="n">
-        <v>-4.58</v>
+        <v>-11.05</v>
       </c>
       <c r="I148" t="n">
         <v>-4.49</v>
@@ -8293,7 +8307,7 @@
         <v>-13.7</v>
       </c>
       <c r="M148" t="n">
-        <v>-9.44</v>
+        <v>-15.15</v>
       </c>
       <c r="N148" t="b">
         <v>0</v>
@@ -8331,7 +8345,7 @@
         <v>-21.3</v>
       </c>
       <c r="H149" t="n">
-        <v>-2.01</v>
+        <v>-0.53</v>
       </c>
       <c r="I149" t="n">
         <v>7.16</v>
@@ -8344,7 +8358,7 @@
         <v>-11.9</v>
       </c>
       <c r="M149" t="n">
-        <v>-6.12</v>
+        <v>-4.55</v>
       </c>
       <c r="N149" t="b">
         <v>0</v>
@@ -8382,7 +8396,7 @@
         <v>-21.8</v>
       </c>
       <c r="H150" t="n">
-        <v>-23.9</v>
+        <v>-24.57</v>
       </c>
       <c r="I150" t="n">
         <v>-18.97</v>
@@ -8395,7 +8409,7 @@
         <v>-26.82</v>
       </c>
       <c r="M150" t="n">
-        <v>-28.76</v>
+        <v>-28.68</v>
       </c>
       <c r="N150" t="b">
         <v>1</v>
@@ -8433,7 +8447,7 @@
         <v>-37.6</v>
       </c>
       <c r="H151" t="n">
-        <v>-3.91</v>
+        <v>-2.12</v>
       </c>
       <c r="I151" t="n">
         <v>15.2</v>
@@ -8446,7 +8460,7 @@
         <v>-10.3</v>
       </c>
       <c r="M151" t="n">
-        <v>-7.01</v>
+        <v>-5.13</v>
       </c>
       <c r="N151" t="b">
         <v>0</v>
@@ -8484,7 +8498,7 @@
         <v>53.8</v>
       </c>
       <c r="H152" t="n">
-        <v>45.38</v>
+        <v>46.28</v>
       </c>
       <c r="I152" t="n">
         <v>4.09</v>
@@ -8497,7 +8511,7 @@
         <v>-8.66</v>
       </c>
       <c r="M152" t="n">
-        <v>41.54</v>
+        <v>43.19</v>
       </c>
       <c r="N152" t="b">
         <v>0</v>
@@ -8539,7 +8553,7 @@
         <v>-5.7</v>
       </c>
       <c r="H153" t="n">
-        <v>46.61</v>
+        <v>37.7</v>
       </c>
       <c r="I153" t="n">
         <v>17.92</v>
@@ -8552,7 +8566,7 @@
         <v>-7.48</v>
       </c>
       <c r="M153" t="n">
-        <v>42.77</v>
+        <v>34.61</v>
       </c>
       <c r="N153" t="b">
         <v>0</v>
@@ -8590,7 +8604,7 @@
         <v>-39.3</v>
       </c>
       <c r="H154" t="n">
-        <v>-2.63</v>
+        <v>-5.91</v>
       </c>
       <c r="I154" t="n">
         <v>11.34</v>
@@ -8603,7 +8617,7 @@
         <v>-5.3</v>
       </c>
       <c r="M154" t="n">
-        <v>-6.47</v>
+        <v>-9.01</v>
       </c>
       <c r="N154" t="b">
         <v>0</v>
@@ -8641,7 +8655,7 @@
         <v>57</v>
       </c>
       <c r="H155" t="n">
-        <v>14.27</v>
+        <v>13.89</v>
       </c>
       <c r="I155" t="n">
         <v>-11.21</v>
@@ -8654,7 +8668,7 @@
         <v>-13.87</v>
       </c>
       <c r="M155" t="n">
-        <v>10.43</v>
+        <v>10.8</v>
       </c>
       <c r="N155" t="b">
         <v>1</v>
@@ -8692,7 +8706,7 @@
         <v>-21.8</v>
       </c>
       <c r="H156" t="n">
-        <v>10.31</v>
+        <v>8.43</v>
       </c>
       <c r="I156" t="n">
         <v>1.71</v>
@@ -8705,7 +8719,7 @@
         <v>-6.18</v>
       </c>
       <c r="M156" t="n">
-        <v>6.47</v>
+        <v>5.34</v>
       </c>
       <c r="N156" t="b">
         <v>1</v>
@@ -8743,7 +8757,7 @@
         <v>1</v>
       </c>
       <c r="H157" t="n">
-        <v>-33.75</v>
+        <v>-35.08</v>
       </c>
       <c r="I157" t="n">
         <v>-11.52</v>
@@ -8756,7 +8770,7 @@
         <v>-16.26</v>
       </c>
       <c r="M157" t="n">
-        <v>-37.64</v>
+        <v>-38.22</v>
       </c>
       <c r="N157" t="b">
         <v>1</v>
@@ -8794,7 +8808,7 @@
         <v>45.4</v>
       </c>
       <c r="H158" t="n">
-        <v>16.5</v>
+        <v>7.31</v>
       </c>
       <c r="I158" t="n">
         <v>-1.72</v>
@@ -8807,7 +8821,7 @@
         <v>-23.15</v>
       </c>
       <c r="M158" t="n">
-        <v>13.36</v>
+        <v>4.26</v>
       </c>
       <c r="N158" t="b">
         <v>1</v>
@@ -8845,7 +8859,7 @@
         <v>49.6</v>
       </c>
       <c r="H159" t="n">
-        <v>26.92</v>
+        <v>25.97</v>
       </c>
       <c r="I159" t="n">
         <v>6.34</v>
@@ -8858,7 +8872,7 @@
         <v>-20.75</v>
       </c>
       <c r="M159" t="n">
-        <v>23.78</v>
+        <v>22.92</v>
       </c>
       <c r="N159" t="b">
         <v>0</v>
@@ -8896,7 +8910,7 @@
         <v>55.3</v>
       </c>
       <c r="H160" t="n">
-        <v>-10.39</v>
+        <v>-14.82</v>
       </c>
       <c r="I160" t="n">
         <v>3.73</v>
@@ -8909,7 +8923,7 @@
         <v>-22.94</v>
       </c>
       <c r="M160" t="n">
-        <v>-13.53</v>
+        <v>-17.87</v>
       </c>
       <c r="N160" t="b">
         <v>0</v>
@@ -8947,7 +8961,7 @@
         <v>76.5</v>
       </c>
       <c r="H161" t="n">
-        <v>20.17</v>
+        <v>16.01</v>
       </c>
       <c r="I161" t="n">
         <v>-5.56</v>
@@ -8960,7 +8974,7 @@
         <v>-33.97</v>
       </c>
       <c r="M161" t="n">
-        <v>17.03</v>
+        <v>12.95</v>
       </c>
       <c r="N161" t="b">
         <v>1</v>
@@ -8998,7 +9012,7 @@
         <v>77.90000000000001</v>
       </c>
       <c r="H162" t="n">
-        <v>15.84</v>
+        <v>16.77</v>
       </c>
       <c r="I162" t="n">
         <v>-3.53</v>
@@ -9011,7 +9025,7 @@
         <v>-20.26</v>
       </c>
       <c r="M162" t="n">
-        <v>12.7</v>
+        <v>13.72</v>
       </c>
       <c r="N162" t="b">
         <v>0</v>
@@ -9049,7 +9063,7 @@
         <v>57.6</v>
       </c>
       <c r="H163" t="n">
-        <v>36.94</v>
+        <v>39.56</v>
       </c>
       <c r="I163" t="n">
         <v>14.81</v>
@@ -9062,7 +9076,7 @@
         <v>-5.11</v>
       </c>
       <c r="M163" t="n">
-        <v>33.81</v>
+        <v>36.5</v>
       </c>
       <c r="N163" t="b">
         <v>0</v>
@@ -9100,7 +9114,7 @@
         <v>32.1</v>
       </c>
       <c r="H164" t="n">
-        <v>17.38</v>
+        <v>26.12</v>
       </c>
       <c r="I164" t="n">
         <v>16.93</v>
@@ -9113,7 +9127,7 @@
         <v>-24.48</v>
       </c>
       <c r="M164" t="n">
-        <v>14.25</v>
+        <v>23.07</v>
       </c>
       <c r="N164" t="b">
         <v>1</v>
@@ -9151,7 +9165,7 @@
         <v>51.8</v>
       </c>
       <c r="H165" t="n">
-        <v>10.38</v>
+        <v>10.4</v>
       </c>
       <c r="I165" t="n">
         <v>10.75</v>
@@ -9164,7 +9178,7 @@
         <v>-25.09</v>
       </c>
       <c r="M165" t="n">
-        <v>7.24</v>
+        <v>7.34</v>
       </c>
       <c r="N165" t="b">
         <v>1</v>
@@ -9202,7 +9216,7 @@
         <v>32.3</v>
       </c>
       <c r="H166" t="n">
-        <v>-25.09</v>
+        <v>-24.84</v>
       </c>
       <c r="I166" t="n">
         <v>-20.76</v>
@@ -9215,7 +9229,7 @@
         <v>-27.91</v>
       </c>
       <c r="M166" t="n">
-        <v>-28.98</v>
+        <v>-27.98</v>
       </c>
       <c r="N166" t="b">
         <v>1</v>
@@ -9253,7 +9267,7 @@
         <v>15.7</v>
       </c>
       <c r="H167" t="n">
-        <v>-4.05</v>
+        <v>-4.25</v>
       </c>
       <c r="I167" t="n">
         <v>-0.87</v>
@@ -9266,7 +9280,7 @@
         <v>-29.01</v>
       </c>
       <c r="M167" t="n">
-        <v>-7.19</v>
+        <v>-7.31</v>
       </c>
       <c r="N167" t="b">
         <v>0</v>
@@ -9304,7 +9318,7 @@
         <v>63.7</v>
       </c>
       <c r="H168" t="n">
-        <v>6.93</v>
+        <v>4.85</v>
       </c>
       <c r="I168" t="n">
         <v>-2.16</v>
@@ -9317,7 +9331,7 @@
         <v>-19.1</v>
       </c>
       <c r="M168" t="n">
-        <v>3.04</v>
+        <v>1.71</v>
       </c>
       <c r="N168" t="b">
         <v>0</v>
@@ -9355,7 +9369,7 @@
         <v>3.7</v>
       </c>
       <c r="H169" t="n">
-        <v>-12.7</v>
+        <v>-9.960000000000001</v>
       </c>
       <c r="I169" t="n">
         <v>-1.11</v>
@@ -9368,7 +9382,7 @@
         <v>-25.46</v>
       </c>
       <c r="M169" t="n">
-        <v>-15.84</v>
+        <v>-13.02</v>
       </c>
       <c r="N169" t="b">
         <v>1</v>
@@ -9406,7 +9420,7 @@
         <v>42.4</v>
       </c>
       <c r="H170" t="n">
-        <v>11.93</v>
+        <v>12.21</v>
       </c>
       <c r="I170" t="n">
         <v>2.16</v>
@@ -9419,7 +9433,7 @@
         <v>-15.76</v>
       </c>
       <c r="M170" t="n">
-        <v>8.039999999999999</v>
+        <v>9.08</v>
       </c>
       <c r="N170" t="b">
         <v>1</v>
@@ -9457,7 +9471,7 @@
         <v>28.2</v>
       </c>
       <c r="H171" t="n">
-        <v>-11.19</v>
+        <v>-9.24</v>
       </c>
       <c r="I171" t="n">
         <v>-1.71</v>
@@ -9470,7 +9484,7 @@
         <v>-23.43</v>
       </c>
       <c r="M171" t="n">
-        <v>-14.33</v>
+        <v>-12.29</v>
       </c>
       <c r="N171" t="b">
         <v>1</v>
@@ -9508,7 +9522,7 @@
         <v>28.6</v>
       </c>
       <c r="H172" t="n">
-        <v>28.55</v>
+        <v>25.32</v>
       </c>
       <c r="I172" t="n">
         <v>2.81</v>
@@ -9521,7 +9535,7 @@
         <v>-18.87</v>
       </c>
       <c r="M172" t="n">
-        <v>24.66</v>
+        <v>22.18</v>
       </c>
       <c r="N172" t="b">
         <v>1</v>
@@ -9559,7 +9573,7 @@
         <v>89.09999999999999</v>
       </c>
       <c r="H173" t="n">
-        <v>39.37</v>
+        <v>35.87</v>
       </c>
       <c r="I173" t="n">
         <v>18.45</v>
@@ -9572,7 +9586,7 @@
         <v>-9.029999999999999</v>
       </c>
       <c r="M173" t="n">
-        <v>36.23</v>
+        <v>32.82</v>
       </c>
       <c r="N173" t="b">
         <v>0</v>
@@ -9610,7 +9624,7 @@
         <v>50.5</v>
       </c>
       <c r="H174" t="n">
-        <v>18.81</v>
+        <v>23.45</v>
       </c>
       <c r="I174" t="n">
         <v>-2.26</v>
@@ -9623,7 +9637,7 @@
         <v>-20.74</v>
       </c>
       <c r="M174" t="n">
-        <v>15.67</v>
+        <v>20.4</v>
       </c>
       <c r="N174" t="b">
         <v>0</v>
@@ -9661,7 +9675,7 @@
         <v>33.1</v>
       </c>
       <c r="H175" t="n">
-        <v>15.47</v>
+        <v>14.48</v>
       </c>
       <c r="I175" t="n">
         <v>4.68</v>
@@ -9674,7 +9688,7 @@
         <v>-26.7</v>
       </c>
       <c r="M175" t="n">
-        <v>12.33</v>
+        <v>11.43</v>
       </c>
       <c r="N175" t="b">
         <v>1</v>
@@ -9712,7 +9726,7 @@
         <v>46.3</v>
       </c>
       <c r="H176" t="n">
-        <v>-15.94</v>
+        <v>-15.96</v>
       </c>
       <c r="I176" t="n">
         <v>-3.24</v>
@@ -9725,7 +9739,7 @@
         <v>-22.77</v>
       </c>
       <c r="M176" t="n">
-        <v>-19.08</v>
+        <v>-19.02</v>
       </c>
       <c r="N176" t="b">
         <v>0</v>
@@ -9763,7 +9777,7 @@
         <v>-13.8</v>
       </c>
       <c r="H177" t="n">
-        <v>12.37</v>
+        <v>13.73</v>
       </c>
       <c r="I177" t="n">
         <v>6.03</v>
@@ -9776,7 +9790,7 @@
         <v>-13.77</v>
       </c>
       <c r="M177" t="n">
-        <v>8.48</v>
+        <v>10.59</v>
       </c>
       <c r="N177" t="b">
         <v>0</v>
@@ -9814,7 +9828,7 @@
         <v>21.8</v>
       </c>
       <c r="H178" t="n">
-        <v>-11.26</v>
+        <v>-10.44</v>
       </c>
       <c r="I178" t="n">
         <v>-6.34</v>
@@ -9827,7 +9841,7 @@
         <v>-30.04</v>
       </c>
       <c r="M178" t="n">
-        <v>-15.14</v>
+        <v>-13.58</v>
       </c>
       <c r="N178" t="b">
         <v>1</v>
@@ -9865,7 +9879,7 @@
         <v>40.3</v>
       </c>
       <c r="H179" t="n">
-        <v>-10.27</v>
+        <v>-10.19</v>
       </c>
       <c r="I179" t="n">
         <v>1.24</v>
@@ -9878,7 +9892,7 @@
         <v>-20.5</v>
       </c>
       <c r="M179" t="n">
-        <v>-14.16</v>
+        <v>-13.33</v>
       </c>
       <c r="N179" t="b">
         <v>1</v>
@@ -9916,7 +9930,7 @@
         <v>36.6</v>
       </c>
       <c r="H180" t="n">
-        <v>206.02</v>
+        <v>227.37</v>
       </c>
       <c r="I180" t="n">
         <v>-4.23</v>
@@ -9929,7 +9943,7 @@
         <v>-11.51</v>
       </c>
       <c r="M180" t="n">
-        <v>202.88</v>
+        <v>224.32</v>
       </c>
       <c r="N180" t="b">
         <v>0</v>
@@ -9967,7 +9981,7 @@
         <v>24.1</v>
       </c>
       <c r="H181" t="n">
-        <v>2.76</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="I181" t="n">
         <v>-1.6</v>
@@ -9980,7 +9994,7 @@
         <v>-22.54</v>
       </c>
       <c r="M181" t="n">
-        <v>-1.13</v>
+        <v>5.41</v>
       </c>
       <c r="N181" t="b">
         <v>1</v>
@@ -10018,7 +10032,7 @@
         <v>50.3</v>
       </c>
       <c r="H182" t="n">
-        <v>-2.1</v>
+        <v>-2.98</v>
       </c>
       <c r="I182" t="n">
         <v>-3.34</v>
@@ -10031,7 +10045,7 @@
         <v>-23.32</v>
       </c>
       <c r="M182" t="n">
-        <v>-5.99</v>
+        <v>-6.12</v>
       </c>
       <c r="N182" t="b">
         <v>0</v>
@@ -10069,7 +10083,7 @@
         <v>24.5</v>
       </c>
       <c r="H183" t="n">
-        <v>-28.71</v>
+        <v>-28.67</v>
       </c>
       <c r="I183" t="n">
         <v>-12.99</v>
@@ -10082,7 +10096,7 @@
         <v>-22.54</v>
       </c>
       <c r="M183" t="n">
-        <v>-32.6</v>
+        <v>-31.81</v>
       </c>
       <c r="N183" t="b">
         <v>1</v>
@@ -10120,7 +10134,7 @@
         <v>-4</v>
       </c>
       <c r="H184" t="n">
-        <v>11.81</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="I184" t="n">
         <v>-1.59</v>
@@ -10133,7 +10147,7 @@
         <v>-25.38</v>
       </c>
       <c r="M184" t="n">
-        <v>8.67</v>
+        <v>5.15</v>
       </c>
       <c r="N184" t="b">
         <v>0</v>
@@ -10171,7 +10185,7 @@
         <v>14.8</v>
       </c>
       <c r="H185" t="n">
-        <v>-33.3</v>
+        <v>-36.18</v>
       </c>
       <c r="I185" t="n">
         <v>-2.48</v>
@@ -10184,7 +10198,7 @@
         <v>-40.98</v>
       </c>
       <c r="M185" t="n">
-        <v>-37.19</v>
+        <v>-39.32</v>
       </c>
       <c r="N185" t="b">
         <v>0</v>
@@ -10222,7 +10236,7 @@
         <v>-27.6</v>
       </c>
       <c r="H186" t="n">
-        <v>8.779999999999999</v>
+        <v>12.06</v>
       </c>
       <c r="I186" t="n">
         <v>-0.36</v>
@@ -10235,7 +10249,7 @@
         <v>-19.41</v>
       </c>
       <c r="M186" t="n">
-        <v>5.64</v>
+        <v>9.01</v>
       </c>
       <c r="N186" t="b">
         <v>0</v>
@@ -10273,7 +10287,7 @@
         <v>9.1</v>
       </c>
       <c r="H187" t="n">
-        <v>-15.85</v>
+        <v>-16.16</v>
       </c>
       <c r="I187" t="n">
         <v>-2.83</v>
@@ -10286,7 +10300,7 @@
         <v>-23.78</v>
       </c>
       <c r="M187" t="n">
-        <v>-18.99</v>
+        <v>-19.22</v>
       </c>
       <c r="N187" t="b">
         <v>0</v>
@@ -10324,7 +10338,7 @@
         <v>11</v>
       </c>
       <c r="H188" t="n">
-        <v>-10.51</v>
+        <v>-9.869999999999999</v>
       </c>
       <c r="I188" t="n">
         <v>3.38</v>
@@ -10337,7 +10351,7 @@
         <v>-18.71</v>
       </c>
       <c r="M188" t="n">
-        <v>-14.4</v>
+        <v>-13.01</v>
       </c>
       <c r="N188" t="b">
         <v>0</v>
@@ -10375,7 +10389,7 @@
         <v>31.2</v>
       </c>
       <c r="H189" t="n">
-        <v>-14.61</v>
+        <v>-14.95</v>
       </c>
       <c r="I189" t="n">
         <v>-11.26</v>
@@ -10388,7 +10402,7 @@
         <v>-22.9</v>
       </c>
       <c r="M189" t="n">
-        <v>-18.5</v>
+        <v>-18.09</v>
       </c>
       <c r="N189" t="b">
         <v>0</v>
@@ -10426,7 +10440,7 @@
         <v>19.3</v>
       </c>
       <c r="H190" t="n">
-        <v>7.84</v>
+        <v>7.44</v>
       </c>
       <c r="I190" t="n">
         <v>11.79</v>
@@ -10439,7 +10453,7 @@
         <v>-16.62</v>
       </c>
       <c r="M190" t="n">
-        <v>3.95</v>
+        <v>4.3</v>
       </c>
       <c r="N190" t="b">
         <v>1</v>
@@ -10477,7 +10491,7 @@
         <v>-8.699999999999999</v>
       </c>
       <c r="H191" t="n">
-        <v>-10</v>
+        <v>-10.88</v>
       </c>
       <c r="I191" t="n">
         <v>17.25</v>
@@ -10490,7 +10504,7 @@
         <v>-4.65</v>
       </c>
       <c r="M191" t="n">
-        <v>-13.89</v>
+        <v>-14.02</v>
       </c>
       <c r="N191" t="b">
         <v>1</v>
@@ -10528,7 +10542,7 @@
         <v>15.2</v>
       </c>
       <c r="H192" t="n">
-        <v>-2.17</v>
+        <v>-5.42</v>
       </c>
       <c r="I192" t="n">
         <v>5.36</v>
@@ -10541,7 +10555,7 @@
         <v>-28.18</v>
       </c>
       <c r="M192" t="n">
-        <v>-5.31</v>
+        <v>-8.470000000000001</v>
       </c>
       <c r="N192" t="b">
         <v>1</v>
@@ -10579,7 +10593,7 @@
         <v>37.2</v>
       </c>
       <c r="H193" t="n">
-        <v>-24.28</v>
+        <v>-25.65</v>
       </c>
       <c r="I193" t="n">
         <v>-7.64</v>
@@ -10592,7 +10606,7 @@
         <v>-26.24</v>
       </c>
       <c r="M193" t="n">
-        <v>-28.17</v>
+        <v>-28.78</v>
       </c>
       <c r="N193" t="b">
         <v>1</v>
@@ -10634,7 +10648,7 @@
         <v>-0.5</v>
       </c>
       <c r="H194" t="n">
-        <v>29.35</v>
+        <v>29.08</v>
       </c>
       <c r="I194" t="n">
         <v>12.75</v>
@@ -10647,7 +10661,7 @@
         <v>-4.72</v>
       </c>
       <c r="M194" t="n">
-        <v>25.47</v>
+        <v>25.95</v>
       </c>
       <c r="N194" t="b">
         <v>0</v>
@@ -10685,7 +10699,7 @@
         <v>-27.9</v>
       </c>
       <c r="H195" t="n">
-        <v>-11.53</v>
+        <v>-14.3</v>
       </c>
       <c r="I195" t="n">
         <v>-5.72</v>
@@ -10698,7 +10712,7 @@
         <v>-11.08</v>
       </c>
       <c r="M195" t="n">
-        <v>-15.42</v>
+        <v>-17.44</v>
       </c>
       <c r="N195" t="b">
         <v>0</v>
@@ -10736,7 +10750,7 @@
         <v>29.8</v>
       </c>
       <c r="H196" t="n">
-        <v>27.51</v>
+        <v>31.4</v>
       </c>
       <c r="I196" t="n">
         <v>-2.74</v>
@@ -10749,7 +10763,7 @@
         <v>-22.36</v>
       </c>
       <c r="M196" t="n">
-        <v>23.62</v>
+        <v>28.26</v>
       </c>
       <c r="N196" t="b">
         <v>1</v>
@@ -10787,7 +10801,7 @@
         <v>60.9</v>
       </c>
       <c r="H197" t="n">
-        <v>4.23</v>
+        <v>5.51</v>
       </c>
       <c r="I197" t="n">
         <v>6.71</v>
@@ -10800,7 +10814,7 @@
         <v>-4.9</v>
       </c>
       <c r="M197" t="n">
-        <v>0.34</v>
+        <v>2.37</v>
       </c>
       <c r="N197" t="b">
         <v>0</v>
@@ -10838,7 +10852,7 @@
         <v>-13.4</v>
       </c>
       <c r="H198" t="n">
-        <v>-27.68</v>
+        <v>-22.21</v>
       </c>
       <c r="I198" t="n">
         <v>0.79</v>
@@ -10851,7 +10865,7 @@
         <v>-15.41</v>
       </c>
       <c r="M198" t="n">
-        <v>-30.82</v>
+        <v>-25.26</v>
       </c>
       <c r="N198" t="b">
         <v>0</v>
@@ -10889,7 +10903,7 @@
         <v>18.2</v>
       </c>
       <c r="H199" t="n">
-        <v>-18.62</v>
+        <v>-19.66</v>
       </c>
       <c r="I199" t="n">
         <v>-11.28</v>
@@ -10902,7 +10916,7 @@
         <v>-16.87</v>
       </c>
       <c r="M199" t="n">
-        <v>-22.5</v>
+        <v>-22.8</v>
       </c>
       <c r="N199" t="b">
         <v>0</v>
@@ -10940,7 +10954,7 @@
         <v>31.2</v>
       </c>
       <c r="H200" t="n">
-        <v>-6.35</v>
+        <v>-6.29</v>
       </c>
       <c r="I200" t="n">
         <v>-3.17</v>
@@ -10953,7 +10967,7 @@
         <v>-23.66</v>
       </c>
       <c r="M200" t="n">
-        <v>-9.49</v>
+        <v>-9.35</v>
       </c>
       <c r="N200" t="b">
         <v>0</v>
@@ -10991,7 +11005,7 @@
         <v>-1.3</v>
       </c>
       <c r="H201" t="n">
-        <v>-16.64</v>
+        <v>-17.27</v>
       </c>
       <c r="I201" t="n">
         <v>5.29</v>
@@ -11004,7 +11018,7 @@
         <v>-11.87</v>
       </c>
       <c r="M201" t="n">
-        <v>-19.78</v>
+        <v>-20.32</v>
       </c>
       <c r="N201" t="b">
         <v>0</v>
@@ -11042,7 +11056,7 @@
         <v>-29.8</v>
       </c>
       <c r="H202" t="n">
-        <v>69.84</v>
+        <v>70.12</v>
       </c>
       <c r="I202" t="n">
         <v>29.88</v>
@@ -11055,7 +11069,7 @@
         <v>-0.29</v>
       </c>
       <c r="M202" t="n">
-        <v>66.7</v>
+        <v>67.06999999999999</v>
       </c>
       <c r="N202" t="b">
         <v>0</v>
@@ -11093,7 +11107,7 @@
         <v>-22.4</v>
       </c>
       <c r="H203" t="n">
-        <v>-14.69</v>
+        <v>-14.03</v>
       </c>
       <c r="I203" t="n">
         <v>5.79</v>
@@ -11106,7 +11120,7 @@
         <v>-9.67</v>
       </c>
       <c r="M203" t="n">
-        <v>-18.58</v>
+        <v>-17.17</v>
       </c>
       <c r="N203" t="b">
         <v>0</v>
@@ -11144,7 +11158,7 @@
         <v>19.3</v>
       </c>
       <c r="H204" t="n">
-        <v>-20.34</v>
+        <v>-21.28</v>
       </c>
       <c r="I204" t="n">
         <v>-16.69</v>
@@ -11157,7 +11171,7 @@
         <v>-36.39</v>
       </c>
       <c r="M204" t="n">
-        <v>-24.23</v>
+        <v>-24.42</v>
       </c>
       <c r="N204" t="b">
         <v>1</v>
@@ -11195,7 +11209,7 @@
         <v>7.6</v>
       </c>
       <c r="H205" t="n">
-        <v>21.64</v>
+        <v>15.68</v>
       </c>
       <c r="I205" t="n">
         <v>6.22</v>
@@ -11208,7 +11222,7 @@
         <v>-10.68</v>
       </c>
       <c r="M205" t="n">
-        <v>18.5</v>
+        <v>12.62</v>
       </c>
       <c r="N205" t="b">
         <v>0</v>
@@ -11246,7 +11260,7 @@
         <v>68.8</v>
       </c>
       <c r="H206" t="n">
-        <v>16.85</v>
+        <v>19.63</v>
       </c>
       <c r="I206" t="n">
         <v>-1.41</v>
@@ -11259,7 +11273,7 @@
         <v>-19.39</v>
       </c>
       <c r="M206" t="n">
-        <v>13.71</v>
+        <v>16.58</v>
       </c>
       <c r="N206" t="b">
         <v>0</v>
@@ -11297,7 +11311,7 @@
         <v>8.5</v>
       </c>
       <c r="H207" t="n">
-        <v>-2.3</v>
+        <v>-3.65</v>
       </c>
       <c r="I207" t="n">
         <v>-4.26</v>
@@ -11310,7 +11324,7 @@
         <v>-23.85</v>
       </c>
       <c r="M207" t="n">
-        <v>-5.44</v>
+        <v>-6.7</v>
       </c>
       <c r="N207" t="b">
         <v>0</v>
@@ -11348,7 +11362,7 @@
         <v>-15.2</v>
       </c>
       <c r="H208" t="n">
-        <v>5.98</v>
+        <v>10.96</v>
       </c>
       <c r="I208" t="n">
         <v>12.27</v>
@@ -11361,7 +11375,7 @@
         <v>-12.27</v>
       </c>
       <c r="M208" t="n">
-        <v>2.85</v>
+        <v>7.9</v>
       </c>
       <c r="N208" t="b">
         <v>0</v>
@@ -11399,7 +11413,7 @@
         <v>-33.1</v>
       </c>
       <c r="H209" t="n">
-        <v>-29.82</v>
+        <v>-29.85</v>
       </c>
       <c r="I209" t="n">
         <v>-13.13</v>
@@ -11412,7 +11426,7 @@
         <v>-21.04</v>
       </c>
       <c r="M209" t="n">
-        <v>-33.7</v>
+        <v>-32.99</v>
       </c>
       <c r="N209" t="b">
         <v>0</v>
@@ -11450,7 +11464,7 @@
         <v>11.8</v>
       </c>
       <c r="H210" t="n">
-        <v>-0.28</v>
+        <v>3.01</v>
       </c>
       <c r="I210" t="n">
         <v>-1.19</v>
@@ -11463,7 +11477,7 @@
         <v>-17.57</v>
       </c>
       <c r="M210" t="n">
-        <v>-4.17</v>
+        <v>-0.13</v>
       </c>
       <c r="N210" t="b">
         <v>1</v>
@@ -11501,7 +11515,7 @@
         <v>27.5</v>
       </c>
       <c r="H211" t="n">
-        <v>18.32</v>
+        <v>6.64</v>
       </c>
       <c r="I211" t="n">
         <v>8.42</v>
@@ -11514,7 +11528,7 @@
         <v>-2.51</v>
       </c>
       <c r="M211" t="n">
-        <v>14.44</v>
+        <v>3.5</v>
       </c>
       <c r="N211" t="b">
         <v>1</v>
@@ -11552,7 +11566,7 @@
         <v>-22.4</v>
       </c>
       <c r="H212" t="n">
-        <v>-9.869999999999999</v>
+        <v>-9.81</v>
       </c>
       <c r="I212" t="n">
         <v>9.42</v>
@@ -11565,7 +11579,7 @@
         <v>-2.79</v>
       </c>
       <c r="M212" t="n">
-        <v>-13.75</v>
+        <v>-12.95</v>
       </c>
       <c r="N212" t="b">
         <v>1</v>
@@ -11603,7 +11617,7 @@
         <v>-14.7</v>
       </c>
       <c r="H213" t="n">
-        <v>-9.34</v>
+        <v>-12.35</v>
       </c>
       <c r="I213" t="n">
         <v>10.3</v>
@@ -11616,7 +11630,7 @@
         <v>-2.6</v>
       </c>
       <c r="M213" t="n">
-        <v>-13.23</v>
+        <v>-15.48</v>
       </c>
       <c r="N213" t="b">
         <v>1</v>
@@ -11658,7 +11672,7 @@
         <v>-9.300000000000001</v>
       </c>
       <c r="H214" t="n">
-        <v>-23.63</v>
+        <v>-24.23</v>
       </c>
       <c r="I214" t="n">
         <v>10.42</v>
@@ -11671,7 +11685,7 @@
         <v>-21.72</v>
       </c>
       <c r="M214" t="n">
-        <v>-27.52</v>
+        <v>-27.36</v>
       </c>
       <c r="N214" t="b">
         <v>1</v>
@@ -11709,7 +11723,7 @@
         <v>-13.5</v>
       </c>
       <c r="H215" t="n">
-        <v>108.85</v>
+        <v>106.2</v>
       </c>
       <c r="I215" t="n">
         <v>18.09</v>
@@ -11722,7 +11736,7 @@
         <v>-14.35</v>
       </c>
       <c r="M215" t="n">
-        <v>104.96</v>
+        <v>103.06</v>
       </c>
       <c r="N215" t="b">
         <v>0</v>
@@ -11760,7 +11774,7 @@
         <v>-27.5</v>
       </c>
       <c r="H216" t="n">
-        <v>-7.25</v>
+        <v>-7.55</v>
       </c>
       <c r="I216" t="n">
         <v>-29.95</v>
@@ -11773,7 +11787,7 @@
         <v>-35.86</v>
       </c>
       <c r="M216" t="n">
-        <v>-10.39</v>
+        <v>-10.61</v>
       </c>
       <c r="N216" t="b">
         <v>0</v>
@@ -11811,7 +11825,7 @@
         <v>11.9</v>
       </c>
       <c r="H217" t="n">
-        <v>-12.68</v>
+        <v>-13.87</v>
       </c>
       <c r="I217" t="n">
         <v>-3.02</v>
@@ -11824,7 +11838,7 @@
         <v>-24.96</v>
       </c>
       <c r="M217" t="n">
-        <v>-15.82</v>
+        <v>-16.93</v>
       </c>
       <c r="N217" t="b">
         <v>0</v>
@@ -11862,7 +11876,7 @@
         <v>5</v>
       </c>
       <c r="H218" t="n">
-        <v>-8.41</v>
+        <v>-9.039999999999999</v>
       </c>
       <c r="I218" t="n">
         <v>0.41</v>
@@ -11875,7 +11889,7 @@
         <v>-13.87</v>
       </c>
       <c r="M218" t="n">
-        <v>-12.3</v>
+        <v>-12.18</v>
       </c>
       <c r="N218" t="b">
         <v>0</v>
@@ -11913,7 +11927,7 @@
         <v>-35.9</v>
       </c>
       <c r="H219" t="n">
-        <v>17.71</v>
+        <v>13.62</v>
       </c>
       <c r="I219" t="n">
         <v>18.67</v>
@@ -11926,7 +11940,7 @@
         <v>-6.77</v>
       </c>
       <c r="M219" t="n">
-        <v>14.57</v>
+        <v>10.57</v>
       </c>
       <c r="N219" t="b">
         <v>0</v>
@@ -11964,7 +11978,7 @@
         <v>-25.2</v>
       </c>
       <c r="H220" t="n">
-        <v>15.86</v>
+        <v>20.17</v>
       </c>
       <c r="I220" t="n">
         <v>22.53</v>
@@ -11977,7 +11991,7 @@
         <v>-19.27</v>
       </c>
       <c r="M220" t="n">
-        <v>12.72</v>
+        <v>17.12</v>
       </c>
       <c r="N220" t="b">
         <v>1</v>
@@ -12015,7 +12029,7 @@
         <v>5.1</v>
       </c>
       <c r="H221" t="n">
-        <v>0.9</v>
+        <v>-0.02</v>
       </c>
       <c r="I221" t="n">
         <v>8.77</v>
@@ -12028,7 +12042,7 @@
         <v>-3.54</v>
       </c>
       <c r="M221" t="n">
-        <v>-2.99</v>
+        <v>-3.16</v>
       </c>
       <c r="N221" t="b">
         <v>1</v>
@@ -12066,7 +12080,7 @@
         <v>20.8</v>
       </c>
       <c r="H222" t="n">
-        <v>-17.89</v>
+        <v>-19.04</v>
       </c>
       <c r="I222" t="n">
         <v>-10.93</v>
@@ -12079,7 +12093,7 @@
         <v>-27.1</v>
       </c>
       <c r="M222" t="n">
-        <v>-21.78</v>
+        <v>-22.18</v>
       </c>
       <c r="N222" t="b">
         <v>0</v>
@@ -12117,7 +12131,7 @@
         <v>-27.7</v>
       </c>
       <c r="H223" t="n">
-        <v>18.01</v>
+        <v>18.66</v>
       </c>
       <c r="I223" t="n">
         <v>-10.22</v>
@@ -12130,7 +12144,7 @@
         <v>-17.14</v>
       </c>
       <c r="M223" t="n">
-        <v>14.87</v>
+        <v>15.6</v>
       </c>
       <c r="N223" t="b">
         <v>0</v>
@@ -12168,7 +12182,7 @@
         <v>-24.7</v>
       </c>
       <c r="H224" t="n">
-        <v>4.69</v>
+        <v>5.57</v>
       </c>
       <c r="I224" t="n">
         <v>1.65</v>
@@ -12181,7 +12195,7 @@
         <v>-19.04</v>
       </c>
       <c r="M224" t="n">
-        <v>1.55</v>
+        <v>2.51</v>
       </c>
       <c r="N224" t="b">
         <v>0</v>
@@ -12219,7 +12233,7 @@
         <v>-34.9</v>
       </c>
       <c r="H225" t="n">
-        <v>-8.66</v>
+        <v>-7.92</v>
       </c>
       <c r="I225" t="n">
         <v>19.9</v>
@@ -12232,7 +12246,7 @@
         <v>-12.62</v>
       </c>
       <c r="M225" t="n">
-        <v>-12.54</v>
+        <v>-11.06</v>
       </c>
       <c r="N225" t="b">
         <v>0</v>
@@ -12270,7 +12284,7 @@
         <v>-29.5</v>
       </c>
       <c r="H226" t="n">
-        <v>-5.34</v>
+        <v>-4.69</v>
       </c>
       <c r="I226" t="n">
         <v>4.05</v>
@@ -12283,7 +12297,7 @@
         <v>-2.43</v>
       </c>
       <c r="M226" t="n">
-        <v>-9.23</v>
+        <v>-7.83</v>
       </c>
       <c r="N226" t="b">
         <v>0</v>
@@ -12321,7 +12335,7 @@
         <v>34.2</v>
       </c>
       <c r="H227" t="n">
-        <v>7.74</v>
+        <v>7.98</v>
       </c>
       <c r="I227" t="n">
         <v>8.15</v>
@@ -12334,7 +12348,7 @@
         <v>-7.63</v>
       </c>
       <c r="M227" t="n">
-        <v>3.86</v>
+        <v>4.85</v>
       </c>
       <c r="N227" t="b">
         <v>1</v>
@@ -12372,7 +12386,7 @@
         <v>42</v>
       </c>
       <c r="H228" t="n">
-        <v>-30.27</v>
+        <v>-29.24</v>
       </c>
       <c r="I228" t="n">
         <v>0.6</v>
@@ -12385,7 +12399,7 @@
         <v>-16.67</v>
       </c>
       <c r="M228" t="n">
-        <v>-34.16</v>
+        <v>-32.38</v>
       </c>
       <c r="N228" t="b">
         <v>1</v>
@@ -12427,7 +12441,7 @@
         <v>-0.4</v>
       </c>
       <c r="H229" t="n">
-        <v>-14.41</v>
+        <v>-15.52</v>
       </c>
       <c r="I229" t="n">
         <v>4.83</v>
@@ -12440,7 +12454,7 @@
         <v>-10.75</v>
       </c>
       <c r="M229" t="n">
-        <v>-18.3</v>
+        <v>-18.66</v>
       </c>
       <c r="N229" t="b">
         <v>0</v>
@@ -12478,7 +12492,7 @@
         <v>64.59999999999999</v>
       </c>
       <c r="H230" t="n">
-        <v>9.4</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="I230" t="n">
         <v>3.01</v>
@@ -12491,7 +12505,7 @@
         <v>-12</v>
       </c>
       <c r="M230" t="n">
-        <v>5.51</v>
+        <v>6.22</v>
       </c>
       <c r="N230" t="b">
         <v>0</v>
@@ -12529,7 +12543,7 @@
         <v>-25.3</v>
       </c>
       <c r="H231" t="n">
-        <v>30.77</v>
+        <v>31.36</v>
       </c>
       <c r="I231" t="n">
         <v>36.1</v>
@@ -12542,7 +12556,7 @@
         <v>-5.66</v>
       </c>
       <c r="M231" t="n">
-        <v>26.89</v>
+        <v>28.22</v>
       </c>
       <c r="N231" t="b">
         <v>1</v>
@@ -12580,7 +12594,7 @@
         <v>-7.7</v>
       </c>
       <c r="H232" t="n">
-        <v>-3.75</v>
+        <v>-2.74</v>
       </c>
       <c r="I232" t="n">
         <v>-6.47</v>
@@ -12593,7 +12607,7 @@
         <v>-23.05</v>
       </c>
       <c r="M232" t="n">
-        <v>-7.64</v>
+        <v>-5.88</v>
       </c>
       <c r="N232" t="b">
         <v>1</v>
@@ -12631,7 +12645,7 @@
         <v>-2.9</v>
       </c>
       <c r="H233" t="n">
-        <v>4.56</v>
+        <v>1.77</v>
       </c>
       <c r="I233" t="n">
         <v>-1.47</v>
@@ -12644,7 +12658,7 @@
         <v>-7.7</v>
       </c>
       <c r="M233" t="n">
-        <v>0.67</v>
+        <v>-1.36</v>
       </c>
       <c r="N233" t="b">
         <v>0</v>
@@ -12682,7 +12696,7 @@
         <v>13.7</v>
       </c>
       <c r="H234" t="n">
-        <v>7.27</v>
+        <v>5.64</v>
       </c>
       <c r="I234" t="n">
         <v>2.74</v>
@@ -12695,7 +12709,7 @@
         <v>-24.02</v>
       </c>
       <c r="M234" t="n">
-        <v>3.38</v>
+        <v>2.5</v>
       </c>
       <c r="N234" t="b">
         <v>1</v>
@@ -12733,7 +12747,7 @@
         <v>21.8</v>
       </c>
       <c r="H235" t="n">
-        <v>-0.49</v>
+        <v>-0.25</v>
       </c>
       <c r="I235" t="n">
         <v>18.32</v>
@@ -12746,7 +12760,7 @@
         <v>-23.27</v>
       </c>
       <c r="M235" t="n">
-        <v>-4.38</v>
+        <v>-3.39</v>
       </c>
       <c r="N235" t="b">
         <v>1</v>
@@ -12784,7 +12798,7 @@
         <v>29.4</v>
       </c>
       <c r="H236" t="n">
-        <v>-4.41</v>
+        <v>-5.28</v>
       </c>
       <c r="I236" t="n">
         <v>-2.62</v>
@@ -12797,7 +12811,7 @@
         <v>-27.18</v>
       </c>
       <c r="M236" t="n">
-        <v>-8.300000000000001</v>
+        <v>-8.42</v>
       </c>
       <c r="N236" t="b">
         <v>1</v>
@@ -12835,7 +12849,7 @@
         <v>-3.7</v>
       </c>
       <c r="H237" t="n">
-        <v>-24.58</v>
+        <v>-24.34</v>
       </c>
       <c r="I237" t="n">
         <v>-8.07</v>
@@ -12848,7 +12862,7 @@
         <v>-22.12</v>
       </c>
       <c r="M237" t="n">
-        <v>-28.46</v>
+        <v>-27.48</v>
       </c>
       <c r="N237" t="b">
         <v>1</v>
@@ -12886,7 +12900,7 @@
         <v>21.3</v>
       </c>
       <c r="H238" t="n">
-        <v>1.54</v>
+        <v>1.6</v>
       </c>
       <c r="I238" t="n">
         <v>0.23</v>
@@ -12899,7 +12913,7 @@
         <v>-0.85</v>
       </c>
       <c r="M238" t="n">
-        <v>-2.35</v>
+        <v>-1.54</v>
       </c>
       <c r="N238" t="b">
         <v>1</v>
@@ -12937,7 +12951,7 @@
         <v>-21.4</v>
       </c>
       <c r="H239" t="n">
-        <v>24.14</v>
+        <v>21.9</v>
       </c>
       <c r="I239" t="n">
         <v>4.55</v>
@@ -12950,7 +12964,7 @@
         <v>-6.39</v>
       </c>
       <c r="M239" t="n">
-        <v>21</v>
+        <v>18.84</v>
       </c>
       <c r="N239" t="b">
         <v>1</v>
@@ -12988,7 +13002,7 @@
         <v>16.3</v>
       </c>
       <c r="H240" t="n">
-        <v>5.89</v>
+        <v>5.88</v>
       </c>
       <c r="I240" t="n">
         <v>-1</v>
@@ -13001,7 +13015,7 @@
         <v>-22.5</v>
       </c>
       <c r="M240" t="n">
-        <v>2</v>
+        <v>2.74</v>
       </c>
       <c r="N240" t="b">
         <v>1</v>
@@ -13039,7 +13053,7 @@
         <v>11.9</v>
       </c>
       <c r="H241" t="n">
-        <v>-2.14</v>
+        <v>-1.52</v>
       </c>
       <c r="I241" t="n">
         <v>7.74</v>
@@ -13052,7 +13066,7 @@
         <v>-9.43</v>
       </c>
       <c r="M241" t="n">
-        <v>-6.02</v>
+        <v>-4.66</v>
       </c>
       <c r="N241" t="b">
         <v>1</v>
@@ -13090,7 +13104,7 @@
         <v>19.4</v>
       </c>
       <c r="H242" t="n">
-        <v>-2</v>
+        <v>-1.62</v>
       </c>
       <c r="I242" t="n">
         <v>10.89</v>
@@ -13103,7 +13117,7 @@
         <v>-2.97</v>
       </c>
       <c r="M242" t="n">
-        <v>-5.89</v>
+        <v>-4.76</v>
       </c>
       <c r="N242" t="b">
         <v>0</v>
@@ -13141,7 +13155,7 @@
         <v>66.7</v>
       </c>
       <c r="H243" t="n">
-        <v>12.55</v>
+        <v>11.58</v>
       </c>
       <c r="I243" t="n">
         <v>4.84</v>
@@ -13154,7 +13168,7 @@
         <v>-11.7</v>
       </c>
       <c r="M243" t="n">
-        <v>8.66</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="N243" t="b">
         <v>0</v>
@@ -13192,7 +13206,7 @@
         <v>3.7</v>
       </c>
       <c r="H244" t="n">
-        <v>13.55</v>
+        <v>10.23</v>
       </c>
       <c r="I244" t="n">
         <v>11.13</v>
@@ -13205,7 +13219,7 @@
         <v>-2.79</v>
       </c>
       <c r="M244" t="n">
-        <v>9.66</v>
+        <v>7.09</v>
       </c>
       <c r="N244" t="b">
         <v>0</v>
@@ -13243,7 +13257,7 @@
         <v>36.8</v>
       </c>
       <c r="H245" t="n">
-        <v>19.02</v>
+        <v>19.58</v>
       </c>
       <c r="I245" t="n">
         <v>15.47</v>
@@ -13256,7 +13270,7 @@
         <v>-0.96</v>
       </c>
       <c r="M245" t="n">
-        <v>15.14</v>
+        <v>16.44</v>
       </c>
       <c r="N245" t="b">
         <v>0</v>
@@ -13294,7 +13308,7 @@
         <v>0.2</v>
       </c>
       <c r="H246" t="n">
-        <v>10.27</v>
+        <v>9.23</v>
       </c>
       <c r="I246" t="n">
         <v>4.35</v>
@@ -13307,7 +13321,7 @@
         <v>-2.79</v>
       </c>
       <c r="M246" t="n">
-        <v>6.38</v>
+        <v>6.09</v>
       </c>
       <c r="N246" t="b">
         <v>1</v>
@@ -13345,7 +13359,7 @@
         <v>-31</v>
       </c>
       <c r="H247" t="n">
-        <v>1.87</v>
+        <v>3.7</v>
       </c>
       <c r="I247" t="n">
         <v>19.41</v>
@@ -13358,7 +13372,7 @@
         <v>-10.33</v>
       </c>
       <c r="M247" t="n">
-        <v>-1.27</v>
+        <v>0.65</v>
       </c>
       <c r="N247" t="b">
         <v>0</v>
@@ -13400,7 +13414,7 @@
         <v>-2</v>
       </c>
       <c r="H248" t="n">
-        <v>-17.34</v>
+        <v>-16.13</v>
       </c>
       <c r="I248" t="n">
         <v>14.61</v>
@@ -13413,7 +13427,7 @@
         <v>-3.45</v>
       </c>
       <c r="M248" t="n">
-        <v>-21.23</v>
+        <v>-19.27</v>
       </c>
       <c r="N248" t="b">
         <v>0</v>
@@ -13451,7 +13465,7 @@
         <v>12.2</v>
       </c>
       <c r="H249" t="n">
-        <v>-41.95</v>
+        <v>-38.48</v>
       </c>
       <c r="I249" t="n">
         <v>3.47</v>
@@ -13464,7 +13478,7 @@
         <v>-27.15</v>
       </c>
       <c r="M249" t="n">
-        <v>-45.84</v>
+        <v>-41.62</v>
       </c>
       <c r="N249" t="b">
         <v>0</v>
@@ -13502,7 +13516,7 @@
         <v>8.4</v>
       </c>
       <c r="H250" t="n">
-        <v>-32.4</v>
+        <v>-34.53</v>
       </c>
       <c r="I250" t="n">
         <v>-0.13</v>
@@ -13515,7 +13529,7 @@
         <v>-10.87</v>
       </c>
       <c r="M250" t="n">
-        <v>-36.29</v>
+        <v>-37.67</v>
       </c>
       <c r="N250" t="b">
         <v>1</v>
@@ -13553,7 +13567,7 @@
         <v>-21.7</v>
       </c>
       <c r="H251" t="n">
-        <v>-0.64</v>
+        <v>-3.67</v>
       </c>
       <c r="I251" t="n">
         <v>5.5</v>
@@ -13566,7 +13580,7 @@
         <v>-4.3</v>
       </c>
       <c r="M251" t="n">
-        <v>-4.53</v>
+        <v>-6.8</v>
       </c>
       <c r="N251" t="b">
         <v>0</v>
@@ -13604,7 +13618,7 @@
         <v>-7.3</v>
       </c>
       <c r="H252" t="n">
-        <v>-20.32</v>
+        <v>-22.11</v>
       </c>
       <c r="I252" t="n">
         <v>-4.12</v>
@@ -13617,7 +13631,7 @@
         <v>-15.02</v>
       </c>
       <c r="M252" t="n">
-        <v>-24.2</v>
+        <v>-25.25</v>
       </c>
       <c r="N252" t="b">
         <v>1</v>
@@ -13655,7 +13669,7 @@
         <v>-26.1</v>
       </c>
       <c r="H253" t="n">
-        <v>-17.55</v>
+        <v>-18.77</v>
       </c>
       <c r="I253" t="n">
         <v>5.05</v>
@@ -13668,7 +13682,7 @@
         <v>-9.27</v>
       </c>
       <c r="M253" t="n">
-        <v>-21.43</v>
+        <v>-21.91</v>
       </c>
       <c r="N253" t="b">
         <v>1</v>
@@ -13706,7 +13720,7 @@
         <v>-18.5</v>
       </c>
       <c r="H254" t="n">
-        <v>38.49</v>
+        <v>35.54</v>
       </c>
       <c r="I254" t="n">
         <v>16.22</v>
@@ -13719,7 +13733,7 @@
         <v>-9.960000000000001</v>
       </c>
       <c r="M254" t="n">
-        <v>35.36</v>
+        <v>32.49</v>
       </c>
       <c r="N254" t="b">
         <v>0</v>
@@ -13757,7 +13771,7 @@
         <v>15.3</v>
       </c>
       <c r="H255" t="n">
-        <v>-37.08</v>
+        <v>-38.69</v>
       </c>
       <c r="I255" t="n">
         <v>-21.4</v>
@@ -13770,7 +13784,7 @@
         <v>-26.97</v>
       </c>
       <c r="M255" t="n">
-        <v>-40.97</v>
+        <v>-41.83</v>
       </c>
       <c r="N255" t="b">
         <v>0</v>
@@ -13808,7 +13822,7 @@
         <v>26.1</v>
       </c>
       <c r="H256" t="n">
-        <v>-8.859999999999999</v>
+        <v>-7.88</v>
       </c>
       <c r="I256" t="n">
         <v>-0.51</v>
@@ -13821,7 +13835,7 @@
         <v>-16.45</v>
       </c>
       <c r="M256" t="n">
-        <v>-12.75</v>
+        <v>-11.02</v>
       </c>
       <c r="N256" t="b">
         <v>1</v>
@@ -13863,7 +13877,7 @@
         <v>-8.199999999999999</v>
       </c>
       <c r="H257" t="n">
-        <v>-8.44</v>
+        <v>-9.32</v>
       </c>
       <c r="I257" t="n">
         <v>17.48</v>
@@ -13876,7 +13890,7 @@
         <v>-10.68</v>
       </c>
       <c r="M257" t="n">
-        <v>-12.32</v>
+        <v>-12.46</v>
       </c>
       <c r="N257" t="b">
         <v>0</v>
@@ -13914,7 +13928,7 @@
         <v>17.9</v>
       </c>
       <c r="H258" t="n">
-        <v>2.5</v>
+        <v>2.19</v>
       </c>
       <c r="I258" t="n">
         <v>12.97</v>
@@ -13927,7 +13941,7 @@
         <v>-8.130000000000001</v>
       </c>
       <c r="M258" t="n">
-        <v>-1.39</v>
+        <v>-0.95</v>
       </c>
       <c r="N258" t="b">
         <v>1</v>
@@ -13965,7 +13979,7 @@
         <v>0.7</v>
       </c>
       <c r="H259" t="n">
-        <v>-14.69</v>
+        <v>-15.75</v>
       </c>
       <c r="I259" t="n">
         <v>14.96</v>
@@ -13978,7 +13992,7 @@
         <v>-8.039999999999999</v>
       </c>
       <c r="M259" t="n">
-        <v>-18.58</v>
+        <v>-18.89</v>
       </c>
       <c r="N259" t="b">
         <v>1</v>
@@ -14016,7 +14030,7 @@
         <v>61.6</v>
       </c>
       <c r="H260" t="n">
-        <v>-2.71</v>
+        <v>-0.61</v>
       </c>
       <c r="I260" t="n">
         <v>11.47</v>
@@ -14029,7 +14043,7 @@
         <v>-12.86</v>
       </c>
       <c r="M260" t="n">
-        <v>-6.6</v>
+        <v>-3.75</v>
       </c>
       <c r="N260" t="b">
         <v>0</v>
@@ -14067,7 +14081,7 @@
         <v>54.3</v>
       </c>
       <c r="H261" t="n">
-        <v>-21.97</v>
+        <v>-25.58</v>
       </c>
       <c r="I261" t="n">
         <v>-2.86</v>
@@ -14080,7 +14094,7 @@
         <v>-24.93</v>
       </c>
       <c r="M261" t="n">
-        <v>-25.86</v>
+        <v>-28.72</v>
       </c>
       <c r="N261" t="b">
         <v>0</v>
@@ -14118,7 +14132,7 @@
         <v>14.8</v>
       </c>
       <c r="H262" t="n">
-        <v>-3.36</v>
+        <v>-6.66</v>
       </c>
       <c r="I262" t="n">
         <v>0.35</v>
@@ -14131,7 +14145,7 @@
         <v>-3.68</v>
       </c>
       <c r="M262" t="n">
-        <v>-7.24</v>
+        <v>-9.800000000000001</v>
       </c>
       <c r="N262" t="b">
         <v>1</v>
@@ -14169,7 +14183,7 @@
         <v>-13.5</v>
       </c>
       <c r="H263" t="n">
-        <v>-11.69</v>
+        <v>-11.6</v>
       </c>
       <c r="I263" t="n">
         <v>-1.88</v>
@@ -14182,7 +14196,7 @@
         <v>-11.4</v>
       </c>
       <c r="M263" t="n">
-        <v>-14.83</v>
+        <v>-14.66</v>
       </c>
       <c r="N263" t="b">
         <v>0</v>
@@ -14220,7 +14234,7 @@
         <v>25.5</v>
       </c>
       <c r="H264" t="n">
-        <v>2.52</v>
+        <v>2.91</v>
       </c>
       <c r="I264" t="n">
         <v>-9.369999999999999</v>
@@ -14233,7 +14247,7 @@
         <v>-22.11</v>
       </c>
       <c r="M264" t="n">
-        <v>-1.37</v>
+        <v>-0.23</v>
       </c>
       <c r="N264" t="b">
         <v>1</v>
@@ -14275,7 +14289,7 @@
         <v>-7.5</v>
       </c>
       <c r="H265" t="n">
-        <v>-3.18</v>
+        <v>-5.58</v>
       </c>
       <c r="I265" t="n">
         <v>4.46</v>
@@ -14288,7 +14302,7 @@
         <v>-8.52</v>
       </c>
       <c r="M265" t="n">
-        <v>-7.07</v>
+        <v>-8.720000000000001</v>
       </c>
       <c r="N265" t="b">
         <v>1</v>
@@ -14326,7 +14340,7 @@
         <v>1.5</v>
       </c>
       <c r="H266" t="n">
-        <v>13.01</v>
+        <v>11.3</v>
       </c>
       <c r="I266" t="n">
         <v>-7.31</v>
@@ -14339,7 +14353,7 @@
         <v>-18.58</v>
       </c>
       <c r="M266" t="n">
-        <v>9.869999999999999</v>
+        <v>8.24</v>
       </c>
       <c r="N266" t="b">
         <v>0</v>
@@ -14377,7 +14391,7 @@
         <v>-11</v>
       </c>
       <c r="H267" t="n">
-        <v>5.58</v>
+        <v>4.27</v>
       </c>
       <c r="I267" t="n">
         <v>10.7</v>
@@ -14390,7 +14404,7 @@
         <v>-9.43</v>
       </c>
       <c r="M267" t="n">
-        <v>1.69</v>
+        <v>1.14</v>
       </c>
       <c r="N267" t="b">
         <v>1</v>
@@ -14428,7 +14442,7 @@
         <v>-11.4</v>
       </c>
       <c r="H268" t="n">
-        <v>-10.82</v>
+        <v>-12.98</v>
       </c>
       <c r="I268" t="n">
         <v>4.36</v>
@@ -14441,7 +14455,7 @@
         <v>-11.36</v>
       </c>
       <c r="M268" t="n">
-        <v>-14.71</v>
+        <v>-16.12</v>
       </c>
       <c r="N268" t="b">
         <v>1</v>
@@ -14479,7 +14493,7 @@
         <v>2.1</v>
       </c>
       <c r="H269" t="n">
-        <v>52.91</v>
+        <v>52.31</v>
       </c>
       <c r="I269" t="n">
         <v>20.72</v>
@@ -14492,7 +14506,7 @@
         <v>-5.79</v>
       </c>
       <c r="M269" t="n">
-        <v>49.02</v>
+        <v>49.17</v>
       </c>
       <c r="N269" t="b">
         <v>0</v>
@@ -14530,7 +14544,7 @@
         <v>27.1</v>
       </c>
       <c r="H270" t="n">
-        <v>-7.41</v>
+        <v>-6.99</v>
       </c>
       <c r="I270" t="n">
         <v>5.02</v>
@@ -14543,7 +14557,7 @@
         <v>-14.35</v>
       </c>
       <c r="M270" t="n">
-        <v>-11.3</v>
+        <v>-10.13</v>
       </c>
       <c r="N270" t="b">
         <v>1</v>
@@ -14581,7 +14595,7 @@
         <v>-21.6</v>
       </c>
       <c r="H271" t="n">
-        <v>-4.61</v>
+        <v>-9</v>
       </c>
       <c r="I271" t="n">
         <v>1.22</v>
@@ -14594,7 +14608,7 @@
         <v>-6.54</v>
       </c>
       <c r="M271" t="n">
-        <v>-8.5</v>
+        <v>-12.14</v>
       </c>
       <c r="N271" t="b">
         <v>0</v>
@@ -14636,7 +14650,7 @@
         <v>-2.2</v>
       </c>
       <c r="H272" t="n">
-        <v>19.34</v>
+        <v>17.51</v>
       </c>
       <c r="I272" t="n">
         <v>-9.050000000000001</v>
@@ -14649,7 +14663,7 @@
         <v>-18.61</v>
       </c>
       <c r="M272" t="n">
-        <v>16.2</v>
+        <v>14.46</v>
       </c>
       <c r="N272" t="b">
         <v>0</v>
@@ -14687,7 +14701,7 @@
         <v>0.7</v>
       </c>
       <c r="H273" t="n">
-        <v>-1.78</v>
+        <v>-0.79</v>
       </c>
       <c r="I273" t="n">
         <v>11.4</v>
@@ -14700,7 +14714,7 @@
         <v>-7.28</v>
       </c>
       <c r="M273" t="n">
-        <v>-5.67</v>
+        <v>-3.93</v>
       </c>
       <c r="N273" t="b">
         <v>0</v>
@@ -14738,7 +14752,7 @@
         <v>-31.7</v>
       </c>
       <c r="H274" t="n">
-        <v>3.34</v>
+        <v>1.54</v>
       </c>
       <c r="I274" t="n">
         <v>17.04</v>
@@ -14751,7 +14765,7 @@
         <v>-4.05</v>
       </c>
       <c r="M274" t="n">
-        <v>-0.55</v>
+        <v>-1.6</v>
       </c>
       <c r="N274" t="b">
         <v>0</v>
@@ -14789,7 +14803,7 @@
         <v>32.2</v>
       </c>
       <c r="H275" t="n">
-        <v>16.88</v>
+        <v>16.6</v>
       </c>
       <c r="I275" t="n">
         <v>6.49</v>
@@ -14802,7 +14816,7 @@
         <v>-3.92</v>
       </c>
       <c r="M275" t="n">
-        <v>12.99</v>
+        <v>13.46</v>
       </c>
       <c r="N275" t="b">
         <v>1</v>
@@ -14891,7 +14905,7 @@
         <v>3.2</v>
       </c>
       <c r="H277" t="n">
-        <v>-22.68</v>
+        <v>-20.88</v>
       </c>
       <c r="I277" t="n">
         <v>-10.41</v>
@@ -14904,7 +14918,7 @@
         <v>-23.7</v>
       </c>
       <c r="M277" t="n">
-        <v>-26.56</v>
+        <v>-24.02</v>
       </c>
       <c r="N277" t="b">
         <v>1</v>
@@ -14942,7 +14956,7 @@
         <v>7.3</v>
       </c>
       <c r="H278" t="n">
-        <v>-1.42</v>
+        <v>-1.07</v>
       </c>
       <c r="I278" t="n">
         <v>-0.57</v>
@@ -14955,7 +14969,7 @@
         <v>-5.89</v>
       </c>
       <c r="M278" t="n">
-        <v>-5.3</v>
+        <v>-4.21</v>
       </c>
       <c r="N278" t="b">
         <v>1</v>
@@ -14993,7 +15007,7 @@
         <v>24.5</v>
       </c>
       <c r="H279" t="n">
-        <v>5.66</v>
+        <v>6.08</v>
       </c>
       <c r="I279" t="n">
         <v>17.24</v>
@@ -15006,7 +15020,7 @@
         <v>-0.47</v>
       </c>
       <c r="M279" t="n">
-        <v>1.77</v>
+        <v>2.94</v>
       </c>
       <c r="N279" t="b">
         <v>0</v>
@@ -15044,7 +15058,7 @@
         <v>-0.3</v>
       </c>
       <c r="H280" t="n">
-        <v>-3.58</v>
+        <v>-4.06</v>
       </c>
       <c r="I280" t="n">
         <v>17.76</v>
@@ -15057,7 +15071,7 @@
         <v>-14.18</v>
       </c>
       <c r="M280" t="n">
-        <v>-7.47</v>
+        <v>-7.2</v>
       </c>
       <c r="N280" t="b">
         <v>1</v>
@@ -15095,7 +15109,7 @@
         <v>4</v>
       </c>
       <c r="H281" t="n">
-        <v>46.1</v>
+        <v>44.94</v>
       </c>
       <c r="I281" t="n">
         <v>8.75</v>
@@ -15108,7 +15122,7 @@
         <v>-11.02</v>
       </c>
       <c r="M281" t="n">
-        <v>42.21</v>
+        <v>41.8</v>
       </c>
       <c r="N281" t="b">
         <v>0</v>
@@ -15146,7 +15160,7 @@
         <v>-6.8</v>
       </c>
       <c r="H282" t="n">
-        <v>48.27</v>
+        <v>42.36</v>
       </c>
       <c r="I282" t="n">
         <v>8.279999999999999</v>
@@ -15159,7 +15173,7 @@
         <v>-6.78</v>
       </c>
       <c r="M282" t="n">
-        <v>44.38</v>
+        <v>39.22</v>
       </c>
       <c r="N282" t="b">
         <v>1</v>
@@ -15197,7 +15211,7 @@
         <v>-42</v>
       </c>
       <c r="H283" t="n">
-        <v>60.1</v>
+        <v>59.52</v>
       </c>
       <c r="I283" t="n">
         <v>-3.61</v>
@@ -15210,7 +15224,7 @@
         <v>-11.94</v>
       </c>
       <c r="M283" t="n">
-        <v>56.96</v>
+        <v>56.47</v>
       </c>
       <c r="N283" t="b">
         <v>0</v>
@@ -15248,7 +15262,7 @@
         <v>14.6</v>
       </c>
       <c r="H284" t="n">
-        <v>-0.5600000000000001</v>
+        <v>0.79</v>
       </c>
       <c r="I284" t="n">
         <v>8.539999999999999</v>
@@ -15261,7 +15275,7 @@
         <v>-13.21</v>
       </c>
       <c r="M284" t="n">
-        <v>-4.45</v>
+        <v>-2.35</v>
       </c>
       <c r="N284" t="b">
         <v>0</v>
@@ -15299,7 +15313,7 @@
         <v>34.6</v>
       </c>
       <c r="H285" t="n">
-        <v>-2.73</v>
+        <v>-1.66</v>
       </c>
       <c r="I285" t="n">
         <v>5.7</v>
@@ -15312,7 +15326,7 @@
         <v>-7.7</v>
       </c>
       <c r="M285" t="n">
-        <v>-6.62</v>
+        <v>-4.8</v>
       </c>
       <c r="N285" t="b">
         <v>1</v>
@@ -15350,7 +15364,7 @@
         <v>-37.2</v>
       </c>
       <c r="H286" t="n">
-        <v>9.92</v>
+        <v>11.14</v>
       </c>
       <c r="I286" t="n">
         <v>21.67</v>
@@ -15363,7 +15377,7 @@
         <v>-6.64</v>
       </c>
       <c r="M286" t="n">
-        <v>6.04</v>
+        <v>8</v>
       </c>
       <c r="N286" t="b">
         <v>0</v>
@@ -15401,7 +15415,7 @@
         <v>-31.2</v>
       </c>
       <c r="H287" t="n">
-        <v>-17.33</v>
+        <v>-21.18</v>
       </c>
       <c r="I287" t="n">
         <v>1.03</v>
@@ -15414,7 +15428,7 @@
         <v>-13.65</v>
       </c>
       <c r="M287" t="n">
-        <v>-21.21</v>
+        <v>-24.32</v>
       </c>
       <c r="N287" t="b">
         <v>0</v>
@@ -15452,7 +15466,7 @@
         <v>10.4</v>
       </c>
       <c r="H288" t="n">
-        <v>25.82</v>
+        <v>23.85</v>
       </c>
       <c r="I288" t="n">
         <v>11.05</v>
@@ -15465,7 +15479,7 @@
         <v>-5.54</v>
       </c>
       <c r="M288" t="n">
-        <v>21.93</v>
+        <v>20.71</v>
       </c>
       <c r="N288" t="b">
         <v>1</v>
@@ -15503,7 +15517,7 @@
         <v>-14.7</v>
       </c>
       <c r="H289" t="n">
-        <v>18.66</v>
+        <v>18.54</v>
       </c>
       <c r="I289" t="n">
         <v>12.94</v>
@@ -15516,7 +15530,7 @@
         <v>-2.34</v>
       </c>
       <c r="M289" t="n">
-        <v>14.78</v>
+        <v>15.4</v>
       </c>
       <c r="N289" t="b">
         <v>0</v>
@@ -15554,7 +15568,7 @@
         <v>-21.5</v>
       </c>
       <c r="H290" t="n">
-        <v>-14.83</v>
+        <v>-15.89</v>
       </c>
       <c r="I290" t="n">
         <v>10.65</v>
@@ -15567,7 +15581,7 @@
         <v>-6.89</v>
       </c>
       <c r="M290" t="n">
-        <v>-17.97</v>
+        <v>-18.94</v>
       </c>
       <c r="N290" t="b">
         <v>1</v>
@@ -15605,7 +15619,7 @@
         <v>20.2</v>
       </c>
       <c r="H291" t="n">
-        <v>-8.5</v>
+        <v>-9.27</v>
       </c>
       <c r="I291" t="n">
         <v>-1.23</v>
@@ -15618,7 +15632,7 @@
         <v>-12.56</v>
       </c>
       <c r="M291" t="n">
-        <v>-12.39</v>
+        <v>-12.41</v>
       </c>
       <c r="N291" t="b">
         <v>0</v>
@@ -15656,7 +15670,7 @@
         <v>3.5</v>
       </c>
       <c r="H292" t="n">
-        <v>43.51</v>
+        <v>49.54</v>
       </c>
       <c r="I292" t="n">
         <v>33.01</v>
@@ -15669,7 +15683,7 @@
         <v>-0.92</v>
       </c>
       <c r="M292" t="n">
-        <v>39.62</v>
+        <v>46.4</v>
       </c>
       <c r="N292" t="b">
         <v>1</v>
@@ -15707,7 +15721,7 @@
         <v>14</v>
       </c>
       <c r="H293" t="n">
-        <v>25.59</v>
+        <v>25.53</v>
       </c>
       <c r="I293" t="n">
         <v>2.89</v>
@@ -15720,7 +15734,7 @@
         <v>-1.94</v>
       </c>
       <c r="M293" t="n">
-        <v>21.71</v>
+        <v>22.4</v>
       </c>
       <c r="N293" t="b">
         <v>0</v>
@@ -15758,7 +15772,7 @@
         <v>19.8</v>
       </c>
       <c r="H294" t="n">
-        <v>8.460000000000001</v>
+        <v>9.74</v>
       </c>
       <c r="I294" t="n">
         <v>4.74</v>
@@ -15771,7 +15785,7 @@
         <v>-9.9</v>
       </c>
       <c r="M294" t="n">
-        <v>4.57</v>
+        <v>6.6</v>
       </c>
       <c r="N294" t="b">
         <v>1</v>
@@ -15813,7 +15827,7 @@
         <v>-7.4</v>
       </c>
       <c r="H295" t="n">
-        <v>4.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I295" t="n">
         <v>-3.85</v>
@@ -15826,7 +15840,7 @@
         <v>-21.11</v>
       </c>
       <c r="M295" t="n">
-        <v>0.13</v>
+        <v>5.66</v>
       </c>
       <c r="N295" t="b">
         <v>0</v>
@@ -15864,7 +15878,7 @@
         <v>-10.8</v>
       </c>
       <c r="H296" t="n">
-        <v>9.09</v>
+        <v>7</v>
       </c>
       <c r="I296" t="n">
         <v>1.78</v>
@@ -15877,7 +15891,7 @@
         <v>-7.51</v>
       </c>
       <c r="M296" t="n">
-        <v>5.2</v>
+        <v>3.86</v>
       </c>
       <c r="N296" t="b">
         <v>0</v>
@@ -15915,7 +15929,7 @@
         <v>-24</v>
       </c>
       <c r="H297" t="n">
-        <v>45.65</v>
+        <v>45.78</v>
       </c>
       <c r="I297" t="n">
         <v>10.85</v>
@@ -15928,7 +15942,7 @@
         <v>-5.43</v>
       </c>
       <c r="M297" t="n">
-        <v>41.76</v>
+        <v>42.64</v>
       </c>
       <c r="N297" t="b">
         <v>0</v>
@@ -15966,7 +15980,7 @@
         <v>-28.3</v>
       </c>
       <c r="H298" t="n">
-        <v>-22.25</v>
+        <v>-22.55</v>
       </c>
       <c r="I298" t="n">
         <v>-8.949999999999999</v>
@@ -15979,7 +15993,7 @@
         <v>-13.18</v>
       </c>
       <c r="M298" t="n">
-        <v>-25.39</v>
+        <v>-25.61</v>
       </c>
       <c r="N298" t="b">
         <v>0</v>
@@ -16017,7 +16031,7 @@
         <v>-30.5</v>
       </c>
       <c r="H299" t="n">
-        <v>1.71</v>
+        <v>-0.91</v>
       </c>
       <c r="I299" t="n">
         <v>2.96</v>
@@ -16030,7 +16044,7 @@
         <v>-17.88</v>
       </c>
       <c r="M299" t="n">
-        <v>-1.43</v>
+        <v>-3.96</v>
       </c>
       <c r="N299" t="b">
         <v>1</v>
@@ -16068,7 +16082,7 @@
         <v>-6</v>
       </c>
       <c r="H300" t="n">
-        <v>-22.02</v>
+        <v>-22.5</v>
       </c>
       <c r="I300" t="n">
         <v>3.31</v>
@@ -16081,7 +16095,7 @@
         <v>-21.48</v>
       </c>
       <c r="M300" t="n">
-        <v>-25.9</v>
+        <v>-25.64</v>
       </c>
       <c r="N300" t="b">
         <v>1</v>
@@ -16119,7 +16133,7 @@
         <v>-42.2</v>
       </c>
       <c r="H301" t="n">
-        <v>10.01</v>
+        <v>11.85</v>
       </c>
       <c r="I301" t="n">
         <v>19.24</v>
@@ -16132,7 +16146,7 @@
         <v>-0.93</v>
       </c>
       <c r="M301" t="n">
-        <v>6.12</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="N301" t="b">
         <v>0</v>
@@ -16170,7 +16184,7 @@
         <v>-34.6</v>
       </c>
       <c r="H302" t="n">
-        <v>1.94</v>
+        <v>-1.18</v>
       </c>
       <c r="I302" t="n">
         <v>23.65</v>
@@ -16183,7 +16197,7 @@
         <v>-3.83</v>
       </c>
       <c r="M302" t="n">
-        <v>-1.95</v>
+        <v>-4.32</v>
       </c>
       <c r="N302" t="b">
         <v>1</v>
@@ -16221,7 +16235,7 @@
         <v>-48.1</v>
       </c>
       <c r="H303" t="n">
-        <v>-8.44</v>
+        <v>-9.69</v>
       </c>
       <c r="I303" t="n">
         <v>2.19</v>
@@ -16234,7 +16248,7 @@
         <v>-13.66</v>
       </c>
       <c r="M303" t="n">
-        <v>-11.58</v>
+        <v>-12.75</v>
       </c>
       <c r="N303" t="b">
         <v>0</v>
@@ -16272,7 +16286,7 @@
         <v>-16.2</v>
       </c>
       <c r="H304" t="n">
-        <v>12.69</v>
+        <v>9.41</v>
       </c>
       <c r="I304" t="n">
         <v>25.77</v>
@@ -16285,7 +16299,7 @@
         <v>-1.7</v>
       </c>
       <c r="M304" t="n">
-        <v>8.81</v>
+        <v>6.27</v>
       </c>
       <c r="N304" t="b">
         <v>1</v>
@@ -16323,7 +16337,7 @@
         <v>-24.9</v>
       </c>
       <c r="H305" t="n">
-        <v>32.15</v>
+        <v>29.55</v>
       </c>
       <c r="I305" t="n">
         <v>10.88</v>
@@ -16336,7 +16350,7 @@
         <v>-4.1</v>
       </c>
       <c r="M305" t="n">
-        <v>28.26</v>
+        <v>26.41</v>
       </c>
       <c r="N305" t="b">
         <v>1</v>
@@ -16378,7 +16392,7 @@
         <v>-8.1</v>
       </c>
       <c r="H306" t="n">
-        <v>20.27</v>
+        <v>17.07</v>
       </c>
       <c r="I306" t="n">
         <v>14.27</v>
@@ -16391,7 +16405,7 @@
         <v>-10.92</v>
       </c>
       <c r="M306" t="n">
-        <v>16.38</v>
+        <v>13.93</v>
       </c>
       <c r="N306" t="b">
         <v>1</v>
@@ -16429,7 +16443,7 @@
         <v>-10.2</v>
       </c>
       <c r="H307" t="n">
-        <v>-10.2</v>
+        <v>-12.03</v>
       </c>
       <c r="I307" t="n">
         <v>15.03</v>
@@ -16442,7 +16456,7 @@
         <v>-1.61</v>
       </c>
       <c r="M307" t="n">
-        <v>-14.08</v>
+        <v>-15.17</v>
       </c>
       <c r="N307" t="b">
         <v>1</v>
@@ -16480,7 +16494,7 @@
         <v>68.90000000000001</v>
       </c>
       <c r="H308" t="n">
-        <v>9.32</v>
+        <v>11.54</v>
       </c>
       <c r="I308" t="n">
         <v>1.84</v>
@@ -16493,7 +16507,7 @@
         <v>-10.43</v>
       </c>
       <c r="M308" t="n">
-        <v>5.44</v>
+        <v>8.4</v>
       </c>
       <c r="N308" t="b">
         <v>1</v>
@@ -16531,7 +16545,7 @@
         <v>-40.8</v>
       </c>
       <c r="H309" t="n">
-        <v>-10.17</v>
+        <v>-10.04</v>
       </c>
       <c r="I309" t="n">
         <v>21.71</v>
@@ -16544,7 +16558,7 @@
         <v>-3.3</v>
       </c>
       <c r="M309" t="n">
-        <v>-14.06</v>
+        <v>-13.18</v>
       </c>
       <c r="N309" t="b">
         <v>1</v>
@@ -16582,7 +16596,7 @@
         <v>-10.1</v>
       </c>
       <c r="H310" t="n">
-        <v>-14.77</v>
+        <v>-14.11</v>
       </c>
       <c r="I310" t="n">
         <v>1.83</v>
@@ -16595,7 +16609,7 @@
         <v>-3.45</v>
       </c>
       <c r="M310" t="n">
-        <v>-18.65</v>
+        <v>-17.25</v>
       </c>
       <c r="N310" t="b">
         <v>0</v>
@@ -16633,7 +16647,7 @@
         <v>40.7</v>
       </c>
       <c r="H311" t="n">
-        <v>43.7</v>
+        <v>48.13</v>
       </c>
       <c r="I311" t="n">
         <v>-4.08</v>
@@ -16646,7 +16660,7 @@
         <v>-11.2</v>
       </c>
       <c r="M311" t="n">
-        <v>39.81</v>
+        <v>44.99</v>
       </c>
       <c r="N311" t="b">
         <v>1</v>
@@ -16684,7 +16698,7 @@
         <v>25.7</v>
       </c>
       <c r="H312" t="n">
-        <v>-9.32</v>
+        <v>-10.08</v>
       </c>
       <c r="I312" t="n">
         <v>11.3</v>
@@ -16697,7 +16711,7 @@
         <v>-11.03</v>
       </c>
       <c r="M312" t="n">
-        <v>-13.21</v>
+        <v>-13.22</v>
       </c>
       <c r="N312" t="b">
         <v>1</v>
@@ -16735,7 +16749,7 @@
         <v>2.3</v>
       </c>
       <c r="H313" t="n">
-        <v>-5.35</v>
+        <v>-5.65</v>
       </c>
       <c r="I313" t="n">
         <v>-0.95</v>
@@ -16748,7 +16762,7 @@
         <v>-7.81</v>
       </c>
       <c r="M313" t="n">
-        <v>-9.24</v>
+        <v>-8.779999999999999</v>
       </c>
       <c r="N313" t="b">
         <v>0</v>
@@ -16880,16 +16894,16 @@
         <v>-2.7</v>
       </c>
       <c r="H2" t="n">
-        <v>-2.98</v>
+        <v>-4.69</v>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="n">
-        <v>-2.98</v>
+        <v>-5.23</v>
       </c>
       <c r="M2" t="n">
-        <v>-2.34</v>
+        <v>-3.96</v>
       </c>
       <c r="N2" t="b">
         <v>1</v>
@@ -16927,7 +16941,7 @@
         <v>26.9</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.99</v>
+        <v>2.29</v>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
@@ -16936,7 +16950,7 @@
         <v>-2.51</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.35</v>
+        <v>3.02</v>
       </c>
       <c r="N3" t="b">
         <v>1</v>
@@ -16974,7 +16988,7 @@
         <v>-18.1</v>
       </c>
       <c r="H4" t="n">
-        <v>1.07</v>
+        <v>1.33</v>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
@@ -16983,7 +16997,7 @@
         <v>-2.69</v>
       </c>
       <c r="M4" t="n">
-        <v>0.14</v>
+        <v>1.12</v>
       </c>
       <c r="N4" t="b">
         <v>1</v>
@@ -17010,7 +17024,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Extended</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
@@ -17021,7 +17035,7 @@
         <v>-21.5</v>
       </c>
       <c r="H5" t="n">
-        <v>5.73</v>
+        <v>3.71</v>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
@@ -17030,7 +17044,7 @@
         <v>-1.4</v>
       </c>
       <c r="M5" t="n">
-        <v>4.8</v>
+        <v>3.51</v>
       </c>
       <c r="N5" t="b">
         <v>1</v>
@@ -17068,7 +17082,7 @@
         <v>41.6</v>
       </c>
       <c r="H6" t="n">
-        <v>-3</v>
+        <v>2.85</v>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
@@ -17077,7 +17091,7 @@
         <v>-4.38</v>
       </c>
       <c r="M6" t="n">
-        <v>-4.58</v>
+        <v>2</v>
       </c>
       <c r="N6" t="b">
         <v>1</v>
@@ -17115,7 +17129,7 @@
         <v>32.1</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.52</v>
+        <v>-0.87</v>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
@@ -17124,7 +17138,7 @@
         <v>-2.19</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.11</v>
+        <v>-1.73</v>
       </c>
       <c r="N7" t="b">
         <v>1</v>
@@ -17162,16 +17176,16 @@
         <v>-14.4</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.19</v>
+        <v>-3.82</v>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="n">
-        <v>-1.54</v>
+        <v>-4.51</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.78</v>
+        <v>-4.68</v>
       </c>
       <c r="N8" t="b">
         <v>1</v>
@@ -17209,7 +17223,7 @@
         <v>-10</v>
       </c>
       <c r="H9" t="n">
-        <v>-3.02</v>
+        <v>-2.67</v>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
@@ -17218,7 +17232,7 @@
         <v>-5.75</v>
       </c>
       <c r="M9" t="n">
-        <v>-4.6</v>
+        <v>-3.52</v>
       </c>
       <c r="N9" t="b">
         <v>1</v>
@@ -17256,16 +17270,16 @@
         <v>6.4</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.14</v>
+        <v>-0.2</v>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="n">
-        <v>-1.45</v>
+        <v>-1.7</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.72</v>
+        <v>-1.05</v>
       </c>
       <c r="N10" t="b">
         <v>1</v>
@@ -17303,7 +17317,7 @@
         <v>20.2</v>
       </c>
       <c r="H11" t="n">
-        <v>1.75</v>
+        <v>2.15</v>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
@@ -17312,7 +17326,7 @@
         <v>-1.07</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.25</v>
+        <v>0.89</v>
       </c>
       <c r="N11" t="b">
         <v>1</v>
@@ -17339,7 +17353,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Extended</t>
         </is>
       </c>
       <c r="E12" t="inlineStr"/>
@@ -17350,7 +17364,7 @@
         <v>43.7</v>
       </c>
       <c r="H12" t="n">
-        <v>3.98</v>
+        <v>6.55</v>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
@@ -17359,7 +17373,7 @@
         <v>-2.44</v>
       </c>
       <c r="M12" t="n">
-        <v>1.98</v>
+        <v>5.28</v>
       </c>
       <c r="N12" t="b">
         <v>1</v>
@@ -17397,16 +17411,16 @@
         <v>1.9</v>
       </c>
       <c r="H13" t="n">
-        <v>-3.03</v>
+        <v>-5.37</v>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="n">
-        <v>-3.2</v>
+        <v>-5.97</v>
       </c>
       <c r="M13" t="n">
-        <v>-5.02</v>
+        <v>-6.63</v>
       </c>
       <c r="N13" t="b">
         <v>1</v>
@@ -17433,7 +17447,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Extended</t>
         </is>
       </c>
       <c r="E14" t="inlineStr"/>
@@ -17444,7 +17458,7 @@
         <v>37.5</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.34</v>
+        <v>5.81</v>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
@@ -17453,7 +17467,7 @@
         <v>-3.95</v>
       </c>
       <c r="M14" t="n">
-        <v>-2.49</v>
+        <v>4.4</v>
       </c>
       <c r="N14" t="b">
         <v>1</v>
@@ -17491,7 +17505,7 @@
         <v>40.2</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.15</v>
+        <v>-0.92</v>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
@@ -17500,7 +17514,7 @@
         <v>-3.87</v>
       </c>
       <c r="M15" t="n">
-        <v>-2.3</v>
+        <v>-2.33</v>
       </c>
       <c r="N15" t="b">
         <v>1</v>
@@ -17527,7 +17541,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Extended</t>
         </is>
       </c>
       <c r="E16" t="inlineStr"/>
@@ -17538,7 +17552,7 @@
         <v>10.7</v>
       </c>
       <c r="H16" t="n">
-        <v>3.18</v>
+        <v>5.32</v>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
@@ -17547,7 +17561,7 @@
         <v>-3.78</v>
       </c>
       <c r="M16" t="n">
-        <v>1.03</v>
+        <v>3.9</v>
       </c>
       <c r="N16" t="b">
         <v>1</v>
@@ -17574,7 +17588,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Extended</t>
         </is>
       </c>
       <c r="E17" t="inlineStr"/>
@@ -17585,7 +17599,7 @@
         <v>25.6</v>
       </c>
       <c r="H17" t="n">
-        <v>2.11</v>
+        <v>7.23</v>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
@@ -17594,7 +17608,7 @@
         <v>-4.85</v>
       </c>
       <c r="M17" t="n">
-        <v>0.73</v>
+        <v>6.58</v>
       </c>
       <c r="N17" t="b">
         <v>1</v>
@@ -17632,16 +17646,18 @@
         <v>-6.9</v>
       </c>
       <c r="H18" t="n">
-        <v>6.44</v>
-      </c>
-      <c r="I18" t="inlineStr"/>
+        <v>7</v>
+      </c>
+      <c r="I18" t="n">
+        <v>7</v>
+      </c>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="n">
         <v>-4.53</v>
       </c>
       <c r="M18" t="n">
-        <v>4.97</v>
+        <v>6.26</v>
       </c>
       <c r="N18" t="b">
         <v>1</v>
@@ -17679,7 +17695,7 @@
         <v>0.3</v>
       </c>
       <c r="H19" t="n">
-        <v>-12.25</v>
+        <v>-13.63</v>
       </c>
       <c r="I19" t="n">
         <v>-10.53</v>
@@ -17687,10 +17703,10 @@
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="n">
-        <v>-13.04</v>
+        <v>-15.78</v>
       </c>
       <c r="M19" t="n">
-        <v>-13.22</v>
+        <v>-13.87</v>
       </c>
       <c r="N19" t="b">
         <v>1</v>
@@ -17728,7 +17744,7 @@
         <v>2.8</v>
       </c>
       <c r="H20" t="n">
-        <v>1.39</v>
+        <v>0.29</v>
       </c>
       <c r="I20" t="n">
         <v>3.18</v>
@@ -17739,7 +17755,7 @@
         <v>-0.88</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.29</v>
+        <v>-0.66</v>
       </c>
       <c r="N20" t="b">
         <v>1</v>
@@ -17777,7 +17793,7 @@
         <v>34.5</v>
       </c>
       <c r="H21" t="n">
-        <v>7.38</v>
+        <v>5.66</v>
       </c>
       <c r="I21" t="n">
         <v>0.66</v>
@@ -17788,7 +17804,7 @@
         <v>-2.64</v>
       </c>
       <c r="M21" t="n">
-        <v>5.69</v>
+        <v>4.71</v>
       </c>
       <c r="N21" t="b">
         <v>1</v>
@@ -17826,7 +17842,7 @@
         <v>24.3</v>
       </c>
       <c r="H22" t="n">
-        <v>15.95</v>
+        <v>28.88</v>
       </c>
       <c r="I22" t="n">
         <v>2.54</v>
@@ -17837,7 +17853,7 @@
         <v>-5.21</v>
       </c>
       <c r="M22" t="n">
-        <v>14.91</v>
+        <v>28.57</v>
       </c>
       <c r="N22" t="b">
         <v>1</v>
@@ -17875,7 +17891,7 @@
         <v>-16.9</v>
       </c>
       <c r="H23" t="n">
-        <v>-7.29</v>
+        <v>-11.25</v>
       </c>
       <c r="I23" t="n">
         <v>-6.47</v>
@@ -17883,10 +17899,10 @@
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="n">
-        <v>-9.02</v>
+        <v>-11.5</v>
       </c>
       <c r="M23" t="n">
-        <v>-8.33</v>
+        <v>-11.56</v>
       </c>
       <c r="N23" t="b">
         <v>1</v>
@@ -17924,7 +17940,7 @@
         <v>20.3</v>
       </c>
       <c r="H24" t="n">
-        <v>-16.02</v>
+        <v>-15.32</v>
       </c>
       <c r="I24" t="n">
         <v>-2.07</v>
@@ -17932,10 +17948,10 @@
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="n">
-        <v>-16.13</v>
+        <v>-17.35</v>
       </c>
       <c r="M24" t="n">
-        <v>-16.91</v>
+        <v>-15.48</v>
       </c>
       <c r="N24" t="b">
         <v>1</v>
@@ -17962,7 +17978,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Retired</t>
         </is>
       </c>
       <c r="E25" t="inlineStr"/>
@@ -17973,7 +17989,7 @@
         <v>0.3</v>
       </c>
       <c r="H25" t="n">
-        <v>-18.83</v>
+        <v>-19.17</v>
       </c>
       <c r="I25" t="n">
         <v>-9.9</v>
@@ -17981,10 +17997,10 @@
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="n">
-        <v>-21.11</v>
+        <v>-21.72</v>
       </c>
       <c r="M25" t="n">
-        <v>-20.21</v>
+        <v>-19.82</v>
       </c>
       <c r="N25" t="b">
         <v>1</v>
@@ -18022,18 +18038,20 @@
         <v>49.4</v>
       </c>
       <c r="H26" t="n">
-        <v>3.93</v>
+        <v>3.68</v>
       </c>
       <c r="I26" t="n">
         <v>2.9</v>
       </c>
-      <c r="J26" t="inlineStr"/>
+      <c r="J26" t="n">
+        <v>3.68</v>
+      </c>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="n">
         <v>-5.67</v>
       </c>
       <c r="M26" t="n">
-        <v>2.74</v>
+        <v>3.22</v>
       </c>
       <c r="N26" t="b">
         <v>1</v>
@@ -18071,18 +18089,20 @@
         <v>4.5</v>
       </c>
       <c r="H27" t="n">
-        <v>-10.17</v>
+        <v>-10.6</v>
       </c>
       <c r="I27" t="n">
         <v>-7.61</v>
       </c>
-      <c r="J27" t="inlineStr"/>
+      <c r="J27" t="n">
+        <v>-10.6</v>
+      </c>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="n">
-        <v>-10.98</v>
+        <v>-11.1</v>
       </c>
       <c r="M27" t="n">
-        <v>-11.36</v>
+        <v>-11.07</v>
       </c>
       <c r="N27" t="b">
         <v>1</v>
@@ -18120,7 +18140,7 @@
         <v>-17.9</v>
       </c>
       <c r="H28" t="n">
-        <v>-7.39</v>
+        <v>-9.4</v>
       </c>
       <c r="I28" t="n">
         <v>0.6</v>
@@ -18133,7 +18153,7 @@
         <v>-4.72</v>
       </c>
       <c r="M28" t="n">
-        <v>-8.609999999999999</v>
+        <v>-9.890000000000001</v>
       </c>
       <c r="N28" t="b">
         <v>1</v>
@@ -18171,7 +18191,7 @@
         <v>2.1</v>
       </c>
       <c r="H29" t="n">
-        <v>-17.66</v>
+        <v>-21.11</v>
       </c>
       <c r="I29" t="n">
         <v>0.25</v>
@@ -18184,7 +18204,7 @@
         <v>-16.43</v>
       </c>
       <c r="M29" t="n">
-        <v>-18.88</v>
+        <v>-21.6</v>
       </c>
       <c r="N29" t="b">
         <v>1</v>
@@ -18222,7 +18242,7 @@
         <v>19.4</v>
       </c>
       <c r="H30" t="n">
-        <v>-12.47</v>
+        <v>-10.22</v>
       </c>
       <c r="I30" t="n">
         <v>-10.01</v>
@@ -18235,7 +18255,7 @@
         <v>-15.23</v>
       </c>
       <c r="M30" t="n">
-        <v>-13.11</v>
+        <v>-10.13</v>
       </c>
       <c r="N30" t="b">
         <v>1</v>
@@ -18273,7 +18293,7 @@
         <v>-2.6</v>
       </c>
       <c r="H31" t="n">
-        <v>-9.19</v>
+        <v>-9.619999999999999</v>
       </c>
       <c r="I31" t="n">
         <v>-4.27</v>
@@ -18286,7 +18306,7 @@
         <v>-4.86</v>
       </c>
       <c r="M31" t="n">
-        <v>-10.05</v>
+        <v>-9.76</v>
       </c>
       <c r="N31" t="b">
         <v>1</v>
@@ -18324,7 +18344,7 @@
         <v>23.8</v>
       </c>
       <c r="H32" t="n">
-        <v>4.35</v>
+        <v>11.92</v>
       </c>
       <c r="I32" t="n">
         <v>1.36</v>
@@ -18337,7 +18357,7 @@
         <v>-9.94</v>
       </c>
       <c r="M32" t="n">
-        <v>4.46</v>
+        <v>12.75</v>
       </c>
       <c r="N32" t="b">
         <v>1</v>
@@ -18375,7 +18395,7 @@
         <v>38.9</v>
       </c>
       <c r="H33" t="n">
-        <v>-10.09</v>
+        <v>-12.42</v>
       </c>
       <c r="I33" t="n">
         <v>-9.220000000000001</v>
@@ -18388,7 +18408,7 @@
         <v>-9.83</v>
       </c>
       <c r="M33" t="n">
-        <v>-9.970000000000001</v>
+        <v>-11.59</v>
       </c>
       <c r="N33" t="b">
         <v>1</v>
@@ -18426,7 +18446,7 @@
         <v>43.2</v>
       </c>
       <c r="H34" t="n">
-        <v>-20.83</v>
+        <v>-20.7</v>
       </c>
       <c r="I34" t="n">
         <v>-3.15</v>
@@ -18439,7 +18459,7 @@
         <v>-17.51</v>
       </c>
       <c r="M34" t="n">
-        <v>-20.88</v>
+        <v>-20.03</v>
       </c>
       <c r="N34" t="b">
         <v>1</v>
@@ -18477,7 +18497,7 @@
         <v>-8.199999999999999</v>
       </c>
       <c r="H35" t="n">
-        <v>-5.01</v>
+        <v>-6.75</v>
       </c>
       <c r="I35" t="n">
         <v>5.34</v>
@@ -18490,7 +18510,7 @@
         <v>-5.27</v>
       </c>
       <c r="M35" t="n">
-        <v>-5.06</v>
+        <v>-6.08</v>
       </c>
       <c r="N35" t="b">
         <v>1</v>
@@ -18528,7 +18548,7 @@
         <v>-23.9</v>
       </c>
       <c r="H36" t="n">
-        <v>-7.28</v>
+        <v>-10.2</v>
       </c>
       <c r="I36" t="n">
         <v>3.28</v>
@@ -18541,7 +18561,7 @@
         <v>-4.46</v>
       </c>
       <c r="M36" t="n">
-        <v>-7.63</v>
+        <v>-9.83</v>
       </c>
       <c r="N36" t="b">
         <v>1</v>
@@ -18583,7 +18603,7 @@
         <v>-6.1</v>
       </c>
       <c r="H37" t="n">
-        <v>7.41</v>
+        <v>4.42</v>
       </c>
       <c r="I37" t="n">
         <v>4.9</v>
@@ -18596,7 +18616,7 @@
         <v>-9</v>
       </c>
       <c r="M37" t="n">
-        <v>7.06</v>
+        <v>4.79</v>
       </c>
       <c r="N37" t="b">
         <v>1</v>
@@ -18634,7 +18654,7 @@
         <v>26.7</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.87</v>
+        <v>-1.12</v>
       </c>
       <c r="I38" t="n">
         <v>-0.05</v>
@@ -18647,7 +18667,7 @@
         <v>-0.87</v>
       </c>
       <c r="M38" t="n">
-        <v>-1.22</v>
+        <v>-0.75</v>
       </c>
       <c r="N38" t="b">
         <v>1</v>
@@ -18685,7 +18705,7 @@
         <v>-3.5</v>
       </c>
       <c r="H39" t="n">
-        <v>-0.34</v>
+        <v>-2.58</v>
       </c>
       <c r="I39" t="n">
         <v>-4.95</v>
@@ -18698,7 +18718,7 @@
         <v>-8.43</v>
       </c>
       <c r="M39" t="n">
-        <v>-0.9</v>
+        <v>-2.41</v>
       </c>
       <c r="N39" t="b">
         <v>1</v>
@@ -18736,7 +18756,7 @@
         <v>-17.9</v>
       </c>
       <c r="H40" t="n">
-        <v>6.27</v>
+        <v>3.59</v>
       </c>
       <c r="I40" t="n">
         <v>-0.5</v>
@@ -18749,7 +18769,7 @@
         <v>-3.43</v>
       </c>
       <c r="M40" t="n">
-        <v>5.71</v>
+        <v>3.76</v>
       </c>
       <c r="N40" t="b">
         <v>1</v>
@@ -18787,7 +18807,7 @@
         <v>53.5</v>
       </c>
       <c r="H41" t="n">
-        <v>2.66</v>
+        <v>1.63</v>
       </c>
       <c r="I41" t="n">
         <v>1.23</v>
@@ -18800,7 +18820,7 @@
         <v>-7.57</v>
       </c>
       <c r="M41" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="N41" t="b">
         <v>1</v>
@@ -18838,7 +18858,7 @@
         <v>-1</v>
       </c>
       <c r="H42" t="n">
-        <v>-14.7</v>
+        <v>-14.06</v>
       </c>
       <c r="I42" t="n">
         <v>-6.26</v>
@@ -18851,7 +18871,7 @@
         <v>-15</v>
       </c>
       <c r="M42" t="n">
-        <v>-15.36</v>
+        <v>-14</v>
       </c>
       <c r="N42" t="b">
         <v>1</v>
@@ -18889,7 +18909,7 @@
         <v>29.7</v>
       </c>
       <c r="H43" t="n">
-        <v>11.21</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="I43" t="n">
         <v>11.27</v>
@@ -18902,7 +18922,7 @@
         <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>10.54</v>
+        <v>9.19</v>
       </c>
       <c r="N43" t="b">
         <v>1</v>
@@ -18940,7 +18960,7 @@
         <v>15.2</v>
       </c>
       <c r="H44" t="n">
-        <v>-33.13</v>
+        <v>-34.95</v>
       </c>
       <c r="I44" t="n">
         <v>-8.77</v>
@@ -18953,7 +18973,7 @@
         <v>-24.79</v>
       </c>
       <c r="M44" t="n">
-        <v>-33.06</v>
+        <v>-34.16</v>
       </c>
       <c r="N44" t="b">
         <v>1</v>
@@ -18991,7 +19011,7 @@
         <v>22.2</v>
       </c>
       <c r="H45" t="n">
-        <v>7.62</v>
+        <v>6.97</v>
       </c>
       <c r="I45" t="n">
         <v>1.01</v>
@@ -19004,7 +19024,7 @@
         <v>-3.94</v>
       </c>
       <c r="M45" t="n">
-        <v>7.69</v>
+        <v>7.76</v>
       </c>
       <c r="N45" t="b">
         <v>1</v>
@@ -19046,7 +19066,7 @@
         <v>-0</v>
       </c>
       <c r="H46" t="n">
-        <v>28.93</v>
+        <v>30.88</v>
       </c>
       <c r="I46" t="n">
         <v>13.5</v>
@@ -19059,7 +19079,7 @@
         <v>-2.53</v>
       </c>
       <c r="M46" t="n">
-        <v>25.48</v>
+        <v>28.18</v>
       </c>
       <c r="N46" t="b">
         <v>1</v>
@@ -19097,7 +19117,7 @@
         <v>10.5</v>
       </c>
       <c r="H47" t="n">
-        <v>0.67</v>
+        <v>0.71</v>
       </c>
       <c r="I47" t="n">
         <v>1.99</v>
@@ -19110,7 +19130,7 @@
         <v>-6.27</v>
       </c>
       <c r="M47" t="n">
-        <v>-2.78</v>
+        <v>-2</v>
       </c>
       <c r="N47" t="b">
         <v>1</v>
@@ -19148,7 +19168,7 @@
         <v>-37</v>
       </c>
       <c r="H48" t="n">
-        <v>26.83</v>
+        <v>24.3</v>
       </c>
       <c r="I48" t="n">
         <v>18.38</v>
@@ -19161,7 +19181,7 @@
         <v>-5.11</v>
       </c>
       <c r="M48" t="n">
-        <v>22.71</v>
+        <v>20.93</v>
       </c>
       <c r="N48" t="b">
         <v>1</v>
@@ -19199,7 +19219,7 @@
         <v>-26.8</v>
       </c>
       <c r="H49" t="n">
-        <v>12.92</v>
+        <v>15.43</v>
       </c>
       <c r="I49" t="n">
         <v>4.56</v>
@@ -19212,7 +19232,7 @@
         <v>-4.09</v>
       </c>
       <c r="M49" t="n">
-        <v>8.81</v>
+        <v>12.06</v>
       </c>
       <c r="N49" t="b">
         <v>1</v>
@@ -19250,7 +19270,7 @@
         <v>-36.5</v>
       </c>
       <c r="H50" t="n">
-        <v>-32.08</v>
+        <v>-32.35</v>
       </c>
       <c r="I50" t="n">
         <v>-27.75</v>
@@ -19263,7 +19283,7 @@
         <v>-31.28</v>
       </c>
       <c r="M50" t="n">
-        <v>-36.1</v>
+        <v>-36.29</v>
       </c>
       <c r="N50" t="b">
         <v>1</v>
@@ -19301,7 +19321,7 @@
         <v>-38.7</v>
       </c>
       <c r="H51" t="n">
-        <v>8.57</v>
+        <v>7.01</v>
       </c>
       <c r="I51" t="n">
         <v>17.17</v>
@@ -19314,7 +19334,7 @@
         <v>-0.54</v>
       </c>
       <c r="M51" t="n">
-        <v>3.79</v>
+        <v>2.99</v>
       </c>
       <c r="N51" t="b">
         <v>1</v>
@@ -19352,7 +19372,7 @@
         <v>-34.6</v>
       </c>
       <c r="H52" t="n">
-        <v>20.01</v>
+        <v>16.77</v>
       </c>
       <c r="I52" t="n">
         <v>6.67</v>
@@ -19365,7 +19385,7 @@
         <v>-3.06</v>
       </c>
       <c r="M52" t="n">
-        <v>15.23</v>
+        <v>12.75</v>
       </c>
       <c r="N52" t="b">
         <v>1</v>
@@ -19403,7 +19423,7 @@
         <v>-11.8</v>
       </c>
       <c r="H53" t="n">
-        <v>-3.44</v>
+        <v>-6.36</v>
       </c>
       <c r="I53" t="n">
         <v>9.76</v>
@@ -19416,7 +19436,7 @@
         <v>-1.63</v>
       </c>
       <c r="M53" t="n">
-        <v>-8.33</v>
+        <v>-10.49</v>
       </c>
       <c r="N53" t="b">
         <v>1</v>
@@ -19454,7 +19474,7 @@
         <v>0.1</v>
       </c>
       <c r="H54" t="n">
-        <v>-16.65</v>
+        <v>-15.34</v>
       </c>
       <c r="I54" t="n">
         <v>-2.83</v>
@@ -19467,7 +19487,7 @@
         <v>-5.45</v>
       </c>
       <c r="M54" t="n">
-        <v>-21.54</v>
+        <v>-19.47</v>
       </c>
       <c r="N54" t="b">
         <v>1</v>
@@ -19505,7 +19525,7 @@
         <v>24.1</v>
       </c>
       <c r="H55" t="n">
-        <v>-14.1</v>
+        <v>-15.22</v>
       </c>
       <c r="I55" t="n">
         <v>-8.31</v>
@@ -19518,7 +19538,7 @@
         <v>-18.31</v>
       </c>
       <c r="M55" t="n">
-        <v>-18.18</v>
+        <v>-18.55</v>
       </c>
       <c r="N55" t="b">
         <v>1</v>
@@ -19556,7 +19576,7 @@
         <v>-15.9</v>
       </c>
       <c r="H56" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="I56" t="n">
         <v>10.45</v>
@@ -19569,7 +19589,7 @@
         <v>-0.31</v>
       </c>
       <c r="M56" t="n">
-        <v>-1.51</v>
+        <v>-3.33</v>
       </c>
       <c r="N56" t="b">
         <v>1</v>
@@ -19607,7 +19627,7 @@
         <v>-21.8</v>
       </c>
       <c r="H57" t="n">
-        <v>-23.9</v>
+        <v>-24.57</v>
       </c>
       <c r="I57" t="n">
         <v>-18.97</v>
@@ -19620,7 +19640,7 @@
         <v>-26.82</v>
       </c>
       <c r="M57" t="n">
-        <v>-28.76</v>
+        <v>-28.68</v>
       </c>
       <c r="N57" t="b">
         <v>1</v>
@@ -19658,7 +19678,7 @@
         <v>57</v>
       </c>
       <c r="H58" t="n">
-        <v>14.27</v>
+        <v>13.89</v>
       </c>
       <c r="I58" t="n">
         <v>-11.21</v>
@@ -19671,7 +19691,7 @@
         <v>-13.87</v>
       </c>
       <c r="M58" t="n">
-        <v>10.43</v>
+        <v>10.8</v>
       </c>
       <c r="N58" t="b">
         <v>1</v>
@@ -19709,7 +19729,7 @@
         <v>-21.8</v>
       </c>
       <c r="H59" t="n">
-        <v>10.31</v>
+        <v>8.43</v>
       </c>
       <c r="I59" t="n">
         <v>1.71</v>
@@ -19722,7 +19742,7 @@
         <v>-6.18</v>
       </c>
       <c r="M59" t="n">
-        <v>6.47</v>
+        <v>5.34</v>
       </c>
       <c r="N59" t="b">
         <v>1</v>
@@ -19760,7 +19780,7 @@
         <v>1</v>
       </c>
       <c r="H60" t="n">
-        <v>-33.75</v>
+        <v>-35.08</v>
       </c>
       <c r="I60" t="n">
         <v>-11.52</v>
@@ -19773,7 +19793,7 @@
         <v>-16.26</v>
       </c>
       <c r="M60" t="n">
-        <v>-37.64</v>
+        <v>-38.22</v>
       </c>
       <c r="N60" t="b">
         <v>1</v>
@@ -19811,7 +19831,7 @@
         <v>45.4</v>
       </c>
       <c r="H61" t="n">
-        <v>16.5</v>
+        <v>7.31</v>
       </c>
       <c r="I61" t="n">
         <v>-1.72</v>
@@ -19824,7 +19844,7 @@
         <v>-23.15</v>
       </c>
       <c r="M61" t="n">
-        <v>13.36</v>
+        <v>4.26</v>
       </c>
       <c r="N61" t="b">
         <v>1</v>
@@ -19862,7 +19882,7 @@
         <v>76.5</v>
       </c>
       <c r="H62" t="n">
-        <v>20.17</v>
+        <v>16.01</v>
       </c>
       <c r="I62" t="n">
         <v>-5.56</v>
@@ -19875,7 +19895,7 @@
         <v>-33.97</v>
       </c>
       <c r="M62" t="n">
-        <v>17.03</v>
+        <v>12.95</v>
       </c>
       <c r="N62" t="b">
         <v>1</v>
@@ -19913,7 +19933,7 @@
         <v>32.1</v>
       </c>
       <c r="H63" t="n">
-        <v>17.38</v>
+        <v>26.12</v>
       </c>
       <c r="I63" t="n">
         <v>16.93</v>
@@ -19926,7 +19946,7 @@
         <v>-24.48</v>
       </c>
       <c r="M63" t="n">
-        <v>14.25</v>
+        <v>23.07</v>
       </c>
       <c r="N63" t="b">
         <v>1</v>
@@ -19964,7 +19984,7 @@
         <v>51.8</v>
       </c>
       <c r="H64" t="n">
-        <v>10.38</v>
+        <v>10.4</v>
       </c>
       <c r="I64" t="n">
         <v>10.75</v>
@@ -19977,7 +19997,7 @@
         <v>-25.09</v>
       </c>
       <c r="M64" t="n">
-        <v>7.24</v>
+        <v>7.34</v>
       </c>
       <c r="N64" t="b">
         <v>1</v>
@@ -20015,7 +20035,7 @@
         <v>32.3</v>
       </c>
       <c r="H65" t="n">
-        <v>-25.09</v>
+        <v>-24.84</v>
       </c>
       <c r="I65" t="n">
         <v>-20.76</v>
@@ -20028,7 +20048,7 @@
         <v>-27.91</v>
       </c>
       <c r="M65" t="n">
-        <v>-28.98</v>
+        <v>-27.98</v>
       </c>
       <c r="N65" t="b">
         <v>1</v>
@@ -20066,7 +20086,7 @@
         <v>3.7</v>
       </c>
       <c r="H66" t="n">
-        <v>-12.7</v>
+        <v>-9.960000000000001</v>
       </c>
       <c r="I66" t="n">
         <v>-1.11</v>
@@ -20079,7 +20099,7 @@
         <v>-25.46</v>
       </c>
       <c r="M66" t="n">
-        <v>-15.84</v>
+        <v>-13.02</v>
       </c>
       <c r="N66" t="b">
         <v>1</v>
@@ -20117,7 +20137,7 @@
         <v>42.4</v>
       </c>
       <c r="H67" t="n">
-        <v>11.93</v>
+        <v>12.21</v>
       </c>
       <c r="I67" t="n">
         <v>2.16</v>
@@ -20130,7 +20150,7 @@
         <v>-15.76</v>
       </c>
       <c r="M67" t="n">
-        <v>8.039999999999999</v>
+        <v>9.08</v>
       </c>
       <c r="N67" t="b">
         <v>1</v>
@@ -20168,7 +20188,7 @@
         <v>28.2</v>
       </c>
       <c r="H68" t="n">
-        <v>-11.19</v>
+        <v>-9.24</v>
       </c>
       <c r="I68" t="n">
         <v>-1.71</v>
@@ -20181,7 +20201,7 @@
         <v>-23.43</v>
       </c>
       <c r="M68" t="n">
-        <v>-14.33</v>
+        <v>-12.29</v>
       </c>
       <c r="N68" t="b">
         <v>1</v>
@@ -20219,7 +20239,7 @@
         <v>28.6</v>
       </c>
       <c r="H69" t="n">
-        <v>28.55</v>
+        <v>25.32</v>
       </c>
       <c r="I69" t="n">
         <v>2.81</v>
@@ -20232,7 +20252,7 @@
         <v>-18.87</v>
       </c>
       <c r="M69" t="n">
-        <v>24.66</v>
+        <v>22.18</v>
       </c>
       <c r="N69" t="b">
         <v>1</v>
@@ -20270,7 +20290,7 @@
         <v>33.1</v>
       </c>
       <c r="H70" t="n">
-        <v>15.47</v>
+        <v>14.48</v>
       </c>
       <c r="I70" t="n">
         <v>4.68</v>
@@ -20283,7 +20303,7 @@
         <v>-26.7</v>
       </c>
       <c r="M70" t="n">
-        <v>12.33</v>
+        <v>11.43</v>
       </c>
       <c r="N70" t="b">
         <v>1</v>
@@ -20321,7 +20341,7 @@
         <v>21.8</v>
       </c>
       <c r="H71" t="n">
-        <v>-11.26</v>
+        <v>-10.44</v>
       </c>
       <c r="I71" t="n">
         <v>-6.34</v>
@@ -20334,7 +20354,7 @@
         <v>-30.04</v>
       </c>
       <c r="M71" t="n">
-        <v>-15.14</v>
+        <v>-13.58</v>
       </c>
       <c r="N71" t="b">
         <v>1</v>
@@ -20372,7 +20392,7 @@
         <v>40.3</v>
       </c>
       <c r="H72" t="n">
-        <v>-10.27</v>
+        <v>-10.19</v>
       </c>
       <c r="I72" t="n">
         <v>1.24</v>
@@ -20385,7 +20405,7 @@
         <v>-20.5</v>
       </c>
       <c r="M72" t="n">
-        <v>-14.16</v>
+        <v>-13.33</v>
       </c>
       <c r="N72" t="b">
         <v>1</v>
@@ -20423,7 +20443,7 @@
         <v>24.1</v>
       </c>
       <c r="H73" t="n">
-        <v>2.76</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="I73" t="n">
         <v>-1.6</v>
@@ -20436,7 +20456,7 @@
         <v>-22.54</v>
       </c>
       <c r="M73" t="n">
-        <v>-1.13</v>
+        <v>5.41</v>
       </c>
       <c r="N73" t="b">
         <v>1</v>
@@ -20474,7 +20494,7 @@
         <v>24.5</v>
       </c>
       <c r="H74" t="n">
-        <v>-28.71</v>
+        <v>-28.67</v>
       </c>
       <c r="I74" t="n">
         <v>-12.99</v>
@@ -20487,7 +20507,7 @@
         <v>-22.54</v>
       </c>
       <c r="M74" t="n">
-        <v>-32.6</v>
+        <v>-31.81</v>
       </c>
       <c r="N74" t="b">
         <v>1</v>
@@ -20525,7 +20545,7 @@
         <v>19.3</v>
       </c>
       <c r="H75" t="n">
-        <v>7.84</v>
+        <v>7.44</v>
       </c>
       <c r="I75" t="n">
         <v>11.79</v>
@@ -20538,7 +20558,7 @@
         <v>-16.62</v>
       </c>
       <c r="M75" t="n">
-        <v>3.95</v>
+        <v>4.3</v>
       </c>
       <c r="N75" t="b">
         <v>1</v>
@@ -20576,7 +20596,7 @@
         <v>-8.699999999999999</v>
       </c>
       <c r="H76" t="n">
-        <v>-10</v>
+        <v>-10.88</v>
       </c>
       <c r="I76" t="n">
         <v>17.25</v>
@@ -20589,7 +20609,7 @@
         <v>-4.65</v>
       </c>
       <c r="M76" t="n">
-        <v>-13.89</v>
+        <v>-14.02</v>
       </c>
       <c r="N76" t="b">
         <v>1</v>
@@ -20627,7 +20647,7 @@
         <v>15.2</v>
       </c>
       <c r="H77" t="n">
-        <v>-2.17</v>
+        <v>-5.42</v>
       </c>
       <c r="I77" t="n">
         <v>5.36</v>
@@ -20640,7 +20660,7 @@
         <v>-28.18</v>
       </c>
       <c r="M77" t="n">
-        <v>-5.31</v>
+        <v>-8.470000000000001</v>
       </c>
       <c r="N77" t="b">
         <v>1</v>
@@ -20678,7 +20698,7 @@
         <v>37.2</v>
       </c>
       <c r="H78" t="n">
-        <v>-24.28</v>
+        <v>-25.65</v>
       </c>
       <c r="I78" t="n">
         <v>-7.64</v>
@@ -20691,7 +20711,7 @@
         <v>-26.24</v>
       </c>
       <c r="M78" t="n">
-        <v>-28.17</v>
+        <v>-28.78</v>
       </c>
       <c r="N78" t="b">
         <v>1</v>
@@ -20729,7 +20749,7 @@
         <v>29.8</v>
       </c>
       <c r="H79" t="n">
-        <v>27.51</v>
+        <v>31.4</v>
       </c>
       <c r="I79" t="n">
         <v>-2.74</v>
@@ -20742,7 +20762,7 @@
         <v>-22.36</v>
       </c>
       <c r="M79" t="n">
-        <v>23.62</v>
+        <v>28.26</v>
       </c>
       <c r="N79" t="b">
         <v>1</v>
@@ -20780,7 +20800,7 @@
         <v>19.3</v>
       </c>
       <c r="H80" t="n">
-        <v>-20.34</v>
+        <v>-21.28</v>
       </c>
       <c r="I80" t="n">
         <v>-16.69</v>
@@ -20793,7 +20813,7 @@
         <v>-36.39</v>
       </c>
       <c r="M80" t="n">
-        <v>-24.23</v>
+        <v>-24.42</v>
       </c>
       <c r="N80" t="b">
         <v>1</v>
@@ -20831,7 +20851,7 @@
         <v>11.8</v>
       </c>
       <c r="H81" t="n">
-        <v>-0.28</v>
+        <v>3.01</v>
       </c>
       <c r="I81" t="n">
         <v>-1.19</v>
@@ -20844,7 +20864,7 @@
         <v>-17.57</v>
       </c>
       <c r="M81" t="n">
-        <v>-4.17</v>
+        <v>-0.13</v>
       </c>
       <c r="N81" t="b">
         <v>1</v>
@@ -20882,7 +20902,7 @@
         <v>27.5</v>
       </c>
       <c r="H82" t="n">
-        <v>18.32</v>
+        <v>6.64</v>
       </c>
       <c r="I82" t="n">
         <v>8.42</v>
@@ -20895,7 +20915,7 @@
         <v>-2.51</v>
       </c>
       <c r="M82" t="n">
-        <v>14.44</v>
+        <v>3.5</v>
       </c>
       <c r="N82" t="b">
         <v>1</v>
@@ -20933,7 +20953,7 @@
         <v>-22.4</v>
       </c>
       <c r="H83" t="n">
-        <v>-9.869999999999999</v>
+        <v>-9.81</v>
       </c>
       <c r="I83" t="n">
         <v>9.42</v>
@@ -20946,7 +20966,7 @@
         <v>-2.79</v>
       </c>
       <c r="M83" t="n">
-        <v>-13.75</v>
+        <v>-12.95</v>
       </c>
       <c r="N83" t="b">
         <v>1</v>
@@ -20984,7 +21004,7 @@
         <v>-14.7</v>
       </c>
       <c r="H84" t="n">
-        <v>-9.34</v>
+        <v>-12.35</v>
       </c>
       <c r="I84" t="n">
         <v>10.3</v>
@@ -20997,7 +21017,7 @@
         <v>-2.6</v>
       </c>
       <c r="M84" t="n">
-        <v>-13.23</v>
+        <v>-15.48</v>
       </c>
       <c r="N84" t="b">
         <v>1</v>
@@ -21039,7 +21059,7 @@
         <v>-9.300000000000001</v>
       </c>
       <c r="H85" t="n">
-        <v>-23.63</v>
+        <v>-24.23</v>
       </c>
       <c r="I85" t="n">
         <v>10.42</v>
@@ -21052,7 +21072,7 @@
         <v>-21.72</v>
       </c>
       <c r="M85" t="n">
-        <v>-27.52</v>
+        <v>-27.36</v>
       </c>
       <c r="N85" t="b">
         <v>1</v>
@@ -21090,7 +21110,7 @@
         <v>-25.2</v>
       </c>
       <c r="H86" t="n">
-        <v>15.86</v>
+        <v>20.17</v>
       </c>
       <c r="I86" t="n">
         <v>22.53</v>
@@ -21103,7 +21123,7 @@
         <v>-19.27</v>
       </c>
       <c r="M86" t="n">
-        <v>12.72</v>
+        <v>17.12</v>
       </c>
       <c r="N86" t="b">
         <v>1</v>
@@ -21141,7 +21161,7 @@
         <v>5.1</v>
       </c>
       <c r="H87" t="n">
-        <v>0.9</v>
+        <v>-0.02</v>
       </c>
       <c r="I87" t="n">
         <v>8.77</v>
@@ -21154,7 +21174,7 @@
         <v>-3.54</v>
       </c>
       <c r="M87" t="n">
-        <v>-2.99</v>
+        <v>-3.16</v>
       </c>
       <c r="N87" t="b">
         <v>1</v>
@@ -21192,7 +21212,7 @@
         <v>34.2</v>
       </c>
       <c r="H88" t="n">
-        <v>7.74</v>
+        <v>7.98</v>
       </c>
       <c r="I88" t="n">
         <v>8.15</v>
@@ -21205,7 +21225,7 @@
         <v>-7.63</v>
       </c>
       <c r="M88" t="n">
-        <v>3.86</v>
+        <v>4.85</v>
       </c>
       <c r="N88" t="b">
         <v>1</v>
@@ -21243,7 +21263,7 @@
         <v>42</v>
       </c>
       <c r="H89" t="n">
-        <v>-30.27</v>
+        <v>-29.24</v>
       </c>
       <c r="I89" t="n">
         <v>0.6</v>
@@ -21256,7 +21276,7 @@
         <v>-16.67</v>
       </c>
       <c r="M89" t="n">
-        <v>-34.16</v>
+        <v>-32.38</v>
       </c>
       <c r="N89" t="b">
         <v>1</v>
@@ -21294,7 +21314,7 @@
         <v>-25.3</v>
       </c>
       <c r="H90" t="n">
-        <v>30.77</v>
+        <v>31.36</v>
       </c>
       <c r="I90" t="n">
         <v>36.1</v>
@@ -21307,7 +21327,7 @@
         <v>-5.66</v>
       </c>
       <c r="M90" t="n">
-        <v>26.89</v>
+        <v>28.22</v>
       </c>
       <c r="N90" t="b">
         <v>1</v>
@@ -21345,7 +21365,7 @@
         <v>-7.7</v>
       </c>
       <c r="H91" t="n">
-        <v>-3.75</v>
+        <v>-2.74</v>
       </c>
       <c r="I91" t="n">
         <v>-6.47</v>
@@ -21358,7 +21378,7 @@
         <v>-23.05</v>
       </c>
       <c r="M91" t="n">
-        <v>-7.64</v>
+        <v>-5.88</v>
       </c>
       <c r="N91" t="b">
         <v>1</v>
@@ -21396,7 +21416,7 @@
         <v>13.7</v>
       </c>
       <c r="H92" t="n">
-        <v>7.27</v>
+        <v>5.64</v>
       </c>
       <c r="I92" t="n">
         <v>2.74</v>
@@ -21409,7 +21429,7 @@
         <v>-24.02</v>
       </c>
       <c r="M92" t="n">
-        <v>3.38</v>
+        <v>2.5</v>
       </c>
       <c r="N92" t="b">
         <v>1</v>
@@ -21447,7 +21467,7 @@
         <v>21.8</v>
       </c>
       <c r="H93" t="n">
-        <v>-0.49</v>
+        <v>-0.25</v>
       </c>
       <c r="I93" t="n">
         <v>18.32</v>
@@ -21460,7 +21480,7 @@
         <v>-23.27</v>
       </c>
       <c r="M93" t="n">
-        <v>-4.38</v>
+        <v>-3.39</v>
       </c>
       <c r="N93" t="b">
         <v>1</v>
@@ -21498,7 +21518,7 @@
         <v>29.4</v>
       </c>
       <c r="H94" t="n">
-        <v>-4.41</v>
+        <v>-5.28</v>
       </c>
       <c r="I94" t="n">
         <v>-2.62</v>
@@ -21511,7 +21531,7 @@
         <v>-27.18</v>
       </c>
       <c r="M94" t="n">
-        <v>-8.300000000000001</v>
+        <v>-8.42</v>
       </c>
       <c r="N94" t="b">
         <v>1</v>
@@ -21549,7 +21569,7 @@
         <v>-3.7</v>
       </c>
       <c r="H95" t="n">
-        <v>-24.58</v>
+        <v>-24.34</v>
       </c>
       <c r="I95" t="n">
         <v>-8.07</v>
@@ -21562,7 +21582,7 @@
         <v>-22.12</v>
       </c>
       <c r="M95" t="n">
-        <v>-28.46</v>
+        <v>-27.48</v>
       </c>
       <c r="N95" t="b">
         <v>1</v>
@@ -21600,7 +21620,7 @@
         <v>21.3</v>
       </c>
       <c r="H96" t="n">
-        <v>1.54</v>
+        <v>1.6</v>
       </c>
       <c r="I96" t="n">
         <v>0.23</v>
@@ -21613,7 +21633,7 @@
         <v>-0.85</v>
       </c>
       <c r="M96" t="n">
-        <v>-2.35</v>
+        <v>-1.54</v>
       </c>
       <c r="N96" t="b">
         <v>1</v>
@@ -21651,7 +21671,7 @@
         <v>-21.4</v>
       </c>
       <c r="H97" t="n">
-        <v>24.14</v>
+        <v>21.9</v>
       </c>
       <c r="I97" t="n">
         <v>4.55</v>
@@ -21664,7 +21684,7 @@
         <v>-6.39</v>
       </c>
       <c r="M97" t="n">
-        <v>21</v>
+        <v>18.84</v>
       </c>
       <c r="N97" t="b">
         <v>1</v>
@@ -21702,7 +21722,7 @@
         <v>16.3</v>
       </c>
       <c r="H98" t="n">
-        <v>5.89</v>
+        <v>5.88</v>
       </c>
       <c r="I98" t="n">
         <v>-1</v>
@@ -21715,7 +21735,7 @@
         <v>-22.5</v>
       </c>
       <c r="M98" t="n">
-        <v>2</v>
+        <v>2.74</v>
       </c>
       <c r="N98" t="b">
         <v>1</v>
@@ -21753,7 +21773,7 @@
         <v>11.9</v>
       </c>
       <c r="H99" t="n">
-        <v>-2.14</v>
+        <v>-1.52</v>
       </c>
       <c r="I99" t="n">
         <v>7.74</v>
@@ -21766,7 +21786,7 @@
         <v>-9.43</v>
       </c>
       <c r="M99" t="n">
-        <v>-6.02</v>
+        <v>-4.66</v>
       </c>
       <c r="N99" t="b">
         <v>1</v>
@@ -21804,7 +21824,7 @@
         <v>0.2</v>
       </c>
       <c r="H100" t="n">
-        <v>10.27</v>
+        <v>9.23</v>
       </c>
       <c r="I100" t="n">
         <v>4.35</v>
@@ -21817,7 +21837,7 @@
         <v>-2.79</v>
       </c>
       <c r="M100" t="n">
-        <v>6.38</v>
+        <v>6.09</v>
       </c>
       <c r="N100" t="b">
         <v>1</v>
@@ -21855,7 +21875,7 @@
         <v>8.4</v>
       </c>
       <c r="H101" t="n">
-        <v>-32.4</v>
+        <v>-34.53</v>
       </c>
       <c r="I101" t="n">
         <v>-0.13</v>
@@ -21868,7 +21888,7 @@
         <v>-10.87</v>
       </c>
       <c r="M101" t="n">
-        <v>-36.29</v>
+        <v>-37.67</v>
       </c>
       <c r="N101" t="b">
         <v>1</v>
@@ -21906,7 +21926,7 @@
         <v>-7.3</v>
       </c>
       <c r="H102" t="n">
-        <v>-20.32</v>
+        <v>-22.11</v>
       </c>
       <c r="I102" t="n">
         <v>-4.12</v>
@@ -21919,7 +21939,7 @@
         <v>-15.02</v>
       </c>
       <c r="M102" t="n">
-        <v>-24.2</v>
+        <v>-25.25</v>
       </c>
       <c r="N102" t="b">
         <v>1</v>
@@ -21957,7 +21977,7 @@
         <v>-26.1</v>
       </c>
       <c r="H103" t="n">
-        <v>-17.55</v>
+        <v>-18.77</v>
       </c>
       <c r="I103" t="n">
         <v>5.05</v>
@@ -21970,7 +21990,7 @@
         <v>-9.27</v>
       </c>
       <c r="M103" t="n">
-        <v>-21.43</v>
+        <v>-21.91</v>
       </c>
       <c r="N103" t="b">
         <v>1</v>
@@ -22008,7 +22028,7 @@
         <v>26.1</v>
       </c>
       <c r="H104" t="n">
-        <v>-8.859999999999999</v>
+        <v>-7.88</v>
       </c>
       <c r="I104" t="n">
         <v>-0.51</v>
@@ -22021,7 +22041,7 @@
         <v>-16.45</v>
       </c>
       <c r="M104" t="n">
-        <v>-12.75</v>
+        <v>-11.02</v>
       </c>
       <c r="N104" t="b">
         <v>1</v>
@@ -22059,7 +22079,7 @@
         <v>17.9</v>
       </c>
       <c r="H105" t="n">
-        <v>2.5</v>
+        <v>2.19</v>
       </c>
       <c r="I105" t="n">
         <v>12.97</v>
@@ -22072,7 +22092,7 @@
         <v>-8.130000000000001</v>
       </c>
       <c r="M105" t="n">
-        <v>-1.39</v>
+        <v>-0.95</v>
       </c>
       <c r="N105" t="b">
         <v>1</v>
@@ -22110,7 +22130,7 @@
         <v>0.7</v>
       </c>
       <c r="H106" t="n">
-        <v>-14.69</v>
+        <v>-15.75</v>
       </c>
       <c r="I106" t="n">
         <v>14.96</v>
@@ -22123,7 +22143,7 @@
         <v>-8.039999999999999</v>
       </c>
       <c r="M106" t="n">
-        <v>-18.58</v>
+        <v>-18.89</v>
       </c>
       <c r="N106" t="b">
         <v>1</v>
@@ -22161,7 +22181,7 @@
         <v>14.8</v>
       </c>
       <c r="H107" t="n">
-        <v>-3.36</v>
+        <v>-6.66</v>
       </c>
       <c r="I107" t="n">
         <v>0.35</v>
@@ -22174,7 +22194,7 @@
         <v>-3.68</v>
       </c>
       <c r="M107" t="n">
-        <v>-7.24</v>
+        <v>-9.800000000000001</v>
       </c>
       <c r="N107" t="b">
         <v>1</v>
@@ -22212,7 +22232,7 @@
         <v>25.5</v>
       </c>
       <c r="H108" t="n">
-        <v>2.52</v>
+        <v>2.91</v>
       </c>
       <c r="I108" t="n">
         <v>-9.369999999999999</v>
@@ -22225,7 +22245,7 @@
         <v>-22.11</v>
       </c>
       <c r="M108" t="n">
-        <v>-1.37</v>
+        <v>-0.23</v>
       </c>
       <c r="N108" t="b">
         <v>1</v>
@@ -22267,7 +22287,7 @@
         <v>-7.5</v>
       </c>
       <c r="H109" t="n">
-        <v>-3.18</v>
+        <v>-5.58</v>
       </c>
       <c r="I109" t="n">
         <v>4.46</v>
@@ -22280,7 +22300,7 @@
         <v>-8.52</v>
       </c>
       <c r="M109" t="n">
-        <v>-7.07</v>
+        <v>-8.720000000000001</v>
       </c>
       <c r="N109" t="b">
         <v>1</v>
@@ -22318,7 +22338,7 @@
         <v>-11</v>
       </c>
       <c r="H110" t="n">
-        <v>5.58</v>
+        <v>4.27</v>
       </c>
       <c r="I110" t="n">
         <v>10.7</v>
@@ -22331,7 +22351,7 @@
         <v>-9.43</v>
       </c>
       <c r="M110" t="n">
-        <v>1.69</v>
+        <v>1.14</v>
       </c>
       <c r="N110" t="b">
         <v>1</v>
@@ -22369,7 +22389,7 @@
         <v>-11.4</v>
       </c>
       <c r="H111" t="n">
-        <v>-10.82</v>
+        <v>-12.98</v>
       </c>
       <c r="I111" t="n">
         <v>4.36</v>
@@ -22382,7 +22402,7 @@
         <v>-11.36</v>
       </c>
       <c r="M111" t="n">
-        <v>-14.71</v>
+        <v>-16.12</v>
       </c>
       <c r="N111" t="b">
         <v>1</v>
@@ -22420,7 +22440,7 @@
         <v>27.1</v>
       </c>
       <c r="H112" t="n">
-        <v>-7.41</v>
+        <v>-6.99</v>
       </c>
       <c r="I112" t="n">
         <v>5.02</v>
@@ -22433,7 +22453,7 @@
         <v>-14.35</v>
       </c>
       <c r="M112" t="n">
-        <v>-11.3</v>
+        <v>-10.13</v>
       </c>
       <c r="N112" t="b">
         <v>1</v>
@@ -22471,7 +22491,7 @@
         <v>32.2</v>
       </c>
       <c r="H113" t="n">
-        <v>16.88</v>
+        <v>16.6</v>
       </c>
       <c r="I113" t="n">
         <v>6.49</v>
@@ -22484,7 +22504,7 @@
         <v>-3.92</v>
       </c>
       <c r="M113" t="n">
-        <v>12.99</v>
+        <v>13.46</v>
       </c>
       <c r="N113" t="b">
         <v>1</v>
@@ -22522,7 +22542,7 @@
         <v>3.2</v>
       </c>
       <c r="H114" t="n">
-        <v>-22.68</v>
+        <v>-20.88</v>
       </c>
       <c r="I114" t="n">
         <v>-10.41</v>
@@ -22535,7 +22555,7 @@
         <v>-23.7</v>
       </c>
       <c r="M114" t="n">
-        <v>-26.56</v>
+        <v>-24.02</v>
       </c>
       <c r="N114" t="b">
         <v>1</v>
@@ -22573,7 +22593,7 @@
         <v>7.3</v>
       </c>
       <c r="H115" t="n">
-        <v>-1.42</v>
+        <v>-1.07</v>
       </c>
       <c r="I115" t="n">
         <v>-0.57</v>
@@ -22586,7 +22606,7 @@
         <v>-5.89</v>
       </c>
       <c r="M115" t="n">
-        <v>-5.3</v>
+        <v>-4.21</v>
       </c>
       <c r="N115" t="b">
         <v>1</v>
@@ -22624,7 +22644,7 @@
         <v>-0.3</v>
       </c>
       <c r="H116" t="n">
-        <v>-3.58</v>
+        <v>-4.06</v>
       </c>
       <c r="I116" t="n">
         <v>17.76</v>
@@ -22637,7 +22657,7 @@
         <v>-14.18</v>
       </c>
       <c r="M116" t="n">
-        <v>-7.47</v>
+        <v>-7.2</v>
       </c>
       <c r="N116" t="b">
         <v>1</v>
@@ -22675,7 +22695,7 @@
         <v>-6.8</v>
       </c>
       <c r="H117" t="n">
-        <v>48.27</v>
+        <v>42.36</v>
       </c>
       <c r="I117" t="n">
         <v>8.279999999999999</v>
@@ -22688,7 +22708,7 @@
         <v>-6.78</v>
       </c>
       <c r="M117" t="n">
-        <v>44.38</v>
+        <v>39.22</v>
       </c>
       <c r="N117" t="b">
         <v>1</v>
@@ -22726,7 +22746,7 @@
         <v>34.6</v>
       </c>
       <c r="H118" t="n">
-        <v>-2.73</v>
+        <v>-1.66</v>
       </c>
       <c r="I118" t="n">
         <v>5.7</v>
@@ -22739,7 +22759,7 @@
         <v>-7.7</v>
       </c>
       <c r="M118" t="n">
-        <v>-6.62</v>
+        <v>-4.8</v>
       </c>
       <c r="N118" t="b">
         <v>1</v>
@@ -22777,7 +22797,7 @@
         <v>10.4</v>
       </c>
       <c r="H119" t="n">
-        <v>25.82</v>
+        <v>23.85</v>
       </c>
       <c r="I119" t="n">
         <v>11.05</v>
@@ -22790,7 +22810,7 @@
         <v>-5.54</v>
       </c>
       <c r="M119" t="n">
-        <v>21.93</v>
+        <v>20.71</v>
       </c>
       <c r="N119" t="b">
         <v>1</v>
@@ -22828,7 +22848,7 @@
         <v>-21.5</v>
       </c>
       <c r="H120" t="n">
-        <v>-14.83</v>
+        <v>-15.89</v>
       </c>
       <c r="I120" t="n">
         <v>10.65</v>
@@ -22841,7 +22861,7 @@
         <v>-6.89</v>
       </c>
       <c r="M120" t="n">
-        <v>-17.97</v>
+        <v>-18.94</v>
       </c>
       <c r="N120" t="b">
         <v>1</v>
@@ -22879,7 +22899,7 @@
         <v>3.5</v>
       </c>
       <c r="H121" t="n">
-        <v>43.51</v>
+        <v>49.54</v>
       </c>
       <c r="I121" t="n">
         <v>33.01</v>
@@ -22892,7 +22912,7 @@
         <v>-0.92</v>
       </c>
       <c r="M121" t="n">
-        <v>39.62</v>
+        <v>46.4</v>
       </c>
       <c r="N121" t="b">
         <v>1</v>
@@ -22930,7 +22950,7 @@
         <v>19.8</v>
       </c>
       <c r="H122" t="n">
-        <v>8.460000000000001</v>
+        <v>9.74</v>
       </c>
       <c r="I122" t="n">
         <v>4.74</v>
@@ -22943,7 +22963,7 @@
         <v>-9.9</v>
       </c>
       <c r="M122" t="n">
-        <v>4.57</v>
+        <v>6.6</v>
       </c>
       <c r="N122" t="b">
         <v>1</v>
@@ -22981,7 +23001,7 @@
         <v>-30.5</v>
       </c>
       <c r="H123" t="n">
-        <v>1.71</v>
+        <v>-0.91</v>
       </c>
       <c r="I123" t="n">
         <v>2.96</v>
@@ -22994,7 +23014,7 @@
         <v>-17.88</v>
       </c>
       <c r="M123" t="n">
-        <v>-1.43</v>
+        <v>-3.96</v>
       </c>
       <c r="N123" t="b">
         <v>1</v>
@@ -23032,7 +23052,7 @@
         <v>-6</v>
       </c>
       <c r="H124" t="n">
-        <v>-22.02</v>
+        <v>-22.5</v>
       </c>
       <c r="I124" t="n">
         <v>3.31</v>
@@ -23045,7 +23065,7 @@
         <v>-21.48</v>
       </c>
       <c r="M124" t="n">
-        <v>-25.9</v>
+        <v>-25.64</v>
       </c>
       <c r="N124" t="b">
         <v>1</v>
@@ -23083,7 +23103,7 @@
         <v>-34.6</v>
       </c>
       <c r="H125" t="n">
-        <v>1.94</v>
+        <v>-1.18</v>
       </c>
       <c r="I125" t="n">
         <v>23.65</v>
@@ -23096,7 +23116,7 @@
         <v>-3.83</v>
       </c>
       <c r="M125" t="n">
-        <v>-1.95</v>
+        <v>-4.32</v>
       </c>
       <c r="N125" t="b">
         <v>1</v>
@@ -23134,7 +23154,7 @@
         <v>-16.2</v>
       </c>
       <c r="H126" t="n">
-        <v>12.69</v>
+        <v>9.41</v>
       </c>
       <c r="I126" t="n">
         <v>25.77</v>
@@ -23147,7 +23167,7 @@
         <v>-1.7</v>
       </c>
       <c r="M126" t="n">
-        <v>8.81</v>
+        <v>6.27</v>
       </c>
       <c r="N126" t="b">
         <v>1</v>
@@ -23185,7 +23205,7 @@
         <v>-24.9</v>
       </c>
       <c r="H127" t="n">
-        <v>32.15</v>
+        <v>29.55</v>
       </c>
       <c r="I127" t="n">
         <v>10.88</v>
@@ -23198,7 +23218,7 @@
         <v>-4.1</v>
       </c>
       <c r="M127" t="n">
-        <v>28.26</v>
+        <v>26.41</v>
       </c>
       <c r="N127" t="b">
         <v>1</v>
@@ -23240,7 +23260,7 @@
         <v>-8.1</v>
       </c>
       <c r="H128" t="n">
-        <v>20.27</v>
+        <v>17.07</v>
       </c>
       <c r="I128" t="n">
         <v>14.27</v>
@@ -23253,7 +23273,7 @@
         <v>-10.92</v>
       </c>
       <c r="M128" t="n">
-        <v>16.38</v>
+        <v>13.93</v>
       </c>
       <c r="N128" t="b">
         <v>1</v>
@@ -23291,7 +23311,7 @@
         <v>-10.2</v>
       </c>
       <c r="H129" t="n">
-        <v>-10.2</v>
+        <v>-12.03</v>
       </c>
       <c r="I129" t="n">
         <v>15.03</v>
@@ -23304,7 +23324,7 @@
         <v>-1.61</v>
       </c>
       <c r="M129" t="n">
-        <v>-14.08</v>
+        <v>-15.17</v>
       </c>
       <c r="N129" t="b">
         <v>1</v>
@@ -23342,7 +23362,7 @@
         <v>68.90000000000001</v>
       </c>
       <c r="H130" t="n">
-        <v>9.32</v>
+        <v>11.54</v>
       </c>
       <c r="I130" t="n">
         <v>1.84</v>
@@ -23355,7 +23375,7 @@
         <v>-10.43</v>
       </c>
       <c r="M130" t="n">
-        <v>5.44</v>
+        <v>8.4</v>
       </c>
       <c r="N130" t="b">
         <v>1</v>
@@ -23393,7 +23413,7 @@
         <v>-40.8</v>
       </c>
       <c r="H131" t="n">
-        <v>-10.17</v>
+        <v>-10.04</v>
       </c>
       <c r="I131" t="n">
         <v>21.71</v>
@@ -23406,7 +23426,7 @@
         <v>-3.3</v>
       </c>
       <c r="M131" t="n">
-        <v>-14.06</v>
+        <v>-13.18</v>
       </c>
       <c r="N131" t="b">
         <v>1</v>
@@ -23444,7 +23464,7 @@
         <v>40.7</v>
       </c>
       <c r="H132" t="n">
-        <v>43.7</v>
+        <v>48.13</v>
       </c>
       <c r="I132" t="n">
         <v>-4.08</v>
@@ -23457,7 +23477,7 @@
         <v>-11.2</v>
       </c>
       <c r="M132" t="n">
-        <v>39.81</v>
+        <v>44.99</v>
       </c>
       <c r="N132" t="b">
         <v>1</v>
@@ -23495,7 +23515,7 @@
         <v>25.7</v>
       </c>
       <c r="H133" t="n">
-        <v>-9.32</v>
+        <v>-10.08</v>
       </c>
       <c r="I133" t="n">
         <v>11.3</v>
@@ -23508,7 +23528,7 @@
         <v>-11.03</v>
       </c>
       <c r="M133" t="n">
-        <v>-13.21</v>
+        <v>-13.22</v>
       </c>
       <c r="N133" t="b">
         <v>1</v>

--- a/STS_holy_grail_v2.xlsx
+++ b/STS_holy_grail_v2.xlsx
@@ -666,7 +666,7 @@
         <v>38.1</v>
       </c>
       <c r="E18" t="n">
-        <v>-3.2</v>
+        <v>-3.19</v>
       </c>
     </row>
     <row r="19">
@@ -789,7 +789,7 @@
         <v>5</v>
       </c>
       <c r="C26" t="n">
-        <v>-3.65</v>
+        <v>-3.64</v>
       </c>
       <c r="D26" t="n">
         <v>40</v>
@@ -1016,7 +1016,7 @@
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="n">
-        <v>-0.85</v>
+        <v>-0.84</v>
       </c>
       <c r="M2" t="n">
         <v>0.32</v>
@@ -1392,7 +1392,7 @@
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="n">
-        <v>-4.82</v>
+        <v>-4.83</v>
       </c>
       <c r="M10" t="n">
         <v>-5.34</v>
@@ -2003,7 +2003,7 @@
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="n">
-        <v>-2.06</v>
+        <v>-2.04</v>
       </c>
       <c r="M23" t="n">
         <v>-2.68</v>
@@ -2097,7 +2097,7 @@
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="n">
-        <v>-3.74</v>
+        <v>-3.73</v>
       </c>
       <c r="M25" t="n">
         <v>-4.66</v>
@@ -2477,7 +2477,7 @@
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="n">
-        <v>-7.29</v>
+        <v>-7.28</v>
       </c>
       <c r="M33" t="n">
         <v>-8.220000000000001</v>
@@ -7829,7 +7829,7 @@
         <v>-34.6</v>
       </c>
       <c r="H139" t="n">
-        <v>15.11</v>
+        <v>15.13</v>
       </c>
       <c r="I139" t="n">
         <v>6.67</v>
@@ -7842,7 +7842,7 @@
         <v>-3.06</v>
       </c>
       <c r="M139" t="n">
-        <v>10.61</v>
+        <v>10.63</v>
       </c>
       <c r="N139" t="b">
         <v>1</v>
@@ -7880,7 +7880,7 @@
         <v>-21.4</v>
       </c>
       <c r="H140" t="n">
-        <v>-1.45</v>
+        <v>-1.44</v>
       </c>
       <c r="I140" t="n">
         <v>2.8</v>
@@ -7893,7 +7893,7 @@
         <v>-2.27</v>
       </c>
       <c r="M140" t="n">
-        <v>-5.95</v>
+        <v>-5.94</v>
       </c>
       <c r="N140" t="b">
         <v>0</v>
@@ -13408,7 +13408,7 @@
         <v>36.8</v>
       </c>
       <c r="H248" t="n">
-        <v>21.94</v>
+        <v>21.95</v>
       </c>
       <c r="I248" t="n">
         <v>15.47</v>
@@ -14028,7 +14028,7 @@
         <v>-8.199999999999999</v>
       </c>
       <c r="H260" t="n">
-        <v>-8.470000000000001</v>
+        <v>-8.44</v>
       </c>
       <c r="I260" t="n">
         <v>17.48</v>
@@ -14041,7 +14041,7 @@
         <v>-10.68</v>
       </c>
       <c r="M260" t="n">
-        <v>-12.08</v>
+        <v>-12.05</v>
       </c>
       <c r="N260" t="b">
         <v>0</v>
@@ -14954,7 +14954,7 @@
         <v>32.2</v>
       </c>
       <c r="H278" t="n">
-        <v>19.1</v>
+        <v>19.11</v>
       </c>
       <c r="I278" t="n">
         <v>6.49</v>
@@ -14967,7 +14967,7 @@
         <v>-3.92</v>
       </c>
       <c r="M278" t="n">
-        <v>15.49</v>
+        <v>15.5</v>
       </c>
       <c r="N278" t="b">
         <v>1</v>
@@ -17049,7 +17049,7 @@
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="n">
-        <v>-0.85</v>
+        <v>-0.84</v>
       </c>
       <c r="M2" t="n">
         <v>0.32</v>
@@ -17519,7 +17519,7 @@
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="n">
-        <v>-2.06</v>
+        <v>-2.04</v>
       </c>
       <c r="M12" t="n">
         <v>-2.68</v>
@@ -17660,7 +17660,7 @@
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="n">
-        <v>-7.29</v>
+        <v>-7.28</v>
       </c>
       <c r="M15" t="n">
         <v>-8.220000000000001</v>
@@ -19621,7 +19621,7 @@
         <v>-34.6</v>
       </c>
       <c r="H54" t="n">
-        <v>15.11</v>
+        <v>15.13</v>
       </c>
       <c r="I54" t="n">
         <v>6.67</v>
@@ -19634,7 +19634,7 @@
         <v>-3.06</v>
       </c>
       <c r="M54" t="n">
-        <v>10.61</v>
+        <v>10.63</v>
       </c>
       <c r="N54" t="b">
         <v>1</v>
@@ -22740,7 +22740,7 @@
         <v>32.2</v>
       </c>
       <c r="H115" t="n">
-        <v>19.1</v>
+        <v>19.11</v>
       </c>
       <c r="I115" t="n">
         <v>6.49</v>
@@ -22753,7 +22753,7 @@
         <v>-3.92</v>
       </c>
       <c r="M115" t="n">
-        <v>15.49</v>
+        <v>15.5</v>
       </c>
       <c r="N115" t="b">
         <v>1</v>

--- a/STS_holy_grail_v2.xlsx
+++ b/STS_holy_grail_v2.xlsx
@@ -464,7 +464,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.95</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="5">
@@ -474,7 +474,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.7</v>
+        <v>-1.3</v>
       </c>
     </row>
     <row r="6">
@@ -484,7 +484,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>45.4</v>
+        <v>42.9</v>
       </c>
     </row>
     <row r="8">
@@ -531,13 +531,13 @@
         <v>61</v>
       </c>
       <c r="C10" t="n">
-        <v>1.81</v>
+        <v>0.86</v>
       </c>
       <c r="D10" t="n">
-        <v>50.82</v>
+        <v>47.54</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.53</v>
+        <v>-0.73</v>
       </c>
     </row>
     <row r="11">
@@ -550,13 +550,13 @@
         <v>79</v>
       </c>
       <c r="C11" t="n">
-        <v>2.01</v>
+        <v>0.22</v>
       </c>
       <c r="D11" t="n">
-        <v>43.04</v>
+        <v>41.77</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.25</v>
+        <v>-2.31</v>
       </c>
     </row>
     <row r="12">
@@ -569,13 +569,13 @@
         <v>142</v>
       </c>
       <c r="C12" t="n">
-        <v>1.53</v>
+        <v>-0.14</v>
       </c>
       <c r="D12" t="n">
-        <v>40.14</v>
+        <v>36.62</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.17</v>
+        <v>-2.08</v>
       </c>
     </row>
     <row r="13">
@@ -588,13 +588,13 @@
         <v>33</v>
       </c>
       <c r="C13" t="n">
-        <v>3.83</v>
+        <v>4.18</v>
       </c>
       <c r="D13" t="n">
         <v>63.64</v>
       </c>
       <c r="E13" t="n">
-        <v>2.34</v>
+        <v>3.45</v>
       </c>
     </row>
     <row r="15">
@@ -641,13 +641,13 @@
         <v>101</v>
       </c>
       <c r="C17" t="n">
-        <v>2.47</v>
+        <v>0.73</v>
       </c>
       <c r="D17" t="n">
-        <v>40.59</v>
+        <v>38.61</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.32</v>
+        <v>-1.3</v>
       </c>
     </row>
     <row r="18">
@@ -660,13 +660,13 @@
         <v>42</v>
       </c>
       <c r="C18" t="n">
-        <v>-0.78</v>
+        <v>-2.27</v>
       </c>
       <c r="D18" t="n">
-        <v>38.1</v>
+        <v>30.95</v>
       </c>
       <c r="E18" t="n">
-        <v>-3.19</v>
+        <v>-3.94</v>
       </c>
     </row>
     <row r="19">
@@ -679,13 +679,13 @@
         <v>45</v>
       </c>
       <c r="C19" t="n">
-        <v>-1.58</v>
+        <v>-3.46</v>
       </c>
       <c r="D19" t="n">
-        <v>37.78</v>
+        <v>33.33</v>
       </c>
       <c r="E19" t="n">
-        <v>-4.12</v>
+        <v>-5.26</v>
       </c>
     </row>
     <row r="20">
@@ -698,13 +698,13 @@
         <v>39</v>
       </c>
       <c r="C20" t="n">
-        <v>-4.85</v>
+        <v>-6</v>
       </c>
       <c r="D20" t="n">
-        <v>38.46</v>
+        <v>35.9</v>
       </c>
       <c r="E20" t="n">
-        <v>-7.4</v>
+        <v>-7.81</v>
       </c>
     </row>
     <row r="21">
@@ -717,13 +717,13 @@
         <v>88</v>
       </c>
       <c r="C21" t="n">
-        <v>7.46</v>
+        <v>6.81</v>
       </c>
       <c r="D21" t="n">
         <v>61.36</v>
       </c>
       <c r="E21" t="n">
-        <v>4.77</v>
+        <v>4.88</v>
       </c>
     </row>
     <row r="23">
@@ -770,13 +770,13 @@
         <v>10</v>
       </c>
       <c r="C25" t="n">
-        <v>6.92</v>
+        <v>4.69</v>
       </c>
       <c r="D25" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="E25" t="n">
-        <v>3.82</v>
+        <v>2.35</v>
       </c>
     </row>
     <row r="26">
@@ -789,13 +789,13 @@
         <v>5</v>
       </c>
       <c r="C26" t="n">
-        <v>-3.64</v>
+        <v>-4.76</v>
       </c>
       <c r="D26" t="n">
         <v>40</v>
       </c>
       <c r="E26" t="n">
-        <v>-7.46</v>
+        <v>-7.8</v>
       </c>
     </row>
     <row r="27">
@@ -808,13 +808,13 @@
         <v>3</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.18</v>
+        <v>-0.44</v>
       </c>
       <c r="D27" t="n">
         <v>33.33</v>
       </c>
       <c r="E27" t="n">
-        <v>-2.96</v>
+        <v>-2.45</v>
       </c>
     </row>
     <row r="29">
@@ -861,13 +861,13 @@
         <v>181</v>
       </c>
       <c r="C31" t="n">
-        <v>3.31</v>
+        <v>1.85</v>
       </c>
       <c r="D31" t="n">
-        <v>43.09</v>
+        <v>39.78</v>
       </c>
       <c r="E31" t="n">
-        <v>0.67</v>
+        <v>-0.04</v>
       </c>
     </row>
     <row r="32">
@@ -880,13 +880,13 @@
         <v>134</v>
       </c>
       <c r="C32" t="n">
-        <v>0.11</v>
+        <v>-1.1</v>
       </c>
       <c r="D32" t="n">
-        <v>48.51</v>
+        <v>47.01</v>
       </c>
       <c r="E32" t="n">
-        <v>-2.55</v>
+        <v>-3</v>
       </c>
     </row>
   </sheetData>
@@ -1010,16 +1010,16 @@
         <v>0.1</v>
       </c>
       <c r="H2" t="n">
-        <v>0.65</v>
+        <v>0.19</v>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="n">
-        <v>-0.84</v>
+        <v>-1.9</v>
       </c>
       <c r="M2" t="n">
-        <v>0.32</v>
+        <v>0.6</v>
       </c>
       <c r="N2" t="b">
         <v>1</v>
@@ -1046,7 +1046,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Extended</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="E3" t="inlineStr"/>
@@ -1057,16 +1057,16 @@
         <v>-31.6</v>
       </c>
       <c r="H3" t="n">
-        <v>5.1</v>
+        <v>-1.71</v>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="n">
-        <v>-0.77</v>
+        <v>-3.1</v>
       </c>
       <c r="M3" t="n">
-        <v>4.77</v>
+        <v>-1.3</v>
       </c>
       <c r="N3" t="b">
         <v>1</v>
@@ -1104,16 +1104,16 @@
         <v>7.6</v>
       </c>
       <c r="H4" t="n">
-        <v>-3.44</v>
+        <v>-2.32</v>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="n">
-        <v>-4.04</v>
+        <v>-6.34</v>
       </c>
       <c r="M4" t="n">
-        <v>-4.4</v>
+        <v>-2.52</v>
       </c>
       <c r="N4" t="b">
         <v>0</v>
@@ -1151,16 +1151,16 @@
         <v>-17.9</v>
       </c>
       <c r="H5" t="n">
-        <v>-3.36</v>
+        <v>-4.59</v>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="n">
-        <v>-6.42</v>
+        <v>-6.52</v>
       </c>
       <c r="M5" t="n">
-        <v>-3.01</v>
+        <v>-3.5</v>
       </c>
       <c r="N5" t="b">
         <v>0</v>
@@ -1198,16 +1198,16 @@
         <v>-2.7</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.45</v>
+        <v>-1.96</v>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="n">
-        <v>-3.59</v>
+        <v>-3.64</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.1</v>
+        <v>-0.87</v>
       </c>
       <c r="N6" t="b">
         <v>1</v>
@@ -1245,7 +1245,7 @@
         <v>-25.3</v>
       </c>
       <c r="H7" t="n">
-        <v>2.16</v>
+        <v>4.35</v>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
@@ -1254,7 +1254,7 @@
         <v>-0.24</v>
       </c>
       <c r="M7" t="n">
-        <v>2.5</v>
+        <v>5.44</v>
       </c>
       <c r="N7" t="b">
         <v>0</v>
@@ -1292,7 +1292,7 @@
         <v>25.6</v>
       </c>
       <c r="H8" t="n">
-        <v>-4.72</v>
+        <v>-3.62</v>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
@@ -1301,7 +1301,7 @@
         <v>-5.59</v>
       </c>
       <c r="M8" t="n">
-        <v>-4.37</v>
+        <v>-2.53</v>
       </c>
       <c r="N8" t="b">
         <v>0</v>
@@ -1328,7 +1328,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Extended</t>
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
@@ -1339,7 +1339,7 @@
         <v>26.9</v>
       </c>
       <c r="H9" t="n">
-        <v>4.96</v>
+        <v>7.4</v>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
@@ -1348,7 +1348,7 @@
         <v>-0.4</v>
       </c>
       <c r="M9" t="n">
-        <v>5.3</v>
+        <v>8.49</v>
       </c>
       <c r="N9" t="b">
         <v>1</v>
@@ -1386,16 +1386,16 @@
         <v>-14.5</v>
       </c>
       <c r="H10" t="n">
-        <v>-4.67</v>
+        <v>-5.52</v>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="n">
-        <v>-4.83</v>
+        <v>-5.52</v>
       </c>
       <c r="M10" t="n">
-        <v>-5.34</v>
+        <v>-5.44</v>
       </c>
       <c r="N10" t="b">
         <v>0</v>
@@ -1433,7 +1433,7 @@
         <v>17.2</v>
       </c>
       <c r="H11" t="n">
-        <v>-5.46</v>
+        <v>-6.29</v>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
@@ -1442,7 +1442,7 @@
         <v>-10.54</v>
       </c>
       <c r="M11" t="n">
-        <v>-6.12</v>
+        <v>-6.21</v>
       </c>
       <c r="N11" t="b">
         <v>0</v>
@@ -1480,7 +1480,7 @@
         <v>-13.2</v>
       </c>
       <c r="H12" t="n">
-        <v>14.14</v>
+        <v>14.34</v>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
@@ -1489,7 +1489,7 @@
         <v>-0.82</v>
       </c>
       <c r="M12" t="n">
-        <v>13.47</v>
+        <v>14.42</v>
       </c>
       <c r="N12" t="b">
         <v>0</v>
@@ -1527,16 +1527,16 @@
         <v>-7.7</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.3</v>
+        <v>-4.17</v>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="n">
-        <v>-3.04</v>
+        <v>-4.37</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.96</v>
+        <v>-4.09</v>
       </c>
       <c r="N13" t="b">
         <v>0</v>
@@ -1574,7 +1574,7 @@
         <v>-18.1</v>
       </c>
       <c r="H14" t="n">
-        <v>-2.84</v>
+        <v>-1.69</v>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
@@ -1583,7 +1583,7 @@
         <v>-3.11</v>
       </c>
       <c r="M14" t="n">
-        <v>-3.51</v>
+        <v>-1.61</v>
       </c>
       <c r="N14" t="b">
         <v>0</v>
@@ -1621,7 +1621,7 @@
         <v>-18.1</v>
       </c>
       <c r="H15" t="n">
-        <v>1.26</v>
+        <v>2.58</v>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
@@ -1630,7 +1630,7 @@
         <v>-2.69</v>
       </c>
       <c r="M15" t="n">
-        <v>0.6</v>
+        <v>2.66</v>
       </c>
       <c r="N15" t="b">
         <v>1</v>
@@ -1668,7 +1668,7 @@
         <v>7.7</v>
       </c>
       <c r="H16" t="n">
-        <v>-5.41</v>
+        <v>-5.39</v>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
@@ -1677,7 +1677,7 @@
         <v>-8.16</v>
       </c>
       <c r="M16" t="n">
-        <v>-6.08</v>
+        <v>-5.31</v>
       </c>
       <c r="N16" t="b">
         <v>0</v>
@@ -1704,7 +1704,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Extended</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="E17" t="inlineStr"/>
@@ -1715,7 +1715,7 @@
         <v>-21.5</v>
       </c>
       <c r="H17" t="n">
-        <v>5.5</v>
+        <v>4.37</v>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
@@ -1724,7 +1724,7 @@
         <v>-1.4</v>
       </c>
       <c r="M17" t="n">
-        <v>4.83</v>
+        <v>4.46</v>
       </c>
       <c r="N17" t="b">
         <v>1</v>
@@ -1762,7 +1762,7 @@
         <v>41.6</v>
       </c>
       <c r="H18" t="n">
-        <v>3.15</v>
+        <v>3.09</v>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
@@ -1771,7 +1771,7 @@
         <v>-4.38</v>
       </c>
       <c r="M18" t="n">
-        <v>1.83</v>
+        <v>2.52</v>
       </c>
       <c r="N18" t="b">
         <v>1</v>
@@ -1809,16 +1809,16 @@
         <v>32.1</v>
       </c>
       <c r="H19" t="n">
-        <v>-2.58</v>
+        <v>-4.54</v>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="n">
-        <v>-4.4</v>
+        <v>-6.94</v>
       </c>
       <c r="M19" t="n">
-        <v>-3.9</v>
+        <v>-5.1</v>
       </c>
       <c r="N19" t="b">
         <v>1</v>
@@ -1856,16 +1856,16 @@
         <v>-14.4</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.3</v>
+        <v>-2.71</v>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="n">
-        <v>-4.51</v>
+        <v>-4.62</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.62</v>
+        <v>-3.27</v>
       </c>
       <c r="N20" t="b">
         <v>1</v>
@@ -1903,7 +1903,7 @@
         <v>-16.8</v>
       </c>
       <c r="H21" t="n">
-        <v>4.98</v>
+        <v>4.83</v>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
@@ -1912,7 +1912,7 @@
         <v>-3.26</v>
       </c>
       <c r="M21" t="n">
-        <v>3.67</v>
+        <v>4.27</v>
       </c>
       <c r="N21" t="b">
         <v>0</v>
@@ -1950,16 +1950,16 @@
         <v>-10</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.33</v>
+        <v>-8.300000000000001</v>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="n">
-        <v>-5.75</v>
+        <v>-9.539999999999999</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.65</v>
+        <v>-8.859999999999999</v>
       </c>
       <c r="N22" t="b">
         <v>1</v>
@@ -1997,16 +1997,16 @@
         <v>6.4</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.36</v>
+        <v>-1.79</v>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="n">
-        <v>-2.04</v>
+        <v>-3.01</v>
       </c>
       <c r="M23" t="n">
-        <v>-2.68</v>
+        <v>-2.35</v>
       </c>
       <c r="N23" t="b">
         <v>1</v>
@@ -2044,7 +2044,7 @@
         <v>-11</v>
       </c>
       <c r="H24" t="n">
-        <v>5.31</v>
+        <v>6.5</v>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
@@ -2053,7 +2053,7 @@
         <v>-0.97</v>
       </c>
       <c r="M24" t="n">
-        <v>3.98</v>
+        <v>5.93</v>
       </c>
       <c r="N24" t="b">
         <v>0</v>
@@ -2091,7 +2091,7 @@
         <v>-23.9</v>
       </c>
       <c r="H25" t="n">
-        <v>-3.33</v>
+        <v>-2.18</v>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
@@ -2100,7 +2100,7 @@
         <v>-3.73</v>
       </c>
       <c r="M25" t="n">
-        <v>-4.66</v>
+        <v>-2.75</v>
       </c>
       <c r="N25" t="b">
         <v>0</v>
@@ -2142,16 +2142,16 @@
         <v>-9.800000000000001</v>
       </c>
       <c r="H26" t="n">
-        <v>-4.28</v>
+        <v>-5.29</v>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="n">
-        <v>-4.44</v>
+        <v>-7.62</v>
       </c>
       <c r="M26" t="n">
-        <v>-5.6</v>
+        <v>-5.86</v>
       </c>
       <c r="N26" t="b">
         <v>0</v>
@@ -2189,7 +2189,7 @@
         <v>-36.1</v>
       </c>
       <c r="H27" t="n">
-        <v>4.2</v>
+        <v>3.46</v>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
@@ -2198,7 +2198,7 @@
         <v>-1.92</v>
       </c>
       <c r="M27" t="n">
-        <v>2.87</v>
+        <v>2.88</v>
       </c>
       <c r="N27" t="b">
         <v>0</v>
@@ -2236,7 +2236,7 @@
         <v>-7.9</v>
       </c>
       <c r="H28" t="n">
-        <v>-10.53</v>
+        <v>-7.44</v>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
@@ -2245,7 +2245,7 @@
         <v>-11.04</v>
       </c>
       <c r="M28" t="n">
-        <v>-11.86</v>
+        <v>-8.01</v>
       </c>
       <c r="N28" t="b">
         <v>0</v>
@@ -2283,16 +2283,16 @@
         <v>2.6</v>
       </c>
       <c r="H29" t="n">
-        <v>-7.98</v>
+        <v>-8.91</v>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="n">
-        <v>-8.640000000000001</v>
+        <v>-10.71</v>
       </c>
       <c r="M29" t="n">
-        <v>-9.789999999999999</v>
+        <v>-9.960000000000001</v>
       </c>
       <c r="N29" t="b">
         <v>0</v>
@@ -2319,7 +2319,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Extended</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="E30" t="inlineStr"/>
@@ -2330,7 +2330,7 @@
         <v>6.3</v>
       </c>
       <c r="H30" t="n">
-        <v>5.29</v>
+        <v>4.98</v>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
@@ -2339,7 +2339,7 @@
         <v>-0.7</v>
       </c>
       <c r="M30" t="n">
-        <v>3.48</v>
+        <v>3.92</v>
       </c>
       <c r="N30" t="b">
         <v>0</v>
@@ -2377,7 +2377,7 @@
         <v>20.2</v>
       </c>
       <c r="H31" t="n">
-        <v>2.69</v>
+        <v>4.34</v>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
@@ -2386,7 +2386,7 @@
         <v>-1.07</v>
       </c>
       <c r="M31" t="n">
-        <v>0.96</v>
+        <v>3.37</v>
       </c>
       <c r="N31" t="b">
         <v>1</v>
@@ -2413,7 +2413,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Extended</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="E32" t="inlineStr"/>
@@ -2424,7 +2424,7 @@
         <v>43.7</v>
       </c>
       <c r="H32" t="n">
-        <v>5.33</v>
+        <v>4.39</v>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
@@ -2433,7 +2433,7 @@
         <v>-2.44</v>
       </c>
       <c r="M32" t="n">
-        <v>3.6</v>
+        <v>3.42</v>
       </c>
       <c r="N32" t="b">
         <v>1</v>
@@ -2471,16 +2471,16 @@
         <v>1.9</v>
       </c>
       <c r="H33" t="n">
-        <v>-6.49</v>
+        <v>-9.949999999999999</v>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="n">
-        <v>-7.28</v>
+        <v>-11.15</v>
       </c>
       <c r="M33" t="n">
-        <v>-8.220000000000001</v>
+        <v>-10.92</v>
       </c>
       <c r="N33" t="b">
         <v>1</v>
@@ -2518,16 +2518,18 @@
         <v>37.5</v>
       </c>
       <c r="H34" t="n">
-        <v>5.24</v>
-      </c>
-      <c r="I34" t="inlineStr"/>
+        <v>5.86</v>
+      </c>
+      <c r="I34" t="n">
+        <v>5.86</v>
+      </c>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="n">
         <v>-3.95</v>
       </c>
       <c r="M34" t="n">
-        <v>3.36</v>
+        <v>4.74</v>
       </c>
       <c r="N34" t="b">
         <v>1</v>
@@ -2565,16 +2567,18 @@
         <v>15</v>
       </c>
       <c r="H35" t="n">
-        <v>-20.56</v>
-      </c>
-      <c r="I35" t="inlineStr"/>
+        <v>-21.11</v>
+      </c>
+      <c r="I35" t="n">
+        <v>-21.11</v>
+      </c>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="n">
-        <v>-22.27</v>
+        <v>-22.89</v>
       </c>
       <c r="M35" t="n">
-        <v>-22.44</v>
+        <v>-22.23</v>
       </c>
       <c r="N35" t="b">
         <v>0</v>
@@ -2612,16 +2616,18 @@
         <v>40.2</v>
       </c>
       <c r="H36" t="n">
-        <v>-1.57</v>
-      </c>
-      <c r="I36" t="inlineStr"/>
+        <v>-1.11</v>
+      </c>
+      <c r="I36" t="n">
+        <v>-1.11</v>
+      </c>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="n">
         <v>-3.87</v>
       </c>
       <c r="M36" t="n">
-        <v>-3.45</v>
+        <v>-2.23</v>
       </c>
       <c r="N36" t="b">
         <v>1</v>
@@ -2659,16 +2665,18 @@
         <v>10.7</v>
       </c>
       <c r="H37" t="n">
-        <v>6.71</v>
-      </c>
-      <c r="I37" t="inlineStr"/>
+        <v>7.3</v>
+      </c>
+      <c r="I37" t="n">
+        <v>7.3</v>
+      </c>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="n">
         <v>-3.78</v>
       </c>
       <c r="M37" t="n">
-        <v>4.83</v>
+        <v>6.18</v>
       </c>
       <c r="N37" t="b">
         <v>1</v>
@@ -2706,7 +2714,7 @@
         <v>25.6</v>
       </c>
       <c r="H38" t="n">
-        <v>7.71</v>
+        <v>10.29</v>
       </c>
       <c r="I38" t="n">
         <v>7.71</v>
@@ -2717,7 +2725,7 @@
         <v>-4.85</v>
       </c>
       <c r="M38" t="n">
-        <v>6.6</v>
+        <v>9.93</v>
       </c>
       <c r="N38" t="b">
         <v>1</v>
@@ -2755,7 +2763,7 @@
         <v>6.3</v>
       </c>
       <c r="H39" t="n">
-        <v>10.03</v>
+        <v>8.85</v>
       </c>
       <c r="I39" t="n">
         <v>7.2</v>
@@ -2766,7 +2774,7 @@
         <v>-0.4</v>
       </c>
       <c r="M39" t="n">
-        <v>8.02</v>
+        <v>7.6</v>
       </c>
       <c r="N39" t="b">
         <v>0</v>
@@ -2804,7 +2812,7 @@
         <v>2.3</v>
       </c>
       <c r="H40" t="n">
-        <v>-7.41</v>
+        <v>-10.2</v>
       </c>
       <c r="I40" t="n">
         <v>-8.85</v>
@@ -2815,7 +2823,7 @@
         <v>-11.75</v>
       </c>
       <c r="M40" t="n">
-        <v>-9.42</v>
+        <v>-11.45</v>
       </c>
       <c r="N40" t="b">
         <v>0</v>
@@ -2853,7 +2861,7 @@
         <v>-4.3</v>
       </c>
       <c r="H41" t="n">
-        <v>7.72</v>
+        <v>6.74</v>
       </c>
       <c r="I41" t="n">
         <v>3.39</v>
@@ -2864,7 +2872,7 @@
         <v>-5.89</v>
       </c>
       <c r="M41" t="n">
-        <v>6.52</v>
+        <v>6.29</v>
       </c>
       <c r="N41" t="b">
         <v>0</v>
@@ -2902,7 +2910,7 @@
         <v>-29.4</v>
       </c>
       <c r="H42" t="n">
-        <v>-6.47</v>
+        <v>-4.93</v>
       </c>
       <c r="I42" t="n">
         <v>-5.75</v>
@@ -2913,7 +2921,7 @@
         <v>-9.640000000000001</v>
       </c>
       <c r="M42" t="n">
-        <v>-7.67</v>
+        <v>-5.38</v>
       </c>
       <c r="N42" t="b">
         <v>0</v>
@@ -2951,7 +2959,7 @@
         <v>-6.9</v>
       </c>
       <c r="H43" t="n">
-        <v>7.29</v>
+        <v>6.92</v>
       </c>
       <c r="I43" t="n">
         <v>6.44</v>
@@ -2962,7 +2970,7 @@
         <v>-4.53</v>
       </c>
       <c r="M43" t="n">
-        <v>6.08</v>
+        <v>6.47</v>
       </c>
       <c r="N43" t="b">
         <v>1</v>
@@ -3000,7 +3008,7 @@
         <v>4.2</v>
       </c>
       <c r="H44" t="n">
-        <v>-11.46</v>
+        <v>-14.35</v>
       </c>
       <c r="I44" t="n">
         <v>-10.83</v>
@@ -3008,10 +3016,10 @@
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="n">
-        <v>-13.81</v>
+        <v>-14.86</v>
       </c>
       <c r="M44" t="n">
-        <v>-12.66</v>
+        <v>-14.8</v>
       </c>
       <c r="N44" t="b">
         <v>0</v>
@@ -3049,7 +3057,7 @@
         <v>-32.4</v>
       </c>
       <c r="H45" t="n">
-        <v>-0.61</v>
+        <v>-2.26</v>
       </c>
       <c r="I45" t="n">
         <v>-2.43</v>
@@ -3060,7 +3068,7 @@
         <v>-12.47</v>
       </c>
       <c r="M45" t="n">
-        <v>-1.16</v>
+        <v>-2.06</v>
       </c>
       <c r="N45" t="b">
         <v>0</v>
@@ -3098,7 +3106,7 @@
         <v>-11</v>
       </c>
       <c r="H46" t="n">
-        <v>-4.66</v>
+        <v>-0.46</v>
       </c>
       <c r="I46" t="n">
         <v>-8.449999999999999</v>
@@ -3109,7 +3117,7 @@
         <v>-18.92</v>
       </c>
       <c r="M46" t="n">
-        <v>-5.2</v>
+        <v>-0.26</v>
       </c>
       <c r="N46" t="b">
         <v>0</v>
@@ -3136,7 +3144,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Extended</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="E47" t="inlineStr"/>
@@ -3147,7 +3155,7 @@
         <v>9.699999999999999</v>
       </c>
       <c r="H47" t="n">
-        <v>8.359999999999999</v>
+        <v>-11.64</v>
       </c>
       <c r="I47" t="n">
         <v>1.27</v>
@@ -3155,10 +3163,10 @@
       <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="n">
-        <v>-6.51</v>
+        <v>-20.79</v>
       </c>
       <c r="M47" t="n">
-        <v>7.67</v>
+        <v>-11.59</v>
       </c>
       <c r="N47" t="b">
         <v>0</v>
@@ -3196,7 +3204,7 @@
         <v>-28.1</v>
       </c>
       <c r="H48" t="n">
-        <v>-9.59</v>
+        <v>-9.199999999999999</v>
       </c>
       <c r="I48" t="n">
         <v>-10.79</v>
@@ -3207,7 +3215,7 @@
         <v>-12.06</v>
       </c>
       <c r="M48" t="n">
-        <v>-10.29</v>
+        <v>-9.15</v>
       </c>
       <c r="N48" t="b">
         <v>0</v>
@@ -3245,7 +3253,7 @@
         <v>-17.7</v>
       </c>
       <c r="H49" t="n">
-        <v>-2.8</v>
+        <v>-7.36</v>
       </c>
       <c r="I49" t="n">
         <v>-0.89</v>
@@ -3253,10 +3261,10 @@
       <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="n">
-        <v>-5.08</v>
+        <v>-7.71</v>
       </c>
       <c r="M49" t="n">
-        <v>-3.49</v>
+        <v>-7.31</v>
       </c>
       <c r="N49" t="b">
         <v>0</v>
@@ -3294,7 +3302,7 @@
         <v>-9.300000000000001</v>
       </c>
       <c r="H50" t="n">
-        <v>-2.38</v>
+        <v>-5.34</v>
       </c>
       <c r="I50" t="n">
         <v>-3.34</v>
@@ -3305,7 +3313,7 @@
         <v>-7.37</v>
       </c>
       <c r="M50" t="n">
-        <v>-3.08</v>
+        <v>-5.29</v>
       </c>
       <c r="N50" t="b">
         <v>0</v>
@@ -3343,7 +3351,7 @@
         <v>0.3</v>
       </c>
       <c r="H51" t="n">
-        <v>-10.95</v>
+        <v>-11.97</v>
       </c>
       <c r="I51" t="n">
         <v>-10.53</v>
@@ -3354,7 +3362,7 @@
         <v>-15.78</v>
       </c>
       <c r="M51" t="n">
-        <v>-11.64</v>
+        <v>-11.92</v>
       </c>
       <c r="N51" t="b">
         <v>1</v>
@@ -3392,7 +3400,7 @@
         <v>12.3</v>
       </c>
       <c r="H52" t="n">
-        <v>9.23</v>
+        <v>5.96</v>
       </c>
       <c r="I52" t="n">
         <v>6.51</v>
@@ -3403,7 +3411,7 @@
         <v>-6.01</v>
       </c>
       <c r="M52" t="n">
-        <v>7.81</v>
+        <v>5.29</v>
       </c>
       <c r="N52" t="b">
         <v>0</v>
@@ -3441,7 +3449,7 @@
         <v>2.8</v>
       </c>
       <c r="H53" t="n">
-        <v>3.05</v>
+        <v>1.95</v>
       </c>
       <c r="I53" t="n">
         <v>3.18</v>
@@ -3452,7 +3460,7 @@
         <v>-0.88</v>
       </c>
       <c r="M53" t="n">
-        <v>1.63</v>
+        <v>1.29</v>
       </c>
       <c r="N53" t="b">
         <v>1</v>
@@ -3490,7 +3498,7 @@
         <v>-1.4</v>
       </c>
       <c r="H54" t="n">
-        <v>11.63</v>
+        <v>10.31</v>
       </c>
       <c r="I54" t="n">
         <v>-4.52</v>
@@ -3501,7 +3509,7 @@
         <v>-7.44</v>
       </c>
       <c r="M54" t="n">
-        <v>10.22</v>
+        <v>9.65</v>
       </c>
       <c r="N54" t="b">
         <v>0</v>
@@ -3539,7 +3547,7 @@
         <v>34.5</v>
       </c>
       <c r="H55" t="n">
-        <v>7.09</v>
+        <v>7.62</v>
       </c>
       <c r="I55" t="n">
         <v>0.66</v>
@@ -3550,7 +3558,7 @@
         <v>-2.64</v>
       </c>
       <c r="M55" t="n">
-        <v>5.67</v>
+        <v>6.96</v>
       </c>
       <c r="N55" t="b">
         <v>1</v>
@@ -3588,7 +3596,7 @@
         <v>-22.7</v>
       </c>
       <c r="H56" t="n">
-        <v>-8</v>
+        <v>-8.380000000000001</v>
       </c>
       <c r="I56" t="n">
         <v>-6.71</v>
@@ -3596,10 +3604,10 @@
       <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="n">
-        <v>-8.67</v>
+        <v>-9.09</v>
       </c>
       <c r="M56" t="n">
-        <v>-9.470000000000001</v>
+        <v>-9.1</v>
       </c>
       <c r="N56" t="b">
         <v>0</v>
@@ -3626,7 +3634,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Extended</t>
+          <t>Retired</t>
         </is>
       </c>
       <c r="E57" t="inlineStr"/>
@@ -3637,7 +3645,7 @@
         <v>24.3</v>
       </c>
       <c r="H57" t="n">
-        <v>33.23</v>
+        <v>36.83</v>
       </c>
       <c r="I57" t="n">
         <v>2.54</v>
@@ -3648,7 +3656,7 @@
         <v>-5.21</v>
       </c>
       <c r="M57" t="n">
-        <v>32.46</v>
+        <v>36.81</v>
       </c>
       <c r="N57" t="b">
         <v>1</v>
@@ -3675,7 +3683,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Retired</t>
         </is>
       </c>
       <c r="E58" t="inlineStr"/>
@@ -3686,7 +3694,7 @@
         <v>56.6</v>
       </c>
       <c r="H58" t="n">
-        <v>-10.08</v>
+        <v>-10.27</v>
       </c>
       <c r="I58" t="n">
         <v>-13.1</v>
@@ -3697,7 +3705,7 @@
         <v>-16.17</v>
       </c>
       <c r="M58" t="n">
-        <v>-10.86</v>
+        <v>-10.29</v>
       </c>
       <c r="N58" t="b">
         <v>0</v>
@@ -3724,7 +3732,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Retired</t>
         </is>
       </c>
       <c r="E59" t="inlineStr"/>
@@ -3735,7 +3743,7 @@
         <v>2.9</v>
       </c>
       <c r="H59" t="n">
-        <v>-11.51</v>
+        <v>-14.65</v>
       </c>
       <c r="I59" t="n">
         <v>-8.470000000000001</v>
@@ -3743,10 +3751,10 @@
       <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="n">
-        <v>-14</v>
+        <v>-15.15</v>
       </c>
       <c r="M59" t="n">
-        <v>-12.29</v>
+        <v>-14.68</v>
       </c>
       <c r="N59" t="b">
         <v>0</v>
@@ -3773,7 +3781,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Retired</t>
         </is>
       </c>
       <c r="E60" t="inlineStr"/>
@@ -3784,7 +3792,7 @@
         <v>-16.9</v>
       </c>
       <c r="H60" t="n">
-        <v>-6.47</v>
+        <v>-8.789999999999999</v>
       </c>
       <c r="I60" t="n">
         <v>-6.47</v>
@@ -3795,7 +3803,7 @@
         <v>-11.5</v>
       </c>
       <c r="M60" t="n">
-        <v>-7.25</v>
+        <v>-8.82</v>
       </c>
       <c r="N60" t="b">
         <v>1</v>
@@ -3833,18 +3841,20 @@
         <v>32.8</v>
       </c>
       <c r="H61" t="n">
-        <v>5.77</v>
+        <v>5.84</v>
       </c>
       <c r="I61" t="n">
         <v>14.96</v>
       </c>
-      <c r="J61" t="inlineStr"/>
+      <c r="J61" t="n">
+        <v>5.84</v>
+      </c>
       <c r="K61" t="inlineStr"/>
       <c r="L61" t="n">
         <v>-0.9</v>
       </c>
       <c r="M61" t="n">
-        <v>5.58</v>
+        <v>6.39</v>
       </c>
       <c r="N61" t="b">
         <v>0</v>
@@ -3882,18 +3892,20 @@
         <v>0.8</v>
       </c>
       <c r="H62" t="n">
-        <v>-5.39</v>
+        <v>-6.26</v>
       </c>
       <c r="I62" t="n">
         <v>-7.73</v>
       </c>
-      <c r="J62" t="inlineStr"/>
+      <c r="J62" t="n">
+        <v>-6.26</v>
+      </c>
       <c r="K62" t="inlineStr"/>
       <c r="L62" t="n">
         <v>-10.12</v>
       </c>
       <c r="M62" t="n">
-        <v>-5.59</v>
+        <v>-5.71</v>
       </c>
       <c r="N62" t="b">
         <v>0</v>
@@ -3931,18 +3943,20 @@
         <v>-9.6</v>
       </c>
       <c r="H63" t="n">
-        <v>-15.22</v>
+        <v>-17.48</v>
       </c>
       <c r="I63" t="n">
         <v>-1.23</v>
       </c>
-      <c r="J63" t="inlineStr"/>
+      <c r="J63" t="n">
+        <v>-17.48</v>
+      </c>
       <c r="K63" t="inlineStr"/>
       <c r="L63" t="n">
         <v>-18.52</v>
       </c>
       <c r="M63" t="n">
-        <v>-15.42</v>
+        <v>-16.93</v>
       </c>
       <c r="N63" t="b">
         <v>0</v>
@@ -3980,7 +3994,7 @@
         <v>20.3</v>
       </c>
       <c r="H64" t="n">
-        <v>-13.45</v>
+        <v>-17.1</v>
       </c>
       <c r="I64" t="n">
         <v>-2.07</v>
@@ -3993,7 +4007,7 @@
         <v>-17.35</v>
       </c>
       <c r="M64" t="n">
-        <v>-14.07</v>
+        <v>-16.97</v>
       </c>
       <c r="N64" t="b">
         <v>1</v>
@@ -4031,7 +4045,7 @@
         <v>0.3</v>
       </c>
       <c r="H65" t="n">
-        <v>-18.35</v>
+        <v>-19.53</v>
       </c>
       <c r="I65" t="n">
         <v>-9.9</v>
@@ -4044,7 +4058,7 @@
         <v>-21.72</v>
       </c>
       <c r="M65" t="n">
-        <v>-19.46</v>
+        <v>-19.9</v>
       </c>
       <c r="N65" t="b">
         <v>1</v>
@@ -4082,7 +4096,7 @@
         <v>49.4</v>
       </c>
       <c r="H66" t="n">
-        <v>4.28</v>
+        <v>1.86</v>
       </c>
       <c r="I66" t="n">
         <v>2.9</v>
@@ -4095,7 +4109,7 @@
         <v>-5.67</v>
       </c>
       <c r="M66" t="n">
-        <v>3.36</v>
+        <v>1.68</v>
       </c>
       <c r="N66" t="b">
         <v>1</v>
@@ -4133,7 +4147,7 @@
         <v>4.5</v>
       </c>
       <c r="H67" t="n">
-        <v>-9.99</v>
+        <v>-10.46</v>
       </c>
       <c r="I67" t="n">
         <v>-7.61</v>
@@ -4146,7 +4160,7 @@
         <v>-11.06</v>
       </c>
       <c r="M67" t="n">
-        <v>-10.92</v>
+        <v>-10.63</v>
       </c>
       <c r="N67" t="b">
         <v>1</v>
@@ -4184,7 +4198,7 @@
         <v>4.2</v>
       </c>
       <c r="H68" t="n">
-        <v>-18.9</v>
+        <v>-19.08</v>
       </c>
       <c r="I68" t="n">
         <v>-6.86</v>
@@ -4197,7 +4211,7 @@
         <v>-20.23</v>
       </c>
       <c r="M68" t="n">
-        <v>-19.82</v>
+        <v>-19.26</v>
       </c>
       <c r="N68" t="b">
         <v>0</v>
@@ -4235,7 +4249,7 @@
         <v>15.4</v>
       </c>
       <c r="H69" t="n">
-        <v>-4.75</v>
+        <v>-4.44</v>
       </c>
       <c r="I69" t="n">
         <v>-1.19</v>
@@ -4248,7 +4262,7 @@
         <v>-7.43</v>
       </c>
       <c r="M69" t="n">
-        <v>-5.68</v>
+        <v>-4.61</v>
       </c>
       <c r="N69" t="b">
         <v>0</v>
@@ -4286,7 +4300,7 @@
         <v>15.5</v>
       </c>
       <c r="H70" t="n">
-        <v>-9.460000000000001</v>
+        <v>-11.5</v>
       </c>
       <c r="I70" t="n">
         <v>-7.36</v>
@@ -4299,7 +4313,7 @@
         <v>-12.98</v>
       </c>
       <c r="M70" t="n">
-        <v>-10.57</v>
+        <v>-11.86</v>
       </c>
       <c r="N70" t="b">
         <v>0</v>
@@ -4341,7 +4355,7 @@
         <v>-8.5</v>
       </c>
       <c r="H71" t="n">
-        <v>-4.62</v>
+        <v>-5.51</v>
       </c>
       <c r="I71" t="n">
         <v>-3.04</v>
@@ -4354,7 +4368,7 @@
         <v>-4.96</v>
       </c>
       <c r="M71" t="n">
-        <v>-5.73</v>
+        <v>-5.87</v>
       </c>
       <c r="N71" t="b">
         <v>0</v>
@@ -4392,7 +4406,7 @@
         <v>1.8</v>
       </c>
       <c r="H72" t="n">
-        <v>-14.37</v>
+        <v>-16</v>
       </c>
       <c r="I72" t="n">
         <v>-6.45</v>
@@ -4405,7 +4419,7 @@
         <v>-13.57</v>
       </c>
       <c r="M72" t="n">
-        <v>-15.48</v>
+        <v>-16.35</v>
       </c>
       <c r="N72" t="b">
         <v>0</v>
@@ -4443,7 +4457,7 @@
         <v>33.9</v>
       </c>
       <c r="H73" t="n">
-        <v>6.27</v>
+        <v>7.98</v>
       </c>
       <c r="I73" t="n">
         <v>-7.74</v>
@@ -4456,7 +4470,7 @@
         <v>-9.449999999999999</v>
       </c>
       <c r="M73" t="n">
-        <v>5.16</v>
+        <v>7.62</v>
       </c>
       <c r="N73" t="b">
         <v>0</v>
@@ -4494,7 +4508,7 @@
         <v>-25</v>
       </c>
       <c r="H74" t="n">
-        <v>-6.25</v>
+        <v>-8.51</v>
       </c>
       <c r="I74" t="n">
         <v>2.51</v>
@@ -4507,7 +4521,7 @@
         <v>-4.88</v>
       </c>
       <c r="M74" t="n">
-        <v>-7.19</v>
+        <v>-8.699999999999999</v>
       </c>
       <c r="N74" t="b">
         <v>0</v>
@@ -4545,7 +4559,7 @@
         <v>-12.6</v>
       </c>
       <c r="H75" t="n">
-        <v>-24.52</v>
+        <v>-24.82</v>
       </c>
       <c r="I75" t="n">
         <v>-7.89</v>
@@ -4558,7 +4572,7 @@
         <v>-21.29</v>
       </c>
       <c r="M75" t="n">
-        <v>-25.48</v>
+        <v>-25.02</v>
       </c>
       <c r="N75" t="b">
         <v>0</v>
@@ -4596,7 +4610,7 @@
         <v>-17.9</v>
       </c>
       <c r="H76" t="n">
-        <v>-9.42</v>
+        <v>-10.3</v>
       </c>
       <c r="I76" t="n">
         <v>0.6</v>
@@ -4609,7 +4623,7 @@
         <v>-4.72</v>
       </c>
       <c r="M76" t="n">
-        <v>-10.37</v>
+        <v>-10.5</v>
       </c>
       <c r="N76" t="b">
         <v>1</v>
@@ -4647,7 +4661,7 @@
         <v>2.1</v>
       </c>
       <c r="H77" t="n">
-        <v>-21.48</v>
+        <v>-22.71</v>
       </c>
       <c r="I77" t="n">
         <v>0.25</v>
@@ -4660,7 +4674,7 @@
         <v>-16.43</v>
       </c>
       <c r="M77" t="n">
-        <v>-22.43</v>
+        <v>-22.92</v>
       </c>
       <c r="N77" t="b">
         <v>1</v>
@@ -4698,7 +4712,7 @@
         <v>19.4</v>
       </c>
       <c r="H78" t="n">
-        <v>-11.55</v>
+        <v>-10.07</v>
       </c>
       <c r="I78" t="n">
         <v>-10.01</v>
@@ -4711,7 +4725,7 @@
         <v>-15.23</v>
       </c>
       <c r="M78" t="n">
-        <v>-11.93</v>
+        <v>-9.699999999999999</v>
       </c>
       <c r="N78" t="b">
         <v>1</v>
@@ -4749,7 +4763,7 @@
         <v>-30.5</v>
       </c>
       <c r="H79" t="n">
-        <v>-21.21</v>
+        <v>-25.24</v>
       </c>
       <c r="I79" t="n">
         <v>-4.6</v>
@@ -4762,7 +4776,7 @@
         <v>-10.37</v>
       </c>
       <c r="M79" t="n">
-        <v>-21.59</v>
+        <v>-24.87</v>
       </c>
       <c r="N79" t="b">
         <v>0</v>
@@ -4800,7 +4814,7 @@
         <v>-20.5</v>
       </c>
       <c r="H80" t="n">
-        <v>-11.43</v>
+        <v>-13.32</v>
       </c>
       <c r="I80" t="n">
         <v>-4.62</v>
@@ -4813,7 +4827,7 @@
         <v>-9.92</v>
       </c>
       <c r="M80" t="n">
-        <v>-11.81</v>
+        <v>-12.95</v>
       </c>
       <c r="N80" t="b">
         <v>0</v>
@@ -4851,7 +4865,7 @@
         <v>-12.3</v>
       </c>
       <c r="H81" t="n">
-        <v>-22.85</v>
+        <v>-24.73</v>
       </c>
       <c r="I81" t="n">
         <v>-4.36</v>
@@ -4864,7 +4878,7 @@
         <v>-13.26</v>
       </c>
       <c r="M81" t="n">
-        <v>-23.44</v>
+        <v>-24.58</v>
       </c>
       <c r="N81" t="b">
         <v>0</v>
@@ -4902,7 +4916,7 @@
         <v>13.7</v>
       </c>
       <c r="H82" t="n">
-        <v>-16.18</v>
+        <v>-18.37</v>
       </c>
       <c r="I82" t="n">
         <v>-12.16</v>
@@ -4915,7 +4929,7 @@
         <v>-13.02</v>
       </c>
       <c r="M82" t="n">
-        <v>-16.77</v>
+        <v>-18.22</v>
       </c>
       <c r="N82" t="b">
         <v>0</v>
@@ -4953,7 +4967,7 @@
         <v>-2.6</v>
       </c>
       <c r="H83" t="n">
-        <v>-7.83</v>
+        <v>-8.779999999999999</v>
       </c>
       <c r="I83" t="n">
         <v>-4.27</v>
@@ -4966,7 +4980,7 @@
         <v>-4.86</v>
       </c>
       <c r="M83" t="n">
-        <v>-8.42</v>
+        <v>-8.630000000000001</v>
       </c>
       <c r="N83" t="b">
         <v>1</v>
@@ -5004,7 +5018,7 @@
         <v>25.6</v>
       </c>
       <c r="H84" t="n">
-        <v>-12.72</v>
+        <v>-12.1</v>
       </c>
       <c r="I84" t="n">
         <v>4.26</v>
@@ -5017,7 +5031,7 @@
         <v>-10.74</v>
       </c>
       <c r="M84" t="n">
-        <v>-13.31</v>
+        <v>-11.95</v>
       </c>
       <c r="N84" t="b">
         <v>0</v>
@@ -5055,7 +5069,7 @@
         <v>23.8</v>
       </c>
       <c r="H85" t="n">
-        <v>12.24</v>
+        <v>10.66</v>
       </c>
       <c r="I85" t="n">
         <v>1.36</v>
@@ -5068,7 +5082,7 @@
         <v>-9.94</v>
       </c>
       <c r="M85" t="n">
-        <v>12.61</v>
+        <v>11.78</v>
       </c>
       <c r="N85" t="b">
         <v>1</v>
@@ -5106,7 +5120,7 @@
         <v>38.9</v>
       </c>
       <c r="H86" t="n">
-        <v>-11.46</v>
+        <v>-12.52</v>
       </c>
       <c r="I86" t="n">
         <v>-9.220000000000001</v>
@@ -5119,7 +5133,7 @@
         <v>-9.83</v>
       </c>
       <c r="M86" t="n">
-        <v>-11.08</v>
+        <v>-11.4</v>
       </c>
       <c r="N86" t="b">
         <v>1</v>
@@ -5157,7 +5171,7 @@
         <v>32.1</v>
       </c>
       <c r="H87" t="n">
-        <v>41.35</v>
+        <v>42.35</v>
       </c>
       <c r="I87" t="n">
         <v>11.84</v>
@@ -5170,7 +5184,7 @@
         <v>-1.82</v>
       </c>
       <c r="M87" t="n">
-        <v>41.73</v>
+        <v>43.47</v>
       </c>
       <c r="N87" t="b">
         <v>0</v>
@@ -5208,7 +5222,7 @@
         <v>53.4</v>
       </c>
       <c r="H88" t="n">
-        <v>12.91</v>
+        <v>13.6</v>
       </c>
       <c r="I88" t="n">
         <v>2.75</v>
@@ -5221,7 +5235,7 @@
         <v>-2.31</v>
       </c>
       <c r="M88" t="n">
-        <v>13.58</v>
+        <v>15.02</v>
       </c>
       <c r="N88" t="b">
         <v>0</v>
@@ -5259,7 +5273,7 @@
         <v>54.1</v>
       </c>
       <c r="H89" t="n">
-        <v>14.24</v>
+        <v>13.06</v>
       </c>
       <c r="I89" t="n">
         <v>5.54</v>
@@ -5272,7 +5286,7 @@
         <v>-0.41</v>
       </c>
       <c r="M89" t="n">
-        <v>14.45</v>
+        <v>14.01</v>
       </c>
       <c r="N89" t="b">
         <v>0</v>
@@ -5310,7 +5324,7 @@
         <v>43.2</v>
       </c>
       <c r="H90" t="n">
-        <v>-21.48</v>
+        <v>-24.92</v>
       </c>
       <c r="I90" t="n">
         <v>-3.15</v>
@@ -5323,7 +5337,7 @@
         <v>-17.51</v>
       </c>
       <c r="M90" t="n">
-        <v>-21.27</v>
+        <v>-23.97</v>
       </c>
       <c r="N90" t="b">
         <v>1</v>
@@ -5361,7 +5375,7 @@
         <v>-8.199999999999999</v>
       </c>
       <c r="H91" t="n">
-        <v>-6.44</v>
+        <v>-7.24</v>
       </c>
       <c r="I91" t="n">
         <v>5.34</v>
@@ -5374,7 +5388,7 @@
         <v>-5.27</v>
       </c>
       <c r="M91" t="n">
-        <v>-6.23</v>
+        <v>-6.29</v>
       </c>
       <c r="N91" t="b">
         <v>1</v>
@@ -5412,7 +5426,7 @@
         <v>-1.2</v>
       </c>
       <c r="H92" t="n">
-        <v>-0.06</v>
+        <v>-2.51</v>
       </c>
       <c r="I92" t="n">
         <v>8.27</v>
@@ -5425,7 +5439,7 @@
         <v>-5.3</v>
       </c>
       <c r="M92" t="n">
-        <v>0.1</v>
+        <v>-1.61</v>
       </c>
       <c r="N92" t="b">
         <v>0</v>
@@ -5463,7 +5477,7 @@
         <v>-23.9</v>
       </c>
       <c r="H93" t="n">
-        <v>-8.869999999999999</v>
+        <v>-11.98</v>
       </c>
       <c r="I93" t="n">
         <v>3.28</v>
@@ -5476,7 +5490,7 @@
         <v>-4.46</v>
       </c>
       <c r="M93" t="n">
-        <v>-8.949999999999999</v>
+        <v>-11.32</v>
       </c>
       <c r="N93" t="b">
         <v>1</v>
@@ -5518,7 +5532,7 @@
         <v>-6.1</v>
       </c>
       <c r="H94" t="n">
-        <v>1.42</v>
+        <v>-1.93</v>
       </c>
       <c r="I94" t="n">
         <v>4.9</v>
@@ -5531,7 +5545,7 @@
         <v>-9</v>
       </c>
       <c r="M94" t="n">
-        <v>1.33</v>
+        <v>-1.27</v>
       </c>
       <c r="N94" t="b">
         <v>1</v>
@@ -5582,7 +5596,7 @@
         <v>-0.87</v>
       </c>
       <c r="M95" t="n">
-        <v>-1.19</v>
+        <v>-0.44</v>
       </c>
       <c r="N95" t="b">
         <v>1</v>
@@ -5620,7 +5634,7 @@
         <v>39.5</v>
       </c>
       <c r="H96" t="n">
-        <v>18.11</v>
+        <v>19.79</v>
       </c>
       <c r="I96" t="n">
         <v>-5.13</v>
@@ -5633,7 +5647,7 @@
         <v>-8.869999999999999</v>
       </c>
       <c r="M96" t="n">
-        <v>18.03</v>
+        <v>20.45</v>
       </c>
       <c r="N96" t="b">
         <v>0</v>
@@ -5671,7 +5685,7 @@
         <v>14.3</v>
       </c>
       <c r="H97" t="n">
-        <v>-5.44</v>
+        <v>-4.27</v>
       </c>
       <c r="I97" t="n">
         <v>-0.43</v>
@@ -5684,7 +5698,7 @@
         <v>-11.86</v>
       </c>
       <c r="M97" t="n">
-        <v>-5.53</v>
+        <v>-3.62</v>
       </c>
       <c r="N97" t="b">
         <v>0</v>
@@ -5722,7 +5736,7 @@
         <v>-11.3</v>
       </c>
       <c r="H98" t="n">
-        <v>-2.45</v>
+        <v>-3.5</v>
       </c>
       <c r="I98" t="n">
         <v>1.31</v>
@@ -5735,7 +5749,7 @@
         <v>-1.88</v>
       </c>
       <c r="M98" t="n">
-        <v>-2.54</v>
+        <v>-2.84</v>
       </c>
       <c r="N98" t="b">
         <v>0</v>
@@ -5773,7 +5787,7 @@
         <v>-23.5</v>
       </c>
       <c r="H99" t="n">
-        <v>-16.17</v>
+        <v>-18.33</v>
       </c>
       <c r="I99" t="n">
         <v>13.29</v>
@@ -5786,7 +5800,7 @@
         <v>-14.04</v>
       </c>
       <c r="M99" t="n">
-        <v>-16.26</v>
+        <v>-17.67</v>
       </c>
       <c r="N99" t="b">
         <v>0</v>
@@ -5824,7 +5838,7 @@
         <v>10.5</v>
       </c>
       <c r="H100" t="n">
-        <v>-9.76</v>
+        <v>-8.859999999999999</v>
       </c>
       <c r="I100" t="n">
         <v>-0.86</v>
@@ -5837,7 +5851,7 @@
         <v>-6.11</v>
       </c>
       <c r="M100" t="n">
-        <v>-9.85</v>
+        <v>-8.199999999999999</v>
       </c>
       <c r="N100" t="b">
         <v>0</v>
@@ -5875,7 +5889,7 @@
         <v>-3.5</v>
       </c>
       <c r="H101" t="n">
-        <v>0.78</v>
+        <v>0.03</v>
       </c>
       <c r="I101" t="n">
         <v>-4.95</v>
@@ -5888,7 +5902,7 @@
         <v>-8.43</v>
       </c>
       <c r="M101" t="n">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="N101" t="b">
         <v>1</v>
@@ -5926,7 +5940,7 @@
         <v>-12.8</v>
       </c>
       <c r="H102" t="n">
-        <v>0.05</v>
+        <v>-0.27</v>
       </c>
       <c r="I102" t="n">
         <v>-1.74</v>
@@ -5939,7 +5953,7 @@
         <v>-2.97</v>
       </c>
       <c r="M102" t="n">
-        <v>-0.24</v>
+        <v>0.19</v>
       </c>
       <c r="N102" t="b">
         <v>0</v>
@@ -5977,7 +5991,7 @@
         <v>2.4</v>
       </c>
       <c r="H103" t="n">
-        <v>18.49</v>
+        <v>17.12</v>
       </c>
       <c r="I103" t="n">
         <v>12.41</v>
@@ -5990,7 +6004,7 @@
         <v>-0.07000000000000001</v>
       </c>
       <c r="M103" t="n">
-        <v>18.2</v>
+        <v>17.58</v>
       </c>
       <c r="N103" t="b">
         <v>0</v>
@@ -6028,7 +6042,7 @@
         <v>-17.9</v>
       </c>
       <c r="H104" t="n">
-        <v>3.28</v>
+        <v>2.26</v>
       </c>
       <c r="I104" t="n">
         <v>-0.5</v>
@@ -6041,7 +6055,7 @@
         <v>-3.43</v>
       </c>
       <c r="M104" t="n">
-        <v>2.99</v>
+        <v>2.71</v>
       </c>
       <c r="N104" t="b">
         <v>1</v>
@@ -6079,7 +6093,7 @@
         <v>11.9</v>
       </c>
       <c r="H105" t="n">
-        <v>-5.34</v>
+        <v>-6.65</v>
       </c>
       <c r="I105" t="n">
         <v>6.88</v>
@@ -6092,7 +6106,7 @@
         <v>-10.93</v>
       </c>
       <c r="M105" t="n">
-        <v>-5.74</v>
+        <v>-6.3</v>
       </c>
       <c r="N105" t="b">
         <v>0</v>
@@ -6130,7 +6144,7 @@
         <v>53.5</v>
       </c>
       <c r="H106" t="n">
-        <v>-4.21</v>
+        <v>-3.43</v>
       </c>
       <c r="I106" t="n">
         <v>1.23</v>
@@ -6143,7 +6157,7 @@
         <v>-7.57</v>
       </c>
       <c r="M106" t="n">
-        <v>-4.6</v>
+        <v>-3.08</v>
       </c>
       <c r="N106" t="b">
         <v>1</v>
@@ -6194,7 +6208,7 @@
         <v>-1.92</v>
       </c>
       <c r="M107" t="n">
-        <v>-2.25</v>
+        <v>-1.51</v>
       </c>
       <c r="N107" t="b">
         <v>0</v>
@@ -6232,7 +6246,7 @@
         <v>-1</v>
       </c>
       <c r="H108" t="n">
-        <v>-13.35</v>
+        <v>-14.09</v>
       </c>
       <c r="I108" t="n">
         <v>-6.26</v>
@@ -6283,7 +6297,7 @@
         <v>29.7</v>
       </c>
       <c r="H109" t="n">
-        <v>8.119999999999999</v>
+        <v>11.69</v>
       </c>
       <c r="I109" t="n">
         <v>11.27</v>
@@ -6296,7 +6310,7 @@
         <v>0</v>
       </c>
       <c r="M109" t="n">
-        <v>7.73</v>
+        <v>12.04</v>
       </c>
       <c r="N109" t="b">
         <v>1</v>
@@ -6334,7 +6348,7 @@
         <v>15.2</v>
       </c>
       <c r="H110" t="n">
-        <v>-33.35</v>
+        <v>-34.47</v>
       </c>
       <c r="I110" t="n">
         <v>-8.77</v>
@@ -6347,7 +6361,7 @@
         <v>-24.79</v>
       </c>
       <c r="M110" t="n">
-        <v>-33.02</v>
+        <v>-33.4</v>
       </c>
       <c r="N110" t="b">
         <v>1</v>
@@ -6385,7 +6399,7 @@
         <v>22.2</v>
       </c>
       <c r="H111" t="n">
-        <v>6.06</v>
+        <v>7.56</v>
       </c>
       <c r="I111" t="n">
         <v>1.01</v>
@@ -6398,7 +6412,7 @@
         <v>-3.94</v>
       </c>
       <c r="M111" t="n">
-        <v>6.4</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="N111" t="b">
         <v>1</v>
@@ -6436,7 +6450,7 @@
         <v>10.8</v>
       </c>
       <c r="H112" t="n">
-        <v>0.21</v>
+        <v>-0.43</v>
       </c>
       <c r="I112" t="n">
         <v>5.62</v>
@@ -6449,7 +6463,7 @@
         <v>-1.59</v>
       </c>
       <c r="M112" t="n">
-        <v>0.54</v>
+        <v>0.64</v>
       </c>
       <c r="N112" t="b">
         <v>0</v>
@@ -6538,7 +6552,7 @@
         <v>16.7</v>
       </c>
       <c r="H114" t="n">
-        <v>-16.4</v>
+        <v>-18.51</v>
       </c>
       <c r="I114" t="n">
         <v>-15.31</v>
@@ -6551,7 +6565,7 @@
         <v>-22</v>
       </c>
       <c r="M114" t="n">
-        <v>-18.06</v>
+        <v>-19.41</v>
       </c>
       <c r="N114" t="b">
         <v>0</v>
@@ -6589,7 +6603,7 @@
         <v>0.3</v>
       </c>
       <c r="H115" t="n">
-        <v>19.62</v>
+        <v>18.7</v>
       </c>
       <c r="I115" t="n">
         <v>6.01</v>
@@ -6602,7 +6616,7 @@
         <v>-3.85</v>
       </c>
       <c r="M115" t="n">
-        <v>16.44</v>
+        <v>16.28</v>
       </c>
       <c r="N115" t="b">
         <v>0</v>
@@ -6644,7 +6658,7 @@
         <v>-0</v>
       </c>
       <c r="H116" t="n">
-        <v>33.66</v>
+        <v>33.32</v>
       </c>
       <c r="I116" t="n">
         <v>13.5</v>
@@ -6657,7 +6671,7 @@
         <v>-2.53</v>
       </c>
       <c r="M116" t="n">
-        <v>30.48</v>
+        <v>30.91</v>
       </c>
       <c r="N116" t="b">
         <v>1</v>
@@ -6759,7 +6773,7 @@
         <v>-0.44</v>
       </c>
       <c r="M118" t="n">
-        <v>1.5</v>
+        <v>2.27</v>
       </c>
       <c r="N118" t="b">
         <v>0</v>
@@ -6801,7 +6815,7 @@
         <v>-3.2</v>
       </c>
       <c r="H119" t="n">
-        <v>14.24</v>
+        <v>13.72</v>
       </c>
       <c r="I119" t="n">
         <v>15.28</v>
@@ -6814,7 +6828,7 @@
         <v>-2.53</v>
       </c>
       <c r="M119" t="n">
-        <v>11.06</v>
+        <v>11.31</v>
       </c>
       <c r="N119" t="b">
         <v>0</v>
@@ -6852,7 +6866,7 @@
         <v>-23.5</v>
       </c>
       <c r="H120" t="n">
-        <v>23.72</v>
+        <v>24.59</v>
       </c>
       <c r="I120" t="n">
         <v>20.48</v>
@@ -6865,7 +6879,7 @@
         <v>-2.25</v>
       </c>
       <c r="M120" t="n">
-        <v>20.55</v>
+        <v>22.17</v>
       </c>
       <c r="N120" t="b">
         <v>0</v>
@@ -6903,7 +6917,7 @@
         <v>-27.3</v>
       </c>
       <c r="H121" t="n">
-        <v>-0.06</v>
+        <v>-0.68</v>
       </c>
       <c r="I121" t="n">
         <v>-8.83</v>
@@ -6916,7 +6930,7 @@
         <v>-19.66</v>
       </c>
       <c r="M121" t="n">
-        <v>-3.23</v>
+        <v>-3.09</v>
       </c>
       <c r="N121" t="b">
         <v>0</v>
@@ -6954,7 +6968,7 @@
         <v>-12.5</v>
       </c>
       <c r="H122" t="n">
-        <v>-7.3</v>
+        <v>-8.99</v>
       </c>
       <c r="I122" t="n">
         <v>21.54</v>
@@ -6967,7 +6981,7 @@
         <v>-0.95</v>
       </c>
       <c r="M122" t="n">
-        <v>-11.14</v>
+        <v>-12.06</v>
       </c>
       <c r="N122" t="b">
         <v>0</v>
@@ -7005,7 +7019,7 @@
         <v>-37</v>
       </c>
       <c r="H123" t="n">
-        <v>25.78</v>
+        <v>25.06</v>
       </c>
       <c r="I123" t="n">
         <v>18.38</v>
@@ -7018,7 +7032,7 @@
         <v>-5.11</v>
       </c>
       <c r="M123" t="n">
-        <v>21.94</v>
+        <v>21.99</v>
       </c>
       <c r="N123" t="b">
         <v>1</v>
@@ -7060,7 +7074,7 @@
         <v>-3.4</v>
       </c>
       <c r="H124" t="n">
-        <v>1.55</v>
+        <v>-0.65</v>
       </c>
       <c r="I124" t="n">
         <v>30.48</v>
@@ -7073,7 +7087,7 @@
         <v>-0.9</v>
       </c>
       <c r="M124" t="n">
-        <v>-2.29</v>
+        <v>-3.72</v>
       </c>
       <c r="N124" t="b">
         <v>0</v>
@@ -7111,7 +7125,7 @@
         <v>-23.4</v>
       </c>
       <c r="H125" t="n">
-        <v>-5.09</v>
+        <v>-7.04</v>
       </c>
       <c r="I125" t="n">
         <v>-3.58</v>
@@ -7124,7 +7138,7 @@
         <v>-17.98</v>
       </c>
       <c r="M125" t="n">
-        <v>-8.93</v>
+        <v>-10.11</v>
       </c>
       <c r="N125" t="b">
         <v>0</v>
@@ -7162,7 +7176,7 @@
         <v>-28.9</v>
       </c>
       <c r="H126" t="n">
-        <v>-17.28</v>
+        <v>-19.12</v>
       </c>
       <c r="I126" t="n">
         <v>-12.9</v>
@@ -7175,7 +7189,7 @@
         <v>-23.19</v>
       </c>
       <c r="M126" t="n">
-        <v>-21.12</v>
+        <v>-22.18</v>
       </c>
       <c r="N126" t="b">
         <v>0</v>
@@ -7213,7 +7227,7 @@
         <v>-26.8</v>
       </c>
       <c r="H127" t="n">
-        <v>15.17</v>
+        <v>16.92</v>
       </c>
       <c r="I127" t="n">
         <v>4.56</v>
@@ -7226,7 +7240,7 @@
         <v>-4.09</v>
       </c>
       <c r="M127" t="n">
-        <v>11.33</v>
+        <v>13.85</v>
       </c>
       <c r="N127" t="b">
         <v>1</v>
@@ -7268,7 +7282,7 @@
         <v>-9.800000000000001</v>
       </c>
       <c r="H128" t="n">
-        <v>-22.15</v>
+        <v>-24.57</v>
       </c>
       <c r="I128" t="n">
         <v>-4.09</v>
@@ -7281,7 +7295,7 @@
         <v>-15.24</v>
       </c>
       <c r="M128" t="n">
-        <v>-27.21</v>
+        <v>-28.84</v>
       </c>
       <c r="N128" t="b">
         <v>0</v>
@@ -7319,7 +7333,7 @@
         <v>21</v>
       </c>
       <c r="H129" t="n">
-        <v>0.97</v>
+        <v>1.05</v>
       </c>
       <c r="I129" t="n">
         <v>-0.72</v>
@@ -7332,7 +7346,7 @@
         <v>-7.35</v>
       </c>
       <c r="M129" t="n">
-        <v>-4.09</v>
+        <v>-3.22</v>
       </c>
       <c r="N129" t="b">
         <v>0</v>
@@ -7370,7 +7384,7 @@
         <v>13.2</v>
       </c>
       <c r="H130" t="n">
-        <v>34.85</v>
+        <v>33.33</v>
       </c>
       <c r="I130" t="n">
         <v>8.130000000000001</v>
@@ -7383,7 +7397,7 @@
         <v>-2.36</v>
       </c>
       <c r="M130" t="n">
-        <v>29.79</v>
+        <v>29.05</v>
       </c>
       <c r="N130" t="b">
         <v>0</v>
@@ -7421,7 +7435,7 @@
         <v>6.1</v>
       </c>
       <c r="H131" t="n">
-        <v>0.85</v>
+        <v>-5.23</v>
       </c>
       <c r="I131" t="n">
         <v>10.43</v>
@@ -7434,7 +7448,7 @@
         <v>-1.51</v>
       </c>
       <c r="M131" t="n">
-        <v>-4.21</v>
+        <v>-9.51</v>
       </c>
       <c r="N131" t="b">
         <v>0</v>
@@ -7472,7 +7486,7 @@
         <v>6.5</v>
       </c>
       <c r="H132" t="n">
-        <v>-9.83</v>
+        <v>-10.98</v>
       </c>
       <c r="I132" t="n">
         <v>-0.04</v>
@@ -7485,7 +7499,7 @@
         <v>-4.12</v>
       </c>
       <c r="M132" t="n">
-        <v>-14.89</v>
+        <v>-15.25</v>
       </c>
       <c r="N132" t="b">
         <v>0</v>
@@ -7523,7 +7537,7 @@
         <v>-36.5</v>
       </c>
       <c r="H133" t="n">
-        <v>-32.51</v>
+        <v>-33.9</v>
       </c>
       <c r="I133" t="n">
         <v>-27.75</v>
@@ -7536,7 +7550,7 @@
         <v>-31.28</v>
       </c>
       <c r="M133" t="n">
-        <v>-37.01</v>
+        <v>-37.63</v>
       </c>
       <c r="N133" t="b">
         <v>1</v>
@@ -7574,7 +7588,7 @@
         <v>-14.5</v>
       </c>
       <c r="H134" t="n">
-        <v>-13.03</v>
+        <v>-13.87</v>
       </c>
       <c r="I134" t="n">
         <v>4.48</v>
@@ -7587,7 +7601,7 @@
         <v>-3.33</v>
       </c>
       <c r="M134" t="n">
-        <v>-17.53</v>
+        <v>-17.6</v>
       </c>
       <c r="N134" t="b">
         <v>0</v>
@@ -7625,7 +7639,7 @@
         <v>1.7</v>
       </c>
       <c r="H135" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-8.609999999999999</v>
       </c>
       <c r="I135" t="n">
         <v>8.859999999999999</v>
@@ -7638,7 +7652,7 @@
         <v>-3.27</v>
       </c>
       <c r="M135" t="n">
-        <v>-5.44</v>
+        <v>-12.33</v>
       </c>
       <c r="N135" t="b">
         <v>0</v>
@@ -7676,7 +7690,7 @@
         <v>48.1</v>
       </c>
       <c r="H136" t="n">
-        <v>2.51</v>
+        <v>0.37</v>
       </c>
       <c r="I136" t="n">
         <v>0.16</v>
@@ -7689,7 +7703,7 @@
         <v>-8.890000000000001</v>
       </c>
       <c r="M136" t="n">
-        <v>-1.99</v>
+        <v>-3.35</v>
       </c>
       <c r="N136" t="b">
         <v>0</v>
@@ -7727,7 +7741,7 @@
         <v>-38.7</v>
       </c>
       <c r="H137" t="n">
-        <v>7.91</v>
+        <v>3.8</v>
       </c>
       <c r="I137" t="n">
         <v>17.17</v>
@@ -7740,7 +7754,7 @@
         <v>-0.54</v>
       </c>
       <c r="M137" t="n">
-        <v>3.41</v>
+        <v>0.08</v>
       </c>
       <c r="N137" t="b">
         <v>1</v>
@@ -7778,7 +7792,7 @@
         <v>24.9</v>
       </c>
       <c r="H138" t="n">
-        <v>-4.18</v>
+        <v>-3.69</v>
       </c>
       <c r="I138" t="n">
         <v>10.45</v>
@@ -7791,7 +7805,7 @@
         <v>-0.49</v>
       </c>
       <c r="M138" t="n">
-        <v>-8.68</v>
+        <v>-7.41</v>
       </c>
       <c r="N138" t="b">
         <v>0</v>
@@ -7829,7 +7843,7 @@
         <v>-34.6</v>
       </c>
       <c r="H139" t="n">
-        <v>15.13</v>
+        <v>13.36</v>
       </c>
       <c r="I139" t="n">
         <v>6.67</v>
@@ -7842,7 +7856,7 @@
         <v>-3.06</v>
       </c>
       <c r="M139" t="n">
-        <v>10.63</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="N139" t="b">
         <v>1</v>
@@ -7880,7 +7894,7 @@
         <v>-21.4</v>
       </c>
       <c r="H140" t="n">
-        <v>-1.44</v>
+        <v>-4.1</v>
       </c>
       <c r="I140" t="n">
         <v>2.8</v>
@@ -7893,7 +7907,7 @@
         <v>-2.27</v>
       </c>
       <c r="M140" t="n">
-        <v>-5.94</v>
+        <v>-7.82</v>
       </c>
       <c r="N140" t="b">
         <v>0</v>
@@ -7931,7 +7945,7 @@
         <v>-11.8</v>
       </c>
       <c r="H141" t="n">
-        <v>-4.69</v>
+        <v>-5.09</v>
       </c>
       <c r="I141" t="n">
         <v>9.76</v>
@@ -7944,7 +7958,7 @@
         <v>-1.63</v>
       </c>
       <c r="M141" t="n">
-        <v>-9.300000000000001</v>
+        <v>-8.92</v>
       </c>
       <c r="N141" t="b">
         <v>1</v>
@@ -7982,7 +7996,7 @@
         <v>0.1</v>
       </c>
       <c r="H142" t="n">
-        <v>-12.69</v>
+        <v>-12.16</v>
       </c>
       <c r="I142" t="n">
         <v>-2.83</v>
@@ -7995,7 +8009,7 @@
         <v>-5.45</v>
       </c>
       <c r="M142" t="n">
-        <v>-17.3</v>
+        <v>-15.99</v>
       </c>
       <c r="N142" t="b">
         <v>1</v>
@@ -8033,7 +8047,7 @@
         <v>-13.8</v>
       </c>
       <c r="H143" t="n">
-        <v>8.449999999999999</v>
+        <v>6.38</v>
       </c>
       <c r="I143" t="n">
         <v>4.67</v>
@@ -8046,7 +8060,7 @@
         <v>-5.7</v>
       </c>
       <c r="M143" t="n">
-        <v>3.84</v>
+        <v>2.54</v>
       </c>
       <c r="N143" t="b">
         <v>0</v>
@@ -8088,7 +8102,7 @@
         <v>-8.800000000000001</v>
       </c>
       <c r="H144" t="n">
-        <v>-1.72</v>
+        <v>-1.62</v>
       </c>
       <c r="I144" t="n">
         <v>15.97</v>
@@ -8101,7 +8115,7 @@
         <v>-0.79</v>
       </c>
       <c r="M144" t="n">
-        <v>-6.33</v>
+        <v>-5.45</v>
       </c>
       <c r="N144" t="b">
         <v>0</v>
@@ -8139,7 +8153,7 @@
         <v>24.1</v>
       </c>
       <c r="H145" t="n">
-        <v>-10.05</v>
+        <v>-12.12</v>
       </c>
       <c r="I145" t="n">
         <v>-8.31</v>
@@ -8152,7 +8166,7 @@
         <v>-18.31</v>
       </c>
       <c r="M145" t="n">
-        <v>-13.86</v>
+        <v>-15.15</v>
       </c>
       <c r="N145" t="b">
         <v>1</v>
@@ -8190,7 +8204,7 @@
         <v>-15.9</v>
       </c>
       <c r="H146" t="n">
-        <v>-1.44</v>
+        <v>-1.91</v>
       </c>
       <c r="I146" t="n">
         <v>10.45</v>
@@ -8203,7 +8217,7 @@
         <v>-0.31</v>
       </c>
       <c r="M146" t="n">
-        <v>-5.25</v>
+        <v>-4.95</v>
       </c>
       <c r="N146" t="b">
         <v>1</v>
@@ -8241,7 +8255,7 @@
         <v>-23.3</v>
       </c>
       <c r="H147" t="n">
-        <v>-6.12</v>
+        <v>-6.34</v>
       </c>
       <c r="I147" t="n">
         <v>-20.42</v>
@@ -8254,7 +8268,7 @@
         <v>-27.45</v>
       </c>
       <c r="M147" t="n">
-        <v>-9.93</v>
+        <v>-9.380000000000001</v>
       </c>
       <c r="N147" t="b">
         <v>0</v>
@@ -8292,7 +8306,7 @@
         <v>28.9</v>
       </c>
       <c r="H148" t="n">
-        <v>-5.05</v>
+        <v>-5.01</v>
       </c>
       <c r="I148" t="n">
         <v>8.06</v>
@@ -8305,7 +8319,7 @@
         <v>-2.79</v>
       </c>
       <c r="M148" t="n">
-        <v>-9.75</v>
+        <v>-8.94</v>
       </c>
       <c r="N148" t="b">
         <v>0</v>
@@ -8343,7 +8357,7 @@
         <v>40.1</v>
       </c>
       <c r="H149" t="n">
-        <v>36.29</v>
+        <v>40.14</v>
       </c>
       <c r="I149" t="n">
         <v>15.9</v>
@@ -8356,7 +8370,7 @@
         <v>-5.87</v>
       </c>
       <c r="M149" t="n">
-        <v>31.58</v>
+        <v>36.21</v>
       </c>
       <c r="N149" t="b">
         <v>0</v>
@@ -8394,7 +8408,7 @@
         <v>-27.3</v>
       </c>
       <c r="H150" t="n">
-        <v>7.83</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="I150" t="n">
         <v>0.75</v>
@@ -8407,7 +8421,7 @@
         <v>-5.46</v>
       </c>
       <c r="M150" t="n">
-        <v>3.25</v>
+        <v>4.41</v>
       </c>
       <c r="N150" t="b">
         <v>0</v>
@@ -8445,7 +8459,7 @@
         <v>19.7</v>
       </c>
       <c r="H151" t="n">
-        <v>-8.199999999999999</v>
+        <v>-12.19</v>
       </c>
       <c r="I151" t="n">
         <v>-4.49</v>
@@ -8458,7 +8472,7 @@
         <v>-13.7</v>
       </c>
       <c r="M151" t="n">
-        <v>-12.79</v>
+        <v>-16</v>
       </c>
       <c r="N151" t="b">
         <v>0</v>
@@ -8496,7 +8510,7 @@
         <v>-21.3</v>
       </c>
       <c r="H152" t="n">
-        <v>-1.84</v>
+        <v>-5.68</v>
       </c>
       <c r="I152" t="n">
         <v>7.16</v>
@@ -8509,7 +8523,7 @@
         <v>-11.9</v>
       </c>
       <c r="M152" t="n">
-        <v>-6.42</v>
+        <v>-9.49</v>
       </c>
       <c r="N152" t="b">
         <v>0</v>
@@ -8547,7 +8561,7 @@
         <v>-21.8</v>
       </c>
       <c r="H153" t="n">
-        <v>-24.99</v>
+        <v>-25.59</v>
       </c>
       <c r="I153" t="n">
         <v>-18.97</v>
@@ -8560,7 +8574,7 @@
         <v>-26.82</v>
       </c>
       <c r="M153" t="n">
-        <v>-29.57</v>
+        <v>-29.4</v>
       </c>
       <c r="N153" t="b">
         <v>1</v>
@@ -8598,7 +8612,7 @@
         <v>-37.6</v>
       </c>
       <c r="H154" t="n">
-        <v>-5.04</v>
+        <v>-8.26</v>
       </c>
       <c r="I154" t="n">
         <v>15.2</v>
@@ -8611,7 +8625,7 @@
         <v>-10.3</v>
       </c>
       <c r="M154" t="n">
-        <v>-8.609999999999999</v>
+        <v>-11.06</v>
       </c>
       <c r="N154" t="b">
         <v>0</v>
@@ -8649,7 +8663,7 @@
         <v>53.8</v>
       </c>
       <c r="H155" t="n">
-        <v>38.18</v>
+        <v>43.13</v>
       </c>
       <c r="I155" t="n">
         <v>4.09</v>
@@ -8662,7 +8676,7 @@
         <v>-8.66</v>
       </c>
       <c r="M155" t="n">
-        <v>34.61</v>
+        <v>40.33</v>
       </c>
       <c r="N155" t="b">
         <v>0</v>
@@ -8704,7 +8718,7 @@
         <v>-5.7</v>
       </c>
       <c r="H156" t="n">
-        <v>38.13</v>
+        <v>32.51</v>
       </c>
       <c r="I156" t="n">
         <v>17.92</v>
@@ -8717,7 +8731,7 @@
         <v>-7.48</v>
       </c>
       <c r="M156" t="n">
-        <v>34.56</v>
+        <v>29.72</v>
       </c>
       <c r="N156" t="b">
         <v>0</v>
@@ -8755,7 +8769,7 @@
         <v>-39.3</v>
       </c>
       <c r="H157" t="n">
-        <v>-6.37</v>
+        <v>-8.539999999999999</v>
       </c>
       <c r="I157" t="n">
         <v>11.34</v>
@@ -8768,7 +8782,7 @@
         <v>-5.3</v>
       </c>
       <c r="M157" t="n">
-        <v>-9.94</v>
+        <v>-11.34</v>
       </c>
       <c r="N157" t="b">
         <v>0</v>
@@ -8806,7 +8820,7 @@
         <v>57</v>
       </c>
       <c r="H158" t="n">
-        <v>15</v>
+        <v>14.33</v>
       </c>
       <c r="I158" t="n">
         <v>-11.21</v>
@@ -8819,7 +8833,7 @@
         <v>-13.87</v>
       </c>
       <c r="M158" t="n">
-        <v>11.43</v>
+        <v>11.53</v>
       </c>
       <c r="N158" t="b">
         <v>1</v>
@@ -8857,7 +8871,7 @@
         <v>-21.8</v>
       </c>
       <c r="H159" t="n">
-        <v>8</v>
+        <v>7.49</v>
       </c>
       <c r="I159" t="n">
         <v>1.71</v>
@@ -8870,7 +8884,7 @@
         <v>-6.18</v>
       </c>
       <c r="M159" t="n">
-        <v>4.44</v>
+        <v>4.69</v>
       </c>
       <c r="N159" t="b">
         <v>1</v>
@@ -8908,7 +8922,7 @@
         <v>1</v>
       </c>
       <c r="H160" t="n">
-        <v>-32.11</v>
+        <v>-34.21</v>
       </c>
       <c r="I160" t="n">
         <v>-11.52</v>
@@ -8921,7 +8935,7 @@
         <v>-16.26</v>
       </c>
       <c r="M160" t="n">
-        <v>-35.72</v>
+        <v>-37.06</v>
       </c>
       <c r="N160" t="b">
         <v>1</v>
@@ -8959,7 +8973,7 @@
         <v>45.4</v>
       </c>
       <c r="H161" t="n">
-        <v>8.699999999999999</v>
+        <v>-0.75</v>
       </c>
       <c r="I161" t="n">
         <v>-1.72</v>
@@ -8972,7 +8986,7 @@
         <v>-23.15</v>
       </c>
       <c r="M161" t="n">
-        <v>5.09</v>
+        <v>-3.59</v>
       </c>
       <c r="N161" t="b">
         <v>1</v>
@@ -9010,7 +9024,7 @@
         <v>49.6</v>
       </c>
       <c r="H162" t="n">
-        <v>27.43</v>
+        <v>22.54</v>
       </c>
       <c r="I162" t="n">
         <v>6.34</v>
@@ -9023,7 +9037,7 @@
         <v>-20.75</v>
       </c>
       <c r="M162" t="n">
-        <v>23.81</v>
+        <v>19.7</v>
       </c>
       <c r="N162" t="b">
         <v>0</v>
@@ -9061,7 +9075,7 @@
         <v>55.3</v>
       </c>
       <c r="H163" t="n">
-        <v>-13.59</v>
+        <v>-14.26</v>
       </c>
       <c r="I163" t="n">
         <v>3.73</v>
@@ -9074,7 +9088,7 @@
         <v>-22.94</v>
       </c>
       <c r="M163" t="n">
-        <v>-17.2</v>
+        <v>-17.11</v>
       </c>
       <c r="N163" t="b">
         <v>0</v>
@@ -9112,7 +9126,7 @@
         <v>76.5</v>
       </c>
       <c r="H164" t="n">
-        <v>17.61</v>
+        <v>13.31</v>
       </c>
       <c r="I164" t="n">
         <v>-5.56</v>
@@ -9125,7 +9139,7 @@
         <v>-33.97</v>
       </c>
       <c r="M164" t="n">
-        <v>13.99</v>
+        <v>10.47</v>
       </c>
       <c r="N164" t="b">
         <v>1</v>
@@ -9163,7 +9177,7 @@
         <v>77.90000000000001</v>
       </c>
       <c r="H165" t="n">
-        <v>16.96</v>
+        <v>13.9</v>
       </c>
       <c r="I165" t="n">
         <v>-3.53</v>
@@ -9176,7 +9190,7 @@
         <v>-20.26</v>
       </c>
       <c r="M165" t="n">
-        <v>13.34</v>
+        <v>11.06</v>
       </c>
       <c r="N165" t="b">
         <v>0</v>
@@ -9214,7 +9228,7 @@
         <v>57.6</v>
       </c>
       <c r="H166" t="n">
-        <v>38.28</v>
+        <v>37.6</v>
       </c>
       <c r="I166" t="n">
         <v>14.81</v>
@@ -9227,7 +9241,7 @@
         <v>-5.11</v>
       </c>
       <c r="M166" t="n">
-        <v>34.67</v>
+        <v>34.76</v>
       </c>
       <c r="N166" t="b">
         <v>0</v>
@@ -9265,7 +9279,7 @@
         <v>32.1</v>
       </c>
       <c r="H167" t="n">
-        <v>22.94</v>
+        <v>20.11</v>
       </c>
       <c r="I167" t="n">
         <v>16.93</v>
@@ -9278,7 +9292,7 @@
         <v>-24.48</v>
       </c>
       <c r="M167" t="n">
-        <v>19.32</v>
+        <v>17.27</v>
       </c>
       <c r="N167" t="b">
         <v>1</v>
@@ -9316,7 +9330,7 @@
         <v>51.8</v>
       </c>
       <c r="H168" t="n">
-        <v>11.66</v>
+        <v>7.58</v>
       </c>
       <c r="I168" t="n">
         <v>10.75</v>
@@ -9329,7 +9343,7 @@
         <v>-25.09</v>
       </c>
       <c r="M168" t="n">
-        <v>8.039999999999999</v>
+        <v>4.74</v>
       </c>
       <c r="N168" t="b">
         <v>1</v>
@@ -9367,7 +9381,7 @@
         <v>32.3</v>
       </c>
       <c r="H169" t="n">
-        <v>-25.05</v>
+        <v>-27.09</v>
       </c>
       <c r="I169" t="n">
         <v>-20.76</v>
@@ -9380,7 +9394,7 @@
         <v>-27.91</v>
       </c>
       <c r="M169" t="n">
-        <v>-28.66</v>
+        <v>-29.93</v>
       </c>
       <c r="N169" t="b">
         <v>1</v>
@@ -9418,7 +9432,7 @@
         <v>15.7</v>
       </c>
       <c r="H170" t="n">
-        <v>-2.64</v>
+        <v>-5.84</v>
       </c>
       <c r="I170" t="n">
         <v>-0.87</v>
@@ -9431,7 +9445,7 @@
         <v>-29.01</v>
       </c>
       <c r="M170" t="n">
-        <v>-6.26</v>
+        <v>-8.69</v>
       </c>
       <c r="N170" t="b">
         <v>0</v>
@@ -9469,7 +9483,7 @@
         <v>63.7</v>
       </c>
       <c r="H171" t="n">
-        <v>6.2</v>
+        <v>6.74</v>
       </c>
       <c r="I171" t="n">
         <v>-2.16</v>
@@ -9482,7 +9496,7 @@
         <v>-19.1</v>
       </c>
       <c r="M171" t="n">
-        <v>2.59</v>
+        <v>3.9</v>
       </c>
       <c r="N171" t="b">
         <v>0</v>
@@ -9520,7 +9534,7 @@
         <v>3.7</v>
       </c>
       <c r="H172" t="n">
-        <v>-9.529999999999999</v>
+        <v>-11.5</v>
       </c>
       <c r="I172" t="n">
         <v>-1.11</v>
@@ -9533,7 +9547,7 @@
         <v>-25.46</v>
       </c>
       <c r="M172" t="n">
-        <v>-13.15</v>
+        <v>-14.34</v>
       </c>
       <c r="N172" t="b">
         <v>1</v>
@@ -9571,7 +9585,7 @@
         <v>42.4</v>
       </c>
       <c r="H173" t="n">
-        <v>10.77</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="I173" t="n">
         <v>2.16</v>
@@ -9584,7 +9598,7 @@
         <v>-15.76</v>
       </c>
       <c r="M173" t="n">
-        <v>7.16</v>
+        <v>5.19</v>
       </c>
       <c r="N173" t="b">
         <v>1</v>
@@ -9622,7 +9636,7 @@
         <v>28.2</v>
       </c>
       <c r="H174" t="n">
-        <v>-0.83</v>
+        <v>-0.37</v>
       </c>
       <c r="I174" t="n">
         <v>-1.71</v>
@@ -9635,7 +9649,7 @@
         <v>-23.43</v>
       </c>
       <c r="M174" t="n">
-        <v>-4.44</v>
+        <v>-3.21</v>
       </c>
       <c r="N174" t="b">
         <v>1</v>
@@ -9673,7 +9687,7 @@
         <v>28.6</v>
       </c>
       <c r="H175" t="n">
-        <v>28</v>
+        <v>29.43</v>
       </c>
       <c r="I175" t="n">
         <v>2.81</v>
@@ -9686,7 +9700,7 @@
         <v>-18.87</v>
       </c>
       <c r="M175" t="n">
-        <v>24.39</v>
+        <v>26.58</v>
       </c>
       <c r="N175" t="b">
         <v>1</v>
@@ -9724,7 +9738,7 @@
         <v>89.09999999999999</v>
       </c>
       <c r="H176" t="n">
-        <v>42.68</v>
+        <v>37.75</v>
       </c>
       <c r="I176" t="n">
         <v>18.45</v>
@@ -9737,7 +9751,7 @@
         <v>-9.029999999999999</v>
       </c>
       <c r="M176" t="n">
-        <v>39.07</v>
+        <v>34.91</v>
       </c>
       <c r="N176" t="b">
         <v>0</v>
@@ -9775,7 +9789,7 @@
         <v>50.5</v>
       </c>
       <c r="H177" t="n">
-        <v>19.2</v>
+        <v>12.44</v>
       </c>
       <c r="I177" t="n">
         <v>-2.26</v>
@@ -9788,7 +9802,7 @@
         <v>-20.74</v>
       </c>
       <c r="M177" t="n">
-        <v>15.58</v>
+        <v>9.6</v>
       </c>
       <c r="N177" t="b">
         <v>0</v>
@@ -9826,7 +9840,7 @@
         <v>33.1</v>
       </c>
       <c r="H178" t="n">
-        <v>16.04</v>
+        <v>13.53</v>
       </c>
       <c r="I178" t="n">
         <v>4.68</v>
@@ -9839,7 +9853,7 @@
         <v>-26.7</v>
       </c>
       <c r="M178" t="n">
-        <v>12.42</v>
+        <v>10.69</v>
       </c>
       <c r="N178" t="b">
         <v>1</v>
@@ -9877,7 +9891,7 @@
         <v>46.3</v>
       </c>
       <c r="H179" t="n">
-        <v>-14.06</v>
+        <v>-13.75</v>
       </c>
       <c r="I179" t="n">
         <v>-3.24</v>
@@ -9890,7 +9904,7 @@
         <v>-22.77</v>
       </c>
       <c r="M179" t="n">
-        <v>-17.67</v>
+        <v>-16.59</v>
       </c>
       <c r="N179" t="b">
         <v>0</v>
@@ -9928,7 +9942,7 @@
         <v>-13.8</v>
       </c>
       <c r="H180" t="n">
-        <v>10.47</v>
+        <v>3.38</v>
       </c>
       <c r="I180" t="n">
         <v>6.03</v>
@@ -9941,7 +9955,7 @@
         <v>-13.77</v>
       </c>
       <c r="M180" t="n">
-        <v>6.85</v>
+        <v>0.54</v>
       </c>
       <c r="N180" t="b">
         <v>0</v>
@@ -9979,7 +9993,7 @@
         <v>21.8</v>
       </c>
       <c r="H181" t="n">
-        <v>-8.890000000000001</v>
+        <v>-12.41</v>
       </c>
       <c r="I181" t="n">
         <v>-6.34</v>
@@ -9992,7 +10006,7 @@
         <v>-30.04</v>
       </c>
       <c r="M181" t="n">
-        <v>-12.51</v>
+        <v>-15.25</v>
       </c>
       <c r="N181" t="b">
         <v>1</v>
@@ -10030,7 +10044,7 @@
         <v>40.3</v>
       </c>
       <c r="H182" t="n">
-        <v>-8.369999999999999</v>
+        <v>-9.68</v>
       </c>
       <c r="I182" t="n">
         <v>1.24</v>
@@ -10043,7 +10057,7 @@
         <v>-20.5</v>
       </c>
       <c r="M182" t="n">
-        <v>-11.99</v>
+        <v>-12.53</v>
       </c>
       <c r="N182" t="b">
         <v>1</v>
@@ -10081,7 +10095,7 @@
         <v>36.6</v>
       </c>
       <c r="H183" t="n">
-        <v>234.2</v>
+        <v>231.51</v>
       </c>
       <c r="I183" t="n">
         <v>-4.23</v>
@@ -10094,7 +10108,7 @@
         <v>-11.51</v>
       </c>
       <c r="M183" t="n">
-        <v>230.58</v>
+        <v>228.66</v>
       </c>
       <c r="N183" t="b">
         <v>0</v>
@@ -10132,7 +10146,7 @@
         <v>24.1</v>
       </c>
       <c r="H184" t="n">
-        <v>11.76</v>
+        <v>10.82</v>
       </c>
       <c r="I184" t="n">
         <v>-1.6</v>
@@ -10145,7 +10159,7 @@
         <v>-22.54</v>
       </c>
       <c r="M184" t="n">
-        <v>8.15</v>
+        <v>7.97</v>
       </c>
       <c r="N184" t="b">
         <v>1</v>
@@ -10183,7 +10197,7 @@
         <v>50.3</v>
       </c>
       <c r="H185" t="n">
-        <v>-7.49</v>
+        <v>-11.42</v>
       </c>
       <c r="I185" t="n">
         <v>-3.34</v>
@@ -10196,7 +10210,7 @@
         <v>-23.32</v>
       </c>
       <c r="M185" t="n">
-        <v>-11.11</v>
+        <v>-14.26</v>
       </c>
       <c r="N185" t="b">
         <v>0</v>
@@ -10234,7 +10248,7 @@
         <v>24.5</v>
       </c>
       <c r="H186" t="n">
-        <v>-25.36</v>
+        <v>-24.99</v>
       </c>
       <c r="I186" t="n">
         <v>-12.99</v>
@@ -10247,7 +10261,7 @@
         <v>-22.54</v>
       </c>
       <c r="M186" t="n">
-        <v>-28.98</v>
+        <v>-27.84</v>
       </c>
       <c r="N186" t="b">
         <v>1</v>
@@ -10285,7 +10299,7 @@
         <v>-4</v>
       </c>
       <c r="H187" t="n">
-        <v>5.11</v>
+        <v>1.42</v>
       </c>
       <c r="I187" t="n">
         <v>-1.59</v>
@@ -10298,7 +10312,7 @@
         <v>-25.38</v>
       </c>
       <c r="M187" t="n">
-        <v>1.49</v>
+        <v>-1.42</v>
       </c>
       <c r="N187" t="b">
         <v>0</v>
@@ -10336,7 +10350,7 @@
         <v>14.8</v>
       </c>
       <c r="H188" t="n">
-        <v>-34.64</v>
+        <v>-36.94</v>
       </c>
       <c r="I188" t="n">
         <v>-2.48</v>
@@ -10349,7 +10363,7 @@
         <v>-40.98</v>
       </c>
       <c r="M188" t="n">
-        <v>-38.25</v>
+        <v>-39.78</v>
       </c>
       <c r="N188" t="b">
         <v>0</v>
@@ -10387,7 +10401,7 @@
         <v>-27.6</v>
       </c>
       <c r="H189" t="n">
-        <v>11.42</v>
+        <v>8.49</v>
       </c>
       <c r="I189" t="n">
         <v>-0.36</v>
@@ -10400,7 +10414,7 @@
         <v>-19.41</v>
       </c>
       <c r="M189" t="n">
-        <v>7.81</v>
+        <v>5.65</v>
       </c>
       <c r="N189" t="b">
         <v>0</v>
@@ -10438,7 +10452,7 @@
         <v>9.1</v>
       </c>
       <c r="H190" t="n">
-        <v>-18.99</v>
+        <v>-22.18</v>
       </c>
       <c r="I190" t="n">
         <v>-2.83</v>
@@ -10451,7 +10465,7 @@
         <v>-23.78</v>
       </c>
       <c r="M190" t="n">
-        <v>-22.61</v>
+        <v>-25.03</v>
       </c>
       <c r="N190" t="b">
         <v>0</v>
@@ -10489,7 +10503,7 @@
         <v>11</v>
       </c>
       <c r="H191" t="n">
-        <v>-10.26</v>
+        <v>-13.45</v>
       </c>
       <c r="I191" t="n">
         <v>3.38</v>
@@ -10502,7 +10516,7 @@
         <v>-18.71</v>
       </c>
       <c r="M191" t="n">
-        <v>-13.87</v>
+        <v>-16.3</v>
       </c>
       <c r="N191" t="b">
         <v>0</v>
@@ -10540,7 +10554,7 @@
         <v>31.2</v>
       </c>
       <c r="H192" t="n">
-        <v>-14.58</v>
+        <v>-14.01</v>
       </c>
       <c r="I192" t="n">
         <v>-11.26</v>
@@ -10553,7 +10567,7 @@
         <v>-22.9</v>
       </c>
       <c r="M192" t="n">
-        <v>-18.2</v>
+        <v>-16.86</v>
       </c>
       <c r="N192" t="b">
         <v>0</v>
@@ -10591,7 +10605,7 @@
         <v>19.3</v>
       </c>
       <c r="H193" t="n">
-        <v>10.4</v>
+        <v>11.21</v>
       </c>
       <c r="I193" t="n">
         <v>11.79</v>
@@ -10604,7 +10618,7 @@
         <v>-16.62</v>
       </c>
       <c r="M193" t="n">
-        <v>6.78</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="N193" t="b">
         <v>1</v>
@@ -10642,7 +10656,7 @@
         <v>-8.699999999999999</v>
       </c>
       <c r="H194" t="n">
-        <v>-14.88</v>
+        <v>-13.57</v>
       </c>
       <c r="I194" t="n">
         <v>17.25</v>
@@ -10655,7 +10669,7 @@
         <v>-4.65</v>
       </c>
       <c r="M194" t="n">
-        <v>-18.49</v>
+        <v>-16.41</v>
       </c>
       <c r="N194" t="b">
         <v>1</v>
@@ -10693,7 +10707,7 @@
         <v>15.2</v>
       </c>
       <c r="H195" t="n">
-        <v>-3.72</v>
+        <v>-8.07</v>
       </c>
       <c r="I195" t="n">
         <v>5.36</v>
@@ -10706,7 +10720,7 @@
         <v>-28.18</v>
       </c>
       <c r="M195" t="n">
-        <v>-7.33</v>
+        <v>-10.92</v>
       </c>
       <c r="N195" t="b">
         <v>1</v>
@@ -10744,7 +10758,7 @@
         <v>37.2</v>
       </c>
       <c r="H196" t="n">
-        <v>-24.83</v>
+        <v>-25.53</v>
       </c>
       <c r="I196" t="n">
         <v>-7.64</v>
@@ -10757,7 +10771,7 @@
         <v>-26.24</v>
       </c>
       <c r="M196" t="n">
-        <v>-28.44</v>
+        <v>-28.37</v>
       </c>
       <c r="N196" t="b">
         <v>1</v>
@@ -10799,7 +10813,7 @@
         <v>-0.5</v>
       </c>
       <c r="H197" t="n">
-        <v>27.72</v>
+        <v>30.66</v>
       </c>
       <c r="I197" t="n">
         <v>12.75</v>
@@ -10812,7 +10826,7 @@
         <v>-4.72</v>
       </c>
       <c r="M197" t="n">
-        <v>24.11</v>
+        <v>27.82</v>
       </c>
       <c r="N197" t="b">
         <v>0</v>
@@ -10850,7 +10864,7 @@
         <v>-27.9</v>
       </c>
       <c r="H198" t="n">
-        <v>-14.39</v>
+        <v>-17.69</v>
       </c>
       <c r="I198" t="n">
         <v>-5.72</v>
@@ -10863,7 +10877,7 @@
         <v>-11.08</v>
       </c>
       <c r="M198" t="n">
-        <v>-18</v>
+        <v>-20.54</v>
       </c>
       <c r="N198" t="b">
         <v>0</v>
@@ -10901,7 +10915,7 @@
         <v>29.8</v>
       </c>
       <c r="H199" t="n">
-        <v>37.27</v>
+        <v>31.61</v>
       </c>
       <c r="I199" t="n">
         <v>-2.74</v>
@@ -10914,7 +10928,7 @@
         <v>-22.36</v>
       </c>
       <c r="M199" t="n">
-        <v>33.66</v>
+        <v>28.77</v>
       </c>
       <c r="N199" t="b">
         <v>1</v>
@@ -10952,7 +10966,7 @@
         <v>60.9</v>
       </c>
       <c r="H200" t="n">
-        <v>5.2</v>
+        <v>4.3</v>
       </c>
       <c r="I200" t="n">
         <v>6.71</v>
@@ -10965,7 +10979,7 @@
         <v>-4.9</v>
       </c>
       <c r="M200" t="n">
-        <v>1.59</v>
+        <v>1.45</v>
       </c>
       <c r="N200" t="b">
         <v>0</v>
@@ -11003,7 +11017,7 @@
         <v>-13.4</v>
       </c>
       <c r="H201" t="n">
-        <v>-23.05</v>
+        <v>-25.96</v>
       </c>
       <c r="I201" t="n">
         <v>0.79</v>
@@ -11016,7 +11030,7 @@
         <v>-15.41</v>
       </c>
       <c r="M201" t="n">
-        <v>-26.66</v>
+        <v>-28.8</v>
       </c>
       <c r="N201" t="b">
         <v>0</v>
@@ -11054,7 +11068,7 @@
         <v>18.2</v>
       </c>
       <c r="H202" t="n">
-        <v>-15.21</v>
+        <v>-16.91</v>
       </c>
       <c r="I202" t="n">
         <v>-11.28</v>
@@ -11067,7 +11081,7 @@
         <v>-16.87</v>
       </c>
       <c r="M202" t="n">
-        <v>-18.83</v>
+        <v>-19.76</v>
       </c>
       <c r="N202" t="b">
         <v>0</v>
@@ -11105,7 +11119,7 @@
         <v>31.2</v>
       </c>
       <c r="H203" t="n">
-        <v>-3.84</v>
+        <v>-4.06</v>
       </c>
       <c r="I203" t="n">
         <v>-3.17</v>
@@ -11118,7 +11132,7 @@
         <v>-23.66</v>
       </c>
       <c r="M203" t="n">
-        <v>-7.45</v>
+        <v>-6.9</v>
       </c>
       <c r="N203" t="b">
         <v>0</v>
@@ -11156,7 +11170,7 @@
         <v>-1.3</v>
       </c>
       <c r="H204" t="n">
-        <v>-18.33</v>
+        <v>-22.08</v>
       </c>
       <c r="I204" t="n">
         <v>5.29</v>
@@ -11169,7 +11183,7 @@
         <v>-11.87</v>
       </c>
       <c r="M204" t="n">
-        <v>-21.94</v>
+        <v>-24.93</v>
       </c>
       <c r="N204" t="b">
         <v>0</v>
@@ -11207,7 +11221,7 @@
         <v>-29.8</v>
       </c>
       <c r="H205" t="n">
-        <v>77.3</v>
+        <v>71.23</v>
       </c>
       <c r="I205" t="n">
         <v>29.88</v>
@@ -11220,7 +11234,7 @@
         <v>-0.29</v>
       </c>
       <c r="M205" t="n">
-        <v>73.68000000000001</v>
+        <v>68.39</v>
       </c>
       <c r="N205" t="b">
         <v>0</v>
@@ -11258,7 +11272,7 @@
         <v>-22.4</v>
       </c>
       <c r="H206" t="n">
-        <v>-16.92</v>
+        <v>-19.64</v>
       </c>
       <c r="I206" t="n">
         <v>5.79</v>
@@ -11271,7 +11285,7 @@
         <v>-9.67</v>
       </c>
       <c r="M206" t="n">
-        <v>-20.54</v>
+        <v>-22.49</v>
       </c>
       <c r="N206" t="b">
         <v>0</v>
@@ -11309,7 +11323,7 @@
         <v>19.3</v>
       </c>
       <c r="H207" t="n">
-        <v>-19.91</v>
+        <v>-20.55</v>
       </c>
       <c r="I207" t="n">
         <v>-16.69</v>
@@ -11322,7 +11336,7 @@
         <v>-36.39</v>
       </c>
       <c r="M207" t="n">
-        <v>-23.52</v>
+        <v>-23.4</v>
       </c>
       <c r="N207" t="b">
         <v>1</v>
@@ -11411,7 +11425,7 @@
         <v>68.8</v>
       </c>
       <c r="H209" t="n">
-        <v>19.89</v>
+        <v>15.56</v>
       </c>
       <c r="I209" t="n">
         <v>-1.41</v>
@@ -11424,7 +11438,7 @@
         <v>-19.39</v>
       </c>
       <c r="M209" t="n">
-        <v>16.28</v>
+        <v>12.72</v>
       </c>
       <c r="N209" t="b">
         <v>0</v>
@@ -11462,7 +11476,7 @@
         <v>8.5</v>
       </c>
       <c r="H210" t="n">
-        <v>-5.74</v>
+        <v>-9.859999999999999</v>
       </c>
       <c r="I210" t="n">
         <v>-4.26</v>
@@ -11475,7 +11489,7 @@
         <v>-23.85</v>
       </c>
       <c r="M210" t="n">
-        <v>-9.359999999999999</v>
+        <v>-12.71</v>
       </c>
       <c r="N210" t="b">
         <v>0</v>
@@ -11513,7 +11527,7 @@
         <v>-15.2</v>
       </c>
       <c r="H211" t="n">
-        <v>11.47</v>
+        <v>8.82</v>
       </c>
       <c r="I211" t="n">
         <v>12.27</v>
@@ -11526,7 +11540,7 @@
         <v>-12.27</v>
       </c>
       <c r="M211" t="n">
-        <v>7.86</v>
+        <v>5.97</v>
       </c>
       <c r="N211" t="b">
         <v>0</v>
@@ -11564,7 +11578,7 @@
         <v>-33.1</v>
       </c>
       <c r="H212" t="n">
-        <v>-28.96</v>
+        <v>-27.01</v>
       </c>
       <c r="I212" t="n">
         <v>-13.13</v>
@@ -11577,7 +11591,7 @@
         <v>-21.04</v>
       </c>
       <c r="M212" t="n">
-        <v>-32.58</v>
+        <v>-29.85</v>
       </c>
       <c r="N212" t="b">
         <v>0</v>
@@ -11615,7 +11629,7 @@
         <v>11.8</v>
       </c>
       <c r="H213" t="n">
-        <v>3.24</v>
+        <v>0.7</v>
       </c>
       <c r="I213" t="n">
         <v>-1.19</v>
@@ -11628,7 +11642,7 @@
         <v>-17.57</v>
       </c>
       <c r="M213" t="n">
-        <v>-0.38</v>
+        <v>-2.14</v>
       </c>
       <c r="N213" t="b">
         <v>1</v>
@@ -11666,7 +11680,7 @@
         <v>27.5</v>
       </c>
       <c r="H214" t="n">
-        <v>8.1</v>
+        <v>5.52</v>
       </c>
       <c r="I214" t="n">
         <v>8.42</v>
@@ -11679,7 +11693,7 @@
         <v>-2.51</v>
       </c>
       <c r="M214" t="n">
-        <v>4.49</v>
+        <v>2.68</v>
       </c>
       <c r="N214" t="b">
         <v>1</v>
@@ -11717,7 +11731,7 @@
         <v>-22.4</v>
       </c>
       <c r="H215" t="n">
-        <v>-8.83</v>
+        <v>-9.73</v>
       </c>
       <c r="I215" t="n">
         <v>9.42</v>
@@ -11730,7 +11744,7 @@
         <v>-2.79</v>
       </c>
       <c r="M215" t="n">
-        <v>-12.44</v>
+        <v>-12.57</v>
       </c>
       <c r="N215" t="b">
         <v>1</v>
@@ -11768,7 +11782,7 @@
         <v>-14.7</v>
       </c>
       <c r="H216" t="n">
-        <v>-11.97</v>
+        <v>-13.19</v>
       </c>
       <c r="I216" t="n">
         <v>10.3</v>
@@ -11781,7 +11795,7 @@
         <v>-2.6</v>
       </c>
       <c r="M216" t="n">
-        <v>-15.58</v>
+        <v>-16.03</v>
       </c>
       <c r="N216" t="b">
         <v>1</v>
@@ -11823,7 +11837,7 @@
         <v>-9.300000000000001</v>
       </c>
       <c r="H217" t="n">
-        <v>-23.65</v>
+        <v>-26.47</v>
       </c>
       <c r="I217" t="n">
         <v>10.42</v>
@@ -11836,7 +11850,7 @@
         <v>-21.72</v>
       </c>
       <c r="M217" t="n">
-        <v>-27.26</v>
+        <v>-29.31</v>
       </c>
       <c r="N217" t="b">
         <v>1</v>
@@ -11874,7 +11888,7 @@
         <v>-13.5</v>
       </c>
       <c r="H218" t="n">
-        <v>100.99</v>
+        <v>91.14</v>
       </c>
       <c r="I218" t="n">
         <v>18.09</v>
@@ -11887,7 +11901,7 @@
         <v>-14.35</v>
       </c>
       <c r="M218" t="n">
-        <v>97.37</v>
+        <v>88.3</v>
       </c>
       <c r="N218" t="b">
         <v>0</v>
@@ -11925,7 +11939,7 @@
         <v>-27.5</v>
       </c>
       <c r="H219" t="n">
-        <v>-12.08</v>
+        <v>-20.75</v>
       </c>
       <c r="I219" t="n">
         <v>-29.95</v>
@@ -11938,7 +11952,7 @@
         <v>-35.86</v>
       </c>
       <c r="M219" t="n">
-        <v>-15.69</v>
+        <v>-23.59</v>
       </c>
       <c r="N219" t="b">
         <v>0</v>
@@ -11976,7 +11990,7 @@
         <v>11.9</v>
       </c>
       <c r="H220" t="n">
-        <v>-15.63</v>
+        <v>-20.34</v>
       </c>
       <c r="I220" t="n">
         <v>-3.02</v>
@@ -11989,7 +12003,7 @@
         <v>-24.96</v>
       </c>
       <c r="M220" t="n">
-        <v>-19.25</v>
+        <v>-23.19</v>
       </c>
       <c r="N220" t="b">
         <v>0</v>
@@ -12027,7 +12041,7 @@
         <v>5</v>
       </c>
       <c r="H221" t="n">
-        <v>-4.41</v>
+        <v>-5.75</v>
       </c>
       <c r="I221" t="n">
         <v>0.41</v>
@@ -12040,7 +12054,7 @@
         <v>-13.87</v>
       </c>
       <c r="M221" t="n">
-        <v>-8.02</v>
+        <v>-8.6</v>
       </c>
       <c r="N221" t="b">
         <v>0</v>
@@ -12078,7 +12092,7 @@
         <v>-35.9</v>
       </c>
       <c r="H222" t="n">
-        <v>11.64</v>
+        <v>7.97</v>
       </c>
       <c r="I222" t="n">
         <v>18.67</v>
@@ -12091,7 +12105,7 @@
         <v>-6.77</v>
       </c>
       <c r="M222" t="n">
-        <v>8.02</v>
+        <v>5.13</v>
       </c>
       <c r="N222" t="b">
         <v>0</v>
@@ -12129,7 +12143,7 @@
         <v>-25.2</v>
       </c>
       <c r="H223" t="n">
-        <v>16.78</v>
+        <v>13.42</v>
       </c>
       <c r="I223" t="n">
         <v>22.53</v>
@@ -12142,7 +12156,7 @@
         <v>-19.27</v>
       </c>
       <c r="M223" t="n">
-        <v>13.17</v>
+        <v>10.58</v>
       </c>
       <c r="N223" t="b">
         <v>1</v>
@@ -12180,7 +12194,7 @@
         <v>5.1</v>
       </c>
       <c r="H224" t="n">
-        <v>3.61</v>
+        <v>2.8</v>
       </c>
       <c r="I224" t="n">
         <v>8.77</v>
@@ -12193,7 +12207,7 @@
         <v>-3.54</v>
       </c>
       <c r="M224" t="n">
-        <v>-0.01</v>
+        <v>-0.04</v>
       </c>
       <c r="N224" t="b">
         <v>1</v>
@@ -12231,7 +12245,7 @@
         <v>20.8</v>
       </c>
       <c r="H225" t="n">
-        <v>-16.4</v>
+        <v>-19.45</v>
       </c>
       <c r="I225" t="n">
         <v>-10.93</v>
@@ -12244,7 +12258,7 @@
         <v>-27.1</v>
       </c>
       <c r="M225" t="n">
-        <v>-20.02</v>
+        <v>-22.3</v>
       </c>
       <c r="N225" t="b">
         <v>0</v>
@@ -12282,7 +12296,7 @@
         <v>-27.7</v>
       </c>
       <c r="H226" t="n">
-        <v>16.21</v>
+        <v>14.24</v>
       </c>
       <c r="I226" t="n">
         <v>-10.22</v>
@@ -12295,7 +12309,7 @@
         <v>-17.14</v>
       </c>
       <c r="M226" t="n">
-        <v>12.6</v>
+        <v>11.39</v>
       </c>
       <c r="N226" t="b">
         <v>0</v>
@@ -12333,7 +12347,7 @@
         <v>-24.7</v>
       </c>
       <c r="H227" t="n">
-        <v>4.56</v>
+        <v>-0.54</v>
       </c>
       <c r="I227" t="n">
         <v>1.65</v>
@@ -12346,7 +12360,7 @@
         <v>-19.04</v>
       </c>
       <c r="M227" t="n">
-        <v>0.95</v>
+        <v>-3.38</v>
       </c>
       <c r="N227" t="b">
         <v>0</v>
@@ -12384,7 +12398,7 @@
         <v>-34.9</v>
       </c>
       <c r="H228" t="n">
-        <v>-11.55</v>
+        <v>-12.74</v>
       </c>
       <c r="I228" t="n">
         <v>19.9</v>
@@ -12397,7 +12411,7 @@
         <v>-12.62</v>
       </c>
       <c r="M228" t="n">
-        <v>-15.17</v>
+        <v>-15.58</v>
       </c>
       <c r="N228" t="b">
         <v>0</v>
@@ -12435,7 +12449,7 @@
         <v>-29.5</v>
       </c>
       <c r="H229" t="n">
-        <v>-6.96</v>
+        <v>-5.26</v>
       </c>
       <c r="I229" t="n">
         <v>4.05</v>
@@ -12448,7 +12462,7 @@
         <v>-2.43</v>
       </c>
       <c r="M229" t="n">
-        <v>-10.57</v>
+        <v>-8.1</v>
       </c>
       <c r="N229" t="b">
         <v>0</v>
@@ -12486,7 +12500,7 @@
         <v>34.2</v>
       </c>
       <c r="H230" t="n">
-        <v>10.58</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="I230" t="n">
         <v>8.15</v>
@@ -12499,7 +12513,7 @@
         <v>-7.63</v>
       </c>
       <c r="M230" t="n">
-        <v>6.97</v>
+        <v>6.63</v>
       </c>
       <c r="N230" t="b">
         <v>1</v>
@@ -12537,7 +12551,7 @@
         <v>42</v>
       </c>
       <c r="H231" t="n">
-        <v>-29.95</v>
+        <v>-31.99</v>
       </c>
       <c r="I231" t="n">
         <v>0.6</v>
@@ -12550,7 +12564,7 @@
         <v>-16.67</v>
       </c>
       <c r="M231" t="n">
-        <v>-33.56</v>
+        <v>-34.83</v>
       </c>
       <c r="N231" t="b">
         <v>1</v>
@@ -12592,7 +12606,7 @@
         <v>-0.4</v>
       </c>
       <c r="H232" t="n">
-        <v>-17.28</v>
+        <v>-18.58</v>
       </c>
       <c r="I232" t="n">
         <v>4.83</v>
@@ -12605,7 +12619,7 @@
         <v>-10.75</v>
       </c>
       <c r="M232" t="n">
-        <v>-20.89</v>
+        <v>-21.43</v>
       </c>
       <c r="N232" t="b">
         <v>0</v>
@@ -12643,7 +12657,7 @@
         <v>64.59999999999999</v>
       </c>
       <c r="H233" t="n">
-        <v>6.17</v>
+        <v>7.93</v>
       </c>
       <c r="I233" t="n">
         <v>3.01</v>
@@ -12656,7 +12670,7 @@
         <v>-12</v>
       </c>
       <c r="M233" t="n">
-        <v>2.56</v>
+        <v>5.08</v>
       </c>
       <c r="N233" t="b">
         <v>0</v>
@@ -12694,7 +12708,7 @@
         <v>-25.3</v>
       </c>
       <c r="H234" t="n">
-        <v>37.65</v>
+        <v>36.06</v>
       </c>
       <c r="I234" t="n">
         <v>36.1</v>
@@ -12707,7 +12721,7 @@
         <v>-5.66</v>
       </c>
       <c r="M234" t="n">
-        <v>34.03</v>
+        <v>33.21</v>
       </c>
       <c r="N234" t="b">
         <v>1</v>
@@ -12745,7 +12759,7 @@
         <v>-7.7</v>
       </c>
       <c r="H235" t="n">
-        <v>-2.18</v>
+        <v>-5</v>
       </c>
       <c r="I235" t="n">
         <v>-6.47</v>
@@ -12758,7 +12772,7 @@
         <v>-23.05</v>
       </c>
       <c r="M235" t="n">
-        <v>-5.79</v>
+        <v>-7.85</v>
       </c>
       <c r="N235" t="b">
         <v>1</v>
@@ -12796,7 +12810,7 @@
         <v>-2.9</v>
       </c>
       <c r="H236" t="n">
-        <v>0.67</v>
+        <v>-1.9</v>
       </c>
       <c r="I236" t="n">
         <v>-1.47</v>
@@ -12809,7 +12823,7 @@
         <v>-7.7</v>
       </c>
       <c r="M236" t="n">
-        <v>-2.95</v>
+        <v>-4.74</v>
       </c>
       <c r="N236" t="b">
         <v>0</v>
@@ -12847,7 +12861,7 @@
         <v>13.7</v>
       </c>
       <c r="H237" t="n">
-        <v>7.95</v>
+        <v>7.06</v>
       </c>
       <c r="I237" t="n">
         <v>2.74</v>
@@ -12860,7 +12874,7 @@
         <v>-24.02</v>
       </c>
       <c r="M237" t="n">
-        <v>4.34</v>
+        <v>4.21</v>
       </c>
       <c r="N237" t="b">
         <v>1</v>
@@ -12898,7 +12912,7 @@
         <v>21.8</v>
       </c>
       <c r="H238" t="n">
-        <v>0.88</v>
+        <v>0.24</v>
       </c>
       <c r="I238" t="n">
         <v>18.32</v>
@@ -12911,7 +12925,7 @@
         <v>-23.27</v>
       </c>
       <c r="M238" t="n">
-        <v>-2.74</v>
+        <v>-2.6</v>
       </c>
       <c r="N238" t="b">
         <v>1</v>
@@ -12949,7 +12963,7 @@
         <v>29.4</v>
       </c>
       <c r="H239" t="n">
-        <v>-2.6</v>
+        <v>-2.23</v>
       </c>
       <c r="I239" t="n">
         <v>-2.62</v>
@@ -12962,7 +12976,7 @@
         <v>-27.18</v>
       </c>
       <c r="M239" t="n">
-        <v>-6.22</v>
+        <v>-5.07</v>
       </c>
       <c r="N239" t="b">
         <v>1</v>
@@ -13000,7 +13014,7 @@
         <v>-3.7</v>
       </c>
       <c r="H240" t="n">
-        <v>-23.66</v>
+        <v>-24.53</v>
       </c>
       <c r="I240" t="n">
         <v>-8.07</v>
@@ -13013,7 +13027,7 @@
         <v>-22.12</v>
       </c>
       <c r="M240" t="n">
-        <v>-27.27</v>
+        <v>-27.37</v>
       </c>
       <c r="N240" t="b">
         <v>1</v>
@@ -13051,7 +13065,7 @@
         <v>21.3</v>
       </c>
       <c r="H241" t="n">
-        <v>1.54</v>
+        <v>1.44</v>
       </c>
       <c r="I241" t="n">
         <v>0.23</v>
@@ -13064,7 +13078,7 @@
         <v>-0.85</v>
       </c>
       <c r="M241" t="n">
-        <v>-2.08</v>
+        <v>-1.4</v>
       </c>
       <c r="N241" t="b">
         <v>1</v>
@@ -13102,7 +13116,7 @@
         <v>-21.4</v>
       </c>
       <c r="H242" t="n">
-        <v>23.6</v>
+        <v>15.58</v>
       </c>
       <c r="I242" t="n">
         <v>4.55</v>
@@ -13115,7 +13129,7 @@
         <v>-6.39</v>
       </c>
       <c r="M242" t="n">
-        <v>19.98</v>
+        <v>12.74</v>
       </c>
       <c r="N242" t="b">
         <v>1</v>
@@ -13153,7 +13167,7 @@
         <v>16.3</v>
       </c>
       <c r="H243" t="n">
-        <v>7.26</v>
+        <v>5.02</v>
       </c>
       <c r="I243" t="n">
         <v>-1</v>
@@ -13166,7 +13180,7 @@
         <v>-22.5</v>
       </c>
       <c r="M243" t="n">
-        <v>3.65</v>
+        <v>2.17</v>
       </c>
       <c r="N243" t="b">
         <v>1</v>
@@ -13204,7 +13218,7 @@
         <v>11.9</v>
       </c>
       <c r="H244" t="n">
-        <v>0.4</v>
+        <v>1.09</v>
       </c>
       <c r="I244" t="n">
         <v>7.74</v>
@@ -13217,7 +13231,7 @@
         <v>-9.43</v>
       </c>
       <c r="M244" t="n">
-        <v>-3.22</v>
+        <v>-1.75</v>
       </c>
       <c r="N244" t="b">
         <v>1</v>
@@ -13255,7 +13269,7 @@
         <v>19.4</v>
       </c>
       <c r="H245" t="n">
-        <v>-2.26</v>
+        <v>-3.63</v>
       </c>
       <c r="I245" t="n">
         <v>10.89</v>
@@ -13268,7 +13282,7 @@
         <v>-2.97</v>
       </c>
       <c r="M245" t="n">
-        <v>-5.88</v>
+        <v>-6.47</v>
       </c>
       <c r="N245" t="b">
         <v>0</v>
@@ -13306,7 +13320,7 @@
         <v>66.7</v>
       </c>
       <c r="H246" t="n">
-        <v>7.24</v>
+        <v>12.21</v>
       </c>
       <c r="I246" t="n">
         <v>4.84</v>
@@ -13319,7 +13333,7 @@
         <v>-11.7</v>
       </c>
       <c r="M246" t="n">
-        <v>3.63</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="N246" t="b">
         <v>0</v>
@@ -13357,7 +13371,7 @@
         <v>3.7</v>
       </c>
       <c r="H247" t="n">
-        <v>10.97</v>
+        <v>8.77</v>
       </c>
       <c r="I247" t="n">
         <v>11.13</v>
@@ -13370,7 +13384,7 @@
         <v>-2.79</v>
       </c>
       <c r="M247" t="n">
-        <v>7.36</v>
+        <v>5.93</v>
       </c>
       <c r="N247" t="b">
         <v>0</v>
@@ -13408,7 +13422,7 @@
         <v>36.8</v>
       </c>
       <c r="H248" t="n">
-        <v>21.95</v>
+        <v>23.92</v>
       </c>
       <c r="I248" t="n">
         <v>15.47</v>
@@ -13421,7 +13435,7 @@
         <v>-0.96</v>
       </c>
       <c r="M248" t="n">
-        <v>18.33</v>
+        <v>21.08</v>
       </c>
       <c r="N248" t="b">
         <v>0</v>
@@ -13459,7 +13473,7 @@
         <v>0.2</v>
       </c>
       <c r="H249" t="n">
-        <v>8.16</v>
+        <v>6.33</v>
       </c>
       <c r="I249" t="n">
         <v>4.35</v>
@@ -13472,7 +13486,7 @@
         <v>-2.79</v>
       </c>
       <c r="M249" t="n">
-        <v>4.55</v>
+        <v>3.49</v>
       </c>
       <c r="N249" t="b">
         <v>1</v>
@@ -13510,7 +13524,7 @@
         <v>-31</v>
       </c>
       <c r="H250" t="n">
-        <v>4.98</v>
+        <v>3.6</v>
       </c>
       <c r="I250" t="n">
         <v>19.41</v>
@@ -13523,7 +13537,7 @@
         <v>-10.33</v>
       </c>
       <c r="M250" t="n">
-        <v>1.36</v>
+        <v>0.76</v>
       </c>
       <c r="N250" t="b">
         <v>0</v>
@@ -13565,7 +13579,7 @@
         <v>-2</v>
       </c>
       <c r="H251" t="n">
-        <v>-15.32</v>
+        <v>-17.52</v>
       </c>
       <c r="I251" t="n">
         <v>14.61</v>
@@ -13578,7 +13592,7 @@
         <v>-3.45</v>
       </c>
       <c r="M251" t="n">
-        <v>-18.94</v>
+        <v>-20.36</v>
       </c>
       <c r="N251" t="b">
         <v>0</v>
@@ -13629,7 +13643,7 @@
         <v>-27.15</v>
       </c>
       <c r="M252" t="n">
-        <v>-42.89</v>
+        <v>-42.12</v>
       </c>
       <c r="N252" t="b">
         <v>0</v>
@@ -13667,7 +13681,7 @@
         <v>8.4</v>
       </c>
       <c r="H253" t="n">
-        <v>-34.67</v>
+        <v>-35.81</v>
       </c>
       <c r="I253" t="n">
         <v>-0.13</v>
@@ -13680,7 +13694,7 @@
         <v>-10.87</v>
       </c>
       <c r="M253" t="n">
-        <v>-38.28</v>
+        <v>-38.65</v>
       </c>
       <c r="N253" t="b">
         <v>1</v>
@@ -13718,7 +13732,7 @@
         <v>-21.7</v>
       </c>
       <c r="H254" t="n">
-        <v>-3.28</v>
+        <v>-4.64</v>
       </c>
       <c r="I254" t="n">
         <v>5.5</v>
@@ -13731,7 +13745,7 @@
         <v>-4.3</v>
       </c>
       <c r="M254" t="n">
-        <v>-6.9</v>
+        <v>-7.48</v>
       </c>
       <c r="N254" t="b">
         <v>0</v>
@@ -13769,7 +13783,7 @@
         <v>-7.3</v>
       </c>
       <c r="H255" t="n">
-        <v>-21.25</v>
+        <v>-22.93</v>
       </c>
       <c r="I255" t="n">
         <v>-4.12</v>
@@ -13782,7 +13796,7 @@
         <v>-15.02</v>
       </c>
       <c r="M255" t="n">
-        <v>-24.87</v>
+        <v>-25.77</v>
       </c>
       <c r="N255" t="b">
         <v>1</v>
@@ -13820,7 +13834,7 @@
         <v>-26.1</v>
       </c>
       <c r="H256" t="n">
-        <v>-17.53</v>
+        <v>-19.15</v>
       </c>
       <c r="I256" t="n">
         <v>5.05</v>
@@ -13833,7 +13847,7 @@
         <v>-9.27</v>
       </c>
       <c r="M256" t="n">
-        <v>-21.15</v>
+        <v>-21.99</v>
       </c>
       <c r="N256" t="b">
         <v>1</v>
@@ -13871,7 +13885,7 @@
         <v>-18.5</v>
       </c>
       <c r="H257" t="n">
-        <v>33.42</v>
+        <v>29.32</v>
       </c>
       <c r="I257" t="n">
         <v>16.22</v>
@@ -13884,7 +13898,7 @@
         <v>-9.960000000000001</v>
       </c>
       <c r="M257" t="n">
-        <v>29.8</v>
+        <v>26.47</v>
       </c>
       <c r="N257" t="b">
         <v>0</v>
@@ -13922,7 +13936,7 @@
         <v>15.3</v>
       </c>
       <c r="H258" t="n">
-        <v>-38.43</v>
+        <v>-40.96</v>
       </c>
       <c r="I258" t="n">
         <v>-21.4</v>
@@ -13935,7 +13949,7 @@
         <v>-26.97</v>
       </c>
       <c r="M258" t="n">
-        <v>-42.04</v>
+        <v>-43.81</v>
       </c>
       <c r="N258" t="b">
         <v>0</v>
@@ -13973,7 +13987,7 @@
         <v>26.1</v>
       </c>
       <c r="H259" t="n">
-        <v>-7.01</v>
+        <v>-7.05</v>
       </c>
       <c r="I259" t="n">
         <v>-0.51</v>
@@ -13986,7 +14000,7 @@
         <v>-16.45</v>
       </c>
       <c r="M259" t="n">
-        <v>-10.63</v>
+        <v>-9.890000000000001</v>
       </c>
       <c r="N259" t="b">
         <v>1</v>
@@ -14028,7 +14042,7 @@
         <v>-8.199999999999999</v>
       </c>
       <c r="H260" t="n">
-        <v>-8.44</v>
+        <v>-6.8</v>
       </c>
       <c r="I260" t="n">
         <v>17.48</v>
@@ -14041,7 +14055,7 @@
         <v>-10.68</v>
       </c>
       <c r="M260" t="n">
-        <v>-12.05</v>
+        <v>-9.65</v>
       </c>
       <c r="N260" t="b">
         <v>0</v>
@@ -14092,7 +14106,7 @@
         <v>-8.130000000000001</v>
       </c>
       <c r="M261" t="n">
-        <v>0.53</v>
+        <v>1.3</v>
       </c>
       <c r="N261" t="b">
         <v>1</v>
@@ -14130,7 +14144,7 @@
         <v>0.7</v>
       </c>
       <c r="H262" t="n">
-        <v>-18.57</v>
+        <v>-19.59</v>
       </c>
       <c r="I262" t="n">
         <v>14.96</v>
@@ -14143,7 +14157,7 @@
         <v>-8.039999999999999</v>
       </c>
       <c r="M262" t="n">
-        <v>-22.19</v>
+        <v>-22.43</v>
       </c>
       <c r="N262" t="b">
         <v>1</v>
@@ -14181,7 +14195,7 @@
         <v>61.6</v>
       </c>
       <c r="H263" t="n">
-        <v>3.73</v>
+        <v>3.95</v>
       </c>
       <c r="I263" t="n">
         <v>11.47</v>
@@ -14194,7 +14208,7 @@
         <v>-12.86</v>
       </c>
       <c r="M263" t="n">
-        <v>0.11</v>
+        <v>1.1</v>
       </c>
       <c r="N263" t="b">
         <v>0</v>
@@ -14232,7 +14246,7 @@
         <v>54.3</v>
       </c>
       <c r="H264" t="n">
-        <v>-23.96</v>
+        <v>-24.13</v>
       </c>
       <c r="I264" t="n">
         <v>-2.86</v>
@@ -14245,7 +14259,7 @@
         <v>-24.93</v>
       </c>
       <c r="M264" t="n">
-        <v>-27.57</v>
+        <v>-26.97</v>
       </c>
       <c r="N264" t="b">
         <v>0</v>
@@ -14283,7 +14297,7 @@
         <v>14.8</v>
       </c>
       <c r="H265" t="n">
-        <v>-2.13</v>
+        <v>-2.53</v>
       </c>
       <c r="I265" t="n">
         <v>0.35</v>
@@ -14296,7 +14310,7 @@
         <v>-3.68</v>
       </c>
       <c r="M265" t="n">
-        <v>-5.74</v>
+        <v>-5.37</v>
       </c>
       <c r="N265" t="b">
         <v>1</v>
@@ -14334,7 +14348,7 @@
         <v>-13.5</v>
       </c>
       <c r="H266" t="n">
-        <v>-8.49</v>
+        <v>-12.06</v>
       </c>
       <c r="I266" t="n">
         <v>-1.88</v>
@@ -14347,7 +14361,7 @@
         <v>-11.4</v>
       </c>
       <c r="M266" t="n">
-        <v>-12.1</v>
+        <v>-14.9</v>
       </c>
       <c r="N266" t="b">
         <v>0</v>
@@ -14385,7 +14399,7 @@
         <v>25.5</v>
       </c>
       <c r="H267" t="n">
-        <v>-0.15</v>
+        <v>1.59</v>
       </c>
       <c r="I267" t="n">
         <v>-9.369999999999999</v>
@@ -14398,7 +14412,7 @@
         <v>-22.11</v>
       </c>
       <c r="M267" t="n">
-        <v>-3.77</v>
+        <v>-1.25</v>
       </c>
       <c r="N267" t="b">
         <v>1</v>
@@ -14440,7 +14454,7 @@
         <v>-7.5</v>
       </c>
       <c r="H268" t="n">
-        <v>-6.68</v>
+        <v>-7.28</v>
       </c>
       <c r="I268" t="n">
         <v>4.46</v>
@@ -14453,7 +14467,7 @@
         <v>-8.52</v>
       </c>
       <c r="M268" t="n">
-        <v>-10.3</v>
+        <v>-10.13</v>
       </c>
       <c r="N268" t="b">
         <v>1</v>
@@ -14542,7 +14556,7 @@
         <v>-11</v>
       </c>
       <c r="H270" t="n">
-        <v>0.52</v>
+        <v>0.26</v>
       </c>
       <c r="I270" t="n">
         <v>10.7</v>
@@ -14555,7 +14569,7 @@
         <v>-9.43</v>
       </c>
       <c r="M270" t="n">
-        <v>-3.1</v>
+        <v>-2.59</v>
       </c>
       <c r="N270" t="b">
         <v>1</v>
@@ -14593,7 +14607,7 @@
         <v>-11.4</v>
       </c>
       <c r="H271" t="n">
-        <v>-11.75</v>
+        <v>-12.88</v>
       </c>
       <c r="I271" t="n">
         <v>4.36</v>
@@ -14606,7 +14620,7 @@
         <v>-11.36</v>
       </c>
       <c r="M271" t="n">
-        <v>-15.36</v>
+        <v>-15.72</v>
       </c>
       <c r="N271" t="b">
         <v>1</v>
@@ -14644,7 +14658,7 @@
         <v>2.1</v>
       </c>
       <c r="H272" t="n">
-        <v>52.07</v>
+        <v>52.15</v>
       </c>
       <c r="I272" t="n">
         <v>20.72</v>
@@ -14657,7 +14671,7 @@
         <v>-5.79</v>
       </c>
       <c r="M272" t="n">
-        <v>48.46</v>
+        <v>49.31</v>
       </c>
       <c r="N272" t="b">
         <v>0</v>
@@ -14695,7 +14709,7 @@
         <v>27.1</v>
       </c>
       <c r="H273" t="n">
-        <v>-2.55</v>
+        <v>-5.61</v>
       </c>
       <c r="I273" t="n">
         <v>5.02</v>
@@ -14708,7 +14722,7 @@
         <v>-14.35</v>
       </c>
       <c r="M273" t="n">
-        <v>-6.16</v>
+        <v>-8.449999999999999</v>
       </c>
       <c r="N273" t="b">
         <v>1</v>
@@ -14746,7 +14760,7 @@
         <v>-21.6</v>
       </c>
       <c r="H274" t="n">
-        <v>-7.76</v>
+        <v>-9.73</v>
       </c>
       <c r="I274" t="n">
         <v>1.22</v>
@@ -14759,7 +14773,7 @@
         <v>-6.54</v>
       </c>
       <c r="M274" t="n">
-        <v>-11.37</v>
+        <v>-12.57</v>
       </c>
       <c r="N274" t="b">
         <v>0</v>
@@ -14801,7 +14815,7 @@
         <v>-2.2</v>
       </c>
       <c r="H275" t="n">
-        <v>16.13</v>
+        <v>13.27</v>
       </c>
       <c r="I275" t="n">
         <v>-9.050000000000001</v>
@@ -14814,7 +14828,7 @@
         <v>-18.61</v>
       </c>
       <c r="M275" t="n">
-        <v>12.52</v>
+        <v>10.43</v>
       </c>
       <c r="N275" t="b">
         <v>0</v>
@@ -14852,7 +14866,7 @@
         <v>0.7</v>
       </c>
       <c r="H276" t="n">
-        <v>0.82</v>
+        <v>0.1</v>
       </c>
       <c r="I276" t="n">
         <v>11.4</v>
@@ -14865,7 +14879,7 @@
         <v>-7.28</v>
       </c>
       <c r="M276" t="n">
-        <v>-2.79</v>
+        <v>-2.74</v>
       </c>
       <c r="N276" t="b">
         <v>0</v>
@@ -14903,7 +14917,7 @@
         <v>-31.7</v>
       </c>
       <c r="H277" t="n">
-        <v>-1.82</v>
+        <v>1.66</v>
       </c>
       <c r="I277" t="n">
         <v>17.04</v>
@@ -14916,7 +14930,7 @@
         <v>-4.05</v>
       </c>
       <c r="M277" t="n">
-        <v>-5.44</v>
+        <v>-1.18</v>
       </c>
       <c r="N277" t="b">
         <v>0</v>
@@ -14954,7 +14968,7 @@
         <v>32.2</v>
       </c>
       <c r="H278" t="n">
-        <v>19.11</v>
+        <v>17.23</v>
       </c>
       <c r="I278" t="n">
         <v>6.49</v>
@@ -14967,7 +14981,7 @@
         <v>-3.92</v>
       </c>
       <c r="M278" t="n">
-        <v>15.5</v>
+        <v>14.38</v>
       </c>
       <c r="N278" t="b">
         <v>1</v>
@@ -15054,7 +15068,7 @@
         <v>3.2</v>
       </c>
       <c r="H280" t="n">
-        <v>-16.35</v>
+        <v>-19.88</v>
       </c>
       <c r="I280" t="n">
         <v>-10.41</v>
@@ -15067,7 +15081,7 @@
         <v>-23.7</v>
       </c>
       <c r="M280" t="n">
-        <v>-19.96</v>
+        <v>-22.72</v>
       </c>
       <c r="N280" t="b">
         <v>1</v>
@@ -15105,7 +15119,7 @@
         <v>7.3</v>
       </c>
       <c r="H281" t="n">
-        <v>-4.43</v>
+        <v>-4.21</v>
       </c>
       <c r="I281" t="n">
         <v>-0.57</v>
@@ -15118,7 +15132,7 @@
         <v>-5.89</v>
       </c>
       <c r="M281" t="n">
-        <v>-8.039999999999999</v>
+        <v>-7.06</v>
       </c>
       <c r="N281" t="b">
         <v>1</v>
@@ -15156,7 +15170,7 @@
         <v>24.5</v>
       </c>
       <c r="H282" t="n">
-        <v>5.78</v>
+        <v>4.59</v>
       </c>
       <c r="I282" t="n">
         <v>17.24</v>
@@ -15169,7 +15183,7 @@
         <v>-0.47</v>
       </c>
       <c r="M282" t="n">
-        <v>2.16</v>
+        <v>1.75</v>
       </c>
       <c r="N282" t="b">
         <v>0</v>
@@ -15207,7 +15221,7 @@
         <v>-0.3</v>
       </c>
       <c r="H283" t="n">
-        <v>-3.49</v>
+        <v>-4.13</v>
       </c>
       <c r="I283" t="n">
         <v>17.76</v>
@@ -15220,7 +15234,7 @@
         <v>-14.18</v>
       </c>
       <c r="M283" t="n">
-        <v>-7.11</v>
+        <v>-6.97</v>
       </c>
       <c r="N283" t="b">
         <v>1</v>
@@ -15258,7 +15272,7 @@
         <v>4</v>
       </c>
       <c r="H284" t="n">
-        <v>39.65</v>
+        <v>37.76</v>
       </c>
       <c r="I284" t="n">
         <v>8.75</v>
@@ -15271,7 +15285,7 @@
         <v>-11.02</v>
       </c>
       <c r="M284" t="n">
-        <v>36.03</v>
+        <v>34.91</v>
       </c>
       <c r="N284" t="b">
         <v>0</v>
@@ -15309,7 +15323,7 @@
         <v>-6.8</v>
       </c>
       <c r="H285" t="n">
-        <v>44.84</v>
+        <v>42.01</v>
       </c>
       <c r="I285" t="n">
         <v>8.279999999999999</v>
@@ -15322,7 +15336,7 @@
         <v>-6.78</v>
       </c>
       <c r="M285" t="n">
-        <v>41.23</v>
+        <v>39.16</v>
       </c>
       <c r="N285" t="b">
         <v>1</v>
@@ -15360,7 +15374,7 @@
         <v>-42</v>
       </c>
       <c r="H286" t="n">
-        <v>56.56</v>
+        <v>55.11</v>
       </c>
       <c r="I286" t="n">
         <v>-3.61</v>
@@ -15373,7 +15387,7 @@
         <v>-11.94</v>
       </c>
       <c r="M286" t="n">
-        <v>52.94</v>
+        <v>52.26</v>
       </c>
       <c r="N286" t="b">
         <v>0</v>
@@ -15411,7 +15425,7 @@
         <v>14.6</v>
       </c>
       <c r="H287" t="n">
-        <v>1.67</v>
+        <v>0.92</v>
       </c>
       <c r="I287" t="n">
         <v>8.539999999999999</v>
@@ -15424,7 +15438,7 @@
         <v>-13.21</v>
       </c>
       <c r="M287" t="n">
-        <v>-1.95</v>
+        <v>-1.92</v>
       </c>
       <c r="N287" t="b">
         <v>0</v>
@@ -15462,7 +15476,7 @@
         <v>34.6</v>
       </c>
       <c r="H288" t="n">
-        <v>-2.04</v>
+        <v>-4.58</v>
       </c>
       <c r="I288" t="n">
         <v>5.7</v>
@@ -15475,7 +15489,7 @@
         <v>-7.7</v>
       </c>
       <c r="M288" t="n">
-        <v>-5.66</v>
+        <v>-7.43</v>
       </c>
       <c r="N288" t="b">
         <v>1</v>
@@ -15513,7 +15527,7 @@
         <v>-37.2</v>
       </c>
       <c r="H289" t="n">
-        <v>10.08</v>
+        <v>7.82</v>
       </c>
       <c r="I289" t="n">
         <v>21.67</v>
@@ -15526,7 +15540,7 @@
         <v>-6.64</v>
       </c>
       <c r="M289" t="n">
-        <v>6.47</v>
+        <v>4.97</v>
       </c>
       <c r="N289" t="b">
         <v>0</v>
@@ -15564,7 +15578,7 @@
         <v>-31.2</v>
       </c>
       <c r="H290" t="n">
-        <v>-19.89</v>
+        <v>-26.24</v>
       </c>
       <c r="I290" t="n">
         <v>1.03</v>
@@ -15577,7 +15591,7 @@
         <v>-13.65</v>
       </c>
       <c r="M290" t="n">
-        <v>-23.5</v>
+        <v>-29.08</v>
       </c>
       <c r="N290" t="b">
         <v>0</v>
@@ -15615,7 +15629,7 @@
         <v>10.4</v>
       </c>
       <c r="H291" t="n">
-        <v>22.84</v>
+        <v>24.05</v>
       </c>
       <c r="I291" t="n">
         <v>11.05</v>
@@ -15628,7 +15642,7 @@
         <v>-5.54</v>
       </c>
       <c r="M291" t="n">
-        <v>19.23</v>
+        <v>21.21</v>
       </c>
       <c r="N291" t="b">
         <v>1</v>
@@ -15666,7 +15680,7 @@
         <v>-14.7</v>
       </c>
       <c r="H292" t="n">
-        <v>15.41</v>
+        <v>15.11</v>
       </c>
       <c r="I292" t="n">
         <v>12.94</v>
@@ -15679,7 +15693,7 @@
         <v>-2.34</v>
       </c>
       <c r="M292" t="n">
-        <v>11.79</v>
+        <v>12.27</v>
       </c>
       <c r="N292" t="b">
         <v>0</v>
@@ -15717,7 +15731,7 @@
         <v>-21.5</v>
       </c>
       <c r="H293" t="n">
-        <v>-16.12</v>
+        <v>-14.55</v>
       </c>
       <c r="I293" t="n">
         <v>10.65</v>
@@ -15730,7 +15744,7 @@
         <v>-6.89</v>
       </c>
       <c r="M293" t="n">
-        <v>-19.73</v>
+        <v>-17.4</v>
       </c>
       <c r="N293" t="b">
         <v>1</v>
@@ -15768,7 +15782,7 @@
         <v>20.2</v>
       </c>
       <c r="H294" t="n">
-        <v>-7.43</v>
+        <v>-7.61</v>
       </c>
       <c r="I294" t="n">
         <v>-1.23</v>
@@ -15781,7 +15795,7 @@
         <v>-12.56</v>
       </c>
       <c r="M294" t="n">
-        <v>-11.04</v>
+        <v>-10.45</v>
       </c>
       <c r="N294" t="b">
         <v>0</v>
@@ -15819,7 +15833,7 @@
         <v>3.5</v>
       </c>
       <c r="H295" t="n">
-        <v>48.27</v>
+        <v>48.66</v>
       </c>
       <c r="I295" t="n">
         <v>33.01</v>
@@ -15832,7 +15846,7 @@
         <v>-0.92</v>
       </c>
       <c r="M295" t="n">
-        <v>44.66</v>
+        <v>45.82</v>
       </c>
       <c r="N295" t="b">
         <v>1</v>
@@ -15870,7 +15884,7 @@
         <v>14</v>
       </c>
       <c r="H296" t="n">
-        <v>22.83</v>
+        <v>21.66</v>
       </c>
       <c r="I296" t="n">
         <v>2.89</v>
@@ -15883,7 +15897,7 @@
         <v>-1.94</v>
       </c>
       <c r="M296" t="n">
-        <v>19.22</v>
+        <v>18.81</v>
       </c>
       <c r="N296" t="b">
         <v>0</v>
@@ -15921,7 +15935,7 @@
         <v>19.8</v>
       </c>
       <c r="H297" t="n">
-        <v>11.16</v>
+        <v>10.42</v>
       </c>
       <c r="I297" t="n">
         <v>4.74</v>
@@ -15934,7 +15948,7 @@
         <v>-9.9</v>
       </c>
       <c r="M297" t="n">
-        <v>7.54</v>
+        <v>7.57</v>
       </c>
       <c r="N297" t="b">
         <v>1</v>
@@ -15976,7 +15990,7 @@
         <v>-7.4</v>
       </c>
       <c r="H298" t="n">
-        <v>4.83</v>
+        <v>1.13</v>
       </c>
       <c r="I298" t="n">
         <v>-3.85</v>
@@ -15989,7 +16003,7 @@
         <v>-21.11</v>
       </c>
       <c r="M298" t="n">
-        <v>1.22</v>
+        <v>-1.71</v>
       </c>
       <c r="N298" t="b">
         <v>0</v>
@@ -16027,7 +16041,7 @@
         <v>-10.8</v>
       </c>
       <c r="H299" t="n">
-        <v>5.94</v>
+        <v>3.31</v>
       </c>
       <c r="I299" t="n">
         <v>1.78</v>
@@ -16040,7 +16054,7 @@
         <v>-7.51</v>
       </c>
       <c r="M299" t="n">
-        <v>2.32</v>
+        <v>0.46</v>
       </c>
       <c r="N299" t="b">
         <v>0</v>
@@ -16078,7 +16092,7 @@
         <v>-24</v>
       </c>
       <c r="H300" t="n">
-        <v>31.11</v>
+        <v>35.42</v>
       </c>
       <c r="I300" t="n">
         <v>10.85</v>
@@ -16091,7 +16105,7 @@
         <v>-5.43</v>
       </c>
       <c r="M300" t="n">
-        <v>27.5</v>
+        <v>32.57</v>
       </c>
       <c r="N300" t="b">
         <v>0</v>
@@ -16129,7 +16143,7 @@
         <v>-28.3</v>
       </c>
       <c r="H301" t="n">
-        <v>-23.54</v>
+        <v>-24.82</v>
       </c>
       <c r="I301" t="n">
         <v>-8.949999999999999</v>
@@ -16142,7 +16156,7 @@
         <v>-13.18</v>
       </c>
       <c r="M301" t="n">
-        <v>-27.15</v>
+        <v>-27.66</v>
       </c>
       <c r="N301" t="b">
         <v>0</v>
@@ -16180,7 +16194,7 @@
         <v>-30.5</v>
       </c>
       <c r="H302" t="n">
-        <v>-2.44</v>
+        <v>-2.41</v>
       </c>
       <c r="I302" t="n">
         <v>2.96</v>
@@ -16193,7 +16207,7 @@
         <v>-17.88</v>
       </c>
       <c r="M302" t="n">
-        <v>-6.05</v>
+        <v>-5.25</v>
       </c>
       <c r="N302" t="b">
         <v>1</v>
@@ -16231,7 +16245,7 @@
         <v>-6</v>
       </c>
       <c r="H303" t="n">
-        <v>-18.8</v>
+        <v>-20.24</v>
       </c>
       <c r="I303" t="n">
         <v>3.31</v>
@@ -16244,7 +16258,7 @@
         <v>-21.48</v>
       </c>
       <c r="M303" t="n">
-        <v>-22.41</v>
+        <v>-23.09</v>
       </c>
       <c r="N303" t="b">
         <v>1</v>
@@ -16282,7 +16296,7 @@
         <v>-42.2</v>
       </c>
       <c r="H304" t="n">
-        <v>7.27</v>
+        <v>3.87</v>
       </c>
       <c r="I304" t="n">
         <v>19.24</v>
@@ -16295,7 +16309,7 @@
         <v>-0.93</v>
       </c>
       <c r="M304" t="n">
-        <v>3.65</v>
+        <v>1.02</v>
       </c>
       <c r="N304" t="b">
         <v>0</v>
@@ -16333,7 +16347,7 @@
         <v>-34.6</v>
       </c>
       <c r="H305" t="n">
-        <v>-2.36</v>
+        <v>-5.47</v>
       </c>
       <c r="I305" t="n">
         <v>23.65</v>
@@ -16346,7 +16360,7 @@
         <v>-3.83</v>
       </c>
       <c r="M305" t="n">
-        <v>-5.97</v>
+        <v>-8.31</v>
       </c>
       <c r="N305" t="b">
         <v>1</v>
@@ -16384,7 +16398,7 @@
         <v>-48.1</v>
       </c>
       <c r="H306" t="n">
-        <v>-10.28</v>
+        <v>-12.48</v>
       </c>
       <c r="I306" t="n">
         <v>2.19</v>
@@ -16397,7 +16411,7 @@
         <v>-13.66</v>
       </c>
       <c r="M306" t="n">
-        <v>-13.9</v>
+        <v>-15.32</v>
       </c>
       <c r="N306" t="b">
         <v>0</v>
@@ -16435,7 +16449,7 @@
         <v>-16.2</v>
       </c>
       <c r="H307" t="n">
-        <v>11.03</v>
+        <v>8.44</v>
       </c>
       <c r="I307" t="n">
         <v>25.77</v>
@@ -16448,7 +16462,7 @@
         <v>-1.7</v>
       </c>
       <c r="M307" t="n">
-        <v>7.42</v>
+        <v>5.59</v>
       </c>
       <c r="N307" t="b">
         <v>1</v>
@@ -16486,7 +16500,7 @@
         <v>-24.9</v>
       </c>
       <c r="H308" t="n">
-        <v>31.46</v>
+        <v>22.23</v>
       </c>
       <c r="I308" t="n">
         <v>10.88</v>
@@ -16499,7 +16513,7 @@
         <v>-4.1</v>
       </c>
       <c r="M308" t="n">
-        <v>27.85</v>
+        <v>19.39</v>
       </c>
       <c r="N308" t="b">
         <v>1</v>
@@ -16541,7 +16555,7 @@
         <v>-8.1</v>
       </c>
       <c r="H309" t="n">
-        <v>16.95</v>
+        <v>13.34</v>
       </c>
       <c r="I309" t="n">
         <v>14.27</v>
@@ -16554,7 +16568,7 @@
         <v>-10.92</v>
       </c>
       <c r="M309" t="n">
-        <v>13.34</v>
+        <v>10.49</v>
       </c>
       <c r="N309" t="b">
         <v>1</v>
@@ -16592,7 +16606,7 @@
         <v>-10.2</v>
       </c>
       <c r="H310" t="n">
-        <v>-10.82</v>
+        <v>-12.15</v>
       </c>
       <c r="I310" t="n">
         <v>15.03</v>
@@ -16605,7 +16619,7 @@
         <v>-1.61</v>
       </c>
       <c r="M310" t="n">
-        <v>-14.44</v>
+        <v>-14.99</v>
       </c>
       <c r="N310" t="b">
         <v>1</v>
@@ -16643,7 +16657,7 @@
         <v>68.90000000000001</v>
       </c>
       <c r="H311" t="n">
-        <v>14.32</v>
+        <v>15.4</v>
       </c>
       <c r="I311" t="n">
         <v>1.84</v>
@@ -16656,7 +16670,7 @@
         <v>-10.43</v>
       </c>
       <c r="M311" t="n">
-        <v>10.7</v>
+        <v>12.56</v>
       </c>
       <c r="N311" t="b">
         <v>1</v>
@@ -16694,7 +16708,7 @@
         <v>-40.8</v>
       </c>
       <c r="H312" t="n">
-        <v>-13.5</v>
+        <v>-14.35</v>
       </c>
       <c r="I312" t="n">
         <v>21.71</v>
@@ -16707,7 +16721,7 @@
         <v>-3.3</v>
       </c>
       <c r="M312" t="n">
-        <v>-17.12</v>
+        <v>-17.19</v>
       </c>
       <c r="N312" t="b">
         <v>1</v>
@@ -16758,7 +16772,7 @@
         <v>-3.45</v>
       </c>
       <c r="M313" t="n">
-        <v>-20.82</v>
+        <v>-20.05</v>
       </c>
       <c r="N313" t="b">
         <v>0</v>
@@ -16796,7 +16810,7 @@
         <v>40.7</v>
       </c>
       <c r="H314" t="n">
-        <v>36.33</v>
+        <v>41.86</v>
       </c>
       <c r="I314" t="n">
         <v>-4.08</v>
@@ -16809,7 +16823,7 @@
         <v>-11.2</v>
       </c>
       <c r="M314" t="n">
-        <v>32.72</v>
+        <v>39.02</v>
       </c>
       <c r="N314" t="b">
         <v>1</v>
@@ -16847,7 +16861,7 @@
         <v>25.7</v>
       </c>
       <c r="H315" t="n">
-        <v>-8.59</v>
+        <v>-8.449999999999999</v>
       </c>
       <c r="I315" t="n">
         <v>11.3</v>
@@ -16860,7 +16874,7 @@
         <v>-11.03</v>
       </c>
       <c r="M315" t="n">
-        <v>-12.2</v>
+        <v>-11.29</v>
       </c>
       <c r="N315" t="b">
         <v>1</v>
@@ -16898,7 +16912,7 @@
         <v>2.3</v>
       </c>
       <c r="H316" t="n">
-        <v>-7.43</v>
+        <v>-7.86</v>
       </c>
       <c r="I316" t="n">
         <v>-0.95</v>
@@ -16911,7 +16925,7 @@
         <v>-7.81</v>
       </c>
       <c r="M316" t="n">
-        <v>-11.04</v>
+        <v>-10.7</v>
       </c>
       <c r="N316" t="b">
         <v>0</v>
@@ -17043,16 +17057,16 @@
         <v>0.1</v>
       </c>
       <c r="H2" t="n">
-        <v>0.65</v>
+        <v>0.19</v>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="n">
-        <v>-0.84</v>
+        <v>-1.9</v>
       </c>
       <c r="M2" t="n">
-        <v>0.32</v>
+        <v>0.6</v>
       </c>
       <c r="N2" t="b">
         <v>1</v>
@@ -17079,7 +17093,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Extended</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="E3" t="inlineStr"/>
@@ -17090,16 +17104,16 @@
         <v>-31.6</v>
       </c>
       <c r="H3" t="n">
-        <v>5.1</v>
+        <v>-1.71</v>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="n">
-        <v>-0.77</v>
+        <v>-3.1</v>
       </c>
       <c r="M3" t="n">
-        <v>4.77</v>
+        <v>-1.3</v>
       </c>
       <c r="N3" t="b">
         <v>1</v>
@@ -17137,16 +17151,16 @@
         <v>-2.7</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.45</v>
+        <v>-1.96</v>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="n">
-        <v>-3.59</v>
+        <v>-3.64</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.1</v>
+        <v>-0.87</v>
       </c>
       <c r="N4" t="b">
         <v>1</v>
@@ -17173,7 +17187,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Extended</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
@@ -17184,7 +17198,7 @@
         <v>26.9</v>
       </c>
       <c r="H5" t="n">
-        <v>4.96</v>
+        <v>7.4</v>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
@@ -17193,7 +17207,7 @@
         <v>-0.4</v>
       </c>
       <c r="M5" t="n">
-        <v>5.3</v>
+        <v>8.49</v>
       </c>
       <c r="N5" t="b">
         <v>1</v>
@@ -17231,7 +17245,7 @@
         <v>-18.1</v>
       </c>
       <c r="H6" t="n">
-        <v>1.26</v>
+        <v>2.58</v>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
@@ -17240,7 +17254,7 @@
         <v>-2.69</v>
       </c>
       <c r="M6" t="n">
-        <v>0.6</v>
+        <v>2.66</v>
       </c>
       <c r="N6" t="b">
         <v>1</v>
@@ -17267,7 +17281,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Extended</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="E7" t="inlineStr"/>
@@ -17278,7 +17292,7 @@
         <v>-21.5</v>
       </c>
       <c r="H7" t="n">
-        <v>5.5</v>
+        <v>4.37</v>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
@@ -17287,7 +17301,7 @@
         <v>-1.4</v>
       </c>
       <c r="M7" t="n">
-        <v>4.83</v>
+        <v>4.46</v>
       </c>
       <c r="N7" t="b">
         <v>1</v>
@@ -17325,7 +17339,7 @@
         <v>41.6</v>
       </c>
       <c r="H8" t="n">
-        <v>3.15</v>
+        <v>3.09</v>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
@@ -17334,7 +17348,7 @@
         <v>-4.38</v>
       </c>
       <c r="M8" t="n">
-        <v>1.83</v>
+        <v>2.52</v>
       </c>
       <c r="N8" t="b">
         <v>1</v>
@@ -17372,16 +17386,16 @@
         <v>32.1</v>
       </c>
       <c r="H9" t="n">
-        <v>-2.58</v>
+        <v>-4.54</v>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="n">
-        <v>-4.4</v>
+        <v>-6.94</v>
       </c>
       <c r="M9" t="n">
-        <v>-3.9</v>
+        <v>-5.1</v>
       </c>
       <c r="N9" t="b">
         <v>1</v>
@@ -17419,16 +17433,16 @@
         <v>-14.4</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.3</v>
+        <v>-2.71</v>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="n">
-        <v>-4.51</v>
+        <v>-4.62</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.62</v>
+        <v>-3.27</v>
       </c>
       <c r="N10" t="b">
         <v>1</v>
@@ -17466,16 +17480,16 @@
         <v>-10</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.33</v>
+        <v>-8.300000000000001</v>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="n">
-        <v>-5.75</v>
+        <v>-9.539999999999999</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.65</v>
+        <v>-8.859999999999999</v>
       </c>
       <c r="N11" t="b">
         <v>1</v>
@@ -17513,16 +17527,16 @@
         <v>6.4</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.36</v>
+        <v>-1.79</v>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="n">
-        <v>-2.04</v>
+        <v>-3.01</v>
       </c>
       <c r="M12" t="n">
-        <v>-2.68</v>
+        <v>-2.35</v>
       </c>
       <c r="N12" t="b">
         <v>1</v>
@@ -17560,7 +17574,7 @@
         <v>20.2</v>
       </c>
       <c r="H13" t="n">
-        <v>2.69</v>
+        <v>4.34</v>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
@@ -17569,7 +17583,7 @@
         <v>-1.07</v>
       </c>
       <c r="M13" t="n">
-        <v>0.96</v>
+        <v>3.37</v>
       </c>
       <c r="N13" t="b">
         <v>1</v>
@@ -17596,7 +17610,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Extended</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="E14" t="inlineStr"/>
@@ -17607,7 +17621,7 @@
         <v>43.7</v>
       </c>
       <c r="H14" t="n">
-        <v>5.33</v>
+        <v>4.39</v>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
@@ -17616,7 +17630,7 @@
         <v>-2.44</v>
       </c>
       <c r="M14" t="n">
-        <v>3.6</v>
+        <v>3.42</v>
       </c>
       <c r="N14" t="b">
         <v>1</v>
@@ -17654,16 +17668,16 @@
         <v>1.9</v>
       </c>
       <c r="H15" t="n">
-        <v>-6.49</v>
+        <v>-9.949999999999999</v>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="n">
-        <v>-7.28</v>
+        <v>-11.15</v>
       </c>
       <c r="M15" t="n">
-        <v>-8.220000000000001</v>
+        <v>-10.92</v>
       </c>
       <c r="N15" t="b">
         <v>1</v>
@@ -17701,16 +17715,18 @@
         <v>37.5</v>
       </c>
       <c r="H16" t="n">
-        <v>5.24</v>
-      </c>
-      <c r="I16" t="inlineStr"/>
+        <v>5.86</v>
+      </c>
+      <c r="I16" t="n">
+        <v>5.86</v>
+      </c>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="n">
         <v>-3.95</v>
       </c>
       <c r="M16" t="n">
-        <v>3.36</v>
+        <v>4.74</v>
       </c>
       <c r="N16" t="b">
         <v>1</v>
@@ -17748,16 +17764,18 @@
         <v>40.2</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.57</v>
-      </c>
-      <c r="I17" t="inlineStr"/>
+        <v>-1.11</v>
+      </c>
+      <c r="I17" t="n">
+        <v>-1.11</v>
+      </c>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="n">
         <v>-3.87</v>
       </c>
       <c r="M17" t="n">
-        <v>-3.45</v>
+        <v>-2.23</v>
       </c>
       <c r="N17" t="b">
         <v>1</v>
@@ -17795,16 +17813,18 @@
         <v>10.7</v>
       </c>
       <c r="H18" t="n">
-        <v>6.71</v>
-      </c>
-      <c r="I18" t="inlineStr"/>
+        <v>7.3</v>
+      </c>
+      <c r="I18" t="n">
+        <v>7.3</v>
+      </c>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="n">
         <v>-3.78</v>
       </c>
       <c r="M18" t="n">
-        <v>4.83</v>
+        <v>6.18</v>
       </c>
       <c r="N18" t="b">
         <v>1</v>
@@ -17842,7 +17862,7 @@
         <v>25.6</v>
       </c>
       <c r="H19" t="n">
-        <v>7.71</v>
+        <v>10.29</v>
       </c>
       <c r="I19" t="n">
         <v>7.71</v>
@@ -17853,7 +17873,7 @@
         <v>-4.85</v>
       </c>
       <c r="M19" t="n">
-        <v>6.6</v>
+        <v>9.93</v>
       </c>
       <c r="N19" t="b">
         <v>1</v>
@@ -17891,7 +17911,7 @@
         <v>-6.9</v>
       </c>
       <c r="H20" t="n">
-        <v>7.29</v>
+        <v>6.92</v>
       </c>
       <c r="I20" t="n">
         <v>6.44</v>
@@ -17902,7 +17922,7 @@
         <v>-4.53</v>
       </c>
       <c r="M20" t="n">
-        <v>6.08</v>
+        <v>6.47</v>
       </c>
       <c r="N20" t="b">
         <v>1</v>
@@ -17940,7 +17960,7 @@
         <v>0.3</v>
       </c>
       <c r="H21" t="n">
-        <v>-10.95</v>
+        <v>-11.97</v>
       </c>
       <c r="I21" t="n">
         <v>-10.53</v>
@@ -17951,7 +17971,7 @@
         <v>-15.78</v>
       </c>
       <c r="M21" t="n">
-        <v>-11.64</v>
+        <v>-11.92</v>
       </c>
       <c r="N21" t="b">
         <v>1</v>
@@ -17989,7 +18009,7 @@
         <v>2.8</v>
       </c>
       <c r="H22" t="n">
-        <v>3.05</v>
+        <v>1.95</v>
       </c>
       <c r="I22" t="n">
         <v>3.18</v>
@@ -18000,7 +18020,7 @@
         <v>-0.88</v>
       </c>
       <c r="M22" t="n">
-        <v>1.63</v>
+        <v>1.29</v>
       </c>
       <c r="N22" t="b">
         <v>1</v>
@@ -18038,7 +18058,7 @@
         <v>34.5</v>
       </c>
       <c r="H23" t="n">
-        <v>7.09</v>
+        <v>7.62</v>
       </c>
       <c r="I23" t="n">
         <v>0.66</v>
@@ -18049,7 +18069,7 @@
         <v>-2.64</v>
       </c>
       <c r="M23" t="n">
-        <v>5.67</v>
+        <v>6.96</v>
       </c>
       <c r="N23" t="b">
         <v>1</v>
@@ -18076,7 +18096,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Extended</t>
+          <t>Retired</t>
         </is>
       </c>
       <c r="E24" t="inlineStr"/>
@@ -18087,7 +18107,7 @@
         <v>24.3</v>
       </c>
       <c r="H24" t="n">
-        <v>33.23</v>
+        <v>36.83</v>
       </c>
       <c r="I24" t="n">
         <v>2.54</v>
@@ -18098,7 +18118,7 @@
         <v>-5.21</v>
       </c>
       <c r="M24" t="n">
-        <v>32.46</v>
+        <v>36.81</v>
       </c>
       <c r="N24" t="b">
         <v>1</v>
@@ -18125,7 +18145,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Retired</t>
         </is>
       </c>
       <c r="E25" t="inlineStr"/>
@@ -18136,7 +18156,7 @@
         <v>-16.9</v>
       </c>
       <c r="H25" t="n">
-        <v>-6.47</v>
+        <v>-8.789999999999999</v>
       </c>
       <c r="I25" t="n">
         <v>-6.47</v>
@@ -18147,7 +18167,7 @@
         <v>-11.5</v>
       </c>
       <c r="M25" t="n">
-        <v>-7.25</v>
+        <v>-8.82</v>
       </c>
       <c r="N25" t="b">
         <v>1</v>
@@ -18185,7 +18205,7 @@
         <v>20.3</v>
       </c>
       <c r="H26" t="n">
-        <v>-13.45</v>
+        <v>-17.1</v>
       </c>
       <c r="I26" t="n">
         <v>-2.07</v>
@@ -18198,7 +18218,7 @@
         <v>-17.35</v>
       </c>
       <c r="M26" t="n">
-        <v>-14.07</v>
+        <v>-16.97</v>
       </c>
       <c r="N26" t="b">
         <v>1</v>
@@ -18236,7 +18256,7 @@
         <v>0.3</v>
       </c>
       <c r="H27" t="n">
-        <v>-18.35</v>
+        <v>-19.53</v>
       </c>
       <c r="I27" t="n">
         <v>-9.9</v>
@@ -18249,7 +18269,7 @@
         <v>-21.72</v>
       </c>
       <c r="M27" t="n">
-        <v>-19.46</v>
+        <v>-19.9</v>
       </c>
       <c r="N27" t="b">
         <v>1</v>
@@ -18287,7 +18307,7 @@
         <v>49.4</v>
       </c>
       <c r="H28" t="n">
-        <v>4.28</v>
+        <v>1.86</v>
       </c>
       <c r="I28" t="n">
         <v>2.9</v>
@@ -18300,7 +18320,7 @@
         <v>-5.67</v>
       </c>
       <c r="M28" t="n">
-        <v>3.36</v>
+        <v>1.68</v>
       </c>
       <c r="N28" t="b">
         <v>1</v>
@@ -18338,7 +18358,7 @@
         <v>4.5</v>
       </c>
       <c r="H29" t="n">
-        <v>-9.99</v>
+        <v>-10.46</v>
       </c>
       <c r="I29" t="n">
         <v>-7.61</v>
@@ -18351,7 +18371,7 @@
         <v>-11.06</v>
       </c>
       <c r="M29" t="n">
-        <v>-10.92</v>
+        <v>-10.63</v>
       </c>
       <c r="N29" t="b">
         <v>1</v>
@@ -18389,7 +18409,7 @@
         <v>-17.9</v>
       </c>
       <c r="H30" t="n">
-        <v>-9.42</v>
+        <v>-10.3</v>
       </c>
       <c r="I30" t="n">
         <v>0.6</v>
@@ -18402,7 +18422,7 @@
         <v>-4.72</v>
       </c>
       <c r="M30" t="n">
-        <v>-10.37</v>
+        <v>-10.5</v>
       </c>
       <c r="N30" t="b">
         <v>1</v>
@@ -18440,7 +18460,7 @@
         <v>2.1</v>
       </c>
       <c r="H31" t="n">
-        <v>-21.48</v>
+        <v>-22.71</v>
       </c>
       <c r="I31" t="n">
         <v>0.25</v>
@@ -18453,7 +18473,7 @@
         <v>-16.43</v>
       </c>
       <c r="M31" t="n">
-        <v>-22.43</v>
+        <v>-22.92</v>
       </c>
       <c r="N31" t="b">
         <v>1</v>
@@ -18491,7 +18511,7 @@
         <v>19.4</v>
       </c>
       <c r="H32" t="n">
-        <v>-11.55</v>
+        <v>-10.07</v>
       </c>
       <c r="I32" t="n">
         <v>-10.01</v>
@@ -18504,7 +18524,7 @@
         <v>-15.23</v>
       </c>
       <c r="M32" t="n">
-        <v>-11.93</v>
+        <v>-9.699999999999999</v>
       </c>
       <c r="N32" t="b">
         <v>1</v>
@@ -18542,7 +18562,7 @@
         <v>-2.6</v>
       </c>
       <c r="H33" t="n">
-        <v>-7.83</v>
+        <v>-8.779999999999999</v>
       </c>
       <c r="I33" t="n">
         <v>-4.27</v>
@@ -18555,7 +18575,7 @@
         <v>-4.86</v>
       </c>
       <c r="M33" t="n">
-        <v>-8.42</v>
+        <v>-8.630000000000001</v>
       </c>
       <c r="N33" t="b">
         <v>1</v>
@@ -18593,7 +18613,7 @@
         <v>23.8</v>
       </c>
       <c r="H34" t="n">
-        <v>12.24</v>
+        <v>10.66</v>
       </c>
       <c r="I34" t="n">
         <v>1.36</v>
@@ -18606,7 +18626,7 @@
         <v>-9.94</v>
       </c>
       <c r="M34" t="n">
-        <v>12.61</v>
+        <v>11.78</v>
       </c>
       <c r="N34" t="b">
         <v>1</v>
@@ -18644,7 +18664,7 @@
         <v>38.9</v>
       </c>
       <c r="H35" t="n">
-        <v>-11.46</v>
+        <v>-12.52</v>
       </c>
       <c r="I35" t="n">
         <v>-9.220000000000001</v>
@@ -18657,7 +18677,7 @@
         <v>-9.83</v>
       </c>
       <c r="M35" t="n">
-        <v>-11.08</v>
+        <v>-11.4</v>
       </c>
       <c r="N35" t="b">
         <v>1</v>
@@ -18695,7 +18715,7 @@
         <v>43.2</v>
       </c>
       <c r="H36" t="n">
-        <v>-21.48</v>
+        <v>-24.92</v>
       </c>
       <c r="I36" t="n">
         <v>-3.15</v>
@@ -18708,7 +18728,7 @@
         <v>-17.51</v>
       </c>
       <c r="M36" t="n">
-        <v>-21.27</v>
+        <v>-23.97</v>
       </c>
       <c r="N36" t="b">
         <v>1</v>
@@ -18746,7 +18766,7 @@
         <v>-8.199999999999999</v>
       </c>
       <c r="H37" t="n">
-        <v>-6.44</v>
+        <v>-7.24</v>
       </c>
       <c r="I37" t="n">
         <v>5.34</v>
@@ -18759,7 +18779,7 @@
         <v>-5.27</v>
       </c>
       <c r="M37" t="n">
-        <v>-6.23</v>
+        <v>-6.29</v>
       </c>
       <c r="N37" t="b">
         <v>1</v>
@@ -18797,7 +18817,7 @@
         <v>-23.9</v>
       </c>
       <c r="H38" t="n">
-        <v>-8.869999999999999</v>
+        <v>-11.98</v>
       </c>
       <c r="I38" t="n">
         <v>3.28</v>
@@ -18810,7 +18830,7 @@
         <v>-4.46</v>
       </c>
       <c r="M38" t="n">
-        <v>-8.949999999999999</v>
+        <v>-11.32</v>
       </c>
       <c r="N38" t="b">
         <v>1</v>
@@ -18852,7 +18872,7 @@
         <v>-6.1</v>
       </c>
       <c r="H39" t="n">
-        <v>1.42</v>
+        <v>-1.93</v>
       </c>
       <c r="I39" t="n">
         <v>4.9</v>
@@ -18865,7 +18885,7 @@
         <v>-9</v>
       </c>
       <c r="M39" t="n">
-        <v>1.33</v>
+        <v>-1.27</v>
       </c>
       <c r="N39" t="b">
         <v>1</v>
@@ -18916,7 +18936,7 @@
         <v>-0.87</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.19</v>
+        <v>-0.44</v>
       </c>
       <c r="N40" t="b">
         <v>1</v>
@@ -18954,7 +18974,7 @@
         <v>-3.5</v>
       </c>
       <c r="H41" t="n">
-        <v>0.78</v>
+        <v>0.03</v>
       </c>
       <c r="I41" t="n">
         <v>-4.95</v>
@@ -18967,7 +18987,7 @@
         <v>-8.43</v>
       </c>
       <c r="M41" t="n">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="N41" t="b">
         <v>1</v>
@@ -19005,7 +19025,7 @@
         <v>-17.9</v>
       </c>
       <c r="H42" t="n">
-        <v>3.28</v>
+        <v>2.26</v>
       </c>
       <c r="I42" t="n">
         <v>-0.5</v>
@@ -19018,7 +19038,7 @@
         <v>-3.43</v>
       </c>
       <c r="M42" t="n">
-        <v>2.99</v>
+        <v>2.71</v>
       </c>
       <c r="N42" t="b">
         <v>1</v>
@@ -19056,7 +19076,7 @@
         <v>53.5</v>
       </c>
       <c r="H43" t="n">
-        <v>-4.21</v>
+        <v>-3.43</v>
       </c>
       <c r="I43" t="n">
         <v>1.23</v>
@@ -19069,7 +19089,7 @@
         <v>-7.57</v>
       </c>
       <c r="M43" t="n">
-        <v>-4.6</v>
+        <v>-3.08</v>
       </c>
       <c r="N43" t="b">
         <v>1</v>
@@ -19107,7 +19127,7 @@
         <v>-1</v>
       </c>
       <c r="H44" t="n">
-        <v>-13.35</v>
+        <v>-14.09</v>
       </c>
       <c r="I44" t="n">
         <v>-6.26</v>
@@ -19158,7 +19178,7 @@
         <v>29.7</v>
       </c>
       <c r="H45" t="n">
-        <v>8.119999999999999</v>
+        <v>11.69</v>
       </c>
       <c r="I45" t="n">
         <v>11.27</v>
@@ -19171,7 +19191,7 @@
         <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>7.73</v>
+        <v>12.04</v>
       </c>
       <c r="N45" t="b">
         <v>1</v>
@@ -19209,7 +19229,7 @@
         <v>15.2</v>
       </c>
       <c r="H46" t="n">
-        <v>-33.35</v>
+        <v>-34.47</v>
       </c>
       <c r="I46" t="n">
         <v>-8.77</v>
@@ -19222,7 +19242,7 @@
         <v>-24.79</v>
       </c>
       <c r="M46" t="n">
-        <v>-33.02</v>
+        <v>-33.4</v>
       </c>
       <c r="N46" t="b">
         <v>1</v>
@@ -19260,7 +19280,7 @@
         <v>22.2</v>
       </c>
       <c r="H47" t="n">
-        <v>6.06</v>
+        <v>7.56</v>
       </c>
       <c r="I47" t="n">
         <v>1.01</v>
@@ -19273,7 +19293,7 @@
         <v>-3.94</v>
       </c>
       <c r="M47" t="n">
-        <v>6.4</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="N47" t="b">
         <v>1</v>
@@ -19315,7 +19335,7 @@
         <v>-0</v>
       </c>
       <c r="H48" t="n">
-        <v>33.66</v>
+        <v>33.32</v>
       </c>
       <c r="I48" t="n">
         <v>13.5</v>
@@ -19328,7 +19348,7 @@
         <v>-2.53</v>
       </c>
       <c r="M48" t="n">
-        <v>30.48</v>
+        <v>30.91</v>
       </c>
       <c r="N48" t="b">
         <v>1</v>
@@ -19417,7 +19437,7 @@
         <v>-37</v>
       </c>
       <c r="H50" t="n">
-        <v>25.78</v>
+        <v>25.06</v>
       </c>
       <c r="I50" t="n">
         <v>18.38</v>
@@ -19430,7 +19450,7 @@
         <v>-5.11</v>
       </c>
       <c r="M50" t="n">
-        <v>21.94</v>
+        <v>21.99</v>
       </c>
       <c r="N50" t="b">
         <v>1</v>
@@ -19468,7 +19488,7 @@
         <v>-26.8</v>
       </c>
       <c r="H51" t="n">
-        <v>15.17</v>
+        <v>16.92</v>
       </c>
       <c r="I51" t="n">
         <v>4.56</v>
@@ -19481,7 +19501,7 @@
         <v>-4.09</v>
       </c>
       <c r="M51" t="n">
-        <v>11.33</v>
+        <v>13.85</v>
       </c>
       <c r="N51" t="b">
         <v>1</v>
@@ -19519,7 +19539,7 @@
         <v>-36.5</v>
       </c>
       <c r="H52" t="n">
-        <v>-32.51</v>
+        <v>-33.9</v>
       </c>
       <c r="I52" t="n">
         <v>-27.75</v>
@@ -19532,7 +19552,7 @@
         <v>-31.28</v>
       </c>
       <c r="M52" t="n">
-        <v>-37.01</v>
+        <v>-37.63</v>
       </c>
       <c r="N52" t="b">
         <v>1</v>
@@ -19570,7 +19590,7 @@
         <v>-38.7</v>
       </c>
       <c r="H53" t="n">
-        <v>7.91</v>
+        <v>3.8</v>
       </c>
       <c r="I53" t="n">
         <v>17.17</v>
@@ -19583,7 +19603,7 @@
         <v>-0.54</v>
       </c>
       <c r="M53" t="n">
-        <v>3.41</v>
+        <v>0.08</v>
       </c>
       <c r="N53" t="b">
         <v>1</v>
@@ -19621,7 +19641,7 @@
         <v>-34.6</v>
       </c>
       <c r="H54" t="n">
-        <v>15.13</v>
+        <v>13.36</v>
       </c>
       <c r="I54" t="n">
         <v>6.67</v>
@@ -19634,7 +19654,7 @@
         <v>-3.06</v>
       </c>
       <c r="M54" t="n">
-        <v>10.63</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="N54" t="b">
         <v>1</v>
@@ -19672,7 +19692,7 @@
         <v>-11.8</v>
       </c>
       <c r="H55" t="n">
-        <v>-4.69</v>
+        <v>-5.09</v>
       </c>
       <c r="I55" t="n">
         <v>9.76</v>
@@ -19685,7 +19705,7 @@
         <v>-1.63</v>
       </c>
       <c r="M55" t="n">
-        <v>-9.300000000000001</v>
+        <v>-8.92</v>
       </c>
       <c r="N55" t="b">
         <v>1</v>
@@ -19723,7 +19743,7 @@
         <v>0.1</v>
       </c>
       <c r="H56" t="n">
-        <v>-12.69</v>
+        <v>-12.16</v>
       </c>
       <c r="I56" t="n">
         <v>-2.83</v>
@@ -19736,7 +19756,7 @@
         <v>-5.45</v>
       </c>
       <c r="M56" t="n">
-        <v>-17.3</v>
+        <v>-15.99</v>
       </c>
       <c r="N56" t="b">
         <v>1</v>
@@ -19774,7 +19794,7 @@
         <v>24.1</v>
       </c>
       <c r="H57" t="n">
-        <v>-10.05</v>
+        <v>-12.12</v>
       </c>
       <c r="I57" t="n">
         <v>-8.31</v>
@@ -19787,7 +19807,7 @@
         <v>-18.31</v>
       </c>
       <c r="M57" t="n">
-        <v>-13.86</v>
+        <v>-15.15</v>
       </c>
       <c r="N57" t="b">
         <v>1</v>
@@ -19825,7 +19845,7 @@
         <v>-15.9</v>
       </c>
       <c r="H58" t="n">
-        <v>-1.44</v>
+        <v>-1.91</v>
       </c>
       <c r="I58" t="n">
         <v>10.45</v>
@@ -19838,7 +19858,7 @@
         <v>-0.31</v>
       </c>
       <c r="M58" t="n">
-        <v>-5.25</v>
+        <v>-4.95</v>
       </c>
       <c r="N58" t="b">
         <v>1</v>
@@ -19876,7 +19896,7 @@
         <v>-21.8</v>
       </c>
       <c r="H59" t="n">
-        <v>-24.99</v>
+        <v>-25.59</v>
       </c>
       <c r="I59" t="n">
         <v>-18.97</v>
@@ -19889,7 +19909,7 @@
         <v>-26.82</v>
       </c>
       <c r="M59" t="n">
-        <v>-29.57</v>
+        <v>-29.4</v>
       </c>
       <c r="N59" t="b">
         <v>1</v>
@@ -19927,7 +19947,7 @@
         <v>57</v>
       </c>
       <c r="H60" t="n">
-        <v>15</v>
+        <v>14.33</v>
       </c>
       <c r="I60" t="n">
         <v>-11.21</v>
@@ -19940,7 +19960,7 @@
         <v>-13.87</v>
       </c>
       <c r="M60" t="n">
-        <v>11.43</v>
+        <v>11.53</v>
       </c>
       <c r="N60" t="b">
         <v>1</v>
@@ -19978,7 +19998,7 @@
         <v>-21.8</v>
       </c>
       <c r="H61" t="n">
-        <v>8</v>
+        <v>7.49</v>
       </c>
       <c r="I61" t="n">
         <v>1.71</v>
@@ -19991,7 +20011,7 @@
         <v>-6.18</v>
       </c>
       <c r="M61" t="n">
-        <v>4.44</v>
+        <v>4.69</v>
       </c>
       <c r="N61" t="b">
         <v>1</v>
@@ -20029,7 +20049,7 @@
         <v>1</v>
       </c>
       <c r="H62" t="n">
-        <v>-32.11</v>
+        <v>-34.21</v>
       </c>
       <c r="I62" t="n">
         <v>-11.52</v>
@@ -20042,7 +20062,7 @@
         <v>-16.26</v>
       </c>
       <c r="M62" t="n">
-        <v>-35.72</v>
+        <v>-37.06</v>
       </c>
       <c r="N62" t="b">
         <v>1</v>
@@ -20080,7 +20100,7 @@
         <v>45.4</v>
       </c>
       <c r="H63" t="n">
-        <v>8.699999999999999</v>
+        <v>-0.75</v>
       </c>
       <c r="I63" t="n">
         <v>-1.72</v>
@@ -20093,7 +20113,7 @@
         <v>-23.15</v>
       </c>
       <c r="M63" t="n">
-        <v>5.09</v>
+        <v>-3.59</v>
       </c>
       <c r="N63" t="b">
         <v>1</v>
@@ -20131,7 +20151,7 @@
         <v>76.5</v>
       </c>
       <c r="H64" t="n">
-        <v>17.61</v>
+        <v>13.31</v>
       </c>
       <c r="I64" t="n">
         <v>-5.56</v>
@@ -20144,7 +20164,7 @@
         <v>-33.97</v>
       </c>
       <c r="M64" t="n">
-        <v>13.99</v>
+        <v>10.47</v>
       </c>
       <c r="N64" t="b">
         <v>1</v>
@@ -20182,7 +20202,7 @@
         <v>32.1</v>
       </c>
       <c r="H65" t="n">
-        <v>22.94</v>
+        <v>20.11</v>
       </c>
       <c r="I65" t="n">
         <v>16.93</v>
@@ -20195,7 +20215,7 @@
         <v>-24.48</v>
       </c>
       <c r="M65" t="n">
-        <v>19.32</v>
+        <v>17.27</v>
       </c>
       <c r="N65" t="b">
         <v>1</v>
@@ -20233,7 +20253,7 @@
         <v>51.8</v>
       </c>
       <c r="H66" t="n">
-        <v>11.66</v>
+        <v>7.58</v>
       </c>
       <c r="I66" t="n">
         <v>10.75</v>
@@ -20246,7 +20266,7 @@
         <v>-25.09</v>
       </c>
       <c r="M66" t="n">
-        <v>8.039999999999999</v>
+        <v>4.74</v>
       </c>
       <c r="N66" t="b">
         <v>1</v>
@@ -20284,7 +20304,7 @@
         <v>32.3</v>
       </c>
       <c r="H67" t="n">
-        <v>-25.05</v>
+        <v>-27.09</v>
       </c>
       <c r="I67" t="n">
         <v>-20.76</v>
@@ -20297,7 +20317,7 @@
         <v>-27.91</v>
       </c>
       <c r="M67" t="n">
-        <v>-28.66</v>
+        <v>-29.93</v>
       </c>
       <c r="N67" t="b">
         <v>1</v>
@@ -20335,7 +20355,7 @@
         <v>3.7</v>
       </c>
       <c r="H68" t="n">
-        <v>-9.529999999999999</v>
+        <v>-11.5</v>
       </c>
       <c r="I68" t="n">
         <v>-1.11</v>
@@ -20348,7 +20368,7 @@
         <v>-25.46</v>
       </c>
       <c r="M68" t="n">
-        <v>-13.15</v>
+        <v>-14.34</v>
       </c>
       <c r="N68" t="b">
         <v>1</v>
@@ -20386,7 +20406,7 @@
         <v>42.4</v>
       </c>
       <c r="H69" t="n">
-        <v>10.77</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="I69" t="n">
         <v>2.16</v>
@@ -20399,7 +20419,7 @@
         <v>-15.76</v>
       </c>
       <c r="M69" t="n">
-        <v>7.16</v>
+        <v>5.19</v>
       </c>
       <c r="N69" t="b">
         <v>1</v>
@@ -20437,7 +20457,7 @@
         <v>28.2</v>
       </c>
       <c r="H70" t="n">
-        <v>-0.83</v>
+        <v>-0.37</v>
       </c>
       <c r="I70" t="n">
         <v>-1.71</v>
@@ -20450,7 +20470,7 @@
         <v>-23.43</v>
       </c>
       <c r="M70" t="n">
-        <v>-4.44</v>
+        <v>-3.21</v>
       </c>
       <c r="N70" t="b">
         <v>1</v>
@@ -20488,7 +20508,7 @@
         <v>28.6</v>
       </c>
       <c r="H71" t="n">
-        <v>28</v>
+        <v>29.43</v>
       </c>
       <c r="I71" t="n">
         <v>2.81</v>
@@ -20501,7 +20521,7 @@
         <v>-18.87</v>
       </c>
       <c r="M71" t="n">
-        <v>24.39</v>
+        <v>26.58</v>
       </c>
       <c r="N71" t="b">
         <v>1</v>
@@ -20539,7 +20559,7 @@
         <v>33.1</v>
       </c>
       <c r="H72" t="n">
-        <v>16.04</v>
+        <v>13.53</v>
       </c>
       <c r="I72" t="n">
         <v>4.68</v>
@@ -20552,7 +20572,7 @@
         <v>-26.7</v>
       </c>
       <c r="M72" t="n">
-        <v>12.42</v>
+        <v>10.69</v>
       </c>
       <c r="N72" t="b">
         <v>1</v>
@@ -20590,7 +20610,7 @@
         <v>21.8</v>
       </c>
       <c r="H73" t="n">
-        <v>-8.890000000000001</v>
+        <v>-12.41</v>
       </c>
       <c r="I73" t="n">
         <v>-6.34</v>
@@ -20603,7 +20623,7 @@
         <v>-30.04</v>
       </c>
       <c r="M73" t="n">
-        <v>-12.51</v>
+        <v>-15.25</v>
       </c>
       <c r="N73" t="b">
         <v>1</v>
@@ -20641,7 +20661,7 @@
         <v>40.3</v>
       </c>
       <c r="H74" t="n">
-        <v>-8.369999999999999</v>
+        <v>-9.68</v>
       </c>
       <c r="I74" t="n">
         <v>1.24</v>
@@ -20654,7 +20674,7 @@
         <v>-20.5</v>
       </c>
       <c r="M74" t="n">
-        <v>-11.99</v>
+        <v>-12.53</v>
       </c>
       <c r="N74" t="b">
         <v>1</v>
@@ -20692,7 +20712,7 @@
         <v>24.1</v>
       </c>
       <c r="H75" t="n">
-        <v>11.76</v>
+        <v>10.82</v>
       </c>
       <c r="I75" t="n">
         <v>-1.6</v>
@@ -20705,7 +20725,7 @@
         <v>-22.54</v>
       </c>
       <c r="M75" t="n">
-        <v>8.15</v>
+        <v>7.97</v>
       </c>
       <c r="N75" t="b">
         <v>1</v>
@@ -20743,7 +20763,7 @@
         <v>24.5</v>
       </c>
       <c r="H76" t="n">
-        <v>-25.36</v>
+        <v>-24.99</v>
       </c>
       <c r="I76" t="n">
         <v>-12.99</v>
@@ -20756,7 +20776,7 @@
         <v>-22.54</v>
       </c>
       <c r="M76" t="n">
-        <v>-28.98</v>
+        <v>-27.84</v>
       </c>
       <c r="N76" t="b">
         <v>1</v>
@@ -20794,7 +20814,7 @@
         <v>19.3</v>
       </c>
       <c r="H77" t="n">
-        <v>10.4</v>
+        <v>11.21</v>
       </c>
       <c r="I77" t="n">
         <v>11.79</v>
@@ -20807,7 +20827,7 @@
         <v>-16.62</v>
       </c>
       <c r="M77" t="n">
-        <v>6.78</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="N77" t="b">
         <v>1</v>
@@ -20845,7 +20865,7 @@
         <v>-8.699999999999999</v>
       </c>
       <c r="H78" t="n">
-        <v>-14.88</v>
+        <v>-13.57</v>
       </c>
       <c r="I78" t="n">
         <v>17.25</v>
@@ -20858,7 +20878,7 @@
         <v>-4.65</v>
       </c>
       <c r="M78" t="n">
-        <v>-18.49</v>
+        <v>-16.41</v>
       </c>
       <c r="N78" t="b">
         <v>1</v>
@@ -20896,7 +20916,7 @@
         <v>15.2</v>
       </c>
       <c r="H79" t="n">
-        <v>-3.72</v>
+        <v>-8.07</v>
       </c>
       <c r="I79" t="n">
         <v>5.36</v>
@@ -20909,7 +20929,7 @@
         <v>-28.18</v>
       </c>
       <c r="M79" t="n">
-        <v>-7.33</v>
+        <v>-10.92</v>
       </c>
       <c r="N79" t="b">
         <v>1</v>
@@ -20947,7 +20967,7 @@
         <v>37.2</v>
       </c>
       <c r="H80" t="n">
-        <v>-24.83</v>
+        <v>-25.53</v>
       </c>
       <c r="I80" t="n">
         <v>-7.64</v>
@@ -20960,7 +20980,7 @@
         <v>-26.24</v>
       </c>
       <c r="M80" t="n">
-        <v>-28.44</v>
+        <v>-28.37</v>
       </c>
       <c r="N80" t="b">
         <v>1</v>
@@ -20998,7 +21018,7 @@
         <v>29.8</v>
       </c>
       <c r="H81" t="n">
-        <v>37.27</v>
+        <v>31.61</v>
       </c>
       <c r="I81" t="n">
         <v>-2.74</v>
@@ -21011,7 +21031,7 @@
         <v>-22.36</v>
       </c>
       <c r="M81" t="n">
-        <v>33.66</v>
+        <v>28.77</v>
       </c>
       <c r="N81" t="b">
         <v>1</v>
@@ -21049,7 +21069,7 @@
         <v>19.3</v>
       </c>
       <c r="H82" t="n">
-        <v>-19.91</v>
+        <v>-20.55</v>
       </c>
       <c r="I82" t="n">
         <v>-16.69</v>
@@ -21062,7 +21082,7 @@
         <v>-36.39</v>
       </c>
       <c r="M82" t="n">
-        <v>-23.52</v>
+        <v>-23.4</v>
       </c>
       <c r="N82" t="b">
         <v>1</v>
@@ -21100,7 +21120,7 @@
         <v>11.8</v>
       </c>
       <c r="H83" t="n">
-        <v>3.24</v>
+        <v>0.7</v>
       </c>
       <c r="I83" t="n">
         <v>-1.19</v>
@@ -21113,7 +21133,7 @@
         <v>-17.57</v>
       </c>
       <c r="M83" t="n">
-        <v>-0.38</v>
+        <v>-2.14</v>
       </c>
       <c r="N83" t="b">
         <v>1</v>
@@ -21151,7 +21171,7 @@
         <v>27.5</v>
       </c>
       <c r="H84" t="n">
-        <v>8.1</v>
+        <v>5.52</v>
       </c>
       <c r="I84" t="n">
         <v>8.42</v>
@@ -21164,7 +21184,7 @@
         <v>-2.51</v>
       </c>
       <c r="M84" t="n">
-        <v>4.49</v>
+        <v>2.68</v>
       </c>
       <c r="N84" t="b">
         <v>1</v>
@@ -21202,7 +21222,7 @@
         <v>-22.4</v>
       </c>
       <c r="H85" t="n">
-        <v>-8.83</v>
+        <v>-9.73</v>
       </c>
       <c r="I85" t="n">
         <v>9.42</v>
@@ -21215,7 +21235,7 @@
         <v>-2.79</v>
       </c>
       <c r="M85" t="n">
-        <v>-12.44</v>
+        <v>-12.57</v>
       </c>
       <c r="N85" t="b">
         <v>1</v>
@@ -21253,7 +21273,7 @@
         <v>-14.7</v>
       </c>
       <c r="H86" t="n">
-        <v>-11.97</v>
+        <v>-13.19</v>
       </c>
       <c r="I86" t="n">
         <v>10.3</v>
@@ -21266,7 +21286,7 @@
         <v>-2.6</v>
       </c>
       <c r="M86" t="n">
-        <v>-15.58</v>
+        <v>-16.03</v>
       </c>
       <c r="N86" t="b">
         <v>1</v>
@@ -21308,7 +21328,7 @@
         <v>-9.300000000000001</v>
       </c>
       <c r="H87" t="n">
-        <v>-23.65</v>
+        <v>-26.47</v>
       </c>
       <c r="I87" t="n">
         <v>10.42</v>
@@ -21321,7 +21341,7 @@
         <v>-21.72</v>
       </c>
       <c r="M87" t="n">
-        <v>-27.26</v>
+        <v>-29.31</v>
       </c>
       <c r="N87" t="b">
         <v>1</v>
@@ -21359,7 +21379,7 @@
         <v>-25.2</v>
       </c>
       <c r="H88" t="n">
-        <v>16.78</v>
+        <v>13.42</v>
       </c>
       <c r="I88" t="n">
         <v>22.53</v>
@@ -21372,7 +21392,7 @@
         <v>-19.27</v>
       </c>
       <c r="M88" t="n">
-        <v>13.17</v>
+        <v>10.58</v>
       </c>
       <c r="N88" t="b">
         <v>1</v>
@@ -21410,7 +21430,7 @@
         <v>5.1</v>
       </c>
       <c r="H89" t="n">
-        <v>3.61</v>
+        <v>2.8</v>
       </c>
       <c r="I89" t="n">
         <v>8.77</v>
@@ -21423,7 +21443,7 @@
         <v>-3.54</v>
       </c>
       <c r="M89" t="n">
-        <v>-0.01</v>
+        <v>-0.04</v>
       </c>
       <c r="N89" t="b">
         <v>1</v>
@@ -21461,7 +21481,7 @@
         <v>34.2</v>
       </c>
       <c r="H90" t="n">
-        <v>10.58</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="I90" t="n">
         <v>8.15</v>
@@ -21474,7 +21494,7 @@
         <v>-7.63</v>
       </c>
       <c r="M90" t="n">
-        <v>6.97</v>
+        <v>6.63</v>
       </c>
       <c r="N90" t="b">
         <v>1</v>
@@ -21512,7 +21532,7 @@
         <v>42</v>
       </c>
       <c r="H91" t="n">
-        <v>-29.95</v>
+        <v>-31.99</v>
       </c>
       <c r="I91" t="n">
         <v>0.6</v>
@@ -21525,7 +21545,7 @@
         <v>-16.67</v>
       </c>
       <c r="M91" t="n">
-        <v>-33.56</v>
+        <v>-34.83</v>
       </c>
       <c r="N91" t="b">
         <v>1</v>
@@ -21563,7 +21583,7 @@
         <v>-25.3</v>
       </c>
       <c r="H92" t="n">
-        <v>37.65</v>
+        <v>36.06</v>
       </c>
       <c r="I92" t="n">
         <v>36.1</v>
@@ -21576,7 +21596,7 @@
         <v>-5.66</v>
       </c>
       <c r="M92" t="n">
-        <v>34.03</v>
+        <v>33.21</v>
       </c>
       <c r="N92" t="b">
         <v>1</v>
@@ -21614,7 +21634,7 @@
         <v>-7.7</v>
       </c>
       <c r="H93" t="n">
-        <v>-2.18</v>
+        <v>-5</v>
       </c>
       <c r="I93" t="n">
         <v>-6.47</v>
@@ -21627,7 +21647,7 @@
         <v>-23.05</v>
       </c>
       <c r="M93" t="n">
-        <v>-5.79</v>
+        <v>-7.85</v>
       </c>
       <c r="N93" t="b">
         <v>1</v>
@@ -21665,7 +21685,7 @@
         <v>13.7</v>
       </c>
       <c r="H94" t="n">
-        <v>7.95</v>
+        <v>7.06</v>
       </c>
       <c r="I94" t="n">
         <v>2.74</v>
@@ -21678,7 +21698,7 @@
         <v>-24.02</v>
       </c>
       <c r="M94" t="n">
-        <v>4.34</v>
+        <v>4.21</v>
       </c>
       <c r="N94" t="b">
         <v>1</v>
@@ -21716,7 +21736,7 @@
         <v>21.8</v>
       </c>
       <c r="H95" t="n">
-        <v>0.88</v>
+        <v>0.24</v>
       </c>
       <c r="I95" t="n">
         <v>18.32</v>
@@ -21729,7 +21749,7 @@
         <v>-23.27</v>
       </c>
       <c r="M95" t="n">
-        <v>-2.74</v>
+        <v>-2.6</v>
       </c>
       <c r="N95" t="b">
         <v>1</v>
@@ -21767,7 +21787,7 @@
         <v>29.4</v>
       </c>
       <c r="H96" t="n">
-        <v>-2.6</v>
+        <v>-2.23</v>
       </c>
       <c r="I96" t="n">
         <v>-2.62</v>
@@ -21780,7 +21800,7 @@
         <v>-27.18</v>
       </c>
       <c r="M96" t="n">
-        <v>-6.22</v>
+        <v>-5.07</v>
       </c>
       <c r="N96" t="b">
         <v>1</v>
@@ -21818,7 +21838,7 @@
         <v>-3.7</v>
       </c>
       <c r="H97" t="n">
-        <v>-23.66</v>
+        <v>-24.53</v>
       </c>
       <c r="I97" t="n">
         <v>-8.07</v>
@@ -21831,7 +21851,7 @@
         <v>-22.12</v>
       </c>
       <c r="M97" t="n">
-        <v>-27.27</v>
+        <v>-27.37</v>
       </c>
       <c r="N97" t="b">
         <v>1</v>
@@ -21869,7 +21889,7 @@
         <v>21.3</v>
       </c>
       <c r="H98" t="n">
-        <v>1.54</v>
+        <v>1.44</v>
       </c>
       <c r="I98" t="n">
         <v>0.23</v>
@@ -21882,7 +21902,7 @@
         <v>-0.85</v>
       </c>
       <c r="M98" t="n">
-        <v>-2.08</v>
+        <v>-1.4</v>
       </c>
       <c r="N98" t="b">
         <v>1</v>
@@ -21920,7 +21940,7 @@
         <v>-21.4</v>
       </c>
       <c r="H99" t="n">
-        <v>23.6</v>
+        <v>15.58</v>
       </c>
       <c r="I99" t="n">
         <v>4.55</v>
@@ -21933,7 +21953,7 @@
         <v>-6.39</v>
       </c>
       <c r="M99" t="n">
-        <v>19.98</v>
+        <v>12.74</v>
       </c>
       <c r="N99" t="b">
         <v>1</v>
@@ -21971,7 +21991,7 @@
         <v>16.3</v>
       </c>
       <c r="H100" t="n">
-        <v>7.26</v>
+        <v>5.02</v>
       </c>
       <c r="I100" t="n">
         <v>-1</v>
@@ -21984,7 +22004,7 @@
         <v>-22.5</v>
       </c>
       <c r="M100" t="n">
-        <v>3.65</v>
+        <v>2.17</v>
       </c>
       <c r="N100" t="b">
         <v>1</v>
@@ -22022,7 +22042,7 @@
         <v>11.9</v>
       </c>
       <c r="H101" t="n">
-        <v>0.4</v>
+        <v>1.09</v>
       </c>
       <c r="I101" t="n">
         <v>7.74</v>
@@ -22035,7 +22055,7 @@
         <v>-9.43</v>
       </c>
       <c r="M101" t="n">
-        <v>-3.22</v>
+        <v>-1.75</v>
       </c>
       <c r="N101" t="b">
         <v>1</v>
@@ -22073,7 +22093,7 @@
         <v>0.2</v>
       </c>
       <c r="H102" t="n">
-        <v>8.16</v>
+        <v>6.33</v>
       </c>
       <c r="I102" t="n">
         <v>4.35</v>
@@ -22086,7 +22106,7 @@
         <v>-2.79</v>
       </c>
       <c r="M102" t="n">
-        <v>4.55</v>
+        <v>3.49</v>
       </c>
       <c r="N102" t="b">
         <v>1</v>
@@ -22124,7 +22144,7 @@
         <v>8.4</v>
       </c>
       <c r="H103" t="n">
-        <v>-34.67</v>
+        <v>-35.81</v>
       </c>
       <c r="I103" t="n">
         <v>-0.13</v>
@@ -22137,7 +22157,7 @@
         <v>-10.87</v>
       </c>
       <c r="M103" t="n">
-        <v>-38.28</v>
+        <v>-38.65</v>
       </c>
       <c r="N103" t="b">
         <v>1</v>
@@ -22175,7 +22195,7 @@
         <v>-7.3</v>
       </c>
       <c r="H104" t="n">
-        <v>-21.25</v>
+        <v>-22.93</v>
       </c>
       <c r="I104" t="n">
         <v>-4.12</v>
@@ -22188,7 +22208,7 @@
         <v>-15.02</v>
       </c>
       <c r="M104" t="n">
-        <v>-24.87</v>
+        <v>-25.77</v>
       </c>
       <c r="N104" t="b">
         <v>1</v>
@@ -22226,7 +22246,7 @@
         <v>-26.1</v>
       </c>
       <c r="H105" t="n">
-        <v>-17.53</v>
+        <v>-19.15</v>
       </c>
       <c r="I105" t="n">
         <v>5.05</v>
@@ -22239,7 +22259,7 @@
         <v>-9.27</v>
       </c>
       <c r="M105" t="n">
-        <v>-21.15</v>
+        <v>-21.99</v>
       </c>
       <c r="N105" t="b">
         <v>1</v>
@@ -22277,7 +22297,7 @@
         <v>26.1</v>
       </c>
       <c r="H106" t="n">
-        <v>-7.01</v>
+        <v>-7.05</v>
       </c>
       <c r="I106" t="n">
         <v>-0.51</v>
@@ -22290,7 +22310,7 @@
         <v>-16.45</v>
       </c>
       <c r="M106" t="n">
-        <v>-10.63</v>
+        <v>-9.890000000000001</v>
       </c>
       <c r="N106" t="b">
         <v>1</v>
@@ -22341,7 +22361,7 @@
         <v>-8.130000000000001</v>
       </c>
       <c r="M107" t="n">
-        <v>0.53</v>
+        <v>1.3</v>
       </c>
       <c r="N107" t="b">
         <v>1</v>
@@ -22379,7 +22399,7 @@
         <v>0.7</v>
       </c>
       <c r="H108" t="n">
-        <v>-18.57</v>
+        <v>-19.59</v>
       </c>
       <c r="I108" t="n">
         <v>14.96</v>
@@ -22392,7 +22412,7 @@
         <v>-8.039999999999999</v>
       </c>
       <c r="M108" t="n">
-        <v>-22.19</v>
+        <v>-22.43</v>
       </c>
       <c r="N108" t="b">
         <v>1</v>
@@ -22430,7 +22450,7 @@
         <v>14.8</v>
       </c>
       <c r="H109" t="n">
-        <v>-2.13</v>
+        <v>-2.53</v>
       </c>
       <c r="I109" t="n">
         <v>0.35</v>
@@ -22443,7 +22463,7 @@
         <v>-3.68</v>
       </c>
       <c r="M109" t="n">
-        <v>-5.74</v>
+        <v>-5.37</v>
       </c>
       <c r="N109" t="b">
         <v>1</v>
@@ -22481,7 +22501,7 @@
         <v>25.5</v>
       </c>
       <c r="H110" t="n">
-        <v>-0.15</v>
+        <v>1.59</v>
       </c>
       <c r="I110" t="n">
         <v>-9.369999999999999</v>
@@ -22494,7 +22514,7 @@
         <v>-22.11</v>
       </c>
       <c r="M110" t="n">
-        <v>-3.77</v>
+        <v>-1.25</v>
       </c>
       <c r="N110" t="b">
         <v>1</v>
@@ -22536,7 +22556,7 @@
         <v>-7.5</v>
       </c>
       <c r="H111" t="n">
-        <v>-6.68</v>
+        <v>-7.28</v>
       </c>
       <c r="I111" t="n">
         <v>4.46</v>
@@ -22549,7 +22569,7 @@
         <v>-8.52</v>
       </c>
       <c r="M111" t="n">
-        <v>-10.3</v>
+        <v>-10.13</v>
       </c>
       <c r="N111" t="b">
         <v>1</v>
@@ -22587,7 +22607,7 @@
         <v>-11</v>
       </c>
       <c r="H112" t="n">
-        <v>0.52</v>
+        <v>0.26</v>
       </c>
       <c r="I112" t="n">
         <v>10.7</v>
@@ -22600,7 +22620,7 @@
         <v>-9.43</v>
       </c>
       <c r="M112" t="n">
-        <v>-3.1</v>
+        <v>-2.59</v>
       </c>
       <c r="N112" t="b">
         <v>1</v>
@@ -22638,7 +22658,7 @@
         <v>-11.4</v>
       </c>
       <c r="H113" t="n">
-        <v>-11.75</v>
+        <v>-12.88</v>
       </c>
       <c r="I113" t="n">
         <v>4.36</v>
@@ -22651,7 +22671,7 @@
         <v>-11.36</v>
       </c>
       <c r="M113" t="n">
-        <v>-15.36</v>
+        <v>-15.72</v>
       </c>
       <c r="N113" t="b">
         <v>1</v>
@@ -22689,7 +22709,7 @@
         <v>27.1</v>
       </c>
       <c r="H114" t="n">
-        <v>-2.55</v>
+        <v>-5.61</v>
       </c>
       <c r="I114" t="n">
         <v>5.02</v>
@@ -22702,7 +22722,7 @@
         <v>-14.35</v>
       </c>
       <c r="M114" t="n">
-        <v>-6.16</v>
+        <v>-8.449999999999999</v>
       </c>
       <c r="N114" t="b">
         <v>1</v>
@@ -22740,7 +22760,7 @@
         <v>32.2</v>
       </c>
       <c r="H115" t="n">
-        <v>19.11</v>
+        <v>17.23</v>
       </c>
       <c r="I115" t="n">
         <v>6.49</v>
@@ -22753,7 +22773,7 @@
         <v>-3.92</v>
       </c>
       <c r="M115" t="n">
-        <v>15.5</v>
+        <v>14.38</v>
       </c>
       <c r="N115" t="b">
         <v>1</v>
@@ -22791,7 +22811,7 @@
         <v>3.2</v>
       </c>
       <c r="H116" t="n">
-        <v>-16.35</v>
+        <v>-19.88</v>
       </c>
       <c r="I116" t="n">
         <v>-10.41</v>
@@ -22804,7 +22824,7 @@
         <v>-23.7</v>
       </c>
       <c r="M116" t="n">
-        <v>-19.96</v>
+        <v>-22.72</v>
       </c>
       <c r="N116" t="b">
         <v>1</v>
@@ -22842,7 +22862,7 @@
         <v>7.3</v>
       </c>
       <c r="H117" t="n">
-        <v>-4.43</v>
+        <v>-4.21</v>
       </c>
       <c r="I117" t="n">
         <v>-0.57</v>
@@ -22855,7 +22875,7 @@
         <v>-5.89</v>
       </c>
       <c r="M117" t="n">
-        <v>-8.039999999999999</v>
+        <v>-7.06</v>
       </c>
       <c r="N117" t="b">
         <v>1</v>
@@ -22893,7 +22913,7 @@
         <v>-0.3</v>
       </c>
       <c r="H118" t="n">
-        <v>-3.49</v>
+        <v>-4.13</v>
       </c>
       <c r="I118" t="n">
         <v>17.76</v>
@@ -22906,7 +22926,7 @@
         <v>-14.18</v>
       </c>
       <c r="M118" t="n">
-        <v>-7.11</v>
+        <v>-6.97</v>
       </c>
       <c r="N118" t="b">
         <v>1</v>
@@ -22944,7 +22964,7 @@
         <v>-6.8</v>
       </c>
       <c r="H119" t="n">
-        <v>44.84</v>
+        <v>42.01</v>
       </c>
       <c r="I119" t="n">
         <v>8.279999999999999</v>
@@ -22957,7 +22977,7 @@
         <v>-6.78</v>
       </c>
       <c r="M119" t="n">
-        <v>41.23</v>
+        <v>39.16</v>
       </c>
       <c r="N119" t="b">
         <v>1</v>
@@ -22995,7 +23015,7 @@
         <v>34.6</v>
       </c>
       <c r="H120" t="n">
-        <v>-2.04</v>
+        <v>-4.58</v>
       </c>
       <c r="I120" t="n">
         <v>5.7</v>
@@ -23008,7 +23028,7 @@
         <v>-7.7</v>
       </c>
       <c r="M120" t="n">
-        <v>-5.66</v>
+        <v>-7.43</v>
       </c>
       <c r="N120" t="b">
         <v>1</v>
@@ -23046,7 +23066,7 @@
         <v>10.4</v>
       </c>
       <c r="H121" t="n">
-        <v>22.84</v>
+        <v>24.05</v>
       </c>
       <c r="I121" t="n">
         <v>11.05</v>
@@ -23059,7 +23079,7 @@
         <v>-5.54</v>
       </c>
       <c r="M121" t="n">
-        <v>19.23</v>
+        <v>21.21</v>
       </c>
       <c r="N121" t="b">
         <v>1</v>
@@ -23097,7 +23117,7 @@
         <v>-21.5</v>
       </c>
       <c r="H122" t="n">
-        <v>-16.12</v>
+        <v>-14.55</v>
       </c>
       <c r="I122" t="n">
         <v>10.65</v>
@@ -23110,7 +23130,7 @@
         <v>-6.89</v>
       </c>
       <c r="M122" t="n">
-        <v>-19.73</v>
+        <v>-17.4</v>
       </c>
       <c r="N122" t="b">
         <v>1</v>
@@ -23148,7 +23168,7 @@
         <v>3.5</v>
       </c>
       <c r="H123" t="n">
-        <v>48.27</v>
+        <v>48.66</v>
       </c>
       <c r="I123" t="n">
         <v>33.01</v>
@@ -23161,7 +23181,7 @@
         <v>-0.92</v>
       </c>
       <c r="M123" t="n">
-        <v>44.66</v>
+        <v>45.82</v>
       </c>
       <c r="N123" t="b">
         <v>1</v>
@@ -23199,7 +23219,7 @@
         <v>19.8</v>
       </c>
       <c r="H124" t="n">
-        <v>11.16</v>
+        <v>10.42</v>
       </c>
       <c r="I124" t="n">
         <v>4.74</v>
@@ -23212,7 +23232,7 @@
         <v>-9.9</v>
       </c>
       <c r="M124" t="n">
-        <v>7.54</v>
+        <v>7.57</v>
       </c>
       <c r="N124" t="b">
         <v>1</v>
@@ -23250,7 +23270,7 @@
         <v>-30.5</v>
       </c>
       <c r="H125" t="n">
-        <v>-2.44</v>
+        <v>-2.41</v>
       </c>
       <c r="I125" t="n">
         <v>2.96</v>
@@ -23263,7 +23283,7 @@
         <v>-17.88</v>
       </c>
       <c r="M125" t="n">
-        <v>-6.05</v>
+        <v>-5.25</v>
       </c>
       <c r="N125" t="b">
         <v>1</v>
@@ -23301,7 +23321,7 @@
         <v>-6</v>
       </c>
       <c r="H126" t="n">
-        <v>-18.8</v>
+        <v>-20.24</v>
       </c>
       <c r="I126" t="n">
         <v>3.31</v>
@@ -23314,7 +23334,7 @@
         <v>-21.48</v>
       </c>
       <c r="M126" t="n">
-        <v>-22.41</v>
+        <v>-23.09</v>
       </c>
       <c r="N126" t="b">
         <v>1</v>
@@ -23352,7 +23372,7 @@
         <v>-34.6</v>
       </c>
       <c r="H127" t="n">
-        <v>-2.36</v>
+        <v>-5.47</v>
       </c>
       <c r="I127" t="n">
         <v>23.65</v>
@@ -23365,7 +23385,7 @@
         <v>-3.83</v>
       </c>
       <c r="M127" t="n">
-        <v>-5.97</v>
+        <v>-8.31</v>
       </c>
       <c r="N127" t="b">
         <v>1</v>
@@ -23403,7 +23423,7 @@
         <v>-16.2</v>
       </c>
       <c r="H128" t="n">
-        <v>11.03</v>
+        <v>8.44</v>
       </c>
       <c r="I128" t="n">
         <v>25.77</v>
@@ -23416,7 +23436,7 @@
         <v>-1.7</v>
       </c>
       <c r="M128" t="n">
-        <v>7.42</v>
+        <v>5.59</v>
       </c>
       <c r="N128" t="b">
         <v>1</v>
@@ -23454,7 +23474,7 @@
         <v>-24.9</v>
       </c>
       <c r="H129" t="n">
-        <v>31.46</v>
+        <v>22.23</v>
       </c>
       <c r="I129" t="n">
         <v>10.88</v>
@@ -23467,7 +23487,7 @@
         <v>-4.1</v>
       </c>
       <c r="M129" t="n">
-        <v>27.85</v>
+        <v>19.39</v>
       </c>
       <c r="N129" t="b">
         <v>1</v>
@@ -23509,7 +23529,7 @@
         <v>-8.1</v>
       </c>
       <c r="H130" t="n">
-        <v>16.95</v>
+        <v>13.34</v>
       </c>
       <c r="I130" t="n">
         <v>14.27</v>
@@ -23522,7 +23542,7 @@
         <v>-10.92</v>
       </c>
       <c r="M130" t="n">
-        <v>13.34</v>
+        <v>10.49</v>
       </c>
       <c r="N130" t="b">
         <v>1</v>
@@ -23560,7 +23580,7 @@
         <v>-10.2</v>
       </c>
       <c r="H131" t="n">
-        <v>-10.82</v>
+        <v>-12.15</v>
       </c>
       <c r="I131" t="n">
         <v>15.03</v>
@@ -23573,7 +23593,7 @@
         <v>-1.61</v>
       </c>
       <c r="M131" t="n">
-        <v>-14.44</v>
+        <v>-14.99</v>
       </c>
       <c r="N131" t="b">
         <v>1</v>
@@ -23611,7 +23631,7 @@
         <v>68.90000000000001</v>
       </c>
       <c r="H132" t="n">
-        <v>14.32</v>
+        <v>15.4</v>
       </c>
       <c r="I132" t="n">
         <v>1.84</v>
@@ -23624,7 +23644,7 @@
         <v>-10.43</v>
       </c>
       <c r="M132" t="n">
-        <v>10.7</v>
+        <v>12.56</v>
       </c>
       <c r="N132" t="b">
         <v>1</v>
@@ -23662,7 +23682,7 @@
         <v>-40.8</v>
       </c>
       <c r="H133" t="n">
-        <v>-13.5</v>
+        <v>-14.35</v>
       </c>
       <c r="I133" t="n">
         <v>21.71</v>
@@ -23675,7 +23695,7 @@
         <v>-3.3</v>
       </c>
       <c r="M133" t="n">
-        <v>-17.12</v>
+        <v>-17.19</v>
       </c>
       <c r="N133" t="b">
         <v>1</v>
@@ -23713,7 +23733,7 @@
         <v>40.7</v>
       </c>
       <c r="H134" t="n">
-        <v>36.33</v>
+        <v>41.86</v>
       </c>
       <c r="I134" t="n">
         <v>-4.08</v>
@@ -23726,7 +23746,7 @@
         <v>-11.2</v>
       </c>
       <c r="M134" t="n">
-        <v>32.72</v>
+        <v>39.02</v>
       </c>
       <c r="N134" t="b">
         <v>1</v>
@@ -23764,7 +23784,7 @@
         <v>25.7</v>
       </c>
       <c r="H135" t="n">
-        <v>-8.59</v>
+        <v>-8.449999999999999</v>
       </c>
       <c r="I135" t="n">
         <v>11.3</v>
@@ -23777,7 +23797,7 @@
         <v>-11.03</v>
       </c>
       <c r="M135" t="n">
-        <v>-12.2</v>
+        <v>-11.29</v>
       </c>
       <c r="N135" t="b">
         <v>1</v>

--- a/STS_holy_grail_v2.xlsx
+++ b/STS_holy_grail_v2.xlsx
@@ -444,7 +444,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="3">
@@ -464,7 +464,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.25</v>
+        <v>1.01</v>
       </c>
     </row>
     <row r="5">
@@ -474,7 +474,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-1.2</v>
+        <v>-0.61</v>
       </c>
     </row>
     <row r="6">
@@ -484,7 +484,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>41.9</v>
+        <v>44.9</v>
       </c>
     </row>
     <row r="8">
@@ -531,13 +531,13 @@
         <v>61</v>
       </c>
       <c r="C10" t="n">
-        <v>0.62</v>
+        <v>1.84</v>
       </c>
       <c r="D10" t="n">
-        <v>44.26</v>
+        <v>49.18</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.57</v>
+        <v>0.47</v>
       </c>
     </row>
     <row r="11">
@@ -550,13 +550,13 @@
         <v>79</v>
       </c>
       <c r="C11" t="n">
-        <v>0.02</v>
+        <v>1.95</v>
       </c>
       <c r="D11" t="n">
-        <v>40.51</v>
+        <v>44.3</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.08</v>
+        <v>-0.33</v>
       </c>
     </row>
     <row r="12">
@@ -566,16 +566,16 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C12" t="n">
-        <v>-0.76</v>
+        <v>-0.8</v>
       </c>
       <c r="D12" t="n">
-        <v>36.91</v>
+        <v>39.86</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.21</v>
+        <v>-2.41</v>
       </c>
     </row>
     <row r="13">
@@ -588,13 +588,13 @@
         <v>33</v>
       </c>
       <c r="C13" t="n">
-        <v>4.65</v>
+        <v>5.3</v>
       </c>
       <c r="D13" t="n">
-        <v>63.64</v>
+        <v>60.61</v>
       </c>
       <c r="E13" t="n">
-        <v>4.31</v>
+        <v>4.79</v>
       </c>
     </row>
     <row r="15">
@@ -638,16 +638,16 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C17" t="n">
-        <v>-0.13</v>
+        <v>-0.61</v>
       </c>
       <c r="D17" t="n">
-        <v>38.32</v>
+        <v>40.57</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.64</v>
+        <v>-2.28</v>
       </c>
     </row>
     <row r="18">
@@ -660,13 +660,13 @@
         <v>43</v>
       </c>
       <c r="C18" t="n">
-        <v>-2.46</v>
+        <v>-1.38</v>
       </c>
       <c r="D18" t="n">
-        <v>32.56</v>
+        <v>37.21</v>
       </c>
       <c r="E18" t="n">
-        <v>-3.68</v>
+        <v>-2.78</v>
       </c>
     </row>
     <row r="19">
@@ -679,13 +679,13 @@
         <v>45</v>
       </c>
       <c r="C19" t="n">
-        <v>-4.59</v>
+        <v>-3.57</v>
       </c>
       <c r="D19" t="n">
-        <v>26.67</v>
+        <v>31.11</v>
       </c>
       <c r="E19" t="n">
-        <v>-5.97</v>
+        <v>-5.13</v>
       </c>
     </row>
     <row r="20">
@@ -698,13 +698,13 @@
         <v>39</v>
       </c>
       <c r="C20" t="n">
-        <v>-6.62</v>
+        <v>-4.93</v>
       </c>
       <c r="D20" t="n">
-        <v>30.77</v>
+        <v>35.9</v>
       </c>
       <c r="E20" t="n">
-        <v>-8.01</v>
+        <v>-6.5</v>
       </c>
     </row>
     <row r="21">
@@ -717,13 +717,13 @@
         <v>88</v>
       </c>
       <c r="C21" t="n">
-        <v>7.54</v>
+        <v>9.1</v>
       </c>
       <c r="D21" t="n">
-        <v>63.64</v>
+        <v>64.77</v>
       </c>
       <c r="E21" t="n">
-        <v>6</v>
+        <v>7.38</v>
       </c>
     </row>
     <row r="23">
@@ -770,13 +770,13 @@
         <v>10</v>
       </c>
       <c r="C25" t="n">
-        <v>5.58</v>
+        <v>7.63</v>
       </c>
       <c r="D25" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="E25" t="n">
-        <v>3.64</v>
+        <v>5.53</v>
       </c>
     </row>
     <row r="26">
@@ -789,13 +789,13 @@
         <v>5</v>
       </c>
       <c r="C26" t="n">
-        <v>-5.71</v>
+        <v>-6.89</v>
       </c>
       <c r="D26" t="n">
         <v>40</v>
       </c>
       <c r="E26" t="n">
-        <v>-8.35</v>
+        <v>-9.720000000000001</v>
       </c>
     </row>
     <row r="27">
@@ -808,13 +808,13 @@
         <v>3</v>
       </c>
       <c r="C27" t="n">
-        <v>0.24</v>
+        <v>6.41</v>
       </c>
       <c r="D27" t="n">
-        <v>33.33</v>
+        <v>66.67</v>
       </c>
       <c r="E27" t="n">
-        <v>-1.37</v>
+        <v>4.62</v>
       </c>
     </row>
     <row r="29">
@@ -858,16 +858,16 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C31" t="n">
-        <v>1.34</v>
+        <v>1.41</v>
       </c>
       <c r="D31" t="n">
-        <v>38.38</v>
+        <v>39.13</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.1</v>
+        <v>-0.19</v>
       </c>
     </row>
     <row r="32">
@@ -880,13 +880,13 @@
         <v>137</v>
       </c>
       <c r="C32" t="n">
-        <v>-1.22</v>
+        <v>0.46</v>
       </c>
       <c r="D32" t="n">
-        <v>46.72</v>
+        <v>52.55</v>
       </c>
       <c r="E32" t="n">
-        <v>-2.68</v>
+        <v>-1.17</v>
       </c>
     </row>
   </sheetData>
@@ -900,7 +900,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O323"/>
+  <dimension ref="A1:O322"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1010,16 +1010,16 @@
         <v>-21.8</v>
       </c>
       <c r="H2" t="n">
-        <v>-3.45</v>
+        <v>-2.98</v>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="n">
-        <v>-4.4</v>
+        <v>-5.26</v>
       </c>
       <c r="M2" t="n">
-        <v>-2.96</v>
+        <v>-2.66</v>
       </c>
       <c r="N2" t="b">
         <v>1</v>
@@ -1057,7 +1057,7 @@
         <v>-15</v>
       </c>
       <c r="H3" t="n">
-        <v>3.87</v>
+        <v>4.95</v>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
@@ -1066,7 +1066,7 @@
         <v>-4.06</v>
       </c>
       <c r="M3" t="n">
-        <v>4.42</v>
+        <v>5.32</v>
       </c>
       <c r="N3" t="b">
         <v>0</v>
@@ -1093,7 +1093,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Extended</t>
         </is>
       </c>
       <c r="E4" t="inlineStr"/>
@@ -1104,16 +1104,16 @@
         <v>-16.7</v>
       </c>
       <c r="H4" t="n">
-        <v>-5.03</v>
+        <v>12.83</v>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="n">
-        <v>-6.71</v>
+        <v>-6.98</v>
       </c>
       <c r="M4" t="n">
-        <v>-4.48</v>
+        <v>13.2</v>
       </c>
       <c r="N4" t="b">
         <v>1</v>
@@ -1151,16 +1151,16 @@
         <v>-26.8</v>
       </c>
       <c r="H5" t="n">
-        <v>-2.98</v>
+        <v>-3.11</v>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="n">
-        <v>-3.18</v>
+        <v>-5.1</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.43</v>
+        <v>-2.74</v>
       </c>
       <c r="N5" t="b">
         <v>0</v>
@@ -1198,16 +1198,16 @@
         <v>-35.9</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.93</v>
+        <v>-3.36</v>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="n">
-        <v>-2.02</v>
+        <v>-3.44</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.39</v>
+        <v>-2.99</v>
       </c>
       <c r="N6" t="b">
         <v>0</v>
@@ -1245,16 +1245,16 @@
         <v>-7.1</v>
       </c>
       <c r="H7" t="n">
-        <v>0.79</v>
+        <v>-1.74</v>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="n">
-        <v>-1.45</v>
+        <v>-2.71</v>
       </c>
       <c r="M7" t="n">
-        <v>1.34</v>
+        <v>-1.37</v>
       </c>
       <c r="N7" t="b">
         <v>0</v>
@@ -1292,7 +1292,7 @@
         <v>-11.5</v>
       </c>
       <c r="H8" t="n">
-        <v>2.18</v>
+        <v>3.64</v>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
@@ -1301,7 +1301,7 @@
         <v>-0.99</v>
       </c>
       <c r="M8" t="n">
-        <v>2.73</v>
+        <v>4.01</v>
       </c>
       <c r="N8" t="b">
         <v>1</v>
@@ -1339,16 +1339,16 @@
         <v>0.1</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.65</v>
+        <v>1.37</v>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="n">
-        <v>-1.9</v>
+        <v>-2.51</v>
       </c>
       <c r="M9" t="n">
-        <v>0.15</v>
+        <v>1.99</v>
       </c>
       <c r="N9" t="b">
         <v>1</v>
@@ -1386,16 +1386,16 @@
         <v>-31.6</v>
       </c>
       <c r="H10" t="n">
-        <v>-3.71</v>
+        <v>-1.91</v>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="n">
-        <v>-4.03</v>
+        <v>-5.01</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.91</v>
+        <v>-1.29</v>
       </c>
       <c r="N10" t="b">
         <v>1</v>
@@ -1433,16 +1433,16 @@
         <v>7.6</v>
       </c>
       <c r="H11" t="n">
-        <v>-5.18</v>
+        <v>-7.82</v>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="n">
-        <v>-6.34</v>
+        <v>-9.35</v>
       </c>
       <c r="M11" t="n">
-        <v>-4.99</v>
+        <v>-7.81</v>
       </c>
       <c r="N11" t="b">
         <v>0</v>
@@ -1480,7 +1480,7 @@
         <v>-17.9</v>
       </c>
       <c r="H12" t="n">
-        <v>-4.25</v>
+        <v>-2.49</v>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
@@ -1489,7 +1489,7 @@
         <v>-6.52</v>
       </c>
       <c r="M12" t="n">
-        <v>-2.78</v>
+        <v>-1.19</v>
       </c>
       <c r="N12" t="b">
         <v>0</v>
@@ -1527,16 +1527,16 @@
         <v>-2.7</v>
       </c>
       <c r="H13" t="n">
-        <v>-6.21</v>
+        <v>-5.93</v>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="n">
-        <v>-6.35</v>
+        <v>-8.800000000000001</v>
       </c>
       <c r="M13" t="n">
-        <v>-4.74</v>
+        <v>-4.63</v>
       </c>
       <c r="N13" t="b">
         <v>1</v>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Extended</t>
         </is>
       </c>
       <c r="E14" t="inlineStr"/>
@@ -1574,7 +1574,7 @@
         <v>-25.3</v>
       </c>
       <c r="H14" t="n">
-        <v>4.28</v>
+        <v>5.9</v>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
@@ -1583,7 +1583,7 @@
         <v>-0.24</v>
       </c>
       <c r="M14" t="n">
-        <v>5.75</v>
+        <v>7.2</v>
       </c>
       <c r="N14" t="b">
         <v>0</v>
@@ -1621,16 +1621,16 @@
         <v>25.6</v>
       </c>
       <c r="H15" t="n">
-        <v>-4.25</v>
+        <v>-6</v>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="n">
-        <v>-6.07</v>
+        <v>-8.34</v>
       </c>
       <c r="M15" t="n">
-        <v>-2.78</v>
+        <v>-4.7</v>
       </c>
       <c r="N15" t="b">
         <v>0</v>
@@ -1657,7 +1657,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Extended</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="E16" t="inlineStr"/>
@@ -1668,16 +1668,16 @@
         <v>26.9</v>
       </c>
       <c r="H16" t="n">
-        <v>6.37</v>
+        <v>-1.93</v>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="n">
-        <v>-0.4</v>
+        <v>-1.99</v>
       </c>
       <c r="M16" t="n">
-        <v>7.84</v>
+        <v>-0.63</v>
       </c>
       <c r="N16" t="b">
         <v>1</v>
@@ -1715,16 +1715,16 @@
         <v>-14.5</v>
       </c>
       <c r="H17" t="n">
-        <v>-6.58</v>
+        <v>-6.66</v>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="n">
-        <v>-6.71</v>
+        <v>-7.31</v>
       </c>
       <c r="M17" t="n">
-        <v>-6.11</v>
+        <v>-6.37</v>
       </c>
       <c r="N17" t="b">
         <v>0</v>
@@ -1762,7 +1762,7 @@
         <v>17.2</v>
       </c>
       <c r="H18" t="n">
-        <v>-3.55</v>
+        <v>-3.66</v>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
@@ -1771,7 +1771,7 @@
         <v>-10.54</v>
       </c>
       <c r="M18" t="n">
-        <v>-3.08</v>
+        <v>-3.36</v>
       </c>
       <c r="N18" t="b">
         <v>0</v>
@@ -1809,7 +1809,7 @@
         <v>-13.2</v>
       </c>
       <c r="H19" t="n">
-        <v>15.56</v>
+        <v>22.75</v>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
@@ -1818,7 +1818,7 @@
         <v>-0.82</v>
       </c>
       <c r="M19" t="n">
-        <v>16.03</v>
+        <v>23.04</v>
       </c>
       <c r="N19" t="b">
         <v>0</v>
@@ -1856,16 +1856,16 @@
         <v>-7.7</v>
       </c>
       <c r="H20" t="n">
-        <v>-6.51</v>
+        <v>-8.34</v>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="n">
-        <v>-7.33</v>
+        <v>-10.1</v>
       </c>
       <c r="M20" t="n">
-        <v>-6.04</v>
+        <v>-8.050000000000001</v>
       </c>
       <c r="N20" t="b">
         <v>0</v>
@@ -1903,16 +1903,16 @@
         <v>-18.1</v>
       </c>
       <c r="H21" t="n">
-        <v>-2.38</v>
+        <v>-4.18</v>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="n">
-        <v>-3.53</v>
+        <v>-4.42</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.91</v>
+        <v>-3.89</v>
       </c>
       <c r="N21" t="b">
         <v>0</v>
@@ -1950,7 +1950,7 @@
         <v>-18.1</v>
       </c>
       <c r="H22" t="n">
-        <v>2.95</v>
+        <v>4.82</v>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
@@ -1959,7 +1959,7 @@
         <v>-2.69</v>
       </c>
       <c r="M22" t="n">
-        <v>3.43</v>
+        <v>5.12</v>
       </c>
       <c r="N22" t="b">
         <v>1</v>
@@ -1997,7 +1997,7 @@
         <v>7.7</v>
       </c>
       <c r="H23" t="n">
-        <v>-5.7</v>
+        <v>-5.95</v>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
@@ -2006,7 +2006,7 @@
         <v>-8.67</v>
       </c>
       <c r="M23" t="n">
-        <v>-5.23</v>
+        <v>-5.66</v>
       </c>
       <c r="N23" t="b">
         <v>0</v>
@@ -2044,7 +2044,7 @@
         <v>-21.5</v>
       </c>
       <c r="H24" t="n">
-        <v>1.04</v>
+        <v>0.97</v>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
@@ -2053,7 +2053,7 @@
         <v>-1.4</v>
       </c>
       <c r="M24" t="n">
-        <v>1.51</v>
+        <v>1.26</v>
       </c>
       <c r="N24" t="b">
         <v>1</v>
@@ -2091,7 +2091,7 @@
         <v>41.6</v>
       </c>
       <c r="H25" t="n">
-        <v>4.36</v>
+        <v>1.75</v>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
@@ -2100,7 +2100,7 @@
         <v>-4.38</v>
       </c>
       <c r="M25" t="n">
-        <v>4.19</v>
+        <v>1.4</v>
       </c>
       <c r="N25" t="b">
         <v>1</v>
@@ -2138,7 +2138,7 @@
         <v>32.1</v>
       </c>
       <c r="H26" t="n">
-        <v>-6.04</v>
+        <v>-3.47</v>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
@@ -2147,7 +2147,7 @@
         <v>-6.94</v>
       </c>
       <c r="M26" t="n">
-        <v>-6.22</v>
+        <v>-3.82</v>
       </c>
       <c r="N26" t="b">
         <v>1</v>
@@ -2185,16 +2185,16 @@
         <v>-14.4</v>
       </c>
       <c r="H27" t="n">
-        <v>-3.67</v>
+        <v>-2.48</v>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="n">
-        <v>-4.61</v>
+        <v>-6.43</v>
       </c>
       <c r="M27" t="n">
-        <v>-3.84</v>
+        <v>-2.83</v>
       </c>
       <c r="N27" t="b">
         <v>1</v>
@@ -2232,7 +2232,7 @@
         <v>-16.8</v>
       </c>
       <c r="H28" t="n">
-        <v>4.27</v>
+        <v>4.93</v>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
@@ -2241,7 +2241,7 @@
         <v>-3.26</v>
       </c>
       <c r="M28" t="n">
-        <v>4.09</v>
+        <v>4.58</v>
       </c>
       <c r="N28" t="b">
         <v>0</v>
@@ -2279,16 +2279,16 @@
         <v>-10</v>
       </c>
       <c r="H29" t="n">
-        <v>-5.16</v>
+        <v>-4.4</v>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="n">
-        <v>-9.539999999999999</v>
+        <v>-10.65</v>
       </c>
       <c r="M29" t="n">
-        <v>-5.33</v>
+        <v>-4.75</v>
       </c>
       <c r="N29" t="b">
         <v>1</v>
@@ -2326,7 +2326,7 @@
         <v>6.4</v>
       </c>
       <c r="H30" t="n">
-        <v>-2.41</v>
+        <v>3.55</v>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
@@ -2335,7 +2335,7 @@
         <v>-3.35</v>
       </c>
       <c r="M30" t="n">
-        <v>-2.59</v>
+        <v>3.2</v>
       </c>
       <c r="N30" t="b">
         <v>1</v>
@@ -2373,16 +2373,18 @@
         <v>-11</v>
       </c>
       <c r="H31" t="n">
-        <v>6.97</v>
-      </c>
-      <c r="I31" t="inlineStr"/>
+        <v>11.67</v>
+      </c>
+      <c r="I31" t="n">
+        <v>11.67</v>
+      </c>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="n">
         <v>-0.97</v>
       </c>
       <c r="M31" t="n">
-        <v>6.79</v>
+        <v>11.31</v>
       </c>
       <c r="N31" t="b">
         <v>0</v>
@@ -2420,16 +2422,18 @@
         <v>-23.9</v>
       </c>
       <c r="H32" t="n">
-        <v>-4.14</v>
-      </c>
-      <c r="I32" t="inlineStr"/>
+        <v>-4.98</v>
+      </c>
+      <c r="I32" t="n">
+        <v>-4.98</v>
+      </c>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="n">
         <v>-5.79</v>
       </c>
       <c r="M32" t="n">
-        <v>-4.32</v>
+        <v>-5.34</v>
       </c>
       <c r="N32" t="b">
         <v>0</v>
@@ -2471,16 +2475,18 @@
         <v>-9.800000000000001</v>
       </c>
       <c r="H33" t="n">
-        <v>-4.46</v>
-      </c>
-      <c r="I33" t="inlineStr"/>
+        <v>-3.41</v>
+      </c>
+      <c r="I33" t="n">
+        <v>-3.41</v>
+      </c>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="n">
         <v>-8.949999999999999</v>
       </c>
       <c r="M33" t="n">
-        <v>-4.64</v>
+        <v>-3.76</v>
       </c>
       <c r="N33" t="b">
         <v>0</v>
@@ -2518,16 +2524,18 @@
         <v>-36.1</v>
       </c>
       <c r="H34" t="n">
-        <v>-1.06</v>
-      </c>
-      <c r="I34" t="inlineStr"/>
+        <v>-1.4</v>
+      </c>
+      <c r="I34" t="n">
+        <v>-1.4</v>
+      </c>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="n">
         <v>-1.92</v>
       </c>
       <c r="M34" t="n">
-        <v>-1.24</v>
+        <v>-1.76</v>
       </c>
       <c r="N34" t="b">
         <v>0</v>
@@ -2565,16 +2573,18 @@
         <v>-7.9</v>
       </c>
       <c r="H35" t="n">
-        <v>-8.41</v>
-      </c>
-      <c r="I35" t="inlineStr"/>
+        <v>-9.98</v>
+      </c>
+      <c r="I35" t="n">
+        <v>-9.98</v>
+      </c>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="n">
-        <v>-11.04</v>
+        <v>-11.78</v>
       </c>
       <c r="M35" t="n">
-        <v>-8.59</v>
+        <v>-10.34</v>
       </c>
       <c r="N35" t="b">
         <v>0</v>
@@ -2612,7 +2622,7 @@
         <v>2.6</v>
       </c>
       <c r="H36" t="n">
-        <v>-7.8</v>
+        <v>-2.28</v>
       </c>
       <c r="I36" t="n">
         <v>-7.8</v>
@@ -2623,7 +2633,7 @@
         <v>-10.71</v>
       </c>
       <c r="M36" t="n">
-        <v>-8.460000000000001</v>
+        <v>-3.12</v>
       </c>
       <c r="N36" t="b">
         <v>0</v>
@@ -2661,7 +2671,7 @@
         <v>6.3</v>
       </c>
       <c r="H37" t="n">
-        <v>0.64</v>
+        <v>3.99</v>
       </c>
       <c r="I37" t="n">
         <v>0.64</v>
@@ -2672,7 +2682,7 @@
         <v>-2.13</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.02</v>
+        <v>3.15</v>
       </c>
       <c r="N37" t="b">
         <v>0</v>
@@ -2699,7 +2709,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Extended</t>
         </is>
       </c>
       <c r="E38" t="inlineStr"/>
@@ -2710,7 +2720,7 @@
         <v>20.2</v>
       </c>
       <c r="H38" t="n">
-        <v>2.63</v>
+        <v>5.34</v>
       </c>
       <c r="I38" t="n">
         <v>3.45</v>
@@ -2721,7 +2731,7 @@
         <v>-1.07</v>
       </c>
       <c r="M38" t="n">
-        <v>2.06</v>
+        <v>4.58</v>
       </c>
       <c r="N38" t="b">
         <v>1</v>
@@ -2759,7 +2769,7 @@
         <v>43.7</v>
       </c>
       <c r="H39" t="n">
-        <v>2.09</v>
+        <v>-1.11</v>
       </c>
       <c r="I39" t="n">
         <v>3.16</v>
@@ -2770,7 +2780,7 @@
         <v>-2.44</v>
       </c>
       <c r="M39" t="n">
-        <v>1.51</v>
+        <v>-1.87</v>
       </c>
       <c r="N39" t="b">
         <v>1</v>
@@ -2808,7 +2818,7 @@
         <v>1.9</v>
       </c>
       <c r="H40" t="n">
-        <v>-11.01</v>
+        <v>-9.67</v>
       </c>
       <c r="I40" t="n">
         <v>-10.64</v>
@@ -2816,10 +2826,10 @@
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="n">
-        <v>-11.27</v>
+        <v>-11.41</v>
       </c>
       <c r="M40" t="n">
-        <v>-11.59</v>
+        <v>-10.42</v>
       </c>
       <c r="N40" t="b">
         <v>1</v>
@@ -2846,7 +2856,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Extended</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="E41" t="inlineStr"/>
@@ -2857,7 +2867,7 @@
         <v>37.5</v>
       </c>
       <c r="H41" t="n">
-        <v>6.02</v>
+        <v>3.08</v>
       </c>
       <c r="I41" t="n">
         <v>5.86</v>
@@ -2868,7 +2878,7 @@
         <v>-3.95</v>
       </c>
       <c r="M41" t="n">
-        <v>5.29</v>
+        <v>2.17</v>
       </c>
       <c r="N41" t="b">
         <v>1</v>
@@ -2906,7 +2916,7 @@
         <v>15</v>
       </c>
       <c r="H42" t="n">
-        <v>-21.13</v>
+        <v>-21.92</v>
       </c>
       <c r="I42" t="n">
         <v>-21.11</v>
@@ -2917,7 +2927,7 @@
         <v>-22.89</v>
       </c>
       <c r="M42" t="n">
-        <v>-21.85</v>
+        <v>-22.83</v>
       </c>
       <c r="N42" t="b">
         <v>0</v>
@@ -2955,7 +2965,7 @@
         <v>40.2</v>
       </c>
       <c r="H43" t="n">
-        <v>-1.57</v>
+        <v>-2.44</v>
       </c>
       <c r="I43" t="n">
         <v>-1.11</v>
@@ -2966,7 +2976,7 @@
         <v>-3.87</v>
       </c>
       <c r="M43" t="n">
-        <v>-2.3</v>
+        <v>-3.35</v>
       </c>
       <c r="N43" t="b">
         <v>1</v>
@@ -2993,7 +3003,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Extended</t>
         </is>
       </c>
       <c r="E44" t="inlineStr"/>
@@ -3004,7 +3014,7 @@
         <v>10.7</v>
       </c>
       <c r="H44" t="n">
-        <v>4.96</v>
+        <v>7.36</v>
       </c>
       <c r="I44" t="n">
         <v>7.3</v>
@@ -3015,7 +3025,7 @@
         <v>-3.78</v>
       </c>
       <c r="M44" t="n">
-        <v>4.24</v>
+        <v>6.46</v>
       </c>
       <c r="N44" t="b">
         <v>1</v>
@@ -3053,7 +3063,7 @@
         <v>25.6</v>
       </c>
       <c r="H45" t="n">
-        <v>9.16</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="I45" t="n">
         <v>7.71</v>
@@ -3064,7 +3074,7 @@
         <v>-4.85</v>
       </c>
       <c r="M45" t="n">
-        <v>9.18</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="N45" t="b">
         <v>1</v>
@@ -3102,7 +3112,7 @@
         <v>6.3</v>
       </c>
       <c r="H46" t="n">
-        <v>8.109999999999999</v>
+        <v>8.98</v>
       </c>
       <c r="I46" t="n">
         <v>7.2</v>
@@ -3113,7 +3123,7 @@
         <v>-0.4</v>
       </c>
       <c r="M46" t="n">
-        <v>7.25</v>
+        <v>7.94</v>
       </c>
       <c r="N46" t="b">
         <v>0</v>
@@ -3151,7 +3161,7 @@
         <v>2.3</v>
       </c>
       <c r="H47" t="n">
-        <v>-11.84</v>
+        <v>-11.54</v>
       </c>
       <c r="I47" t="n">
         <v>-8.85</v>
@@ -3159,10 +3169,10 @@
       <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="n">
-        <v>-12.42</v>
+        <v>-14.2</v>
       </c>
       <c r="M47" t="n">
-        <v>-12.7</v>
+        <v>-12.58</v>
       </c>
       <c r="N47" t="b">
         <v>0</v>
@@ -3200,7 +3210,7 @@
         <v>-4.3</v>
       </c>
       <c r="H48" t="n">
-        <v>6.46</v>
+        <v>7.46</v>
       </c>
       <c r="I48" t="n">
         <v>3.39</v>
@@ -3211,7 +3221,7 @@
         <v>-5.89</v>
       </c>
       <c r="M48" t="n">
-        <v>6.4</v>
+        <v>7.22</v>
       </c>
       <c r="N48" t="b">
         <v>0</v>
@@ -3249,7 +3259,7 @@
         <v>-29.4</v>
       </c>
       <c r="H49" t="n">
-        <v>-5.68</v>
+        <v>-7.19</v>
       </c>
       <c r="I49" t="n">
         <v>-5.75</v>
@@ -3260,7 +3270,7 @@
         <v>-9.640000000000001</v>
       </c>
       <c r="M49" t="n">
-        <v>-5.74</v>
+        <v>-7.43</v>
       </c>
       <c r="N49" t="b">
         <v>0</v>
@@ -3287,7 +3297,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Extended</t>
         </is>
       </c>
       <c r="E50" t="inlineStr"/>
@@ -3298,7 +3308,7 @@
         <v>-6.9</v>
       </c>
       <c r="H50" t="n">
-        <v>4.55</v>
+        <v>7.09</v>
       </c>
       <c r="I50" t="n">
         <v>6.44</v>
@@ -3309,7 +3319,7 @@
         <v>-4.53</v>
       </c>
       <c r="M50" t="n">
-        <v>4.49</v>
+        <v>6.85</v>
       </c>
       <c r="N50" t="b">
         <v>1</v>
@@ -3347,7 +3357,7 @@
         <v>4.2</v>
       </c>
       <c r="H51" t="n">
-        <v>-16.19</v>
+        <v>-16.08</v>
       </c>
       <c r="I51" t="n">
         <v>-10.83</v>
@@ -3355,10 +3365,10 @@
       <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="n">
-        <v>-16.31</v>
+        <v>-18.01</v>
       </c>
       <c r="M51" t="n">
-        <v>-16.25</v>
+        <v>-16.32</v>
       </c>
       <c r="N51" t="b">
         <v>0</v>
@@ -3396,7 +3406,7 @@
         <v>-32.4</v>
       </c>
       <c r="H52" t="n">
-        <v>-2.17</v>
+        <v>-3.22</v>
       </c>
       <c r="I52" t="n">
         <v>-2.43</v>
@@ -3407,7 +3417,7 @@
         <v>-12.47</v>
       </c>
       <c r="M52" t="n">
-        <v>-1.58</v>
+        <v>-2.81</v>
       </c>
       <c r="N52" t="b">
         <v>0</v>
@@ -3445,7 +3455,7 @@
         <v>-11</v>
       </c>
       <c r="H53" t="n">
-        <v>2.24</v>
+        <v>3.34</v>
       </c>
       <c r="I53" t="n">
         <v>-8.449999999999999</v>
@@ -3456,7 +3466,7 @@
         <v>-18.92</v>
       </c>
       <c r="M53" t="n">
-        <v>2.83</v>
+        <v>3.75</v>
       </c>
       <c r="N53" t="b">
         <v>0</v>
@@ -3483,7 +3493,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Retired</t>
         </is>
       </c>
       <c r="E54" t="inlineStr"/>
@@ -3494,7 +3504,7 @@
         <v>9.699999999999999</v>
       </c>
       <c r="H54" t="n">
-        <v>-7.96</v>
+        <v>-7.14</v>
       </c>
       <c r="I54" t="n">
         <v>1.27</v>
@@ -3505,7 +3515,7 @@
         <v>-20.79</v>
       </c>
       <c r="M54" t="n">
-        <v>-7.52</v>
+        <v>-6.87</v>
       </c>
       <c r="N54" t="b">
         <v>0</v>
@@ -3532,7 +3542,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Retired</t>
         </is>
       </c>
       <c r="E55" t="inlineStr"/>
@@ -3543,7 +3553,7 @@
         <v>-28.1</v>
       </c>
       <c r="H55" t="n">
-        <v>-10.15</v>
+        <v>-11.01</v>
       </c>
       <c r="I55" t="n">
         <v>-10.79</v>
@@ -3554,7 +3564,7 @@
         <v>-12.06</v>
       </c>
       <c r="M55" t="n">
-        <v>-9.710000000000001</v>
+        <v>-10.75</v>
       </c>
       <c r="N55" t="b">
         <v>0</v>
@@ -3630,7 +3640,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Retired</t>
         </is>
       </c>
       <c r="E57" t="inlineStr"/>
@@ -3641,7 +3651,7 @@
         <v>-9.300000000000001</v>
       </c>
       <c r="H57" t="n">
-        <v>-7.73</v>
+        <v>-5.84</v>
       </c>
       <c r="I57" t="n">
         <v>-3.34</v>
@@ -3652,7 +3662,7 @@
         <v>-8.77</v>
       </c>
       <c r="M57" t="n">
-        <v>-7.29</v>
+        <v>-5.58</v>
       </c>
       <c r="N57" t="b">
         <v>0</v>
@@ -3679,7 +3689,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Retired</t>
         </is>
       </c>
       <c r="E58" t="inlineStr"/>
@@ -3690,7 +3700,7 @@
         <v>0.3</v>
       </c>
       <c r="H58" t="n">
-        <v>-14.59</v>
+        <v>-15.48</v>
       </c>
       <c r="I58" t="n">
         <v>-10.53</v>
@@ -3698,10 +3708,10 @@
       <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="n">
-        <v>-15.78</v>
+        <v>-17.73</v>
       </c>
       <c r="M58" t="n">
-        <v>-14.15</v>
+        <v>-15.22</v>
       </c>
       <c r="N58" t="b">
         <v>1</v>
@@ -3739,18 +3749,20 @@
         <v>12.3</v>
       </c>
       <c r="H59" t="n">
-        <v>1.58</v>
+        <v>3.26</v>
       </c>
       <c r="I59" t="n">
         <v>6.51</v>
       </c>
-      <c r="J59" t="inlineStr"/>
+      <c r="J59" t="n">
+        <v>3.26</v>
+      </c>
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="n">
         <v>-6.01</v>
       </c>
       <c r="M59" t="n">
-        <v>1.31</v>
+        <v>2.81</v>
       </c>
       <c r="N59" t="b">
         <v>0</v>
@@ -3788,18 +3800,20 @@
         <v>2.8</v>
       </c>
       <c r="H60" t="n">
-        <v>1.51</v>
+        <v>3.44</v>
       </c>
       <c r="I60" t="n">
         <v>3.18</v>
       </c>
-      <c r="J60" t="inlineStr"/>
+      <c r="J60" t="n">
+        <v>3.44</v>
+      </c>
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="n">
         <v>-0.88</v>
       </c>
       <c r="M60" t="n">
-        <v>1.24</v>
+        <v>2.99</v>
       </c>
       <c r="N60" t="b">
         <v>1</v>
@@ -3837,18 +3851,20 @@
         <v>-1.4</v>
       </c>
       <c r="H61" t="n">
-        <v>9.98</v>
+        <v>11.27</v>
       </c>
       <c r="I61" t="n">
         <v>-4.52</v>
       </c>
-      <c r="J61" t="inlineStr"/>
+      <c r="J61" t="n">
+        <v>11.27</v>
+      </c>
       <c r="K61" t="inlineStr"/>
       <c r="L61" t="n">
         <v>-7.44</v>
       </c>
       <c r="M61" t="n">
-        <v>9.710000000000001</v>
+        <v>10.82</v>
       </c>
       <c r="N61" t="b">
         <v>0</v>
@@ -3886,18 +3902,20 @@
         <v>34.5</v>
       </c>
       <c r="H62" t="n">
-        <v>8.039999999999999</v>
+        <v>8.66</v>
       </c>
       <c r="I62" t="n">
         <v>0.66</v>
       </c>
-      <c r="J62" t="inlineStr"/>
+      <c r="J62" t="n">
+        <v>8.66</v>
+      </c>
       <c r="K62" t="inlineStr"/>
       <c r="L62" t="n">
         <v>-2.64</v>
       </c>
       <c r="M62" t="n">
-        <v>7.77</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="N62" t="b">
         <v>1</v>
@@ -3935,7 +3953,7 @@
         <v>-22.7</v>
       </c>
       <c r="H63" t="n">
-        <v>-8.48</v>
+        <v>-9.83</v>
       </c>
       <c r="I63" t="n">
         <v>-6.71</v>
@@ -3948,7 +3966,7 @@
         <v>-9.58</v>
       </c>
       <c r="M63" t="n">
-        <v>-8.81</v>
+        <v>-10.34</v>
       </c>
       <c r="N63" t="b">
         <v>0</v>
@@ -3986,7 +4004,7 @@
         <v>24.3</v>
       </c>
       <c r="H64" t="n">
-        <v>38.29</v>
+        <v>41.83</v>
       </c>
       <c r="I64" t="n">
         <v>2.54</v>
@@ -3999,7 +4017,7 @@
         <v>-5.21</v>
       </c>
       <c r="M64" t="n">
-        <v>38.65</v>
+        <v>42.02</v>
       </c>
       <c r="N64" t="b">
         <v>1</v>
@@ -4037,7 +4055,7 @@
         <v>56.6</v>
       </c>
       <c r="H65" t="n">
-        <v>-6.43</v>
+        <v>-5.81</v>
       </c>
       <c r="I65" t="n">
         <v>-13.1</v>
@@ -4050,7 +4068,7 @@
         <v>-16.17</v>
       </c>
       <c r="M65" t="n">
-        <v>-6.06</v>
+        <v>-5.62</v>
       </c>
       <c r="N65" t="b">
         <v>0</v>
@@ -4088,7 +4106,7 @@
         <v>2.9</v>
       </c>
       <c r="H66" t="n">
-        <v>-16.43</v>
+        <v>-16.49</v>
       </c>
       <c r="I66" t="n">
         <v>-8.470000000000001</v>
@@ -4101,7 +4119,7 @@
         <v>-15.65</v>
       </c>
       <c r="M66" t="n">
-        <v>-16.06</v>
+        <v>-16.3</v>
       </c>
       <c r="N66" t="b">
         <v>0</v>
@@ -4139,7 +4157,7 @@
         <v>-16.9</v>
       </c>
       <c r="H67" t="n">
-        <v>-6.9</v>
+        <v>-6.47</v>
       </c>
       <c r="I67" t="n">
         <v>-6.47</v>
@@ -4152,7 +4170,7 @@
         <v>-11.5</v>
       </c>
       <c r="M67" t="n">
-        <v>-6.53</v>
+        <v>-6.28</v>
       </c>
       <c r="N67" t="b">
         <v>1</v>
@@ -4190,7 +4208,7 @@
         <v>32.8</v>
       </c>
       <c r="H68" t="n">
-        <v>5.7</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="I68" t="n">
         <v>14.96</v>
@@ -4203,7 +4221,7 @@
         <v>-0.9</v>
       </c>
       <c r="M68" t="n">
-        <v>6.64</v>
+        <v>9.4</v>
       </c>
       <c r="N68" t="b">
         <v>0</v>
@@ -4241,7 +4259,7 @@
         <v>0.8</v>
       </c>
       <c r="H69" t="n">
-        <v>-5.83</v>
+        <v>-7.85</v>
       </c>
       <c r="I69" t="n">
         <v>-7.73</v>
@@ -4254,7 +4272,7 @@
         <v>-10.12</v>
       </c>
       <c r="M69" t="n">
-        <v>-4.89</v>
+        <v>-7.09</v>
       </c>
       <c r="N69" t="b">
         <v>0</v>
@@ -4292,7 +4310,7 @@
         <v>-9.6</v>
       </c>
       <c r="H70" t="n">
-        <v>-16.44</v>
+        <v>-17.89</v>
       </c>
       <c r="I70" t="n">
         <v>-1.23</v>
@@ -4305,7 +4323,7 @@
         <v>-18.52</v>
       </c>
       <c r="M70" t="n">
-        <v>-15.5</v>
+        <v>-17.13</v>
       </c>
       <c r="N70" t="b">
         <v>0</v>
@@ -4343,7 +4361,7 @@
         <v>20.3</v>
       </c>
       <c r="H71" t="n">
-        <v>-20.18</v>
+        <v>-16.28</v>
       </c>
       <c r="I71" t="n">
         <v>-2.07</v>
@@ -4356,7 +4374,7 @@
         <v>-17.35</v>
       </c>
       <c r="M71" t="n">
-        <v>-19.66</v>
+        <v>-15.94</v>
       </c>
       <c r="N71" t="b">
         <v>1</v>
@@ -4394,7 +4412,7 @@
         <v>0.3</v>
       </c>
       <c r="H72" t="n">
-        <v>-17.73</v>
+        <v>-16.11</v>
       </c>
       <c r="I72" t="n">
         <v>-9.9</v>
@@ -4407,7 +4425,7 @@
         <v>-21.72</v>
       </c>
       <c r="M72" t="n">
-        <v>-17.71</v>
+        <v>-16.26</v>
       </c>
       <c r="N72" t="b">
         <v>1</v>
@@ -4445,7 +4463,7 @@
         <v>49.4</v>
       </c>
       <c r="H73" t="n">
-        <v>5.41</v>
+        <v>6.16</v>
       </c>
       <c r="I73" t="n">
         <v>2.9</v>
@@ -4458,7 +4476,7 @@
         <v>-5.67</v>
       </c>
       <c r="M73" t="n">
-        <v>5.62</v>
+        <v>6.2</v>
       </c>
       <c r="N73" t="b">
         <v>1</v>
@@ -4496,7 +4514,7 @@
         <v>4.5</v>
       </c>
       <c r="H74" t="n">
-        <v>-11.46</v>
+        <v>-11.43</v>
       </c>
       <c r="I74" t="n">
         <v>-7.61</v>
@@ -4509,7 +4527,7 @@
         <v>-11.06</v>
       </c>
       <c r="M74" t="n">
-        <v>-11.25</v>
+        <v>-11.4</v>
       </c>
       <c r="N74" t="b">
         <v>1</v>
@@ -4547,7 +4565,7 @@
         <v>4.2</v>
       </c>
       <c r="H75" t="n">
-        <v>-20.76</v>
+        <v>-21.82</v>
       </c>
       <c r="I75" t="n">
         <v>-6.86</v>
@@ -4560,7 +4578,7 @@
         <v>-20.23</v>
       </c>
       <c r="M75" t="n">
-        <v>-20.54</v>
+        <v>-21.79</v>
       </c>
       <c r="N75" t="b">
         <v>0</v>
@@ -4598,7 +4616,7 @@
         <v>15.4</v>
       </c>
       <c r="H76" t="n">
-        <v>-7.15</v>
+        <v>-7.63</v>
       </c>
       <c r="I76" t="n">
         <v>-1.19</v>
@@ -4611,7 +4629,7 @@
         <v>-7.43</v>
       </c>
       <c r="M76" t="n">
-        <v>-6.94</v>
+        <v>-7.59</v>
       </c>
       <c r="N76" t="b">
         <v>0</v>
@@ -4649,7 +4667,7 @@
         <v>15.5</v>
       </c>
       <c r="H77" t="n">
-        <v>-12.2</v>
+        <v>-11.66</v>
       </c>
       <c r="I77" t="n">
         <v>-7.36</v>
@@ -4662,7 +4680,7 @@
         <v>-12.98</v>
       </c>
       <c r="M77" t="n">
-        <v>-12.17</v>
+        <v>-11.81</v>
       </c>
       <c r="N77" t="b">
         <v>0</v>
@@ -4704,7 +4722,7 @@
         <v>-8.5</v>
       </c>
       <c r="H78" t="n">
-        <v>-0.6899999999999999</v>
+        <v>14.98</v>
       </c>
       <c r="I78" t="n">
         <v>-3.04</v>
@@ -4717,7 +4735,7 @@
         <v>-4.96</v>
       </c>
       <c r="M78" t="n">
-        <v>-0.65</v>
+        <v>14.84</v>
       </c>
       <c r="N78" t="b">
         <v>0</v>
@@ -4755,7 +4773,7 @@
         <v>1.8</v>
       </c>
       <c r="H79" t="n">
-        <v>-12.75</v>
+        <v>-12.26</v>
       </c>
       <c r="I79" t="n">
         <v>-6.45</v>
@@ -4768,7 +4786,7 @@
         <v>-13.57</v>
       </c>
       <c r="M79" t="n">
-        <v>-12.72</v>
+        <v>-12.41</v>
       </c>
       <c r="N79" t="b">
         <v>0</v>
@@ -4806,7 +4824,7 @@
         <v>33.9</v>
       </c>
       <c r="H80" t="n">
-        <v>12.82</v>
+        <v>17.14</v>
       </c>
       <c r="I80" t="n">
         <v>-7.74</v>
@@ -4819,7 +4837,7 @@
         <v>-9.449999999999999</v>
       </c>
       <c r="M80" t="n">
-        <v>12.85</v>
+        <v>17</v>
       </c>
       <c r="N80" t="b">
         <v>0</v>
@@ -4857,7 +4875,7 @@
         <v>-25</v>
       </c>
       <c r="H81" t="n">
-        <v>-9.24</v>
+        <v>-8.24</v>
       </c>
       <c r="I81" t="n">
         <v>2.51</v>
@@ -4870,7 +4888,7 @@
         <v>-4.88</v>
       </c>
       <c r="M81" t="n">
-        <v>-9.039999999999999</v>
+        <v>-8.220000000000001</v>
       </c>
       <c r="N81" t="b">
         <v>0</v>
@@ -4908,7 +4926,7 @@
         <v>-12.6</v>
       </c>
       <c r="H82" t="n">
-        <v>-23.19</v>
+        <v>-23.09</v>
       </c>
       <c r="I82" t="n">
         <v>-7.89</v>
@@ -4921,7 +4939,7 @@
         <v>-21.29</v>
       </c>
       <c r="M82" t="n">
-        <v>-23</v>
+        <v>-23.08</v>
       </c>
       <c r="N82" t="b">
         <v>0</v>
@@ -4959,7 +4977,7 @@
         <v>-17.9</v>
       </c>
       <c r="H83" t="n">
-        <v>-8.42</v>
+        <v>-7.83</v>
       </c>
       <c r="I83" t="n">
         <v>0.6</v>
@@ -4972,7 +4990,7 @@
         <v>-4.72</v>
       </c>
       <c r="M83" t="n">
-        <v>-8.23</v>
+        <v>-7.82</v>
       </c>
       <c r="N83" t="b">
         <v>1</v>
@@ -5010,7 +5028,7 @@
         <v>2.1</v>
       </c>
       <c r="H84" t="n">
-        <v>-27.24</v>
+        <v>-25.92</v>
       </c>
       <c r="I84" t="n">
         <v>0.25</v>
@@ -5023,7 +5041,7 @@
         <v>-16.43</v>
       </c>
       <c r="M84" t="n">
-        <v>-27.05</v>
+        <v>-25.91</v>
       </c>
       <c r="N84" t="b">
         <v>1</v>
@@ -5061,7 +5079,7 @@
         <v>19.4</v>
       </c>
       <c r="H85" t="n">
-        <v>-12.85</v>
+        <v>-11.58</v>
       </c>
       <c r="I85" t="n">
         <v>-10.01</v>
@@ -5074,7 +5092,7 @@
         <v>-15.23</v>
       </c>
       <c r="M85" t="n">
-        <v>-12.1</v>
+        <v>-11</v>
       </c>
       <c r="N85" t="b">
         <v>1</v>
@@ -5112,7 +5130,7 @@
         <v>-30.5</v>
       </c>
       <c r="H86" t="n">
-        <v>-22.06</v>
+        <v>-22.74</v>
       </c>
       <c r="I86" t="n">
         <v>-4.6</v>
@@ -5125,7 +5143,7 @@
         <v>-10.37</v>
       </c>
       <c r="M86" t="n">
-        <v>-21.3</v>
+        <v>-22.16</v>
       </c>
       <c r="N86" t="b">
         <v>0</v>
@@ -5163,7 +5181,7 @@
         <v>-20.5</v>
       </c>
       <c r="H87" t="n">
-        <v>-16.29</v>
+        <v>-13.81</v>
       </c>
       <c r="I87" t="n">
         <v>-4.62</v>
@@ -5176,7 +5194,7 @@
         <v>-9.92</v>
       </c>
       <c r="M87" t="n">
-        <v>-15.53</v>
+        <v>-13.22</v>
       </c>
       <c r="N87" t="b">
         <v>0</v>
@@ -5214,7 +5232,7 @@
         <v>-12.3</v>
       </c>
       <c r="H88" t="n">
-        <v>-20.84</v>
+        <v>-22.51</v>
       </c>
       <c r="I88" t="n">
         <v>-4.36</v>
@@ -5227,7 +5245,7 @@
         <v>-13.26</v>
       </c>
       <c r="M88" t="n">
-        <v>-20.3</v>
+        <v>-22.14</v>
       </c>
       <c r="N88" t="b">
         <v>0</v>
@@ -5265,7 +5283,7 @@
         <v>13.7</v>
       </c>
       <c r="H89" t="n">
-        <v>-21.53</v>
+        <v>-22.23</v>
       </c>
       <c r="I89" t="n">
         <v>-12.16</v>
@@ -5278,7 +5296,7 @@
         <v>-13.02</v>
       </c>
       <c r="M89" t="n">
-        <v>-20.99</v>
+        <v>-21.86</v>
       </c>
       <c r="N89" t="b">
         <v>0</v>
@@ -5316,7 +5334,7 @@
         <v>-2.6</v>
       </c>
       <c r="H90" t="n">
-        <v>-11.67</v>
+        <v>-10.59</v>
       </c>
       <c r="I90" t="n">
         <v>-4.27</v>
@@ -5329,7 +5347,7 @@
         <v>-4.86</v>
       </c>
       <c r="M90" t="n">
-        <v>-11.13</v>
+        <v>-10.23</v>
       </c>
       <c r="N90" t="b">
         <v>1</v>
@@ -5367,7 +5385,7 @@
         <v>25.6</v>
       </c>
       <c r="H91" t="n">
-        <v>-8.83</v>
+        <v>-7.1</v>
       </c>
       <c r="I91" t="n">
         <v>4.26</v>
@@ -5380,7 +5398,7 @@
         <v>-10.74</v>
       </c>
       <c r="M91" t="n">
-        <v>-8.279999999999999</v>
+        <v>-6.74</v>
       </c>
       <c r="N91" t="b">
         <v>0</v>
@@ -5418,7 +5436,7 @@
         <v>23.8</v>
       </c>
       <c r="H92" t="n">
-        <v>13.23</v>
+        <v>8.32</v>
       </c>
       <c r="I92" t="n">
         <v>1.36</v>
@@ -5431,7 +5449,7 @@
         <v>-9.94</v>
       </c>
       <c r="M92" t="n">
-        <v>14.73</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="N92" t="b">
         <v>1</v>
@@ -5469,7 +5487,7 @@
         <v>38.9</v>
       </c>
       <c r="H93" t="n">
-        <v>-13.67</v>
+        <v>-11.99</v>
       </c>
       <c r="I93" t="n">
         <v>-9.220000000000001</v>
@@ -5482,7 +5500,7 @@
         <v>-9.83</v>
       </c>
       <c r="M93" t="n">
-        <v>-12.16</v>
+        <v>-10.66</v>
       </c>
       <c r="N93" t="b">
         <v>1</v>
@@ -5520,7 +5538,7 @@
         <v>32.1</v>
       </c>
       <c r="H94" t="n">
-        <v>43.28</v>
+        <v>39.11</v>
       </c>
       <c r="I94" t="n">
         <v>11.84</v>
@@ -5533,7 +5551,7 @@
         <v>-1.82</v>
       </c>
       <c r="M94" t="n">
-        <v>44.78</v>
+        <v>40.44</v>
       </c>
       <c r="N94" t="b">
         <v>0</v>
@@ -5571,7 +5589,7 @@
         <v>53.4</v>
       </c>
       <c r="H95" t="n">
-        <v>13.03</v>
+        <v>19.11</v>
       </c>
       <c r="I95" t="n">
         <v>2.75</v>
@@ -5584,7 +5602,7 @@
         <v>-2.31</v>
       </c>
       <c r="M95" t="n">
-        <v>14.83</v>
+        <v>20.74</v>
       </c>
       <c r="N95" t="b">
         <v>0</v>
@@ -5622,7 +5640,7 @@
         <v>54.1</v>
       </c>
       <c r="H96" t="n">
-        <v>14.8</v>
+        <v>21.97</v>
       </c>
       <c r="I96" t="n">
         <v>5.54</v>
@@ -5635,7 +5653,7 @@
         <v>-0.41</v>
       </c>
       <c r="M96" t="n">
-        <v>16.13</v>
+        <v>23.13</v>
       </c>
       <c r="N96" t="b">
         <v>0</v>
@@ -5673,7 +5691,7 @@
         <v>43.2</v>
       </c>
       <c r="H97" t="n">
-        <v>-23.97</v>
+        <v>-21.24</v>
       </c>
       <c r="I97" t="n">
         <v>-3.15</v>
@@ -5686,7 +5704,7 @@
         <v>-17.51</v>
       </c>
       <c r="M97" t="n">
-        <v>-22.64</v>
+        <v>-20.08</v>
       </c>
       <c r="N97" t="b">
         <v>1</v>
@@ -5724,7 +5742,7 @@
         <v>-8.199999999999999</v>
       </c>
       <c r="H98" t="n">
-        <v>-7.19</v>
+        <v>-6.9</v>
       </c>
       <c r="I98" t="n">
         <v>5.34</v>
@@ -5737,7 +5755,7 @@
         <v>-5.27</v>
       </c>
       <c r="M98" t="n">
-        <v>-5.86</v>
+        <v>-5.74</v>
       </c>
       <c r="N98" t="b">
         <v>1</v>
@@ -5775,7 +5793,7 @@
         <v>-1.2</v>
       </c>
       <c r="H99" t="n">
-        <v>-4.5</v>
+        <v>-3.71</v>
       </c>
       <c r="I99" t="n">
         <v>8.27</v>
@@ -5788,7 +5806,7 @@
         <v>-5.3</v>
       </c>
       <c r="M99" t="n">
-        <v>-3.21</v>
+        <v>-2.6</v>
       </c>
       <c r="N99" t="b">
         <v>0</v>
@@ -5826,7 +5844,7 @@
         <v>-23.9</v>
       </c>
       <c r="H100" t="n">
-        <v>-13.31</v>
+        <v>-13.22</v>
       </c>
       <c r="I100" t="n">
         <v>3.28</v>
@@ -5839,7 +5857,7 @@
         <v>-4.46</v>
       </c>
       <c r="M100" t="n">
-        <v>-12.26</v>
+        <v>-12.36</v>
       </c>
       <c r="N100" t="b">
         <v>1</v>
@@ -5881,7 +5899,7 @@
         <v>-6.1</v>
       </c>
       <c r="H101" t="n">
-        <v>-4.57</v>
+        <v>-5.02</v>
       </c>
       <c r="I101" t="n">
         <v>4.9</v>
@@ -5894,7 +5912,7 @@
         <v>-9</v>
       </c>
       <c r="M101" t="n">
-        <v>-3.53</v>
+        <v>-4.15</v>
       </c>
       <c r="N101" t="b">
         <v>1</v>
@@ -5932,7 +5950,7 @@
         <v>26.7</v>
       </c>
       <c r="H102" t="n">
-        <v>-1.31</v>
+        <v>-1.19</v>
       </c>
       <c r="I102" t="n">
         <v>-0.05</v>
@@ -5945,7 +5963,7 @@
         <v>-0.87</v>
       </c>
       <c r="M102" t="n">
-        <v>-0.26</v>
+        <v>-0.32</v>
       </c>
       <c r="N102" t="b">
         <v>1</v>
@@ -5983,7 +6001,7 @@
         <v>39.5</v>
       </c>
       <c r="H103" t="n">
-        <v>17.52</v>
+        <v>18.78</v>
       </c>
       <c r="I103" t="n">
         <v>-5.13</v>
@@ -5996,7 +6014,7 @@
         <v>-8.869999999999999</v>
       </c>
       <c r="M103" t="n">
-        <v>18.57</v>
+        <v>19.65</v>
       </c>
       <c r="N103" t="b">
         <v>0</v>
@@ -6034,7 +6052,7 @@
         <v>14.3</v>
       </c>
       <c r="H104" t="n">
-        <v>-1.42</v>
+        <v>-0.9</v>
       </c>
       <c r="I104" t="n">
         <v>-0.43</v>
@@ -6047,7 +6065,7 @@
         <v>-11.86</v>
       </c>
       <c r="M104" t="n">
-        <v>-0.38</v>
+        <v>-0.03</v>
       </c>
       <c r="N104" t="b">
         <v>0</v>
@@ -6085,7 +6103,7 @@
         <v>-11.3</v>
       </c>
       <c r="H105" t="n">
-        <v>-5.88</v>
+        <v>-4.06</v>
       </c>
       <c r="I105" t="n">
         <v>1.31</v>
@@ -6098,7 +6116,7 @@
         <v>-1.88</v>
       </c>
       <c r="M105" t="n">
-        <v>-4.83</v>
+        <v>-3.19</v>
       </c>
       <c r="N105" t="b">
         <v>0</v>
@@ -6136,7 +6154,7 @@
         <v>-23.5</v>
       </c>
       <c r="H106" t="n">
-        <v>-42.46</v>
+        <v>-35.73</v>
       </c>
       <c r="I106" t="n">
         <v>13.29</v>
@@ -6149,7 +6167,7 @@
         <v>-14.04</v>
       </c>
       <c r="M106" t="n">
-        <v>-41.41</v>
+        <v>-34.86</v>
       </c>
       <c r="N106" t="b">
         <v>0</v>
@@ -6187,7 +6205,7 @@
         <v>10.5</v>
       </c>
       <c r="H107" t="n">
-        <v>-7.08</v>
+        <v>-6.25</v>
       </c>
       <c r="I107" t="n">
         <v>-0.86</v>
@@ -6200,7 +6218,7 @@
         <v>-6.11</v>
       </c>
       <c r="M107" t="n">
-        <v>-6.03</v>
+        <v>-5.38</v>
       </c>
       <c r="N107" t="b">
         <v>0</v>
@@ -6238,7 +6256,7 @@
         <v>-3.5</v>
       </c>
       <c r="H108" t="n">
-        <v>0.54</v>
+        <v>1.25</v>
       </c>
       <c r="I108" t="n">
         <v>-4.95</v>
@@ -6251,7 +6269,7 @@
         <v>-8.43</v>
       </c>
       <c r="M108" t="n">
-        <v>1.39</v>
+        <v>1.91</v>
       </c>
       <c r="N108" t="b">
         <v>1</v>
@@ -6289,7 +6307,7 @@
         <v>-12.8</v>
       </c>
       <c r="H109" t="n">
-        <v>-0.03</v>
+        <v>0.98</v>
       </c>
       <c r="I109" t="n">
         <v>-1.74</v>
@@ -6302,7 +6320,7 @@
         <v>-2.97</v>
       </c>
       <c r="M109" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.65</v>
       </c>
       <c r="N109" t="b">
         <v>0</v>
@@ -6340,7 +6358,7 @@
         <v>2.4</v>
       </c>
       <c r="H110" t="n">
-        <v>16.86</v>
+        <v>18.72</v>
       </c>
       <c r="I110" t="n">
         <v>12.41</v>
@@ -6353,7 +6371,7 @@
         <v>-0.07000000000000001</v>
       </c>
       <c r="M110" t="n">
-        <v>17.7</v>
+        <v>19.39</v>
       </c>
       <c r="N110" t="b">
         <v>0</v>
@@ -6391,7 +6409,7 @@
         <v>-17.9</v>
       </c>
       <c r="H111" t="n">
-        <v>2.48</v>
+        <v>1.15</v>
       </c>
       <c r="I111" t="n">
         <v>-0.5</v>
@@ -6404,7 +6422,7 @@
         <v>-3.43</v>
       </c>
       <c r="M111" t="n">
-        <v>3.32</v>
+        <v>1.81</v>
       </c>
       <c r="N111" t="b">
         <v>1</v>
@@ -6442,7 +6460,7 @@
         <v>11.9</v>
       </c>
       <c r="H112" t="n">
-        <v>-9.66</v>
+        <v>-8.75</v>
       </c>
       <c r="I112" t="n">
         <v>6.88</v>
@@ -6455,7 +6473,7 @@
         <v>-10.93</v>
       </c>
       <c r="M112" t="n">
-        <v>-8.92</v>
+        <v>-8.19</v>
       </c>
       <c r="N112" t="b">
         <v>0</v>
@@ -6493,7 +6511,7 @@
         <v>53.5</v>
       </c>
       <c r="H113" t="n">
-        <v>-0.92</v>
+        <v>4.13</v>
       </c>
       <c r="I113" t="n">
         <v>1.23</v>
@@ -6506,7 +6524,7 @@
         <v>-7.57</v>
       </c>
       <c r="M113" t="n">
-        <v>-0.38</v>
+        <v>4.69</v>
       </c>
       <c r="N113" t="b">
         <v>1</v>
@@ -6544,7 +6562,7 @@
         <v>18.1</v>
       </c>
       <c r="H114" t="n">
-        <v>-1.66</v>
+        <v>-1.76</v>
       </c>
       <c r="I114" t="n">
         <v>-1.69</v>
@@ -6557,7 +6575,7 @@
         <v>-1.92</v>
       </c>
       <c r="M114" t="n">
-        <v>-0.92</v>
+        <v>-1.2</v>
       </c>
       <c r="N114" t="b">
         <v>0</v>
@@ -6595,7 +6613,7 @@
         <v>-1</v>
       </c>
       <c r="H115" t="n">
-        <v>-17.22</v>
+        <v>-14.52</v>
       </c>
       <c r="I115" t="n">
         <v>-6.26</v>
@@ -6608,7 +6626,7 @@
         <v>-15</v>
       </c>
       <c r="M115" t="n">
-        <v>-16.48</v>
+        <v>-13.96</v>
       </c>
       <c r="N115" t="b">
         <v>1</v>
@@ -6646,7 +6664,7 @@
         <v>29.7</v>
       </c>
       <c r="H116" t="n">
-        <v>10.45</v>
+        <v>7.22</v>
       </c>
       <c r="I116" t="n">
         <v>11.27</v>
@@ -6659,7 +6677,7 @@
         <v>0</v>
       </c>
       <c r="M116" t="n">
-        <v>11.19</v>
+        <v>7.78</v>
       </c>
       <c r="N116" t="b">
         <v>1</v>
@@ -6697,7 +6715,7 @@
         <v>15.2</v>
       </c>
       <c r="H117" t="n">
-        <v>-34.65</v>
+        <v>-35.32</v>
       </c>
       <c r="I117" t="n">
         <v>-8.77</v>
@@ -6710,7 +6728,7 @@
         <v>-24.79</v>
       </c>
       <c r="M117" t="n">
-        <v>-33.19</v>
+        <v>-34.03</v>
       </c>
       <c r="N117" t="b">
         <v>1</v>
@@ -6748,7 +6766,7 @@
         <v>22.2</v>
       </c>
       <c r="H118" t="n">
-        <v>6.16</v>
+        <v>4.51</v>
       </c>
       <c r="I118" t="n">
         <v>1.01</v>
@@ -6761,7 +6779,7 @@
         <v>-3.94</v>
       </c>
       <c r="M118" t="n">
-        <v>7.62</v>
+        <v>5.79</v>
       </c>
       <c r="N118" t="b">
         <v>1</v>
@@ -6799,7 +6817,7 @@
         <v>10.8</v>
       </c>
       <c r="H119" t="n">
-        <v>-0.71</v>
+        <v>-5.05</v>
       </c>
       <c r="I119" t="n">
         <v>5.62</v>
@@ -6812,7 +6830,7 @@
         <v>-1.59</v>
       </c>
       <c r="M119" t="n">
-        <v>0.75</v>
+        <v>-3.76</v>
       </c>
       <c r="N119" t="b">
         <v>0</v>
@@ -6850,7 +6868,7 @@
         <v>-2.1</v>
       </c>
       <c r="H120" t="n">
-        <v>-4.38</v>
+        <v>-5.54</v>
       </c>
       <c r="I120" t="n">
         <v>0.67</v>
@@ -6863,7 +6881,7 @@
         <v>-7.84</v>
       </c>
       <c r="M120" t="n">
-        <v>-2.92</v>
+        <v>-4.25</v>
       </c>
       <c r="N120" t="b">
         <v>0</v>
@@ -6901,7 +6919,7 @@
         <v>16.7</v>
       </c>
       <c r="H121" t="n">
-        <v>-19.41</v>
+        <v>-20.86</v>
       </c>
       <c r="I121" t="n">
         <v>-15.31</v>
@@ -6914,7 +6932,7 @@
         <v>-22</v>
       </c>
       <c r="M121" t="n">
-        <v>-19.92</v>
+        <v>-21.55</v>
       </c>
       <c r="N121" t="b">
         <v>0</v>
@@ -6952,7 +6970,7 @@
         <v>0.3</v>
       </c>
       <c r="H122" t="n">
-        <v>19</v>
+        <v>23.59</v>
       </c>
       <c r="I122" t="n">
         <v>6.01</v>
@@ -6965,7 +6983,7 @@
         <v>-3.85</v>
       </c>
       <c r="M122" t="n">
-        <v>16.98</v>
+        <v>21.39</v>
       </c>
       <c r="N122" t="b">
         <v>0</v>
@@ -7058,7 +7076,7 @@
         <v>10.5</v>
       </c>
       <c r="H124" t="n">
-        <v>-0.04</v>
+        <v>2.78</v>
       </c>
       <c r="I124" t="n">
         <v>1.99</v>
@@ -7071,7 +7089,7 @@
         <v>-6.27</v>
       </c>
       <c r="M124" t="n">
-        <v>-2.05</v>
+        <v>0.59</v>
       </c>
       <c r="N124" t="b">
         <v>1</v>
@@ -7109,7 +7127,7 @@
         <v>30.4</v>
       </c>
       <c r="H125" t="n">
-        <v>4.41</v>
+        <v>3.71</v>
       </c>
       <c r="I125" t="n">
         <v>8.539999999999999</v>
@@ -7122,7 +7140,7 @@
         <v>-0.44</v>
       </c>
       <c r="M125" t="n">
-        <v>2.4</v>
+        <v>1.52</v>
       </c>
       <c r="N125" t="b">
         <v>0</v>
@@ -7164,7 +7182,7 @@
         <v>-3.2</v>
       </c>
       <c r="H126" t="n">
-        <v>14.85</v>
+        <v>12.61</v>
       </c>
       <c r="I126" t="n">
         <v>15.28</v>
@@ -7177,7 +7195,7 @@
         <v>-2.53</v>
       </c>
       <c r="M126" t="n">
-        <v>12.83</v>
+        <v>10.41</v>
       </c>
       <c r="N126" t="b">
         <v>0</v>
@@ -7215,7 +7233,7 @@
         <v>-23.5</v>
       </c>
       <c r="H127" t="n">
-        <v>20.74</v>
+        <v>16.43</v>
       </c>
       <c r="I127" t="n">
         <v>20.48</v>
@@ -7228,7 +7246,7 @@
         <v>-2.25</v>
       </c>
       <c r="M127" t="n">
-        <v>18.73</v>
+        <v>14.24</v>
       </c>
       <c r="N127" t="b">
         <v>0</v>
@@ -7266,7 +7284,7 @@
         <v>-27.3</v>
       </c>
       <c r="H128" t="n">
-        <v>0.06</v>
+        <v>5.6</v>
       </c>
       <c r="I128" t="n">
         <v>-8.83</v>
@@ -7279,7 +7297,7 @@
         <v>-19.66</v>
       </c>
       <c r="M128" t="n">
-        <v>-1.95</v>
+        <v>3.4</v>
       </c>
       <c r="N128" t="b">
         <v>0</v>
@@ -7317,7 +7335,7 @@
         <v>-12.5</v>
       </c>
       <c r="H129" t="n">
-        <v>-9.59</v>
+        <v>-10.98</v>
       </c>
       <c r="I129" t="n">
         <v>21.54</v>
@@ -7330,7 +7348,7 @@
         <v>-0.95</v>
       </c>
       <c r="M129" t="n">
-        <v>-12.25</v>
+        <v>-13.83</v>
       </c>
       <c r="N129" t="b">
         <v>0</v>
@@ -7368,7 +7386,7 @@
         <v>-37</v>
       </c>
       <c r="H130" t="n">
-        <v>35.27</v>
+        <v>36.04</v>
       </c>
       <c r="I130" t="n">
         <v>18.38</v>
@@ -7381,7 +7399,7 @@
         <v>-5.11</v>
       </c>
       <c r="M130" t="n">
-        <v>32.61</v>
+        <v>33.19</v>
       </c>
       <c r="N130" t="b">
         <v>1</v>
@@ -7423,7 +7441,7 @@
         <v>-3.4</v>
       </c>
       <c r="H131" t="n">
-        <v>4.65</v>
+        <v>8.56</v>
       </c>
       <c r="I131" t="n">
         <v>30.48</v>
@@ -7436,7 +7454,7 @@
         <v>-0.9</v>
       </c>
       <c r="M131" t="n">
-        <v>1.98</v>
+        <v>5.71</v>
       </c>
       <c r="N131" t="b">
         <v>0</v>
@@ -7474,7 +7492,7 @@
         <v>-23.4</v>
       </c>
       <c r="H132" t="n">
-        <v>-11.25</v>
+        <v>-8.99</v>
       </c>
       <c r="I132" t="n">
         <v>-3.58</v>
@@ -7487,7 +7505,7 @@
         <v>-17.98</v>
       </c>
       <c r="M132" t="n">
-        <v>-13.92</v>
+        <v>-11.84</v>
       </c>
       <c r="N132" t="b">
         <v>0</v>
@@ -7525,7 +7543,7 @@
         <v>-28.9</v>
       </c>
       <c r="H133" t="n">
-        <v>-20.72</v>
+        <v>-20.53</v>
       </c>
       <c r="I133" t="n">
         <v>-12.9</v>
@@ -7538,7 +7556,7 @@
         <v>-23.19</v>
       </c>
       <c r="M133" t="n">
-        <v>-23.39</v>
+        <v>-23.37</v>
       </c>
       <c r="N133" t="b">
         <v>0</v>
@@ -7576,7 +7594,7 @@
         <v>-26.8</v>
       </c>
       <c r="H134" t="n">
-        <v>17.08</v>
+        <v>20.17</v>
       </c>
       <c r="I134" t="n">
         <v>4.56</v>
@@ -7589,7 +7607,7 @@
         <v>-4.09</v>
       </c>
       <c r="M134" t="n">
-        <v>14.42</v>
+        <v>17.32</v>
       </c>
       <c r="N134" t="b">
         <v>1</v>
@@ -7631,7 +7649,7 @@
         <v>-9.800000000000001</v>
       </c>
       <c r="H135" t="n">
-        <v>-27.67</v>
+        <v>-27.23</v>
       </c>
       <c r="I135" t="n">
         <v>-4.09</v>
@@ -7644,7 +7662,7 @@
         <v>-15.24</v>
       </c>
       <c r="M135" t="n">
-        <v>-31.54</v>
+        <v>-31.28</v>
       </c>
       <c r="N135" t="b">
         <v>0</v>
@@ -7682,7 +7700,7 @@
         <v>21</v>
       </c>
       <c r="H136" t="n">
-        <v>1.7</v>
+        <v>2.14</v>
       </c>
       <c r="I136" t="n">
         <v>-0.72</v>
@@ -7695,7 +7713,7 @@
         <v>-7.35</v>
       </c>
       <c r="M136" t="n">
-        <v>-2.17</v>
+        <v>-1.91</v>
       </c>
       <c r="N136" t="b">
         <v>0</v>
@@ -7733,7 +7751,7 @@
         <v>13.2</v>
       </c>
       <c r="H137" t="n">
-        <v>33.83</v>
+        <v>35.49</v>
       </c>
       <c r="I137" t="n">
         <v>8.130000000000001</v>
@@ -7746,7 +7764,7 @@
         <v>-2.36</v>
       </c>
       <c r="M137" t="n">
-        <v>29.97</v>
+        <v>31.44</v>
       </c>
       <c r="N137" t="b">
         <v>0</v>
@@ -7784,7 +7802,7 @@
         <v>6.1</v>
       </c>
       <c r="H138" t="n">
-        <v>-2.38</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="I138" t="n">
         <v>10.43</v>
@@ -7797,7 +7815,7 @@
         <v>-1.51</v>
       </c>
       <c r="M138" t="n">
-        <v>-6.25</v>
+        <v>-4.74</v>
       </c>
       <c r="N138" t="b">
         <v>0</v>
@@ -7835,7 +7853,7 @@
         <v>6.5</v>
       </c>
       <c r="H139" t="n">
-        <v>-12.13</v>
+        <v>-8.82</v>
       </c>
       <c r="I139" t="n">
         <v>-0.04</v>
@@ -7848,7 +7866,7 @@
         <v>-4.12</v>
       </c>
       <c r="M139" t="n">
-        <v>-16</v>
+        <v>-12.87</v>
       </c>
       <c r="N139" t="b">
         <v>0</v>
@@ -7886,7 +7904,7 @@
         <v>-36.5</v>
       </c>
       <c r="H140" t="n">
-        <v>-34.82</v>
+        <v>-35.19</v>
       </c>
       <c r="I140" t="n">
         <v>-27.75</v>
@@ -7899,7 +7917,7 @@
         <v>-31.28</v>
       </c>
       <c r="M140" t="n">
-        <v>-38.13</v>
+        <v>-38.69</v>
       </c>
       <c r="N140" t="b">
         <v>1</v>
@@ -7937,7 +7955,7 @@
         <v>-14.5</v>
       </c>
       <c r="H141" t="n">
-        <v>-14.63</v>
+        <v>-15.27</v>
       </c>
       <c r="I141" t="n">
         <v>4.48</v>
@@ -7950,7 +7968,7 @@
         <v>-3.33</v>
       </c>
       <c r="M141" t="n">
-        <v>-17.95</v>
+        <v>-18.77</v>
       </c>
       <c r="N141" t="b">
         <v>0</v>
@@ -7988,7 +8006,7 @@
         <v>1.7</v>
       </c>
       <c r="H142" t="n">
-        <v>-5.97</v>
+        <v>-6.67</v>
       </c>
       <c r="I142" t="n">
         <v>8.859999999999999</v>
@@ -8001,7 +8019,7 @@
         <v>-3.27</v>
       </c>
       <c r="M142" t="n">
-        <v>-9.289999999999999</v>
+        <v>-10.18</v>
       </c>
       <c r="N142" t="b">
         <v>0</v>
@@ -8039,7 +8057,7 @@
         <v>48.1</v>
       </c>
       <c r="H143" t="n">
-        <v>-1.71</v>
+        <v>-2.19</v>
       </c>
       <c r="I143" t="n">
         <v>0.16</v>
@@ -8052,7 +8070,7 @@
         <v>-8.890000000000001</v>
       </c>
       <c r="M143" t="n">
-        <v>-5.03</v>
+        <v>-5.7</v>
       </c>
       <c r="N143" t="b">
         <v>0</v>
@@ -8090,7 +8108,7 @@
         <v>-38.7</v>
       </c>
       <c r="H144" t="n">
-        <v>5.26</v>
+        <v>6.49</v>
       </c>
       <c r="I144" t="n">
         <v>17.17</v>
@@ -8103,7 +8121,7 @@
         <v>-0.54</v>
       </c>
       <c r="M144" t="n">
-        <v>1.94</v>
+        <v>2.99</v>
       </c>
       <c r="N144" t="b">
         <v>1</v>
@@ -8141,7 +8159,7 @@
         <v>24.9</v>
       </c>
       <c r="H145" t="n">
-        <v>-1.6</v>
+        <v>-3.08</v>
       </c>
       <c r="I145" t="n">
         <v>10.45</v>
@@ -8154,7 +8172,7 @@
         <v>-0.49</v>
       </c>
       <c r="M145" t="n">
-        <v>-4.92</v>
+        <v>-6.58</v>
       </c>
       <c r="N145" t="b">
         <v>0</v>
@@ -8192,7 +8210,7 @@
         <v>-34.6</v>
       </c>
       <c r="H146" t="n">
-        <v>13.53</v>
+        <v>17.45</v>
       </c>
       <c r="I146" t="n">
         <v>6.67</v>
@@ -8205,7 +8223,7 @@
         <v>-3.06</v>
       </c>
       <c r="M146" t="n">
-        <v>10.21</v>
+        <v>13.95</v>
       </c>
       <c r="N146" t="b">
         <v>1</v>
@@ -8243,7 +8261,7 @@
         <v>-21.4</v>
       </c>
       <c r="H147" t="n">
-        <v>-3.62</v>
+        <v>-6.01</v>
       </c>
       <c r="I147" t="n">
         <v>2.8</v>
@@ -8256,7 +8274,7 @@
         <v>-2.27</v>
       </c>
       <c r="M147" t="n">
-        <v>-6.93</v>
+        <v>-9.51</v>
       </c>
       <c r="N147" t="b">
         <v>0</v>
@@ -8294,7 +8312,7 @@
         <v>-11.8</v>
       </c>
       <c r="H148" t="n">
-        <v>-6.27</v>
+        <v>-5.01</v>
       </c>
       <c r="I148" t="n">
         <v>9.76</v>
@@ -8307,7 +8325,7 @@
         <v>-1.63</v>
       </c>
       <c r="M148" t="n">
-        <v>-9.699999999999999</v>
+        <v>-8.619999999999999</v>
       </c>
       <c r="N148" t="b">
         <v>1</v>
@@ -8345,7 +8363,7 @@
         <v>0.1</v>
       </c>
       <c r="H149" t="n">
-        <v>-14.74</v>
+        <v>-11.54</v>
       </c>
       <c r="I149" t="n">
         <v>-2.83</v>
@@ -8358,7 +8376,7 @@
         <v>-5.45</v>
       </c>
       <c r="M149" t="n">
-        <v>-18.17</v>
+        <v>-15.15</v>
       </c>
       <c r="N149" t="b">
         <v>1</v>
@@ -8396,7 +8414,7 @@
         <v>-13.8</v>
       </c>
       <c r="H150" t="n">
-        <v>10.79</v>
+        <v>24.95</v>
       </c>
       <c r="I150" t="n">
         <v>4.67</v>
@@ -8409,7 +8427,7 @@
         <v>-5.7</v>
       </c>
       <c r="M150" t="n">
-        <v>7.36</v>
+        <v>21.34</v>
       </c>
       <c r="N150" t="b">
         <v>0</v>
@@ -8451,7 +8469,7 @@
         <v>-8.800000000000001</v>
       </c>
       <c r="H151" t="n">
-        <v>-0.76</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="I151" t="n">
         <v>15.97</v>
@@ -8464,7 +8482,7 @@
         <v>-0.79</v>
       </c>
       <c r="M151" t="n">
-        <v>-4.19</v>
+        <v>-3.05</v>
       </c>
       <c r="N151" t="b">
         <v>0</v>
@@ -8502,7 +8520,7 @@
         <v>24.1</v>
       </c>
       <c r="H152" t="n">
-        <v>-11.21</v>
+        <v>-7.05</v>
       </c>
       <c r="I152" t="n">
         <v>-8.31</v>
@@ -8515,7 +8533,7 @@
         <v>-18.31</v>
       </c>
       <c r="M152" t="n">
-        <v>-13.85</v>
+        <v>-9.869999999999999</v>
       </c>
       <c r="N152" t="b">
         <v>1</v>
@@ -8553,7 +8571,7 @@
         <v>-15.9</v>
       </c>
       <c r="H153" t="n">
-        <v>0.16</v>
+        <v>2.66</v>
       </c>
       <c r="I153" t="n">
         <v>10.45</v>
@@ -8566,7 +8584,7 @@
         <v>-0.31</v>
       </c>
       <c r="M153" t="n">
-        <v>-2.48</v>
+        <v>-0.15</v>
       </c>
       <c r="N153" t="b">
         <v>1</v>
@@ -8604,7 +8622,7 @@
         <v>-23.3</v>
       </c>
       <c r="H154" t="n">
-        <v>-9.51</v>
+        <v>-15.21</v>
       </c>
       <c r="I154" t="n">
         <v>-20.42</v>
@@ -8617,7 +8635,7 @@
         <v>-27.45</v>
       </c>
       <c r="M154" t="n">
-        <v>-12.14</v>
+        <v>-18.03</v>
       </c>
       <c r="N154" t="b">
         <v>0</v>
@@ -8655,7 +8673,7 @@
         <v>28.9</v>
       </c>
       <c r="H155" t="n">
-        <v>-4.22</v>
+        <v>-3.21</v>
       </c>
       <c r="I155" t="n">
         <v>8.06</v>
@@ -8668,7 +8686,7 @@
         <v>-2.79</v>
       </c>
       <c r="M155" t="n">
-        <v>-7.74</v>
+        <v>-6.92</v>
       </c>
       <c r="N155" t="b">
         <v>0</v>
@@ -8706,7 +8724,7 @@
         <v>40.1</v>
       </c>
       <c r="H156" t="n">
-        <v>43.11</v>
+        <v>43.83</v>
       </c>
       <c r="I156" t="n">
         <v>15.9</v>
@@ -8719,7 +8737,7 @@
         <v>-5.87</v>
       </c>
       <c r="M156" t="n">
-        <v>39.59</v>
+        <v>40.13</v>
       </c>
       <c r="N156" t="b">
         <v>0</v>
@@ -8757,7 +8775,7 @@
         <v>-27.3</v>
       </c>
       <c r="H157" t="n">
-        <v>6.56</v>
+        <v>2.59</v>
       </c>
       <c r="I157" t="n">
         <v>0.75</v>
@@ -8770,7 +8788,7 @@
         <v>-5.46</v>
       </c>
       <c r="M157" t="n">
-        <v>3.16</v>
+        <v>-1</v>
       </c>
       <c r="N157" t="b">
         <v>0</v>
@@ -8808,7 +8826,7 @@
         <v>19.7</v>
       </c>
       <c r="H158" t="n">
-        <v>-14.32</v>
+        <v>-13.85</v>
       </c>
       <c r="I158" t="n">
         <v>-4.49</v>
@@ -8821,7 +8839,7 @@
         <v>-13.7</v>
       </c>
       <c r="M158" t="n">
-        <v>-17.72</v>
+        <v>-17.44</v>
       </c>
       <c r="N158" t="b">
         <v>0</v>
@@ -8859,7 +8877,7 @@
         <v>-21.3</v>
       </c>
       <c r="H159" t="n">
-        <v>-6.93</v>
+        <v>-6.22</v>
       </c>
       <c r="I159" t="n">
         <v>7.16</v>
@@ -8872,7 +8890,7 @@
         <v>-11.9</v>
       </c>
       <c r="M159" t="n">
-        <v>-10.33</v>
+        <v>-9.800000000000001</v>
       </c>
       <c r="N159" t="b">
         <v>0</v>
@@ -8910,7 +8928,7 @@
         <v>-21.8</v>
       </c>
       <c r="H160" t="n">
-        <v>-29.89</v>
+        <v>-32.09</v>
       </c>
       <c r="I160" t="n">
         <v>-18.97</v>
@@ -8923,7 +8941,7 @@
         <v>-26.82</v>
       </c>
       <c r="M160" t="n">
-        <v>-33.29</v>
+        <v>-35.68</v>
       </c>
       <c r="N160" t="b">
         <v>1</v>
@@ -8961,7 +8979,7 @@
         <v>-37.6</v>
       </c>
       <c r="H161" t="n">
-        <v>-11.14</v>
+        <v>-10.87</v>
       </c>
       <c r="I161" t="n">
         <v>15.2</v>
@@ -8974,7 +8992,7 @@
         <v>-10.3</v>
       </c>
       <c r="M161" t="n">
-        <v>-13.53</v>
+        <v>-13.45</v>
       </c>
       <c r="N161" t="b">
         <v>0</v>
@@ -9012,7 +9030,7 @@
         <v>53.8</v>
       </c>
       <c r="H162" t="n">
-        <v>48.03</v>
+        <v>50.52</v>
       </c>
       <c r="I162" t="n">
         <v>4.09</v>
@@ -9025,7 +9043,7 @@
         <v>-8.66</v>
       </c>
       <c r="M162" t="n">
-        <v>45.63</v>
+        <v>47.94</v>
       </c>
       <c r="N162" t="b">
         <v>0</v>
@@ -9067,7 +9085,7 @@
         <v>-5.7</v>
       </c>
       <c r="H163" t="n">
-        <v>36.07</v>
+        <v>44.98</v>
       </c>
       <c r="I163" t="n">
         <v>17.92</v>
@@ -9080,7 +9098,7 @@
         <v>-7.48</v>
       </c>
       <c r="M163" t="n">
-        <v>33.67</v>
+        <v>42.4</v>
       </c>
       <c r="N163" t="b">
         <v>0</v>
@@ -9118,7 +9136,7 @@
         <v>-39.3</v>
       </c>
       <c r="H164" t="n">
-        <v>-6.4</v>
+        <v>-4</v>
       </c>
       <c r="I164" t="n">
         <v>11.34</v>
@@ -9131,7 +9149,7 @@
         <v>-5.3</v>
       </c>
       <c r="M164" t="n">
-        <v>-8.789999999999999</v>
+        <v>-6.58</v>
       </c>
       <c r="N164" t="b">
         <v>0</v>
@@ -9169,7 +9187,7 @@
         <v>57</v>
       </c>
       <c r="H165" t="n">
-        <v>15.54</v>
+        <v>21.33</v>
       </c>
       <c r="I165" t="n">
         <v>-11.21</v>
@@ -9182,7 +9200,7 @@
         <v>-13.87</v>
       </c>
       <c r="M165" t="n">
-        <v>13.14</v>
+        <v>18.75</v>
       </c>
       <c r="N165" t="b">
         <v>1</v>
@@ -9220,7 +9238,7 @@
         <v>-21.8</v>
       </c>
       <c r="H166" t="n">
-        <v>5.69</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="I166" t="n">
         <v>1.71</v>
@@ -9233,7 +9251,7 @@
         <v>-6.18</v>
       </c>
       <c r="M166" t="n">
-        <v>3.29</v>
+        <v>6.95</v>
       </c>
       <c r="N166" t="b">
         <v>1</v>
@@ -9271,7 +9289,7 @@
         <v>1</v>
       </c>
       <c r="H167" t="n">
-        <v>-33.12</v>
+        <v>-33.47</v>
       </c>
       <c r="I167" t="n">
         <v>-11.52</v>
@@ -9284,7 +9302,7 @@
         <v>-16.26</v>
       </c>
       <c r="M167" t="n">
-        <v>-35.57</v>
+        <v>-36.09</v>
       </c>
       <c r="N167" t="b">
         <v>1</v>
@@ -9322,7 +9340,7 @@
         <v>45.4</v>
       </c>
       <c r="H168" t="n">
-        <v>1.47</v>
+        <v>2.41</v>
       </c>
       <c r="I168" t="n">
         <v>-1.72</v>
@@ -9335,7 +9353,7 @@
         <v>-23.15</v>
       </c>
       <c r="M168" t="n">
-        <v>-0.98</v>
+        <v>-0.22</v>
       </c>
       <c r="N168" t="b">
         <v>1</v>
@@ -9373,7 +9391,7 @@
         <v>49.6</v>
       </c>
       <c r="H169" t="n">
-        <v>28.53</v>
+        <v>30.41</v>
       </c>
       <c r="I169" t="n">
         <v>6.34</v>
@@ -9386,7 +9404,7 @@
         <v>-20.75</v>
       </c>
       <c r="M169" t="n">
-        <v>26.09</v>
+        <v>27.79</v>
       </c>
       <c r="N169" t="b">
         <v>0</v>
@@ -9424,7 +9442,7 @@
         <v>55.3</v>
       </c>
       <c r="H170" t="n">
-        <v>-14.03</v>
+        <v>-12.5</v>
       </c>
       <c r="I170" t="n">
         <v>3.73</v>
@@ -9437,7 +9455,7 @@
         <v>-22.94</v>
       </c>
       <c r="M170" t="n">
-        <v>-16.48</v>
+        <v>-15.13</v>
       </c>
       <c r="N170" t="b">
         <v>0</v>
@@ -9475,7 +9493,7 @@
         <v>76.5</v>
       </c>
       <c r="H171" t="n">
-        <v>15.1</v>
+        <v>18.26</v>
       </c>
       <c r="I171" t="n">
         <v>-5.56</v>
@@ -9488,7 +9506,7 @@
         <v>-33.97</v>
       </c>
       <c r="M171" t="n">
-        <v>12.65</v>
+        <v>15.63</v>
       </c>
       <c r="N171" t="b">
         <v>1</v>
@@ -9526,7 +9544,7 @@
         <v>77.90000000000001</v>
       </c>
       <c r="H172" t="n">
-        <v>15.1</v>
+        <v>18.59</v>
       </c>
       <c r="I172" t="n">
         <v>-3.53</v>
@@ -9539,7 +9557,7 @@
         <v>-20.26</v>
       </c>
       <c r="M172" t="n">
-        <v>12.66</v>
+        <v>15.97</v>
       </c>
       <c r="N172" t="b">
         <v>0</v>
@@ -9577,7 +9595,7 @@
         <v>57.6</v>
       </c>
       <c r="H173" t="n">
-        <v>40.37</v>
+        <v>41.89</v>
       </c>
       <c r="I173" t="n">
         <v>14.81</v>
@@ -9590,7 +9608,7 @@
         <v>-5.11</v>
       </c>
       <c r="M173" t="n">
-        <v>37.93</v>
+        <v>39.26</v>
       </c>
       <c r="N173" t="b">
         <v>0</v>
@@ -9628,7 +9646,7 @@
         <v>32.1</v>
       </c>
       <c r="H174" t="n">
-        <v>22.19</v>
+        <v>20.32</v>
       </c>
       <c r="I174" t="n">
         <v>16.93</v>
@@ -9641,7 +9659,7 @@
         <v>-24.48</v>
       </c>
       <c r="M174" t="n">
-        <v>19.74</v>
+        <v>17.7</v>
       </c>
       <c r="N174" t="b">
         <v>1</v>
@@ -9679,7 +9697,7 @@
         <v>51.8</v>
       </c>
       <c r="H175" t="n">
-        <v>9.01</v>
+        <v>9.15</v>
       </c>
       <c r="I175" t="n">
         <v>10.75</v>
@@ -9692,7 +9710,7 @@
         <v>-25.09</v>
       </c>
       <c r="M175" t="n">
-        <v>6.56</v>
+        <v>6.52</v>
       </c>
       <c r="N175" t="b">
         <v>1</v>
@@ -9730,7 +9748,7 @@
         <v>32.3</v>
       </c>
       <c r="H176" t="n">
-        <v>-28.05</v>
+        <v>-26.1</v>
       </c>
       <c r="I176" t="n">
         <v>-20.76</v>
@@ -9743,7 +9761,7 @@
         <v>-27.91</v>
       </c>
       <c r="M176" t="n">
-        <v>-30.49</v>
+        <v>-28.72</v>
       </c>
       <c r="N176" t="b">
         <v>1</v>
@@ -9781,7 +9799,7 @@
         <v>15.7</v>
       </c>
       <c r="H177" t="n">
-        <v>-4.5</v>
+        <v>-0.36</v>
       </c>
       <c r="I177" t="n">
         <v>-0.87</v>
@@ -9794,7 +9812,7 @@
         <v>-29.01</v>
       </c>
       <c r="M177" t="n">
-        <v>-6.94</v>
+        <v>-2.98</v>
       </c>
       <c r="N177" t="b">
         <v>0</v>
@@ -9832,7 +9850,7 @@
         <v>63.7</v>
       </c>
       <c r="H178" t="n">
-        <v>6.84</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="I178" t="n">
         <v>-2.16</v>
@@ -9845,7 +9863,7 @@
         <v>-19.1</v>
       </c>
       <c r="M178" t="n">
-        <v>4.39</v>
+        <v>6.9</v>
       </c>
       <c r="N178" t="b">
         <v>0</v>
@@ -9883,7 +9901,7 @@
         <v>3.7</v>
       </c>
       <c r="H179" t="n">
-        <v>-8.390000000000001</v>
+        <v>-9.9</v>
       </c>
       <c r="I179" t="n">
         <v>-1.11</v>
@@ -9896,7 +9914,7 @@
         <v>-25.46</v>
       </c>
       <c r="M179" t="n">
-        <v>-10.84</v>
+        <v>-12.53</v>
       </c>
       <c r="N179" t="b">
         <v>1</v>
@@ -9934,7 +9952,7 @@
         <v>42.4</v>
       </c>
       <c r="H180" t="n">
-        <v>5.73</v>
+        <v>10.81</v>
       </c>
       <c r="I180" t="n">
         <v>2.16</v>
@@ -9947,7 +9965,7 @@
         <v>-15.76</v>
       </c>
       <c r="M180" t="n">
-        <v>3.29</v>
+        <v>8.19</v>
       </c>
       <c r="N180" t="b">
         <v>1</v>
@@ -9985,7 +10003,7 @@
         <v>28.2</v>
       </c>
       <c r="H181" t="n">
-        <v>2.19</v>
+        <v>9.17</v>
       </c>
       <c r="I181" t="n">
         <v>-1.71</v>
@@ -9998,7 +10016,7 @@
         <v>-23.43</v>
       </c>
       <c r="M181" t="n">
-        <v>-0.25</v>
+        <v>6.54</v>
       </c>
       <c r="N181" t="b">
         <v>1</v>
@@ -10036,7 +10054,7 @@
         <v>28.6</v>
       </c>
       <c r="H182" t="n">
-        <v>31.17</v>
+        <v>40.09</v>
       </c>
       <c r="I182" t="n">
         <v>2.81</v>
@@ -10049,7 +10067,7 @@
         <v>-18.87</v>
       </c>
       <c r="M182" t="n">
-        <v>28.73</v>
+        <v>37.46</v>
       </c>
       <c r="N182" t="b">
         <v>1</v>
@@ -10087,7 +10105,7 @@
         <v>89.09999999999999</v>
       </c>
       <c r="H183" t="n">
-        <v>36.36</v>
+        <v>37.32</v>
       </c>
       <c r="I183" t="n">
         <v>18.45</v>
@@ -10100,7 +10118,7 @@
         <v>-9.029999999999999</v>
       </c>
       <c r="M183" t="n">
-        <v>33.92</v>
+        <v>34.7</v>
       </c>
       <c r="N183" t="b">
         <v>0</v>
@@ -10138,7 +10156,7 @@
         <v>50.5</v>
       </c>
       <c r="H184" t="n">
-        <v>16.51</v>
+        <v>16.29</v>
       </c>
       <c r="I184" t="n">
         <v>-2.26</v>
@@ -10151,7 +10169,7 @@
         <v>-20.74</v>
       </c>
       <c r="M184" t="n">
-        <v>14.07</v>
+        <v>13.66</v>
       </c>
       <c r="N184" t="b">
         <v>0</v>
@@ -10189,7 +10207,7 @@
         <v>33.1</v>
       </c>
       <c r="H185" t="n">
-        <v>19.69</v>
+        <v>28.87</v>
       </c>
       <c r="I185" t="n">
         <v>4.68</v>
@@ -10202,7 +10220,7 @@
         <v>-26.7</v>
       </c>
       <c r="M185" t="n">
-        <v>17.24</v>
+        <v>26.24</v>
       </c>
       <c r="N185" t="b">
         <v>1</v>
@@ -10240,7 +10258,7 @@
         <v>46.3</v>
       </c>
       <c r="H186" t="n">
-        <v>-9.390000000000001</v>
+        <v>-6.21</v>
       </c>
       <c r="I186" t="n">
         <v>-3.24</v>
@@ -10253,7 +10271,7 @@
         <v>-22.77</v>
       </c>
       <c r="M186" t="n">
-        <v>-11.83</v>
+        <v>-8.84</v>
       </c>
       <c r="N186" t="b">
         <v>0</v>
@@ -10291,7 +10309,7 @@
         <v>-13.8</v>
       </c>
       <c r="H187" t="n">
-        <v>9.609999999999999</v>
+        <v>12.82</v>
       </c>
       <c r="I187" t="n">
         <v>6.03</v>
@@ -10304,7 +10322,7 @@
         <v>-13.77</v>
       </c>
       <c r="M187" t="n">
-        <v>7.17</v>
+        <v>10.2</v>
       </c>
       <c r="N187" t="b">
         <v>0</v>
@@ -10342,7 +10360,7 @@
         <v>21.8</v>
       </c>
       <c r="H188" t="n">
-        <v>-13.36</v>
+        <v>-10.78</v>
       </c>
       <c r="I188" t="n">
         <v>-6.34</v>
@@ -10355,7 +10373,7 @@
         <v>-30.04</v>
       </c>
       <c r="M188" t="n">
-        <v>-15.8</v>
+        <v>-13.4</v>
       </c>
       <c r="N188" t="b">
         <v>1</v>
@@ -10393,7 +10411,7 @@
         <v>40.3</v>
       </c>
       <c r="H189" t="n">
-        <v>-12.12</v>
+        <v>-9.890000000000001</v>
       </c>
       <c r="I189" t="n">
         <v>1.24</v>
@@ -10406,7 +10424,7 @@
         <v>-20.5</v>
       </c>
       <c r="M189" t="n">
-        <v>-14.56</v>
+        <v>-12.52</v>
       </c>
       <c r="N189" t="b">
         <v>1</v>
@@ -10444,7 +10462,7 @@
         <v>36.6</v>
       </c>
       <c r="H190" t="n">
-        <v>223.59</v>
+        <v>217.49</v>
       </c>
       <c r="I190" t="n">
         <v>-4.23</v>
@@ -10457,7 +10475,7 @@
         <v>-11.51</v>
       </c>
       <c r="M190" t="n">
-        <v>221.15</v>
+        <v>214.87</v>
       </c>
       <c r="N190" t="b">
         <v>0</v>
@@ -10495,7 +10513,7 @@
         <v>24.1</v>
       </c>
       <c r="H191" t="n">
-        <v>10.04</v>
+        <v>14.57</v>
       </c>
       <c r="I191" t="n">
         <v>-1.6</v>
@@ -10508,7 +10526,7 @@
         <v>-22.54</v>
       </c>
       <c r="M191" t="n">
-        <v>7.59</v>
+        <v>11.94</v>
       </c>
       <c r="N191" t="b">
         <v>1</v>
@@ -10546,7 +10564,7 @@
         <v>50.3</v>
       </c>
       <c r="H192" t="n">
-        <v>-17.73</v>
+        <v>-17.49</v>
       </c>
       <c r="I192" t="n">
         <v>-3.34</v>
@@ -10559,7 +10577,7 @@
         <v>-23.32</v>
       </c>
       <c r="M192" t="n">
-        <v>-20.18</v>
+        <v>-20.11</v>
       </c>
       <c r="N192" t="b">
         <v>0</v>
@@ -10597,7 +10615,7 @@
         <v>24.5</v>
       </c>
       <c r="H193" t="n">
-        <v>-26.19</v>
+        <v>-26.13</v>
       </c>
       <c r="I193" t="n">
         <v>-12.99</v>
@@ -10610,7 +10628,7 @@
         <v>-22.54</v>
       </c>
       <c r="M193" t="n">
-        <v>-28.64</v>
+        <v>-28.76</v>
       </c>
       <c r="N193" t="b">
         <v>1</v>
@@ -10648,7 +10666,7 @@
         <v>-4</v>
       </c>
       <c r="H194" t="n">
-        <v>-5.11</v>
+        <v>-6.11</v>
       </c>
       <c r="I194" t="n">
         <v>-1.59</v>
@@ -10661,7 +10679,7 @@
         <v>-25.38</v>
       </c>
       <c r="M194" t="n">
-        <v>-7.55</v>
+        <v>-8.74</v>
       </c>
       <c r="N194" t="b">
         <v>0</v>
@@ -10699,7 +10717,7 @@
         <v>14.8</v>
       </c>
       <c r="H195" t="n">
-        <v>-36.26</v>
+        <v>-38.26</v>
       </c>
       <c r="I195" t="n">
         <v>-2.48</v>
@@ -10712,7 +10730,7 @@
         <v>-40.98</v>
       </c>
       <c r="M195" t="n">
-        <v>-38.7</v>
+        <v>-40.89</v>
       </c>
       <c r="N195" t="b">
         <v>0</v>
@@ -10750,7 +10768,7 @@
         <v>-27.6</v>
       </c>
       <c r="H196" t="n">
-        <v>1.64</v>
+        <v>0.29</v>
       </c>
       <c r="I196" t="n">
         <v>-0.36</v>
@@ -10763,7 +10781,7 @@
         <v>-19.41</v>
       </c>
       <c r="M196" t="n">
-        <v>-0.8</v>
+        <v>-2.34</v>
       </c>
       <c r="N196" t="b">
         <v>0</v>
@@ -10801,7 +10819,7 @@
         <v>9.1</v>
       </c>
       <c r="H197" t="n">
-        <v>-23.83</v>
+        <v>-23.26</v>
       </c>
       <c r="I197" t="n">
         <v>-2.83</v>
@@ -10814,7 +10832,7 @@
         <v>-23.78</v>
       </c>
       <c r="M197" t="n">
-        <v>-26.27</v>
+        <v>-25.89</v>
       </c>
       <c r="N197" t="b">
         <v>0</v>
@@ -10852,7 +10870,7 @@
         <v>11</v>
       </c>
       <c r="H198" t="n">
-        <v>-11.54</v>
+        <v>-4.67</v>
       </c>
       <c r="I198" t="n">
         <v>3.38</v>
@@ -10865,7 +10883,7 @@
         <v>-18.71</v>
       </c>
       <c r="M198" t="n">
-        <v>-13.98</v>
+        <v>-7.29</v>
       </c>
       <c r="N198" t="b">
         <v>0</v>
@@ -10903,7 +10921,7 @@
         <v>31.2</v>
       </c>
       <c r="H199" t="n">
-        <v>-11.4</v>
+        <v>-8.94</v>
       </c>
       <c r="I199" t="n">
         <v>-11.26</v>
@@ -10916,7 +10934,7 @@
         <v>-22.9</v>
       </c>
       <c r="M199" t="n">
-        <v>-13.84</v>
+        <v>-11.57</v>
       </c>
       <c r="N199" t="b">
         <v>0</v>
@@ -10954,7 +10972,7 @@
         <v>19.3</v>
       </c>
       <c r="H200" t="n">
-        <v>11.1</v>
+        <v>15.22</v>
       </c>
       <c r="I200" t="n">
         <v>11.79</v>
@@ -10967,7 +10985,7 @@
         <v>-16.62</v>
       </c>
       <c r="M200" t="n">
-        <v>8.65</v>
+        <v>12.6</v>
       </c>
       <c r="N200" t="b">
         <v>1</v>
@@ -11005,7 +11023,7 @@
         <v>-8.699999999999999</v>
       </c>
       <c r="H201" t="n">
-        <v>-9.619999999999999</v>
+        <v>-12.16</v>
       </c>
       <c r="I201" t="n">
         <v>17.25</v>
@@ -11018,7 +11036,7 @@
         <v>-4.65</v>
       </c>
       <c r="M201" t="n">
-        <v>-12.06</v>
+        <v>-14.79</v>
       </c>
       <c r="N201" t="b">
         <v>1</v>
@@ -11056,7 +11074,7 @@
         <v>15.2</v>
       </c>
       <c r="H202" t="n">
-        <v>-6.33</v>
+        <v>3.88</v>
       </c>
       <c r="I202" t="n">
         <v>5.36</v>
@@ -11069,7 +11087,7 @@
         <v>-28.18</v>
       </c>
       <c r="M202" t="n">
-        <v>-8.77</v>
+        <v>1.26</v>
       </c>
       <c r="N202" t="b">
         <v>1</v>
@@ -11107,7 +11125,7 @@
         <v>37.2</v>
       </c>
       <c r="H203" t="n">
-        <v>-23.52</v>
+        <v>-21.82</v>
       </c>
       <c r="I203" t="n">
         <v>-7.64</v>
@@ -11120,7 +11138,7 @@
         <v>-26.24</v>
       </c>
       <c r="M203" t="n">
-        <v>-25.96</v>
+        <v>-24.45</v>
       </c>
       <c r="N203" t="b">
         <v>1</v>
@@ -11162,7 +11180,7 @@
         <v>-0.5</v>
       </c>
       <c r="H204" t="n">
-        <v>29.6</v>
+        <v>33.6</v>
       </c>
       <c r="I204" t="n">
         <v>12.75</v>
@@ -11175,7 +11193,7 @@
         <v>-4.72</v>
       </c>
       <c r="M204" t="n">
-        <v>27.15</v>
+        <v>30.98</v>
       </c>
       <c r="N204" t="b">
         <v>0</v>
@@ -11213,7 +11231,7 @@
         <v>-27.9</v>
       </c>
       <c r="H205" t="n">
-        <v>-20.29</v>
+        <v>-22.82</v>
       </c>
       <c r="I205" t="n">
         <v>-5.72</v>
@@ -11226,7 +11244,7 @@
         <v>-11.08</v>
       </c>
       <c r="M205" t="n">
-        <v>-22.73</v>
+        <v>-25.45</v>
       </c>
       <c r="N205" t="b">
         <v>0</v>
@@ -11264,7 +11282,7 @@
         <v>29.8</v>
       </c>
       <c r="H206" t="n">
-        <v>34.3</v>
+        <v>40.5</v>
       </c>
       <c r="I206" t="n">
         <v>-2.74</v>
@@ -11277,7 +11295,7 @@
         <v>-22.36</v>
       </c>
       <c r="M206" t="n">
-        <v>31.86</v>
+        <v>37.88</v>
       </c>
       <c r="N206" t="b">
         <v>1</v>
@@ -11315,7 +11333,7 @@
         <v>60.9</v>
       </c>
       <c r="H207" t="n">
-        <v>3.37</v>
+        <v>3.3</v>
       </c>
       <c r="I207" t="n">
         <v>6.71</v>
@@ -11328,7 +11346,7 @@
         <v>-4.9</v>
       </c>
       <c r="M207" t="n">
-        <v>0.93</v>
+        <v>0.68</v>
       </c>
       <c r="N207" t="b">
         <v>0</v>
@@ -11366,7 +11384,7 @@
         <v>-13.4</v>
       </c>
       <c r="H208" t="n">
-        <v>-27.64</v>
+        <v>-28.74</v>
       </c>
       <c r="I208" t="n">
         <v>0.79</v>
@@ -11379,7 +11397,7 @@
         <v>-15.41</v>
       </c>
       <c r="M208" t="n">
-        <v>-30.08</v>
+        <v>-31.37</v>
       </c>
       <c r="N208" t="b">
         <v>0</v>
@@ -11417,7 +11435,7 @@
         <v>18.2</v>
       </c>
       <c r="H209" t="n">
-        <v>-15.57</v>
+        <v>-12.05</v>
       </c>
       <c r="I209" t="n">
         <v>-11.28</v>
@@ -11430,7 +11448,7 @@
         <v>-16.87</v>
       </c>
       <c r="M209" t="n">
-        <v>-18.02</v>
+        <v>-14.67</v>
       </c>
       <c r="N209" t="b">
         <v>0</v>
@@ -11468,7 +11486,7 @@
         <v>31.2</v>
       </c>
       <c r="H210" t="n">
-        <v>0.22</v>
+        <v>3.76</v>
       </c>
       <c r="I210" t="n">
         <v>-3.17</v>
@@ -11481,7 +11499,7 @@
         <v>-23.66</v>
       </c>
       <c r="M210" t="n">
-        <v>-2.22</v>
+        <v>1.13</v>
       </c>
       <c r="N210" t="b">
         <v>0</v>
@@ -11519,7 +11537,7 @@
         <v>-1.3</v>
       </c>
       <c r="H211" t="n">
-        <v>-16.84</v>
+        <v>-17.27</v>
       </c>
       <c r="I211" t="n">
         <v>5.29</v>
@@ -11532,7 +11550,7 @@
         <v>-11.87</v>
       </c>
       <c r="M211" t="n">
-        <v>-19.28</v>
+        <v>-19.89</v>
       </c>
       <c r="N211" t="b">
         <v>0</v>
@@ -11570,7 +11588,7 @@
         <v>-29.8</v>
       </c>
       <c r="H212" t="n">
-        <v>68.31999999999999</v>
+        <v>71.8</v>
       </c>
       <c r="I212" t="n">
         <v>29.88</v>
@@ -11583,7 +11601,7 @@
         <v>-0.29</v>
       </c>
       <c r="M212" t="n">
-        <v>65.88</v>
+        <v>69.18000000000001</v>
       </c>
       <c r="N212" t="b">
         <v>0</v>
@@ -11621,7 +11639,7 @@
         <v>-22.4</v>
       </c>
       <c r="H213" t="n">
-        <v>-19.78</v>
+        <v>-19.92</v>
       </c>
       <c r="I213" t="n">
         <v>5.79</v>
@@ -11634,7 +11652,7 @@
         <v>-9.67</v>
       </c>
       <c r="M213" t="n">
-        <v>-22.23</v>
+        <v>-22.55</v>
       </c>
       <c r="N213" t="b">
         <v>0</v>
@@ -11672,7 +11690,7 @@
         <v>19.3</v>
       </c>
       <c r="H214" t="n">
-        <v>-21.75</v>
+        <v>-20.97</v>
       </c>
       <c r="I214" t="n">
         <v>-16.69</v>
@@ -11685,7 +11703,7 @@
         <v>-36.39</v>
       </c>
       <c r="M214" t="n">
-        <v>-24.19</v>
+        <v>-23.6</v>
       </c>
       <c r="N214" t="b">
         <v>1</v>
@@ -11723,7 +11741,7 @@
         <v>7.6</v>
       </c>
       <c r="H215" t="n">
-        <v>-0.73</v>
+        <v>-3.39</v>
       </c>
       <c r="I215" t="n">
         <v>6.22</v>
@@ -11736,7 +11754,7 @@
         <v>-10.68</v>
       </c>
       <c r="M215" t="n">
-        <v>-3.17</v>
+        <v>-6.02</v>
       </c>
       <c r="N215" t="b">
         <v>0</v>
@@ -11774,7 +11792,7 @@
         <v>68.8</v>
       </c>
       <c r="H216" t="n">
-        <v>16.3</v>
+        <v>17.06</v>
       </c>
       <c r="I216" t="n">
         <v>-1.41</v>
@@ -11787,7 +11805,7 @@
         <v>-19.39</v>
       </c>
       <c r="M216" t="n">
-        <v>13.86</v>
+        <v>14.43</v>
       </c>
       <c r="N216" t="b">
         <v>0</v>
@@ -11825,7 +11843,7 @@
         <v>8.5</v>
       </c>
       <c r="H217" t="n">
-        <v>-12.97</v>
+        <v>-15.41</v>
       </c>
       <c r="I217" t="n">
         <v>-4.26</v>
@@ -11838,7 +11856,7 @@
         <v>-23.85</v>
       </c>
       <c r="M217" t="n">
-        <v>-15.42</v>
+        <v>-18.03</v>
       </c>
       <c r="N217" t="b">
         <v>0</v>
@@ -11876,7 +11894,7 @@
         <v>-15.2</v>
       </c>
       <c r="H218" t="n">
-        <v>5.03</v>
+        <v>6.21</v>
       </c>
       <c r="I218" t="n">
         <v>12.27</v>
@@ -11889,7 +11907,7 @@
         <v>-12.27</v>
       </c>
       <c r="M218" t="n">
-        <v>2.59</v>
+        <v>3.58</v>
       </c>
       <c r="N218" t="b">
         <v>0</v>
@@ -11927,7 +11945,7 @@
         <v>-33.1</v>
       </c>
       <c r="H219" t="n">
-        <v>-24.45</v>
+        <v>-25.17</v>
       </c>
       <c r="I219" t="n">
         <v>-13.13</v>
@@ -11940,7 +11958,7 @@
         <v>-21.04</v>
       </c>
       <c r="M219" t="n">
-        <v>-26.89</v>
+        <v>-27.8</v>
       </c>
       <c r="N219" t="b">
         <v>0</v>
@@ -11978,7 +11996,7 @@
         <v>11.8</v>
       </c>
       <c r="H220" t="n">
-        <v>2.97</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="I220" t="n">
         <v>-1.19</v>
@@ -11991,7 +12009,7 @@
         <v>-17.57</v>
       </c>
       <c r="M220" t="n">
-        <v>0.52</v>
+        <v>6.42</v>
       </c>
       <c r="N220" t="b">
         <v>1</v>
@@ -12029,7 +12047,7 @@
         <v>27.5</v>
       </c>
       <c r="H221" t="n">
-        <v>5.56</v>
+        <v>11.69</v>
       </c>
       <c r="I221" t="n">
         <v>8.42</v>
@@ -12042,7 +12060,7 @@
         <v>-2.51</v>
       </c>
       <c r="M221" t="n">
-        <v>3.12</v>
+        <v>9.07</v>
       </c>
       <c r="N221" t="b">
         <v>1</v>
@@ -12080,7 +12098,7 @@
         <v>-22.4</v>
       </c>
       <c r="H222" t="n">
-        <v>-11.38</v>
+        <v>-10.98</v>
       </c>
       <c r="I222" t="n">
         <v>9.42</v>
@@ -12093,7 +12111,7 @@
         <v>-2.79</v>
       </c>
       <c r="M222" t="n">
-        <v>-13.82</v>
+        <v>-13.61</v>
       </c>
       <c r="N222" t="b">
         <v>1</v>
@@ -12131,7 +12149,7 @@
         <v>-14.7</v>
       </c>
       <c r="H223" t="n">
-        <v>-15.07</v>
+        <v>-15.91</v>
       </c>
       <c r="I223" t="n">
         <v>10.3</v>
@@ -12144,7 +12162,7 @@
         <v>-2.6</v>
       </c>
       <c r="M223" t="n">
-        <v>-17.51</v>
+        <v>-18.54</v>
       </c>
       <c r="N223" t="b">
         <v>1</v>
@@ -12186,7 +12204,7 @@
         <v>-9.300000000000001</v>
       </c>
       <c r="H224" t="n">
-        <v>-28.18</v>
+        <v>-29.35</v>
       </c>
       <c r="I224" t="n">
         <v>10.42</v>
@@ -12199,7 +12217,7 @@
         <v>-21.72</v>
       </c>
       <c r="M224" t="n">
-        <v>-30.62</v>
+        <v>-31.97</v>
       </c>
       <c r="N224" t="b">
         <v>1</v>
@@ -12237,7 +12255,7 @@
         <v>-13.5</v>
       </c>
       <c r="H225" t="n">
-        <v>91.94</v>
+        <v>103.31</v>
       </c>
       <c r="I225" t="n">
         <v>18.09</v>
@@ -12250,7 +12268,7 @@
         <v>-14.35</v>
       </c>
       <c r="M225" t="n">
-        <v>89.5</v>
+        <v>100.69</v>
       </c>
       <c r="N225" t="b">
         <v>0</v>
@@ -12288,7 +12306,7 @@
         <v>-27.5</v>
       </c>
       <c r="H226" t="n">
-        <v>-19.78</v>
+        <v>-18.59</v>
       </c>
       <c r="I226" t="n">
         <v>-29.95</v>
@@ -12301,7 +12319,7 @@
         <v>-35.86</v>
       </c>
       <c r="M226" t="n">
-        <v>-22.23</v>
+        <v>-21.22</v>
       </c>
       <c r="N226" t="b">
         <v>0</v>
@@ -12339,7 +12357,7 @@
         <v>11.9</v>
       </c>
       <c r="H227" t="n">
-        <v>-24.7</v>
+        <v>-26.43</v>
       </c>
       <c r="I227" t="n">
         <v>-3.02</v>
@@ -12352,7 +12370,7 @@
         <v>-24.96</v>
       </c>
       <c r="M227" t="n">
-        <v>-27.14</v>
+        <v>-29.06</v>
       </c>
       <c r="N227" t="b">
         <v>0</v>
@@ -12390,7 +12408,7 @@
         <v>5</v>
       </c>
       <c r="H228" t="n">
-        <v>-4.96</v>
+        <v>-4.51</v>
       </c>
       <c r="I228" t="n">
         <v>0.41</v>
@@ -12403,7 +12421,7 @@
         <v>-13.87</v>
       </c>
       <c r="M228" t="n">
-        <v>-7.4</v>
+        <v>-7.14</v>
       </c>
       <c r="N228" t="b">
         <v>0</v>
@@ -12441,7 +12459,7 @@
         <v>-35.9</v>
       </c>
       <c r="H229" t="n">
-        <v>11.8</v>
+        <v>12.43</v>
       </c>
       <c r="I229" t="n">
         <v>18.67</v>
@@ -12454,7 +12472,7 @@
         <v>-6.77</v>
       </c>
       <c r="M229" t="n">
-        <v>9.359999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="N229" t="b">
         <v>0</v>
@@ -12492,7 +12510,7 @@
         <v>-25.2</v>
       </c>
       <c r="H230" t="n">
-        <v>16.16</v>
+        <v>18.09</v>
       </c>
       <c r="I230" t="n">
         <v>22.53</v>
@@ -12505,7 +12523,7 @@
         <v>-19.27</v>
       </c>
       <c r="M230" t="n">
-        <v>13.71</v>
+        <v>15.46</v>
       </c>
       <c r="N230" t="b">
         <v>1</v>
@@ -12543,7 +12561,7 @@
         <v>5.1</v>
       </c>
       <c r="H231" t="n">
-        <v>0.76</v>
+        <v>0.62</v>
       </c>
       <c r="I231" t="n">
         <v>8.77</v>
@@ -12556,7 +12574,7 @@
         <v>-3.54</v>
       </c>
       <c r="M231" t="n">
-        <v>-1.68</v>
+        <v>-2</v>
       </c>
       <c r="N231" t="b">
         <v>1</v>
@@ -12594,7 +12612,7 @@
         <v>20.8</v>
       </c>
       <c r="H232" t="n">
-        <v>-20.35</v>
+        <v>-18.77</v>
       </c>
       <c r="I232" t="n">
         <v>-10.93</v>
@@ -12607,7 +12625,7 @@
         <v>-27.1</v>
       </c>
       <c r="M232" t="n">
-        <v>-22.8</v>
+        <v>-21.39</v>
       </c>
       <c r="N232" t="b">
         <v>0</v>
@@ -12645,7 +12663,7 @@
         <v>-27.7</v>
       </c>
       <c r="H233" t="n">
-        <v>11.03</v>
+        <v>12.75</v>
       </c>
       <c r="I233" t="n">
         <v>-10.22</v>
@@ -12658,7 +12676,7 @@
         <v>-17.14</v>
       </c>
       <c r="M233" t="n">
-        <v>8.59</v>
+        <v>10.12</v>
       </c>
       <c r="N233" t="b">
         <v>0</v>
@@ -12696,7 +12714,7 @@
         <v>-24.7</v>
       </c>
       <c r="H234" t="n">
-        <v>1.26</v>
+        <v>-1.31</v>
       </c>
       <c r="I234" t="n">
         <v>1.65</v>
@@ -12709,7 +12727,7 @@
         <v>-19.04</v>
       </c>
       <c r="M234" t="n">
-        <v>-1.18</v>
+        <v>-3.93</v>
       </c>
       <c r="N234" t="b">
         <v>0</v>
@@ -12747,7 +12765,7 @@
         <v>-34.9</v>
       </c>
       <c r="H235" t="n">
-        <v>-13.13</v>
+        <v>-12.76</v>
       </c>
       <c r="I235" t="n">
         <v>19.9</v>
@@ -12760,7 +12778,7 @@
         <v>-12.62</v>
       </c>
       <c r="M235" t="n">
-        <v>-15.57</v>
+        <v>-15.39</v>
       </c>
       <c r="N235" t="b">
         <v>0</v>
@@ -12798,7 +12816,7 @@
         <v>-29.5</v>
       </c>
       <c r="H236" t="n">
-        <v>-8.09</v>
+        <v>-10.03</v>
       </c>
       <c r="I236" t="n">
         <v>4.05</v>
@@ -12811,7 +12829,7 @@
         <v>-2.43</v>
       </c>
       <c r="M236" t="n">
-        <v>-10.53</v>
+        <v>-12.66</v>
       </c>
       <c r="N236" t="b">
         <v>0</v>
@@ -12849,7 +12867,7 @@
         <v>34.2</v>
       </c>
       <c r="H237" t="n">
-        <v>7.83</v>
+        <v>10.03</v>
       </c>
       <c r="I237" t="n">
         <v>8.15</v>
@@ -12862,7 +12880,7 @@
         <v>-7.63</v>
       </c>
       <c r="M237" t="n">
-        <v>5.38</v>
+        <v>7.4</v>
       </c>
       <c r="N237" t="b">
         <v>1</v>
@@ -12900,7 +12918,7 @@
         <v>42</v>
       </c>
       <c r="H238" t="n">
-        <v>-31.36</v>
+        <v>-32.27</v>
       </c>
       <c r="I238" t="n">
         <v>0.6</v>
@@ -12913,7 +12931,7 @@
         <v>-16.67</v>
       </c>
       <c r="M238" t="n">
-        <v>-33.81</v>
+        <v>-34.9</v>
       </c>
       <c r="N238" t="b">
         <v>1</v>
@@ -12955,7 +12973,7 @@
         <v>-0.4</v>
       </c>
       <c r="H239" t="n">
-        <v>-19.94</v>
+        <v>-17.53</v>
       </c>
       <c r="I239" t="n">
         <v>4.83</v>
@@ -12968,7 +12986,7 @@
         <v>-10.75</v>
       </c>
       <c r="M239" t="n">
-        <v>-22.38</v>
+        <v>-20.15</v>
       </c>
       <c r="N239" t="b">
         <v>0</v>
@@ -13006,7 +13024,7 @@
         <v>64.59999999999999</v>
       </c>
       <c r="H240" t="n">
-        <v>9.41</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="I240" t="n">
         <v>3.01</v>
@@ -13019,7 +13037,7 @@
         <v>-12</v>
       </c>
       <c r="M240" t="n">
-        <v>6.97</v>
+        <v>6.76</v>
       </c>
       <c r="N240" t="b">
         <v>0</v>
@@ -13057,7 +13075,7 @@
         <v>-25.3</v>
       </c>
       <c r="H241" t="n">
-        <v>36.65</v>
+        <v>41.24</v>
       </c>
       <c r="I241" t="n">
         <v>36.1</v>
@@ -13070,7 +13088,7 @@
         <v>-5.66</v>
       </c>
       <c r="M241" t="n">
-        <v>34.21</v>
+        <v>38.61</v>
       </c>
       <c r="N241" t="b">
         <v>1</v>
@@ -13108,7 +13126,7 @@
         <v>-7.7</v>
       </c>
       <c r="H242" t="n">
-        <v>-0.6899999999999999</v>
+        <v>-0.2</v>
       </c>
       <c r="I242" t="n">
         <v>-6.47</v>
@@ -13121,7 +13139,7 @@
         <v>-23.05</v>
       </c>
       <c r="M242" t="n">
-        <v>-3.13</v>
+        <v>-2.82</v>
       </c>
       <c r="N242" t="b">
         <v>1</v>
@@ -13210,7 +13228,7 @@
         <v>13.7</v>
       </c>
       <c r="H244" t="n">
-        <v>9.49</v>
+        <v>12.64</v>
       </c>
       <c r="I244" t="n">
         <v>2.74</v>
@@ -13223,7 +13241,7 @@
         <v>-24.02</v>
       </c>
       <c r="M244" t="n">
-        <v>7.05</v>
+        <v>10.01</v>
       </c>
       <c r="N244" t="b">
         <v>1</v>
@@ -13261,7 +13279,7 @@
         <v>21.8</v>
       </c>
       <c r="H245" t="n">
-        <v>-0.07000000000000001</v>
+        <v>2.75</v>
       </c>
       <c r="I245" t="n">
         <v>18.32</v>
@@ -13274,7 +13292,7 @@
         <v>-23.27</v>
       </c>
       <c r="M245" t="n">
-        <v>-2.51</v>
+        <v>0.13</v>
       </c>
       <c r="N245" t="b">
         <v>1</v>
@@ -13312,7 +13330,7 @@
         <v>29.4</v>
       </c>
       <c r="H246" t="n">
-        <v>4.23</v>
+        <v>6.62</v>
       </c>
       <c r="I246" t="n">
         <v>-2.62</v>
@@ -13325,7 +13343,7 @@
         <v>-27.18</v>
       </c>
       <c r="M246" t="n">
-        <v>1.79</v>
+        <v>3.99</v>
       </c>
       <c r="N246" t="b">
         <v>1</v>
@@ -13363,7 +13381,7 @@
         <v>-3.7</v>
       </c>
       <c r="H247" t="n">
-        <v>-23.5</v>
+        <v>-18.24</v>
       </c>
       <c r="I247" t="n">
         <v>-8.07</v>
@@ -13376,7 +13394,7 @@
         <v>-22.12</v>
       </c>
       <c r="M247" t="n">
-        <v>-25.95</v>
+        <v>-20.87</v>
       </c>
       <c r="N247" t="b">
         <v>1</v>
@@ -13414,7 +13432,7 @@
         <v>21.3</v>
       </c>
       <c r="H248" t="n">
-        <v>1.69</v>
+        <v>2.12</v>
       </c>
       <c r="I248" t="n">
         <v>0.23</v>
@@ -13427,7 +13445,7 @@
         <v>-0.85</v>
       </c>
       <c r="M248" t="n">
-        <v>-0.75</v>
+        <v>-0.51</v>
       </c>
       <c r="N248" t="b">
         <v>1</v>
@@ -13465,7 +13483,7 @@
         <v>-21.4</v>
       </c>
       <c r="H249" t="n">
-        <v>15.72</v>
+        <v>15.51</v>
       </c>
       <c r="I249" t="n">
         <v>4.55</v>
@@ -13478,7 +13496,7 @@
         <v>-6.39</v>
       </c>
       <c r="M249" t="n">
-        <v>13.27</v>
+        <v>12.89</v>
       </c>
       <c r="N249" t="b">
         <v>1</v>
@@ -13516,7 +13534,7 @@
         <v>16.3</v>
       </c>
       <c r="H250" t="n">
-        <v>2.56</v>
+        <v>5.92</v>
       </c>
       <c r="I250" t="n">
         <v>-1</v>
@@ -13529,7 +13547,7 @@
         <v>-22.5</v>
       </c>
       <c r="M250" t="n">
-        <v>0.11</v>
+        <v>3.3</v>
       </c>
       <c r="N250" t="b">
         <v>1</v>
@@ -13567,7 +13585,7 @@
         <v>11.9</v>
       </c>
       <c r="H251" t="n">
-        <v>-9.08</v>
+        <v>-4.98</v>
       </c>
       <c r="I251" t="n">
         <v>7.74</v>
@@ -13580,7 +13598,7 @@
         <v>-9.43</v>
       </c>
       <c r="M251" t="n">
-        <v>-11.52</v>
+        <v>-7.6</v>
       </c>
       <c r="N251" t="b">
         <v>1</v>
@@ -13618,7 +13636,7 @@
         <v>19.4</v>
       </c>
       <c r="H252" t="n">
-        <v>-7.3</v>
+        <v>-5.17</v>
       </c>
       <c r="I252" t="n">
         <v>10.89</v>
@@ -13631,7 +13649,7 @@
         <v>-2.97</v>
       </c>
       <c r="M252" t="n">
-        <v>-9.75</v>
+        <v>-7.8</v>
       </c>
       <c r="N252" t="b">
         <v>0</v>
@@ -13669,7 +13687,7 @@
         <v>66.7</v>
       </c>
       <c r="H253" t="n">
-        <v>13.7</v>
+        <v>13.4</v>
       </c>
       <c r="I253" t="n">
         <v>4.84</v>
@@ -13682,7 +13700,7 @@
         <v>-11.7</v>
       </c>
       <c r="M253" t="n">
-        <v>11.26</v>
+        <v>10.77</v>
       </c>
       <c r="N253" t="b">
         <v>0</v>
@@ -13720,7 +13738,7 @@
         <v>3.7</v>
       </c>
       <c r="H254" t="n">
-        <v>9.699999999999999</v>
+        <v>12.81</v>
       </c>
       <c r="I254" t="n">
         <v>11.13</v>
@@ -13733,7 +13751,7 @@
         <v>-2.79</v>
       </c>
       <c r="M254" t="n">
-        <v>7.26</v>
+        <v>10.19</v>
       </c>
       <c r="N254" t="b">
         <v>0</v>
@@ -13771,7 +13789,7 @@
         <v>36.8</v>
       </c>
       <c r="H255" t="n">
-        <v>27.36</v>
+        <v>30.37</v>
       </c>
       <c r="I255" t="n">
         <v>15.47</v>
@@ -13784,7 +13802,7 @@
         <v>-0.96</v>
       </c>
       <c r="M255" t="n">
-        <v>24.92</v>
+        <v>27.75</v>
       </c>
       <c r="N255" t="b">
         <v>0</v>
@@ -13822,7 +13840,7 @@
         <v>0.2</v>
       </c>
       <c r="H256" t="n">
-        <v>4.86</v>
+        <v>6.25</v>
       </c>
       <c r="I256" t="n">
         <v>4.35</v>
@@ -13835,7 +13853,7 @@
         <v>-2.79</v>
       </c>
       <c r="M256" t="n">
-        <v>2.42</v>
+        <v>3.62</v>
       </c>
       <c r="N256" t="b">
         <v>1</v>
@@ -13873,7 +13891,7 @@
         <v>-31</v>
       </c>
       <c r="H257" t="n">
-        <v>-0.03</v>
+        <v>-3.13</v>
       </c>
       <c r="I257" t="n">
         <v>19.41</v>
@@ -13886,7 +13904,7 @@
         <v>-10.33</v>
       </c>
       <c r="M257" t="n">
-        <v>-2.48</v>
+        <v>-5.75</v>
       </c>
       <c r="N257" t="b">
         <v>0</v>
@@ -13928,7 +13946,7 @@
         <v>-2</v>
       </c>
       <c r="H258" t="n">
-        <v>-15.37</v>
+        <v>-12.81</v>
       </c>
       <c r="I258" t="n">
         <v>14.61</v>
@@ -13941,7 +13959,7 @@
         <v>-3.45</v>
       </c>
       <c r="M258" t="n">
-        <v>-17.81</v>
+        <v>-15.44</v>
       </c>
       <c r="N258" t="b">
         <v>0</v>
@@ -13979,7 +13997,7 @@
         <v>12.2</v>
       </c>
       <c r="H259" t="n">
-        <v>-39.57</v>
+        <v>-39.53</v>
       </c>
       <c r="I259" t="n">
         <v>3.47</v>
@@ -13992,7 +14010,7 @@
         <v>-27.15</v>
       </c>
       <c r="M259" t="n">
-        <v>-42.01</v>
+        <v>-42.16</v>
       </c>
       <c r="N259" t="b">
         <v>0</v>
@@ -14030,7 +14048,7 @@
         <v>8.4</v>
       </c>
       <c r="H260" t="n">
-        <v>-35.26</v>
+        <v>-35.04</v>
       </c>
       <c r="I260" t="n">
         <v>-0.13</v>
@@ -14043,7 +14061,7 @@
         <v>-10.87</v>
       </c>
       <c r="M260" t="n">
-        <v>-37.7</v>
+        <v>-37.67</v>
       </c>
       <c r="N260" t="b">
         <v>1</v>
@@ -14081,7 +14099,7 @@
         <v>-21.7</v>
       </c>
       <c r="H261" t="n">
-        <v>-5.2</v>
+        <v>-5.07</v>
       </c>
       <c r="I261" t="n">
         <v>5.5</v>
@@ -14094,7 +14112,7 @@
         <v>-4.3</v>
       </c>
       <c r="M261" t="n">
-        <v>-7.64</v>
+        <v>-7.69</v>
       </c>
       <c r="N261" t="b">
         <v>0</v>
@@ -14132,7 +14150,7 @@
         <v>-7.3</v>
       </c>
       <c r="H262" t="n">
-        <v>-24.1</v>
+        <v>-22.59</v>
       </c>
       <c r="I262" t="n">
         <v>-4.12</v>
@@ -14145,7 +14163,7 @@
         <v>-15.02</v>
       </c>
       <c r="M262" t="n">
-        <v>-26.54</v>
+        <v>-25.21</v>
       </c>
       <c r="N262" t="b">
         <v>1</v>
@@ -14183,7 +14201,7 @@
         <v>-26.1</v>
       </c>
       <c r="H263" t="n">
-        <v>-20.54</v>
+        <v>-20.07</v>
       </c>
       <c r="I263" t="n">
         <v>5.05</v>
@@ -14196,7 +14214,7 @@
         <v>-9.27</v>
       </c>
       <c r="M263" t="n">
-        <v>-22.99</v>
+        <v>-22.7</v>
       </c>
       <c r="N263" t="b">
         <v>1</v>
@@ -14234,7 +14252,7 @@
         <v>-18.5</v>
       </c>
       <c r="H264" t="n">
-        <v>31.83</v>
+        <v>35.52</v>
       </c>
       <c r="I264" t="n">
         <v>16.22</v>
@@ -14247,7 +14265,7 @@
         <v>-9.960000000000001</v>
       </c>
       <c r="M264" t="n">
-        <v>29.39</v>
+        <v>32.9</v>
       </c>
       <c r="N264" t="b">
         <v>0</v>
@@ -14285,7 +14303,7 @@
         <v>15.3</v>
       </c>
       <c r="H265" t="n">
-        <v>-38.21</v>
+        <v>-38.19</v>
       </c>
       <c r="I265" t="n">
         <v>-21.4</v>
@@ -14298,7 +14316,7 @@
         <v>-26.97</v>
       </c>
       <c r="M265" t="n">
-        <v>-40.65</v>
+        <v>-40.82</v>
       </c>
       <c r="N265" t="b">
         <v>0</v>
@@ -14336,7 +14354,7 @@
         <v>26.1</v>
       </c>
       <c r="H266" t="n">
-        <v>-7.28</v>
+        <v>-5.53</v>
       </c>
       <c r="I266" t="n">
         <v>-0.51</v>
@@ -14349,7 +14367,7 @@
         <v>-16.45</v>
       </c>
       <c r="M266" t="n">
-        <v>-9.73</v>
+        <v>-8.16</v>
       </c>
       <c r="N266" t="b">
         <v>1</v>
@@ -14391,7 +14409,7 @@
         <v>-8.199999999999999</v>
       </c>
       <c r="H267" t="n">
-        <v>-10.07</v>
+        <v>-13.81</v>
       </c>
       <c r="I267" t="n">
         <v>17.48</v>
@@ -14404,7 +14422,7 @@
         <v>-10.68</v>
       </c>
       <c r="M267" t="n">
-        <v>-12.51</v>
+        <v>-16.44</v>
       </c>
       <c r="N267" t="b">
         <v>0</v>
@@ -14442,7 +14460,7 @@
         <v>17.9</v>
       </c>
       <c r="H268" t="n">
-        <v>2.82</v>
+        <v>5.68</v>
       </c>
       <c r="I268" t="n">
         <v>12.97</v>
@@ -14455,7 +14473,7 @@
         <v>-8.130000000000001</v>
       </c>
       <c r="M268" t="n">
-        <v>0.38</v>
+        <v>3.06</v>
       </c>
       <c r="N268" t="b">
         <v>1</v>
@@ -14493,7 +14511,7 @@
         <v>0.7</v>
       </c>
       <c r="H269" t="n">
-        <v>-20.01</v>
+        <v>-20.07</v>
       </c>
       <c r="I269" t="n">
         <v>14.96</v>
@@ -14506,7 +14524,7 @@
         <v>-8.039999999999999</v>
       </c>
       <c r="M269" t="n">
-        <v>-22.45</v>
+        <v>-22.69</v>
       </c>
       <c r="N269" t="b">
         <v>1</v>
@@ -14544,7 +14562,7 @@
         <v>61.6</v>
       </c>
       <c r="H270" t="n">
-        <v>5.94</v>
+        <v>6.95</v>
       </c>
       <c r="I270" t="n">
         <v>11.47</v>
@@ -14557,7 +14575,7 @@
         <v>-12.86</v>
       </c>
       <c r="M270" t="n">
-        <v>3.49</v>
+        <v>4.32</v>
       </c>
       <c r="N270" t="b">
         <v>0</v>
@@ -14595,7 +14613,7 @@
         <v>54.3</v>
       </c>
       <c r="H271" t="n">
-        <v>-25.47</v>
+        <v>-24.86</v>
       </c>
       <c r="I271" t="n">
         <v>-2.86</v>
@@ -14608,7 +14626,7 @@
         <v>-24.93</v>
       </c>
       <c r="M271" t="n">
-        <v>-27.91</v>
+        <v>-27.49</v>
       </c>
       <c r="N271" t="b">
         <v>0</v>
@@ -14646,7 +14664,7 @@
         <v>14.8</v>
       </c>
       <c r="H272" t="n">
-        <v>-4.06</v>
+        <v>-3.63</v>
       </c>
       <c r="I272" t="n">
         <v>0.35</v>
@@ -14659,7 +14677,7 @@
         <v>-3.68</v>
       </c>
       <c r="M272" t="n">
-        <v>-6.5</v>
+        <v>-6.25</v>
       </c>
       <c r="N272" t="b">
         <v>1</v>
@@ -14697,7 +14715,7 @@
         <v>-13.5</v>
       </c>
       <c r="H273" t="n">
-        <v>-21.04</v>
+        <v>-19.58</v>
       </c>
       <c r="I273" t="n">
         <v>-1.88</v>
@@ -14710,7 +14728,7 @@
         <v>-11.4</v>
       </c>
       <c r="M273" t="n">
-        <v>-23.48</v>
+        <v>-22.21</v>
       </c>
       <c r="N273" t="b">
         <v>0</v>
@@ -14748,7 +14766,7 @@
         <v>25.5</v>
       </c>
       <c r="H274" t="n">
-        <v>2.85</v>
+        <v>1.38</v>
       </c>
       <c r="I274" t="n">
         <v>-9.369999999999999</v>
@@ -14761,7 +14779,7 @@
         <v>-22.11</v>
       </c>
       <c r="M274" t="n">
-        <v>0.41</v>
+        <v>-1.25</v>
       </c>
       <c r="N274" t="b">
         <v>1</v>
@@ -14803,7 +14821,7 @@
         <v>-7.5</v>
       </c>
       <c r="H275" t="n">
-        <v>-8.74</v>
+        <v>-10.7</v>
       </c>
       <c r="I275" t="n">
         <v>4.46</v>
@@ -14816,7 +14834,7 @@
         <v>-8.52</v>
       </c>
       <c r="M275" t="n">
-        <v>-11.18</v>
+        <v>-13.32</v>
       </c>
       <c r="N275" t="b">
         <v>1</v>
@@ -14854,7 +14872,7 @@
         <v>1.5</v>
       </c>
       <c r="H276" t="n">
-        <v>5.44</v>
+        <v>4.33</v>
       </c>
       <c r="I276" t="n">
         <v>-7.31</v>
@@ -14867,7 +14885,7 @@
         <v>-18.58</v>
       </c>
       <c r="M276" t="n">
-        <v>3</v>
+        <v>1.7</v>
       </c>
       <c r="N276" t="b">
         <v>0</v>
@@ -14905,7 +14923,7 @@
         <v>-11</v>
       </c>
       <c r="H277" t="n">
-        <v>-1.54</v>
+        <v>7.26</v>
       </c>
       <c r="I277" t="n">
         <v>10.7</v>
@@ -14918,7 +14936,7 @@
         <v>-9.43</v>
       </c>
       <c r="M277" t="n">
-        <v>-3.98</v>
+        <v>4.63</v>
       </c>
       <c r="N277" t="b">
         <v>1</v>
@@ -14956,7 +14974,7 @@
         <v>-11.4</v>
       </c>
       <c r="H278" t="n">
-        <v>-18.78</v>
+        <v>-18.58</v>
       </c>
       <c r="I278" t="n">
         <v>4.36</v>
@@ -14969,7 +14987,7 @@
         <v>-11.36</v>
       </c>
       <c r="M278" t="n">
-        <v>-21.23</v>
+        <v>-21.2</v>
       </c>
       <c r="N278" t="b">
         <v>1</v>
@@ -15007,7 +15025,7 @@
         <v>2.1</v>
       </c>
       <c r="H279" t="n">
-        <v>50.77</v>
+        <v>56.91</v>
       </c>
       <c r="I279" t="n">
         <v>20.72</v>
@@ -15020,7 +15038,7 @@
         <v>-5.79</v>
       </c>
       <c r="M279" t="n">
-        <v>48.12</v>
+        <v>54.28</v>
       </c>
       <c r="N279" t="b">
         <v>0</v>
@@ -15058,7 +15076,7 @@
         <v>27.1</v>
       </c>
       <c r="H280" t="n">
-        <v>-4.4</v>
+        <v>-1.93</v>
       </c>
       <c r="I280" t="n">
         <v>5.02</v>
@@ -15071,7 +15089,7 @@
         <v>-14.35</v>
       </c>
       <c r="M280" t="n">
-        <v>-6.84</v>
+        <v>-4.56</v>
       </c>
       <c r="N280" t="b">
         <v>1</v>
@@ -15109,7 +15127,7 @@
         <v>-21.6</v>
       </c>
       <c r="H281" t="n">
-        <v>-11.08</v>
+        <v>-11.71</v>
       </c>
       <c r="I281" t="n">
         <v>1.22</v>
@@ -15122,7 +15140,7 @@
         <v>-6.54</v>
       </c>
       <c r="M281" t="n">
-        <v>-13.52</v>
+        <v>-14.34</v>
       </c>
       <c r="N281" t="b">
         <v>0</v>
@@ -15164,7 +15182,7 @@
         <v>-2.2</v>
       </c>
       <c r="H282" t="n">
-        <v>9.42</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="I282" t="n">
         <v>-9.050000000000001</v>
@@ -15177,7 +15195,7 @@
         <v>-18.61</v>
       </c>
       <c r="M282" t="n">
-        <v>6.98</v>
+        <v>5.48</v>
       </c>
       <c r="N282" t="b">
         <v>0</v>
@@ -15215,7 +15233,7 @@
         <v>0.7</v>
       </c>
       <c r="H283" t="n">
-        <v>-4.48</v>
+        <v>-3.69</v>
       </c>
       <c r="I283" t="n">
         <v>11.4</v>
@@ -15228,7 +15246,7 @@
         <v>-7.28</v>
       </c>
       <c r="M283" t="n">
-        <v>-6.92</v>
+        <v>-6.32</v>
       </c>
       <c r="N283" t="b">
         <v>0</v>
@@ -15266,7 +15284,7 @@
         <v>-31.7</v>
       </c>
       <c r="H284" t="n">
-        <v>3.71</v>
+        <v>6.38</v>
       </c>
       <c r="I284" t="n">
         <v>17.04</v>
@@ -15279,7 +15297,7 @@
         <v>-4.05</v>
       </c>
       <c r="M284" t="n">
-        <v>1.27</v>
+        <v>3.75</v>
       </c>
       <c r="N284" t="b">
         <v>0</v>
@@ -15317,7 +15335,7 @@
         <v>32.2</v>
       </c>
       <c r="H285" t="n">
-        <v>15.49</v>
+        <v>18.14</v>
       </c>
       <c r="I285" t="n">
         <v>6.49</v>
@@ -15330,7 +15348,7 @@
         <v>-3.92</v>
       </c>
       <c r="M285" t="n">
-        <v>13.05</v>
+        <v>15.51</v>
       </c>
       <c r="N285" t="b">
         <v>1</v>
@@ -15347,17 +15365,17 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>AVB</t>
+          <t>AAON</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>DLB</t>
+          <t>D200G</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>Extended</t>
+          <t>Retired</t>
         </is>
       </c>
       <c r="E286" t="inlineStr"/>
@@ -15365,28 +15383,30 @@
         <v>2.4</v>
       </c>
       <c r="G286" t="n">
-        <v>-60.8</v>
+        <v>3.2</v>
       </c>
       <c r="H286" t="n">
-        <v>167.79</v>
+        <v>-22.3</v>
       </c>
       <c r="I286" t="n">
-        <v>-1.42</v>
-      </c>
-      <c r="J286" t="inlineStr"/>
+        <v>-10.41</v>
+      </c>
+      <c r="J286" t="n">
+        <v>-23.06</v>
+      </c>
       <c r="K286" t="inlineStr"/>
       <c r="L286" t="n">
-        <v>-6.52</v>
+        <v>-23.7</v>
       </c>
       <c r="M286" t="n">
-        <v>163.77</v>
+        <v>-24.74</v>
       </c>
       <c r="N286" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O286" t="inlineStr">
         <is>
-          <t>&lt;-10</t>
+          <t>0..10</t>
         </is>
       </c>
     </row>
@@ -15396,7 +15416,7 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>AAON</t>
+          <t>LYB</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
@@ -15414,23 +15434,23 @@
         <v>2.4</v>
       </c>
       <c r="G287" t="n">
-        <v>3.2</v>
+        <v>7.3</v>
       </c>
       <c r="H287" t="n">
-        <v>-22.3</v>
+        <v>-5.02</v>
       </c>
       <c r="I287" t="n">
-        <v>-10.41</v>
+        <v>-0.57</v>
       </c>
       <c r="J287" t="n">
-        <v>-23.06</v>
+        <v>6.3</v>
       </c>
       <c r="K287" t="inlineStr"/>
       <c r="L287" t="n">
-        <v>-23.7</v>
+        <v>-5.89</v>
       </c>
       <c r="M287" t="n">
-        <v>-24.74</v>
+        <v>-7.64</v>
       </c>
       <c r="N287" t="b">
         <v>1</v>
@@ -15447,12 +15467,12 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>LYB</t>
+          <t>NUE</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>D200G</t>
+          <t>B2</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
@@ -15465,30 +15485,30 @@
         <v>2.4</v>
       </c>
       <c r="G288" t="n">
-        <v>7.3</v>
+        <v>24.5</v>
       </c>
       <c r="H288" t="n">
-        <v>-5.53</v>
+        <v>1.19</v>
       </c>
       <c r="I288" t="n">
-        <v>-0.57</v>
+        <v>17.24</v>
       </c>
       <c r="J288" t="n">
-        <v>6.3</v>
+        <v>13.02</v>
       </c>
       <c r="K288" t="inlineStr"/>
       <c r="L288" t="n">
-        <v>-5.89</v>
+        <v>-0.47</v>
       </c>
       <c r="M288" t="n">
-        <v>-7.97</v>
+        <v>-1.43</v>
       </c>
       <c r="N288" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O288" t="inlineStr">
         <is>
-          <t>0..10</t>
+          <t>&gt;20</t>
         </is>
       </c>
     </row>
@@ -15498,12 +15518,12 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>NUE</t>
+          <t>AEIS</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>B2</t>
+          <t>DLB</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
@@ -15513,33 +15533,33 @@
       </c>
       <c r="E289" t="inlineStr"/>
       <c r="F289" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="G289" t="n">
-        <v>24.5</v>
+        <v>-0.3</v>
       </c>
       <c r="H289" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="I289" t="n">
-        <v>17.24</v>
+        <v>17.76</v>
       </c>
       <c r="J289" t="n">
-        <v>13.02</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="K289" t="inlineStr"/>
       <c r="L289" t="n">
-        <v>-0.47</v>
+        <v>-14.18</v>
       </c>
       <c r="M289" t="n">
-        <v>-2.44</v>
+        <v>-1.14</v>
       </c>
       <c r="N289" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O289" t="inlineStr">
         <is>
-          <t>&gt;20</t>
+          <t>-10..0</t>
         </is>
       </c>
     </row>
@@ -15549,12 +15569,12 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>AEIS</t>
+          <t>GTLB</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>DLB</t>
+          <t>D200G</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
@@ -15567,30 +15587,30 @@
         <v>2.3</v>
       </c>
       <c r="G290" t="n">
-        <v>-0.3</v>
+        <v>4</v>
       </c>
       <c r="H290" t="n">
-        <v>-2.75</v>
+        <v>48.9</v>
       </c>
       <c r="I290" t="n">
-        <v>17.76</v>
+        <v>8.75</v>
       </c>
       <c r="J290" t="n">
-        <v>8.460000000000001</v>
+        <v>23.71</v>
       </c>
       <c r="K290" t="inlineStr"/>
       <c r="L290" t="n">
-        <v>-14.18</v>
+        <v>-11.02</v>
       </c>
       <c r="M290" t="n">
-        <v>-5.2</v>
+        <v>46.28</v>
       </c>
       <c r="N290" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O290" t="inlineStr">
         <is>
-          <t>-10..0</t>
+          <t>0..10</t>
         </is>
       </c>
     </row>
@@ -15600,12 +15620,12 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>GTLB</t>
+          <t>SWKS</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>D200G</t>
+          <t>DLB</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
@@ -15618,30 +15638,30 @@
         <v>2.3</v>
       </c>
       <c r="G291" t="n">
-        <v>4</v>
+        <v>-6.8</v>
       </c>
       <c r="H291" t="n">
-        <v>40.86</v>
+        <v>34.82</v>
       </c>
       <c r="I291" t="n">
-        <v>8.75</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="J291" t="n">
-        <v>23.71</v>
+        <v>9.32</v>
       </c>
       <c r="K291" t="inlineStr"/>
       <c r="L291" t="n">
-        <v>-11.02</v>
+        <v>-6.78</v>
       </c>
       <c r="M291" t="n">
-        <v>38.41</v>
+        <v>32.2</v>
       </c>
       <c r="N291" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O291" t="inlineStr">
         <is>
-          <t>0..10</t>
+          <t>-10..0</t>
         </is>
       </c>
     </row>
@@ -15651,7 +15671,7 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>SWKS</t>
+          <t>MSTR</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
@@ -15669,30 +15689,30 @@
         <v>2.3</v>
       </c>
       <c r="G292" t="n">
-        <v>-6.8</v>
+        <v>-42</v>
       </c>
       <c r="H292" t="n">
-        <v>38.59</v>
+        <v>58.42</v>
       </c>
       <c r="I292" t="n">
-        <v>8.279999999999999</v>
+        <v>-3.61</v>
       </c>
       <c r="J292" t="n">
-        <v>9.32</v>
+        <v>-8.68</v>
       </c>
       <c r="K292" t="inlineStr"/>
       <c r="L292" t="n">
-        <v>-6.78</v>
+        <v>-11.94</v>
       </c>
       <c r="M292" t="n">
-        <v>36.14</v>
+        <v>55.8</v>
       </c>
       <c r="N292" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O292" t="inlineStr">
         <is>
-          <t>-10..0</t>
+          <t>&lt;-10</t>
         </is>
       </c>
     </row>
@@ -15702,12 +15722,12 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>MSTR</t>
+          <t>PWR</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>DLB</t>
+          <t>B2</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
@@ -15720,30 +15740,30 @@
         <v>2.3</v>
       </c>
       <c r="G293" t="n">
-        <v>-42</v>
+        <v>14.6</v>
       </c>
       <c r="H293" t="n">
-        <v>51.11</v>
+        <v>3.78</v>
       </c>
       <c r="I293" t="n">
-        <v>-3.61</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="J293" t="n">
-        <v>-8.68</v>
+        <v>9.029999999999999</v>
       </c>
       <c r="K293" t="inlineStr"/>
       <c r="L293" t="n">
-        <v>-11.94</v>
+        <v>-13.21</v>
       </c>
       <c r="M293" t="n">
-        <v>48.67</v>
+        <v>1.15</v>
       </c>
       <c r="N293" t="b">
         <v>0</v>
       </c>
       <c r="O293" t="inlineStr">
         <is>
-          <t>&lt;-10</t>
+          <t>10..20</t>
         </is>
       </c>
     </row>
@@ -15753,12 +15773,12 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>PWR</t>
+          <t>ATI</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>B2</t>
+          <t>S2</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
@@ -15771,30 +15791,30 @@
         <v>2.3</v>
       </c>
       <c r="G294" t="n">
-        <v>14.6</v>
+        <v>34.6</v>
       </c>
       <c r="H294" t="n">
-        <v>0.63</v>
+        <v>0.95</v>
       </c>
       <c r="I294" t="n">
-        <v>8.539999999999999</v>
+        <v>5.7</v>
       </c>
       <c r="J294" t="n">
-        <v>9.029999999999999</v>
+        <v>19.6</v>
       </c>
       <c r="K294" t="inlineStr"/>
       <c r="L294" t="n">
-        <v>-13.21</v>
+        <v>-7.7</v>
       </c>
       <c r="M294" t="n">
-        <v>-1.81</v>
+        <v>-1.68</v>
       </c>
       <c r="N294" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O294" t="inlineStr">
         <is>
-          <t>10..20</t>
+          <t>&gt;20</t>
         </is>
       </c>
     </row>
@@ -15804,12 +15824,12 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>ATI</t>
+          <t>GLOB</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>DLB</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
@@ -15822,30 +15842,30 @@
         <v>2.3</v>
       </c>
       <c r="G295" t="n">
-        <v>34.6</v>
+        <v>-37.2</v>
       </c>
       <c r="H295" t="n">
-        <v>0.03</v>
+        <v>18</v>
       </c>
       <c r="I295" t="n">
-        <v>5.7</v>
+        <v>21.67</v>
       </c>
       <c r="J295" t="n">
-        <v>19.6</v>
+        <v>19.05</v>
       </c>
       <c r="K295" t="inlineStr"/>
       <c r="L295" t="n">
-        <v>-7.7</v>
+        <v>-6.64</v>
       </c>
       <c r="M295" t="n">
-        <v>-2.42</v>
+        <v>15.37</v>
       </c>
       <c r="N295" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O295" t="inlineStr">
         <is>
-          <t>&gt;20</t>
+          <t>&lt;-10</t>
         </is>
       </c>
     </row>
@@ -15855,7 +15875,7 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>GLOB</t>
+          <t>FLUT</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
@@ -15873,23 +15893,23 @@
         <v>2.3</v>
       </c>
       <c r="G296" t="n">
-        <v>-37.2</v>
+        <v>-31.2</v>
       </c>
       <c r="H296" t="n">
-        <v>10.72</v>
+        <v>-26.39</v>
       </c>
       <c r="I296" t="n">
-        <v>21.67</v>
+        <v>1.03</v>
       </c>
       <c r="J296" t="n">
-        <v>19.05</v>
+        <v>-10.59</v>
       </c>
       <c r="K296" t="inlineStr"/>
       <c r="L296" t="n">
-        <v>-6.64</v>
+        <v>-13.65</v>
       </c>
       <c r="M296" t="n">
-        <v>8.279999999999999</v>
+        <v>-29.02</v>
       </c>
       <c r="N296" t="b">
         <v>0</v>
@@ -15906,12 +15926,12 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>FLUT</t>
+          <t>NTNX</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>DLB</t>
+          <t>D200G</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
@@ -15924,30 +15944,30 @@
         <v>2.3</v>
       </c>
       <c r="G297" t="n">
-        <v>-31.2</v>
+        <v>10.4</v>
       </c>
       <c r="H297" t="n">
-        <v>-28.25</v>
+        <v>29.14</v>
       </c>
       <c r="I297" t="n">
-        <v>1.03</v>
+        <v>11.05</v>
       </c>
       <c r="J297" t="n">
-        <v>-10.59</v>
+        <v>18.87</v>
       </c>
       <c r="K297" t="inlineStr"/>
       <c r="L297" t="n">
-        <v>-13.65</v>
+        <v>-5.54</v>
       </c>
       <c r="M297" t="n">
-        <v>-30.69</v>
+        <v>26.52</v>
       </c>
       <c r="N297" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O297" t="inlineStr">
         <is>
-          <t>&lt;-10</t>
+          <t>10..20</t>
         </is>
       </c>
     </row>
@@ -15957,12 +15977,12 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>NTNX</t>
+          <t>CRSP</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>D200G</t>
+          <t>DLB</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
@@ -15972,33 +15992,33 @@
       </c>
       <c r="E298" t="inlineStr"/>
       <c r="F298" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="G298" t="n">
-        <v>10.4</v>
+        <v>-14.7</v>
       </c>
       <c r="H298" t="n">
-        <v>27.14</v>
+        <v>17.98</v>
       </c>
       <c r="I298" t="n">
-        <v>11.05</v>
+        <v>12.94</v>
       </c>
       <c r="J298" t="n">
-        <v>18.87</v>
+        <v>12.73</v>
       </c>
       <c r="K298" t="inlineStr"/>
       <c r="L298" t="n">
-        <v>-5.54</v>
+        <v>-2.34</v>
       </c>
       <c r="M298" t="n">
-        <v>24.7</v>
+        <v>15.36</v>
       </c>
       <c r="N298" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O298" t="inlineStr">
         <is>
-          <t>10..20</t>
+          <t>&lt;-10</t>
         </is>
       </c>
     </row>
@@ -16008,7 +16028,7 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>CRSP</t>
+          <t>CHWY</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
@@ -16026,26 +16046,26 @@
         <v>2.2</v>
       </c>
       <c r="G299" t="n">
-        <v>-14.7</v>
+        <v>-21.5</v>
       </c>
       <c r="H299" t="n">
-        <v>17.73</v>
+        <v>-18.64</v>
       </c>
       <c r="I299" t="n">
-        <v>12.94</v>
+        <v>10.65</v>
       </c>
       <c r="J299" t="n">
-        <v>12.73</v>
+        <v>5.79</v>
       </c>
       <c r="K299" t="inlineStr"/>
       <c r="L299" t="n">
-        <v>-2.34</v>
+        <v>-6.89</v>
       </c>
       <c r="M299" t="n">
-        <v>15.28</v>
+        <v>-21.27</v>
       </c>
       <c r="N299" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O299" t="inlineStr">
         <is>
@@ -16059,12 +16079,12 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>CHWY</t>
+          <t>CAT</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>DLB</t>
+          <t>B2</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
@@ -16077,30 +16097,30 @@
         <v>2.2</v>
       </c>
       <c r="G300" t="n">
-        <v>-21.5</v>
+        <v>20.2</v>
       </c>
       <c r="H300" t="n">
-        <v>-16.44</v>
+        <v>-6.89</v>
       </c>
       <c r="I300" t="n">
-        <v>10.65</v>
+        <v>-1.23</v>
       </c>
       <c r="J300" t="n">
-        <v>5.79</v>
+        <v>-5.25</v>
       </c>
       <c r="K300" t="inlineStr"/>
       <c r="L300" t="n">
-        <v>-6.89</v>
+        <v>-12.56</v>
       </c>
       <c r="M300" t="n">
-        <v>-18.88</v>
+        <v>-9.52</v>
       </c>
       <c r="N300" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O300" t="inlineStr">
         <is>
-          <t>&lt;-10</t>
+          <t>&gt;20</t>
         </is>
       </c>
     </row>
@@ -16110,12 +16130,12 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>CAT</t>
+          <t>AVTR</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>B2</t>
+          <t>D200G</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
@@ -16128,30 +16148,30 @@
         <v>2.2</v>
       </c>
       <c r="G301" t="n">
-        <v>20.2</v>
+        <v>3.5</v>
       </c>
       <c r="H301" t="n">
-        <v>-8.640000000000001</v>
+        <v>46.14</v>
       </c>
       <c r="I301" t="n">
-        <v>-1.23</v>
+        <v>33.01</v>
       </c>
       <c r="J301" t="n">
-        <v>-5.25</v>
+        <v>29.61</v>
       </c>
       <c r="K301" t="inlineStr"/>
       <c r="L301" t="n">
-        <v>-12.56</v>
+        <v>-0.92</v>
       </c>
       <c r="M301" t="n">
-        <v>-11.09</v>
+        <v>43.51</v>
       </c>
       <c r="N301" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O301" t="inlineStr">
         <is>
-          <t>&gt;20</t>
+          <t>0..10</t>
         </is>
       </c>
     </row>
@@ -16161,12 +16181,12 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>AVTR</t>
+          <t>APA</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>D200G</t>
+          <t>B2</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
@@ -16179,30 +16199,30 @@
         <v>2.2</v>
       </c>
       <c r="G302" t="n">
-        <v>3.5</v>
+        <v>14</v>
       </c>
       <c r="H302" t="n">
-        <v>46.33</v>
+        <v>24.56</v>
       </c>
       <c r="I302" t="n">
-        <v>33.01</v>
+        <v>2.89</v>
       </c>
       <c r="J302" t="n">
-        <v>29.61</v>
+        <v>21.77</v>
       </c>
       <c r="K302" t="inlineStr"/>
       <c r="L302" t="n">
-        <v>-0.92</v>
+        <v>-1.94</v>
       </c>
       <c r="M302" t="n">
-        <v>43.89</v>
+        <v>21.93</v>
       </c>
       <c r="N302" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O302" t="inlineStr">
         <is>
-          <t>0..10</t>
+          <t>10..20</t>
         </is>
       </c>
     </row>
@@ -16212,7 +16232,7 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>KEYS</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
@@ -16230,26 +16250,26 @@
         <v>2.2</v>
       </c>
       <c r="G303" t="n">
-        <v>14</v>
+        <v>19.8</v>
       </c>
       <c r="H303" t="n">
-        <v>19.38</v>
+        <v>14.76</v>
       </c>
       <c r="I303" t="n">
-        <v>2.89</v>
+        <v>4.74</v>
       </c>
       <c r="J303" t="n">
-        <v>21.77</v>
+        <v>4.67</v>
       </c>
       <c r="K303" t="inlineStr"/>
       <c r="L303" t="n">
-        <v>-1.94</v>
+        <v>-9.9</v>
       </c>
       <c r="M303" t="n">
-        <v>16.94</v>
+        <v>12.13</v>
       </c>
       <c r="N303" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O303" t="inlineStr">
         <is>
@@ -16263,12 +16283,12 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>KEYS</t>
+          <t>GDDY</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>B2</t>
+          <t>DLB</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
@@ -16276,35 +16296,39 @@
           <t>Retired</t>
         </is>
       </c>
-      <c r="E304" t="inlineStr"/>
+      <c r="E304" t="inlineStr">
+        <is>
+          <t>WR30</t>
+        </is>
+      </c>
       <c r="F304" t="n">
         <v>2.2</v>
       </c>
       <c r="G304" t="n">
-        <v>19.8</v>
+        <v>-7.4</v>
       </c>
       <c r="H304" t="n">
-        <v>11.74</v>
+        <v>4.66</v>
       </c>
       <c r="I304" t="n">
-        <v>4.74</v>
+        <v>-3.85</v>
       </c>
       <c r="J304" t="n">
-        <v>4.67</v>
+        <v>3.39</v>
       </c>
       <c r="K304" t="inlineStr"/>
       <c r="L304" t="n">
-        <v>-9.9</v>
+        <v>-21.11</v>
       </c>
       <c r="M304" t="n">
-        <v>9.289999999999999</v>
+        <v>2.04</v>
       </c>
       <c r="N304" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O304" t="inlineStr">
         <is>
-          <t>10..20</t>
+          <t>-10..0</t>
         </is>
       </c>
     </row>
@@ -16314,7 +16338,7 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>GDDY</t>
+          <t>CE</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
@@ -16327,39 +16351,35 @@
           <t>Retired</t>
         </is>
       </c>
-      <c r="E305" t="inlineStr">
-        <is>
-          <t>WR30</t>
-        </is>
-      </c>
+      <c r="E305" t="inlineStr"/>
       <c r="F305" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="G305" t="n">
-        <v>-7.4</v>
+        <v>-10.8</v>
       </c>
       <c r="H305" t="n">
-        <v>3.08</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="I305" t="n">
-        <v>-3.85</v>
+        <v>1.78</v>
       </c>
       <c r="J305" t="n">
-        <v>3.39</v>
+        <v>0.45</v>
       </c>
       <c r="K305" t="inlineStr"/>
       <c r="L305" t="n">
-        <v>-21.11</v>
+        <v>-7.51</v>
       </c>
       <c r="M305" t="n">
-        <v>0.63</v>
+        <v>-3.19</v>
       </c>
       <c r="N305" t="b">
         <v>0</v>
       </c>
       <c r="O305" t="inlineStr">
         <is>
-          <t>-10..0</t>
+          <t>&lt;-10</t>
         </is>
       </c>
     </row>
@@ -16369,7 +16389,7 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>CE</t>
+          <t>ZS</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
@@ -16387,23 +16407,23 @@
         <v>2.1</v>
       </c>
       <c r="G306" t="n">
-        <v>-10.8</v>
+        <v>-24</v>
       </c>
       <c r="H306" t="n">
-        <v>-0.18</v>
+        <v>35</v>
       </c>
       <c r="I306" t="n">
-        <v>1.78</v>
+        <v>10.85</v>
       </c>
       <c r="J306" t="n">
-        <v>0.45</v>
+        <v>26.12</v>
       </c>
       <c r="K306" t="inlineStr"/>
       <c r="L306" t="n">
-        <v>-7.51</v>
+        <v>-5.43</v>
       </c>
       <c r="M306" t="n">
-        <v>-2.62</v>
+        <v>32.38</v>
       </c>
       <c r="N306" t="b">
         <v>0</v>
@@ -16420,7 +16440,7 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>ZS</t>
+          <t>XPEV</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
@@ -16438,23 +16458,23 @@
         <v>2.1</v>
       </c>
       <c r="G307" t="n">
-        <v>-24</v>
+        <v>-28.3</v>
       </c>
       <c r="H307" t="n">
-        <v>35.44</v>
+        <v>-28.83</v>
       </c>
       <c r="I307" t="n">
-        <v>10.85</v>
+        <v>-8.949999999999999</v>
       </c>
       <c r="J307" t="n">
-        <v>26.12</v>
+        <v>-11.3</v>
       </c>
       <c r="K307" t="inlineStr"/>
       <c r="L307" t="n">
-        <v>-5.43</v>
+        <v>-13.18</v>
       </c>
       <c r="M307" t="n">
-        <v>33</v>
+        <v>-31.45</v>
       </c>
       <c r="N307" t="b">
         <v>0</v>
@@ -16471,7 +16491,7 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>XPEV</t>
+          <t>CELH</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
@@ -16489,26 +16509,26 @@
         <v>2.1</v>
       </c>
       <c r="G308" t="n">
-        <v>-28.3</v>
+        <v>-30.5</v>
       </c>
       <c r="H308" t="n">
-        <v>-27.77</v>
+        <v>-4.46</v>
       </c>
       <c r="I308" t="n">
-        <v>-8.949999999999999</v>
+        <v>2.96</v>
       </c>
       <c r="J308" t="n">
-        <v>-11.3</v>
+        <v>4.22</v>
       </c>
       <c r="K308" t="inlineStr"/>
       <c r="L308" t="n">
-        <v>-13.18</v>
+        <v>-17.88</v>
       </c>
       <c r="M308" t="n">
-        <v>-30.21</v>
+        <v>-7.09</v>
       </c>
       <c r="N308" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O308" t="inlineStr">
         <is>
@@ -16522,7 +16542,7 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>CELH</t>
+          <t>FN</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
@@ -16540,30 +16560,30 @@
         <v>2.1</v>
       </c>
       <c r="G309" t="n">
-        <v>-30.5</v>
+        <v>-6</v>
       </c>
       <c r="H309" t="n">
-        <v>-4.67</v>
+        <v>-12.17</v>
       </c>
       <c r="I309" t="n">
-        <v>2.96</v>
+        <v>3.31</v>
       </c>
       <c r="J309" t="n">
-        <v>4.22</v>
+        <v>-6.11</v>
       </c>
       <c r="K309" t="inlineStr"/>
       <c r="L309" t="n">
-        <v>-17.88</v>
+        <v>-21.48</v>
       </c>
       <c r="M309" t="n">
-        <v>-7.11</v>
+        <v>-14.8</v>
       </c>
       <c r="N309" t="b">
         <v>1</v>
       </c>
       <c r="O309" t="inlineStr">
         <is>
-          <t>&lt;-10</t>
+          <t>-10..0</t>
         </is>
       </c>
     </row>
@@ -16573,7 +16593,7 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>FN</t>
+          <t>AVAV</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
@@ -16591,30 +16611,30 @@
         <v>2.1</v>
       </c>
       <c r="G310" t="n">
-        <v>-6</v>
+        <v>-42.2</v>
       </c>
       <c r="H310" t="n">
-        <v>-17.46</v>
+        <v>0.33</v>
       </c>
       <c r="I310" t="n">
-        <v>3.31</v>
+        <v>19.24</v>
       </c>
       <c r="J310" t="n">
-        <v>-6.11</v>
+        <v>22.85</v>
       </c>
       <c r="K310" t="inlineStr"/>
       <c r="L310" t="n">
-        <v>-21.48</v>
+        <v>-0.93</v>
       </c>
       <c r="M310" t="n">
-        <v>-19.9</v>
+        <v>-2.11</v>
       </c>
       <c r="N310" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O310" t="inlineStr">
         <is>
-          <t>-10..0</t>
+          <t>&lt;-10</t>
         </is>
       </c>
     </row>
@@ -16624,7 +16644,7 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>AVAV</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
@@ -16642,26 +16662,26 @@
         <v>2.1</v>
       </c>
       <c r="G311" t="n">
-        <v>-42.2</v>
+        <v>-34.6</v>
       </c>
       <c r="H311" t="n">
-        <v>0.33</v>
+        <v>2.02</v>
       </c>
       <c r="I311" t="n">
-        <v>19.24</v>
+        <v>23.65</v>
       </c>
       <c r="J311" t="n">
-        <v>22.85</v>
+        <v>3.79</v>
       </c>
       <c r="K311" t="inlineStr"/>
       <c r="L311" t="n">
-        <v>-0.93</v>
+        <v>-3.83</v>
       </c>
       <c r="M311" t="n">
-        <v>-2.11</v>
+        <v>-0.61</v>
       </c>
       <c r="N311" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O311" t="inlineStr">
         <is>
@@ -16675,7 +16695,7 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>OKLO</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
@@ -16693,26 +16713,26 @@
         <v>2.1</v>
       </c>
       <c r="G312" t="n">
-        <v>-34.6</v>
+        <v>-48.1</v>
       </c>
       <c r="H312" t="n">
-        <v>-5.22</v>
+        <v>-14.76</v>
       </c>
       <c r="I312" t="n">
-        <v>23.65</v>
+        <v>2.19</v>
       </c>
       <c r="J312" t="n">
-        <v>3.79</v>
+        <v>-2.45</v>
       </c>
       <c r="K312" t="inlineStr"/>
       <c r="L312" t="n">
-        <v>-3.83</v>
+        <v>-13.66</v>
       </c>
       <c r="M312" t="n">
-        <v>-7.66</v>
+        <v>-17.39</v>
       </c>
       <c r="N312" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O312" t="inlineStr">
         <is>
@@ -16726,7 +16746,7 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>OKLO</t>
+          <t>BDC</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
@@ -16744,26 +16764,26 @@
         <v>2.1</v>
       </c>
       <c r="G313" t="n">
-        <v>-48.1</v>
+        <v>-16.2</v>
       </c>
       <c r="H313" t="n">
-        <v>-12.69</v>
+        <v>6.92</v>
       </c>
       <c r="I313" t="n">
-        <v>2.19</v>
+        <v>25.77</v>
       </c>
       <c r="J313" t="n">
-        <v>-2.45</v>
+        <v>27.71</v>
       </c>
       <c r="K313" t="inlineStr"/>
       <c r="L313" t="n">
-        <v>-13.66</v>
+        <v>-1.7</v>
       </c>
       <c r="M313" t="n">
-        <v>-15.13</v>
+        <v>4.29</v>
       </c>
       <c r="N313" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O313" t="inlineStr">
         <is>
@@ -16777,7 +16797,7 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>BDC</t>
+          <t>CDE</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
@@ -16795,23 +16815,23 @@
         <v>2.1</v>
       </c>
       <c r="G314" t="n">
-        <v>-16.2</v>
+        <v>-24.9</v>
       </c>
       <c r="H314" t="n">
-        <v>6.57</v>
+        <v>20.11</v>
       </c>
       <c r="I314" t="n">
-        <v>25.77</v>
+        <v>10.88</v>
       </c>
       <c r="J314" t="n">
-        <v>27.71</v>
+        <v>26.61</v>
       </c>
       <c r="K314" t="inlineStr"/>
       <c r="L314" t="n">
-        <v>-1.7</v>
+        <v>-4.1</v>
       </c>
       <c r="M314" t="n">
-        <v>4.13</v>
+        <v>17.48</v>
       </c>
       <c r="N314" t="b">
         <v>1</v>
@@ -16828,7 +16848,7 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>CDE</t>
+          <t>APPF</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
@@ -16841,35 +16861,39 @@
           <t>Retired</t>
         </is>
       </c>
-      <c r="E315" t="inlineStr"/>
+      <c r="E315" t="inlineStr">
+        <is>
+          <t>WR20</t>
+        </is>
+      </c>
       <c r="F315" t="n">
         <v>2.1</v>
       </c>
       <c r="G315" t="n">
-        <v>-24.9</v>
+        <v>-8.1</v>
       </c>
       <c r="H315" t="n">
-        <v>20.38</v>
+        <v>16.96</v>
       </c>
       <c r="I315" t="n">
-        <v>10.88</v>
+        <v>14.27</v>
       </c>
       <c r="J315" t="n">
-        <v>26.61</v>
+        <v>16.8</v>
       </c>
       <c r="K315" t="inlineStr"/>
       <c r="L315" t="n">
-        <v>-4.1</v>
+        <v>-10.92</v>
       </c>
       <c r="M315" t="n">
-        <v>17.94</v>
+        <v>14.34</v>
       </c>
       <c r="N315" t="b">
         <v>1</v>
       </c>
       <c r="O315" t="inlineStr">
         <is>
-          <t>&lt;-10</t>
+          <t>-10..0</t>
         </is>
       </c>
     </row>
@@ -16879,7 +16903,7 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>APPF</t>
+          <t>FND</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
@@ -16892,39 +16916,35 @@
           <t>Retired</t>
         </is>
       </c>
-      <c r="E316" t="inlineStr">
-        <is>
-          <t>WR20</t>
-        </is>
-      </c>
+      <c r="E316" t="inlineStr"/>
       <c r="F316" t="n">
         <v>2.1</v>
       </c>
       <c r="G316" t="n">
-        <v>-8.1</v>
+        <v>-10.2</v>
       </c>
       <c r="H316" t="n">
-        <v>14.83</v>
+        <v>-12.77</v>
       </c>
       <c r="I316" t="n">
-        <v>14.27</v>
+        <v>15.03</v>
       </c>
       <c r="J316" t="n">
-        <v>16.8</v>
+        <v>6.22</v>
       </c>
       <c r="K316" t="inlineStr"/>
       <c r="L316" t="n">
-        <v>-10.92</v>
+        <v>-1.61</v>
       </c>
       <c r="M316" t="n">
-        <v>12.39</v>
+        <v>-15.4</v>
       </c>
       <c r="N316" t="b">
         <v>1</v>
       </c>
       <c r="O316" t="inlineStr">
         <is>
-          <t>-10..0</t>
+          <t>&lt;-10</t>
         </is>
       </c>
     </row>
@@ -16934,12 +16954,12 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>FND</t>
+          <t>PBF</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>DLB</t>
+          <t>S2</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
@@ -16949,33 +16969,33 @@
       </c>
       <c r="E317" t="inlineStr"/>
       <c r="F317" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="G317" t="n">
-        <v>-10.2</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="H317" t="n">
-        <v>-13.19</v>
+        <v>27.74</v>
       </c>
       <c r="I317" t="n">
-        <v>15.03</v>
+        <v>1.84</v>
       </c>
       <c r="J317" t="n">
-        <v>6.22</v>
+        <v>16.66</v>
       </c>
       <c r="K317" t="inlineStr"/>
       <c r="L317" t="n">
-        <v>-1.61</v>
+        <v>-10.43</v>
       </c>
       <c r="M317" t="n">
-        <v>-15.63</v>
+        <v>25.11</v>
       </c>
       <c r="N317" t="b">
         <v>1</v>
       </c>
       <c r="O317" t="inlineStr">
         <is>
-          <t>&lt;-10</t>
+          <t>&gt;20</t>
         </is>
       </c>
     </row>
@@ -16985,12 +17005,12 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>PBF</t>
+          <t>WHR</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>DLB</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
@@ -17003,30 +17023,30 @@
         <v>2</v>
       </c>
       <c r="G318" t="n">
-        <v>68.90000000000001</v>
+        <v>-40.8</v>
       </c>
       <c r="H318" t="n">
-        <v>19.39</v>
+        <v>-16.86</v>
       </c>
       <c r="I318" t="n">
-        <v>1.84</v>
+        <v>21.71</v>
       </c>
       <c r="J318" t="n">
-        <v>16.66</v>
+        <v>7.12</v>
       </c>
       <c r="K318" t="inlineStr"/>
       <c r="L318" t="n">
-        <v>-10.43</v>
+        <v>-3.3</v>
       </c>
       <c r="M318" t="n">
-        <v>16.95</v>
+        <v>-19.48</v>
       </c>
       <c r="N318" t="b">
         <v>1</v>
       </c>
       <c r="O318" t="inlineStr">
         <is>
-          <t>&gt;20</t>
+          <t>&lt;-10</t>
         </is>
       </c>
     </row>
@@ -17036,7 +17056,7 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>WHR</t>
+          <t>CAVA</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
@@ -17054,26 +17074,26 @@
         <v>2</v>
       </c>
       <c r="G319" t="n">
-        <v>-40.8</v>
+        <v>-10.1</v>
       </c>
       <c r="H319" t="n">
-        <v>-16.31</v>
+        <v>-12.68</v>
       </c>
       <c r="I319" t="n">
-        <v>21.71</v>
+        <v>1.83</v>
       </c>
       <c r="J319" t="n">
-        <v>7.12</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="K319" t="inlineStr"/>
       <c r="L319" t="n">
-        <v>-3.3</v>
+        <v>-3.45</v>
       </c>
       <c r="M319" t="n">
-        <v>-18.76</v>
+        <v>-15.31</v>
       </c>
       <c r="N319" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O319" t="inlineStr">
         <is>
@@ -17087,12 +17107,12 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>CAVA</t>
+          <t>TWLO</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>DLB</t>
+          <t>B2</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
@@ -17105,30 +17125,30 @@
         <v>2</v>
       </c>
       <c r="G320" t="n">
-        <v>-10.1</v>
+        <v>40.7</v>
       </c>
       <c r="H320" t="n">
-        <v>-13.16</v>
+        <v>48.92</v>
       </c>
       <c r="I320" t="n">
-        <v>1.83</v>
+        <v>-4.08</v>
       </c>
       <c r="J320" t="n">
-        <v>9.529999999999999</v>
+        <v>14.73</v>
       </c>
       <c r="K320" t="inlineStr"/>
       <c r="L320" t="n">
-        <v>-3.45</v>
+        <v>-11.2</v>
       </c>
       <c r="M320" t="n">
-        <v>-15.61</v>
+        <v>46.3</v>
       </c>
       <c r="N320" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O320" t="inlineStr">
         <is>
-          <t>&lt;-10</t>
+          <t>&gt;20</t>
         </is>
       </c>
     </row>
@@ -17138,7 +17158,7 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>TWLO</t>
+          <t>CGNX</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
@@ -17156,23 +17176,23 @@
         <v>2</v>
       </c>
       <c r="G321" t="n">
-        <v>40.7</v>
+        <v>25.7</v>
       </c>
       <c r="H321" t="n">
-        <v>44.57</v>
+        <v>-3.04</v>
       </c>
       <c r="I321" t="n">
-        <v>-4.08</v>
+        <v>11.3</v>
       </c>
       <c r="J321" t="n">
-        <v>14.73</v>
+        <v>-1.32</v>
       </c>
       <c r="K321" t="inlineStr"/>
       <c r="L321" t="n">
-        <v>-11.2</v>
+        <v>-11.03</v>
       </c>
       <c r="M321" t="n">
-        <v>42.12</v>
+        <v>-5.66</v>
       </c>
       <c r="N321" t="b">
         <v>1</v>
@@ -17189,12 +17209,12 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>CGNX</t>
+          <t>DOW</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>B2</t>
+          <t>D200G</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
@@ -17207,79 +17227,28 @@
         <v>2</v>
       </c>
       <c r="G322" t="n">
-        <v>25.7</v>
+        <v>2.3</v>
       </c>
       <c r="H322" t="n">
-        <v>-5.49</v>
+        <v>-8.85</v>
       </c>
       <c r="I322" t="n">
-        <v>11.3</v>
+        <v>-0.95</v>
       </c>
       <c r="J322" t="n">
-        <v>-1.32</v>
+        <v>1.86</v>
       </c>
       <c r="K322" t="inlineStr"/>
       <c r="L322" t="n">
-        <v>-11.03</v>
+        <v>-7.81</v>
       </c>
       <c r="M322" t="n">
-        <v>-7.93</v>
+        <v>-11.48</v>
       </c>
       <c r="N322" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O322" t="inlineStr">
-        <is>
-          <t>&gt;20</t>
-        </is>
-      </c>
-    </row>
-    <row r="323">
-      <c r="A323" s="1" t="n">
-        <v>46224</v>
-      </c>
-      <c r="B323" t="inlineStr">
-        <is>
-          <t>DOW</t>
-        </is>
-      </c>
-      <c r="C323" t="inlineStr">
-        <is>
-          <t>D200G</t>
-        </is>
-      </c>
-      <c r="D323" t="inlineStr">
-        <is>
-          <t>Retired</t>
-        </is>
-      </c>
-      <c r="E323" t="inlineStr"/>
-      <c r="F323" t="n">
-        <v>2</v>
-      </c>
-      <c r="G323" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="H323" t="n">
-        <v>-9.02</v>
-      </c>
-      <c r="I323" t="n">
-        <v>-0.95</v>
-      </c>
-      <c r="J323" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="K323" t="inlineStr"/>
-      <c r="L323" t="n">
-        <v>-7.81</v>
-      </c>
-      <c r="M323" t="n">
-        <v>-11.46</v>
-      </c>
-      <c r="N323" t="b">
-        <v>0</v>
-      </c>
-      <c r="O323" t="inlineStr">
         <is>
           <t>0..10</t>
         </is>
@@ -17406,16 +17375,16 @@
         <v>-21.8</v>
       </c>
       <c r="H2" t="n">
-        <v>-3.45</v>
+        <v>-2.98</v>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="n">
-        <v>-4.4</v>
+        <v>-5.26</v>
       </c>
       <c r="M2" t="n">
-        <v>-2.96</v>
+        <v>-2.66</v>
       </c>
       <c r="N2" t="b">
         <v>1</v>
@@ -17442,7 +17411,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Extended</t>
         </is>
       </c>
       <c r="E3" t="inlineStr"/>
@@ -17453,16 +17422,16 @@
         <v>-16.7</v>
       </c>
       <c r="H3" t="n">
-        <v>-5.03</v>
+        <v>12.83</v>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="n">
-        <v>-6.71</v>
+        <v>-6.98</v>
       </c>
       <c r="M3" t="n">
-        <v>-4.48</v>
+        <v>13.2</v>
       </c>
       <c r="N3" t="b">
         <v>1</v>
@@ -17500,7 +17469,7 @@
         <v>-11.5</v>
       </c>
       <c r="H4" t="n">
-        <v>2.18</v>
+        <v>3.64</v>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
@@ -17509,7 +17478,7 @@
         <v>-0.99</v>
       </c>
       <c r="M4" t="n">
-        <v>2.73</v>
+        <v>4.01</v>
       </c>
       <c r="N4" t="b">
         <v>1</v>
@@ -17547,16 +17516,16 @@
         <v>0.1</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.65</v>
+        <v>1.37</v>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="n">
-        <v>-1.9</v>
+        <v>-2.51</v>
       </c>
       <c r="M5" t="n">
-        <v>0.15</v>
+        <v>1.99</v>
       </c>
       <c r="N5" t="b">
         <v>1</v>
@@ -17594,16 +17563,16 @@
         <v>-31.6</v>
       </c>
       <c r="H6" t="n">
-        <v>-3.71</v>
+        <v>-1.91</v>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="n">
-        <v>-4.03</v>
+        <v>-5.01</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.91</v>
+        <v>-1.29</v>
       </c>
       <c r="N6" t="b">
         <v>1</v>
@@ -17641,16 +17610,16 @@
         <v>-2.7</v>
       </c>
       <c r="H7" t="n">
-        <v>-6.21</v>
+        <v>-5.93</v>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="n">
-        <v>-6.35</v>
+        <v>-8.800000000000001</v>
       </c>
       <c r="M7" t="n">
-        <v>-4.74</v>
+        <v>-4.63</v>
       </c>
       <c r="N7" t="b">
         <v>1</v>
@@ -17677,7 +17646,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Extended</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
@@ -17688,16 +17657,16 @@
         <v>26.9</v>
       </c>
       <c r="H8" t="n">
-        <v>6.37</v>
+        <v>-1.93</v>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="n">
-        <v>-0.4</v>
+        <v>-1.99</v>
       </c>
       <c r="M8" t="n">
-        <v>7.84</v>
+        <v>-0.63</v>
       </c>
       <c r="N8" t="b">
         <v>1</v>
@@ -17735,7 +17704,7 @@
         <v>-18.1</v>
       </c>
       <c r="H9" t="n">
-        <v>2.95</v>
+        <v>4.82</v>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
@@ -17744,7 +17713,7 @@
         <v>-2.69</v>
       </c>
       <c r="M9" t="n">
-        <v>3.43</v>
+        <v>5.12</v>
       </c>
       <c r="N9" t="b">
         <v>1</v>
@@ -17782,7 +17751,7 @@
         <v>-21.5</v>
       </c>
       <c r="H10" t="n">
-        <v>1.04</v>
+        <v>0.97</v>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
@@ -17791,7 +17760,7 @@
         <v>-1.4</v>
       </c>
       <c r="M10" t="n">
-        <v>1.51</v>
+        <v>1.26</v>
       </c>
       <c r="N10" t="b">
         <v>1</v>
@@ -17829,7 +17798,7 @@
         <v>41.6</v>
       </c>
       <c r="H11" t="n">
-        <v>4.36</v>
+        <v>1.75</v>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
@@ -17838,7 +17807,7 @@
         <v>-4.38</v>
       </c>
       <c r="M11" t="n">
-        <v>4.19</v>
+        <v>1.4</v>
       </c>
       <c r="N11" t="b">
         <v>1</v>
@@ -17876,7 +17845,7 @@
         <v>32.1</v>
       </c>
       <c r="H12" t="n">
-        <v>-6.04</v>
+        <v>-3.47</v>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
@@ -17885,7 +17854,7 @@
         <v>-6.94</v>
       </c>
       <c r="M12" t="n">
-        <v>-6.22</v>
+        <v>-3.82</v>
       </c>
       <c r="N12" t="b">
         <v>1</v>
@@ -17923,16 +17892,16 @@
         <v>-14.4</v>
       </c>
       <c r="H13" t="n">
-        <v>-3.67</v>
+        <v>-2.48</v>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="n">
-        <v>-4.61</v>
+        <v>-6.43</v>
       </c>
       <c r="M13" t="n">
-        <v>-3.84</v>
+        <v>-2.83</v>
       </c>
       <c r="N13" t="b">
         <v>1</v>
@@ -17970,16 +17939,16 @@
         <v>-10</v>
       </c>
       <c r="H14" t="n">
-        <v>-5.16</v>
+        <v>-4.4</v>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="n">
-        <v>-9.539999999999999</v>
+        <v>-10.65</v>
       </c>
       <c r="M14" t="n">
-        <v>-5.33</v>
+        <v>-4.75</v>
       </c>
       <c r="N14" t="b">
         <v>1</v>
@@ -18017,7 +17986,7 @@
         <v>6.4</v>
       </c>
       <c r="H15" t="n">
-        <v>-2.41</v>
+        <v>3.55</v>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
@@ -18026,7 +17995,7 @@
         <v>-3.35</v>
       </c>
       <c r="M15" t="n">
-        <v>-2.59</v>
+        <v>3.2</v>
       </c>
       <c r="N15" t="b">
         <v>1</v>
@@ -18053,7 +18022,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Extended</t>
         </is>
       </c>
       <c r="E16" t="inlineStr"/>
@@ -18064,7 +18033,7 @@
         <v>20.2</v>
       </c>
       <c r="H16" t="n">
-        <v>2.63</v>
+        <v>5.34</v>
       </c>
       <c r="I16" t="n">
         <v>3.45</v>
@@ -18075,7 +18044,7 @@
         <v>-1.07</v>
       </c>
       <c r="M16" t="n">
-        <v>2.06</v>
+        <v>4.58</v>
       </c>
       <c r="N16" t="b">
         <v>1</v>
@@ -18113,7 +18082,7 @@
         <v>43.7</v>
       </c>
       <c r="H17" t="n">
-        <v>2.09</v>
+        <v>-1.11</v>
       </c>
       <c r="I17" t="n">
         <v>3.16</v>
@@ -18124,7 +18093,7 @@
         <v>-2.44</v>
       </c>
       <c r="M17" t="n">
-        <v>1.51</v>
+        <v>-1.87</v>
       </c>
       <c r="N17" t="b">
         <v>1</v>
@@ -18162,7 +18131,7 @@
         <v>1.9</v>
       </c>
       <c r="H18" t="n">
-        <v>-11.01</v>
+        <v>-9.67</v>
       </c>
       <c r="I18" t="n">
         <v>-10.64</v>
@@ -18170,10 +18139,10 @@
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="n">
-        <v>-11.27</v>
+        <v>-11.41</v>
       </c>
       <c r="M18" t="n">
-        <v>-11.59</v>
+        <v>-10.42</v>
       </c>
       <c r="N18" t="b">
         <v>1</v>
@@ -18200,7 +18169,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Extended</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="E19" t="inlineStr"/>
@@ -18211,7 +18180,7 @@
         <v>37.5</v>
       </c>
       <c r="H19" t="n">
-        <v>6.02</v>
+        <v>3.08</v>
       </c>
       <c r="I19" t="n">
         <v>5.86</v>
@@ -18222,7 +18191,7 @@
         <v>-3.95</v>
       </c>
       <c r="M19" t="n">
-        <v>5.29</v>
+        <v>2.17</v>
       </c>
       <c r="N19" t="b">
         <v>1</v>
@@ -18260,7 +18229,7 @@
         <v>40.2</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.57</v>
+        <v>-2.44</v>
       </c>
       <c r="I20" t="n">
         <v>-1.11</v>
@@ -18271,7 +18240,7 @@
         <v>-3.87</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.3</v>
+        <v>-3.35</v>
       </c>
       <c r="N20" t="b">
         <v>1</v>
@@ -18298,7 +18267,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Extended</t>
         </is>
       </c>
       <c r="E21" t="inlineStr"/>
@@ -18309,7 +18278,7 @@
         <v>10.7</v>
       </c>
       <c r="H21" t="n">
-        <v>4.96</v>
+        <v>7.36</v>
       </c>
       <c r="I21" t="n">
         <v>7.3</v>
@@ -18320,7 +18289,7 @@
         <v>-3.78</v>
       </c>
       <c r="M21" t="n">
-        <v>4.24</v>
+        <v>6.46</v>
       </c>
       <c r="N21" t="b">
         <v>1</v>
@@ -18358,7 +18327,7 @@
         <v>25.6</v>
       </c>
       <c r="H22" t="n">
-        <v>9.16</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="I22" t="n">
         <v>7.71</v>
@@ -18369,7 +18338,7 @@
         <v>-4.85</v>
       </c>
       <c r="M22" t="n">
-        <v>9.18</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="N22" t="b">
         <v>1</v>
@@ -18396,7 +18365,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Extended</t>
         </is>
       </c>
       <c r="E23" t="inlineStr"/>
@@ -18407,7 +18376,7 @@
         <v>-6.9</v>
       </c>
       <c r="H23" t="n">
-        <v>4.55</v>
+        <v>7.09</v>
       </c>
       <c r="I23" t="n">
         <v>6.44</v>
@@ -18418,7 +18387,7 @@
         <v>-4.53</v>
       </c>
       <c r="M23" t="n">
-        <v>4.49</v>
+        <v>6.85</v>
       </c>
       <c r="N23" t="b">
         <v>1</v>
@@ -18445,7 +18414,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Retired</t>
         </is>
       </c>
       <c r="E24" t="inlineStr"/>
@@ -18456,7 +18425,7 @@
         <v>0.3</v>
       </c>
       <c r="H24" t="n">
-        <v>-14.59</v>
+        <v>-15.48</v>
       </c>
       <c r="I24" t="n">
         <v>-10.53</v>
@@ -18464,10 +18433,10 @@
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="n">
-        <v>-15.78</v>
+        <v>-17.73</v>
       </c>
       <c r="M24" t="n">
-        <v>-14.15</v>
+        <v>-15.22</v>
       </c>
       <c r="N24" t="b">
         <v>1</v>
@@ -18505,18 +18474,20 @@
         <v>2.8</v>
       </c>
       <c r="H25" t="n">
-        <v>1.51</v>
+        <v>3.44</v>
       </c>
       <c r="I25" t="n">
         <v>3.18</v>
       </c>
-      <c r="J25" t="inlineStr"/>
+      <c r="J25" t="n">
+        <v>3.44</v>
+      </c>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="n">
         <v>-0.88</v>
       </c>
       <c r="M25" t="n">
-        <v>1.24</v>
+        <v>2.99</v>
       </c>
       <c r="N25" t="b">
         <v>1</v>
@@ -18554,18 +18525,20 @@
         <v>34.5</v>
       </c>
       <c r="H26" t="n">
-        <v>8.039999999999999</v>
+        <v>8.66</v>
       </c>
       <c r="I26" t="n">
         <v>0.66</v>
       </c>
-      <c r="J26" t="inlineStr"/>
+      <c r="J26" t="n">
+        <v>8.66</v>
+      </c>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="n">
         <v>-2.64</v>
       </c>
       <c r="M26" t="n">
-        <v>7.77</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="N26" t="b">
         <v>1</v>
@@ -18603,7 +18576,7 @@
         <v>24.3</v>
       </c>
       <c r="H27" t="n">
-        <v>38.29</v>
+        <v>41.83</v>
       </c>
       <c r="I27" t="n">
         <v>2.54</v>
@@ -18616,7 +18589,7 @@
         <v>-5.21</v>
       </c>
       <c r="M27" t="n">
-        <v>38.65</v>
+        <v>42.02</v>
       </c>
       <c r="N27" t="b">
         <v>1</v>
@@ -18654,7 +18627,7 @@
         <v>-16.9</v>
       </c>
       <c r="H28" t="n">
-        <v>-6.9</v>
+        <v>-6.47</v>
       </c>
       <c r="I28" t="n">
         <v>-6.47</v>
@@ -18667,7 +18640,7 @@
         <v>-11.5</v>
       </c>
       <c r="M28" t="n">
-        <v>-6.53</v>
+        <v>-6.28</v>
       </c>
       <c r="N28" t="b">
         <v>1</v>
@@ -18705,7 +18678,7 @@
         <v>20.3</v>
       </c>
       <c r="H29" t="n">
-        <v>-20.18</v>
+        <v>-16.28</v>
       </c>
       <c r="I29" t="n">
         <v>-2.07</v>
@@ -18718,7 +18691,7 @@
         <v>-17.35</v>
       </c>
       <c r="M29" t="n">
-        <v>-19.66</v>
+        <v>-15.94</v>
       </c>
       <c r="N29" t="b">
         <v>1</v>
@@ -18756,7 +18729,7 @@
         <v>0.3</v>
       </c>
       <c r="H30" t="n">
-        <v>-17.73</v>
+        <v>-16.11</v>
       </c>
       <c r="I30" t="n">
         <v>-9.9</v>
@@ -18769,7 +18742,7 @@
         <v>-21.72</v>
       </c>
       <c r="M30" t="n">
-        <v>-17.71</v>
+        <v>-16.26</v>
       </c>
       <c r="N30" t="b">
         <v>1</v>
@@ -18807,7 +18780,7 @@
         <v>49.4</v>
       </c>
       <c r="H31" t="n">
-        <v>5.41</v>
+        <v>6.16</v>
       </c>
       <c r="I31" t="n">
         <v>2.9</v>
@@ -18820,7 +18793,7 @@
         <v>-5.67</v>
       </c>
       <c r="M31" t="n">
-        <v>5.62</v>
+        <v>6.2</v>
       </c>
       <c r="N31" t="b">
         <v>1</v>
@@ -18858,7 +18831,7 @@
         <v>4.5</v>
       </c>
       <c r="H32" t="n">
-        <v>-11.46</v>
+        <v>-11.43</v>
       </c>
       <c r="I32" t="n">
         <v>-7.61</v>
@@ -18871,7 +18844,7 @@
         <v>-11.06</v>
       </c>
       <c r="M32" t="n">
-        <v>-11.25</v>
+        <v>-11.4</v>
       </c>
       <c r="N32" t="b">
         <v>1</v>
@@ -18909,7 +18882,7 @@
         <v>-17.9</v>
       </c>
       <c r="H33" t="n">
-        <v>-8.42</v>
+        <v>-7.83</v>
       </c>
       <c r="I33" t="n">
         <v>0.6</v>
@@ -18922,7 +18895,7 @@
         <v>-4.72</v>
       </c>
       <c r="M33" t="n">
-        <v>-8.23</v>
+        <v>-7.82</v>
       </c>
       <c r="N33" t="b">
         <v>1</v>
@@ -18960,7 +18933,7 @@
         <v>2.1</v>
       </c>
       <c r="H34" t="n">
-        <v>-27.24</v>
+        <v>-25.92</v>
       </c>
       <c r="I34" t="n">
         <v>0.25</v>
@@ -18973,7 +18946,7 @@
         <v>-16.43</v>
       </c>
       <c r="M34" t="n">
-        <v>-27.05</v>
+        <v>-25.91</v>
       </c>
       <c r="N34" t="b">
         <v>1</v>
@@ -19011,7 +18984,7 @@
         <v>19.4</v>
       </c>
       <c r="H35" t="n">
-        <v>-12.85</v>
+        <v>-11.58</v>
       </c>
       <c r="I35" t="n">
         <v>-10.01</v>
@@ -19024,7 +18997,7 @@
         <v>-15.23</v>
       </c>
       <c r="M35" t="n">
-        <v>-12.1</v>
+        <v>-11</v>
       </c>
       <c r="N35" t="b">
         <v>1</v>
@@ -19062,7 +19035,7 @@
         <v>-2.6</v>
       </c>
       <c r="H36" t="n">
-        <v>-11.67</v>
+        <v>-10.59</v>
       </c>
       <c r="I36" t="n">
         <v>-4.27</v>
@@ -19075,7 +19048,7 @@
         <v>-4.86</v>
       </c>
       <c r="M36" t="n">
-        <v>-11.13</v>
+        <v>-10.23</v>
       </c>
       <c r="N36" t="b">
         <v>1</v>
@@ -19113,7 +19086,7 @@
         <v>23.8</v>
       </c>
       <c r="H37" t="n">
-        <v>13.23</v>
+        <v>8.32</v>
       </c>
       <c r="I37" t="n">
         <v>1.36</v>
@@ -19126,7 +19099,7 @@
         <v>-9.94</v>
       </c>
       <c r="M37" t="n">
-        <v>14.73</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="N37" t="b">
         <v>1</v>
@@ -19164,7 +19137,7 @@
         <v>38.9</v>
       </c>
       <c r="H38" t="n">
-        <v>-13.67</v>
+        <v>-11.99</v>
       </c>
       <c r="I38" t="n">
         <v>-9.220000000000001</v>
@@ -19177,7 +19150,7 @@
         <v>-9.83</v>
       </c>
       <c r="M38" t="n">
-        <v>-12.16</v>
+        <v>-10.66</v>
       </c>
       <c r="N38" t="b">
         <v>1</v>
@@ -19215,7 +19188,7 @@
         <v>43.2</v>
       </c>
       <c r="H39" t="n">
-        <v>-23.97</v>
+        <v>-21.24</v>
       </c>
       <c r="I39" t="n">
         <v>-3.15</v>
@@ -19228,7 +19201,7 @@
         <v>-17.51</v>
       </c>
       <c r="M39" t="n">
-        <v>-22.64</v>
+        <v>-20.08</v>
       </c>
       <c r="N39" t="b">
         <v>1</v>
@@ -19266,7 +19239,7 @@
         <v>-8.199999999999999</v>
       </c>
       <c r="H40" t="n">
-        <v>-7.19</v>
+        <v>-6.9</v>
       </c>
       <c r="I40" t="n">
         <v>5.34</v>
@@ -19279,7 +19252,7 @@
         <v>-5.27</v>
       </c>
       <c r="M40" t="n">
-        <v>-5.86</v>
+        <v>-5.74</v>
       </c>
       <c r="N40" t="b">
         <v>1</v>
@@ -19317,7 +19290,7 @@
         <v>-23.9</v>
       </c>
       <c r="H41" t="n">
-        <v>-13.31</v>
+        <v>-13.22</v>
       </c>
       <c r="I41" t="n">
         <v>3.28</v>
@@ -19330,7 +19303,7 @@
         <v>-4.46</v>
       </c>
       <c r="M41" t="n">
-        <v>-12.26</v>
+        <v>-12.36</v>
       </c>
       <c r="N41" t="b">
         <v>1</v>
@@ -19372,7 +19345,7 @@
         <v>-6.1</v>
       </c>
       <c r="H42" t="n">
-        <v>-4.57</v>
+        <v>-5.02</v>
       </c>
       <c r="I42" t="n">
         <v>4.9</v>
@@ -19385,7 +19358,7 @@
         <v>-9</v>
       </c>
       <c r="M42" t="n">
-        <v>-3.53</v>
+        <v>-4.15</v>
       </c>
       <c r="N42" t="b">
         <v>1</v>
@@ -19423,7 +19396,7 @@
         <v>26.7</v>
       </c>
       <c r="H43" t="n">
-        <v>-1.31</v>
+        <v>-1.19</v>
       </c>
       <c r="I43" t="n">
         <v>-0.05</v>
@@ -19436,7 +19409,7 @@
         <v>-0.87</v>
       </c>
       <c r="M43" t="n">
-        <v>-0.26</v>
+        <v>-0.32</v>
       </c>
       <c r="N43" t="b">
         <v>1</v>
@@ -19474,7 +19447,7 @@
         <v>-3.5</v>
       </c>
       <c r="H44" t="n">
-        <v>0.54</v>
+        <v>1.25</v>
       </c>
       <c r="I44" t="n">
         <v>-4.95</v>
@@ -19487,7 +19460,7 @@
         <v>-8.43</v>
       </c>
       <c r="M44" t="n">
-        <v>1.39</v>
+        <v>1.91</v>
       </c>
       <c r="N44" t="b">
         <v>1</v>
@@ -19525,7 +19498,7 @@
         <v>-17.9</v>
       </c>
       <c r="H45" t="n">
-        <v>2.48</v>
+        <v>1.15</v>
       </c>
       <c r="I45" t="n">
         <v>-0.5</v>
@@ -19538,7 +19511,7 @@
         <v>-3.43</v>
       </c>
       <c r="M45" t="n">
-        <v>3.32</v>
+        <v>1.81</v>
       </c>
       <c r="N45" t="b">
         <v>1</v>
@@ -19576,7 +19549,7 @@
         <v>53.5</v>
       </c>
       <c r="H46" t="n">
-        <v>-0.92</v>
+        <v>4.13</v>
       </c>
       <c r="I46" t="n">
         <v>1.23</v>
@@ -19589,7 +19562,7 @@
         <v>-7.57</v>
       </c>
       <c r="M46" t="n">
-        <v>-0.38</v>
+        <v>4.69</v>
       </c>
       <c r="N46" t="b">
         <v>1</v>
@@ -19627,7 +19600,7 @@
         <v>-1</v>
       </c>
       <c r="H47" t="n">
-        <v>-17.22</v>
+        <v>-14.52</v>
       </c>
       <c r="I47" t="n">
         <v>-6.26</v>
@@ -19640,7 +19613,7 @@
         <v>-15</v>
       </c>
       <c r="M47" t="n">
-        <v>-16.48</v>
+        <v>-13.96</v>
       </c>
       <c r="N47" t="b">
         <v>1</v>
@@ -19678,7 +19651,7 @@
         <v>29.7</v>
       </c>
       <c r="H48" t="n">
-        <v>10.45</v>
+        <v>7.22</v>
       </c>
       <c r="I48" t="n">
         <v>11.27</v>
@@ -19691,7 +19664,7 @@
         <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>11.19</v>
+        <v>7.78</v>
       </c>
       <c r="N48" t="b">
         <v>1</v>
@@ -19729,7 +19702,7 @@
         <v>15.2</v>
       </c>
       <c r="H49" t="n">
-        <v>-34.65</v>
+        <v>-35.32</v>
       </c>
       <c r="I49" t="n">
         <v>-8.77</v>
@@ -19742,7 +19715,7 @@
         <v>-24.79</v>
       </c>
       <c r="M49" t="n">
-        <v>-33.19</v>
+        <v>-34.03</v>
       </c>
       <c r="N49" t="b">
         <v>1</v>
@@ -19780,7 +19753,7 @@
         <v>22.2</v>
       </c>
       <c r="H50" t="n">
-        <v>6.16</v>
+        <v>4.51</v>
       </c>
       <c r="I50" t="n">
         <v>1.01</v>
@@ -19793,7 +19766,7 @@
         <v>-3.94</v>
       </c>
       <c r="M50" t="n">
-        <v>7.62</v>
+        <v>5.79</v>
       </c>
       <c r="N50" t="b">
         <v>1</v>
@@ -19886,7 +19859,7 @@
         <v>10.5</v>
       </c>
       <c r="H52" t="n">
-        <v>-0.04</v>
+        <v>2.78</v>
       </c>
       <c r="I52" t="n">
         <v>1.99</v>
@@ -19899,7 +19872,7 @@
         <v>-6.27</v>
       </c>
       <c r="M52" t="n">
-        <v>-2.05</v>
+        <v>0.59</v>
       </c>
       <c r="N52" t="b">
         <v>1</v>
@@ -19937,7 +19910,7 @@
         <v>-37</v>
       </c>
       <c r="H53" t="n">
-        <v>35.27</v>
+        <v>36.04</v>
       </c>
       <c r="I53" t="n">
         <v>18.38</v>
@@ -19950,7 +19923,7 @@
         <v>-5.11</v>
       </c>
       <c r="M53" t="n">
-        <v>32.61</v>
+        <v>33.19</v>
       </c>
       <c r="N53" t="b">
         <v>1</v>
@@ -19988,7 +19961,7 @@
         <v>-26.8</v>
       </c>
       <c r="H54" t="n">
-        <v>17.08</v>
+        <v>20.17</v>
       </c>
       <c r="I54" t="n">
         <v>4.56</v>
@@ -20001,7 +19974,7 @@
         <v>-4.09</v>
       </c>
       <c r="M54" t="n">
-        <v>14.42</v>
+        <v>17.32</v>
       </c>
       <c r="N54" t="b">
         <v>1</v>
@@ -20039,7 +20012,7 @@
         <v>-36.5</v>
       </c>
       <c r="H55" t="n">
-        <v>-34.82</v>
+        <v>-35.19</v>
       </c>
       <c r="I55" t="n">
         <v>-27.75</v>
@@ -20052,7 +20025,7 @@
         <v>-31.28</v>
       </c>
       <c r="M55" t="n">
-        <v>-38.13</v>
+        <v>-38.69</v>
       </c>
       <c r="N55" t="b">
         <v>1</v>
@@ -20090,7 +20063,7 @@
         <v>-38.7</v>
       </c>
       <c r="H56" t="n">
-        <v>5.26</v>
+        <v>6.49</v>
       </c>
       <c r="I56" t="n">
         <v>17.17</v>
@@ -20103,7 +20076,7 @@
         <v>-0.54</v>
       </c>
       <c r="M56" t="n">
-        <v>1.94</v>
+        <v>2.99</v>
       </c>
       <c r="N56" t="b">
         <v>1</v>
@@ -20141,7 +20114,7 @@
         <v>-34.6</v>
       </c>
       <c r="H57" t="n">
-        <v>13.53</v>
+        <v>17.45</v>
       </c>
       <c r="I57" t="n">
         <v>6.67</v>
@@ -20154,7 +20127,7 @@
         <v>-3.06</v>
       </c>
       <c r="M57" t="n">
-        <v>10.21</v>
+        <v>13.95</v>
       </c>
       <c r="N57" t="b">
         <v>1</v>
@@ -20192,7 +20165,7 @@
         <v>-11.8</v>
       </c>
       <c r="H58" t="n">
-        <v>-6.27</v>
+        <v>-5.01</v>
       </c>
       <c r="I58" t="n">
         <v>9.76</v>
@@ -20205,7 +20178,7 @@
         <v>-1.63</v>
       </c>
       <c r="M58" t="n">
-        <v>-9.699999999999999</v>
+        <v>-8.619999999999999</v>
       </c>
       <c r="N58" t="b">
         <v>1</v>
@@ -20243,7 +20216,7 @@
         <v>0.1</v>
       </c>
       <c r="H59" t="n">
-        <v>-14.74</v>
+        <v>-11.54</v>
       </c>
       <c r="I59" t="n">
         <v>-2.83</v>
@@ -20256,7 +20229,7 @@
         <v>-5.45</v>
       </c>
       <c r="M59" t="n">
-        <v>-18.17</v>
+        <v>-15.15</v>
       </c>
       <c r="N59" t="b">
         <v>1</v>
@@ -20294,7 +20267,7 @@
         <v>24.1</v>
       </c>
       <c r="H60" t="n">
-        <v>-11.21</v>
+        <v>-7.05</v>
       </c>
       <c r="I60" t="n">
         <v>-8.31</v>
@@ -20307,7 +20280,7 @@
         <v>-18.31</v>
       </c>
       <c r="M60" t="n">
-        <v>-13.85</v>
+        <v>-9.869999999999999</v>
       </c>
       <c r="N60" t="b">
         <v>1</v>
@@ -20345,7 +20318,7 @@
         <v>-15.9</v>
       </c>
       <c r="H61" t="n">
-        <v>0.16</v>
+        <v>2.66</v>
       </c>
       <c r="I61" t="n">
         <v>10.45</v>
@@ -20358,7 +20331,7 @@
         <v>-0.31</v>
       </c>
       <c r="M61" t="n">
-        <v>-2.48</v>
+        <v>-0.15</v>
       </c>
       <c r="N61" t="b">
         <v>1</v>
@@ -20396,7 +20369,7 @@
         <v>-21.8</v>
       </c>
       <c r="H62" t="n">
-        <v>-29.89</v>
+        <v>-32.09</v>
       </c>
       <c r="I62" t="n">
         <v>-18.97</v>
@@ -20409,7 +20382,7 @@
         <v>-26.82</v>
       </c>
       <c r="M62" t="n">
-        <v>-33.29</v>
+        <v>-35.68</v>
       </c>
       <c r="N62" t="b">
         <v>1</v>
@@ -20447,7 +20420,7 @@
         <v>57</v>
       </c>
       <c r="H63" t="n">
-        <v>15.54</v>
+        <v>21.33</v>
       </c>
       <c r="I63" t="n">
         <v>-11.21</v>
@@ -20460,7 +20433,7 @@
         <v>-13.87</v>
       </c>
       <c r="M63" t="n">
-        <v>13.14</v>
+        <v>18.75</v>
       </c>
       <c r="N63" t="b">
         <v>1</v>
@@ -20498,7 +20471,7 @@
         <v>-21.8</v>
       </c>
       <c r="H64" t="n">
-        <v>5.69</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="I64" t="n">
         <v>1.71</v>
@@ -20511,7 +20484,7 @@
         <v>-6.18</v>
       </c>
       <c r="M64" t="n">
-        <v>3.29</v>
+        <v>6.95</v>
       </c>
       <c r="N64" t="b">
         <v>1</v>
@@ -20549,7 +20522,7 @@
         <v>1</v>
       </c>
       <c r="H65" t="n">
-        <v>-33.12</v>
+        <v>-33.47</v>
       </c>
       <c r="I65" t="n">
         <v>-11.52</v>
@@ -20562,7 +20535,7 @@
         <v>-16.26</v>
       </c>
       <c r="M65" t="n">
-        <v>-35.57</v>
+        <v>-36.09</v>
       </c>
       <c r="N65" t="b">
         <v>1</v>
@@ -20600,7 +20573,7 @@
         <v>45.4</v>
       </c>
       <c r="H66" t="n">
-        <v>1.47</v>
+        <v>2.41</v>
       </c>
       <c r="I66" t="n">
         <v>-1.72</v>
@@ -20613,7 +20586,7 @@
         <v>-23.15</v>
       </c>
       <c r="M66" t="n">
-        <v>-0.98</v>
+        <v>-0.22</v>
       </c>
       <c r="N66" t="b">
         <v>1</v>
@@ -20651,7 +20624,7 @@
         <v>76.5</v>
       </c>
       <c r="H67" t="n">
-        <v>15.1</v>
+        <v>18.26</v>
       </c>
       <c r="I67" t="n">
         <v>-5.56</v>
@@ -20664,7 +20637,7 @@
         <v>-33.97</v>
       </c>
       <c r="M67" t="n">
-        <v>12.65</v>
+        <v>15.63</v>
       </c>
       <c r="N67" t="b">
         <v>1</v>
@@ -20702,7 +20675,7 @@
         <v>32.1</v>
       </c>
       <c r="H68" t="n">
-        <v>22.19</v>
+        <v>20.32</v>
       </c>
       <c r="I68" t="n">
         <v>16.93</v>
@@ -20715,7 +20688,7 @@
         <v>-24.48</v>
       </c>
       <c r="M68" t="n">
-        <v>19.74</v>
+        <v>17.7</v>
       </c>
       <c r="N68" t="b">
         <v>1</v>
@@ -20753,7 +20726,7 @@
         <v>51.8</v>
       </c>
       <c r="H69" t="n">
-        <v>9.01</v>
+        <v>9.15</v>
       </c>
       <c r="I69" t="n">
         <v>10.75</v>
@@ -20766,7 +20739,7 @@
         <v>-25.09</v>
       </c>
       <c r="M69" t="n">
-        <v>6.56</v>
+        <v>6.52</v>
       </c>
       <c r="N69" t="b">
         <v>1</v>
@@ -20804,7 +20777,7 @@
         <v>32.3</v>
       </c>
       <c r="H70" t="n">
-        <v>-28.05</v>
+        <v>-26.1</v>
       </c>
       <c r="I70" t="n">
         <v>-20.76</v>
@@ -20817,7 +20790,7 @@
         <v>-27.91</v>
       </c>
       <c r="M70" t="n">
-        <v>-30.49</v>
+        <v>-28.72</v>
       </c>
       <c r="N70" t="b">
         <v>1</v>
@@ -20855,7 +20828,7 @@
         <v>3.7</v>
       </c>
       <c r="H71" t="n">
-        <v>-8.390000000000001</v>
+        <v>-9.9</v>
       </c>
       <c r="I71" t="n">
         <v>-1.11</v>
@@ -20868,7 +20841,7 @@
         <v>-25.46</v>
       </c>
       <c r="M71" t="n">
-        <v>-10.84</v>
+        <v>-12.53</v>
       </c>
       <c r="N71" t="b">
         <v>1</v>
@@ -20906,7 +20879,7 @@
         <v>42.4</v>
       </c>
       <c r="H72" t="n">
-        <v>5.73</v>
+        <v>10.81</v>
       </c>
       <c r="I72" t="n">
         <v>2.16</v>
@@ -20919,7 +20892,7 @@
         <v>-15.76</v>
       </c>
       <c r="M72" t="n">
-        <v>3.29</v>
+        <v>8.19</v>
       </c>
       <c r="N72" t="b">
         <v>1</v>
@@ -20957,7 +20930,7 @@
         <v>28.2</v>
       </c>
       <c r="H73" t="n">
-        <v>2.19</v>
+        <v>9.17</v>
       </c>
       <c r="I73" t="n">
         <v>-1.71</v>
@@ -20970,7 +20943,7 @@
         <v>-23.43</v>
       </c>
       <c r="M73" t="n">
-        <v>-0.25</v>
+        <v>6.54</v>
       </c>
       <c r="N73" t="b">
         <v>1</v>
@@ -21008,7 +20981,7 @@
         <v>28.6</v>
       </c>
       <c r="H74" t="n">
-        <v>31.17</v>
+        <v>40.09</v>
       </c>
       <c r="I74" t="n">
         <v>2.81</v>
@@ -21021,7 +20994,7 @@
         <v>-18.87</v>
       </c>
       <c r="M74" t="n">
-        <v>28.73</v>
+        <v>37.46</v>
       </c>
       <c r="N74" t="b">
         <v>1</v>
@@ -21059,7 +21032,7 @@
         <v>33.1</v>
       </c>
       <c r="H75" t="n">
-        <v>19.69</v>
+        <v>28.87</v>
       </c>
       <c r="I75" t="n">
         <v>4.68</v>
@@ -21072,7 +21045,7 @@
         <v>-26.7</v>
       </c>
       <c r="M75" t="n">
-        <v>17.24</v>
+        <v>26.24</v>
       </c>
       <c r="N75" t="b">
         <v>1</v>
@@ -21110,7 +21083,7 @@
         <v>21.8</v>
       </c>
       <c r="H76" t="n">
-        <v>-13.36</v>
+        <v>-10.78</v>
       </c>
       <c r="I76" t="n">
         <v>-6.34</v>
@@ -21123,7 +21096,7 @@
         <v>-30.04</v>
       </c>
       <c r="M76" t="n">
-        <v>-15.8</v>
+        <v>-13.4</v>
       </c>
       <c r="N76" t="b">
         <v>1</v>
@@ -21161,7 +21134,7 @@
         <v>40.3</v>
       </c>
       <c r="H77" t="n">
-        <v>-12.12</v>
+        <v>-9.890000000000001</v>
       </c>
       <c r="I77" t="n">
         <v>1.24</v>
@@ -21174,7 +21147,7 @@
         <v>-20.5</v>
       </c>
       <c r="M77" t="n">
-        <v>-14.56</v>
+        <v>-12.52</v>
       </c>
       <c r="N77" t="b">
         <v>1</v>
@@ -21212,7 +21185,7 @@
         <v>24.1</v>
       </c>
       <c r="H78" t="n">
-        <v>10.04</v>
+        <v>14.57</v>
       </c>
       <c r="I78" t="n">
         <v>-1.6</v>
@@ -21225,7 +21198,7 @@
         <v>-22.54</v>
       </c>
       <c r="M78" t="n">
-        <v>7.59</v>
+        <v>11.94</v>
       </c>
       <c r="N78" t="b">
         <v>1</v>
@@ -21263,7 +21236,7 @@
         <v>24.5</v>
       </c>
       <c r="H79" t="n">
-        <v>-26.19</v>
+        <v>-26.13</v>
       </c>
       <c r="I79" t="n">
         <v>-12.99</v>
@@ -21276,7 +21249,7 @@
         <v>-22.54</v>
       </c>
       <c r="M79" t="n">
-        <v>-28.64</v>
+        <v>-28.76</v>
       </c>
       <c r="N79" t="b">
         <v>1</v>
@@ -21314,7 +21287,7 @@
         <v>19.3</v>
       </c>
       <c r="H80" t="n">
-        <v>11.1</v>
+        <v>15.22</v>
       </c>
       <c r="I80" t="n">
         <v>11.79</v>
@@ -21327,7 +21300,7 @@
         <v>-16.62</v>
       </c>
       <c r="M80" t="n">
-        <v>8.65</v>
+        <v>12.6</v>
       </c>
       <c r="N80" t="b">
         <v>1</v>
@@ -21365,7 +21338,7 @@
         <v>-8.699999999999999</v>
       </c>
       <c r="H81" t="n">
-        <v>-9.619999999999999</v>
+        <v>-12.16</v>
       </c>
       <c r="I81" t="n">
         <v>17.25</v>
@@ -21378,7 +21351,7 @@
         <v>-4.65</v>
       </c>
       <c r="M81" t="n">
-        <v>-12.06</v>
+        <v>-14.79</v>
       </c>
       <c r="N81" t="b">
         <v>1</v>
@@ -21416,7 +21389,7 @@
         <v>15.2</v>
       </c>
       <c r="H82" t="n">
-        <v>-6.33</v>
+        <v>3.88</v>
       </c>
       <c r="I82" t="n">
         <v>5.36</v>
@@ -21429,7 +21402,7 @@
         <v>-28.18</v>
       </c>
       <c r="M82" t="n">
-        <v>-8.77</v>
+        <v>1.26</v>
       </c>
       <c r="N82" t="b">
         <v>1</v>
@@ -21467,7 +21440,7 @@
         <v>37.2</v>
       </c>
       <c r="H83" t="n">
-        <v>-23.52</v>
+        <v>-21.82</v>
       </c>
       <c r="I83" t="n">
         <v>-7.64</v>
@@ -21480,7 +21453,7 @@
         <v>-26.24</v>
       </c>
       <c r="M83" t="n">
-        <v>-25.96</v>
+        <v>-24.45</v>
       </c>
       <c r="N83" t="b">
         <v>1</v>
@@ -21518,7 +21491,7 @@
         <v>29.8</v>
       </c>
       <c r="H84" t="n">
-        <v>34.3</v>
+        <v>40.5</v>
       </c>
       <c r="I84" t="n">
         <v>-2.74</v>
@@ -21531,7 +21504,7 @@
         <v>-22.36</v>
       </c>
       <c r="M84" t="n">
-        <v>31.86</v>
+        <v>37.88</v>
       </c>
       <c r="N84" t="b">
         <v>1</v>
@@ -21569,7 +21542,7 @@
         <v>19.3</v>
       </c>
       <c r="H85" t="n">
-        <v>-21.75</v>
+        <v>-20.97</v>
       </c>
       <c r="I85" t="n">
         <v>-16.69</v>
@@ -21582,7 +21555,7 @@
         <v>-36.39</v>
       </c>
       <c r="M85" t="n">
-        <v>-24.19</v>
+        <v>-23.6</v>
       </c>
       <c r="N85" t="b">
         <v>1</v>
@@ -21620,7 +21593,7 @@
         <v>11.8</v>
       </c>
       <c r="H86" t="n">
-        <v>2.97</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="I86" t="n">
         <v>-1.19</v>
@@ -21633,7 +21606,7 @@
         <v>-17.57</v>
       </c>
       <c r="M86" t="n">
-        <v>0.52</v>
+        <v>6.42</v>
       </c>
       <c r="N86" t="b">
         <v>1</v>
@@ -21671,7 +21644,7 @@
         <v>27.5</v>
       </c>
       <c r="H87" t="n">
-        <v>5.56</v>
+        <v>11.69</v>
       </c>
       <c r="I87" t="n">
         <v>8.42</v>
@@ -21684,7 +21657,7 @@
         <v>-2.51</v>
       </c>
       <c r="M87" t="n">
-        <v>3.12</v>
+        <v>9.07</v>
       </c>
       <c r="N87" t="b">
         <v>1</v>
@@ -21722,7 +21695,7 @@
         <v>-22.4</v>
       </c>
       <c r="H88" t="n">
-        <v>-11.38</v>
+        <v>-10.98</v>
       </c>
       <c r="I88" t="n">
         <v>9.42</v>
@@ -21735,7 +21708,7 @@
         <v>-2.79</v>
       </c>
       <c r="M88" t="n">
-        <v>-13.82</v>
+        <v>-13.61</v>
       </c>
       <c r="N88" t="b">
         <v>1</v>
@@ -21773,7 +21746,7 @@
         <v>-14.7</v>
       </c>
       <c r="H89" t="n">
-        <v>-15.07</v>
+        <v>-15.91</v>
       </c>
       <c r="I89" t="n">
         <v>10.3</v>
@@ -21786,7 +21759,7 @@
         <v>-2.6</v>
       </c>
       <c r="M89" t="n">
-        <v>-17.51</v>
+        <v>-18.54</v>
       </c>
       <c r="N89" t="b">
         <v>1</v>
@@ -21828,7 +21801,7 @@
         <v>-9.300000000000001</v>
       </c>
       <c r="H90" t="n">
-        <v>-28.18</v>
+        <v>-29.35</v>
       </c>
       <c r="I90" t="n">
         <v>10.42</v>
@@ -21841,7 +21814,7 @@
         <v>-21.72</v>
       </c>
       <c r="M90" t="n">
-        <v>-30.62</v>
+        <v>-31.97</v>
       </c>
       <c r="N90" t="b">
         <v>1</v>
@@ -21879,7 +21852,7 @@
         <v>-25.2</v>
       </c>
       <c r="H91" t="n">
-        <v>16.16</v>
+        <v>18.09</v>
       </c>
       <c r="I91" t="n">
         <v>22.53</v>
@@ -21892,7 +21865,7 @@
         <v>-19.27</v>
       </c>
       <c r="M91" t="n">
-        <v>13.71</v>
+        <v>15.46</v>
       </c>
       <c r="N91" t="b">
         <v>1</v>
@@ -21930,7 +21903,7 @@
         <v>5.1</v>
       </c>
       <c r="H92" t="n">
-        <v>0.76</v>
+        <v>0.62</v>
       </c>
       <c r="I92" t="n">
         <v>8.77</v>
@@ -21943,7 +21916,7 @@
         <v>-3.54</v>
       </c>
       <c r="M92" t="n">
-        <v>-1.68</v>
+        <v>-2</v>
       </c>
       <c r="N92" t="b">
         <v>1</v>
@@ -21981,7 +21954,7 @@
         <v>34.2</v>
       </c>
       <c r="H93" t="n">
-        <v>7.83</v>
+        <v>10.03</v>
       </c>
       <c r="I93" t="n">
         <v>8.15</v>
@@ -21994,7 +21967,7 @@
         <v>-7.63</v>
       </c>
       <c r="M93" t="n">
-        <v>5.38</v>
+        <v>7.4</v>
       </c>
       <c r="N93" t="b">
         <v>1</v>
@@ -22032,7 +22005,7 @@
         <v>42</v>
       </c>
       <c r="H94" t="n">
-        <v>-31.36</v>
+        <v>-32.27</v>
       </c>
       <c r="I94" t="n">
         <v>0.6</v>
@@ -22045,7 +22018,7 @@
         <v>-16.67</v>
       </c>
       <c r="M94" t="n">
-        <v>-33.81</v>
+        <v>-34.9</v>
       </c>
       <c r="N94" t="b">
         <v>1</v>
@@ -22083,7 +22056,7 @@
         <v>-25.3</v>
       </c>
       <c r="H95" t="n">
-        <v>36.65</v>
+        <v>41.24</v>
       </c>
       <c r="I95" t="n">
         <v>36.1</v>
@@ -22096,7 +22069,7 @@
         <v>-5.66</v>
       </c>
       <c r="M95" t="n">
-        <v>34.21</v>
+        <v>38.61</v>
       </c>
       <c r="N95" t="b">
         <v>1</v>
@@ -22134,7 +22107,7 @@
         <v>-7.7</v>
       </c>
       <c r="H96" t="n">
-        <v>-0.6899999999999999</v>
+        <v>-0.2</v>
       </c>
       <c r="I96" t="n">
         <v>-6.47</v>
@@ -22147,7 +22120,7 @@
         <v>-23.05</v>
       </c>
       <c r="M96" t="n">
-        <v>-3.13</v>
+        <v>-2.82</v>
       </c>
       <c r="N96" t="b">
         <v>1</v>
@@ -22185,7 +22158,7 @@
         <v>13.7</v>
       </c>
       <c r="H97" t="n">
-        <v>9.49</v>
+        <v>12.64</v>
       </c>
       <c r="I97" t="n">
         <v>2.74</v>
@@ -22198,7 +22171,7 @@
         <v>-24.02</v>
       </c>
       <c r="M97" t="n">
-        <v>7.05</v>
+        <v>10.01</v>
       </c>
       <c r="N97" t="b">
         <v>1</v>
@@ -22236,7 +22209,7 @@
         <v>21.8</v>
       </c>
       <c r="H98" t="n">
-        <v>-0.07000000000000001</v>
+        <v>2.75</v>
       </c>
       <c r="I98" t="n">
         <v>18.32</v>
@@ -22249,7 +22222,7 @@
         <v>-23.27</v>
       </c>
       <c r="M98" t="n">
-        <v>-2.51</v>
+        <v>0.13</v>
       </c>
       <c r="N98" t="b">
         <v>1</v>
@@ -22287,7 +22260,7 @@
         <v>29.4</v>
       </c>
       <c r="H99" t="n">
-        <v>4.23</v>
+        <v>6.62</v>
       </c>
       <c r="I99" t="n">
         <v>-2.62</v>
@@ -22300,7 +22273,7 @@
         <v>-27.18</v>
       </c>
       <c r="M99" t="n">
-        <v>1.79</v>
+        <v>3.99</v>
       </c>
       <c r="N99" t="b">
         <v>1</v>
@@ -22338,7 +22311,7 @@
         <v>-3.7</v>
       </c>
       <c r="H100" t="n">
-        <v>-23.5</v>
+        <v>-18.24</v>
       </c>
       <c r="I100" t="n">
         <v>-8.07</v>
@@ -22351,7 +22324,7 @@
         <v>-22.12</v>
       </c>
       <c r="M100" t="n">
-        <v>-25.95</v>
+        <v>-20.87</v>
       </c>
       <c r="N100" t="b">
         <v>1</v>
@@ -22389,7 +22362,7 @@
         <v>21.3</v>
       </c>
       <c r="H101" t="n">
-        <v>1.69</v>
+        <v>2.12</v>
       </c>
       <c r="I101" t="n">
         <v>0.23</v>
@@ -22402,7 +22375,7 @@
         <v>-0.85</v>
       </c>
       <c r="M101" t="n">
-        <v>-0.75</v>
+        <v>-0.51</v>
       </c>
       <c r="N101" t="b">
         <v>1</v>
@@ -22440,7 +22413,7 @@
         <v>-21.4</v>
       </c>
       <c r="H102" t="n">
-        <v>15.72</v>
+        <v>15.51</v>
       </c>
       <c r="I102" t="n">
         <v>4.55</v>
@@ -22453,7 +22426,7 @@
         <v>-6.39</v>
       </c>
       <c r="M102" t="n">
-        <v>13.27</v>
+        <v>12.89</v>
       </c>
       <c r="N102" t="b">
         <v>1</v>
@@ -22491,7 +22464,7 @@
         <v>16.3</v>
       </c>
       <c r="H103" t="n">
-        <v>2.56</v>
+        <v>5.92</v>
       </c>
       <c r="I103" t="n">
         <v>-1</v>
@@ -22504,7 +22477,7 @@
         <v>-22.5</v>
       </c>
       <c r="M103" t="n">
-        <v>0.11</v>
+        <v>3.3</v>
       </c>
       <c r="N103" t="b">
         <v>1</v>
@@ -22542,7 +22515,7 @@
         <v>11.9</v>
       </c>
       <c r="H104" t="n">
-        <v>-9.08</v>
+        <v>-4.98</v>
       </c>
       <c r="I104" t="n">
         <v>7.74</v>
@@ -22555,7 +22528,7 @@
         <v>-9.43</v>
       </c>
       <c r="M104" t="n">
-        <v>-11.52</v>
+        <v>-7.6</v>
       </c>
       <c r="N104" t="b">
         <v>1</v>
@@ -22593,7 +22566,7 @@
         <v>0.2</v>
       </c>
       <c r="H105" t="n">
-        <v>4.86</v>
+        <v>6.25</v>
       </c>
       <c r="I105" t="n">
         <v>4.35</v>
@@ -22606,7 +22579,7 @@
         <v>-2.79</v>
       </c>
       <c r="M105" t="n">
-        <v>2.42</v>
+        <v>3.62</v>
       </c>
       <c r="N105" t="b">
         <v>1</v>
@@ -22644,7 +22617,7 @@
         <v>8.4</v>
       </c>
       <c r="H106" t="n">
-        <v>-35.26</v>
+        <v>-35.04</v>
       </c>
       <c r="I106" t="n">
         <v>-0.13</v>
@@ -22657,7 +22630,7 @@
         <v>-10.87</v>
       </c>
       <c r="M106" t="n">
-        <v>-37.7</v>
+        <v>-37.67</v>
       </c>
       <c r="N106" t="b">
         <v>1</v>
@@ -22695,7 +22668,7 @@
         <v>-7.3</v>
       </c>
       <c r="H107" t="n">
-        <v>-24.1</v>
+        <v>-22.59</v>
       </c>
       <c r="I107" t="n">
         <v>-4.12</v>
@@ -22708,7 +22681,7 @@
         <v>-15.02</v>
       </c>
       <c r="M107" t="n">
-        <v>-26.54</v>
+        <v>-25.21</v>
       </c>
       <c r="N107" t="b">
         <v>1</v>
@@ -22746,7 +22719,7 @@
         <v>-26.1</v>
       </c>
       <c r="H108" t="n">
-        <v>-20.54</v>
+        <v>-20.07</v>
       </c>
       <c r="I108" t="n">
         <v>5.05</v>
@@ -22759,7 +22732,7 @@
         <v>-9.27</v>
       </c>
       <c r="M108" t="n">
-        <v>-22.99</v>
+        <v>-22.7</v>
       </c>
       <c r="N108" t="b">
         <v>1</v>
@@ -22797,7 +22770,7 @@
         <v>26.1</v>
       </c>
       <c r="H109" t="n">
-        <v>-7.28</v>
+        <v>-5.53</v>
       </c>
       <c r="I109" t="n">
         <v>-0.51</v>
@@ -22810,7 +22783,7 @@
         <v>-16.45</v>
       </c>
       <c r="M109" t="n">
-        <v>-9.73</v>
+        <v>-8.16</v>
       </c>
       <c r="N109" t="b">
         <v>1</v>
@@ -22848,7 +22821,7 @@
         <v>17.9</v>
       </c>
       <c r="H110" t="n">
-        <v>2.82</v>
+        <v>5.68</v>
       </c>
       <c r="I110" t="n">
         <v>12.97</v>
@@ -22861,7 +22834,7 @@
         <v>-8.130000000000001</v>
       </c>
       <c r="M110" t="n">
-        <v>0.38</v>
+        <v>3.06</v>
       </c>
       <c r="N110" t="b">
         <v>1</v>
@@ -22899,7 +22872,7 @@
         <v>0.7</v>
       </c>
       <c r="H111" t="n">
-        <v>-20.01</v>
+        <v>-20.07</v>
       </c>
       <c r="I111" t="n">
         <v>14.96</v>
@@ -22912,7 +22885,7 @@
         <v>-8.039999999999999</v>
       </c>
       <c r="M111" t="n">
-        <v>-22.45</v>
+        <v>-22.69</v>
       </c>
       <c r="N111" t="b">
         <v>1</v>
@@ -22950,7 +22923,7 @@
         <v>14.8</v>
       </c>
       <c r="H112" t="n">
-        <v>-4.06</v>
+        <v>-3.63</v>
       </c>
       <c r="I112" t="n">
         <v>0.35</v>
@@ -22963,7 +22936,7 @@
         <v>-3.68</v>
       </c>
       <c r="M112" t="n">
-        <v>-6.5</v>
+        <v>-6.25</v>
       </c>
       <c r="N112" t="b">
         <v>1</v>
@@ -23001,7 +22974,7 @@
         <v>25.5</v>
       </c>
       <c r="H113" t="n">
-        <v>2.85</v>
+        <v>1.38</v>
       </c>
       <c r="I113" t="n">
         <v>-9.369999999999999</v>
@@ -23014,7 +22987,7 @@
         <v>-22.11</v>
       </c>
       <c r="M113" t="n">
-        <v>0.41</v>
+        <v>-1.25</v>
       </c>
       <c r="N113" t="b">
         <v>1</v>
@@ -23056,7 +23029,7 @@
         <v>-7.5</v>
       </c>
       <c r="H114" t="n">
-        <v>-8.74</v>
+        <v>-10.7</v>
       </c>
       <c r="I114" t="n">
         <v>4.46</v>
@@ -23069,7 +23042,7 @@
         <v>-8.52</v>
       </c>
       <c r="M114" t="n">
-        <v>-11.18</v>
+        <v>-13.32</v>
       </c>
       <c r="N114" t="b">
         <v>1</v>
@@ -23107,7 +23080,7 @@
         <v>-11</v>
       </c>
       <c r="H115" t="n">
-        <v>-1.54</v>
+        <v>7.26</v>
       </c>
       <c r="I115" t="n">
         <v>10.7</v>
@@ -23120,7 +23093,7 @@
         <v>-9.43</v>
       </c>
       <c r="M115" t="n">
-        <v>-3.98</v>
+        <v>4.63</v>
       </c>
       <c r="N115" t="b">
         <v>1</v>
@@ -23158,7 +23131,7 @@
         <v>-11.4</v>
       </c>
       <c r="H116" t="n">
-        <v>-18.78</v>
+        <v>-18.58</v>
       </c>
       <c r="I116" t="n">
         <v>4.36</v>
@@ -23171,7 +23144,7 @@
         <v>-11.36</v>
       </c>
       <c r="M116" t="n">
-        <v>-21.23</v>
+        <v>-21.2</v>
       </c>
       <c r="N116" t="b">
         <v>1</v>
@@ -23209,7 +23182,7 @@
         <v>27.1</v>
       </c>
       <c r="H117" t="n">
-        <v>-4.4</v>
+        <v>-1.93</v>
       </c>
       <c r="I117" t="n">
         <v>5.02</v>
@@ -23222,7 +23195,7 @@
         <v>-14.35</v>
       </c>
       <c r="M117" t="n">
-        <v>-6.84</v>
+        <v>-4.56</v>
       </c>
       <c r="N117" t="b">
         <v>1</v>
@@ -23260,7 +23233,7 @@
         <v>32.2</v>
       </c>
       <c r="H118" t="n">
-        <v>15.49</v>
+        <v>18.14</v>
       </c>
       <c r="I118" t="n">
         <v>6.49</v>
@@ -23273,7 +23246,7 @@
         <v>-3.92</v>
       </c>
       <c r="M118" t="n">
-        <v>13.05</v>
+        <v>15.51</v>
       </c>
       <c r="N118" t="b">
         <v>1</v>
@@ -23362,7 +23335,7 @@
         <v>7.3</v>
       </c>
       <c r="H120" t="n">
-        <v>-5.53</v>
+        <v>-5.02</v>
       </c>
       <c r="I120" t="n">
         <v>-0.57</v>
@@ -23375,7 +23348,7 @@
         <v>-5.89</v>
       </c>
       <c r="M120" t="n">
-        <v>-7.97</v>
+        <v>-7.64</v>
       </c>
       <c r="N120" t="b">
         <v>1</v>
@@ -23413,7 +23386,7 @@
         <v>-0.3</v>
       </c>
       <c r="H121" t="n">
-        <v>-2.75</v>
+        <v>1.49</v>
       </c>
       <c r="I121" t="n">
         <v>17.76</v>
@@ -23426,7 +23399,7 @@
         <v>-14.18</v>
       </c>
       <c r="M121" t="n">
-        <v>-5.2</v>
+        <v>-1.14</v>
       </c>
       <c r="N121" t="b">
         <v>1</v>
@@ -23464,7 +23437,7 @@
         <v>-6.8</v>
       </c>
       <c r="H122" t="n">
-        <v>38.59</v>
+        <v>34.82</v>
       </c>
       <c r="I122" t="n">
         <v>8.279999999999999</v>
@@ -23477,7 +23450,7 @@
         <v>-6.78</v>
       </c>
       <c r="M122" t="n">
-        <v>36.14</v>
+        <v>32.2</v>
       </c>
       <c r="N122" t="b">
         <v>1</v>
@@ -23515,7 +23488,7 @@
         <v>34.6</v>
       </c>
       <c r="H123" t="n">
-        <v>0.03</v>
+        <v>0.95</v>
       </c>
       <c r="I123" t="n">
         <v>5.7</v>
@@ -23528,7 +23501,7 @@
         <v>-7.7</v>
       </c>
       <c r="M123" t="n">
-        <v>-2.42</v>
+        <v>-1.68</v>
       </c>
       <c r="N123" t="b">
         <v>1</v>
@@ -23566,7 +23539,7 @@
         <v>10.4</v>
       </c>
       <c r="H124" t="n">
-        <v>27.14</v>
+        <v>29.14</v>
       </c>
       <c r="I124" t="n">
         <v>11.05</v>
@@ -23579,7 +23552,7 @@
         <v>-5.54</v>
       </c>
       <c r="M124" t="n">
-        <v>24.7</v>
+        <v>26.52</v>
       </c>
       <c r="N124" t="b">
         <v>1</v>
@@ -23617,7 +23590,7 @@
         <v>-21.5</v>
       </c>
       <c r="H125" t="n">
-        <v>-16.44</v>
+        <v>-18.64</v>
       </c>
       <c r="I125" t="n">
         <v>10.65</v>
@@ -23630,7 +23603,7 @@
         <v>-6.89</v>
       </c>
       <c r="M125" t="n">
-        <v>-18.88</v>
+        <v>-21.27</v>
       </c>
       <c r="N125" t="b">
         <v>1</v>
@@ -23668,7 +23641,7 @@
         <v>3.5</v>
       </c>
       <c r="H126" t="n">
-        <v>46.33</v>
+        <v>46.14</v>
       </c>
       <c r="I126" t="n">
         <v>33.01</v>
@@ -23681,7 +23654,7 @@
         <v>-0.92</v>
       </c>
       <c r="M126" t="n">
-        <v>43.89</v>
+        <v>43.51</v>
       </c>
       <c r="N126" t="b">
         <v>1</v>
@@ -23719,7 +23692,7 @@
         <v>19.8</v>
       </c>
       <c r="H127" t="n">
-        <v>11.74</v>
+        <v>14.76</v>
       </c>
       <c r="I127" t="n">
         <v>4.74</v>
@@ -23732,7 +23705,7 @@
         <v>-9.9</v>
       </c>
       <c r="M127" t="n">
-        <v>9.289999999999999</v>
+        <v>12.13</v>
       </c>
       <c r="N127" t="b">
         <v>1</v>
@@ -23770,7 +23743,7 @@
         <v>-30.5</v>
       </c>
       <c r="H128" t="n">
-        <v>-4.67</v>
+        <v>-4.46</v>
       </c>
       <c r="I128" t="n">
         <v>2.96</v>
@@ -23783,7 +23756,7 @@
         <v>-17.88</v>
       </c>
       <c r="M128" t="n">
-        <v>-7.11</v>
+        <v>-7.09</v>
       </c>
       <c r="N128" t="b">
         <v>1</v>
@@ -23821,7 +23794,7 @@
         <v>-6</v>
       </c>
       <c r="H129" t="n">
-        <v>-17.46</v>
+        <v>-12.17</v>
       </c>
       <c r="I129" t="n">
         <v>3.31</v>
@@ -23834,7 +23807,7 @@
         <v>-21.48</v>
       </c>
       <c r="M129" t="n">
-        <v>-19.9</v>
+        <v>-14.8</v>
       </c>
       <c r="N129" t="b">
         <v>1</v>
@@ -23872,7 +23845,7 @@
         <v>-34.6</v>
       </c>
       <c r="H130" t="n">
-        <v>-5.22</v>
+        <v>2.02</v>
       </c>
       <c r="I130" t="n">
         <v>23.65</v>
@@ -23885,7 +23858,7 @@
         <v>-3.83</v>
       </c>
       <c r="M130" t="n">
-        <v>-7.66</v>
+        <v>-0.61</v>
       </c>
       <c r="N130" t="b">
         <v>1</v>
@@ -23923,7 +23896,7 @@
         <v>-16.2</v>
       </c>
       <c r="H131" t="n">
-        <v>6.57</v>
+        <v>6.92</v>
       </c>
       <c r="I131" t="n">
         <v>25.77</v>
@@ -23936,7 +23909,7 @@
         <v>-1.7</v>
       </c>
       <c r="M131" t="n">
-        <v>4.13</v>
+        <v>4.29</v>
       </c>
       <c r="N131" t="b">
         <v>1</v>
@@ -23974,7 +23947,7 @@
         <v>-24.9</v>
       </c>
       <c r="H132" t="n">
-        <v>20.38</v>
+        <v>20.11</v>
       </c>
       <c r="I132" t="n">
         <v>10.88</v>
@@ -23987,7 +23960,7 @@
         <v>-4.1</v>
       </c>
       <c r="M132" t="n">
-        <v>17.94</v>
+        <v>17.48</v>
       </c>
       <c r="N132" t="b">
         <v>1</v>
@@ -24029,7 +24002,7 @@
         <v>-8.1</v>
       </c>
       <c r="H133" t="n">
-        <v>14.83</v>
+        <v>16.96</v>
       </c>
       <c r="I133" t="n">
         <v>14.27</v>
@@ -24042,7 +24015,7 @@
         <v>-10.92</v>
       </c>
       <c r="M133" t="n">
-        <v>12.39</v>
+        <v>14.34</v>
       </c>
       <c r="N133" t="b">
         <v>1</v>
@@ -24080,7 +24053,7 @@
         <v>-10.2</v>
       </c>
       <c r="H134" t="n">
-        <v>-13.19</v>
+        <v>-12.77</v>
       </c>
       <c r="I134" t="n">
         <v>15.03</v>
@@ -24093,7 +24066,7 @@
         <v>-1.61</v>
       </c>
       <c r="M134" t="n">
-        <v>-15.63</v>
+        <v>-15.4</v>
       </c>
       <c r="N134" t="b">
         <v>1</v>
@@ -24131,7 +24104,7 @@
         <v>68.90000000000001</v>
       </c>
       <c r="H135" t="n">
-        <v>19.39</v>
+        <v>27.74</v>
       </c>
       <c r="I135" t="n">
         <v>1.84</v>
@@ -24144,7 +24117,7 @@
         <v>-10.43</v>
       </c>
       <c r="M135" t="n">
-        <v>16.95</v>
+        <v>25.11</v>
       </c>
       <c r="N135" t="b">
         <v>1</v>
@@ -24182,7 +24155,7 @@
         <v>-40.8</v>
       </c>
       <c r="H136" t="n">
-        <v>-16.31</v>
+        <v>-16.86</v>
       </c>
       <c r="I136" t="n">
         <v>21.71</v>
@@ -24195,7 +24168,7 @@
         <v>-3.3</v>
       </c>
       <c r="M136" t="n">
-        <v>-18.76</v>
+        <v>-19.48</v>
       </c>
       <c r="N136" t="b">
         <v>1</v>
@@ -24233,7 +24206,7 @@
         <v>40.7</v>
       </c>
       <c r="H137" t="n">
-        <v>44.57</v>
+        <v>48.92</v>
       </c>
       <c r="I137" t="n">
         <v>-4.08</v>
@@ -24246,7 +24219,7 @@
         <v>-11.2</v>
       </c>
       <c r="M137" t="n">
-        <v>42.12</v>
+        <v>46.3</v>
       </c>
       <c r="N137" t="b">
         <v>1</v>
@@ -24284,7 +24257,7 @@
         <v>25.7</v>
       </c>
       <c r="H138" t="n">
-        <v>-5.49</v>
+        <v>-3.04</v>
       </c>
       <c r="I138" t="n">
         <v>11.3</v>
@@ -24297,7 +24270,7 @@
         <v>-11.03</v>
       </c>
       <c r="M138" t="n">
-        <v>-7.93</v>
+        <v>-5.66</v>
       </c>
       <c r="N138" t="b">
         <v>1</v>

--- a/STS_holy_grail_v2.xlsx
+++ b/STS_holy_grail_v2.xlsx
@@ -464,7 +464,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
     </row>
     <row r="5">
@@ -474,7 +474,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.6899999999999999</v>
+        <v>-0.68</v>
       </c>
     </row>
     <row r="6">
@@ -484,7 +484,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>46.3</v>
+        <v>47.2</v>
       </c>
     </row>
     <row r="8">
@@ -531,13 +531,13 @@
         <v>61</v>
       </c>
       <c r="C10" t="n">
-        <v>3.81</v>
+        <v>3.82</v>
       </c>
       <c r="D10" t="n">
-        <v>55.74</v>
+        <v>57.38</v>
       </c>
       <c r="E10" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="11">
@@ -550,13 +550,13 @@
         <v>79</v>
       </c>
       <c r="C11" t="n">
-        <v>3.24</v>
+        <v>3.27</v>
       </c>
       <c r="D11" t="n">
-        <v>43.04</v>
+        <v>44.3</v>
       </c>
       <c r="E11" t="n">
-        <v>0.21</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="12">
@@ -569,13 +569,13 @@
         <v>149</v>
       </c>
       <c r="C12" t="n">
-        <v>-1.03</v>
+        <v>-1.02</v>
       </c>
       <c r="D12" t="n">
         <v>39.6</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.37</v>
+        <v>-3.36</v>
       </c>
     </row>
     <row r="13">
@@ -588,13 +588,13 @@
         <v>33</v>
       </c>
       <c r="C13" t="n">
-        <v>6.05</v>
+        <v>6.12</v>
       </c>
       <c r="D13" t="n">
-        <v>66.67</v>
+        <v>69.7</v>
       </c>
       <c r="E13" t="n">
-        <v>4.82</v>
+        <v>4.86</v>
       </c>
     </row>
     <row r="15">
@@ -641,13 +641,13 @@
         <v>107</v>
       </c>
       <c r="C17" t="n">
-        <v>-1.01</v>
+        <v>-1</v>
       </c>
       <c r="D17" t="n">
         <v>39.25</v>
       </c>
       <c r="E17" t="n">
-        <v>-3.41</v>
+        <v>-3.4</v>
       </c>
     </row>
     <row r="18">
@@ -698,13 +698,13 @@
         <v>39</v>
       </c>
       <c r="C20" t="n">
-        <v>-3</v>
+        <v>-2.94</v>
       </c>
       <c r="D20" t="n">
-        <v>38.46</v>
+        <v>41.03</v>
       </c>
       <c r="E20" t="n">
-        <v>-5.31</v>
+        <v>-5.26</v>
       </c>
     </row>
     <row r="21">
@@ -717,13 +717,13 @@
         <v>88</v>
       </c>
       <c r="C21" t="n">
-        <v>10.93</v>
+        <v>10.96</v>
       </c>
       <c r="D21" t="n">
-        <v>69.31999999999999</v>
+        <v>71.59</v>
       </c>
       <c r="E21" t="n">
-        <v>8.470000000000001</v>
+        <v>8.49</v>
       </c>
     </row>
     <row r="23">
@@ -861,13 +861,13 @@
         <v>185</v>
       </c>
       <c r="C31" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="D31" t="n">
-        <v>38.38</v>
+        <v>40</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.63</v>
+        <v>-0.61</v>
       </c>
     </row>
     <row r="32">
@@ -880,7 +880,7 @@
         <v>137</v>
       </c>
       <c r="C32" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="D32" t="n">
         <v>56.93</v>
@@ -1433,7 +1433,7 @@
         <v>-31.6</v>
       </c>
       <c r="H11" t="n">
-        <v>2.16</v>
+        <v>2.35</v>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
@@ -1442,7 +1442,7 @@
         <v>-5.01</v>
       </c>
       <c r="M11" t="n">
-        <v>2.05</v>
+        <v>2.23</v>
       </c>
       <c r="N11" t="b">
         <v>1</v>
@@ -1768,7 +1768,7 @@
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="n">
-        <v>-8.66</v>
+        <v>-8.789999999999999</v>
       </c>
       <c r="M18" t="n">
         <v>-8.49</v>
@@ -2591,7 +2591,7 @@
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="n">
-        <v>-3.89</v>
+        <v>-3.92</v>
       </c>
       <c r="M35" t="n">
         <v>-3.94</v>
@@ -4736,7 +4736,7 @@
         <v>15.5</v>
       </c>
       <c r="H78" t="n">
-        <v>-15.2</v>
+        <v>-14.98</v>
       </c>
       <c r="I78" t="n">
         <v>-7.36</v>
@@ -4749,7 +4749,7 @@
         <v>-12.98</v>
       </c>
       <c r="M78" t="n">
-        <v>-16.09</v>
+        <v>-15.86</v>
       </c>
       <c r="N78" t="b">
         <v>0</v>
@@ -7922,7 +7922,7 @@
         <v>6.5</v>
       </c>
       <c r="H140" t="n">
-        <v>-10.9</v>
+        <v>-10.67</v>
       </c>
       <c r="I140" t="n">
         <v>-0.04</v>
@@ -7935,7 +7935,7 @@
         <v>-4.12</v>
       </c>
       <c r="M140" t="n">
-        <v>-15.72</v>
+        <v>-15.5</v>
       </c>
       <c r="N140" t="b">
         <v>0</v>
@@ -8126,7 +8126,7 @@
         <v>48.1</v>
       </c>
       <c r="H144" t="n">
-        <v>-2.19</v>
+        <v>0.04</v>
       </c>
       <c r="I144" t="n">
         <v>0.16</v>
@@ -8139,7 +8139,7 @@
         <v>-8.890000000000001</v>
       </c>
       <c r="M144" t="n">
-        <v>-5.7</v>
+        <v>-4.23</v>
       </c>
       <c r="N144" t="b">
         <v>0</v>
@@ -8742,7 +8742,7 @@
         <v>28.9</v>
       </c>
       <c r="H156" t="n">
-        <v>-0.15</v>
+        <v>0.24</v>
       </c>
       <c r="I156" t="n">
         <v>8.06</v>
@@ -8755,7 +8755,7 @@
         <v>-2.79</v>
       </c>
       <c r="M156" t="n">
-        <v>-4.63</v>
+        <v>-4.24</v>
       </c>
       <c r="N156" t="b">
         <v>0</v>
@@ -9868,7 +9868,7 @@
         <v>15.7</v>
       </c>
       <c r="H178" t="n">
-        <v>-0.36</v>
+        <v>1.98</v>
       </c>
       <c r="I178" t="n">
         <v>-0.87</v>
@@ -9881,7 +9881,7 @@
         <v>-29.01</v>
       </c>
       <c r="M178" t="n">
-        <v>-2.98</v>
+        <v>-1.4</v>
       </c>
       <c r="N178" t="b">
         <v>0</v>
@@ -13552,7 +13552,7 @@
         <v>-21.4</v>
       </c>
       <c r="H250" t="n">
-        <v>15.51</v>
+        <v>16.87</v>
       </c>
       <c r="I250" t="n">
         <v>4.55</v>
@@ -13565,7 +13565,7 @@
         <v>-6.39</v>
       </c>
       <c r="M250" t="n">
-        <v>12.89</v>
+        <v>13.49</v>
       </c>
       <c r="N250" t="b">
         <v>1</v>
@@ -15404,7 +15404,7 @@
         <v>32.2</v>
       </c>
       <c r="H286" t="n">
-        <v>23.56</v>
+        <v>23.57</v>
       </c>
       <c r="I286" t="n">
         <v>6.49</v>
@@ -17632,7 +17632,7 @@
         <v>-31.6</v>
       </c>
       <c r="H6" t="n">
-        <v>2.16</v>
+        <v>2.35</v>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
@@ -17641,7 +17641,7 @@
         <v>-5.01</v>
       </c>
       <c r="M6" t="n">
-        <v>2.05</v>
+        <v>2.23</v>
       </c>
       <c r="N6" t="b">
         <v>1</v>
@@ -22494,7 +22494,7 @@
         <v>-21.4</v>
       </c>
       <c r="H102" t="n">
-        <v>15.51</v>
+        <v>16.87</v>
       </c>
       <c r="I102" t="n">
         <v>4.55</v>
@@ -22507,7 +22507,7 @@
         <v>-6.39</v>
       </c>
       <c r="M102" t="n">
-        <v>12.89</v>
+        <v>13.49</v>
       </c>
       <c r="N102" t="b">
         <v>1</v>
@@ -23314,7 +23314,7 @@
         <v>32.2</v>
       </c>
       <c r="H118" t="n">
-        <v>23.56</v>
+        <v>23.57</v>
       </c>
       <c r="I118" t="n">
         <v>6.49</v>

--- a/STS_holy_grail_v2.xlsx
+++ b/STS_holy_grail_v2.xlsx
@@ -464,7 +464,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.86</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="5">
@@ -474,7 +474,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.99</v>
+        <v>-0.71</v>
       </c>
     </row>
     <row r="6">
@@ -484,7 +484,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>46.8</v>
+        <v>48.3</v>
       </c>
     </row>
     <row r="8">
@@ -531,13 +531,13 @@
         <v>64</v>
       </c>
       <c r="C10" t="n">
-        <v>2.96</v>
+        <v>4.14</v>
       </c>
       <c r="D10" t="n">
-        <v>54.69</v>
+        <v>53.12</v>
       </c>
       <c r="E10" t="n">
-        <v>0.42</v>
+        <v>0.98</v>
       </c>
     </row>
     <row r="11">
@@ -550,13 +550,13 @@
         <v>79</v>
       </c>
       <c r="C11" t="n">
-        <v>0.91</v>
+        <v>1.91</v>
       </c>
       <c r="D11" t="n">
-        <v>41.77</v>
+        <v>45.57</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.7</v>
+        <v>-2.31</v>
       </c>
     </row>
     <row r="12">
@@ -569,13 +569,13 @@
         <v>155</v>
       </c>
       <c r="C12" t="n">
-        <v>0.6</v>
+        <v>1.12</v>
       </c>
       <c r="D12" t="n">
-        <v>42.58</v>
+        <v>41.94</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.2</v>
+        <v>-2.3</v>
       </c>
     </row>
     <row r="13">
@@ -588,13 +588,13 @@
         <v>33</v>
       </c>
       <c r="C13" t="n">
-        <v>7.88</v>
+        <v>9.73</v>
       </c>
       <c r="D13" t="n">
-        <v>63.64</v>
+        <v>75.76000000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>6.05</v>
+        <v>7.29</v>
       </c>
     </row>
     <row r="15">
@@ -641,13 +641,13 @@
         <v>111</v>
       </c>
       <c r="C17" t="n">
-        <v>0.86</v>
+        <v>1.45</v>
       </c>
       <c r="D17" t="n">
-        <v>41.44</v>
+        <v>42.34</v>
       </c>
       <c r="E17" t="n">
-        <v>-2</v>
+        <v>-2.03</v>
       </c>
     </row>
     <row r="18">
@@ -660,13 +660,13 @@
         <v>47</v>
       </c>
       <c r="C18" t="n">
-        <v>-0.1</v>
+        <v>0.13</v>
       </c>
       <c r="D18" t="n">
-        <v>46.81</v>
+        <v>40.43</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.56</v>
+        <v>-2.95</v>
       </c>
     </row>
     <row r="19">
@@ -679,13 +679,13 @@
         <v>45</v>
       </c>
       <c r="C19" t="n">
-        <v>-2.37</v>
+        <v>-1.3</v>
       </c>
       <c r="D19" t="n">
-        <v>37.78</v>
+        <v>44.44</v>
       </c>
       <c r="E19" t="n">
-        <v>-5.24</v>
+        <v>-4.8</v>
       </c>
     </row>
     <row r="20">
@@ -698,13 +698,13 @@
         <v>40</v>
       </c>
       <c r="C20" t="n">
-        <v>-3.94</v>
+        <v>-2.82</v>
       </c>
       <c r="D20" t="n">
-        <v>40</v>
+        <v>37.5</v>
       </c>
       <c r="E20" t="n">
-        <v>-6.75</v>
+        <v>-6.25</v>
       </c>
     </row>
     <row r="21">
@@ -717,13 +717,13 @@
         <v>88</v>
       </c>
       <c r="C21" t="n">
-        <v>8.949999999999999</v>
+        <v>10.39</v>
       </c>
       <c r="D21" t="n">
-        <v>61.36</v>
+        <v>67.05</v>
       </c>
       <c r="E21" t="n">
-        <v>5.91</v>
+        <v>6.76</v>
       </c>
     </row>
     <row r="23">
@@ -770,13 +770,13 @@
         <v>10</v>
       </c>
       <c r="C25" t="n">
-        <v>9.48</v>
+        <v>10.91</v>
       </c>
       <c r="D25" t="n">
         <v>70</v>
       </c>
       <c r="E25" t="n">
-        <v>6.02</v>
+        <v>6.83</v>
       </c>
     </row>
     <row r="26">
@@ -789,13 +789,13 @@
         <v>5</v>
       </c>
       <c r="C26" t="n">
-        <v>-5.63</v>
+        <v>-4.87</v>
       </c>
       <c r="D26" t="n">
         <v>40</v>
       </c>
       <c r="E26" t="n">
-        <v>-9.789999999999999</v>
+        <v>-9.66</v>
       </c>
     </row>
     <row r="27">
@@ -808,13 +808,13 @@
         <v>3</v>
       </c>
       <c r="C27" t="n">
-        <v>9.109999999999999</v>
+        <v>10.95</v>
       </c>
       <c r="D27" t="n">
         <v>66.67</v>
       </c>
       <c r="E27" t="n">
-        <v>5.98</v>
+        <v>7.21</v>
       </c>
     </row>
     <row r="29">
@@ -861,13 +861,13 @@
         <v>190</v>
       </c>
       <c r="C31" t="n">
-        <v>2.85</v>
+        <v>3.89</v>
       </c>
       <c r="D31" t="n">
-        <v>45.26</v>
+        <v>47.37</v>
       </c>
       <c r="E31" t="n">
-        <v>0.02</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="32">
@@ -880,13 +880,13 @@
         <v>141</v>
       </c>
       <c r="C32" t="n">
-        <v>0.51</v>
+        <v>1.21</v>
       </c>
       <c r="D32" t="n">
-        <v>48.94</v>
+        <v>49.65</v>
       </c>
       <c r="E32" t="n">
-        <v>-2.35</v>
+        <v>-2.27</v>
       </c>
     </row>
   </sheetData>
@@ -1010,16 +1010,16 @@
         <v>-24.3</v>
       </c>
       <c r="H2" t="n">
-        <v>0.7</v>
+        <v>-1.78</v>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="n">
-        <v>-0.66</v>
+        <v>-1.96</v>
       </c>
       <c r="M2" t="n">
-        <v>0.82</v>
+        <v>-2.26</v>
       </c>
       <c r="N2" t="b">
         <v>0</v>
@@ -1057,7 +1057,7 @@
         <v>-22.1</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.1</v>
+        <v>0.44</v>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
@@ -1066,7 +1066,7 @@
         <v>-2.86</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.98</v>
+        <v>-0.04</v>
       </c>
       <c r="N3" t="b">
         <v>0</v>
@@ -1104,7 +1104,7 @@
         <v>-16.6</v>
       </c>
       <c r="H4" t="n">
-        <v>1.93</v>
+        <v>2.47</v>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
@@ -1113,7 +1113,7 @@
         <v>-1.04</v>
       </c>
       <c r="M4" t="n">
-        <v>2.17</v>
+        <v>2.11</v>
       </c>
       <c r="N4" t="b">
         <v>1</v>
@@ -1151,7 +1151,7 @@
         <v>-7.4</v>
       </c>
       <c r="H5" t="n">
-        <v>0.49</v>
+        <v>-0.16</v>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
@@ -1160,7 +1160,7 @@
         <v>-1.56</v>
       </c>
       <c r="M5" t="n">
-        <v>0.73</v>
+        <v>-0.52</v>
       </c>
       <c r="N5" t="b">
         <v>0</v>
@@ -1198,7 +1198,7 @@
         <v>-5</v>
       </c>
       <c r="H6" t="n">
-        <v>1.22</v>
+        <v>0.43</v>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
@@ -1207,7 +1207,7 @@
         <v>-1.75</v>
       </c>
       <c r="M6" t="n">
-        <v>1.46</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="N6" t="b">
         <v>1</v>
@@ -1245,7 +1245,7 @@
         <v>12.5</v>
       </c>
       <c r="H7" t="n">
-        <v>0.35</v>
+        <v>-0.61</v>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
@@ -1254,7 +1254,7 @@
         <v>-2.56</v>
       </c>
       <c r="M7" t="n">
-        <v>0.59</v>
+        <v>-0.97</v>
       </c>
       <c r="N7" t="b">
         <v>1</v>
@@ -1292,7 +1292,7 @@
         <v>-1.1</v>
       </c>
       <c r="H8" t="n">
-        <v>2.96</v>
+        <v>2.48</v>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
@@ -1301,7 +1301,7 @@
         <v>-0.36</v>
       </c>
       <c r="M8" t="n">
-        <v>3.19</v>
+        <v>2.12</v>
       </c>
       <c r="N8" t="b">
         <v>0</v>
@@ -1339,7 +1339,7 @@
         <v>-17.3</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.11</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
@@ -1348,7 +1348,7 @@
         <v>-4.07</v>
       </c>
       <c r="M9" t="n">
-        <v>0.43</v>
+        <v>-0.74</v>
       </c>
       <c r="N9" t="b">
         <v>1</v>
@@ -1386,7 +1386,7 @@
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>1.15</v>
+        <v>-0.74</v>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
@@ -1395,7 +1395,7 @@
         <v>-1.46</v>
       </c>
       <c r="M10" t="n">
-        <v>1.69</v>
+        <v>-0.79</v>
       </c>
       <c r="N10" t="b">
         <v>0</v>
@@ -1433,7 +1433,7 @@
         <v>-29.3</v>
       </c>
       <c r="H11" t="n">
-        <v>2.72</v>
+        <v>2.63</v>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
@@ -1442,7 +1442,7 @@
         <v>-3.13</v>
       </c>
       <c r="M11" t="n">
-        <v>2.17</v>
+        <v>1.48</v>
       </c>
       <c r="N11" t="b">
         <v>0</v>
@@ -1480,7 +1480,7 @@
         <v>-21.8</v>
       </c>
       <c r="H12" t="n">
-        <v>-3.73</v>
+        <v>-3.82</v>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
@@ -1489,7 +1489,7 @@
         <v>-5.33</v>
       </c>
       <c r="M12" t="n">
-        <v>-4.71</v>
+        <v>-5.4</v>
       </c>
       <c r="N12" t="b">
         <v>1</v>
@@ -1527,7 +1527,7 @@
         <v>-15</v>
       </c>
       <c r="H13" t="n">
-        <v>7.31</v>
+        <v>9.67</v>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
@@ -1536,7 +1536,7 @@
         <v>-4.06</v>
       </c>
       <c r="M13" t="n">
-        <v>6.39</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="N13" t="b">
         <v>0</v>
@@ -1574,7 +1574,7 @@
         <v>-16.7</v>
       </c>
       <c r="H14" t="n">
-        <v>24.38</v>
+        <v>25.21</v>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
@@ -1583,7 +1583,7 @@
         <v>-6.98</v>
       </c>
       <c r="M14" t="n">
-        <v>23.46</v>
+        <v>23.68</v>
       </c>
       <c r="N14" t="b">
         <v>1</v>
@@ -1621,7 +1621,7 @@
         <v>-26.8</v>
       </c>
       <c r="H15" t="n">
-        <v>2.51</v>
+        <v>3.04</v>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
@@ -1630,7 +1630,7 @@
         <v>-5.1</v>
       </c>
       <c r="M15" t="n">
-        <v>1.59</v>
+        <v>1.51</v>
       </c>
       <c r="N15" t="b">
         <v>0</v>
@@ -1668,7 +1668,7 @@
         <v>-35.9</v>
       </c>
       <c r="H16" t="n">
-        <v>-4.9</v>
+        <v>-0.55</v>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
@@ -1677,7 +1677,7 @@
         <v>-6.37</v>
       </c>
       <c r="M16" t="n">
-        <v>-5.82</v>
+        <v>-2.08</v>
       </c>
       <c r="N16" t="b">
         <v>0</v>
@@ -1715,7 +1715,7 @@
         <v>-7.1</v>
       </c>
       <c r="H17" t="n">
-        <v>8.26</v>
+        <v>10.2</v>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
@@ -1724,7 +1724,7 @@
         <v>-2.71</v>
       </c>
       <c r="M17" t="n">
-        <v>7.33</v>
+        <v>8.66</v>
       </c>
       <c r="N17" t="b">
         <v>0</v>
@@ -1762,7 +1762,7 @@
         <v>-11.5</v>
       </c>
       <c r="H18" t="n">
-        <v>6.96</v>
+        <v>5.5</v>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
@@ -1771,7 +1771,7 @@
         <v>-0.99</v>
       </c>
       <c r="M18" t="n">
-        <v>6.04</v>
+        <v>3.97</v>
       </c>
       <c r="N18" t="b">
         <v>1</v>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Extended</t>
         </is>
       </c>
       <c r="E19" t="inlineStr"/>
@@ -1809,16 +1809,18 @@
         <v>0.1</v>
       </c>
       <c r="H19" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="I19" t="inlineStr"/>
+        <v>6.41</v>
+      </c>
+      <c r="I19" t="n">
+        <v>6.41</v>
+      </c>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="n">
         <v>-2.51</v>
       </c>
       <c r="M19" t="n">
-        <v>0.95</v>
+        <v>5.14</v>
       </c>
       <c r="N19" t="b">
         <v>1</v>
@@ -1856,16 +1858,18 @@
         <v>-31.6</v>
       </c>
       <c r="H20" t="n">
-        <v>-5</v>
-      </c>
-      <c r="I20" t="inlineStr"/>
+        <v>-2.12</v>
+      </c>
+      <c r="I20" t="n">
+        <v>-2.12</v>
+      </c>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="n">
         <v>-8.140000000000001</v>
       </c>
       <c r="M20" t="n">
-        <v>-5.67</v>
+        <v>-3.39</v>
       </c>
       <c r="N20" t="b">
         <v>1</v>
@@ -1903,7 +1907,7 @@
         <v>7.6</v>
       </c>
       <c r="H21" t="n">
-        <v>-3.6</v>
+        <v>0.21</v>
       </c>
       <c r="I21" t="n">
         <v>-3.6</v>
@@ -1914,7 +1918,7 @@
         <v>-9.359999999999999</v>
       </c>
       <c r="M21" t="n">
-        <v>-4.89</v>
+        <v>-1.68</v>
       </c>
       <c r="N21" t="b">
         <v>0</v>
@@ -1952,7 +1956,7 @@
         <v>-17.9</v>
       </c>
       <c r="H22" t="n">
-        <v>-7.32</v>
+        <v>-7.24</v>
       </c>
       <c r="I22" t="n">
         <v>-6.13</v>
@@ -1960,10 +1964,10 @@
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="n">
-        <v>-10.47</v>
+        <v>-10.48</v>
       </c>
       <c r="M22" t="n">
-        <v>-7.3</v>
+        <v>-7.83</v>
       </c>
       <c r="N22" t="b">
         <v>0</v>
@@ -2001,7 +2005,7 @@
         <v>-2.7</v>
       </c>
       <c r="H23" t="n">
-        <v>-5.84</v>
+        <v>-8.279999999999999</v>
       </c>
       <c r="I23" t="n">
         <v>-3.77</v>
@@ -2009,10 +2013,10 @@
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="n">
-        <v>-9.24</v>
+        <v>-9.34</v>
       </c>
       <c r="M23" t="n">
-        <v>-5.83</v>
+        <v>-8.869999999999999</v>
       </c>
       <c r="N23" t="b">
         <v>1</v>
@@ -2050,7 +2054,7 @@
         <v>-25.3</v>
       </c>
       <c r="H24" t="n">
-        <v>0.17</v>
+        <v>0.3</v>
       </c>
       <c r="I24" t="n">
         <v>4.1</v>
@@ -2061,7 +2065,7 @@
         <v>-0.92</v>
       </c>
       <c r="M24" t="n">
-        <v>0.18</v>
+        <v>-0.29</v>
       </c>
       <c r="N24" t="b">
         <v>0</v>
@@ -2099,7 +2103,7 @@
         <v>25.6</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.52</v>
+        <v>0.74</v>
       </c>
       <c r="I25" t="n">
         <v>-0.42</v>
@@ -2110,7 +2114,7 @@
         <v>-8.35</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.51</v>
+        <v>0.15</v>
       </c>
       <c r="N25" t="b">
         <v>0</v>
@@ -2148,7 +2152,7 @@
         <v>26.9</v>
       </c>
       <c r="H26" t="n">
-        <v>-9.34</v>
+        <v>-3.78</v>
       </c>
       <c r="I26" t="n">
         <v>-3.24</v>
@@ -2159,7 +2163,7 @@
         <v>-12.88</v>
       </c>
       <c r="M26" t="n">
-        <v>-9.33</v>
+        <v>-4.37</v>
       </c>
       <c r="N26" t="b">
         <v>1</v>
@@ -2197,7 +2201,7 @@
         <v>-14.5</v>
       </c>
       <c r="H27" t="n">
-        <v>-8.18</v>
+        <v>-3.26</v>
       </c>
       <c r="I27" t="n">
         <v>-3.75</v>
@@ -2208,7 +2212,7 @@
         <v>-9.01</v>
       </c>
       <c r="M27" t="n">
-        <v>-9.19</v>
+        <v>-4.87</v>
       </c>
       <c r="N27" t="b">
         <v>0</v>
@@ -2246,7 +2250,7 @@
         <v>17.2</v>
       </c>
       <c r="H28" t="n">
-        <v>-2</v>
+        <v>-0.41</v>
       </c>
       <c r="I28" t="n">
         <v>-1.49</v>
@@ -2257,7 +2261,7 @@
         <v>-10.54</v>
       </c>
       <c r="M28" t="n">
-        <v>-3</v>
+        <v>-2.02</v>
       </c>
       <c r="N28" t="b">
         <v>0</v>
@@ -2295,7 +2299,7 @@
         <v>-13.2</v>
       </c>
       <c r="H29" t="n">
-        <v>22.09</v>
+        <v>23.49</v>
       </c>
       <c r="I29" t="n">
         <v>23.71</v>
@@ -2306,7 +2310,7 @@
         <v>-0.82</v>
       </c>
       <c r="M29" t="n">
-        <v>21.08</v>
+        <v>21.88</v>
       </c>
       <c r="N29" t="b">
         <v>0</v>
@@ -2344,7 +2348,7 @@
         <v>-7.7</v>
       </c>
       <c r="H30" t="n">
-        <v>-10.15</v>
+        <v>-9.470000000000001</v>
       </c>
       <c r="I30" t="n">
         <v>-9.67</v>
@@ -2355,7 +2359,7 @@
         <v>-12.32</v>
       </c>
       <c r="M30" t="n">
-        <v>-11.15</v>
+        <v>-11.08</v>
       </c>
       <c r="N30" t="b">
         <v>0</v>
@@ -2393,7 +2397,7 @@
         <v>-18.1</v>
       </c>
       <c r="H31" t="n">
-        <v>-1.98</v>
+        <v>1.89</v>
       </c>
       <c r="I31" t="n">
         <v>-2.43</v>
@@ -2404,7 +2408,7 @@
         <v>-6.41</v>
       </c>
       <c r="M31" t="n">
-        <v>-2.98</v>
+        <v>0.28</v>
       </c>
       <c r="N31" t="b">
         <v>0</v>
@@ -2442,7 +2446,7 @@
         <v>-18.1</v>
       </c>
       <c r="H32" t="n">
-        <v>8.68</v>
+        <v>9.35</v>
       </c>
       <c r="I32" t="n">
         <v>4.46</v>
@@ -2453,7 +2457,7 @@
         <v>-2.69</v>
       </c>
       <c r="M32" t="n">
-        <v>7.67</v>
+        <v>7.74</v>
       </c>
       <c r="N32" t="b">
         <v>1</v>
@@ -2491,7 +2495,7 @@
         <v>7.7</v>
       </c>
       <c r="H33" t="n">
-        <v>-3.28</v>
+        <v>-1.82</v>
       </c>
       <c r="I33" t="n">
         <v>-6.85</v>
@@ -2502,7 +2506,7 @@
         <v>-9.359999999999999</v>
       </c>
       <c r="M33" t="n">
-        <v>-4.28</v>
+        <v>-3.42</v>
       </c>
       <c r="N33" t="b">
         <v>0</v>
@@ -2540,7 +2544,7 @@
         <v>-21.5</v>
       </c>
       <c r="H34" t="n">
-        <v>-3.33</v>
+        <v>-6.61</v>
       </c>
       <c r="I34" t="n">
         <v>-1.68</v>
@@ -2548,10 +2552,10 @@
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="n">
-        <v>-5.21</v>
+        <v>-6.82</v>
       </c>
       <c r="M34" t="n">
-        <v>-4.34</v>
+        <v>-8.220000000000001</v>
       </c>
       <c r="N34" t="b">
         <v>1</v>
@@ -2578,7 +2582,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Extended</t>
         </is>
       </c>
       <c r="E35" t="inlineStr"/>
@@ -2589,7 +2593,7 @@
         <v>41.6</v>
       </c>
       <c r="H35" t="n">
-        <v>3.86</v>
+        <v>5.24</v>
       </c>
       <c r="I35" t="n">
         <v>3.43</v>
@@ -2600,7 +2604,7 @@
         <v>-4.38</v>
       </c>
       <c r="M35" t="n">
-        <v>2.21</v>
+        <v>2.98</v>
       </c>
       <c r="N35" t="b">
         <v>1</v>
@@ -2638,7 +2642,7 @@
         <v>32.1</v>
       </c>
       <c r="H36" t="n">
-        <v>-2.22</v>
+        <v>-3.12</v>
       </c>
       <c r="I36" t="n">
         <v>-3.47</v>
@@ -2649,7 +2653,7 @@
         <v>-6.94</v>
       </c>
       <c r="M36" t="n">
-        <v>-3.88</v>
+        <v>-5.38</v>
       </c>
       <c r="N36" t="b">
         <v>1</v>
@@ -2687,7 +2691,7 @@
         <v>-14.4</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.48</v>
+        <v>-1.24</v>
       </c>
       <c r="I37" t="n">
         <v>-2.38</v>
@@ -2698,7 +2702,7 @@
         <v>-6.46</v>
       </c>
       <c r="M37" t="n">
-        <v>-2.14</v>
+        <v>-3.51</v>
       </c>
       <c r="N37" t="b">
         <v>1</v>
@@ -2736,7 +2740,7 @@
         <v>-16.8</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.19</v>
+        <v>-1.36</v>
       </c>
       <c r="I38" t="n">
         <v>1.99</v>
@@ -2747,7 +2751,7 @@
         <v>-5.75</v>
       </c>
       <c r="M38" t="n">
-        <v>-1.84</v>
+        <v>-3.62</v>
       </c>
       <c r="N38" t="b">
         <v>0</v>
@@ -2785,7 +2789,7 @@
         <v>-10</v>
       </c>
       <c r="H39" t="n">
-        <v>-4.16</v>
+        <v>-3.35</v>
       </c>
       <c r="I39" t="n">
         <v>-3.29</v>
@@ -2796,7 +2800,7 @@
         <v>-10.65</v>
       </c>
       <c r="M39" t="n">
-        <v>-5.81</v>
+        <v>-5.62</v>
       </c>
       <c r="N39" t="b">
         <v>1</v>
@@ -2834,7 +2838,7 @@
         <v>6.4</v>
       </c>
       <c r="H40" t="n">
-        <v>4.66</v>
+        <v>4.43</v>
       </c>
       <c r="I40" t="n">
         <v>1.48</v>
@@ -2845,7 +2849,7 @@
         <v>-3.35</v>
       </c>
       <c r="M40" t="n">
-        <v>3</v>
+        <v>2.16</v>
       </c>
       <c r="N40" t="b">
         <v>1</v>
@@ -2883,7 +2887,7 @@
         <v>-11</v>
       </c>
       <c r="H41" t="n">
-        <v>47.71</v>
+        <v>48.25</v>
       </c>
       <c r="I41" t="n">
         <v>11.67</v>
@@ -2894,7 +2898,7 @@
         <v>-0.97</v>
       </c>
       <c r="M41" t="n">
-        <v>46.04</v>
+        <v>45.98</v>
       </c>
       <c r="N41" t="b">
         <v>0</v>
@@ -2932,7 +2936,7 @@
         <v>-23.9</v>
       </c>
       <c r="H42" t="n">
-        <v>-6.94</v>
+        <v>-4.63</v>
       </c>
       <c r="I42" t="n">
         <v>-4.98</v>
@@ -2943,7 +2947,7 @@
         <v>-7.87</v>
       </c>
       <c r="M42" t="n">
-        <v>-8.6</v>
+        <v>-6.91</v>
       </c>
       <c r="N42" t="b">
         <v>0</v>
@@ -2985,7 +2989,7 @@
         <v>-9.800000000000001</v>
       </c>
       <c r="H43" t="n">
-        <v>6.78</v>
+        <v>7.58</v>
       </c>
       <c r="I43" t="n">
         <v>-3.41</v>
@@ -2996,7 +3000,7 @@
         <v>-8.949999999999999</v>
       </c>
       <c r="M43" t="n">
-        <v>5.12</v>
+        <v>5.31</v>
       </c>
       <c r="N43" t="b">
         <v>0</v>
@@ -3034,7 +3038,7 @@
         <v>-36.1</v>
       </c>
       <c r="H44" t="n">
-        <v>-4.67</v>
+        <v>-2.8</v>
       </c>
       <c r="I44" t="n">
         <v>-1.4</v>
@@ -3045,7 +3049,7 @@
         <v>-7.04</v>
       </c>
       <c r="M44" t="n">
-        <v>-6.33</v>
+        <v>-5.07</v>
       </c>
       <c r="N44" t="b">
         <v>0</v>
@@ -3083,7 +3087,7 @@
         <v>-7.9</v>
       </c>
       <c r="H45" t="n">
-        <v>-9.390000000000001</v>
+        <v>-10.14</v>
       </c>
       <c r="I45" t="n">
         <v>-8.83</v>
@@ -3094,7 +3098,7 @@
         <v>-12.99</v>
       </c>
       <c r="M45" t="n">
-        <v>-11.05</v>
+        <v>-12.41</v>
       </c>
       <c r="N45" t="b">
         <v>0</v>
@@ -3132,7 +3136,7 @@
         <v>2.6</v>
       </c>
       <c r="H46" t="n">
-        <v>-3.68</v>
+        <v>-4.98</v>
       </c>
       <c r="I46" t="n">
         <v>-7.8</v>
@@ -3143,7 +3147,7 @@
         <v>-12.2</v>
       </c>
       <c r="M46" t="n">
-        <v>-5.83</v>
+        <v>-7.74</v>
       </c>
       <c r="N46" t="b">
         <v>0</v>
@@ -3181,7 +3185,7 @@
         <v>6.3</v>
       </c>
       <c r="H47" t="n">
-        <v>5.6</v>
+        <v>6.23</v>
       </c>
       <c r="I47" t="n">
         <v>0.64</v>
@@ -3192,7 +3196,7 @@
         <v>-2.13</v>
       </c>
       <c r="M47" t="n">
-        <v>3.45</v>
+        <v>3.46</v>
       </c>
       <c r="N47" t="b">
         <v>0</v>
@@ -3230,7 +3234,7 @@
         <v>20.2</v>
       </c>
       <c r="H48" t="n">
-        <v>3.33</v>
+        <v>2.16</v>
       </c>
       <c r="I48" t="n">
         <v>3.45</v>
@@ -3241,7 +3245,7 @@
         <v>-1.07</v>
       </c>
       <c r="M48" t="n">
-        <v>1.26</v>
+        <v>-0.52</v>
       </c>
       <c r="N48" t="b">
         <v>1</v>
@@ -3279,7 +3283,7 @@
         <v>43.7</v>
       </c>
       <c r="H49" t="n">
-        <v>1.57</v>
+        <v>2.11</v>
       </c>
       <c r="I49" t="n">
         <v>3.16</v>
@@ -3290,7 +3294,7 @@
         <v>-2.44</v>
       </c>
       <c r="M49" t="n">
-        <v>-0.5</v>
+        <v>-0.57</v>
       </c>
       <c r="N49" t="b">
         <v>1</v>
@@ -3328,7 +3332,7 @@
         <v>1.9</v>
       </c>
       <c r="H50" t="n">
-        <v>-6.59</v>
+        <v>-5.22</v>
       </c>
       <c r="I50" t="n">
         <v>-10.64</v>
@@ -3339,7 +3343,7 @@
         <v>-14.75</v>
       </c>
       <c r="M50" t="n">
-        <v>-8.66</v>
+        <v>-7.9</v>
       </c>
       <c r="N50" t="b">
         <v>1</v>
@@ -3366,7 +3370,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Extended</t>
+          <t>Retired</t>
         </is>
       </c>
       <c r="E51" t="inlineStr"/>
@@ -3377,7 +3381,7 @@
         <v>37.5</v>
       </c>
       <c r="H51" t="n">
-        <v>7.09</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="I51" t="n">
         <v>5.86</v>
@@ -3388,7 +3392,7 @@
         <v>-3.95</v>
       </c>
       <c r="M51" t="n">
-        <v>4.87</v>
+        <v>5.62</v>
       </c>
       <c r="N51" t="b">
         <v>1</v>
@@ -3415,7 +3419,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Retired</t>
         </is>
       </c>
       <c r="E52" t="inlineStr"/>
@@ -3426,7 +3430,7 @@
         <v>15</v>
       </c>
       <c r="H52" t="n">
-        <v>-26.8</v>
+        <v>-24.38</v>
       </c>
       <c r="I52" t="n">
         <v>-21.11</v>
@@ -3437,7 +3441,7 @@
         <v>-28.65</v>
       </c>
       <c r="M52" t="n">
-        <v>-29.02</v>
+        <v>-27.21</v>
       </c>
       <c r="N52" t="b">
         <v>0</v>
@@ -3464,7 +3468,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Extended</t>
+          <t>Retired</t>
         </is>
       </c>
       <c r="E53" t="inlineStr"/>
@@ -3475,7 +3479,7 @@
         <v>40.2</v>
       </c>
       <c r="H53" t="n">
-        <v>11.68</v>
+        <v>10.95</v>
       </c>
       <c r="I53" t="n">
         <v>-1.11</v>
@@ -3486,7 +3490,7 @@
         <v>-5.29</v>
       </c>
       <c r="M53" t="n">
-        <v>9.449999999999999</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="N53" t="b">
         <v>1</v>
@@ -3513,7 +3517,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Retired</t>
         </is>
       </c>
       <c r="E54" t="inlineStr"/>
@@ -3524,7 +3528,7 @@
         <v>10.7</v>
       </c>
       <c r="H54" t="n">
-        <v>-0.14</v>
+        <v>-0.09</v>
       </c>
       <c r="I54" t="n">
         <v>7.3</v>
@@ -3535,7 +3539,7 @@
         <v>-3.78</v>
       </c>
       <c r="M54" t="n">
-        <v>-2.36</v>
+        <v>-2.93</v>
       </c>
       <c r="N54" t="b">
         <v>1</v>
@@ -3573,18 +3577,20 @@
         <v>25.6</v>
       </c>
       <c r="H55" t="n">
-        <v>12.04</v>
+        <v>12.1</v>
       </c>
       <c r="I55" t="n">
         <v>7.71</v>
       </c>
-      <c r="J55" t="inlineStr"/>
+      <c r="J55" t="n">
+        <v>12.1</v>
+      </c>
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="n">
         <v>-4.85</v>
       </c>
       <c r="M55" t="n">
-        <v>10.58</v>
+        <v>10.04</v>
       </c>
       <c r="N55" t="b">
         <v>1</v>
@@ -3622,7 +3628,7 @@
         <v>6.3</v>
       </c>
       <c r="H56" t="n">
-        <v>6.4</v>
+        <v>6.44</v>
       </c>
       <c r="I56" t="n">
         <v>7.2</v>
@@ -3635,7 +3641,7 @@
         <v>-0.4</v>
       </c>
       <c r="M56" t="n">
-        <v>4.05</v>
+        <v>3.47</v>
       </c>
       <c r="N56" t="b">
         <v>0</v>
@@ -3673,7 +3679,7 @@
         <v>2.3</v>
       </c>
       <c r="H57" t="n">
-        <v>-11.78</v>
+        <v>-11.05</v>
       </c>
       <c r="I57" t="n">
         <v>-8.85</v>
@@ -3686,7 +3692,7 @@
         <v>-14.2</v>
       </c>
       <c r="M57" t="n">
-        <v>-14.13</v>
+        <v>-14.01</v>
       </c>
       <c r="N57" t="b">
         <v>0</v>
@@ -3724,7 +3730,7 @@
         <v>-4.3</v>
       </c>
       <c r="H58" t="n">
-        <v>3.38</v>
+        <v>3.42</v>
       </c>
       <c r="I58" t="n">
         <v>3.39</v>
@@ -3737,7 +3743,7 @@
         <v>-5.89</v>
       </c>
       <c r="M58" t="n">
-        <v>1.84</v>
+        <v>1.27</v>
       </c>
       <c r="N58" t="b">
         <v>0</v>
@@ -3775,7 +3781,7 @@
         <v>-29.4</v>
       </c>
       <c r="H59" t="n">
-        <v>-6.75</v>
+        <v>-2.73</v>
       </c>
       <c r="I59" t="n">
         <v>-5.75</v>
@@ -3788,7 +3794,7 @@
         <v>-10.11</v>
       </c>
       <c r="M59" t="n">
-        <v>-8.289999999999999</v>
+        <v>-4.88</v>
       </c>
       <c r="N59" t="b">
         <v>0</v>
@@ -3826,7 +3832,7 @@
         <v>-6.9</v>
       </c>
       <c r="H60" t="n">
-        <v>14.56</v>
+        <v>14.85</v>
       </c>
       <c r="I60" t="n">
         <v>6.44</v>
@@ -3839,7 +3845,7 @@
         <v>-4.53</v>
       </c>
       <c r="M60" t="n">
-        <v>13.02</v>
+        <v>12.7</v>
       </c>
       <c r="N60" t="b">
         <v>1</v>
@@ -3877,7 +3883,7 @@
         <v>4.2</v>
       </c>
       <c r="H61" t="n">
-        <v>-15.75</v>
+        <v>-14.55</v>
       </c>
       <c r="I61" t="n">
         <v>-10.83</v>
@@ -3890,7 +3896,7 @@
         <v>-18.5</v>
       </c>
       <c r="M61" t="n">
-        <v>-17.29</v>
+        <v>-16.7</v>
       </c>
       <c r="N61" t="b">
         <v>0</v>
@@ -3928,7 +3934,7 @@
         <v>-32.4</v>
       </c>
       <c r="H62" t="n">
-        <v>-1.92</v>
+        <v>-0.45</v>
       </c>
       <c r="I62" t="n">
         <v>-2.43</v>
@@ -3941,7 +3947,7 @@
         <v>-12.47</v>
       </c>
       <c r="M62" t="n">
-        <v>-2.8</v>
+        <v>-1.94</v>
       </c>
       <c r="N62" t="b">
         <v>0</v>
@@ -3979,7 +3985,7 @@
         <v>-11</v>
       </c>
       <c r="H63" t="n">
-        <v>3.34</v>
+        <v>4.49</v>
       </c>
       <c r="I63" t="n">
         <v>-8.449999999999999</v>
@@ -3992,7 +3998,7 @@
         <v>-18.92</v>
       </c>
       <c r="M63" t="n">
-        <v>2.45</v>
+        <v>3</v>
       </c>
       <c r="N63" t="b">
         <v>0</v>
@@ -4030,7 +4036,7 @@
         <v>9.699999999999999</v>
       </c>
       <c r="H64" t="n">
-        <v>-1.96</v>
+        <v>1.89</v>
       </c>
       <c r="I64" t="n">
         <v>1.27</v>
@@ -4043,7 +4049,7 @@
         <v>-20.79</v>
       </c>
       <c r="M64" t="n">
-        <v>-2.99</v>
+        <v>0.25</v>
       </c>
       <c r="N64" t="b">
         <v>0</v>
@@ -4081,7 +4087,7 @@
         <v>-28.1</v>
       </c>
       <c r="H65" t="n">
-        <v>-13.46</v>
+        <v>-12.04</v>
       </c>
       <c r="I65" t="n">
         <v>-10.79</v>
@@ -4094,7 +4100,7 @@
         <v>-13.67</v>
       </c>
       <c r="M65" t="n">
-        <v>-14.5</v>
+        <v>-13.68</v>
       </c>
       <c r="N65" t="b">
         <v>0</v>
@@ -4132,7 +4138,7 @@
         <v>-17.7</v>
       </c>
       <c r="H66" t="n">
-        <v>-1.23</v>
+        <v>-1.47</v>
       </c>
       <c r="I66" t="n">
         <v>-0.89</v>
@@ -4145,7 +4151,7 @@
         <v>-11.37</v>
       </c>
       <c r="M66" t="n">
-        <v>-2.27</v>
+        <v>-3.11</v>
       </c>
       <c r="N66" t="b">
         <v>0</v>
@@ -4183,7 +4189,7 @@
         <v>-9.300000000000001</v>
       </c>
       <c r="H67" t="n">
-        <v>-5.77</v>
+        <v>-6.15</v>
       </c>
       <c r="I67" t="n">
         <v>-3.34</v>
@@ -4196,7 +4202,7 @@
         <v>-8.77</v>
       </c>
       <c r="M67" t="n">
-        <v>-6.81</v>
+        <v>-7.79</v>
       </c>
       <c r="N67" t="b">
         <v>0</v>
@@ -4234,7 +4240,7 @@
         <v>0.3</v>
       </c>
       <c r="H68" t="n">
-        <v>-17.07</v>
+        <v>-17.11</v>
       </c>
       <c r="I68" t="n">
         <v>-10.53</v>
@@ -4247,7 +4253,7 @@
         <v>-17.73</v>
       </c>
       <c r="M68" t="n">
-        <v>-18.11</v>
+        <v>-18.75</v>
       </c>
       <c r="N68" t="b">
         <v>1</v>
@@ -4285,7 +4291,7 @@
         <v>12.3</v>
       </c>
       <c r="H69" t="n">
-        <v>1.18</v>
+        <v>-0.43</v>
       </c>
       <c r="I69" t="n">
         <v>6.51</v>
@@ -4298,7 +4304,7 @@
         <v>-6.01</v>
       </c>
       <c r="M69" t="n">
-        <v>-0.58</v>
+        <v>-2.8</v>
       </c>
       <c r="N69" t="b">
         <v>0</v>
@@ -4336,7 +4342,7 @@
         <v>2.8</v>
       </c>
       <c r="H70" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="I70" t="n">
         <v>3.18</v>
@@ -4349,7 +4355,7 @@
         <v>-0.88</v>
       </c>
       <c r="M70" t="n">
-        <v>1.39</v>
+        <v>0.93</v>
       </c>
       <c r="N70" t="b">
         <v>1</v>
@@ -4387,7 +4393,7 @@
         <v>-1.4</v>
       </c>
       <c r="H71" t="n">
-        <v>11.99</v>
+        <v>13.34</v>
       </c>
       <c r="I71" t="n">
         <v>-4.52</v>
@@ -4400,7 +4406,7 @@
         <v>-7.44</v>
       </c>
       <c r="M71" t="n">
-        <v>10.24</v>
+        <v>10.97</v>
       </c>
       <c r="N71" t="b">
         <v>0</v>
@@ -4438,7 +4444,7 @@
         <v>34.5</v>
       </c>
       <c r="H72" t="n">
-        <v>10.6</v>
+        <v>12.05</v>
       </c>
       <c r="I72" t="n">
         <v>0.66</v>
@@ -4451,7 +4457,7 @@
         <v>-2.64</v>
       </c>
       <c r="M72" t="n">
-        <v>8.84</v>
+        <v>9.69</v>
       </c>
       <c r="N72" t="b">
         <v>1</v>
@@ -4489,7 +4495,7 @@
         <v>-22.7</v>
       </c>
       <c r="H73" t="n">
-        <v>-11.59</v>
+        <v>-10.1</v>
       </c>
       <c r="I73" t="n">
         <v>-6.71</v>
@@ -4502,7 +4508,7 @@
         <v>-9.58</v>
       </c>
       <c r="M73" t="n">
-        <v>-13.41</v>
+        <v>-12.53</v>
       </c>
       <c r="N73" t="b">
         <v>0</v>
@@ -4540,7 +4546,7 @@
         <v>24.3</v>
       </c>
       <c r="H74" t="n">
-        <v>59.22</v>
+        <v>63.36</v>
       </c>
       <c r="I74" t="n">
         <v>2.54</v>
@@ -4553,7 +4559,7 @@
         <v>-5.21</v>
       </c>
       <c r="M74" t="n">
-        <v>58.1</v>
+        <v>61.64</v>
       </c>
       <c r="N74" t="b">
         <v>1</v>
@@ -4591,7 +4597,7 @@
         <v>56.6</v>
       </c>
       <c r="H75" t="n">
-        <v>-2.8</v>
+        <v>0.23</v>
       </c>
       <c r="I75" t="n">
         <v>-13.1</v>
@@ -4604,7 +4610,7 @@
         <v>-16.17</v>
       </c>
       <c r="M75" t="n">
-        <v>-3.91</v>
+        <v>-1.48</v>
       </c>
       <c r="N75" t="b">
         <v>0</v>
@@ -4642,7 +4648,7 @@
         <v>2.9</v>
       </c>
       <c r="H76" t="n">
-        <v>-18.02</v>
+        <v>-16.75</v>
       </c>
       <c r="I76" t="n">
         <v>-8.470000000000001</v>
@@ -4655,7 +4661,7 @@
         <v>-15.65</v>
       </c>
       <c r="M76" t="n">
-        <v>-19.13</v>
+        <v>-18.47</v>
       </c>
       <c r="N76" t="b">
         <v>0</v>
@@ -4693,7 +4699,7 @@
         <v>-16.9</v>
       </c>
       <c r="H77" t="n">
-        <v>-11.9</v>
+        <v>-9.41</v>
       </c>
       <c r="I77" t="n">
         <v>-6.47</v>
@@ -4706,7 +4712,7 @@
         <v>-11.5</v>
       </c>
       <c r="M77" t="n">
-        <v>-13.01</v>
+        <v>-11.13</v>
       </c>
       <c r="N77" t="b">
         <v>1</v>
@@ -4744,7 +4750,7 @@
         <v>32.8</v>
       </c>
       <c r="H78" t="n">
-        <v>9.619999999999999</v>
+        <v>2.05</v>
       </c>
       <c r="I78" t="n">
         <v>14.96</v>
@@ -4757,7 +4763,7 @@
         <v>-0.9</v>
       </c>
       <c r="M78" t="n">
-        <v>9.09</v>
+        <v>0.92</v>
       </c>
       <c r="N78" t="b">
         <v>0</v>
@@ -4795,7 +4801,7 @@
         <v>0.8</v>
       </c>
       <c r="H79" t="n">
-        <v>-3.43</v>
+        <v>-3.05</v>
       </c>
       <c r="I79" t="n">
         <v>-7.73</v>
@@ -4808,7 +4814,7 @@
         <v>-10.12</v>
       </c>
       <c r="M79" t="n">
-        <v>-3.96</v>
+        <v>-4.18</v>
       </c>
       <c r="N79" t="b">
         <v>0</v>
@@ -4846,7 +4852,7 @@
         <v>-9.6</v>
       </c>
       <c r="H80" t="n">
-        <v>-14.68</v>
+        <v>-15.17</v>
       </c>
       <c r="I80" t="n">
         <v>-1.23</v>
@@ -4859,7 +4865,7 @@
         <v>-18.52</v>
       </c>
       <c r="M80" t="n">
-        <v>-15.21</v>
+        <v>-16.3</v>
       </c>
       <c r="N80" t="b">
         <v>0</v>
@@ -4897,7 +4903,7 @@
         <v>20.3</v>
       </c>
       <c r="H81" t="n">
-        <v>-20.99</v>
+        <v>-20.61</v>
       </c>
       <c r="I81" t="n">
         <v>-2.07</v>
@@ -4910,7 +4916,7 @@
         <v>-17.35</v>
       </c>
       <c r="M81" t="n">
-        <v>-21.94</v>
+        <v>-22.17</v>
       </c>
       <c r="N81" t="b">
         <v>1</v>
@@ -4948,7 +4954,7 @@
         <v>0.3</v>
       </c>
       <c r="H82" t="n">
-        <v>-18.87</v>
+        <v>-18.86</v>
       </c>
       <c r="I82" t="n">
         <v>-9.9</v>
@@ -4961,7 +4967,7 @@
         <v>-21.72</v>
       </c>
       <c r="M82" t="n">
-        <v>-20.32</v>
+        <v>-20.92</v>
       </c>
       <c r="N82" t="b">
         <v>1</v>
@@ -4999,7 +5005,7 @@
         <v>49.4</v>
       </c>
       <c r="H83" t="n">
-        <v>6.6</v>
+        <v>14.51</v>
       </c>
       <c r="I83" t="n">
         <v>2.9</v>
@@ -5012,7 +5018,7 @@
         <v>-5.67</v>
       </c>
       <c r="M83" t="n">
-        <v>5.33</v>
+        <v>12.64</v>
       </c>
       <c r="N83" t="b">
         <v>1</v>
@@ -5050,7 +5056,7 @@
         <v>4.5</v>
       </c>
       <c r="H84" t="n">
-        <v>-9.199999999999999</v>
+        <v>-9.07</v>
       </c>
       <c r="I84" t="n">
         <v>-7.61</v>
@@ -5063,7 +5069,7 @@
         <v>-11.06</v>
       </c>
       <c r="M84" t="n">
-        <v>-10.46</v>
+        <v>-10.94</v>
       </c>
       <c r="N84" t="b">
         <v>1</v>
@@ -5101,7 +5107,7 @@
         <v>4.2</v>
       </c>
       <c r="H85" t="n">
-        <v>-20.19</v>
+        <v>-19.23</v>
       </c>
       <c r="I85" t="n">
         <v>-6.86</v>
@@ -5114,7 +5120,7 @@
         <v>-20.23</v>
       </c>
       <c r="M85" t="n">
-        <v>-21.46</v>
+        <v>-21.1</v>
       </c>
       <c r="N85" t="b">
         <v>0</v>
@@ -5152,7 +5158,7 @@
         <v>15.4</v>
       </c>
       <c r="H86" t="n">
-        <v>-6.18</v>
+        <v>-4.06</v>
       </c>
       <c r="I86" t="n">
         <v>-1.19</v>
@@ -5165,7 +5171,7 @@
         <v>-7.43</v>
       </c>
       <c r="M86" t="n">
-        <v>-7.44</v>
+        <v>-5.94</v>
       </c>
       <c r="N86" t="b">
         <v>0</v>
@@ -5203,7 +5209,7 @@
         <v>15.5</v>
       </c>
       <c r="H87" t="n">
-        <v>-6.09</v>
+        <v>-5.3</v>
       </c>
       <c r="I87" t="n">
         <v>-7.36</v>
@@ -5216,7 +5222,7 @@
         <v>-12.98</v>
       </c>
       <c r="M87" t="n">
-        <v>-7.54</v>
+        <v>-7.35</v>
       </c>
       <c r="N87" t="b">
         <v>0</v>
@@ -5258,7 +5264,7 @@
         <v>-8.5</v>
       </c>
       <c r="H88" t="n">
-        <v>12.85</v>
+        <v>13.23</v>
       </c>
       <c r="I88" t="n">
         <v>-3.04</v>
@@ -5271,7 +5277,7 @@
         <v>-4.96</v>
       </c>
       <c r="M88" t="n">
-        <v>11.4</v>
+        <v>11.17</v>
       </c>
       <c r="N88" t="b">
         <v>0</v>
@@ -5309,7 +5315,7 @@
         <v>1.8</v>
       </c>
       <c r="H89" t="n">
-        <v>-12.35</v>
+        <v>-11.9</v>
       </c>
       <c r="I89" t="n">
         <v>-6.45</v>
@@ -5322,7 +5328,7 @@
         <v>-13.57</v>
       </c>
       <c r="M89" t="n">
-        <v>-13.79</v>
+        <v>-13.96</v>
       </c>
       <c r="N89" t="b">
         <v>0</v>
@@ -5360,7 +5366,7 @@
         <v>33.9</v>
       </c>
       <c r="H90" t="n">
-        <v>20.61</v>
+        <v>24.74</v>
       </c>
       <c r="I90" t="n">
         <v>-7.74</v>
@@ -5373,7 +5379,7 @@
         <v>-9.449999999999999</v>
       </c>
       <c r="M90" t="n">
-        <v>19.16</v>
+        <v>22.68</v>
       </c>
       <c r="N90" t="b">
         <v>0</v>
@@ -5411,7 +5417,7 @@
         <v>-25</v>
       </c>
       <c r="H91" t="n">
-        <v>-8.449999999999999</v>
+        <v>-8.73</v>
       </c>
       <c r="I91" t="n">
         <v>2.51</v>
@@ -5424,7 +5430,7 @@
         <v>-4.88</v>
       </c>
       <c r="M91" t="n">
-        <v>-9.73</v>
+        <v>-10.62</v>
       </c>
       <c r="N91" t="b">
         <v>0</v>
@@ -5462,7 +5468,7 @@
         <v>-12.6</v>
       </c>
       <c r="H92" t="n">
-        <v>-20.76</v>
+        <v>-24.2</v>
       </c>
       <c r="I92" t="n">
         <v>-7.89</v>
@@ -5475,7 +5481,7 @@
         <v>-21.29</v>
       </c>
       <c r="M92" t="n">
-        <v>-22.05</v>
+        <v>-26.1</v>
       </c>
       <c r="N92" t="b">
         <v>0</v>
@@ -5513,7 +5519,7 @@
         <v>-17.9</v>
       </c>
       <c r="H93" t="n">
-        <v>1.19</v>
+        <v>2.26</v>
       </c>
       <c r="I93" t="n">
         <v>0.6</v>
@@ -5526,7 +5532,7 @@
         <v>-4.72</v>
       </c>
       <c r="M93" t="n">
-        <v>-0.1</v>
+        <v>0.36</v>
       </c>
       <c r="N93" t="b">
         <v>1</v>
@@ -5564,7 +5570,7 @@
         <v>2.1</v>
       </c>
       <c r="H94" t="n">
-        <v>-22.84</v>
+        <v>-22.71</v>
       </c>
       <c r="I94" t="n">
         <v>0.25</v>
@@ -5577,7 +5583,7 @@
         <v>-16.43</v>
       </c>
       <c r="M94" t="n">
-        <v>-24.13</v>
+        <v>-24.61</v>
       </c>
       <c r="N94" t="b">
         <v>1</v>
@@ -5615,7 +5621,7 @@
         <v>19.4</v>
       </c>
       <c r="H95" t="n">
-        <v>-10.4</v>
+        <v>-8.51</v>
       </c>
       <c r="I95" t="n">
         <v>-10.01</v>
@@ -5628,7 +5634,7 @@
         <v>-15.23</v>
       </c>
       <c r="M95" t="n">
-        <v>-11.11</v>
+        <v>-9.83</v>
       </c>
       <c r="N95" t="b">
         <v>1</v>
@@ -5666,7 +5672,7 @@
         <v>-30.5</v>
       </c>
       <c r="H96" t="n">
-        <v>-18.72</v>
+        <v>-11.43</v>
       </c>
       <c r="I96" t="n">
         <v>-4.6</v>
@@ -5679,7 +5685,7 @@
         <v>-10.37</v>
       </c>
       <c r="M96" t="n">
-        <v>-19.43</v>
+        <v>-12.74</v>
       </c>
       <c r="N96" t="b">
         <v>0</v>
@@ -5717,7 +5723,7 @@
         <v>-20.5</v>
       </c>
       <c r="H97" t="n">
-        <v>-15.7</v>
+        <v>-19.58</v>
       </c>
       <c r="I97" t="n">
         <v>-4.62</v>
@@ -5730,7 +5736,7 @@
         <v>-9.92</v>
       </c>
       <c r="M97" t="n">
-        <v>-16.41</v>
+        <v>-20.9</v>
       </c>
       <c r="N97" t="b">
         <v>0</v>
@@ -5768,7 +5774,7 @@
         <v>-12.3</v>
       </c>
       <c r="H98" t="n">
-        <v>-17.12</v>
+        <v>-20.45</v>
       </c>
       <c r="I98" t="n">
         <v>-4.36</v>
@@ -5781,7 +5787,7 @@
         <v>-13.26</v>
       </c>
       <c r="M98" t="n">
-        <v>-18.05</v>
+        <v>-21.99</v>
       </c>
       <c r="N98" t="b">
         <v>0</v>
@@ -5819,7 +5825,7 @@
         <v>13.7</v>
       </c>
       <c r="H99" t="n">
-        <v>-15.59</v>
+        <v>-17.09</v>
       </c>
       <c r="I99" t="n">
         <v>-12.16</v>
@@ -5832,7 +5838,7 @@
         <v>-13.02</v>
       </c>
       <c r="M99" t="n">
-        <v>-16.52</v>
+        <v>-18.62</v>
       </c>
       <c r="N99" t="b">
         <v>0</v>
@@ -5870,7 +5876,7 @@
         <v>-2.6</v>
       </c>
       <c r="H100" t="n">
-        <v>-10.56</v>
+        <v>-9.24</v>
       </c>
       <c r="I100" t="n">
         <v>-4.27</v>
@@ -5883,7 +5889,7 @@
         <v>-4.86</v>
       </c>
       <c r="M100" t="n">
-        <v>-11.5</v>
+        <v>-10.78</v>
       </c>
       <c r="N100" t="b">
         <v>1</v>
@@ -5921,7 +5927,7 @@
         <v>25.6</v>
       </c>
       <c r="H101" t="n">
-        <v>-4.17</v>
+        <v>-2.17</v>
       </c>
       <c r="I101" t="n">
         <v>4.26</v>
@@ -5934,7 +5940,7 @@
         <v>-10.74</v>
       </c>
       <c r="M101" t="n">
-        <v>-5.1</v>
+        <v>-3.7</v>
       </c>
       <c r="N101" t="b">
         <v>0</v>
@@ -5972,7 +5978,7 @@
         <v>23.8</v>
       </c>
       <c r="H102" t="n">
-        <v>1.29</v>
+        <v>2.9</v>
       </c>
       <c r="I102" t="n">
         <v>1.36</v>
@@ -5985,7 +5991,7 @@
         <v>-9.94</v>
       </c>
       <c r="M102" t="n">
-        <v>1.33</v>
+        <v>2.34</v>
       </c>
       <c r="N102" t="b">
         <v>1</v>
@@ -6023,7 +6029,7 @@
         <v>38.9</v>
       </c>
       <c r="H103" t="n">
-        <v>-10.46</v>
+        <v>-11.43</v>
       </c>
       <c r="I103" t="n">
         <v>-9.220000000000001</v>
@@ -6036,7 +6042,7 @@
         <v>-9.83</v>
       </c>
       <c r="M103" t="n">
-        <v>-10.42</v>
+        <v>-11.98</v>
       </c>
       <c r="N103" t="b">
         <v>1</v>
@@ -6074,7 +6080,7 @@
         <v>32.1</v>
       </c>
       <c r="H104" t="n">
-        <v>38.51</v>
+        <v>45.63</v>
       </c>
       <c r="I104" t="n">
         <v>11.84</v>
@@ -6087,7 +6093,7 @@
         <v>-1.82</v>
       </c>
       <c r="M104" t="n">
-        <v>38.55</v>
+        <v>45.07</v>
       </c>
       <c r="N104" t="b">
         <v>0</v>
@@ -6125,7 +6131,7 @@
         <v>53.4</v>
       </c>
       <c r="H105" t="n">
-        <v>29.42</v>
+        <v>26.49</v>
       </c>
       <c r="I105" t="n">
         <v>2.75</v>
@@ -6138,7 +6144,7 @@
         <v>-2.31</v>
       </c>
       <c r="M105" t="n">
-        <v>29.76</v>
+        <v>26.24</v>
       </c>
       <c r="N105" t="b">
         <v>0</v>
@@ -6176,7 +6182,7 @@
         <v>54.1</v>
       </c>
       <c r="H106" t="n">
-        <v>34.51</v>
+        <v>32.1</v>
       </c>
       <c r="I106" t="n">
         <v>5.54</v>
@@ -6189,7 +6195,7 @@
         <v>-0.41</v>
       </c>
       <c r="M106" t="n">
-        <v>34.39</v>
+        <v>31.37</v>
       </c>
       <c r="N106" t="b">
         <v>0</v>
@@ -6227,7 +6233,7 @@
         <v>43.2</v>
       </c>
       <c r="H107" t="n">
-        <v>-17.01</v>
+        <v>-18.02</v>
       </c>
       <c r="I107" t="n">
         <v>-3.15</v>
@@ -6240,7 +6246,7 @@
         <v>-17.51</v>
       </c>
       <c r="M107" t="n">
-        <v>-17.14</v>
+        <v>-18.74</v>
       </c>
       <c r="N107" t="b">
         <v>1</v>
@@ -6278,7 +6284,7 @@
         <v>-8.199999999999999</v>
       </c>
       <c r="H108" t="n">
-        <v>-2.97</v>
+        <v>-1.78</v>
       </c>
       <c r="I108" t="n">
         <v>5.34</v>
@@ -6291,7 +6297,7 @@
         <v>-5.27</v>
       </c>
       <c r="M108" t="n">
-        <v>-3.09</v>
+        <v>-2.51</v>
       </c>
       <c r="N108" t="b">
         <v>1</v>
@@ -6329,7 +6335,7 @@
         <v>-1.2</v>
       </c>
       <c r="H109" t="n">
-        <v>3.15</v>
+        <v>3.68</v>
       </c>
       <c r="I109" t="n">
         <v>8.27</v>
@@ -6342,7 +6348,7 @@
         <v>-5.3</v>
       </c>
       <c r="M109" t="n">
-        <v>2.98</v>
+        <v>2.91</v>
       </c>
       <c r="N109" t="b">
         <v>0</v>
@@ -6380,7 +6386,7 @@
         <v>-23.9</v>
       </c>
       <c r="H110" t="n">
-        <v>-8.970000000000001</v>
+        <v>-4.61</v>
       </c>
       <c r="I110" t="n">
         <v>3.28</v>
@@ -6393,7 +6399,7 @@
         <v>-4.46</v>
       </c>
       <c r="M110" t="n">
-        <v>-9.390000000000001</v>
+        <v>-5.64</v>
       </c>
       <c r="N110" t="b">
         <v>1</v>
@@ -6435,7 +6441,7 @@
         <v>-6.1</v>
       </c>
       <c r="H111" t="n">
-        <v>-13.04</v>
+        <v>-17.4</v>
       </c>
       <c r="I111" t="n">
         <v>4.9</v>
@@ -6448,7 +6454,7 @@
         <v>-9</v>
       </c>
       <c r="M111" t="n">
-        <v>-13.46</v>
+        <v>-18.42</v>
       </c>
       <c r="N111" t="b">
         <v>1</v>
@@ -6486,7 +6492,7 @@
         <v>26.7</v>
       </c>
       <c r="H112" t="n">
-        <v>-0.72</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="I112" t="n">
         <v>-0.05</v>
@@ -6499,7 +6505,7 @@
         <v>-0.87</v>
       </c>
       <c r="M112" t="n">
-        <v>-1.14</v>
+        <v>-1.72</v>
       </c>
       <c r="N112" t="b">
         <v>1</v>
@@ -6537,7 +6543,7 @@
         <v>39.5</v>
       </c>
       <c r="H113" t="n">
-        <v>15.7</v>
+        <v>22.14</v>
       </c>
       <c r="I113" t="n">
         <v>-5.13</v>
@@ -6550,7 +6556,7 @@
         <v>-8.869999999999999</v>
       </c>
       <c r="M113" t="n">
-        <v>15.28</v>
+        <v>21.12</v>
       </c>
       <c r="N113" t="b">
         <v>0</v>
@@ -6588,7 +6594,7 @@
         <v>14.3</v>
       </c>
       <c r="H114" t="n">
-        <v>9.390000000000001</v>
+        <v>13.57</v>
       </c>
       <c r="I114" t="n">
         <v>-0.43</v>
@@ -6601,7 +6607,7 @@
         <v>-11.86</v>
       </c>
       <c r="M114" t="n">
-        <v>8.960000000000001</v>
+        <v>12.54</v>
       </c>
       <c r="N114" t="b">
         <v>0</v>
@@ -6639,7 +6645,7 @@
         <v>-11.3</v>
       </c>
       <c r="H115" t="n">
-        <v>5.63</v>
+        <v>10.44</v>
       </c>
       <c r="I115" t="n">
         <v>1.31</v>
@@ -6652,7 +6658,7 @@
         <v>-1.88</v>
       </c>
       <c r="M115" t="n">
-        <v>5.21</v>
+        <v>9.42</v>
       </c>
       <c r="N115" t="b">
         <v>0</v>
@@ -6690,7 +6696,7 @@
         <v>-23.5</v>
       </c>
       <c r="H116" t="n">
-        <v>-31.29</v>
+        <v>-35.16</v>
       </c>
       <c r="I116" t="n">
         <v>13.29</v>
@@ -6703,7 +6709,7 @@
         <v>-14.04</v>
       </c>
       <c r="M116" t="n">
-        <v>-31.71</v>
+        <v>-36.18</v>
       </c>
       <c r="N116" t="b">
         <v>0</v>
@@ -6741,7 +6747,7 @@
         <v>10.5</v>
       </c>
       <c r="H117" t="n">
-        <v>-6.62</v>
+        <v>-6.82</v>
       </c>
       <c r="I117" t="n">
         <v>-0.86</v>
@@ -6754,7 +6760,7 @@
         <v>-6.11</v>
       </c>
       <c r="M117" t="n">
-        <v>-7.04</v>
+        <v>-7.84</v>
       </c>
       <c r="N117" t="b">
         <v>0</v>
@@ -6792,7 +6798,7 @@
         <v>-3.5</v>
       </c>
       <c r="H118" t="n">
-        <v>-2.19</v>
+        <v>-3.69</v>
       </c>
       <c r="I118" t="n">
         <v>-4.95</v>
@@ -6805,7 +6811,7 @@
         <v>-8.43</v>
       </c>
       <c r="M118" t="n">
-        <v>-2.82</v>
+        <v>-4.92</v>
       </c>
       <c r="N118" t="b">
         <v>1</v>
@@ -6843,7 +6849,7 @@
         <v>-12.8</v>
       </c>
       <c r="H119" t="n">
-        <v>12.83</v>
+        <v>16.69</v>
       </c>
       <c r="I119" t="n">
         <v>-1.74</v>
@@ -6856,7 +6862,7 @@
         <v>-2.97</v>
       </c>
       <c r="M119" t="n">
-        <v>12.2</v>
+        <v>15.46</v>
       </c>
       <c r="N119" t="b">
         <v>0</v>
@@ -6894,7 +6900,7 @@
         <v>2.4</v>
       </c>
       <c r="H120" t="n">
-        <v>24.18</v>
+        <v>30.6</v>
       </c>
       <c r="I120" t="n">
         <v>12.41</v>
@@ -6907,7 +6913,7 @@
         <v>-0.07000000000000001</v>
       </c>
       <c r="M120" t="n">
-        <v>23.56</v>
+        <v>29.37</v>
       </c>
       <c r="N120" t="b">
         <v>0</v>
@@ -6945,7 +6951,7 @@
         <v>-17.9</v>
       </c>
       <c r="H121" t="n">
-        <v>7</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I121" t="n">
         <v>-0.5</v>
@@ -6958,7 +6964,7 @@
         <v>-3.43</v>
       </c>
       <c r="M121" t="n">
-        <v>6.38</v>
+        <v>7.47</v>
       </c>
       <c r="N121" t="b">
         <v>1</v>
@@ -6996,7 +7002,7 @@
         <v>11.9</v>
       </c>
       <c r="H122" t="n">
-        <v>-5.38</v>
+        <v>-4.5</v>
       </c>
       <c r="I122" t="n">
         <v>6.88</v>
@@ -7009,7 +7015,7 @@
         <v>-10.93</v>
       </c>
       <c r="M122" t="n">
-        <v>-6.11</v>
+        <v>-5.84</v>
       </c>
       <c r="N122" t="b">
         <v>0</v>
@@ -7047,7 +7053,7 @@
         <v>53.5</v>
       </c>
       <c r="H123" t="n">
-        <v>7.7</v>
+        <v>12.46</v>
       </c>
       <c r="I123" t="n">
         <v>1.23</v>
@@ -7060,7 +7066,7 @@
         <v>-7.57</v>
       </c>
       <c r="M123" t="n">
-        <v>6.97</v>
+        <v>11.12</v>
       </c>
       <c r="N123" t="b">
         <v>1</v>
@@ -7098,7 +7104,7 @@
         <v>18.1</v>
       </c>
       <c r="H124" t="n">
-        <v>-2.09</v>
+        <v>-2.16</v>
       </c>
       <c r="I124" t="n">
         <v>-1.69</v>
@@ -7111,7 +7117,7 @@
         <v>-1.92</v>
       </c>
       <c r="M124" t="n">
-        <v>-2.82</v>
+        <v>-3.49</v>
       </c>
       <c r="N124" t="b">
         <v>0</v>
@@ -7149,7 +7155,7 @@
         <v>-1</v>
       </c>
       <c r="H125" t="n">
-        <v>-9.1</v>
+        <v>-8.289999999999999</v>
       </c>
       <c r="I125" t="n">
         <v>-6.26</v>
@@ -7162,7 +7168,7 @@
         <v>-15</v>
       </c>
       <c r="M125" t="n">
-        <v>-9.83</v>
+        <v>-9.619999999999999</v>
       </c>
       <c r="N125" t="b">
         <v>1</v>
@@ -7200,7 +7206,7 @@
         <v>29.7</v>
       </c>
       <c r="H126" t="n">
-        <v>3.32</v>
+        <v>7.04</v>
       </c>
       <c r="I126" t="n">
         <v>11.27</v>
@@ -7213,7 +7219,7 @@
         <v>0</v>
       </c>
       <c r="M126" t="n">
-        <v>2.59</v>
+        <v>5.7</v>
       </c>
       <c r="N126" t="b">
         <v>1</v>
@@ -7251,7 +7257,7 @@
         <v>15.2</v>
       </c>
       <c r="H127" t="n">
-        <v>-38.99</v>
+        <v>-37.21</v>
       </c>
       <c r="I127" t="n">
         <v>-8.77</v>
@@ -7264,7 +7270,7 @@
         <v>-24.79</v>
       </c>
       <c r="M127" t="n">
-        <v>-38.99</v>
+        <v>-37.81</v>
       </c>
       <c r="N127" t="b">
         <v>1</v>
@@ -7302,7 +7308,7 @@
         <v>22.2</v>
       </c>
       <c r="H128" t="n">
-        <v>4.01</v>
+        <v>4.79</v>
       </c>
       <c r="I128" t="n">
         <v>1.01</v>
@@ -7315,7 +7321,7 @@
         <v>-3.94</v>
       </c>
       <c r="M128" t="n">
-        <v>4.01</v>
+        <v>4.19</v>
       </c>
       <c r="N128" t="b">
         <v>1</v>
@@ -7353,7 +7359,7 @@
         <v>10.8</v>
       </c>
       <c r="H129" t="n">
-        <v>2.78</v>
+        <v>3.4</v>
       </c>
       <c r="I129" t="n">
         <v>5.62</v>
@@ -7366,7 +7372,7 @@
         <v>-1.59</v>
       </c>
       <c r="M129" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="N129" t="b">
         <v>0</v>
@@ -7404,7 +7410,7 @@
         <v>-2.1</v>
       </c>
       <c r="H130" t="n">
-        <v>-8.289999999999999</v>
+        <v>-10.66</v>
       </c>
       <c r="I130" t="n">
         <v>0.67</v>
@@ -7417,7 +7423,7 @@
         <v>-7.84</v>
       </c>
       <c r="M130" t="n">
-        <v>-8.289999999999999</v>
+        <v>-11.26</v>
       </c>
       <c r="N130" t="b">
         <v>0</v>
@@ -7455,7 +7461,7 @@
         <v>16.7</v>
       </c>
       <c r="H131" t="n">
-        <v>-22.85</v>
+        <v>-23.09</v>
       </c>
       <c r="I131" t="n">
         <v>-15.31</v>
@@ -7468,7 +7474,7 @@
         <v>-22</v>
       </c>
       <c r="M131" t="n">
-        <v>-24.85</v>
+        <v>-25.7</v>
       </c>
       <c r="N131" t="b">
         <v>0</v>
@@ -7506,7 +7512,7 @@
         <v>0.3</v>
       </c>
       <c r="H132" t="n">
-        <v>26.58</v>
+        <v>25.96</v>
       </c>
       <c r="I132" t="n">
         <v>6.01</v>
@@ -7519,7 +7525,7 @@
         <v>-3.85</v>
       </c>
       <c r="M132" t="n">
-        <v>23.06</v>
+        <v>21.82</v>
       </c>
       <c r="N132" t="b">
         <v>0</v>
@@ -7561,7 +7567,7 @@
         <v>-0</v>
       </c>
       <c r="H133" t="n">
-        <v>35.64</v>
+        <v>41.02</v>
       </c>
       <c r="I133" t="n">
         <v>13.5</v>
@@ -7574,7 +7580,7 @@
         <v>-2.53</v>
       </c>
       <c r="M133" t="n">
-        <v>32.12</v>
+        <v>36.88</v>
       </c>
       <c r="N133" t="b">
         <v>1</v>
@@ -7612,7 +7618,7 @@
         <v>10.5</v>
       </c>
       <c r="H134" t="n">
-        <v>7.28</v>
+        <v>7.94</v>
       </c>
       <c r="I134" t="n">
         <v>1.99</v>
@@ -7625,7 +7631,7 @@
         <v>-6.27</v>
       </c>
       <c r="M134" t="n">
-        <v>3.76</v>
+        <v>3.8</v>
       </c>
       <c r="N134" t="b">
         <v>1</v>
@@ -7663,7 +7669,7 @@
         <v>30.4</v>
       </c>
       <c r="H135" t="n">
-        <v>5.46</v>
+        <v>4.8</v>
       </c>
       <c r="I135" t="n">
         <v>8.539999999999999</v>
@@ -7676,7 +7682,7 @@
         <v>-0.44</v>
       </c>
       <c r="M135" t="n">
-        <v>1.93</v>
+        <v>0.66</v>
       </c>
       <c r="N135" t="b">
         <v>0</v>
@@ -7718,7 +7724,7 @@
         <v>-3.2</v>
       </c>
       <c r="H136" t="n">
-        <v>13.25</v>
+        <v>12.51</v>
       </c>
       <c r="I136" t="n">
         <v>15.28</v>
@@ -7731,7 +7737,7 @@
         <v>-2.53</v>
       </c>
       <c r="M136" t="n">
-        <v>9.720000000000001</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="N136" t="b">
         <v>0</v>
@@ -7769,7 +7775,7 @@
         <v>-23.5</v>
       </c>
       <c r="H137" t="n">
-        <v>20.68</v>
+        <v>18.29</v>
       </c>
       <c r="I137" t="n">
         <v>20.48</v>
@@ -7782,7 +7788,7 @@
         <v>-2.25</v>
       </c>
       <c r="M137" t="n">
-        <v>17.15</v>
+        <v>14.15</v>
       </c>
       <c r="N137" t="b">
         <v>0</v>
@@ -7820,7 +7826,7 @@
         <v>-27.3</v>
       </c>
       <c r="H138" t="n">
-        <v>5.14</v>
+        <v>4.57</v>
       </c>
       <c r="I138" t="n">
         <v>-8.83</v>
@@ -7833,7 +7839,7 @@
         <v>-19.66</v>
       </c>
       <c r="M138" t="n">
-        <v>1.62</v>
+        <v>0.43</v>
       </c>
       <c r="N138" t="b">
         <v>0</v>
@@ -7871,7 +7877,7 @@
         <v>-12.5</v>
       </c>
       <c r="H139" t="n">
-        <v>-7.8</v>
+        <v>-5.61</v>
       </c>
       <c r="I139" t="n">
         <v>21.54</v>
@@ -7884,7 +7890,7 @@
         <v>-0.95</v>
       </c>
       <c r="M139" t="n">
-        <v>-11.99</v>
+        <v>-10.42</v>
       </c>
       <c r="N139" t="b">
         <v>0</v>
@@ -7922,7 +7928,7 @@
         <v>-37</v>
       </c>
       <c r="H140" t="n">
-        <v>40.24</v>
+        <v>45.58</v>
       </c>
       <c r="I140" t="n">
         <v>18.38</v>
@@ -7935,7 +7941,7 @@
         <v>-5.11</v>
       </c>
       <c r="M140" t="n">
-        <v>36.05</v>
+        <v>40.77</v>
       </c>
       <c r="N140" t="b">
         <v>1</v>
@@ -7977,7 +7983,7 @@
         <v>-3.4</v>
       </c>
       <c r="H141" t="n">
-        <v>7.99</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="I141" t="n">
         <v>30.48</v>
@@ -7990,7 +7996,7 @@
         <v>-0.9</v>
       </c>
       <c r="M141" t="n">
-        <v>3.8</v>
+        <v>5.05</v>
       </c>
       <c r="N141" t="b">
         <v>0</v>
@@ -8028,7 +8034,7 @@
         <v>-23.4</v>
       </c>
       <c r="H142" t="n">
-        <v>-7.73</v>
+        <v>-6.03</v>
       </c>
       <c r="I142" t="n">
         <v>-3.58</v>
@@ -8041,7 +8047,7 @@
         <v>-17.98</v>
       </c>
       <c r="M142" t="n">
-        <v>-11.92</v>
+        <v>-10.84</v>
       </c>
       <c r="N142" t="b">
         <v>0</v>
@@ -8079,7 +8085,7 @@
         <v>-28.9</v>
       </c>
       <c r="H143" t="n">
-        <v>-18.29</v>
+        <v>-17.8</v>
       </c>
       <c r="I143" t="n">
         <v>-12.9</v>
@@ -8092,7 +8098,7 @@
         <v>-23.19</v>
       </c>
       <c r="M143" t="n">
-        <v>-22.48</v>
+        <v>-22.61</v>
       </c>
       <c r="N143" t="b">
         <v>0</v>
@@ -8130,7 +8136,7 @@
         <v>-26.8</v>
       </c>
       <c r="H144" t="n">
-        <v>18.53</v>
+        <v>16.64</v>
       </c>
       <c r="I144" t="n">
         <v>4.56</v>
@@ -8143,7 +8149,7 @@
         <v>-4.09</v>
       </c>
       <c r="M144" t="n">
-        <v>14.34</v>
+        <v>11.83</v>
       </c>
       <c r="N144" t="b">
         <v>1</v>
@@ -8185,7 +8191,7 @@
         <v>-9.800000000000001</v>
       </c>
       <c r="H145" t="n">
-        <v>-24.5</v>
+        <v>-25.16</v>
       </c>
       <c r="I145" t="n">
         <v>-4.09</v>
@@ -8198,7 +8204,7 @@
         <v>-15.24</v>
       </c>
       <c r="M145" t="n">
-        <v>-29.91</v>
+        <v>-31.2</v>
       </c>
       <c r="N145" t="b">
         <v>0</v>
@@ -8236,7 +8242,7 @@
         <v>21</v>
       </c>
       <c r="H146" t="n">
-        <v>4.64</v>
+        <v>3.02</v>
       </c>
       <c r="I146" t="n">
         <v>-0.72</v>
@@ -8249,7 +8255,7 @@
         <v>-7.35</v>
       </c>
       <c r="M146" t="n">
-        <v>-0.76</v>
+        <v>-3.01</v>
       </c>
       <c r="N146" t="b">
         <v>0</v>
@@ -8287,7 +8293,7 @@
         <v>13.2</v>
       </c>
       <c r="H147" t="n">
-        <v>40.51</v>
+        <v>41.67</v>
       </c>
       <c r="I147" t="n">
         <v>8.130000000000001</v>
@@ -8300,7 +8306,7 @@
         <v>-2.36</v>
       </c>
       <c r="M147" t="n">
-        <v>35.1</v>
+        <v>35.63</v>
       </c>
       <c r="N147" t="b">
         <v>0</v>
@@ -8338,7 +8344,7 @@
         <v>6.1</v>
       </c>
       <c r="H148" t="n">
-        <v>8.779999999999999</v>
+        <v>13.79</v>
       </c>
       <c r="I148" t="n">
         <v>10.43</v>
@@ -8351,7 +8357,7 @@
         <v>-1.51</v>
       </c>
       <c r="M148" t="n">
-        <v>3.38</v>
+        <v>7.75</v>
       </c>
       <c r="N148" t="b">
         <v>0</v>
@@ -8389,7 +8395,7 @@
         <v>6.5</v>
       </c>
       <c r="H149" t="n">
-        <v>-8.18</v>
+        <v>-8.210000000000001</v>
       </c>
       <c r="I149" t="n">
         <v>-0.04</v>
@@ -8402,7 +8408,7 @@
         <v>-4.12</v>
       </c>
       <c r="M149" t="n">
-        <v>-13.58</v>
+        <v>-14.25</v>
       </c>
       <c r="N149" t="b">
         <v>0</v>
@@ -8440,7 +8446,7 @@
         <v>-36.5</v>
       </c>
       <c r="H150" t="n">
-        <v>-33.9</v>
+        <v>-35.3</v>
       </c>
       <c r="I150" t="n">
         <v>-27.75</v>
@@ -8453,7 +8459,7 @@
         <v>-31.28</v>
       </c>
       <c r="M150" t="n">
-        <v>-38.75</v>
+        <v>-40.77</v>
       </c>
       <c r="N150" t="b">
         <v>1</v>
@@ -8491,7 +8497,7 @@
         <v>-14.5</v>
       </c>
       <c r="H151" t="n">
-        <v>-16.6</v>
+        <v>-15.86</v>
       </c>
       <c r="I151" t="n">
         <v>4.48</v>
@@ -8504,7 +8510,7 @@
         <v>-3.33</v>
       </c>
       <c r="M151" t="n">
-        <v>-21.45</v>
+        <v>-21.34</v>
       </c>
       <c r="N151" t="b">
         <v>0</v>
@@ -8542,7 +8548,7 @@
         <v>1.7</v>
       </c>
       <c r="H152" t="n">
-        <v>-1.79</v>
+        <v>0.67</v>
       </c>
       <c r="I152" t="n">
         <v>8.859999999999999</v>
@@ -8555,7 +8561,7 @@
         <v>-3.27</v>
       </c>
       <c r="M152" t="n">
-        <v>-6.64</v>
+        <v>-4.81</v>
       </c>
       <c r="N152" t="b">
         <v>0</v>
@@ -8593,7 +8599,7 @@
         <v>48.1</v>
       </c>
       <c r="H153" t="n">
-        <v>-0.28</v>
+        <v>11.25</v>
       </c>
       <c r="I153" t="n">
         <v>0.16</v>
@@ -8606,7 +8612,7 @@
         <v>-8.890000000000001</v>
       </c>
       <c r="M153" t="n">
-        <v>-5.13</v>
+        <v>5.77</v>
       </c>
       <c r="N153" t="b">
         <v>0</v>
@@ -8644,7 +8650,7 @@
         <v>-38.7</v>
       </c>
       <c r="H154" t="n">
-        <v>14.52</v>
+        <v>13.98</v>
       </c>
       <c r="I154" t="n">
         <v>17.17</v>
@@ -8657,7 +8663,7 @@
         <v>-0.54</v>
       </c>
       <c r="M154" t="n">
-        <v>9.67</v>
+        <v>8.51</v>
       </c>
       <c r="N154" t="b">
         <v>1</v>
@@ -8695,7 +8701,7 @@
         <v>24.9</v>
       </c>
       <c r="H155" t="n">
-        <v>-2.01</v>
+        <v>-0.17</v>
       </c>
       <c r="I155" t="n">
         <v>10.45</v>
@@ -8708,7 +8714,7 @@
         <v>-0.49</v>
       </c>
       <c r="M155" t="n">
-        <v>-6.86</v>
+        <v>-5.64</v>
       </c>
       <c r="N155" t="b">
         <v>0</v>
@@ -8746,7 +8752,7 @@
         <v>-34.6</v>
       </c>
       <c r="H156" t="n">
-        <v>21.18</v>
+        <v>21.72</v>
       </c>
       <c r="I156" t="n">
         <v>6.67</v>
@@ -8759,7 +8765,7 @@
         <v>-3.06</v>
       </c>
       <c r="M156" t="n">
-        <v>16.33</v>
+        <v>16.24</v>
       </c>
       <c r="N156" t="b">
         <v>1</v>
@@ -8797,7 +8803,7 @@
         <v>-21.4</v>
       </c>
       <c r="H157" t="n">
-        <v>-0.86</v>
+        <v>-2.62</v>
       </c>
       <c r="I157" t="n">
         <v>2.8</v>
@@ -8810,7 +8816,7 @@
         <v>-2.27</v>
       </c>
       <c r="M157" t="n">
-        <v>-5.71</v>
+        <v>-8.1</v>
       </c>
       <c r="N157" t="b">
         <v>0</v>
@@ -8848,7 +8854,7 @@
         <v>-11.8</v>
       </c>
       <c r="H158" t="n">
-        <v>-2.47</v>
+        <v>-4.41</v>
       </c>
       <c r="I158" t="n">
         <v>9.76</v>
@@ -8861,7 +8867,7 @@
         <v>-1.63</v>
       </c>
       <c r="M158" t="n">
-        <v>-7.43</v>
+        <v>-9.99</v>
       </c>
       <c r="N158" t="b">
         <v>1</v>
@@ -8899,7 +8905,7 @@
         <v>0.1</v>
       </c>
       <c r="H159" t="n">
-        <v>-12.92</v>
+        <v>-14.72</v>
       </c>
       <c r="I159" t="n">
         <v>-2.83</v>
@@ -8912,7 +8918,7 @@
         <v>-5.45</v>
       </c>
       <c r="M159" t="n">
-        <v>-17.88</v>
+        <v>-20.31</v>
       </c>
       <c r="N159" t="b">
         <v>1</v>
@@ -8950,7 +8956,7 @@
         <v>-13.8</v>
       </c>
       <c r="H160" t="n">
-        <v>26.79</v>
+        <v>29.91</v>
       </c>
       <c r="I160" t="n">
         <v>4.67</v>
@@ -8963,7 +8969,7 @@
         <v>-5.7</v>
       </c>
       <c r="M160" t="n">
-        <v>21.83</v>
+        <v>24.32</v>
       </c>
       <c r="N160" t="b">
         <v>0</v>
@@ -9005,7 +9011,7 @@
         <v>-8.800000000000001</v>
       </c>
       <c r="H161" t="n">
-        <v>6.64</v>
+        <v>7.24</v>
       </c>
       <c r="I161" t="n">
         <v>15.97</v>
@@ -9018,7 +9024,7 @@
         <v>-0.79</v>
       </c>
       <c r="M161" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="N161" t="b">
         <v>0</v>
@@ -9056,7 +9062,7 @@
         <v>24.1</v>
       </c>
       <c r="H162" t="n">
-        <v>4.27</v>
+        <v>4.92</v>
       </c>
       <c r="I162" t="n">
         <v>-8.31</v>
@@ -9069,7 +9075,7 @@
         <v>-18.31</v>
       </c>
       <c r="M162" t="n">
-        <v>0.12</v>
+        <v>0.14</v>
       </c>
       <c r="N162" t="b">
         <v>1</v>
@@ -9107,7 +9113,7 @@
         <v>-15.9</v>
       </c>
       <c r="H163" t="n">
-        <v>9.15</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="I163" t="n">
         <v>10.45</v>
@@ -9120,7 +9126,7 @@
         <v>-0.31</v>
       </c>
       <c r="M163" t="n">
-        <v>5</v>
+        <v>4.85</v>
       </c>
       <c r="N163" t="b">
         <v>1</v>
@@ -9158,7 +9164,7 @@
         <v>-23.3</v>
       </c>
       <c r="H164" t="n">
-        <v>-17.65</v>
+        <v>-14.66</v>
       </c>
       <c r="I164" t="n">
         <v>-20.42</v>
@@ -9171,7 +9177,7 @@
         <v>-27.45</v>
       </c>
       <c r="M164" t="n">
-        <v>-21.81</v>
+        <v>-19.44</v>
       </c>
       <c r="N164" t="b">
         <v>0</v>
@@ -9209,7 +9215,7 @@
         <v>28.9</v>
       </c>
       <c r="H165" t="n">
-        <v>2.64</v>
+        <v>5.77</v>
       </c>
       <c r="I165" t="n">
         <v>8.06</v>
@@ -9222,7 +9228,7 @@
         <v>-2.79</v>
       </c>
       <c r="M165" t="n">
-        <v>-2.42</v>
+        <v>0.08</v>
       </c>
       <c r="N165" t="b">
         <v>0</v>
@@ -9260,7 +9266,7 @@
         <v>40.1</v>
       </c>
       <c r="H166" t="n">
-        <v>42.17</v>
+        <v>48.67</v>
       </c>
       <c r="I166" t="n">
         <v>15.9</v>
@@ -9273,7 +9279,7 @@
         <v>-5.87</v>
       </c>
       <c r="M166" t="n">
-        <v>37.11</v>
+        <v>42.98</v>
       </c>
       <c r="N166" t="b">
         <v>0</v>
@@ -9311,7 +9317,7 @@
         <v>-27.3</v>
       </c>
       <c r="H167" t="n">
-        <v>4.83</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="I167" t="n">
         <v>0.75</v>
@@ -9324,7 +9330,7 @@
         <v>-5.46</v>
       </c>
       <c r="M167" t="n">
-        <v>-0.1</v>
+        <v>4.04</v>
       </c>
       <c r="N167" t="b">
         <v>0</v>
@@ -9362,7 +9368,7 @@
         <v>19.7</v>
       </c>
       <c r="H168" t="n">
-        <v>-18.71</v>
+        <v>-13.83</v>
       </c>
       <c r="I168" t="n">
         <v>-4.49</v>
@@ -9375,7 +9381,7 @@
         <v>-13.7</v>
       </c>
       <c r="M168" t="n">
-        <v>-23.64</v>
+        <v>-19.4</v>
       </c>
       <c r="N168" t="b">
         <v>0</v>
@@ -9413,7 +9419,7 @@
         <v>-21.3</v>
       </c>
       <c r="H169" t="n">
-        <v>-7.58</v>
+        <v>-6.45</v>
       </c>
       <c r="I169" t="n">
         <v>7.16</v>
@@ -9426,7 +9432,7 @@
         <v>-11.9</v>
       </c>
       <c r="M169" t="n">
-        <v>-12.51</v>
+        <v>-12.02</v>
       </c>
       <c r="N169" t="b">
         <v>0</v>
@@ -9464,7 +9470,7 @@
         <v>-21.8</v>
       </c>
       <c r="H170" t="n">
-        <v>-32.38</v>
+        <v>-33.12</v>
       </c>
       <c r="I170" t="n">
         <v>-18.97</v>
@@ -9477,7 +9483,7 @@
         <v>-26.82</v>
       </c>
       <c r="M170" t="n">
-        <v>-37.31</v>
+        <v>-38.69</v>
       </c>
       <c r="N170" t="b">
         <v>1</v>
@@ -9515,7 +9521,7 @@
         <v>-37.6</v>
       </c>
       <c r="H171" t="n">
-        <v>-12.72</v>
+        <v>-11.82</v>
       </c>
       <c r="I171" t="n">
         <v>15.2</v>
@@ -9528,7 +9534,7 @@
         <v>-10.3</v>
       </c>
       <c r="M171" t="n">
-        <v>-16.63</v>
+        <v>-16.36</v>
       </c>
       <c r="N171" t="b">
         <v>0</v>
@@ -9566,7 +9572,7 @@
         <v>53.8</v>
       </c>
       <c r="H172" t="n">
-        <v>55.89</v>
+        <v>64.33</v>
       </c>
       <c r="I172" t="n">
         <v>4.09</v>
@@ -9579,7 +9585,7 @@
         <v>-8.66</v>
       </c>
       <c r="M172" t="n">
-        <v>51.97</v>
+        <v>59.79</v>
       </c>
       <c r="N172" t="b">
         <v>0</v>
@@ -9621,7 +9627,7 @@
         <v>-5.7</v>
       </c>
       <c r="H173" t="n">
-        <v>52.56</v>
+        <v>55.85</v>
       </c>
       <c r="I173" t="n">
         <v>17.92</v>
@@ -9634,7 +9640,7 @@
         <v>-7.48</v>
       </c>
       <c r="M173" t="n">
-        <v>48.64</v>
+        <v>51.31</v>
       </c>
       <c r="N173" t="b">
         <v>0</v>
@@ -9672,7 +9678,7 @@
         <v>-39.3</v>
       </c>
       <c r="H174" t="n">
-        <v>3.17</v>
+        <v>3.26</v>
       </c>
       <c r="I174" t="n">
         <v>11.34</v>
@@ -9685,7 +9691,7 @@
         <v>-5.3</v>
       </c>
       <c r="M174" t="n">
-        <v>-0.75</v>
+        <v>-1.27</v>
       </c>
       <c r="N174" t="b">
         <v>0</v>
@@ -9723,7 +9729,7 @@
         <v>57</v>
       </c>
       <c r="H175" t="n">
-        <v>29.97</v>
+        <v>30.59</v>
       </c>
       <c r="I175" t="n">
         <v>-11.21</v>
@@ -9774,7 +9780,7 @@
         <v>-21.8</v>
       </c>
       <c r="H176" t="n">
-        <v>9.859999999999999</v>
+        <v>9.33</v>
       </c>
       <c r="I176" t="n">
         <v>1.71</v>
@@ -9787,7 +9793,7 @@
         <v>-6.18</v>
       </c>
       <c r="M176" t="n">
-        <v>5.94</v>
+        <v>4.79</v>
       </c>
       <c r="N176" t="b">
         <v>1</v>
@@ -9825,7 +9831,7 @@
         <v>1</v>
       </c>
       <c r="H177" t="n">
-        <v>-31.03</v>
+        <v>-33.55</v>
       </c>
       <c r="I177" t="n">
         <v>-11.52</v>
@@ -9838,7 +9844,7 @@
         <v>-16.26</v>
       </c>
       <c r="M177" t="n">
-        <v>-35</v>
+        <v>-38.14</v>
       </c>
       <c r="N177" t="b">
         <v>1</v>
@@ -9876,7 +9882,7 @@
         <v>45.4</v>
       </c>
       <c r="H178" t="n">
-        <v>-3.57</v>
+        <v>-6.72</v>
       </c>
       <c r="I178" t="n">
         <v>-1.72</v>
@@ -9889,7 +9895,7 @@
         <v>-23.15</v>
       </c>
       <c r="M178" t="n">
-        <v>-7.53</v>
+        <v>-11.31</v>
       </c>
       <c r="N178" t="b">
         <v>1</v>
@@ -9927,7 +9933,7 @@
         <v>49.6</v>
       </c>
       <c r="H179" t="n">
-        <v>33.62</v>
+        <v>33.92</v>
       </c>
       <c r="I179" t="n">
         <v>6.34</v>
@@ -9940,7 +9946,7 @@
         <v>-20.75</v>
       </c>
       <c r="M179" t="n">
-        <v>29.65</v>
+        <v>29.33</v>
       </c>
       <c r="N179" t="b">
         <v>0</v>
@@ -9978,7 +9984,7 @@
         <v>55.3</v>
       </c>
       <c r="H180" t="n">
-        <v>-25.6</v>
+        <v>-24.85</v>
       </c>
       <c r="I180" t="n">
         <v>3.73</v>
@@ -9991,7 +9997,7 @@
         <v>-22.94</v>
       </c>
       <c r="M180" t="n">
-        <v>-29.56</v>
+        <v>-29.43</v>
       </c>
       <c r="N180" t="b">
         <v>0</v>
@@ -10029,7 +10035,7 @@
         <v>76.5</v>
       </c>
       <c r="H181" t="n">
-        <v>6.47</v>
+        <v>4.64</v>
       </c>
       <c r="I181" t="n">
         <v>-5.56</v>
@@ -10042,7 +10048,7 @@
         <v>-33.97</v>
       </c>
       <c r="M181" t="n">
-        <v>2.51</v>
+        <v>0.06</v>
       </c>
       <c r="N181" t="b">
         <v>1</v>
@@ -10080,7 +10086,7 @@
         <v>77.90000000000001</v>
       </c>
       <c r="H182" t="n">
-        <v>11.94</v>
+        <v>11.2</v>
       </c>
       <c r="I182" t="n">
         <v>-3.53</v>
@@ -10093,7 +10099,7 @@
         <v>-20.26</v>
       </c>
       <c r="M182" t="n">
-        <v>7.98</v>
+        <v>6.62</v>
       </c>
       <c r="N182" t="b">
         <v>0</v>
@@ -10131,7 +10137,7 @@
         <v>57.6</v>
       </c>
       <c r="H183" t="n">
-        <v>55.99</v>
+        <v>61.4</v>
       </c>
       <c r="I183" t="n">
         <v>14.81</v>
@@ -10144,7 +10150,7 @@
         <v>-5.11</v>
       </c>
       <c r="M183" t="n">
-        <v>52.03</v>
+        <v>56.81</v>
       </c>
       <c r="N183" t="b">
         <v>0</v>
@@ -10233,7 +10239,7 @@
         <v>51.8</v>
       </c>
       <c r="H185" t="n">
-        <v>6.28</v>
+        <v>4.79</v>
       </c>
       <c r="I185" t="n">
         <v>10.75</v>
@@ -10246,7 +10252,7 @@
         <v>-25.09</v>
       </c>
       <c r="M185" t="n">
-        <v>2.31</v>
+        <v>0.21</v>
       </c>
       <c r="N185" t="b">
         <v>1</v>
@@ -10284,7 +10290,7 @@
         <v>32.3</v>
       </c>
       <c r="H186" t="n">
-        <v>-24.15</v>
+        <v>-24.95</v>
       </c>
       <c r="I186" t="n">
         <v>-20.76</v>
@@ -10297,7 +10303,7 @@
         <v>-27.91</v>
       </c>
       <c r="M186" t="n">
-        <v>-28.11</v>
+        <v>-29.53</v>
       </c>
       <c r="N186" t="b">
         <v>1</v>
@@ -10335,7 +10341,7 @@
         <v>15.7</v>
       </c>
       <c r="H187" t="n">
-        <v>-5.07</v>
+        <v>-2.68</v>
       </c>
       <c r="I187" t="n">
         <v>-0.87</v>
@@ -10348,7 +10354,7 @@
         <v>-29.01</v>
       </c>
       <c r="M187" t="n">
-        <v>-9.029999999999999</v>
+        <v>-7.27</v>
       </c>
       <c r="N187" t="b">
         <v>0</v>
@@ -10386,7 +10392,7 @@
         <v>63.7</v>
       </c>
       <c r="H188" t="n">
-        <v>-10.25</v>
+        <v>-9.300000000000001</v>
       </c>
       <c r="I188" t="n">
         <v>-2.16</v>
@@ -10399,7 +10405,7 @@
         <v>-19.1</v>
       </c>
       <c r="M188" t="n">
-        <v>-14.21</v>
+        <v>-13.89</v>
       </c>
       <c r="N188" t="b">
         <v>0</v>
@@ -10437,7 +10443,7 @@
         <v>3.7</v>
       </c>
       <c r="H189" t="n">
-        <v>-13.71</v>
+        <v>-4.92</v>
       </c>
       <c r="I189" t="n">
         <v>-1.11</v>
@@ -10450,7 +10456,7 @@
         <v>-25.46</v>
       </c>
       <c r="M189" t="n">
-        <v>-17.68</v>
+        <v>-9.5</v>
       </c>
       <c r="N189" t="b">
         <v>1</v>
@@ -10488,7 +10494,7 @@
         <v>42.4</v>
       </c>
       <c r="H190" t="n">
-        <v>-1.79</v>
+        <v>6.86</v>
       </c>
       <c r="I190" t="n">
         <v>2.16</v>
@@ -10501,7 +10507,7 @@
         <v>-15.76</v>
       </c>
       <c r="M190" t="n">
-        <v>-5.75</v>
+        <v>2.28</v>
       </c>
       <c r="N190" t="b">
         <v>1</v>
@@ -10539,7 +10545,7 @@
         <v>28.2</v>
       </c>
       <c r="H191" t="n">
-        <v>7.48</v>
+        <v>10.82</v>
       </c>
       <c r="I191" t="n">
         <v>-1.71</v>
@@ -10552,7 +10558,7 @@
         <v>-23.43</v>
       </c>
       <c r="M191" t="n">
-        <v>3.52</v>
+        <v>6.24</v>
       </c>
       <c r="N191" t="b">
         <v>1</v>
@@ -10590,7 +10596,7 @@
         <v>28.6</v>
       </c>
       <c r="H192" t="n">
-        <v>19.08</v>
+        <v>20.79</v>
       </c>
       <c r="I192" t="n">
         <v>2.81</v>
@@ -10603,7 +10609,7 @@
         <v>-18.87</v>
       </c>
       <c r="M192" t="n">
-        <v>15.12</v>
+        <v>16.2</v>
       </c>
       <c r="N192" t="b">
         <v>1</v>
@@ -10641,7 +10647,7 @@
         <v>89.09999999999999</v>
       </c>
       <c r="H193" t="n">
-        <v>45.64</v>
+        <v>48.56</v>
       </c>
       <c r="I193" t="n">
         <v>18.45</v>
@@ -10654,7 +10660,7 @@
         <v>-9.029999999999999</v>
       </c>
       <c r="M193" t="n">
-        <v>41.68</v>
+        <v>43.97</v>
       </c>
       <c r="N193" t="b">
         <v>0</v>
@@ -10692,7 +10698,7 @@
         <v>50.5</v>
       </c>
       <c r="H194" t="n">
-        <v>3.77</v>
+        <v>1.46</v>
       </c>
       <c r="I194" t="n">
         <v>-2.26</v>
@@ -10705,7 +10711,7 @@
         <v>-20.74</v>
       </c>
       <c r="M194" t="n">
-        <v>-0.19</v>
+        <v>-3.12</v>
       </c>
       <c r="N194" t="b">
         <v>0</v>
@@ -10743,7 +10749,7 @@
         <v>33.1</v>
       </c>
       <c r="H195" t="n">
-        <v>29.22</v>
+        <v>35.96</v>
       </c>
       <c r="I195" t="n">
         <v>4.68</v>
@@ -10756,7 +10762,7 @@
         <v>-26.7</v>
       </c>
       <c r="M195" t="n">
-        <v>25.26</v>
+        <v>31.38</v>
       </c>
       <c r="N195" t="b">
         <v>1</v>
@@ -10794,7 +10800,7 @@
         <v>46.3</v>
       </c>
       <c r="H196" t="n">
-        <v>-9.710000000000001</v>
+        <v>-10.16</v>
       </c>
       <c r="I196" t="n">
         <v>-3.24</v>
@@ -10807,7 +10813,7 @@
         <v>-22.77</v>
       </c>
       <c r="M196" t="n">
-        <v>-13.67</v>
+        <v>-14.74</v>
       </c>
       <c r="N196" t="b">
         <v>0</v>
@@ -10845,7 +10851,7 @@
         <v>-13.8</v>
       </c>
       <c r="H197" t="n">
-        <v>16.4</v>
+        <v>15.4</v>
       </c>
       <c r="I197" t="n">
         <v>6.03</v>
@@ -10858,7 +10864,7 @@
         <v>-13.77</v>
       </c>
       <c r="M197" t="n">
-        <v>12.44</v>
+        <v>10.82</v>
       </c>
       <c r="N197" t="b">
         <v>0</v>
@@ -10896,7 +10902,7 @@
         <v>21.8</v>
       </c>
       <c r="H198" t="n">
-        <v>-17.13</v>
+        <v>-14.65</v>
       </c>
       <c r="I198" t="n">
         <v>-6.34</v>
@@ -10909,7 +10915,7 @@
         <v>-30.04</v>
       </c>
       <c r="M198" t="n">
-        <v>-21.09</v>
+        <v>-19.23</v>
       </c>
       <c r="N198" t="b">
         <v>1</v>
@@ -10947,7 +10953,7 @@
         <v>40.3</v>
       </c>
       <c r="H199" t="n">
-        <v>-8.33</v>
+        <v>-4.26</v>
       </c>
       <c r="I199" t="n">
         <v>1.24</v>
@@ -10960,7 +10966,7 @@
         <v>-20.5</v>
       </c>
       <c r="M199" t="n">
-        <v>-12.29</v>
+        <v>-8.84</v>
       </c>
       <c r="N199" t="b">
         <v>1</v>
@@ -11049,7 +11055,7 @@
         <v>24.1</v>
       </c>
       <c r="H201" t="n">
-        <v>8.859999999999999</v>
+        <v>3.34</v>
       </c>
       <c r="I201" t="n">
         <v>-1.6</v>
@@ -11062,7 +11068,7 @@
         <v>-22.54</v>
       </c>
       <c r="M201" t="n">
-        <v>4.9</v>
+        <v>-1.24</v>
       </c>
       <c r="N201" t="b">
         <v>1</v>
@@ -11100,7 +11106,7 @@
         <v>50.3</v>
       </c>
       <c r="H202" t="n">
-        <v>-23.95</v>
+        <v>-19.48</v>
       </c>
       <c r="I202" t="n">
         <v>-3.34</v>
@@ -11113,7 +11119,7 @@
         <v>-23.32</v>
       </c>
       <c r="M202" t="n">
-        <v>-27.91</v>
+        <v>-24.07</v>
       </c>
       <c r="N202" t="b">
         <v>0</v>
@@ -11151,7 +11157,7 @@
         <v>24.5</v>
       </c>
       <c r="H203" t="n">
-        <v>-26.36</v>
+        <v>-27.78</v>
       </c>
       <c r="I203" t="n">
         <v>-12.99</v>
@@ -11164,7 +11170,7 @@
         <v>-22.54</v>
       </c>
       <c r="M203" t="n">
-        <v>-30.32</v>
+        <v>-32.36</v>
       </c>
       <c r="N203" t="b">
         <v>1</v>
@@ -11202,7 +11208,7 @@
         <v>-4</v>
       </c>
       <c r="H204" t="n">
-        <v>-17</v>
+        <v>-19.18</v>
       </c>
       <c r="I204" t="n">
         <v>-1.59</v>
@@ -11215,7 +11221,7 @@
         <v>-25.38</v>
       </c>
       <c r="M204" t="n">
-        <v>-20.96</v>
+        <v>-23.76</v>
       </c>
       <c r="N204" t="b">
         <v>0</v>
@@ -11253,7 +11259,7 @@
         <v>14.8</v>
       </c>
       <c r="H205" t="n">
-        <v>-35.06</v>
+        <v>-35.58</v>
       </c>
       <c r="I205" t="n">
         <v>-2.48</v>
@@ -11266,7 +11272,7 @@
         <v>-40.98</v>
       </c>
       <c r="M205" t="n">
-        <v>-39.02</v>
+        <v>-40.16</v>
       </c>
       <c r="N205" t="b">
         <v>0</v>
@@ -11304,7 +11310,7 @@
         <v>-27.6</v>
       </c>
       <c r="H206" t="n">
-        <v>-2.21</v>
+        <v>-5.85</v>
       </c>
       <c r="I206" t="n">
         <v>-0.36</v>
@@ -11317,7 +11323,7 @@
         <v>-19.41</v>
       </c>
       <c r="M206" t="n">
-        <v>-6.17</v>
+        <v>-10.44</v>
       </c>
       <c r="N206" t="b">
         <v>0</v>
@@ -11355,7 +11361,7 @@
         <v>9.1</v>
       </c>
       <c r="H207" t="n">
-        <v>-29.75</v>
+        <v>-29.13</v>
       </c>
       <c r="I207" t="n">
         <v>-2.83</v>
@@ -11406,7 +11412,7 @@
         <v>11</v>
       </c>
       <c r="H208" t="n">
-        <v>7.1</v>
+        <v>13.09</v>
       </c>
       <c r="I208" t="n">
         <v>3.38</v>
@@ -11419,7 +11425,7 @@
         <v>-18.71</v>
       </c>
       <c r="M208" t="n">
-        <v>3.14</v>
+        <v>8.51</v>
       </c>
       <c r="N208" t="b">
         <v>0</v>
@@ -11457,7 +11463,7 @@
         <v>31.2</v>
       </c>
       <c r="H209" t="n">
-        <v>-10.58</v>
+        <v>-11.11</v>
       </c>
       <c r="I209" t="n">
         <v>-11.26</v>
@@ -11470,7 +11476,7 @@
         <v>-22.9</v>
       </c>
       <c r="M209" t="n">
-        <v>-14.54</v>
+        <v>-15.69</v>
       </c>
       <c r="N209" t="b">
         <v>0</v>
@@ -11508,7 +11514,7 @@
         <v>19.3</v>
       </c>
       <c r="H210" t="n">
-        <v>10.49</v>
+        <v>11.59</v>
       </c>
       <c r="I210" t="n">
         <v>11.79</v>
@@ -11521,7 +11527,7 @@
         <v>-16.62</v>
       </c>
       <c r="M210" t="n">
-        <v>6.53</v>
+        <v>7</v>
       </c>
       <c r="N210" t="b">
         <v>1</v>
@@ -11559,7 +11565,7 @@
         <v>-8.699999999999999</v>
       </c>
       <c r="H211" t="n">
-        <v>-10.08</v>
+        <v>-11.27</v>
       </c>
       <c r="I211" t="n">
         <v>17.25</v>
@@ -11572,7 +11578,7 @@
         <v>-4.65</v>
       </c>
       <c r="M211" t="n">
-        <v>-14.04</v>
+        <v>-15.85</v>
       </c>
       <c r="N211" t="b">
         <v>1</v>
@@ -11610,7 +11616,7 @@
         <v>15.2</v>
       </c>
       <c r="H212" t="n">
-        <v>-1.6</v>
+        <v>1.74</v>
       </c>
       <c r="I212" t="n">
         <v>5.36</v>
@@ -11623,7 +11629,7 @@
         <v>-28.18</v>
       </c>
       <c r="M212" t="n">
-        <v>-5.56</v>
+        <v>-2.84</v>
       </c>
       <c r="N212" t="b">
         <v>1</v>
@@ -11661,7 +11667,7 @@
         <v>37.2</v>
       </c>
       <c r="H213" t="n">
-        <v>-24.95</v>
+        <v>-23.77</v>
       </c>
       <c r="I213" t="n">
         <v>-7.64</v>
@@ -11674,7 +11680,7 @@
         <v>-26.24</v>
       </c>
       <c r="M213" t="n">
-        <v>-28.91</v>
+        <v>-28.35</v>
       </c>
       <c r="N213" t="b">
         <v>1</v>
@@ -11716,7 +11722,7 @@
         <v>-0.5</v>
       </c>
       <c r="H214" t="n">
-        <v>36</v>
+        <v>40.2</v>
       </c>
       <c r="I214" t="n">
         <v>12.75</v>
@@ -11729,7 +11735,7 @@
         <v>-4.72</v>
       </c>
       <c r="M214" t="n">
-        <v>32.04</v>
+        <v>35.62</v>
       </c>
       <c r="N214" t="b">
         <v>0</v>
@@ -11767,7 +11773,7 @@
         <v>-27.9</v>
       </c>
       <c r="H215" t="n">
-        <v>-19.58</v>
+        <v>-24.72</v>
       </c>
       <c r="I215" t="n">
         <v>-5.72</v>
@@ -11780,7 +11786,7 @@
         <v>-11.08</v>
       </c>
       <c r="M215" t="n">
-        <v>-23.54</v>
+        <v>-29.3</v>
       </c>
       <c r="N215" t="b">
         <v>0</v>
@@ -11818,7 +11824,7 @@
         <v>29.8</v>
       </c>
       <c r="H216" t="n">
-        <v>41.18</v>
+        <v>41.04</v>
       </c>
       <c r="I216" t="n">
         <v>-2.74</v>
@@ -11831,7 +11837,7 @@
         <v>-22.36</v>
       </c>
       <c r="M216" t="n">
-        <v>37.22</v>
+        <v>36.45</v>
       </c>
       <c r="N216" t="b">
         <v>1</v>
@@ -11869,7 +11875,7 @@
         <v>60.9</v>
       </c>
       <c r="H217" t="n">
-        <v>2.63</v>
+        <v>2.44</v>
       </c>
       <c r="I217" t="n">
         <v>6.71</v>
@@ -11882,7 +11888,7 @@
         <v>-4.9</v>
       </c>
       <c r="M217" t="n">
-        <v>-1.33</v>
+        <v>-2.14</v>
       </c>
       <c r="N217" t="b">
         <v>0</v>
@@ -11920,7 +11926,7 @@
         <v>-13.4</v>
       </c>
       <c r="H218" t="n">
-        <v>-24.11</v>
+        <v>-24.15</v>
       </c>
       <c r="I218" t="n">
         <v>0.79</v>
@@ -11933,7 +11939,7 @@
         <v>-15.41</v>
       </c>
       <c r="M218" t="n">
-        <v>-28.07</v>
+        <v>-28.73</v>
       </c>
       <c r="N218" t="b">
         <v>0</v>
@@ -11971,7 +11977,7 @@
         <v>18.2</v>
       </c>
       <c r="H219" t="n">
-        <v>-12.78</v>
+        <v>-14.85</v>
       </c>
       <c r="I219" t="n">
         <v>-11.28</v>
@@ -11984,7 +11990,7 @@
         <v>-16.87</v>
       </c>
       <c r="M219" t="n">
-        <v>-16.75</v>
+        <v>-19.43</v>
       </c>
       <c r="N219" t="b">
         <v>0</v>
@@ -12022,7 +12028,7 @@
         <v>31.2</v>
       </c>
       <c r="H220" t="n">
-        <v>-2.19</v>
+        <v>-2.73</v>
       </c>
       <c r="I220" t="n">
         <v>-3.17</v>
@@ -12035,7 +12041,7 @@
         <v>-23.66</v>
       </c>
       <c r="M220" t="n">
-        <v>-6.16</v>
+        <v>-7.31</v>
       </c>
       <c r="N220" t="b">
         <v>0</v>
@@ -12073,7 +12079,7 @@
         <v>-1.3</v>
       </c>
       <c r="H221" t="n">
-        <v>-17.04</v>
+        <v>-17.29</v>
       </c>
       <c r="I221" t="n">
         <v>5.29</v>
@@ -12086,7 +12092,7 @@
         <v>-11.87</v>
       </c>
       <c r="M221" t="n">
-        <v>-21</v>
+        <v>-21.88</v>
       </c>
       <c r="N221" t="b">
         <v>0</v>
@@ -12124,7 +12130,7 @@
         <v>-29.8</v>
       </c>
       <c r="H222" t="n">
-        <v>75.29000000000001</v>
+        <v>71.54000000000001</v>
       </c>
       <c r="I222" t="n">
         <v>29.88</v>
@@ -12137,7 +12143,7 @@
         <v>-0.29</v>
       </c>
       <c r="M222" t="n">
-        <v>71.33</v>
+        <v>66.95</v>
       </c>
       <c r="N222" t="b">
         <v>0</v>
@@ -12175,7 +12181,7 @@
         <v>-22.4</v>
       </c>
       <c r="H223" t="n">
-        <v>-15.6</v>
+        <v>-15.91</v>
       </c>
       <c r="I223" t="n">
         <v>5.79</v>
@@ -12188,7 +12194,7 @@
         <v>-9.67</v>
       </c>
       <c r="M223" t="n">
-        <v>-19.56</v>
+        <v>-20.5</v>
       </c>
       <c r="N223" t="b">
         <v>0</v>
@@ -12226,7 +12232,7 @@
         <v>19.3</v>
       </c>
       <c r="H224" t="n">
-        <v>-23.81</v>
+        <v>-26.62</v>
       </c>
       <c r="I224" t="n">
         <v>-16.69</v>
@@ -12239,7 +12245,7 @@
         <v>-36.39</v>
       </c>
       <c r="M224" t="n">
-        <v>-27.77</v>
+        <v>-31.2</v>
       </c>
       <c r="N224" t="b">
         <v>1</v>
@@ -12277,7 +12283,7 @@
         <v>7.6</v>
       </c>
       <c r="H225" t="n">
-        <v>-17.04</v>
+        <v>-16.81</v>
       </c>
       <c r="I225" t="n">
         <v>6.22</v>
@@ -12290,7 +12296,7 @@
         <v>-10.68</v>
       </c>
       <c r="M225" t="n">
-        <v>-21</v>
+        <v>-21.4</v>
       </c>
       <c r="N225" t="b">
         <v>0</v>
@@ -12328,7 +12334,7 @@
         <v>68.8</v>
       </c>
       <c r="H226" t="n">
-        <v>18</v>
+        <v>15.61</v>
       </c>
       <c r="I226" t="n">
         <v>-1.41</v>
@@ -12341,7 +12347,7 @@
         <v>-19.39</v>
       </c>
       <c r="M226" t="n">
-        <v>14.04</v>
+        <v>11.02</v>
       </c>
       <c r="N226" t="b">
         <v>0</v>
@@ -12379,7 +12385,7 @@
         <v>8.5</v>
       </c>
       <c r="H227" t="n">
-        <v>-28.18</v>
+        <v>-29.09</v>
       </c>
       <c r="I227" t="n">
         <v>-4.26</v>
@@ -12392,7 +12398,7 @@
         <v>-23.85</v>
       </c>
       <c r="M227" t="n">
-        <v>-32.14</v>
+        <v>-33.67</v>
       </c>
       <c r="N227" t="b">
         <v>0</v>
@@ -12430,7 +12436,7 @@
         <v>-15.2</v>
       </c>
       <c r="H228" t="n">
-        <v>3.11</v>
+        <v>2.82</v>
       </c>
       <c r="I228" t="n">
         <v>12.27</v>
@@ -12443,7 +12449,7 @@
         <v>-12.27</v>
       </c>
       <c r="M228" t="n">
-        <v>-0.86</v>
+        <v>-1.77</v>
       </c>
       <c r="N228" t="b">
         <v>0</v>
@@ -12481,7 +12487,7 @@
         <v>-33.1</v>
       </c>
       <c r="H229" t="n">
-        <v>-15.03</v>
+        <v>-12.34</v>
       </c>
       <c r="I229" t="n">
         <v>-13.13</v>
@@ -12494,7 +12500,7 @@
         <v>-21.04</v>
       </c>
       <c r="M229" t="n">
-        <v>-18.99</v>
+        <v>-16.92</v>
       </c>
       <c r="N229" t="b">
         <v>0</v>
@@ -12532,7 +12538,7 @@
         <v>11.8</v>
       </c>
       <c r="H230" t="n">
-        <v>16.49</v>
+        <v>19.32</v>
       </c>
       <c r="I230" t="n">
         <v>-1.19</v>
@@ -12545,7 +12551,7 @@
         <v>-17.57</v>
       </c>
       <c r="M230" t="n">
-        <v>12.52</v>
+        <v>14.74</v>
       </c>
       <c r="N230" t="b">
         <v>1</v>
@@ -12583,7 +12589,7 @@
         <v>27.5</v>
       </c>
       <c r="H231" t="n">
-        <v>9.93</v>
+        <v>12.35</v>
       </c>
       <c r="I231" t="n">
         <v>8.42</v>
@@ -12596,7 +12602,7 @@
         <v>-2.51</v>
       </c>
       <c r="M231" t="n">
-        <v>5.96</v>
+        <v>7.77</v>
       </c>
       <c r="N231" t="b">
         <v>1</v>
@@ -12634,7 +12640,7 @@
         <v>-22.4</v>
       </c>
       <c r="H232" t="n">
-        <v>-9.890000000000001</v>
+        <v>-10.49</v>
       </c>
       <c r="I232" t="n">
         <v>9.42</v>
@@ -12647,7 +12653,7 @@
         <v>-2.79</v>
       </c>
       <c r="M232" t="n">
-        <v>-13.85</v>
+        <v>-15.08</v>
       </c>
       <c r="N232" t="b">
         <v>1</v>
@@ -12685,7 +12691,7 @@
         <v>-14.7</v>
       </c>
       <c r="H233" t="n">
-        <v>-19.48</v>
+        <v>-21.64</v>
       </c>
       <c r="I233" t="n">
         <v>10.3</v>
@@ -12698,7 +12704,7 @@
         <v>-2.6</v>
       </c>
       <c r="M233" t="n">
-        <v>-23.44</v>
+        <v>-26.22</v>
       </c>
       <c r="N233" t="b">
         <v>1</v>
@@ -12740,7 +12746,7 @@
         <v>-9.300000000000001</v>
       </c>
       <c r="H234" t="n">
-        <v>-21.53</v>
+        <v>-20.57</v>
       </c>
       <c r="I234" t="n">
         <v>10.42</v>
@@ -12753,7 +12759,7 @@
         <v>-21.72</v>
       </c>
       <c r="M234" t="n">
-        <v>-25.49</v>
+        <v>-25.16</v>
       </c>
       <c r="N234" t="b">
         <v>1</v>
@@ -12791,7 +12797,7 @@
         <v>-13.5</v>
       </c>
       <c r="H235" t="n">
-        <v>117.94</v>
+        <v>121.38</v>
       </c>
       <c r="I235" t="n">
         <v>18.09</v>
@@ -12804,7 +12810,7 @@
         <v>-14.35</v>
       </c>
       <c r="M235" t="n">
-        <v>113.98</v>
+        <v>116.8</v>
       </c>
       <c r="N235" t="b">
         <v>0</v>
@@ -12842,7 +12848,7 @@
         <v>-27.5</v>
       </c>
       <c r="H236" t="n">
-        <v>-13.82</v>
+        <v>-8.949999999999999</v>
       </c>
       <c r="I236" t="n">
         <v>-29.95</v>
@@ -12855,7 +12861,7 @@
         <v>-35.86</v>
       </c>
       <c r="M236" t="n">
-        <v>-17.78</v>
+        <v>-13.54</v>
       </c>
       <c r="N236" t="b">
         <v>0</v>
@@ -12893,7 +12899,7 @@
         <v>11.9</v>
       </c>
       <c r="H237" t="n">
-        <v>-35.76</v>
+        <v>-35.66</v>
       </c>
       <c r="I237" t="n">
         <v>-3.02</v>
@@ -12906,7 +12912,7 @@
         <v>-24.96</v>
       </c>
       <c r="M237" t="n">
-        <v>-39.72</v>
+        <v>-40.25</v>
       </c>
       <c r="N237" t="b">
         <v>0</v>
@@ -12944,7 +12950,7 @@
         <v>5</v>
       </c>
       <c r="H238" t="n">
-        <v>3.06</v>
+        <v>3.31</v>
       </c>
       <c r="I238" t="n">
         <v>0.41</v>
@@ -12957,7 +12963,7 @@
         <v>-13.87</v>
       </c>
       <c r="M238" t="n">
-        <v>-0.9</v>
+        <v>-1.28</v>
       </c>
       <c r="N238" t="b">
         <v>0</v>
@@ -12995,7 +13001,7 @@
         <v>-35.9</v>
       </c>
       <c r="H239" t="n">
-        <v>10.49</v>
+        <v>15.14</v>
       </c>
       <c r="I239" t="n">
         <v>18.67</v>
@@ -13008,7 +13014,7 @@
         <v>-6.77</v>
       </c>
       <c r="M239" t="n">
-        <v>6.53</v>
+        <v>10.55</v>
       </c>
       <c r="N239" t="b">
         <v>0</v>
@@ -13046,7 +13052,7 @@
         <v>-25.2</v>
       </c>
       <c r="H240" t="n">
-        <v>8.77</v>
+        <v>9.44</v>
       </c>
       <c r="I240" t="n">
         <v>22.53</v>
@@ -13059,7 +13065,7 @@
         <v>-19.27</v>
       </c>
       <c r="M240" t="n">
-        <v>4.81</v>
+        <v>4.85</v>
       </c>
       <c r="N240" t="b">
         <v>1</v>
@@ -13097,7 +13103,7 @@
         <v>5.1</v>
       </c>
       <c r="H241" t="n">
-        <v>2.8</v>
+        <v>3.59</v>
       </c>
       <c r="I241" t="n">
         <v>8.77</v>
@@ -13110,7 +13116,7 @@
         <v>-3.54</v>
       </c>
       <c r="M241" t="n">
-        <v>-1.16</v>
+        <v>-1</v>
       </c>
       <c r="N241" t="b">
         <v>1</v>
@@ -13148,7 +13154,7 @@
         <v>20.8</v>
       </c>
       <c r="H242" t="n">
-        <v>-19.55</v>
+        <v>-19.87</v>
       </c>
       <c r="I242" t="n">
         <v>-10.93</v>
@@ -13161,7 +13167,7 @@
         <v>-27.1</v>
       </c>
       <c r="M242" t="n">
-        <v>-23.52</v>
+        <v>-24.45</v>
       </c>
       <c r="N242" t="b">
         <v>0</v>
@@ -13199,7 +13205,7 @@
         <v>-27.7</v>
       </c>
       <c r="H243" t="n">
-        <v>2.45</v>
+        <v>6.85</v>
       </c>
       <c r="I243" t="n">
         <v>-10.22</v>
@@ -13212,7 +13218,7 @@
         <v>-17.14</v>
       </c>
       <c r="M243" t="n">
-        <v>-1.51</v>
+        <v>2.27</v>
       </c>
       <c r="N243" t="b">
         <v>0</v>
@@ -13263,7 +13269,7 @@
         <v>-19.04</v>
       </c>
       <c r="M244" t="n">
-        <v>-5.16</v>
+        <v>-5.78</v>
       </c>
       <c r="N244" t="b">
         <v>0</v>
@@ -13301,7 +13307,7 @@
         <v>-34.9</v>
       </c>
       <c r="H245" t="n">
-        <v>-14.09</v>
+        <v>-19.02</v>
       </c>
       <c r="I245" t="n">
         <v>19.9</v>
@@ -13314,7 +13320,7 @@
         <v>-12.62</v>
       </c>
       <c r="M245" t="n">
-        <v>-18.05</v>
+        <v>-23.6</v>
       </c>
       <c r="N245" t="b">
         <v>0</v>
@@ -13352,7 +13358,7 @@
         <v>-29.5</v>
       </c>
       <c r="H246" t="n">
-        <v>-11.81</v>
+        <v>-6.63</v>
       </c>
       <c r="I246" t="n">
         <v>4.05</v>
@@ -13365,7 +13371,7 @@
         <v>-2.43</v>
       </c>
       <c r="M246" t="n">
-        <v>-15.77</v>
+        <v>-11.22</v>
       </c>
       <c r="N246" t="b">
         <v>0</v>
@@ -13403,7 +13409,7 @@
         <v>34.2</v>
       </c>
       <c r="H247" t="n">
-        <v>7.71</v>
+        <v>8.26</v>
       </c>
       <c r="I247" t="n">
         <v>8.15</v>
@@ -13416,7 +13422,7 @@
         <v>-7.63</v>
       </c>
       <c r="M247" t="n">
-        <v>3.75</v>
+        <v>3.67</v>
       </c>
       <c r="N247" t="b">
         <v>1</v>
@@ -13454,7 +13460,7 @@
         <v>42</v>
       </c>
       <c r="H248" t="n">
-        <v>-31.67</v>
+        <v>-31.9</v>
       </c>
       <c r="I248" t="n">
         <v>0.6</v>
@@ -13467,7 +13473,7 @@
         <v>-16.67</v>
       </c>
       <c r="M248" t="n">
-        <v>-35.63</v>
+        <v>-36.48</v>
       </c>
       <c r="N248" t="b">
         <v>1</v>
@@ -13509,7 +13515,7 @@
         <v>-0.4</v>
       </c>
       <c r="H249" t="n">
-        <v>-10.94</v>
+        <v>-12.8</v>
       </c>
       <c r="I249" t="n">
         <v>4.83</v>
@@ -13522,7 +13528,7 @@
         <v>-10.75</v>
       </c>
       <c r="M249" t="n">
-        <v>-14.9</v>
+        <v>-17.38</v>
       </c>
       <c r="N249" t="b">
         <v>0</v>
@@ -13560,7 +13566,7 @@
         <v>64.59999999999999</v>
       </c>
       <c r="H250" t="n">
-        <v>15.74</v>
+        <v>19.2</v>
       </c>
       <c r="I250" t="n">
         <v>3.01</v>
@@ -13573,7 +13579,7 @@
         <v>-12</v>
       </c>
       <c r="M250" t="n">
-        <v>11.78</v>
+        <v>14.62</v>
       </c>
       <c r="N250" t="b">
         <v>0</v>
@@ -13611,7 +13617,7 @@
         <v>-25.3</v>
       </c>
       <c r="H251" t="n">
-        <v>43.15</v>
+        <v>40.03</v>
       </c>
       <c r="I251" t="n">
         <v>36.1</v>
@@ -13624,7 +13630,7 @@
         <v>-5.66</v>
       </c>
       <c r="M251" t="n">
-        <v>39.19</v>
+        <v>35.44</v>
       </c>
       <c r="N251" t="b">
         <v>1</v>
@@ -13662,7 +13668,7 @@
         <v>-7.7</v>
       </c>
       <c r="H252" t="n">
-        <v>0.9</v>
+        <v>-0.03</v>
       </c>
       <c r="I252" t="n">
         <v>-6.47</v>
@@ -13675,7 +13681,7 @@
         <v>-23.05</v>
       </c>
       <c r="M252" t="n">
-        <v>-3.06</v>
+        <v>-4.61</v>
       </c>
       <c r="N252" t="b">
         <v>1</v>
@@ -13713,7 +13719,7 @@
         <v>-2.9</v>
       </c>
       <c r="H253" t="n">
-        <v>-6.68</v>
+        <v>-6.86</v>
       </c>
       <c r="I253" t="n">
         <v>-1.47</v>
@@ -13726,7 +13732,7 @@
         <v>-7.7</v>
       </c>
       <c r="M253" t="n">
-        <v>-10.64</v>
+        <v>-11.45</v>
       </c>
       <c r="N253" t="b">
         <v>0</v>
@@ -13764,7 +13770,7 @@
         <v>13.7</v>
       </c>
       <c r="H254" t="n">
-        <v>15.27</v>
+        <v>17.83</v>
       </c>
       <c r="I254" t="n">
         <v>2.74</v>
@@ -13777,7 +13783,7 @@
         <v>-24.02</v>
       </c>
       <c r="M254" t="n">
-        <v>11.31</v>
+        <v>13.25</v>
       </c>
       <c r="N254" t="b">
         <v>1</v>
@@ -13815,7 +13821,7 @@
         <v>21.8</v>
       </c>
       <c r="H255" t="n">
-        <v>-6.5</v>
+        <v>-7.4</v>
       </c>
       <c r="I255" t="n">
         <v>18.32</v>
@@ -13828,7 +13834,7 @@
         <v>-23.27</v>
       </c>
       <c r="M255" t="n">
-        <v>-10.46</v>
+        <v>-11.99</v>
       </c>
       <c r="N255" t="b">
         <v>1</v>
@@ -13866,7 +13872,7 @@
         <v>29.4</v>
       </c>
       <c r="H256" t="n">
-        <v>-0.9</v>
+        <v>-0.27</v>
       </c>
       <c r="I256" t="n">
         <v>-2.62</v>
@@ -13917,7 +13923,7 @@
         <v>-3.7</v>
       </c>
       <c r="H257" t="n">
-        <v>-24.03</v>
+        <v>-23.51</v>
       </c>
       <c r="I257" t="n">
         <v>-8.07</v>
@@ -13930,7 +13936,7 @@
         <v>-22.12</v>
       </c>
       <c r="M257" t="n">
-        <v>-27.99</v>
+        <v>-28.1</v>
       </c>
       <c r="N257" t="b">
         <v>1</v>
@@ -13968,7 +13974,7 @@
         <v>21.3</v>
       </c>
       <c r="H258" t="n">
-        <v>1.77</v>
+        <v>1.9</v>
       </c>
       <c r="I258" t="n">
         <v>0.23</v>
@@ -13981,7 +13987,7 @@
         <v>-0.85</v>
       </c>
       <c r="M258" t="n">
-        <v>-2.19</v>
+        <v>-2.68</v>
       </c>
       <c r="N258" t="b">
         <v>1</v>
@@ -14019,7 +14025,7 @@
         <v>-21.4</v>
       </c>
       <c r="H259" t="n">
-        <v>13.68</v>
+        <v>15.99</v>
       </c>
       <c r="I259" t="n">
         <v>4.55</v>
@@ -14032,7 +14038,7 @@
         <v>-6.39</v>
       </c>
       <c r="M259" t="n">
-        <v>9.720000000000001</v>
+        <v>11.4</v>
       </c>
       <c r="N259" t="b">
         <v>1</v>
@@ -14070,7 +14076,7 @@
         <v>16.3</v>
       </c>
       <c r="H260" t="n">
-        <v>0.44</v>
+        <v>3.79</v>
       </c>
       <c r="I260" t="n">
         <v>-1</v>
@@ -14083,7 +14089,7 @@
         <v>-22.5</v>
       </c>
       <c r="M260" t="n">
-        <v>-3.52</v>
+        <v>-0.8</v>
       </c>
       <c r="N260" t="b">
         <v>1</v>
@@ -14121,7 +14127,7 @@
         <v>11.9</v>
       </c>
       <c r="H261" t="n">
-        <v>-5.18</v>
+        <v>-2.92</v>
       </c>
       <c r="I261" t="n">
         <v>7.74</v>
@@ -14134,7 +14140,7 @@
         <v>-9.43</v>
       </c>
       <c r="M261" t="n">
-        <v>-9.140000000000001</v>
+        <v>-7.5</v>
       </c>
       <c r="N261" t="b">
         <v>1</v>
@@ -14172,7 +14178,7 @@
         <v>19.4</v>
       </c>
       <c r="H262" t="n">
-        <v>-1.82</v>
+        <v>-0.05</v>
       </c>
       <c r="I262" t="n">
         <v>10.89</v>
@@ -14185,7 +14191,7 @@
         <v>-2.97</v>
       </c>
       <c r="M262" t="n">
-        <v>-5.78</v>
+        <v>-4.63</v>
       </c>
       <c r="N262" t="b">
         <v>0</v>
@@ -14223,7 +14229,7 @@
         <v>66.7</v>
       </c>
       <c r="H263" t="n">
-        <v>14.04</v>
+        <v>19.84</v>
       </c>
       <c r="I263" t="n">
         <v>4.84</v>
@@ -14236,7 +14242,7 @@
         <v>-11.7</v>
       </c>
       <c r="M263" t="n">
-        <v>10.08</v>
+        <v>15.26</v>
       </c>
       <c r="N263" t="b">
         <v>0</v>
@@ -14274,7 +14280,7 @@
         <v>3.7</v>
       </c>
       <c r="H264" t="n">
-        <v>16.43</v>
+        <v>16.7</v>
       </c>
       <c r="I264" t="n">
         <v>11.13</v>
@@ -14287,7 +14293,7 @@
         <v>-2.79</v>
       </c>
       <c r="M264" t="n">
-        <v>12.47</v>
+        <v>12.12</v>
       </c>
       <c r="N264" t="b">
         <v>0</v>
@@ -14325,7 +14331,7 @@
         <v>36.8</v>
       </c>
       <c r="H265" t="n">
-        <v>40.07</v>
+        <v>43.77</v>
       </c>
       <c r="I265" t="n">
         <v>15.47</v>
@@ -14338,7 +14344,7 @@
         <v>-0.96</v>
       </c>
       <c r="M265" t="n">
-        <v>36.11</v>
+        <v>39.19</v>
       </c>
       <c r="N265" t="b">
         <v>0</v>
@@ -14376,7 +14382,7 @@
         <v>0.2</v>
       </c>
       <c r="H266" t="n">
-        <v>12.13</v>
+        <v>11.71</v>
       </c>
       <c r="I266" t="n">
         <v>4.35</v>
@@ -14389,7 +14395,7 @@
         <v>-2.79</v>
       </c>
       <c r="M266" t="n">
-        <v>8.16</v>
+        <v>7.13</v>
       </c>
       <c r="N266" t="b">
         <v>1</v>
@@ -14427,7 +14433,7 @@
         <v>-31</v>
       </c>
       <c r="H267" t="n">
-        <v>-3.31</v>
+        <v>-13.44</v>
       </c>
       <c r="I267" t="n">
         <v>19.41</v>
@@ -14440,7 +14446,7 @@
         <v>-10.33</v>
       </c>
       <c r="M267" t="n">
-        <v>-7.27</v>
+        <v>-18.03</v>
       </c>
       <c r="N267" t="b">
         <v>0</v>
@@ -14482,7 +14488,7 @@
         <v>-2</v>
       </c>
       <c r="H268" t="n">
-        <v>-8.02</v>
+        <v>-4.12</v>
       </c>
       <c r="I268" t="n">
         <v>14.61</v>
@@ -14495,7 +14501,7 @@
         <v>-3.45</v>
       </c>
       <c r="M268" t="n">
-        <v>-11.98</v>
+        <v>-8.710000000000001</v>
       </c>
       <c r="N268" t="b">
         <v>0</v>
@@ -14533,7 +14539,7 @@
         <v>12.2</v>
       </c>
       <c r="H269" t="n">
-        <v>-35.31</v>
+        <v>-37.36</v>
       </c>
       <c r="I269" t="n">
         <v>3.47</v>
@@ -14546,7 +14552,7 @@
         <v>-27.15</v>
       </c>
       <c r="M269" t="n">
-        <v>-39.27</v>
+        <v>-41.95</v>
       </c>
       <c r="N269" t="b">
         <v>0</v>
@@ -14584,7 +14590,7 @@
         <v>8.4</v>
       </c>
       <c r="H270" t="n">
-        <v>-33.3</v>
+        <v>-35.22</v>
       </c>
       <c r="I270" t="n">
         <v>-0.13</v>
@@ -14597,7 +14603,7 @@
         <v>-10.87</v>
       </c>
       <c r="M270" t="n">
-        <v>-37.26</v>
+        <v>-39.8</v>
       </c>
       <c r="N270" t="b">
         <v>1</v>
@@ -14635,7 +14641,7 @@
         <v>-21.7</v>
       </c>
       <c r="H271" t="n">
-        <v>-3.33</v>
+        <v>-4.75</v>
       </c>
       <c r="I271" t="n">
         <v>5.5</v>
@@ -14648,7 +14654,7 @@
         <v>-4.3</v>
       </c>
       <c r="M271" t="n">
-        <v>-7.29</v>
+        <v>-9.33</v>
       </c>
       <c r="N271" t="b">
         <v>0</v>
@@ -14686,7 +14692,7 @@
         <v>-7.3</v>
       </c>
       <c r="H272" t="n">
-        <v>-16.96</v>
+        <v>-16.13</v>
       </c>
       <c r="I272" t="n">
         <v>-4.12</v>
@@ -14699,7 +14705,7 @@
         <v>-15.02</v>
       </c>
       <c r="M272" t="n">
-        <v>-20.92</v>
+        <v>-20.71</v>
       </c>
       <c r="N272" t="b">
         <v>1</v>
@@ -14737,7 +14743,7 @@
         <v>-26.1</v>
       </c>
       <c r="H273" t="n">
-        <v>-25</v>
+        <v>-26.34</v>
       </c>
       <c r="I273" t="n">
         <v>5.05</v>
@@ -14750,7 +14756,7 @@
         <v>-9.27</v>
       </c>
       <c r="M273" t="n">
-        <v>-28.96</v>
+        <v>-30.93</v>
       </c>
       <c r="N273" t="b">
         <v>1</v>
@@ -14788,7 +14794,7 @@
         <v>-18.5</v>
       </c>
       <c r="H274" t="n">
-        <v>37.48</v>
+        <v>38.57</v>
       </c>
       <c r="I274" t="n">
         <v>16.22</v>
@@ -14801,7 +14807,7 @@
         <v>-9.960000000000001</v>
       </c>
       <c r="M274" t="n">
-        <v>33.52</v>
+        <v>33.99</v>
       </c>
       <c r="N274" t="b">
         <v>0</v>
@@ -14839,7 +14845,7 @@
         <v>15.3</v>
       </c>
       <c r="H275" t="n">
-        <v>-37.33</v>
+        <v>-38.49</v>
       </c>
       <c r="I275" t="n">
         <v>-21.4</v>
@@ -14852,7 +14858,7 @@
         <v>-26.97</v>
       </c>
       <c r="M275" t="n">
-        <v>-41.29</v>
+        <v>-43.07</v>
       </c>
       <c r="N275" t="b">
         <v>0</v>
@@ -14890,7 +14896,7 @@
         <v>26.1</v>
       </c>
       <c r="H276" t="n">
-        <v>-4.35</v>
+        <v>-3.83</v>
       </c>
       <c r="I276" t="n">
         <v>-0.51</v>
@@ -14903,7 +14909,7 @@
         <v>-16.45</v>
       </c>
       <c r="M276" t="n">
-        <v>-8.31</v>
+        <v>-8.41</v>
       </c>
       <c r="N276" t="b">
         <v>1</v>
@@ -14945,7 +14951,7 @@
         <v>-8.199999999999999</v>
       </c>
       <c r="H277" t="n">
-        <v>-15.31</v>
+        <v>-13.61</v>
       </c>
       <c r="I277" t="n">
         <v>17.48</v>
@@ -14958,7 +14964,7 @@
         <v>-10.68</v>
       </c>
       <c r="M277" t="n">
-        <v>-19.27</v>
+        <v>-18.19</v>
       </c>
       <c r="N277" t="b">
         <v>0</v>
@@ -14996,7 +15002,7 @@
         <v>17.9</v>
       </c>
       <c r="H278" t="n">
-        <v>3.2</v>
+        <v>3.49</v>
       </c>
       <c r="I278" t="n">
         <v>12.97</v>
@@ -15009,7 +15015,7 @@
         <v>-8.130000000000001</v>
       </c>
       <c r="M278" t="n">
-        <v>-0.76</v>
+        <v>-1.1</v>
       </c>
       <c r="N278" t="b">
         <v>1</v>
@@ -15047,7 +15053,7 @@
         <v>0.7</v>
       </c>
       <c r="H279" t="n">
-        <v>-20.99</v>
+        <v>-19.94</v>
       </c>
       <c r="I279" t="n">
         <v>14.96</v>
@@ -15060,7 +15066,7 @@
         <v>-8.039999999999999</v>
       </c>
       <c r="M279" t="n">
-        <v>-24.96</v>
+        <v>-24.52</v>
       </c>
       <c r="N279" t="b">
         <v>1</v>
@@ -15098,7 +15104,7 @@
         <v>61.6</v>
       </c>
       <c r="H280" t="n">
-        <v>5.92</v>
+        <v>13.45</v>
       </c>
       <c r="I280" t="n">
         <v>11.47</v>
@@ -15111,7 +15117,7 @@
         <v>-12.86</v>
       </c>
       <c r="M280" t="n">
-        <v>1.96</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="N280" t="b">
         <v>0</v>
@@ -15149,7 +15155,7 @@
         <v>54.3</v>
       </c>
       <c r="H281" t="n">
-        <v>-24.58</v>
+        <v>-23.63</v>
       </c>
       <c r="I281" t="n">
         <v>-2.86</v>
@@ -15162,7 +15168,7 @@
         <v>-24.93</v>
       </c>
       <c r="M281" t="n">
-        <v>-28.54</v>
+        <v>-28.21</v>
       </c>
       <c r="N281" t="b">
         <v>0</v>
@@ -15200,7 +15206,7 @@
         <v>14.8</v>
       </c>
       <c r="H282" t="n">
-        <v>-1.49</v>
+        <v>-2.16</v>
       </c>
       <c r="I282" t="n">
         <v>0.35</v>
@@ -15213,7 +15219,7 @@
         <v>-3.68</v>
       </c>
       <c r="M282" t="n">
-        <v>-5.45</v>
+        <v>-6.74</v>
       </c>
       <c r="N282" t="b">
         <v>1</v>
@@ -15251,7 +15257,7 @@
         <v>-13.5</v>
       </c>
       <c r="H283" t="n">
-        <v>-17.42</v>
+        <v>-18.63</v>
       </c>
       <c r="I283" t="n">
         <v>-1.88</v>
@@ -15264,7 +15270,7 @@
         <v>-11.4</v>
       </c>
       <c r="M283" t="n">
-        <v>-21.38</v>
+        <v>-23.21</v>
       </c>
       <c r="N283" t="b">
         <v>0</v>
@@ -15302,7 +15308,7 @@
         <v>25.5</v>
       </c>
       <c r="H284" t="n">
-        <v>3.59</v>
+        <v>7.88</v>
       </c>
       <c r="I284" t="n">
         <v>-9.369999999999999</v>
@@ -15315,7 +15321,7 @@
         <v>-22.11</v>
       </c>
       <c r="M284" t="n">
-        <v>-0.37</v>
+        <v>3.3</v>
       </c>
       <c r="N284" t="b">
         <v>1</v>
@@ -15357,7 +15363,7 @@
         <v>-7.5</v>
       </c>
       <c r="H285" t="n">
-        <v>-12.93</v>
+        <v>-10.71</v>
       </c>
       <c r="I285" t="n">
         <v>4.46</v>
@@ -15370,7 +15376,7 @@
         <v>-8.52</v>
       </c>
       <c r="M285" t="n">
-        <v>-16.89</v>
+        <v>-15.3</v>
       </c>
       <c r="N285" t="b">
         <v>1</v>
@@ -15408,7 +15414,7 @@
         <v>1.5</v>
       </c>
       <c r="H286" t="n">
-        <v>0.84</v>
+        <v>0.55</v>
       </c>
       <c r="I286" t="n">
         <v>-7.31</v>
@@ -15421,7 +15427,7 @@
         <v>-18.58</v>
       </c>
       <c r="M286" t="n">
-        <v>-3.12</v>
+        <v>-4.03</v>
       </c>
       <c r="N286" t="b">
         <v>0</v>
@@ -15459,7 +15465,7 @@
         <v>-11</v>
       </c>
       <c r="H287" t="n">
-        <v>13.79</v>
+        <v>15.54</v>
       </c>
       <c r="I287" t="n">
         <v>10.7</v>
@@ -15472,7 +15478,7 @@
         <v>-9.43</v>
       </c>
       <c r="M287" t="n">
-        <v>9.83</v>
+        <v>10.96</v>
       </c>
       <c r="N287" t="b">
         <v>1</v>
@@ -15510,7 +15516,7 @@
         <v>-11.4</v>
       </c>
       <c r="H288" t="n">
-        <v>-18.78</v>
+        <v>-18.81</v>
       </c>
       <c r="I288" t="n">
         <v>4.36</v>
@@ -15523,7 +15529,7 @@
         <v>-11.36</v>
       </c>
       <c r="M288" t="n">
-        <v>-22.75</v>
+        <v>-23.39</v>
       </c>
       <c r="N288" t="b">
         <v>1</v>
@@ -15561,7 +15567,7 @@
         <v>2.1</v>
       </c>
       <c r="H289" t="n">
-        <v>58.58</v>
+        <v>60.18</v>
       </c>
       <c r="I289" t="n">
         <v>20.72</v>
@@ -15574,7 +15580,7 @@
         <v>-5.79</v>
       </c>
       <c r="M289" t="n">
-        <v>54.62</v>
+        <v>55.6</v>
       </c>
       <c r="N289" t="b">
         <v>0</v>
@@ -15612,7 +15618,7 @@
         <v>27.1</v>
       </c>
       <c r="H290" t="n">
-        <v>-4.89</v>
+        <v>-4.07</v>
       </c>
       <c r="I290" t="n">
         <v>5.02</v>
@@ -15625,7 +15631,7 @@
         <v>-14.35</v>
       </c>
       <c r="M290" t="n">
-        <v>-8.85</v>
+        <v>-8.66</v>
       </c>
       <c r="N290" t="b">
         <v>1</v>
@@ -15663,7 +15669,7 @@
         <v>-21.6</v>
       </c>
       <c r="H291" t="n">
-        <v>-14.17</v>
+        <v>-14.87</v>
       </c>
       <c r="I291" t="n">
         <v>1.22</v>
@@ -15676,7 +15682,7 @@
         <v>-6.54</v>
       </c>
       <c r="M291" t="n">
-        <v>-18.13</v>
+        <v>-19.45</v>
       </c>
       <c r="N291" t="b">
         <v>0</v>
@@ -15718,7 +15724,7 @@
         <v>-2.2</v>
       </c>
       <c r="H292" t="n">
-        <v>4.08</v>
+        <v>6.04</v>
       </c>
       <c r="I292" t="n">
         <v>-9.050000000000001</v>
@@ -15731,7 +15737,7 @@
         <v>-18.61</v>
       </c>
       <c r="M292" t="n">
-        <v>0.12</v>
+        <v>1.45</v>
       </c>
       <c r="N292" t="b">
         <v>0</v>
@@ -15769,7 +15775,7 @@
         <v>0.7</v>
       </c>
       <c r="H293" t="n">
-        <v>0.59</v>
+        <v>3.16</v>
       </c>
       <c r="I293" t="n">
         <v>11.4</v>
@@ -15782,7 +15788,7 @@
         <v>-7.28</v>
       </c>
       <c r="M293" t="n">
-        <v>-3.37</v>
+        <v>-1.42</v>
       </c>
       <c r="N293" t="b">
         <v>0</v>
@@ -15820,7 +15826,7 @@
         <v>-31.7</v>
       </c>
       <c r="H294" t="n">
-        <v>18.96</v>
+        <v>18.24</v>
       </c>
       <c r="I294" t="n">
         <v>17.04</v>
@@ -15833,7 +15839,7 @@
         <v>-4.05</v>
       </c>
       <c r="M294" t="n">
-        <v>15</v>
+        <v>13.66</v>
       </c>
       <c r="N294" t="b">
         <v>0</v>
@@ -15871,7 +15877,7 @@
         <v>32.2</v>
       </c>
       <c r="H295" t="n">
-        <v>15.04</v>
+        <v>14.81</v>
       </c>
       <c r="I295" t="n">
         <v>6.49</v>
@@ -15884,7 +15890,7 @@
         <v>-3.92</v>
       </c>
       <c r="M295" t="n">
-        <v>11.08</v>
+        <v>10.23</v>
       </c>
       <c r="N295" t="b">
         <v>1</v>
@@ -15922,7 +15928,7 @@
         <v>3.2</v>
       </c>
       <c r="H296" t="n">
-        <v>-19.31</v>
+        <v>-19.11</v>
       </c>
       <c r="I296" t="n">
         <v>-10.41</v>
@@ -15935,7 +15941,7 @@
         <v>-23.7</v>
       </c>
       <c r="M296" t="n">
-        <v>-23.27</v>
+        <v>-23.69</v>
       </c>
       <c r="N296" t="b">
         <v>1</v>
@@ -15973,7 +15979,7 @@
         <v>7.3</v>
       </c>
       <c r="H297" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-1.32</v>
       </c>
       <c r="I297" t="n">
         <v>-0.57</v>
@@ -15986,7 +15992,7 @@
         <v>-5.89</v>
       </c>
       <c r="M297" t="n">
-        <v>-4.77</v>
+        <v>-5.9</v>
       </c>
       <c r="N297" t="b">
         <v>1</v>
@@ -16024,7 +16030,7 @@
         <v>24.5</v>
       </c>
       <c r="H298" t="n">
-        <v>5.55</v>
+        <v>7.35</v>
       </c>
       <c r="I298" t="n">
         <v>17.24</v>
@@ -16037,7 +16043,7 @@
         <v>-0.47</v>
       </c>
       <c r="M298" t="n">
-        <v>1.59</v>
+        <v>2.76</v>
       </c>
       <c r="N298" t="b">
         <v>0</v>
@@ -16075,7 +16081,7 @@
         <v>-0.3</v>
       </c>
       <c r="H299" t="n">
-        <v>-1.92</v>
+        <v>-0.39</v>
       </c>
       <c r="I299" t="n">
         <v>17.76</v>
@@ -16088,7 +16094,7 @@
         <v>-14.18</v>
       </c>
       <c r="M299" t="n">
-        <v>-5.88</v>
+        <v>-4.98</v>
       </c>
       <c r="N299" t="b">
         <v>1</v>
@@ -16126,7 +16132,7 @@
         <v>4</v>
       </c>
       <c r="H300" t="n">
-        <v>59.67</v>
+        <v>64.23</v>
       </c>
       <c r="I300" t="n">
         <v>8.75</v>
@@ -16139,7 +16145,7 @@
         <v>-11.02</v>
       </c>
       <c r="M300" t="n">
-        <v>55.7</v>
+        <v>59.64</v>
       </c>
       <c r="N300" t="b">
         <v>0</v>
@@ -16177,7 +16183,7 @@
         <v>-6.8</v>
       </c>
       <c r="H301" t="n">
-        <v>30.92</v>
+        <v>23.78</v>
       </c>
       <c r="I301" t="n">
         <v>8.279999999999999</v>
@@ -16190,7 +16196,7 @@
         <v>-6.78</v>
       </c>
       <c r="M301" t="n">
-        <v>26.96</v>
+        <v>19.2</v>
       </c>
       <c r="N301" t="b">
         <v>1</v>
@@ -16228,7 +16234,7 @@
         <v>-42</v>
       </c>
       <c r="H302" t="n">
-        <v>49.51</v>
+        <v>52.34</v>
       </c>
       <c r="I302" t="n">
         <v>-3.61</v>
@@ -16241,7 +16247,7 @@
         <v>-11.94</v>
       </c>
       <c r="M302" t="n">
-        <v>45.55</v>
+        <v>47.76</v>
       </c>
       <c r="N302" t="b">
         <v>0</v>
@@ -16279,7 +16285,7 @@
         <v>14.6</v>
       </c>
       <c r="H303" t="n">
-        <v>7.36</v>
+        <v>10.58</v>
       </c>
       <c r="I303" t="n">
         <v>8.539999999999999</v>
@@ -16292,7 +16298,7 @@
         <v>-13.21</v>
       </c>
       <c r="M303" t="n">
-        <v>3.39</v>
+        <v>6</v>
       </c>
       <c r="N303" t="b">
         <v>0</v>
@@ -16330,7 +16336,7 @@
         <v>34.6</v>
       </c>
       <c r="H304" t="n">
-        <v>-0.64</v>
+        <v>1.32</v>
       </c>
       <c r="I304" t="n">
         <v>5.7</v>
@@ -16343,7 +16349,7 @@
         <v>-7.7</v>
       </c>
       <c r="M304" t="n">
-        <v>-4.61</v>
+        <v>-3.27</v>
       </c>
       <c r="N304" t="b">
         <v>1</v>
@@ -16381,7 +16387,7 @@
         <v>-37.2</v>
       </c>
       <c r="H305" t="n">
-        <v>18.22</v>
+        <v>15.89</v>
       </c>
       <c r="I305" t="n">
         <v>21.67</v>
@@ -16394,7 +16400,7 @@
         <v>-6.64</v>
       </c>
       <c r="M305" t="n">
-        <v>14.26</v>
+        <v>11.31</v>
       </c>
       <c r="N305" t="b">
         <v>0</v>
@@ -16432,7 +16438,7 @@
         <v>-31.2</v>
       </c>
       <c r="H306" t="n">
-        <v>-21.47</v>
+        <v>-23.21</v>
       </c>
       <c r="I306" t="n">
         <v>1.03</v>
@@ -16445,7 +16451,7 @@
         <v>-13.65</v>
       </c>
       <c r="M306" t="n">
-        <v>-25.44</v>
+        <v>-27.79</v>
       </c>
       <c r="N306" t="b">
         <v>0</v>
@@ -16483,7 +16489,7 @@
         <v>10.4</v>
       </c>
       <c r="H307" t="n">
-        <v>32.02</v>
+        <v>34.76</v>
       </c>
       <c r="I307" t="n">
         <v>11.05</v>
@@ -16496,7 +16502,7 @@
         <v>-5.54</v>
       </c>
       <c r="M307" t="n">
-        <v>28.05</v>
+        <v>30.18</v>
       </c>
       <c r="N307" t="b">
         <v>1</v>
@@ -16534,7 +16540,7 @@
         <v>-14.7</v>
       </c>
       <c r="H308" t="n">
-        <v>7.34</v>
+        <v>13.62</v>
       </c>
       <c r="I308" t="n">
         <v>12.94</v>
@@ -16547,7 +16553,7 @@
         <v>-2.34</v>
       </c>
       <c r="M308" t="n">
-        <v>3.38</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="N308" t="b">
         <v>0</v>
@@ -16585,7 +16591,7 @@
         <v>-21.5</v>
       </c>
       <c r="H309" t="n">
-        <v>-13.18</v>
+        <v>-12.99</v>
       </c>
       <c r="I309" t="n">
         <v>10.65</v>
@@ -16598,7 +16604,7 @@
         <v>-6.89</v>
       </c>
       <c r="M309" t="n">
-        <v>-17.14</v>
+        <v>-17.58</v>
       </c>
       <c r="N309" t="b">
         <v>1</v>
@@ -16636,7 +16642,7 @@
         <v>20.2</v>
       </c>
       <c r="H310" t="n">
-        <v>-10.29</v>
+        <v>-9.81</v>
       </c>
       <c r="I310" t="n">
         <v>-1.23</v>
@@ -16649,7 +16655,7 @@
         <v>-12.56</v>
       </c>
       <c r="M310" t="n">
-        <v>-14.25</v>
+        <v>-14.39</v>
       </c>
       <c r="N310" t="b">
         <v>0</v>
@@ -16687,7 +16693,7 @@
         <v>3.5</v>
       </c>
       <c r="H311" t="n">
-        <v>49.64</v>
+        <v>52.36</v>
       </c>
       <c r="I311" t="n">
         <v>33.01</v>
@@ -16700,7 +16706,7 @@
         <v>-0.92</v>
       </c>
       <c r="M311" t="n">
-        <v>45.67</v>
+        <v>47.77</v>
       </c>
       <c r="N311" t="b">
         <v>1</v>
@@ -16738,7 +16744,7 @@
         <v>14</v>
       </c>
       <c r="H312" t="n">
-        <v>30.68</v>
+        <v>31.86</v>
       </c>
       <c r="I312" t="n">
         <v>2.89</v>
@@ -16751,7 +16757,7 @@
         <v>-1.94</v>
       </c>
       <c r="M312" t="n">
-        <v>26.72</v>
+        <v>27.27</v>
       </c>
       <c r="N312" t="b">
         <v>0</v>
@@ -16789,7 +16795,7 @@
         <v>19.8</v>
       </c>
       <c r="H313" t="n">
-        <v>15</v>
+        <v>17.48</v>
       </c>
       <c r="I313" t="n">
         <v>4.74</v>
@@ -16802,7 +16808,7 @@
         <v>-9.9</v>
       </c>
       <c r="M313" t="n">
-        <v>11.04</v>
+        <v>12.9</v>
       </c>
       <c r="N313" t="b">
         <v>1</v>
@@ -16844,7 +16850,7 @@
         <v>-7.4</v>
       </c>
       <c r="H314" t="n">
-        <v>11.36</v>
+        <v>12.62</v>
       </c>
       <c r="I314" t="n">
         <v>-3.85</v>
@@ -16857,7 +16863,7 @@
         <v>-21.11</v>
       </c>
       <c r="M314" t="n">
-        <v>7.4</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="N314" t="b">
         <v>0</v>
@@ -16895,7 +16901,7 @@
         <v>-10.8</v>
       </c>
       <c r="H315" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.28</v>
       </c>
       <c r="I315" t="n">
         <v>1.78</v>
@@ -16908,7 +16914,7 @@
         <v>-7.51</v>
       </c>
       <c r="M315" t="n">
-        <v>-3.15</v>
+        <v>-3.3</v>
       </c>
       <c r="N315" t="b">
         <v>0</v>
@@ -16946,7 +16952,7 @@
         <v>-24</v>
       </c>
       <c r="H316" t="n">
-        <v>47.25</v>
+        <v>58.74</v>
       </c>
       <c r="I316" t="n">
         <v>10.85</v>
@@ -16959,7 +16965,7 @@
         <v>-5.43</v>
       </c>
       <c r="M316" t="n">
-        <v>43.29</v>
+        <v>54.16</v>
       </c>
       <c r="N316" t="b">
         <v>0</v>
@@ -16997,7 +17003,7 @@
         <v>-28.3</v>
       </c>
       <c r="H317" t="n">
-        <v>-27.84</v>
+        <v>-25.2</v>
       </c>
       <c r="I317" t="n">
         <v>-8.949999999999999</v>
@@ -17010,7 +17016,7 @@
         <v>-13.18</v>
       </c>
       <c r="M317" t="n">
-        <v>-31.8</v>
+        <v>-29.78</v>
       </c>
       <c r="N317" t="b">
         <v>0</v>
@@ -17048,7 +17054,7 @@
         <v>-30.5</v>
       </c>
       <c r="H318" t="n">
-        <v>-4.5</v>
+        <v>-0.38</v>
       </c>
       <c r="I318" t="n">
         <v>2.96</v>
@@ -17061,7 +17067,7 @@
         <v>-17.88</v>
       </c>
       <c r="M318" t="n">
-        <v>-8.460000000000001</v>
+        <v>-4.97</v>
       </c>
       <c r="N318" t="b">
         <v>1</v>
@@ -17099,7 +17105,7 @@
         <v>-6</v>
       </c>
       <c r="H319" t="n">
-        <v>-5.19</v>
+        <v>-5.4</v>
       </c>
       <c r="I319" t="n">
         <v>3.31</v>
@@ -17112,7 +17118,7 @@
         <v>-21.48</v>
       </c>
       <c r="M319" t="n">
-        <v>-9.15</v>
+        <v>-9.98</v>
       </c>
       <c r="N319" t="b">
         <v>1</v>
@@ -17150,7 +17156,7 @@
         <v>-42.2</v>
       </c>
       <c r="H320" t="n">
-        <v>-2.93</v>
+        <v>-3.27</v>
       </c>
       <c r="I320" t="n">
         <v>19.24</v>
@@ -17163,7 +17169,7 @@
         <v>-0.93</v>
       </c>
       <c r="M320" t="n">
-        <v>-6.89</v>
+        <v>-7.86</v>
       </c>
       <c r="N320" t="b">
         <v>0</v>
@@ -17201,7 +17207,7 @@
         <v>-34.6</v>
       </c>
       <c r="H321" t="n">
-        <v>0</v>
+        <v>-1.09</v>
       </c>
       <c r="I321" t="n">
         <v>23.65</v>
@@ -17214,7 +17220,7 @@
         <v>-3.83</v>
       </c>
       <c r="M321" t="n">
-        <v>-3.96</v>
+        <v>-5.68</v>
       </c>
       <c r="N321" t="b">
         <v>1</v>
@@ -17252,7 +17258,7 @@
         <v>-48.1</v>
       </c>
       <c r="H322" t="n">
-        <v>-18.47</v>
+        <v>-18.16</v>
       </c>
       <c r="I322" t="n">
         <v>2.19</v>
@@ -17265,7 +17271,7 @@
         <v>-13.66</v>
       </c>
       <c r="M322" t="n">
-        <v>-22.43</v>
+        <v>-22.74</v>
       </c>
       <c r="N322" t="b">
         <v>0</v>
@@ -17303,7 +17309,7 @@
         <v>-16.2</v>
       </c>
       <c r="H323" t="n">
-        <v>6.58</v>
+        <v>7.78</v>
       </c>
       <c r="I323" t="n">
         <v>25.77</v>
@@ -17316,7 +17322,7 @@
         <v>-1.7</v>
       </c>
       <c r="M323" t="n">
-        <v>2.62</v>
+        <v>3.19</v>
       </c>
       <c r="N323" t="b">
         <v>1</v>
@@ -17354,7 +17360,7 @@
         <v>-24.9</v>
       </c>
       <c r="H324" t="n">
-        <v>15.39</v>
+        <v>17.17</v>
       </c>
       <c r="I324" t="n">
         <v>10.88</v>
@@ -17367,7 +17373,7 @@
         <v>-4.1</v>
       </c>
       <c r="M324" t="n">
-        <v>11.43</v>
+        <v>12.58</v>
       </c>
       <c r="N324" t="b">
         <v>1</v>
@@ -17409,7 +17415,7 @@
         <v>-8.1</v>
       </c>
       <c r="H325" t="n">
-        <v>13.07</v>
+        <v>15.79</v>
       </c>
       <c r="I325" t="n">
         <v>14.27</v>
@@ -17422,7 +17428,7 @@
         <v>-10.92</v>
       </c>
       <c r="M325" t="n">
-        <v>9.109999999999999</v>
+        <v>11.21</v>
       </c>
       <c r="N325" t="b">
         <v>1</v>
@@ -17460,7 +17466,7 @@
         <v>-10.2</v>
       </c>
       <c r="H326" t="n">
-        <v>-11.88</v>
+        <v>-13.78</v>
       </c>
       <c r="I326" t="n">
         <v>15.03</v>
@@ -17473,7 +17479,7 @@
         <v>-1.61</v>
       </c>
       <c r="M326" t="n">
-        <v>-15.84</v>
+        <v>-18.36</v>
       </c>
       <c r="N326" t="b">
         <v>1</v>
@@ -17511,7 +17517,7 @@
         <v>68.90000000000001</v>
       </c>
       <c r="H327" t="n">
-        <v>38.6</v>
+        <v>30.73</v>
       </c>
       <c r="I327" t="n">
         <v>1.84</v>
@@ -17524,7 +17530,7 @@
         <v>-10.43</v>
       </c>
       <c r="M327" t="n">
-        <v>34.63</v>
+        <v>26.15</v>
       </c>
       <c r="N327" t="b">
         <v>1</v>
@@ -17562,7 +17568,7 @@
         <v>-40.8</v>
       </c>
       <c r="H328" t="n">
-        <v>-20.46</v>
+        <v>-21.36</v>
       </c>
       <c r="I328" t="n">
         <v>21.71</v>
@@ -17575,7 +17581,7 @@
         <v>-3.3</v>
       </c>
       <c r="M328" t="n">
-        <v>-24.42</v>
+        <v>-25.94</v>
       </c>
       <c r="N328" t="b">
         <v>1</v>
@@ -17613,7 +17619,7 @@
         <v>-10.1</v>
       </c>
       <c r="H329" t="n">
-        <v>-12.83</v>
+        <v>-13.9</v>
       </c>
       <c r="I329" t="n">
         <v>1.83</v>
@@ -17626,7 +17632,7 @@
         <v>-3.45</v>
       </c>
       <c r="M329" t="n">
-        <v>-16.79</v>
+        <v>-18.48</v>
       </c>
       <c r="N329" t="b">
         <v>0</v>
@@ -17664,7 +17670,7 @@
         <v>40.7</v>
       </c>
       <c r="H330" t="n">
-        <v>36.32</v>
+        <v>43.09</v>
       </c>
       <c r="I330" t="n">
         <v>-4.08</v>
@@ -17677,7 +17683,7 @@
         <v>-11.2</v>
       </c>
       <c r="M330" t="n">
-        <v>32.36</v>
+        <v>38.51</v>
       </c>
       <c r="N330" t="b">
         <v>1</v>
@@ -17715,7 +17721,7 @@
         <v>25.7</v>
       </c>
       <c r="H331" t="n">
-        <v>-5.08</v>
+        <v>-1.95</v>
       </c>
       <c r="I331" t="n">
         <v>11.3</v>
@@ -17728,7 +17734,7 @@
         <v>-11.03</v>
       </c>
       <c r="M331" t="n">
-        <v>-9.039999999999999</v>
+        <v>-6.53</v>
       </c>
       <c r="N331" t="b">
         <v>1</v>
@@ -17766,7 +17772,7 @@
         <v>2.3</v>
       </c>
       <c r="H332" t="n">
-        <v>-5.55</v>
+        <v>-6.11</v>
       </c>
       <c r="I332" t="n">
         <v>-0.95</v>
@@ -17779,7 +17785,7 @@
         <v>-7.81</v>
       </c>
       <c r="M332" t="n">
-        <v>-9.51</v>
+        <v>-10.69</v>
       </c>
       <c r="N332" t="b">
         <v>0</v>
@@ -17911,7 +17917,7 @@
         <v>-16.6</v>
       </c>
       <c r="H2" t="n">
-        <v>1.93</v>
+        <v>2.47</v>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
@@ -17920,7 +17926,7 @@
         <v>-1.04</v>
       </c>
       <c r="M2" t="n">
-        <v>2.17</v>
+        <v>2.11</v>
       </c>
       <c r="N2" t="b">
         <v>1</v>
@@ -17958,7 +17964,7 @@
         <v>-5</v>
       </c>
       <c r="H3" t="n">
-        <v>1.22</v>
+        <v>0.43</v>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
@@ -17967,7 +17973,7 @@
         <v>-1.75</v>
       </c>
       <c r="M3" t="n">
-        <v>1.46</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="N3" t="b">
         <v>1</v>
@@ -18005,7 +18011,7 @@
         <v>12.5</v>
       </c>
       <c r="H4" t="n">
-        <v>0.35</v>
+        <v>-0.61</v>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
@@ -18014,7 +18020,7 @@
         <v>-2.56</v>
       </c>
       <c r="M4" t="n">
-        <v>0.59</v>
+        <v>-0.97</v>
       </c>
       <c r="N4" t="b">
         <v>1</v>
@@ -18052,7 +18058,7 @@
         <v>-17.3</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.11</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
@@ -18061,7 +18067,7 @@
         <v>-4.07</v>
       </c>
       <c r="M5" t="n">
-        <v>0.43</v>
+        <v>-0.74</v>
       </c>
       <c r="N5" t="b">
         <v>1</v>
@@ -18099,7 +18105,7 @@
         <v>-21.8</v>
       </c>
       <c r="H6" t="n">
-        <v>-3.73</v>
+        <v>-3.82</v>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
@@ -18108,7 +18114,7 @@
         <v>-5.33</v>
       </c>
       <c r="M6" t="n">
-        <v>-4.71</v>
+        <v>-5.4</v>
       </c>
       <c r="N6" t="b">
         <v>1</v>
@@ -18146,7 +18152,7 @@
         <v>-16.7</v>
       </c>
       <c r="H7" t="n">
-        <v>24.38</v>
+        <v>25.21</v>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
@@ -18155,7 +18161,7 @@
         <v>-6.98</v>
       </c>
       <c r="M7" t="n">
-        <v>23.46</v>
+        <v>23.68</v>
       </c>
       <c r="N7" t="b">
         <v>1</v>
@@ -18193,7 +18199,7 @@
         <v>-11.5</v>
       </c>
       <c r="H8" t="n">
-        <v>6.96</v>
+        <v>5.5</v>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
@@ -18202,7 +18208,7 @@
         <v>-0.99</v>
       </c>
       <c r="M8" t="n">
-        <v>6.04</v>
+        <v>3.97</v>
       </c>
       <c r="N8" t="b">
         <v>1</v>
@@ -18229,7 +18235,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Extended</t>
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
@@ -18240,16 +18246,18 @@
         <v>0.1</v>
       </c>
       <c r="H9" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="I9" t="inlineStr"/>
+        <v>6.41</v>
+      </c>
+      <c r="I9" t="n">
+        <v>6.41</v>
+      </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="n">
         <v>-2.51</v>
       </c>
       <c r="M9" t="n">
-        <v>0.95</v>
+        <v>5.14</v>
       </c>
       <c r="N9" t="b">
         <v>1</v>
@@ -18287,16 +18295,18 @@
         <v>-31.6</v>
       </c>
       <c r="H10" t="n">
-        <v>-5</v>
-      </c>
-      <c r="I10" t="inlineStr"/>
+        <v>-2.12</v>
+      </c>
+      <c r="I10" t="n">
+        <v>-2.12</v>
+      </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="n">
         <v>-8.140000000000001</v>
       </c>
       <c r="M10" t="n">
-        <v>-5.67</v>
+        <v>-3.39</v>
       </c>
       <c r="N10" t="b">
         <v>1</v>
@@ -18334,7 +18344,7 @@
         <v>-2.7</v>
       </c>
       <c r="H11" t="n">
-        <v>-5.84</v>
+        <v>-8.279999999999999</v>
       </c>
       <c r="I11" t="n">
         <v>-3.77</v>
@@ -18342,10 +18352,10 @@
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="n">
-        <v>-9.24</v>
+        <v>-9.34</v>
       </c>
       <c r="M11" t="n">
-        <v>-5.83</v>
+        <v>-8.869999999999999</v>
       </c>
       <c r="N11" t="b">
         <v>1</v>
@@ -18383,7 +18393,7 @@
         <v>26.9</v>
       </c>
       <c r="H12" t="n">
-        <v>-9.34</v>
+        <v>-3.78</v>
       </c>
       <c r="I12" t="n">
         <v>-3.24</v>
@@ -18394,7 +18404,7 @@
         <v>-12.88</v>
       </c>
       <c r="M12" t="n">
-        <v>-9.33</v>
+        <v>-4.37</v>
       </c>
       <c r="N12" t="b">
         <v>1</v>
@@ -18432,7 +18442,7 @@
         <v>-18.1</v>
       </c>
       <c r="H13" t="n">
-        <v>8.68</v>
+        <v>9.35</v>
       </c>
       <c r="I13" t="n">
         <v>4.46</v>
@@ -18443,7 +18453,7 @@
         <v>-2.69</v>
       </c>
       <c r="M13" t="n">
-        <v>7.67</v>
+        <v>7.74</v>
       </c>
       <c r="N13" t="b">
         <v>1</v>
@@ -18481,7 +18491,7 @@
         <v>-21.5</v>
       </c>
       <c r="H14" t="n">
-        <v>-3.33</v>
+        <v>-6.61</v>
       </c>
       <c r="I14" t="n">
         <v>-1.68</v>
@@ -18489,10 +18499,10 @@
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="n">
-        <v>-5.21</v>
+        <v>-6.82</v>
       </c>
       <c r="M14" t="n">
-        <v>-4.34</v>
+        <v>-8.220000000000001</v>
       </c>
       <c r="N14" t="b">
         <v>1</v>
@@ -18519,7 +18529,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Extended</t>
         </is>
       </c>
       <c r="E15" t="inlineStr"/>
@@ -18530,7 +18540,7 @@
         <v>41.6</v>
       </c>
       <c r="H15" t="n">
-        <v>3.86</v>
+        <v>5.24</v>
       </c>
       <c r="I15" t="n">
         <v>3.43</v>
@@ -18541,7 +18551,7 @@
         <v>-4.38</v>
       </c>
       <c r="M15" t="n">
-        <v>2.21</v>
+        <v>2.98</v>
       </c>
       <c r="N15" t="b">
         <v>1</v>
@@ -18579,7 +18589,7 @@
         <v>32.1</v>
       </c>
       <c r="H16" t="n">
-        <v>-2.22</v>
+        <v>-3.12</v>
       </c>
       <c r="I16" t="n">
         <v>-3.47</v>
@@ -18590,7 +18600,7 @@
         <v>-6.94</v>
       </c>
       <c r="M16" t="n">
-        <v>-3.88</v>
+        <v>-5.38</v>
       </c>
       <c r="N16" t="b">
         <v>1</v>
@@ -18628,7 +18638,7 @@
         <v>-14.4</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.48</v>
+        <v>-1.24</v>
       </c>
       <c r="I17" t="n">
         <v>-2.38</v>
@@ -18639,7 +18649,7 @@
         <v>-6.46</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.14</v>
+        <v>-3.51</v>
       </c>
       <c r="N17" t="b">
         <v>1</v>
@@ -18677,7 +18687,7 @@
         <v>-10</v>
       </c>
       <c r="H18" t="n">
-        <v>-4.16</v>
+        <v>-3.35</v>
       </c>
       <c r="I18" t="n">
         <v>-3.29</v>
@@ -18688,7 +18698,7 @@
         <v>-10.65</v>
       </c>
       <c r="M18" t="n">
-        <v>-5.81</v>
+        <v>-5.62</v>
       </c>
       <c r="N18" t="b">
         <v>1</v>
@@ -18726,7 +18736,7 @@
         <v>6.4</v>
       </c>
       <c r="H19" t="n">
-        <v>4.66</v>
+        <v>4.43</v>
       </c>
       <c r="I19" t="n">
         <v>1.48</v>
@@ -18737,7 +18747,7 @@
         <v>-3.35</v>
       </c>
       <c r="M19" t="n">
-        <v>3</v>
+        <v>2.16</v>
       </c>
       <c r="N19" t="b">
         <v>1</v>
@@ -18775,7 +18785,7 @@
         <v>20.2</v>
       </c>
       <c r="H20" t="n">
-        <v>3.33</v>
+        <v>2.16</v>
       </c>
       <c r="I20" t="n">
         <v>3.45</v>
@@ -18786,7 +18796,7 @@
         <v>-1.07</v>
       </c>
       <c r="M20" t="n">
-        <v>1.26</v>
+        <v>-0.52</v>
       </c>
       <c r="N20" t="b">
         <v>1</v>
@@ -18824,7 +18834,7 @@
         <v>43.7</v>
       </c>
       <c r="H21" t="n">
-        <v>1.57</v>
+        <v>2.11</v>
       </c>
       <c r="I21" t="n">
         <v>3.16</v>
@@ -18835,7 +18845,7 @@
         <v>-2.44</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.5</v>
+        <v>-0.57</v>
       </c>
       <c r="N21" t="b">
         <v>1</v>
@@ -18873,7 +18883,7 @@
         <v>1.9</v>
       </c>
       <c r="H22" t="n">
-        <v>-6.59</v>
+        <v>-5.22</v>
       </c>
       <c r="I22" t="n">
         <v>-10.64</v>
@@ -18884,7 +18894,7 @@
         <v>-14.75</v>
       </c>
       <c r="M22" t="n">
-        <v>-8.66</v>
+        <v>-7.9</v>
       </c>
       <c r="N22" t="b">
         <v>1</v>
@@ -18911,7 +18921,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Extended</t>
+          <t>Retired</t>
         </is>
       </c>
       <c r="E23" t="inlineStr"/>
@@ -18922,7 +18932,7 @@
         <v>37.5</v>
       </c>
       <c r="H23" t="n">
-        <v>7.09</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="I23" t="n">
         <v>5.86</v>
@@ -18933,7 +18943,7 @@
         <v>-3.95</v>
       </c>
       <c r="M23" t="n">
-        <v>4.87</v>
+        <v>5.62</v>
       </c>
       <c r="N23" t="b">
         <v>1</v>
@@ -18960,7 +18970,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Extended</t>
+          <t>Retired</t>
         </is>
       </c>
       <c r="E24" t="inlineStr"/>
@@ -18971,7 +18981,7 @@
         <v>40.2</v>
       </c>
       <c r="H24" t="n">
-        <v>11.68</v>
+        <v>10.95</v>
       </c>
       <c r="I24" t="n">
         <v>-1.11</v>
@@ -18982,7 +18992,7 @@
         <v>-5.29</v>
       </c>
       <c r="M24" t="n">
-        <v>9.449999999999999</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="N24" t="b">
         <v>1</v>
@@ -19009,7 +19019,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Retired</t>
         </is>
       </c>
       <c r="E25" t="inlineStr"/>
@@ -19020,7 +19030,7 @@
         <v>10.7</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.14</v>
+        <v>-0.09</v>
       </c>
       <c r="I25" t="n">
         <v>7.3</v>
@@ -19031,7 +19041,7 @@
         <v>-3.78</v>
       </c>
       <c r="M25" t="n">
-        <v>-2.36</v>
+        <v>-2.93</v>
       </c>
       <c r="N25" t="b">
         <v>1</v>
@@ -19069,18 +19079,20 @@
         <v>25.6</v>
       </c>
       <c r="H26" t="n">
-        <v>12.04</v>
+        <v>12.1</v>
       </c>
       <c r="I26" t="n">
         <v>7.71</v>
       </c>
-      <c r="J26" t="inlineStr"/>
+      <c r="J26" t="n">
+        <v>12.1</v>
+      </c>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="n">
         <v>-4.85</v>
       </c>
       <c r="M26" t="n">
-        <v>10.58</v>
+        <v>10.04</v>
       </c>
       <c r="N26" t="b">
         <v>1</v>
@@ -19118,7 +19130,7 @@
         <v>-6.9</v>
       </c>
       <c r="H27" t="n">
-        <v>14.56</v>
+        <v>14.85</v>
       </c>
       <c r="I27" t="n">
         <v>6.44</v>
@@ -19131,7 +19143,7 @@
         <v>-4.53</v>
       </c>
       <c r="M27" t="n">
-        <v>13.02</v>
+        <v>12.7</v>
       </c>
       <c r="N27" t="b">
         <v>1</v>
@@ -19169,7 +19181,7 @@
         <v>0.3</v>
       </c>
       <c r="H28" t="n">
-        <v>-17.07</v>
+        <v>-17.11</v>
       </c>
       <c r="I28" t="n">
         <v>-10.53</v>
@@ -19182,7 +19194,7 @@
         <v>-17.73</v>
       </c>
       <c r="M28" t="n">
-        <v>-18.11</v>
+        <v>-18.75</v>
       </c>
       <c r="N28" t="b">
         <v>1</v>
@@ -19220,7 +19232,7 @@
         <v>2.8</v>
       </c>
       <c r="H29" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="I29" t="n">
         <v>3.18</v>
@@ -19233,7 +19245,7 @@
         <v>-0.88</v>
       </c>
       <c r="M29" t="n">
-        <v>1.39</v>
+        <v>0.93</v>
       </c>
       <c r="N29" t="b">
         <v>1</v>
@@ -19271,7 +19283,7 @@
         <v>34.5</v>
       </c>
       <c r="H30" t="n">
-        <v>10.6</v>
+        <v>12.05</v>
       </c>
       <c r="I30" t="n">
         <v>0.66</v>
@@ -19284,7 +19296,7 @@
         <v>-2.64</v>
       </c>
       <c r="M30" t="n">
-        <v>8.84</v>
+        <v>9.69</v>
       </c>
       <c r="N30" t="b">
         <v>1</v>
@@ -19322,7 +19334,7 @@
         <v>24.3</v>
       </c>
       <c r="H31" t="n">
-        <v>59.22</v>
+        <v>63.36</v>
       </c>
       <c r="I31" t="n">
         <v>2.54</v>
@@ -19335,7 +19347,7 @@
         <v>-5.21</v>
       </c>
       <c r="M31" t="n">
-        <v>58.1</v>
+        <v>61.64</v>
       </c>
       <c r="N31" t="b">
         <v>1</v>
@@ -19373,7 +19385,7 @@
         <v>-16.9</v>
       </c>
       <c r="H32" t="n">
-        <v>-11.9</v>
+        <v>-9.41</v>
       </c>
       <c r="I32" t="n">
         <v>-6.47</v>
@@ -19386,7 +19398,7 @@
         <v>-11.5</v>
       </c>
       <c r="M32" t="n">
-        <v>-13.01</v>
+        <v>-11.13</v>
       </c>
       <c r="N32" t="b">
         <v>1</v>
@@ -19424,7 +19436,7 @@
         <v>20.3</v>
       </c>
       <c r="H33" t="n">
-        <v>-20.99</v>
+        <v>-20.61</v>
       </c>
       <c r="I33" t="n">
         <v>-2.07</v>
@@ -19437,7 +19449,7 @@
         <v>-17.35</v>
       </c>
       <c r="M33" t="n">
-        <v>-21.94</v>
+        <v>-22.17</v>
       </c>
       <c r="N33" t="b">
         <v>1</v>
@@ -19475,7 +19487,7 @@
         <v>0.3</v>
       </c>
       <c r="H34" t="n">
-        <v>-18.87</v>
+        <v>-18.86</v>
       </c>
       <c r="I34" t="n">
         <v>-9.9</v>
@@ -19488,7 +19500,7 @@
         <v>-21.72</v>
       </c>
       <c r="M34" t="n">
-        <v>-20.32</v>
+        <v>-20.92</v>
       </c>
       <c r="N34" t="b">
         <v>1</v>
@@ -19526,7 +19538,7 @@
         <v>49.4</v>
       </c>
       <c r="H35" t="n">
-        <v>6.6</v>
+        <v>14.51</v>
       </c>
       <c r="I35" t="n">
         <v>2.9</v>
@@ -19539,7 +19551,7 @@
         <v>-5.67</v>
       </c>
       <c r="M35" t="n">
-        <v>5.33</v>
+        <v>12.64</v>
       </c>
       <c r="N35" t="b">
         <v>1</v>
@@ -19577,7 +19589,7 @@
         <v>4.5</v>
       </c>
       <c r="H36" t="n">
-        <v>-9.199999999999999</v>
+        <v>-9.07</v>
       </c>
       <c r="I36" t="n">
         <v>-7.61</v>
@@ -19590,7 +19602,7 @@
         <v>-11.06</v>
       </c>
       <c r="M36" t="n">
-        <v>-10.46</v>
+        <v>-10.94</v>
       </c>
       <c r="N36" t="b">
         <v>1</v>
@@ -19628,7 +19640,7 @@
         <v>-17.9</v>
       </c>
       <c r="H37" t="n">
-        <v>1.19</v>
+        <v>2.26</v>
       </c>
       <c r="I37" t="n">
         <v>0.6</v>
@@ -19641,7 +19653,7 @@
         <v>-4.72</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.1</v>
+        <v>0.36</v>
       </c>
       <c r="N37" t="b">
         <v>1</v>
@@ -19679,7 +19691,7 @@
         <v>2.1</v>
       </c>
       <c r="H38" t="n">
-        <v>-22.84</v>
+        <v>-22.71</v>
       </c>
       <c r="I38" t="n">
         <v>0.25</v>
@@ -19692,7 +19704,7 @@
         <v>-16.43</v>
       </c>
       <c r="M38" t="n">
-        <v>-24.13</v>
+        <v>-24.61</v>
       </c>
       <c r="N38" t="b">
         <v>1</v>
@@ -19730,7 +19742,7 @@
         <v>19.4</v>
       </c>
       <c r="H39" t="n">
-        <v>-10.4</v>
+        <v>-8.51</v>
       </c>
       <c r="I39" t="n">
         <v>-10.01</v>
@@ -19743,7 +19755,7 @@
         <v>-15.23</v>
       </c>
       <c r="M39" t="n">
-        <v>-11.11</v>
+        <v>-9.83</v>
       </c>
       <c r="N39" t="b">
         <v>1</v>
@@ -19781,7 +19793,7 @@
         <v>-2.6</v>
       </c>
       <c r="H40" t="n">
-        <v>-10.56</v>
+        <v>-9.24</v>
       </c>
       <c r="I40" t="n">
         <v>-4.27</v>
@@ -19794,7 +19806,7 @@
         <v>-4.86</v>
       </c>
       <c r="M40" t="n">
-        <v>-11.5</v>
+        <v>-10.78</v>
       </c>
       <c r="N40" t="b">
         <v>1</v>
@@ -19832,7 +19844,7 @@
         <v>23.8</v>
       </c>
       <c r="H41" t="n">
-        <v>1.29</v>
+        <v>2.9</v>
       </c>
       <c r="I41" t="n">
         <v>1.36</v>
@@ -19845,7 +19857,7 @@
         <v>-9.94</v>
       </c>
       <c r="M41" t="n">
-        <v>1.33</v>
+        <v>2.34</v>
       </c>
       <c r="N41" t="b">
         <v>1</v>
@@ -19883,7 +19895,7 @@
         <v>38.9</v>
       </c>
       <c r="H42" t="n">
-        <v>-10.46</v>
+        <v>-11.43</v>
       </c>
       <c r="I42" t="n">
         <v>-9.220000000000001</v>
@@ -19896,7 +19908,7 @@
         <v>-9.83</v>
       </c>
       <c r="M42" t="n">
-        <v>-10.42</v>
+        <v>-11.98</v>
       </c>
       <c r="N42" t="b">
         <v>1</v>
@@ -19934,7 +19946,7 @@
         <v>43.2</v>
       </c>
       <c r="H43" t="n">
-        <v>-17.01</v>
+        <v>-18.02</v>
       </c>
       <c r="I43" t="n">
         <v>-3.15</v>
@@ -19947,7 +19959,7 @@
         <v>-17.51</v>
       </c>
       <c r="M43" t="n">
-        <v>-17.14</v>
+        <v>-18.74</v>
       </c>
       <c r="N43" t="b">
         <v>1</v>
@@ -19985,7 +19997,7 @@
         <v>-8.199999999999999</v>
       </c>
       <c r="H44" t="n">
-        <v>-2.97</v>
+        <v>-1.78</v>
       </c>
       <c r="I44" t="n">
         <v>5.34</v>
@@ -19998,7 +20010,7 @@
         <v>-5.27</v>
       </c>
       <c r="M44" t="n">
-        <v>-3.09</v>
+        <v>-2.51</v>
       </c>
       <c r="N44" t="b">
         <v>1</v>
@@ -20036,7 +20048,7 @@
         <v>-23.9</v>
       </c>
       <c r="H45" t="n">
-        <v>-8.970000000000001</v>
+        <v>-4.61</v>
       </c>
       <c r="I45" t="n">
         <v>3.28</v>
@@ -20049,7 +20061,7 @@
         <v>-4.46</v>
       </c>
       <c r="M45" t="n">
-        <v>-9.390000000000001</v>
+        <v>-5.64</v>
       </c>
       <c r="N45" t="b">
         <v>1</v>
@@ -20091,7 +20103,7 @@
         <v>-6.1</v>
       </c>
       <c r="H46" t="n">
-        <v>-13.04</v>
+        <v>-17.4</v>
       </c>
       <c r="I46" t="n">
         <v>4.9</v>
@@ -20104,7 +20116,7 @@
         <v>-9</v>
       </c>
       <c r="M46" t="n">
-        <v>-13.46</v>
+        <v>-18.42</v>
       </c>
       <c r="N46" t="b">
         <v>1</v>
@@ -20142,7 +20154,7 @@
         <v>26.7</v>
       </c>
       <c r="H47" t="n">
-        <v>-0.72</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="I47" t="n">
         <v>-0.05</v>
@@ -20155,7 +20167,7 @@
         <v>-0.87</v>
       </c>
       <c r="M47" t="n">
-        <v>-1.14</v>
+        <v>-1.72</v>
       </c>
       <c r="N47" t="b">
         <v>1</v>
@@ -20193,7 +20205,7 @@
         <v>-3.5</v>
       </c>
       <c r="H48" t="n">
-        <v>-2.19</v>
+        <v>-3.69</v>
       </c>
       <c r="I48" t="n">
         <v>-4.95</v>
@@ -20206,7 +20218,7 @@
         <v>-8.43</v>
       </c>
       <c r="M48" t="n">
-        <v>-2.82</v>
+        <v>-4.92</v>
       </c>
       <c r="N48" t="b">
         <v>1</v>
@@ -20244,7 +20256,7 @@
         <v>-17.9</v>
       </c>
       <c r="H49" t="n">
-        <v>7</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I49" t="n">
         <v>-0.5</v>
@@ -20257,7 +20269,7 @@
         <v>-3.43</v>
       </c>
       <c r="M49" t="n">
-        <v>6.38</v>
+        <v>7.47</v>
       </c>
       <c r="N49" t="b">
         <v>1</v>
@@ -20295,7 +20307,7 @@
         <v>53.5</v>
       </c>
       <c r="H50" t="n">
-        <v>7.7</v>
+        <v>12.46</v>
       </c>
       <c r="I50" t="n">
         <v>1.23</v>
@@ -20308,7 +20320,7 @@
         <v>-7.57</v>
       </c>
       <c r="M50" t="n">
-        <v>6.97</v>
+        <v>11.12</v>
       </c>
       <c r="N50" t="b">
         <v>1</v>
@@ -20346,7 +20358,7 @@
         <v>-1</v>
       </c>
       <c r="H51" t="n">
-        <v>-9.1</v>
+        <v>-8.289999999999999</v>
       </c>
       <c r="I51" t="n">
         <v>-6.26</v>
@@ -20359,7 +20371,7 @@
         <v>-15</v>
       </c>
       <c r="M51" t="n">
-        <v>-9.83</v>
+        <v>-9.619999999999999</v>
       </c>
       <c r="N51" t="b">
         <v>1</v>
@@ -20397,7 +20409,7 @@
         <v>29.7</v>
       </c>
       <c r="H52" t="n">
-        <v>3.32</v>
+        <v>7.04</v>
       </c>
       <c r="I52" t="n">
         <v>11.27</v>
@@ -20410,7 +20422,7 @@
         <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>2.59</v>
+        <v>5.7</v>
       </c>
       <c r="N52" t="b">
         <v>1</v>
@@ -20448,7 +20460,7 @@
         <v>15.2</v>
       </c>
       <c r="H53" t="n">
-        <v>-38.99</v>
+        <v>-37.21</v>
       </c>
       <c r="I53" t="n">
         <v>-8.77</v>
@@ -20461,7 +20473,7 @@
         <v>-24.79</v>
       </c>
       <c r="M53" t="n">
-        <v>-38.99</v>
+        <v>-37.81</v>
       </c>
       <c r="N53" t="b">
         <v>1</v>
@@ -20499,7 +20511,7 @@
         <v>22.2</v>
       </c>
       <c r="H54" t="n">
-        <v>4.01</v>
+        <v>4.79</v>
       </c>
       <c r="I54" t="n">
         <v>1.01</v>
@@ -20512,7 +20524,7 @@
         <v>-3.94</v>
       </c>
       <c r="M54" t="n">
-        <v>4.01</v>
+        <v>4.19</v>
       </c>
       <c r="N54" t="b">
         <v>1</v>
@@ -20554,7 +20566,7 @@
         <v>-0</v>
       </c>
       <c r="H55" t="n">
-        <v>35.64</v>
+        <v>41.02</v>
       </c>
       <c r="I55" t="n">
         <v>13.5</v>
@@ -20567,7 +20579,7 @@
         <v>-2.53</v>
       </c>
       <c r="M55" t="n">
-        <v>32.12</v>
+        <v>36.88</v>
       </c>
       <c r="N55" t="b">
         <v>1</v>
@@ -20605,7 +20617,7 @@
         <v>10.5</v>
       </c>
       <c r="H56" t="n">
-        <v>7.28</v>
+        <v>7.94</v>
       </c>
       <c r="I56" t="n">
         <v>1.99</v>
@@ -20618,7 +20630,7 @@
         <v>-6.27</v>
       </c>
       <c r="M56" t="n">
-        <v>3.76</v>
+        <v>3.8</v>
       </c>
       <c r="N56" t="b">
         <v>1</v>
@@ -20656,7 +20668,7 @@
         <v>-37</v>
       </c>
       <c r="H57" t="n">
-        <v>40.24</v>
+        <v>45.58</v>
       </c>
       <c r="I57" t="n">
         <v>18.38</v>
@@ -20669,7 +20681,7 @@
         <v>-5.11</v>
       </c>
       <c r="M57" t="n">
-        <v>36.05</v>
+        <v>40.77</v>
       </c>
       <c r="N57" t="b">
         <v>1</v>
@@ -20707,7 +20719,7 @@
         <v>-26.8</v>
       </c>
       <c r="H58" t="n">
-        <v>18.53</v>
+        <v>16.64</v>
       </c>
       <c r="I58" t="n">
         <v>4.56</v>
@@ -20720,7 +20732,7 @@
         <v>-4.09</v>
       </c>
       <c r="M58" t="n">
-        <v>14.34</v>
+        <v>11.83</v>
       </c>
       <c r="N58" t="b">
         <v>1</v>
@@ -20758,7 +20770,7 @@
         <v>-36.5</v>
       </c>
       <c r="H59" t="n">
-        <v>-33.9</v>
+        <v>-35.3</v>
       </c>
       <c r="I59" t="n">
         <v>-27.75</v>
@@ -20771,7 +20783,7 @@
         <v>-31.28</v>
       </c>
       <c r="M59" t="n">
-        <v>-38.75</v>
+        <v>-40.77</v>
       </c>
       <c r="N59" t="b">
         <v>1</v>
@@ -20809,7 +20821,7 @@
         <v>-38.7</v>
       </c>
       <c r="H60" t="n">
-        <v>14.52</v>
+        <v>13.98</v>
       </c>
       <c r="I60" t="n">
         <v>17.17</v>
@@ -20822,7 +20834,7 @@
         <v>-0.54</v>
       </c>
       <c r="M60" t="n">
-        <v>9.67</v>
+        <v>8.51</v>
       </c>
       <c r="N60" t="b">
         <v>1</v>
@@ -20860,7 +20872,7 @@
         <v>-34.6</v>
       </c>
       <c r="H61" t="n">
-        <v>21.18</v>
+        <v>21.72</v>
       </c>
       <c r="I61" t="n">
         <v>6.67</v>
@@ -20873,7 +20885,7 @@
         <v>-3.06</v>
       </c>
       <c r="M61" t="n">
-        <v>16.33</v>
+        <v>16.24</v>
       </c>
       <c r="N61" t="b">
         <v>1</v>
@@ -20911,7 +20923,7 @@
         <v>-11.8</v>
       </c>
       <c r="H62" t="n">
-        <v>-2.47</v>
+        <v>-4.41</v>
       </c>
       <c r="I62" t="n">
         <v>9.76</v>
@@ -20924,7 +20936,7 @@
         <v>-1.63</v>
       </c>
       <c r="M62" t="n">
-        <v>-7.43</v>
+        <v>-9.99</v>
       </c>
       <c r="N62" t="b">
         <v>1</v>
@@ -20962,7 +20974,7 @@
         <v>0.1</v>
       </c>
       <c r="H63" t="n">
-        <v>-12.92</v>
+        <v>-14.72</v>
       </c>
       <c r="I63" t="n">
         <v>-2.83</v>
@@ -20975,7 +20987,7 @@
         <v>-5.45</v>
       </c>
       <c r="M63" t="n">
-        <v>-17.88</v>
+        <v>-20.31</v>
       </c>
       <c r="N63" t="b">
         <v>1</v>
@@ -21013,7 +21025,7 @@
         <v>24.1</v>
       </c>
       <c r="H64" t="n">
-        <v>4.27</v>
+        <v>4.92</v>
       </c>
       <c r="I64" t="n">
         <v>-8.31</v>
@@ -21026,7 +21038,7 @@
         <v>-18.31</v>
       </c>
       <c r="M64" t="n">
-        <v>0.12</v>
+        <v>0.14</v>
       </c>
       <c r="N64" t="b">
         <v>1</v>
@@ -21064,7 +21076,7 @@
         <v>-15.9</v>
       </c>
       <c r="H65" t="n">
-        <v>9.15</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="I65" t="n">
         <v>10.45</v>
@@ -21077,7 +21089,7 @@
         <v>-0.31</v>
       </c>
       <c r="M65" t="n">
-        <v>5</v>
+        <v>4.85</v>
       </c>
       <c r="N65" t="b">
         <v>1</v>
@@ -21115,7 +21127,7 @@
         <v>-21.8</v>
       </c>
       <c r="H66" t="n">
-        <v>-32.38</v>
+        <v>-33.12</v>
       </c>
       <c r="I66" t="n">
         <v>-18.97</v>
@@ -21128,7 +21140,7 @@
         <v>-26.82</v>
       </c>
       <c r="M66" t="n">
-        <v>-37.31</v>
+        <v>-38.69</v>
       </c>
       <c r="N66" t="b">
         <v>1</v>
@@ -21166,7 +21178,7 @@
         <v>57</v>
       </c>
       <c r="H67" t="n">
-        <v>29.97</v>
+        <v>30.59</v>
       </c>
       <c r="I67" t="n">
         <v>-11.21</v>
@@ -21217,7 +21229,7 @@
         <v>-21.8</v>
       </c>
       <c r="H68" t="n">
-        <v>9.859999999999999</v>
+        <v>9.33</v>
       </c>
       <c r="I68" t="n">
         <v>1.71</v>
@@ -21230,7 +21242,7 @@
         <v>-6.18</v>
       </c>
       <c r="M68" t="n">
-        <v>5.94</v>
+        <v>4.79</v>
       </c>
       <c r="N68" t="b">
         <v>1</v>
@@ -21268,7 +21280,7 @@
         <v>1</v>
       </c>
       <c r="H69" t="n">
-        <v>-31.03</v>
+        <v>-33.55</v>
       </c>
       <c r="I69" t="n">
         <v>-11.52</v>
@@ -21281,7 +21293,7 @@
         <v>-16.26</v>
       </c>
       <c r="M69" t="n">
-        <v>-35</v>
+        <v>-38.14</v>
       </c>
       <c r="N69" t="b">
         <v>1</v>
@@ -21319,7 +21331,7 @@
         <v>45.4</v>
       </c>
       <c r="H70" t="n">
-        <v>-3.57</v>
+        <v>-6.72</v>
       </c>
       <c r="I70" t="n">
         <v>-1.72</v>
@@ -21332,7 +21344,7 @@
         <v>-23.15</v>
       </c>
       <c r="M70" t="n">
-        <v>-7.53</v>
+        <v>-11.31</v>
       </c>
       <c r="N70" t="b">
         <v>1</v>
@@ -21370,7 +21382,7 @@
         <v>76.5</v>
       </c>
       <c r="H71" t="n">
-        <v>6.47</v>
+        <v>4.64</v>
       </c>
       <c r="I71" t="n">
         <v>-5.56</v>
@@ -21383,7 +21395,7 @@
         <v>-33.97</v>
       </c>
       <c r="M71" t="n">
-        <v>2.51</v>
+        <v>0.06</v>
       </c>
       <c r="N71" t="b">
         <v>1</v>
@@ -21472,7 +21484,7 @@
         <v>51.8</v>
       </c>
       <c r="H73" t="n">
-        <v>6.28</v>
+        <v>4.79</v>
       </c>
       <c r="I73" t="n">
         <v>10.75</v>
@@ -21485,7 +21497,7 @@
         <v>-25.09</v>
       </c>
       <c r="M73" t="n">
-        <v>2.31</v>
+        <v>0.21</v>
       </c>
       <c r="N73" t="b">
         <v>1</v>
@@ -21523,7 +21535,7 @@
         <v>32.3</v>
       </c>
       <c r="H74" t="n">
-        <v>-24.15</v>
+        <v>-24.95</v>
       </c>
       <c r="I74" t="n">
         <v>-20.76</v>
@@ -21536,7 +21548,7 @@
         <v>-27.91</v>
       </c>
       <c r="M74" t="n">
-        <v>-28.11</v>
+        <v>-29.53</v>
       </c>
       <c r="N74" t="b">
         <v>1</v>
@@ -21574,7 +21586,7 @@
         <v>3.7</v>
       </c>
       <c r="H75" t="n">
-        <v>-13.71</v>
+        <v>-4.92</v>
       </c>
       <c r="I75" t="n">
         <v>-1.11</v>
@@ -21587,7 +21599,7 @@
         <v>-25.46</v>
       </c>
       <c r="M75" t="n">
-        <v>-17.68</v>
+        <v>-9.5</v>
       </c>
       <c r="N75" t="b">
         <v>1</v>
@@ -21625,7 +21637,7 @@
         <v>42.4</v>
       </c>
       <c r="H76" t="n">
-        <v>-1.79</v>
+        <v>6.86</v>
       </c>
       <c r="I76" t="n">
         <v>2.16</v>
@@ -21638,7 +21650,7 @@
         <v>-15.76</v>
       </c>
       <c r="M76" t="n">
-        <v>-5.75</v>
+        <v>2.28</v>
       </c>
       <c r="N76" t="b">
         <v>1</v>
@@ -21676,7 +21688,7 @@
         <v>28.2</v>
       </c>
       <c r="H77" t="n">
-        <v>7.48</v>
+        <v>10.82</v>
       </c>
       <c r="I77" t="n">
         <v>-1.71</v>
@@ -21689,7 +21701,7 @@
         <v>-23.43</v>
       </c>
       <c r="M77" t="n">
-        <v>3.52</v>
+        <v>6.24</v>
       </c>
       <c r="N77" t="b">
         <v>1</v>
@@ -21727,7 +21739,7 @@
         <v>28.6</v>
       </c>
       <c r="H78" t="n">
-        <v>19.08</v>
+        <v>20.79</v>
       </c>
       <c r="I78" t="n">
         <v>2.81</v>
@@ -21740,7 +21752,7 @@
         <v>-18.87</v>
       </c>
       <c r="M78" t="n">
-        <v>15.12</v>
+        <v>16.2</v>
       </c>
       <c r="N78" t="b">
         <v>1</v>
@@ -21778,7 +21790,7 @@
         <v>33.1</v>
       </c>
       <c r="H79" t="n">
-        <v>29.22</v>
+        <v>35.96</v>
       </c>
       <c r="I79" t="n">
         <v>4.68</v>
@@ -21791,7 +21803,7 @@
         <v>-26.7</v>
       </c>
       <c r="M79" t="n">
-        <v>25.26</v>
+        <v>31.38</v>
       </c>
       <c r="N79" t="b">
         <v>1</v>
@@ -21829,7 +21841,7 @@
         <v>21.8</v>
       </c>
       <c r="H80" t="n">
-        <v>-17.13</v>
+        <v>-14.65</v>
       </c>
       <c r="I80" t="n">
         <v>-6.34</v>
@@ -21842,7 +21854,7 @@
         <v>-30.04</v>
       </c>
       <c r="M80" t="n">
-        <v>-21.09</v>
+        <v>-19.23</v>
       </c>
       <c r="N80" t="b">
         <v>1</v>
@@ -21880,7 +21892,7 @@
         <v>40.3</v>
       </c>
       <c r="H81" t="n">
-        <v>-8.33</v>
+        <v>-4.26</v>
       </c>
       <c r="I81" t="n">
         <v>1.24</v>
@@ -21893,7 +21905,7 @@
         <v>-20.5</v>
       </c>
       <c r="M81" t="n">
-        <v>-12.29</v>
+        <v>-8.84</v>
       </c>
       <c r="N81" t="b">
         <v>1</v>
@@ -21931,7 +21943,7 @@
         <v>24.1</v>
       </c>
       <c r="H82" t="n">
-        <v>8.859999999999999</v>
+        <v>3.34</v>
       </c>
       <c r="I82" t="n">
         <v>-1.6</v>
@@ -21944,7 +21956,7 @@
         <v>-22.54</v>
       </c>
       <c r="M82" t="n">
-        <v>4.9</v>
+        <v>-1.24</v>
       </c>
       <c r="N82" t="b">
         <v>1</v>
@@ -21982,7 +21994,7 @@
         <v>24.5</v>
       </c>
       <c r="H83" t="n">
-        <v>-26.36</v>
+        <v>-27.78</v>
       </c>
       <c r="I83" t="n">
         <v>-12.99</v>
@@ -21995,7 +22007,7 @@
         <v>-22.54</v>
       </c>
       <c r="M83" t="n">
-        <v>-30.32</v>
+        <v>-32.36</v>
       </c>
       <c r="N83" t="b">
         <v>1</v>
@@ -22033,7 +22045,7 @@
         <v>19.3</v>
       </c>
       <c r="H84" t="n">
-        <v>10.49</v>
+        <v>11.59</v>
       </c>
       <c r="I84" t="n">
         <v>11.79</v>
@@ -22046,7 +22058,7 @@
         <v>-16.62</v>
       </c>
       <c r="M84" t="n">
-        <v>6.53</v>
+        <v>7</v>
       </c>
       <c r="N84" t="b">
         <v>1</v>
@@ -22084,7 +22096,7 @@
         <v>-8.699999999999999</v>
       </c>
       <c r="H85" t="n">
-        <v>-10.08</v>
+        <v>-11.27</v>
       </c>
       <c r="I85" t="n">
         <v>17.25</v>
@@ -22097,7 +22109,7 @@
         <v>-4.65</v>
       </c>
       <c r="M85" t="n">
-        <v>-14.04</v>
+        <v>-15.85</v>
       </c>
       <c r="N85" t="b">
         <v>1</v>
@@ -22135,7 +22147,7 @@
         <v>15.2</v>
       </c>
       <c r="H86" t="n">
-        <v>-1.6</v>
+        <v>1.74</v>
       </c>
       <c r="I86" t="n">
         <v>5.36</v>
@@ -22148,7 +22160,7 @@
         <v>-28.18</v>
       </c>
       <c r="M86" t="n">
-        <v>-5.56</v>
+        <v>-2.84</v>
       </c>
       <c r="N86" t="b">
         <v>1</v>
@@ -22186,7 +22198,7 @@
         <v>37.2</v>
       </c>
       <c r="H87" t="n">
-        <v>-24.95</v>
+        <v>-23.77</v>
       </c>
       <c r="I87" t="n">
         <v>-7.64</v>
@@ -22199,7 +22211,7 @@
         <v>-26.24</v>
       </c>
       <c r="M87" t="n">
-        <v>-28.91</v>
+        <v>-28.35</v>
       </c>
       <c r="N87" t="b">
         <v>1</v>
@@ -22237,7 +22249,7 @@
         <v>29.8</v>
       </c>
       <c r="H88" t="n">
-        <v>41.18</v>
+        <v>41.04</v>
       </c>
       <c r="I88" t="n">
         <v>-2.74</v>
@@ -22250,7 +22262,7 @@
         <v>-22.36</v>
       </c>
       <c r="M88" t="n">
-        <v>37.22</v>
+        <v>36.45</v>
       </c>
       <c r="N88" t="b">
         <v>1</v>
@@ -22288,7 +22300,7 @@
         <v>19.3</v>
       </c>
       <c r="H89" t="n">
-        <v>-23.81</v>
+        <v>-26.62</v>
       </c>
       <c r="I89" t="n">
         <v>-16.69</v>
@@ -22301,7 +22313,7 @@
         <v>-36.39</v>
       </c>
       <c r="M89" t="n">
-        <v>-27.77</v>
+        <v>-31.2</v>
       </c>
       <c r="N89" t="b">
         <v>1</v>
@@ -22339,7 +22351,7 @@
         <v>11.8</v>
       </c>
       <c r="H90" t="n">
-        <v>16.49</v>
+        <v>19.32</v>
       </c>
       <c r="I90" t="n">
         <v>-1.19</v>
@@ -22352,7 +22364,7 @@
         <v>-17.57</v>
       </c>
       <c r="M90" t="n">
-        <v>12.52</v>
+        <v>14.74</v>
       </c>
       <c r="N90" t="b">
         <v>1</v>
@@ -22390,7 +22402,7 @@
         <v>27.5</v>
       </c>
       <c r="H91" t="n">
-        <v>9.93</v>
+        <v>12.35</v>
       </c>
       <c r="I91" t="n">
         <v>8.42</v>
@@ -22403,7 +22415,7 @@
         <v>-2.51</v>
       </c>
       <c r="M91" t="n">
-        <v>5.96</v>
+        <v>7.77</v>
       </c>
       <c r="N91" t="b">
         <v>1</v>
@@ -22441,7 +22453,7 @@
         <v>-22.4</v>
       </c>
       <c r="H92" t="n">
-        <v>-9.890000000000001</v>
+        <v>-10.49</v>
       </c>
       <c r="I92" t="n">
         <v>9.42</v>
@@ -22454,7 +22466,7 @@
         <v>-2.79</v>
       </c>
       <c r="M92" t="n">
-        <v>-13.85</v>
+        <v>-15.08</v>
       </c>
       <c r="N92" t="b">
         <v>1</v>
@@ -22492,7 +22504,7 @@
         <v>-14.7</v>
       </c>
       <c r="H93" t="n">
-        <v>-19.48</v>
+        <v>-21.64</v>
       </c>
       <c r="I93" t="n">
         <v>10.3</v>
@@ -22505,7 +22517,7 @@
         <v>-2.6</v>
       </c>
       <c r="M93" t="n">
-        <v>-23.44</v>
+        <v>-26.22</v>
       </c>
       <c r="N93" t="b">
         <v>1</v>
@@ -22547,7 +22559,7 @@
         <v>-9.300000000000001</v>
       </c>
       <c r="H94" t="n">
-        <v>-21.53</v>
+        <v>-20.57</v>
       </c>
       <c r="I94" t="n">
         <v>10.42</v>
@@ -22560,7 +22572,7 @@
         <v>-21.72</v>
       </c>
       <c r="M94" t="n">
-        <v>-25.49</v>
+        <v>-25.16</v>
       </c>
       <c r="N94" t="b">
         <v>1</v>
@@ -22598,7 +22610,7 @@
         <v>-25.2</v>
       </c>
       <c r="H95" t="n">
-        <v>8.77</v>
+        <v>9.44</v>
       </c>
       <c r="I95" t="n">
         <v>22.53</v>
@@ -22611,7 +22623,7 @@
         <v>-19.27</v>
       </c>
       <c r="M95" t="n">
-        <v>4.81</v>
+        <v>4.85</v>
       </c>
       <c r="N95" t="b">
         <v>1</v>
@@ -22649,7 +22661,7 @@
         <v>5.1</v>
       </c>
       <c r="H96" t="n">
-        <v>2.8</v>
+        <v>3.59</v>
       </c>
       <c r="I96" t="n">
         <v>8.77</v>
@@ -22662,7 +22674,7 @@
         <v>-3.54</v>
       </c>
       <c r="M96" t="n">
-        <v>-1.16</v>
+        <v>-1</v>
       </c>
       <c r="N96" t="b">
         <v>1</v>
@@ -22700,7 +22712,7 @@
         <v>34.2</v>
       </c>
       <c r="H97" t="n">
-        <v>7.71</v>
+        <v>8.26</v>
       </c>
       <c r="I97" t="n">
         <v>8.15</v>
@@ -22713,7 +22725,7 @@
         <v>-7.63</v>
       </c>
       <c r="M97" t="n">
-        <v>3.75</v>
+        <v>3.67</v>
       </c>
       <c r="N97" t="b">
         <v>1</v>
@@ -22751,7 +22763,7 @@
         <v>42</v>
       </c>
       <c r="H98" t="n">
-        <v>-31.67</v>
+        <v>-31.9</v>
       </c>
       <c r="I98" t="n">
         <v>0.6</v>
@@ -22764,7 +22776,7 @@
         <v>-16.67</v>
       </c>
       <c r="M98" t="n">
-        <v>-35.63</v>
+        <v>-36.48</v>
       </c>
       <c r="N98" t="b">
         <v>1</v>
@@ -22802,7 +22814,7 @@
         <v>-25.3</v>
       </c>
       <c r="H99" t="n">
-        <v>43.15</v>
+        <v>40.03</v>
       </c>
       <c r="I99" t="n">
         <v>36.1</v>
@@ -22815,7 +22827,7 @@
         <v>-5.66</v>
       </c>
       <c r="M99" t="n">
-        <v>39.19</v>
+        <v>35.44</v>
       </c>
       <c r="N99" t="b">
         <v>1</v>
@@ -22853,7 +22865,7 @@
         <v>-7.7</v>
       </c>
       <c r="H100" t="n">
-        <v>0.9</v>
+        <v>-0.03</v>
       </c>
       <c r="I100" t="n">
         <v>-6.47</v>
@@ -22866,7 +22878,7 @@
         <v>-23.05</v>
       </c>
       <c r="M100" t="n">
-        <v>-3.06</v>
+        <v>-4.61</v>
       </c>
       <c r="N100" t="b">
         <v>1</v>
@@ -22904,7 +22916,7 @@
         <v>13.7</v>
       </c>
       <c r="H101" t="n">
-        <v>15.27</v>
+        <v>17.83</v>
       </c>
       <c r="I101" t="n">
         <v>2.74</v>
@@ -22917,7 +22929,7 @@
         <v>-24.02</v>
       </c>
       <c r="M101" t="n">
-        <v>11.31</v>
+        <v>13.25</v>
       </c>
       <c r="N101" t="b">
         <v>1</v>
@@ -22955,7 +22967,7 @@
         <v>21.8</v>
       </c>
       <c r="H102" t="n">
-        <v>-6.5</v>
+        <v>-7.4</v>
       </c>
       <c r="I102" t="n">
         <v>18.32</v>
@@ -22968,7 +22980,7 @@
         <v>-23.27</v>
       </c>
       <c r="M102" t="n">
-        <v>-10.46</v>
+        <v>-11.99</v>
       </c>
       <c r="N102" t="b">
         <v>1</v>
@@ -23006,7 +23018,7 @@
         <v>29.4</v>
       </c>
       <c r="H103" t="n">
-        <v>-0.9</v>
+        <v>-0.27</v>
       </c>
       <c r="I103" t="n">
         <v>-2.62</v>
@@ -23057,7 +23069,7 @@
         <v>-3.7</v>
       </c>
       <c r="H104" t="n">
-        <v>-24.03</v>
+        <v>-23.51</v>
       </c>
       <c r="I104" t="n">
         <v>-8.07</v>
@@ -23070,7 +23082,7 @@
         <v>-22.12</v>
       </c>
       <c r="M104" t="n">
-        <v>-27.99</v>
+        <v>-28.1</v>
       </c>
       <c r="N104" t="b">
         <v>1</v>
@@ -23108,7 +23120,7 @@
         <v>21.3</v>
       </c>
       <c r="H105" t="n">
-        <v>1.77</v>
+        <v>1.9</v>
       </c>
       <c r="I105" t="n">
         <v>0.23</v>
@@ -23121,7 +23133,7 @@
         <v>-0.85</v>
       </c>
       <c r="M105" t="n">
-        <v>-2.19</v>
+        <v>-2.68</v>
       </c>
       <c r="N105" t="b">
         <v>1</v>
@@ -23159,7 +23171,7 @@
         <v>-21.4</v>
       </c>
       <c r="H106" t="n">
-        <v>13.68</v>
+        <v>15.99</v>
       </c>
       <c r="I106" t="n">
         <v>4.55</v>
@@ -23172,7 +23184,7 @@
         <v>-6.39</v>
       </c>
       <c r="M106" t="n">
-        <v>9.720000000000001</v>
+        <v>11.4</v>
       </c>
       <c r="N106" t="b">
         <v>1</v>
@@ -23210,7 +23222,7 @@
         <v>16.3</v>
       </c>
       <c r="H107" t="n">
-        <v>0.44</v>
+        <v>3.79</v>
       </c>
       <c r="I107" t="n">
         <v>-1</v>
@@ -23223,7 +23235,7 @@
         <v>-22.5</v>
       </c>
       <c r="M107" t="n">
-        <v>-3.52</v>
+        <v>-0.8</v>
       </c>
       <c r="N107" t="b">
         <v>1</v>
@@ -23261,7 +23273,7 @@
         <v>11.9</v>
       </c>
       <c r="H108" t="n">
-        <v>-5.18</v>
+        <v>-2.92</v>
       </c>
       <c r="I108" t="n">
         <v>7.74</v>
@@ -23274,7 +23286,7 @@
         <v>-9.43</v>
       </c>
       <c r="M108" t="n">
-        <v>-9.140000000000001</v>
+        <v>-7.5</v>
       </c>
       <c r="N108" t="b">
         <v>1</v>
@@ -23312,7 +23324,7 @@
         <v>0.2</v>
       </c>
       <c r="H109" t="n">
-        <v>12.13</v>
+        <v>11.71</v>
       </c>
       <c r="I109" t="n">
         <v>4.35</v>
@@ -23325,7 +23337,7 @@
         <v>-2.79</v>
       </c>
       <c r="M109" t="n">
-        <v>8.16</v>
+        <v>7.13</v>
       </c>
       <c r="N109" t="b">
         <v>1</v>
@@ -23363,7 +23375,7 @@
         <v>8.4</v>
       </c>
       <c r="H110" t="n">
-        <v>-33.3</v>
+        <v>-35.22</v>
       </c>
       <c r="I110" t="n">
         <v>-0.13</v>
@@ -23376,7 +23388,7 @@
         <v>-10.87</v>
       </c>
       <c r="M110" t="n">
-        <v>-37.26</v>
+        <v>-39.8</v>
       </c>
       <c r="N110" t="b">
         <v>1</v>
@@ -23414,7 +23426,7 @@
         <v>-7.3</v>
       </c>
       <c r="H111" t="n">
-        <v>-16.96</v>
+        <v>-16.13</v>
       </c>
       <c r="I111" t="n">
         <v>-4.12</v>
@@ -23427,7 +23439,7 @@
         <v>-15.02</v>
       </c>
       <c r="M111" t="n">
-        <v>-20.92</v>
+        <v>-20.71</v>
       </c>
       <c r="N111" t="b">
         <v>1</v>
@@ -23465,7 +23477,7 @@
         <v>-26.1</v>
       </c>
       <c r="H112" t="n">
-        <v>-25</v>
+        <v>-26.34</v>
       </c>
       <c r="I112" t="n">
         <v>5.05</v>
@@ -23478,7 +23490,7 @@
         <v>-9.27</v>
       </c>
       <c r="M112" t="n">
-        <v>-28.96</v>
+        <v>-30.93</v>
       </c>
       <c r="N112" t="b">
         <v>1</v>
@@ -23516,7 +23528,7 @@
         <v>26.1</v>
       </c>
       <c r="H113" t="n">
-        <v>-4.35</v>
+        <v>-3.83</v>
       </c>
       <c r="I113" t="n">
         <v>-0.51</v>
@@ -23529,7 +23541,7 @@
         <v>-16.45</v>
       </c>
       <c r="M113" t="n">
-        <v>-8.31</v>
+        <v>-8.41</v>
       </c>
       <c r="N113" t="b">
         <v>1</v>
@@ -23567,7 +23579,7 @@
         <v>17.9</v>
       </c>
       <c r="H114" t="n">
-        <v>3.2</v>
+        <v>3.49</v>
       </c>
       <c r="I114" t="n">
         <v>12.97</v>
@@ -23580,7 +23592,7 @@
         <v>-8.130000000000001</v>
       </c>
       <c r="M114" t="n">
-        <v>-0.76</v>
+        <v>-1.1</v>
       </c>
       <c r="N114" t="b">
         <v>1</v>
@@ -23618,7 +23630,7 @@
         <v>0.7</v>
       </c>
       <c r="H115" t="n">
-        <v>-20.99</v>
+        <v>-19.94</v>
       </c>
       <c r="I115" t="n">
         <v>14.96</v>
@@ -23631,7 +23643,7 @@
         <v>-8.039999999999999</v>
       </c>
       <c r="M115" t="n">
-        <v>-24.96</v>
+        <v>-24.52</v>
       </c>
       <c r="N115" t="b">
         <v>1</v>
@@ -23669,7 +23681,7 @@
         <v>14.8</v>
       </c>
       <c r="H116" t="n">
-        <v>-1.49</v>
+        <v>-2.16</v>
       </c>
       <c r="I116" t="n">
         <v>0.35</v>
@@ -23682,7 +23694,7 @@
         <v>-3.68</v>
       </c>
       <c r="M116" t="n">
-        <v>-5.45</v>
+        <v>-6.74</v>
       </c>
       <c r="N116" t="b">
         <v>1</v>
@@ -23720,7 +23732,7 @@
         <v>25.5</v>
       </c>
       <c r="H117" t="n">
-        <v>3.59</v>
+        <v>7.88</v>
       </c>
       <c r="I117" t="n">
         <v>-9.369999999999999</v>
@@ -23733,7 +23745,7 @@
         <v>-22.11</v>
       </c>
       <c r="M117" t="n">
-        <v>-0.37</v>
+        <v>3.3</v>
       </c>
       <c r="N117" t="b">
         <v>1</v>
@@ -23775,7 +23787,7 @@
         <v>-7.5</v>
       </c>
       <c r="H118" t="n">
-        <v>-12.93</v>
+        <v>-10.71</v>
       </c>
       <c r="I118" t="n">
         <v>4.46</v>
@@ -23788,7 +23800,7 @@
         <v>-8.52</v>
       </c>
       <c r="M118" t="n">
-        <v>-16.89</v>
+        <v>-15.3</v>
       </c>
       <c r="N118" t="b">
         <v>1</v>
@@ -23826,7 +23838,7 @@
         <v>-11</v>
       </c>
       <c r="H119" t="n">
-        <v>13.79</v>
+        <v>15.54</v>
       </c>
       <c r="I119" t="n">
         <v>10.7</v>
@@ -23839,7 +23851,7 @@
         <v>-9.43</v>
       </c>
       <c r="M119" t="n">
-        <v>9.83</v>
+        <v>10.96</v>
       </c>
       <c r="N119" t="b">
         <v>1</v>
@@ -23877,7 +23889,7 @@
         <v>-11.4</v>
       </c>
       <c r="H120" t="n">
-        <v>-18.78</v>
+        <v>-18.81</v>
       </c>
       <c r="I120" t="n">
         <v>4.36</v>
@@ -23890,7 +23902,7 @@
         <v>-11.36</v>
       </c>
       <c r="M120" t="n">
-        <v>-22.75</v>
+        <v>-23.39</v>
       </c>
       <c r="N120" t="b">
         <v>1</v>
@@ -23928,7 +23940,7 @@
         <v>27.1</v>
       </c>
       <c r="H121" t="n">
-        <v>-4.89</v>
+        <v>-4.07</v>
       </c>
       <c r="I121" t="n">
         <v>5.02</v>
@@ -23941,7 +23953,7 @@
         <v>-14.35</v>
       </c>
       <c r="M121" t="n">
-        <v>-8.85</v>
+        <v>-8.66</v>
       </c>
       <c r="N121" t="b">
         <v>1</v>
@@ -23979,7 +23991,7 @@
         <v>32.2</v>
       </c>
       <c r="H122" t="n">
-        <v>15.04</v>
+        <v>14.81</v>
       </c>
       <c r="I122" t="n">
         <v>6.49</v>
@@ -23992,7 +24004,7 @@
         <v>-3.92</v>
       </c>
       <c r="M122" t="n">
-        <v>11.08</v>
+        <v>10.23</v>
       </c>
       <c r="N122" t="b">
         <v>1</v>
@@ -24030,7 +24042,7 @@
         <v>3.2</v>
       </c>
       <c r="H123" t="n">
-        <v>-19.31</v>
+        <v>-19.11</v>
       </c>
       <c r="I123" t="n">
         <v>-10.41</v>
@@ -24043,7 +24055,7 @@
         <v>-23.7</v>
       </c>
       <c r="M123" t="n">
-        <v>-23.27</v>
+        <v>-23.69</v>
       </c>
       <c r="N123" t="b">
         <v>1</v>
@@ -24081,7 +24093,7 @@
         <v>7.3</v>
       </c>
       <c r="H124" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-1.32</v>
       </c>
       <c r="I124" t="n">
         <v>-0.57</v>
@@ -24094,7 +24106,7 @@
         <v>-5.89</v>
       </c>
       <c r="M124" t="n">
-        <v>-4.77</v>
+        <v>-5.9</v>
       </c>
       <c r="N124" t="b">
         <v>1</v>
@@ -24132,7 +24144,7 @@
         <v>-0.3</v>
       </c>
       <c r="H125" t="n">
-        <v>-1.92</v>
+        <v>-0.39</v>
       </c>
       <c r="I125" t="n">
         <v>17.76</v>
@@ -24145,7 +24157,7 @@
         <v>-14.18</v>
       </c>
       <c r="M125" t="n">
-        <v>-5.88</v>
+        <v>-4.98</v>
       </c>
       <c r="N125" t="b">
         <v>1</v>
@@ -24183,7 +24195,7 @@
         <v>-6.8</v>
       </c>
       <c r="H126" t="n">
-        <v>30.92</v>
+        <v>23.78</v>
       </c>
       <c r="I126" t="n">
         <v>8.279999999999999</v>
@@ -24196,7 +24208,7 @@
         <v>-6.78</v>
       </c>
       <c r="M126" t="n">
-        <v>26.96</v>
+        <v>19.2</v>
       </c>
       <c r="N126" t="b">
         <v>1</v>
@@ -24234,7 +24246,7 @@
         <v>34.6</v>
       </c>
       <c r="H127" t="n">
-        <v>-0.64</v>
+        <v>1.32</v>
       </c>
       <c r="I127" t="n">
         <v>5.7</v>
@@ -24247,7 +24259,7 @@
         <v>-7.7</v>
       </c>
       <c r="M127" t="n">
-        <v>-4.61</v>
+        <v>-3.27</v>
       </c>
       <c r="N127" t="b">
         <v>1</v>
@@ -24285,7 +24297,7 @@
         <v>10.4</v>
       </c>
       <c r="H128" t="n">
-        <v>32.02</v>
+        <v>34.76</v>
       </c>
       <c r="I128" t="n">
         <v>11.05</v>
@@ -24298,7 +24310,7 @@
         <v>-5.54</v>
       </c>
       <c r="M128" t="n">
-        <v>28.05</v>
+        <v>30.18</v>
       </c>
       <c r="N128" t="b">
         <v>1</v>
@@ -24336,7 +24348,7 @@
         <v>-21.5</v>
       </c>
       <c r="H129" t="n">
-        <v>-13.18</v>
+        <v>-12.99</v>
       </c>
       <c r="I129" t="n">
         <v>10.65</v>
@@ -24349,7 +24361,7 @@
         <v>-6.89</v>
       </c>
       <c r="M129" t="n">
-        <v>-17.14</v>
+        <v>-17.58</v>
       </c>
       <c r="N129" t="b">
         <v>1</v>
@@ -24387,7 +24399,7 @@
         <v>3.5</v>
       </c>
       <c r="H130" t="n">
-        <v>49.64</v>
+        <v>52.36</v>
       </c>
       <c r="I130" t="n">
         <v>33.01</v>
@@ -24400,7 +24412,7 @@
         <v>-0.92</v>
       </c>
       <c r="M130" t="n">
-        <v>45.67</v>
+        <v>47.77</v>
       </c>
       <c r="N130" t="b">
         <v>1</v>
@@ -24438,7 +24450,7 @@
         <v>19.8</v>
       </c>
       <c r="H131" t="n">
-        <v>15</v>
+        <v>17.48</v>
       </c>
       <c r="I131" t="n">
         <v>4.74</v>
@@ -24451,7 +24463,7 @@
         <v>-9.9</v>
       </c>
       <c r="M131" t="n">
-        <v>11.04</v>
+        <v>12.9</v>
       </c>
       <c r="N131" t="b">
         <v>1</v>
@@ -24489,7 +24501,7 @@
         <v>-30.5</v>
       </c>
       <c r="H132" t="n">
-        <v>-4.5</v>
+        <v>-0.38</v>
       </c>
       <c r="I132" t="n">
         <v>2.96</v>
@@ -24502,7 +24514,7 @@
         <v>-17.88</v>
       </c>
       <c r="M132" t="n">
-        <v>-8.460000000000001</v>
+        <v>-4.97</v>
       </c>
       <c r="N132" t="b">
         <v>1</v>
@@ -24540,7 +24552,7 @@
         <v>-6</v>
       </c>
       <c r="H133" t="n">
-        <v>-5.19</v>
+        <v>-5.4</v>
       </c>
       <c r="I133" t="n">
         <v>3.31</v>
@@ -24553,7 +24565,7 @@
         <v>-21.48</v>
       </c>
       <c r="M133" t="n">
-        <v>-9.15</v>
+        <v>-9.98</v>
       </c>
       <c r="N133" t="b">
         <v>1</v>
@@ -24591,7 +24603,7 @@
         <v>-34.6</v>
       </c>
       <c r="H134" t="n">
-        <v>0</v>
+        <v>-1.09</v>
       </c>
       <c r="I134" t="n">
         <v>23.65</v>
@@ -24604,7 +24616,7 @@
         <v>-3.83</v>
       </c>
       <c r="M134" t="n">
-        <v>-3.96</v>
+        <v>-5.68</v>
       </c>
       <c r="N134" t="b">
         <v>1</v>
@@ -24642,7 +24654,7 @@
         <v>-16.2</v>
       </c>
       <c r="H135" t="n">
-        <v>6.58</v>
+        <v>7.78</v>
       </c>
       <c r="I135" t="n">
         <v>25.77</v>
@@ -24655,7 +24667,7 @@
         <v>-1.7</v>
       </c>
       <c r="M135" t="n">
-        <v>2.62</v>
+        <v>3.19</v>
       </c>
       <c r="N135" t="b">
         <v>1</v>
@@ -24693,7 +24705,7 @@
         <v>-24.9</v>
       </c>
       <c r="H136" t="n">
-        <v>15.39</v>
+        <v>17.17</v>
       </c>
       <c r="I136" t="n">
         <v>10.88</v>
@@ -24706,7 +24718,7 @@
         <v>-4.1</v>
       </c>
       <c r="M136" t="n">
-        <v>11.43</v>
+        <v>12.58</v>
       </c>
       <c r="N136" t="b">
         <v>1</v>
@@ -24748,7 +24760,7 @@
         <v>-8.1</v>
       </c>
       <c r="H137" t="n">
-        <v>13.07</v>
+        <v>15.79</v>
       </c>
       <c r="I137" t="n">
         <v>14.27</v>
@@ -24761,7 +24773,7 @@
         <v>-10.92</v>
       </c>
       <c r="M137" t="n">
-        <v>9.109999999999999</v>
+        <v>11.21</v>
       </c>
       <c r="N137" t="b">
         <v>1</v>
@@ -24799,7 +24811,7 @@
         <v>-10.2</v>
       </c>
       <c r="H138" t="n">
-        <v>-11.88</v>
+        <v>-13.78</v>
       </c>
       <c r="I138" t="n">
         <v>15.03</v>
@@ -24812,7 +24824,7 @@
         <v>-1.61</v>
       </c>
       <c r="M138" t="n">
-        <v>-15.84</v>
+        <v>-18.36</v>
       </c>
       <c r="N138" t="b">
         <v>1</v>
@@ -24850,7 +24862,7 @@
         <v>68.90000000000001</v>
       </c>
       <c r="H139" t="n">
-        <v>38.6</v>
+        <v>30.73</v>
       </c>
       <c r="I139" t="n">
         <v>1.84</v>
@@ -24863,7 +24875,7 @@
         <v>-10.43</v>
       </c>
       <c r="M139" t="n">
-        <v>34.63</v>
+        <v>26.15</v>
       </c>
       <c r="N139" t="b">
         <v>1</v>
@@ -24901,7 +24913,7 @@
         <v>-40.8</v>
       </c>
       <c r="H140" t="n">
-        <v>-20.46</v>
+        <v>-21.36</v>
       </c>
       <c r="I140" t="n">
         <v>21.71</v>
@@ -24914,7 +24926,7 @@
         <v>-3.3</v>
       </c>
       <c r="M140" t="n">
-        <v>-24.42</v>
+        <v>-25.94</v>
       </c>
       <c r="N140" t="b">
         <v>1</v>
@@ -24952,7 +24964,7 @@
         <v>40.7</v>
       </c>
       <c r="H141" t="n">
-        <v>36.32</v>
+        <v>43.09</v>
       </c>
       <c r="I141" t="n">
         <v>-4.08</v>
@@ -24965,7 +24977,7 @@
         <v>-11.2</v>
       </c>
       <c r="M141" t="n">
-        <v>32.36</v>
+        <v>38.51</v>
       </c>
       <c r="N141" t="b">
         <v>1</v>
@@ -25003,7 +25015,7 @@
         <v>25.7</v>
       </c>
       <c r="H142" t="n">
-        <v>-5.08</v>
+        <v>-1.95</v>
       </c>
       <c r="I142" t="n">
         <v>11.3</v>
@@ -25016,7 +25028,7 @@
         <v>-11.03</v>
       </c>
       <c r="M142" t="n">
-        <v>-9.039999999999999</v>
+        <v>-6.53</v>
       </c>
       <c r="N142" t="b">
         <v>1</v>

--- a/STS_holy_grail_v2.xlsx
+++ b/STS_holy_grail_v2.xlsx
@@ -464,7 +464,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.75</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="5">
@@ -474,7 +474,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.71</v>
+        <v>-0.5600000000000001</v>
       </c>
     </row>
     <row r="6">
@@ -550,13 +550,13 @@
         <v>79</v>
       </c>
       <c r="C11" t="n">
-        <v>1.91</v>
+        <v>2.52</v>
       </c>
       <c r="D11" t="n">
         <v>45.57</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.31</v>
+        <v>-1.72</v>
       </c>
     </row>
     <row r="12">
@@ -569,13 +569,13 @@
         <v>155</v>
       </c>
       <c r="C12" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="D12" t="n">
         <v>41.94</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.3</v>
+        <v>-2.29</v>
       </c>
     </row>
     <row r="13">
@@ -641,13 +641,13 @@
         <v>111</v>
       </c>
       <c r="C17" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="D17" t="n">
         <v>42.34</v>
       </c>
       <c r="E17" t="n">
-        <v>-2.03</v>
+        <v>-2.01</v>
       </c>
     </row>
     <row r="18">
@@ -717,13 +717,13 @@
         <v>88</v>
       </c>
       <c r="C21" t="n">
-        <v>10.39</v>
+        <v>10.94</v>
       </c>
       <c r="D21" t="n">
         <v>67.05</v>
       </c>
       <c r="E21" t="n">
-        <v>6.76</v>
+        <v>7.29</v>
       </c>
     </row>
     <row r="23">
@@ -861,13 +861,13 @@
         <v>190</v>
       </c>
       <c r="C31" t="n">
-        <v>3.89</v>
+        <v>4.15</v>
       </c>
       <c r="D31" t="n">
         <v>47.37</v>
       </c>
       <c r="E31" t="n">
-        <v>0.45</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="32">
@@ -880,7 +880,7 @@
         <v>141</v>
       </c>
       <c r="C32" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="D32" t="n">
         <v>49.65</v>
@@ -1016,7 +1016,7 @@
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="n">
-        <v>-1.96</v>
+        <v>-1.95</v>
       </c>
       <c r="M2" t="n">
         <v>-2.26</v>
@@ -2013,7 +2013,7 @@
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="n">
-        <v>-9.34</v>
+        <v>-9.369999999999999</v>
       </c>
       <c r="M23" t="n">
         <v>-8.869999999999999</v>
@@ -2552,7 +2552,7 @@
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="n">
-        <v>-6.82</v>
+        <v>-6.81</v>
       </c>
       <c r="M34" t="n">
         <v>-8.220000000000001</v>
@@ -3985,7 +3985,7 @@
         <v>-11</v>
       </c>
       <c r="H63" t="n">
-        <v>4.49</v>
+        <v>5.22</v>
       </c>
       <c r="I63" t="n">
         <v>-8.449999999999999</v>
@@ -3998,7 +3998,7 @@
         <v>-18.92</v>
       </c>
       <c r="M63" t="n">
-        <v>3</v>
+        <v>3.73</v>
       </c>
       <c r="N63" t="b">
         <v>0</v>
@@ -4138,7 +4138,7 @@
         <v>-17.7</v>
       </c>
       <c r="H66" t="n">
-        <v>-1.47</v>
+        <v>-0.88</v>
       </c>
       <c r="I66" t="n">
         <v>-0.89</v>
@@ -4151,7 +4151,7 @@
         <v>-11.37</v>
       </c>
       <c r="M66" t="n">
-        <v>-3.11</v>
+        <v>-2.52</v>
       </c>
       <c r="N66" t="b">
         <v>0</v>
@@ -9933,7 +9933,7 @@
         <v>49.6</v>
       </c>
       <c r="H179" t="n">
-        <v>33.92</v>
+        <v>33.95</v>
       </c>
       <c r="I179" t="n">
         <v>6.34</v>
@@ -9946,7 +9946,7 @@
         <v>-20.75</v>
       </c>
       <c r="M179" t="n">
-        <v>29.33</v>
+        <v>29.36</v>
       </c>
       <c r="N179" t="b">
         <v>0</v>
@@ -10188,7 +10188,7 @@
         <v>32.1</v>
       </c>
       <c r="H184" t="n">
-        <v>13.81</v>
+        <v>14.51</v>
       </c>
       <c r="I184" t="n">
         <v>16.93</v>
@@ -10201,7 +10201,7 @@
         <v>-24.48</v>
       </c>
       <c r="M184" t="n">
-        <v>9.85</v>
+        <v>9.93</v>
       </c>
       <c r="N184" t="b">
         <v>1</v>
@@ -11004,7 +11004,7 @@
         <v>36.6</v>
       </c>
       <c r="H200" t="n">
-        <v>231.04</v>
+        <v>278.09</v>
       </c>
       <c r="I200" t="n">
         <v>-4.23</v>
@@ -11017,7 +11017,7 @@
         <v>-11.51</v>
       </c>
       <c r="M200" t="n">
-        <v>227.08</v>
+        <v>273.5</v>
       </c>
       <c r="N200" t="b">
         <v>0</v>
@@ -12130,7 +12130,7 @@
         <v>-29.8</v>
       </c>
       <c r="H222" t="n">
-        <v>71.54000000000001</v>
+        <v>71.56</v>
       </c>
       <c r="I222" t="n">
         <v>29.88</v>
@@ -12143,7 +12143,7 @@
         <v>-0.29</v>
       </c>
       <c r="M222" t="n">
-        <v>66.95</v>
+        <v>66.97</v>
       </c>
       <c r="N222" t="b">
         <v>0</v>
@@ -13001,7 +13001,7 @@
         <v>-35.9</v>
       </c>
       <c r="H239" t="n">
-        <v>15.14</v>
+        <v>15.56</v>
       </c>
       <c r="I239" t="n">
         <v>18.67</v>
@@ -13014,7 +13014,7 @@
         <v>-6.77</v>
       </c>
       <c r="M239" t="n">
-        <v>10.55</v>
+        <v>10.98</v>
       </c>
       <c r="N239" t="b">
         <v>0</v>
@@ -14331,7 +14331,7 @@
         <v>36.8</v>
       </c>
       <c r="H265" t="n">
-        <v>43.77</v>
+        <v>44.1</v>
       </c>
       <c r="I265" t="n">
         <v>15.47</v>
@@ -14344,7 +14344,7 @@
         <v>-0.96</v>
       </c>
       <c r="M265" t="n">
-        <v>39.19</v>
+        <v>39.51</v>
       </c>
       <c r="N265" t="b">
         <v>0</v>
@@ -14539,7 +14539,7 @@
         <v>12.2</v>
       </c>
       <c r="H269" t="n">
-        <v>-37.36</v>
+        <v>-37.33</v>
       </c>
       <c r="I269" t="n">
         <v>3.47</v>
@@ -14552,7 +14552,7 @@
         <v>-27.15</v>
       </c>
       <c r="M269" t="n">
-        <v>-41.95</v>
+        <v>-41.91</v>
       </c>
       <c r="N269" t="b">
         <v>0</v>
@@ -18352,7 +18352,7 @@
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="n">
-        <v>-9.34</v>
+        <v>-9.369999999999999</v>
       </c>
       <c r="M11" t="n">
         <v>-8.869999999999999</v>
@@ -18499,7 +18499,7 @@
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="n">
-        <v>-6.82</v>
+        <v>-6.81</v>
       </c>
       <c r="M14" t="n">
         <v>-8.220000000000001</v>
@@ -21433,7 +21433,7 @@
         <v>32.1</v>
       </c>
       <c r="H72" t="n">
-        <v>13.81</v>
+        <v>14.51</v>
       </c>
       <c r="I72" t="n">
         <v>16.93</v>
@@ -21446,7 +21446,7 @@
         <v>-24.48</v>
       </c>
       <c r="M72" t="n">
-        <v>9.85</v>
+        <v>9.93</v>
       </c>
       <c r="N72" t="b">
         <v>1</v>

--- a/STS_holy_grail_v2.xlsx
+++ b/STS_holy_grail_v2.xlsx
@@ -464,7 +464,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.98</v>
+        <v>0.82</v>
       </c>
     </row>
     <row r="5">
@@ -474,7 +474,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-3.24</v>
+        <v>-1.72</v>
       </c>
     </row>
     <row r="6">
@@ -484,7 +484,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>42</v>
+        <v>48.9</v>
       </c>
     </row>
     <row r="8">
@@ -531,13 +531,13 @@
         <v>64</v>
       </c>
       <c r="C10" t="n">
-        <v>0.91</v>
+        <v>1.36</v>
       </c>
       <c r="D10" t="n">
-        <v>57.81</v>
+        <v>60.94</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.06</v>
+        <v>-0.9</v>
       </c>
     </row>
     <row r="11">
@@ -550,13 +550,13 @@
         <v>79</v>
       </c>
       <c r="C11" t="n">
-        <v>-4.46</v>
+        <v>-3.72</v>
       </c>
       <c r="D11" t="n">
-        <v>26.58</v>
+        <v>29.11</v>
       </c>
       <c r="E11" t="n">
-        <v>-7.49</v>
+        <v>-7.04</v>
       </c>
     </row>
     <row r="12">
@@ -569,13 +569,13 @@
         <v>156</v>
       </c>
       <c r="C12" t="n">
-        <v>-2.08</v>
+        <v>1.13</v>
       </c>
       <c r="D12" t="n">
-        <v>37.18</v>
+        <v>48.72</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.28</v>
+        <v>-1.36</v>
       </c>
     </row>
     <row r="13">
@@ -588,13 +588,13 @@
         <v>34</v>
       </c>
       <c r="C13" t="n">
-        <v>8.539999999999999</v>
+        <v>8.94</v>
       </c>
       <c r="D13" t="n">
-        <v>70.59</v>
+        <v>73.53</v>
       </c>
       <c r="E13" t="n">
-        <v>7.35</v>
+        <v>7.48</v>
       </c>
     </row>
     <row r="15">
@@ -641,13 +641,13 @@
         <v>111</v>
       </c>
       <c r="C17" t="n">
-        <v>-1.78</v>
+        <v>1.5</v>
       </c>
       <c r="D17" t="n">
-        <v>37.84</v>
+        <v>47.75</v>
       </c>
       <c r="E17" t="n">
-        <v>-4.07</v>
+        <v>-1.07</v>
       </c>
     </row>
     <row r="18">
@@ -660,13 +660,13 @@
         <v>48</v>
       </c>
       <c r="C18" t="n">
-        <v>-2.62</v>
+        <v>0.35</v>
       </c>
       <c r="D18" t="n">
-        <v>37.5</v>
+        <v>52.08</v>
       </c>
       <c r="E18" t="n">
-        <v>-4.46</v>
+        <v>-1.76</v>
       </c>
     </row>
     <row r="19">
@@ -679,13 +679,13 @@
         <v>45</v>
       </c>
       <c r="C19" t="n">
-        <v>-3.61</v>
+        <v>-0.51</v>
       </c>
       <c r="D19" t="n">
-        <v>33.33</v>
+        <v>44.44</v>
       </c>
       <c r="E19" t="n">
-        <v>-5.91</v>
+        <v>-3.1</v>
       </c>
     </row>
     <row r="20">
@@ -698,13 +698,13 @@
         <v>40</v>
       </c>
       <c r="C20" t="n">
-        <v>-6.93</v>
+        <v>-6.51</v>
       </c>
       <c r="D20" t="n">
         <v>37.5</v>
       </c>
       <c r="E20" t="n">
-        <v>-9.18</v>
+        <v>-9.029999999999999</v>
       </c>
     </row>
     <row r="21">
@@ -717,13 +717,13 @@
         <v>89</v>
       </c>
       <c r="C21" t="n">
-        <v>4.9</v>
+        <v>4.2</v>
       </c>
       <c r="D21" t="n">
         <v>56.18</v>
       </c>
       <c r="E21" t="n">
-        <v>2.48</v>
+        <v>1.49</v>
       </c>
     </row>
     <row r="23">
@@ -770,13 +770,13 @@
         <v>10</v>
       </c>
       <c r="C25" t="n">
-        <v>9.15</v>
+        <v>14.48</v>
       </c>
       <c r="D25" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="E25" t="n">
-        <v>6.28</v>
+        <v>11.32</v>
       </c>
     </row>
     <row r="26">
@@ -789,13 +789,13 @@
         <v>5</v>
       </c>
       <c r="C26" t="n">
-        <v>-5.46</v>
+        <v>-1.74</v>
       </c>
       <c r="D26" t="n">
         <v>40</v>
       </c>
       <c r="E26" t="n">
-        <v>-9.039999999999999</v>
+        <v>-5.61</v>
       </c>
     </row>
     <row r="27">
@@ -808,13 +808,13 @@
         <v>3</v>
       </c>
       <c r="C27" t="n">
-        <v>10.53</v>
+        <v>16.65</v>
       </c>
       <c r="D27" t="n">
         <v>66.67</v>
       </c>
       <c r="E27" t="n">
-        <v>7.98</v>
+        <v>13.81</v>
       </c>
     </row>
     <row r="29">
@@ -861,13 +861,13 @@
         <v>191</v>
       </c>
       <c r="C31" t="n">
-        <v>0.22</v>
+        <v>2.41</v>
       </c>
       <c r="D31" t="n">
-        <v>42.41</v>
+        <v>50.79</v>
       </c>
       <c r="E31" t="n">
-        <v>-2.02</v>
+        <v>-0.12</v>
       </c>
     </row>
     <row r="32">
@@ -880,13 +880,13 @@
         <v>142</v>
       </c>
       <c r="C32" t="n">
-        <v>-2.6</v>
+        <v>-1.32</v>
       </c>
       <c r="D32" t="n">
-        <v>41.55</v>
+        <v>46.48</v>
       </c>
       <c r="E32" t="n">
-        <v>-4.87</v>
+        <v>-3.87</v>
       </c>
     </row>
   </sheetData>
@@ -1010,7 +1010,7 @@
         <v>-9.4</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
@@ -1019,7 +1019,7 @@
         <v>-1.66</v>
       </c>
       <c r="M2" t="n">
-        <v>0.6899999999999999</v>
+        <v>2.86</v>
       </c>
       <c r="N2" t="b">
         <v>0</v>
@@ -1057,16 +1057,16 @@
         <v>51.4</v>
       </c>
       <c r="H3" t="n">
-        <v>-2.18</v>
+        <v>-1.95</v>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="n">
-        <v>-2.32</v>
+        <v>-4.91</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.19</v>
+        <v>-1.24</v>
       </c>
       <c r="N3" t="b">
         <v>1</v>
@@ -1104,7 +1104,7 @@
         <v>-24.3</v>
       </c>
       <c r="H4" t="n">
-        <v>-2.82</v>
+        <v>-1.07</v>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
@@ -1113,7 +1113,7 @@
         <v>-3.62</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.14</v>
+        <v>-0.68</v>
       </c>
       <c r="N4" t="b">
         <v>0</v>
@@ -1151,16 +1151,16 @@
         <v>-22.1</v>
       </c>
       <c r="H5" t="n">
-        <v>-6.19</v>
+        <v>-4.32</v>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="n">
-        <v>-6.79</v>
+        <v>-9.27</v>
       </c>
       <c r="M5" t="n">
-        <v>-5.51</v>
+        <v>-3.92</v>
       </c>
       <c r="N5" t="b">
         <v>0</v>
@@ -1198,7 +1198,7 @@
         <v>-16.6</v>
       </c>
       <c r="H6" t="n">
-        <v>3.76</v>
+        <v>3.33</v>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
@@ -1207,7 +1207,7 @@
         <v>-1.04</v>
       </c>
       <c r="M6" t="n">
-        <v>4.55</v>
+        <v>3.84</v>
       </c>
       <c r="N6" t="b">
         <v>1</v>
@@ -1245,7 +1245,7 @@
         <v>-7.4</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.15</v>
+        <v>0.98</v>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
@@ -1254,7 +1254,7 @@
         <v>-2.54</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.35</v>
+        <v>1.5</v>
       </c>
       <c r="N7" t="b">
         <v>0</v>
@@ -1281,7 +1281,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Extended</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
@@ -1292,7 +1292,7 @@
         <v>-5</v>
       </c>
       <c r="H8" t="n">
-        <v>4.03</v>
+        <v>6.54</v>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
@@ -1301,7 +1301,7 @@
         <v>-1.75</v>
       </c>
       <c r="M8" t="n">
-        <v>4.82</v>
+        <v>7.05</v>
       </c>
       <c r="N8" t="b">
         <v>1</v>
@@ -1328,7 +1328,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Extended</t>
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
@@ -1339,7 +1339,7 @@
         <v>12.5</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.3</v>
+        <v>7.42</v>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
@@ -1348,7 +1348,7 @@
         <v>-2.59</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.51</v>
+        <v>7.93</v>
       </c>
       <c r="N9" t="b">
         <v>1</v>
@@ -1386,7 +1386,7 @@
         <v>-1.1</v>
       </c>
       <c r="H10" t="n">
-        <v>6.81</v>
+        <v>9.19</v>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
@@ -1395,7 +1395,7 @@
         <v>-0.36</v>
       </c>
       <c r="M10" t="n">
-        <v>7.61</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="N10" t="b">
         <v>0</v>
@@ -1433,7 +1433,7 @@
         <v>-17.3</v>
       </c>
       <c r="H11" t="n">
-        <v>-4.51</v>
+        <v>0.87</v>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
@@ -1442,7 +1442,7 @@
         <v>-6.51</v>
       </c>
       <c r="M11" t="n">
-        <v>-3.41</v>
+        <v>1.69</v>
       </c>
       <c r="N11" t="b">
         <v>1</v>
@@ -1469,7 +1469,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Extended</t>
         </is>
       </c>
       <c r="E12" t="inlineStr"/>
@@ -1480,7 +1480,7 @@
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>4.14</v>
+        <v>6.66</v>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
@@ -1489,7 +1489,7 @@
         <v>-1.46</v>
       </c>
       <c r="M12" t="n">
-        <v>5.23</v>
+        <v>7.48</v>
       </c>
       <c r="N12" t="b">
         <v>0</v>
@@ -1516,7 +1516,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Extended</t>
         </is>
       </c>
       <c r="E13" t="inlineStr"/>
@@ -1527,7 +1527,7 @@
         <v>-29.3</v>
       </c>
       <c r="H13" t="n">
-        <v>4.38</v>
+        <v>9.82</v>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
@@ -1536,7 +1536,7 @@
         <v>-3.13</v>
       </c>
       <c r="M13" t="n">
-        <v>4.39</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="N13" t="b">
         <v>0</v>
@@ -1574,7 +1574,7 @@
         <v>-21.8</v>
       </c>
       <c r="H14" t="n">
-        <v>-3.37</v>
+        <v>0.36</v>
       </c>
       <c r="I14" t="n">
         <v>-3.37</v>
@@ -1585,7 +1585,7 @@
         <v>-5.33</v>
       </c>
       <c r="M14" t="n">
-        <v>-3.78</v>
+        <v>-0.33</v>
       </c>
       <c r="N14" t="b">
         <v>1</v>
@@ -1623,7 +1623,7 @@
         <v>-15</v>
       </c>
       <c r="H15" t="n">
-        <v>12.26</v>
+        <v>17.08</v>
       </c>
       <c r="I15" t="n">
         <v>12.31</v>
@@ -1634,7 +1634,7 @@
         <v>-4.06</v>
       </c>
       <c r="M15" t="n">
-        <v>11.9</v>
+        <v>16.43</v>
       </c>
       <c r="N15" t="b">
         <v>0</v>
@@ -1672,7 +1672,7 @@
         <v>-16.7</v>
       </c>
       <c r="H16" t="n">
-        <v>24.91</v>
+        <v>29.93</v>
       </c>
       <c r="I16" t="n">
         <v>26.03</v>
@@ -1683,7 +1683,7 @@
         <v>-6.98</v>
       </c>
       <c r="M16" t="n">
-        <v>24.55</v>
+        <v>29.29</v>
       </c>
       <c r="N16" t="b">
         <v>1</v>
@@ -1721,7 +1721,7 @@
         <v>-26.8</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.59</v>
+        <v>1.85</v>
       </c>
       <c r="I17" t="n">
         <v>1.39</v>
@@ -1732,7 +1732,7 @@
         <v>-5.1</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.95</v>
+        <v>1.21</v>
       </c>
       <c r="N17" t="b">
         <v>0</v>
@@ -1770,7 +1770,7 @@
         <v>-35.9</v>
       </c>
       <c r="H18" t="n">
-        <v>-6.22</v>
+        <v>-3.1</v>
       </c>
       <c r="I18" t="n">
         <v>-6.92</v>
@@ -1781,7 +1781,7 @@
         <v>-7.58</v>
       </c>
       <c r="M18" t="n">
-        <v>-6.58</v>
+        <v>-3.74</v>
       </c>
       <c r="N18" t="b">
         <v>0</v>
@@ -1819,7 +1819,7 @@
         <v>-7.1</v>
       </c>
       <c r="H19" t="n">
-        <v>7.24</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="I19" t="n">
         <v>9.390000000000001</v>
@@ -1830,7 +1830,7 @@
         <v>-2.71</v>
       </c>
       <c r="M19" t="n">
-        <v>6.88</v>
+        <v>7.63</v>
       </c>
       <c r="N19" t="b">
         <v>0</v>
@@ -1868,7 +1868,7 @@
         <v>-11.5</v>
       </c>
       <c r="H20" t="n">
-        <v>8.720000000000001</v>
+        <v>14.06</v>
       </c>
       <c r="I20" t="n">
         <v>7.47</v>
@@ -1879,7 +1879,7 @@
         <v>-0.99</v>
       </c>
       <c r="M20" t="n">
-        <v>8.359999999999999</v>
+        <v>13.41</v>
       </c>
       <c r="N20" t="b">
         <v>1</v>
@@ -1917,7 +1917,7 @@
         <v>0.1</v>
       </c>
       <c r="H21" t="n">
-        <v>11.28</v>
+        <v>14.47</v>
       </c>
       <c r="I21" t="n">
         <v>6.41</v>
@@ -1928,7 +1928,7 @@
         <v>-2.51</v>
       </c>
       <c r="M21" t="n">
-        <v>11.18</v>
+        <v>14.08</v>
       </c>
       <c r="N21" t="b">
         <v>1</v>
@@ -1966,7 +1966,7 @@
         <v>-31.6</v>
       </c>
       <c r="H22" t="n">
-        <v>-5.47</v>
+        <v>-3.91</v>
       </c>
       <c r="I22" t="n">
         <v>-2.12</v>
@@ -1977,7 +1977,7 @@
         <v>-8.140000000000001</v>
       </c>
       <c r="M22" t="n">
-        <v>-5.58</v>
+        <v>-4.3</v>
       </c>
       <c r="N22" t="b">
         <v>1</v>
@@ -2004,7 +2004,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Extended</t>
         </is>
       </c>
       <c r="E23" t="inlineStr"/>
@@ -2015,7 +2015,7 @@
         <v>7.6</v>
       </c>
       <c r="H23" t="n">
-        <v>3.83</v>
+        <v>9.56</v>
       </c>
       <c r="I23" t="n">
         <v>-3.6</v>
@@ -2026,7 +2026,7 @@
         <v>-9.359999999999999</v>
       </c>
       <c r="M23" t="n">
-        <v>3.11</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="N23" t="b">
         <v>0</v>
@@ -2064,7 +2064,7 @@
         <v>-17.9</v>
       </c>
       <c r="H24" t="n">
-        <v>-13.64</v>
+        <v>-11.13</v>
       </c>
       <c r="I24" t="n">
         <v>-6.13</v>
@@ -2075,7 +2075,7 @@
         <v>-14.51</v>
       </c>
       <c r="M24" t="n">
-        <v>-13.07</v>
+        <v>-10.84</v>
       </c>
       <c r="N24" t="b">
         <v>0</v>
@@ -2113,7 +2113,7 @@
         <v>-2.7</v>
       </c>
       <c r="H25" t="n">
-        <v>-10.61</v>
+        <v>-8.66</v>
       </c>
       <c r="I25" t="n">
         <v>-3.77</v>
@@ -2124,7 +2124,7 @@
         <v>-12.44</v>
       </c>
       <c r="M25" t="n">
-        <v>-10.04</v>
+        <v>-8.369999999999999</v>
       </c>
       <c r="N25" t="b">
         <v>1</v>
@@ -2151,7 +2151,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Extended</t>
         </is>
       </c>
       <c r="E26" t="inlineStr"/>
@@ -2162,7 +2162,7 @@
         <v>-25.3</v>
       </c>
       <c r="H26" t="n">
-        <v>1.24</v>
+        <v>5.88</v>
       </c>
       <c r="I26" t="n">
         <v>4.1</v>
@@ -2173,7 +2173,7 @@
         <v>-0.92</v>
       </c>
       <c r="M26" t="n">
-        <v>1.81</v>
+        <v>6.17</v>
       </c>
       <c r="N26" t="b">
         <v>0</v>
@@ -2211,7 +2211,7 @@
         <v>25.6</v>
       </c>
       <c r="H27" t="n">
-        <v>8.140000000000001</v>
+        <v>8.68</v>
       </c>
       <c r="I27" t="n">
         <v>-0.42</v>
@@ -2222,7 +2222,7 @@
         <v>-8.35</v>
       </c>
       <c r="M27" t="n">
-        <v>8.710000000000001</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="N27" t="b">
         <v>0</v>
@@ -2260,7 +2260,7 @@
         <v>26.9</v>
       </c>
       <c r="H28" t="n">
-        <v>-1.39</v>
+        <v>1.91</v>
       </c>
       <c r="I28" t="n">
         <v>-3.24</v>
@@ -2271,7 +2271,7 @@
         <v>-12.88</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.82</v>
+        <v>2.2</v>
       </c>
       <c r="N28" t="b">
         <v>1</v>
@@ -2309,7 +2309,7 @@
         <v>-14.5</v>
       </c>
       <c r="H29" t="n">
-        <v>-3.43</v>
+        <v>-3.47</v>
       </c>
       <c r="I29" t="n">
         <v>-3.75</v>
@@ -2320,7 +2320,7 @@
         <v>-9.01</v>
       </c>
       <c r="M29" t="n">
-        <v>-3.87</v>
+        <v>-4.19</v>
       </c>
       <c r="N29" t="b">
         <v>0</v>
@@ -2358,7 +2358,7 @@
         <v>17.2</v>
       </c>
       <c r="H30" t="n">
-        <v>0.3</v>
+        <v>4.63</v>
       </c>
       <c r="I30" t="n">
         <v>-1.49</v>
@@ -2369,7 +2369,7 @@
         <v>-10.54</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.14</v>
+        <v>3.91</v>
       </c>
       <c r="N30" t="b">
         <v>0</v>
@@ -2407,7 +2407,7 @@
         <v>-13.2</v>
       </c>
       <c r="H31" t="n">
-        <v>15.3</v>
+        <v>13.53</v>
       </c>
       <c r="I31" t="n">
         <v>23.71</v>
@@ -2418,7 +2418,7 @@
         <v>-0.82</v>
       </c>
       <c r="M31" t="n">
-        <v>14.87</v>
+        <v>12.8</v>
       </c>
       <c r="N31" t="b">
         <v>0</v>
@@ -2456,7 +2456,7 @@
         <v>-7.7</v>
       </c>
       <c r="H32" t="n">
-        <v>-10.09</v>
+        <v>-3.89</v>
       </c>
       <c r="I32" t="n">
         <v>-9.67</v>
@@ -2467,7 +2467,7 @@
         <v>-12.32</v>
       </c>
       <c r="M32" t="n">
-        <v>-10.53</v>
+        <v>-4.61</v>
       </c>
       <c r="N32" t="b">
         <v>0</v>
@@ -2505,7 +2505,7 @@
         <v>-18.1</v>
       </c>
       <c r="H33" t="n">
-        <v>2.02</v>
+        <v>3.23</v>
       </c>
       <c r="I33" t="n">
         <v>-2.43</v>
@@ -2516,7 +2516,7 @@
         <v>-6.41</v>
       </c>
       <c r="M33" t="n">
-        <v>1.58</v>
+        <v>2.51</v>
       </c>
       <c r="N33" t="b">
         <v>0</v>
@@ -2554,7 +2554,7 @@
         <v>-18.1</v>
       </c>
       <c r="H34" t="n">
-        <v>10.59</v>
+        <v>13.98</v>
       </c>
       <c r="I34" t="n">
         <v>4.46</v>
@@ -2565,7 +2565,7 @@
         <v>-2.69</v>
       </c>
       <c r="M34" t="n">
-        <v>10.16</v>
+        <v>13.26</v>
       </c>
       <c r="N34" t="b">
         <v>1</v>
@@ -2603,7 +2603,7 @@
         <v>7.7</v>
       </c>
       <c r="H35" t="n">
-        <v>-1.65</v>
+        <v>4.5</v>
       </c>
       <c r="I35" t="n">
         <v>-6.85</v>
@@ -2614,7 +2614,7 @@
         <v>-9.359999999999999</v>
       </c>
       <c r="M35" t="n">
-        <v>-2.08</v>
+        <v>3.78</v>
       </c>
       <c r="N35" t="b">
         <v>0</v>
@@ -2652,7 +2652,7 @@
         <v>-21.5</v>
       </c>
       <c r="H36" t="n">
-        <v>-4.27</v>
+        <v>2.32</v>
       </c>
       <c r="I36" t="n">
         <v>-1.68</v>
@@ -2663,7 +2663,7 @@
         <v>-8.130000000000001</v>
       </c>
       <c r="M36" t="n">
-        <v>-4.71</v>
+        <v>1.6</v>
       </c>
       <c r="N36" t="b">
         <v>1</v>
@@ -2690,7 +2690,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Retired</t>
         </is>
       </c>
       <c r="E37" t="inlineStr"/>
@@ -2701,7 +2701,7 @@
         <v>41.6</v>
       </c>
       <c r="H37" t="n">
-        <v>3.84</v>
+        <v>5.6</v>
       </c>
       <c r="I37" t="n">
         <v>3.43</v>
@@ -2712,7 +2712,7 @@
         <v>-4.38</v>
       </c>
       <c r="M37" t="n">
-        <v>2.75</v>
+        <v>4.23</v>
       </c>
       <c r="N37" t="b">
         <v>1</v>
@@ -2739,7 +2739,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Retired</t>
         </is>
       </c>
       <c r="E38" t="inlineStr"/>
@@ -2750,7 +2750,7 @@
         <v>32.1</v>
       </c>
       <c r="H38" t="n">
-        <v>4.05</v>
+        <v>7.32</v>
       </c>
       <c r="I38" t="n">
         <v>-3.47</v>
@@ -2761,7 +2761,7 @@
         <v>-6.94</v>
       </c>
       <c r="M38" t="n">
-        <v>2.96</v>
+        <v>5.94</v>
       </c>
       <c r="N38" t="b">
         <v>1</v>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Retired</t>
         </is>
       </c>
       <c r="E39" t="inlineStr"/>
@@ -2799,7 +2799,7 @@
         <v>-14.4</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.72</v>
+        <v>1.16</v>
       </c>
       <c r="I39" t="n">
         <v>-2.38</v>
@@ -2810,7 +2810,7 @@
         <v>-6.46</v>
       </c>
       <c r="M39" t="n">
-        <v>-2.81</v>
+        <v>-0.21</v>
       </c>
       <c r="N39" t="b">
         <v>1</v>
@@ -2837,7 +2837,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Retired</t>
         </is>
       </c>
       <c r="E40" t="inlineStr"/>
@@ -2848,7 +2848,7 @@
         <v>-16.8</v>
       </c>
       <c r="H40" t="n">
-        <v>-5.42</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="I40" t="n">
         <v>1.99</v>
@@ -2859,7 +2859,7 @@
         <v>-7.67</v>
       </c>
       <c r="M40" t="n">
-        <v>-6.51</v>
+        <v>-1.45</v>
       </c>
       <c r="N40" t="b">
         <v>0</v>
@@ -2886,7 +2886,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Retired</t>
         </is>
       </c>
       <c r="E41" t="inlineStr"/>
@@ -2897,7 +2897,7 @@
         <v>-10</v>
       </c>
       <c r="H41" t="n">
-        <v>-12.1</v>
+        <v>-8.07</v>
       </c>
       <c r="I41" t="n">
         <v>-3.29</v>
@@ -2908,7 +2908,7 @@
         <v>-14.66</v>
       </c>
       <c r="M41" t="n">
-        <v>-13.19</v>
+        <v>-9.44</v>
       </c>
       <c r="N41" t="b">
         <v>1</v>
@@ -2935,7 +2935,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Extended</t>
+          <t>Retired</t>
         </is>
       </c>
       <c r="E42" t="inlineStr"/>
@@ -2946,7 +2946,7 @@
         <v>6.4</v>
       </c>
       <c r="H42" t="n">
-        <v>6.05</v>
+        <v>10.98</v>
       </c>
       <c r="I42" t="n">
         <v>1.48</v>
@@ -2957,7 +2957,7 @@
         <v>-3.35</v>
       </c>
       <c r="M42" t="n">
-        <v>4.96</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="N42" t="b">
         <v>1</v>
@@ -2995,18 +2995,20 @@
         <v>-11</v>
       </c>
       <c r="H43" t="n">
-        <v>47.64</v>
+        <v>47.26</v>
       </c>
       <c r="I43" t="n">
         <v>11.67</v>
       </c>
-      <c r="J43" t="inlineStr"/>
+      <c r="J43" t="n">
+        <v>47.26</v>
+      </c>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="n">
         <v>-0.97</v>
       </c>
       <c r="M43" t="n">
-        <v>46.54</v>
+        <v>45.88</v>
       </c>
       <c r="N43" t="b">
         <v>0</v>
@@ -3044,18 +3046,20 @@
         <v>-23.9</v>
       </c>
       <c r="H44" t="n">
-        <v>-4.68</v>
+        <v>-2.11</v>
       </c>
       <c r="I44" t="n">
         <v>-4.98</v>
       </c>
-      <c r="J44" t="inlineStr"/>
+      <c r="J44" t="n">
+        <v>-2.11</v>
+      </c>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="n">
         <v>-7.87</v>
       </c>
       <c r="M44" t="n">
-        <v>-5.78</v>
+        <v>-3.49</v>
       </c>
       <c r="N44" t="b">
         <v>0</v>
@@ -3097,18 +3101,20 @@
         <v>-9.800000000000001</v>
       </c>
       <c r="H45" t="n">
-        <v>5.66</v>
+        <v>12.07</v>
       </c>
       <c r="I45" t="n">
         <v>-3.41</v>
       </c>
-      <c r="J45" t="inlineStr"/>
+      <c r="J45" t="n">
+        <v>12.07</v>
+      </c>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="n">
         <v>-8.949999999999999</v>
       </c>
       <c r="M45" t="n">
-        <v>4.56</v>
+        <v>10.68</v>
       </c>
       <c r="N45" t="b">
         <v>0</v>
@@ -3146,18 +3152,20 @@
         <v>-36.1</v>
       </c>
       <c r="H46" t="n">
-        <v>-3.22</v>
+        <v>1.92</v>
       </c>
       <c r="I46" t="n">
         <v>-1.4</v>
       </c>
-      <c r="J46" t="inlineStr"/>
+      <c r="J46" t="n">
+        <v>1.92</v>
+      </c>
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="n">
         <v>-7.04</v>
       </c>
       <c r="M46" t="n">
-        <v>-4.32</v>
+        <v>0.54</v>
       </c>
       <c r="N46" t="b">
         <v>0</v>
@@ -3195,18 +3203,20 @@
         <v>-7.9</v>
       </c>
       <c r="H47" t="n">
-        <v>-10.65</v>
+        <v>-7.19</v>
       </c>
       <c r="I47" t="n">
         <v>-8.83</v>
       </c>
-      <c r="J47" t="inlineStr"/>
+      <c r="J47" t="n">
+        <v>-7.19</v>
+      </c>
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="n">
         <v>-12.99</v>
       </c>
       <c r="M47" t="n">
-        <v>-11.75</v>
+        <v>-8.57</v>
       </c>
       <c r="N47" t="b">
         <v>0</v>
@@ -3244,7 +3254,7 @@
         <v>2.6</v>
       </c>
       <c r="H48" t="n">
-        <v>0.27</v>
+        <v>5.57</v>
       </c>
       <c r="I48" t="n">
         <v>-7.8</v>
@@ -3257,7 +3267,7 @@
         <v>-12.2</v>
       </c>
       <c r="M48" t="n">
-        <v>-1.31</v>
+        <v>3.7</v>
       </c>
       <c r="N48" t="b">
         <v>0</v>
@@ -3295,7 +3305,7 @@
         <v>6.3</v>
       </c>
       <c r="H49" t="n">
-        <v>4.06</v>
+        <v>5.34</v>
       </c>
       <c r="I49" t="n">
         <v>0.64</v>
@@ -3308,7 +3318,7 @@
         <v>-2.13</v>
       </c>
       <c r="M49" t="n">
-        <v>2.48</v>
+        <v>3.47</v>
       </c>
       <c r="N49" t="b">
         <v>0</v>
@@ -3346,7 +3356,7 @@
         <v>20.2</v>
       </c>
       <c r="H50" t="n">
-        <v>1.8</v>
+        <v>1.53</v>
       </c>
       <c r="I50" t="n">
         <v>3.45</v>
@@ -3359,7 +3369,7 @@
         <v>-1.07</v>
       </c>
       <c r="M50" t="n">
-        <v>0.3</v>
+        <v>-0.26</v>
       </c>
       <c r="N50" t="b">
         <v>1</v>
@@ -3397,7 +3407,7 @@
         <v>43.7</v>
       </c>
       <c r="H51" t="n">
-        <v>8.029999999999999</v>
+        <v>12.36</v>
       </c>
       <c r="I51" t="n">
         <v>3.16</v>
@@ -3410,7 +3420,7 @@
         <v>-2.44</v>
       </c>
       <c r="M51" t="n">
-        <v>6.53</v>
+        <v>10.58</v>
       </c>
       <c r="N51" t="b">
         <v>1</v>
@@ -3448,7 +3458,7 @@
         <v>1.9</v>
       </c>
       <c r="H52" t="n">
-        <v>-7.87</v>
+        <v>-4.5</v>
       </c>
       <c r="I52" t="n">
         <v>-10.64</v>
@@ -3461,7 +3471,7 @@
         <v>-14.75</v>
       </c>
       <c r="M52" t="n">
-        <v>-9.369999999999999</v>
+        <v>-6.29</v>
       </c>
       <c r="N52" t="b">
         <v>1</v>
@@ -3499,7 +3509,7 @@
         <v>37.5</v>
       </c>
       <c r="H53" t="n">
-        <v>8.529999999999999</v>
+        <v>10.05</v>
       </c>
       <c r="I53" t="n">
         <v>5.86</v>
@@ -3512,7 +3522,7 @@
         <v>-3.95</v>
       </c>
       <c r="M53" t="n">
-        <v>6.88</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="N53" t="b">
         <v>1</v>
@@ -3550,7 +3560,7 @@
         <v>15</v>
       </c>
       <c r="H54" t="n">
-        <v>-29.66</v>
+        <v>-29.5</v>
       </c>
       <c r="I54" t="n">
         <v>-21.11</v>
@@ -3563,7 +3573,7 @@
         <v>-28.65</v>
       </c>
       <c r="M54" t="n">
-        <v>-31.31</v>
+        <v>-31.44</v>
       </c>
       <c r="N54" t="b">
         <v>0</v>
@@ -3601,7 +3611,7 @@
         <v>40.2</v>
       </c>
       <c r="H55" t="n">
-        <v>13.21</v>
+        <v>13.38</v>
       </c>
       <c r="I55" t="n">
         <v>-1.11</v>
@@ -3614,7 +3624,7 @@
         <v>-5.29</v>
       </c>
       <c r="M55" t="n">
-        <v>11.56</v>
+        <v>11.44</v>
       </c>
       <c r="N55" t="b">
         <v>1</v>
@@ -3652,7 +3662,7 @@
         <v>10.7</v>
       </c>
       <c r="H56" t="n">
-        <v>1.88</v>
+        <v>0.47</v>
       </c>
       <c r="I56" t="n">
         <v>7.3</v>
@@ -3665,7 +3675,7 @@
         <v>-3.78</v>
       </c>
       <c r="M56" t="n">
-        <v>0.23</v>
+        <v>-1.47</v>
       </c>
       <c r="N56" t="b">
         <v>1</v>
@@ -3703,7 +3713,7 @@
         <v>25.6</v>
       </c>
       <c r="H57" t="n">
-        <v>12.91</v>
+        <v>17.37</v>
       </c>
       <c r="I57" t="n">
         <v>7.71</v>
@@ -3716,7 +3726,7 @@
         <v>-4.85</v>
       </c>
       <c r="M57" t="n">
-        <v>12.03</v>
+        <v>16.2</v>
       </c>
       <c r="N57" t="b">
         <v>1</v>
@@ -3754,7 +3764,7 @@
         <v>6.3</v>
       </c>
       <c r="H58" t="n">
-        <v>-0.71</v>
+        <v>1.14</v>
       </c>
       <c r="I58" t="n">
         <v>7.2</v>
@@ -3767,7 +3777,7 @@
         <v>-0.4</v>
       </c>
       <c r="M58" t="n">
-        <v>-2.49</v>
+        <v>-0.93</v>
       </c>
       <c r="N58" t="b">
         <v>0</v>
@@ -3805,7 +3815,7 @@
         <v>2.3</v>
       </c>
       <c r="H59" t="n">
-        <v>-14.64</v>
+        <v>-13.47</v>
       </c>
       <c r="I59" t="n">
         <v>-8.85</v>
@@ -3818,7 +3828,7 @@
         <v>-14.2</v>
       </c>
       <c r="M59" t="n">
-        <v>-16.41</v>
+        <v>-15.54</v>
       </c>
       <c r="N59" t="b">
         <v>0</v>
@@ -3856,7 +3866,7 @@
         <v>-4.3</v>
       </c>
       <c r="H60" t="n">
-        <v>-2.46</v>
+        <v>1.66</v>
       </c>
       <c r="I60" t="n">
         <v>3.39</v>
@@ -3869,7 +3879,7 @@
         <v>-5.89</v>
       </c>
       <c r="M60" t="n">
-        <v>-3.44</v>
+        <v>0.4</v>
       </c>
       <c r="N60" t="b">
         <v>0</v>
@@ -3907,7 +3917,7 @@
         <v>-29.4</v>
       </c>
       <c r="H61" t="n">
-        <v>-10.39</v>
+        <v>-9.390000000000001</v>
       </c>
       <c r="I61" t="n">
         <v>-5.75</v>
@@ -3920,7 +3930,7 @@
         <v>-10.11</v>
       </c>
       <c r="M61" t="n">
-        <v>-11.37</v>
+        <v>-10.65</v>
       </c>
       <c r="N61" t="b">
         <v>0</v>
@@ -3958,7 +3968,7 @@
         <v>-6.9</v>
       </c>
       <c r="H62" t="n">
-        <v>15.15</v>
+        <v>20.56</v>
       </c>
       <c r="I62" t="n">
         <v>6.44</v>
@@ -3971,7 +3981,7 @@
         <v>-4.53</v>
       </c>
       <c r="M62" t="n">
-        <v>14.18</v>
+        <v>19.3</v>
       </c>
       <c r="N62" t="b">
         <v>1</v>
@@ -4009,7 +4019,7 @@
         <v>4.2</v>
       </c>
       <c r="H63" t="n">
-        <v>-20.59</v>
+        <v>-18.36</v>
       </c>
       <c r="I63" t="n">
         <v>-10.83</v>
@@ -4022,7 +4032,7 @@
         <v>-18.5</v>
       </c>
       <c r="M63" t="n">
-        <v>-21.56</v>
+        <v>-19.62</v>
       </c>
       <c r="N63" t="b">
         <v>0</v>
@@ -4060,7 +4070,7 @@
         <v>-32.4</v>
       </c>
       <c r="H64" t="n">
-        <v>-0.23</v>
+        <v>2.6</v>
       </c>
       <c r="I64" t="n">
         <v>-2.43</v>
@@ -4073,7 +4083,7 @@
         <v>-12.47</v>
       </c>
       <c r="M64" t="n">
-        <v>-0.54</v>
+        <v>2</v>
       </c>
       <c r="N64" t="b">
         <v>0</v>
@@ -4111,7 +4121,7 @@
         <v>-11</v>
       </c>
       <c r="H65" t="n">
-        <v>1.92</v>
+        <v>4.52</v>
       </c>
       <c r="I65" t="n">
         <v>-8.449999999999999</v>
@@ -4124,7 +4134,7 @@
         <v>-18.92</v>
       </c>
       <c r="M65" t="n">
-        <v>1.6</v>
+        <v>3.92</v>
       </c>
       <c r="N65" t="b">
         <v>0</v>
@@ -4162,7 +4172,7 @@
         <v>9.699999999999999</v>
       </c>
       <c r="H66" t="n">
-        <v>-5.93</v>
+        <v>-3.24</v>
       </c>
       <c r="I66" t="n">
         <v>1.27</v>
@@ -4175,7 +4185,7 @@
         <v>-20.79</v>
       </c>
       <c r="M66" t="n">
-        <v>-6.4</v>
+        <v>-4</v>
       </c>
       <c r="N66" t="b">
         <v>0</v>
@@ -4213,7 +4223,7 @@
         <v>-28.1</v>
       </c>
       <c r="H67" t="n">
-        <v>-11.49</v>
+        <v>-9.140000000000001</v>
       </c>
       <c r="I67" t="n">
         <v>-10.79</v>
@@ -4226,7 +4236,7 @@
         <v>-13.67</v>
       </c>
       <c r="M67" t="n">
-        <v>-11.96</v>
+        <v>-9.9</v>
       </c>
       <c r="N67" t="b">
         <v>0</v>
@@ -4264,7 +4274,7 @@
         <v>-17.7</v>
       </c>
       <c r="H68" t="n">
-        <v>-2.48</v>
+        <v>2.91</v>
       </c>
       <c r="I68" t="n">
         <v>-0.89</v>
@@ -4277,7 +4287,7 @@
         <v>-11.37</v>
       </c>
       <c r="M68" t="n">
-        <v>-2.95</v>
+        <v>2.16</v>
       </c>
       <c r="N68" t="b">
         <v>0</v>
@@ -4315,7 +4325,7 @@
         <v>-9.300000000000001</v>
       </c>
       <c r="H69" t="n">
-        <v>-14.81</v>
+        <v>-12.97</v>
       </c>
       <c r="I69" t="n">
         <v>-3.34</v>
@@ -4328,7 +4338,7 @@
         <v>-8.77</v>
       </c>
       <c r="M69" t="n">
-        <v>-15.28</v>
+        <v>-13.73</v>
       </c>
       <c r="N69" t="b">
         <v>0</v>
@@ -4366,7 +4376,7 @@
         <v>0.3</v>
       </c>
       <c r="H70" t="n">
-        <v>-17.99</v>
+        <v>-16.14</v>
       </c>
       <c r="I70" t="n">
         <v>-10.53</v>
@@ -4379,7 +4389,7 @@
         <v>-17.73</v>
       </c>
       <c r="M70" t="n">
-        <v>-18.46</v>
+        <v>-16.89</v>
       </c>
       <c r="N70" t="b">
         <v>1</v>
@@ -4417,7 +4427,7 @@
         <v>12.3</v>
       </c>
       <c r="H71" t="n">
-        <v>1.78</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="I71" t="n">
         <v>6.51</v>
@@ -4430,7 +4440,7 @@
         <v>-6.01</v>
       </c>
       <c r="M71" t="n">
-        <v>0.6</v>
+        <v>6.57</v>
       </c>
       <c r="N71" t="b">
         <v>0</v>
@@ -4468,7 +4478,7 @@
         <v>2.8</v>
       </c>
       <c r="H72" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="I72" t="n">
         <v>3.18</v>
@@ -4481,7 +4491,7 @@
         <v>-0.88</v>
       </c>
       <c r="M72" t="n">
-        <v>-0.63</v>
+        <v>-0.57</v>
       </c>
       <c r="N72" t="b">
         <v>1</v>
@@ -4519,7 +4529,7 @@
         <v>-1.4</v>
       </c>
       <c r="H73" t="n">
-        <v>1.63</v>
+        <v>2.13</v>
       </c>
       <c r="I73" t="n">
         <v>-4.52</v>
@@ -4532,7 +4542,7 @@
         <v>-7.44</v>
       </c>
       <c r="M73" t="n">
-        <v>0.45</v>
+        <v>0.66</v>
       </c>
       <c r="N73" t="b">
         <v>0</v>
@@ -4570,7 +4580,7 @@
         <v>34.5</v>
       </c>
       <c r="H74" t="n">
-        <v>9.07</v>
+        <v>9.26</v>
       </c>
       <c r="I74" t="n">
         <v>0.66</v>
@@ -4583,7 +4593,7 @@
         <v>-2.64</v>
       </c>
       <c r="M74" t="n">
-        <v>7.88</v>
+        <v>7.78</v>
       </c>
       <c r="N74" t="b">
         <v>1</v>
@@ -4621,7 +4631,7 @@
         <v>-22.7</v>
       </c>
       <c r="H75" t="n">
-        <v>-13.76</v>
+        <v>-13.02</v>
       </c>
       <c r="I75" t="n">
         <v>-6.71</v>
@@ -4634,7 +4644,7 @@
         <v>-9.58</v>
       </c>
       <c r="M75" t="n">
-        <v>-15.01</v>
+        <v>-14.56</v>
       </c>
       <c r="N75" t="b">
         <v>0</v>
@@ -4672,7 +4682,7 @@
         <v>24.3</v>
       </c>
       <c r="H76" t="n">
-        <v>49.61</v>
+        <v>41.06</v>
       </c>
       <c r="I76" t="n">
         <v>2.54</v>
@@ -4685,7 +4695,7 @@
         <v>-5.21</v>
       </c>
       <c r="M76" t="n">
-        <v>49.07</v>
+        <v>40.23</v>
       </c>
       <c r="N76" t="b">
         <v>1</v>
@@ -4723,7 +4733,7 @@
         <v>56.6</v>
       </c>
       <c r="H77" t="n">
-        <v>-6.06</v>
+        <v>-0.78</v>
       </c>
       <c r="I77" t="n">
         <v>-13.1</v>
@@ -4736,7 +4746,7 @@
         <v>-16.17</v>
       </c>
       <c r="M77" t="n">
-        <v>-6.61</v>
+        <v>-1.61</v>
       </c>
       <c r="N77" t="b">
         <v>0</v>
@@ -4774,7 +4784,7 @@
         <v>2.9</v>
       </c>
       <c r="H78" t="n">
-        <v>-21.65</v>
+        <v>-19.79</v>
       </c>
       <c r="I78" t="n">
         <v>-8.470000000000001</v>
@@ -4787,7 +4797,7 @@
         <v>-15.65</v>
       </c>
       <c r="M78" t="n">
-        <v>-22.19</v>
+        <v>-20.62</v>
       </c>
       <c r="N78" t="b">
         <v>0</v>
@@ -4825,7 +4835,7 @@
         <v>-16.9</v>
       </c>
       <c r="H79" t="n">
-        <v>-9.42</v>
+        <v>-5.24</v>
       </c>
       <c r="I79" t="n">
         <v>-6.47</v>
@@ -4838,7 +4848,7 @@
         <v>-11.5</v>
       </c>
       <c r="M79" t="n">
-        <v>-9.970000000000001</v>
+        <v>-6.07</v>
       </c>
       <c r="N79" t="b">
         <v>1</v>
@@ -4876,7 +4886,7 @@
         <v>32.8</v>
       </c>
       <c r="H80" t="n">
-        <v>2.93</v>
+        <v>4.25</v>
       </c>
       <c r="I80" t="n">
         <v>14.96</v>
@@ -4889,7 +4899,7 @@
         <v>-0.9</v>
       </c>
       <c r="M80" t="n">
-        <v>2.96</v>
+        <v>4</v>
       </c>
       <c r="N80" t="b">
         <v>0</v>
@@ -4927,7 +4937,7 @@
         <v>0.8</v>
       </c>
       <c r="H81" t="n">
-        <v>-7.15</v>
+        <v>-7.67</v>
       </c>
       <c r="I81" t="n">
         <v>-7.73</v>
@@ -4940,7 +4950,7 @@
         <v>-10.12</v>
       </c>
       <c r="M81" t="n">
-        <v>-7.12</v>
+        <v>-7.92</v>
       </c>
       <c r="N81" t="b">
         <v>0</v>
@@ -4978,7 +4988,7 @@
         <v>-9.6</v>
       </c>
       <c r="H82" t="n">
-        <v>-14.57</v>
+        <v>-14.7</v>
       </c>
       <c r="I82" t="n">
         <v>-1.23</v>
@@ -4991,7 +5001,7 @@
         <v>-18.52</v>
       </c>
       <c r="M82" t="n">
-        <v>-14.54</v>
+        <v>-14.95</v>
       </c>
       <c r="N82" t="b">
         <v>0</v>
@@ -5029,7 +5039,7 @@
         <v>20.3</v>
       </c>
       <c r="H83" t="n">
-        <v>-23.01</v>
+        <v>-19.23</v>
       </c>
       <c r="I83" t="n">
         <v>-2.07</v>
@@ -5042,7 +5052,7 @@
         <v>-17.35</v>
       </c>
       <c r="M83" t="n">
-        <v>-23.4</v>
+        <v>-19.9</v>
       </c>
       <c r="N83" t="b">
         <v>1</v>
@@ -5080,7 +5090,7 @@
         <v>0.3</v>
       </c>
       <c r="H84" t="n">
-        <v>-22.33</v>
+        <v>-20.92</v>
       </c>
       <c r="I84" t="n">
         <v>-9.9</v>
@@ -5093,7 +5103,7 @@
         <v>-21.72</v>
       </c>
       <c r="M84" t="n">
-        <v>-23.21</v>
+        <v>-22.09</v>
       </c>
       <c r="N84" t="b">
         <v>1</v>
@@ -5131,7 +5141,7 @@
         <v>49.4</v>
       </c>
       <c r="H85" t="n">
-        <v>4.02</v>
+        <v>4.01</v>
       </c>
       <c r="I85" t="n">
         <v>2.9</v>
@@ -5144,7 +5154,7 @@
         <v>-5.67</v>
       </c>
       <c r="M85" t="n">
-        <v>3.32</v>
+        <v>3.03</v>
       </c>
       <c r="N85" t="b">
         <v>1</v>
@@ -5182,7 +5192,7 @@
         <v>4.5</v>
       </c>
       <c r="H86" t="n">
-        <v>-7.52</v>
+        <v>-4.31</v>
       </c>
       <c r="I86" t="n">
         <v>-7.61</v>
@@ -5195,7 +5205,7 @@
         <v>-11.06</v>
       </c>
       <c r="M86" t="n">
-        <v>-8.220000000000001</v>
+        <v>-5.29</v>
       </c>
       <c r="N86" t="b">
         <v>1</v>
@@ -5233,7 +5243,7 @@
         <v>4.2</v>
       </c>
       <c r="H87" t="n">
-        <v>-20.32</v>
+        <v>-18.02</v>
       </c>
       <c r="I87" t="n">
         <v>-6.86</v>
@@ -5246,7 +5256,7 @@
         <v>-20.23</v>
       </c>
       <c r="M87" t="n">
-        <v>-21.02</v>
+        <v>-19</v>
       </c>
       <c r="N87" t="b">
         <v>0</v>
@@ -5284,7 +5294,7 @@
         <v>15.4</v>
       </c>
       <c r="H88" t="n">
-        <v>0.06</v>
+        <v>2.86</v>
       </c>
       <c r="I88" t="n">
         <v>-1.19</v>
@@ -5297,7 +5307,7 @@
         <v>-7.43</v>
       </c>
       <c r="M88" t="n">
-        <v>-0.63</v>
+        <v>1.87</v>
       </c>
       <c r="N88" t="b">
         <v>0</v>
@@ -5335,7 +5345,7 @@
         <v>15.5</v>
       </c>
       <c r="H89" t="n">
-        <v>-5.52</v>
+        <v>-3.08</v>
       </c>
       <c r="I89" t="n">
         <v>-7.36</v>
@@ -5348,7 +5358,7 @@
         <v>-12.98</v>
       </c>
       <c r="M89" t="n">
-        <v>-6.4</v>
+        <v>-4.24</v>
       </c>
       <c r="N89" t="b">
         <v>0</v>
@@ -5390,7 +5400,7 @@
         <v>-8.5</v>
       </c>
       <c r="H90" t="n">
-        <v>17.36</v>
+        <v>22.79</v>
       </c>
       <c r="I90" t="n">
         <v>-3.04</v>
@@ -5403,7 +5413,7 @@
         <v>-4.96</v>
       </c>
       <c r="M90" t="n">
-        <v>16.47</v>
+        <v>21.63</v>
       </c>
       <c r="N90" t="b">
         <v>0</v>
@@ -5441,7 +5451,7 @@
         <v>1.8</v>
       </c>
       <c r="H91" t="n">
-        <v>-12.48</v>
+        <v>-8.48</v>
       </c>
       <c r="I91" t="n">
         <v>-6.45</v>
@@ -5454,7 +5464,7 @@
         <v>-13.57</v>
       </c>
       <c r="M91" t="n">
-        <v>-13.36</v>
+        <v>-9.65</v>
       </c>
       <c r="N91" t="b">
         <v>0</v>
@@ -5492,7 +5502,7 @@
         <v>33.9</v>
       </c>
       <c r="H92" t="n">
-        <v>8.359999999999999</v>
+        <v>10.97</v>
       </c>
       <c r="I92" t="n">
         <v>-7.74</v>
@@ -5505,7 +5515,7 @@
         <v>-9.449999999999999</v>
       </c>
       <c r="M92" t="n">
-        <v>7.48</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="N92" t="b">
         <v>0</v>
@@ -5543,7 +5553,7 @@
         <v>-25</v>
       </c>
       <c r="H93" t="n">
-        <v>-9.69</v>
+        <v>-8.539999999999999</v>
       </c>
       <c r="I93" t="n">
         <v>2.51</v>
@@ -5556,7 +5566,7 @@
         <v>-4.88</v>
       </c>
       <c r="M93" t="n">
-        <v>-10.4</v>
+        <v>-9.539999999999999</v>
       </c>
       <c r="N93" t="b">
         <v>0</v>
@@ -5594,7 +5604,7 @@
         <v>-12.6</v>
       </c>
       <c r="H94" t="n">
-        <v>-21.97</v>
+        <v>-18.13</v>
       </c>
       <c r="I94" t="n">
         <v>-7.89</v>
@@ -5607,7 +5617,7 @@
         <v>-21.29</v>
       </c>
       <c r="M94" t="n">
-        <v>-22.7</v>
+        <v>-19.14</v>
       </c>
       <c r="N94" t="b">
         <v>0</v>
@@ -5645,7 +5655,7 @@
         <v>-17.9</v>
       </c>
       <c r="H95" t="n">
-        <v>-0.55</v>
+        <v>3.72</v>
       </c>
       <c r="I95" t="n">
         <v>0.6</v>
@@ -5658,7 +5668,7 @@
         <v>-4.72</v>
       </c>
       <c r="M95" t="n">
-        <v>-1.28</v>
+        <v>2.71</v>
       </c>
       <c r="N95" t="b">
         <v>1</v>
@@ -5696,7 +5706,7 @@
         <v>2.1</v>
       </c>
       <c r="H96" t="n">
-        <v>-20.29</v>
+        <v>-14.51</v>
       </c>
       <c r="I96" t="n">
         <v>0.25</v>
@@ -5709,7 +5719,7 @@
         <v>-16.43</v>
       </c>
       <c r="M96" t="n">
-        <v>-21.01</v>
+        <v>-15.52</v>
       </c>
       <c r="N96" t="b">
         <v>1</v>
@@ -5798,7 +5808,7 @@
         <v>-30.5</v>
       </c>
       <c r="H98" t="n">
-        <v>-13.33</v>
+        <v>-8.789999999999999</v>
       </c>
       <c r="I98" t="n">
         <v>-4.6</v>
@@ -5811,7 +5821,7 @@
         <v>-10.37</v>
       </c>
       <c r="M98" t="n">
-        <v>-13.48</v>
+        <v>-9.220000000000001</v>
       </c>
       <c r="N98" t="b">
         <v>0</v>
@@ -5849,7 +5859,7 @@
         <v>-20.5</v>
       </c>
       <c r="H99" t="n">
-        <v>-18.83</v>
+        <v>-16.02</v>
       </c>
       <c r="I99" t="n">
         <v>-4.62</v>
@@ -5862,7 +5872,7 @@
         <v>-9.92</v>
       </c>
       <c r="M99" t="n">
-        <v>-18.98</v>
+        <v>-16.45</v>
       </c>
       <c r="N99" t="b">
         <v>0</v>
@@ -5900,7 +5910,7 @@
         <v>-12.3</v>
       </c>
       <c r="H100" t="n">
-        <v>-16.77</v>
+        <v>-12.67</v>
       </c>
       <c r="I100" t="n">
         <v>-4.36</v>
@@ -5913,7 +5923,7 @@
         <v>-13.26</v>
       </c>
       <c r="M100" t="n">
-        <v>-17.14</v>
+        <v>-13.32</v>
       </c>
       <c r="N100" t="b">
         <v>0</v>
@@ -5951,7 +5961,7 @@
         <v>13.7</v>
       </c>
       <c r="H101" t="n">
-        <v>-22.23</v>
+        <v>-18.53</v>
       </c>
       <c r="I101" t="n">
         <v>-12.16</v>
@@ -5964,7 +5974,7 @@
         <v>-13.02</v>
       </c>
       <c r="M101" t="n">
-        <v>-22.59</v>
+        <v>-19.18</v>
       </c>
       <c r="N101" t="b">
         <v>0</v>
@@ -6002,7 +6012,7 @@
         <v>-2.6</v>
       </c>
       <c r="H102" t="n">
-        <v>-10.4</v>
+        <v>-7.92</v>
       </c>
       <c r="I102" t="n">
         <v>-4.27</v>
@@ -6015,7 +6025,7 @@
         <v>-4.86</v>
       </c>
       <c r="M102" t="n">
-        <v>-10.76</v>
+        <v>-8.57</v>
       </c>
       <c r="N102" t="b">
         <v>1</v>
@@ -6053,7 +6063,7 @@
         <v>25.6</v>
       </c>
       <c r="H103" t="n">
-        <v>5.76</v>
+        <v>13.74</v>
       </c>
       <c r="I103" t="n">
         <v>4.26</v>
@@ -6066,7 +6076,7 @@
         <v>-10.74</v>
       </c>
       <c r="M103" t="n">
-        <v>5.4</v>
+        <v>13.08</v>
       </c>
       <c r="N103" t="b">
         <v>0</v>
@@ -6104,7 +6114,7 @@
         <v>23.8</v>
       </c>
       <c r="H104" t="n">
-        <v>-2.77</v>
+        <v>-1.13</v>
       </c>
       <c r="I104" t="n">
         <v>1.36</v>
@@ -6117,7 +6127,7 @@
         <v>-9.94</v>
       </c>
       <c r="M104" t="n">
-        <v>-2.17</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="N104" t="b">
         <v>1</v>
@@ -6155,7 +6165,7 @@
         <v>38.9</v>
       </c>
       <c r="H105" t="n">
-        <v>-11.73</v>
+        <v>-11.26</v>
       </c>
       <c r="I105" t="n">
         <v>-9.220000000000001</v>
@@ -6168,7 +6178,7 @@
         <v>-9.83</v>
       </c>
       <c r="M105" t="n">
-        <v>-11.13</v>
+        <v>-10.95</v>
       </c>
       <c r="N105" t="b">
         <v>1</v>
@@ -6206,7 +6216,7 @@
         <v>32.1</v>
       </c>
       <c r="H106" t="n">
-        <v>42.28</v>
+        <v>40.27</v>
       </c>
       <c r="I106" t="n">
         <v>11.84</v>
@@ -6219,7 +6229,7 @@
         <v>-1.82</v>
       </c>
       <c r="M106" t="n">
-        <v>42.88</v>
+        <v>40.59</v>
       </c>
       <c r="N106" t="b">
         <v>0</v>
@@ -6257,7 +6267,7 @@
         <v>53.4</v>
       </c>
       <c r="H107" t="n">
-        <v>34.08</v>
+        <v>29.49</v>
       </c>
       <c r="I107" t="n">
         <v>2.75</v>
@@ -6270,7 +6280,7 @@
         <v>-2.31</v>
       </c>
       <c r="M107" t="n">
-        <v>34.98</v>
+        <v>30.11</v>
       </c>
       <c r="N107" t="b">
         <v>0</v>
@@ -6308,7 +6318,7 @@
         <v>54.1</v>
       </c>
       <c r="H108" t="n">
-        <v>40.78</v>
+        <v>38.46</v>
       </c>
       <c r="I108" t="n">
         <v>5.54</v>
@@ -6321,7 +6331,7 @@
         <v>-0.41</v>
       </c>
       <c r="M108" t="n">
-        <v>41.21</v>
+        <v>38.61</v>
       </c>
       <c r="N108" t="b">
         <v>0</v>
@@ -6359,7 +6369,7 @@
         <v>43.2</v>
       </c>
       <c r="H109" t="n">
-        <v>-14.35</v>
+        <v>-10.09</v>
       </c>
       <c r="I109" t="n">
         <v>-3.15</v>
@@ -6372,7 +6382,7 @@
         <v>-17.51</v>
       </c>
       <c r="M109" t="n">
-        <v>-13.92</v>
+        <v>-9.94</v>
       </c>
       <c r="N109" t="b">
         <v>1</v>
@@ -6410,7 +6420,7 @@
         <v>-8.199999999999999</v>
       </c>
       <c r="H110" t="n">
-        <v>-0.15</v>
+        <v>3.58</v>
       </c>
       <c r="I110" t="n">
         <v>5.34</v>
@@ -6423,7 +6433,7 @@
         <v>-5.27</v>
       </c>
       <c r="M110" t="n">
-        <v>0.28</v>
+        <v>3.73</v>
       </c>
       <c r="N110" t="b">
         <v>1</v>
@@ -6461,7 +6471,7 @@
         <v>-1.2</v>
       </c>
       <c r="H111" t="n">
-        <v>2.67</v>
+        <v>4.51</v>
       </c>
       <c r="I111" t="n">
         <v>8.27</v>
@@ -6474,7 +6484,7 @@
         <v>-5.3</v>
       </c>
       <c r="M111" t="n">
-        <v>3.06</v>
+        <v>4.62</v>
       </c>
       <c r="N111" t="b">
         <v>0</v>
@@ -6512,7 +6522,7 @@
         <v>-23.9</v>
       </c>
       <c r="H112" t="n">
-        <v>-9.460000000000001</v>
+        <v>-6.69</v>
       </c>
       <c r="I112" t="n">
         <v>3.28</v>
@@ -6525,7 +6535,7 @@
         <v>-4.46</v>
       </c>
       <c r="M112" t="n">
-        <v>-9.32</v>
+        <v>-6.83</v>
       </c>
       <c r="N112" t="b">
         <v>1</v>
@@ -6567,7 +6577,7 @@
         <v>-6.1</v>
       </c>
       <c r="H113" t="n">
-        <v>-16.21</v>
+        <v>-16.48</v>
       </c>
       <c r="I113" t="n">
         <v>4.9</v>
@@ -6580,7 +6590,7 @@
         <v>-9</v>
       </c>
       <c r="M113" t="n">
-        <v>-16.07</v>
+        <v>-16.62</v>
       </c>
       <c r="N113" t="b">
         <v>1</v>
@@ -6618,7 +6628,7 @@
         <v>26.7</v>
       </c>
       <c r="H114" t="n">
-        <v>-0.84</v>
+        <v>-0.85</v>
       </c>
       <c r="I114" t="n">
         <v>-0.05</v>
@@ -6631,7 +6641,7 @@
         <v>-0.87</v>
       </c>
       <c r="M114" t="n">
-        <v>-0.7</v>
+        <v>-1</v>
       </c>
       <c r="N114" t="b">
         <v>1</v>
@@ -6669,7 +6679,7 @@
         <v>39.5</v>
       </c>
       <c r="H115" t="n">
-        <v>9.76</v>
+        <v>7.05</v>
       </c>
       <c r="I115" t="n">
         <v>-5.13</v>
@@ -6682,7 +6692,7 @@
         <v>-8.869999999999999</v>
       </c>
       <c r="M115" t="n">
-        <v>9.9</v>
+        <v>6.9</v>
       </c>
       <c r="N115" t="b">
         <v>0</v>
@@ -6720,7 +6730,7 @@
         <v>14.3</v>
       </c>
       <c r="H116" t="n">
-        <v>14.66</v>
+        <v>18.41</v>
       </c>
       <c r="I116" t="n">
         <v>-0.43</v>
@@ -6733,7 +6743,7 @@
         <v>-11.86</v>
       </c>
       <c r="M116" t="n">
-        <v>14.8</v>
+        <v>18.27</v>
       </c>
       <c r="N116" t="b">
         <v>0</v>
@@ -6771,7 +6781,7 @@
         <v>-11.3</v>
       </c>
       <c r="H117" t="n">
-        <v>3.58</v>
+        <v>1.9</v>
       </c>
       <c r="I117" t="n">
         <v>1.31</v>
@@ -6784,7 +6794,7 @@
         <v>-1.88</v>
       </c>
       <c r="M117" t="n">
-        <v>3.72</v>
+        <v>1.75</v>
       </c>
       <c r="N117" t="b">
         <v>0</v>
@@ -6822,7 +6832,7 @@
         <v>-23.5</v>
       </c>
       <c r="H118" t="n">
-        <v>-30.11</v>
+        <v>-25.22</v>
       </c>
       <c r="I118" t="n">
         <v>13.29</v>
@@ -6835,7 +6845,7 @@
         <v>-14.04</v>
       </c>
       <c r="M118" t="n">
-        <v>-29.96</v>
+        <v>-25.36</v>
       </c>
       <c r="N118" t="b">
         <v>0</v>
@@ -6873,7 +6883,7 @@
         <v>10.5</v>
       </c>
       <c r="H119" t="n">
-        <v>-6.75</v>
+        <v>-4.97</v>
       </c>
       <c r="I119" t="n">
         <v>-0.86</v>
@@ -6886,7 +6896,7 @@
         <v>-6.11</v>
       </c>
       <c r="M119" t="n">
-        <v>-6.61</v>
+        <v>-5.12</v>
       </c>
       <c r="N119" t="b">
         <v>0</v>
@@ -6975,7 +6985,7 @@
         <v>-12.8</v>
       </c>
       <c r="H121" t="n">
-        <v>9.68</v>
+        <v>11.4</v>
       </c>
       <c r="I121" t="n">
         <v>-1.74</v>
@@ -6988,7 +6998,7 @@
         <v>-2.97</v>
       </c>
       <c r="M121" t="n">
-        <v>9.619999999999999</v>
+        <v>11.06</v>
       </c>
       <c r="N121" t="b">
         <v>0</v>
@@ -7026,7 +7036,7 @@
         <v>2.4</v>
       </c>
       <c r="H122" t="n">
-        <v>25.55</v>
+        <v>25.26</v>
       </c>
       <c r="I122" t="n">
         <v>12.41</v>
@@ -7039,7 +7049,7 @@
         <v>-0.07000000000000001</v>
       </c>
       <c r="M122" t="n">
-        <v>25.49</v>
+        <v>24.91</v>
       </c>
       <c r="N122" t="b">
         <v>0</v>
@@ -7077,7 +7087,7 @@
         <v>-17.9</v>
       </c>
       <c r="H123" t="n">
-        <v>0.7</v>
+        <v>-0.46</v>
       </c>
       <c r="I123" t="n">
         <v>-0.5</v>
@@ -7090,7 +7100,7 @@
         <v>-3.43</v>
       </c>
       <c r="M123" t="n">
-        <v>0.64</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="N123" t="b">
         <v>1</v>
@@ -7128,7 +7138,7 @@
         <v>11.9</v>
       </c>
       <c r="H124" t="n">
-        <v>-3.52</v>
+        <v>-1.7</v>
       </c>
       <c r="I124" t="n">
         <v>6.88</v>
@@ -7141,7 +7151,7 @@
         <v>-10.93</v>
       </c>
       <c r="M124" t="n">
-        <v>-3.69</v>
+        <v>-2.15</v>
       </c>
       <c r="N124" t="b">
         <v>0</v>
@@ -7179,7 +7189,7 @@
         <v>53.5</v>
       </c>
       <c r="H125" t="n">
-        <v>5.35</v>
+        <v>7.03</v>
       </c>
       <c r="I125" t="n">
         <v>1.23</v>
@@ -7192,7 +7202,7 @@
         <v>-7.57</v>
       </c>
       <c r="M125" t="n">
-        <v>5.18</v>
+        <v>6.57</v>
       </c>
       <c r="N125" t="b">
         <v>1</v>
@@ -7230,7 +7240,7 @@
         <v>18.1</v>
       </c>
       <c r="H126" t="n">
-        <v>-2.82</v>
+        <v>-2.99</v>
       </c>
       <c r="I126" t="n">
         <v>-1.69</v>
@@ -7243,7 +7253,7 @@
         <v>-1.92</v>
       </c>
       <c r="M126" t="n">
-        <v>-2.99</v>
+        <v>-3.44</v>
       </c>
       <c r="N126" t="b">
         <v>0</v>
@@ -7281,7 +7291,7 @@
         <v>-1</v>
       </c>
       <c r="H127" t="n">
-        <v>-9.92</v>
+        <v>-11.96</v>
       </c>
       <c r="I127" t="n">
         <v>-6.26</v>
@@ -7294,7 +7304,7 @@
         <v>-15</v>
       </c>
       <c r="M127" t="n">
-        <v>-10.08</v>
+        <v>-12.41</v>
       </c>
       <c r="N127" t="b">
         <v>1</v>
@@ -7332,7 +7342,7 @@
         <v>29.7</v>
       </c>
       <c r="H128" t="n">
-        <v>1.54</v>
+        <v>2.81</v>
       </c>
       <c r="I128" t="n">
         <v>11.27</v>
@@ -7345,7 +7355,7 @@
         <v>0</v>
       </c>
       <c r="M128" t="n">
-        <v>1.37</v>
+        <v>2.35</v>
       </c>
       <c r="N128" t="b">
         <v>1</v>
@@ -7383,7 +7393,7 @@
         <v>15.2</v>
       </c>
       <c r="H129" t="n">
-        <v>-40.43</v>
+        <v>-36.73</v>
       </c>
       <c r="I129" t="n">
         <v>-8.77</v>
@@ -7396,7 +7406,7 @@
         <v>-24.79</v>
       </c>
       <c r="M129" t="n">
-        <v>-39.87</v>
+        <v>-36.46</v>
       </c>
       <c r="N129" t="b">
         <v>1</v>
@@ -7434,7 +7444,7 @@
         <v>22.2</v>
       </c>
       <c r="H130" t="n">
-        <v>7.27</v>
+        <v>9.67</v>
       </c>
       <c r="I130" t="n">
         <v>1.01</v>
@@ -7447,7 +7457,7 @@
         <v>-3.94</v>
       </c>
       <c r="M130" t="n">
-        <v>7.83</v>
+        <v>9.94</v>
       </c>
       <c r="N130" t="b">
         <v>1</v>
@@ -7485,7 +7495,7 @@
         <v>10.8</v>
       </c>
       <c r="H131" t="n">
-        <v>9.83</v>
+        <v>11.57</v>
       </c>
       <c r="I131" t="n">
         <v>5.62</v>
@@ -7498,7 +7508,7 @@
         <v>-1.59</v>
       </c>
       <c r="M131" t="n">
-        <v>10.39</v>
+        <v>11.85</v>
       </c>
       <c r="N131" t="b">
         <v>0</v>
@@ -7536,7 +7546,7 @@
         <v>-2.1</v>
       </c>
       <c r="H132" t="n">
-        <v>-17.12</v>
+        <v>-16.67</v>
       </c>
       <c r="I132" t="n">
         <v>0.67</v>
@@ -7549,7 +7559,7 @@
         <v>-7.84</v>
       </c>
       <c r="M132" t="n">
-        <v>-16.56</v>
+        <v>-16.4</v>
       </c>
       <c r="N132" t="b">
         <v>0</v>
@@ -7587,7 +7597,7 @@
         <v>16.7</v>
       </c>
       <c r="H133" t="n">
-        <v>-28.93</v>
+        <v>-25.98</v>
       </c>
       <c r="I133" t="n">
         <v>-15.31</v>
@@ -7600,7 +7610,7 @@
         <v>-22</v>
       </c>
       <c r="M133" t="n">
-        <v>-30.36</v>
+        <v>-27.7</v>
       </c>
       <c r="N133" t="b">
         <v>0</v>
@@ -7638,7 +7648,7 @@
         <v>0.3</v>
       </c>
       <c r="H134" t="n">
-        <v>33.32</v>
+        <v>37.37</v>
       </c>
       <c r="I134" t="n">
         <v>6.01</v>
@@ -7651,7 +7661,7 @@
         <v>-3.85</v>
       </c>
       <c r="M134" t="n">
-        <v>30.37</v>
+        <v>34.14</v>
       </c>
       <c r="N134" t="b">
         <v>0</v>
@@ -7693,7 +7703,7 @@
         <v>-0</v>
       </c>
       <c r="H135" t="n">
-        <v>41.6</v>
+        <v>49.07</v>
       </c>
       <c r="I135" t="n">
         <v>13.5</v>
@@ -7706,7 +7716,7 @@
         <v>-2.53</v>
       </c>
       <c r="M135" t="n">
-        <v>38.66</v>
+        <v>45.83</v>
       </c>
       <c r="N135" t="b">
         <v>1</v>
@@ -7744,7 +7754,7 @@
         <v>10.5</v>
       </c>
       <c r="H136" t="n">
-        <v>11.55</v>
+        <v>16.56</v>
       </c>
       <c r="I136" t="n">
         <v>1.99</v>
@@ -7757,7 +7767,7 @@
         <v>-6.27</v>
       </c>
       <c r="M136" t="n">
-        <v>8.6</v>
+        <v>13.32</v>
       </c>
       <c r="N136" t="b">
         <v>1</v>
@@ -7795,7 +7805,7 @@
         <v>30.4</v>
       </c>
       <c r="H137" t="n">
-        <v>4.61</v>
+        <v>6.05</v>
       </c>
       <c r="I137" t="n">
         <v>8.539999999999999</v>
@@ -7808,7 +7818,7 @@
         <v>-0.44</v>
       </c>
       <c r="M137" t="n">
-        <v>1.66</v>
+        <v>2.81</v>
       </c>
       <c r="N137" t="b">
         <v>0</v>
@@ -7850,7 +7860,7 @@
         <v>-3.2</v>
       </c>
       <c r="H138" t="n">
-        <v>13.83</v>
+        <v>18.57</v>
       </c>
       <c r="I138" t="n">
         <v>15.28</v>
@@ -7863,7 +7873,7 @@
         <v>-2.53</v>
       </c>
       <c r="M138" t="n">
-        <v>10.88</v>
+        <v>15.33</v>
       </c>
       <c r="N138" t="b">
         <v>0</v>
@@ -7901,7 +7911,7 @@
         <v>-23.5</v>
       </c>
       <c r="H139" t="n">
-        <v>11.53</v>
+        <v>17.89</v>
       </c>
       <c r="I139" t="n">
         <v>20.48</v>
@@ -7914,7 +7924,7 @@
         <v>-2.25</v>
       </c>
       <c r="M139" t="n">
-        <v>8.59</v>
+        <v>14.65</v>
       </c>
       <c r="N139" t="b">
         <v>0</v>
@@ -7952,7 +7962,7 @@
         <v>-27.3</v>
       </c>
       <c r="H140" t="n">
-        <v>5.85</v>
+        <v>12.9</v>
       </c>
       <c r="I140" t="n">
         <v>-8.83</v>
@@ -7965,7 +7975,7 @@
         <v>-19.66</v>
       </c>
       <c r="M140" t="n">
-        <v>2.91</v>
+        <v>9.66</v>
       </c>
       <c r="N140" t="b">
         <v>0</v>
@@ -8003,7 +8013,7 @@
         <v>-12.5</v>
       </c>
       <c r="H141" t="n">
-        <v>-12.57</v>
+        <v>-10.78</v>
       </c>
       <c r="I141" t="n">
         <v>21.54</v>
@@ -8016,7 +8026,7 @@
         <v>-0.95</v>
       </c>
       <c r="M141" t="n">
-        <v>-16.18</v>
+        <v>-14.68</v>
       </c>
       <c r="N141" t="b">
         <v>0</v>
@@ -8054,7 +8064,7 @@
         <v>-37</v>
       </c>
       <c r="H142" t="n">
-        <v>42.82</v>
+        <v>50.36</v>
       </c>
       <c r="I142" t="n">
         <v>18.38</v>
@@ -8067,7 +8077,7 @@
         <v>-5.11</v>
       </c>
       <c r="M142" t="n">
-        <v>39.21</v>
+        <v>46.46</v>
       </c>
       <c r="N142" t="b">
         <v>1</v>
@@ -8109,7 +8119,7 @@
         <v>-3.4</v>
       </c>
       <c r="H143" t="n">
-        <v>6.44</v>
+        <v>11.74</v>
       </c>
       <c r="I143" t="n">
         <v>30.48</v>
@@ -8122,7 +8132,7 @@
         <v>-0.9</v>
       </c>
       <c r="M143" t="n">
-        <v>2.84</v>
+        <v>7.84</v>
       </c>
       <c r="N143" t="b">
         <v>0</v>
@@ -8160,7 +8170,7 @@
         <v>-23.4</v>
       </c>
       <c r="H144" t="n">
-        <v>-5.59</v>
+        <v>-0.38</v>
       </c>
       <c r="I144" t="n">
         <v>-3.58</v>
@@ -8173,7 +8183,7 @@
         <v>-17.98</v>
       </c>
       <c r="M144" t="n">
-        <v>-9.199999999999999</v>
+        <v>-4.27</v>
       </c>
       <c r="N144" t="b">
         <v>0</v>
@@ -8211,7 +8221,7 @@
         <v>-28.9</v>
       </c>
       <c r="H145" t="n">
-        <v>-18.62</v>
+        <v>-15.68</v>
       </c>
       <c r="I145" t="n">
         <v>-12.9</v>
@@ -8224,7 +8234,7 @@
         <v>-23.19</v>
       </c>
       <c r="M145" t="n">
-        <v>-22.22</v>
+        <v>-19.58</v>
       </c>
       <c r="N145" t="b">
         <v>0</v>
@@ -8262,7 +8272,7 @@
         <v>-26.8</v>
       </c>
       <c r="H146" t="n">
-        <v>27.29</v>
+        <v>30.62</v>
       </c>
       <c r="I146" t="n">
         <v>4.56</v>
@@ -8275,7 +8285,7 @@
         <v>-4.09</v>
       </c>
       <c r="M146" t="n">
-        <v>23.69</v>
+        <v>26.72</v>
       </c>
       <c r="N146" t="b">
         <v>1</v>
@@ -8317,7 +8327,7 @@
         <v>-9.800000000000001</v>
       </c>
       <c r="H147" t="n">
-        <v>-22.02</v>
+        <v>-20.57</v>
       </c>
       <c r="I147" t="n">
         <v>-4.09</v>
@@ -8330,7 +8340,7 @@
         <v>-15.24</v>
       </c>
       <c r="M147" t="n">
-        <v>-26.84</v>
+        <v>-25.68</v>
       </c>
       <c r="N147" t="b">
         <v>0</v>
@@ -8368,7 +8378,7 @@
         <v>21</v>
       </c>
       <c r="H148" t="n">
-        <v>1.9</v>
+        <v>1.35</v>
       </c>
       <c r="I148" t="n">
         <v>-0.72</v>
@@ -8381,7 +8391,7 @@
         <v>-7.35</v>
       </c>
       <c r="M148" t="n">
-        <v>-2.92</v>
+        <v>-3.77</v>
       </c>
       <c r="N148" t="b">
         <v>0</v>
@@ -8419,7 +8429,7 @@
         <v>13.2</v>
       </c>
       <c r="H149" t="n">
-        <v>48.79</v>
+        <v>51.02</v>
       </c>
       <c r="I149" t="n">
         <v>8.130000000000001</v>
@@ -8432,7 +8442,7 @@
         <v>-2.36</v>
       </c>
       <c r="M149" t="n">
-        <v>43.97</v>
+        <v>45.91</v>
       </c>
       <c r="N149" t="b">
         <v>0</v>
@@ -8470,7 +8480,7 @@
         <v>6.1</v>
       </c>
       <c r="H150" t="n">
-        <v>-0.58</v>
+        <v>7.05</v>
       </c>
       <c r="I150" t="n">
         <v>10.43</v>
@@ -8483,7 +8493,7 @@
         <v>-1.51</v>
       </c>
       <c r="M150" t="n">
-        <v>-5.4</v>
+        <v>1.93</v>
       </c>
       <c r="N150" t="b">
         <v>0</v>
@@ -8521,7 +8531,7 @@
         <v>6.5</v>
       </c>
       <c r="H151" t="n">
-        <v>-6.04</v>
+        <v>-3.58</v>
       </c>
       <c r="I151" t="n">
         <v>-0.04</v>
@@ -8534,7 +8544,7 @@
         <v>-4.12</v>
       </c>
       <c r="M151" t="n">
-        <v>-10.86</v>
+        <v>-8.699999999999999</v>
       </c>
       <c r="N151" t="b">
         <v>0</v>
@@ -8572,7 +8582,7 @@
         <v>-36.5</v>
       </c>
       <c r="H152" t="n">
-        <v>-34.76</v>
+        <v>-29.67</v>
       </c>
       <c r="I152" t="n">
         <v>-27.75</v>
@@ -8585,7 +8595,7 @@
         <v>-31.28</v>
       </c>
       <c r="M152" t="n">
-        <v>-39.02</v>
+        <v>-34.23</v>
       </c>
       <c r="N152" t="b">
         <v>1</v>
@@ -8623,7 +8633,7 @@
         <v>-14.5</v>
       </c>
       <c r="H153" t="n">
-        <v>-16.61</v>
+        <v>-10.81</v>
       </c>
       <c r="I153" t="n">
         <v>4.48</v>
@@ -8636,7 +8646,7 @@
         <v>-3.33</v>
       </c>
       <c r="M153" t="n">
-        <v>-20.87</v>
+        <v>-15.37</v>
       </c>
       <c r="N153" t="b">
         <v>0</v>
@@ -8674,7 +8684,7 @@
         <v>1.7</v>
       </c>
       <c r="H154" t="n">
-        <v>-5.73</v>
+        <v>-1.1</v>
       </c>
       <c r="I154" t="n">
         <v>8.859999999999999</v>
@@ -8687,7 +8697,7 @@
         <v>-3.27</v>
       </c>
       <c r="M154" t="n">
-        <v>-10</v>
+        <v>-5.66</v>
       </c>
       <c r="N154" t="b">
         <v>0</v>
@@ -8725,7 +8735,7 @@
         <v>48.1</v>
       </c>
       <c r="H155" t="n">
-        <v>10.1</v>
+        <v>11.33</v>
       </c>
       <c r="I155" t="n">
         <v>0.16</v>
@@ -8738,7 +8748,7 @@
         <v>-8.890000000000001</v>
       </c>
       <c r="M155" t="n">
-        <v>5.84</v>
+        <v>6.78</v>
       </c>
       <c r="N155" t="b">
         <v>0</v>
@@ -8776,7 +8786,7 @@
         <v>-38.7</v>
       </c>
       <c r="H156" t="n">
-        <v>15.67</v>
+        <v>22.94</v>
       </c>
       <c r="I156" t="n">
         <v>17.17</v>
@@ -8789,7 +8799,7 @@
         <v>-0.54</v>
       </c>
       <c r="M156" t="n">
-        <v>11.41</v>
+        <v>18.38</v>
       </c>
       <c r="N156" t="b">
         <v>1</v>
@@ -8827,7 +8837,7 @@
         <v>24.9</v>
       </c>
       <c r="H157" t="n">
-        <v>1.68</v>
+        <v>5.61</v>
       </c>
       <c r="I157" t="n">
         <v>10.45</v>
@@ -8840,7 +8850,7 @@
         <v>-0.49</v>
       </c>
       <c r="M157" t="n">
-        <v>-2.58</v>
+        <v>1.06</v>
       </c>
       <c r="N157" t="b">
         <v>0</v>
@@ -8878,7 +8888,7 @@
         <v>-34.6</v>
       </c>
       <c r="H158" t="n">
-        <v>15.51</v>
+        <v>22.75</v>
       </c>
       <c r="I158" t="n">
         <v>6.67</v>
@@ -8891,7 +8901,7 @@
         <v>-3.06</v>
       </c>
       <c r="M158" t="n">
-        <v>11.25</v>
+        <v>18.19</v>
       </c>
       <c r="N158" t="b">
         <v>1</v>
@@ -8929,7 +8939,7 @@
         <v>-21.4</v>
       </c>
       <c r="H159" t="n">
-        <v>-2.24</v>
+        <v>0.58</v>
       </c>
       <c r="I159" t="n">
         <v>2.8</v>
@@ -8942,7 +8952,7 @@
         <v>-2.27</v>
       </c>
       <c r="M159" t="n">
-        <v>-6.51</v>
+        <v>-3.98</v>
       </c>
       <c r="N159" t="b">
         <v>0</v>
@@ -8980,7 +8990,7 @@
         <v>-11.8</v>
       </c>
       <c r="H160" t="n">
-        <v>-0.93</v>
+        <v>2.76</v>
       </c>
       <c r="I160" t="n">
         <v>9.76</v>
@@ -8993,7 +9003,7 @@
         <v>-1.63</v>
       </c>
       <c r="M160" t="n">
-        <v>-5.3</v>
+        <v>-1.91</v>
       </c>
       <c r="N160" t="b">
         <v>1</v>
@@ -9031,7 +9041,7 @@
         <v>0.1</v>
       </c>
       <c r="H161" t="n">
-        <v>-12.44</v>
+        <v>-7.73</v>
       </c>
       <c r="I161" t="n">
         <v>-2.83</v>
@@ -9044,7 +9054,7 @@
         <v>-5.45</v>
       </c>
       <c r="M161" t="n">
-        <v>-16.81</v>
+        <v>-12.4</v>
       </c>
       <c r="N161" t="b">
         <v>1</v>
@@ -9082,7 +9092,7 @@
         <v>-13.8</v>
       </c>
       <c r="H162" t="n">
-        <v>22.25</v>
+        <v>19.24</v>
       </c>
       <c r="I162" t="n">
         <v>4.67</v>
@@ -9095,7 +9105,7 @@
         <v>-5.7</v>
       </c>
       <c r="M162" t="n">
-        <v>17.88</v>
+        <v>14.57</v>
       </c>
       <c r="N162" t="b">
         <v>0</v>
@@ -9137,7 +9147,7 @@
         <v>-8.800000000000001</v>
       </c>
       <c r="H163" t="n">
-        <v>8.960000000000001</v>
+        <v>13.45</v>
       </c>
       <c r="I163" t="n">
         <v>15.97</v>
@@ -9150,7 +9160,7 @@
         <v>-0.79</v>
       </c>
       <c r="M163" t="n">
-        <v>4.59</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="N163" t="b">
         <v>0</v>
@@ -9188,7 +9198,7 @@
         <v>24.1</v>
       </c>
       <c r="H164" t="n">
-        <v>2.77</v>
+        <v>2.93</v>
       </c>
       <c r="I164" t="n">
         <v>-8.31</v>
@@ -9201,7 +9211,7 @@
         <v>-18.31</v>
       </c>
       <c r="M164" t="n">
-        <v>-0.8</v>
+        <v>-0.93</v>
       </c>
       <c r="N164" t="b">
         <v>1</v>
@@ -9239,7 +9249,7 @@
         <v>-15.9</v>
       </c>
       <c r="H165" t="n">
-        <v>10</v>
+        <v>13.57</v>
       </c>
       <c r="I165" t="n">
         <v>10.45</v>
@@ -9252,7 +9262,7 @@
         <v>-0.31</v>
       </c>
       <c r="M165" t="n">
-        <v>6.43</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="N165" t="b">
         <v>1</v>
@@ -9290,7 +9300,7 @@
         <v>-23.3</v>
       </c>
       <c r="H166" t="n">
-        <v>-17.67</v>
+        <v>-14.17</v>
       </c>
       <c r="I166" t="n">
         <v>-20.42</v>
@@ -9303,7 +9313,7 @@
         <v>-27.45</v>
       </c>
       <c r="M166" t="n">
-        <v>-21.25</v>
+        <v>-18.03</v>
       </c>
       <c r="N166" t="b">
         <v>0</v>
@@ -9341,7 +9351,7 @@
         <v>28.9</v>
       </c>
       <c r="H167" t="n">
-        <v>1.52</v>
+        <v>-1.86</v>
       </c>
       <c r="I167" t="n">
         <v>8.06</v>
@@ -9354,7 +9364,7 @@
         <v>-2.79</v>
       </c>
       <c r="M167" t="n">
-        <v>-2.95</v>
+        <v>-6.63</v>
       </c>
       <c r="N167" t="b">
         <v>0</v>
@@ -9392,7 +9402,7 @@
         <v>40.1</v>
       </c>
       <c r="H168" t="n">
-        <v>34.75</v>
+        <v>32.2</v>
       </c>
       <c r="I168" t="n">
         <v>15.9</v>
@@ -9405,7 +9415,7 @@
         <v>-5.87</v>
       </c>
       <c r="M168" t="n">
-        <v>30.28</v>
+        <v>27.43</v>
       </c>
       <c r="N168" t="b">
         <v>0</v>
@@ -9443,7 +9453,7 @@
         <v>-27.3</v>
       </c>
       <c r="H169" t="n">
-        <v>5.5</v>
+        <v>5.84</v>
       </c>
       <c r="I169" t="n">
         <v>0.75</v>
@@ -9456,7 +9466,7 @@
         <v>-5.46</v>
       </c>
       <c r="M169" t="n">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="N169" t="b">
         <v>0</v>
@@ -9494,7 +9504,7 @@
         <v>19.7</v>
       </c>
       <c r="H170" t="n">
-        <v>-26.11</v>
+        <v>-25.62</v>
       </c>
       <c r="I170" t="n">
         <v>-4.49</v>
@@ -9507,7 +9517,7 @@
         <v>-13.7</v>
       </c>
       <c r="M170" t="n">
-        <v>-30.46</v>
+        <v>-30.26</v>
       </c>
       <c r="N170" t="b">
         <v>0</v>
@@ -9545,7 +9555,7 @@
         <v>-21.3</v>
       </c>
       <c r="H171" t="n">
-        <v>-15.81</v>
+        <v>-10.66</v>
       </c>
       <c r="I171" t="n">
         <v>7.16</v>
@@ -9558,7 +9568,7 @@
         <v>-11.9</v>
       </c>
       <c r="M171" t="n">
-        <v>-20.16</v>
+        <v>-15.3</v>
       </c>
       <c r="N171" t="b">
         <v>0</v>
@@ -9596,7 +9606,7 @@
         <v>-21.8</v>
       </c>
       <c r="H172" t="n">
-        <v>-36.71</v>
+        <v>-32.58</v>
       </c>
       <c r="I172" t="n">
         <v>-18.97</v>
@@ -9609,7 +9619,7 @@
         <v>-26.82</v>
       </c>
       <c r="M172" t="n">
-        <v>-41.06</v>
+        <v>-37.23</v>
       </c>
       <c r="N172" t="b">
         <v>1</v>
@@ -9647,7 +9657,7 @@
         <v>-37.6</v>
       </c>
       <c r="H173" t="n">
-        <v>-18.13</v>
+        <v>-15.2</v>
       </c>
       <c r="I173" t="n">
         <v>15.2</v>
@@ -9655,12 +9665,14 @@
       <c r="J173" t="n">
         <v>26.06</v>
       </c>
-      <c r="K173" t="inlineStr"/>
+      <c r="K173" t="n">
+        <v>-15.2</v>
+      </c>
       <c r="L173" t="n">
         <v>-10.3</v>
       </c>
       <c r="M173" t="n">
-        <v>-21.46</v>
+        <v>-18.82</v>
       </c>
       <c r="N173" t="b">
         <v>0</v>
@@ -9698,7 +9710,7 @@
         <v>53.8</v>
       </c>
       <c r="H174" t="n">
-        <v>50.02</v>
+        <v>47.61</v>
       </c>
       <c r="I174" t="n">
         <v>4.09</v>
@@ -9706,12 +9718,14 @@
       <c r="J174" t="n">
         <v>-0.04</v>
       </c>
-      <c r="K174" t="inlineStr"/>
+      <c r="K174" t="n">
+        <v>47.61</v>
+      </c>
       <c r="L174" t="n">
         <v>-8.66</v>
       </c>
       <c r="M174" t="n">
-        <v>46.68</v>
+        <v>43.99</v>
       </c>
       <c r="N174" t="b">
         <v>0</v>
@@ -9753,7 +9767,7 @@
         <v>-5.7</v>
       </c>
       <c r="H175" t="n">
-        <v>37.63</v>
+        <v>44.08</v>
       </c>
       <c r="I175" t="n">
         <v>17.92</v>
@@ -9761,12 +9775,14 @@
       <c r="J175" t="n">
         <v>56.62</v>
       </c>
-      <c r="K175" t="inlineStr"/>
+      <c r="K175" t="n">
+        <v>44.08</v>
+      </c>
       <c r="L175" t="n">
         <v>-7.48</v>
       </c>
       <c r="M175" t="n">
-        <v>34.3</v>
+        <v>40.45</v>
       </c>
       <c r="N175" t="b">
         <v>0</v>
@@ -9804,7 +9820,7 @@
         <v>-39.3</v>
       </c>
       <c r="H176" t="n">
-        <v>5.89</v>
+        <v>12.62</v>
       </c>
       <c r="I176" t="n">
         <v>11.34</v>
@@ -9812,12 +9828,14 @@
       <c r="J176" t="n">
         <v>23.06</v>
       </c>
-      <c r="K176" t="inlineStr"/>
+      <c r="K176" t="n">
+        <v>12.62</v>
+      </c>
       <c r="L176" t="n">
         <v>-5.3</v>
       </c>
       <c r="M176" t="n">
-        <v>2.55</v>
+        <v>8.99</v>
       </c>
       <c r="N176" t="b">
         <v>0</v>
@@ -9855,7 +9873,7 @@
         <v>57</v>
       </c>
       <c r="H177" t="n">
-        <v>37.47</v>
+        <v>34.25</v>
       </c>
       <c r="I177" t="n">
         <v>-11.21</v>
@@ -9863,12 +9881,14 @@
       <c r="J177" t="n">
         <v>1.87</v>
       </c>
-      <c r="K177" t="inlineStr"/>
+      <c r="K177" t="n">
+        <v>34.25</v>
+      </c>
       <c r="L177" t="n">
         <v>-13.87</v>
       </c>
       <c r="M177" t="n">
-        <v>34.14</v>
+        <v>30.63</v>
       </c>
       <c r="N177" t="b">
         <v>1</v>
@@ -9906,7 +9926,7 @@
         <v>-21.8</v>
       </c>
       <c r="H178" t="n">
-        <v>16.15</v>
+        <v>20.63</v>
       </c>
       <c r="I178" t="n">
         <v>1.71</v>
@@ -9914,12 +9934,14 @@
       <c r="J178" t="n">
         <v>15.07</v>
       </c>
-      <c r="K178" t="inlineStr"/>
+      <c r="K178" t="n">
+        <v>20.63</v>
+      </c>
       <c r="L178" t="n">
         <v>-6.18</v>
       </c>
       <c r="M178" t="n">
-        <v>12.81</v>
+        <v>17</v>
       </c>
       <c r="N178" t="b">
         <v>1</v>
@@ -9957,7 +9979,7 @@
         <v>1</v>
       </c>
       <c r="H179" t="n">
-        <v>-33.09</v>
+        <v>-31.18</v>
       </c>
       <c r="I179" t="n">
         <v>-11.52</v>
@@ -9972,7 +9994,7 @@
         <v>-16.26</v>
       </c>
       <c r="M179" t="n">
-        <v>-36.47</v>
+        <v>-34.85</v>
       </c>
       <c r="N179" t="b">
         <v>1</v>
@@ -10010,7 +10032,7 @@
         <v>45.4</v>
       </c>
       <c r="H180" t="n">
-        <v>-16.63</v>
+        <v>-14.25</v>
       </c>
       <c r="I180" t="n">
         <v>-1.72</v>
@@ -10025,7 +10047,7 @@
         <v>-23.15</v>
       </c>
       <c r="M180" t="n">
-        <v>-20</v>
+        <v>-17.92</v>
       </c>
       <c r="N180" t="b">
         <v>1</v>
@@ -10063,7 +10085,7 @@
         <v>49.6</v>
       </c>
       <c r="H181" t="n">
-        <v>19.35</v>
+        <v>17.38</v>
       </c>
       <c r="I181" t="n">
         <v>6.34</v>
@@ -10078,7 +10100,7 @@
         <v>-20.75</v>
       </c>
       <c r="M181" t="n">
-        <v>15.97</v>
+        <v>13.71</v>
       </c>
       <c r="N181" t="b">
         <v>0</v>
@@ -10116,7 +10138,7 @@
         <v>55.3</v>
       </c>
       <c r="H182" t="n">
-        <v>-31.13</v>
+        <v>-32.57</v>
       </c>
       <c r="I182" t="n">
         <v>3.73</v>
@@ -10131,7 +10153,7 @@
         <v>-22.94</v>
       </c>
       <c r="M182" t="n">
-        <v>-34.5</v>
+        <v>-36.25</v>
       </c>
       <c r="N182" t="b">
         <v>0</v>
@@ -10169,7 +10191,7 @@
         <v>76.5</v>
       </c>
       <c r="H183" t="n">
-        <v>-7.17</v>
+        <v>-7.73</v>
       </c>
       <c r="I183" t="n">
         <v>-5.56</v>
@@ -10184,7 +10206,7 @@
         <v>-33.97</v>
       </c>
       <c r="M183" t="n">
-        <v>-10.55</v>
+        <v>-11.4</v>
       </c>
       <c r="N183" t="b">
         <v>1</v>
@@ -10222,7 +10244,7 @@
         <v>77.90000000000001</v>
       </c>
       <c r="H184" t="n">
-        <v>-1.2</v>
+        <v>0.65</v>
       </c>
       <c r="I184" t="n">
         <v>-3.53</v>
@@ -10237,7 +10259,7 @@
         <v>-20.26</v>
       </c>
       <c r="M184" t="n">
-        <v>-4.58</v>
+        <v>-3.02</v>
       </c>
       <c r="N184" t="b">
         <v>0</v>
@@ -10275,7 +10297,7 @@
         <v>57.6</v>
       </c>
       <c r="H185" t="n">
-        <v>38.66</v>
+        <v>28.82</v>
       </c>
       <c r="I185" t="n">
         <v>14.81</v>
@@ -10290,7 +10312,7 @@
         <v>-5.11</v>
       </c>
       <c r="M185" t="n">
-        <v>35.28</v>
+        <v>25.14</v>
       </c>
       <c r="N185" t="b">
         <v>0</v>
@@ -10328,7 +10350,7 @@
         <v>32.1</v>
       </c>
       <c r="H186" t="n">
-        <v>-3.65</v>
+        <v>-2.4</v>
       </c>
       <c r="I186" t="n">
         <v>16.93</v>
@@ -10343,7 +10365,7 @@
         <v>-24.48</v>
       </c>
       <c r="M186" t="n">
-        <v>-7.03</v>
+        <v>-6.08</v>
       </c>
       <c r="N186" t="b">
         <v>1</v>
@@ -10381,7 +10403,7 @@
         <v>51.8</v>
       </c>
       <c r="H187" t="n">
-        <v>-8.050000000000001</v>
+        <v>-7.53</v>
       </c>
       <c r="I187" t="n">
         <v>10.75</v>
@@ -10396,7 +10418,7 @@
         <v>-25.09</v>
       </c>
       <c r="M187" t="n">
-        <v>-11.43</v>
+        <v>-11.2</v>
       </c>
       <c r="N187" t="b">
         <v>1</v>
@@ -10434,7 +10456,7 @@
         <v>32.3</v>
       </c>
       <c r="H188" t="n">
-        <v>-33.71</v>
+        <v>-34.71</v>
       </c>
       <c r="I188" t="n">
         <v>-20.76</v>
@@ -10449,7 +10471,7 @@
         <v>-27.91</v>
       </c>
       <c r="M188" t="n">
-        <v>-37.09</v>
+        <v>-38.38</v>
       </c>
       <c r="N188" t="b">
         <v>1</v>
@@ -10487,7 +10509,7 @@
         <v>15.7</v>
       </c>
       <c r="H189" t="n">
-        <v>-12.49</v>
+        <v>-14.02</v>
       </c>
       <c r="I189" t="n">
         <v>-0.87</v>
@@ -10502,7 +10524,7 @@
         <v>-29.01</v>
       </c>
       <c r="M189" t="n">
-        <v>-15.87</v>
+        <v>-17.69</v>
       </c>
       <c r="N189" t="b">
         <v>0</v>
@@ -10540,7 +10562,7 @@
         <v>63.7</v>
       </c>
       <c r="H190" t="n">
-        <v>-17.35</v>
+        <v>-19.98</v>
       </c>
       <c r="I190" t="n">
         <v>-2.16</v>
@@ -10555,7 +10577,7 @@
         <v>-19.1</v>
       </c>
       <c r="M190" t="n">
-        <v>-20.73</v>
+        <v>-23.65</v>
       </c>
       <c r="N190" t="b">
         <v>0</v>
@@ -10593,7 +10615,7 @@
         <v>3.7</v>
       </c>
       <c r="H191" t="n">
-        <v>-14.76</v>
+        <v>-9.66</v>
       </c>
       <c r="I191" t="n">
         <v>-1.11</v>
@@ -10608,7 +10630,7 @@
         <v>-25.46</v>
       </c>
       <c r="M191" t="n">
-        <v>-18.14</v>
+        <v>-13.33</v>
       </c>
       <c r="N191" t="b">
         <v>1</v>
@@ -10646,7 +10668,7 @@
         <v>42.4</v>
       </c>
       <c r="H192" t="n">
-        <v>-13.37</v>
+        <v>-13.23</v>
       </c>
       <c r="I192" t="n">
         <v>2.16</v>
@@ -10661,7 +10683,7 @@
         <v>-15.76</v>
       </c>
       <c r="M192" t="n">
-        <v>-16.75</v>
+        <v>-16.9</v>
       </c>
       <c r="N192" t="b">
         <v>1</v>
@@ -10699,7 +10721,7 @@
         <v>28.2</v>
       </c>
       <c r="H193" t="n">
-        <v>-6.02</v>
+        <v>-10.24</v>
       </c>
       <c r="I193" t="n">
         <v>-1.71</v>
@@ -10714,7 +10736,7 @@
         <v>-23.43</v>
       </c>
       <c r="M193" t="n">
-        <v>-9.4</v>
+        <v>-13.91</v>
       </c>
       <c r="N193" t="b">
         <v>1</v>
@@ -10752,7 +10774,7 @@
         <v>28.6</v>
       </c>
       <c r="H194" t="n">
-        <v>11.38</v>
+        <v>-0.16</v>
       </c>
       <c r="I194" t="n">
         <v>2.81</v>
@@ -10767,7 +10789,7 @@
         <v>-18.87</v>
       </c>
       <c r="M194" t="n">
-        <v>8</v>
+        <v>-3.84</v>
       </c>
       <c r="N194" t="b">
         <v>1</v>
@@ -10805,7 +10827,7 @@
         <v>89.09999999999999</v>
       </c>
       <c r="H195" t="n">
-        <v>28.75</v>
+        <v>20</v>
       </c>
       <c r="I195" t="n">
         <v>18.45</v>
@@ -10820,7 +10842,7 @@
         <v>-9.029999999999999</v>
       </c>
       <c r="M195" t="n">
-        <v>25.37</v>
+        <v>16.32</v>
       </c>
       <c r="N195" t="b">
         <v>0</v>
@@ -10858,7 +10880,7 @@
         <v>50.5</v>
       </c>
       <c r="H196" t="n">
-        <v>-4.91</v>
+        <v>-7.58</v>
       </c>
       <c r="I196" t="n">
         <v>-2.26</v>
@@ -10873,7 +10895,7 @@
         <v>-20.74</v>
       </c>
       <c r="M196" t="n">
-        <v>-8.289999999999999</v>
+        <v>-11.25</v>
       </c>
       <c r="N196" t="b">
         <v>0</v>
@@ -10911,7 +10933,7 @@
         <v>33.1</v>
       </c>
       <c r="H197" t="n">
-        <v>10.45</v>
+        <v>7.15</v>
       </c>
       <c r="I197" t="n">
         <v>4.68</v>
@@ -10926,7 +10948,7 @@
         <v>-26.7</v>
       </c>
       <c r="M197" t="n">
-        <v>7.07</v>
+        <v>3.48</v>
       </c>
       <c r="N197" t="b">
         <v>1</v>
@@ -10964,7 +10986,7 @@
         <v>46.3</v>
       </c>
       <c r="H198" t="n">
-        <v>-20.86</v>
+        <v>-23.8</v>
       </c>
       <c r="I198" t="n">
         <v>-3.24</v>
@@ -10979,7 +11001,7 @@
         <v>-22.77</v>
       </c>
       <c r="M198" t="n">
-        <v>-24.24</v>
+        <v>-27.48</v>
       </c>
       <c r="N198" t="b">
         <v>0</v>
@@ -11017,7 +11039,7 @@
         <v>-13.8</v>
       </c>
       <c r="H199" t="n">
-        <v>7.56</v>
+        <v>14.64</v>
       </c>
       <c r="I199" t="n">
         <v>6.03</v>
@@ -11032,7 +11054,7 @@
         <v>-13.77</v>
       </c>
       <c r="M199" t="n">
-        <v>4.18</v>
+        <v>10.97</v>
       </c>
       <c r="N199" t="b">
         <v>0</v>
@@ -11070,7 +11092,7 @@
         <v>21.8</v>
       </c>
       <c r="H200" t="n">
-        <v>-27.13</v>
+        <v>-28.51</v>
       </c>
       <c r="I200" t="n">
         <v>-6.34</v>
@@ -11085,7 +11107,7 @@
         <v>-30.04</v>
       </c>
       <c r="M200" t="n">
-        <v>-30.51</v>
+        <v>-32.18</v>
       </c>
       <c r="N200" t="b">
         <v>1</v>
@@ -11123,7 +11145,7 @@
         <v>40.3</v>
       </c>
       <c r="H201" t="n">
-        <v>-19.82</v>
+        <v>-21.3</v>
       </c>
       <c r="I201" t="n">
         <v>1.24</v>
@@ -11138,7 +11160,7 @@
         <v>-20.5</v>
       </c>
       <c r="M201" t="n">
-        <v>-23.2</v>
+        <v>-24.97</v>
       </c>
       <c r="N201" t="b">
         <v>1</v>
@@ -11176,7 +11198,7 @@
         <v>36.6</v>
       </c>
       <c r="H202" t="n">
-        <v>280.27</v>
+        <v>297.41</v>
       </c>
       <c r="I202" t="n">
         <v>-4.23</v>
@@ -11191,7 +11213,7 @@
         <v>-11.51</v>
       </c>
       <c r="M202" t="n">
-        <v>276.89</v>
+        <v>293.74</v>
       </c>
       <c r="N202" t="b">
         <v>0</v>
@@ -11229,7 +11251,7 @@
         <v>24.1</v>
       </c>
       <c r="H203" t="n">
-        <v>-11.41</v>
+        <v>-15.35</v>
       </c>
       <c r="I203" t="n">
         <v>-1.6</v>
@@ -11244,7 +11266,7 @@
         <v>-22.54</v>
       </c>
       <c r="M203" t="n">
-        <v>-14.79</v>
+        <v>-19.03</v>
       </c>
       <c r="N203" t="b">
         <v>1</v>
@@ -11282,7 +11304,7 @@
         <v>50.3</v>
       </c>
       <c r="H204" t="n">
-        <v>-28.46</v>
+        <v>-27.3</v>
       </c>
       <c r="I204" t="n">
         <v>-3.34</v>
@@ -11297,7 +11319,7 @@
         <v>-23.32</v>
       </c>
       <c r="M204" t="n">
-        <v>-31.84</v>
+        <v>-30.97</v>
       </c>
       <c r="N204" t="b">
         <v>0</v>
@@ -11335,7 +11357,7 @@
         <v>24.5</v>
       </c>
       <c r="H205" t="n">
-        <v>-34.58</v>
+        <v>-34.29</v>
       </c>
       <c r="I205" t="n">
         <v>-12.99</v>
@@ -11350,7 +11372,7 @@
         <v>-22.54</v>
       </c>
       <c r="M205" t="n">
-        <v>-37.96</v>
+        <v>-37.97</v>
       </c>
       <c r="N205" t="b">
         <v>1</v>
@@ -11388,7 +11410,7 @@
         <v>-4</v>
       </c>
       <c r="H206" t="n">
-        <v>-31.07</v>
+        <v>-30.23</v>
       </c>
       <c r="I206" t="n">
         <v>-1.59</v>
@@ -11403,7 +11425,7 @@
         <v>-25.38</v>
       </c>
       <c r="M206" t="n">
-        <v>-34.45</v>
+        <v>-33.91</v>
       </c>
       <c r="N206" t="b">
         <v>0</v>
@@ -11441,7 +11463,7 @@
         <v>14.8</v>
       </c>
       <c r="H207" t="n">
-        <v>-38.96</v>
+        <v>-37.14</v>
       </c>
       <c r="I207" t="n">
         <v>-2.48</v>
@@ -11456,7 +11478,7 @@
         <v>-40.98</v>
       </c>
       <c r="M207" t="n">
-        <v>-42.34</v>
+        <v>-40.81</v>
       </c>
       <c r="N207" t="b">
         <v>0</v>
@@ -11494,7 +11516,7 @@
         <v>-27.6</v>
       </c>
       <c r="H208" t="n">
-        <v>-21.34</v>
+        <v>-17.42</v>
       </c>
       <c r="I208" t="n">
         <v>-0.36</v>
@@ -11509,7 +11531,7 @@
         <v>-19.41</v>
       </c>
       <c r="M208" t="n">
-        <v>-24.72</v>
+        <v>-21.09</v>
       </c>
       <c r="N208" t="b">
         <v>0</v>
@@ -11547,7 +11569,7 @@
         <v>9.1</v>
       </c>
       <c r="H209" t="n">
-        <v>-40.61</v>
+        <v>-35.05</v>
       </c>
       <c r="I209" t="n">
         <v>-2.83</v>
@@ -11562,7 +11584,7 @@
         <v>-23.78</v>
       </c>
       <c r="M209" t="n">
-        <v>-43.99</v>
+        <v>-38.72</v>
       </c>
       <c r="N209" t="b">
         <v>0</v>
@@ -11600,7 +11622,7 @@
         <v>11</v>
       </c>
       <c r="H210" t="n">
-        <v>-9.58</v>
+        <v>-10.35</v>
       </c>
       <c r="I210" t="n">
         <v>3.38</v>
@@ -11615,7 +11637,7 @@
         <v>-18.71</v>
       </c>
       <c r="M210" t="n">
-        <v>-12.96</v>
+        <v>-14.03</v>
       </c>
       <c r="N210" t="b">
         <v>0</v>
@@ -11653,7 +11675,7 @@
         <v>31.2</v>
       </c>
       <c r="H211" t="n">
-        <v>-18.72</v>
+        <v>-20.7</v>
       </c>
       <c r="I211" t="n">
         <v>-11.26</v>
@@ -11668,7 +11690,7 @@
         <v>-22.9</v>
       </c>
       <c r="M211" t="n">
-        <v>-22.1</v>
+        <v>-24.37</v>
       </c>
       <c r="N211" t="b">
         <v>0</v>
@@ -11706,7 +11728,7 @@
         <v>19.3</v>
       </c>
       <c r="H212" t="n">
-        <v>-0.39</v>
+        <v>-4.89</v>
       </c>
       <c r="I212" t="n">
         <v>11.79</v>
@@ -11721,7 +11743,7 @@
         <v>-16.62</v>
       </c>
       <c r="M212" t="n">
-        <v>-3.77</v>
+        <v>-8.57</v>
       </c>
       <c r="N212" t="b">
         <v>1</v>
@@ -11759,7 +11781,7 @@
         <v>-8.699999999999999</v>
       </c>
       <c r="H213" t="n">
-        <v>-11.93</v>
+        <v>-9.24</v>
       </c>
       <c r="I213" t="n">
         <v>17.25</v>
@@ -11774,7 +11796,7 @@
         <v>-4.65</v>
       </c>
       <c r="M213" t="n">
-        <v>-15.31</v>
+        <v>-12.91</v>
       </c>
       <c r="N213" t="b">
         <v>1</v>
@@ -11812,7 +11834,7 @@
         <v>15.2</v>
       </c>
       <c r="H214" t="n">
-        <v>-14.3</v>
+        <v>-18.44</v>
       </c>
       <c r="I214" t="n">
         <v>5.36</v>
@@ -11827,7 +11849,7 @@
         <v>-28.18</v>
       </c>
       <c r="M214" t="n">
-        <v>-17.68</v>
+        <v>-22.11</v>
       </c>
       <c r="N214" t="b">
         <v>1</v>
@@ -11865,7 +11887,7 @@
         <v>37.2</v>
       </c>
       <c r="H215" t="n">
-        <v>-32.41</v>
+        <v>-34.14</v>
       </c>
       <c r="I215" t="n">
         <v>-7.64</v>
@@ -11880,7 +11902,7 @@
         <v>-26.24</v>
       </c>
       <c r="M215" t="n">
-        <v>-35.79</v>
+        <v>-37.81</v>
       </c>
       <c r="N215" t="b">
         <v>1</v>
@@ -11922,7 +11944,7 @@
         <v>-0.5</v>
       </c>
       <c r="H216" t="n">
-        <v>38.79</v>
+        <v>49.03</v>
       </c>
       <c r="I216" t="n">
         <v>12.75</v>
@@ -11937,7 +11959,7 @@
         <v>-4.72</v>
       </c>
       <c r="M216" t="n">
-        <v>35.41</v>
+        <v>45.36</v>
       </c>
       <c r="N216" t="b">
         <v>0</v>
@@ -11975,7 +11997,7 @@
         <v>-27.9</v>
       </c>
       <c r="H217" t="n">
-        <v>-27.06</v>
+        <v>-49.33</v>
       </c>
       <c r="I217" t="n">
         <v>-5.72</v>
@@ -11990,7 +12012,7 @@
         <v>-11.08</v>
       </c>
       <c r="M217" t="n">
-        <v>-30.44</v>
+        <v>-53</v>
       </c>
       <c r="N217" t="b">
         <v>0</v>
@@ -12028,7 +12050,7 @@
         <v>29.8</v>
       </c>
       <c r="H218" t="n">
-        <v>20.68</v>
+        <v>8.59</v>
       </c>
       <c r="I218" t="n">
         <v>-2.74</v>
@@ -12043,7 +12065,7 @@
         <v>-22.36</v>
       </c>
       <c r="M218" t="n">
-        <v>17.3</v>
+        <v>4.92</v>
       </c>
       <c r="N218" t="b">
         <v>1</v>
@@ -12081,7 +12103,7 @@
         <v>60.9</v>
       </c>
       <c r="H219" t="n">
-        <v>-1.21</v>
+        <v>-2.91</v>
       </c>
       <c r="I219" t="n">
         <v>6.71</v>
@@ -12096,7 +12118,7 @@
         <v>-4.9</v>
       </c>
       <c r="M219" t="n">
-        <v>-4.59</v>
+        <v>-6.58</v>
       </c>
       <c r="N219" t="b">
         <v>0</v>
@@ -12134,7 +12156,7 @@
         <v>-13.4</v>
       </c>
       <c r="H220" t="n">
-        <v>-37.62</v>
+        <v>-35.81</v>
       </c>
       <c r="I220" t="n">
         <v>0.79</v>
@@ -12149,7 +12171,7 @@
         <v>-15.41</v>
       </c>
       <c r="M220" t="n">
-        <v>-41</v>
+        <v>-39.48</v>
       </c>
       <c r="N220" t="b">
         <v>0</v>
@@ -12187,7 +12209,7 @@
         <v>18.2</v>
       </c>
       <c r="H221" t="n">
-        <v>-19.43</v>
+        <v>-19.06</v>
       </c>
       <c r="I221" t="n">
         <v>-11.28</v>
@@ -12202,7 +12224,7 @@
         <v>-16.87</v>
       </c>
       <c r="M221" t="n">
-        <v>-22.81</v>
+        <v>-22.73</v>
       </c>
       <c r="N221" t="b">
         <v>0</v>
@@ -12240,7 +12262,7 @@
         <v>31.2</v>
       </c>
       <c r="H222" t="n">
-        <v>-12.47</v>
+        <v>-15.35</v>
       </c>
       <c r="I222" t="n">
         <v>-3.17</v>
@@ -12255,7 +12277,7 @@
         <v>-23.66</v>
       </c>
       <c r="M222" t="n">
-        <v>-15.85</v>
+        <v>-19.03</v>
       </c>
       <c r="N222" t="b">
         <v>0</v>
@@ -12293,7 +12315,7 @@
         <v>-1.3</v>
       </c>
       <c r="H223" t="n">
-        <v>-26.01</v>
+        <v>-22.31</v>
       </c>
       <c r="I223" t="n">
         <v>5.29</v>
@@ -12308,7 +12330,7 @@
         <v>-11.87</v>
       </c>
       <c r="M223" t="n">
-        <v>-29.39</v>
+        <v>-25.98</v>
       </c>
       <c r="N223" t="b">
         <v>0</v>
@@ -12346,7 +12368,7 @@
         <v>-29.8</v>
       </c>
       <c r="H224" t="n">
-        <v>46.64</v>
+        <v>43.81</v>
       </c>
       <c r="I224" t="n">
         <v>29.88</v>
@@ -12361,7 +12383,7 @@
         <v>-0.29</v>
       </c>
       <c r="M224" t="n">
-        <v>43.26</v>
+        <v>40.14</v>
       </c>
       <c r="N224" t="b">
         <v>0</v>
@@ -12399,7 +12421,7 @@
         <v>-22.4</v>
       </c>
       <c r="H225" t="n">
-        <v>-20.66</v>
+        <v>-13.64</v>
       </c>
       <c r="I225" t="n">
         <v>5.79</v>
@@ -12414,7 +12436,7 @@
         <v>-9.67</v>
       </c>
       <c r="M225" t="n">
-        <v>-24.04</v>
+        <v>-17.32</v>
       </c>
       <c r="N225" t="b">
         <v>0</v>
@@ -12452,7 +12474,7 @@
         <v>19.3</v>
       </c>
       <c r="H226" t="n">
-        <v>-33.04</v>
+        <v>-34.19</v>
       </c>
       <c r="I226" t="n">
         <v>-16.69</v>
@@ -12467,7 +12489,7 @@
         <v>-36.39</v>
       </c>
       <c r="M226" t="n">
-        <v>-36.42</v>
+        <v>-37.87</v>
       </c>
       <c r="N226" t="b">
         <v>1</v>
@@ -12505,7 +12527,7 @@
         <v>7.6</v>
       </c>
       <c r="H227" t="n">
-        <v>-25.61</v>
+        <v>-23.64</v>
       </c>
       <c r="I227" t="n">
         <v>6.22</v>
@@ -12520,7 +12542,7 @@
         <v>-10.68</v>
       </c>
       <c r="M227" t="n">
-        <v>-28.99</v>
+        <v>-27.31</v>
       </c>
       <c r="N227" t="b">
         <v>0</v>
@@ -12558,7 +12580,7 @@
         <v>68.8</v>
       </c>
       <c r="H228" t="n">
-        <v>8.52</v>
+        <v>6.89</v>
       </c>
       <c r="I228" t="n">
         <v>-1.41</v>
@@ -12573,7 +12595,7 @@
         <v>-19.39</v>
       </c>
       <c r="M228" t="n">
-        <v>5.14</v>
+        <v>3.21</v>
       </c>
       <c r="N228" t="b">
         <v>0</v>
@@ -12611,7 +12633,7 @@
         <v>8.5</v>
       </c>
       <c r="H229" t="n">
-        <v>-37.67</v>
+        <v>-36.82</v>
       </c>
       <c r="I229" t="n">
         <v>-4.26</v>
@@ -12626,7 +12648,7 @@
         <v>-23.85</v>
       </c>
       <c r="M229" t="n">
-        <v>-41.05</v>
+        <v>-40.5</v>
       </c>
       <c r="N229" t="b">
         <v>0</v>
@@ -12664,7 +12686,7 @@
         <v>-15.2</v>
       </c>
       <c r="H230" t="n">
-        <v>-10.79</v>
+        <v>-16.72</v>
       </c>
       <c r="I230" t="n">
         <v>12.27</v>
@@ -12679,7 +12701,7 @@
         <v>-12.27</v>
       </c>
       <c r="M230" t="n">
-        <v>-14.17</v>
+        <v>-20.39</v>
       </c>
       <c r="N230" t="b">
         <v>0</v>
@@ -12717,7 +12739,7 @@
         <v>-33.1</v>
       </c>
       <c r="H231" t="n">
-        <v>-11.88</v>
+        <v>-6.05</v>
       </c>
       <c r="I231" t="n">
         <v>-13.13</v>
@@ -12732,7 +12754,7 @@
         <v>-21.04</v>
       </c>
       <c r="M231" t="n">
-        <v>-15.26</v>
+        <v>-9.720000000000001</v>
       </c>
       <c r="N231" t="b">
         <v>0</v>
@@ -12770,7 +12792,7 @@
         <v>11.8</v>
       </c>
       <c r="H232" t="n">
-        <v>5.32</v>
+        <v>-1.89</v>
       </c>
       <c r="I232" t="n">
         <v>-1.19</v>
@@ -12785,7 +12807,7 @@
         <v>-17.57</v>
       </c>
       <c r="M232" t="n">
-        <v>1.94</v>
+        <v>-5.56</v>
       </c>
       <c r="N232" t="b">
         <v>1</v>
@@ -12823,7 +12845,7 @@
         <v>27.5</v>
       </c>
       <c r="H233" t="n">
-        <v>8.4</v>
+        <v>4.86</v>
       </c>
       <c r="I233" t="n">
         <v>8.42</v>
@@ -12838,7 +12860,7 @@
         <v>-2.51</v>
       </c>
       <c r="M233" t="n">
-        <v>5.03</v>
+        <v>1.19</v>
       </c>
       <c r="N233" t="b">
         <v>1</v>
@@ -12876,7 +12898,7 @@
         <v>-22.4</v>
       </c>
       <c r="H234" t="n">
-        <v>-9.630000000000001</v>
+        <v>-7.4</v>
       </c>
       <c r="I234" t="n">
         <v>9.42</v>
@@ -12891,7 +12913,7 @@
         <v>-2.79</v>
       </c>
       <c r="M234" t="n">
-        <v>-13.01</v>
+        <v>-11.07</v>
       </c>
       <c r="N234" t="b">
         <v>1</v>
@@ -12929,7 +12951,7 @@
         <v>-14.7</v>
       </c>
       <c r="H235" t="n">
-        <v>-21.35</v>
+        <v>-18.07</v>
       </c>
       <c r="I235" t="n">
         <v>10.3</v>
@@ -12944,7 +12966,7 @@
         <v>-2.6</v>
       </c>
       <c r="M235" t="n">
-        <v>-24.73</v>
+        <v>-21.74</v>
       </c>
       <c r="N235" t="b">
         <v>1</v>
@@ -12986,7 +13008,7 @@
         <v>-9.300000000000001</v>
       </c>
       <c r="H236" t="n">
-        <v>-24.56</v>
+        <v>-21.88</v>
       </c>
       <c r="I236" t="n">
         <v>10.42</v>
@@ -13001,7 +13023,7 @@
         <v>-21.72</v>
       </c>
       <c r="M236" t="n">
-        <v>-27.94</v>
+        <v>-25.56</v>
       </c>
       <c r="N236" t="b">
         <v>1</v>
@@ -13039,7 +13061,7 @@
         <v>-13.5</v>
       </c>
       <c r="H237" t="n">
-        <v>119.1</v>
+        <v>132.44</v>
       </c>
       <c r="I237" t="n">
         <v>18.09</v>
@@ -13054,7 +13076,7 @@
         <v>-14.35</v>
       </c>
       <c r="M237" t="n">
-        <v>115.72</v>
+        <v>128.77</v>
       </c>
       <c r="N237" t="b">
         <v>0</v>
@@ -13092,7 +13114,7 @@
         <v>-27.5</v>
       </c>
       <c r="H238" t="n">
-        <v>-10</v>
+        <v>-3.2</v>
       </c>
       <c r="I238" t="n">
         <v>-29.95</v>
@@ -13107,7 +13129,7 @@
         <v>-35.86</v>
       </c>
       <c r="M238" t="n">
-        <v>-13.38</v>
+        <v>-6.87</v>
       </c>
       <c r="N238" t="b">
         <v>0</v>
@@ -13145,7 +13167,7 @@
         <v>11.9</v>
       </c>
       <c r="H239" t="n">
-        <v>-52.7</v>
+        <v>-52.22</v>
       </c>
       <c r="I239" t="n">
         <v>-3.02</v>
@@ -13160,7 +13182,7 @@
         <v>-24.96</v>
       </c>
       <c r="M239" t="n">
-        <v>-56.08</v>
+        <v>-55.9</v>
       </c>
       <c r="N239" t="b">
         <v>0</v>
@@ -13198,7 +13220,7 @@
         <v>5</v>
       </c>
       <c r="H240" t="n">
-        <v>-9.039999999999999</v>
+        <v>-8.880000000000001</v>
       </c>
       <c r="I240" t="n">
         <v>0.41</v>
@@ -13213,7 +13235,7 @@
         <v>-13.87</v>
       </c>
       <c r="M240" t="n">
-        <v>-12.42</v>
+        <v>-12.56</v>
       </c>
       <c r="N240" t="b">
         <v>0</v>
@@ -13251,7 +13273,7 @@
         <v>-35.9</v>
       </c>
       <c r="H241" t="n">
-        <v>6.7</v>
+        <v>9.9</v>
       </c>
       <c r="I241" t="n">
         <v>18.67</v>
@@ -13266,7 +13288,7 @@
         <v>-6.77</v>
       </c>
       <c r="M241" t="n">
-        <v>3.32</v>
+        <v>6.23</v>
       </c>
       <c r="N241" t="b">
         <v>0</v>
@@ -13304,7 +13326,7 @@
         <v>-25.2</v>
       </c>
       <c r="H242" t="n">
-        <v>-12.3</v>
+        <v>-7.08</v>
       </c>
       <c r="I242" t="n">
         <v>22.53</v>
@@ -13319,7 +13341,7 @@
         <v>-19.27</v>
       </c>
       <c r="M242" t="n">
-        <v>-15.68</v>
+        <v>-10.76</v>
       </c>
       <c r="N242" t="b">
         <v>1</v>
@@ -13357,7 +13379,7 @@
         <v>5.1</v>
       </c>
       <c r="H243" t="n">
-        <v>2.64</v>
+        <v>6.89</v>
       </c>
       <c r="I243" t="n">
         <v>8.77</v>
@@ -13372,7 +13394,7 @@
         <v>-3.54</v>
       </c>
       <c r="M243" t="n">
-        <v>-0.74</v>
+        <v>3.22</v>
       </c>
       <c r="N243" t="b">
         <v>1</v>
@@ -13410,7 +13432,7 @@
         <v>20.8</v>
       </c>
       <c r="H244" t="n">
-        <v>-26.45</v>
+        <v>-29.12</v>
       </c>
       <c r="I244" t="n">
         <v>-10.93</v>
@@ -13425,7 +13447,7 @@
         <v>-27.1</v>
       </c>
       <c r="M244" t="n">
-        <v>-29.83</v>
+        <v>-32.79</v>
       </c>
       <c r="N244" t="b">
         <v>0</v>
@@ -13463,7 +13485,7 @@
         <v>-27.7</v>
       </c>
       <c r="H245" t="n">
-        <v>2.98</v>
+        <v>9.48</v>
       </c>
       <c r="I245" t="n">
         <v>-10.22</v>
@@ -13478,7 +13500,7 @@
         <v>-17.14</v>
       </c>
       <c r="M245" t="n">
-        <v>-0.4</v>
+        <v>5.81</v>
       </c>
       <c r="N245" t="b">
         <v>0</v>
@@ -13516,7 +13538,7 @@
         <v>-24.7</v>
       </c>
       <c r="H246" t="n">
-        <v>-14.45</v>
+        <v>-10.9</v>
       </c>
       <c r="I246" t="n">
         <v>1.65</v>
@@ -13531,7 +13553,7 @@
         <v>-19.04</v>
       </c>
       <c r="M246" t="n">
-        <v>-17.83</v>
+        <v>-14.57</v>
       </c>
       <c r="N246" t="b">
         <v>0</v>
@@ -13569,7 +13591,7 @@
         <v>-34.9</v>
       </c>
       <c r="H247" t="n">
-        <v>-17.64</v>
+        <v>-13.84</v>
       </c>
       <c r="I247" t="n">
         <v>19.9</v>
@@ -13584,7 +13606,7 @@
         <v>-12.62</v>
       </c>
       <c r="M247" t="n">
-        <v>-21.02</v>
+        <v>-17.52</v>
       </c>
       <c r="N247" t="b">
         <v>0</v>
@@ -13622,7 +13644,7 @@
         <v>-29.5</v>
       </c>
       <c r="H248" t="n">
-        <v>-8.9</v>
+        <v>-7.28</v>
       </c>
       <c r="I248" t="n">
         <v>4.05</v>
@@ -13637,7 +13659,7 @@
         <v>-2.43</v>
       </c>
       <c r="M248" t="n">
-        <v>-12.28</v>
+        <v>-10.96</v>
       </c>
       <c r="N248" t="b">
         <v>0</v>
@@ -13675,7 +13697,7 @@
         <v>34.2</v>
       </c>
       <c r="H249" t="n">
-        <v>6.53</v>
+        <v>4.58</v>
       </c>
       <c r="I249" t="n">
         <v>8.15</v>
@@ -13690,7 +13712,7 @@
         <v>-7.63</v>
       </c>
       <c r="M249" t="n">
-        <v>3.15</v>
+        <v>0.91</v>
       </c>
       <c r="N249" t="b">
         <v>1</v>
@@ -13728,7 +13750,7 @@
         <v>42</v>
       </c>
       <c r="H250" t="n">
-        <v>-32.97</v>
+        <v>-32.82</v>
       </c>
       <c r="I250" t="n">
         <v>0.6</v>
@@ -13743,7 +13765,7 @@
         <v>-16.67</v>
       </c>
       <c r="M250" t="n">
-        <v>-36.35</v>
+        <v>-36.5</v>
       </c>
       <c r="N250" t="b">
         <v>1</v>
@@ -13785,7 +13807,7 @@
         <v>-0.4</v>
       </c>
       <c r="H251" t="n">
-        <v>-4.7</v>
+        <v>2.79</v>
       </c>
       <c r="I251" t="n">
         <v>4.83</v>
@@ -13800,7 +13822,7 @@
         <v>-10.75</v>
       </c>
       <c r="M251" t="n">
-        <v>-8.08</v>
+        <v>-0.88</v>
       </c>
       <c r="N251" t="b">
         <v>0</v>
@@ -13838,7 +13860,7 @@
         <v>64.59999999999999</v>
       </c>
       <c r="H252" t="n">
-        <v>12.65</v>
+        <v>11.34</v>
       </c>
       <c r="I252" t="n">
         <v>3.01</v>
@@ -13853,7 +13875,7 @@
         <v>-12</v>
       </c>
       <c r="M252" t="n">
-        <v>9.27</v>
+        <v>7.67</v>
       </c>
       <c r="N252" t="b">
         <v>0</v>
@@ -13891,7 +13913,7 @@
         <v>-25.3</v>
       </c>
       <c r="H253" t="n">
-        <v>43.41</v>
+        <v>51.86</v>
       </c>
       <c r="I253" t="n">
         <v>36.1</v>
@@ -13906,7 +13928,7 @@
         <v>-5.66</v>
       </c>
       <c r="M253" t="n">
-        <v>40.03</v>
+        <v>48.19</v>
       </c>
       <c r="N253" t="b">
         <v>1</v>
@@ -13944,7 +13966,7 @@
         <v>-7.7</v>
       </c>
       <c r="H254" t="n">
-        <v>-14.32</v>
+        <v>-13.61</v>
       </c>
       <c r="I254" t="n">
         <v>-6.47</v>
@@ -13959,7 +13981,7 @@
         <v>-23.05</v>
       </c>
       <c r="M254" t="n">
-        <v>-17.7</v>
+        <v>-17.28</v>
       </c>
       <c r="N254" t="b">
         <v>1</v>
@@ -13997,7 +14019,7 @@
         <v>-2.9</v>
       </c>
       <c r="H255" t="n">
-        <v>-15.07</v>
+        <v>-13.35</v>
       </c>
       <c r="I255" t="n">
         <v>-1.47</v>
@@ -14012,7 +14034,7 @@
         <v>-7.7</v>
       </c>
       <c r="M255" t="n">
-        <v>-18.45</v>
+        <v>-17.02</v>
       </c>
       <c r="N255" t="b">
         <v>0</v>
@@ -14050,7 +14072,7 @@
         <v>13.7</v>
       </c>
       <c r="H256" t="n">
-        <v>8.800000000000001</v>
+        <v>4.38</v>
       </c>
       <c r="I256" t="n">
         <v>2.74</v>
@@ -14065,7 +14087,7 @@
         <v>-24.02</v>
       </c>
       <c r="M256" t="n">
-        <v>5.42</v>
+        <v>0.71</v>
       </c>
       <c r="N256" t="b">
         <v>1</v>
@@ -14103,7 +14125,7 @@
         <v>21.8</v>
       </c>
       <c r="H257" t="n">
-        <v>-17.06</v>
+        <v>-18.32</v>
       </c>
       <c r="I257" t="n">
         <v>18.32</v>
@@ -14118,7 +14140,7 @@
         <v>-23.27</v>
       </c>
       <c r="M257" t="n">
-        <v>-20.43</v>
+        <v>-22</v>
       </c>
       <c r="N257" t="b">
         <v>1</v>
@@ -14156,7 +14178,7 @@
         <v>29.4</v>
       </c>
       <c r="H258" t="n">
-        <v>-18.26</v>
+        <v>-21.46</v>
       </c>
       <c r="I258" t="n">
         <v>-2.62</v>
@@ -14171,7 +14193,7 @@
         <v>-27.18</v>
       </c>
       <c r="M258" t="n">
-        <v>-21.64</v>
+        <v>-25.13</v>
       </c>
       <c r="N258" t="b">
         <v>1</v>
@@ -14209,7 +14231,7 @@
         <v>-3.7</v>
       </c>
       <c r="H259" t="n">
-        <v>-28.01</v>
+        <v>-27.92</v>
       </c>
       <c r="I259" t="n">
         <v>-8.07</v>
@@ -14224,7 +14246,7 @@
         <v>-22.12</v>
       </c>
       <c r="M259" t="n">
-        <v>-31.39</v>
+        <v>-31.59</v>
       </c>
       <c r="N259" t="b">
         <v>1</v>
@@ -14262,7 +14284,7 @@
         <v>21.3</v>
       </c>
       <c r="H260" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="I260" t="n">
         <v>0.23</v>
@@ -14277,7 +14299,7 @@
         <v>-0.85</v>
       </c>
       <c r="M260" t="n">
-        <v>-1.91</v>
+        <v>-2.22</v>
       </c>
       <c r="N260" t="b">
         <v>1</v>
@@ -14315,7 +14337,7 @@
         <v>-21.4</v>
       </c>
       <c r="H261" t="n">
-        <v>1.24</v>
+        <v>5.73</v>
       </c>
       <c r="I261" t="n">
         <v>4.55</v>
@@ -14330,7 +14352,7 @@
         <v>-6.39</v>
       </c>
       <c r="M261" t="n">
-        <v>-2.14</v>
+        <v>2.05</v>
       </c>
       <c r="N261" t="b">
         <v>1</v>
@@ -14368,7 +14390,7 @@
         <v>16.3</v>
       </c>
       <c r="H262" t="n">
-        <v>-7.27</v>
+        <v>-9.93</v>
       </c>
       <c r="I262" t="n">
         <v>-1</v>
@@ -14383,7 +14405,7 @@
         <v>-22.5</v>
       </c>
       <c r="M262" t="n">
-        <v>-10.65</v>
+        <v>-13.6</v>
       </c>
       <c r="N262" t="b">
         <v>1</v>
@@ -14421,7 +14443,7 @@
         <v>11.9</v>
       </c>
       <c r="H263" t="n">
-        <v>-6.84</v>
+        <v>-8.99</v>
       </c>
       <c r="I263" t="n">
         <v>7.74</v>
@@ -14436,7 +14458,7 @@
         <v>-9.43</v>
       </c>
       <c r="M263" t="n">
-        <v>-10.22</v>
+        <v>-12.66</v>
       </c>
       <c r="N263" t="b">
         <v>1</v>
@@ -14474,7 +14496,7 @@
         <v>19.4</v>
       </c>
       <c r="H264" t="n">
-        <v>1.85</v>
+        <v>0.95</v>
       </c>
       <c r="I264" t="n">
         <v>10.89</v>
@@ -14489,7 +14511,7 @@
         <v>-2.97</v>
       </c>
       <c r="M264" t="n">
-        <v>-1.53</v>
+        <v>-2.73</v>
       </c>
       <c r="N264" t="b">
         <v>0</v>
@@ -14527,7 +14549,7 @@
         <v>66.7</v>
       </c>
       <c r="H265" t="n">
-        <v>7.33</v>
+        <v>5.96</v>
       </c>
       <c r="I265" t="n">
         <v>4.84</v>
@@ -14542,7 +14564,7 @@
         <v>-11.7</v>
       </c>
       <c r="M265" t="n">
-        <v>3.95</v>
+        <v>2.29</v>
       </c>
       <c r="N265" t="b">
         <v>0</v>
@@ -14580,7 +14602,7 @@
         <v>3.7</v>
       </c>
       <c r="H266" t="n">
-        <v>17.74</v>
+        <v>22.65</v>
       </c>
       <c r="I266" t="n">
         <v>11.13</v>
@@ -14595,7 +14617,7 @@
         <v>-2.79</v>
       </c>
       <c r="M266" t="n">
-        <v>14.36</v>
+        <v>18.98</v>
       </c>
       <c r="N266" t="b">
         <v>0</v>
@@ -14633,7 +14655,7 @@
         <v>36.8</v>
       </c>
       <c r="H267" t="n">
-        <v>35.01</v>
+        <v>30.45</v>
       </c>
       <c r="I267" t="n">
         <v>15.47</v>
@@ -14648,7 +14670,7 @@
         <v>-0.96</v>
       </c>
       <c r="M267" t="n">
-        <v>31.63</v>
+        <v>26.78</v>
       </c>
       <c r="N267" t="b">
         <v>0</v>
@@ -14686,7 +14708,7 @@
         <v>0.2</v>
       </c>
       <c r="H268" t="n">
-        <v>13.15</v>
+        <v>11.85</v>
       </c>
       <c r="I268" t="n">
         <v>4.35</v>
@@ -14701,7 +14723,7 @@
         <v>-2.79</v>
       </c>
       <c r="M268" t="n">
-        <v>9.77</v>
+        <v>8.17</v>
       </c>
       <c r="N268" t="b">
         <v>1</v>
@@ -14739,7 +14761,7 @@
         <v>-31</v>
       </c>
       <c r="H269" t="n">
-        <v>-28.43</v>
+        <v>-24.49</v>
       </c>
       <c r="I269" t="n">
         <v>19.41</v>
@@ -14754,7 +14776,7 @@
         <v>-10.33</v>
       </c>
       <c r="M269" t="n">
-        <v>-31.81</v>
+        <v>-28.16</v>
       </c>
       <c r="N269" t="b">
         <v>0</v>
@@ -14796,7 +14818,7 @@
         <v>-2</v>
       </c>
       <c r="H270" t="n">
-        <v>-2.51</v>
+        <v>1.75</v>
       </c>
       <c r="I270" t="n">
         <v>14.61</v>
@@ -14811,7 +14833,7 @@
         <v>-3.45</v>
       </c>
       <c r="M270" t="n">
-        <v>-5.89</v>
+        <v>-1.93</v>
       </c>
       <c r="N270" t="b">
         <v>0</v>
@@ -14849,7 +14871,7 @@
         <v>12.2</v>
       </c>
       <c r="H271" t="n">
-        <v>-35.52</v>
+        <v>-32.2</v>
       </c>
       <c r="I271" t="n">
         <v>3.47</v>
@@ -14864,7 +14886,7 @@
         <v>-27.15</v>
       </c>
       <c r="M271" t="n">
-        <v>-38.9</v>
+        <v>-35.88</v>
       </c>
       <c r="N271" t="b">
         <v>0</v>
@@ -14902,7 +14924,7 @@
         <v>8.4</v>
       </c>
       <c r="H272" t="n">
-        <v>-37.45</v>
+        <v>-37.98</v>
       </c>
       <c r="I272" t="n">
         <v>-0.13</v>
@@ -14917,7 +14939,7 @@
         <v>-10.87</v>
       </c>
       <c r="M272" t="n">
-        <v>-40.83</v>
+        <v>-41.65</v>
       </c>
       <c r="N272" t="b">
         <v>1</v>
@@ -14955,7 +14977,7 @@
         <v>-21.7</v>
       </c>
       <c r="H273" t="n">
-        <v>-9.529999999999999</v>
+        <v>-8.77</v>
       </c>
       <c r="I273" t="n">
         <v>5.5</v>
@@ -14970,7 +14992,7 @@
         <v>-4.3</v>
       </c>
       <c r="M273" t="n">
-        <v>-12.91</v>
+        <v>-12.44</v>
       </c>
       <c r="N273" t="b">
         <v>0</v>
@@ -15008,7 +15030,7 @@
         <v>-7.3</v>
       </c>
       <c r="H274" t="n">
-        <v>-19.59</v>
+        <v>-18.72</v>
       </c>
       <c r="I274" t="n">
         <v>-4.12</v>
@@ -15023,7 +15045,7 @@
         <v>-15.02</v>
       </c>
       <c r="M274" t="n">
-        <v>-22.97</v>
+        <v>-22.39</v>
       </c>
       <c r="N274" t="b">
         <v>1</v>
@@ -15061,7 +15083,7 @@
         <v>-26.1</v>
       </c>
       <c r="H275" t="n">
-        <v>-29.59</v>
+        <v>-25.18</v>
       </c>
       <c r="I275" t="n">
         <v>5.05</v>
@@ -15076,7 +15098,7 @@
         <v>-9.27</v>
       </c>
       <c r="M275" t="n">
-        <v>-32.97</v>
+        <v>-28.86</v>
       </c>
       <c r="N275" t="b">
         <v>1</v>
@@ -15114,7 +15136,7 @@
         <v>-18.5</v>
       </c>
       <c r="H276" t="n">
-        <v>37.71</v>
+        <v>46.16</v>
       </c>
       <c r="I276" t="n">
         <v>16.22</v>
@@ -15129,7 +15151,7 @@
         <v>-9.960000000000001</v>
       </c>
       <c r="M276" t="n">
-        <v>34.33</v>
+        <v>42.48</v>
       </c>
       <c r="N276" t="b">
         <v>0</v>
@@ -15220,7 +15242,7 @@
         <v>26.1</v>
       </c>
       <c r="H278" t="n">
-        <v>-13.58</v>
+        <v>-16.97</v>
       </c>
       <c r="I278" t="n">
         <v>-0.51</v>
@@ -15235,7 +15257,7 @@
         <v>-16.45</v>
       </c>
       <c r="M278" t="n">
-        <v>-16.96</v>
+        <v>-20.64</v>
       </c>
       <c r="N278" t="b">
         <v>1</v>
@@ -15277,7 +15299,7 @@
         <v>-8.199999999999999</v>
       </c>
       <c r="H279" t="n">
-        <v>-20</v>
+        <v>-13.88</v>
       </c>
       <c r="I279" t="n">
         <v>17.48</v>
@@ -15292,7 +15314,7 @@
         <v>-10.68</v>
       </c>
       <c r="M279" t="n">
-        <v>-23.38</v>
+        <v>-17.55</v>
       </c>
       <c r="N279" t="b">
         <v>0</v>
@@ -15330,7 +15352,7 @@
         <v>17.9</v>
       </c>
       <c r="H280" t="n">
-        <v>-2.66</v>
+        <v>-4.92</v>
       </c>
       <c r="I280" t="n">
         <v>12.97</v>
@@ -15345,7 +15367,7 @@
         <v>-8.130000000000001</v>
       </c>
       <c r="M280" t="n">
-        <v>-6.04</v>
+        <v>-8.6</v>
       </c>
       <c r="N280" t="b">
         <v>1</v>
@@ -15383,7 +15405,7 @@
         <v>0.7</v>
       </c>
       <c r="H281" t="n">
-        <v>-22.68</v>
+        <v>-21.02</v>
       </c>
       <c r="I281" t="n">
         <v>14.96</v>
@@ -15398,7 +15420,7 @@
         <v>-8.039999999999999</v>
       </c>
       <c r="M281" t="n">
-        <v>-26.06</v>
+        <v>-24.69</v>
       </c>
       <c r="N281" t="b">
         <v>1</v>
@@ -15436,7 +15458,7 @@
         <v>61.6</v>
       </c>
       <c r="H282" t="n">
-        <v>4.19</v>
+        <v>3</v>
       </c>
       <c r="I282" t="n">
         <v>11.47</v>
@@ -15451,7 +15473,7 @@
         <v>-12.86</v>
       </c>
       <c r="M282" t="n">
-        <v>0.8100000000000001</v>
+        <v>-0.68</v>
       </c>
       <c r="N282" t="b">
         <v>0</v>
@@ -15489,7 +15511,7 @@
         <v>54.3</v>
       </c>
       <c r="H283" t="n">
-        <v>-23.01</v>
+        <v>-19.4</v>
       </c>
       <c r="I283" t="n">
         <v>-2.86</v>
@@ -15504,7 +15526,7 @@
         <v>-24.93</v>
       </c>
       <c r="M283" t="n">
-        <v>-26.39</v>
+        <v>-23.08</v>
       </c>
       <c r="N283" t="b">
         <v>0</v>
@@ -15542,7 +15564,7 @@
         <v>14.8</v>
       </c>
       <c r="H284" t="n">
-        <v>-6.63</v>
+        <v>-6.36</v>
       </c>
       <c r="I284" t="n">
         <v>0.35</v>
@@ -15557,7 +15579,7 @@
         <v>-3.68</v>
       </c>
       <c r="M284" t="n">
-        <v>-10.01</v>
+        <v>-10.03</v>
       </c>
       <c r="N284" t="b">
         <v>1</v>
@@ -15595,7 +15617,7 @@
         <v>-13.5</v>
       </c>
       <c r="H285" t="n">
-        <v>-21.45</v>
+        <v>-19.75</v>
       </c>
       <c r="I285" t="n">
         <v>-1.88</v>
@@ -15610,7 +15632,7 @@
         <v>-11.4</v>
       </c>
       <c r="M285" t="n">
-        <v>-24.83</v>
+        <v>-23.42</v>
       </c>
       <c r="N285" t="b">
         <v>0</v>
@@ -15648,7 +15670,7 @@
         <v>25.5</v>
       </c>
       <c r="H286" t="n">
-        <v>5.88</v>
+        <v>9.02</v>
       </c>
       <c r="I286" t="n">
         <v>-9.369999999999999</v>
@@ -15663,7 +15685,7 @@
         <v>-22.11</v>
       </c>
       <c r="M286" t="n">
-        <v>2.5</v>
+        <v>5.35</v>
       </c>
       <c r="N286" t="b">
         <v>1</v>
@@ -15705,7 +15727,7 @@
         <v>-7.5</v>
       </c>
       <c r="H287" t="n">
-        <v>-10.66</v>
+        <v>-8.609999999999999</v>
       </c>
       <c r="I287" t="n">
         <v>4.46</v>
@@ -15720,7 +15742,7 @@
         <v>-8.52</v>
       </c>
       <c r="M287" t="n">
-        <v>-14.04</v>
+        <v>-12.28</v>
       </c>
       <c r="N287" t="b">
         <v>1</v>
@@ -15758,7 +15780,7 @@
         <v>1.5</v>
       </c>
       <c r="H288" t="n">
-        <v>-1.1</v>
+        <v>2.21</v>
       </c>
       <c r="I288" t="n">
         <v>-7.31</v>
@@ -15773,7 +15795,7 @@
         <v>-18.58</v>
       </c>
       <c r="M288" t="n">
-        <v>-4.48</v>
+        <v>-1.46</v>
       </c>
       <c r="N288" t="b">
         <v>0</v>
@@ -15811,7 +15833,7 @@
         <v>-11</v>
       </c>
       <c r="H289" t="n">
-        <v>13.89</v>
+        <v>21.38</v>
       </c>
       <c r="I289" t="n">
         <v>10.7</v>
@@ -15826,7 +15848,7 @@
         <v>-9.43</v>
       </c>
       <c r="M289" t="n">
-        <v>10.51</v>
+        <v>17.71</v>
       </c>
       <c r="N289" t="b">
         <v>1</v>
@@ -15864,7 +15886,7 @@
         <v>-11.4</v>
       </c>
       <c r="H290" t="n">
-        <v>-18.91</v>
+        <v>-17.09</v>
       </c>
       <c r="I290" t="n">
         <v>4.36</v>
@@ -15879,7 +15901,7 @@
         <v>-11.36</v>
       </c>
       <c r="M290" t="n">
-        <v>-22.29</v>
+        <v>-20.76</v>
       </c>
       <c r="N290" t="b">
         <v>1</v>
@@ -15917,7 +15939,7 @@
         <v>2.1</v>
       </c>
       <c r="H291" t="n">
-        <v>64.86</v>
+        <v>74.43000000000001</v>
       </c>
       <c r="I291" t="n">
         <v>20.72</v>
@@ -15932,7 +15954,7 @@
         <v>-5.79</v>
       </c>
       <c r="M291" t="n">
-        <v>61.48</v>
+        <v>70.75</v>
       </c>
       <c r="N291" t="b">
         <v>0</v>
@@ -15970,7 +15992,7 @@
         <v>27.1</v>
       </c>
       <c r="H292" t="n">
-        <v>-12.48</v>
+        <v>-18.5</v>
       </c>
       <c r="I292" t="n">
         <v>5.02</v>
@@ -15985,7 +16007,7 @@
         <v>-14.35</v>
       </c>
       <c r="M292" t="n">
-        <v>-15.86</v>
+        <v>-22.17</v>
       </c>
       <c r="N292" t="b">
         <v>1</v>
@@ -16023,7 +16045,7 @@
         <v>-21.6</v>
       </c>
       <c r="H293" t="n">
-        <v>-17.64</v>
+        <v>-17.47</v>
       </c>
       <c r="I293" t="n">
         <v>1.22</v>
@@ -16038,7 +16060,7 @@
         <v>-6.54</v>
       </c>
       <c r="M293" t="n">
-        <v>-21.02</v>
+        <v>-21.14</v>
       </c>
       <c r="N293" t="b">
         <v>0</v>
@@ -16080,7 +16102,7 @@
         <v>-2.2</v>
       </c>
       <c r="H294" t="n">
-        <v>-1.69</v>
+        <v>1.14</v>
       </c>
       <c r="I294" t="n">
         <v>-9.050000000000001</v>
@@ -16095,7 +16117,7 @@
         <v>-18.61</v>
       </c>
       <c r="M294" t="n">
-        <v>-5.07</v>
+        <v>-2.53</v>
       </c>
       <c r="N294" t="b">
         <v>0</v>
@@ -16133,7 +16155,7 @@
         <v>0.7</v>
       </c>
       <c r="H295" t="n">
-        <v>-1.65</v>
+        <v>6.16</v>
       </c>
       <c r="I295" t="n">
         <v>11.4</v>
@@ -16148,7 +16170,7 @@
         <v>-7.28</v>
       </c>
       <c r="M295" t="n">
-        <v>-5.03</v>
+        <v>2.49</v>
       </c>
       <c r="N295" t="b">
         <v>0</v>
@@ -16186,7 +16208,7 @@
         <v>-31.7</v>
       </c>
       <c r="H296" t="n">
-        <v>21.54</v>
+        <v>24.8</v>
       </c>
       <c r="I296" t="n">
         <v>17.04</v>
@@ -16201,7 +16223,7 @@
         <v>-4.05</v>
       </c>
       <c r="M296" t="n">
-        <v>18.17</v>
+        <v>21.12</v>
       </c>
       <c r="N296" t="b">
         <v>0</v>
@@ -16239,7 +16261,7 @@
         <v>32.2</v>
       </c>
       <c r="H297" t="n">
-        <v>10.76</v>
+        <v>7.39</v>
       </c>
       <c r="I297" t="n">
         <v>6.49</v>
@@ -16254,7 +16276,7 @@
         <v>-3.92</v>
       </c>
       <c r="M297" t="n">
-        <v>7.38</v>
+        <v>3.72</v>
       </c>
       <c r="N297" t="b">
         <v>1</v>
@@ -16292,7 +16314,7 @@
         <v>3.2</v>
       </c>
       <c r="H298" t="n">
-        <v>-24.39</v>
+        <v>-27.43</v>
       </c>
       <c r="I298" t="n">
         <v>-10.41</v>
@@ -16307,7 +16329,7 @@
         <v>-23.7</v>
       </c>
       <c r="M298" t="n">
-        <v>-27.77</v>
+        <v>-31.1</v>
       </c>
       <c r="N298" t="b">
         <v>1</v>
@@ -16345,7 +16367,7 @@
         <v>7.3</v>
       </c>
       <c r="H299" t="n">
-        <v>0.5600000000000001</v>
+        <v>3.02</v>
       </c>
       <c r="I299" t="n">
         <v>-0.57</v>
@@ -16360,7 +16382,7 @@
         <v>-5.89</v>
       </c>
       <c r="M299" t="n">
-        <v>-2.82</v>
+        <v>-0.65</v>
       </c>
       <c r="N299" t="b">
         <v>1</v>
@@ -16398,7 +16420,7 @@
         <v>24.5</v>
       </c>
       <c r="H300" t="n">
-        <v>10.25</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="I300" t="n">
         <v>17.24</v>
@@ -16413,7 +16435,7 @@
         <v>-0.47</v>
       </c>
       <c r="M300" t="n">
-        <v>6.88</v>
+        <v>5.54</v>
       </c>
       <c r="N300" t="b">
         <v>0</v>
@@ -16451,7 +16473,7 @@
         <v>-0.3</v>
       </c>
       <c r="H301" t="n">
-        <v>-10.02</v>
+        <v>-13.02</v>
       </c>
       <c r="I301" t="n">
         <v>17.76</v>
@@ -16466,7 +16488,7 @@
         <v>-14.18</v>
       </c>
       <c r="M301" t="n">
-        <v>-13.4</v>
+        <v>-16.69</v>
       </c>
       <c r="N301" t="b">
         <v>1</v>
@@ -16504,7 +16526,7 @@
         <v>4</v>
       </c>
       <c r="H302" t="n">
-        <v>58.47</v>
+        <v>66.76000000000001</v>
       </c>
       <c r="I302" t="n">
         <v>8.75</v>
@@ -16519,7 +16541,7 @@
         <v>-11.02</v>
       </c>
       <c r="M302" t="n">
-        <v>55.09</v>
+        <v>63.09</v>
       </c>
       <c r="N302" t="b">
         <v>0</v>
@@ -16557,7 +16579,7 @@
         <v>-6.8</v>
       </c>
       <c r="H303" t="n">
-        <v>24.66</v>
+        <v>28.24</v>
       </c>
       <c r="I303" t="n">
         <v>8.279999999999999</v>
@@ -16572,7 +16594,7 @@
         <v>-6.78</v>
       </c>
       <c r="M303" t="n">
-        <v>21.28</v>
+        <v>24.57</v>
       </c>
       <c r="N303" t="b">
         <v>1</v>
@@ -16610,7 +16632,7 @@
         <v>-42</v>
       </c>
       <c r="H304" t="n">
-        <v>41.39</v>
+        <v>49.33</v>
       </c>
       <c r="I304" t="n">
         <v>-3.61</v>
@@ -16625,7 +16647,7 @@
         <v>-11.94</v>
       </c>
       <c r="M304" t="n">
-        <v>38.01</v>
+        <v>45.66</v>
       </c>
       <c r="N304" t="b">
         <v>0</v>
@@ -16663,7 +16685,7 @@
         <v>14.6</v>
       </c>
       <c r="H305" t="n">
-        <v>3.47</v>
+        <v>0.6</v>
       </c>
       <c r="I305" t="n">
         <v>8.539999999999999</v>
@@ -16678,7 +16700,7 @@
         <v>-13.21</v>
       </c>
       <c r="M305" t="n">
-        <v>0.09</v>
+        <v>-3.07</v>
       </c>
       <c r="N305" t="b">
         <v>0</v>
@@ -16716,7 +16738,7 @@
         <v>34.6</v>
       </c>
       <c r="H306" t="n">
-        <v>-0.8</v>
+        <v>-0.02</v>
       </c>
       <c r="I306" t="n">
         <v>5.7</v>
@@ -16731,7 +16753,7 @@
         <v>-7.7</v>
       </c>
       <c r="M306" t="n">
-        <v>-4.18</v>
+        <v>-3.69</v>
       </c>
       <c r="N306" t="b">
         <v>1</v>
@@ -16769,7 +16791,7 @@
         <v>-37.2</v>
       </c>
       <c r="H307" t="n">
-        <v>17.65</v>
+        <v>25.18</v>
       </c>
       <c r="I307" t="n">
         <v>21.67</v>
@@ -16784,7 +16806,7 @@
         <v>-6.64</v>
       </c>
       <c r="M307" t="n">
-        <v>14.27</v>
+        <v>21.5</v>
       </c>
       <c r="N307" t="b">
         <v>0</v>
@@ -16822,7 +16844,7 @@
         <v>-31.2</v>
       </c>
       <c r="H308" t="n">
-        <v>-28.52</v>
+        <v>-26.67</v>
       </c>
       <c r="I308" t="n">
         <v>1.03</v>
@@ -16837,7 +16859,7 @@
         <v>-13.65</v>
       </c>
       <c r="M308" t="n">
-        <v>-31.9</v>
+        <v>-30.35</v>
       </c>
       <c r="N308" t="b">
         <v>0</v>
@@ -16875,7 +16897,7 @@
         <v>10.4</v>
       </c>
       <c r="H309" t="n">
-        <v>26.13</v>
+        <v>26.36</v>
       </c>
       <c r="I309" t="n">
         <v>11.05</v>
@@ -16890,7 +16912,7 @@
         <v>-5.54</v>
       </c>
       <c r="M309" t="n">
-        <v>22.75</v>
+        <v>22.69</v>
       </c>
       <c r="N309" t="b">
         <v>1</v>
@@ -16928,7 +16950,7 @@
         <v>-14.7</v>
       </c>
       <c r="H310" t="n">
-        <v>6.87</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="I310" t="n">
         <v>12.94</v>
@@ -16943,7 +16965,7 @@
         <v>-2.34</v>
       </c>
       <c r="M310" t="n">
-        <v>3.49</v>
+        <v>5.97</v>
       </c>
       <c r="N310" t="b">
         <v>0</v>
@@ -16981,7 +17003,7 @@
         <v>-21.5</v>
       </c>
       <c r="H311" t="n">
-        <v>-4.36</v>
+        <v>-2.16</v>
       </c>
       <c r="I311" t="n">
         <v>10.65</v>
@@ -16996,7 +17018,7 @@
         <v>-6.89</v>
       </c>
       <c r="M311" t="n">
-        <v>-7.74</v>
+        <v>-5.83</v>
       </c>
       <c r="N311" t="b">
         <v>1</v>
@@ -17034,7 +17056,7 @@
         <v>20.2</v>
       </c>
       <c r="H312" t="n">
-        <v>-15.61</v>
+        <v>-17.11</v>
       </c>
       <c r="I312" t="n">
         <v>-1.23</v>
@@ -17049,7 +17071,7 @@
         <v>-12.56</v>
       </c>
       <c r="M312" t="n">
-        <v>-18.99</v>
+        <v>-20.78</v>
       </c>
       <c r="N312" t="b">
         <v>0</v>
@@ -17087,7 +17109,7 @@
         <v>3.5</v>
       </c>
       <c r="H313" t="n">
-        <v>52.65</v>
+        <v>56.44</v>
       </c>
       <c r="I313" t="n">
         <v>33.01</v>
@@ -17102,7 +17124,7 @@
         <v>-0.92</v>
       </c>
       <c r="M313" t="n">
-        <v>49.27</v>
+        <v>52.77</v>
       </c>
       <c r="N313" t="b">
         <v>1</v>
@@ -17140,7 +17162,7 @@
         <v>14</v>
       </c>
       <c r="H314" t="n">
-        <v>36.14</v>
+        <v>35.74</v>
       </c>
       <c r="I314" t="n">
         <v>2.89</v>
@@ -17155,7 +17177,7 @@
         <v>-1.94</v>
       </c>
       <c r="M314" t="n">
-        <v>32.76</v>
+        <v>32.06</v>
       </c>
       <c r="N314" t="b">
         <v>0</v>
@@ -17193,7 +17215,7 @@
         <v>19.8</v>
       </c>
       <c r="H315" t="n">
-        <v>9.77</v>
+        <v>5</v>
       </c>
       <c r="I315" t="n">
         <v>4.74</v>
@@ -17208,7 +17230,7 @@
         <v>-9.9</v>
       </c>
       <c r="M315" t="n">
-        <v>6.39</v>
+        <v>1.32</v>
       </c>
       <c r="N315" t="b">
         <v>1</v>
@@ -17250,7 +17272,7 @@
         <v>-7.4</v>
       </c>
       <c r="H316" t="n">
-        <v>11.55</v>
+        <v>15.79</v>
       </c>
       <c r="I316" t="n">
         <v>-3.85</v>
@@ -17265,7 +17287,7 @@
         <v>-21.11</v>
       </c>
       <c r="M316" t="n">
-        <v>8.17</v>
+        <v>12.12</v>
       </c>
       <c r="N316" t="b">
         <v>0</v>
@@ -17303,7 +17325,7 @@
         <v>-10.8</v>
       </c>
       <c r="H317" t="n">
-        <v>3.08</v>
+        <v>4.48</v>
       </c>
       <c r="I317" t="n">
         <v>1.78</v>
@@ -17318,7 +17340,7 @@
         <v>-7.51</v>
       </c>
       <c r="M317" t="n">
-        <v>-0.3</v>
+        <v>0.8</v>
       </c>
       <c r="N317" t="b">
         <v>0</v>
@@ -17356,7 +17378,7 @@
         <v>-24</v>
       </c>
       <c r="H318" t="n">
-        <v>49.95</v>
+        <v>49.71</v>
       </c>
       <c r="I318" t="n">
         <v>10.85</v>
@@ -17371,7 +17393,7 @@
         <v>-5.43</v>
       </c>
       <c r="M318" t="n">
-        <v>46.57</v>
+        <v>46.03</v>
       </c>
       <c r="N318" t="b">
         <v>0</v>
@@ -17409,7 +17431,7 @@
         <v>-28.3</v>
       </c>
       <c r="H319" t="n">
-        <v>-28.83</v>
+        <v>-27.24</v>
       </c>
       <c r="I319" t="n">
         <v>-8.949999999999999</v>
@@ -17424,7 +17446,7 @@
         <v>-13.18</v>
       </c>
       <c r="M319" t="n">
-        <v>-32.2</v>
+        <v>-30.91</v>
       </c>
       <c r="N319" t="b">
         <v>0</v>
@@ -17462,7 +17484,7 @@
         <v>-30.5</v>
       </c>
       <c r="H320" t="n">
-        <v>-5.3</v>
+        <v>-1.85</v>
       </c>
       <c r="I320" t="n">
         <v>2.96</v>
@@ -17477,7 +17499,7 @@
         <v>-17.88</v>
       </c>
       <c r="M320" t="n">
-        <v>-8.68</v>
+        <v>-5.52</v>
       </c>
       <c r="N320" t="b">
         <v>1</v>
@@ -17515,7 +17537,7 @@
         <v>-6</v>
       </c>
       <c r="H321" t="n">
-        <v>-23.55</v>
+        <v>-25.06</v>
       </c>
       <c r="I321" t="n">
         <v>3.31</v>
@@ -17530,7 +17552,7 @@
         <v>-21.48</v>
       </c>
       <c r="M321" t="n">
-        <v>-26.93</v>
+        <v>-28.73</v>
       </c>
       <c r="N321" t="b">
         <v>1</v>
@@ -17568,7 +17590,7 @@
         <v>-42.2</v>
       </c>
       <c r="H322" t="n">
-        <v>-14.92</v>
+        <v>-13.07</v>
       </c>
       <c r="I322" t="n">
         <v>19.24</v>
@@ -17583,7 +17605,7 @@
         <v>-0.93</v>
       </c>
       <c r="M322" t="n">
-        <v>-18.3</v>
+        <v>-16.75</v>
       </c>
       <c r="N322" t="b">
         <v>0</v>
@@ -17621,7 +17643,7 @@
         <v>-34.6</v>
       </c>
       <c r="H323" t="n">
-        <v>-0.76</v>
+        <v>11.03</v>
       </c>
       <c r="I323" t="n">
         <v>23.65</v>
@@ -17636,7 +17658,7 @@
         <v>-3.83</v>
       </c>
       <c r="M323" t="n">
-        <v>-4.14</v>
+        <v>7.35</v>
       </c>
       <c r="N323" t="b">
         <v>1</v>
@@ -17674,7 +17696,7 @@
         <v>-48.1</v>
       </c>
       <c r="H324" t="n">
-        <v>-31.51</v>
+        <v>-29.22</v>
       </c>
       <c r="I324" t="n">
         <v>2.19</v>
@@ -17689,7 +17711,7 @@
         <v>-13.66</v>
       </c>
       <c r="M324" t="n">
-        <v>-34.89</v>
+        <v>-32.9</v>
       </c>
       <c r="N324" t="b">
         <v>0</v>
@@ -17727,7 +17749,7 @@
         <v>-16.2</v>
       </c>
       <c r="H325" t="n">
-        <v>2.72</v>
+        <v>2.91</v>
       </c>
       <c r="I325" t="n">
         <v>25.77</v>
@@ -17742,7 +17764,7 @@
         <v>-1.7</v>
       </c>
       <c r="M325" t="n">
-        <v>-0.66</v>
+        <v>-0.77</v>
       </c>
       <c r="N325" t="b">
         <v>1</v>
@@ -17780,7 +17802,7 @@
         <v>-24.9</v>
       </c>
       <c r="H326" t="n">
-        <v>2.46</v>
+        <v>5.4</v>
       </c>
       <c r="I326" t="n">
         <v>10.88</v>
@@ -17795,7 +17817,7 @@
         <v>-4.1</v>
       </c>
       <c r="M326" t="n">
-        <v>-0.92</v>
+        <v>1.73</v>
       </c>
       <c r="N326" t="b">
         <v>1</v>
@@ -17837,7 +17859,7 @@
         <v>-8.1</v>
       </c>
       <c r="H327" t="n">
-        <v>16.36</v>
+        <v>25.19</v>
       </c>
       <c r="I327" t="n">
         <v>14.27</v>
@@ -17852,7 +17874,7 @@
         <v>-10.92</v>
       </c>
       <c r="M327" t="n">
-        <v>12.98</v>
+        <v>21.52</v>
       </c>
       <c r="N327" t="b">
         <v>1</v>
@@ -17890,7 +17912,7 @@
         <v>-10.2</v>
       </c>
       <c r="H328" t="n">
-        <v>-16.2</v>
+        <v>-13.28</v>
       </c>
       <c r="I328" t="n">
         <v>15.03</v>
@@ -17905,7 +17927,7 @@
         <v>-1.61</v>
       </c>
       <c r="M328" t="n">
-        <v>-19.58</v>
+        <v>-16.96</v>
       </c>
       <c r="N328" t="b">
         <v>1</v>
@@ -17943,7 +17965,7 @@
         <v>68.90000000000001</v>
       </c>
       <c r="H329" t="n">
-        <v>38.86</v>
+        <v>34.95</v>
       </c>
       <c r="I329" t="n">
         <v>1.84</v>
@@ -17958,7 +17980,7 @@
         <v>-10.43</v>
       </c>
       <c r="M329" t="n">
-        <v>35.48</v>
+        <v>31.28</v>
       </c>
       <c r="N329" t="b">
         <v>1</v>
@@ -17996,7 +18018,7 @@
         <v>-40.8</v>
       </c>
       <c r="H330" t="n">
-        <v>-24.63</v>
+        <v>-23.51</v>
       </c>
       <c r="I330" t="n">
         <v>21.71</v>
@@ -18011,7 +18033,7 @@
         <v>-3.3</v>
       </c>
       <c r="M330" t="n">
-        <v>-28.01</v>
+        <v>-27.19</v>
       </c>
       <c r="N330" t="b">
         <v>1</v>
@@ -18049,7 +18071,7 @@
         <v>-10.1</v>
       </c>
       <c r="H331" t="n">
-        <v>-17.19</v>
+        <v>-11.08</v>
       </c>
       <c r="I331" t="n">
         <v>1.83</v>
@@ -18064,7 +18086,7 @@
         <v>-3.45</v>
       </c>
       <c r="M331" t="n">
-        <v>-20.57</v>
+        <v>-14.75</v>
       </c>
       <c r="N331" t="b">
         <v>0</v>
@@ -18102,7 +18124,7 @@
         <v>40.7</v>
       </c>
       <c r="H332" t="n">
-        <v>34.02</v>
+        <v>35.15</v>
       </c>
       <c r="I332" t="n">
         <v>-4.08</v>
@@ -18117,7 +18139,7 @@
         <v>-11.2</v>
       </c>
       <c r="M332" t="n">
-        <v>30.64</v>
+        <v>31.47</v>
       </c>
       <c r="N332" t="b">
         <v>1</v>
@@ -18155,7 +18177,7 @@
         <v>25.7</v>
       </c>
       <c r="H333" t="n">
-        <v>-10.75</v>
+        <v>-13.25</v>
       </c>
       <c r="I333" t="n">
         <v>11.3</v>
@@ -18170,7 +18192,7 @@
         <v>-11.03</v>
       </c>
       <c r="M333" t="n">
-        <v>-14.13</v>
+        <v>-16.92</v>
       </c>
       <c r="N333" t="b">
         <v>1</v>
@@ -18208,7 +18230,7 @@
         <v>2.3</v>
       </c>
       <c r="H334" t="n">
-        <v>-3.56</v>
+        <v>-2.01</v>
       </c>
       <c r="I334" t="n">
         <v>-0.95</v>
@@ -18223,7 +18245,7 @@
         <v>-7.81</v>
       </c>
       <c r="M334" t="n">
-        <v>-6.94</v>
+        <v>-5.68</v>
       </c>
       <c r="N334" t="b">
         <v>0</v>
@@ -18355,16 +18377,16 @@
         <v>51.4</v>
       </c>
       <c r="H2" t="n">
-        <v>-2.18</v>
+        <v>-1.95</v>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="n">
-        <v>-2.32</v>
+        <v>-4.91</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.19</v>
+        <v>-1.24</v>
       </c>
       <c r="N2" t="b">
         <v>1</v>
@@ -18402,7 +18424,7 @@
         <v>-16.6</v>
       </c>
       <c r="H3" t="n">
-        <v>3.76</v>
+        <v>3.33</v>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
@@ -18411,7 +18433,7 @@
         <v>-1.04</v>
       </c>
       <c r="M3" t="n">
-        <v>4.55</v>
+        <v>3.84</v>
       </c>
       <c r="N3" t="b">
         <v>1</v>
@@ -18438,7 +18460,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Extended</t>
         </is>
       </c>
       <c r="E4" t="inlineStr"/>
@@ -18449,7 +18471,7 @@
         <v>-5</v>
       </c>
       <c r="H4" t="n">
-        <v>4.03</v>
+        <v>6.54</v>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
@@ -18458,7 +18480,7 @@
         <v>-1.75</v>
       </c>
       <c r="M4" t="n">
-        <v>4.82</v>
+        <v>7.05</v>
       </c>
       <c r="N4" t="b">
         <v>1</v>
@@ -18485,7 +18507,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Extended</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
@@ -18496,7 +18518,7 @@
         <v>12.5</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.3</v>
+        <v>7.42</v>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
@@ -18505,7 +18527,7 @@
         <v>-2.59</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.51</v>
+        <v>7.93</v>
       </c>
       <c r="N5" t="b">
         <v>1</v>
@@ -18543,7 +18565,7 @@
         <v>-17.3</v>
       </c>
       <c r="H6" t="n">
-        <v>-4.51</v>
+        <v>0.87</v>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
@@ -18552,7 +18574,7 @@
         <v>-6.51</v>
       </c>
       <c r="M6" t="n">
-        <v>-3.41</v>
+        <v>1.69</v>
       </c>
       <c r="N6" t="b">
         <v>1</v>
@@ -18590,7 +18612,7 @@
         <v>-21.8</v>
       </c>
       <c r="H7" t="n">
-        <v>-3.37</v>
+        <v>0.36</v>
       </c>
       <c r="I7" t="n">
         <v>-3.37</v>
@@ -18601,7 +18623,7 @@
         <v>-5.33</v>
       </c>
       <c r="M7" t="n">
-        <v>-3.78</v>
+        <v>-0.33</v>
       </c>
       <c r="N7" t="b">
         <v>1</v>
@@ -18639,7 +18661,7 @@
         <v>-16.7</v>
       </c>
       <c r="H8" t="n">
-        <v>24.91</v>
+        <v>29.93</v>
       </c>
       <c r="I8" t="n">
         <v>26.03</v>
@@ -18650,7 +18672,7 @@
         <v>-6.98</v>
       </c>
       <c r="M8" t="n">
-        <v>24.55</v>
+        <v>29.29</v>
       </c>
       <c r="N8" t="b">
         <v>1</v>
@@ -18688,7 +18710,7 @@
         <v>-11.5</v>
       </c>
       <c r="H9" t="n">
-        <v>8.720000000000001</v>
+        <v>14.06</v>
       </c>
       <c r="I9" t="n">
         <v>7.47</v>
@@ -18699,7 +18721,7 @@
         <v>-0.99</v>
       </c>
       <c r="M9" t="n">
-        <v>8.359999999999999</v>
+        <v>13.41</v>
       </c>
       <c r="N9" t="b">
         <v>1</v>
@@ -18737,7 +18759,7 @@
         <v>0.1</v>
       </c>
       <c r="H10" t="n">
-        <v>11.28</v>
+        <v>14.47</v>
       </c>
       <c r="I10" t="n">
         <v>6.41</v>
@@ -18748,7 +18770,7 @@
         <v>-2.51</v>
       </c>
       <c r="M10" t="n">
-        <v>11.18</v>
+        <v>14.08</v>
       </c>
       <c r="N10" t="b">
         <v>1</v>
@@ -18786,7 +18808,7 @@
         <v>-31.6</v>
       </c>
       <c r="H11" t="n">
-        <v>-5.47</v>
+        <v>-3.91</v>
       </c>
       <c r="I11" t="n">
         <v>-2.12</v>
@@ -18797,7 +18819,7 @@
         <v>-8.140000000000001</v>
       </c>
       <c r="M11" t="n">
-        <v>-5.58</v>
+        <v>-4.3</v>
       </c>
       <c r="N11" t="b">
         <v>1</v>
@@ -18835,7 +18857,7 @@
         <v>-2.7</v>
       </c>
       <c r="H12" t="n">
-        <v>-10.61</v>
+        <v>-8.66</v>
       </c>
       <c r="I12" t="n">
         <v>-3.77</v>
@@ -18846,7 +18868,7 @@
         <v>-12.44</v>
       </c>
       <c r="M12" t="n">
-        <v>-10.04</v>
+        <v>-8.369999999999999</v>
       </c>
       <c r="N12" t="b">
         <v>1</v>
@@ -18884,7 +18906,7 @@
         <v>26.9</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.39</v>
+        <v>1.91</v>
       </c>
       <c r="I13" t="n">
         <v>-3.24</v>
@@ -18895,7 +18917,7 @@
         <v>-12.88</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.82</v>
+        <v>2.2</v>
       </c>
       <c r="N13" t="b">
         <v>1</v>
@@ -18933,7 +18955,7 @@
         <v>-18.1</v>
       </c>
       <c r="H14" t="n">
-        <v>10.59</v>
+        <v>13.98</v>
       </c>
       <c r="I14" t="n">
         <v>4.46</v>
@@ -18944,7 +18966,7 @@
         <v>-2.69</v>
       </c>
       <c r="M14" t="n">
-        <v>10.16</v>
+        <v>13.26</v>
       </c>
       <c r="N14" t="b">
         <v>1</v>
@@ -18982,7 +19004,7 @@
         <v>-21.5</v>
       </c>
       <c r="H15" t="n">
-        <v>-4.27</v>
+        <v>2.32</v>
       </c>
       <c r="I15" t="n">
         <v>-1.68</v>
@@ -18993,7 +19015,7 @@
         <v>-8.130000000000001</v>
       </c>
       <c r="M15" t="n">
-        <v>-4.71</v>
+        <v>1.6</v>
       </c>
       <c r="N15" t="b">
         <v>1</v>
@@ -19020,7 +19042,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Retired</t>
         </is>
       </c>
       <c r="E16" t="inlineStr"/>
@@ -19031,7 +19053,7 @@
         <v>41.6</v>
       </c>
       <c r="H16" t="n">
-        <v>3.84</v>
+        <v>5.6</v>
       </c>
       <c r="I16" t="n">
         <v>3.43</v>
@@ -19042,7 +19064,7 @@
         <v>-4.38</v>
       </c>
       <c r="M16" t="n">
-        <v>2.75</v>
+        <v>4.23</v>
       </c>
       <c r="N16" t="b">
         <v>1</v>
@@ -19069,7 +19091,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Retired</t>
         </is>
       </c>
       <c r="E17" t="inlineStr"/>
@@ -19080,7 +19102,7 @@
         <v>32.1</v>
       </c>
       <c r="H17" t="n">
-        <v>4.05</v>
+        <v>7.32</v>
       </c>
       <c r="I17" t="n">
         <v>-3.47</v>
@@ -19091,7 +19113,7 @@
         <v>-6.94</v>
       </c>
       <c r="M17" t="n">
-        <v>2.96</v>
+        <v>5.94</v>
       </c>
       <c r="N17" t="b">
         <v>1</v>
@@ -19118,7 +19140,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Retired</t>
         </is>
       </c>
       <c r="E18" t="inlineStr"/>
@@ -19129,7 +19151,7 @@
         <v>-14.4</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.72</v>
+        <v>1.16</v>
       </c>
       <c r="I18" t="n">
         <v>-2.38</v>
@@ -19140,7 +19162,7 @@
         <v>-6.46</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.81</v>
+        <v>-0.21</v>
       </c>
       <c r="N18" t="b">
         <v>1</v>
@@ -19167,7 +19189,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Retired</t>
         </is>
       </c>
       <c r="E19" t="inlineStr"/>
@@ -19178,7 +19200,7 @@
         <v>-10</v>
       </c>
       <c r="H19" t="n">
-        <v>-12.1</v>
+        <v>-8.07</v>
       </c>
       <c r="I19" t="n">
         <v>-3.29</v>
@@ -19189,7 +19211,7 @@
         <v>-14.66</v>
       </c>
       <c r="M19" t="n">
-        <v>-13.19</v>
+        <v>-9.44</v>
       </c>
       <c r="N19" t="b">
         <v>1</v>
@@ -19216,7 +19238,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Extended</t>
+          <t>Retired</t>
         </is>
       </c>
       <c r="E20" t="inlineStr"/>
@@ -19227,7 +19249,7 @@
         <v>6.4</v>
       </c>
       <c r="H20" t="n">
-        <v>6.05</v>
+        <v>10.98</v>
       </c>
       <c r="I20" t="n">
         <v>1.48</v>
@@ -19238,7 +19260,7 @@
         <v>-3.35</v>
       </c>
       <c r="M20" t="n">
-        <v>4.96</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="N20" t="b">
         <v>1</v>
@@ -19276,7 +19298,7 @@
         <v>20.2</v>
       </c>
       <c r="H21" t="n">
-        <v>1.8</v>
+        <v>1.53</v>
       </c>
       <c r="I21" t="n">
         <v>3.45</v>
@@ -19289,7 +19311,7 @@
         <v>-1.07</v>
       </c>
       <c r="M21" t="n">
-        <v>0.3</v>
+        <v>-0.26</v>
       </c>
       <c r="N21" t="b">
         <v>1</v>
@@ -19327,7 +19349,7 @@
         <v>43.7</v>
       </c>
       <c r="H22" t="n">
-        <v>8.029999999999999</v>
+        <v>12.36</v>
       </c>
       <c r="I22" t="n">
         <v>3.16</v>
@@ -19340,7 +19362,7 @@
         <v>-2.44</v>
       </c>
       <c r="M22" t="n">
-        <v>6.53</v>
+        <v>10.58</v>
       </c>
       <c r="N22" t="b">
         <v>1</v>
@@ -19378,7 +19400,7 @@
         <v>1.9</v>
       </c>
       <c r="H23" t="n">
-        <v>-7.87</v>
+        <v>-4.5</v>
       </c>
       <c r="I23" t="n">
         <v>-10.64</v>
@@ -19391,7 +19413,7 @@
         <v>-14.75</v>
       </c>
       <c r="M23" t="n">
-        <v>-9.369999999999999</v>
+        <v>-6.29</v>
       </c>
       <c r="N23" t="b">
         <v>1</v>
@@ -19429,7 +19451,7 @@
         <v>37.5</v>
       </c>
       <c r="H24" t="n">
-        <v>8.529999999999999</v>
+        <v>10.05</v>
       </c>
       <c r="I24" t="n">
         <v>5.86</v>
@@ -19442,7 +19464,7 @@
         <v>-3.95</v>
       </c>
       <c r="M24" t="n">
-        <v>6.88</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="N24" t="b">
         <v>1</v>
@@ -19480,7 +19502,7 @@
         <v>40.2</v>
       </c>
       <c r="H25" t="n">
-        <v>13.21</v>
+        <v>13.38</v>
       </c>
       <c r="I25" t="n">
         <v>-1.11</v>
@@ -19493,7 +19515,7 @@
         <v>-5.29</v>
       </c>
       <c r="M25" t="n">
-        <v>11.56</v>
+        <v>11.44</v>
       </c>
       <c r="N25" t="b">
         <v>1</v>
@@ -19531,7 +19553,7 @@
         <v>10.7</v>
       </c>
       <c r="H26" t="n">
-        <v>1.88</v>
+        <v>0.47</v>
       </c>
       <c r="I26" t="n">
         <v>7.3</v>
@@ -19544,7 +19566,7 @@
         <v>-3.78</v>
       </c>
       <c r="M26" t="n">
-        <v>0.23</v>
+        <v>-1.47</v>
       </c>
       <c r="N26" t="b">
         <v>1</v>
@@ -19582,7 +19604,7 @@
         <v>25.6</v>
       </c>
       <c r="H27" t="n">
-        <v>12.91</v>
+        <v>17.37</v>
       </c>
       <c r="I27" t="n">
         <v>7.71</v>
@@ -19595,7 +19617,7 @@
         <v>-4.85</v>
       </c>
       <c r="M27" t="n">
-        <v>12.03</v>
+        <v>16.2</v>
       </c>
       <c r="N27" t="b">
         <v>1</v>
@@ -19633,7 +19655,7 @@
         <v>-6.9</v>
       </c>
       <c r="H28" t="n">
-        <v>15.15</v>
+        <v>20.56</v>
       </c>
       <c r="I28" t="n">
         <v>6.44</v>
@@ -19646,7 +19668,7 @@
         <v>-4.53</v>
       </c>
       <c r="M28" t="n">
-        <v>14.18</v>
+        <v>19.3</v>
       </c>
       <c r="N28" t="b">
         <v>1</v>
@@ -19684,7 +19706,7 @@
         <v>0.3</v>
       </c>
       <c r="H29" t="n">
-        <v>-17.99</v>
+        <v>-16.14</v>
       </c>
       <c r="I29" t="n">
         <v>-10.53</v>
@@ -19697,7 +19719,7 @@
         <v>-17.73</v>
       </c>
       <c r="M29" t="n">
-        <v>-18.46</v>
+        <v>-16.89</v>
       </c>
       <c r="N29" t="b">
         <v>1</v>
@@ -19735,7 +19757,7 @@
         <v>2.8</v>
       </c>
       <c r="H30" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="I30" t="n">
         <v>3.18</v>
@@ -19748,7 +19770,7 @@
         <v>-0.88</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.63</v>
+        <v>-0.57</v>
       </c>
       <c r="N30" t="b">
         <v>1</v>
@@ -19786,7 +19808,7 @@
         <v>34.5</v>
       </c>
       <c r="H31" t="n">
-        <v>9.07</v>
+        <v>9.26</v>
       </c>
       <c r="I31" t="n">
         <v>0.66</v>
@@ -19799,7 +19821,7 @@
         <v>-2.64</v>
       </c>
       <c r="M31" t="n">
-        <v>7.88</v>
+        <v>7.78</v>
       </c>
       <c r="N31" t="b">
         <v>1</v>
@@ -19837,7 +19859,7 @@
         <v>24.3</v>
       </c>
       <c r="H32" t="n">
-        <v>49.61</v>
+        <v>41.06</v>
       </c>
       <c r="I32" t="n">
         <v>2.54</v>
@@ -19850,7 +19872,7 @@
         <v>-5.21</v>
       </c>
       <c r="M32" t="n">
-        <v>49.07</v>
+        <v>40.23</v>
       </c>
       <c r="N32" t="b">
         <v>1</v>
@@ -19888,7 +19910,7 @@
         <v>-16.9</v>
       </c>
       <c r="H33" t="n">
-        <v>-9.42</v>
+        <v>-5.24</v>
       </c>
       <c r="I33" t="n">
         <v>-6.47</v>
@@ -19901,7 +19923,7 @@
         <v>-11.5</v>
       </c>
       <c r="M33" t="n">
-        <v>-9.970000000000001</v>
+        <v>-6.07</v>
       </c>
       <c r="N33" t="b">
         <v>1</v>
@@ -19939,7 +19961,7 @@
         <v>20.3</v>
       </c>
       <c r="H34" t="n">
-        <v>-23.01</v>
+        <v>-19.23</v>
       </c>
       <c r="I34" t="n">
         <v>-2.07</v>
@@ -19952,7 +19974,7 @@
         <v>-17.35</v>
       </c>
       <c r="M34" t="n">
-        <v>-23.4</v>
+        <v>-19.9</v>
       </c>
       <c r="N34" t="b">
         <v>1</v>
@@ -19990,7 +20012,7 @@
         <v>0.3</v>
       </c>
       <c r="H35" t="n">
-        <v>-22.33</v>
+        <v>-20.92</v>
       </c>
       <c r="I35" t="n">
         <v>-9.9</v>
@@ -20003,7 +20025,7 @@
         <v>-21.72</v>
       </c>
       <c r="M35" t="n">
-        <v>-23.21</v>
+        <v>-22.09</v>
       </c>
       <c r="N35" t="b">
         <v>1</v>
@@ -20041,7 +20063,7 @@
         <v>49.4</v>
       </c>
       <c r="H36" t="n">
-        <v>4.02</v>
+        <v>4.01</v>
       </c>
       <c r="I36" t="n">
         <v>2.9</v>
@@ -20054,7 +20076,7 @@
         <v>-5.67</v>
       </c>
       <c r="M36" t="n">
-        <v>3.32</v>
+        <v>3.03</v>
       </c>
       <c r="N36" t="b">
         <v>1</v>
@@ -20092,7 +20114,7 @@
         <v>4.5</v>
       </c>
       <c r="H37" t="n">
-        <v>-7.52</v>
+        <v>-4.31</v>
       </c>
       <c r="I37" t="n">
         <v>-7.61</v>
@@ -20105,7 +20127,7 @@
         <v>-11.06</v>
       </c>
       <c r="M37" t="n">
-        <v>-8.220000000000001</v>
+        <v>-5.29</v>
       </c>
       <c r="N37" t="b">
         <v>1</v>
@@ -20143,7 +20165,7 @@
         <v>-17.9</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.55</v>
+        <v>3.72</v>
       </c>
       <c r="I38" t="n">
         <v>0.6</v>
@@ -20156,7 +20178,7 @@
         <v>-4.72</v>
       </c>
       <c r="M38" t="n">
-        <v>-1.28</v>
+        <v>2.71</v>
       </c>
       <c r="N38" t="b">
         <v>1</v>
@@ -20194,7 +20216,7 @@
         <v>2.1</v>
       </c>
       <c r="H39" t="n">
-        <v>-20.29</v>
+        <v>-14.51</v>
       </c>
       <c r="I39" t="n">
         <v>0.25</v>
@@ -20207,7 +20229,7 @@
         <v>-16.43</v>
       </c>
       <c r="M39" t="n">
-        <v>-21.01</v>
+        <v>-15.52</v>
       </c>
       <c r="N39" t="b">
         <v>1</v>
@@ -20296,7 +20318,7 @@
         <v>-2.6</v>
       </c>
       <c r="H41" t="n">
-        <v>-10.4</v>
+        <v>-7.92</v>
       </c>
       <c r="I41" t="n">
         <v>-4.27</v>
@@ -20309,7 +20331,7 @@
         <v>-4.86</v>
       </c>
       <c r="M41" t="n">
-        <v>-10.76</v>
+        <v>-8.57</v>
       </c>
       <c r="N41" t="b">
         <v>1</v>
@@ -20347,7 +20369,7 @@
         <v>23.8</v>
       </c>
       <c r="H42" t="n">
-        <v>-2.77</v>
+        <v>-1.13</v>
       </c>
       <c r="I42" t="n">
         <v>1.36</v>
@@ -20360,7 +20382,7 @@
         <v>-9.94</v>
       </c>
       <c r="M42" t="n">
-        <v>-2.17</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="N42" t="b">
         <v>1</v>
@@ -20398,7 +20420,7 @@
         <v>38.9</v>
       </c>
       <c r="H43" t="n">
-        <v>-11.73</v>
+        <v>-11.26</v>
       </c>
       <c r="I43" t="n">
         <v>-9.220000000000001</v>
@@ -20411,7 +20433,7 @@
         <v>-9.83</v>
       </c>
       <c r="M43" t="n">
-        <v>-11.13</v>
+        <v>-10.95</v>
       </c>
       <c r="N43" t="b">
         <v>1</v>
@@ -20449,7 +20471,7 @@
         <v>43.2</v>
       </c>
       <c r="H44" t="n">
-        <v>-14.35</v>
+        <v>-10.09</v>
       </c>
       <c r="I44" t="n">
         <v>-3.15</v>
@@ -20462,7 +20484,7 @@
         <v>-17.51</v>
       </c>
       <c r="M44" t="n">
-        <v>-13.92</v>
+        <v>-9.94</v>
       </c>
       <c r="N44" t="b">
         <v>1</v>
@@ -20500,7 +20522,7 @@
         <v>-8.199999999999999</v>
       </c>
       <c r="H45" t="n">
-        <v>-0.15</v>
+        <v>3.58</v>
       </c>
       <c r="I45" t="n">
         <v>5.34</v>
@@ -20513,7 +20535,7 @@
         <v>-5.27</v>
       </c>
       <c r="M45" t="n">
-        <v>0.28</v>
+        <v>3.73</v>
       </c>
       <c r="N45" t="b">
         <v>1</v>
@@ -20551,7 +20573,7 @@
         <v>-23.9</v>
       </c>
       <c r="H46" t="n">
-        <v>-9.460000000000001</v>
+        <v>-6.69</v>
       </c>
       <c r="I46" t="n">
         <v>3.28</v>
@@ -20564,7 +20586,7 @@
         <v>-4.46</v>
       </c>
       <c r="M46" t="n">
-        <v>-9.32</v>
+        <v>-6.83</v>
       </c>
       <c r="N46" t="b">
         <v>1</v>
@@ -20606,7 +20628,7 @@
         <v>-6.1</v>
       </c>
       <c r="H47" t="n">
-        <v>-16.21</v>
+        <v>-16.48</v>
       </c>
       <c r="I47" t="n">
         <v>4.9</v>
@@ -20619,7 +20641,7 @@
         <v>-9</v>
       </c>
       <c r="M47" t="n">
-        <v>-16.07</v>
+        <v>-16.62</v>
       </c>
       <c r="N47" t="b">
         <v>1</v>
@@ -20657,7 +20679,7 @@
         <v>26.7</v>
       </c>
       <c r="H48" t="n">
-        <v>-0.84</v>
+        <v>-0.85</v>
       </c>
       <c r="I48" t="n">
         <v>-0.05</v>
@@ -20670,7 +20692,7 @@
         <v>-0.87</v>
       </c>
       <c r="M48" t="n">
-        <v>-0.7</v>
+        <v>-1</v>
       </c>
       <c r="N48" t="b">
         <v>1</v>
@@ -20759,7 +20781,7 @@
         <v>-17.9</v>
       </c>
       <c r="H50" t="n">
-        <v>0.7</v>
+        <v>-0.46</v>
       </c>
       <c r="I50" t="n">
         <v>-0.5</v>
@@ -20772,7 +20794,7 @@
         <v>-3.43</v>
       </c>
       <c r="M50" t="n">
-        <v>0.64</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="N50" t="b">
         <v>1</v>
@@ -20810,7 +20832,7 @@
         <v>53.5</v>
       </c>
       <c r="H51" t="n">
-        <v>5.35</v>
+        <v>7.03</v>
       </c>
       <c r="I51" t="n">
         <v>1.23</v>
@@ -20823,7 +20845,7 @@
         <v>-7.57</v>
       </c>
       <c r="M51" t="n">
-        <v>5.18</v>
+        <v>6.57</v>
       </c>
       <c r="N51" t="b">
         <v>1</v>
@@ -20861,7 +20883,7 @@
         <v>-1</v>
       </c>
       <c r="H52" t="n">
-        <v>-9.92</v>
+        <v>-11.96</v>
       </c>
       <c r="I52" t="n">
         <v>-6.26</v>
@@ -20874,7 +20896,7 @@
         <v>-15</v>
       </c>
       <c r="M52" t="n">
-        <v>-10.08</v>
+        <v>-12.41</v>
       </c>
       <c r="N52" t="b">
         <v>1</v>
@@ -20912,7 +20934,7 @@
         <v>29.7</v>
       </c>
       <c r="H53" t="n">
-        <v>1.54</v>
+        <v>2.81</v>
       </c>
       <c r="I53" t="n">
         <v>11.27</v>
@@ -20925,7 +20947,7 @@
         <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>1.37</v>
+        <v>2.35</v>
       </c>
       <c r="N53" t="b">
         <v>1</v>
@@ -20963,7 +20985,7 @@
         <v>15.2</v>
       </c>
       <c r="H54" t="n">
-        <v>-40.43</v>
+        <v>-36.73</v>
       </c>
       <c r="I54" t="n">
         <v>-8.77</v>
@@ -20976,7 +20998,7 @@
         <v>-24.79</v>
       </c>
       <c r="M54" t="n">
-        <v>-39.87</v>
+        <v>-36.46</v>
       </c>
       <c r="N54" t="b">
         <v>1</v>
@@ -21014,7 +21036,7 @@
         <v>22.2</v>
       </c>
       <c r="H55" t="n">
-        <v>7.27</v>
+        <v>9.67</v>
       </c>
       <c r="I55" t="n">
         <v>1.01</v>
@@ -21027,7 +21049,7 @@
         <v>-3.94</v>
       </c>
       <c r="M55" t="n">
-        <v>7.83</v>
+        <v>9.94</v>
       </c>
       <c r="N55" t="b">
         <v>1</v>
@@ -21069,7 +21091,7 @@
         <v>-0</v>
       </c>
       <c r="H56" t="n">
-        <v>41.6</v>
+        <v>49.07</v>
       </c>
       <c r="I56" t="n">
         <v>13.5</v>
@@ -21082,7 +21104,7 @@
         <v>-2.53</v>
       </c>
       <c r="M56" t="n">
-        <v>38.66</v>
+        <v>45.83</v>
       </c>
       <c r="N56" t="b">
         <v>1</v>
@@ -21120,7 +21142,7 @@
         <v>10.5</v>
       </c>
       <c r="H57" t="n">
-        <v>11.55</v>
+        <v>16.56</v>
       </c>
       <c r="I57" t="n">
         <v>1.99</v>
@@ -21133,7 +21155,7 @@
         <v>-6.27</v>
       </c>
       <c r="M57" t="n">
-        <v>8.6</v>
+        <v>13.32</v>
       </c>
       <c r="N57" t="b">
         <v>1</v>
@@ -21171,7 +21193,7 @@
         <v>-37</v>
       </c>
       <c r="H58" t="n">
-        <v>42.82</v>
+        <v>50.36</v>
       </c>
       <c r="I58" t="n">
         <v>18.38</v>
@@ -21184,7 +21206,7 @@
         <v>-5.11</v>
       </c>
       <c r="M58" t="n">
-        <v>39.21</v>
+        <v>46.46</v>
       </c>
       <c r="N58" t="b">
         <v>1</v>
@@ -21222,7 +21244,7 @@
         <v>-26.8</v>
       </c>
       <c r="H59" t="n">
-        <v>27.29</v>
+        <v>30.62</v>
       </c>
       <c r="I59" t="n">
         <v>4.56</v>
@@ -21235,7 +21257,7 @@
         <v>-4.09</v>
       </c>
       <c r="M59" t="n">
-        <v>23.69</v>
+        <v>26.72</v>
       </c>
       <c r="N59" t="b">
         <v>1</v>
@@ -21273,7 +21295,7 @@
         <v>-36.5</v>
       </c>
       <c r="H60" t="n">
-        <v>-34.76</v>
+        <v>-29.67</v>
       </c>
       <c r="I60" t="n">
         <v>-27.75</v>
@@ -21286,7 +21308,7 @@
         <v>-31.28</v>
       </c>
       <c r="M60" t="n">
-        <v>-39.02</v>
+        <v>-34.23</v>
       </c>
       <c r="N60" t="b">
         <v>1</v>
@@ -21324,7 +21346,7 @@
         <v>-38.7</v>
       </c>
       <c r="H61" t="n">
-        <v>15.67</v>
+        <v>22.94</v>
       </c>
       <c r="I61" t="n">
         <v>17.17</v>
@@ -21337,7 +21359,7 @@
         <v>-0.54</v>
       </c>
       <c r="M61" t="n">
-        <v>11.41</v>
+        <v>18.38</v>
       </c>
       <c r="N61" t="b">
         <v>1</v>
@@ -21375,7 +21397,7 @@
         <v>-34.6</v>
       </c>
       <c r="H62" t="n">
-        <v>15.51</v>
+        <v>22.75</v>
       </c>
       <c r="I62" t="n">
         <v>6.67</v>
@@ -21388,7 +21410,7 @@
         <v>-3.06</v>
       </c>
       <c r="M62" t="n">
-        <v>11.25</v>
+        <v>18.19</v>
       </c>
       <c r="N62" t="b">
         <v>1</v>
@@ -21426,7 +21448,7 @@
         <v>-11.8</v>
       </c>
       <c r="H63" t="n">
-        <v>-0.93</v>
+        <v>2.76</v>
       </c>
       <c r="I63" t="n">
         <v>9.76</v>
@@ -21439,7 +21461,7 @@
         <v>-1.63</v>
       </c>
       <c r="M63" t="n">
-        <v>-5.3</v>
+        <v>-1.91</v>
       </c>
       <c r="N63" t="b">
         <v>1</v>
@@ -21477,7 +21499,7 @@
         <v>0.1</v>
       </c>
       <c r="H64" t="n">
-        <v>-12.44</v>
+        <v>-7.73</v>
       </c>
       <c r="I64" t="n">
         <v>-2.83</v>
@@ -21490,7 +21512,7 @@
         <v>-5.45</v>
       </c>
       <c r="M64" t="n">
-        <v>-16.81</v>
+        <v>-12.4</v>
       </c>
       <c r="N64" t="b">
         <v>1</v>
@@ -21528,7 +21550,7 @@
         <v>24.1</v>
       </c>
       <c r="H65" t="n">
-        <v>2.77</v>
+        <v>2.93</v>
       </c>
       <c r="I65" t="n">
         <v>-8.31</v>
@@ -21541,7 +21563,7 @@
         <v>-18.31</v>
       </c>
       <c r="M65" t="n">
-        <v>-0.8</v>
+        <v>-0.93</v>
       </c>
       <c r="N65" t="b">
         <v>1</v>
@@ -21579,7 +21601,7 @@
         <v>-15.9</v>
       </c>
       <c r="H66" t="n">
-        <v>10</v>
+        <v>13.57</v>
       </c>
       <c r="I66" t="n">
         <v>10.45</v>
@@ -21592,7 +21614,7 @@
         <v>-0.31</v>
       </c>
       <c r="M66" t="n">
-        <v>6.43</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="N66" t="b">
         <v>1</v>
@@ -21630,7 +21652,7 @@
         <v>-21.8</v>
       </c>
       <c r="H67" t="n">
-        <v>-36.71</v>
+        <v>-32.58</v>
       </c>
       <c r="I67" t="n">
         <v>-18.97</v>
@@ -21643,7 +21665,7 @@
         <v>-26.82</v>
       </c>
       <c r="M67" t="n">
-        <v>-41.06</v>
+        <v>-37.23</v>
       </c>
       <c r="N67" t="b">
         <v>1</v>
@@ -21681,7 +21703,7 @@
         <v>57</v>
       </c>
       <c r="H68" t="n">
-        <v>37.47</v>
+        <v>34.25</v>
       </c>
       <c r="I68" t="n">
         <v>-11.21</v>
@@ -21689,12 +21711,14 @@
       <c r="J68" t="n">
         <v>1.87</v>
       </c>
-      <c r="K68" t="inlineStr"/>
+      <c r="K68" t="n">
+        <v>34.25</v>
+      </c>
       <c r="L68" t="n">
         <v>-13.87</v>
       </c>
       <c r="M68" t="n">
-        <v>34.14</v>
+        <v>30.63</v>
       </c>
       <c r="N68" t="b">
         <v>1</v>
@@ -21732,7 +21756,7 @@
         <v>-21.8</v>
       </c>
       <c r="H69" t="n">
-        <v>16.15</v>
+        <v>20.63</v>
       </c>
       <c r="I69" t="n">
         <v>1.71</v>
@@ -21740,12 +21764,14 @@
       <c r="J69" t="n">
         <v>15.07</v>
       </c>
-      <c r="K69" t="inlineStr"/>
+      <c r="K69" t="n">
+        <v>20.63</v>
+      </c>
       <c r="L69" t="n">
         <v>-6.18</v>
       </c>
       <c r="M69" t="n">
-        <v>12.81</v>
+        <v>17</v>
       </c>
       <c r="N69" t="b">
         <v>1</v>
@@ -21783,7 +21809,7 @@
         <v>1</v>
       </c>
       <c r="H70" t="n">
-        <v>-33.09</v>
+        <v>-31.18</v>
       </c>
       <c r="I70" t="n">
         <v>-11.52</v>
@@ -21798,7 +21824,7 @@
         <v>-16.26</v>
       </c>
       <c r="M70" t="n">
-        <v>-36.47</v>
+        <v>-34.85</v>
       </c>
       <c r="N70" t="b">
         <v>1</v>
@@ -21836,7 +21862,7 @@
         <v>45.4</v>
       </c>
       <c r="H71" t="n">
-        <v>-16.63</v>
+        <v>-14.25</v>
       </c>
       <c r="I71" t="n">
         <v>-1.72</v>
@@ -21851,7 +21877,7 @@
         <v>-23.15</v>
       </c>
       <c r="M71" t="n">
-        <v>-20</v>
+        <v>-17.92</v>
       </c>
       <c r="N71" t="b">
         <v>1</v>
@@ -21889,7 +21915,7 @@
         <v>76.5</v>
       </c>
       <c r="H72" t="n">
-        <v>-7.17</v>
+        <v>-7.73</v>
       </c>
       <c r="I72" t="n">
         <v>-5.56</v>
@@ -21904,7 +21930,7 @@
         <v>-33.97</v>
       </c>
       <c r="M72" t="n">
-        <v>-10.55</v>
+        <v>-11.4</v>
       </c>
       <c r="N72" t="b">
         <v>1</v>
@@ -21942,7 +21968,7 @@
         <v>32.1</v>
       </c>
       <c r="H73" t="n">
-        <v>-3.65</v>
+        <v>-2.4</v>
       </c>
       <c r="I73" t="n">
         <v>16.93</v>
@@ -21957,7 +21983,7 @@
         <v>-24.48</v>
       </c>
       <c r="M73" t="n">
-        <v>-7.03</v>
+        <v>-6.08</v>
       </c>
       <c r="N73" t="b">
         <v>1</v>
@@ -21995,7 +22021,7 @@
         <v>51.8</v>
       </c>
       <c r="H74" t="n">
-        <v>-8.050000000000001</v>
+        <v>-7.53</v>
       </c>
       <c r="I74" t="n">
         <v>10.75</v>
@@ -22010,7 +22036,7 @@
         <v>-25.09</v>
       </c>
       <c r="M74" t="n">
-        <v>-11.43</v>
+        <v>-11.2</v>
       </c>
       <c r="N74" t="b">
         <v>1</v>
@@ -22048,7 +22074,7 @@
         <v>32.3</v>
       </c>
       <c r="H75" t="n">
-        <v>-33.71</v>
+        <v>-34.71</v>
       </c>
       <c r="I75" t="n">
         <v>-20.76</v>
@@ -22063,7 +22089,7 @@
         <v>-27.91</v>
       </c>
       <c r="M75" t="n">
-        <v>-37.09</v>
+        <v>-38.38</v>
       </c>
       <c r="N75" t="b">
         <v>1</v>
@@ -22101,7 +22127,7 @@
         <v>3.7</v>
       </c>
       <c r="H76" t="n">
-        <v>-14.76</v>
+        <v>-9.66</v>
       </c>
       <c r="I76" t="n">
         <v>-1.11</v>
@@ -22116,7 +22142,7 @@
         <v>-25.46</v>
       </c>
       <c r="M76" t="n">
-        <v>-18.14</v>
+        <v>-13.33</v>
       </c>
       <c r="N76" t="b">
         <v>1</v>
@@ -22154,7 +22180,7 @@
         <v>42.4</v>
       </c>
       <c r="H77" t="n">
-        <v>-13.37</v>
+        <v>-13.23</v>
       </c>
       <c r="I77" t="n">
         <v>2.16</v>
@@ -22169,7 +22195,7 @@
         <v>-15.76</v>
       </c>
       <c r="M77" t="n">
-        <v>-16.75</v>
+        <v>-16.9</v>
       </c>
       <c r="N77" t="b">
         <v>1</v>
@@ -22207,7 +22233,7 @@
         <v>28.2</v>
       </c>
       <c r="H78" t="n">
-        <v>-6.02</v>
+        <v>-10.24</v>
       </c>
       <c r="I78" t="n">
         <v>-1.71</v>
@@ -22222,7 +22248,7 @@
         <v>-23.43</v>
       </c>
       <c r="M78" t="n">
-        <v>-9.4</v>
+        <v>-13.91</v>
       </c>
       <c r="N78" t="b">
         <v>1</v>
@@ -22260,7 +22286,7 @@
         <v>28.6</v>
       </c>
       <c r="H79" t="n">
-        <v>11.38</v>
+        <v>-0.16</v>
       </c>
       <c r="I79" t="n">
         <v>2.81</v>
@@ -22275,7 +22301,7 @@
         <v>-18.87</v>
       </c>
       <c r="M79" t="n">
-        <v>8</v>
+        <v>-3.84</v>
       </c>
       <c r="N79" t="b">
         <v>1</v>
@@ -22313,7 +22339,7 @@
         <v>33.1</v>
       </c>
       <c r="H80" t="n">
-        <v>10.45</v>
+        <v>7.15</v>
       </c>
       <c r="I80" t="n">
         <v>4.68</v>
@@ -22328,7 +22354,7 @@
         <v>-26.7</v>
       </c>
       <c r="M80" t="n">
-        <v>7.07</v>
+        <v>3.48</v>
       </c>
       <c r="N80" t="b">
         <v>1</v>
@@ -22366,7 +22392,7 @@
         <v>21.8</v>
       </c>
       <c r="H81" t="n">
-        <v>-27.13</v>
+        <v>-28.51</v>
       </c>
       <c r="I81" t="n">
         <v>-6.34</v>
@@ -22381,7 +22407,7 @@
         <v>-30.04</v>
       </c>
       <c r="M81" t="n">
-        <v>-30.51</v>
+        <v>-32.18</v>
       </c>
       <c r="N81" t="b">
         <v>1</v>
@@ -22419,7 +22445,7 @@
         <v>40.3</v>
       </c>
       <c r="H82" t="n">
-        <v>-19.82</v>
+        <v>-21.3</v>
       </c>
       <c r="I82" t="n">
         <v>1.24</v>
@@ -22434,7 +22460,7 @@
         <v>-20.5</v>
       </c>
       <c r="M82" t="n">
-        <v>-23.2</v>
+        <v>-24.97</v>
       </c>
       <c r="N82" t="b">
         <v>1</v>
@@ -22472,7 +22498,7 @@
         <v>24.1</v>
       </c>
       <c r="H83" t="n">
-        <v>-11.41</v>
+        <v>-15.35</v>
       </c>
       <c r="I83" t="n">
         <v>-1.6</v>
@@ -22487,7 +22513,7 @@
         <v>-22.54</v>
       </c>
       <c r="M83" t="n">
-        <v>-14.79</v>
+        <v>-19.03</v>
       </c>
       <c r="N83" t="b">
         <v>1</v>
@@ -22525,7 +22551,7 @@
         <v>24.5</v>
       </c>
       <c r="H84" t="n">
-        <v>-34.58</v>
+        <v>-34.29</v>
       </c>
       <c r="I84" t="n">
         <v>-12.99</v>
@@ -22540,7 +22566,7 @@
         <v>-22.54</v>
       </c>
       <c r="M84" t="n">
-        <v>-37.96</v>
+        <v>-37.97</v>
       </c>
       <c r="N84" t="b">
         <v>1</v>
@@ -22578,7 +22604,7 @@
         <v>19.3</v>
       </c>
       <c r="H85" t="n">
-        <v>-0.39</v>
+        <v>-4.89</v>
       </c>
       <c r="I85" t="n">
         <v>11.79</v>
@@ -22593,7 +22619,7 @@
         <v>-16.62</v>
       </c>
       <c r="M85" t="n">
-        <v>-3.77</v>
+        <v>-8.57</v>
       </c>
       <c r="N85" t="b">
         <v>1</v>
@@ -22631,7 +22657,7 @@
         <v>-8.699999999999999</v>
       </c>
       <c r="H86" t="n">
-        <v>-11.93</v>
+        <v>-9.24</v>
       </c>
       <c r="I86" t="n">
         <v>17.25</v>
@@ -22646,7 +22672,7 @@
         <v>-4.65</v>
       </c>
       <c r="M86" t="n">
-        <v>-15.31</v>
+        <v>-12.91</v>
       </c>
       <c r="N86" t="b">
         <v>1</v>
@@ -22684,7 +22710,7 @@
         <v>15.2</v>
       </c>
       <c r="H87" t="n">
-        <v>-14.3</v>
+        <v>-18.44</v>
       </c>
       <c r="I87" t="n">
         <v>5.36</v>
@@ -22699,7 +22725,7 @@
         <v>-28.18</v>
       </c>
       <c r="M87" t="n">
-        <v>-17.68</v>
+        <v>-22.11</v>
       </c>
       <c r="N87" t="b">
         <v>1</v>
@@ -22737,7 +22763,7 @@
         <v>37.2</v>
       </c>
       <c r="H88" t="n">
-        <v>-32.41</v>
+        <v>-34.14</v>
       </c>
       <c r="I88" t="n">
         <v>-7.64</v>
@@ -22752,7 +22778,7 @@
         <v>-26.24</v>
       </c>
       <c r="M88" t="n">
-        <v>-35.79</v>
+        <v>-37.81</v>
       </c>
       <c r="N88" t="b">
         <v>1</v>
@@ -22790,7 +22816,7 @@
         <v>29.8</v>
       </c>
       <c r="H89" t="n">
-        <v>20.68</v>
+        <v>8.59</v>
       </c>
       <c r="I89" t="n">
         <v>-2.74</v>
@@ -22805,7 +22831,7 @@
         <v>-22.36</v>
       </c>
       <c r="M89" t="n">
-        <v>17.3</v>
+        <v>4.92</v>
       </c>
       <c r="N89" t="b">
         <v>1</v>
@@ -22843,7 +22869,7 @@
         <v>19.3</v>
       </c>
       <c r="H90" t="n">
-        <v>-33.04</v>
+        <v>-34.19</v>
       </c>
       <c r="I90" t="n">
         <v>-16.69</v>
@@ -22858,7 +22884,7 @@
         <v>-36.39</v>
       </c>
       <c r="M90" t="n">
-        <v>-36.42</v>
+        <v>-37.87</v>
       </c>
       <c r="N90" t="b">
         <v>1</v>
@@ -22896,7 +22922,7 @@
         <v>11.8</v>
       </c>
       <c r="H91" t="n">
-        <v>5.32</v>
+        <v>-1.89</v>
       </c>
       <c r="I91" t="n">
         <v>-1.19</v>
@@ -22911,7 +22937,7 @@
         <v>-17.57</v>
       </c>
       <c r="M91" t="n">
-        <v>1.94</v>
+        <v>-5.56</v>
       </c>
       <c r="N91" t="b">
         <v>1</v>
@@ -22949,7 +22975,7 @@
         <v>27.5</v>
       </c>
       <c r="H92" t="n">
-        <v>8.4</v>
+        <v>4.86</v>
       </c>
       <c r="I92" t="n">
         <v>8.42</v>
@@ -22964,7 +22990,7 @@
         <v>-2.51</v>
       </c>
       <c r="M92" t="n">
-        <v>5.03</v>
+        <v>1.19</v>
       </c>
       <c r="N92" t="b">
         <v>1</v>
@@ -23002,7 +23028,7 @@
         <v>-22.4</v>
       </c>
       <c r="H93" t="n">
-        <v>-9.630000000000001</v>
+        <v>-7.4</v>
       </c>
       <c r="I93" t="n">
         <v>9.42</v>
@@ -23017,7 +23043,7 @@
         <v>-2.79</v>
       </c>
       <c r="M93" t="n">
-        <v>-13.01</v>
+        <v>-11.07</v>
       </c>
       <c r="N93" t="b">
         <v>1</v>
@@ -23055,7 +23081,7 @@
         <v>-14.7</v>
       </c>
       <c r="H94" t="n">
-        <v>-21.35</v>
+        <v>-18.07</v>
       </c>
       <c r="I94" t="n">
         <v>10.3</v>
@@ -23070,7 +23096,7 @@
         <v>-2.6</v>
       </c>
       <c r="M94" t="n">
-        <v>-24.73</v>
+        <v>-21.74</v>
       </c>
       <c r="N94" t="b">
         <v>1</v>
@@ -23112,7 +23138,7 @@
         <v>-9.300000000000001</v>
       </c>
       <c r="H95" t="n">
-        <v>-24.56</v>
+        <v>-21.88</v>
       </c>
       <c r="I95" t="n">
         <v>10.42</v>
@@ -23127,7 +23153,7 @@
         <v>-21.72</v>
       </c>
       <c r="M95" t="n">
-        <v>-27.94</v>
+        <v>-25.56</v>
       </c>
       <c r="N95" t="b">
         <v>1</v>
@@ -23165,7 +23191,7 @@
         <v>-25.2</v>
       </c>
       <c r="H96" t="n">
-        <v>-12.3</v>
+        <v>-7.08</v>
       </c>
       <c r="I96" t="n">
         <v>22.53</v>
@@ -23180,7 +23206,7 @@
         <v>-19.27</v>
       </c>
       <c r="M96" t="n">
-        <v>-15.68</v>
+        <v>-10.76</v>
       </c>
       <c r="N96" t="b">
         <v>1</v>
@@ -23218,7 +23244,7 @@
         <v>5.1</v>
       </c>
       <c r="H97" t="n">
-        <v>2.64</v>
+        <v>6.89</v>
       </c>
       <c r="I97" t="n">
         <v>8.77</v>
@@ -23233,7 +23259,7 @@
         <v>-3.54</v>
       </c>
       <c r="M97" t="n">
-        <v>-0.74</v>
+        <v>3.22</v>
       </c>
       <c r="N97" t="b">
         <v>1</v>
@@ -23271,7 +23297,7 @@
         <v>34.2</v>
       </c>
       <c r="H98" t="n">
-        <v>6.53</v>
+        <v>4.58</v>
       </c>
       <c r="I98" t="n">
         <v>8.15</v>
@@ -23286,7 +23312,7 @@
         <v>-7.63</v>
       </c>
       <c r="M98" t="n">
-        <v>3.15</v>
+        <v>0.91</v>
       </c>
       <c r="N98" t="b">
         <v>1</v>
@@ -23324,7 +23350,7 @@
         <v>42</v>
       </c>
       <c r="H99" t="n">
-        <v>-32.97</v>
+        <v>-32.82</v>
       </c>
       <c r="I99" t="n">
         <v>0.6</v>
@@ -23339,7 +23365,7 @@
         <v>-16.67</v>
       </c>
       <c r="M99" t="n">
-        <v>-36.35</v>
+        <v>-36.5</v>
       </c>
       <c r="N99" t="b">
         <v>1</v>
@@ -23377,7 +23403,7 @@
         <v>-25.3</v>
       </c>
       <c r="H100" t="n">
-        <v>43.41</v>
+        <v>51.86</v>
       </c>
       <c r="I100" t="n">
         <v>36.1</v>
@@ -23392,7 +23418,7 @@
         <v>-5.66</v>
       </c>
       <c r="M100" t="n">
-        <v>40.03</v>
+        <v>48.19</v>
       </c>
       <c r="N100" t="b">
         <v>1</v>
@@ -23430,7 +23456,7 @@
         <v>-7.7</v>
       </c>
       <c r="H101" t="n">
-        <v>-14.32</v>
+        <v>-13.61</v>
       </c>
       <c r="I101" t="n">
         <v>-6.47</v>
@@ -23445,7 +23471,7 @@
         <v>-23.05</v>
       </c>
       <c r="M101" t="n">
-        <v>-17.7</v>
+        <v>-17.28</v>
       </c>
       <c r="N101" t="b">
         <v>1</v>
@@ -23483,7 +23509,7 @@
         <v>13.7</v>
       </c>
       <c r="H102" t="n">
-        <v>8.800000000000001</v>
+        <v>4.38</v>
       </c>
       <c r="I102" t="n">
         <v>2.74</v>
@@ -23498,7 +23524,7 @@
         <v>-24.02</v>
       </c>
       <c r="M102" t="n">
-        <v>5.42</v>
+        <v>0.71</v>
       </c>
       <c r="N102" t="b">
         <v>1</v>
@@ -23536,7 +23562,7 @@
         <v>21.8</v>
       </c>
       <c r="H103" t="n">
-        <v>-17.06</v>
+        <v>-18.32</v>
       </c>
       <c r="I103" t="n">
         <v>18.32</v>
@@ -23551,7 +23577,7 @@
         <v>-23.27</v>
       </c>
       <c r="M103" t="n">
-        <v>-20.43</v>
+        <v>-22</v>
       </c>
       <c r="N103" t="b">
         <v>1</v>
@@ -23589,7 +23615,7 @@
         <v>29.4</v>
       </c>
       <c r="H104" t="n">
-        <v>-18.26</v>
+        <v>-21.46</v>
       </c>
       <c r="I104" t="n">
         <v>-2.62</v>
@@ -23604,7 +23630,7 @@
         <v>-27.18</v>
       </c>
       <c r="M104" t="n">
-        <v>-21.64</v>
+        <v>-25.13</v>
       </c>
       <c r="N104" t="b">
         <v>1</v>
@@ -23642,7 +23668,7 @@
         <v>-3.7</v>
       </c>
       <c r="H105" t="n">
-        <v>-28.01</v>
+        <v>-27.92</v>
       </c>
       <c r="I105" t="n">
         <v>-8.07</v>
@@ -23657,7 +23683,7 @@
         <v>-22.12</v>
       </c>
       <c r="M105" t="n">
-        <v>-31.39</v>
+        <v>-31.59</v>
       </c>
       <c r="N105" t="b">
         <v>1</v>
@@ -23695,7 +23721,7 @@
         <v>21.3</v>
       </c>
       <c r="H106" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="I106" t="n">
         <v>0.23</v>
@@ -23710,7 +23736,7 @@
         <v>-0.85</v>
       </c>
       <c r="M106" t="n">
-        <v>-1.91</v>
+        <v>-2.22</v>
       </c>
       <c r="N106" t="b">
         <v>1</v>
@@ -23748,7 +23774,7 @@
         <v>-21.4</v>
       </c>
       <c r="H107" t="n">
-        <v>1.24</v>
+        <v>5.73</v>
       </c>
       <c r="I107" t="n">
         <v>4.55</v>
@@ -23763,7 +23789,7 @@
         <v>-6.39</v>
       </c>
       <c r="M107" t="n">
-        <v>-2.14</v>
+        <v>2.05</v>
       </c>
       <c r="N107" t="b">
         <v>1</v>
@@ -23801,7 +23827,7 @@
         <v>16.3</v>
       </c>
       <c r="H108" t="n">
-        <v>-7.27</v>
+        <v>-9.93</v>
       </c>
       <c r="I108" t="n">
         <v>-1</v>
@@ -23816,7 +23842,7 @@
         <v>-22.5</v>
       </c>
       <c r="M108" t="n">
-        <v>-10.65</v>
+        <v>-13.6</v>
       </c>
       <c r="N108" t="b">
         <v>1</v>
@@ -23854,7 +23880,7 @@
         <v>11.9</v>
       </c>
       <c r="H109" t="n">
-        <v>-6.84</v>
+        <v>-8.99</v>
       </c>
       <c r="I109" t="n">
         <v>7.74</v>
@@ -23869,7 +23895,7 @@
         <v>-9.43</v>
       </c>
       <c r="M109" t="n">
-        <v>-10.22</v>
+        <v>-12.66</v>
       </c>
       <c r="N109" t="b">
         <v>1</v>
@@ -23907,7 +23933,7 @@
         <v>0.2</v>
       </c>
       <c r="H110" t="n">
-        <v>13.15</v>
+        <v>11.85</v>
       </c>
       <c r="I110" t="n">
         <v>4.35</v>
@@ -23922,7 +23948,7 @@
         <v>-2.79</v>
       </c>
       <c r="M110" t="n">
-        <v>9.77</v>
+        <v>8.17</v>
       </c>
       <c r="N110" t="b">
         <v>1</v>
@@ -23960,7 +23986,7 @@
         <v>8.4</v>
       </c>
       <c r="H111" t="n">
-        <v>-37.45</v>
+        <v>-37.98</v>
       </c>
       <c r="I111" t="n">
         <v>-0.13</v>
@@ -23975,7 +24001,7 @@
         <v>-10.87</v>
       </c>
       <c r="M111" t="n">
-        <v>-40.83</v>
+        <v>-41.65</v>
       </c>
       <c r="N111" t="b">
         <v>1</v>
@@ -24013,7 +24039,7 @@
         <v>-7.3</v>
       </c>
       <c r="H112" t="n">
-        <v>-19.59</v>
+        <v>-18.72</v>
       </c>
       <c r="I112" t="n">
         <v>-4.12</v>
@@ -24028,7 +24054,7 @@
         <v>-15.02</v>
       </c>
       <c r="M112" t="n">
-        <v>-22.97</v>
+        <v>-22.39</v>
       </c>
       <c r="N112" t="b">
         <v>1</v>
@@ -24066,7 +24092,7 @@
         <v>-26.1</v>
       </c>
       <c r="H113" t="n">
-        <v>-29.59</v>
+        <v>-25.18</v>
       </c>
       <c r="I113" t="n">
         <v>5.05</v>
@@ -24081,7 +24107,7 @@
         <v>-9.27</v>
       </c>
       <c r="M113" t="n">
-        <v>-32.97</v>
+        <v>-28.86</v>
       </c>
       <c r="N113" t="b">
         <v>1</v>
@@ -24119,7 +24145,7 @@
         <v>26.1</v>
       </c>
       <c r="H114" t="n">
-        <v>-13.58</v>
+        <v>-16.97</v>
       </c>
       <c r="I114" t="n">
         <v>-0.51</v>
@@ -24134,7 +24160,7 @@
         <v>-16.45</v>
       </c>
       <c r="M114" t="n">
-        <v>-16.96</v>
+        <v>-20.64</v>
       </c>
       <c r="N114" t="b">
         <v>1</v>
@@ -24172,7 +24198,7 @@
         <v>17.9</v>
       </c>
       <c r="H115" t="n">
-        <v>-2.66</v>
+        <v>-4.92</v>
       </c>
       <c r="I115" t="n">
         <v>12.97</v>
@@ -24187,7 +24213,7 @@
         <v>-8.130000000000001</v>
       </c>
       <c r="M115" t="n">
-        <v>-6.04</v>
+        <v>-8.6</v>
       </c>
       <c r="N115" t="b">
         <v>1</v>
@@ -24225,7 +24251,7 @@
         <v>0.7</v>
       </c>
       <c r="H116" t="n">
-        <v>-22.68</v>
+        <v>-21.02</v>
       </c>
       <c r="I116" t="n">
         <v>14.96</v>
@@ -24240,7 +24266,7 @@
         <v>-8.039999999999999</v>
       </c>
       <c r="M116" t="n">
-        <v>-26.06</v>
+        <v>-24.69</v>
       </c>
       <c r="N116" t="b">
         <v>1</v>
@@ -24278,7 +24304,7 @@
         <v>14.8</v>
       </c>
       <c r="H117" t="n">
-        <v>-6.63</v>
+        <v>-6.36</v>
       </c>
       <c r="I117" t="n">
         <v>0.35</v>
@@ -24293,7 +24319,7 @@
         <v>-3.68</v>
       </c>
       <c r="M117" t="n">
-        <v>-10.01</v>
+        <v>-10.03</v>
       </c>
       <c r="N117" t="b">
         <v>1</v>
@@ -24331,7 +24357,7 @@
         <v>25.5</v>
       </c>
       <c r="H118" t="n">
-        <v>5.88</v>
+        <v>9.02</v>
       </c>
       <c r="I118" t="n">
         <v>-9.369999999999999</v>
@@ -24346,7 +24372,7 @@
         <v>-22.11</v>
       </c>
       <c r="M118" t="n">
-        <v>2.5</v>
+        <v>5.35</v>
       </c>
       <c r="N118" t="b">
         <v>1</v>
@@ -24388,7 +24414,7 @@
         <v>-7.5</v>
       </c>
       <c r="H119" t="n">
-        <v>-10.66</v>
+        <v>-8.609999999999999</v>
       </c>
       <c r="I119" t="n">
         <v>4.46</v>
@@ -24403,7 +24429,7 @@
         <v>-8.52</v>
       </c>
       <c r="M119" t="n">
-        <v>-14.04</v>
+        <v>-12.28</v>
       </c>
       <c r="N119" t="b">
         <v>1</v>
@@ -24441,7 +24467,7 @@
         <v>-11</v>
       </c>
       <c r="H120" t="n">
-        <v>13.89</v>
+        <v>21.38</v>
       </c>
       <c r="I120" t="n">
         <v>10.7</v>
@@ -24456,7 +24482,7 @@
         <v>-9.43</v>
       </c>
       <c r="M120" t="n">
-        <v>10.51</v>
+        <v>17.71</v>
       </c>
       <c r="N120" t="b">
         <v>1</v>
@@ -24494,7 +24520,7 @@
         <v>-11.4</v>
       </c>
       <c r="H121" t="n">
-        <v>-18.91</v>
+        <v>-17.09</v>
       </c>
       <c r="I121" t="n">
         <v>4.36</v>
@@ -24509,7 +24535,7 @@
         <v>-11.36</v>
       </c>
       <c r="M121" t="n">
-        <v>-22.29</v>
+        <v>-20.76</v>
       </c>
       <c r="N121" t="b">
         <v>1</v>
@@ -24547,7 +24573,7 @@
         <v>27.1</v>
       </c>
       <c r="H122" t="n">
-        <v>-12.48</v>
+        <v>-18.5</v>
       </c>
       <c r="I122" t="n">
         <v>5.02</v>
@@ -24562,7 +24588,7 @@
         <v>-14.35</v>
       </c>
       <c r="M122" t="n">
-        <v>-15.86</v>
+        <v>-22.17</v>
       </c>
       <c r="N122" t="b">
         <v>1</v>
@@ -24600,7 +24626,7 @@
         <v>32.2</v>
       </c>
       <c r="H123" t="n">
-        <v>10.76</v>
+        <v>7.39</v>
       </c>
       <c r="I123" t="n">
         <v>6.49</v>
@@ -24615,7 +24641,7 @@
         <v>-3.92</v>
       </c>
       <c r="M123" t="n">
-        <v>7.38</v>
+        <v>3.72</v>
       </c>
       <c r="N123" t="b">
         <v>1</v>
@@ -24653,7 +24679,7 @@
         <v>3.2</v>
       </c>
       <c r="H124" t="n">
-        <v>-24.39</v>
+        <v>-27.43</v>
       </c>
       <c r="I124" t="n">
         <v>-10.41</v>
@@ -24668,7 +24694,7 @@
         <v>-23.7</v>
       </c>
       <c r="M124" t="n">
-        <v>-27.77</v>
+        <v>-31.1</v>
       </c>
       <c r="N124" t="b">
         <v>1</v>
@@ -24706,7 +24732,7 @@
         <v>7.3</v>
       </c>
       <c r="H125" t="n">
-        <v>0.5600000000000001</v>
+        <v>3.02</v>
       </c>
       <c r="I125" t="n">
         <v>-0.57</v>
@@ -24721,7 +24747,7 @@
         <v>-5.89</v>
       </c>
       <c r="M125" t="n">
-        <v>-2.82</v>
+        <v>-0.65</v>
       </c>
       <c r="N125" t="b">
         <v>1</v>
@@ -24759,7 +24785,7 @@
         <v>-0.3</v>
       </c>
       <c r="H126" t="n">
-        <v>-10.02</v>
+        <v>-13.02</v>
       </c>
       <c r="I126" t="n">
         <v>17.76</v>
@@ -24774,7 +24800,7 @@
         <v>-14.18</v>
       </c>
       <c r="M126" t="n">
-        <v>-13.4</v>
+        <v>-16.69</v>
       </c>
       <c r="N126" t="b">
         <v>1</v>
@@ -24812,7 +24838,7 @@
         <v>-6.8</v>
       </c>
       <c r="H127" t="n">
-        <v>24.66</v>
+        <v>28.24</v>
       </c>
       <c r="I127" t="n">
         <v>8.279999999999999</v>
@@ -24827,7 +24853,7 @@
         <v>-6.78</v>
       </c>
       <c r="M127" t="n">
-        <v>21.28</v>
+        <v>24.57</v>
       </c>
       <c r="N127" t="b">
         <v>1</v>
@@ -24865,7 +24891,7 @@
         <v>34.6</v>
       </c>
       <c r="H128" t="n">
-        <v>-0.8</v>
+        <v>-0.02</v>
       </c>
       <c r="I128" t="n">
         <v>5.7</v>
@@ -24880,7 +24906,7 @@
         <v>-7.7</v>
       </c>
       <c r="M128" t="n">
-        <v>-4.18</v>
+        <v>-3.69</v>
       </c>
       <c r="N128" t="b">
         <v>1</v>
@@ -24918,7 +24944,7 @@
         <v>10.4</v>
       </c>
       <c r="H129" t="n">
-        <v>26.13</v>
+        <v>26.36</v>
       </c>
       <c r="I129" t="n">
         <v>11.05</v>
@@ -24933,7 +24959,7 @@
         <v>-5.54</v>
       </c>
       <c r="M129" t="n">
-        <v>22.75</v>
+        <v>22.69</v>
       </c>
       <c r="N129" t="b">
         <v>1</v>
@@ -24971,7 +24997,7 @@
         <v>-21.5</v>
       </c>
       <c r="H130" t="n">
-        <v>-4.36</v>
+        <v>-2.16</v>
       </c>
       <c r="I130" t="n">
         <v>10.65</v>
@@ -24986,7 +25012,7 @@
         <v>-6.89</v>
       </c>
       <c r="M130" t="n">
-        <v>-7.74</v>
+        <v>-5.83</v>
       </c>
       <c r="N130" t="b">
         <v>1</v>
@@ -25024,7 +25050,7 @@
         <v>3.5</v>
       </c>
       <c r="H131" t="n">
-        <v>52.65</v>
+        <v>56.44</v>
       </c>
       <c r="I131" t="n">
         <v>33.01</v>
@@ -25039,7 +25065,7 @@
         <v>-0.92</v>
       </c>
       <c r="M131" t="n">
-        <v>49.27</v>
+        <v>52.77</v>
       </c>
       <c r="N131" t="b">
         <v>1</v>
@@ -25077,7 +25103,7 @@
         <v>19.8</v>
       </c>
       <c r="H132" t="n">
-        <v>9.77</v>
+        <v>5</v>
       </c>
       <c r="I132" t="n">
         <v>4.74</v>
@@ -25092,7 +25118,7 @@
         <v>-9.9</v>
       </c>
       <c r="M132" t="n">
-        <v>6.39</v>
+        <v>1.32</v>
       </c>
       <c r="N132" t="b">
         <v>1</v>
@@ -25130,7 +25156,7 @@
         <v>-30.5</v>
       </c>
       <c r="H133" t="n">
-        <v>-5.3</v>
+        <v>-1.85</v>
       </c>
       <c r="I133" t="n">
         <v>2.96</v>
@@ -25145,7 +25171,7 @@
         <v>-17.88</v>
       </c>
       <c r="M133" t="n">
-        <v>-8.68</v>
+        <v>-5.52</v>
       </c>
       <c r="N133" t="b">
         <v>1</v>
@@ -25183,7 +25209,7 @@
         <v>-6</v>
       </c>
       <c r="H134" t="n">
-        <v>-23.55</v>
+        <v>-25.06</v>
       </c>
       <c r="I134" t="n">
         <v>3.31</v>
@@ -25198,7 +25224,7 @@
         <v>-21.48</v>
       </c>
       <c r="M134" t="n">
-        <v>-26.93</v>
+        <v>-28.73</v>
       </c>
       <c r="N134" t="b">
         <v>1</v>
@@ -25236,7 +25262,7 @@
         <v>-34.6</v>
       </c>
       <c r="H135" t="n">
-        <v>-0.76</v>
+        <v>11.03</v>
       </c>
       <c r="I135" t="n">
         <v>23.65</v>
@@ -25251,7 +25277,7 @@
         <v>-3.83</v>
       </c>
       <c r="M135" t="n">
-        <v>-4.14</v>
+        <v>7.35</v>
       </c>
       <c r="N135" t="b">
         <v>1</v>
@@ -25289,7 +25315,7 @@
         <v>-16.2</v>
       </c>
       <c r="H136" t="n">
-        <v>2.72</v>
+        <v>2.91</v>
       </c>
       <c r="I136" t="n">
         <v>25.77</v>
@@ -25304,7 +25330,7 @@
         <v>-1.7</v>
       </c>
       <c r="M136" t="n">
-        <v>-0.66</v>
+        <v>-0.77</v>
       </c>
       <c r="N136" t="b">
         <v>1</v>
@@ -25342,7 +25368,7 @@
         <v>-24.9</v>
       </c>
       <c r="H137" t="n">
-        <v>2.46</v>
+        <v>5.4</v>
       </c>
       <c r="I137" t="n">
         <v>10.88</v>
@@ -25357,7 +25383,7 @@
         <v>-4.1</v>
       </c>
       <c r="M137" t="n">
-        <v>-0.92</v>
+        <v>1.73</v>
       </c>
       <c r="N137" t="b">
         <v>1</v>
@@ -25399,7 +25425,7 @@
         <v>-8.1</v>
       </c>
       <c r="H138" t="n">
-        <v>16.36</v>
+        <v>25.19</v>
       </c>
       <c r="I138" t="n">
         <v>14.27</v>
@@ -25414,7 +25440,7 @@
         <v>-10.92</v>
       </c>
       <c r="M138" t="n">
-        <v>12.98</v>
+        <v>21.52</v>
       </c>
       <c r="N138" t="b">
         <v>1</v>
@@ -25452,7 +25478,7 @@
         <v>-10.2</v>
       </c>
       <c r="H139" t="n">
-        <v>-16.2</v>
+        <v>-13.28</v>
       </c>
       <c r="I139" t="n">
         <v>15.03</v>
@@ -25467,7 +25493,7 @@
         <v>-1.61</v>
       </c>
       <c r="M139" t="n">
-        <v>-19.58</v>
+        <v>-16.96</v>
       </c>
       <c r="N139" t="b">
         <v>1</v>
@@ -25505,7 +25531,7 @@
         <v>68.90000000000001</v>
       </c>
       <c r="H140" t="n">
-        <v>38.86</v>
+        <v>34.95</v>
       </c>
       <c r="I140" t="n">
         <v>1.84</v>
@@ -25520,7 +25546,7 @@
         <v>-10.43</v>
       </c>
       <c r="M140" t="n">
-        <v>35.48</v>
+        <v>31.28</v>
       </c>
       <c r="N140" t="b">
         <v>1</v>
@@ -25558,7 +25584,7 @@
         <v>-40.8</v>
       </c>
       <c r="H141" t="n">
-        <v>-24.63</v>
+        <v>-23.51</v>
       </c>
       <c r="I141" t="n">
         <v>21.71</v>
@@ -25573,7 +25599,7 @@
         <v>-3.3</v>
       </c>
       <c r="M141" t="n">
-        <v>-28.01</v>
+        <v>-27.19</v>
       </c>
       <c r="N141" t="b">
         <v>1</v>
@@ -25611,7 +25637,7 @@
         <v>40.7</v>
       </c>
       <c r="H142" t="n">
-        <v>34.02</v>
+        <v>35.15</v>
       </c>
       <c r="I142" t="n">
         <v>-4.08</v>
@@ -25626,7 +25652,7 @@
         <v>-11.2</v>
       </c>
       <c r="M142" t="n">
-        <v>30.64</v>
+        <v>31.47</v>
       </c>
       <c r="N142" t="b">
         <v>1</v>
@@ -25664,7 +25690,7 @@
         <v>25.7</v>
       </c>
       <c r="H143" t="n">
-        <v>-10.75</v>
+        <v>-13.25</v>
       </c>
       <c r="I143" t="n">
         <v>11.3</v>
@@ -25679,7 +25705,7 @@
         <v>-11.03</v>
       </c>
       <c r="M143" t="n">
-        <v>-14.13</v>
+        <v>-16.92</v>
       </c>
       <c r="N143" t="b">
         <v>1</v>

--- a/STS_holy_grail_v2.xlsx
+++ b/STS_holy_grail_v2.xlsx
@@ -464,7 +464,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.82</v>
+        <v>0.84</v>
       </c>
     </row>
     <row r="5">
@@ -474,7 +474,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-1.72</v>
+        <v>-1.71</v>
       </c>
     </row>
     <row r="6">
@@ -531,13 +531,13 @@
         <v>64</v>
       </c>
       <c r="C10" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="D10" t="n">
         <v>60.94</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.9</v>
+        <v>-0.91</v>
       </c>
     </row>
     <row r="11">
@@ -569,13 +569,13 @@
         <v>156</v>
       </c>
       <c r="C12" t="n">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="D12" t="n">
         <v>48.72</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.36</v>
+        <v>-1.34</v>
       </c>
     </row>
     <row r="13">
@@ -588,13 +588,13 @@
         <v>34</v>
       </c>
       <c r="C13" t="n">
-        <v>8.94</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="D13" t="n">
         <v>73.53</v>
       </c>
       <c r="E13" t="n">
-        <v>7.48</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="15">
@@ -660,13 +660,13 @@
         <v>48</v>
       </c>
       <c r="C18" t="n">
-        <v>0.35</v>
+        <v>0.44</v>
       </c>
       <c r="D18" t="n">
         <v>52.08</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.76</v>
+        <v>-1.68</v>
       </c>
     </row>
     <row r="19">
@@ -679,13 +679,13 @@
         <v>45</v>
       </c>
       <c r="C19" t="n">
-        <v>-0.51</v>
+        <v>-0.5</v>
       </c>
       <c r="D19" t="n">
         <v>44.44</v>
       </c>
       <c r="E19" t="n">
-        <v>-3.1</v>
+        <v>-3.09</v>
       </c>
     </row>
     <row r="20">
@@ -698,7 +698,7 @@
         <v>40</v>
       </c>
       <c r="C20" t="n">
-        <v>-6.51</v>
+        <v>-6.5</v>
       </c>
       <c r="D20" t="n">
         <v>37.5</v>
@@ -880,13 +880,13 @@
         <v>142</v>
       </c>
       <c r="C32" t="n">
-        <v>-1.32</v>
+        <v>-1.28</v>
       </c>
       <c r="D32" t="n">
         <v>46.48</v>
       </c>
       <c r="E32" t="n">
-        <v>-3.87</v>
+        <v>-3.83</v>
       </c>
     </row>
   </sheetData>
@@ -3764,7 +3764,7 @@
         <v>6.3</v>
       </c>
       <c r="H58" t="n">
-        <v>1.14</v>
+        <v>1.42</v>
       </c>
       <c r="I58" t="n">
         <v>7.2</v>
@@ -3777,7 +3777,7 @@
         <v>-0.4</v>
       </c>
       <c r="M58" t="n">
-        <v>-0.93</v>
+        <v>-0.64</v>
       </c>
       <c r="N58" t="b">
         <v>0</v>
@@ -5757,7 +5757,7 @@
         <v>19.4</v>
       </c>
       <c r="H97" t="n">
-        <v>-6.86</v>
+        <v>-5.82</v>
       </c>
       <c r="I97" t="n">
         <v>-10.01</v>
@@ -5770,7 +5770,7 @@
         <v>-15.23</v>
       </c>
       <c r="M97" t="n">
-        <v>-7.01</v>
+        <v>-6.25</v>
       </c>
       <c r="N97" t="b">
         <v>1</v>
@@ -6934,7 +6934,7 @@
         <v>-3.5</v>
       </c>
       <c r="H120" t="n">
-        <v>-6.53</v>
+        <v>-2.18</v>
       </c>
       <c r="I120" t="n">
         <v>-4.95</v>
@@ -6947,7 +6947,7 @@
         <v>-8.43</v>
       </c>
       <c r="M120" t="n">
-        <v>-6.59</v>
+        <v>-2.53</v>
       </c>
       <c r="N120" t="b">
         <v>1</v>
@@ -15189,7 +15189,7 @@
         <v>15.3</v>
       </c>
       <c r="H277" t="n">
-        <v>-43.75</v>
+        <v>-44.57</v>
       </c>
       <c r="I277" t="n">
         <v>-21.4</v>
@@ -15204,7 +15204,7 @@
         <v>-26.97</v>
       </c>
       <c r="M277" t="n">
-        <v>-47.13</v>
+        <v>-48.24</v>
       </c>
       <c r="N277" t="b">
         <v>0</v>
@@ -20267,7 +20267,7 @@
         <v>19.4</v>
       </c>
       <c r="H40" t="n">
-        <v>-6.86</v>
+        <v>-5.82</v>
       </c>
       <c r="I40" t="n">
         <v>-10.01</v>
@@ -20280,7 +20280,7 @@
         <v>-15.23</v>
       </c>
       <c r="M40" t="n">
-        <v>-7.01</v>
+        <v>-6.25</v>
       </c>
       <c r="N40" t="b">
         <v>1</v>
@@ -20730,7 +20730,7 @@
         <v>-3.5</v>
       </c>
       <c r="H49" t="n">
-        <v>-6.53</v>
+        <v>-2.18</v>
       </c>
       <c r="I49" t="n">
         <v>-4.95</v>
@@ -20743,7 +20743,7 @@
         <v>-8.43</v>
       </c>
       <c r="M49" t="n">
-        <v>-6.59</v>
+        <v>-2.53</v>
       </c>
       <c r="N49" t="b">
         <v>1</v>

--- a/STS_holy_grail_v2.xlsx
+++ b/STS_holy_grail_v2.xlsx
@@ -464,7 +464,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.84</v>
+        <v>-1.77</v>
       </c>
     </row>
     <row r="5">
@@ -474,7 +474,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-1.71</v>
+        <v>-3.18</v>
       </c>
     </row>
     <row r="6">
@@ -484,7 +484,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>48.9</v>
+        <v>44.1</v>
       </c>
     </row>
     <row r="8">
@@ -531,13 +531,13 @@
         <v>64</v>
       </c>
       <c r="C10" t="n">
-        <v>1.35</v>
+        <v>-1.21</v>
       </c>
       <c r="D10" t="n">
-        <v>60.94</v>
+        <v>56.25</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.91</v>
+        <v>-2.35</v>
       </c>
     </row>
     <row r="11">
@@ -550,13 +550,13 @@
         <v>79</v>
       </c>
       <c r="C11" t="n">
-        <v>-3.72</v>
+        <v>-7.71</v>
       </c>
       <c r="D11" t="n">
-        <v>29.11</v>
+        <v>25.32</v>
       </c>
       <c r="E11" t="n">
-        <v>-7.04</v>
+        <v>-9.890000000000001</v>
       </c>
     </row>
     <row r="12">
@@ -569,13 +569,13 @@
         <v>156</v>
       </c>
       <c r="C12" t="n">
-        <v>1.16</v>
+        <v>-0.67</v>
       </c>
       <c r="D12" t="n">
-        <v>48.72</v>
+        <v>44.87</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.34</v>
+        <v>-2.03</v>
       </c>
     </row>
     <row r="13">
@@ -588,13 +588,13 @@
         <v>34</v>
       </c>
       <c r="C13" t="n">
-        <v>8.970000000000001</v>
+        <v>5.95</v>
       </c>
       <c r="D13" t="n">
-        <v>73.53</v>
+        <v>61.76</v>
       </c>
       <c r="E13" t="n">
-        <v>7.5</v>
+        <v>5.59</v>
       </c>
     </row>
     <row r="15">
@@ -641,13 +641,13 @@
         <v>111</v>
       </c>
       <c r="C17" t="n">
-        <v>1.5</v>
+        <v>-0.27</v>
       </c>
       <c r="D17" t="n">
-        <v>47.75</v>
+        <v>45.05</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.07</v>
+        <v>-1.71</v>
       </c>
     </row>
     <row r="18">
@@ -660,13 +660,13 @@
         <v>48</v>
       </c>
       <c r="C18" t="n">
-        <v>0.44</v>
+        <v>-1.42</v>
       </c>
       <c r="D18" t="n">
-        <v>52.08</v>
+        <v>45.83</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.68</v>
+        <v>-2.41</v>
       </c>
     </row>
     <row r="19">
@@ -679,13 +679,13 @@
         <v>45</v>
       </c>
       <c r="C19" t="n">
-        <v>-0.5</v>
+        <v>-2.63</v>
       </c>
       <c r="D19" t="n">
-        <v>44.44</v>
+        <v>37.78</v>
       </c>
       <c r="E19" t="n">
-        <v>-3.09</v>
+        <v>-4.09</v>
       </c>
     </row>
     <row r="20">
@@ -698,13 +698,13 @@
         <v>40</v>
       </c>
       <c r="C20" t="n">
-        <v>-6.5</v>
+        <v>-8.6</v>
       </c>
       <c r="D20" t="n">
-        <v>37.5</v>
+        <v>32.5</v>
       </c>
       <c r="E20" t="n">
-        <v>-9.029999999999999</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="21">
@@ -717,13 +717,13 @@
         <v>89</v>
       </c>
       <c r="C21" t="n">
-        <v>4.2</v>
+        <v>-0.33</v>
       </c>
       <c r="D21" t="n">
-        <v>56.18</v>
+        <v>50.56</v>
       </c>
       <c r="E21" t="n">
-        <v>1.49</v>
+        <v>-1.91</v>
       </c>
     </row>
     <row r="23">
@@ -770,13 +770,13 @@
         <v>10</v>
       </c>
       <c r="C25" t="n">
-        <v>14.48</v>
+        <v>10.77</v>
       </c>
       <c r="D25" t="n">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="E25" t="n">
-        <v>11.32</v>
+        <v>8.75</v>
       </c>
     </row>
     <row r="26">
@@ -789,13 +789,13 @@
         <v>5</v>
       </c>
       <c r="C26" t="n">
-        <v>-1.74</v>
+        <v>-4.12</v>
       </c>
       <c r="D26" t="n">
         <v>40</v>
       </c>
       <c r="E26" t="n">
-        <v>-5.61</v>
+        <v>-6.84</v>
       </c>
     </row>
     <row r="27">
@@ -808,13 +808,13 @@
         <v>3</v>
       </c>
       <c r="C27" t="n">
-        <v>16.65</v>
+        <v>16.47</v>
       </c>
       <c r="D27" t="n">
         <v>66.67</v>
       </c>
       <c r="E27" t="n">
-        <v>13.81</v>
+        <v>14.77</v>
       </c>
     </row>
     <row r="29">
@@ -861,13 +861,13 @@
         <v>191</v>
       </c>
       <c r="C31" t="n">
-        <v>2.41</v>
+        <v>-0.42</v>
       </c>
       <c r="D31" t="n">
-        <v>50.79</v>
+        <v>45.03</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.12</v>
+        <v>-1.82</v>
       </c>
     </row>
     <row r="32">
@@ -880,13 +880,13 @@
         <v>142</v>
       </c>
       <c r="C32" t="n">
-        <v>-1.28</v>
+        <v>-3.58</v>
       </c>
       <c r="D32" t="n">
-        <v>46.48</v>
+        <v>42.96</v>
       </c>
       <c r="E32" t="n">
-        <v>-3.83</v>
+        <v>-5</v>
       </c>
     </row>
   </sheetData>
@@ -1010,7 +1010,7 @@
         <v>-9.4</v>
       </c>
       <c r="H2" t="n">
-        <v>2.46</v>
+        <v>4.55</v>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
@@ -1019,7 +1019,7 @@
         <v>-1.66</v>
       </c>
       <c r="M2" t="n">
-        <v>2.86</v>
+        <v>6.06</v>
       </c>
       <c r="N2" t="b">
         <v>0</v>
@@ -1057,16 +1057,16 @@
         <v>51.4</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.95</v>
+        <v>-5.98</v>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="n">
-        <v>-4.91</v>
+        <v>-7.85</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.24</v>
+        <v>-4.17</v>
       </c>
       <c r="N3" t="b">
         <v>1</v>
@@ -1104,16 +1104,16 @@
         <v>-24.3</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.07</v>
+        <v>-4.03</v>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="n">
-        <v>-3.62</v>
+        <v>-4.61</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.68</v>
+        <v>-2.53</v>
       </c>
       <c r="N4" t="b">
         <v>0</v>
@@ -1151,7 +1151,7 @@
         <v>-22.1</v>
       </c>
       <c r="H5" t="n">
-        <v>-4.32</v>
+        <v>-3.49</v>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
@@ -1160,7 +1160,7 @@
         <v>-9.27</v>
       </c>
       <c r="M5" t="n">
-        <v>-3.92</v>
+        <v>-1.99</v>
       </c>
       <c r="N5" t="b">
         <v>0</v>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Extended</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
@@ -1198,7 +1198,7 @@
         <v>-16.6</v>
       </c>
       <c r="H6" t="n">
-        <v>3.33</v>
+        <v>5.26</v>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
@@ -1207,7 +1207,7 @@
         <v>-1.04</v>
       </c>
       <c r="M6" t="n">
-        <v>3.84</v>
+        <v>6.87</v>
       </c>
       <c r="N6" t="b">
         <v>1</v>
@@ -1245,7 +1245,7 @@
         <v>-7.4</v>
       </c>
       <c r="H7" t="n">
-        <v>0.98</v>
+        <v>1.97</v>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
@@ -1254,7 +1254,7 @@
         <v>-2.54</v>
       </c>
       <c r="M7" t="n">
-        <v>1.5</v>
+        <v>3.58</v>
       </c>
       <c r="N7" t="b">
         <v>0</v>
@@ -1292,7 +1292,7 @@
         <v>-5</v>
       </c>
       <c r="H8" t="n">
-        <v>6.54</v>
+        <v>8.85</v>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
@@ -1301,7 +1301,7 @@
         <v>-1.75</v>
       </c>
       <c r="M8" t="n">
-        <v>7.05</v>
+        <v>10.46</v>
       </c>
       <c r="N8" t="b">
         <v>1</v>
@@ -1339,7 +1339,7 @@
         <v>12.5</v>
       </c>
       <c r="H9" t="n">
-        <v>7.42</v>
+        <v>7.63</v>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
@@ -1348,7 +1348,7 @@
         <v>-2.59</v>
       </c>
       <c r="M9" t="n">
-        <v>7.93</v>
+        <v>9.24</v>
       </c>
       <c r="N9" t="b">
         <v>1</v>
@@ -1386,7 +1386,7 @@
         <v>-1.1</v>
       </c>
       <c r="H10" t="n">
-        <v>9.19</v>
+        <v>10.02</v>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
@@ -1395,7 +1395,7 @@
         <v>-0.36</v>
       </c>
       <c r="M10" t="n">
-        <v>9.699999999999999</v>
+        <v>11.64</v>
       </c>
       <c r="N10" t="b">
         <v>0</v>
@@ -1433,7 +1433,7 @@
         <v>-17.3</v>
       </c>
       <c r="H11" t="n">
-        <v>0.87</v>
+        <v>1.31</v>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
@@ -1442,7 +1442,7 @@
         <v>-6.51</v>
       </c>
       <c r="M11" t="n">
-        <v>1.69</v>
+        <v>3.22</v>
       </c>
       <c r="N11" t="b">
         <v>1</v>
@@ -1480,7 +1480,7 @@
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>6.66</v>
+        <v>6.41</v>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
@@ -1489,7 +1489,7 @@
         <v>-1.46</v>
       </c>
       <c r="M12" t="n">
-        <v>7.48</v>
+        <v>8.32</v>
       </c>
       <c r="N12" t="b">
         <v>0</v>
@@ -1527,7 +1527,7 @@
         <v>-29.3</v>
       </c>
       <c r="H13" t="n">
-        <v>9.82</v>
+        <v>9.789999999999999</v>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
@@ -1536,7 +1536,7 @@
         <v>-3.13</v>
       </c>
       <c r="M13" t="n">
-        <v>9.539999999999999</v>
+        <v>10.62</v>
       </c>
       <c r="N13" t="b">
         <v>0</v>
@@ -1574,7 +1574,7 @@
         <v>-21.8</v>
       </c>
       <c r="H14" t="n">
-        <v>0.36</v>
+        <v>-1.28</v>
       </c>
       <c r="I14" t="n">
         <v>-3.37</v>
@@ -1585,7 +1585,7 @@
         <v>-5.33</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.33</v>
+        <v>-0.86</v>
       </c>
       <c r="N14" t="b">
         <v>1</v>
@@ -1623,7 +1623,7 @@
         <v>-15</v>
       </c>
       <c r="H15" t="n">
-        <v>17.08</v>
+        <v>13.96</v>
       </c>
       <c r="I15" t="n">
         <v>12.31</v>
@@ -1634,7 +1634,7 @@
         <v>-4.06</v>
       </c>
       <c r="M15" t="n">
-        <v>16.43</v>
+        <v>14.43</v>
       </c>
       <c r="N15" t="b">
         <v>0</v>
@@ -1672,7 +1672,7 @@
         <v>-16.7</v>
       </c>
       <c r="H16" t="n">
-        <v>29.93</v>
+        <v>29.03</v>
       </c>
       <c r="I16" t="n">
         <v>26.03</v>
@@ -1683,7 +1683,7 @@
         <v>-6.98</v>
       </c>
       <c r="M16" t="n">
-        <v>29.29</v>
+        <v>29.5</v>
       </c>
       <c r="N16" t="b">
         <v>1</v>
@@ -1721,7 +1721,7 @@
         <v>-26.8</v>
       </c>
       <c r="H17" t="n">
-        <v>1.85</v>
+        <v>-0.4</v>
       </c>
       <c r="I17" t="n">
         <v>1.39</v>
@@ -1732,7 +1732,7 @@
         <v>-5.1</v>
       </c>
       <c r="M17" t="n">
-        <v>1.21</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="N17" t="b">
         <v>0</v>
@@ -1770,7 +1770,7 @@
         <v>-35.9</v>
       </c>
       <c r="H18" t="n">
-        <v>-3.1</v>
+        <v>-5.69</v>
       </c>
       <c r="I18" t="n">
         <v>-6.92</v>
@@ -1781,7 +1781,7 @@
         <v>-7.58</v>
       </c>
       <c r="M18" t="n">
-        <v>-3.74</v>
+        <v>-5.22</v>
       </c>
       <c r="N18" t="b">
         <v>0</v>
@@ -1819,7 +1819,7 @@
         <v>-7.1</v>
       </c>
       <c r="H19" t="n">
-        <v>8.279999999999999</v>
+        <v>6.94</v>
       </c>
       <c r="I19" t="n">
         <v>9.390000000000001</v>
@@ -1830,7 +1830,7 @@
         <v>-2.71</v>
       </c>
       <c r="M19" t="n">
-        <v>7.63</v>
+        <v>7.41</v>
       </c>
       <c r="N19" t="b">
         <v>0</v>
@@ -1868,7 +1868,7 @@
         <v>-11.5</v>
       </c>
       <c r="H20" t="n">
-        <v>14.06</v>
+        <v>16.44</v>
       </c>
       <c r="I20" t="n">
         <v>7.47</v>
@@ -1879,7 +1879,7 @@
         <v>-0.99</v>
       </c>
       <c r="M20" t="n">
-        <v>13.41</v>
+        <v>16.91</v>
       </c>
       <c r="N20" t="b">
         <v>1</v>
@@ -1917,7 +1917,7 @@
         <v>0.1</v>
       </c>
       <c r="H21" t="n">
-        <v>14.47</v>
+        <v>15.42</v>
       </c>
       <c r="I21" t="n">
         <v>6.41</v>
@@ -1928,7 +1928,7 @@
         <v>-2.51</v>
       </c>
       <c r="M21" t="n">
-        <v>14.08</v>
+        <v>16.14</v>
       </c>
       <c r="N21" t="b">
         <v>1</v>
@@ -1966,7 +1966,7 @@
         <v>-31.6</v>
       </c>
       <c r="H22" t="n">
-        <v>-3.91</v>
+        <v>-4.32</v>
       </c>
       <c r="I22" t="n">
         <v>-2.12</v>
@@ -1977,7 +1977,7 @@
         <v>-8.140000000000001</v>
       </c>
       <c r="M22" t="n">
-        <v>-4.3</v>
+        <v>-3.6</v>
       </c>
       <c r="N22" t="b">
         <v>1</v>
@@ -2015,7 +2015,7 @@
         <v>7.6</v>
       </c>
       <c r="H23" t="n">
-        <v>9.56</v>
+        <v>6.85</v>
       </c>
       <c r="I23" t="n">
         <v>-3.6</v>
@@ -2026,7 +2026,7 @@
         <v>-9.359999999999999</v>
       </c>
       <c r="M23" t="n">
-        <v>8.550000000000001</v>
+        <v>6.96</v>
       </c>
       <c r="N23" t="b">
         <v>0</v>
@@ -2064,7 +2064,7 @@
         <v>-17.9</v>
       </c>
       <c r="H24" t="n">
-        <v>-11.13</v>
+        <v>-12.17</v>
       </c>
       <c r="I24" t="n">
         <v>-6.13</v>
@@ -2075,7 +2075,7 @@
         <v>-14.51</v>
       </c>
       <c r="M24" t="n">
-        <v>-10.84</v>
+        <v>-10.78</v>
       </c>
       <c r="N24" t="b">
         <v>0</v>
@@ -2113,7 +2113,7 @@
         <v>-2.7</v>
       </c>
       <c r="H25" t="n">
-        <v>-8.66</v>
+        <v>-9.380000000000001</v>
       </c>
       <c r="I25" t="n">
         <v>-3.77</v>
@@ -2124,7 +2124,7 @@
         <v>-12.44</v>
       </c>
       <c r="M25" t="n">
-        <v>-8.369999999999999</v>
+        <v>-7.98</v>
       </c>
       <c r="N25" t="b">
         <v>1</v>
@@ -2162,7 +2162,7 @@
         <v>-25.3</v>
       </c>
       <c r="H26" t="n">
-        <v>5.88</v>
+        <v>6.88</v>
       </c>
       <c r="I26" t="n">
         <v>4.1</v>
@@ -2173,7 +2173,7 @@
         <v>-0.92</v>
       </c>
       <c r="M26" t="n">
-        <v>6.17</v>
+        <v>8.27</v>
       </c>
       <c r="N26" t="b">
         <v>0</v>
@@ -2211,7 +2211,7 @@
         <v>25.6</v>
       </c>
       <c r="H27" t="n">
-        <v>8.68</v>
+        <v>6.6</v>
       </c>
       <c r="I27" t="n">
         <v>-0.42</v>
@@ -2222,7 +2222,7 @@
         <v>-8.35</v>
       </c>
       <c r="M27" t="n">
-        <v>8.970000000000001</v>
+        <v>7.99</v>
       </c>
       <c r="N27" t="b">
         <v>0</v>
@@ -2260,7 +2260,7 @@
         <v>26.9</v>
       </c>
       <c r="H28" t="n">
-        <v>1.91</v>
+        <v>-2.93</v>
       </c>
       <c r="I28" t="n">
         <v>-3.24</v>
@@ -2271,7 +2271,7 @@
         <v>-12.88</v>
       </c>
       <c r="M28" t="n">
-        <v>2.2</v>
+        <v>-1.54</v>
       </c>
       <c r="N28" t="b">
         <v>1</v>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Retired</t>
         </is>
       </c>
       <c r="E29" t="inlineStr"/>
@@ -2309,7 +2309,7 @@
         <v>-14.5</v>
       </c>
       <c r="H29" t="n">
-        <v>-3.47</v>
+        <v>-5.22</v>
       </c>
       <c r="I29" t="n">
         <v>-3.75</v>
@@ -2320,7 +2320,7 @@
         <v>-9.01</v>
       </c>
       <c r="M29" t="n">
-        <v>-4.19</v>
+        <v>-4.83</v>
       </c>
       <c r="N29" t="b">
         <v>0</v>
@@ -2347,7 +2347,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Retired</t>
         </is>
       </c>
       <c r="E30" t="inlineStr"/>
@@ -2358,7 +2358,7 @@
         <v>17.2</v>
       </c>
       <c r="H30" t="n">
-        <v>4.63</v>
+        <v>4.29</v>
       </c>
       <c r="I30" t="n">
         <v>-1.49</v>
@@ -2369,7 +2369,7 @@
         <v>-10.54</v>
       </c>
       <c r="M30" t="n">
-        <v>3.91</v>
+        <v>4.68</v>
       </c>
       <c r="N30" t="b">
         <v>0</v>
@@ -2396,7 +2396,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Extended</t>
+          <t>Retired</t>
         </is>
       </c>
       <c r="E31" t="inlineStr"/>
@@ -2407,7 +2407,7 @@
         <v>-13.2</v>
       </c>
       <c r="H31" t="n">
-        <v>13.53</v>
+        <v>11.82</v>
       </c>
       <c r="I31" t="n">
         <v>23.71</v>
@@ -2418,7 +2418,7 @@
         <v>-0.82</v>
       </c>
       <c r="M31" t="n">
-        <v>12.8</v>
+        <v>12.21</v>
       </c>
       <c r="N31" t="b">
         <v>0</v>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Retired</t>
         </is>
       </c>
       <c r="E32" t="inlineStr"/>
@@ -2456,7 +2456,7 @@
         <v>-7.7</v>
       </c>
       <c r="H32" t="n">
-        <v>-3.89</v>
+        <v>-4.03</v>
       </c>
       <c r="I32" t="n">
         <v>-9.67</v>
@@ -2467,7 +2467,7 @@
         <v>-12.32</v>
       </c>
       <c r="M32" t="n">
-        <v>-4.61</v>
+        <v>-3.64</v>
       </c>
       <c r="N32" t="b">
         <v>0</v>
@@ -2494,7 +2494,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Retired</t>
         </is>
       </c>
       <c r="E33" t="inlineStr"/>
@@ -2505,7 +2505,7 @@
         <v>-18.1</v>
       </c>
       <c r="H33" t="n">
-        <v>3.23</v>
+        <v>1.42</v>
       </c>
       <c r="I33" t="n">
         <v>-2.43</v>
@@ -2516,7 +2516,7 @@
         <v>-6.41</v>
       </c>
       <c r="M33" t="n">
-        <v>2.51</v>
+        <v>1.81</v>
       </c>
       <c r="N33" t="b">
         <v>0</v>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Extended</t>
+          <t>Retired</t>
         </is>
       </c>
       <c r="E34" t="inlineStr"/>
@@ -2554,7 +2554,7 @@
         <v>-18.1</v>
       </c>
       <c r="H34" t="n">
-        <v>13.98</v>
+        <v>16.62</v>
       </c>
       <c r="I34" t="n">
         <v>4.46</v>
@@ -2565,7 +2565,7 @@
         <v>-2.69</v>
       </c>
       <c r="M34" t="n">
-        <v>13.26</v>
+        <v>17.01</v>
       </c>
       <c r="N34" t="b">
         <v>1</v>
@@ -2592,7 +2592,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Retired</t>
         </is>
       </c>
       <c r="E35" t="inlineStr"/>
@@ -2603,7 +2603,7 @@
         <v>7.7</v>
       </c>
       <c r="H35" t="n">
-        <v>4.5</v>
+        <v>3.46</v>
       </c>
       <c r="I35" t="n">
         <v>-6.85</v>
@@ -2614,7 +2614,7 @@
         <v>-9.359999999999999</v>
       </c>
       <c r="M35" t="n">
-        <v>3.78</v>
+        <v>3.85</v>
       </c>
       <c r="N35" t="b">
         <v>0</v>
@@ -2641,7 +2641,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Retired</t>
         </is>
       </c>
       <c r="E36" t="inlineStr"/>
@@ -2652,7 +2652,7 @@
         <v>-21.5</v>
       </c>
       <c r="H36" t="n">
-        <v>2.32</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I36" t="n">
         <v>-1.68</v>
@@ -2663,7 +2663,7 @@
         <v>-8.130000000000001</v>
       </c>
       <c r="M36" t="n">
-        <v>1.6</v>
+        <v>0.46</v>
       </c>
       <c r="N36" t="b">
         <v>1</v>
@@ -2701,18 +2701,20 @@
         <v>41.6</v>
       </c>
       <c r="H37" t="n">
-        <v>5.6</v>
+        <v>4.19</v>
       </c>
       <c r="I37" t="n">
         <v>3.43</v>
       </c>
-      <c r="J37" t="inlineStr"/>
+      <c r="J37" t="n">
+        <v>4.19</v>
+      </c>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="n">
         <v>-4.38</v>
       </c>
       <c r="M37" t="n">
-        <v>4.23</v>
+        <v>3.94</v>
       </c>
       <c r="N37" t="b">
         <v>1</v>
@@ -2750,18 +2752,20 @@
         <v>32.1</v>
       </c>
       <c r="H38" t="n">
-        <v>7.32</v>
+        <v>5.05</v>
       </c>
       <c r="I38" t="n">
         <v>-3.47</v>
       </c>
-      <c r="J38" t="inlineStr"/>
+      <c r="J38" t="n">
+        <v>5.05</v>
+      </c>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="n">
         <v>-6.94</v>
       </c>
       <c r="M38" t="n">
-        <v>5.94</v>
+        <v>4.8</v>
       </c>
       <c r="N38" t="b">
         <v>1</v>
@@ -2799,18 +2803,20 @@
         <v>-14.4</v>
       </c>
       <c r="H39" t="n">
-        <v>1.16</v>
+        <v>1.37</v>
       </c>
       <c r="I39" t="n">
         <v>-2.38</v>
       </c>
-      <c r="J39" t="inlineStr"/>
+      <c r="J39" t="n">
+        <v>1.37</v>
+      </c>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="n">
         <v>-6.46</v>
       </c>
       <c r="M39" t="n">
-        <v>-0.21</v>
+        <v>1.11</v>
       </c>
       <c r="N39" t="b">
         <v>1</v>
@@ -2848,18 +2854,20 @@
         <v>-16.8</v>
       </c>
       <c r="H40" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.85</v>
       </c>
       <c r="I40" t="n">
         <v>1.99</v>
       </c>
-      <c r="J40" t="inlineStr"/>
+      <c r="J40" t="n">
+        <v>-0.85</v>
+      </c>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="n">
         <v>-7.67</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.45</v>
+        <v>-1.11</v>
       </c>
       <c r="N40" t="b">
         <v>0</v>
@@ -2897,18 +2905,20 @@
         <v>-10</v>
       </c>
       <c r="H41" t="n">
-        <v>-8.07</v>
+        <v>-10.78</v>
       </c>
       <c r="I41" t="n">
         <v>-3.29</v>
       </c>
-      <c r="J41" t="inlineStr"/>
+      <c r="J41" t="n">
+        <v>-10.78</v>
+      </c>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="n">
         <v>-14.66</v>
       </c>
       <c r="M41" t="n">
-        <v>-9.44</v>
+        <v>-11.04</v>
       </c>
       <c r="N41" t="b">
         <v>1</v>
@@ -2946,18 +2956,20 @@
         <v>6.4</v>
       </c>
       <c r="H42" t="n">
-        <v>10.98</v>
+        <v>12.18</v>
       </c>
       <c r="I42" t="n">
         <v>1.48</v>
       </c>
-      <c r="J42" t="inlineStr"/>
+      <c r="J42" t="n">
+        <v>12.18</v>
+      </c>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="n">
         <v>-3.35</v>
       </c>
       <c r="M42" t="n">
-        <v>9.609999999999999</v>
+        <v>11.92</v>
       </c>
       <c r="N42" t="b">
         <v>1</v>
@@ -2995,7 +3007,7 @@
         <v>-11</v>
       </c>
       <c r="H43" t="n">
-        <v>47.26</v>
+        <v>47.13</v>
       </c>
       <c r="I43" t="n">
         <v>11.67</v>
@@ -3008,7 +3020,7 @@
         <v>-0.97</v>
       </c>
       <c r="M43" t="n">
-        <v>45.88</v>
+        <v>46.87</v>
       </c>
       <c r="N43" t="b">
         <v>0</v>
@@ -3046,7 +3058,7 @@
         <v>-23.9</v>
       </c>
       <c r="H44" t="n">
-        <v>-2.11</v>
+        <v>-1.91</v>
       </c>
       <c r="I44" t="n">
         <v>-4.98</v>
@@ -3059,7 +3071,7 @@
         <v>-7.87</v>
       </c>
       <c r="M44" t="n">
-        <v>-3.49</v>
+        <v>-2.17</v>
       </c>
       <c r="N44" t="b">
         <v>0</v>
@@ -3101,7 +3113,7 @@
         <v>-9.800000000000001</v>
       </c>
       <c r="H45" t="n">
-        <v>12.07</v>
+        <v>9.66</v>
       </c>
       <c r="I45" t="n">
         <v>-3.41</v>
@@ -3114,7 +3126,7 @@
         <v>-8.949999999999999</v>
       </c>
       <c r="M45" t="n">
-        <v>10.68</v>
+        <v>9.4</v>
       </c>
       <c r="N45" t="b">
         <v>0</v>
@@ -3152,7 +3164,7 @@
         <v>-36.1</v>
       </c>
       <c r="H46" t="n">
-        <v>1.92</v>
+        <v>-0.12</v>
       </c>
       <c r="I46" t="n">
         <v>-1.4</v>
@@ -3165,7 +3177,7 @@
         <v>-7.04</v>
       </c>
       <c r="M46" t="n">
-        <v>0.54</v>
+        <v>-0.38</v>
       </c>
       <c r="N46" t="b">
         <v>0</v>
@@ -3203,7 +3215,7 @@
         <v>-7.9</v>
       </c>
       <c r="H47" t="n">
-        <v>-7.19</v>
+        <v>-7.05</v>
       </c>
       <c r="I47" t="n">
         <v>-8.83</v>
@@ -3216,7 +3228,7 @@
         <v>-12.99</v>
       </c>
       <c r="M47" t="n">
-        <v>-8.57</v>
+        <v>-7.31</v>
       </c>
       <c r="N47" t="b">
         <v>0</v>
@@ -3254,7 +3266,7 @@
         <v>2.6</v>
       </c>
       <c r="H48" t="n">
-        <v>5.57</v>
+        <v>5.99</v>
       </c>
       <c r="I48" t="n">
         <v>-7.8</v>
@@ -3267,7 +3279,7 @@
         <v>-12.2</v>
       </c>
       <c r="M48" t="n">
-        <v>3.7</v>
+        <v>5.24</v>
       </c>
       <c r="N48" t="b">
         <v>0</v>
@@ -3305,7 +3317,7 @@
         <v>6.3</v>
       </c>
       <c r="H49" t="n">
-        <v>5.34</v>
+        <v>3.54</v>
       </c>
       <c r="I49" t="n">
         <v>0.64</v>
@@ -3318,7 +3330,7 @@
         <v>-2.13</v>
       </c>
       <c r="M49" t="n">
-        <v>3.47</v>
+        <v>2.8</v>
       </c>
       <c r="N49" t="b">
         <v>0</v>
@@ -3356,7 +3368,7 @@
         <v>20.2</v>
       </c>
       <c r="H50" t="n">
-        <v>1.53</v>
+        <v>0.17</v>
       </c>
       <c r="I50" t="n">
         <v>3.45</v>
@@ -3369,7 +3381,7 @@
         <v>-1.07</v>
       </c>
       <c r="M50" t="n">
-        <v>-0.26</v>
+        <v>-0.49</v>
       </c>
       <c r="N50" t="b">
         <v>1</v>
@@ -3407,7 +3419,7 @@
         <v>43.7</v>
       </c>
       <c r="H51" t="n">
-        <v>12.36</v>
+        <v>12.67</v>
       </c>
       <c r="I51" t="n">
         <v>3.16</v>
@@ -3420,7 +3432,7 @@
         <v>-2.44</v>
       </c>
       <c r="M51" t="n">
-        <v>10.58</v>
+        <v>12.01</v>
       </c>
       <c r="N51" t="b">
         <v>1</v>
@@ -3458,7 +3470,7 @@
         <v>1.9</v>
       </c>
       <c r="H52" t="n">
-        <v>-4.5</v>
+        <v>-4.81</v>
       </c>
       <c r="I52" t="n">
         <v>-10.64</v>
@@ -3471,7 +3483,7 @@
         <v>-14.75</v>
       </c>
       <c r="M52" t="n">
-        <v>-6.29</v>
+        <v>-5.47</v>
       </c>
       <c r="N52" t="b">
         <v>1</v>
@@ -3509,7 +3521,7 @@
         <v>37.5</v>
       </c>
       <c r="H53" t="n">
-        <v>10.05</v>
+        <v>7.86</v>
       </c>
       <c r="I53" t="n">
         <v>5.86</v>
@@ -3522,7 +3534,7 @@
         <v>-3.95</v>
       </c>
       <c r="M53" t="n">
-        <v>8.109999999999999</v>
+        <v>7.05</v>
       </c>
       <c r="N53" t="b">
         <v>1</v>
@@ -3560,7 +3572,7 @@
         <v>15</v>
       </c>
       <c r="H54" t="n">
-        <v>-29.5</v>
+        <v>-32.63</v>
       </c>
       <c r="I54" t="n">
         <v>-21.11</v>
@@ -3573,7 +3585,7 @@
         <v>-28.65</v>
       </c>
       <c r="M54" t="n">
-        <v>-31.44</v>
+        <v>-33.44</v>
       </c>
       <c r="N54" t="b">
         <v>0</v>
@@ -3611,7 +3623,7 @@
         <v>40.2</v>
       </c>
       <c r="H55" t="n">
-        <v>13.38</v>
+        <v>10.56</v>
       </c>
       <c r="I55" t="n">
         <v>-1.11</v>
@@ -3624,7 +3636,7 @@
         <v>-5.29</v>
       </c>
       <c r="M55" t="n">
-        <v>11.44</v>
+        <v>9.75</v>
       </c>
       <c r="N55" t="b">
         <v>1</v>
@@ -3662,7 +3674,7 @@
         <v>10.7</v>
       </c>
       <c r="H56" t="n">
-        <v>0.47</v>
+        <v>1.42</v>
       </c>
       <c r="I56" t="n">
         <v>7.3</v>
@@ -3675,7 +3687,7 @@
         <v>-3.78</v>
       </c>
       <c r="M56" t="n">
-        <v>-1.47</v>
+        <v>0.61</v>
       </c>
       <c r="N56" t="b">
         <v>1</v>
@@ -3713,7 +3725,7 @@
         <v>25.6</v>
       </c>
       <c r="H57" t="n">
-        <v>17.37</v>
+        <v>13.03</v>
       </c>
       <c r="I57" t="n">
         <v>7.71</v>
@@ -3726,7 +3738,7 @@
         <v>-4.85</v>
       </c>
       <c r="M57" t="n">
-        <v>16.2</v>
+        <v>12.97</v>
       </c>
       <c r="N57" t="b">
         <v>1</v>
@@ -3764,7 +3776,7 @@
         <v>6.3</v>
       </c>
       <c r="H58" t="n">
-        <v>1.42</v>
+        <v>-2.1</v>
       </c>
       <c r="I58" t="n">
         <v>7.2</v>
@@ -3777,7 +3789,7 @@
         <v>-0.4</v>
       </c>
       <c r="M58" t="n">
-        <v>-0.64</v>
+        <v>-3.03</v>
       </c>
       <c r="N58" t="b">
         <v>0</v>
@@ -3815,7 +3827,7 @@
         <v>2.3</v>
       </c>
       <c r="H59" t="n">
-        <v>-13.47</v>
+        <v>-14.8</v>
       </c>
       <c r="I59" t="n">
         <v>-8.85</v>
@@ -3828,7 +3840,7 @@
         <v>-14.2</v>
       </c>
       <c r="M59" t="n">
-        <v>-15.54</v>
+        <v>-15.74</v>
       </c>
       <c r="N59" t="b">
         <v>0</v>
@@ -3866,7 +3878,7 @@
         <v>-4.3</v>
       </c>
       <c r="H60" t="n">
-        <v>1.66</v>
+        <v>1.1</v>
       </c>
       <c r="I60" t="n">
         <v>3.39</v>
@@ -3879,7 +3891,7 @@
         <v>-5.89</v>
       </c>
       <c r="M60" t="n">
-        <v>0.4</v>
+        <v>0.96</v>
       </c>
       <c r="N60" t="b">
         <v>0</v>
@@ -3917,7 +3929,7 @@
         <v>-29.4</v>
       </c>
       <c r="H61" t="n">
-        <v>-9.390000000000001</v>
+        <v>-11.65</v>
       </c>
       <c r="I61" t="n">
         <v>-5.75</v>
@@ -3930,7 +3942,7 @@
         <v>-10.11</v>
       </c>
       <c r="M61" t="n">
-        <v>-10.65</v>
+        <v>-11.79</v>
       </c>
       <c r="N61" t="b">
         <v>0</v>
@@ -3968,7 +3980,7 @@
         <v>-6.9</v>
       </c>
       <c r="H62" t="n">
-        <v>20.56</v>
+        <v>19.55</v>
       </c>
       <c r="I62" t="n">
         <v>6.44</v>
@@ -3981,7 +3993,7 @@
         <v>-4.53</v>
       </c>
       <c r="M62" t="n">
-        <v>19.3</v>
+        <v>19.41</v>
       </c>
       <c r="N62" t="b">
         <v>1</v>
@@ -4019,7 +4031,7 @@
         <v>4.2</v>
       </c>
       <c r="H63" t="n">
-        <v>-18.36</v>
+        <v>-20.29</v>
       </c>
       <c r="I63" t="n">
         <v>-10.83</v>
@@ -4032,7 +4044,7 @@
         <v>-18.5</v>
       </c>
       <c r="M63" t="n">
-        <v>-19.62</v>
+        <v>-20.43</v>
       </c>
       <c r="N63" t="b">
         <v>0</v>
@@ -4070,7 +4082,7 @@
         <v>-32.4</v>
       </c>
       <c r="H64" t="n">
-        <v>2.6</v>
+        <v>5.16</v>
       </c>
       <c r="I64" t="n">
         <v>-2.43</v>
@@ -4083,7 +4095,7 @@
         <v>-12.47</v>
       </c>
       <c r="M64" t="n">
-        <v>2</v>
+        <v>5.67</v>
       </c>
       <c r="N64" t="b">
         <v>0</v>
@@ -4121,7 +4133,7 @@
         <v>-11</v>
       </c>
       <c r="H65" t="n">
-        <v>4.52</v>
+        <v>4.12</v>
       </c>
       <c r="I65" t="n">
         <v>-8.449999999999999</v>
@@ -4134,7 +4146,7 @@
         <v>-18.92</v>
       </c>
       <c r="M65" t="n">
-        <v>3.92</v>
+        <v>4.63</v>
       </c>
       <c r="N65" t="b">
         <v>0</v>
@@ -4172,7 +4184,7 @@
         <v>9.699999999999999</v>
       </c>
       <c r="H66" t="n">
-        <v>-3.24</v>
+        <v>-10.87</v>
       </c>
       <c r="I66" t="n">
         <v>1.27</v>
@@ -4185,7 +4197,7 @@
         <v>-20.79</v>
       </c>
       <c r="M66" t="n">
-        <v>-4</v>
+        <v>-10.52</v>
       </c>
       <c r="N66" t="b">
         <v>0</v>
@@ -4223,7 +4235,7 @@
         <v>-28.1</v>
       </c>
       <c r="H67" t="n">
-        <v>-9.140000000000001</v>
+        <v>-8.619999999999999</v>
       </c>
       <c r="I67" t="n">
         <v>-10.79</v>
@@ -4236,7 +4248,7 @@
         <v>-13.67</v>
       </c>
       <c r="M67" t="n">
-        <v>-9.9</v>
+        <v>-8.27</v>
       </c>
       <c r="N67" t="b">
         <v>0</v>
@@ -4274,7 +4286,7 @@
         <v>-17.7</v>
       </c>
       <c r="H68" t="n">
-        <v>2.91</v>
+        <v>4.15</v>
       </c>
       <c r="I68" t="n">
         <v>-0.89</v>
@@ -4287,7 +4299,7 @@
         <v>-11.37</v>
       </c>
       <c r="M68" t="n">
-        <v>2.16</v>
+        <v>4.51</v>
       </c>
       <c r="N68" t="b">
         <v>0</v>
@@ -4325,7 +4337,7 @@
         <v>-9.300000000000001</v>
       </c>
       <c r="H69" t="n">
-        <v>-12.97</v>
+        <v>-16.24</v>
       </c>
       <c r="I69" t="n">
         <v>-3.34</v>
@@ -4338,7 +4350,7 @@
         <v>-8.77</v>
       </c>
       <c r="M69" t="n">
-        <v>-13.73</v>
+        <v>-15.88</v>
       </c>
       <c r="N69" t="b">
         <v>0</v>
@@ -4376,7 +4388,7 @@
         <v>0.3</v>
       </c>
       <c r="H70" t="n">
-        <v>-16.14</v>
+        <v>-16.32</v>
       </c>
       <c r="I70" t="n">
         <v>-10.53</v>
@@ -4389,7 +4401,7 @@
         <v>-17.73</v>
       </c>
       <c r="M70" t="n">
-        <v>-16.89</v>
+        <v>-15.97</v>
       </c>
       <c r="N70" t="b">
         <v>1</v>
@@ -4427,7 +4439,7 @@
         <v>12.3</v>
       </c>
       <c r="H71" t="n">
-        <v>8.039999999999999</v>
+        <v>6.63</v>
       </c>
       <c r="I71" t="n">
         <v>6.51</v>
@@ -4440,7 +4452,7 @@
         <v>-6.01</v>
       </c>
       <c r="M71" t="n">
-        <v>6.57</v>
+        <v>6.28</v>
       </c>
       <c r="N71" t="b">
         <v>0</v>
@@ -4478,7 +4490,7 @@
         <v>2.8</v>
       </c>
       <c r="H72" t="n">
-        <v>0.9</v>
+        <v>-0.88</v>
       </c>
       <c r="I72" t="n">
         <v>3.18</v>
@@ -4491,7 +4503,7 @@
         <v>-0.88</v>
       </c>
       <c r="M72" t="n">
-        <v>-0.57</v>
+        <v>-1.23</v>
       </c>
       <c r="N72" t="b">
         <v>1</v>
@@ -4529,7 +4541,7 @@
         <v>-1.4</v>
       </c>
       <c r="H73" t="n">
-        <v>2.13</v>
+        <v>-1</v>
       </c>
       <c r="I73" t="n">
         <v>-4.52</v>
@@ -4542,7 +4554,7 @@
         <v>-7.44</v>
       </c>
       <c r="M73" t="n">
-        <v>0.66</v>
+        <v>-1.36</v>
       </c>
       <c r="N73" t="b">
         <v>0</v>
@@ -4580,7 +4592,7 @@
         <v>34.5</v>
       </c>
       <c r="H74" t="n">
-        <v>9.26</v>
+        <v>6.8</v>
       </c>
       <c r="I74" t="n">
         <v>0.66</v>
@@ -4593,7 +4605,7 @@
         <v>-2.64</v>
       </c>
       <c r="M74" t="n">
-        <v>7.78</v>
+        <v>6.44</v>
       </c>
       <c r="N74" t="b">
         <v>1</v>
@@ -4631,7 +4643,7 @@
         <v>-22.7</v>
       </c>
       <c r="H75" t="n">
-        <v>-13.02</v>
+        <v>-15.57</v>
       </c>
       <c r="I75" t="n">
         <v>-6.71</v>
@@ -4644,7 +4656,7 @@
         <v>-9.58</v>
       </c>
       <c r="M75" t="n">
-        <v>-14.56</v>
+        <v>-15.98</v>
       </c>
       <c r="N75" t="b">
         <v>0</v>
@@ -4682,7 +4694,7 @@
         <v>24.3</v>
       </c>
       <c r="H76" t="n">
-        <v>41.06</v>
+        <v>31.13</v>
       </c>
       <c r="I76" t="n">
         <v>2.54</v>
@@ -4695,7 +4707,7 @@
         <v>-5.21</v>
       </c>
       <c r="M76" t="n">
-        <v>40.23</v>
+        <v>31.42</v>
       </c>
       <c r="N76" t="b">
         <v>1</v>
@@ -4733,7 +4745,7 @@
         <v>56.6</v>
       </c>
       <c r="H77" t="n">
-        <v>-0.78</v>
+        <v>-6.39</v>
       </c>
       <c r="I77" t="n">
         <v>-13.1</v>
@@ -4746,7 +4758,7 @@
         <v>-16.17</v>
       </c>
       <c r="M77" t="n">
-        <v>-1.61</v>
+        <v>-6.1</v>
       </c>
       <c r="N77" t="b">
         <v>0</v>
@@ -4784,7 +4796,7 @@
         <v>2.9</v>
       </c>
       <c r="H78" t="n">
-        <v>-19.79</v>
+        <v>-21.09</v>
       </c>
       <c r="I78" t="n">
         <v>-8.470000000000001</v>
@@ -4797,7 +4809,7 @@
         <v>-15.65</v>
       </c>
       <c r="M78" t="n">
-        <v>-20.62</v>
+        <v>-20.8</v>
       </c>
       <c r="N78" t="b">
         <v>0</v>
@@ -4835,7 +4847,7 @@
         <v>-16.9</v>
       </c>
       <c r="H79" t="n">
-        <v>-5.24</v>
+        <v>-5.8</v>
       </c>
       <c r="I79" t="n">
         <v>-6.47</v>
@@ -4848,7 +4860,7 @@
         <v>-11.5</v>
       </c>
       <c r="M79" t="n">
-        <v>-6.07</v>
+        <v>-5.51</v>
       </c>
       <c r="N79" t="b">
         <v>1</v>
@@ -4886,7 +4898,7 @@
         <v>32.8</v>
       </c>
       <c r="H80" t="n">
-        <v>4.25</v>
+        <v>1.41</v>
       </c>
       <c r="I80" t="n">
         <v>14.96</v>
@@ -4899,7 +4911,7 @@
         <v>-0.9</v>
       </c>
       <c r="M80" t="n">
-        <v>4</v>
+        <v>2.27</v>
       </c>
       <c r="N80" t="b">
         <v>0</v>
@@ -4937,7 +4949,7 @@
         <v>0.8</v>
       </c>
       <c r="H81" t="n">
-        <v>-7.67</v>
+        <v>-11.84</v>
       </c>
       <c r="I81" t="n">
         <v>-7.73</v>
@@ -4950,7 +4962,7 @@
         <v>-10.12</v>
       </c>
       <c r="M81" t="n">
-        <v>-7.92</v>
+        <v>-10.99</v>
       </c>
       <c r="N81" t="b">
         <v>0</v>
@@ -4988,7 +5000,7 @@
         <v>-9.6</v>
       </c>
       <c r="H82" t="n">
-        <v>-14.7</v>
+        <v>-17.64</v>
       </c>
       <c r="I82" t="n">
         <v>-1.23</v>
@@ -5001,7 +5013,7 @@
         <v>-18.52</v>
       </c>
       <c r="M82" t="n">
-        <v>-14.95</v>
+        <v>-16.78</v>
       </c>
       <c r="N82" t="b">
         <v>0</v>
@@ -5039,7 +5051,7 @@
         <v>20.3</v>
       </c>
       <c r="H83" t="n">
-        <v>-19.23</v>
+        <v>-19.27</v>
       </c>
       <c r="I83" t="n">
         <v>-2.07</v>
@@ -5052,7 +5064,7 @@
         <v>-17.35</v>
       </c>
       <c r="M83" t="n">
-        <v>-19.9</v>
+        <v>-18.84</v>
       </c>
       <c r="N83" t="b">
         <v>1</v>
@@ -5090,7 +5102,7 @@
         <v>0.3</v>
       </c>
       <c r="H84" t="n">
-        <v>-20.92</v>
+        <v>-22.49</v>
       </c>
       <c r="I84" t="n">
         <v>-9.9</v>
@@ -5103,7 +5115,7 @@
         <v>-21.72</v>
       </c>
       <c r="M84" t="n">
-        <v>-22.09</v>
+        <v>-22.54</v>
       </c>
       <c r="N84" t="b">
         <v>1</v>
@@ -5141,7 +5153,7 @@
         <v>49.4</v>
       </c>
       <c r="H85" t="n">
-        <v>4.01</v>
+        <v>-4.75</v>
       </c>
       <c r="I85" t="n">
         <v>2.9</v>
@@ -5154,7 +5166,7 @@
         <v>-5.67</v>
       </c>
       <c r="M85" t="n">
-        <v>3.03</v>
+        <v>-4.62</v>
       </c>
       <c r="N85" t="b">
         <v>1</v>
@@ -5192,7 +5204,7 @@
         <v>4.5</v>
       </c>
       <c r="H86" t="n">
-        <v>-4.31</v>
+        <v>-3.76</v>
       </c>
       <c r="I86" t="n">
         <v>-7.61</v>
@@ -5205,7 +5217,7 @@
         <v>-11.06</v>
       </c>
       <c r="M86" t="n">
-        <v>-5.29</v>
+        <v>-3.63</v>
       </c>
       <c r="N86" t="b">
         <v>1</v>
@@ -5243,7 +5255,7 @@
         <v>4.2</v>
       </c>
       <c r="H87" t="n">
-        <v>-18.02</v>
+        <v>-18.83</v>
       </c>
       <c r="I87" t="n">
         <v>-6.86</v>
@@ -5256,7 +5268,7 @@
         <v>-20.23</v>
       </c>
       <c r="M87" t="n">
-        <v>-19</v>
+        <v>-18.7</v>
       </c>
       <c r="N87" t="b">
         <v>0</v>
@@ -5294,7 +5306,7 @@
         <v>15.4</v>
       </c>
       <c r="H88" t="n">
-        <v>2.86</v>
+        <v>1.53</v>
       </c>
       <c r="I88" t="n">
         <v>-1.19</v>
@@ -5307,7 +5319,7 @@
         <v>-7.43</v>
       </c>
       <c r="M88" t="n">
-        <v>1.87</v>
+        <v>1.67</v>
       </c>
       <c r="N88" t="b">
         <v>0</v>
@@ -5345,7 +5357,7 @@
         <v>15.5</v>
       </c>
       <c r="H89" t="n">
-        <v>-3.08</v>
+        <v>-3.94</v>
       </c>
       <c r="I89" t="n">
         <v>-7.36</v>
@@ -5358,7 +5370,7 @@
         <v>-12.98</v>
       </c>
       <c r="M89" t="n">
-        <v>-4.24</v>
+        <v>-3.99</v>
       </c>
       <c r="N89" t="b">
         <v>0</v>
@@ -5400,7 +5412,7 @@
         <v>-8.5</v>
       </c>
       <c r="H90" t="n">
-        <v>22.79</v>
+        <v>25.39</v>
       </c>
       <c r="I90" t="n">
         <v>-3.04</v>
@@ -5413,7 +5425,7 @@
         <v>-4.96</v>
       </c>
       <c r="M90" t="n">
-        <v>21.63</v>
+        <v>25.34</v>
       </c>
       <c r="N90" t="b">
         <v>0</v>
@@ -5451,7 +5463,7 @@
         <v>1.8</v>
       </c>
       <c r="H91" t="n">
-        <v>-8.48</v>
+        <v>-10.84</v>
       </c>
       <c r="I91" t="n">
         <v>-6.45</v>
@@ -5464,7 +5476,7 @@
         <v>-13.57</v>
       </c>
       <c r="M91" t="n">
-        <v>-9.65</v>
+        <v>-10.88</v>
       </c>
       <c r="N91" t="b">
         <v>0</v>
@@ -5502,7 +5514,7 @@
         <v>33.9</v>
       </c>
       <c r="H92" t="n">
-        <v>10.97</v>
+        <v>2.47</v>
       </c>
       <c r="I92" t="n">
         <v>-7.74</v>
@@ -5515,7 +5527,7 @@
         <v>-9.449999999999999</v>
       </c>
       <c r="M92" t="n">
-        <v>9.800000000000001</v>
+        <v>2.42</v>
       </c>
       <c r="N92" t="b">
         <v>0</v>
@@ -5553,7 +5565,7 @@
         <v>-25</v>
       </c>
       <c r="H93" t="n">
-        <v>-8.539999999999999</v>
+        <v>-8.779999999999999</v>
       </c>
       <c r="I93" t="n">
         <v>2.51</v>
@@ -5566,7 +5578,7 @@
         <v>-4.88</v>
       </c>
       <c r="M93" t="n">
-        <v>-9.539999999999999</v>
+        <v>-8.66</v>
       </c>
       <c r="N93" t="b">
         <v>0</v>
@@ -5604,7 +5616,7 @@
         <v>-12.6</v>
       </c>
       <c r="H94" t="n">
-        <v>-18.13</v>
+        <v>-18.01</v>
       </c>
       <c r="I94" t="n">
         <v>-7.89</v>
@@ -5617,7 +5629,7 @@
         <v>-21.29</v>
       </c>
       <c r="M94" t="n">
-        <v>-19.14</v>
+        <v>-17.9</v>
       </c>
       <c r="N94" t="b">
         <v>0</v>
@@ -5655,7 +5667,7 @@
         <v>-17.9</v>
       </c>
       <c r="H95" t="n">
-        <v>3.72</v>
+        <v>5.84</v>
       </c>
       <c r="I95" t="n">
         <v>0.6</v>
@@ -5668,7 +5680,7 @@
         <v>-4.72</v>
       </c>
       <c r="M95" t="n">
-        <v>2.71</v>
+        <v>5.94</v>
       </c>
       <c r="N95" t="b">
         <v>1</v>
@@ -5719,7 +5731,7 @@
         <v>-16.43</v>
       </c>
       <c r="M96" t="n">
-        <v>-15.52</v>
+        <v>-14.41</v>
       </c>
       <c r="N96" t="b">
         <v>1</v>
@@ -5757,7 +5769,7 @@
         <v>19.4</v>
       </c>
       <c r="H97" t="n">
-        <v>-5.82</v>
+        <v>-5.31</v>
       </c>
       <c r="I97" t="n">
         <v>-10.01</v>
@@ -5770,7 +5782,7 @@
         <v>-15.23</v>
       </c>
       <c r="M97" t="n">
-        <v>-6.25</v>
+        <v>-4.63</v>
       </c>
       <c r="N97" t="b">
         <v>1</v>
@@ -5808,7 +5820,7 @@
         <v>-30.5</v>
       </c>
       <c r="H98" t="n">
-        <v>-8.789999999999999</v>
+        <v>-6</v>
       </c>
       <c r="I98" t="n">
         <v>-4.6</v>
@@ -5821,7 +5833,7 @@
         <v>-10.37</v>
       </c>
       <c r="M98" t="n">
-        <v>-9.220000000000001</v>
+        <v>-5.32</v>
       </c>
       <c r="N98" t="b">
         <v>0</v>
@@ -5859,7 +5871,7 @@
         <v>-20.5</v>
       </c>
       <c r="H99" t="n">
-        <v>-16.02</v>
+        <v>-15.48</v>
       </c>
       <c r="I99" t="n">
         <v>-4.62</v>
@@ -5872,7 +5884,7 @@
         <v>-9.92</v>
       </c>
       <c r="M99" t="n">
-        <v>-16.45</v>
+        <v>-14.8</v>
       </c>
       <c r="N99" t="b">
         <v>0</v>
@@ -5910,7 +5922,7 @@
         <v>-12.3</v>
       </c>
       <c r="H100" t="n">
-        <v>-12.67</v>
+        <v>-14.93</v>
       </c>
       <c r="I100" t="n">
         <v>-4.36</v>
@@ -5923,7 +5935,7 @@
         <v>-13.26</v>
       </c>
       <c r="M100" t="n">
-        <v>-13.32</v>
+        <v>-14.47</v>
       </c>
       <c r="N100" t="b">
         <v>0</v>
@@ -5961,7 +5973,7 @@
         <v>13.7</v>
       </c>
       <c r="H101" t="n">
-        <v>-18.53</v>
+        <v>-19.98</v>
       </c>
       <c r="I101" t="n">
         <v>-12.16</v>
@@ -5974,7 +5986,7 @@
         <v>-13.02</v>
       </c>
       <c r="M101" t="n">
-        <v>-19.18</v>
+        <v>-19.52</v>
       </c>
       <c r="N101" t="b">
         <v>0</v>
@@ -6012,7 +6024,7 @@
         <v>-2.6</v>
       </c>
       <c r="H102" t="n">
-        <v>-7.92</v>
+        <v>-8.68</v>
       </c>
       <c r="I102" t="n">
         <v>-4.27</v>
@@ -6025,7 +6037,7 @@
         <v>-4.86</v>
       </c>
       <c r="M102" t="n">
-        <v>-8.57</v>
+        <v>-8.220000000000001</v>
       </c>
       <c r="N102" t="b">
         <v>1</v>
@@ -6063,7 +6075,7 @@
         <v>25.6</v>
       </c>
       <c r="H103" t="n">
-        <v>13.74</v>
+        <v>8.58</v>
       </c>
       <c r="I103" t="n">
         <v>4.26</v>
@@ -6076,7 +6088,7 @@
         <v>-10.74</v>
       </c>
       <c r="M103" t="n">
-        <v>13.08</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="N103" t="b">
         <v>0</v>
@@ -6114,7 +6126,7 @@
         <v>23.8</v>
       </c>
       <c r="H104" t="n">
-        <v>-1.13</v>
+        <v>-4.17</v>
       </c>
       <c r="I104" t="n">
         <v>1.36</v>
@@ -6127,7 +6139,7 @@
         <v>-9.94</v>
       </c>
       <c r="M104" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-2.75</v>
       </c>
       <c r="N104" t="b">
         <v>1</v>
@@ -6165,7 +6177,7 @@
         <v>38.9</v>
       </c>
       <c r="H105" t="n">
-        <v>-11.26</v>
+        <v>-10.88</v>
       </c>
       <c r="I105" t="n">
         <v>-9.220000000000001</v>
@@ -6178,7 +6190,7 @@
         <v>-9.83</v>
       </c>
       <c r="M105" t="n">
-        <v>-10.95</v>
+        <v>-9.460000000000001</v>
       </c>
       <c r="N105" t="b">
         <v>1</v>
@@ -6216,7 +6228,7 @@
         <v>32.1</v>
       </c>
       <c r="H106" t="n">
-        <v>40.27</v>
+        <v>37.45</v>
       </c>
       <c r="I106" t="n">
         <v>11.84</v>
@@ -6229,7 +6241,7 @@
         <v>-1.82</v>
       </c>
       <c r="M106" t="n">
-        <v>40.59</v>
+        <v>38.87</v>
       </c>
       <c r="N106" t="b">
         <v>0</v>
@@ -6267,7 +6279,7 @@
         <v>53.4</v>
       </c>
       <c r="H107" t="n">
-        <v>29.49</v>
+        <v>29.68</v>
       </c>
       <c r="I107" t="n">
         <v>2.75</v>
@@ -6280,7 +6292,7 @@
         <v>-2.31</v>
       </c>
       <c r="M107" t="n">
-        <v>30.11</v>
+        <v>31.4</v>
       </c>
       <c r="N107" t="b">
         <v>0</v>
@@ -6318,7 +6330,7 @@
         <v>54.1</v>
       </c>
       <c r="H108" t="n">
-        <v>38.46</v>
+        <v>38.79</v>
       </c>
       <c r="I108" t="n">
         <v>5.54</v>
@@ -6331,7 +6343,7 @@
         <v>-0.41</v>
       </c>
       <c r="M108" t="n">
-        <v>38.61</v>
+        <v>40.04</v>
       </c>
       <c r="N108" t="b">
         <v>0</v>
@@ -6369,7 +6381,7 @@
         <v>43.2</v>
       </c>
       <c r="H109" t="n">
-        <v>-10.09</v>
+        <v>-9.42</v>
       </c>
       <c r="I109" t="n">
         <v>-3.15</v>
@@ -6382,7 +6394,7 @@
         <v>-17.51</v>
       </c>
       <c r="M109" t="n">
-        <v>-9.94</v>
+        <v>-8.16</v>
       </c>
       <c r="N109" t="b">
         <v>1</v>
@@ -6420,7 +6432,7 @@
         <v>-8.199999999999999</v>
       </c>
       <c r="H110" t="n">
-        <v>3.58</v>
+        <v>5.55</v>
       </c>
       <c r="I110" t="n">
         <v>5.34</v>
@@ -6433,7 +6445,7 @@
         <v>-5.27</v>
       </c>
       <c r="M110" t="n">
-        <v>3.73</v>
+        <v>6.81</v>
       </c>
       <c r="N110" t="b">
         <v>1</v>
@@ -6471,7 +6483,7 @@
         <v>-1.2</v>
       </c>
       <c r="H111" t="n">
-        <v>4.51</v>
+        <v>3.94</v>
       </c>
       <c r="I111" t="n">
         <v>8.27</v>
@@ -6484,7 +6496,7 @@
         <v>-5.3</v>
       </c>
       <c r="M111" t="n">
-        <v>4.62</v>
+        <v>5.15</v>
       </c>
       <c r="N111" t="b">
         <v>0</v>
@@ -6522,7 +6534,7 @@
         <v>-23.9</v>
       </c>
       <c r="H112" t="n">
-        <v>-6.69</v>
+        <v>-6.58</v>
       </c>
       <c r="I112" t="n">
         <v>3.28</v>
@@ -6535,7 +6547,7 @@
         <v>-4.46</v>
       </c>
       <c r="M112" t="n">
-        <v>-6.83</v>
+        <v>-5.62</v>
       </c>
       <c r="N112" t="b">
         <v>1</v>
@@ -6577,7 +6589,7 @@
         <v>-6.1</v>
       </c>
       <c r="H113" t="n">
-        <v>-16.48</v>
+        <v>-17.05</v>
       </c>
       <c r="I113" t="n">
         <v>4.9</v>
@@ -6590,7 +6602,7 @@
         <v>-9</v>
       </c>
       <c r="M113" t="n">
-        <v>-16.62</v>
+        <v>-16.08</v>
       </c>
       <c r="N113" t="b">
         <v>1</v>
@@ -6628,7 +6640,7 @@
         <v>26.7</v>
       </c>
       <c r="H114" t="n">
-        <v>-0.85</v>
+        <v>-1.14</v>
       </c>
       <c r="I114" t="n">
         <v>-0.05</v>
@@ -6641,7 +6653,7 @@
         <v>-0.87</v>
       </c>
       <c r="M114" t="n">
-        <v>-1</v>
+        <v>-0.18</v>
       </c>
       <c r="N114" t="b">
         <v>1</v>
@@ -6679,7 +6691,7 @@
         <v>39.5</v>
       </c>
       <c r="H115" t="n">
-        <v>7.05</v>
+        <v>0.27</v>
       </c>
       <c r="I115" t="n">
         <v>-5.13</v>
@@ -6692,7 +6704,7 @@
         <v>-8.869999999999999</v>
       </c>
       <c r="M115" t="n">
-        <v>6.9</v>
+        <v>1.24</v>
       </c>
       <c r="N115" t="b">
         <v>0</v>
@@ -6730,7 +6742,7 @@
         <v>14.3</v>
       </c>
       <c r="H116" t="n">
-        <v>18.41</v>
+        <v>12.68</v>
       </c>
       <c r="I116" t="n">
         <v>-0.43</v>
@@ -6743,7 +6755,7 @@
         <v>-11.86</v>
       </c>
       <c r="M116" t="n">
-        <v>18.27</v>
+        <v>13.65</v>
       </c>
       <c r="N116" t="b">
         <v>0</v>
@@ -6781,7 +6793,7 @@
         <v>-11.3</v>
       </c>
       <c r="H117" t="n">
-        <v>1.9</v>
+        <v>0.55</v>
       </c>
       <c r="I117" t="n">
         <v>1.31</v>
@@ -6794,7 +6806,7 @@
         <v>-1.88</v>
       </c>
       <c r="M117" t="n">
-        <v>1.75</v>
+        <v>1.52</v>
       </c>
       <c r="N117" t="b">
         <v>0</v>
@@ -6832,7 +6844,7 @@
         <v>-23.5</v>
       </c>
       <c r="H118" t="n">
-        <v>-25.22</v>
+        <v>-25.1</v>
       </c>
       <c r="I118" t="n">
         <v>13.29</v>
@@ -6845,7 +6857,7 @@
         <v>-14.04</v>
       </c>
       <c r="M118" t="n">
-        <v>-25.36</v>
+        <v>-24.13</v>
       </c>
       <c r="N118" t="b">
         <v>0</v>
@@ -6883,7 +6895,7 @@
         <v>10.5</v>
       </c>
       <c r="H119" t="n">
-        <v>-4.97</v>
+        <v>-5.42</v>
       </c>
       <c r="I119" t="n">
         <v>-0.86</v>
@@ -6896,7 +6908,7 @@
         <v>-6.11</v>
       </c>
       <c r="M119" t="n">
-        <v>-5.12</v>
+        <v>-4.45</v>
       </c>
       <c r="N119" t="b">
         <v>0</v>
@@ -6934,7 +6946,7 @@
         <v>-3.5</v>
       </c>
       <c r="H120" t="n">
-        <v>-2.18</v>
+        <v>-2.93</v>
       </c>
       <c r="I120" t="n">
         <v>-4.95</v>
@@ -6947,7 +6959,7 @@
         <v>-8.43</v>
       </c>
       <c r="M120" t="n">
-        <v>-2.53</v>
+        <v>-2.17</v>
       </c>
       <c r="N120" t="b">
         <v>1</v>
@@ -6985,7 +6997,7 @@
         <v>-12.8</v>
       </c>
       <c r="H121" t="n">
-        <v>11.4</v>
+        <v>9.85</v>
       </c>
       <c r="I121" t="n">
         <v>-1.74</v>
@@ -6998,7 +7010,7 @@
         <v>-2.97</v>
       </c>
       <c r="M121" t="n">
-        <v>11.06</v>
+        <v>10.61</v>
       </c>
       <c r="N121" t="b">
         <v>0</v>
@@ -7036,7 +7048,7 @@
         <v>2.4</v>
       </c>
       <c r="H122" t="n">
-        <v>25.26</v>
+        <v>16.22</v>
       </c>
       <c r="I122" t="n">
         <v>12.41</v>
@@ -7049,7 +7061,7 @@
         <v>-0.07000000000000001</v>
       </c>
       <c r="M122" t="n">
-        <v>24.91</v>
+        <v>16.98</v>
       </c>
       <c r="N122" t="b">
         <v>0</v>
@@ -7087,7 +7099,7 @@
         <v>-17.9</v>
       </c>
       <c r="H123" t="n">
-        <v>-0.46</v>
+        <v>-2.15</v>
       </c>
       <c r="I123" t="n">
         <v>-0.5</v>
@@ -7100,7 +7112,7 @@
         <v>-3.43</v>
       </c>
       <c r="M123" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-1.39</v>
       </c>
       <c r="N123" t="b">
         <v>1</v>
@@ -7138,7 +7150,7 @@
         <v>11.9</v>
       </c>
       <c r="H124" t="n">
-        <v>-1.7</v>
+        <v>-2.49</v>
       </c>
       <c r="I124" t="n">
         <v>6.88</v>
@@ -7151,7 +7163,7 @@
         <v>-10.93</v>
       </c>
       <c r="M124" t="n">
-        <v>-2.15</v>
+        <v>-1.83</v>
       </c>
       <c r="N124" t="b">
         <v>0</v>
@@ -7189,7 +7201,7 @@
         <v>53.5</v>
       </c>
       <c r="H125" t="n">
-        <v>7.03</v>
+        <v>0.58</v>
       </c>
       <c r="I125" t="n">
         <v>1.23</v>
@@ -7202,7 +7214,7 @@
         <v>-7.57</v>
       </c>
       <c r="M125" t="n">
-        <v>6.57</v>
+        <v>1.24</v>
       </c>
       <c r="N125" t="b">
         <v>1</v>
@@ -7240,7 +7252,7 @@
         <v>18.1</v>
       </c>
       <c r="H126" t="n">
-        <v>-2.99</v>
+        <v>-4.48</v>
       </c>
       <c r="I126" t="n">
         <v>-1.69</v>
@@ -7253,7 +7265,7 @@
         <v>-1.92</v>
       </c>
       <c r="M126" t="n">
-        <v>-3.44</v>
+        <v>-3.82</v>
       </c>
       <c r="N126" t="b">
         <v>0</v>
@@ -7291,7 +7303,7 @@
         <v>-1</v>
       </c>
       <c r="H127" t="n">
-        <v>-11.96</v>
+        <v>-10.84</v>
       </c>
       <c r="I127" t="n">
         <v>-6.26</v>
@@ -7304,7 +7316,7 @@
         <v>-15</v>
       </c>
       <c r="M127" t="n">
-        <v>-12.41</v>
+        <v>-10.19</v>
       </c>
       <c r="N127" t="b">
         <v>1</v>
@@ -7342,7 +7354,7 @@
         <v>29.7</v>
       </c>
       <c r="H128" t="n">
-        <v>2.81</v>
+        <v>1.27</v>
       </c>
       <c r="I128" t="n">
         <v>11.27</v>
@@ -7355,7 +7367,7 @@
         <v>0</v>
       </c>
       <c r="M128" t="n">
-        <v>2.35</v>
+        <v>1.93</v>
       </c>
       <c r="N128" t="b">
         <v>1</v>
@@ -7393,7 +7405,7 @@
         <v>15.2</v>
       </c>
       <c r="H129" t="n">
-        <v>-36.73</v>
+        <v>-39.35</v>
       </c>
       <c r="I129" t="n">
         <v>-8.77</v>
@@ -7406,7 +7418,7 @@
         <v>-24.79</v>
       </c>
       <c r="M129" t="n">
-        <v>-36.46</v>
+        <v>-37.97</v>
       </c>
       <c r="N129" t="b">
         <v>1</v>
@@ -7444,7 +7456,7 @@
         <v>22.2</v>
       </c>
       <c r="H130" t="n">
-        <v>9.67</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="I130" t="n">
         <v>1.01</v>
@@ -7457,7 +7469,7 @@
         <v>-3.94</v>
       </c>
       <c r="M130" t="n">
-        <v>9.94</v>
+        <v>11.33</v>
       </c>
       <c r="N130" t="b">
         <v>1</v>
@@ -7495,7 +7507,7 @@
         <v>10.8</v>
       </c>
       <c r="H131" t="n">
-        <v>11.57</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="I131" t="n">
         <v>5.62</v>
@@ -7508,7 +7520,7 @@
         <v>-1.59</v>
       </c>
       <c r="M131" t="n">
-        <v>11.85</v>
+        <v>10.25</v>
       </c>
       <c r="N131" t="b">
         <v>0</v>
@@ -7546,7 +7558,7 @@
         <v>-2.1</v>
       </c>
       <c r="H132" t="n">
-        <v>-16.67</v>
+        <v>-20.51</v>
       </c>
       <c r="I132" t="n">
         <v>0.67</v>
@@ -7559,7 +7571,7 @@
         <v>-7.84</v>
       </c>
       <c r="M132" t="n">
-        <v>-16.4</v>
+        <v>-19.13</v>
       </c>
       <c r="N132" t="b">
         <v>0</v>
@@ -7597,7 +7609,7 @@
         <v>16.7</v>
       </c>
       <c r="H133" t="n">
-        <v>-25.98</v>
+        <v>-28.39</v>
       </c>
       <c r="I133" t="n">
         <v>-15.31</v>
@@ -7610,7 +7622,7 @@
         <v>-22</v>
       </c>
       <c r="M133" t="n">
-        <v>-27.7</v>
+        <v>-28.98</v>
       </c>
       <c r="N133" t="b">
         <v>0</v>
@@ -7648,7 +7660,7 @@
         <v>0.3</v>
       </c>
       <c r="H134" t="n">
-        <v>37.37</v>
+        <v>32.29</v>
       </c>
       <c r="I134" t="n">
         <v>6.01</v>
@@ -7661,7 +7673,7 @@
         <v>-3.85</v>
       </c>
       <c r="M134" t="n">
-        <v>34.14</v>
+        <v>30.19</v>
       </c>
       <c r="N134" t="b">
         <v>0</v>
@@ -7703,7 +7715,7 @@
         <v>-0</v>
       </c>
       <c r="H135" t="n">
-        <v>49.07</v>
+        <v>47.8</v>
       </c>
       <c r="I135" t="n">
         <v>13.5</v>
@@ -7716,7 +7728,7 @@
         <v>-2.53</v>
       </c>
       <c r="M135" t="n">
-        <v>45.83</v>
+        <v>45.7</v>
       </c>
       <c r="N135" t="b">
         <v>1</v>
@@ -7754,7 +7766,7 @@
         <v>10.5</v>
       </c>
       <c r="H136" t="n">
-        <v>16.56</v>
+        <v>16.61</v>
       </c>
       <c r="I136" t="n">
         <v>1.99</v>
@@ -7767,7 +7779,7 @@
         <v>-6.27</v>
       </c>
       <c r="M136" t="n">
-        <v>13.32</v>
+        <v>14.51</v>
       </c>
       <c r="N136" t="b">
         <v>1</v>
@@ -7805,7 +7817,7 @@
         <v>30.4</v>
       </c>
       <c r="H137" t="n">
-        <v>6.05</v>
+        <v>5.96</v>
       </c>
       <c r="I137" t="n">
         <v>8.539999999999999</v>
@@ -7818,7 +7830,7 @@
         <v>-0.44</v>
       </c>
       <c r="M137" t="n">
-        <v>2.81</v>
+        <v>3.86</v>
       </c>
       <c r="N137" t="b">
         <v>0</v>
@@ -7860,7 +7872,7 @@
         <v>-3.2</v>
       </c>
       <c r="H138" t="n">
-        <v>18.57</v>
+        <v>15.06</v>
       </c>
       <c r="I138" t="n">
         <v>15.28</v>
@@ -7873,7 +7885,7 @@
         <v>-2.53</v>
       </c>
       <c r="M138" t="n">
-        <v>15.33</v>
+        <v>12.96</v>
       </c>
       <c r="N138" t="b">
         <v>0</v>
@@ -7911,7 +7923,7 @@
         <v>-23.5</v>
       </c>
       <c r="H139" t="n">
-        <v>17.89</v>
+        <v>13.32</v>
       </c>
       <c r="I139" t="n">
         <v>20.48</v>
@@ -7924,7 +7936,7 @@
         <v>-2.25</v>
       </c>
       <c r="M139" t="n">
-        <v>14.65</v>
+        <v>11.22</v>
       </c>
       <c r="N139" t="b">
         <v>0</v>
@@ -7962,7 +7974,7 @@
         <v>-27.3</v>
       </c>
       <c r="H140" t="n">
-        <v>12.9</v>
+        <v>12.84</v>
       </c>
       <c r="I140" t="n">
         <v>-8.83</v>
@@ -7975,7 +7987,7 @@
         <v>-19.66</v>
       </c>
       <c r="M140" t="n">
-        <v>9.66</v>
+        <v>10.74</v>
       </c>
       <c r="N140" t="b">
         <v>0</v>
@@ -8013,7 +8025,7 @@
         <v>-12.5</v>
       </c>
       <c r="H141" t="n">
-        <v>-10.78</v>
+        <v>-11.98</v>
       </c>
       <c r="I141" t="n">
         <v>21.54</v>
@@ -8026,7 +8038,7 @@
         <v>-0.95</v>
       </c>
       <c r="M141" t="n">
-        <v>-14.68</v>
+        <v>-14.72</v>
       </c>
       <c r="N141" t="b">
         <v>0</v>
@@ -8064,7 +8076,7 @@
         <v>-37</v>
       </c>
       <c r="H142" t="n">
-        <v>50.36</v>
+        <v>47.83</v>
       </c>
       <c r="I142" t="n">
         <v>18.38</v>
@@ -8077,7 +8089,7 @@
         <v>-5.11</v>
       </c>
       <c r="M142" t="n">
-        <v>46.46</v>
+        <v>45.08</v>
       </c>
       <c r="N142" t="b">
         <v>1</v>
@@ -8119,7 +8131,7 @@
         <v>-3.4</v>
       </c>
       <c r="H143" t="n">
-        <v>11.74</v>
+        <v>4.73</v>
       </c>
       <c r="I143" t="n">
         <v>30.48</v>
@@ -8132,7 +8144,7 @@
         <v>-0.9</v>
       </c>
       <c r="M143" t="n">
-        <v>7.84</v>
+        <v>1.98</v>
       </c>
       <c r="N143" t="b">
         <v>0</v>
@@ -8170,7 +8182,7 @@
         <v>-23.4</v>
       </c>
       <c r="H144" t="n">
-        <v>-0.38</v>
+        <v>0.25</v>
       </c>
       <c r="I144" t="n">
         <v>-3.58</v>
@@ -8183,7 +8195,7 @@
         <v>-17.98</v>
       </c>
       <c r="M144" t="n">
-        <v>-4.27</v>
+        <v>-2.5</v>
       </c>
       <c r="N144" t="b">
         <v>0</v>
@@ -8221,7 +8233,7 @@
         <v>-28.9</v>
       </c>
       <c r="H145" t="n">
-        <v>-15.68</v>
+        <v>-14.26</v>
       </c>
       <c r="I145" t="n">
         <v>-12.9</v>
@@ -8234,7 +8246,7 @@
         <v>-23.19</v>
       </c>
       <c r="M145" t="n">
-        <v>-19.58</v>
+        <v>-17.01</v>
       </c>
       <c r="N145" t="b">
         <v>0</v>
@@ -8272,7 +8284,7 @@
         <v>-26.8</v>
       </c>
       <c r="H146" t="n">
-        <v>30.62</v>
+        <v>27.37</v>
       </c>
       <c r="I146" t="n">
         <v>4.56</v>
@@ -8285,7 +8297,7 @@
         <v>-4.09</v>
       </c>
       <c r="M146" t="n">
-        <v>26.72</v>
+        <v>24.63</v>
       </c>
       <c r="N146" t="b">
         <v>1</v>
@@ -8327,7 +8339,7 @@
         <v>-9.800000000000001</v>
       </c>
       <c r="H147" t="n">
-        <v>-20.57</v>
+        <v>-20.83</v>
       </c>
       <c r="I147" t="n">
         <v>-4.09</v>
@@ -8340,7 +8352,7 @@
         <v>-15.24</v>
       </c>
       <c r="M147" t="n">
-        <v>-25.68</v>
+        <v>-24.78</v>
       </c>
       <c r="N147" t="b">
         <v>0</v>
@@ -8378,7 +8390,7 @@
         <v>21</v>
       </c>
       <c r="H148" t="n">
-        <v>1.35</v>
+        <v>0.39</v>
       </c>
       <c r="I148" t="n">
         <v>-0.72</v>
@@ -8391,7 +8403,7 @@
         <v>-7.35</v>
       </c>
       <c r="M148" t="n">
-        <v>-3.77</v>
+        <v>-3.56</v>
       </c>
       <c r="N148" t="b">
         <v>0</v>
@@ -8429,7 +8441,7 @@
         <v>13.2</v>
       </c>
       <c r="H149" t="n">
-        <v>51.02</v>
+        <v>52.29</v>
       </c>
       <c r="I149" t="n">
         <v>8.130000000000001</v>
@@ -8442,7 +8454,7 @@
         <v>-2.36</v>
       </c>
       <c r="M149" t="n">
-        <v>45.91</v>
+        <v>48.33</v>
       </c>
       <c r="N149" t="b">
         <v>0</v>
@@ -8480,7 +8492,7 @@
         <v>6.1</v>
       </c>
       <c r="H150" t="n">
-        <v>7.05</v>
+        <v>4.36</v>
       </c>
       <c r="I150" t="n">
         <v>10.43</v>
@@ -8493,7 +8505,7 @@
         <v>-1.51</v>
       </c>
       <c r="M150" t="n">
-        <v>1.93</v>
+        <v>0.4</v>
       </c>
       <c r="N150" t="b">
         <v>0</v>
@@ -8531,7 +8543,7 @@
         <v>6.5</v>
       </c>
       <c r="H151" t="n">
-        <v>-3.58</v>
+        <v>-3.52</v>
       </c>
       <c r="I151" t="n">
         <v>-0.04</v>
@@ -8544,7 +8556,7 @@
         <v>-4.12</v>
       </c>
       <c r="M151" t="n">
-        <v>-8.699999999999999</v>
+        <v>-7.47</v>
       </c>
       <c r="N151" t="b">
         <v>0</v>
@@ -8582,7 +8594,7 @@
         <v>-36.5</v>
       </c>
       <c r="H152" t="n">
-        <v>-29.67</v>
+        <v>-34.49</v>
       </c>
       <c r="I152" t="n">
         <v>-27.75</v>
@@ -8595,7 +8607,7 @@
         <v>-31.28</v>
       </c>
       <c r="M152" t="n">
-        <v>-34.23</v>
+        <v>-37.9</v>
       </c>
       <c r="N152" t="b">
         <v>1</v>
@@ -8633,7 +8645,7 @@
         <v>-14.5</v>
       </c>
       <c r="H153" t="n">
-        <v>-10.81</v>
+        <v>-8.99</v>
       </c>
       <c r="I153" t="n">
         <v>4.48</v>
@@ -8646,7 +8658,7 @@
         <v>-3.33</v>
       </c>
       <c r="M153" t="n">
-        <v>-15.37</v>
+        <v>-12.39</v>
       </c>
       <c r="N153" t="b">
         <v>0</v>
@@ -8684,7 +8696,7 @@
         <v>1.7</v>
       </c>
       <c r="H154" t="n">
-        <v>-1.1</v>
+        <v>-3.1</v>
       </c>
       <c r="I154" t="n">
         <v>8.859999999999999</v>
@@ -8697,7 +8709,7 @@
         <v>-3.27</v>
       </c>
       <c r="M154" t="n">
-        <v>-5.66</v>
+        <v>-6.5</v>
       </c>
       <c r="N154" t="b">
         <v>0</v>
@@ -8735,7 +8747,7 @@
         <v>48.1</v>
       </c>
       <c r="H155" t="n">
-        <v>11.33</v>
+        <v>6.43</v>
       </c>
       <c r="I155" t="n">
         <v>0.16</v>
@@ -8748,7 +8760,7 @@
         <v>-8.890000000000001</v>
       </c>
       <c r="M155" t="n">
-        <v>6.78</v>
+        <v>3.03</v>
       </c>
       <c r="N155" t="b">
         <v>0</v>
@@ -8786,7 +8798,7 @@
         <v>-38.7</v>
       </c>
       <c r="H156" t="n">
-        <v>22.94</v>
+        <v>24.13</v>
       </c>
       <c r="I156" t="n">
         <v>17.17</v>
@@ -8799,7 +8811,7 @@
         <v>-0.54</v>
       </c>
       <c r="M156" t="n">
-        <v>18.38</v>
+        <v>20.72</v>
       </c>
       <c r="N156" t="b">
         <v>1</v>
@@ -8837,7 +8849,7 @@
         <v>24.9</v>
       </c>
       <c r="H157" t="n">
-        <v>5.61</v>
+        <v>3.65</v>
       </c>
       <c r="I157" t="n">
         <v>10.45</v>
@@ -8850,7 +8862,7 @@
         <v>-0.49</v>
       </c>
       <c r="M157" t="n">
-        <v>1.06</v>
+        <v>0.24</v>
       </c>
       <c r="N157" t="b">
         <v>0</v>
@@ -8888,7 +8900,7 @@
         <v>-34.6</v>
       </c>
       <c r="H158" t="n">
-        <v>22.75</v>
+        <v>17.93</v>
       </c>
       <c r="I158" t="n">
         <v>6.67</v>
@@ -8901,7 +8913,7 @@
         <v>-3.06</v>
       </c>
       <c r="M158" t="n">
-        <v>18.19</v>
+        <v>14.53</v>
       </c>
       <c r="N158" t="b">
         <v>1</v>
@@ -8939,7 +8951,7 @@
         <v>-21.4</v>
       </c>
       <c r="H159" t="n">
-        <v>0.58</v>
+        <v>-2.3</v>
       </c>
       <c r="I159" t="n">
         <v>2.8</v>
@@ -8952,7 +8964,7 @@
         <v>-2.27</v>
       </c>
       <c r="M159" t="n">
-        <v>-3.98</v>
+        <v>-5.7</v>
       </c>
       <c r="N159" t="b">
         <v>0</v>
@@ -8990,7 +9002,7 @@
         <v>-11.8</v>
       </c>
       <c r="H160" t="n">
-        <v>2.76</v>
+        <v>4.92</v>
       </c>
       <c r="I160" t="n">
         <v>9.76</v>
@@ -9003,7 +9015,7 @@
         <v>-1.63</v>
       </c>
       <c r="M160" t="n">
-        <v>-1.91</v>
+        <v>1.41</v>
       </c>
       <c r="N160" t="b">
         <v>1</v>
@@ -9041,7 +9053,7 @@
         <v>0.1</v>
       </c>
       <c r="H161" t="n">
-        <v>-7.73</v>
+        <v>-6.1</v>
       </c>
       <c r="I161" t="n">
         <v>-2.83</v>
@@ -9054,7 +9066,7 @@
         <v>-5.45</v>
       </c>
       <c r="M161" t="n">
-        <v>-12.4</v>
+        <v>-9.609999999999999</v>
       </c>
       <c r="N161" t="b">
         <v>1</v>
@@ -9092,7 +9104,7 @@
         <v>-13.8</v>
       </c>
       <c r="H162" t="n">
-        <v>19.24</v>
+        <v>15.81</v>
       </c>
       <c r="I162" t="n">
         <v>4.67</v>
@@ -9105,7 +9117,7 @@
         <v>-5.7</v>
       </c>
       <c r="M162" t="n">
-        <v>14.57</v>
+        <v>12.29</v>
       </c>
       <c r="N162" t="b">
         <v>0</v>
@@ -9147,7 +9159,7 @@
         <v>-8.800000000000001</v>
       </c>
       <c r="H163" t="n">
-        <v>13.45</v>
+        <v>11.21</v>
       </c>
       <c r="I163" t="n">
         <v>15.97</v>
@@ -9160,7 +9172,7 @@
         <v>-0.79</v>
       </c>
       <c r="M163" t="n">
-        <v>8.789999999999999</v>
+        <v>7.7</v>
       </c>
       <c r="N163" t="b">
         <v>0</v>
@@ -9198,7 +9210,7 @@
         <v>24.1</v>
       </c>
       <c r="H164" t="n">
-        <v>2.93</v>
+        <v>2.61</v>
       </c>
       <c r="I164" t="n">
         <v>-8.31</v>
@@ -9211,7 +9223,7 @@
         <v>-18.31</v>
       </c>
       <c r="M164" t="n">
-        <v>-0.93</v>
+        <v>-0.11</v>
       </c>
       <c r="N164" t="b">
         <v>1</v>
@@ -9249,7 +9261,7 @@
         <v>-15.9</v>
       </c>
       <c r="H165" t="n">
-        <v>13.57</v>
+        <v>10.88</v>
       </c>
       <c r="I165" t="n">
         <v>10.45</v>
@@ -9262,7 +9274,7 @@
         <v>-0.31</v>
       </c>
       <c r="M165" t="n">
-        <v>9.710000000000001</v>
+        <v>8.16</v>
       </c>
       <c r="N165" t="b">
         <v>1</v>
@@ -9300,7 +9312,7 @@
         <v>-23.3</v>
       </c>
       <c r="H166" t="n">
-        <v>-14.17</v>
+        <v>-14.97</v>
       </c>
       <c r="I166" t="n">
         <v>-20.42</v>
@@ -9313,7 +9325,7 @@
         <v>-27.45</v>
       </c>
       <c r="M166" t="n">
-        <v>-18.03</v>
+        <v>-17.69</v>
       </c>
       <c r="N166" t="b">
         <v>0</v>
@@ -9351,7 +9363,7 @@
         <v>28.9</v>
       </c>
       <c r="H167" t="n">
-        <v>-1.86</v>
+        <v>-4.06</v>
       </c>
       <c r="I167" t="n">
         <v>8.06</v>
@@ -9364,7 +9376,7 @@
         <v>-2.79</v>
       </c>
       <c r="M167" t="n">
-        <v>-6.63</v>
+        <v>-7.67</v>
       </c>
       <c r="N167" t="b">
         <v>0</v>
@@ -9402,7 +9414,7 @@
         <v>40.1</v>
       </c>
       <c r="H168" t="n">
-        <v>32.2</v>
+        <v>22.91</v>
       </c>
       <c r="I168" t="n">
         <v>15.9</v>
@@ -9415,7 +9427,7 @@
         <v>-5.87</v>
       </c>
       <c r="M168" t="n">
-        <v>27.43</v>
+        <v>19.31</v>
       </c>
       <c r="N168" t="b">
         <v>0</v>
@@ -9453,7 +9465,7 @@
         <v>-27.3</v>
       </c>
       <c r="H169" t="n">
-        <v>5.84</v>
+        <v>1.67</v>
       </c>
       <c r="I169" t="n">
         <v>0.75</v>
@@ -9461,12 +9473,14 @@
       <c r="J169" t="n">
         <v>8.66</v>
       </c>
-      <c r="K169" t="inlineStr"/>
+      <c r="K169" t="n">
+        <v>1.67</v>
+      </c>
       <c r="L169" t="n">
         <v>-5.46</v>
       </c>
       <c r="M169" t="n">
-        <v>1.19</v>
+        <v>-1.81</v>
       </c>
       <c r="N169" t="b">
         <v>0</v>
@@ -9504,7 +9518,7 @@
         <v>19.7</v>
       </c>
       <c r="H170" t="n">
-        <v>-25.62</v>
+        <v>-29.25</v>
       </c>
       <c r="I170" t="n">
         <v>-4.49</v>
@@ -9512,12 +9526,14 @@
       <c r="J170" t="n">
         <v>-11.3</v>
       </c>
-      <c r="K170" t="inlineStr"/>
+      <c r="K170" t="n">
+        <v>-29.25</v>
+      </c>
       <c r="L170" t="n">
         <v>-13.7</v>
       </c>
       <c r="M170" t="n">
-        <v>-30.26</v>
+        <v>-32.74</v>
       </c>
       <c r="N170" t="b">
         <v>0</v>
@@ -9555,7 +9571,7 @@
         <v>-21.3</v>
       </c>
       <c r="H171" t="n">
-        <v>-10.66</v>
+        <v>-13.85</v>
       </c>
       <c r="I171" t="n">
         <v>7.16</v>
@@ -9563,12 +9579,14 @@
       <c r="J171" t="n">
         <v>6.1</v>
       </c>
-      <c r="K171" t="inlineStr"/>
+      <c r="K171" t="n">
+        <v>-13.85</v>
+      </c>
       <c r="L171" t="n">
         <v>-11.9</v>
       </c>
       <c r="M171" t="n">
-        <v>-15.3</v>
+        <v>-17.34</v>
       </c>
       <c r="N171" t="b">
         <v>0</v>
@@ -9606,7 +9624,7 @@
         <v>-21.8</v>
       </c>
       <c r="H172" t="n">
-        <v>-32.58</v>
+        <v>-35.76</v>
       </c>
       <c r="I172" t="n">
         <v>-18.97</v>
@@ -9614,12 +9632,14 @@
       <c r="J172" t="n">
         <v>-25.46</v>
       </c>
-      <c r="K172" t="inlineStr"/>
+      <c r="K172" t="n">
+        <v>-35.76</v>
+      </c>
       <c r="L172" t="n">
         <v>-26.82</v>
       </c>
       <c r="M172" t="n">
-        <v>-37.23</v>
+        <v>-39.24</v>
       </c>
       <c r="N172" t="b">
         <v>1</v>
@@ -9657,7 +9677,7 @@
         <v>-37.6</v>
       </c>
       <c r="H173" t="n">
-        <v>-15.2</v>
+        <v>-15.86</v>
       </c>
       <c r="I173" t="n">
         <v>15.2</v>
@@ -9672,7 +9692,7 @@
         <v>-10.3</v>
       </c>
       <c r="M173" t="n">
-        <v>-18.82</v>
+        <v>-18.34</v>
       </c>
       <c r="N173" t="b">
         <v>0</v>
@@ -9710,7 +9730,7 @@
         <v>53.8</v>
       </c>
       <c r="H174" t="n">
-        <v>47.61</v>
+        <v>32.56</v>
       </c>
       <c r="I174" t="n">
         <v>4.09</v>
@@ -9725,7 +9745,7 @@
         <v>-8.66</v>
       </c>
       <c r="M174" t="n">
-        <v>43.99</v>
+        <v>30.08</v>
       </c>
       <c r="N174" t="b">
         <v>0</v>
@@ -9767,7 +9787,7 @@
         <v>-5.7</v>
       </c>
       <c r="H175" t="n">
-        <v>44.08</v>
+        <v>34.31</v>
       </c>
       <c r="I175" t="n">
         <v>17.92</v>
@@ -9782,7 +9802,7 @@
         <v>-7.48</v>
       </c>
       <c r="M175" t="n">
-        <v>40.45</v>
+        <v>31.83</v>
       </c>
       <c r="N175" t="b">
         <v>0</v>
@@ -9820,7 +9840,7 @@
         <v>-39.3</v>
       </c>
       <c r="H176" t="n">
-        <v>12.62</v>
+        <v>10.9</v>
       </c>
       <c r="I176" t="n">
         <v>11.34</v>
@@ -9835,7 +9855,7 @@
         <v>-5.3</v>
       </c>
       <c r="M176" t="n">
-        <v>8.99</v>
+        <v>8.42</v>
       </c>
       <c r="N176" t="b">
         <v>0</v>
@@ -9873,7 +9893,7 @@
         <v>57</v>
       </c>
       <c r="H177" t="n">
-        <v>34.25</v>
+        <v>34.89</v>
       </c>
       <c r="I177" t="n">
         <v>-11.21</v>
@@ -9888,7 +9908,7 @@
         <v>-13.87</v>
       </c>
       <c r="M177" t="n">
-        <v>30.63</v>
+        <v>32.41</v>
       </c>
       <c r="N177" t="b">
         <v>1</v>
@@ -9926,7 +9946,7 @@
         <v>-21.8</v>
       </c>
       <c r="H178" t="n">
-        <v>20.63</v>
+        <v>19.72</v>
       </c>
       <c r="I178" t="n">
         <v>1.71</v>
@@ -9941,7 +9961,7 @@
         <v>-6.18</v>
       </c>
       <c r="M178" t="n">
-        <v>17</v>
+        <v>17.23</v>
       </c>
       <c r="N178" t="b">
         <v>1</v>
@@ -9979,7 +9999,7 @@
         <v>1</v>
       </c>
       <c r="H179" t="n">
-        <v>-31.18</v>
+        <v>-35.53</v>
       </c>
       <c r="I179" t="n">
         <v>-11.52</v>
@@ -9994,7 +10014,7 @@
         <v>-16.26</v>
       </c>
       <c r="M179" t="n">
-        <v>-34.85</v>
+        <v>-38.06</v>
       </c>
       <c r="N179" t="b">
         <v>1</v>
@@ -10032,7 +10052,7 @@
         <v>45.4</v>
       </c>
       <c r="H180" t="n">
-        <v>-14.25</v>
+        <v>-20.2</v>
       </c>
       <c r="I180" t="n">
         <v>-1.72</v>
@@ -10047,7 +10067,7 @@
         <v>-23.15</v>
       </c>
       <c r="M180" t="n">
-        <v>-17.92</v>
+        <v>-22.73</v>
       </c>
       <c r="N180" t="b">
         <v>1</v>
@@ -10085,7 +10105,7 @@
         <v>49.6</v>
       </c>
       <c r="H181" t="n">
-        <v>17.38</v>
+        <v>10.86</v>
       </c>
       <c r="I181" t="n">
         <v>6.34</v>
@@ -10100,7 +10120,7 @@
         <v>-20.75</v>
       </c>
       <c r="M181" t="n">
-        <v>13.71</v>
+        <v>8.33</v>
       </c>
       <c r="N181" t="b">
         <v>0</v>
@@ -10138,7 +10158,7 @@
         <v>55.3</v>
       </c>
       <c r="H182" t="n">
-        <v>-32.57</v>
+        <v>-37.2</v>
       </c>
       <c r="I182" t="n">
         <v>3.73</v>
@@ -10153,7 +10173,7 @@
         <v>-22.94</v>
       </c>
       <c r="M182" t="n">
-        <v>-36.25</v>
+        <v>-39.72</v>
       </c>
       <c r="N182" t="b">
         <v>0</v>
@@ -10191,7 +10211,7 @@
         <v>76.5</v>
       </c>
       <c r="H183" t="n">
-        <v>-7.73</v>
+        <v>-14.05</v>
       </c>
       <c r="I183" t="n">
         <v>-5.56</v>
@@ -10206,7 +10226,7 @@
         <v>-33.97</v>
       </c>
       <c r="M183" t="n">
-        <v>-11.4</v>
+        <v>-16.58</v>
       </c>
       <c r="N183" t="b">
         <v>1</v>
@@ -10244,7 +10264,7 @@
         <v>77.90000000000001</v>
       </c>
       <c r="H184" t="n">
-        <v>0.65</v>
+        <v>-5.01</v>
       </c>
       <c r="I184" t="n">
         <v>-3.53</v>
@@ -10259,7 +10279,7 @@
         <v>-20.26</v>
       </c>
       <c r="M184" t="n">
-        <v>-3.02</v>
+        <v>-7.54</v>
       </c>
       <c r="N184" t="b">
         <v>0</v>
@@ -10297,7 +10317,7 @@
         <v>57.6</v>
       </c>
       <c r="H185" t="n">
-        <v>28.82</v>
+        <v>21.13</v>
       </c>
       <c r="I185" t="n">
         <v>14.81</v>
@@ -10312,7 +10332,7 @@
         <v>-5.11</v>
       </c>
       <c r="M185" t="n">
-        <v>25.14</v>
+        <v>18.6</v>
       </c>
       <c r="N185" t="b">
         <v>0</v>
@@ -10350,7 +10370,7 @@
         <v>32.1</v>
       </c>
       <c r="H186" t="n">
-        <v>-2.4</v>
+        <v>-14.29</v>
       </c>
       <c r="I186" t="n">
         <v>16.93</v>
@@ -10365,7 +10385,7 @@
         <v>-24.48</v>
       </c>
       <c r="M186" t="n">
-        <v>-6.08</v>
+        <v>-16.81</v>
       </c>
       <c r="N186" t="b">
         <v>1</v>
@@ -10403,7 +10423,7 @@
         <v>51.8</v>
       </c>
       <c r="H187" t="n">
-        <v>-7.53</v>
+        <v>-12.47</v>
       </c>
       <c r="I187" t="n">
         <v>10.75</v>
@@ -10418,7 +10438,7 @@
         <v>-25.09</v>
       </c>
       <c r="M187" t="n">
-        <v>-11.2</v>
+        <v>-15</v>
       </c>
       <c r="N187" t="b">
         <v>1</v>
@@ -10456,7 +10476,7 @@
         <v>32.3</v>
       </c>
       <c r="H188" t="n">
-        <v>-34.71</v>
+        <v>-37.91</v>
       </c>
       <c r="I188" t="n">
         <v>-20.76</v>
@@ -10471,7 +10491,7 @@
         <v>-27.91</v>
       </c>
       <c r="M188" t="n">
-        <v>-38.38</v>
+        <v>-40.44</v>
       </c>
       <c r="N188" t="b">
         <v>1</v>
@@ -10509,7 +10529,7 @@
         <v>15.7</v>
       </c>
       <c r="H189" t="n">
-        <v>-14.02</v>
+        <v>-18.01</v>
       </c>
       <c r="I189" t="n">
         <v>-0.87</v>
@@ -10524,7 +10544,7 @@
         <v>-29.01</v>
       </c>
       <c r="M189" t="n">
-        <v>-17.69</v>
+        <v>-20.54</v>
       </c>
       <c r="N189" t="b">
         <v>0</v>
@@ -10562,7 +10582,7 @@
         <v>63.7</v>
       </c>
       <c r="H190" t="n">
-        <v>-19.98</v>
+        <v>-25.98</v>
       </c>
       <c r="I190" t="n">
         <v>-2.16</v>
@@ -10577,7 +10597,7 @@
         <v>-19.1</v>
       </c>
       <c r="M190" t="n">
-        <v>-23.65</v>
+        <v>-28.51</v>
       </c>
       <c r="N190" t="b">
         <v>0</v>
@@ -10615,7 +10635,7 @@
         <v>3.7</v>
       </c>
       <c r="H191" t="n">
-        <v>-9.66</v>
+        <v>-13.68</v>
       </c>
       <c r="I191" t="n">
         <v>-1.11</v>
@@ -10630,7 +10650,7 @@
         <v>-25.46</v>
       </c>
       <c r="M191" t="n">
-        <v>-13.33</v>
+        <v>-16.21</v>
       </c>
       <c r="N191" t="b">
         <v>1</v>
@@ -10668,7 +10688,7 @@
         <v>42.4</v>
       </c>
       <c r="H192" t="n">
-        <v>-13.23</v>
+        <v>-21.77</v>
       </c>
       <c r="I192" t="n">
         <v>2.16</v>
@@ -10683,7 +10703,7 @@
         <v>-15.76</v>
       </c>
       <c r="M192" t="n">
-        <v>-16.9</v>
+        <v>-24.3</v>
       </c>
       <c r="N192" t="b">
         <v>1</v>
@@ -10721,7 +10741,7 @@
         <v>28.2</v>
       </c>
       <c r="H193" t="n">
-        <v>-10.24</v>
+        <v>-18.63</v>
       </c>
       <c r="I193" t="n">
         <v>-1.71</v>
@@ -10736,7 +10756,7 @@
         <v>-23.43</v>
       </c>
       <c r="M193" t="n">
-        <v>-13.91</v>
+        <v>-21.15</v>
       </c>
       <c r="N193" t="b">
         <v>1</v>
@@ -10774,7 +10794,7 @@
         <v>28.6</v>
       </c>
       <c r="H194" t="n">
-        <v>-0.16</v>
+        <v>-13.07</v>
       </c>
       <c r="I194" t="n">
         <v>2.81</v>
@@ -10789,7 +10809,7 @@
         <v>-18.87</v>
       </c>
       <c r="M194" t="n">
-        <v>-3.84</v>
+        <v>-15.59</v>
       </c>
       <c r="N194" t="b">
         <v>1</v>
@@ -10827,7 +10847,7 @@
         <v>89.09999999999999</v>
       </c>
       <c r="H195" t="n">
-        <v>20</v>
+        <v>14.5</v>
       </c>
       <c r="I195" t="n">
         <v>18.45</v>
@@ -10842,7 +10862,7 @@
         <v>-9.029999999999999</v>
       </c>
       <c r="M195" t="n">
-        <v>16.32</v>
+        <v>11.98</v>
       </c>
       <c r="N195" t="b">
         <v>0</v>
@@ -10880,7 +10900,7 @@
         <v>50.5</v>
       </c>
       <c r="H196" t="n">
-        <v>-7.58</v>
+        <v>-12.93</v>
       </c>
       <c r="I196" t="n">
         <v>-2.26</v>
@@ -10895,7 +10915,7 @@
         <v>-20.74</v>
       </c>
       <c r="M196" t="n">
-        <v>-11.25</v>
+        <v>-15.45</v>
       </c>
       <c r="N196" t="b">
         <v>0</v>
@@ -10933,7 +10953,7 @@
         <v>33.1</v>
       </c>
       <c r="H197" t="n">
-        <v>7.15</v>
+        <v>1.56</v>
       </c>
       <c r="I197" t="n">
         <v>4.68</v>
@@ -10948,7 +10968,7 @@
         <v>-26.7</v>
       </c>
       <c r="M197" t="n">
-        <v>3.48</v>
+        <v>-0.97</v>
       </c>
       <c r="N197" t="b">
         <v>1</v>
@@ -10986,7 +11006,7 @@
         <v>46.3</v>
       </c>
       <c r="H198" t="n">
-        <v>-23.8</v>
+        <v>-27.48</v>
       </c>
       <c r="I198" t="n">
         <v>-3.24</v>
@@ -11001,7 +11021,7 @@
         <v>-22.77</v>
       </c>
       <c r="M198" t="n">
-        <v>-27.48</v>
+        <v>-30</v>
       </c>
       <c r="N198" t="b">
         <v>0</v>
@@ -11039,7 +11059,7 @@
         <v>-13.8</v>
       </c>
       <c r="H199" t="n">
-        <v>14.64</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="I199" t="n">
         <v>6.03</v>
@@ -11054,7 +11074,7 @@
         <v>-13.77</v>
       </c>
       <c r="M199" t="n">
-        <v>10.97</v>
+        <v>6.6</v>
       </c>
       <c r="N199" t="b">
         <v>0</v>
@@ -11092,7 +11112,7 @@
         <v>21.8</v>
       </c>
       <c r="H200" t="n">
-        <v>-28.51</v>
+        <v>-33.78</v>
       </c>
       <c r="I200" t="n">
         <v>-6.34</v>
@@ -11107,7 +11127,7 @@
         <v>-30.04</v>
       </c>
       <c r="M200" t="n">
-        <v>-32.18</v>
+        <v>-36.31</v>
       </c>
       <c r="N200" t="b">
         <v>1</v>
@@ -11145,7 +11165,7 @@
         <v>40.3</v>
       </c>
       <c r="H201" t="n">
-        <v>-21.3</v>
+        <v>-27.72</v>
       </c>
       <c r="I201" t="n">
         <v>1.24</v>
@@ -11160,7 +11180,7 @@
         <v>-20.5</v>
       </c>
       <c r="M201" t="n">
-        <v>-24.97</v>
+        <v>-30.25</v>
       </c>
       <c r="N201" t="b">
         <v>1</v>
@@ -11198,7 +11218,7 @@
         <v>36.6</v>
       </c>
       <c r="H202" t="n">
-        <v>297.41</v>
+        <v>266.34</v>
       </c>
       <c r="I202" t="n">
         <v>-4.23</v>
@@ -11213,7 +11233,7 @@
         <v>-11.51</v>
       </c>
       <c r="M202" t="n">
-        <v>293.74</v>
+        <v>263.82</v>
       </c>
       <c r="N202" t="b">
         <v>0</v>
@@ -11251,7 +11271,7 @@
         <v>24.1</v>
       </c>
       <c r="H203" t="n">
-        <v>-15.35</v>
+        <v>-20.32</v>
       </c>
       <c r="I203" t="n">
         <v>-1.6</v>
@@ -11266,7 +11286,7 @@
         <v>-22.54</v>
       </c>
       <c r="M203" t="n">
-        <v>-19.03</v>
+        <v>-22.85</v>
       </c>
       <c r="N203" t="b">
         <v>1</v>
@@ -11304,7 +11324,7 @@
         <v>50.3</v>
       </c>
       <c r="H204" t="n">
-        <v>-27.3</v>
+        <v>-35.27</v>
       </c>
       <c r="I204" t="n">
         <v>-3.34</v>
@@ -11319,7 +11339,7 @@
         <v>-23.32</v>
       </c>
       <c r="M204" t="n">
-        <v>-30.97</v>
+        <v>-37.79</v>
       </c>
       <c r="N204" t="b">
         <v>0</v>
@@ -11357,7 +11377,7 @@
         <v>24.5</v>
       </c>
       <c r="H205" t="n">
-        <v>-34.29</v>
+        <v>-35.8</v>
       </c>
       <c r="I205" t="n">
         <v>-12.99</v>
@@ -11372,7 +11392,7 @@
         <v>-22.54</v>
       </c>
       <c r="M205" t="n">
-        <v>-37.97</v>
+        <v>-38.32</v>
       </c>
       <c r="N205" t="b">
         <v>1</v>
@@ -11410,7 +11430,7 @@
         <v>-4</v>
       </c>
       <c r="H206" t="n">
-        <v>-30.23</v>
+        <v>-36.93</v>
       </c>
       <c r="I206" t="n">
         <v>-1.59</v>
@@ -11425,7 +11445,7 @@
         <v>-25.38</v>
       </c>
       <c r="M206" t="n">
-        <v>-33.91</v>
+        <v>-39.46</v>
       </c>
       <c r="N206" t="b">
         <v>0</v>
@@ -11463,7 +11483,7 @@
         <v>14.8</v>
       </c>
       <c r="H207" t="n">
-        <v>-37.14</v>
+        <v>-37.28</v>
       </c>
       <c r="I207" t="n">
         <v>-2.48</v>
@@ -11478,7 +11498,7 @@
         <v>-40.98</v>
       </c>
       <c r="M207" t="n">
-        <v>-40.81</v>
+        <v>-39.81</v>
       </c>
       <c r="N207" t="b">
         <v>0</v>
@@ -11516,7 +11536,7 @@
         <v>-27.6</v>
       </c>
       <c r="H208" t="n">
-        <v>-17.42</v>
+        <v>-23.05</v>
       </c>
       <c r="I208" t="n">
         <v>-0.36</v>
@@ -11531,7 +11551,7 @@
         <v>-19.41</v>
       </c>
       <c r="M208" t="n">
-        <v>-21.09</v>
+        <v>-25.58</v>
       </c>
       <c r="N208" t="b">
         <v>0</v>
@@ -11569,7 +11589,7 @@
         <v>9.1</v>
       </c>
       <c r="H209" t="n">
-        <v>-35.05</v>
+        <v>-39.89</v>
       </c>
       <c r="I209" t="n">
         <v>-2.83</v>
@@ -11584,7 +11604,7 @@
         <v>-23.78</v>
       </c>
       <c r="M209" t="n">
-        <v>-38.72</v>
+        <v>-42.41</v>
       </c>
       <c r="N209" t="b">
         <v>0</v>
@@ -11622,7 +11642,7 @@
         <v>11</v>
       </c>
       <c r="H210" t="n">
-        <v>-10.35</v>
+        <v>-16.34</v>
       </c>
       <c r="I210" t="n">
         <v>3.38</v>
@@ -11637,7 +11657,7 @@
         <v>-18.71</v>
       </c>
       <c r="M210" t="n">
-        <v>-14.03</v>
+        <v>-18.86</v>
       </c>
       <c r="N210" t="b">
         <v>0</v>
@@ -11675,7 +11695,7 @@
         <v>31.2</v>
       </c>
       <c r="H211" t="n">
-        <v>-20.7</v>
+        <v>-24.66</v>
       </c>
       <c r="I211" t="n">
         <v>-11.26</v>
@@ -11690,7 +11710,7 @@
         <v>-22.9</v>
       </c>
       <c r="M211" t="n">
-        <v>-24.37</v>
+        <v>-27.19</v>
       </c>
       <c r="N211" t="b">
         <v>0</v>
@@ -11728,7 +11748,7 @@
         <v>19.3</v>
       </c>
       <c r="H212" t="n">
-        <v>-4.89</v>
+        <v>-9.94</v>
       </c>
       <c r="I212" t="n">
         <v>11.79</v>
@@ -11743,7 +11763,7 @@
         <v>-16.62</v>
       </c>
       <c r="M212" t="n">
-        <v>-8.57</v>
+        <v>-12.46</v>
       </c>
       <c r="N212" t="b">
         <v>1</v>
@@ -11781,7 +11801,7 @@
         <v>-8.699999999999999</v>
       </c>
       <c r="H213" t="n">
-        <v>-9.24</v>
+        <v>-11.18</v>
       </c>
       <c r="I213" t="n">
         <v>17.25</v>
@@ -11796,7 +11816,7 @@
         <v>-4.65</v>
       </c>
       <c r="M213" t="n">
-        <v>-12.91</v>
+        <v>-13.71</v>
       </c>
       <c r="N213" t="b">
         <v>1</v>
@@ -11834,7 +11854,7 @@
         <v>15.2</v>
       </c>
       <c r="H214" t="n">
-        <v>-18.44</v>
+        <v>-24.2</v>
       </c>
       <c r="I214" t="n">
         <v>5.36</v>
@@ -11849,7 +11869,7 @@
         <v>-28.18</v>
       </c>
       <c r="M214" t="n">
-        <v>-22.11</v>
+        <v>-26.73</v>
       </c>
       <c r="N214" t="b">
         <v>1</v>
@@ -11887,7 +11907,7 @@
         <v>37.2</v>
       </c>
       <c r="H215" t="n">
-        <v>-34.14</v>
+        <v>-38.08</v>
       </c>
       <c r="I215" t="n">
         <v>-7.64</v>
@@ -11902,7 +11922,7 @@
         <v>-26.24</v>
       </c>
       <c r="M215" t="n">
-        <v>-37.81</v>
+        <v>-40.61</v>
       </c>
       <c r="N215" t="b">
         <v>1</v>
@@ -11944,7 +11964,7 @@
         <v>-0.5</v>
       </c>
       <c r="H216" t="n">
-        <v>49.03</v>
+        <v>45.73</v>
       </c>
       <c r="I216" t="n">
         <v>12.75</v>
@@ -11959,7 +11979,7 @@
         <v>-4.72</v>
       </c>
       <c r="M216" t="n">
-        <v>45.36</v>
+        <v>43.21</v>
       </c>
       <c r="N216" t="b">
         <v>0</v>
@@ -11997,7 +12017,7 @@
         <v>-27.9</v>
       </c>
       <c r="H217" t="n">
-        <v>-49.33</v>
+        <v>-48.97</v>
       </c>
       <c r="I217" t="n">
         <v>-5.72</v>
@@ -12012,7 +12032,7 @@
         <v>-11.08</v>
       </c>
       <c r="M217" t="n">
-        <v>-53</v>
+        <v>-51.5</v>
       </c>
       <c r="N217" t="b">
         <v>0</v>
@@ -12050,7 +12070,7 @@
         <v>29.8</v>
       </c>
       <c r="H218" t="n">
-        <v>8.59</v>
+        <v>2.96</v>
       </c>
       <c r="I218" t="n">
         <v>-2.74</v>
@@ -12065,7 +12085,7 @@
         <v>-22.36</v>
       </c>
       <c r="M218" t="n">
-        <v>4.92</v>
+        <v>0.43</v>
       </c>
       <c r="N218" t="b">
         <v>1</v>
@@ -12103,7 +12123,7 @@
         <v>60.9</v>
       </c>
       <c r="H219" t="n">
-        <v>-2.91</v>
+        <v>-5.57</v>
       </c>
       <c r="I219" t="n">
         <v>6.71</v>
@@ -12118,7 +12138,7 @@
         <v>-4.9</v>
       </c>
       <c r="M219" t="n">
-        <v>-6.58</v>
+        <v>-8.09</v>
       </c>
       <c r="N219" t="b">
         <v>0</v>
@@ -12156,7 +12176,7 @@
         <v>-13.4</v>
       </c>
       <c r="H220" t="n">
-        <v>-35.81</v>
+        <v>-40.13</v>
       </c>
       <c r="I220" t="n">
         <v>0.79</v>
@@ -12171,7 +12191,7 @@
         <v>-15.41</v>
       </c>
       <c r="M220" t="n">
-        <v>-39.48</v>
+        <v>-42.66</v>
       </c>
       <c r="N220" t="b">
         <v>0</v>
@@ -12209,7 +12229,7 @@
         <v>18.2</v>
       </c>
       <c r="H221" t="n">
-        <v>-19.06</v>
+        <v>-20.9</v>
       </c>
       <c r="I221" t="n">
         <v>-11.28</v>
@@ -12224,7 +12244,7 @@
         <v>-16.87</v>
       </c>
       <c r="M221" t="n">
-        <v>-22.73</v>
+        <v>-23.43</v>
       </c>
       <c r="N221" t="b">
         <v>0</v>
@@ -12262,7 +12282,7 @@
         <v>31.2</v>
       </c>
       <c r="H222" t="n">
-        <v>-15.35</v>
+        <v>-19.48</v>
       </c>
       <c r="I222" t="n">
         <v>-3.17</v>
@@ -12277,7 +12297,7 @@
         <v>-23.66</v>
       </c>
       <c r="M222" t="n">
-        <v>-19.03</v>
+        <v>-22</v>
       </c>
       <c r="N222" t="b">
         <v>0</v>
@@ -12315,7 +12335,7 @@
         <v>-1.3</v>
       </c>
       <c r="H223" t="n">
-        <v>-22.31</v>
+        <v>-22.81</v>
       </c>
       <c r="I223" t="n">
         <v>5.29</v>
@@ -12330,7 +12350,7 @@
         <v>-11.87</v>
       </c>
       <c r="M223" t="n">
-        <v>-25.98</v>
+        <v>-25.34</v>
       </c>
       <c r="N223" t="b">
         <v>0</v>
@@ -12368,7 +12388,7 @@
         <v>-29.8</v>
       </c>
       <c r="H224" t="n">
-        <v>43.81</v>
+        <v>29.63</v>
       </c>
       <c r="I224" t="n">
         <v>29.88</v>
@@ -12383,7 +12403,7 @@
         <v>-0.29</v>
       </c>
       <c r="M224" t="n">
-        <v>40.14</v>
+        <v>27.1</v>
       </c>
       <c r="N224" t="b">
         <v>0</v>
@@ -12421,7 +12441,7 @@
         <v>-22.4</v>
       </c>
       <c r="H225" t="n">
-        <v>-13.64</v>
+        <v>-17.79</v>
       </c>
       <c r="I225" t="n">
         <v>5.79</v>
@@ -12436,7 +12456,7 @@
         <v>-9.67</v>
       </c>
       <c r="M225" t="n">
-        <v>-17.32</v>
+        <v>-20.32</v>
       </c>
       <c r="N225" t="b">
         <v>0</v>
@@ -12474,7 +12494,7 @@
         <v>19.3</v>
       </c>
       <c r="H226" t="n">
-        <v>-34.19</v>
+        <v>-37.52</v>
       </c>
       <c r="I226" t="n">
         <v>-16.69</v>
@@ -12489,7 +12509,7 @@
         <v>-36.39</v>
       </c>
       <c r="M226" t="n">
-        <v>-37.87</v>
+        <v>-40.05</v>
       </c>
       <c r="N226" t="b">
         <v>1</v>
@@ -12527,7 +12547,7 @@
         <v>7.6</v>
       </c>
       <c r="H227" t="n">
-        <v>-23.64</v>
+        <v>-32.41</v>
       </c>
       <c r="I227" t="n">
         <v>6.22</v>
@@ -12542,7 +12562,7 @@
         <v>-10.68</v>
       </c>
       <c r="M227" t="n">
-        <v>-27.31</v>
+        <v>-34.93</v>
       </c>
       <c r="N227" t="b">
         <v>0</v>
@@ -12580,7 +12600,7 @@
         <v>68.8</v>
       </c>
       <c r="H228" t="n">
-        <v>6.89</v>
+        <v>0.52</v>
       </c>
       <c r="I228" t="n">
         <v>-1.41</v>
@@ -12595,7 +12615,7 @@
         <v>-19.39</v>
       </c>
       <c r="M228" t="n">
-        <v>3.21</v>
+        <v>-2</v>
       </c>
       <c r="N228" t="b">
         <v>0</v>
@@ -12633,7 +12653,7 @@
         <v>8.5</v>
       </c>
       <c r="H229" t="n">
-        <v>-36.82</v>
+        <v>-43.24</v>
       </c>
       <c r="I229" t="n">
         <v>-4.26</v>
@@ -12648,7 +12668,7 @@
         <v>-23.85</v>
       </c>
       <c r="M229" t="n">
-        <v>-40.5</v>
+        <v>-45.77</v>
       </c>
       <c r="N229" t="b">
         <v>0</v>
@@ -12686,7 +12706,7 @@
         <v>-15.2</v>
       </c>
       <c r="H230" t="n">
-        <v>-16.72</v>
+        <v>-23.36</v>
       </c>
       <c r="I230" t="n">
         <v>12.27</v>
@@ -12701,7 +12721,7 @@
         <v>-12.27</v>
       </c>
       <c r="M230" t="n">
-        <v>-20.39</v>
+        <v>-25.89</v>
       </c>
       <c r="N230" t="b">
         <v>0</v>
@@ -12739,7 +12759,7 @@
         <v>-33.1</v>
       </c>
       <c r="H231" t="n">
-        <v>-6.05</v>
+        <v>-5.55</v>
       </c>
       <c r="I231" t="n">
         <v>-13.13</v>
@@ -12754,7 +12774,7 @@
         <v>-21.04</v>
       </c>
       <c r="M231" t="n">
-        <v>-9.720000000000001</v>
+        <v>-8.08</v>
       </c>
       <c r="N231" t="b">
         <v>0</v>
@@ -12792,7 +12812,7 @@
         <v>11.8</v>
       </c>
       <c r="H232" t="n">
-        <v>-1.89</v>
+        <v>-5.2</v>
       </c>
       <c r="I232" t="n">
         <v>-1.19</v>
@@ -12807,7 +12827,7 @@
         <v>-17.57</v>
       </c>
       <c r="M232" t="n">
-        <v>-5.56</v>
+        <v>-7.72</v>
       </c>
       <c r="N232" t="b">
         <v>1</v>
@@ -12845,7 +12865,7 @@
         <v>27.5</v>
       </c>
       <c r="H233" t="n">
-        <v>4.86</v>
+        <v>1.6</v>
       </c>
       <c r="I233" t="n">
         <v>8.42</v>
@@ -12860,7 +12880,7 @@
         <v>-2.51</v>
       </c>
       <c r="M233" t="n">
-        <v>1.19</v>
+        <v>-0.92</v>
       </c>
       <c r="N233" t="b">
         <v>1</v>
@@ -12898,7 +12918,7 @@
         <v>-22.4</v>
       </c>
       <c r="H234" t="n">
-        <v>-7.4</v>
+        <v>-6.73</v>
       </c>
       <c r="I234" t="n">
         <v>9.42</v>
@@ -12913,7 +12933,7 @@
         <v>-2.79</v>
       </c>
       <c r="M234" t="n">
-        <v>-11.07</v>
+        <v>-9.25</v>
       </c>
       <c r="N234" t="b">
         <v>1</v>
@@ -12951,7 +12971,7 @@
         <v>-14.7</v>
       </c>
       <c r="H235" t="n">
-        <v>-18.07</v>
+        <v>-19.57</v>
       </c>
       <c r="I235" t="n">
         <v>10.3</v>
@@ -12966,7 +12986,7 @@
         <v>-2.6</v>
       </c>
       <c r="M235" t="n">
-        <v>-21.74</v>
+        <v>-22.1</v>
       </c>
       <c r="N235" t="b">
         <v>1</v>
@@ -13008,7 +13028,7 @@
         <v>-9.300000000000001</v>
       </c>
       <c r="H236" t="n">
-        <v>-21.88</v>
+        <v>-21.7</v>
       </c>
       <c r="I236" t="n">
         <v>10.42</v>
@@ -13023,7 +13043,7 @@
         <v>-21.72</v>
       </c>
       <c r="M236" t="n">
-        <v>-25.56</v>
+        <v>-24.23</v>
       </c>
       <c r="N236" t="b">
         <v>1</v>
@@ -13061,7 +13081,7 @@
         <v>-13.5</v>
       </c>
       <c r="H237" t="n">
-        <v>132.44</v>
+        <v>122.49</v>
       </c>
       <c r="I237" t="n">
         <v>18.09</v>
@@ -13076,7 +13096,7 @@
         <v>-14.35</v>
       </c>
       <c r="M237" t="n">
-        <v>128.77</v>
+        <v>119.96</v>
       </c>
       <c r="N237" t="b">
         <v>0</v>
@@ -13114,7 +13134,7 @@
         <v>-27.5</v>
       </c>
       <c r="H238" t="n">
-        <v>-3.2</v>
+        <v>-6.19</v>
       </c>
       <c r="I238" t="n">
         <v>-29.95</v>
@@ -13129,7 +13149,7 @@
         <v>-35.86</v>
       </c>
       <c r="M238" t="n">
-        <v>-6.87</v>
+        <v>-8.720000000000001</v>
       </c>
       <c r="N238" t="b">
         <v>0</v>
@@ -13167,7 +13187,7 @@
         <v>11.9</v>
       </c>
       <c r="H239" t="n">
-        <v>-52.22</v>
+        <v>-57.27</v>
       </c>
       <c r="I239" t="n">
         <v>-3.02</v>
@@ -13182,7 +13202,7 @@
         <v>-24.96</v>
       </c>
       <c r="M239" t="n">
-        <v>-55.9</v>
+        <v>-59.8</v>
       </c>
       <c r="N239" t="b">
         <v>0</v>
@@ -13220,7 +13240,7 @@
         <v>5</v>
       </c>
       <c r="H240" t="n">
-        <v>-8.880000000000001</v>
+        <v>-11.51</v>
       </c>
       <c r="I240" t="n">
         <v>0.41</v>
@@ -13235,7 +13255,7 @@
         <v>-13.87</v>
       </c>
       <c r="M240" t="n">
-        <v>-12.56</v>
+        <v>-14.04</v>
       </c>
       <c r="N240" t="b">
         <v>0</v>
@@ -13273,7 +13293,7 @@
         <v>-35.9</v>
       </c>
       <c r="H241" t="n">
-        <v>9.9</v>
+        <v>4.8</v>
       </c>
       <c r="I241" t="n">
         <v>18.67</v>
@@ -13288,7 +13308,7 @@
         <v>-6.77</v>
       </c>
       <c r="M241" t="n">
-        <v>6.23</v>
+        <v>2.27</v>
       </c>
       <c r="N241" t="b">
         <v>0</v>
@@ -13326,7 +13346,7 @@
         <v>-25.2</v>
       </c>
       <c r="H242" t="n">
-        <v>-7.08</v>
+        <v>-18.15</v>
       </c>
       <c r="I242" t="n">
         <v>22.53</v>
@@ -13341,7 +13361,7 @@
         <v>-19.27</v>
       </c>
       <c r="M242" t="n">
-        <v>-10.76</v>
+        <v>-20.68</v>
       </c>
       <c r="N242" t="b">
         <v>1</v>
@@ -13379,7 +13399,7 @@
         <v>5.1</v>
       </c>
       <c r="H243" t="n">
-        <v>6.89</v>
+        <v>5.78</v>
       </c>
       <c r="I243" t="n">
         <v>8.77</v>
@@ -13394,7 +13414,7 @@
         <v>-3.54</v>
       </c>
       <c r="M243" t="n">
-        <v>3.22</v>
+        <v>3.26</v>
       </c>
       <c r="N243" t="b">
         <v>1</v>
@@ -13432,7 +13452,7 @@
         <v>20.8</v>
       </c>
       <c r="H244" t="n">
-        <v>-29.12</v>
+        <v>-31.87</v>
       </c>
       <c r="I244" t="n">
         <v>-10.93</v>
@@ -13447,7 +13467,7 @@
         <v>-27.1</v>
       </c>
       <c r="M244" t="n">
-        <v>-32.79</v>
+        <v>-34.4</v>
       </c>
       <c r="N244" t="b">
         <v>0</v>
@@ -13485,7 +13505,7 @@
         <v>-27.7</v>
       </c>
       <c r="H245" t="n">
-        <v>9.48</v>
+        <v>3.14</v>
       </c>
       <c r="I245" t="n">
         <v>-10.22</v>
@@ -13500,7 +13520,7 @@
         <v>-17.14</v>
       </c>
       <c r="M245" t="n">
-        <v>5.81</v>
+        <v>0.61</v>
       </c>
       <c r="N245" t="b">
         <v>0</v>
@@ -13538,7 +13558,7 @@
         <v>-24.7</v>
       </c>
       <c r="H246" t="n">
-        <v>-10.9</v>
+        <v>-13.98</v>
       </c>
       <c r="I246" t="n">
         <v>1.65</v>
@@ -13553,7 +13573,7 @@
         <v>-19.04</v>
       </c>
       <c r="M246" t="n">
-        <v>-14.57</v>
+        <v>-16.51</v>
       </c>
       <c r="N246" t="b">
         <v>0</v>
@@ -13591,7 +13611,7 @@
         <v>-34.9</v>
       </c>
       <c r="H247" t="n">
-        <v>-13.84</v>
+        <v>-13.75</v>
       </c>
       <c r="I247" t="n">
         <v>19.9</v>
@@ -13606,7 +13626,7 @@
         <v>-12.62</v>
       </c>
       <c r="M247" t="n">
-        <v>-17.52</v>
+        <v>-16.27</v>
       </c>
       <c r="N247" t="b">
         <v>0</v>
@@ -13644,7 +13664,7 @@
         <v>-29.5</v>
       </c>
       <c r="H248" t="n">
-        <v>-7.28</v>
+        <v>-8.25</v>
       </c>
       <c r="I248" t="n">
         <v>4.05</v>
@@ -13659,7 +13679,7 @@
         <v>-2.43</v>
       </c>
       <c r="M248" t="n">
-        <v>-10.96</v>
+        <v>-10.78</v>
       </c>
       <c r="N248" t="b">
         <v>0</v>
@@ -13697,7 +13717,7 @@
         <v>34.2</v>
       </c>
       <c r="H249" t="n">
-        <v>4.58</v>
+        <v>1.94</v>
       </c>
       <c r="I249" t="n">
         <v>8.15</v>
@@ -13712,7 +13732,7 @@
         <v>-7.63</v>
       </c>
       <c r="M249" t="n">
-        <v>0.91</v>
+        <v>-0.58</v>
       </c>
       <c r="N249" t="b">
         <v>1</v>
@@ -13750,7 +13770,7 @@
         <v>42</v>
       </c>
       <c r="H250" t="n">
-        <v>-32.82</v>
+        <v>-33.44</v>
       </c>
       <c r="I250" t="n">
         <v>0.6</v>
@@ -13765,7 +13785,7 @@
         <v>-16.67</v>
       </c>
       <c r="M250" t="n">
-        <v>-36.5</v>
+        <v>-35.96</v>
       </c>
       <c r="N250" t="b">
         <v>1</v>
@@ -13807,7 +13827,7 @@
         <v>-0.4</v>
       </c>
       <c r="H251" t="n">
-        <v>2.79</v>
+        <v>1.28</v>
       </c>
       <c r="I251" t="n">
         <v>4.83</v>
@@ -13822,7 +13842,7 @@
         <v>-10.75</v>
       </c>
       <c r="M251" t="n">
-        <v>-0.88</v>
+        <v>-1.25</v>
       </c>
       <c r="N251" t="b">
         <v>0</v>
@@ -13860,7 +13880,7 @@
         <v>64.59999999999999</v>
       </c>
       <c r="H252" t="n">
-        <v>11.34</v>
+        <v>3.52</v>
       </c>
       <c r="I252" t="n">
         <v>3.01</v>
@@ -13875,7 +13895,7 @@
         <v>-12</v>
       </c>
       <c r="M252" t="n">
-        <v>7.67</v>
+        <v>0.99</v>
       </c>
       <c r="N252" t="b">
         <v>0</v>
@@ -13913,7 +13933,7 @@
         <v>-25.3</v>
       </c>
       <c r="H253" t="n">
-        <v>51.86</v>
+        <v>50.43</v>
       </c>
       <c r="I253" t="n">
         <v>36.1</v>
@@ -13928,7 +13948,7 @@
         <v>-5.66</v>
       </c>
       <c r="M253" t="n">
-        <v>48.19</v>
+        <v>47.9</v>
       </c>
       <c r="N253" t="b">
         <v>1</v>
@@ -13966,7 +13986,7 @@
         <v>-7.7</v>
       </c>
       <c r="H254" t="n">
-        <v>-13.61</v>
+        <v>-18.84</v>
       </c>
       <c r="I254" t="n">
         <v>-6.47</v>
@@ -13981,7 +14001,7 @@
         <v>-23.05</v>
       </c>
       <c r="M254" t="n">
-        <v>-17.28</v>
+        <v>-21.36</v>
       </c>
       <c r="N254" t="b">
         <v>1</v>
@@ -14019,7 +14039,7 @@
         <v>-2.9</v>
       </c>
       <c r="H255" t="n">
-        <v>-13.35</v>
+        <v>-14.82</v>
       </c>
       <c r="I255" t="n">
         <v>-1.47</v>
@@ -14034,7 +14054,7 @@
         <v>-7.7</v>
       </c>
       <c r="M255" t="n">
-        <v>-17.02</v>
+        <v>-17.35</v>
       </c>
       <c r="N255" t="b">
         <v>0</v>
@@ -14072,7 +14092,7 @@
         <v>13.7</v>
       </c>
       <c r="H256" t="n">
-        <v>4.38</v>
+        <v>-1.39</v>
       </c>
       <c r="I256" t="n">
         <v>2.74</v>
@@ -14087,7 +14107,7 @@
         <v>-24.02</v>
       </c>
       <c r="M256" t="n">
-        <v>0.71</v>
+        <v>-3.92</v>
       </c>
       <c r="N256" t="b">
         <v>1</v>
@@ -14125,7 +14145,7 @@
         <v>21.8</v>
       </c>
       <c r="H257" t="n">
-        <v>-18.32</v>
+        <v>-21.58</v>
       </c>
       <c r="I257" t="n">
         <v>18.32</v>
@@ -14140,7 +14160,7 @@
         <v>-23.27</v>
       </c>
       <c r="M257" t="n">
-        <v>-22</v>
+        <v>-24.11</v>
       </c>
       <c r="N257" t="b">
         <v>1</v>
@@ -14178,7 +14198,7 @@
         <v>29.4</v>
       </c>
       <c r="H258" t="n">
-        <v>-21.46</v>
+        <v>-25.27</v>
       </c>
       <c r="I258" t="n">
         <v>-2.62</v>
@@ -14193,7 +14213,7 @@
         <v>-27.18</v>
       </c>
       <c r="M258" t="n">
-        <v>-25.13</v>
+        <v>-27.8</v>
       </c>
       <c r="N258" t="b">
         <v>1</v>
@@ -14231,7 +14251,7 @@
         <v>-3.7</v>
       </c>
       <c r="H259" t="n">
-        <v>-27.92</v>
+        <v>-30.61</v>
       </c>
       <c r="I259" t="n">
         <v>-8.07</v>
@@ -14246,7 +14266,7 @@
         <v>-22.12</v>
       </c>
       <c r="M259" t="n">
-        <v>-31.59</v>
+        <v>-33.13</v>
       </c>
       <c r="N259" t="b">
         <v>1</v>
@@ -14284,7 +14304,7 @@
         <v>21.3</v>
       </c>
       <c r="H260" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="I260" t="n">
         <v>0.23</v>
@@ -14299,7 +14319,7 @@
         <v>-0.85</v>
       </c>
       <c r="M260" t="n">
-        <v>-2.22</v>
+        <v>-1.1</v>
       </c>
       <c r="N260" t="b">
         <v>1</v>
@@ -14337,7 +14357,7 @@
         <v>-21.4</v>
       </c>
       <c r="H261" t="n">
-        <v>5.73</v>
+        <v>3.96</v>
       </c>
       <c r="I261" t="n">
         <v>4.55</v>
@@ -14352,7 +14372,7 @@
         <v>-6.39</v>
       </c>
       <c r="M261" t="n">
-        <v>2.05</v>
+        <v>1.43</v>
       </c>
       <c r="N261" t="b">
         <v>1</v>
@@ -14390,7 +14410,7 @@
         <v>16.3</v>
       </c>
       <c r="H262" t="n">
-        <v>-9.93</v>
+        <v>-16.17</v>
       </c>
       <c r="I262" t="n">
         <v>-1</v>
@@ -14405,7 +14425,7 @@
         <v>-22.5</v>
       </c>
       <c r="M262" t="n">
-        <v>-13.6</v>
+        <v>-18.69</v>
       </c>
       <c r="N262" t="b">
         <v>1</v>
@@ -14443,7 +14463,7 @@
         <v>11.9</v>
       </c>
       <c r="H263" t="n">
-        <v>-8.99</v>
+        <v>-11.8</v>
       </c>
       <c r="I263" t="n">
         <v>7.74</v>
@@ -14458,7 +14478,7 @@
         <v>-9.43</v>
       </c>
       <c r="M263" t="n">
-        <v>-12.66</v>
+        <v>-14.33</v>
       </c>
       <c r="N263" t="b">
         <v>1</v>
@@ -14496,7 +14516,7 @@
         <v>19.4</v>
       </c>
       <c r="H264" t="n">
-        <v>0.95</v>
+        <v>0.86</v>
       </c>
       <c r="I264" t="n">
         <v>10.89</v>
@@ -14511,7 +14531,7 @@
         <v>-2.97</v>
       </c>
       <c r="M264" t="n">
-        <v>-2.73</v>
+        <v>-1.67</v>
       </c>
       <c r="N264" t="b">
         <v>0</v>
@@ -14549,7 +14569,7 @@
         <v>66.7</v>
       </c>
       <c r="H265" t="n">
-        <v>5.96</v>
+        <v>-2.13</v>
       </c>
       <c r="I265" t="n">
         <v>4.84</v>
@@ -14564,7 +14584,7 @@
         <v>-11.7</v>
       </c>
       <c r="M265" t="n">
-        <v>2.29</v>
+        <v>-4.66</v>
       </c>
       <c r="N265" t="b">
         <v>0</v>
@@ -14602,7 +14622,7 @@
         <v>3.7</v>
       </c>
       <c r="H266" t="n">
-        <v>22.65</v>
+        <v>22.59</v>
       </c>
       <c r="I266" t="n">
         <v>11.13</v>
@@ -14617,7 +14637,7 @@
         <v>-2.79</v>
       </c>
       <c r="M266" t="n">
-        <v>18.98</v>
+        <v>20.06</v>
       </c>
       <c r="N266" t="b">
         <v>0</v>
@@ -14655,7 +14675,7 @@
         <v>36.8</v>
       </c>
       <c r="H267" t="n">
-        <v>30.45</v>
+        <v>23.83</v>
       </c>
       <c r="I267" t="n">
         <v>15.47</v>
@@ -14670,7 +14690,7 @@
         <v>-0.96</v>
       </c>
       <c r="M267" t="n">
-        <v>26.78</v>
+        <v>21.3</v>
       </c>
       <c r="N267" t="b">
         <v>0</v>
@@ -14708,7 +14728,7 @@
         <v>0.2</v>
       </c>
       <c r="H268" t="n">
-        <v>11.85</v>
+        <v>13.94</v>
       </c>
       <c r="I268" t="n">
         <v>4.35</v>
@@ -14723,7 +14743,7 @@
         <v>-2.79</v>
       </c>
       <c r="M268" t="n">
-        <v>8.17</v>
+        <v>11.42</v>
       </c>
       <c r="N268" t="b">
         <v>1</v>
@@ -14761,7 +14781,7 @@
         <v>-31</v>
       </c>
       <c r="H269" t="n">
-        <v>-24.49</v>
+        <v>-30.94</v>
       </c>
       <c r="I269" t="n">
         <v>19.41</v>
@@ -14776,7 +14796,7 @@
         <v>-10.33</v>
       </c>
       <c r="M269" t="n">
-        <v>-28.16</v>
+        <v>-33.47</v>
       </c>
       <c r="N269" t="b">
         <v>0</v>
@@ -14818,7 +14838,7 @@
         <v>-2</v>
       </c>
       <c r="H270" t="n">
-        <v>1.75</v>
+        <v>-1.84</v>
       </c>
       <c r="I270" t="n">
         <v>14.61</v>
@@ -14833,7 +14853,7 @@
         <v>-3.45</v>
       </c>
       <c r="M270" t="n">
-        <v>-1.93</v>
+        <v>-4.36</v>
       </c>
       <c r="N270" t="b">
         <v>0</v>
@@ -14871,7 +14891,7 @@
         <v>12.2</v>
       </c>
       <c r="H271" t="n">
-        <v>-32.2</v>
+        <v>-32.71</v>
       </c>
       <c r="I271" t="n">
         <v>3.47</v>
@@ -14886,7 +14906,7 @@
         <v>-27.15</v>
       </c>
       <c r="M271" t="n">
-        <v>-35.88</v>
+        <v>-35.23</v>
       </c>
       <c r="N271" t="b">
         <v>0</v>
@@ -14924,7 +14944,7 @@
         <v>8.4</v>
       </c>
       <c r="H272" t="n">
-        <v>-37.98</v>
+        <v>-38.98</v>
       </c>
       <c r="I272" t="n">
         <v>-0.13</v>
@@ -14939,7 +14959,7 @@
         <v>-10.87</v>
       </c>
       <c r="M272" t="n">
-        <v>-41.65</v>
+        <v>-41.51</v>
       </c>
       <c r="N272" t="b">
         <v>1</v>
@@ -14977,7 +14997,7 @@
         <v>-21.7</v>
       </c>
       <c r="H273" t="n">
-        <v>-8.77</v>
+        <v>-6.44</v>
       </c>
       <c r="I273" t="n">
         <v>5.5</v>
@@ -14992,7 +15012,7 @@
         <v>-4.3</v>
       </c>
       <c r="M273" t="n">
-        <v>-12.44</v>
+        <v>-8.970000000000001</v>
       </c>
       <c r="N273" t="b">
         <v>0</v>
@@ -15030,7 +15050,7 @@
         <v>-7.3</v>
       </c>
       <c r="H274" t="n">
-        <v>-18.72</v>
+        <v>-22.04</v>
       </c>
       <c r="I274" t="n">
         <v>-4.12</v>
@@ -15045,7 +15065,7 @@
         <v>-15.02</v>
       </c>
       <c r="M274" t="n">
-        <v>-22.39</v>
+        <v>-24.57</v>
       </c>
       <c r="N274" t="b">
         <v>1</v>
@@ -15083,7 +15103,7 @@
         <v>-26.1</v>
       </c>
       <c r="H275" t="n">
-        <v>-25.18</v>
+        <v>-23.83</v>
       </c>
       <c r="I275" t="n">
         <v>5.05</v>
@@ -15098,7 +15118,7 @@
         <v>-9.27</v>
       </c>
       <c r="M275" t="n">
-        <v>-28.86</v>
+        <v>-26.36</v>
       </c>
       <c r="N275" t="b">
         <v>1</v>
@@ -15136,7 +15156,7 @@
         <v>-18.5</v>
       </c>
       <c r="H276" t="n">
-        <v>46.16</v>
+        <v>39.67</v>
       </c>
       <c r="I276" t="n">
         <v>16.22</v>
@@ -15151,7 +15171,7 @@
         <v>-9.960000000000001</v>
       </c>
       <c r="M276" t="n">
-        <v>42.48</v>
+        <v>37.14</v>
       </c>
       <c r="N276" t="b">
         <v>0</v>
@@ -15189,7 +15209,7 @@
         <v>15.3</v>
       </c>
       <c r="H277" t="n">
-        <v>-44.57</v>
+        <v>-44.74</v>
       </c>
       <c r="I277" t="n">
         <v>-21.4</v>
@@ -15204,7 +15224,7 @@
         <v>-26.97</v>
       </c>
       <c r="M277" t="n">
-        <v>-48.24</v>
+        <v>-47.27</v>
       </c>
       <c r="N277" t="b">
         <v>0</v>
@@ -15242,7 +15262,7 @@
         <v>26.1</v>
       </c>
       <c r="H278" t="n">
-        <v>-16.97</v>
+        <v>-19.34</v>
       </c>
       <c r="I278" t="n">
         <v>-0.51</v>
@@ -15257,7 +15277,7 @@
         <v>-16.45</v>
       </c>
       <c r="M278" t="n">
-        <v>-20.64</v>
+        <v>-21.86</v>
       </c>
       <c r="N278" t="b">
         <v>1</v>
@@ -15299,7 +15319,7 @@
         <v>-8.199999999999999</v>
       </c>
       <c r="H279" t="n">
-        <v>-13.88</v>
+        <v>-17.07</v>
       </c>
       <c r="I279" t="n">
         <v>17.48</v>
@@ -15314,7 +15334,7 @@
         <v>-10.68</v>
       </c>
       <c r="M279" t="n">
-        <v>-17.55</v>
+        <v>-19.6</v>
       </c>
       <c r="N279" t="b">
         <v>0</v>
@@ -15352,7 +15372,7 @@
         <v>17.9</v>
       </c>
       <c r="H280" t="n">
-        <v>-4.92</v>
+        <v>-7.58</v>
       </c>
       <c r="I280" t="n">
         <v>12.97</v>
@@ -15367,7 +15387,7 @@
         <v>-8.130000000000001</v>
       </c>
       <c r="M280" t="n">
-        <v>-8.6</v>
+        <v>-10.11</v>
       </c>
       <c r="N280" t="b">
         <v>1</v>
@@ -15405,7 +15425,7 @@
         <v>0.7</v>
       </c>
       <c r="H281" t="n">
-        <v>-21.02</v>
+        <v>-26.11</v>
       </c>
       <c r="I281" t="n">
         <v>14.96</v>
@@ -15420,7 +15440,7 @@
         <v>-8.039999999999999</v>
       </c>
       <c r="M281" t="n">
-        <v>-24.69</v>
+        <v>-28.64</v>
       </c>
       <c r="N281" t="b">
         <v>1</v>
@@ -15458,7 +15478,7 @@
         <v>61.6</v>
       </c>
       <c r="H282" t="n">
-        <v>3</v>
+        <v>-4.41</v>
       </c>
       <c r="I282" t="n">
         <v>11.47</v>
@@ -15473,7 +15493,7 @@
         <v>-12.86</v>
       </c>
       <c r="M282" t="n">
-        <v>-0.68</v>
+        <v>-6.93</v>
       </c>
       <c r="N282" t="b">
         <v>0</v>
@@ -15511,7 +15531,7 @@
         <v>54.3</v>
       </c>
       <c r="H283" t="n">
-        <v>-19.4</v>
+        <v>-20.19</v>
       </c>
       <c r="I283" t="n">
         <v>-2.86</v>
@@ -15526,7 +15546,7 @@
         <v>-24.93</v>
       </c>
       <c r="M283" t="n">
-        <v>-23.08</v>
+        <v>-22.72</v>
       </c>
       <c r="N283" t="b">
         <v>0</v>
@@ -15564,7 +15584,7 @@
         <v>14.8</v>
       </c>
       <c r="H284" t="n">
-        <v>-6.36</v>
+        <v>-7.22</v>
       </c>
       <c r="I284" t="n">
         <v>0.35</v>
@@ -15579,7 +15599,7 @@
         <v>-3.68</v>
       </c>
       <c r="M284" t="n">
-        <v>-10.03</v>
+        <v>-9.75</v>
       </c>
       <c r="N284" t="b">
         <v>1</v>
@@ -15617,7 +15637,7 @@
         <v>-13.5</v>
       </c>
       <c r="H285" t="n">
-        <v>-19.75</v>
+        <v>-21.45</v>
       </c>
       <c r="I285" t="n">
         <v>-1.88</v>
@@ -15632,7 +15652,7 @@
         <v>-11.4</v>
       </c>
       <c r="M285" t="n">
-        <v>-23.42</v>
+        <v>-23.98</v>
       </c>
       <c r="N285" t="b">
         <v>0</v>
@@ -15670,7 +15690,7 @@
         <v>25.5</v>
       </c>
       <c r="H286" t="n">
-        <v>9.02</v>
+        <v>2.3</v>
       </c>
       <c r="I286" t="n">
         <v>-9.369999999999999</v>
@@ -15685,7 +15705,7 @@
         <v>-22.11</v>
       </c>
       <c r="M286" t="n">
-        <v>5.35</v>
+        <v>-0.23</v>
       </c>
       <c r="N286" t="b">
         <v>1</v>
@@ -15727,7 +15747,7 @@
         <v>-7.5</v>
       </c>
       <c r="H287" t="n">
-        <v>-8.609999999999999</v>
+        <v>-12.1</v>
       </c>
       <c r="I287" t="n">
         <v>4.46</v>
@@ -15742,7 +15762,7 @@
         <v>-8.52</v>
       </c>
       <c r="M287" t="n">
-        <v>-12.28</v>
+        <v>-14.63</v>
       </c>
       <c r="N287" t="b">
         <v>1</v>
@@ -15780,7 +15800,7 @@
         <v>1.5</v>
       </c>
       <c r="H288" t="n">
-        <v>2.21</v>
+        <v>-1.39</v>
       </c>
       <c r="I288" t="n">
         <v>-7.31</v>
@@ -15795,7 +15815,7 @@
         <v>-18.58</v>
       </c>
       <c r="M288" t="n">
-        <v>-1.46</v>
+        <v>-3.92</v>
       </c>
       <c r="N288" t="b">
         <v>0</v>
@@ -15833,7 +15853,7 @@
         <v>-11</v>
       </c>
       <c r="H289" t="n">
-        <v>21.38</v>
+        <v>16.61</v>
       </c>
       <c r="I289" t="n">
         <v>10.7</v>
@@ -15848,7 +15868,7 @@
         <v>-9.43</v>
       </c>
       <c r="M289" t="n">
-        <v>17.71</v>
+        <v>14.08</v>
       </c>
       <c r="N289" t="b">
         <v>1</v>
@@ -15886,7 +15906,7 @@
         <v>-11.4</v>
       </c>
       <c r="H290" t="n">
-        <v>-17.09</v>
+        <v>-17.45</v>
       </c>
       <c r="I290" t="n">
         <v>4.36</v>
@@ -15901,7 +15921,7 @@
         <v>-11.36</v>
       </c>
       <c r="M290" t="n">
-        <v>-20.76</v>
+        <v>-19.98</v>
       </c>
       <c r="N290" t="b">
         <v>1</v>
@@ -15939,7 +15959,7 @@
         <v>2.1</v>
       </c>
       <c r="H291" t="n">
-        <v>74.43000000000001</v>
+        <v>73.58</v>
       </c>
       <c r="I291" t="n">
         <v>20.72</v>
@@ -15954,7 +15974,7 @@
         <v>-5.79</v>
       </c>
       <c r="M291" t="n">
-        <v>70.75</v>
+        <v>71.05</v>
       </c>
       <c r="N291" t="b">
         <v>0</v>
@@ -15992,7 +16012,7 @@
         <v>27.1</v>
       </c>
       <c r="H292" t="n">
-        <v>-18.5</v>
+        <v>-21.12</v>
       </c>
       <c r="I292" t="n">
         <v>5.02</v>
@@ -16007,7 +16027,7 @@
         <v>-14.35</v>
       </c>
       <c r="M292" t="n">
-        <v>-22.17</v>
+        <v>-23.65</v>
       </c>
       <c r="N292" t="b">
         <v>1</v>
@@ -16045,7 +16065,7 @@
         <v>-21.6</v>
       </c>
       <c r="H293" t="n">
-        <v>-17.47</v>
+        <v>-19.74</v>
       </c>
       <c r="I293" t="n">
         <v>1.22</v>
@@ -16060,7 +16080,7 @@
         <v>-6.54</v>
       </c>
       <c r="M293" t="n">
-        <v>-21.14</v>
+        <v>-22.26</v>
       </c>
       <c r="N293" t="b">
         <v>0</v>
@@ -16102,7 +16122,7 @@
         <v>-2.2</v>
       </c>
       <c r="H294" t="n">
-        <v>1.14</v>
+        <v>-3.84</v>
       </c>
       <c r="I294" t="n">
         <v>-9.050000000000001</v>
@@ -16117,7 +16137,7 @@
         <v>-18.61</v>
       </c>
       <c r="M294" t="n">
-        <v>-2.53</v>
+        <v>-6.36</v>
       </c>
       <c r="N294" t="b">
         <v>0</v>
@@ -16155,7 +16175,7 @@
         <v>0.7</v>
       </c>
       <c r="H295" t="n">
-        <v>6.16</v>
+        <v>4.18</v>
       </c>
       <c r="I295" t="n">
         <v>11.4</v>
@@ -16170,7 +16190,7 @@
         <v>-7.28</v>
       </c>
       <c r="M295" t="n">
-        <v>2.49</v>
+        <v>1.66</v>
       </c>
       <c r="N295" t="b">
         <v>0</v>
@@ -16208,7 +16228,7 @@
         <v>-31.7</v>
       </c>
       <c r="H296" t="n">
-        <v>24.8</v>
+        <v>23.7</v>
       </c>
       <c r="I296" t="n">
         <v>17.04</v>
@@ -16223,7 +16243,7 @@
         <v>-4.05</v>
       </c>
       <c r="M296" t="n">
-        <v>21.12</v>
+        <v>21.17</v>
       </c>
       <c r="N296" t="b">
         <v>0</v>
@@ -16261,7 +16281,7 @@
         <v>32.2</v>
       </c>
       <c r="H297" t="n">
-        <v>7.39</v>
+        <v>4.03</v>
       </c>
       <c r="I297" t="n">
         <v>6.49</v>
@@ -16276,7 +16296,7 @@
         <v>-3.92</v>
       </c>
       <c r="M297" t="n">
-        <v>3.72</v>
+        <v>1.5</v>
       </c>
       <c r="N297" t="b">
         <v>1</v>
@@ -16314,7 +16334,7 @@
         <v>3.2</v>
       </c>
       <c r="H298" t="n">
-        <v>-27.43</v>
+        <v>-30.78</v>
       </c>
       <c r="I298" t="n">
         <v>-10.41</v>
@@ -16329,7 +16349,7 @@
         <v>-23.7</v>
       </c>
       <c r="M298" t="n">
-        <v>-31.1</v>
+        <v>-33.31</v>
       </c>
       <c r="N298" t="b">
         <v>1</v>
@@ -16367,7 +16387,7 @@
         <v>7.3</v>
       </c>
       <c r="H299" t="n">
-        <v>3.02</v>
+        <v>5.22</v>
       </c>
       <c r="I299" t="n">
         <v>-0.57</v>
@@ -16382,7 +16402,7 @@
         <v>-5.89</v>
       </c>
       <c r="M299" t="n">
-        <v>-0.65</v>
+        <v>2.7</v>
       </c>
       <c r="N299" t="b">
         <v>1</v>
@@ -16420,7 +16440,7 @@
         <v>24.5</v>
       </c>
       <c r="H300" t="n">
-        <v>9.220000000000001</v>
+        <v>9.9</v>
       </c>
       <c r="I300" t="n">
         <v>17.24</v>
@@ -16435,7 +16455,7 @@
         <v>-0.47</v>
       </c>
       <c r="M300" t="n">
-        <v>5.54</v>
+        <v>7.38</v>
       </c>
       <c r="N300" t="b">
         <v>0</v>
@@ -16473,7 +16493,7 @@
         <v>-0.3</v>
       </c>
       <c r="H301" t="n">
-        <v>-13.02</v>
+        <v>-17.86</v>
       </c>
       <c r="I301" t="n">
         <v>17.76</v>
@@ -16488,7 +16508,7 @@
         <v>-14.18</v>
       </c>
       <c r="M301" t="n">
-        <v>-16.69</v>
+        <v>-20.38</v>
       </c>
       <c r="N301" t="b">
         <v>1</v>
@@ -16526,7 +16546,7 @@
         <v>4</v>
       </c>
       <c r="H302" t="n">
-        <v>66.76000000000001</v>
+        <v>57.28</v>
       </c>
       <c r="I302" t="n">
         <v>8.75</v>
@@ -16541,7 +16561,7 @@
         <v>-11.02</v>
       </c>
       <c r="M302" t="n">
-        <v>63.09</v>
+        <v>54.75</v>
       </c>
       <c r="N302" t="b">
         <v>0</v>
@@ -16579,7 +16599,7 @@
         <v>-6.8</v>
       </c>
       <c r="H303" t="n">
-        <v>28.24</v>
+        <v>29.22</v>
       </c>
       <c r="I303" t="n">
         <v>8.279999999999999</v>
@@ -16594,7 +16614,7 @@
         <v>-6.78</v>
       </c>
       <c r="M303" t="n">
-        <v>24.57</v>
+        <v>26.69</v>
       </c>
       <c r="N303" t="b">
         <v>1</v>
@@ -16632,7 +16652,7 @@
         <v>-42</v>
       </c>
       <c r="H304" t="n">
-        <v>49.33</v>
+        <v>35.06</v>
       </c>
       <c r="I304" t="n">
         <v>-3.61</v>
@@ -16647,7 +16667,7 @@
         <v>-11.94</v>
       </c>
       <c r="M304" t="n">
-        <v>45.66</v>
+        <v>32.53</v>
       </c>
       <c r="N304" t="b">
         <v>0</v>
@@ -16685,7 +16705,7 @@
         <v>14.6</v>
       </c>
       <c r="H305" t="n">
-        <v>0.6</v>
+        <v>-1.02</v>
       </c>
       <c r="I305" t="n">
         <v>8.539999999999999</v>
@@ -16700,7 +16720,7 @@
         <v>-13.21</v>
       </c>
       <c r="M305" t="n">
-        <v>-3.07</v>
+        <v>-3.55</v>
       </c>
       <c r="N305" t="b">
         <v>0</v>
@@ -16738,7 +16758,7 @@
         <v>34.6</v>
       </c>
       <c r="H306" t="n">
-        <v>-0.02</v>
+        <v>-1.99</v>
       </c>
       <c r="I306" t="n">
         <v>5.7</v>
@@ -16753,7 +16773,7 @@
         <v>-7.7</v>
       </c>
       <c r="M306" t="n">
-        <v>-3.69</v>
+        <v>-4.51</v>
       </c>
       <c r="N306" t="b">
         <v>1</v>
@@ -16791,7 +16811,7 @@
         <v>-37.2</v>
       </c>
       <c r="H307" t="n">
-        <v>25.18</v>
+        <v>26.23</v>
       </c>
       <c r="I307" t="n">
         <v>21.67</v>
@@ -16806,7 +16826,7 @@
         <v>-6.64</v>
       </c>
       <c r="M307" t="n">
-        <v>21.5</v>
+        <v>23.7</v>
       </c>
       <c r="N307" t="b">
         <v>0</v>
@@ -16844,7 +16864,7 @@
         <v>-31.2</v>
       </c>
       <c r="H308" t="n">
-        <v>-26.67</v>
+        <v>-27.23</v>
       </c>
       <c r="I308" t="n">
         <v>1.03</v>
@@ -16859,7 +16879,7 @@
         <v>-13.65</v>
       </c>
       <c r="M308" t="n">
-        <v>-30.35</v>
+        <v>-29.76</v>
       </c>
       <c r="N308" t="b">
         <v>0</v>
@@ -16897,7 +16917,7 @@
         <v>10.4</v>
       </c>
       <c r="H309" t="n">
-        <v>26.36</v>
+        <v>20.87</v>
       </c>
       <c r="I309" t="n">
         <v>11.05</v>
@@ -16912,7 +16932,7 @@
         <v>-5.54</v>
       </c>
       <c r="M309" t="n">
-        <v>22.69</v>
+        <v>18.35</v>
       </c>
       <c r="N309" t="b">
         <v>1</v>
@@ -16950,7 +16970,7 @@
         <v>-14.7</v>
       </c>
       <c r="H310" t="n">
-        <v>9.640000000000001</v>
+        <v>4.81</v>
       </c>
       <c r="I310" t="n">
         <v>12.94</v>
@@ -16965,7 +16985,7 @@
         <v>-2.34</v>
       </c>
       <c r="M310" t="n">
-        <v>5.97</v>
+        <v>2.28</v>
       </c>
       <c r="N310" t="b">
         <v>0</v>
@@ -17003,7 +17023,7 @@
         <v>-21.5</v>
       </c>
       <c r="H311" t="n">
-        <v>-2.16</v>
+        <v>-3.72</v>
       </c>
       <c r="I311" t="n">
         <v>10.65</v>
@@ -17018,7 +17038,7 @@
         <v>-6.89</v>
       </c>
       <c r="M311" t="n">
-        <v>-5.83</v>
+        <v>-6.25</v>
       </c>
       <c r="N311" t="b">
         <v>1</v>
@@ -17056,7 +17076,7 @@
         <v>20.2</v>
       </c>
       <c r="H312" t="n">
-        <v>-17.11</v>
+        <v>-17.66</v>
       </c>
       <c r="I312" t="n">
         <v>-1.23</v>
@@ -17071,7 +17091,7 @@
         <v>-12.56</v>
       </c>
       <c r="M312" t="n">
-        <v>-20.78</v>
+        <v>-20.19</v>
       </c>
       <c r="N312" t="b">
         <v>0</v>
@@ -17109,7 +17129,7 @@
         <v>3.5</v>
       </c>
       <c r="H313" t="n">
-        <v>56.44</v>
+        <v>59.65</v>
       </c>
       <c r="I313" t="n">
         <v>33.01</v>
@@ -17124,7 +17144,7 @@
         <v>-0.92</v>
       </c>
       <c r="M313" t="n">
-        <v>52.77</v>
+        <v>57.12</v>
       </c>
       <c r="N313" t="b">
         <v>1</v>
@@ -17162,7 +17182,7 @@
         <v>14</v>
       </c>
       <c r="H314" t="n">
-        <v>35.74</v>
+        <v>41.26</v>
       </c>
       <c r="I314" t="n">
         <v>2.89</v>
@@ -17177,7 +17197,7 @@
         <v>-1.94</v>
       </c>
       <c r="M314" t="n">
-        <v>32.06</v>
+        <v>38.73</v>
       </c>
       <c r="N314" t="b">
         <v>0</v>
@@ -17215,7 +17235,7 @@
         <v>19.8</v>
       </c>
       <c r="H315" t="n">
-        <v>5</v>
+        <v>1.66</v>
       </c>
       <c r="I315" t="n">
         <v>4.74</v>
@@ -17230,7 +17250,7 @@
         <v>-9.9</v>
       </c>
       <c r="M315" t="n">
-        <v>1.32</v>
+        <v>-0.87</v>
       </c>
       <c r="N315" t="b">
         <v>1</v>
@@ -17272,7 +17292,7 @@
         <v>-7.4</v>
       </c>
       <c r="H316" t="n">
-        <v>15.79</v>
+        <v>14.35</v>
       </c>
       <c r="I316" t="n">
         <v>-3.85</v>
@@ -17287,7 +17307,7 @@
         <v>-21.11</v>
       </c>
       <c r="M316" t="n">
-        <v>12.12</v>
+        <v>11.83</v>
       </c>
       <c r="N316" t="b">
         <v>0</v>
@@ -17325,7 +17345,7 @@
         <v>-10.8</v>
       </c>
       <c r="H317" t="n">
-        <v>4.48</v>
+        <v>6.84</v>
       </c>
       <c r="I317" t="n">
         <v>1.78</v>
@@ -17340,7 +17360,7 @@
         <v>-7.51</v>
       </c>
       <c r="M317" t="n">
-        <v>0.8</v>
+        <v>4.31</v>
       </c>
       <c r="N317" t="b">
         <v>0</v>
@@ -17378,7 +17398,7 @@
         <v>-24</v>
       </c>
       <c r="H318" t="n">
-        <v>49.71</v>
+        <v>40.84</v>
       </c>
       <c r="I318" t="n">
         <v>10.85</v>
@@ -17393,7 +17413,7 @@
         <v>-5.43</v>
       </c>
       <c r="M318" t="n">
-        <v>46.03</v>
+        <v>38.32</v>
       </c>
       <c r="N318" t="b">
         <v>0</v>
@@ -17431,7 +17451,7 @@
         <v>-28.3</v>
       </c>
       <c r="H319" t="n">
-        <v>-27.24</v>
+        <v>-30.26</v>
       </c>
       <c r="I319" t="n">
         <v>-8.949999999999999</v>
@@ -17446,7 +17466,7 @@
         <v>-13.18</v>
       </c>
       <c r="M319" t="n">
-        <v>-30.91</v>
+        <v>-32.79</v>
       </c>
       <c r="N319" t="b">
         <v>0</v>
@@ -17484,7 +17504,7 @@
         <v>-30.5</v>
       </c>
       <c r="H320" t="n">
-        <v>-1.85</v>
+        <v>-1.74</v>
       </c>
       <c r="I320" t="n">
         <v>2.96</v>
@@ -17499,7 +17519,7 @@
         <v>-17.88</v>
       </c>
       <c r="M320" t="n">
-        <v>-5.52</v>
+        <v>-4.27</v>
       </c>
       <c r="N320" t="b">
         <v>1</v>
@@ -17537,7 +17557,7 @@
         <v>-6</v>
       </c>
       <c r="H321" t="n">
-        <v>-25.06</v>
+        <v>-29.28</v>
       </c>
       <c r="I321" t="n">
         <v>3.31</v>
@@ -17552,7 +17572,7 @@
         <v>-21.48</v>
       </c>
       <c r="M321" t="n">
-        <v>-28.73</v>
+        <v>-31.81</v>
       </c>
       <c r="N321" t="b">
         <v>1</v>
@@ -17590,7 +17610,7 @@
         <v>-42.2</v>
       </c>
       <c r="H322" t="n">
-        <v>-13.07</v>
+        <v>-14.08</v>
       </c>
       <c r="I322" t="n">
         <v>19.24</v>
@@ -17605,7 +17625,7 @@
         <v>-0.93</v>
       </c>
       <c r="M322" t="n">
-        <v>-16.75</v>
+        <v>-16.61</v>
       </c>
       <c r="N322" t="b">
         <v>0</v>
@@ -17643,7 +17663,7 @@
         <v>-34.6</v>
       </c>
       <c r="H323" t="n">
-        <v>11.03</v>
+        <v>11.2</v>
       </c>
       <c r="I323" t="n">
         <v>23.65</v>
@@ -17658,7 +17678,7 @@
         <v>-3.83</v>
       </c>
       <c r="M323" t="n">
-        <v>7.35</v>
+        <v>8.67</v>
       </c>
       <c r="N323" t="b">
         <v>1</v>
@@ -17696,7 +17716,7 @@
         <v>-48.1</v>
       </c>
       <c r="H324" t="n">
-        <v>-29.22</v>
+        <v>-34.03</v>
       </c>
       <c r="I324" t="n">
         <v>2.19</v>
@@ -17711,7 +17731,7 @@
         <v>-13.66</v>
       </c>
       <c r="M324" t="n">
-        <v>-32.9</v>
+        <v>-36.56</v>
       </c>
       <c r="N324" t="b">
         <v>0</v>
@@ -17749,7 +17769,7 @@
         <v>-16.2</v>
       </c>
       <c r="H325" t="n">
-        <v>2.91</v>
+        <v>1.54</v>
       </c>
       <c r="I325" t="n">
         <v>25.77</v>
@@ -17764,7 +17784,7 @@
         <v>-1.7</v>
       </c>
       <c r="M325" t="n">
-        <v>-0.77</v>
+        <v>-0.99</v>
       </c>
       <c r="N325" t="b">
         <v>1</v>
@@ -17802,7 +17822,7 @@
         <v>-24.9</v>
       </c>
       <c r="H326" t="n">
-        <v>5.4</v>
+        <v>5.81</v>
       </c>
       <c r="I326" t="n">
         <v>10.88</v>
@@ -17817,7 +17837,7 @@
         <v>-4.1</v>
       </c>
       <c r="M326" t="n">
-        <v>1.73</v>
+        <v>3.29</v>
       </c>
       <c r="N326" t="b">
         <v>1</v>
@@ -17859,7 +17879,7 @@
         <v>-8.1</v>
       </c>
       <c r="H327" t="n">
-        <v>25.19</v>
+        <v>21.48</v>
       </c>
       <c r="I327" t="n">
         <v>14.27</v>
@@ -17874,7 +17894,7 @@
         <v>-10.92</v>
       </c>
       <c r="M327" t="n">
-        <v>21.52</v>
+        <v>18.95</v>
       </c>
       <c r="N327" t="b">
         <v>1</v>
@@ -17912,7 +17932,7 @@
         <v>-10.2</v>
       </c>
       <c r="H328" t="n">
-        <v>-13.28</v>
+        <v>-14.25</v>
       </c>
       <c r="I328" t="n">
         <v>15.03</v>
@@ -17927,7 +17947,7 @@
         <v>-1.61</v>
       </c>
       <c r="M328" t="n">
-        <v>-16.96</v>
+        <v>-16.78</v>
       </c>
       <c r="N328" t="b">
         <v>1</v>
@@ -17965,7 +17985,7 @@
         <v>68.90000000000001</v>
       </c>
       <c r="H329" t="n">
-        <v>34.95</v>
+        <v>31.12</v>
       </c>
       <c r="I329" t="n">
         <v>1.84</v>
@@ -17980,7 +18000,7 @@
         <v>-10.43</v>
       </c>
       <c r="M329" t="n">
-        <v>31.28</v>
+        <v>28.59</v>
       </c>
       <c r="N329" t="b">
         <v>1</v>
@@ -18018,7 +18038,7 @@
         <v>-40.8</v>
       </c>
       <c r="H330" t="n">
-        <v>-23.51</v>
+        <v>-23.92</v>
       </c>
       <c r="I330" t="n">
         <v>21.71</v>
@@ -18033,7 +18053,7 @@
         <v>-3.3</v>
       </c>
       <c r="M330" t="n">
-        <v>-27.19</v>
+        <v>-26.45</v>
       </c>
       <c r="N330" t="b">
         <v>1</v>
@@ -18071,7 +18091,7 @@
         <v>-10.1</v>
       </c>
       <c r="H331" t="n">
-        <v>-11.08</v>
+        <v>-8.109999999999999</v>
       </c>
       <c r="I331" t="n">
         <v>1.83</v>
@@ -18086,7 +18106,7 @@
         <v>-3.45</v>
       </c>
       <c r="M331" t="n">
-        <v>-14.75</v>
+        <v>-10.63</v>
       </c>
       <c r="N331" t="b">
         <v>0</v>
@@ -18124,7 +18144,7 @@
         <v>40.7</v>
       </c>
       <c r="H332" t="n">
-        <v>35.15</v>
+        <v>20.8</v>
       </c>
       <c r="I332" t="n">
         <v>-4.08</v>
@@ -18139,7 +18159,7 @@
         <v>-11.2</v>
       </c>
       <c r="M332" t="n">
-        <v>31.47</v>
+        <v>18.27</v>
       </c>
       <c r="N332" t="b">
         <v>1</v>
@@ -18177,7 +18197,7 @@
         <v>25.7</v>
       </c>
       <c r="H333" t="n">
-        <v>-13.25</v>
+        <v>-15.86</v>
       </c>
       <c r="I333" t="n">
         <v>11.3</v>
@@ -18192,7 +18212,7 @@
         <v>-11.03</v>
       </c>
       <c r="M333" t="n">
-        <v>-16.92</v>
+        <v>-18.39</v>
       </c>
       <c r="N333" t="b">
         <v>1</v>
@@ -18230,7 +18250,7 @@
         <v>2.3</v>
       </c>
       <c r="H334" t="n">
-        <v>-2.01</v>
+        <v>-1.12</v>
       </c>
       <c r="I334" t="n">
         <v>-0.95</v>
@@ -18245,7 +18265,7 @@
         <v>-7.81</v>
       </c>
       <c r="M334" t="n">
-        <v>-5.68</v>
+        <v>-3.65</v>
       </c>
       <c r="N334" t="b">
         <v>0</v>
@@ -18377,16 +18397,16 @@
         <v>51.4</v>
       </c>
       <c r="H2" t="n">
-        <v>-1.95</v>
+        <v>-5.98</v>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="n">
-        <v>-4.91</v>
+        <v>-7.85</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.24</v>
+        <v>-4.17</v>
       </c>
       <c r="N2" t="b">
         <v>1</v>
@@ -18413,7 +18433,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Extended</t>
         </is>
       </c>
       <c r="E3" t="inlineStr"/>
@@ -18424,7 +18444,7 @@
         <v>-16.6</v>
       </c>
       <c r="H3" t="n">
-        <v>3.33</v>
+        <v>5.26</v>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
@@ -18433,7 +18453,7 @@
         <v>-1.04</v>
       </c>
       <c r="M3" t="n">
-        <v>3.84</v>
+        <v>6.87</v>
       </c>
       <c r="N3" t="b">
         <v>1</v>
@@ -18471,7 +18491,7 @@
         <v>-5</v>
       </c>
       <c r="H4" t="n">
-        <v>6.54</v>
+        <v>8.85</v>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
@@ -18480,7 +18500,7 @@
         <v>-1.75</v>
       </c>
       <c r="M4" t="n">
-        <v>7.05</v>
+        <v>10.46</v>
       </c>
       <c r="N4" t="b">
         <v>1</v>
@@ -18518,7 +18538,7 @@
         <v>12.5</v>
       </c>
       <c r="H5" t="n">
-        <v>7.42</v>
+        <v>7.63</v>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
@@ -18527,7 +18547,7 @@
         <v>-2.59</v>
       </c>
       <c r="M5" t="n">
-        <v>7.93</v>
+        <v>9.24</v>
       </c>
       <c r="N5" t="b">
         <v>1</v>
@@ -18565,7 +18585,7 @@
         <v>-17.3</v>
       </c>
       <c r="H6" t="n">
-        <v>0.87</v>
+        <v>1.31</v>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
@@ -18574,7 +18594,7 @@
         <v>-6.51</v>
       </c>
       <c r="M6" t="n">
-        <v>1.69</v>
+        <v>3.22</v>
       </c>
       <c r="N6" t="b">
         <v>1</v>
@@ -18612,7 +18632,7 @@
         <v>-21.8</v>
       </c>
       <c r="H7" t="n">
-        <v>0.36</v>
+        <v>-1.28</v>
       </c>
       <c r="I7" t="n">
         <v>-3.37</v>
@@ -18623,7 +18643,7 @@
         <v>-5.33</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.33</v>
+        <v>-0.86</v>
       </c>
       <c r="N7" t="b">
         <v>1</v>
@@ -18661,7 +18681,7 @@
         <v>-16.7</v>
       </c>
       <c r="H8" t="n">
-        <v>29.93</v>
+        <v>29.03</v>
       </c>
       <c r="I8" t="n">
         <v>26.03</v>
@@ -18672,7 +18692,7 @@
         <v>-6.98</v>
       </c>
       <c r="M8" t="n">
-        <v>29.29</v>
+        <v>29.5</v>
       </c>
       <c r="N8" t="b">
         <v>1</v>
@@ -18710,7 +18730,7 @@
         <v>-11.5</v>
       </c>
       <c r="H9" t="n">
-        <v>14.06</v>
+        <v>16.44</v>
       </c>
       <c r="I9" t="n">
         <v>7.47</v>
@@ -18721,7 +18741,7 @@
         <v>-0.99</v>
       </c>
       <c r="M9" t="n">
-        <v>13.41</v>
+        <v>16.91</v>
       </c>
       <c r="N9" t="b">
         <v>1</v>
@@ -18759,7 +18779,7 @@
         <v>0.1</v>
       </c>
       <c r="H10" t="n">
-        <v>14.47</v>
+        <v>15.42</v>
       </c>
       <c r="I10" t="n">
         <v>6.41</v>
@@ -18770,7 +18790,7 @@
         <v>-2.51</v>
       </c>
       <c r="M10" t="n">
-        <v>14.08</v>
+        <v>16.14</v>
       </c>
       <c r="N10" t="b">
         <v>1</v>
@@ -18808,7 +18828,7 @@
         <v>-31.6</v>
       </c>
       <c r="H11" t="n">
-        <v>-3.91</v>
+        <v>-4.32</v>
       </c>
       <c r="I11" t="n">
         <v>-2.12</v>
@@ -18819,7 +18839,7 @@
         <v>-8.140000000000001</v>
       </c>
       <c r="M11" t="n">
-        <v>-4.3</v>
+        <v>-3.6</v>
       </c>
       <c r="N11" t="b">
         <v>1</v>
@@ -18857,7 +18877,7 @@
         <v>-2.7</v>
       </c>
       <c r="H12" t="n">
-        <v>-8.66</v>
+        <v>-9.380000000000001</v>
       </c>
       <c r="I12" t="n">
         <v>-3.77</v>
@@ -18868,7 +18888,7 @@
         <v>-12.44</v>
       </c>
       <c r="M12" t="n">
-        <v>-8.369999999999999</v>
+        <v>-7.98</v>
       </c>
       <c r="N12" t="b">
         <v>1</v>
@@ -18906,7 +18926,7 @@
         <v>26.9</v>
       </c>
       <c r="H13" t="n">
-        <v>1.91</v>
+        <v>-2.93</v>
       </c>
       <c r="I13" t="n">
         <v>-3.24</v>
@@ -18917,7 +18937,7 @@
         <v>-12.88</v>
       </c>
       <c r="M13" t="n">
-        <v>2.2</v>
+        <v>-1.54</v>
       </c>
       <c r="N13" t="b">
         <v>1</v>
@@ -18944,7 +18964,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Extended</t>
+          <t>Retired</t>
         </is>
       </c>
       <c r="E14" t="inlineStr"/>
@@ -18955,7 +18975,7 @@
         <v>-18.1</v>
       </c>
       <c r="H14" t="n">
-        <v>13.98</v>
+        <v>16.62</v>
       </c>
       <c r="I14" t="n">
         <v>4.46</v>
@@ -18966,7 +18986,7 @@
         <v>-2.69</v>
       </c>
       <c r="M14" t="n">
-        <v>13.26</v>
+        <v>17.01</v>
       </c>
       <c r="N14" t="b">
         <v>1</v>
@@ -18993,7 +19013,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Retired</t>
         </is>
       </c>
       <c r="E15" t="inlineStr"/>
@@ -19004,7 +19024,7 @@
         <v>-21.5</v>
       </c>
       <c r="H15" t="n">
-        <v>2.32</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I15" t="n">
         <v>-1.68</v>
@@ -19015,7 +19035,7 @@
         <v>-8.130000000000001</v>
       </c>
       <c r="M15" t="n">
-        <v>1.6</v>
+        <v>0.46</v>
       </c>
       <c r="N15" t="b">
         <v>1</v>
@@ -19053,18 +19073,20 @@
         <v>41.6</v>
       </c>
       <c r="H16" t="n">
-        <v>5.6</v>
+        <v>4.19</v>
       </c>
       <c r="I16" t="n">
         <v>3.43</v>
       </c>
-      <c r="J16" t="inlineStr"/>
+      <c r="J16" t="n">
+        <v>4.19</v>
+      </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="n">
         <v>-4.38</v>
       </c>
       <c r="M16" t="n">
-        <v>4.23</v>
+        <v>3.94</v>
       </c>
       <c r="N16" t="b">
         <v>1</v>
@@ -19102,18 +19124,20 @@
         <v>32.1</v>
       </c>
       <c r="H17" t="n">
-        <v>7.32</v>
+        <v>5.05</v>
       </c>
       <c r="I17" t="n">
         <v>-3.47</v>
       </c>
-      <c r="J17" t="inlineStr"/>
+      <c r="J17" t="n">
+        <v>5.05</v>
+      </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="n">
         <v>-6.94</v>
       </c>
       <c r="M17" t="n">
-        <v>5.94</v>
+        <v>4.8</v>
       </c>
       <c r="N17" t="b">
         <v>1</v>
@@ -19151,18 +19175,20 @@
         <v>-14.4</v>
       </c>
       <c r="H18" t="n">
-        <v>1.16</v>
+        <v>1.37</v>
       </c>
       <c r="I18" t="n">
         <v>-2.38</v>
       </c>
-      <c r="J18" t="inlineStr"/>
+      <c r="J18" t="n">
+        <v>1.37</v>
+      </c>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="n">
         <v>-6.46</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.21</v>
+        <v>1.11</v>
       </c>
       <c r="N18" t="b">
         <v>1</v>
@@ -19200,18 +19226,20 @@
         <v>-10</v>
       </c>
       <c r="H19" t="n">
-        <v>-8.07</v>
+        <v>-10.78</v>
       </c>
       <c r="I19" t="n">
         <v>-3.29</v>
       </c>
-      <c r="J19" t="inlineStr"/>
+      <c r="J19" t="n">
+        <v>-10.78</v>
+      </c>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="n">
         <v>-14.66</v>
       </c>
       <c r="M19" t="n">
-        <v>-9.44</v>
+        <v>-11.04</v>
       </c>
       <c r="N19" t="b">
         <v>1</v>
@@ -19249,18 +19277,20 @@
         <v>6.4</v>
       </c>
       <c r="H20" t="n">
-        <v>10.98</v>
+        <v>12.18</v>
       </c>
       <c r="I20" t="n">
         <v>1.48</v>
       </c>
-      <c r="J20" t="inlineStr"/>
+      <c r="J20" t="n">
+        <v>12.18</v>
+      </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="n">
         <v>-3.35</v>
       </c>
       <c r="M20" t="n">
-        <v>9.609999999999999</v>
+        <v>11.92</v>
       </c>
       <c r="N20" t="b">
         <v>1</v>
@@ -19298,7 +19328,7 @@
         <v>20.2</v>
       </c>
       <c r="H21" t="n">
-        <v>1.53</v>
+        <v>0.17</v>
       </c>
       <c r="I21" t="n">
         <v>3.45</v>
@@ -19311,7 +19341,7 @@
         <v>-1.07</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.26</v>
+        <v>-0.49</v>
       </c>
       <c r="N21" t="b">
         <v>1</v>
@@ -19349,7 +19379,7 @@
         <v>43.7</v>
       </c>
       <c r="H22" t="n">
-        <v>12.36</v>
+        <v>12.67</v>
       </c>
       <c r="I22" t="n">
         <v>3.16</v>
@@ -19362,7 +19392,7 @@
         <v>-2.44</v>
       </c>
       <c r="M22" t="n">
-        <v>10.58</v>
+        <v>12.01</v>
       </c>
       <c r="N22" t="b">
         <v>1</v>
@@ -19400,7 +19430,7 @@
         <v>1.9</v>
       </c>
       <c r="H23" t="n">
-        <v>-4.5</v>
+        <v>-4.81</v>
       </c>
       <c r="I23" t="n">
         <v>-10.64</v>
@@ -19413,7 +19443,7 @@
         <v>-14.75</v>
       </c>
       <c r="M23" t="n">
-        <v>-6.29</v>
+        <v>-5.47</v>
       </c>
       <c r="N23" t="b">
         <v>1</v>
@@ -19451,7 +19481,7 @@
         <v>37.5</v>
       </c>
       <c r="H24" t="n">
-        <v>10.05</v>
+        <v>7.86</v>
       </c>
       <c r="I24" t="n">
         <v>5.86</v>
@@ -19464,7 +19494,7 @@
         <v>-3.95</v>
       </c>
       <c r="M24" t="n">
-        <v>8.109999999999999</v>
+        <v>7.05</v>
       </c>
       <c r="N24" t="b">
         <v>1</v>
@@ -19502,7 +19532,7 @@
         <v>40.2</v>
       </c>
       <c r="H25" t="n">
-        <v>13.38</v>
+        <v>10.56</v>
       </c>
       <c r="I25" t="n">
         <v>-1.11</v>
@@ -19515,7 +19545,7 @@
         <v>-5.29</v>
       </c>
       <c r="M25" t="n">
-        <v>11.44</v>
+        <v>9.75</v>
       </c>
       <c r="N25" t="b">
         <v>1</v>
@@ -19553,7 +19583,7 @@
         <v>10.7</v>
       </c>
       <c r="H26" t="n">
-        <v>0.47</v>
+        <v>1.42</v>
       </c>
       <c r="I26" t="n">
         <v>7.3</v>
@@ -19566,7 +19596,7 @@
         <v>-3.78</v>
       </c>
       <c r="M26" t="n">
-        <v>-1.47</v>
+        <v>0.61</v>
       </c>
       <c r="N26" t="b">
         <v>1</v>
@@ -19604,7 +19634,7 @@
         <v>25.6</v>
       </c>
       <c r="H27" t="n">
-        <v>17.37</v>
+        <v>13.03</v>
       </c>
       <c r="I27" t="n">
         <v>7.71</v>
@@ -19617,7 +19647,7 @@
         <v>-4.85</v>
       </c>
       <c r="M27" t="n">
-        <v>16.2</v>
+        <v>12.97</v>
       </c>
       <c r="N27" t="b">
         <v>1</v>
@@ -19655,7 +19685,7 @@
         <v>-6.9</v>
       </c>
       <c r="H28" t="n">
-        <v>20.56</v>
+        <v>19.55</v>
       </c>
       <c r="I28" t="n">
         <v>6.44</v>
@@ -19668,7 +19698,7 @@
         <v>-4.53</v>
       </c>
       <c r="M28" t="n">
-        <v>19.3</v>
+        <v>19.41</v>
       </c>
       <c r="N28" t="b">
         <v>1</v>
@@ -19706,7 +19736,7 @@
         <v>0.3</v>
       </c>
       <c r="H29" t="n">
-        <v>-16.14</v>
+        <v>-16.32</v>
       </c>
       <c r="I29" t="n">
         <v>-10.53</v>
@@ -19719,7 +19749,7 @@
         <v>-17.73</v>
       </c>
       <c r="M29" t="n">
-        <v>-16.89</v>
+        <v>-15.97</v>
       </c>
       <c r="N29" t="b">
         <v>1</v>
@@ -19757,7 +19787,7 @@
         <v>2.8</v>
       </c>
       <c r="H30" t="n">
-        <v>0.9</v>
+        <v>-0.88</v>
       </c>
       <c r="I30" t="n">
         <v>3.18</v>
@@ -19770,7 +19800,7 @@
         <v>-0.88</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.57</v>
+        <v>-1.23</v>
       </c>
       <c r="N30" t="b">
         <v>1</v>
@@ -19808,7 +19838,7 @@
         <v>34.5</v>
       </c>
       <c r="H31" t="n">
-        <v>9.26</v>
+        <v>6.8</v>
       </c>
       <c r="I31" t="n">
         <v>0.66</v>
@@ -19821,7 +19851,7 @@
         <v>-2.64</v>
       </c>
       <c r="M31" t="n">
-        <v>7.78</v>
+        <v>6.44</v>
       </c>
       <c r="N31" t="b">
         <v>1</v>
@@ -19859,7 +19889,7 @@
         <v>24.3</v>
       </c>
       <c r="H32" t="n">
-        <v>41.06</v>
+        <v>31.13</v>
       </c>
       <c r="I32" t="n">
         <v>2.54</v>
@@ -19872,7 +19902,7 @@
         <v>-5.21</v>
       </c>
       <c r="M32" t="n">
-        <v>40.23</v>
+        <v>31.42</v>
       </c>
       <c r="N32" t="b">
         <v>1</v>
@@ -19910,7 +19940,7 @@
         <v>-16.9</v>
       </c>
       <c r="H33" t="n">
-        <v>-5.24</v>
+        <v>-5.8</v>
       </c>
       <c r="I33" t="n">
         <v>-6.47</v>
@@ -19923,7 +19953,7 @@
         <v>-11.5</v>
       </c>
       <c r="M33" t="n">
-        <v>-6.07</v>
+        <v>-5.51</v>
       </c>
       <c r="N33" t="b">
         <v>1</v>
@@ -19961,7 +19991,7 @@
         <v>20.3</v>
       </c>
       <c r="H34" t="n">
-        <v>-19.23</v>
+        <v>-19.27</v>
       </c>
       <c r="I34" t="n">
         <v>-2.07</v>
@@ -19974,7 +20004,7 @@
         <v>-17.35</v>
       </c>
       <c r="M34" t="n">
-        <v>-19.9</v>
+        <v>-18.84</v>
       </c>
       <c r="N34" t="b">
         <v>1</v>
@@ -20012,7 +20042,7 @@
         <v>0.3</v>
       </c>
       <c r="H35" t="n">
-        <v>-20.92</v>
+        <v>-22.49</v>
       </c>
       <c r="I35" t="n">
         <v>-9.9</v>
@@ -20025,7 +20055,7 @@
         <v>-21.72</v>
       </c>
       <c r="M35" t="n">
-        <v>-22.09</v>
+        <v>-22.54</v>
       </c>
       <c r="N35" t="b">
         <v>1</v>
@@ -20063,7 +20093,7 @@
         <v>49.4</v>
       </c>
       <c r="H36" t="n">
-        <v>4.01</v>
+        <v>-4.75</v>
       </c>
       <c r="I36" t="n">
         <v>2.9</v>
@@ -20076,7 +20106,7 @@
         <v>-5.67</v>
       </c>
       <c r="M36" t="n">
-        <v>3.03</v>
+        <v>-4.62</v>
       </c>
       <c r="N36" t="b">
         <v>1</v>
@@ -20114,7 +20144,7 @@
         <v>4.5</v>
       </c>
       <c r="H37" t="n">
-        <v>-4.31</v>
+        <v>-3.76</v>
       </c>
       <c r="I37" t="n">
         <v>-7.61</v>
@@ -20127,7 +20157,7 @@
         <v>-11.06</v>
       </c>
       <c r="M37" t="n">
-        <v>-5.29</v>
+        <v>-3.63</v>
       </c>
       <c r="N37" t="b">
         <v>1</v>
@@ -20165,7 +20195,7 @@
         <v>-17.9</v>
       </c>
       <c r="H38" t="n">
-        <v>3.72</v>
+        <v>5.84</v>
       </c>
       <c r="I38" t="n">
         <v>0.6</v>
@@ -20178,7 +20208,7 @@
         <v>-4.72</v>
       </c>
       <c r="M38" t="n">
-        <v>2.71</v>
+        <v>5.94</v>
       </c>
       <c r="N38" t="b">
         <v>1</v>
@@ -20229,7 +20259,7 @@
         <v>-16.43</v>
       </c>
       <c r="M39" t="n">
-        <v>-15.52</v>
+        <v>-14.41</v>
       </c>
       <c r="N39" t="b">
         <v>1</v>
@@ -20267,7 +20297,7 @@
         <v>19.4</v>
       </c>
       <c r="H40" t="n">
-        <v>-5.82</v>
+        <v>-5.31</v>
       </c>
       <c r="I40" t="n">
         <v>-10.01</v>
@@ -20280,7 +20310,7 @@
         <v>-15.23</v>
       </c>
       <c r="M40" t="n">
-        <v>-6.25</v>
+        <v>-4.63</v>
       </c>
       <c r="N40" t="b">
         <v>1</v>
@@ -20318,7 +20348,7 @@
         <v>-2.6</v>
       </c>
       <c r="H41" t="n">
-        <v>-7.92</v>
+        <v>-8.68</v>
       </c>
       <c r="I41" t="n">
         <v>-4.27</v>
@@ -20331,7 +20361,7 @@
         <v>-4.86</v>
       </c>
       <c r="M41" t="n">
-        <v>-8.57</v>
+        <v>-8.220000000000001</v>
       </c>
       <c r="N41" t="b">
         <v>1</v>
@@ -20369,7 +20399,7 @@
         <v>23.8</v>
       </c>
       <c r="H42" t="n">
-        <v>-1.13</v>
+        <v>-4.17</v>
       </c>
       <c r="I42" t="n">
         <v>1.36</v>
@@ -20382,7 +20412,7 @@
         <v>-9.94</v>
       </c>
       <c r="M42" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-2.75</v>
       </c>
       <c r="N42" t="b">
         <v>1</v>
@@ -20420,7 +20450,7 @@
         <v>38.9</v>
       </c>
       <c r="H43" t="n">
-        <v>-11.26</v>
+        <v>-10.88</v>
       </c>
       <c r="I43" t="n">
         <v>-9.220000000000001</v>
@@ -20433,7 +20463,7 @@
         <v>-9.83</v>
       </c>
       <c r="M43" t="n">
-        <v>-10.95</v>
+        <v>-9.460000000000001</v>
       </c>
       <c r="N43" t="b">
         <v>1</v>
@@ -20471,7 +20501,7 @@
         <v>43.2</v>
       </c>
       <c r="H44" t="n">
-        <v>-10.09</v>
+        <v>-9.42</v>
       </c>
       <c r="I44" t="n">
         <v>-3.15</v>
@@ -20484,7 +20514,7 @@
         <v>-17.51</v>
       </c>
       <c r="M44" t="n">
-        <v>-9.94</v>
+        <v>-8.16</v>
       </c>
       <c r="N44" t="b">
         <v>1</v>
@@ -20522,7 +20552,7 @@
         <v>-8.199999999999999</v>
       </c>
       <c r="H45" t="n">
-        <v>3.58</v>
+        <v>5.55</v>
       </c>
       <c r="I45" t="n">
         <v>5.34</v>
@@ -20535,7 +20565,7 @@
         <v>-5.27</v>
       </c>
       <c r="M45" t="n">
-        <v>3.73</v>
+        <v>6.81</v>
       </c>
       <c r="N45" t="b">
         <v>1</v>
@@ -20573,7 +20603,7 @@
         <v>-23.9</v>
       </c>
       <c r="H46" t="n">
-        <v>-6.69</v>
+        <v>-6.58</v>
       </c>
       <c r="I46" t="n">
         <v>3.28</v>
@@ -20586,7 +20616,7 @@
         <v>-4.46</v>
       </c>
       <c r="M46" t="n">
-        <v>-6.83</v>
+        <v>-5.62</v>
       </c>
       <c r="N46" t="b">
         <v>1</v>
@@ -20628,7 +20658,7 @@
         <v>-6.1</v>
       </c>
       <c r="H47" t="n">
-        <v>-16.48</v>
+        <v>-17.05</v>
       </c>
       <c r="I47" t="n">
         <v>4.9</v>
@@ -20641,7 +20671,7 @@
         <v>-9</v>
       </c>
       <c r="M47" t="n">
-        <v>-16.62</v>
+        <v>-16.08</v>
       </c>
       <c r="N47" t="b">
         <v>1</v>
@@ -20679,7 +20709,7 @@
         <v>26.7</v>
       </c>
       <c r="H48" t="n">
-        <v>-0.85</v>
+        <v>-1.14</v>
       </c>
       <c r="I48" t="n">
         <v>-0.05</v>
@@ -20692,7 +20722,7 @@
         <v>-0.87</v>
       </c>
       <c r="M48" t="n">
-        <v>-1</v>
+        <v>-0.18</v>
       </c>
       <c r="N48" t="b">
         <v>1</v>
@@ -20730,7 +20760,7 @@
         <v>-3.5</v>
       </c>
       <c r="H49" t="n">
-        <v>-2.18</v>
+        <v>-2.93</v>
       </c>
       <c r="I49" t="n">
         <v>-4.95</v>
@@ -20743,7 +20773,7 @@
         <v>-8.43</v>
       </c>
       <c r="M49" t="n">
-        <v>-2.53</v>
+        <v>-2.17</v>
       </c>
       <c r="N49" t="b">
         <v>1</v>
@@ -20781,7 +20811,7 @@
         <v>-17.9</v>
       </c>
       <c r="H50" t="n">
-        <v>-0.46</v>
+        <v>-2.15</v>
       </c>
       <c r="I50" t="n">
         <v>-0.5</v>
@@ -20794,7 +20824,7 @@
         <v>-3.43</v>
       </c>
       <c r="M50" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-1.39</v>
       </c>
       <c r="N50" t="b">
         <v>1</v>
@@ -20832,7 +20862,7 @@
         <v>53.5</v>
       </c>
       <c r="H51" t="n">
-        <v>7.03</v>
+        <v>0.58</v>
       </c>
       <c r="I51" t="n">
         <v>1.23</v>
@@ -20845,7 +20875,7 @@
         <v>-7.57</v>
       </c>
       <c r="M51" t="n">
-        <v>6.57</v>
+        <v>1.24</v>
       </c>
       <c r="N51" t="b">
         <v>1</v>
@@ -20883,7 +20913,7 @@
         <v>-1</v>
       </c>
       <c r="H52" t="n">
-        <v>-11.96</v>
+        <v>-10.84</v>
       </c>
       <c r="I52" t="n">
         <v>-6.26</v>
@@ -20896,7 +20926,7 @@
         <v>-15</v>
       </c>
       <c r="M52" t="n">
-        <v>-12.41</v>
+        <v>-10.19</v>
       </c>
       <c r="N52" t="b">
         <v>1</v>
@@ -20934,7 +20964,7 @@
         <v>29.7</v>
       </c>
       <c r="H53" t="n">
-        <v>2.81</v>
+        <v>1.27</v>
       </c>
       <c r="I53" t="n">
         <v>11.27</v>
@@ -20947,7 +20977,7 @@
         <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>2.35</v>
+        <v>1.93</v>
       </c>
       <c r="N53" t="b">
         <v>1</v>
@@ -20985,7 +21015,7 @@
         <v>15.2</v>
       </c>
       <c r="H54" t="n">
-        <v>-36.73</v>
+        <v>-39.35</v>
       </c>
       <c r="I54" t="n">
         <v>-8.77</v>
@@ -20998,7 +21028,7 @@
         <v>-24.79</v>
       </c>
       <c r="M54" t="n">
-        <v>-36.46</v>
+        <v>-37.97</v>
       </c>
       <c r="N54" t="b">
         <v>1</v>
@@ -21036,7 +21066,7 @@
         <v>22.2</v>
       </c>
       <c r="H55" t="n">
-        <v>9.67</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="I55" t="n">
         <v>1.01</v>
@@ -21049,7 +21079,7 @@
         <v>-3.94</v>
       </c>
       <c r="M55" t="n">
-        <v>9.94</v>
+        <v>11.33</v>
       </c>
       <c r="N55" t="b">
         <v>1</v>
@@ -21091,7 +21121,7 @@
         <v>-0</v>
       </c>
       <c r="H56" t="n">
-        <v>49.07</v>
+        <v>47.8</v>
       </c>
       <c r="I56" t="n">
         <v>13.5</v>
@@ -21104,7 +21134,7 @@
         <v>-2.53</v>
       </c>
       <c r="M56" t="n">
-        <v>45.83</v>
+        <v>45.7</v>
       </c>
       <c r="N56" t="b">
         <v>1</v>
@@ -21142,7 +21172,7 @@
         <v>10.5</v>
       </c>
       <c r="H57" t="n">
-        <v>16.56</v>
+        <v>16.61</v>
       </c>
       <c r="I57" t="n">
         <v>1.99</v>
@@ -21155,7 +21185,7 @@
         <v>-6.27</v>
       </c>
       <c r="M57" t="n">
-        <v>13.32</v>
+        <v>14.51</v>
       </c>
       <c r="N57" t="b">
         <v>1</v>
@@ -21193,7 +21223,7 @@
         <v>-37</v>
       </c>
       <c r="H58" t="n">
-        <v>50.36</v>
+        <v>47.83</v>
       </c>
       <c r="I58" t="n">
         <v>18.38</v>
@@ -21206,7 +21236,7 @@
         <v>-5.11</v>
       </c>
       <c r="M58" t="n">
-        <v>46.46</v>
+        <v>45.08</v>
       </c>
       <c r="N58" t="b">
         <v>1</v>
@@ -21244,7 +21274,7 @@
         <v>-26.8</v>
       </c>
       <c r="H59" t="n">
-        <v>30.62</v>
+        <v>27.37</v>
       </c>
       <c r="I59" t="n">
         <v>4.56</v>
@@ -21257,7 +21287,7 @@
         <v>-4.09</v>
       </c>
       <c r="M59" t="n">
-        <v>26.72</v>
+        <v>24.63</v>
       </c>
       <c r="N59" t="b">
         <v>1</v>
@@ -21295,7 +21325,7 @@
         <v>-36.5</v>
       </c>
       <c r="H60" t="n">
-        <v>-29.67</v>
+        <v>-34.49</v>
       </c>
       <c r="I60" t="n">
         <v>-27.75</v>
@@ -21308,7 +21338,7 @@
         <v>-31.28</v>
       </c>
       <c r="M60" t="n">
-        <v>-34.23</v>
+        <v>-37.9</v>
       </c>
       <c r="N60" t="b">
         <v>1</v>
@@ -21346,7 +21376,7 @@
         <v>-38.7</v>
       </c>
       <c r="H61" t="n">
-        <v>22.94</v>
+        <v>24.13</v>
       </c>
       <c r="I61" t="n">
         <v>17.17</v>
@@ -21359,7 +21389,7 @@
         <v>-0.54</v>
       </c>
       <c r="M61" t="n">
-        <v>18.38</v>
+        <v>20.72</v>
       </c>
       <c r="N61" t="b">
         <v>1</v>
@@ -21397,7 +21427,7 @@
         <v>-34.6</v>
       </c>
       <c r="H62" t="n">
-        <v>22.75</v>
+        <v>17.93</v>
       </c>
       <c r="I62" t="n">
         <v>6.67</v>
@@ -21410,7 +21440,7 @@
         <v>-3.06</v>
       </c>
       <c r="M62" t="n">
-        <v>18.19</v>
+        <v>14.53</v>
       </c>
       <c r="N62" t="b">
         <v>1</v>
@@ -21448,7 +21478,7 @@
         <v>-11.8</v>
       </c>
       <c r="H63" t="n">
-        <v>2.76</v>
+        <v>4.92</v>
       </c>
       <c r="I63" t="n">
         <v>9.76</v>
@@ -21461,7 +21491,7 @@
         <v>-1.63</v>
       </c>
       <c r="M63" t="n">
-        <v>-1.91</v>
+        <v>1.41</v>
       </c>
       <c r="N63" t="b">
         <v>1</v>
@@ -21499,7 +21529,7 @@
         <v>0.1</v>
       </c>
       <c r="H64" t="n">
-        <v>-7.73</v>
+        <v>-6.1</v>
       </c>
       <c r="I64" t="n">
         <v>-2.83</v>
@@ -21512,7 +21542,7 @@
         <v>-5.45</v>
       </c>
       <c r="M64" t="n">
-        <v>-12.4</v>
+        <v>-9.609999999999999</v>
       </c>
       <c r="N64" t="b">
         <v>1</v>
@@ -21550,7 +21580,7 @@
         <v>24.1</v>
       </c>
       <c r="H65" t="n">
-        <v>2.93</v>
+        <v>2.61</v>
       </c>
       <c r="I65" t="n">
         <v>-8.31</v>
@@ -21563,7 +21593,7 @@
         <v>-18.31</v>
       </c>
       <c r="M65" t="n">
-        <v>-0.93</v>
+        <v>-0.11</v>
       </c>
       <c r="N65" t="b">
         <v>1</v>
@@ -21601,7 +21631,7 @@
         <v>-15.9</v>
       </c>
       <c r="H66" t="n">
-        <v>13.57</v>
+        <v>10.88</v>
       </c>
       <c r="I66" t="n">
         <v>10.45</v>
@@ -21614,7 +21644,7 @@
         <v>-0.31</v>
       </c>
       <c r="M66" t="n">
-        <v>9.710000000000001</v>
+        <v>8.16</v>
       </c>
       <c r="N66" t="b">
         <v>1</v>
@@ -21652,7 +21682,7 @@
         <v>-21.8</v>
       </c>
       <c r="H67" t="n">
-        <v>-32.58</v>
+        <v>-35.76</v>
       </c>
       <c r="I67" t="n">
         <v>-18.97</v>
@@ -21660,12 +21690,14 @@
       <c r="J67" t="n">
         <v>-25.46</v>
       </c>
-      <c r="K67" t="inlineStr"/>
+      <c r="K67" t="n">
+        <v>-35.76</v>
+      </c>
       <c r="L67" t="n">
         <v>-26.82</v>
       </c>
       <c r="M67" t="n">
-        <v>-37.23</v>
+        <v>-39.24</v>
       </c>
       <c r="N67" t="b">
         <v>1</v>
@@ -21703,7 +21735,7 @@
         <v>57</v>
       </c>
       <c r="H68" t="n">
-        <v>34.25</v>
+        <v>34.89</v>
       </c>
       <c r="I68" t="n">
         <v>-11.21</v>
@@ -21718,7 +21750,7 @@
         <v>-13.87</v>
       </c>
       <c r="M68" t="n">
-        <v>30.63</v>
+        <v>32.41</v>
       </c>
       <c r="N68" t="b">
         <v>1</v>
@@ -21756,7 +21788,7 @@
         <v>-21.8</v>
       </c>
       <c r="H69" t="n">
-        <v>20.63</v>
+        <v>19.72</v>
       </c>
       <c r="I69" t="n">
         <v>1.71</v>
@@ -21771,7 +21803,7 @@
         <v>-6.18</v>
       </c>
       <c r="M69" t="n">
-        <v>17</v>
+        <v>17.23</v>
       </c>
       <c r="N69" t="b">
         <v>1</v>
@@ -21809,7 +21841,7 @@
         <v>1</v>
       </c>
       <c r="H70" t="n">
-        <v>-31.18</v>
+        <v>-35.53</v>
       </c>
       <c r="I70" t="n">
         <v>-11.52</v>
@@ -21824,7 +21856,7 @@
         <v>-16.26</v>
       </c>
       <c r="M70" t="n">
-        <v>-34.85</v>
+        <v>-38.06</v>
       </c>
       <c r="N70" t="b">
         <v>1</v>
@@ -21862,7 +21894,7 @@
         <v>45.4</v>
       </c>
       <c r="H71" t="n">
-        <v>-14.25</v>
+        <v>-20.2</v>
       </c>
       <c r="I71" t="n">
         <v>-1.72</v>
@@ -21877,7 +21909,7 @@
         <v>-23.15</v>
       </c>
       <c r="M71" t="n">
-        <v>-17.92</v>
+        <v>-22.73</v>
       </c>
       <c r="N71" t="b">
         <v>1</v>
@@ -21915,7 +21947,7 @@
         <v>76.5</v>
       </c>
       <c r="H72" t="n">
-        <v>-7.73</v>
+        <v>-14.05</v>
       </c>
       <c r="I72" t="n">
         <v>-5.56</v>
@@ -21930,7 +21962,7 @@
         <v>-33.97</v>
       </c>
       <c r="M72" t="n">
-        <v>-11.4</v>
+        <v>-16.58</v>
       </c>
       <c r="N72" t="b">
         <v>1</v>
@@ -21968,7 +22000,7 @@
         <v>32.1</v>
       </c>
       <c r="H73" t="n">
-        <v>-2.4</v>
+        <v>-14.29</v>
       </c>
       <c r="I73" t="n">
         <v>16.93</v>
@@ -21983,7 +22015,7 @@
         <v>-24.48</v>
       </c>
       <c r="M73" t="n">
-        <v>-6.08</v>
+        <v>-16.81</v>
       </c>
       <c r="N73" t="b">
         <v>1</v>
@@ -22021,7 +22053,7 @@
         <v>51.8</v>
       </c>
       <c r="H74" t="n">
-        <v>-7.53</v>
+        <v>-12.47</v>
       </c>
       <c r="I74" t="n">
         <v>10.75</v>
@@ -22036,7 +22068,7 @@
         <v>-25.09</v>
       </c>
       <c r="M74" t="n">
-        <v>-11.2</v>
+        <v>-15</v>
       </c>
       <c r="N74" t="b">
         <v>1</v>
@@ -22074,7 +22106,7 @@
         <v>32.3</v>
       </c>
       <c r="H75" t="n">
-        <v>-34.71</v>
+        <v>-37.91</v>
       </c>
       <c r="I75" t="n">
         <v>-20.76</v>
@@ -22089,7 +22121,7 @@
         <v>-27.91</v>
       </c>
       <c r="M75" t="n">
-        <v>-38.38</v>
+        <v>-40.44</v>
       </c>
       <c r="N75" t="b">
         <v>1</v>
@@ -22127,7 +22159,7 @@
         <v>3.7</v>
       </c>
       <c r="H76" t="n">
-        <v>-9.66</v>
+        <v>-13.68</v>
       </c>
       <c r="I76" t="n">
         <v>-1.11</v>
@@ -22142,7 +22174,7 @@
         <v>-25.46</v>
       </c>
       <c r="M76" t="n">
-        <v>-13.33</v>
+        <v>-16.21</v>
       </c>
       <c r="N76" t="b">
         <v>1</v>
@@ -22180,7 +22212,7 @@
         <v>42.4</v>
       </c>
       <c r="H77" t="n">
-        <v>-13.23</v>
+        <v>-21.77</v>
       </c>
       <c r="I77" t="n">
         <v>2.16</v>
@@ -22195,7 +22227,7 @@
         <v>-15.76</v>
       </c>
       <c r="M77" t="n">
-        <v>-16.9</v>
+        <v>-24.3</v>
       </c>
       <c r="N77" t="b">
         <v>1</v>
@@ -22233,7 +22265,7 @@
         <v>28.2</v>
       </c>
       <c r="H78" t="n">
-        <v>-10.24</v>
+        <v>-18.63</v>
       </c>
       <c r="I78" t="n">
         <v>-1.71</v>
@@ -22248,7 +22280,7 @@
         <v>-23.43</v>
       </c>
       <c r="M78" t="n">
-        <v>-13.91</v>
+        <v>-21.15</v>
       </c>
       <c r="N78" t="b">
         <v>1</v>
@@ -22286,7 +22318,7 @@
         <v>28.6</v>
       </c>
       <c r="H79" t="n">
-        <v>-0.16</v>
+        <v>-13.07</v>
       </c>
       <c r="I79" t="n">
         <v>2.81</v>
@@ -22301,7 +22333,7 @@
         <v>-18.87</v>
       </c>
       <c r="M79" t="n">
-        <v>-3.84</v>
+        <v>-15.59</v>
       </c>
       <c r="N79" t="b">
         <v>1</v>
@@ -22339,7 +22371,7 @@
         <v>33.1</v>
       </c>
       <c r="H80" t="n">
-        <v>7.15</v>
+        <v>1.56</v>
       </c>
       <c r="I80" t="n">
         <v>4.68</v>
@@ -22354,7 +22386,7 @@
         <v>-26.7</v>
       </c>
       <c r="M80" t="n">
-        <v>3.48</v>
+        <v>-0.97</v>
       </c>
       <c r="N80" t="b">
         <v>1</v>
@@ -22392,7 +22424,7 @@
         <v>21.8</v>
       </c>
       <c r="H81" t="n">
-        <v>-28.51</v>
+        <v>-33.78</v>
       </c>
       <c r="I81" t="n">
         <v>-6.34</v>
@@ -22407,7 +22439,7 @@
         <v>-30.04</v>
       </c>
       <c r="M81" t="n">
-        <v>-32.18</v>
+        <v>-36.31</v>
       </c>
       <c r="N81" t="b">
         <v>1</v>
@@ -22445,7 +22477,7 @@
         <v>40.3</v>
       </c>
       <c r="H82" t="n">
-        <v>-21.3</v>
+        <v>-27.72</v>
       </c>
       <c r="I82" t="n">
         <v>1.24</v>
@@ -22460,7 +22492,7 @@
         <v>-20.5</v>
       </c>
       <c r="M82" t="n">
-        <v>-24.97</v>
+        <v>-30.25</v>
       </c>
       <c r="N82" t="b">
         <v>1</v>
@@ -22498,7 +22530,7 @@
         <v>24.1</v>
       </c>
       <c r="H83" t="n">
-        <v>-15.35</v>
+        <v>-20.32</v>
       </c>
       <c r="I83" t="n">
         <v>-1.6</v>
@@ -22513,7 +22545,7 @@
         <v>-22.54</v>
       </c>
       <c r="M83" t="n">
-        <v>-19.03</v>
+        <v>-22.85</v>
       </c>
       <c r="N83" t="b">
         <v>1</v>
@@ -22551,7 +22583,7 @@
         <v>24.5</v>
       </c>
       <c r="H84" t="n">
-        <v>-34.29</v>
+        <v>-35.8</v>
       </c>
       <c r="I84" t="n">
         <v>-12.99</v>
@@ -22566,7 +22598,7 @@
         <v>-22.54</v>
       </c>
       <c r="M84" t="n">
-        <v>-37.97</v>
+        <v>-38.32</v>
       </c>
       <c r="N84" t="b">
         <v>1</v>
@@ -22604,7 +22636,7 @@
         <v>19.3</v>
       </c>
       <c r="H85" t="n">
-        <v>-4.89</v>
+        <v>-9.94</v>
       </c>
       <c r="I85" t="n">
         <v>11.79</v>
@@ -22619,7 +22651,7 @@
         <v>-16.62</v>
       </c>
       <c r="M85" t="n">
-        <v>-8.57</v>
+        <v>-12.46</v>
       </c>
       <c r="N85" t="b">
         <v>1</v>
@@ -22657,7 +22689,7 @@
         <v>-8.699999999999999</v>
       </c>
       <c r="H86" t="n">
-        <v>-9.24</v>
+        <v>-11.18</v>
       </c>
       <c r="I86" t="n">
         <v>17.25</v>
@@ -22672,7 +22704,7 @@
         <v>-4.65</v>
       </c>
       <c r="M86" t="n">
-        <v>-12.91</v>
+        <v>-13.71</v>
       </c>
       <c r="N86" t="b">
         <v>1</v>
@@ -22710,7 +22742,7 @@
         <v>15.2</v>
       </c>
       <c r="H87" t="n">
-        <v>-18.44</v>
+        <v>-24.2</v>
       </c>
       <c r="I87" t="n">
         <v>5.36</v>
@@ -22725,7 +22757,7 @@
         <v>-28.18</v>
       </c>
       <c r="M87" t="n">
-        <v>-22.11</v>
+        <v>-26.73</v>
       </c>
       <c r="N87" t="b">
         <v>1</v>
@@ -22763,7 +22795,7 @@
         <v>37.2</v>
       </c>
       <c r="H88" t="n">
-        <v>-34.14</v>
+        <v>-38.08</v>
       </c>
       <c r="I88" t="n">
         <v>-7.64</v>
@@ -22778,7 +22810,7 @@
         <v>-26.24</v>
       </c>
       <c r="M88" t="n">
-        <v>-37.81</v>
+        <v>-40.61</v>
       </c>
       <c r="N88" t="b">
         <v>1</v>
@@ -22816,7 +22848,7 @@
         <v>29.8</v>
       </c>
       <c r="H89" t="n">
-        <v>8.59</v>
+        <v>2.96</v>
       </c>
       <c r="I89" t="n">
         <v>-2.74</v>
@@ -22831,7 +22863,7 @@
         <v>-22.36</v>
       </c>
       <c r="M89" t="n">
-        <v>4.92</v>
+        <v>0.43</v>
       </c>
       <c r="N89" t="b">
         <v>1</v>
@@ -22869,7 +22901,7 @@
         <v>19.3</v>
       </c>
       <c r="H90" t="n">
-        <v>-34.19</v>
+        <v>-37.52</v>
       </c>
       <c r="I90" t="n">
         <v>-16.69</v>
@@ -22884,7 +22916,7 @@
         <v>-36.39</v>
       </c>
       <c r="M90" t="n">
-        <v>-37.87</v>
+        <v>-40.05</v>
       </c>
       <c r="N90" t="b">
         <v>1</v>
@@ -22922,7 +22954,7 @@
         <v>11.8</v>
       </c>
       <c r="H91" t="n">
-        <v>-1.89</v>
+        <v>-5.2</v>
       </c>
       <c r="I91" t="n">
         <v>-1.19</v>
@@ -22937,7 +22969,7 @@
         <v>-17.57</v>
       </c>
       <c r="M91" t="n">
-        <v>-5.56</v>
+        <v>-7.72</v>
       </c>
       <c r="N91" t="b">
         <v>1</v>
@@ -22975,7 +23007,7 @@
         <v>27.5</v>
       </c>
       <c r="H92" t="n">
-        <v>4.86</v>
+        <v>1.6</v>
       </c>
       <c r="I92" t="n">
         <v>8.42</v>
@@ -22990,7 +23022,7 @@
         <v>-2.51</v>
       </c>
       <c r="M92" t="n">
-        <v>1.19</v>
+        <v>-0.92</v>
       </c>
       <c r="N92" t="b">
         <v>1</v>
@@ -23028,7 +23060,7 @@
         <v>-22.4</v>
       </c>
       <c r="H93" t="n">
-        <v>-7.4</v>
+        <v>-6.73</v>
       </c>
       <c r="I93" t="n">
         <v>9.42</v>
@@ -23043,7 +23075,7 @@
         <v>-2.79</v>
       </c>
       <c r="M93" t="n">
-        <v>-11.07</v>
+        <v>-9.25</v>
       </c>
       <c r="N93" t="b">
         <v>1</v>
@@ -23081,7 +23113,7 @@
         <v>-14.7</v>
       </c>
       <c r="H94" t="n">
-        <v>-18.07</v>
+        <v>-19.57</v>
       </c>
       <c r="I94" t="n">
         <v>10.3</v>
@@ -23096,7 +23128,7 @@
         <v>-2.6</v>
       </c>
       <c r="M94" t="n">
-        <v>-21.74</v>
+        <v>-22.1</v>
       </c>
       <c r="N94" t="b">
         <v>1</v>
@@ -23138,7 +23170,7 @@
         <v>-9.300000000000001</v>
       </c>
       <c r="H95" t="n">
-        <v>-21.88</v>
+        <v>-21.7</v>
       </c>
       <c r="I95" t="n">
         <v>10.42</v>
@@ -23153,7 +23185,7 @@
         <v>-21.72</v>
       </c>
       <c r="M95" t="n">
-        <v>-25.56</v>
+        <v>-24.23</v>
       </c>
       <c r="N95" t="b">
         <v>1</v>
@@ -23191,7 +23223,7 @@
         <v>-25.2</v>
       </c>
       <c r="H96" t="n">
-        <v>-7.08</v>
+        <v>-18.15</v>
       </c>
       <c r="I96" t="n">
         <v>22.53</v>
@@ -23206,7 +23238,7 @@
         <v>-19.27</v>
       </c>
       <c r="M96" t="n">
-        <v>-10.76</v>
+        <v>-20.68</v>
       </c>
       <c r="N96" t="b">
         <v>1</v>
@@ -23244,7 +23276,7 @@
         <v>5.1</v>
       </c>
       <c r="H97" t="n">
-        <v>6.89</v>
+        <v>5.78</v>
       </c>
       <c r="I97" t="n">
         <v>8.77</v>
@@ -23259,7 +23291,7 @@
         <v>-3.54</v>
       </c>
       <c r="M97" t="n">
-        <v>3.22</v>
+        <v>3.26</v>
       </c>
       <c r="N97" t="b">
         <v>1</v>
@@ -23297,7 +23329,7 @@
         <v>34.2</v>
       </c>
       <c r="H98" t="n">
-        <v>4.58</v>
+        <v>1.94</v>
       </c>
       <c r="I98" t="n">
         <v>8.15</v>
@@ -23312,7 +23344,7 @@
         <v>-7.63</v>
       </c>
       <c r="M98" t="n">
-        <v>0.91</v>
+        <v>-0.58</v>
       </c>
       <c r="N98" t="b">
         <v>1</v>
@@ -23350,7 +23382,7 @@
         <v>42</v>
       </c>
       <c r="H99" t="n">
-        <v>-32.82</v>
+        <v>-33.44</v>
       </c>
       <c r="I99" t="n">
         <v>0.6</v>
@@ -23365,7 +23397,7 @@
         <v>-16.67</v>
       </c>
       <c r="M99" t="n">
-        <v>-36.5</v>
+        <v>-35.96</v>
       </c>
       <c r="N99" t="b">
         <v>1</v>
@@ -23403,7 +23435,7 @@
         <v>-25.3</v>
       </c>
       <c r="H100" t="n">
-        <v>51.86</v>
+        <v>50.43</v>
       </c>
       <c r="I100" t="n">
         <v>36.1</v>
@@ -23418,7 +23450,7 @@
         <v>-5.66</v>
       </c>
       <c r="M100" t="n">
-        <v>48.19</v>
+        <v>47.9</v>
       </c>
       <c r="N100" t="b">
         <v>1</v>
@@ -23456,7 +23488,7 @@
         <v>-7.7</v>
       </c>
       <c r="H101" t="n">
-        <v>-13.61</v>
+        <v>-18.84</v>
       </c>
       <c r="I101" t="n">
         <v>-6.47</v>
@@ -23471,7 +23503,7 @@
         <v>-23.05</v>
       </c>
       <c r="M101" t="n">
-        <v>-17.28</v>
+        <v>-21.36</v>
       </c>
       <c r="N101" t="b">
         <v>1</v>
@@ -23509,7 +23541,7 @@
         <v>13.7</v>
       </c>
       <c r="H102" t="n">
-        <v>4.38</v>
+        <v>-1.39</v>
       </c>
       <c r="I102" t="n">
         <v>2.74</v>
@@ -23524,7 +23556,7 @@
         <v>-24.02</v>
       </c>
       <c r="M102" t="n">
-        <v>0.71</v>
+        <v>-3.92</v>
       </c>
       <c r="N102" t="b">
         <v>1</v>
@@ -23562,7 +23594,7 @@
         <v>21.8</v>
       </c>
       <c r="H103" t="n">
-        <v>-18.32</v>
+        <v>-21.58</v>
       </c>
       <c r="I103" t="n">
         <v>18.32</v>
@@ -23577,7 +23609,7 @@
         <v>-23.27</v>
       </c>
       <c r="M103" t="n">
-        <v>-22</v>
+        <v>-24.11</v>
       </c>
       <c r="N103" t="b">
         <v>1</v>
@@ -23615,7 +23647,7 @@
         <v>29.4</v>
       </c>
       <c r="H104" t="n">
-        <v>-21.46</v>
+        <v>-25.27</v>
       </c>
       <c r="I104" t="n">
         <v>-2.62</v>
@@ -23630,7 +23662,7 @@
         <v>-27.18</v>
       </c>
       <c r="M104" t="n">
-        <v>-25.13</v>
+        <v>-27.8</v>
       </c>
       <c r="N104" t="b">
         <v>1</v>
@@ -23668,7 +23700,7 @@
         <v>-3.7</v>
       </c>
       <c r="H105" t="n">
-        <v>-27.92</v>
+        <v>-30.61</v>
       </c>
       <c r="I105" t="n">
         <v>-8.07</v>
@@ -23683,7 +23715,7 @@
         <v>-22.12</v>
       </c>
       <c r="M105" t="n">
-        <v>-31.59</v>
+        <v>-33.13</v>
       </c>
       <c r="N105" t="b">
         <v>1</v>
@@ -23721,7 +23753,7 @@
         <v>21.3</v>
       </c>
       <c r="H106" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="I106" t="n">
         <v>0.23</v>
@@ -23736,7 +23768,7 @@
         <v>-0.85</v>
       </c>
       <c r="M106" t="n">
-        <v>-2.22</v>
+        <v>-1.1</v>
       </c>
       <c r="N106" t="b">
         <v>1</v>
@@ -23774,7 +23806,7 @@
         <v>-21.4</v>
       </c>
       <c r="H107" t="n">
-        <v>5.73</v>
+        <v>3.96</v>
       </c>
       <c r="I107" t="n">
         <v>4.55</v>
@@ -23789,7 +23821,7 @@
         <v>-6.39</v>
       </c>
       <c r="M107" t="n">
-        <v>2.05</v>
+        <v>1.43</v>
       </c>
       <c r="N107" t="b">
         <v>1</v>
@@ -23827,7 +23859,7 @@
         <v>16.3</v>
       </c>
       <c r="H108" t="n">
-        <v>-9.93</v>
+        <v>-16.17</v>
       </c>
       <c r="I108" t="n">
         <v>-1</v>
@@ -23842,7 +23874,7 @@
         <v>-22.5</v>
       </c>
       <c r="M108" t="n">
-        <v>-13.6</v>
+        <v>-18.69</v>
       </c>
       <c r="N108" t="b">
         <v>1</v>
@@ -23880,7 +23912,7 @@
         <v>11.9</v>
       </c>
       <c r="H109" t="n">
-        <v>-8.99</v>
+        <v>-11.8</v>
       </c>
       <c r="I109" t="n">
         <v>7.74</v>
@@ -23895,7 +23927,7 @@
         <v>-9.43</v>
       </c>
       <c r="M109" t="n">
-        <v>-12.66</v>
+        <v>-14.33</v>
       </c>
       <c r="N109" t="b">
         <v>1</v>
@@ -23933,7 +23965,7 @@
         <v>0.2</v>
       </c>
       <c r="H110" t="n">
-        <v>11.85</v>
+        <v>13.94</v>
       </c>
       <c r="I110" t="n">
         <v>4.35</v>
@@ -23948,7 +23980,7 @@
         <v>-2.79</v>
       </c>
       <c r="M110" t="n">
-        <v>8.17</v>
+        <v>11.42</v>
       </c>
       <c r="N110" t="b">
         <v>1</v>
@@ -23986,7 +24018,7 @@
         <v>8.4</v>
       </c>
       <c r="H111" t="n">
-        <v>-37.98</v>
+        <v>-38.98</v>
       </c>
       <c r="I111" t="n">
         <v>-0.13</v>
@@ -24001,7 +24033,7 @@
         <v>-10.87</v>
       </c>
       <c r="M111" t="n">
-        <v>-41.65</v>
+        <v>-41.51</v>
       </c>
       <c r="N111" t="b">
         <v>1</v>
@@ -24039,7 +24071,7 @@
         <v>-7.3</v>
       </c>
       <c r="H112" t="n">
-        <v>-18.72</v>
+        <v>-22.04</v>
       </c>
       <c r="I112" t="n">
         <v>-4.12</v>
@@ -24054,7 +24086,7 @@
         <v>-15.02</v>
       </c>
       <c r="M112" t="n">
-        <v>-22.39</v>
+        <v>-24.57</v>
       </c>
       <c r="N112" t="b">
         <v>1</v>
@@ -24092,7 +24124,7 @@
         <v>-26.1</v>
       </c>
       <c r="H113" t="n">
-        <v>-25.18</v>
+        <v>-23.83</v>
       </c>
       <c r="I113" t="n">
         <v>5.05</v>
@@ -24107,7 +24139,7 @@
         <v>-9.27</v>
       </c>
       <c r="M113" t="n">
-        <v>-28.86</v>
+        <v>-26.36</v>
       </c>
       <c r="N113" t="b">
         <v>1</v>
@@ -24145,7 +24177,7 @@
         <v>26.1</v>
       </c>
       <c r="H114" t="n">
-        <v>-16.97</v>
+        <v>-19.34</v>
       </c>
       <c r="I114" t="n">
         <v>-0.51</v>
@@ -24160,7 +24192,7 @@
         <v>-16.45</v>
       </c>
       <c r="M114" t="n">
-        <v>-20.64</v>
+        <v>-21.86</v>
       </c>
       <c r="N114" t="b">
         <v>1</v>
@@ -24198,7 +24230,7 @@
         <v>17.9</v>
       </c>
       <c r="H115" t="n">
-        <v>-4.92</v>
+        <v>-7.58</v>
       </c>
       <c r="I115" t="n">
         <v>12.97</v>
@@ -24213,7 +24245,7 @@
         <v>-8.130000000000001</v>
       </c>
       <c r="M115" t="n">
-        <v>-8.6</v>
+        <v>-10.11</v>
       </c>
       <c r="N115" t="b">
         <v>1</v>
@@ -24251,7 +24283,7 @@
         <v>0.7</v>
       </c>
       <c r="H116" t="n">
-        <v>-21.02</v>
+        <v>-26.11</v>
       </c>
       <c r="I116" t="n">
         <v>14.96</v>
@@ -24266,7 +24298,7 @@
         <v>-8.039999999999999</v>
       </c>
       <c r="M116" t="n">
-        <v>-24.69</v>
+        <v>-28.64</v>
       </c>
       <c r="N116" t="b">
         <v>1</v>
@@ -24304,7 +24336,7 @@
         <v>14.8</v>
       </c>
       <c r="H117" t="n">
-        <v>-6.36</v>
+        <v>-7.22</v>
       </c>
       <c r="I117" t="n">
         <v>0.35</v>
@@ -24319,7 +24351,7 @@
         <v>-3.68</v>
       </c>
       <c r="M117" t="n">
-        <v>-10.03</v>
+        <v>-9.75</v>
       </c>
       <c r="N117" t="b">
         <v>1</v>
@@ -24357,7 +24389,7 @@
         <v>25.5</v>
       </c>
       <c r="H118" t="n">
-        <v>9.02</v>
+        <v>2.3</v>
       </c>
       <c r="I118" t="n">
         <v>-9.369999999999999</v>
@@ -24372,7 +24404,7 @@
         <v>-22.11</v>
       </c>
       <c r="M118" t="n">
-        <v>5.35</v>
+        <v>-0.23</v>
       </c>
       <c r="N118" t="b">
         <v>1</v>
@@ -24414,7 +24446,7 @@
         <v>-7.5</v>
       </c>
       <c r="H119" t="n">
-        <v>-8.609999999999999</v>
+        <v>-12.1</v>
       </c>
       <c r="I119" t="n">
         <v>4.46</v>
@@ -24429,7 +24461,7 @@
         <v>-8.52</v>
       </c>
       <c r="M119" t="n">
-        <v>-12.28</v>
+        <v>-14.63</v>
       </c>
       <c r="N119" t="b">
         <v>1</v>
@@ -24467,7 +24499,7 @@
         <v>-11</v>
       </c>
       <c r="H120" t="n">
-        <v>21.38</v>
+        <v>16.61</v>
       </c>
       <c r="I120" t="n">
         <v>10.7</v>
@@ -24482,7 +24514,7 @@
         <v>-9.43</v>
       </c>
       <c r="M120" t="n">
-        <v>17.71</v>
+        <v>14.08</v>
       </c>
       <c r="N120" t="b">
         <v>1</v>
@@ -24520,7 +24552,7 @@
         <v>-11.4</v>
       </c>
       <c r="H121" t="n">
-        <v>-17.09</v>
+        <v>-17.45</v>
       </c>
       <c r="I121" t="n">
         <v>4.36</v>
@@ -24535,7 +24567,7 @@
         <v>-11.36</v>
       </c>
       <c r="M121" t="n">
-        <v>-20.76</v>
+        <v>-19.98</v>
       </c>
       <c r="N121" t="b">
         <v>1</v>
@@ -24573,7 +24605,7 @@
         <v>27.1</v>
       </c>
       <c r="H122" t="n">
-        <v>-18.5</v>
+        <v>-21.12</v>
       </c>
       <c r="I122" t="n">
         <v>5.02</v>
@@ -24588,7 +24620,7 @@
         <v>-14.35</v>
       </c>
       <c r="M122" t="n">
-        <v>-22.17</v>
+        <v>-23.65</v>
       </c>
       <c r="N122" t="b">
         <v>1</v>
@@ -24626,7 +24658,7 @@
         <v>32.2</v>
       </c>
       <c r="H123" t="n">
-        <v>7.39</v>
+        <v>4.03</v>
       </c>
       <c r="I123" t="n">
         <v>6.49</v>
@@ -24641,7 +24673,7 @@
         <v>-3.92</v>
       </c>
       <c r="M123" t="n">
-        <v>3.72</v>
+        <v>1.5</v>
       </c>
       <c r="N123" t="b">
         <v>1</v>
@@ -24679,7 +24711,7 @@
         <v>3.2</v>
       </c>
       <c r="H124" t="n">
-        <v>-27.43</v>
+        <v>-30.78</v>
       </c>
       <c r="I124" t="n">
         <v>-10.41</v>
@@ -24694,7 +24726,7 @@
         <v>-23.7</v>
       </c>
       <c r="M124" t="n">
-        <v>-31.1</v>
+        <v>-33.31</v>
       </c>
       <c r="N124" t="b">
         <v>1</v>
@@ -24732,7 +24764,7 @@
         <v>7.3</v>
       </c>
       <c r="H125" t="n">
-        <v>3.02</v>
+        <v>5.22</v>
       </c>
       <c r="I125" t="n">
         <v>-0.57</v>
@@ -24747,7 +24779,7 @@
         <v>-5.89</v>
       </c>
       <c r="M125" t="n">
-        <v>-0.65</v>
+        <v>2.7</v>
       </c>
       <c r="N125" t="b">
         <v>1</v>
@@ -24785,7 +24817,7 @@
         <v>-0.3</v>
       </c>
       <c r="H126" t="n">
-        <v>-13.02</v>
+        <v>-17.86</v>
       </c>
       <c r="I126" t="n">
         <v>17.76</v>
@@ -24800,7 +24832,7 @@
         <v>-14.18</v>
       </c>
       <c r="M126" t="n">
-        <v>-16.69</v>
+        <v>-20.38</v>
       </c>
       <c r="N126" t="b">
         <v>1</v>
@@ -24838,7 +24870,7 @@
         <v>-6.8</v>
       </c>
       <c r="H127" t="n">
-        <v>28.24</v>
+        <v>29.22</v>
       </c>
       <c r="I127" t="n">
         <v>8.279999999999999</v>
@@ -24853,7 +24885,7 @@
         <v>-6.78</v>
       </c>
       <c r="M127" t="n">
-        <v>24.57</v>
+        <v>26.69</v>
       </c>
       <c r="N127" t="b">
         <v>1</v>
@@ -24891,7 +24923,7 @@
         <v>34.6</v>
       </c>
       <c r="H128" t="n">
-        <v>-0.02</v>
+        <v>-1.99</v>
       </c>
       <c r="I128" t="n">
         <v>5.7</v>
@@ -24906,7 +24938,7 @@
         <v>-7.7</v>
       </c>
       <c r="M128" t="n">
-        <v>-3.69</v>
+        <v>-4.51</v>
       </c>
       <c r="N128" t="b">
         <v>1</v>
@@ -24944,7 +24976,7 @@
         <v>10.4</v>
       </c>
       <c r="H129" t="n">
-        <v>26.36</v>
+        <v>20.87</v>
       </c>
       <c r="I129" t="n">
         <v>11.05</v>
@@ -24959,7 +24991,7 @@
         <v>-5.54</v>
       </c>
       <c r="M129" t="n">
-        <v>22.69</v>
+        <v>18.35</v>
       </c>
       <c r="N129" t="b">
         <v>1</v>
@@ -24997,7 +25029,7 @@
         <v>-21.5</v>
       </c>
       <c r="H130" t="n">
-        <v>-2.16</v>
+        <v>-3.72</v>
       </c>
       <c r="I130" t="n">
         <v>10.65</v>
@@ -25012,7 +25044,7 @@
         <v>-6.89</v>
       </c>
       <c r="M130" t="n">
-        <v>-5.83</v>
+        <v>-6.25</v>
       </c>
       <c r="N130" t="b">
         <v>1</v>
@@ -25050,7 +25082,7 @@
         <v>3.5</v>
       </c>
       <c r="H131" t="n">
-        <v>56.44</v>
+        <v>59.65</v>
       </c>
       <c r="I131" t="n">
         <v>33.01</v>
@@ -25065,7 +25097,7 @@
         <v>-0.92</v>
       </c>
       <c r="M131" t="n">
-        <v>52.77</v>
+        <v>57.12</v>
       </c>
       <c r="N131" t="b">
         <v>1</v>
@@ -25103,7 +25135,7 @@
         <v>19.8</v>
       </c>
       <c r="H132" t="n">
-        <v>5</v>
+        <v>1.66</v>
       </c>
       <c r="I132" t="n">
         <v>4.74</v>
@@ -25118,7 +25150,7 @@
         <v>-9.9</v>
       </c>
       <c r="M132" t="n">
-        <v>1.32</v>
+        <v>-0.87</v>
       </c>
       <c r="N132" t="b">
         <v>1</v>
@@ -25156,7 +25188,7 @@
         <v>-30.5</v>
       </c>
       <c r="H133" t="n">
-        <v>-1.85</v>
+        <v>-1.74</v>
       </c>
       <c r="I133" t="n">
         <v>2.96</v>
@@ -25171,7 +25203,7 @@
         <v>-17.88</v>
       </c>
       <c r="M133" t="n">
-        <v>-5.52</v>
+        <v>-4.27</v>
       </c>
       <c r="N133" t="b">
         <v>1</v>
@@ -25209,7 +25241,7 @@
         <v>-6</v>
       </c>
       <c r="H134" t="n">
-        <v>-25.06</v>
+        <v>-29.28</v>
       </c>
       <c r="I134" t="n">
         <v>3.31</v>
@@ -25224,7 +25256,7 @@
         <v>-21.48</v>
       </c>
       <c r="M134" t="n">
-        <v>-28.73</v>
+        <v>-31.81</v>
       </c>
       <c r="N134" t="b">
         <v>1</v>
@@ -25262,7 +25294,7 @@
         <v>-34.6</v>
       </c>
       <c r="H135" t="n">
-        <v>11.03</v>
+        <v>11.2</v>
       </c>
       <c r="I135" t="n">
         <v>23.65</v>
@@ -25277,7 +25309,7 @@
         <v>-3.83</v>
       </c>
       <c r="M135" t="n">
-        <v>7.35</v>
+        <v>8.67</v>
       </c>
       <c r="N135" t="b">
         <v>1</v>
@@ -25315,7 +25347,7 @@
         <v>-16.2</v>
       </c>
       <c r="H136" t="n">
-        <v>2.91</v>
+        <v>1.54</v>
       </c>
       <c r="I136" t="n">
         <v>25.77</v>
@@ -25330,7 +25362,7 @@
         <v>-1.7</v>
       </c>
       <c r="M136" t="n">
-        <v>-0.77</v>
+        <v>-0.99</v>
       </c>
       <c r="N136" t="b">
         <v>1</v>
@@ -25368,7 +25400,7 @@
         <v>-24.9</v>
       </c>
       <c r="H137" t="n">
-        <v>5.4</v>
+        <v>5.81</v>
       </c>
       <c r="I137" t="n">
         <v>10.88</v>
@@ -25383,7 +25415,7 @@
         <v>-4.1</v>
       </c>
       <c r="M137" t="n">
-        <v>1.73</v>
+        <v>3.29</v>
       </c>
       <c r="N137" t="b">
         <v>1</v>
@@ -25425,7 +25457,7 @@
         <v>-8.1</v>
       </c>
       <c r="H138" t="n">
-        <v>25.19</v>
+        <v>21.48</v>
       </c>
       <c r="I138" t="n">
         <v>14.27</v>
@@ -25440,7 +25472,7 @@
         <v>-10.92</v>
       </c>
       <c r="M138" t="n">
-        <v>21.52</v>
+        <v>18.95</v>
       </c>
       <c r="N138" t="b">
         <v>1</v>
@@ -25478,7 +25510,7 @@
         <v>-10.2</v>
       </c>
       <c r="H139" t="n">
-        <v>-13.28</v>
+        <v>-14.25</v>
       </c>
       <c r="I139" t="n">
         <v>15.03</v>
@@ -25493,7 +25525,7 @@
         <v>-1.61</v>
       </c>
       <c r="M139" t="n">
-        <v>-16.96</v>
+        <v>-16.78</v>
       </c>
       <c r="N139" t="b">
         <v>1</v>
@@ -25531,7 +25563,7 @@
         <v>68.90000000000001</v>
       </c>
       <c r="H140" t="n">
-        <v>34.95</v>
+        <v>31.12</v>
       </c>
       <c r="I140" t="n">
         <v>1.84</v>
@@ -25546,7 +25578,7 @@
         <v>-10.43</v>
       </c>
       <c r="M140" t="n">
-        <v>31.28</v>
+        <v>28.59</v>
       </c>
       <c r="N140" t="b">
         <v>1</v>
@@ -25584,7 +25616,7 @@
         <v>-40.8</v>
       </c>
       <c r="H141" t="n">
-        <v>-23.51</v>
+        <v>-23.92</v>
       </c>
       <c r="I141" t="n">
         <v>21.71</v>
@@ -25599,7 +25631,7 @@
         <v>-3.3</v>
       </c>
       <c r="M141" t="n">
-        <v>-27.19</v>
+        <v>-26.45</v>
       </c>
       <c r="N141" t="b">
         <v>1</v>
@@ -25637,7 +25669,7 @@
         <v>40.7</v>
       </c>
       <c r="H142" t="n">
-        <v>35.15</v>
+        <v>20.8</v>
       </c>
       <c r="I142" t="n">
         <v>-4.08</v>
@@ -25652,7 +25684,7 @@
         <v>-11.2</v>
       </c>
       <c r="M142" t="n">
-        <v>31.47</v>
+        <v>18.27</v>
       </c>
       <c r="N142" t="b">
         <v>1</v>
@@ -25690,7 +25722,7 @@
         <v>25.7</v>
       </c>
       <c r="H143" t="n">
-        <v>-13.25</v>
+        <v>-15.86</v>
       </c>
       <c r="I143" t="n">
         <v>11.3</v>
@@ -25705,7 +25737,7 @@
         <v>-11.03</v>
       </c>
       <c r="M143" t="n">
-        <v>-16.92</v>
+        <v>-18.39</v>
       </c>
       <c r="N143" t="b">
         <v>1</v>

--- a/STS_holy_grail_v2.xlsx
+++ b/STS_holy_grail_v2.xlsx
@@ -464,7 +464,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-1.22</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="5">
@@ -474,7 +474,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-3.06</v>
+        <v>-2.11</v>
       </c>
     </row>
     <row r="6">
@@ -484,7 +484,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>44.7</v>
+        <v>48</v>
       </c>
     </row>
     <row r="8">
@@ -531,13 +531,13 @@
         <v>64</v>
       </c>
       <c r="C10" t="n">
-        <v>-0.45</v>
+        <v>1.17</v>
       </c>
       <c r="D10" t="n">
-        <v>56.25</v>
+        <v>62.5</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.01</v>
+        <v>-1.26</v>
       </c>
     </row>
     <row r="11">
@@ -550,13 +550,13 @@
         <v>79</v>
       </c>
       <c r="C11" t="n">
-        <v>-6.37</v>
+        <v>-3.73</v>
       </c>
       <c r="D11" t="n">
-        <v>26.58</v>
+        <v>30.38</v>
       </c>
       <c r="E11" t="n">
-        <v>-8.99</v>
+        <v>-7.23</v>
       </c>
     </row>
     <row r="12">
@@ -569,13 +569,13 @@
         <v>156</v>
       </c>
       <c r="C12" t="n">
-        <v>-0.61</v>
+        <v>0.72</v>
       </c>
       <c r="D12" t="n">
-        <v>44.87</v>
+        <v>46.15</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.4</v>
+        <v>-1.95</v>
       </c>
     </row>
     <row r="13">
@@ -588,13 +588,13 @@
         <v>34</v>
       </c>
       <c r="C13" t="n">
-        <v>6.47</v>
+        <v>9.06</v>
       </c>
       <c r="D13" t="n">
-        <v>64.70999999999999</v>
+        <v>70.59</v>
       </c>
       <c r="E13" t="n">
-        <v>5.7</v>
+        <v>7.41</v>
       </c>
     </row>
     <row r="15">
@@ -641,13 +641,13 @@
         <v>111</v>
       </c>
       <c r="C17" t="n">
-        <v>-0.14</v>
+        <v>1.26</v>
       </c>
       <c r="D17" t="n">
         <v>45.05</v>
       </c>
       <c r="E17" t="n">
-        <v>-2.01</v>
+        <v>-1.48</v>
       </c>
     </row>
     <row r="18">
@@ -660,13 +660,13 @@
         <v>48</v>
       </c>
       <c r="C18" t="n">
-        <v>-1.54</v>
+        <v>-0.39</v>
       </c>
       <c r="D18" t="n">
-        <v>45.83</v>
+        <v>50</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.96</v>
+        <v>-2.69</v>
       </c>
     </row>
     <row r="19">
@@ -679,13 +679,13 @@
         <v>45</v>
       </c>
       <c r="C19" t="n">
-        <v>-1.89</v>
+        <v>0.85</v>
       </c>
       <c r="D19" t="n">
-        <v>37.78</v>
+        <v>51.11</v>
       </c>
       <c r="E19" t="n">
-        <v>-3.78</v>
+        <v>-1.92</v>
       </c>
     </row>
     <row r="20">
@@ -698,13 +698,13 @@
         <v>40</v>
       </c>
       <c r="C20" t="n">
-        <v>-7.96</v>
+        <v>-6.64</v>
       </c>
       <c r="D20" t="n">
         <v>35</v>
       </c>
       <c r="E20" t="n">
-        <v>-9.789999999999999</v>
+        <v>-9.35</v>
       </c>
     </row>
     <row r="21">
@@ -717,13 +717,13 @@
         <v>89</v>
       </c>
       <c r="C21" t="n">
-        <v>0.97</v>
+        <v>3.45</v>
       </c>
       <c r="D21" t="n">
-        <v>51.69</v>
+        <v>55.06</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.04</v>
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="23">
@@ -770,13 +770,13 @@
         <v>10</v>
       </c>
       <c r="C25" t="n">
-        <v>10.91</v>
+        <v>13.13</v>
       </c>
       <c r="D25" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="E25" t="n">
-        <v>8.460000000000001</v>
+        <v>9.789999999999999</v>
       </c>
     </row>
     <row r="26">
@@ -789,13 +789,13 @@
         <v>5</v>
       </c>
       <c r="C26" t="n">
-        <v>-4.6</v>
+        <v>-6.49</v>
       </c>
       <c r="D26" t="n">
         <v>40</v>
       </c>
       <c r="E26" t="n">
-        <v>-7.76</v>
+        <v>-10.54</v>
       </c>
     </row>
     <row r="27">
@@ -808,13 +808,13 @@
         <v>3</v>
       </c>
       <c r="C27" t="n">
-        <v>17.99</v>
+        <v>18.56</v>
       </c>
       <c r="D27" t="n">
         <v>66.67</v>
       </c>
       <c r="E27" t="n">
-        <v>15.86</v>
+        <v>15.54</v>
       </c>
     </row>
     <row r="29">
@@ -861,13 +861,13 @@
         <v>210</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.6</v>
+        <v>1.22</v>
       </c>
       <c r="D31" t="n">
-        <v>44.29</v>
+        <v>46.67</v>
       </c>
       <c r="E31" t="n">
-        <v>-2.51</v>
+        <v>-1.57</v>
       </c>
     </row>
     <row r="32">
@@ -880,13 +880,13 @@
         <v>123</v>
       </c>
       <c r="C32" t="n">
-        <v>-2.29</v>
+        <v>-0.45</v>
       </c>
       <c r="D32" t="n">
-        <v>45.53</v>
+        <v>50.41</v>
       </c>
       <c r="E32" t="n">
-        <v>-4</v>
+        <v>-3.04</v>
       </c>
     </row>
   </sheetData>
@@ -1010,7 +1010,7 @@
         <v>-9.4</v>
       </c>
       <c r="H2" t="n">
-        <v>1.37</v>
+        <v>1.45</v>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
@@ -1019,7 +1019,7 @@
         <v>-1.66</v>
       </c>
       <c r="M2" t="n">
-        <v>2.46</v>
+        <v>1.68</v>
       </c>
       <c r="N2" t="b">
         <v>0</v>
@@ -1057,7 +1057,7 @@
         <v>51.4</v>
       </c>
       <c r="H3" t="n">
-        <v>-5.32</v>
+        <v>-0.34</v>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
@@ -1066,7 +1066,7 @@
         <v>-7.85</v>
       </c>
       <c r="M3" t="n">
-        <v>-3.93</v>
+        <v>0.21</v>
       </c>
       <c r="N3" t="b">
         <v>1</v>
@@ -1104,7 +1104,7 @@
         <v>-24.3</v>
       </c>
       <c r="H4" t="n">
-        <v>-4.46</v>
+        <v>-3.12</v>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
@@ -1113,7 +1113,7 @@
         <v>-6.24</v>
       </c>
       <c r="M4" t="n">
-        <v>-3.38</v>
+        <v>-2.89</v>
       </c>
       <c r="N4" t="b">
         <v>0</v>
@@ -1151,7 +1151,7 @@
         <v>-22.1</v>
       </c>
       <c r="H5" t="n">
-        <v>-7.55</v>
+        <v>-7.16</v>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
@@ -1160,7 +1160,7 @@
         <v>-9.27</v>
       </c>
       <c r="M5" t="n">
-        <v>-6.47</v>
+        <v>-6.93</v>
       </c>
       <c r="N5" t="b">
         <v>0</v>
@@ -1198,16 +1198,18 @@
         <v>-16.6</v>
       </c>
       <c r="H6" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="I6" t="inlineStr"/>
+        <v>-0.75</v>
+      </c>
+      <c r="I6" t="n">
+        <v>-0.75</v>
+      </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="n">
-        <v>-1.04</v>
+        <v>-1.39</v>
       </c>
       <c r="M6" t="n">
-        <v>3.24</v>
+        <v>-0.41</v>
       </c>
       <c r="N6" t="b">
         <v>1</v>
@@ -1245,16 +1247,18 @@
         <v>-7.4</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.08</v>
-      </c>
-      <c r="I7" t="inlineStr"/>
+        <v>-2.38</v>
+      </c>
+      <c r="I7" t="n">
+        <v>-2.38</v>
+      </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="n">
-        <v>-2.54</v>
+        <v>-3.12</v>
       </c>
       <c r="M7" t="n">
-        <v>1.12</v>
+        <v>-2.03</v>
       </c>
       <c r="N7" t="b">
         <v>0</v>
@@ -1292,16 +1296,18 @@
         <v>-5</v>
       </c>
       <c r="H8" t="n">
-        <v>8.949999999999999</v>
-      </c>
-      <c r="I8" t="inlineStr"/>
+        <v>12.26</v>
+      </c>
+      <c r="I8" t="n">
+        <v>12.26</v>
+      </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="n">
         <v>-1.75</v>
       </c>
       <c r="M8" t="n">
-        <v>10.15</v>
+        <v>12.61</v>
       </c>
       <c r="N8" t="b">
         <v>1</v>
@@ -1339,16 +1345,18 @@
         <v>12.5</v>
       </c>
       <c r="H9" t="n">
-        <v>7.42</v>
-      </c>
-      <c r="I9" t="inlineStr"/>
+        <v>7.44</v>
+      </c>
+      <c r="I9" t="n">
+        <v>7.44</v>
+      </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="n">
         <v>-2.59</v>
       </c>
       <c r="M9" t="n">
-        <v>8.619999999999999</v>
+        <v>7.79</v>
       </c>
       <c r="N9" t="b">
         <v>1</v>
@@ -1386,16 +1394,18 @@
         <v>-1.1</v>
       </c>
       <c r="H10" t="n">
-        <v>9.16</v>
-      </c>
-      <c r="I10" t="inlineStr"/>
+        <v>10.88</v>
+      </c>
+      <c r="I10" t="n">
+        <v>10.88</v>
+      </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="n">
         <v>-0.36</v>
       </c>
       <c r="M10" t="n">
-        <v>10.35</v>
+        <v>11.23</v>
       </c>
       <c r="N10" t="b">
         <v>0</v>
@@ -1433,16 +1443,18 @@
         <v>-17.3</v>
       </c>
       <c r="H11" t="n">
-        <v>-0</v>
-      </c>
-      <c r="I11" t="inlineStr"/>
+        <v>0.29</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1.16</v>
+      </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="n">
         <v>-6.51</v>
       </c>
       <c r="M11" t="n">
-        <v>1.5</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="N11" t="b">
         <v>1</v>
@@ -1480,16 +1492,18 @@
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>6.77</v>
-      </c>
-      <c r="I12" t="inlineStr"/>
+        <v>7.66</v>
+      </c>
+      <c r="I12" t="n">
+        <v>9.16</v>
+      </c>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="n">
         <v>-1.46</v>
       </c>
       <c r="M12" t="n">
-        <v>8.27</v>
+        <v>8.31</v>
       </c>
       <c r="N12" t="b">
         <v>0</v>
@@ -1527,7 +1541,7 @@
         <v>-29.3</v>
       </c>
       <c r="H13" t="n">
-        <v>10.02</v>
+        <v>10.97</v>
       </c>
       <c r="I13" t="n">
         <v>10.02</v>
@@ -1538,7 +1552,7 @@
         <v>-3.13</v>
       </c>
       <c r="M13" t="n">
-        <v>10.44</v>
+        <v>10.53</v>
       </c>
       <c r="N13" t="b">
         <v>0</v>
@@ -1576,7 +1590,7 @@
         <v>-21.8</v>
       </c>
       <c r="H14" t="n">
-        <v>-1.73</v>
+        <v>0.25</v>
       </c>
       <c r="I14" t="n">
         <v>-3.37</v>
@@ -1587,7 +1601,7 @@
         <v>-5.33</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.73</v>
+        <v>-0.62</v>
       </c>
       <c r="N14" t="b">
         <v>1</v>
@@ -1625,7 +1639,7 @@
         <v>-15</v>
       </c>
       <c r="H15" t="n">
-        <v>11.51</v>
+        <v>13.77</v>
       </c>
       <c r="I15" t="n">
         <v>12.31</v>
@@ -1636,7 +1650,7 @@
         <v>-4.06</v>
       </c>
       <c r="M15" t="n">
-        <v>11.56</v>
+        <v>12.96</v>
       </c>
       <c r="N15" t="b">
         <v>0</v>
@@ -1674,7 +1688,7 @@
         <v>-16.7</v>
       </c>
       <c r="H16" t="n">
-        <v>26.63</v>
+        <v>27.16</v>
       </c>
       <c r="I16" t="n">
         <v>26.03</v>
@@ -1685,7 +1699,7 @@
         <v>-6.98</v>
       </c>
       <c r="M16" t="n">
-        <v>26.68</v>
+        <v>26.34</v>
       </c>
       <c r="N16" t="b">
         <v>1</v>
@@ -1723,7 +1737,7 @@
         <v>-26.8</v>
       </c>
       <c r="H17" t="n">
-        <v>0.86</v>
+        <v>3.18</v>
       </c>
       <c r="I17" t="n">
         <v>1.39</v>
@@ -1734,7 +1748,7 @@
         <v>-5.1</v>
       </c>
       <c r="M17" t="n">
-        <v>0.91</v>
+        <v>2.36</v>
       </c>
       <c r="N17" t="b">
         <v>0</v>
@@ -1772,7 +1786,7 @@
         <v>-35.9</v>
       </c>
       <c r="H18" t="n">
-        <v>-2.53</v>
+        <v>-2.77</v>
       </c>
       <c r="I18" t="n">
         <v>-6.92</v>
@@ -1783,7 +1797,7 @@
         <v>-7.58</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.48</v>
+        <v>-3.58</v>
       </c>
       <c r="N18" t="b">
         <v>0</v>
@@ -1821,7 +1835,7 @@
         <v>-7.1</v>
       </c>
       <c r="H19" t="n">
-        <v>7.27</v>
+        <v>8.16</v>
       </c>
       <c r="I19" t="n">
         <v>9.390000000000001</v>
@@ -1832,7 +1846,7 @@
         <v>-2.71</v>
       </c>
       <c r="M19" t="n">
-        <v>7.32</v>
+        <v>7.34</v>
       </c>
       <c r="N19" t="b">
         <v>0</v>
@@ -1870,7 +1884,7 @@
         <v>-11.5</v>
       </c>
       <c r="H20" t="n">
-        <v>16.14</v>
+        <v>18.34</v>
       </c>
       <c r="I20" t="n">
         <v>7.47</v>
@@ -1881,7 +1895,7 @@
         <v>-0.99</v>
       </c>
       <c r="M20" t="n">
-        <v>16.19</v>
+        <v>17.52</v>
       </c>
       <c r="N20" t="b">
         <v>1</v>
@@ -1919,7 +1933,7 @@
         <v>0.1</v>
       </c>
       <c r="H21" t="n">
-        <v>19.7</v>
+        <v>18.54</v>
       </c>
       <c r="I21" t="n">
         <v>6.41</v>
@@ -1930,7 +1944,7 @@
         <v>-2.51</v>
       </c>
       <c r="M21" t="n">
-        <v>20</v>
+        <v>17.98</v>
       </c>
       <c r="N21" t="b">
         <v>1</v>
@@ -1968,7 +1982,7 @@
         <v>-31.6</v>
       </c>
       <c r="H22" t="n">
-        <v>-5.55</v>
+        <v>-2.84</v>
       </c>
       <c r="I22" t="n">
         <v>-2.12</v>
@@ -1979,7 +1993,7 @@
         <v>-8.140000000000001</v>
       </c>
       <c r="M22" t="n">
-        <v>-5.25</v>
+        <v>-3.4</v>
       </c>
       <c r="N22" t="b">
         <v>1</v>
@@ -2006,7 +2020,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Extended</t>
+          <t>Retired</t>
         </is>
       </c>
       <c r="E23" t="inlineStr"/>
@@ -2017,7 +2031,7 @@
         <v>7.6</v>
       </c>
       <c r="H23" t="n">
-        <v>8.119999999999999</v>
+        <v>5.95</v>
       </c>
       <c r="I23" t="n">
         <v>-3.6</v>
@@ -2028,7 +2042,7 @@
         <v>-9.359999999999999</v>
       </c>
       <c r="M23" t="n">
-        <v>7.8</v>
+        <v>4.77</v>
       </c>
       <c r="N23" t="b">
         <v>0</v>
@@ -2066,18 +2080,20 @@
         <v>-17.9</v>
       </c>
       <c r="H24" t="n">
-        <v>-11.73</v>
+        <v>-10.02</v>
       </c>
       <c r="I24" t="n">
         <v>-6.13</v>
       </c>
-      <c r="J24" t="inlineStr"/>
+      <c r="J24" t="n">
+        <v>-9.92</v>
+      </c>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="n">
         <v>-14.51</v>
       </c>
       <c r="M24" t="n">
-        <v>-10.76</v>
+        <v>-9.9</v>
       </c>
       <c r="N24" t="b">
         <v>0</v>
@@ -2115,18 +2131,20 @@
         <v>-2.7</v>
       </c>
       <c r="H25" t="n">
-        <v>-10.36</v>
+        <v>-9.199999999999999</v>
       </c>
       <c r="I25" t="n">
         <v>-3.77</v>
       </c>
-      <c r="J25" t="inlineStr"/>
+      <c r="J25" t="n">
+        <v>-9.539999999999999</v>
+      </c>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="n">
         <v>-12.44</v>
       </c>
       <c r="M25" t="n">
-        <v>-9.390000000000001</v>
+        <v>-9.08</v>
       </c>
       <c r="N25" t="b">
         <v>1</v>
@@ -2164,18 +2182,20 @@
         <v>-25.3</v>
       </c>
       <c r="H26" t="n">
-        <v>7.29</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="I26" t="n">
         <v>4.1</v>
       </c>
-      <c r="J26" t="inlineStr"/>
+      <c r="J26" t="n">
+        <v>9.06</v>
+      </c>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="n">
         <v>-0.92</v>
       </c>
       <c r="M26" t="n">
-        <v>8.26</v>
+        <v>8.9</v>
       </c>
       <c r="N26" t="b">
         <v>0</v>
@@ -2213,18 +2233,20 @@
         <v>25.6</v>
       </c>
       <c r="H27" t="n">
-        <v>5.78</v>
+        <v>8.26</v>
       </c>
       <c r="I27" t="n">
         <v>-0.42</v>
       </c>
-      <c r="J27" t="inlineStr"/>
+      <c r="J27" t="n">
+        <v>9.140000000000001</v>
+      </c>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="n">
         <v>-8.35</v>
       </c>
       <c r="M27" t="n">
-        <v>6.76</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="N27" t="b">
         <v>0</v>
@@ -2262,18 +2284,20 @@
         <v>26.9</v>
       </c>
       <c r="H28" t="n">
-        <v>-2.37</v>
+        <v>-0.39</v>
       </c>
       <c r="I28" t="n">
         <v>-3.24</v>
       </c>
-      <c r="J28" t="inlineStr"/>
+      <c r="J28" t="n">
+        <v>-1.02</v>
+      </c>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="n">
         <v>-12.88</v>
       </c>
       <c r="M28" t="n">
-        <v>-1.4</v>
+        <v>-0.27</v>
       </c>
       <c r="N28" t="b">
         <v>1</v>
@@ -2311,7 +2335,7 @@
         <v>-14.5</v>
       </c>
       <c r="H29" t="n">
-        <v>-5.69</v>
+        <v>-9.300000000000001</v>
       </c>
       <c r="I29" t="n">
         <v>-3.75</v>
@@ -2324,7 +2348,7 @@
         <v>-9.01</v>
       </c>
       <c r="M29" t="n">
-        <v>-5.72</v>
+        <v>-10.2</v>
       </c>
       <c r="N29" t="b">
         <v>0</v>
@@ -2362,7 +2386,7 @@
         <v>17.2</v>
       </c>
       <c r="H30" t="n">
-        <v>5.34</v>
+        <v>4.28</v>
       </c>
       <c r="I30" t="n">
         <v>-1.49</v>
@@ -2375,7 +2399,7 @@
         <v>-10.54</v>
       </c>
       <c r="M30" t="n">
-        <v>5.31</v>
+        <v>3.39</v>
       </c>
       <c r="N30" t="b">
         <v>0</v>
@@ -2413,7 +2437,7 @@
         <v>-13.2</v>
       </c>
       <c r="H31" t="n">
-        <v>14.04</v>
+        <v>14.12</v>
       </c>
       <c r="I31" t="n">
         <v>23.71</v>
@@ -2426,7 +2450,7 @@
         <v>-0.82</v>
       </c>
       <c r="M31" t="n">
-        <v>14.01</v>
+        <v>13.23</v>
       </c>
       <c r="N31" t="b">
         <v>0</v>
@@ -2464,7 +2488,7 @@
         <v>-7.7</v>
       </c>
       <c r="H32" t="n">
-        <v>-4.88</v>
+        <v>-5.21</v>
       </c>
       <c r="I32" t="n">
         <v>-9.67</v>
@@ -2477,7 +2501,7 @@
         <v>-12.32</v>
       </c>
       <c r="M32" t="n">
-        <v>-4.91</v>
+        <v>-6.11</v>
       </c>
       <c r="N32" t="b">
         <v>0</v>
@@ -2515,7 +2539,7 @@
         <v>-18.1</v>
       </c>
       <c r="H33" t="n">
-        <v>1.94</v>
+        <v>-1.4</v>
       </c>
       <c r="I33" t="n">
         <v>-2.43</v>
@@ -2528,7 +2552,7 @@
         <v>-6.41</v>
       </c>
       <c r="M33" t="n">
-        <v>1.91</v>
+        <v>-2.3</v>
       </c>
       <c r="N33" t="b">
         <v>0</v>
@@ -2566,7 +2590,7 @@
         <v>-18.1</v>
       </c>
       <c r="H34" t="n">
-        <v>17.38</v>
+        <v>17.63</v>
       </c>
       <c r="I34" t="n">
         <v>4.46</v>
@@ -2579,7 +2603,7 @@
         <v>-2.69</v>
       </c>
       <c r="M34" t="n">
-        <v>17.35</v>
+        <v>16.74</v>
       </c>
       <c r="N34" t="b">
         <v>1</v>
@@ -2617,7 +2641,7 @@
         <v>7.7</v>
       </c>
       <c r="H35" t="n">
-        <v>4.45</v>
+        <v>2.27</v>
       </c>
       <c r="I35" t="n">
         <v>-6.85</v>
@@ -2630,7 +2654,7 @@
         <v>-9.359999999999999</v>
       </c>
       <c r="M35" t="n">
-        <v>4.42</v>
+        <v>1.38</v>
       </c>
       <c r="N35" t="b">
         <v>0</v>
@@ -2668,7 +2692,7 @@
         <v>-21.5</v>
       </c>
       <c r="H36" t="n">
-        <v>-3.7</v>
+        <v>-2.87</v>
       </c>
       <c r="I36" t="n">
         <v>-1.68</v>
@@ -2681,7 +2705,7 @@
         <v>-8.130000000000001</v>
       </c>
       <c r="M36" t="n">
-        <v>-3.73</v>
+        <v>-3.76</v>
       </c>
       <c r="N36" t="b">
         <v>1</v>
@@ -2719,7 +2743,7 @@
         <v>41.6</v>
       </c>
       <c r="H37" t="n">
-        <v>3.03</v>
+        <v>6.9</v>
       </c>
       <c r="I37" t="n">
         <v>3.43</v>
@@ -2732,7 +2756,7 @@
         <v>-4.38</v>
       </c>
       <c r="M37" t="n">
-        <v>2.35</v>
+        <v>5.35</v>
       </c>
       <c r="N37" t="b">
         <v>1</v>
@@ -2770,7 +2794,7 @@
         <v>32.1</v>
       </c>
       <c r="H38" t="n">
-        <v>6.6</v>
+        <v>11.51</v>
       </c>
       <c r="I38" t="n">
         <v>-3.47</v>
@@ -2783,7 +2807,7 @@
         <v>-6.94</v>
       </c>
       <c r="M38" t="n">
-        <v>5.92</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="N38" t="b">
         <v>1</v>
@@ -2821,7 +2845,7 @@
         <v>-14.4</v>
       </c>
       <c r="H39" t="n">
-        <v>1.72</v>
+        <v>3.67</v>
       </c>
       <c r="I39" t="n">
         <v>-2.38</v>
@@ -2834,7 +2858,7 @@
         <v>-6.46</v>
       </c>
       <c r="M39" t="n">
-        <v>1.04</v>
+        <v>2.12</v>
       </c>
       <c r="N39" t="b">
         <v>1</v>
@@ -2872,7 +2896,7 @@
         <v>-16.8</v>
       </c>
       <c r="H40" t="n">
-        <v>-2.41</v>
+        <v>-0.06</v>
       </c>
       <c r="I40" t="n">
         <v>1.99</v>
@@ -2885,7 +2909,7 @@
         <v>-7.67</v>
       </c>
       <c r="M40" t="n">
-        <v>-3.09</v>
+        <v>-1.6</v>
       </c>
       <c r="N40" t="b">
         <v>0</v>
@@ -2923,7 +2947,7 @@
         <v>-10</v>
       </c>
       <c r="H41" t="n">
-        <v>-10.96</v>
+        <v>-10.24</v>
       </c>
       <c r="I41" t="n">
         <v>-3.29</v>
@@ -2936,7 +2960,7 @@
         <v>-14.66</v>
       </c>
       <c r="M41" t="n">
-        <v>-11.64</v>
+        <v>-11.78</v>
       </c>
       <c r="N41" t="b">
         <v>1</v>
@@ -2974,7 +2998,7 @@
         <v>6.4</v>
       </c>
       <c r="H42" t="n">
-        <v>12.86</v>
+        <v>16.43</v>
       </c>
       <c r="I42" t="n">
         <v>1.48</v>
@@ -2987,7 +3011,7 @@
         <v>-3.35</v>
       </c>
       <c r="M42" t="n">
-        <v>12.18</v>
+        <v>14.89</v>
       </c>
       <c r="N42" t="b">
         <v>1</v>
@@ -3025,7 +3049,7 @@
         <v>-11</v>
       </c>
       <c r="H43" t="n">
-        <v>47.19</v>
+        <v>48.2</v>
       </c>
       <c r="I43" t="n">
         <v>11.67</v>
@@ -3038,7 +3062,7 @@
         <v>-0.97</v>
       </c>
       <c r="M43" t="n">
-        <v>46.51</v>
+        <v>46.65</v>
       </c>
       <c r="N43" t="b">
         <v>0</v>
@@ -3076,7 +3100,7 @@
         <v>-23.9</v>
       </c>
       <c r="H44" t="n">
-        <v>-2.94</v>
+        <v>-3.63</v>
       </c>
       <c r="I44" t="n">
         <v>-4.98</v>
@@ -3089,7 +3113,7 @@
         <v>-7.87</v>
       </c>
       <c r="M44" t="n">
-        <v>-3.63</v>
+        <v>-5.18</v>
       </c>
       <c r="N44" t="b">
         <v>0</v>
@@ -3131,7 +3155,7 @@
         <v>-9.800000000000001</v>
       </c>
       <c r="H45" t="n">
-        <v>10.03</v>
+        <v>11.92</v>
       </c>
       <c r="I45" t="n">
         <v>-3.41</v>
@@ -3144,7 +3168,7 @@
         <v>-8.949999999999999</v>
       </c>
       <c r="M45" t="n">
-        <v>9.34</v>
+        <v>10.37</v>
       </c>
       <c r="N45" t="b">
         <v>0</v>
@@ -3182,7 +3206,7 @@
         <v>-36.1</v>
       </c>
       <c r="H46" t="n">
-        <v>0.5600000000000001</v>
+        <v>-0.71</v>
       </c>
       <c r="I46" t="n">
         <v>-1.4</v>
@@ -3195,7 +3219,7 @@
         <v>-7.04</v>
       </c>
       <c r="M46" t="n">
-        <v>-0.13</v>
+        <v>-2.26</v>
       </c>
       <c r="N46" t="b">
         <v>0</v>
@@ -3233,7 +3257,7 @@
         <v>-7.9</v>
       </c>
       <c r="H47" t="n">
-        <v>-9.48</v>
+        <v>-8.5</v>
       </c>
       <c r="I47" t="n">
         <v>-8.83</v>
@@ -3246,7 +3270,7 @@
         <v>-12.99</v>
       </c>
       <c r="M47" t="n">
-        <v>-10.17</v>
+        <v>-10.05</v>
       </c>
       <c r="N47" t="b">
         <v>0</v>
@@ -3284,7 +3308,7 @@
         <v>2.6</v>
       </c>
       <c r="H48" t="n">
-        <v>7.21</v>
+        <v>11.64</v>
       </c>
       <c r="I48" t="n">
         <v>-7.8</v>
@@ -3297,7 +3321,7 @@
         <v>-12.2</v>
       </c>
       <c r="M48" t="n">
-        <v>6.04</v>
+        <v>9.6</v>
       </c>
       <c r="N48" t="b">
         <v>0</v>
@@ -3335,7 +3359,7 @@
         <v>6.3</v>
       </c>
       <c r="H49" t="n">
-        <v>3.07</v>
+        <v>7.5</v>
       </c>
       <c r="I49" t="n">
         <v>0.64</v>
@@ -3348,7 +3372,7 @@
         <v>-2.13</v>
       </c>
       <c r="M49" t="n">
-        <v>1.9</v>
+        <v>5.45</v>
       </c>
       <c r="N49" t="b">
         <v>0</v>
@@ -3386,7 +3410,7 @@
         <v>20.2</v>
       </c>
       <c r="H50" t="n">
-        <v>0.61</v>
+        <v>1.2</v>
       </c>
       <c r="I50" t="n">
         <v>3.45</v>
@@ -3399,7 +3423,7 @@
         <v>-1.07</v>
       </c>
       <c r="M50" t="n">
-        <v>-0.48</v>
+        <v>-0.76</v>
       </c>
       <c r="N50" t="b">
         <v>1</v>
@@ -3437,7 +3461,7 @@
         <v>43.7</v>
       </c>
       <c r="H51" t="n">
-        <v>13.28</v>
+        <v>15.43</v>
       </c>
       <c r="I51" t="n">
         <v>3.16</v>
@@ -3450,7 +3474,7 @@
         <v>-2.44</v>
       </c>
       <c r="M51" t="n">
-        <v>12.19</v>
+        <v>13.47</v>
       </c>
       <c r="N51" t="b">
         <v>1</v>
@@ -3488,7 +3512,7 @@
         <v>1.9</v>
       </c>
       <c r="H52" t="n">
-        <v>-5.06</v>
+        <v>-3.81</v>
       </c>
       <c r="I52" t="n">
         <v>-10.64</v>
@@ -3501,7 +3525,7 @@
         <v>-14.75</v>
       </c>
       <c r="M52" t="n">
-        <v>-6.15</v>
+        <v>-5.77</v>
       </c>
       <c r="N52" t="b">
         <v>1</v>
@@ -3539,7 +3563,7 @@
         <v>37.5</v>
       </c>
       <c r="H53" t="n">
-        <v>7.82</v>
+        <v>23.93</v>
       </c>
       <c r="I53" t="n">
         <v>5.86</v>
@@ -3552,7 +3576,7 @@
         <v>-3.95</v>
       </c>
       <c r="M53" t="n">
-        <v>6.58</v>
+        <v>21.82</v>
       </c>
       <c r="N53" t="b">
         <v>1</v>
@@ -3590,7 +3614,7 @@
         <v>15</v>
       </c>
       <c r="H54" t="n">
-        <v>-31.03</v>
+        <v>-29.09</v>
       </c>
       <c r="I54" t="n">
         <v>-21.11</v>
@@ -3603,7 +3627,7 @@
         <v>-28.65</v>
       </c>
       <c r="M54" t="n">
-        <v>-32.27</v>
+        <v>-31.2</v>
       </c>
       <c r="N54" t="b">
         <v>0</v>
@@ -3641,7 +3665,7 @@
         <v>40.2</v>
       </c>
       <c r="H55" t="n">
-        <v>10.98</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="I55" t="n">
         <v>-1.11</v>
@@ -3654,7 +3678,7 @@
         <v>-5.29</v>
       </c>
       <c r="M55" t="n">
-        <v>9.75</v>
+        <v>7.36</v>
       </c>
       <c r="N55" t="b">
         <v>1</v>
@@ -3692,7 +3716,7 @@
         <v>10.7</v>
       </c>
       <c r="H56" t="n">
-        <v>1.74</v>
+        <v>1.06</v>
       </c>
       <c r="I56" t="n">
         <v>7.3</v>
@@ -3705,7 +3729,7 @@
         <v>-3.78</v>
       </c>
       <c r="M56" t="n">
-        <v>0.5</v>
+        <v>-1.05</v>
       </c>
       <c r="N56" t="b">
         <v>1</v>
@@ -3743,7 +3767,7 @@
         <v>25.6</v>
       </c>
       <c r="H57" t="n">
-        <v>14.5</v>
+        <v>19.74</v>
       </c>
       <c r="I57" t="n">
         <v>7.71</v>
@@ -3756,7 +3780,7 @@
         <v>-4.85</v>
       </c>
       <c r="M57" t="n">
-        <v>14.02</v>
+        <v>18.39</v>
       </c>
       <c r="N57" t="b">
         <v>1</v>
@@ -3794,7 +3818,7 @@
         <v>6.3</v>
       </c>
       <c r="H58" t="n">
-        <v>-3.06</v>
+        <v>0.89</v>
       </c>
       <c r="I58" t="n">
         <v>7.2</v>
@@ -3807,7 +3831,7 @@
         <v>-0.4</v>
       </c>
       <c r="M58" t="n">
-        <v>-4.42</v>
+        <v>-1.35</v>
       </c>
       <c r="N58" t="b">
         <v>0</v>
@@ -3845,7 +3869,7 @@
         <v>2.3</v>
       </c>
       <c r="H59" t="n">
-        <v>-14.25</v>
+        <v>-11.21</v>
       </c>
       <c r="I59" t="n">
         <v>-8.85</v>
@@ -3858,7 +3882,7 @@
         <v>-14.2</v>
       </c>
       <c r="M59" t="n">
-        <v>-15.62</v>
+        <v>-13.45</v>
       </c>
       <c r="N59" t="b">
         <v>0</v>
@@ -3896,7 +3920,7 @@
         <v>-4.3</v>
       </c>
       <c r="H60" t="n">
-        <v>1.89</v>
+        <v>5.61</v>
       </c>
       <c r="I60" t="n">
         <v>3.39</v>
@@ -3909,7 +3933,7 @@
         <v>-5.89</v>
       </c>
       <c r="M60" t="n">
-        <v>1.33</v>
+        <v>4.18</v>
       </c>
       <c r="N60" t="b">
         <v>0</v>
@@ -3947,7 +3971,7 @@
         <v>-29.4</v>
       </c>
       <c r="H61" t="n">
-        <v>-12.03</v>
+        <v>-14.6</v>
       </c>
       <c r="I61" t="n">
         <v>-5.75</v>
@@ -3960,7 +3984,7 @@
         <v>-10.11</v>
       </c>
       <c r="M61" t="n">
-        <v>-12.59</v>
+        <v>-16.03</v>
       </c>
       <c r="N61" t="b">
         <v>0</v>
@@ -3998,7 +4022,7 @@
         <v>-6.9</v>
       </c>
       <c r="H62" t="n">
-        <v>20.29</v>
+        <v>18.01</v>
       </c>
       <c r="I62" t="n">
         <v>6.44</v>
@@ -4011,7 +4035,7 @@
         <v>-4.53</v>
       </c>
       <c r="M62" t="n">
-        <v>19.72</v>
+        <v>16.58</v>
       </c>
       <c r="N62" t="b">
         <v>1</v>
@@ -4049,7 +4073,7 @@
         <v>4.2</v>
       </c>
       <c r="H63" t="n">
-        <v>-19.93</v>
+        <v>-18.08</v>
       </c>
       <c r="I63" t="n">
         <v>-10.83</v>
@@ -4062,7 +4086,7 @@
         <v>-18.5</v>
       </c>
       <c r="M63" t="n">
-        <v>-20.5</v>
+        <v>-19.51</v>
       </c>
       <c r="N63" t="b">
         <v>0</v>
@@ -4100,7 +4124,7 @@
         <v>-32.4</v>
       </c>
       <c r="H64" t="n">
-        <v>4.74</v>
+        <v>3.42</v>
       </c>
       <c r="I64" t="n">
         <v>-2.43</v>
@@ -4113,7 +4137,7 @@
         <v>-12.47</v>
       </c>
       <c r="M64" t="n">
-        <v>4.83</v>
+        <v>2.65</v>
       </c>
       <c r="N64" t="b">
         <v>0</v>
@@ -4151,7 +4175,7 @@
         <v>-11</v>
       </c>
       <c r="H65" t="n">
-        <v>3.83</v>
+        <v>0.64</v>
       </c>
       <c r="I65" t="n">
         <v>-8.449999999999999</v>
@@ -4164,7 +4188,7 @@
         <v>-18.92</v>
       </c>
       <c r="M65" t="n">
-        <v>3.92</v>
+        <v>-0.13</v>
       </c>
       <c r="N65" t="b">
         <v>0</v>
@@ -4202,7 +4226,7 @@
         <v>9.699999999999999</v>
       </c>
       <c r="H66" t="n">
-        <v>-7.94</v>
+        <v>3.17</v>
       </c>
       <c r="I66" t="n">
         <v>1.27</v>
@@ -4215,7 +4239,7 @@
         <v>-20.79</v>
       </c>
       <c r="M66" t="n">
-        <v>-8</v>
+        <v>2.24</v>
       </c>
       <c r="N66" t="b">
         <v>0</v>
@@ -4253,7 +4277,7 @@
         <v>-28.1</v>
       </c>
       <c r="H67" t="n">
-        <v>-7.27</v>
+        <v>-8.380000000000001</v>
       </c>
       <c r="I67" t="n">
         <v>-10.79</v>
@@ -4266,7 +4290,7 @@
         <v>-13.67</v>
       </c>
       <c r="M67" t="n">
-        <v>-7.33</v>
+        <v>-9.300000000000001</v>
       </c>
       <c r="N67" t="b">
         <v>0</v>
@@ -4304,7 +4328,7 @@
         <v>-17.7</v>
       </c>
       <c r="H68" t="n">
-        <v>2.4</v>
+        <v>4.32</v>
       </c>
       <c r="I68" t="n">
         <v>-0.89</v>
@@ -4317,7 +4341,7 @@
         <v>-11.37</v>
       </c>
       <c r="M68" t="n">
-        <v>2.33</v>
+        <v>3.39</v>
       </c>
       <c r="N68" t="b">
         <v>0</v>
@@ -4355,7 +4379,7 @@
         <v>-9.300000000000001</v>
       </c>
       <c r="H69" t="n">
-        <v>-18.98</v>
+        <v>-20.03</v>
       </c>
       <c r="I69" t="n">
         <v>-3.34</v>
@@ -4368,7 +4392,7 @@
         <v>-8.77</v>
       </c>
       <c r="M69" t="n">
-        <v>-19.04</v>
+        <v>-20.95</v>
       </c>
       <c r="N69" t="b">
         <v>0</v>
@@ -4406,7 +4430,7 @@
         <v>0.3</v>
       </c>
       <c r="H70" t="n">
-        <v>-18.57</v>
+        <v>-15.89</v>
       </c>
       <c r="I70" t="n">
         <v>-10.53</v>
@@ -4419,7 +4443,7 @@
         <v>-17.73</v>
       </c>
       <c r="M70" t="n">
-        <v>-18.63</v>
+        <v>-16.82</v>
       </c>
       <c r="N70" t="b">
         <v>1</v>
@@ -4457,7 +4481,7 @@
         <v>12.3</v>
       </c>
       <c r="H71" t="n">
-        <v>4.07</v>
+        <v>2.61</v>
       </c>
       <c r="I71" t="n">
         <v>6.51</v>
@@ -4470,7 +4494,7 @@
         <v>-6.01</v>
       </c>
       <c r="M71" t="n">
-        <v>3.29</v>
+        <v>0.96</v>
       </c>
       <c r="N71" t="b">
         <v>0</v>
@@ -4508,7 +4532,7 @@
         <v>2.8</v>
       </c>
       <c r="H72" t="n">
-        <v>-0.22</v>
+        <v>3.27</v>
       </c>
       <c r="I72" t="n">
         <v>3.18</v>
@@ -4521,7 +4545,7 @@
         <v>-0.88</v>
       </c>
       <c r="M72" t="n">
-        <v>-1</v>
+        <v>1.63</v>
       </c>
       <c r="N72" t="b">
         <v>1</v>
@@ -4559,7 +4583,7 @@
         <v>-1.4</v>
       </c>
       <c r="H73" t="n">
-        <v>2.5</v>
+        <v>4.92</v>
       </c>
       <c r="I73" t="n">
         <v>-4.52</v>
@@ -4572,7 +4596,7 @@
         <v>-7.44</v>
       </c>
       <c r="M73" t="n">
-        <v>1.72</v>
+        <v>3.28</v>
       </c>
       <c r="N73" t="b">
         <v>0</v>
@@ -4610,7 +4634,7 @@
         <v>34.5</v>
       </c>
       <c r="H74" t="n">
-        <v>8.75</v>
+        <v>13.16</v>
       </c>
       <c r="I74" t="n">
         <v>0.66</v>
@@ -4623,7 +4647,7 @@
         <v>-2.64</v>
       </c>
       <c r="M74" t="n">
-        <v>7.97</v>
+        <v>11.51</v>
       </c>
       <c r="N74" t="b">
         <v>1</v>
@@ -4661,7 +4685,7 @@
         <v>-22.7</v>
       </c>
       <c r="H75" t="n">
-        <v>-15.95</v>
+        <v>-16.96</v>
       </c>
       <c r="I75" t="n">
         <v>-6.71</v>
@@ -4674,7 +4698,7 @@
         <v>-9.58</v>
       </c>
       <c r="M75" t="n">
-        <v>-16.79</v>
+        <v>-18.67</v>
       </c>
       <c r="N75" t="b">
         <v>0</v>
@@ -4712,7 +4736,7 @@
         <v>24.3</v>
       </c>
       <c r="H76" t="n">
-        <v>34.39</v>
+        <v>38.45</v>
       </c>
       <c r="I76" t="n">
         <v>2.54</v>
@@ -4725,7 +4749,7 @@
         <v>-5.21</v>
       </c>
       <c r="M76" t="n">
-        <v>34.25</v>
+        <v>37.45</v>
       </c>
       <c r="N76" t="b">
         <v>1</v>
@@ -4763,7 +4787,7 @@
         <v>56.6</v>
       </c>
       <c r="H77" t="n">
-        <v>-3.47</v>
+        <v>0.83</v>
       </c>
       <c r="I77" t="n">
         <v>-13.1</v>
@@ -4776,7 +4800,7 @@
         <v>-16.17</v>
       </c>
       <c r="M77" t="n">
-        <v>-3.61</v>
+        <v>-0.17</v>
       </c>
       <c r="N77" t="b">
         <v>0</v>
@@ -4814,7 +4838,7 @@
         <v>2.9</v>
       </c>
       <c r="H78" t="n">
-        <v>-20.37</v>
+        <v>-17.74</v>
       </c>
       <c r="I78" t="n">
         <v>-8.470000000000001</v>
@@ -4827,7 +4851,7 @@
         <v>-15.65</v>
       </c>
       <c r="M78" t="n">
-        <v>-20.5</v>
+        <v>-18.74</v>
       </c>
       <c r="N78" t="b">
         <v>0</v>
@@ -4865,7 +4889,7 @@
         <v>-16.9</v>
       </c>
       <c r="H79" t="n">
-        <v>-3.03</v>
+        <v>1.33</v>
       </c>
       <c r="I79" t="n">
         <v>-6.47</v>
@@ -4878,7 +4902,7 @@
         <v>-11.5</v>
       </c>
       <c r="M79" t="n">
-        <v>-3.17</v>
+        <v>0.33</v>
       </c>
       <c r="N79" t="b">
         <v>1</v>
@@ -4916,7 +4940,7 @@
         <v>32.8</v>
       </c>
       <c r="H80" t="n">
-        <v>2.19</v>
+        <v>5.84</v>
       </c>
       <c r="I80" t="n">
         <v>14.96</v>
@@ -4929,7 +4953,7 @@
         <v>-0.9</v>
       </c>
       <c r="M80" t="n">
-        <v>2.63</v>
+        <v>5.42</v>
       </c>
       <c r="N80" t="b">
         <v>0</v>
@@ -4967,7 +4991,7 @@
         <v>0.8</v>
       </c>
       <c r="H81" t="n">
-        <v>-10.28</v>
+        <v>-9.42</v>
       </c>
       <c r="I81" t="n">
         <v>-7.73</v>
@@ -5018,7 +5042,7 @@
         <v>-9.6</v>
       </c>
       <c r="H82" t="n">
-        <v>-18.04</v>
+        <v>-16.6</v>
       </c>
       <c r="I82" t="n">
         <v>-1.23</v>
@@ -5031,7 +5055,7 @@
         <v>-18.52</v>
       </c>
       <c r="M82" t="n">
-        <v>-17.6</v>
+        <v>-17.02</v>
       </c>
       <c r="N82" t="b">
         <v>0</v>
@@ -5069,7 +5093,7 @@
         <v>20.3</v>
       </c>
       <c r="H83" t="n">
-        <v>-19.81</v>
+        <v>-26.39</v>
       </c>
       <c r="I83" t="n">
         <v>-2.07</v>
@@ -5082,7 +5106,7 @@
         <v>-17.35</v>
       </c>
       <c r="M83" t="n">
-        <v>-19.8</v>
+        <v>-27.23</v>
       </c>
       <c r="N83" t="b">
         <v>1</v>
@@ -5120,7 +5144,7 @@
         <v>0.3</v>
       </c>
       <c r="H84" t="n">
-        <v>-22.09</v>
+        <v>-21.9</v>
       </c>
       <c r="I84" t="n">
         <v>-9.9</v>
@@ -5133,7 +5157,7 @@
         <v>-21.72</v>
       </c>
       <c r="M84" t="n">
-        <v>-22.57</v>
+        <v>-23.24</v>
       </c>
       <c r="N84" t="b">
         <v>1</v>
@@ -5171,7 +5195,7 @@
         <v>49.4</v>
       </c>
       <c r="H85" t="n">
-        <v>-2.11</v>
+        <v>0.18</v>
       </c>
       <c r="I85" t="n">
         <v>2.9</v>
@@ -5184,7 +5208,7 @@
         <v>-5.67</v>
       </c>
       <c r="M85" t="n">
-        <v>-2.4</v>
+        <v>-0.97</v>
       </c>
       <c r="N85" t="b">
         <v>1</v>
@@ -5222,7 +5246,7 @@
         <v>4.5</v>
       </c>
       <c r="H86" t="n">
-        <v>-3.75</v>
+        <v>-2.01</v>
       </c>
       <c r="I86" t="n">
         <v>-7.61</v>
@@ -5235,7 +5259,7 @@
         <v>-11.06</v>
       </c>
       <c r="M86" t="n">
-        <v>-4.04</v>
+        <v>-3.16</v>
       </c>
       <c r="N86" t="b">
         <v>1</v>
@@ -5273,7 +5297,7 @@
         <v>4.2</v>
       </c>
       <c r="H87" t="n">
-        <v>-19.69</v>
+        <v>-18.35</v>
       </c>
       <c r="I87" t="n">
         <v>-6.86</v>
@@ -5286,7 +5310,7 @@
         <v>-20.23</v>
       </c>
       <c r="M87" t="n">
-        <v>-19.98</v>
+        <v>-19.51</v>
       </c>
       <c r="N87" t="b">
         <v>0</v>
@@ -5324,7 +5348,7 @@
         <v>15.4</v>
       </c>
       <c r="H88" t="n">
-        <v>2.91</v>
+        <v>5.47</v>
       </c>
       <c r="I88" t="n">
         <v>-1.19</v>
@@ -5337,7 +5361,7 @@
         <v>-7.43</v>
       </c>
       <c r="M88" t="n">
-        <v>2.62</v>
+        <v>4.32</v>
       </c>
       <c r="N88" t="b">
         <v>0</v>
@@ -5375,7 +5399,7 @@
         <v>15.5</v>
       </c>
       <c r="H89" t="n">
-        <v>-4.74</v>
+        <v>-0.97</v>
       </c>
       <c r="I89" t="n">
         <v>-7.36</v>
@@ -5388,7 +5412,7 @@
         <v>-12.98</v>
       </c>
       <c r="M89" t="n">
-        <v>-5.21</v>
+        <v>-2.31</v>
       </c>
       <c r="N89" t="b">
         <v>0</v>
@@ -5430,7 +5454,7 @@
         <v>-8.5</v>
       </c>
       <c r="H90" t="n">
-        <v>29.35</v>
+        <v>31.17</v>
       </c>
       <c r="I90" t="n">
         <v>-3.04</v>
@@ -5443,7 +5467,7 @@
         <v>-4.96</v>
       </c>
       <c r="M90" t="n">
-        <v>28.88</v>
+        <v>29.83</v>
       </c>
       <c r="N90" t="b">
         <v>0</v>
@@ -5481,7 +5505,7 @@
         <v>1.8</v>
       </c>
       <c r="H91" t="n">
-        <v>-10.15</v>
+        <v>-7.25</v>
       </c>
       <c r="I91" t="n">
         <v>-6.45</v>
@@ -5494,7 +5518,7 @@
         <v>-13.57</v>
       </c>
       <c r="M91" t="n">
-        <v>-10.62</v>
+        <v>-8.59</v>
       </c>
       <c r="N91" t="b">
         <v>0</v>
@@ -5532,7 +5556,7 @@
         <v>33.9</v>
       </c>
       <c r="H92" t="n">
-        <v>3.09</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="I92" t="n">
         <v>-7.74</v>
@@ -5545,7 +5569,7 @@
         <v>-9.449999999999999</v>
       </c>
       <c r="M92" t="n">
-        <v>2.62</v>
+        <v>6.78</v>
       </c>
       <c r="N92" t="b">
         <v>0</v>
@@ -5583,7 +5607,7 @@
         <v>-25</v>
       </c>
       <c r="H93" t="n">
-        <v>-10.2</v>
+        <v>-7.93</v>
       </c>
       <c r="I93" t="n">
         <v>2.51</v>
@@ -5596,7 +5620,7 @@
         <v>-4.88</v>
       </c>
       <c r="M93" t="n">
-        <v>-10.51</v>
+        <v>-9.1</v>
       </c>
       <c r="N93" t="b">
         <v>0</v>
@@ -5634,7 +5658,7 @@
         <v>-12.6</v>
       </c>
       <c r="H94" t="n">
-        <v>-14.62</v>
+        <v>-15.82</v>
       </c>
       <c r="I94" t="n">
         <v>-7.89</v>
@@ -5647,7 +5671,7 @@
         <v>-21.29</v>
       </c>
       <c r="M94" t="n">
-        <v>-14.94</v>
+        <v>-17</v>
       </c>
       <c r="N94" t="b">
         <v>0</v>
@@ -5685,7 +5709,7 @@
         <v>-17.9</v>
       </c>
       <c r="H95" t="n">
-        <v>5.6</v>
+        <v>6.87</v>
       </c>
       <c r="I95" t="n">
         <v>0.6</v>
@@ -5698,7 +5722,7 @@
         <v>-4.72</v>
       </c>
       <c r="M95" t="n">
-        <v>5.28</v>
+        <v>5.69</v>
       </c>
       <c r="N95" t="b">
         <v>1</v>
@@ -5736,7 +5760,7 @@
         <v>2.1</v>
       </c>
       <c r="H96" t="n">
-        <v>-15.93</v>
+        <v>-6.92</v>
       </c>
       <c r="I96" t="n">
         <v>0.25</v>
@@ -5749,7 +5773,7 @@
         <v>-16.43</v>
       </c>
       <c r="M96" t="n">
-        <v>-16.25</v>
+        <v>-8.1</v>
       </c>
       <c r="N96" t="b">
         <v>1</v>
@@ -5787,7 +5811,7 @@
         <v>19.4</v>
       </c>
       <c r="H97" t="n">
-        <v>-6.16</v>
+        <v>-7.24</v>
       </c>
       <c r="I97" t="n">
         <v>-10.01</v>
@@ -5800,7 +5824,7 @@
         <v>-15.23</v>
       </c>
       <c r="M97" t="n">
-        <v>-5.9</v>
+        <v>-7.84</v>
       </c>
       <c r="N97" t="b">
         <v>1</v>
@@ -5838,7 +5862,7 @@
         <v>-30.5</v>
       </c>
       <c r="H98" t="n">
-        <v>-2.36</v>
+        <v>-4.58</v>
       </c>
       <c r="I98" t="n">
         <v>-4.6</v>
@@ -5851,7 +5875,7 @@
         <v>-10.37</v>
       </c>
       <c r="M98" t="n">
-        <v>-2.11</v>
+        <v>-5.18</v>
       </c>
       <c r="N98" t="b">
         <v>0</v>
@@ -5889,7 +5913,7 @@
         <v>-20.5</v>
       </c>
       <c r="H99" t="n">
-        <v>-17.96</v>
+        <v>-19.37</v>
       </c>
       <c r="I99" t="n">
         <v>-4.62</v>
@@ -5902,7 +5926,7 @@
         <v>-9.92</v>
       </c>
       <c r="M99" t="n">
-        <v>-17.71</v>
+        <v>-19.97</v>
       </c>
       <c r="N99" t="b">
         <v>0</v>
@@ -5940,7 +5964,7 @@
         <v>-12.3</v>
       </c>
       <c r="H100" t="n">
-        <v>-16.26</v>
+        <v>-15.36</v>
       </c>
       <c r="I100" t="n">
         <v>-4.36</v>
@@ -5953,7 +5977,7 @@
         <v>-13.26</v>
       </c>
       <c r="M100" t="n">
-        <v>-16.22</v>
+        <v>-16.18</v>
       </c>
       <c r="N100" t="b">
         <v>0</v>
@@ -5991,7 +6015,7 @@
         <v>13.7</v>
       </c>
       <c r="H101" t="n">
-        <v>-21.21</v>
+        <v>-20.25</v>
       </c>
       <c r="I101" t="n">
         <v>-12.16</v>
@@ -6004,7 +6028,7 @@
         <v>-13.02</v>
       </c>
       <c r="M101" t="n">
-        <v>-21.17</v>
+        <v>-21.07</v>
       </c>
       <c r="N101" t="b">
         <v>0</v>
@@ -6042,7 +6066,7 @@
         <v>-2.6</v>
       </c>
       <c r="H102" t="n">
-        <v>-8.91</v>
+        <v>-7.39</v>
       </c>
       <c r="I102" t="n">
         <v>-4.27</v>
@@ -6055,7 +6079,7 @@
         <v>-4.86</v>
       </c>
       <c r="M102" t="n">
-        <v>-8.869999999999999</v>
+        <v>-8.210000000000001</v>
       </c>
       <c r="N102" t="b">
         <v>1</v>
@@ -6093,7 +6117,7 @@
         <v>25.6</v>
       </c>
       <c r="H103" t="n">
-        <v>8.74</v>
+        <v>11.25</v>
       </c>
       <c r="I103" t="n">
         <v>4.26</v>
@@ -6106,7 +6130,7 @@
         <v>-10.74</v>
       </c>
       <c r="M103" t="n">
-        <v>8.779999999999999</v>
+        <v>10.43</v>
       </c>
       <c r="N103" t="b">
         <v>0</v>
@@ -6144,7 +6168,7 @@
         <v>23.8</v>
       </c>
       <c r="H104" t="n">
-        <v>-3.17</v>
+        <v>3.37</v>
       </c>
       <c r="I104" t="n">
         <v>1.36</v>
@@ -6157,7 +6181,7 @@
         <v>-9.94</v>
       </c>
       <c r="M104" t="n">
-        <v>-2.17</v>
+        <v>3.52</v>
       </c>
       <c r="N104" t="b">
         <v>1</v>
@@ -6195,7 +6219,7 @@
         <v>38.9</v>
       </c>
       <c r="H105" t="n">
-        <v>-10.17</v>
+        <v>-10.18</v>
       </c>
       <c r="I105" t="n">
         <v>-9.220000000000001</v>
@@ -6208,7 +6232,7 @@
         <v>-9.83</v>
       </c>
       <c r="M105" t="n">
-        <v>-9.16</v>
+        <v>-10.03</v>
       </c>
       <c r="N105" t="b">
         <v>1</v>
@@ -6246,7 +6270,7 @@
         <v>32.1</v>
       </c>
       <c r="H106" t="n">
-        <v>37.51</v>
+        <v>48.09</v>
       </c>
       <c r="I106" t="n">
         <v>11.84</v>
@@ -6259,7 +6283,7 @@
         <v>-1.82</v>
       </c>
       <c r="M106" t="n">
-        <v>38.52</v>
+        <v>48.24</v>
       </c>
       <c r="N106" t="b">
         <v>0</v>
@@ -6297,7 +6321,7 @@
         <v>53.4</v>
       </c>
       <c r="H107" t="n">
-        <v>26.36</v>
+        <v>27.36</v>
       </c>
       <c r="I107" t="n">
         <v>2.75</v>
@@ -6310,7 +6334,7 @@
         <v>-2.31</v>
       </c>
       <c r="M107" t="n">
-        <v>27.66</v>
+        <v>27.82</v>
       </c>
       <c r="N107" t="b">
         <v>0</v>
@@ -6348,7 +6372,7 @@
         <v>54.1</v>
       </c>
       <c r="H108" t="n">
-        <v>37.52</v>
+        <v>35.86</v>
       </c>
       <c r="I108" t="n">
         <v>5.54</v>
@@ -6361,7 +6385,7 @@
         <v>-0.41</v>
       </c>
       <c r="M108" t="n">
-        <v>38.36</v>
+        <v>35.84</v>
       </c>
       <c r="N108" t="b">
         <v>0</v>
@@ -6399,7 +6423,7 @@
         <v>43.2</v>
       </c>
       <c r="H109" t="n">
-        <v>-11.84</v>
+        <v>-10.98</v>
       </c>
       <c r="I109" t="n">
         <v>-3.15</v>
@@ -6450,7 +6474,7 @@
         <v>-8.199999999999999</v>
       </c>
       <c r="H110" t="n">
-        <v>4.62</v>
+        <v>6.35</v>
       </c>
       <c r="I110" t="n">
         <v>5.34</v>
@@ -6463,7 +6487,7 @@
         <v>-5.27</v>
       </c>
       <c r="M110" t="n">
-        <v>5.46</v>
+        <v>6.33</v>
       </c>
       <c r="N110" t="b">
         <v>1</v>
@@ -6501,7 +6525,7 @@
         <v>-1.2</v>
       </c>
       <c r="H111" t="n">
-        <v>1.65</v>
+        <v>2.94</v>
       </c>
       <c r="I111" t="n">
         <v>8.27</v>
@@ -6514,7 +6538,7 @@
         <v>-5.3</v>
       </c>
       <c r="M111" t="n">
-        <v>2.44</v>
+        <v>2.88</v>
       </c>
       <c r="N111" t="b">
         <v>0</v>
@@ -6552,7 +6576,7 @@
         <v>-23.9</v>
       </c>
       <c r="H112" t="n">
-        <v>-6.52</v>
+        <v>-3.94</v>
       </c>
       <c r="I112" t="n">
         <v>3.28</v>
@@ -6565,7 +6589,7 @@
         <v>-4.46</v>
       </c>
       <c r="M112" t="n">
-        <v>-5.97</v>
+        <v>-4.25</v>
       </c>
       <c r="N112" t="b">
         <v>1</v>
@@ -6607,7 +6631,7 @@
         <v>-6.1</v>
       </c>
       <c r="H113" t="n">
-        <v>-21.02</v>
+        <v>-22.07</v>
       </c>
       <c r="I113" t="n">
         <v>4.9</v>
@@ -6620,7 +6644,7 @@
         <v>-9</v>
       </c>
       <c r="M113" t="n">
-        <v>-20.47</v>
+        <v>-22.39</v>
       </c>
       <c r="N113" t="b">
         <v>0</v>
@@ -6658,7 +6682,7 @@
         <v>26.7</v>
       </c>
       <c r="H114" t="n">
-        <v>-0.92</v>
+        <v>-0.6</v>
       </c>
       <c r="I114" t="n">
         <v>-0.05</v>
@@ -6671,7 +6695,7 @@
         <v>-0.87</v>
       </c>
       <c r="M114" t="n">
-        <v>-0.38</v>
+        <v>-0.92</v>
       </c>
       <c r="N114" t="b">
         <v>1</v>
@@ -6709,7 +6733,7 @@
         <v>39.5</v>
       </c>
       <c r="H115" t="n">
-        <v>0.7</v>
+        <v>3.97</v>
       </c>
       <c r="I115" t="n">
         <v>-5.13</v>
@@ -6722,7 +6746,7 @@
         <v>-8.869999999999999</v>
       </c>
       <c r="M115" t="n">
-        <v>1.25</v>
+        <v>3.65</v>
       </c>
       <c r="N115" t="b">
         <v>0</v>
@@ -6760,7 +6784,7 @@
         <v>14.3</v>
       </c>
       <c r="H116" t="n">
-        <v>13.71</v>
+        <v>15.85</v>
       </c>
       <c r="I116" t="n">
         <v>-0.43</v>
@@ -6773,7 +6797,7 @@
         <v>-11.86</v>
       </c>
       <c r="M116" t="n">
-        <v>14.25</v>
+        <v>15.54</v>
       </c>
       <c r="N116" t="b">
         <v>0</v>
@@ -6811,7 +6835,7 @@
         <v>-11.3</v>
       </c>
       <c r="H117" t="n">
-        <v>-2.48</v>
+        <v>0.32</v>
       </c>
       <c r="I117" t="n">
         <v>1.31</v>
@@ -6824,7 +6848,7 @@
         <v>-1.88</v>
       </c>
       <c r="M117" t="n">
-        <v>-1.93</v>
+        <v>0</v>
       </c>
       <c r="N117" t="b">
         <v>0</v>
@@ -6862,7 +6886,7 @@
         <v>-23.5</v>
       </c>
       <c r="H118" t="n">
-        <v>-24.14</v>
+        <v>-22.77</v>
       </c>
       <c r="I118" t="n">
         <v>13.29</v>
@@ -6875,7 +6899,7 @@
         <v>-14.04</v>
       </c>
       <c r="M118" t="n">
-        <v>-23.59</v>
+        <v>-23.08</v>
       </c>
       <c r="N118" t="b">
         <v>0</v>
@@ -6913,7 +6937,7 @@
         <v>10.5</v>
       </c>
       <c r="H119" t="n">
-        <v>-7.23</v>
+        <v>-5.62</v>
       </c>
       <c r="I119" t="n">
         <v>-0.86</v>
@@ -6926,7 +6950,7 @@
         <v>-6.11</v>
       </c>
       <c r="M119" t="n">
-        <v>-6.69</v>
+        <v>-5.94</v>
       </c>
       <c r="N119" t="b">
         <v>0</v>
@@ -6964,7 +6988,7 @@
         <v>-3.5</v>
       </c>
       <c r="H120" t="n">
-        <v>-2.56</v>
+        <v>2.59</v>
       </c>
       <c r="I120" t="n">
         <v>-4.95</v>
@@ -6977,7 +7001,7 @@
         <v>-8.43</v>
       </c>
       <c r="M120" t="n">
-        <v>-2.22</v>
+        <v>2.07</v>
       </c>
       <c r="N120" t="b">
         <v>1</v>
@@ -7015,7 +7039,7 @@
         <v>-12.8</v>
       </c>
       <c r="H121" t="n">
-        <v>8.17</v>
+        <v>12.83</v>
       </c>
       <c r="I121" t="n">
         <v>-1.74</v>
@@ -7028,7 +7052,7 @@
         <v>-2.97</v>
       </c>
       <c r="M121" t="n">
-        <v>8.52</v>
+        <v>12.31</v>
       </c>
       <c r="N121" t="b">
         <v>0</v>
@@ -7066,7 +7090,7 @@
         <v>2.4</v>
       </c>
       <c r="H122" t="n">
-        <v>21.29</v>
+        <v>26.02</v>
       </c>
       <c r="I122" t="n">
         <v>12.41</v>
@@ -7079,7 +7103,7 @@
         <v>-0.07000000000000001</v>
       </c>
       <c r="M122" t="n">
-        <v>21.63</v>
+        <v>25.5</v>
       </c>
       <c r="N122" t="b">
         <v>0</v>
@@ -7117,7 +7141,7 @@
         <v>-17.9</v>
       </c>
       <c r="H123" t="n">
-        <v>-1.2</v>
+        <v>6.18</v>
       </c>
       <c r="I123" t="n">
         <v>-0.5</v>
@@ -7130,7 +7154,7 @@
         <v>-3.43</v>
       </c>
       <c r="M123" t="n">
-        <v>-0.86</v>
+        <v>5.66</v>
       </c>
       <c r="N123" t="b">
         <v>1</v>
@@ -7168,7 +7192,7 @@
         <v>11.9</v>
       </c>
       <c r="H124" t="n">
-        <v>-2.81</v>
+        <v>-1.63</v>
       </c>
       <c r="I124" t="n">
         <v>6.88</v>
@@ -7181,7 +7205,7 @@
         <v>-10.93</v>
       </c>
       <c r="M124" t="n">
-        <v>-2.58</v>
+        <v>-2.25</v>
       </c>
       <c r="N124" t="b">
         <v>0</v>
@@ -7219,7 +7243,7 @@
         <v>53.5</v>
       </c>
       <c r="H125" t="n">
-        <v>5.6</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="I125" t="n">
         <v>1.23</v>
@@ -7232,7 +7256,7 @@
         <v>-7.57</v>
       </c>
       <c r="M125" t="n">
-        <v>5.84</v>
+        <v>8.65</v>
       </c>
       <c r="N125" t="b">
         <v>1</v>
@@ -7270,7 +7294,7 @@
         <v>18.1</v>
       </c>
       <c r="H126" t="n">
-        <v>-3.68</v>
+        <v>-4.15</v>
       </c>
       <c r="I126" t="n">
         <v>-1.69</v>
@@ -7283,7 +7307,7 @@
         <v>-1.92</v>
       </c>
       <c r="M126" t="n">
-        <v>-3.44</v>
+        <v>-4.77</v>
       </c>
       <c r="N126" t="b">
         <v>0</v>
@@ -7321,7 +7345,7 @@
         <v>-1</v>
       </c>
       <c r="H127" t="n">
-        <v>-12.45</v>
+        <v>-12.52</v>
       </c>
       <c r="I127" t="n">
         <v>-6.26</v>
@@ -7334,7 +7358,7 @@
         <v>-15</v>
       </c>
       <c r="M127" t="n">
-        <v>-12.21</v>
+        <v>-13.15</v>
       </c>
       <c r="N127" t="b">
         <v>1</v>
@@ -7372,7 +7396,7 @@
         <v>29.7</v>
       </c>
       <c r="H128" t="n">
-        <v>4.8</v>
+        <v>11.14</v>
       </c>
       <c r="I128" t="n">
         <v>11.27</v>
@@ -7385,7 +7409,7 @@
         <v>0</v>
       </c>
       <c r="M128" t="n">
-        <v>5.04</v>
+        <v>10.52</v>
       </c>
       <c r="N128" t="b">
         <v>1</v>
@@ -7423,7 +7447,7 @@
         <v>15.2</v>
       </c>
       <c r="H129" t="n">
-        <v>-38.8</v>
+        <v>-31.29</v>
       </c>
       <c r="I129" t="n">
         <v>-8.77</v>
@@ -7436,7 +7460,7 @@
         <v>-24.79</v>
       </c>
       <c r="M129" t="n">
-        <v>-37.83</v>
+        <v>-31.18</v>
       </c>
       <c r="N129" t="b">
         <v>1</v>
@@ -7474,7 +7498,7 @@
         <v>22.2</v>
       </c>
       <c r="H130" t="n">
-        <v>9.92</v>
+        <v>12.66</v>
       </c>
       <c r="I130" t="n">
         <v>1.01</v>
@@ -7487,7 +7511,7 @@
         <v>-3.94</v>
       </c>
       <c r="M130" t="n">
-        <v>10.88</v>
+        <v>12.77</v>
       </c>
       <c r="N130" t="b">
         <v>1</v>
@@ -7525,7 +7549,7 @@
         <v>10.8</v>
       </c>
       <c r="H131" t="n">
-        <v>10.36</v>
+        <v>12.83</v>
       </c>
       <c r="I131" t="n">
         <v>5.62</v>
@@ -7538,7 +7562,7 @@
         <v>-1.59</v>
       </c>
       <c r="M131" t="n">
-        <v>11.33</v>
+        <v>12.94</v>
       </c>
       <c r="N131" t="b">
         <v>0</v>
@@ -7576,7 +7600,7 @@
         <v>-2.1</v>
       </c>
       <c r="H132" t="n">
-        <v>-21.02</v>
+        <v>-20.26</v>
       </c>
       <c r="I132" t="n">
         <v>0.67</v>
@@ -7589,7 +7613,7 @@
         <v>-7.84</v>
       </c>
       <c r="M132" t="n">
-        <v>-20.06</v>
+        <v>-20.15</v>
       </c>
       <c r="N132" t="b">
         <v>0</v>
@@ -7627,7 +7651,7 @@
         <v>16.7</v>
       </c>
       <c r="H133" t="n">
-        <v>-29.6</v>
+        <v>-26.22</v>
       </c>
       <c r="I133" t="n">
         <v>-15.31</v>
@@ -7640,7 +7664,7 @@
         <v>-22</v>
       </c>
       <c r="M133" t="n">
-        <v>-30.62</v>
+        <v>-28.11</v>
       </c>
       <c r="N133" t="b">
         <v>0</v>
@@ -7678,7 +7702,7 @@
         <v>0.3</v>
       </c>
       <c r="H134" t="n">
-        <v>35.85</v>
+        <v>44.39</v>
       </c>
       <c r="I134" t="n">
         <v>6.01</v>
@@ -7691,7 +7715,7 @@
         <v>-3.85</v>
       </c>
       <c r="M134" t="n">
-        <v>33.32</v>
+        <v>40.98</v>
       </c>
       <c r="N134" t="b">
         <v>0</v>
@@ -7733,7 +7757,7 @@
         <v>-0</v>
       </c>
       <c r="H135" t="n">
-        <v>50.86</v>
+        <v>52.65</v>
       </c>
       <c r="I135" t="n">
         <v>13.5</v>
@@ -7746,7 +7770,7 @@
         <v>-2.53</v>
       </c>
       <c r="M135" t="n">
-        <v>48.34</v>
+        <v>49.24</v>
       </c>
       <c r="N135" t="b">
         <v>1</v>
@@ -7784,7 +7808,7 @@
         <v>10.5</v>
       </c>
       <c r="H136" t="n">
-        <v>16.5</v>
+        <v>18.72</v>
       </c>
       <c r="I136" t="n">
         <v>1.99</v>
@@ -7797,7 +7821,7 @@
         <v>-6.27</v>
       </c>
       <c r="M136" t="n">
-        <v>13.98</v>
+        <v>15.31</v>
       </c>
       <c r="N136" t="b">
         <v>1</v>
@@ -7835,7 +7859,7 @@
         <v>30.4</v>
       </c>
       <c r="H137" t="n">
-        <v>6.64</v>
+        <v>8.18</v>
       </c>
       <c r="I137" t="n">
         <v>8.539999999999999</v>
@@ -7848,7 +7872,7 @@
         <v>-0.44</v>
       </c>
       <c r="M137" t="n">
-        <v>4.12</v>
+        <v>4.77</v>
       </c>
       <c r="N137" t="b">
         <v>0</v>
@@ -7890,7 +7914,7 @@
         <v>-3.2</v>
       </c>
       <c r="H138" t="n">
-        <v>17.7</v>
+        <v>22.38</v>
       </c>
       <c r="I138" t="n">
         <v>15.28</v>
@@ -7903,7 +7927,7 @@
         <v>-2.53</v>
       </c>
       <c r="M138" t="n">
-        <v>15.18</v>
+        <v>18.97</v>
       </c>
       <c r="N138" t="b">
         <v>0</v>
@@ -7941,7 +7965,7 @@
         <v>-23.5</v>
       </c>
       <c r="H139" t="n">
-        <v>17.5</v>
+        <v>23</v>
       </c>
       <c r="I139" t="n">
         <v>20.48</v>
@@ -7954,7 +7978,7 @@
         <v>-2.25</v>
       </c>
       <c r="M139" t="n">
-        <v>14.97</v>
+        <v>19.58</v>
       </c>
       <c r="N139" t="b">
         <v>0</v>
@@ -7992,7 +8016,7 @@
         <v>-27.3</v>
       </c>
       <c r="H140" t="n">
-        <v>17.63</v>
+        <v>23.74</v>
       </c>
       <c r="I140" t="n">
         <v>-8.83</v>
@@ -8005,7 +8029,7 @@
         <v>-19.66</v>
       </c>
       <c r="M140" t="n">
-        <v>15.1</v>
+        <v>20.33</v>
       </c>
       <c r="N140" t="b">
         <v>0</v>
@@ -8043,7 +8067,7 @@
         <v>-12.5</v>
       </c>
       <c r="H141" t="n">
-        <v>-10.88</v>
+        <v>-8.789999999999999</v>
       </c>
       <c r="I141" t="n">
         <v>21.54</v>
@@ -8056,7 +8080,7 @@
         <v>-0.95</v>
       </c>
       <c r="M141" t="n">
-        <v>-14.07</v>
+        <v>-12.87</v>
       </c>
       <c r="N141" t="b">
         <v>0</v>
@@ -8094,7 +8118,7 @@
         <v>-37</v>
       </c>
       <c r="H142" t="n">
-        <v>50.12</v>
+        <v>60.29</v>
       </c>
       <c r="I142" t="n">
         <v>18.38</v>
@@ -8107,7 +8131,7 @@
         <v>-5.11</v>
       </c>
       <c r="M142" t="n">
-        <v>46.94</v>
+        <v>56.21</v>
       </c>
       <c r="N142" t="b">
         <v>1</v>
@@ -8149,7 +8173,7 @@
         <v>-3.4</v>
       </c>
       <c r="H143" t="n">
-        <v>6.93</v>
+        <v>11.74</v>
       </c>
       <c r="I143" t="n">
         <v>30.48</v>
@@ -8162,7 +8186,7 @@
         <v>-0.9</v>
       </c>
       <c r="M143" t="n">
-        <v>3.74</v>
+        <v>7.66</v>
       </c>
       <c r="N143" t="b">
         <v>0</v>
@@ -8200,7 +8224,7 @@
         <v>-23.4</v>
       </c>
       <c r="H144" t="n">
-        <v>1.51</v>
+        <v>-1.32</v>
       </c>
       <c r="I144" t="n">
         <v>-3.58</v>
@@ -8213,7 +8237,7 @@
         <v>-17.98</v>
       </c>
       <c r="M144" t="n">
-        <v>-1.67</v>
+        <v>-5.39</v>
       </c>
       <c r="N144" t="b">
         <v>0</v>
@@ -8251,7 +8275,7 @@
         <v>-28.9</v>
       </c>
       <c r="H145" t="n">
-        <v>-13.74</v>
+        <v>-13.78</v>
       </c>
       <c r="I145" t="n">
         <v>-12.9</v>
@@ -8264,7 +8288,7 @@
         <v>-23.19</v>
       </c>
       <c r="M145" t="n">
-        <v>-16.92</v>
+        <v>-17.85</v>
       </c>
       <c r="N145" t="b">
         <v>0</v>
@@ -8302,7 +8326,7 @@
         <v>-26.8</v>
       </c>
       <c r="H146" t="n">
-        <v>27.97</v>
+        <v>25.57</v>
       </c>
       <c r="I146" t="n">
         <v>4.56</v>
@@ -8315,7 +8339,7 @@
         <v>-4.09</v>
       </c>
       <c r="M146" t="n">
-        <v>24.79</v>
+        <v>21.5</v>
       </c>
       <c r="N146" t="b">
         <v>1</v>
@@ -8357,7 +8381,7 @@
         <v>-9.800000000000001</v>
       </c>
       <c r="H147" t="n">
-        <v>-20.9</v>
+        <v>-19.93</v>
       </c>
       <c r="I147" t="n">
         <v>-4.09</v>
@@ -8370,7 +8394,7 @@
         <v>-15.24</v>
       </c>
       <c r="M147" t="n">
-        <v>-25.29</v>
+        <v>-25.22</v>
       </c>
       <c r="N147" t="b">
         <v>0</v>
@@ -8408,7 +8432,7 @@
         <v>21</v>
       </c>
       <c r="H148" t="n">
-        <v>0.27</v>
+        <v>3.36</v>
       </c>
       <c r="I148" t="n">
         <v>-0.72</v>
@@ -8421,7 +8445,7 @@
         <v>-7.35</v>
       </c>
       <c r="M148" t="n">
-        <v>-4.12</v>
+        <v>-1.94</v>
       </c>
       <c r="N148" t="b">
         <v>0</v>
@@ -8459,7 +8483,7 @@
         <v>13.2</v>
       </c>
       <c r="H149" t="n">
-        <v>60.98</v>
+        <v>58.62</v>
       </c>
       <c r="I149" t="n">
         <v>8.130000000000001</v>
@@ -8472,7 +8496,7 @@
         <v>-2.36</v>
       </c>
       <c r="M149" t="n">
-        <v>56.59</v>
+        <v>53.33</v>
       </c>
       <c r="N149" t="b">
         <v>0</v>
@@ -8510,7 +8534,7 @@
         <v>6.1</v>
       </c>
       <c r="H150" t="n">
-        <v>2.65</v>
+        <v>3.65</v>
       </c>
       <c r="I150" t="n">
         <v>10.43</v>
@@ -8523,7 +8547,7 @@
         <v>-1.51</v>
       </c>
       <c r="M150" t="n">
-        <v>-1.74</v>
+        <v>-1.64</v>
       </c>
       <c r="N150" t="b">
         <v>0</v>
@@ -8561,7 +8585,7 @@
         <v>6.5</v>
       </c>
       <c r="H151" t="n">
-        <v>-3.32</v>
+        <v>0.23</v>
       </c>
       <c r="I151" t="n">
         <v>-0.04</v>
@@ -8574,7 +8598,7 @@
         <v>-4.12</v>
       </c>
       <c r="M151" t="n">
-        <v>-7.71</v>
+        <v>-5.07</v>
       </c>
       <c r="N151" t="b">
         <v>0</v>
@@ -8612,7 +8636,7 @@
         <v>-36.5</v>
       </c>
       <c r="H152" t="n">
-        <v>-34.33</v>
+        <v>-32.57</v>
       </c>
       <c r="I152" t="n">
         <v>-27.75</v>
@@ -8625,7 +8649,7 @@
         <v>-31.28</v>
       </c>
       <c r="M152" t="n">
-        <v>-38.17</v>
+        <v>-37.3</v>
       </c>
       <c r="N152" t="b">
         <v>1</v>
@@ -8663,7 +8687,7 @@
         <v>-14.5</v>
       </c>
       <c r="H153" t="n">
-        <v>-11.36</v>
+        <v>-9.06</v>
       </c>
       <c r="I153" t="n">
         <v>4.48</v>
@@ -8676,7 +8700,7 @@
         <v>-3.33</v>
       </c>
       <c r="M153" t="n">
-        <v>-15.2</v>
+        <v>-13.79</v>
       </c>
       <c r="N153" t="b">
         <v>0</v>
@@ -8714,7 +8738,7 @@
         <v>1.7</v>
       </c>
       <c r="H154" t="n">
-        <v>-0.86</v>
+        <v>-5.51</v>
       </c>
       <c r="I154" t="n">
         <v>8.859999999999999</v>
@@ -8727,7 +8751,7 @@
         <v>-3.27</v>
       </c>
       <c r="M154" t="n">
-        <v>-4.7</v>
+        <v>-10.24</v>
       </c>
       <c r="N154" t="b">
         <v>0</v>
@@ -8765,7 +8789,7 @@
         <v>48.1</v>
       </c>
       <c r="H155" t="n">
-        <v>6.9</v>
+        <v>9.59</v>
       </c>
       <c r="I155" t="n">
         <v>0.16</v>
@@ -8778,7 +8802,7 @@
         <v>-8.890000000000001</v>
       </c>
       <c r="M155" t="n">
-        <v>3.06</v>
+        <v>4.85</v>
       </c>
       <c r="N155" t="b">
         <v>0</v>
@@ -8816,7 +8840,7 @@
         <v>-38.7</v>
       </c>
       <c r="H156" t="n">
-        <v>22.21</v>
+        <v>26.39</v>
       </c>
       <c r="I156" t="n">
         <v>17.17</v>
@@ -8829,7 +8853,7 @@
         <v>-0.54</v>
       </c>
       <c r="M156" t="n">
-        <v>18.37</v>
+        <v>21.66</v>
       </c>
       <c r="N156" t="b">
         <v>1</v>
@@ -8867,7 +8891,7 @@
         <v>24.9</v>
       </c>
       <c r="H157" t="n">
-        <v>2.46</v>
+        <v>1.27</v>
       </c>
       <c r="I157" t="n">
         <v>10.45</v>
@@ -8880,7 +8904,7 @@
         <v>-0.49</v>
       </c>
       <c r="M157" t="n">
-        <v>-1.38</v>
+        <v>-3.47</v>
       </c>
       <c r="N157" t="b">
         <v>0</v>
@@ -8918,7 +8942,7 @@
         <v>-34.6</v>
       </c>
       <c r="H158" t="n">
-        <v>19.64</v>
+        <v>20.12</v>
       </c>
       <c r="I158" t="n">
         <v>6.67</v>
@@ -8931,7 +8955,7 @@
         <v>-3.06</v>
       </c>
       <c r="M158" t="n">
-        <v>15.8</v>
+        <v>15.38</v>
       </c>
       <c r="N158" t="b">
         <v>1</v>
@@ -8969,7 +8993,7 @@
         <v>-21.4</v>
       </c>
       <c r="H159" t="n">
-        <v>-3.24</v>
+        <v>-9.9</v>
       </c>
       <c r="I159" t="n">
         <v>2.8</v>
@@ -8982,7 +9006,7 @@
         <v>-2.27</v>
       </c>
       <c r="M159" t="n">
-        <v>-7.08</v>
+        <v>-14.64</v>
       </c>
       <c r="N159" t="b">
         <v>0</v>
@@ -9020,7 +9044,7 @@
         <v>-11.8</v>
       </c>
       <c r="H160" t="n">
-        <v>4.3</v>
+        <v>5.1</v>
       </c>
       <c r="I160" t="n">
         <v>9.76</v>
@@ -9028,12 +9052,14 @@
       <c r="J160" t="n">
         <v>10.33</v>
       </c>
-      <c r="K160" t="inlineStr"/>
+      <c r="K160" t="n">
+        <v>5.1</v>
+      </c>
       <c r="L160" t="n">
         <v>-1.63</v>
       </c>
       <c r="M160" t="n">
-        <v>0.35</v>
+        <v>0.25</v>
       </c>
       <c r="N160" t="b">
         <v>1</v>
@@ -9071,7 +9097,7 @@
         <v>0.1</v>
       </c>
       <c r="H161" t="n">
-        <v>-6.05</v>
+        <v>-2.62</v>
       </c>
       <c r="I161" t="n">
         <v>-2.83</v>
@@ -9079,12 +9105,14 @@
       <c r="J161" t="n">
         <v>1.23</v>
       </c>
-      <c r="K161" t="inlineStr"/>
+      <c r="K161" t="n">
+        <v>-2.62</v>
+      </c>
       <c r="L161" t="n">
         <v>-5.45</v>
       </c>
       <c r="M161" t="n">
-        <v>-10</v>
+        <v>-7.47</v>
       </c>
       <c r="N161" t="b">
         <v>1</v>
@@ -9122,7 +9150,7 @@
         <v>-13.8</v>
       </c>
       <c r="H162" t="n">
-        <v>15.79</v>
+        <v>14.93</v>
       </c>
       <c r="I162" t="n">
         <v>4.67</v>
@@ -9130,12 +9158,14 @@
       <c r="J162" t="n">
         <v>4.13</v>
       </c>
-      <c r="K162" t="inlineStr"/>
+      <c r="K162" t="n">
+        <v>14.93</v>
+      </c>
       <c r="L162" t="n">
         <v>-5.7</v>
       </c>
       <c r="M162" t="n">
-        <v>11.84</v>
+        <v>10.08</v>
       </c>
       <c r="N162" t="b">
         <v>0</v>
@@ -9177,7 +9207,7 @@
         <v>-8.800000000000001</v>
       </c>
       <c r="H163" t="n">
-        <v>12.33</v>
+        <v>11.01</v>
       </c>
       <c r="I163" t="n">
         <v>15.97</v>
@@ -9185,12 +9215,14 @@
       <c r="J163" t="n">
         <v>16.69</v>
       </c>
-      <c r="K163" t="inlineStr"/>
+      <c r="K163" t="n">
+        <v>11.01</v>
+      </c>
       <c r="L163" t="n">
         <v>-0.79</v>
       </c>
       <c r="M163" t="n">
-        <v>8.380000000000001</v>
+        <v>6.16</v>
       </c>
       <c r="N163" t="b">
         <v>0</v>
@@ -9228,7 +9260,7 @@
         <v>24.1</v>
       </c>
       <c r="H164" t="n">
-        <v>2.5</v>
+        <v>2.89</v>
       </c>
       <c r="I164" t="n">
         <v>-8.31</v>
@@ -9236,12 +9268,14 @@
       <c r="J164" t="n">
         <v>-17.97</v>
       </c>
-      <c r="K164" t="inlineStr"/>
+      <c r="K164" t="n">
+        <v>2.87</v>
+      </c>
       <c r="L164" t="n">
         <v>-18.31</v>
       </c>
       <c r="M164" t="n">
-        <v>-0.66</v>
+        <v>-1.15</v>
       </c>
       <c r="N164" t="b">
         <v>1</v>
@@ -9279,7 +9313,7 @@
         <v>-15.9</v>
       </c>
       <c r="H165" t="n">
-        <v>15.14</v>
+        <v>20.25</v>
       </c>
       <c r="I165" t="n">
         <v>10.45</v>
@@ -9287,12 +9321,14 @@
       <c r="J165" t="n">
         <v>17.86</v>
       </c>
-      <c r="K165" t="inlineStr"/>
+      <c r="K165" t="n">
+        <v>19.53</v>
+      </c>
       <c r="L165" t="n">
         <v>-0.31</v>
       </c>
       <c r="M165" t="n">
-        <v>11.99</v>
+        <v>16.21</v>
       </c>
       <c r="N165" t="b">
         <v>1</v>
@@ -9330,7 +9366,7 @@
         <v>-23.3</v>
       </c>
       <c r="H166" t="n">
-        <v>-14.44</v>
+        <v>-17.44</v>
       </c>
       <c r="I166" t="n">
         <v>-20.42</v>
@@ -9338,12 +9374,14 @@
       <c r="J166" t="n">
         <v>-13.44</v>
       </c>
-      <c r="K166" t="inlineStr"/>
+      <c r="K166" t="n">
+        <v>-15.39</v>
+      </c>
       <c r="L166" t="n">
         <v>-27.45</v>
       </c>
       <c r="M166" t="n">
-        <v>-17.59</v>
+        <v>-21.48</v>
       </c>
       <c r="N166" t="b">
         <v>0</v>
@@ -9381,7 +9419,7 @@
         <v>28.9</v>
       </c>
       <c r="H167" t="n">
-        <v>-4.86</v>
+        <v>-4.18</v>
       </c>
       <c r="I167" t="n">
         <v>8.06</v>
@@ -9396,7 +9434,7 @@
         <v>-2.79</v>
       </c>
       <c r="M167" t="n">
-        <v>-8.9</v>
+        <v>-9.119999999999999</v>
       </c>
       <c r="N167" t="b">
         <v>0</v>
@@ -9434,7 +9472,7 @@
         <v>40.1</v>
       </c>
       <c r="H168" t="n">
-        <v>23.3</v>
+        <v>29.37</v>
       </c>
       <c r="I168" t="n">
         <v>15.9</v>
@@ -9449,7 +9487,7 @@
         <v>-5.87</v>
       </c>
       <c r="M168" t="n">
-        <v>19.25</v>
+        <v>24.43</v>
       </c>
       <c r="N168" t="b">
         <v>0</v>
@@ -9487,7 +9525,7 @@
         <v>-27.3</v>
       </c>
       <c r="H169" t="n">
-        <v>1.69</v>
+        <v>1.24</v>
       </c>
       <c r="I169" t="n">
         <v>0.75</v>
@@ -9502,7 +9540,7 @@
         <v>-5.46</v>
       </c>
       <c r="M169" t="n">
-        <v>-2.23</v>
+        <v>-3.58</v>
       </c>
       <c r="N169" t="b">
         <v>0</v>
@@ -9540,7 +9578,7 @@
         <v>19.7</v>
       </c>
       <c r="H170" t="n">
-        <v>-29.71</v>
+        <v>-27.27</v>
       </c>
       <c r="I170" t="n">
         <v>-4.49</v>
@@ -9555,7 +9593,7 @@
         <v>-13.7</v>
       </c>
       <c r="M170" t="n">
-        <v>-33.63</v>
+        <v>-32.09</v>
       </c>
       <c r="N170" t="b">
         <v>0</v>
@@ -9593,7 +9631,7 @@
         <v>-21.3</v>
       </c>
       <c r="H171" t="n">
-        <v>-15.33</v>
+        <v>-11.78</v>
       </c>
       <c r="I171" t="n">
         <v>7.16</v>
@@ -9608,7 +9646,7 @@
         <v>-11.9</v>
       </c>
       <c r="M171" t="n">
-        <v>-19.26</v>
+        <v>-16.6</v>
       </c>
       <c r="N171" t="b">
         <v>0</v>
@@ -9646,7 +9684,7 @@
         <v>-21.8</v>
       </c>
       <c r="H172" t="n">
-        <v>-35.04</v>
+        <v>-35.33</v>
       </c>
       <c r="I172" t="n">
         <v>-18.97</v>
@@ -9661,7 +9699,7 @@
         <v>-26.82</v>
       </c>
       <c r="M172" t="n">
-        <v>-38.96</v>
+        <v>-40.15</v>
       </c>
       <c r="N172" t="b">
         <v>1</v>
@@ -9699,7 +9737,7 @@
         <v>-37.6</v>
       </c>
       <c r="H173" t="n">
-        <v>-18.46</v>
+        <v>-19.36</v>
       </c>
       <c r="I173" t="n">
         <v>15.2</v>
@@ -9714,7 +9752,7 @@
         <v>-10.3</v>
       </c>
       <c r="M173" t="n">
-        <v>-21.38</v>
+        <v>-23.16</v>
       </c>
       <c r="N173" t="b">
         <v>0</v>
@@ -9752,7 +9790,7 @@
         <v>53.8</v>
       </c>
       <c r="H174" t="n">
-        <v>34.45</v>
+        <v>47.7</v>
       </c>
       <c r="I174" t="n">
         <v>4.09</v>
@@ -9767,7 +9805,7 @@
         <v>-8.66</v>
       </c>
       <c r="M174" t="n">
-        <v>31.54</v>
+        <v>43.9</v>
       </c>
       <c r="N174" t="b">
         <v>0</v>
@@ -9809,7 +9847,7 @@
         <v>-5.7</v>
       </c>
       <c r="H175" t="n">
-        <v>34.91</v>
+        <v>37</v>
       </c>
       <c r="I175" t="n">
         <v>17.92</v>
@@ -9824,7 +9862,7 @@
         <v>-7.48</v>
       </c>
       <c r="M175" t="n">
-        <v>31.99</v>
+        <v>33.2</v>
       </c>
       <c r="N175" t="b">
         <v>0</v>
@@ -9862,7 +9900,7 @@
         <v>-39.3</v>
       </c>
       <c r="H176" t="n">
-        <v>11.06</v>
+        <v>14.47</v>
       </c>
       <c r="I176" t="n">
         <v>11.34</v>
@@ -9877,7 +9915,7 @@
         <v>-5.3</v>
       </c>
       <c r="M176" t="n">
-        <v>8.15</v>
+        <v>10.67</v>
       </c>
       <c r="N176" t="b">
         <v>0</v>
@@ -9915,7 +9953,7 @@
         <v>57</v>
       </c>
       <c r="H177" t="n">
-        <v>33.95</v>
+        <v>35.19</v>
       </c>
       <c r="I177" t="n">
         <v>-11.21</v>
@@ -9930,7 +9968,7 @@
         <v>-13.87</v>
       </c>
       <c r="M177" t="n">
-        <v>31.04</v>
+        <v>31.39</v>
       </c>
       <c r="N177" t="b">
         <v>1</v>
@@ -9968,7 +10006,7 @@
         <v>-21.8</v>
       </c>
       <c r="H178" t="n">
-        <v>19.46</v>
+        <v>24.65</v>
       </c>
       <c r="I178" t="n">
         <v>1.71</v>
@@ -9983,7 +10021,7 @@
         <v>-6.18</v>
       </c>
       <c r="M178" t="n">
-        <v>16.54</v>
+        <v>20.85</v>
       </c>
       <c r="N178" t="b">
         <v>1</v>
@@ -10021,7 +10059,7 @@
         <v>1</v>
       </c>
       <c r="H179" t="n">
-        <v>-35.81</v>
+        <v>-38.31</v>
       </c>
       <c r="I179" t="n">
         <v>-11.52</v>
@@ -10036,7 +10074,7 @@
         <v>-16.26</v>
       </c>
       <c r="M179" t="n">
-        <v>-38.77</v>
+        <v>-42.16</v>
       </c>
       <c r="N179" t="b">
         <v>1</v>
@@ -10074,7 +10112,7 @@
         <v>45.4</v>
       </c>
       <c r="H180" t="n">
-        <v>-20.11</v>
+        <v>-20.63</v>
       </c>
       <c r="I180" t="n">
         <v>-1.72</v>
@@ -10089,7 +10127,7 @@
         <v>-23.15</v>
       </c>
       <c r="M180" t="n">
-        <v>-23.07</v>
+        <v>-24.47</v>
       </c>
       <c r="N180" t="b">
         <v>0</v>
@@ -10127,7 +10165,7 @@
         <v>49.6</v>
       </c>
       <c r="H181" t="n">
-        <v>15.36</v>
+        <v>19.1</v>
       </c>
       <c r="I181" t="n">
         <v>6.34</v>
@@ -10142,7 +10180,7 @@
         <v>-20.75</v>
       </c>
       <c r="M181" t="n">
-        <v>12.4</v>
+        <v>15.25</v>
       </c>
       <c r="N181" t="b">
         <v>0</v>
@@ -10180,7 +10218,7 @@
         <v>55.3</v>
       </c>
       <c r="H182" t="n">
-        <v>-33.37</v>
+        <v>-28.4</v>
       </c>
       <c r="I182" t="n">
         <v>3.73</v>
@@ -10195,7 +10233,7 @@
         <v>-22.94</v>
       </c>
       <c r="M182" t="n">
-        <v>-36.33</v>
+        <v>-32.25</v>
       </c>
       <c r="N182" t="b">
         <v>0</v>
@@ -10233,7 +10271,7 @@
         <v>76.5</v>
       </c>
       <c r="H183" t="n">
-        <v>-9.300000000000001</v>
+        <v>-8.83</v>
       </c>
       <c r="I183" t="n">
         <v>-5.56</v>
@@ -10248,7 +10286,7 @@
         <v>-33.97</v>
       </c>
       <c r="M183" t="n">
-        <v>-12.26</v>
+        <v>-12.68</v>
       </c>
       <c r="N183" t="b">
         <v>0</v>
@@ -10286,7 +10324,7 @@
         <v>77.90000000000001</v>
       </c>
       <c r="H184" t="n">
-        <v>-2.19</v>
+        <v>-1.25</v>
       </c>
       <c r="I184" t="n">
         <v>-3.53</v>
@@ -10301,7 +10339,7 @@
         <v>-20.26</v>
       </c>
       <c r="M184" t="n">
-        <v>-5.16</v>
+        <v>-5.1</v>
       </c>
       <c r="N184" t="b">
         <v>0</v>
@@ -10339,7 +10377,7 @@
         <v>57.6</v>
       </c>
       <c r="H185" t="n">
-        <v>22.75</v>
+        <v>27.8</v>
       </c>
       <c r="I185" t="n">
         <v>14.81</v>
@@ -10354,7 +10392,7 @@
         <v>-5.11</v>
       </c>
       <c r="M185" t="n">
-        <v>19.79</v>
+        <v>23.96</v>
       </c>
       <c r="N185" t="b">
         <v>0</v>
@@ -10392,7 +10430,7 @@
         <v>32.1</v>
       </c>
       <c r="H186" t="n">
-        <v>-11.82</v>
+        <v>-11.13</v>
       </c>
       <c r="I186" t="n">
         <v>16.93</v>
@@ -10407,7 +10445,7 @@
         <v>-24.48</v>
       </c>
       <c r="M186" t="n">
-        <v>-14.78</v>
+        <v>-14.97</v>
       </c>
       <c r="N186" t="b">
         <v>0</v>
@@ -10445,7 +10483,7 @@
         <v>51.8</v>
       </c>
       <c r="H187" t="n">
-        <v>-12.24</v>
+        <v>-11.18</v>
       </c>
       <c r="I187" t="n">
         <v>10.75</v>
@@ -10460,7 +10498,7 @@
         <v>-25.09</v>
       </c>
       <c r="M187" t="n">
-        <v>-15.2</v>
+        <v>-15.02</v>
       </c>
       <c r="N187" t="b">
         <v>0</v>
@@ -10498,7 +10536,7 @@
         <v>32.3</v>
       </c>
       <c r="H188" t="n">
-        <v>-38.04</v>
+        <v>-39.58</v>
       </c>
       <c r="I188" t="n">
         <v>-20.76</v>
@@ -10513,7 +10551,7 @@
         <v>-27.91</v>
       </c>
       <c r="M188" t="n">
-        <v>-41</v>
+        <v>-43.43</v>
       </c>
       <c r="N188" t="b">
         <v>1</v>
@@ -10551,7 +10589,7 @@
         <v>15.7</v>
       </c>
       <c r="H189" t="n">
-        <v>-17.55</v>
+        <v>-16.2</v>
       </c>
       <c r="I189" t="n">
         <v>-0.87</v>
@@ -10566,7 +10604,7 @@
         <v>-29.01</v>
       </c>
       <c r="M189" t="n">
-        <v>-20.51</v>
+        <v>-20.05</v>
       </c>
       <c r="N189" t="b">
         <v>0</v>
@@ -10604,7 +10642,7 @@
         <v>63.7</v>
       </c>
       <c r="H190" t="n">
-        <v>-23.46</v>
+        <v>-19.28</v>
       </c>
       <c r="I190" t="n">
         <v>-2.16</v>
@@ -10619,7 +10657,7 @@
         <v>-19.1</v>
       </c>
       <c r="M190" t="n">
-        <v>-26.42</v>
+        <v>-23.13</v>
       </c>
       <c r="N190" t="b">
         <v>0</v>
@@ -10657,7 +10695,7 @@
         <v>3.7</v>
       </c>
       <c r="H191" t="n">
-        <v>-13.44</v>
+        <v>-10.18</v>
       </c>
       <c r="I191" t="n">
         <v>-1.11</v>
@@ -10672,7 +10710,7 @@
         <v>-25.46</v>
       </c>
       <c r="M191" t="n">
-        <v>-16.4</v>
+        <v>-14.03</v>
       </c>
       <c r="N191" t="b">
         <v>1</v>
@@ -10710,7 +10748,7 @@
         <v>42.4</v>
       </c>
       <c r="H192" t="n">
-        <v>-20.44</v>
+        <v>-19.56</v>
       </c>
       <c r="I192" t="n">
         <v>2.16</v>
@@ -10725,7 +10763,7 @@
         <v>-15.76</v>
       </c>
       <c r="M192" t="n">
-        <v>-23.4</v>
+        <v>-23.41</v>
       </c>
       <c r="N192" t="b">
         <v>1</v>
@@ -10763,7 +10801,7 @@
         <v>28.2</v>
       </c>
       <c r="H193" t="n">
-        <v>-14.72</v>
+        <v>-13.73</v>
       </c>
       <c r="I193" t="n">
         <v>-1.71</v>
@@ -10778,7 +10816,7 @@
         <v>-23.43</v>
       </c>
       <c r="M193" t="n">
-        <v>-17.68</v>
+        <v>-17.57</v>
       </c>
       <c r="N193" t="b">
         <v>1</v>
@@ -10816,7 +10854,7 @@
         <v>28.6</v>
       </c>
       <c r="H194" t="n">
-        <v>-13.44</v>
+        <v>-3.11</v>
       </c>
       <c r="I194" t="n">
         <v>2.81</v>
@@ -10831,7 +10869,7 @@
         <v>-18.87</v>
       </c>
       <c r="M194" t="n">
-        <v>-16.4</v>
+        <v>-6.96</v>
       </c>
       <c r="N194" t="b">
         <v>1</v>
@@ -10869,7 +10907,7 @@
         <v>89.09999999999999</v>
       </c>
       <c r="H195" t="n">
-        <v>15.45</v>
+        <v>23.33</v>
       </c>
       <c r="I195" t="n">
         <v>18.45</v>
@@ -10884,7 +10922,7 @@
         <v>-9.029999999999999</v>
       </c>
       <c r="M195" t="n">
-        <v>12.49</v>
+        <v>19.49</v>
       </c>
       <c r="N195" t="b">
         <v>0</v>
@@ -10922,7 +10960,7 @@
         <v>50.5</v>
       </c>
       <c r="H196" t="n">
-        <v>-10.82</v>
+        <v>-9.91</v>
       </c>
       <c r="I196" t="n">
         <v>-2.26</v>
@@ -10937,7 +10975,7 @@
         <v>-20.74</v>
       </c>
       <c r="M196" t="n">
-        <v>-13.78</v>
+        <v>-13.76</v>
       </c>
       <c r="N196" t="b">
         <v>0</v>
@@ -10975,7 +11013,7 @@
         <v>33.1</v>
       </c>
       <c r="H197" t="n">
-        <v>2.84</v>
+        <v>4.83</v>
       </c>
       <c r="I197" t="n">
         <v>4.68</v>
@@ -10990,7 +11028,7 @@
         <v>-26.7</v>
       </c>
       <c r="M197" t="n">
-        <v>-0.12</v>
+        <v>0.98</v>
       </c>
       <c r="N197" t="b">
         <v>0</v>
@@ -11028,7 +11066,7 @@
         <v>46.3</v>
       </c>
       <c r="H198" t="n">
-        <v>-26.8</v>
+        <v>-27.54</v>
       </c>
       <c r="I198" t="n">
         <v>-3.24</v>
@@ -11043,7 +11081,7 @@
         <v>-22.77</v>
       </c>
       <c r="M198" t="n">
-        <v>-29.76</v>
+        <v>-31.39</v>
       </c>
       <c r="N198" t="b">
         <v>0</v>
@@ -11081,7 +11119,7 @@
         <v>-13.8</v>
       </c>
       <c r="H199" t="n">
-        <v>9.390000000000001</v>
+        <v>5.7</v>
       </c>
       <c r="I199" t="n">
         <v>6.03</v>
@@ -11096,7 +11134,7 @@
         <v>-13.77</v>
       </c>
       <c r="M199" t="n">
-        <v>6.43</v>
+        <v>1.86</v>
       </c>
       <c r="N199" t="b">
         <v>0</v>
@@ -11134,7 +11172,7 @@
         <v>21.8</v>
       </c>
       <c r="H200" t="n">
-        <v>-30.1</v>
+        <v>-27.95</v>
       </c>
       <c r="I200" t="n">
         <v>-6.34</v>
@@ -11149,7 +11187,7 @@
         <v>-30.04</v>
       </c>
       <c r="M200" t="n">
-        <v>-33.06</v>
+        <v>-31.8</v>
       </c>
       <c r="N200" t="b">
         <v>1</v>
@@ -11187,7 +11225,7 @@
         <v>40.3</v>
       </c>
       <c r="H201" t="n">
-        <v>-30.06</v>
+        <v>-31.09</v>
       </c>
       <c r="I201" t="n">
         <v>1.24</v>
@@ -11202,7 +11240,7 @@
         <v>-20.5</v>
       </c>
       <c r="M201" t="n">
-        <v>-33.02</v>
+        <v>-34.94</v>
       </c>
       <c r="N201" t="b">
         <v>0</v>
@@ -11240,7 +11278,7 @@
         <v>36.6</v>
       </c>
       <c r="H202" t="n">
-        <v>281.26</v>
+        <v>313.06</v>
       </c>
       <c r="I202" t="n">
         <v>-4.23</v>
@@ -11255,7 +11293,7 @@
         <v>-11.51</v>
       </c>
       <c r="M202" t="n">
-        <v>278.3</v>
+        <v>309.21</v>
       </c>
       <c r="N202" t="b">
         <v>0</v>
@@ -11293,7 +11331,7 @@
         <v>24.1</v>
       </c>
       <c r="H203" t="n">
-        <v>-16.34</v>
+        <v>-14.07</v>
       </c>
       <c r="I203" t="n">
         <v>-1.6</v>
@@ -11308,7 +11346,7 @@
         <v>-22.54</v>
       </c>
       <c r="M203" t="n">
-        <v>-19.3</v>
+        <v>-17.92</v>
       </c>
       <c r="N203" t="b">
         <v>1</v>
@@ -11346,7 +11384,7 @@
         <v>50.3</v>
       </c>
       <c r="H204" t="n">
-        <v>-34.87</v>
+        <v>-31.61</v>
       </c>
       <c r="I204" t="n">
         <v>-3.34</v>
@@ -11361,7 +11399,7 @@
         <v>-23.32</v>
       </c>
       <c r="M204" t="n">
-        <v>-37.83</v>
+        <v>-35.46</v>
       </c>
       <c r="N204" t="b">
         <v>0</v>
@@ -11399,7 +11437,7 @@
         <v>24.5</v>
       </c>
       <c r="H205" t="n">
-        <v>-32.65</v>
+        <v>-29.93</v>
       </c>
       <c r="I205" t="n">
         <v>-12.99</v>
@@ -11414,7 +11452,7 @@
         <v>-22.54</v>
       </c>
       <c r="M205" t="n">
-        <v>-35.61</v>
+        <v>-33.78</v>
       </c>
       <c r="N205" t="b">
         <v>1</v>
@@ -11452,7 +11490,7 @@
         <v>-4</v>
       </c>
       <c r="H206" t="n">
-        <v>-38.23</v>
+        <v>-34.76</v>
       </c>
       <c r="I206" t="n">
         <v>-1.59</v>
@@ -11467,7 +11505,7 @@
         <v>-25.38</v>
       </c>
       <c r="M206" t="n">
-        <v>-41.19</v>
+        <v>-38.61</v>
       </c>
       <c r="N206" t="b">
         <v>0</v>
@@ -11505,7 +11543,7 @@
         <v>14.8</v>
       </c>
       <c r="H207" t="n">
-        <v>-37.88</v>
+        <v>-33.62</v>
       </c>
       <c r="I207" t="n">
         <v>-2.48</v>
@@ -11520,7 +11558,7 @@
         <v>-40.98</v>
       </c>
       <c r="M207" t="n">
-        <v>-40.84</v>
+        <v>-37.47</v>
       </c>
       <c r="N207" t="b">
         <v>0</v>
@@ -11558,7 +11596,7 @@
         <v>-27.6</v>
       </c>
       <c r="H208" t="n">
-        <v>-23.34</v>
+        <v>-22.13</v>
       </c>
       <c r="I208" t="n">
         <v>-0.36</v>
@@ -11573,7 +11611,7 @@
         <v>-19.41</v>
       </c>
       <c r="M208" t="n">
-        <v>-26.3</v>
+        <v>-25.98</v>
       </c>
       <c r="N208" t="b">
         <v>0</v>
@@ -11611,7 +11649,7 @@
         <v>9.1</v>
       </c>
       <c r="H209" t="n">
-        <v>-37.93</v>
+        <v>-34.33</v>
       </c>
       <c r="I209" t="n">
         <v>-2.83</v>
@@ -11626,7 +11664,7 @@
         <v>-23.78</v>
       </c>
       <c r="M209" t="n">
-        <v>-40.89</v>
+        <v>-38.18</v>
       </c>
       <c r="N209" t="b">
         <v>0</v>
@@ -11664,7 +11702,7 @@
         <v>11</v>
       </c>
       <c r="H210" t="n">
-        <v>-13.45</v>
+        <v>-9.140000000000001</v>
       </c>
       <c r="I210" t="n">
         <v>3.38</v>
@@ -11679,7 +11717,7 @@
         <v>-18.71</v>
       </c>
       <c r="M210" t="n">
-        <v>-16.41</v>
+        <v>-12.99</v>
       </c>
       <c r="N210" t="b">
         <v>0</v>
@@ -11717,7 +11755,7 @@
         <v>31.2</v>
       </c>
       <c r="H211" t="n">
-        <v>-24.36</v>
+        <v>-25.71</v>
       </c>
       <c r="I211" t="n">
         <v>-11.26</v>
@@ -11732,7 +11770,7 @@
         <v>-22.9</v>
       </c>
       <c r="M211" t="n">
-        <v>-27.32</v>
+        <v>-29.56</v>
       </c>
       <c r="N211" t="b">
         <v>0</v>
@@ -11770,7 +11808,7 @@
         <v>19.3</v>
       </c>
       <c r="H212" t="n">
-        <v>-7.02</v>
+        <v>-4.26</v>
       </c>
       <c r="I212" t="n">
         <v>11.79</v>
@@ -11785,7 +11823,7 @@
         <v>-16.62</v>
       </c>
       <c r="M212" t="n">
-        <v>-9.98</v>
+        <v>-8.109999999999999</v>
       </c>
       <c r="N212" t="b">
         <v>0</v>
@@ -11823,7 +11861,7 @@
         <v>-8.699999999999999</v>
       </c>
       <c r="H213" t="n">
-        <v>-12.46</v>
+        <v>-10.76</v>
       </c>
       <c r="I213" t="n">
         <v>17.25</v>
@@ -11838,7 +11876,7 @@
         <v>-4.65</v>
       </c>
       <c r="M213" t="n">
-        <v>-15.42</v>
+        <v>-14.61</v>
       </c>
       <c r="N213" t="b">
         <v>1</v>
@@ -11876,7 +11914,7 @@
         <v>15.2</v>
       </c>
       <c r="H214" t="n">
-        <v>-24.49</v>
+        <v>-22.69</v>
       </c>
       <c r="I214" t="n">
         <v>5.36</v>
@@ -11891,7 +11929,7 @@
         <v>-28.18</v>
       </c>
       <c r="M214" t="n">
-        <v>-27.45</v>
+        <v>-26.54</v>
       </c>
       <c r="N214" t="b">
         <v>0</v>
@@ -11929,7 +11967,7 @@
         <v>37.2</v>
       </c>
       <c r="H215" t="n">
-        <v>-37.91</v>
+        <v>-37.72</v>
       </c>
       <c r="I215" t="n">
         <v>-7.64</v>
@@ -11944,7 +11982,7 @@
         <v>-26.24</v>
       </c>
       <c r="M215" t="n">
-        <v>-40.87</v>
+        <v>-41.56</v>
       </c>
       <c r="N215" t="b">
         <v>1</v>
@@ -11986,7 +12024,7 @@
         <v>-0.5</v>
       </c>
       <c r="H216" t="n">
-        <v>45.66</v>
+        <v>46.04</v>
       </c>
       <c r="I216" t="n">
         <v>12.75</v>
@@ -12001,7 +12039,7 @@
         <v>-4.72</v>
       </c>
       <c r="M216" t="n">
-        <v>42.69</v>
+        <v>42.19</v>
       </c>
       <c r="N216" t="b">
         <v>0</v>
@@ -12039,7 +12077,7 @@
         <v>-27.9</v>
       </c>
       <c r="H217" t="n">
-        <v>-51.67</v>
+        <v>-54.65</v>
       </c>
       <c r="I217" t="n">
         <v>-5.72</v>
@@ -12054,7 +12092,7 @@
         <v>-11.08</v>
       </c>
       <c r="M217" t="n">
-        <v>-54.64</v>
+        <v>-58.5</v>
       </c>
       <c r="N217" t="b">
         <v>0</v>
@@ -12092,7 +12130,7 @@
         <v>29.8</v>
       </c>
       <c r="H218" t="n">
-        <v>7.09</v>
+        <v>6.65</v>
       </c>
       <c r="I218" t="n">
         <v>-2.74</v>
@@ -12107,7 +12145,7 @@
         <v>-22.36</v>
       </c>
       <c r="M218" t="n">
-        <v>4.13</v>
+        <v>2.8</v>
       </c>
       <c r="N218" t="b">
         <v>1</v>
@@ -12145,7 +12183,7 @@
         <v>60.9</v>
       </c>
       <c r="H219" t="n">
-        <v>-4.66</v>
+        <v>-4.51</v>
       </c>
       <c r="I219" t="n">
         <v>6.71</v>
@@ -12160,7 +12198,7 @@
         <v>-4.9</v>
       </c>
       <c r="M219" t="n">
-        <v>-7.62</v>
+        <v>-8.359999999999999</v>
       </c>
       <c r="N219" t="b">
         <v>0</v>
@@ -12198,7 +12236,7 @@
         <v>-13.4</v>
       </c>
       <c r="H220" t="n">
-        <v>-40</v>
+        <v>-39.47</v>
       </c>
       <c r="I220" t="n">
         <v>0.79</v>
@@ -12213,7 +12251,7 @@
         <v>-15.41</v>
       </c>
       <c r="M220" t="n">
-        <v>-42.96</v>
+        <v>-43.32</v>
       </c>
       <c r="N220" t="b">
         <v>0</v>
@@ -12251,7 +12289,7 @@
         <v>18.2</v>
       </c>
       <c r="H221" t="n">
-        <v>-19.69</v>
+        <v>-15.5</v>
       </c>
       <c r="I221" t="n">
         <v>-11.28</v>
@@ -12266,7 +12304,7 @@
         <v>-16.87</v>
       </c>
       <c r="M221" t="n">
-        <v>-22.65</v>
+        <v>-19.35</v>
       </c>
       <c r="N221" t="b">
         <v>0</v>
@@ -12304,7 +12342,7 @@
         <v>31.2</v>
       </c>
       <c r="H222" t="n">
-        <v>-16.96</v>
+        <v>-20.43</v>
       </c>
       <c r="I222" t="n">
         <v>-3.17</v>
@@ -12319,7 +12357,7 @@
         <v>-23.66</v>
       </c>
       <c r="M222" t="n">
-        <v>-19.92</v>
+        <v>-24.28</v>
       </c>
       <c r="N222" t="b">
         <v>0</v>
@@ -12357,7 +12395,7 @@
         <v>-1.3</v>
       </c>
       <c r="H223" t="n">
-        <v>-22.79</v>
+        <v>-19.36</v>
       </c>
       <c r="I223" t="n">
         <v>5.29</v>
@@ -12372,7 +12410,7 @@
         <v>-11.87</v>
       </c>
       <c r="M223" t="n">
-        <v>-25.75</v>
+        <v>-23.21</v>
       </c>
       <c r="N223" t="b">
         <v>0</v>
@@ -12410,7 +12448,7 @@
         <v>-29.8</v>
       </c>
       <c r="H224" t="n">
-        <v>31.56</v>
+        <v>45.78</v>
       </c>
       <c r="I224" t="n">
         <v>29.88</v>
@@ -12425,7 +12463,7 @@
         <v>-0.29</v>
       </c>
       <c r="M224" t="n">
-        <v>28.6</v>
+        <v>41.93</v>
       </c>
       <c r="N224" t="b">
         <v>0</v>
@@ -12463,7 +12501,7 @@
         <v>-22.4</v>
       </c>
       <c r="H225" t="n">
-        <v>-18.88</v>
+        <v>-17.45</v>
       </c>
       <c r="I225" t="n">
         <v>5.79</v>
@@ -12478,7 +12516,7 @@
         <v>-9.67</v>
       </c>
       <c r="M225" t="n">
-        <v>-21.84</v>
+        <v>-21.29</v>
       </c>
       <c r="N225" t="b">
         <v>0</v>
@@ -12516,7 +12554,7 @@
         <v>19.3</v>
       </c>
       <c r="H226" t="n">
-        <v>-37.42</v>
+        <v>-34.67</v>
       </c>
       <c r="I226" t="n">
         <v>-16.69</v>
@@ -12531,7 +12569,7 @@
         <v>-36.39</v>
       </c>
       <c r="M226" t="n">
-        <v>-40.38</v>
+        <v>-38.52</v>
       </c>
       <c r="N226" t="b">
         <v>1</v>
@@ -12569,7 +12607,7 @@
         <v>7.6</v>
       </c>
       <c r="H227" t="n">
-        <v>-31.18</v>
+        <v>-30.93</v>
       </c>
       <c r="I227" t="n">
         <v>6.22</v>
@@ -12584,7 +12622,7 @@
         <v>-10.68</v>
       </c>
       <c r="M227" t="n">
-        <v>-34.14</v>
+        <v>-34.78</v>
       </c>
       <c r="N227" t="b">
         <v>0</v>
@@ -12622,7 +12660,7 @@
         <v>68.8</v>
       </c>
       <c r="H228" t="n">
-        <v>2.29</v>
+        <v>5.08</v>
       </c>
       <c r="I228" t="n">
         <v>-1.41</v>
@@ -12637,7 +12675,7 @@
         <v>-19.39</v>
       </c>
       <c r="M228" t="n">
-        <v>-0.67</v>
+        <v>1.23</v>
       </c>
       <c r="N228" t="b">
         <v>0</v>
@@ -12675,7 +12713,7 @@
         <v>8.5</v>
       </c>
       <c r="H229" t="n">
-        <v>-42.84</v>
+        <v>-40.88</v>
       </c>
       <c r="I229" t="n">
         <v>-4.26</v>
@@ -12690,7 +12728,7 @@
         <v>-23.85</v>
       </c>
       <c r="M229" t="n">
-        <v>-45.8</v>
+        <v>-44.73</v>
       </c>
       <c r="N229" t="b">
         <v>0</v>
@@ -12728,7 +12766,7 @@
         <v>-15.2</v>
       </c>
       <c r="H230" t="n">
-        <v>-22.58</v>
+        <v>-19.1</v>
       </c>
       <c r="I230" t="n">
         <v>12.27</v>
@@ -12743,7 +12781,7 @@
         <v>-12.27</v>
       </c>
       <c r="M230" t="n">
-        <v>-25.54</v>
+        <v>-22.95</v>
       </c>
       <c r="N230" t="b">
         <v>0</v>
@@ -12781,7 +12819,7 @@
         <v>-33.1</v>
       </c>
       <c r="H231" t="n">
-        <v>-4.81</v>
+        <v>-13.99</v>
       </c>
       <c r="I231" t="n">
         <v>-13.13</v>
@@ -12796,7 +12834,7 @@
         <v>-21.04</v>
       </c>
       <c r="M231" t="n">
-        <v>-7.78</v>
+        <v>-17.84</v>
       </c>
       <c r="N231" t="b">
         <v>0</v>
@@ -12834,7 +12872,7 @@
         <v>11.8</v>
       </c>
       <c r="H232" t="n">
-        <v>-3.91</v>
+        <v>-1.29</v>
       </c>
       <c r="I232" t="n">
         <v>-1.19</v>
@@ -12849,7 +12887,7 @@
         <v>-17.57</v>
       </c>
       <c r="M232" t="n">
-        <v>-6.87</v>
+        <v>-5.14</v>
       </c>
       <c r="N232" t="b">
         <v>1</v>
@@ -12887,7 +12925,7 @@
         <v>27.5</v>
       </c>
       <c r="H233" t="n">
-        <v>2.35</v>
+        <v>3.41</v>
       </c>
       <c r="I233" t="n">
         <v>8.42</v>
@@ -12902,7 +12940,7 @@
         <v>-2.51</v>
       </c>
       <c r="M233" t="n">
-        <v>-0.61</v>
+        <v>-0.44</v>
       </c>
       <c r="N233" t="b">
         <v>1</v>
@@ -12940,7 +12978,7 @@
         <v>-22.4</v>
       </c>
       <c r="H234" t="n">
-        <v>-6.45</v>
+        <v>-5.43</v>
       </c>
       <c r="I234" t="n">
         <v>9.42</v>
@@ -12955,7 +12993,7 @@
         <v>-2.79</v>
       </c>
       <c r="M234" t="n">
-        <v>-9.41</v>
+        <v>-9.279999999999999</v>
       </c>
       <c r="N234" t="b">
         <v>0</v>
@@ -12993,7 +13031,7 @@
         <v>-14.7</v>
       </c>
       <c r="H235" t="n">
-        <v>-20.98</v>
+        <v>-21.26</v>
       </c>
       <c r="I235" t="n">
         <v>10.3</v>
@@ -13008,7 +13046,7 @@
         <v>-2.6</v>
       </c>
       <c r="M235" t="n">
-        <v>-23.94</v>
+        <v>-25.11</v>
       </c>
       <c r="N235" t="b">
         <v>1</v>
@@ -13050,7 +13088,7 @@
         <v>-9.300000000000001</v>
       </c>
       <c r="H236" t="n">
-        <v>-21.03</v>
+        <v>-21.54</v>
       </c>
       <c r="I236" t="n">
         <v>10.42</v>
@@ -13065,7 +13103,7 @@
         <v>-21.72</v>
       </c>
       <c r="M236" t="n">
-        <v>-23.99</v>
+        <v>-25.39</v>
       </c>
       <c r="N236" t="b">
         <v>1</v>
@@ -13103,7 +13141,7 @@
         <v>-13.5</v>
       </c>
       <c r="H237" t="n">
-        <v>129.91</v>
+        <v>141.42</v>
       </c>
       <c r="I237" t="n">
         <v>18.09</v>
@@ -13118,7 +13156,7 @@
         <v>-14.35</v>
       </c>
       <c r="M237" t="n">
-        <v>126.94</v>
+        <v>137.57</v>
       </c>
       <c r="N237" t="b">
         <v>0</v>
@@ -13156,7 +13194,7 @@
         <v>-27.5</v>
       </c>
       <c r="H238" t="n">
-        <v>-3.92</v>
+        <v>-0.51</v>
       </c>
       <c r="I238" t="n">
         <v>-29.95</v>
@@ -13171,7 +13209,7 @@
         <v>-35.86</v>
       </c>
       <c r="M238" t="n">
-        <v>-6.88</v>
+        <v>-4.36</v>
       </c>
       <c r="N238" t="b">
         <v>0</v>
@@ -13209,7 +13247,7 @@
         <v>11.9</v>
       </c>
       <c r="H239" t="n">
-        <v>-57.46</v>
+        <v>-56.55</v>
       </c>
       <c r="I239" t="n">
         <v>-3.02</v>
@@ -13224,7 +13262,7 @@
         <v>-24.96</v>
       </c>
       <c r="M239" t="n">
-        <v>-60.42</v>
+        <v>-60.4</v>
       </c>
       <c r="N239" t="b">
         <v>0</v>
@@ -13262,7 +13300,7 @@
         <v>5</v>
       </c>
       <c r="H240" t="n">
-        <v>-11.22</v>
+        <v>-6.71</v>
       </c>
       <c r="I240" t="n">
         <v>0.41</v>
@@ -13277,7 +13315,7 @@
         <v>-13.87</v>
       </c>
       <c r="M240" t="n">
-        <v>-14.18</v>
+        <v>-10.55</v>
       </c>
       <c r="N240" t="b">
         <v>0</v>
@@ -13315,7 +13353,7 @@
         <v>-35.9</v>
       </c>
       <c r="H241" t="n">
-        <v>5.91</v>
+        <v>5.54</v>
       </c>
       <c r="I241" t="n">
         <v>18.67</v>
@@ -13330,7 +13368,7 @@
         <v>-6.77</v>
       </c>
       <c r="M241" t="n">
-        <v>2.95</v>
+        <v>1.69</v>
       </c>
       <c r="N241" t="b">
         <v>0</v>
@@ -13368,7 +13406,7 @@
         <v>-25.2</v>
       </c>
       <c r="H242" t="n">
-        <v>-18.51</v>
+        <v>-17.58</v>
       </c>
       <c r="I242" t="n">
         <v>22.53</v>
@@ -13383,7 +13421,7 @@
         <v>-19.27</v>
       </c>
       <c r="M242" t="n">
-        <v>-21.47</v>
+        <v>-21.42</v>
       </c>
       <c r="N242" t="b">
         <v>0</v>
@@ -13421,7 +13459,7 @@
         <v>5.1</v>
       </c>
       <c r="H243" t="n">
-        <v>7.54</v>
+        <v>12.95</v>
       </c>
       <c r="I243" t="n">
         <v>8.77</v>
@@ -13436,7 +13474,7 @@
         <v>-3.54</v>
       </c>
       <c r="M243" t="n">
-        <v>4.58</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="N243" t="b">
         <v>1</v>
@@ -13474,7 +13512,7 @@
         <v>20.8</v>
       </c>
       <c r="H244" t="n">
-        <v>-31.98</v>
+        <v>-29.98</v>
       </c>
       <c r="I244" t="n">
         <v>-10.93</v>
@@ -13489,7 +13527,7 @@
         <v>-27.1</v>
       </c>
       <c r="M244" t="n">
-        <v>-34.94</v>
+        <v>-33.83</v>
       </c>
       <c r="N244" t="b">
         <v>0</v>
@@ -13527,7 +13565,7 @@
         <v>-27.7</v>
       </c>
       <c r="H245" t="n">
-        <v>0.33</v>
+        <v>5.47</v>
       </c>
       <c r="I245" t="n">
         <v>-10.22</v>
@@ -13542,7 +13580,7 @@
         <v>-17.14</v>
       </c>
       <c r="M245" t="n">
-        <v>-2.63</v>
+        <v>1.63</v>
       </c>
       <c r="N245" t="b">
         <v>0</v>
@@ -13580,7 +13618,7 @@
         <v>-24.7</v>
       </c>
       <c r="H246" t="n">
-        <v>-16.6</v>
+        <v>-15.42</v>
       </c>
       <c r="I246" t="n">
         <v>1.65</v>
@@ -13595,7 +13633,7 @@
         <v>-19.04</v>
       </c>
       <c r="M246" t="n">
-        <v>-19.56</v>
+        <v>-19.27</v>
       </c>
       <c r="N246" t="b">
         <v>0</v>
@@ -13633,7 +13671,7 @@
         <v>-34.9</v>
       </c>
       <c r="H247" t="n">
-        <v>-15</v>
+        <v>-15.98</v>
       </c>
       <c r="I247" t="n">
         <v>19.9</v>
@@ -13648,7 +13686,7 @@
         <v>-12.62</v>
       </c>
       <c r="M247" t="n">
-        <v>-17.96</v>
+        <v>-19.83</v>
       </c>
       <c r="N247" t="b">
         <v>0</v>
@@ -13686,7 +13724,7 @@
         <v>-29.5</v>
       </c>
       <c r="H248" t="n">
-        <v>-8.66</v>
+        <v>-6.96</v>
       </c>
       <c r="I248" t="n">
         <v>4.05</v>
@@ -13701,7 +13739,7 @@
         <v>-2.43</v>
       </c>
       <c r="M248" t="n">
-        <v>-11.62</v>
+        <v>-10.81</v>
       </c>
       <c r="N248" t="b">
         <v>0</v>
@@ -13739,7 +13777,7 @@
         <v>34.2</v>
       </c>
       <c r="H249" t="n">
-        <v>2.73</v>
+        <v>4.09</v>
       </c>
       <c r="I249" t="n">
         <v>8.15</v>
@@ -13754,7 +13792,7 @@
         <v>-7.63</v>
       </c>
       <c r="M249" t="n">
-        <v>-0.23</v>
+        <v>0.24</v>
       </c>
       <c r="N249" t="b">
         <v>1</v>
@@ -13792,7 +13830,7 @@
         <v>42</v>
       </c>
       <c r="H250" t="n">
-        <v>-33.18</v>
+        <v>-34.98</v>
       </c>
       <c r="I250" t="n">
         <v>0.6</v>
@@ -13807,7 +13845,7 @@
         <v>-16.67</v>
       </c>
       <c r="M250" t="n">
-        <v>-36.15</v>
+        <v>-38.83</v>
       </c>
       <c r="N250" t="b">
         <v>1</v>
@@ -13849,7 +13887,7 @@
         <v>-0.4</v>
       </c>
       <c r="H251" t="n">
-        <v>-0.23</v>
+        <v>2.69</v>
       </c>
       <c r="I251" t="n">
         <v>4.83</v>
@@ -13864,7 +13902,7 @@
         <v>-10.75</v>
       </c>
       <c r="M251" t="n">
-        <v>-3.19</v>
+        <v>-1.16</v>
       </c>
       <c r="N251" t="b">
         <v>0</v>
@@ -13902,7 +13940,7 @@
         <v>64.59999999999999</v>
       </c>
       <c r="H252" t="n">
-        <v>4.97</v>
+        <v>6.53</v>
       </c>
       <c r="I252" t="n">
         <v>3.01</v>
@@ -13917,7 +13955,7 @@
         <v>-12</v>
       </c>
       <c r="M252" t="n">
-        <v>2.01</v>
+        <v>2.68</v>
       </c>
       <c r="N252" t="b">
         <v>0</v>
@@ -13955,7 +13993,7 @@
         <v>-25.3</v>
       </c>
       <c r="H253" t="n">
-        <v>52.16</v>
+        <v>60.85</v>
       </c>
       <c r="I253" t="n">
         <v>36.1</v>
@@ -13970,7 +14008,7 @@
         <v>-5.66</v>
       </c>
       <c r="M253" t="n">
-        <v>49.2</v>
+        <v>57</v>
       </c>
       <c r="N253" t="b">
         <v>0</v>
@@ -14008,7 +14046,7 @@
         <v>-7.7</v>
       </c>
       <c r="H254" t="n">
-        <v>-13.8</v>
+        <v>-13.67</v>
       </c>
       <c r="I254" t="n">
         <v>-6.47</v>
@@ -14023,7 +14061,7 @@
         <v>-23.05</v>
       </c>
       <c r="M254" t="n">
-        <v>-16.77</v>
+        <v>-17.52</v>
       </c>
       <c r="N254" t="b">
         <v>1</v>
@@ -14061,7 +14099,7 @@
         <v>-2.9</v>
       </c>
       <c r="H255" t="n">
-        <v>-16.85</v>
+        <v>-13.51</v>
       </c>
       <c r="I255" t="n">
         <v>-1.47</v>
@@ -14076,7 +14114,7 @@
         <v>-7.7</v>
       </c>
       <c r="M255" t="n">
-        <v>-19.81</v>
+        <v>-17.36</v>
       </c>
       <c r="N255" t="b">
         <v>0</v>
@@ -14114,7 +14152,7 @@
         <v>13.7</v>
       </c>
       <c r="H256" t="n">
-        <v>2.71</v>
+        <v>4.97</v>
       </c>
       <c r="I256" t="n">
         <v>2.74</v>
@@ -14129,7 +14167,7 @@
         <v>-24.02</v>
       </c>
       <c r="M256" t="n">
-        <v>-0.25</v>
+        <v>1.12</v>
       </c>
       <c r="N256" t="b">
         <v>1</v>
@@ -14167,7 +14205,7 @@
         <v>21.8</v>
       </c>
       <c r="H257" t="n">
-        <v>-21.94</v>
+        <v>-26.36</v>
       </c>
       <c r="I257" t="n">
         <v>18.32</v>
@@ -14182,7 +14220,7 @@
         <v>-23.27</v>
       </c>
       <c r="M257" t="n">
-        <v>-24.9</v>
+        <v>-30.21</v>
       </c>
       <c r="N257" t="b">
         <v>1</v>
@@ -14220,7 +14258,7 @@
         <v>29.4</v>
       </c>
       <c r="H258" t="n">
-        <v>-23.38</v>
+        <v>-24.78</v>
       </c>
       <c r="I258" t="n">
         <v>-2.62</v>
@@ -14235,7 +14273,7 @@
         <v>-27.18</v>
       </c>
       <c r="M258" t="n">
-        <v>-26.34</v>
+        <v>-28.63</v>
       </c>
       <c r="N258" t="b">
         <v>1</v>
@@ -14273,7 +14311,7 @@
         <v>-3.7</v>
       </c>
       <c r="H259" t="n">
-        <v>-29.17</v>
+        <v>-27.66</v>
       </c>
       <c r="I259" t="n">
         <v>-8.07</v>
@@ -14288,7 +14326,7 @@
         <v>-22.12</v>
       </c>
       <c r="M259" t="n">
-        <v>-32.13</v>
+        <v>-31.5</v>
       </c>
       <c r="N259" t="b">
         <v>1</v>
@@ -14326,7 +14364,7 @@
         <v>21.3</v>
       </c>
       <c r="H260" t="n">
-        <v>1.42</v>
+        <v>1.75</v>
       </c>
       <c r="I260" t="n">
         <v>0.23</v>
@@ -14341,7 +14379,7 @@
         <v>-0.85</v>
       </c>
       <c r="M260" t="n">
-        <v>-1.54</v>
+        <v>-2.1</v>
       </c>
       <c r="N260" t="b">
         <v>1</v>
@@ -14379,7 +14417,7 @@
         <v>-21.4</v>
       </c>
       <c r="H261" t="n">
-        <v>2.26</v>
+        <v>2.87</v>
       </c>
       <c r="I261" t="n">
         <v>4.55</v>
@@ -14394,7 +14432,7 @@
         <v>-6.39</v>
       </c>
       <c r="M261" t="n">
-        <v>-0.7</v>
+        <v>-0.98</v>
       </c>
       <c r="N261" t="b">
         <v>1</v>
@@ -14432,7 +14470,7 @@
         <v>16.3</v>
       </c>
       <c r="H262" t="n">
-        <v>-15.78</v>
+        <v>-17.89</v>
       </c>
       <c r="I262" t="n">
         <v>-1</v>
@@ -14447,7 +14485,7 @@
         <v>-22.5</v>
       </c>
       <c r="M262" t="n">
-        <v>-18.74</v>
+        <v>-21.73</v>
       </c>
       <c r="N262" t="b">
         <v>1</v>
@@ -14485,7 +14523,7 @@
         <v>11.9</v>
       </c>
       <c r="H263" t="n">
-        <v>-10.6</v>
+        <v>-10.94</v>
       </c>
       <c r="I263" t="n">
         <v>7.74</v>
@@ -14500,7 +14538,7 @@
         <v>-9.43</v>
       </c>
       <c r="M263" t="n">
-        <v>-13.56</v>
+        <v>-14.78</v>
       </c>
       <c r="N263" t="b">
         <v>0</v>
@@ -14538,7 +14576,7 @@
         <v>19.4</v>
       </c>
       <c r="H264" t="n">
-        <v>2.8</v>
+        <v>3.97</v>
       </c>
       <c r="I264" t="n">
         <v>10.89</v>
@@ -14553,7 +14591,7 @@
         <v>-2.97</v>
       </c>
       <c r="M264" t="n">
-        <v>-0.16</v>
+        <v>0.12</v>
       </c>
       <c r="N264" t="b">
         <v>0</v>
@@ -14591,7 +14629,7 @@
         <v>66.7</v>
       </c>
       <c r="H265" t="n">
-        <v>-0.71</v>
+        <v>-0.63</v>
       </c>
       <c r="I265" t="n">
         <v>4.84</v>
@@ -14606,7 +14644,7 @@
         <v>-11.7</v>
       </c>
       <c r="M265" t="n">
-        <v>-3.67</v>
+        <v>-4.48</v>
       </c>
       <c r="N265" t="b">
         <v>0</v>
@@ -14644,7 +14682,7 @@
         <v>3.7</v>
       </c>
       <c r="H266" t="n">
-        <v>23.21</v>
+        <v>30</v>
       </c>
       <c r="I266" t="n">
         <v>11.13</v>
@@ -14659,7 +14697,7 @@
         <v>-2.79</v>
       </c>
       <c r="M266" t="n">
-        <v>20.25</v>
+        <v>26.15</v>
       </c>
       <c r="N266" t="b">
         <v>0</v>
@@ -14697,7 +14735,7 @@
         <v>36.8</v>
       </c>
       <c r="H267" t="n">
-        <v>26</v>
+        <v>31.98</v>
       </c>
       <c r="I267" t="n">
         <v>15.47</v>
@@ -14712,7 +14750,7 @@
         <v>-0.96</v>
       </c>
       <c r="M267" t="n">
-        <v>23.04</v>
+        <v>28.13</v>
       </c>
       <c r="N267" t="b">
         <v>0</v>
@@ -14750,7 +14788,7 @@
         <v>0.2</v>
       </c>
       <c r="H268" t="n">
-        <v>19.38</v>
+        <v>22.49</v>
       </c>
       <c r="I268" t="n">
         <v>4.35</v>
@@ -14765,7 +14803,7 @@
         <v>-2.79</v>
       </c>
       <c r="M268" t="n">
-        <v>16.42</v>
+        <v>18.64</v>
       </c>
       <c r="N268" t="b">
         <v>1</v>
@@ -14803,7 +14841,7 @@
         <v>-31</v>
       </c>
       <c r="H269" t="n">
-        <v>-28.89</v>
+        <v>-30.54</v>
       </c>
       <c r="I269" t="n">
         <v>19.41</v>
@@ -14818,7 +14856,7 @@
         <v>-10.33</v>
       </c>
       <c r="M269" t="n">
-        <v>-31.85</v>
+        <v>-34.39</v>
       </c>
       <c r="N269" t="b">
         <v>0</v>
@@ -14860,7 +14898,7 @@
         <v>-2</v>
       </c>
       <c r="H270" t="n">
-        <v>0.09</v>
+        <v>2.82</v>
       </c>
       <c r="I270" t="n">
         <v>14.61</v>
@@ -14875,7 +14913,7 @@
         <v>-3.45</v>
       </c>
       <c r="M270" t="n">
-        <v>-2.87</v>
+        <v>-1.03</v>
       </c>
       <c r="N270" t="b">
         <v>0</v>
@@ -14913,7 +14951,7 @@
         <v>12.2</v>
       </c>
       <c r="H271" t="n">
-        <v>-33.07</v>
+        <v>-31.84</v>
       </c>
       <c r="I271" t="n">
         <v>3.47</v>
@@ -14928,7 +14966,7 @@
         <v>-27.15</v>
       </c>
       <c r="M271" t="n">
-        <v>-36.03</v>
+        <v>-35.69</v>
       </c>
       <c r="N271" t="b">
         <v>0</v>
@@ -14966,7 +15004,7 @@
         <v>8.4</v>
       </c>
       <c r="H272" t="n">
-        <v>-38.79</v>
+        <v>-42.87</v>
       </c>
       <c r="I272" t="n">
         <v>-0.13</v>
@@ -14981,7 +15019,7 @@
         <v>-10.87</v>
       </c>
       <c r="M272" t="n">
-        <v>-41.75</v>
+        <v>-46.72</v>
       </c>
       <c r="N272" t="b">
         <v>1</v>
@@ -15019,7 +15057,7 @@
         <v>-21.7</v>
       </c>
       <c r="H273" t="n">
-        <v>-5.95</v>
+        <v>-8.07</v>
       </c>
       <c r="I273" t="n">
         <v>5.5</v>
@@ -15034,7 +15072,7 @@
         <v>-4.3</v>
       </c>
       <c r="M273" t="n">
-        <v>-8.91</v>
+        <v>-11.92</v>
       </c>
       <c r="N273" t="b">
         <v>0</v>
@@ -15072,7 +15110,7 @@
         <v>-7.3</v>
       </c>
       <c r="H274" t="n">
-        <v>-22.37</v>
+        <v>-20.36</v>
       </c>
       <c r="I274" t="n">
         <v>-4.12</v>
@@ -15087,7 +15125,7 @@
         <v>-15.02</v>
       </c>
       <c r="M274" t="n">
-        <v>-25.33</v>
+        <v>-24.2</v>
       </c>
       <c r="N274" t="b">
         <v>1</v>
@@ -15125,7 +15163,7 @@
         <v>-26.1</v>
       </c>
       <c r="H275" t="n">
-        <v>-26.2</v>
+        <v>-25.42</v>
       </c>
       <c r="I275" t="n">
         <v>5.05</v>
@@ -15140,7 +15178,7 @@
         <v>-9.27</v>
       </c>
       <c r="M275" t="n">
-        <v>-29.16</v>
+        <v>-29.27</v>
       </c>
       <c r="N275" t="b">
         <v>0</v>
@@ -15178,7 +15216,7 @@
         <v>-18.5</v>
       </c>
       <c r="H276" t="n">
-        <v>43</v>
+        <v>50.63</v>
       </c>
       <c r="I276" t="n">
         <v>16.22</v>
@@ -15193,7 +15231,7 @@
         <v>-9.960000000000001</v>
       </c>
       <c r="M276" t="n">
-        <v>40.04</v>
+        <v>46.79</v>
       </c>
       <c r="N276" t="b">
         <v>0</v>
@@ -15231,7 +15269,7 @@
         <v>15.3</v>
       </c>
       <c r="H277" t="n">
-        <v>-44.78</v>
+        <v>-47.65</v>
       </c>
       <c r="I277" t="n">
         <v>-21.4</v>
@@ -15246,7 +15284,7 @@
         <v>-26.97</v>
       </c>
       <c r="M277" t="n">
-        <v>-47.74</v>
+        <v>-51.5</v>
       </c>
       <c r="N277" t="b">
         <v>0</v>
@@ -15284,7 +15322,7 @@
         <v>26.1</v>
       </c>
       <c r="H278" t="n">
-        <v>-17.93</v>
+        <v>-21.45</v>
       </c>
       <c r="I278" t="n">
         <v>-0.51</v>
@@ -15299,7 +15337,7 @@
         <v>-16.45</v>
       </c>
       <c r="M278" t="n">
-        <v>-20.89</v>
+        <v>-25.3</v>
       </c>
       <c r="N278" t="b">
         <v>0</v>
@@ -15341,7 +15379,7 @@
         <v>-8.199999999999999</v>
       </c>
       <c r="H279" t="n">
-        <v>-17.89</v>
+        <v>-24.76</v>
       </c>
       <c r="I279" t="n">
         <v>17.48</v>
@@ -15356,7 +15394,7 @@
         <v>-10.68</v>
       </c>
       <c r="M279" t="n">
-        <v>-20.85</v>
+        <v>-28.61</v>
       </c>
       <c r="N279" t="b">
         <v>0</v>
@@ -15394,7 +15432,7 @@
         <v>17.9</v>
       </c>
       <c r="H280" t="n">
-        <v>-6.79</v>
+        <v>-5.45</v>
       </c>
       <c r="I280" t="n">
         <v>12.97</v>
@@ -15409,7 +15447,7 @@
         <v>-8.130000000000001</v>
       </c>
       <c r="M280" t="n">
-        <v>-9.75</v>
+        <v>-9.300000000000001</v>
       </c>
       <c r="N280" t="b">
         <v>1</v>
@@ -15447,7 +15485,7 @@
         <v>0.7</v>
       </c>
       <c r="H281" t="n">
-        <v>-27.47</v>
+        <v>-23.78</v>
       </c>
       <c r="I281" t="n">
         <v>14.96</v>
@@ -15462,7 +15500,7 @@
         <v>-8.039999999999999</v>
       </c>
       <c r="M281" t="n">
-        <v>-30.43</v>
+        <v>-27.63</v>
       </c>
       <c r="N281" t="b">
         <v>0</v>
@@ -15500,7 +15538,7 @@
         <v>61.6</v>
       </c>
       <c r="H282" t="n">
-        <v>0.72</v>
+        <v>5.64</v>
       </c>
       <c r="I282" t="n">
         <v>11.47</v>
@@ -15515,7 +15553,7 @@
         <v>-12.86</v>
       </c>
       <c r="M282" t="n">
-        <v>-2.24</v>
+        <v>1.8</v>
       </c>
       <c r="N282" t="b">
         <v>0</v>
@@ -15553,7 +15591,7 @@
         <v>54.3</v>
       </c>
       <c r="H283" t="n">
-        <v>-20.32</v>
+        <v>-24.67</v>
       </c>
       <c r="I283" t="n">
         <v>-2.86</v>
@@ -15568,7 +15606,7 @@
         <v>-24.93</v>
       </c>
       <c r="M283" t="n">
-        <v>-23.28</v>
+        <v>-28.51</v>
       </c>
       <c r="N283" t="b">
         <v>0</v>
@@ -15606,7 +15644,7 @@
         <v>14.8</v>
       </c>
       <c r="H284" t="n">
-        <v>-7.06</v>
+        <v>-8.31</v>
       </c>
       <c r="I284" t="n">
         <v>0.35</v>
@@ -15621,7 +15659,7 @@
         <v>-3.68</v>
       </c>
       <c r="M284" t="n">
-        <v>-10.02</v>
+        <v>-12.15</v>
       </c>
       <c r="N284" t="b">
         <v>1</v>
@@ -15659,7 +15697,7 @@
         <v>-13.5</v>
       </c>
       <c r="H285" t="n">
-        <v>-17.84</v>
+        <v>-14.68</v>
       </c>
       <c r="I285" t="n">
         <v>-1.88</v>
@@ -15674,7 +15712,7 @@
         <v>-11.4</v>
       </c>
       <c r="M285" t="n">
-        <v>-20.8</v>
+        <v>-18.53</v>
       </c>
       <c r="N285" t="b">
         <v>0</v>
@@ -15712,7 +15750,7 @@
         <v>25.5</v>
       </c>
       <c r="H286" t="n">
-        <v>4.82</v>
+        <v>12.21</v>
       </c>
       <c r="I286" t="n">
         <v>-9.369999999999999</v>
@@ -15727,7 +15765,7 @@
         <v>-22.11</v>
       </c>
       <c r="M286" t="n">
-        <v>1.86</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="N286" t="b">
         <v>1</v>
@@ -15769,7 +15807,7 @@
         <v>-7.5</v>
       </c>
       <c r="H287" t="n">
-        <v>-17.07</v>
+        <v>-26.94</v>
       </c>
       <c r="I287" t="n">
         <v>4.46</v>
@@ -15784,7 +15822,7 @@
         <v>-8.52</v>
       </c>
       <c r="M287" t="n">
-        <v>-20.03</v>
+        <v>-30.79</v>
       </c>
       <c r="N287" t="b">
         <v>1</v>
@@ -15822,7 +15860,7 @@
         <v>1.5</v>
       </c>
       <c r="H288" t="n">
-        <v>-0.58</v>
+        <v>1.96</v>
       </c>
       <c r="I288" t="n">
         <v>-7.31</v>
@@ -15837,7 +15875,7 @@
         <v>-18.58</v>
       </c>
       <c r="M288" t="n">
-        <v>-3.54</v>
+        <v>-1.89</v>
       </c>
       <c r="N288" t="b">
         <v>0</v>
@@ -15875,7 +15913,7 @@
         <v>-11</v>
       </c>
       <c r="H289" t="n">
-        <v>18.39</v>
+        <v>25.61</v>
       </c>
       <c r="I289" t="n">
         <v>10.7</v>
@@ -15890,7 +15928,7 @@
         <v>-9.43</v>
       </c>
       <c r="M289" t="n">
-        <v>15.43</v>
+        <v>21.76</v>
       </c>
       <c r="N289" t="b">
         <v>1</v>
@@ -15928,7 +15966,7 @@
         <v>-11.4</v>
       </c>
       <c r="H290" t="n">
-        <v>-18.81</v>
+        <v>-20.7</v>
       </c>
       <c r="I290" t="n">
         <v>4.36</v>
@@ -15943,7 +15981,7 @@
         <v>-11.36</v>
       </c>
       <c r="M290" t="n">
-        <v>-21.77</v>
+        <v>-24.55</v>
       </c>
       <c r="N290" t="b">
         <v>1</v>
@@ -15981,7 +16019,7 @@
         <v>2.1</v>
       </c>
       <c r="H291" t="n">
-        <v>74.52</v>
+        <v>80.04000000000001</v>
       </c>
       <c r="I291" t="n">
         <v>20.72</v>
@@ -15996,7 +16034,7 @@
         <v>-5.79</v>
       </c>
       <c r="M291" t="n">
-        <v>71.56</v>
+        <v>76.19</v>
       </c>
       <c r="N291" t="b">
         <v>0</v>
@@ -16034,7 +16072,7 @@
         <v>27.1</v>
       </c>
       <c r="H292" t="n">
-        <v>-17.25</v>
+        <v>-17.97</v>
       </c>
       <c r="I292" t="n">
         <v>5.02</v>
@@ -16049,7 +16087,7 @@
         <v>-14.35</v>
       </c>
       <c r="M292" t="n">
-        <v>-20.21</v>
+        <v>-21.82</v>
       </c>
       <c r="N292" t="b">
         <v>1</v>
@@ -16087,7 +16125,7 @@
         <v>-21.6</v>
       </c>
       <c r="H293" t="n">
-        <v>-20.44</v>
+        <v>-20.59</v>
       </c>
       <c r="I293" t="n">
         <v>1.22</v>
@@ -16102,7 +16140,7 @@
         <v>-6.54</v>
       </c>
       <c r="M293" t="n">
-        <v>-23.4</v>
+        <v>-24.43</v>
       </c>
       <c r="N293" t="b">
         <v>0</v>
@@ -16144,7 +16182,7 @@
         <v>-2.2</v>
       </c>
       <c r="H294" t="n">
-        <v>-6.12</v>
+        <v>-0.86</v>
       </c>
       <c r="I294" t="n">
         <v>-9.050000000000001</v>
@@ -16159,7 +16197,7 @@
         <v>-18.61</v>
       </c>
       <c r="M294" t="n">
-        <v>-9.08</v>
+        <v>-4.71</v>
       </c>
       <c r="N294" t="b">
         <v>0</v>
@@ -16197,7 +16235,7 @@
         <v>0.7</v>
       </c>
       <c r="H295" t="n">
-        <v>3.62</v>
+        <v>7.22</v>
       </c>
       <c r="I295" t="n">
         <v>11.4</v>
@@ -16212,7 +16250,7 @@
         <v>-7.28</v>
       </c>
       <c r="M295" t="n">
-        <v>0.66</v>
+        <v>3.37</v>
       </c>
       <c r="N295" t="b">
         <v>0</v>
@@ -16250,7 +16288,7 @@
         <v>-31.7</v>
       </c>
       <c r="H296" t="n">
-        <v>27.02</v>
+        <v>19.9</v>
       </c>
       <c r="I296" t="n">
         <v>17.04</v>
@@ -16265,7 +16303,7 @@
         <v>-4.05</v>
       </c>
       <c r="M296" t="n">
-        <v>24.06</v>
+        <v>16.05</v>
       </c>
       <c r="N296" t="b">
         <v>0</v>
@@ -16303,7 +16341,7 @@
         <v>32.2</v>
       </c>
       <c r="H297" t="n">
-        <v>6.17</v>
+        <v>7.61</v>
       </c>
       <c r="I297" t="n">
         <v>6.49</v>
@@ -16318,7 +16356,7 @@
         <v>-3.92</v>
       </c>
       <c r="M297" t="n">
-        <v>3.21</v>
+        <v>3.76</v>
       </c>
       <c r="N297" t="b">
         <v>1</v>
@@ -16356,7 +16394,7 @@
         <v>3.2</v>
       </c>
       <c r="H298" t="n">
-        <v>-29.27</v>
+        <v>-29.37</v>
       </c>
       <c r="I298" t="n">
         <v>-10.41</v>
@@ -16371,7 +16409,7 @@
         <v>-23.7</v>
       </c>
       <c r="M298" t="n">
-        <v>-32.23</v>
+        <v>-33.22</v>
       </c>
       <c r="N298" t="b">
         <v>1</v>
@@ -16409,7 +16447,7 @@
         <v>7.3</v>
       </c>
       <c r="H299" t="n">
-        <v>4.73</v>
+        <v>4.01</v>
       </c>
       <c r="I299" t="n">
         <v>-0.57</v>
@@ -16424,7 +16462,7 @@
         <v>-5.89</v>
       </c>
       <c r="M299" t="n">
-        <v>1.77</v>
+        <v>0.16</v>
       </c>
       <c r="N299" t="b">
         <v>0</v>
@@ -16462,7 +16500,7 @@
         <v>24.5</v>
       </c>
       <c r="H300" t="n">
-        <v>11.81</v>
+        <v>13.44</v>
       </c>
       <c r="I300" t="n">
         <v>17.24</v>
@@ -16477,7 +16515,7 @@
         <v>-0.47</v>
       </c>
       <c r="M300" t="n">
-        <v>8.85</v>
+        <v>9.59</v>
       </c>
       <c r="N300" t="b">
         <v>0</v>
@@ -16515,7 +16553,7 @@
         <v>-0.3</v>
       </c>
       <c r="H301" t="n">
-        <v>-16.89</v>
+        <v>-14.58</v>
       </c>
       <c r="I301" t="n">
         <v>17.76</v>
@@ -16530,7 +16568,7 @@
         <v>-14.18</v>
       </c>
       <c r="M301" t="n">
-        <v>-19.85</v>
+        <v>-18.43</v>
       </c>
       <c r="N301" t="b">
         <v>1</v>
@@ -16568,7 +16606,7 @@
         <v>4</v>
       </c>
       <c r="H302" t="n">
-        <v>58.86</v>
+        <v>65.3</v>
       </c>
       <c r="I302" t="n">
         <v>8.75</v>
@@ -16583,7 +16621,7 @@
         <v>-11.02</v>
       </c>
       <c r="M302" t="n">
-        <v>55.9</v>
+        <v>61.45</v>
       </c>
       <c r="N302" t="b">
         <v>0</v>
@@ -16621,7 +16659,7 @@
         <v>-6.8</v>
       </c>
       <c r="H303" t="n">
-        <v>30.07</v>
+        <v>33.3</v>
       </c>
       <c r="I303" t="n">
         <v>8.279999999999999</v>
@@ -16636,7 +16674,7 @@
         <v>-6.78</v>
       </c>
       <c r="M303" t="n">
-        <v>27.11</v>
+        <v>29.45</v>
       </c>
       <c r="N303" t="b">
         <v>0</v>
@@ -16674,7 +16712,7 @@
         <v>-42</v>
       </c>
       <c r="H304" t="n">
-        <v>34.26</v>
+        <v>51.5</v>
       </c>
       <c r="I304" t="n">
         <v>-3.61</v>
@@ -16689,7 +16727,7 @@
         <v>-11.94</v>
       </c>
       <c r="M304" t="n">
-        <v>31.3</v>
+        <v>47.65</v>
       </c>
       <c r="N304" t="b">
         <v>0</v>
@@ -16727,7 +16765,7 @@
         <v>14.6</v>
       </c>
       <c r="H305" t="n">
-        <v>-3.13</v>
+        <v>-5.83</v>
       </c>
       <c r="I305" t="n">
         <v>8.539999999999999</v>
@@ -16742,7 +16780,7 @@
         <v>-13.21</v>
       </c>
       <c r="M305" t="n">
-        <v>-6.09</v>
+        <v>-9.68</v>
       </c>
       <c r="N305" t="b">
         <v>0</v>
@@ -16780,7 +16818,7 @@
         <v>34.6</v>
       </c>
       <c r="H306" t="n">
-        <v>-0.04</v>
+        <v>-4.57</v>
       </c>
       <c r="I306" t="n">
         <v>5.7</v>
@@ -16795,7 +16833,7 @@
         <v>-7.7</v>
       </c>
       <c r="M306" t="n">
-        <v>-3</v>
+        <v>-8.42</v>
       </c>
       <c r="N306" t="b">
         <v>1</v>
@@ -16833,7 +16871,7 @@
         <v>-37.2</v>
       </c>
       <c r="H307" t="n">
-        <v>28.08</v>
+        <v>37.84</v>
       </c>
       <c r="I307" t="n">
         <v>21.67</v>
@@ -16848,7 +16886,7 @@
         <v>-6.64</v>
       </c>
       <c r="M307" t="n">
-        <v>25.12</v>
+        <v>33.99</v>
       </c>
       <c r="N307" t="b">
         <v>0</v>
@@ -16886,7 +16924,7 @@
         <v>-31.2</v>
       </c>
       <c r="H308" t="n">
-        <v>-25.52</v>
+        <v>-24.67</v>
       </c>
       <c r="I308" t="n">
         <v>1.03</v>
@@ -16901,7 +16939,7 @@
         <v>-13.65</v>
       </c>
       <c r="M308" t="n">
-        <v>-28.48</v>
+        <v>-28.52</v>
       </c>
       <c r="N308" t="b">
         <v>0</v>
@@ -16939,7 +16977,7 @@
         <v>10.4</v>
       </c>
       <c r="H309" t="n">
-        <v>21.94</v>
+        <v>26.6</v>
       </c>
       <c r="I309" t="n">
         <v>11.05</v>
@@ -16954,7 +16992,7 @@
         <v>-5.54</v>
       </c>
       <c r="M309" t="n">
-        <v>18.98</v>
+        <v>22.75</v>
       </c>
       <c r="N309" t="b">
         <v>1</v>
@@ -16992,7 +17030,7 @@
         <v>-14.7</v>
       </c>
       <c r="H310" t="n">
-        <v>6.49</v>
+        <v>7.47</v>
       </c>
       <c r="I310" t="n">
         <v>12.94</v>
@@ -17007,7 +17045,7 @@
         <v>-2.34</v>
       </c>
       <c r="M310" t="n">
-        <v>3.53</v>
+        <v>3.62</v>
       </c>
       <c r="N310" t="b">
         <v>0</v>
@@ -17045,7 +17083,7 @@
         <v>-21.5</v>
       </c>
       <c r="H311" t="n">
-        <v>-5.74</v>
+        <v>-2.07</v>
       </c>
       <c r="I311" t="n">
         <v>10.65</v>
@@ -17060,7 +17098,7 @@
         <v>-6.89</v>
       </c>
       <c r="M311" t="n">
-        <v>-8.699999999999999</v>
+        <v>-5.91</v>
       </c>
       <c r="N311" t="b">
         <v>1</v>
@@ -17098,7 +17136,7 @@
         <v>20.2</v>
       </c>
       <c r="H312" t="n">
-        <v>-18.22</v>
+        <v>-16.6</v>
       </c>
       <c r="I312" t="n">
         <v>-1.23</v>
@@ -17113,7 +17151,7 @@
         <v>-12.56</v>
       </c>
       <c r="M312" t="n">
-        <v>-21.18</v>
+        <v>-20.44</v>
       </c>
       <c r="N312" t="b">
         <v>0</v>
@@ -17151,7 +17189,7 @@
         <v>3.5</v>
       </c>
       <c r="H313" t="n">
-        <v>58.39</v>
+        <v>67.81999999999999</v>
       </c>
       <c r="I313" t="n">
         <v>33.01</v>
@@ -17166,7 +17204,7 @@
         <v>-0.92</v>
       </c>
       <c r="M313" t="n">
-        <v>55.43</v>
+        <v>63.97</v>
       </c>
       <c r="N313" t="b">
         <v>1</v>
@@ -17204,7 +17242,7 @@
         <v>14</v>
       </c>
       <c r="H314" t="n">
-        <v>43.01</v>
+        <v>42.64</v>
       </c>
       <c r="I314" t="n">
         <v>2.89</v>
@@ -17219,7 +17257,7 @@
         <v>-1.94</v>
       </c>
       <c r="M314" t="n">
-        <v>40.05</v>
+        <v>38.79</v>
       </c>
       <c r="N314" t="b">
         <v>0</v>
@@ -17257,7 +17295,7 @@
         <v>19.8</v>
       </c>
       <c r="H315" t="n">
-        <v>3.09</v>
+        <v>4.77</v>
       </c>
       <c r="I315" t="n">
         <v>4.74</v>
@@ -17272,7 +17310,7 @@
         <v>-9.9</v>
       </c>
       <c r="M315" t="n">
-        <v>0.13</v>
+        <v>0.92</v>
       </c>
       <c r="N315" t="b">
         <v>0</v>
@@ -17314,7 +17352,7 @@
         <v>-7.4</v>
       </c>
       <c r="H316" t="n">
-        <v>15.15</v>
+        <v>16.79</v>
       </c>
       <c r="I316" t="n">
         <v>-3.85</v>
@@ -17329,7 +17367,7 @@
         <v>-21.11</v>
       </c>
       <c r="M316" t="n">
-        <v>12.19</v>
+        <v>12.94</v>
       </c>
       <c r="N316" t="b">
         <v>0</v>
@@ -17367,7 +17405,7 @@
         <v>-10.8</v>
       </c>
       <c r="H317" t="n">
-        <v>7.72</v>
+        <v>6.34</v>
       </c>
       <c r="I317" t="n">
         <v>1.78</v>
@@ -17382,7 +17420,7 @@
         <v>-7.51</v>
       </c>
       <c r="M317" t="n">
-        <v>4.76</v>
+        <v>2.5</v>
       </c>
       <c r="N317" t="b">
         <v>0</v>
@@ -17420,7 +17458,7 @@
         <v>-24</v>
       </c>
       <c r="H318" t="n">
-        <v>44.34</v>
+        <v>57.11</v>
       </c>
       <c r="I318" t="n">
         <v>10.85</v>
@@ -17435,7 +17473,7 @@
         <v>-5.43</v>
       </c>
       <c r="M318" t="n">
-        <v>41.38</v>
+        <v>53.26</v>
       </c>
       <c r="N318" t="b">
         <v>0</v>
@@ -17473,7 +17511,7 @@
         <v>-28.3</v>
       </c>
       <c r="H319" t="n">
-        <v>-30.41</v>
+        <v>-29.28</v>
       </c>
       <c r="I319" t="n">
         <v>-8.949999999999999</v>
@@ -17488,7 +17526,7 @@
         <v>-13.18</v>
       </c>
       <c r="M319" t="n">
-        <v>-33.37</v>
+        <v>-33.13</v>
       </c>
       <c r="N319" t="b">
         <v>0</v>
@@ -17526,7 +17564,7 @@
         <v>-30.5</v>
       </c>
       <c r="H320" t="n">
-        <v>3.59</v>
+        <v>-1.32</v>
       </c>
       <c r="I320" t="n">
         <v>2.96</v>
@@ -17541,7 +17579,7 @@
         <v>-17.88</v>
       </c>
       <c r="M320" t="n">
-        <v>0.63</v>
+        <v>-5.17</v>
       </c>
       <c r="N320" t="b">
         <v>1</v>
@@ -17579,7 +17617,7 @@
         <v>-6</v>
       </c>
       <c r="H321" t="n">
-        <v>-29.44</v>
+        <v>-30.73</v>
       </c>
       <c r="I321" t="n">
         <v>3.31</v>
@@ -17594,7 +17632,7 @@
         <v>-21.48</v>
       </c>
       <c r="M321" t="n">
-        <v>-32.4</v>
+        <v>-34.58</v>
       </c>
       <c r="N321" t="b">
         <v>1</v>
@@ -17632,7 +17670,7 @@
         <v>-42.2</v>
       </c>
       <c r="H322" t="n">
-        <v>-16.83</v>
+        <v>-17.1</v>
       </c>
       <c r="I322" t="n">
         <v>19.24</v>
@@ -17647,7 +17685,7 @@
         <v>-0.93</v>
       </c>
       <c r="M322" t="n">
-        <v>-19.79</v>
+        <v>-20.95</v>
       </c>
       <c r="N322" t="b">
         <v>0</v>
@@ -17685,7 +17723,7 @@
         <v>-34.6</v>
       </c>
       <c r="H323" t="n">
-        <v>11.78</v>
+        <v>20.79</v>
       </c>
       <c r="I323" t="n">
         <v>23.65</v>
@@ -17700,7 +17738,7 @@
         <v>-3.83</v>
       </c>
       <c r="M323" t="n">
-        <v>8.82</v>
+        <v>16.94</v>
       </c>
       <c r="N323" t="b">
         <v>1</v>
@@ -17738,7 +17776,7 @@
         <v>-48.1</v>
       </c>
       <c r="H324" t="n">
-        <v>-35.75</v>
+        <v>-34.6</v>
       </c>
       <c r="I324" t="n">
         <v>2.19</v>
@@ -17753,7 +17791,7 @@
         <v>-13.66</v>
       </c>
       <c r="M324" t="n">
-        <v>-38.72</v>
+        <v>-38.45</v>
       </c>
       <c r="N324" t="b">
         <v>0</v>
@@ -17791,7 +17829,7 @@
         <v>-16.2</v>
       </c>
       <c r="H325" t="n">
-        <v>2.37</v>
+        <v>6.42</v>
       </c>
       <c r="I325" t="n">
         <v>25.77</v>
@@ -17806,7 +17844,7 @@
         <v>-1.7</v>
       </c>
       <c r="M325" t="n">
-        <v>-0.6</v>
+        <v>2.58</v>
       </c>
       <c r="N325" t="b">
         <v>1</v>
@@ -17844,7 +17882,7 @@
         <v>-24.9</v>
       </c>
       <c r="H326" t="n">
-        <v>4.86</v>
+        <v>3.49</v>
       </c>
       <c r="I326" t="n">
         <v>10.88</v>
@@ -17859,7 +17897,7 @@
         <v>-4.1</v>
       </c>
       <c r="M326" t="n">
-        <v>1.9</v>
+        <v>-0.36</v>
       </c>
       <c r="N326" t="b">
         <v>1</v>
@@ -17901,7 +17939,7 @@
         <v>-8.1</v>
       </c>
       <c r="H327" t="n">
-        <v>21.35</v>
+        <v>24.38</v>
       </c>
       <c r="I327" t="n">
         <v>14.27</v>
@@ -17916,7 +17954,7 @@
         <v>-10.92</v>
       </c>
       <c r="M327" t="n">
-        <v>18.39</v>
+        <v>20.54</v>
       </c>
       <c r="N327" t="b">
         <v>1</v>
@@ -17954,7 +17992,7 @@
         <v>-10.2</v>
       </c>
       <c r="H328" t="n">
-        <v>-16.64</v>
+        <v>-14.52</v>
       </c>
       <c r="I328" t="n">
         <v>15.03</v>
@@ -17969,7 +18007,7 @@
         <v>-1.61</v>
       </c>
       <c r="M328" t="n">
-        <v>-19.6</v>
+        <v>-18.36</v>
       </c>
       <c r="N328" t="b">
         <v>1</v>
@@ -18007,7 +18045,7 @@
         <v>68.90000000000001</v>
       </c>
       <c r="H329" t="n">
-        <v>26.06</v>
+        <v>26.5</v>
       </c>
       <c r="I329" t="n">
         <v>1.84</v>
@@ -18022,7 +18060,7 @@
         <v>-10.43</v>
       </c>
       <c r="M329" t="n">
-        <v>23.1</v>
+        <v>22.65</v>
       </c>
       <c r="N329" t="b">
         <v>1</v>
@@ -18060,7 +18098,7 @@
         <v>-40.8</v>
       </c>
       <c r="H330" t="n">
-        <v>-27.82</v>
+        <v>-27.63</v>
       </c>
       <c r="I330" t="n">
         <v>21.71</v>
@@ -18075,7 +18113,7 @@
         <v>-3.3</v>
       </c>
       <c r="M330" t="n">
-        <v>-30.78</v>
+        <v>-31.48</v>
       </c>
       <c r="N330" t="b">
         <v>1</v>
@@ -18113,7 +18151,7 @@
         <v>-10.1</v>
       </c>
       <c r="H331" t="n">
-        <v>-7.06</v>
+        <v>-11.72</v>
       </c>
       <c r="I331" t="n">
         <v>1.83</v>
@@ -18128,7 +18166,7 @@
         <v>-3.45</v>
       </c>
       <c r="M331" t="n">
-        <v>-10.02</v>
+        <v>-15.57</v>
       </c>
       <c r="N331" t="b">
         <v>0</v>
@@ -18166,7 +18204,7 @@
         <v>40.7</v>
       </c>
       <c r="H332" t="n">
-        <v>27.18</v>
+        <v>31.82</v>
       </c>
       <c r="I332" t="n">
         <v>-4.08</v>
@@ -18181,7 +18219,7 @@
         <v>-11.2</v>
       </c>
       <c r="M332" t="n">
-        <v>24.22</v>
+        <v>27.98</v>
       </c>
       <c r="N332" t="b">
         <v>1</v>
@@ -18219,7 +18257,7 @@
         <v>25.7</v>
       </c>
       <c r="H333" t="n">
-        <v>-14.04</v>
+        <v>-9.539999999999999</v>
       </c>
       <c r="I333" t="n">
         <v>11.3</v>
@@ -18234,7 +18272,7 @@
         <v>-11.03</v>
       </c>
       <c r="M333" t="n">
-        <v>-17</v>
+        <v>-13.39</v>
       </c>
       <c r="N333" t="b">
         <v>1</v>
@@ -18272,7 +18310,7 @@
         <v>2.3</v>
       </c>
       <c r="H334" t="n">
-        <v>-0.62</v>
+        <v>0.37</v>
       </c>
       <c r="I334" t="n">
         <v>-0.95</v>
@@ -18287,7 +18325,7 @@
         <v>-7.81</v>
       </c>
       <c r="M334" t="n">
-        <v>-3.58</v>
+        <v>-3.48</v>
       </c>
       <c r="N334" t="b">
         <v>0</v>
@@ -18419,7 +18457,7 @@
         <v>51.4</v>
       </c>
       <c r="H2" t="n">
-        <v>-5.32</v>
+        <v>-0.34</v>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
@@ -18428,7 +18466,7 @@
         <v>-7.85</v>
       </c>
       <c r="M2" t="n">
-        <v>-3.93</v>
+        <v>0.21</v>
       </c>
       <c r="N2" t="b">
         <v>1</v>
@@ -18466,16 +18504,18 @@
         <v>-16.6</v>
       </c>
       <c r="H3" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="I3" t="inlineStr"/>
+        <v>-0.75</v>
+      </c>
+      <c r="I3" t="n">
+        <v>-0.75</v>
+      </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="n">
-        <v>-1.04</v>
+        <v>-1.39</v>
       </c>
       <c r="M3" t="n">
-        <v>3.24</v>
+        <v>-0.41</v>
       </c>
       <c r="N3" t="b">
         <v>1</v>
@@ -18513,16 +18553,18 @@
         <v>-5</v>
       </c>
       <c r="H4" t="n">
-        <v>8.949999999999999</v>
-      </c>
-      <c r="I4" t="inlineStr"/>
+        <v>12.26</v>
+      </c>
+      <c r="I4" t="n">
+        <v>12.26</v>
+      </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="n">
         <v>-1.75</v>
       </c>
       <c r="M4" t="n">
-        <v>10.15</v>
+        <v>12.61</v>
       </c>
       <c r="N4" t="b">
         <v>1</v>
@@ -18560,16 +18602,18 @@
         <v>12.5</v>
       </c>
       <c r="H5" t="n">
-        <v>7.42</v>
-      </c>
-      <c r="I5" t="inlineStr"/>
+        <v>7.44</v>
+      </c>
+      <c r="I5" t="n">
+        <v>7.44</v>
+      </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="n">
         <v>-2.59</v>
       </c>
       <c r="M5" t="n">
-        <v>8.619999999999999</v>
+        <v>7.79</v>
       </c>
       <c r="N5" t="b">
         <v>1</v>
@@ -18607,16 +18651,18 @@
         <v>-17.3</v>
       </c>
       <c r="H6" t="n">
-        <v>-0</v>
-      </c>
-      <c r="I6" t="inlineStr"/>
+        <v>0.29</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1.16</v>
+      </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="n">
         <v>-6.51</v>
       </c>
       <c r="M6" t="n">
-        <v>1.5</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="N6" t="b">
         <v>1</v>
@@ -18654,7 +18700,7 @@
         <v>-21.8</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.73</v>
+        <v>0.25</v>
       </c>
       <c r="I7" t="n">
         <v>-3.37</v>
@@ -18665,7 +18711,7 @@
         <v>-5.33</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.73</v>
+        <v>-0.62</v>
       </c>
       <c r="N7" t="b">
         <v>1</v>
@@ -18703,7 +18749,7 @@
         <v>-16.7</v>
       </c>
       <c r="H8" t="n">
-        <v>26.63</v>
+        <v>27.16</v>
       </c>
       <c r="I8" t="n">
         <v>26.03</v>
@@ -18714,7 +18760,7 @@
         <v>-6.98</v>
       </c>
       <c r="M8" t="n">
-        <v>26.68</v>
+        <v>26.34</v>
       </c>
       <c r="N8" t="b">
         <v>1</v>
@@ -18752,7 +18798,7 @@
         <v>-11.5</v>
       </c>
       <c r="H9" t="n">
-        <v>16.14</v>
+        <v>18.34</v>
       </c>
       <c r="I9" t="n">
         <v>7.47</v>
@@ -18763,7 +18809,7 @@
         <v>-0.99</v>
       </c>
       <c r="M9" t="n">
-        <v>16.19</v>
+        <v>17.52</v>
       </c>
       <c r="N9" t="b">
         <v>1</v>
@@ -18801,7 +18847,7 @@
         <v>0.1</v>
       </c>
       <c r="H10" t="n">
-        <v>19.7</v>
+        <v>18.54</v>
       </c>
       <c r="I10" t="n">
         <v>6.41</v>
@@ -18812,7 +18858,7 @@
         <v>-2.51</v>
       </c>
       <c r="M10" t="n">
-        <v>20</v>
+        <v>17.98</v>
       </c>
       <c r="N10" t="b">
         <v>1</v>
@@ -18850,7 +18896,7 @@
         <v>-31.6</v>
       </c>
       <c r="H11" t="n">
-        <v>-5.55</v>
+        <v>-2.84</v>
       </c>
       <c r="I11" t="n">
         <v>-2.12</v>
@@ -18861,7 +18907,7 @@
         <v>-8.140000000000001</v>
       </c>
       <c r="M11" t="n">
-        <v>-5.25</v>
+        <v>-3.4</v>
       </c>
       <c r="N11" t="b">
         <v>1</v>
@@ -18899,18 +18945,20 @@
         <v>-2.7</v>
       </c>
       <c r="H12" t="n">
-        <v>-10.36</v>
+        <v>-9.199999999999999</v>
       </c>
       <c r="I12" t="n">
         <v>-3.77</v>
       </c>
-      <c r="J12" t="inlineStr"/>
+      <c r="J12" t="n">
+        <v>-9.539999999999999</v>
+      </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="n">
         <v>-12.44</v>
       </c>
       <c r="M12" t="n">
-        <v>-9.390000000000001</v>
+        <v>-9.08</v>
       </c>
       <c r="N12" t="b">
         <v>1</v>
@@ -18948,18 +18996,20 @@
         <v>26.9</v>
       </c>
       <c r="H13" t="n">
-        <v>-2.37</v>
+        <v>-0.39</v>
       </c>
       <c r="I13" t="n">
         <v>-3.24</v>
       </c>
-      <c r="J13" t="inlineStr"/>
+      <c r="J13" t="n">
+        <v>-1.02</v>
+      </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="n">
         <v>-12.88</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.4</v>
+        <v>-0.27</v>
       </c>
       <c r="N13" t="b">
         <v>1</v>
@@ -18997,7 +19047,7 @@
         <v>-18.1</v>
       </c>
       <c r="H14" t="n">
-        <v>17.38</v>
+        <v>17.63</v>
       </c>
       <c r="I14" t="n">
         <v>4.46</v>
@@ -19010,7 +19060,7 @@
         <v>-2.69</v>
       </c>
       <c r="M14" t="n">
-        <v>17.35</v>
+        <v>16.74</v>
       </c>
       <c r="N14" t="b">
         <v>1</v>
@@ -19048,7 +19098,7 @@
         <v>-21.5</v>
       </c>
       <c r="H15" t="n">
-        <v>-3.7</v>
+        <v>-2.87</v>
       </c>
       <c r="I15" t="n">
         <v>-1.68</v>
@@ -19061,7 +19111,7 @@
         <v>-8.130000000000001</v>
       </c>
       <c r="M15" t="n">
-        <v>-3.73</v>
+        <v>-3.76</v>
       </c>
       <c r="N15" t="b">
         <v>1</v>
@@ -19099,7 +19149,7 @@
         <v>41.6</v>
       </c>
       <c r="H16" t="n">
-        <v>3.03</v>
+        <v>6.9</v>
       </c>
       <c r="I16" t="n">
         <v>3.43</v>
@@ -19112,7 +19162,7 @@
         <v>-4.38</v>
       </c>
       <c r="M16" t="n">
-        <v>2.35</v>
+        <v>5.35</v>
       </c>
       <c r="N16" t="b">
         <v>1</v>
@@ -19150,7 +19200,7 @@
         <v>32.1</v>
       </c>
       <c r="H17" t="n">
-        <v>6.6</v>
+        <v>11.51</v>
       </c>
       <c r="I17" t="n">
         <v>-3.47</v>
@@ -19163,7 +19213,7 @@
         <v>-6.94</v>
       </c>
       <c r="M17" t="n">
-        <v>5.92</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="N17" t="b">
         <v>1</v>
@@ -19201,7 +19251,7 @@
         <v>-14.4</v>
       </c>
       <c r="H18" t="n">
-        <v>1.72</v>
+        <v>3.67</v>
       </c>
       <c r="I18" t="n">
         <v>-2.38</v>
@@ -19214,7 +19264,7 @@
         <v>-6.46</v>
       </c>
       <c r="M18" t="n">
-        <v>1.04</v>
+        <v>2.12</v>
       </c>
       <c r="N18" t="b">
         <v>1</v>
@@ -19252,7 +19302,7 @@
         <v>-10</v>
       </c>
       <c r="H19" t="n">
-        <v>-10.96</v>
+        <v>-10.24</v>
       </c>
       <c r="I19" t="n">
         <v>-3.29</v>
@@ -19265,7 +19315,7 @@
         <v>-14.66</v>
       </c>
       <c r="M19" t="n">
-        <v>-11.64</v>
+        <v>-11.78</v>
       </c>
       <c r="N19" t="b">
         <v>1</v>
@@ -19303,7 +19353,7 @@
         <v>6.4</v>
       </c>
       <c r="H20" t="n">
-        <v>12.86</v>
+        <v>16.43</v>
       </c>
       <c r="I20" t="n">
         <v>1.48</v>
@@ -19316,7 +19366,7 @@
         <v>-3.35</v>
       </c>
       <c r="M20" t="n">
-        <v>12.18</v>
+        <v>14.89</v>
       </c>
       <c r="N20" t="b">
         <v>1</v>
@@ -19354,7 +19404,7 @@
         <v>20.2</v>
       </c>
       <c r="H21" t="n">
-        <v>0.61</v>
+        <v>1.2</v>
       </c>
       <c r="I21" t="n">
         <v>3.45</v>
@@ -19367,7 +19417,7 @@
         <v>-1.07</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.48</v>
+        <v>-0.76</v>
       </c>
       <c r="N21" t="b">
         <v>1</v>
@@ -19405,7 +19455,7 @@
         <v>43.7</v>
       </c>
       <c r="H22" t="n">
-        <v>13.28</v>
+        <v>15.43</v>
       </c>
       <c r="I22" t="n">
         <v>3.16</v>
@@ -19418,7 +19468,7 @@
         <v>-2.44</v>
       </c>
       <c r="M22" t="n">
-        <v>12.19</v>
+        <v>13.47</v>
       </c>
       <c r="N22" t="b">
         <v>1</v>
@@ -19456,7 +19506,7 @@
         <v>1.9</v>
       </c>
       <c r="H23" t="n">
-        <v>-5.06</v>
+        <v>-3.81</v>
       </c>
       <c r="I23" t="n">
         <v>-10.64</v>
@@ -19469,7 +19519,7 @@
         <v>-14.75</v>
       </c>
       <c r="M23" t="n">
-        <v>-6.15</v>
+        <v>-5.77</v>
       </c>
       <c r="N23" t="b">
         <v>1</v>
@@ -19507,7 +19557,7 @@
         <v>37.5</v>
       </c>
       <c r="H24" t="n">
-        <v>7.82</v>
+        <v>23.93</v>
       </c>
       <c r="I24" t="n">
         <v>5.86</v>
@@ -19520,7 +19570,7 @@
         <v>-3.95</v>
       </c>
       <c r="M24" t="n">
-        <v>6.58</v>
+        <v>21.82</v>
       </c>
       <c r="N24" t="b">
         <v>1</v>
@@ -19558,7 +19608,7 @@
         <v>40.2</v>
       </c>
       <c r="H25" t="n">
-        <v>10.98</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="I25" t="n">
         <v>-1.11</v>
@@ -19571,7 +19621,7 @@
         <v>-5.29</v>
       </c>
       <c r="M25" t="n">
-        <v>9.75</v>
+        <v>7.36</v>
       </c>
       <c r="N25" t="b">
         <v>1</v>
@@ -19609,7 +19659,7 @@
         <v>10.7</v>
       </c>
       <c r="H26" t="n">
-        <v>1.74</v>
+        <v>1.06</v>
       </c>
       <c r="I26" t="n">
         <v>7.3</v>
@@ -19622,7 +19672,7 @@
         <v>-3.78</v>
       </c>
       <c r="M26" t="n">
-        <v>0.5</v>
+        <v>-1.05</v>
       </c>
       <c r="N26" t="b">
         <v>1</v>
@@ -19660,7 +19710,7 @@
         <v>25.6</v>
       </c>
       <c r="H27" t="n">
-        <v>14.5</v>
+        <v>19.74</v>
       </c>
       <c r="I27" t="n">
         <v>7.71</v>
@@ -19673,7 +19723,7 @@
         <v>-4.85</v>
       </c>
       <c r="M27" t="n">
-        <v>14.02</v>
+        <v>18.39</v>
       </c>
       <c r="N27" t="b">
         <v>1</v>
@@ -19711,7 +19761,7 @@
         <v>-6.9</v>
       </c>
       <c r="H28" t="n">
-        <v>20.29</v>
+        <v>18.01</v>
       </c>
       <c r="I28" t="n">
         <v>6.44</v>
@@ -19724,7 +19774,7 @@
         <v>-4.53</v>
       </c>
       <c r="M28" t="n">
-        <v>19.72</v>
+        <v>16.58</v>
       </c>
       <c r="N28" t="b">
         <v>1</v>
@@ -19762,7 +19812,7 @@
         <v>0.3</v>
       </c>
       <c r="H29" t="n">
-        <v>-18.57</v>
+        <v>-15.89</v>
       </c>
       <c r="I29" t="n">
         <v>-10.53</v>
@@ -19775,7 +19825,7 @@
         <v>-17.73</v>
       </c>
       <c r="M29" t="n">
-        <v>-18.63</v>
+        <v>-16.82</v>
       </c>
       <c r="N29" t="b">
         <v>1</v>
@@ -19813,7 +19863,7 @@
         <v>2.8</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.22</v>
+        <v>3.27</v>
       </c>
       <c r="I30" t="n">
         <v>3.18</v>
@@ -19826,7 +19876,7 @@
         <v>-0.88</v>
       </c>
       <c r="M30" t="n">
-        <v>-1</v>
+        <v>1.63</v>
       </c>
       <c r="N30" t="b">
         <v>1</v>
@@ -19864,7 +19914,7 @@
         <v>34.5</v>
       </c>
       <c r="H31" t="n">
-        <v>8.75</v>
+        <v>13.16</v>
       </c>
       <c r="I31" t="n">
         <v>0.66</v>
@@ -19877,7 +19927,7 @@
         <v>-2.64</v>
       </c>
       <c r="M31" t="n">
-        <v>7.97</v>
+        <v>11.51</v>
       </c>
       <c r="N31" t="b">
         <v>1</v>
@@ -19915,7 +19965,7 @@
         <v>24.3</v>
       </c>
       <c r="H32" t="n">
-        <v>34.39</v>
+        <v>38.45</v>
       </c>
       <c r="I32" t="n">
         <v>2.54</v>
@@ -19928,7 +19978,7 @@
         <v>-5.21</v>
       </c>
       <c r="M32" t="n">
-        <v>34.25</v>
+        <v>37.45</v>
       </c>
       <c r="N32" t="b">
         <v>1</v>
@@ -19966,7 +20016,7 @@
         <v>-16.9</v>
       </c>
       <c r="H33" t="n">
-        <v>-3.03</v>
+        <v>1.33</v>
       </c>
       <c r="I33" t="n">
         <v>-6.47</v>
@@ -19979,7 +20029,7 @@
         <v>-11.5</v>
       </c>
       <c r="M33" t="n">
-        <v>-3.17</v>
+        <v>0.33</v>
       </c>
       <c r="N33" t="b">
         <v>1</v>
@@ -20017,7 +20067,7 @@
         <v>20.3</v>
       </c>
       <c r="H34" t="n">
-        <v>-19.81</v>
+        <v>-26.39</v>
       </c>
       <c r="I34" t="n">
         <v>-2.07</v>
@@ -20030,7 +20080,7 @@
         <v>-17.35</v>
       </c>
       <c r="M34" t="n">
-        <v>-19.8</v>
+        <v>-27.23</v>
       </c>
       <c r="N34" t="b">
         <v>1</v>
@@ -20068,7 +20118,7 @@
         <v>0.3</v>
       </c>
       <c r="H35" t="n">
-        <v>-22.09</v>
+        <v>-21.9</v>
       </c>
       <c r="I35" t="n">
         <v>-9.9</v>
@@ -20081,7 +20131,7 @@
         <v>-21.72</v>
       </c>
       <c r="M35" t="n">
-        <v>-22.57</v>
+        <v>-23.24</v>
       </c>
       <c r="N35" t="b">
         <v>1</v>
@@ -20119,7 +20169,7 @@
         <v>49.4</v>
       </c>
       <c r="H36" t="n">
-        <v>-2.11</v>
+        <v>0.18</v>
       </c>
       <c r="I36" t="n">
         <v>2.9</v>
@@ -20132,7 +20182,7 @@
         <v>-5.67</v>
       </c>
       <c r="M36" t="n">
-        <v>-2.4</v>
+        <v>-0.97</v>
       </c>
       <c r="N36" t="b">
         <v>1</v>
@@ -20170,7 +20220,7 @@
         <v>4.5</v>
       </c>
       <c r="H37" t="n">
-        <v>-3.75</v>
+        <v>-2.01</v>
       </c>
       <c r="I37" t="n">
         <v>-7.61</v>
@@ -20183,7 +20233,7 @@
         <v>-11.06</v>
       </c>
       <c r="M37" t="n">
-        <v>-4.04</v>
+        <v>-3.16</v>
       </c>
       <c r="N37" t="b">
         <v>1</v>
@@ -20221,7 +20271,7 @@
         <v>-17.9</v>
       </c>
       <c r="H38" t="n">
-        <v>5.6</v>
+        <v>6.87</v>
       </c>
       <c r="I38" t="n">
         <v>0.6</v>
@@ -20234,7 +20284,7 @@
         <v>-4.72</v>
       </c>
       <c r="M38" t="n">
-        <v>5.28</v>
+        <v>5.69</v>
       </c>
       <c r="N38" t="b">
         <v>1</v>
@@ -20272,7 +20322,7 @@
         <v>2.1</v>
       </c>
       <c r="H39" t="n">
-        <v>-15.93</v>
+        <v>-6.92</v>
       </c>
       <c r="I39" t="n">
         <v>0.25</v>
@@ -20285,7 +20335,7 @@
         <v>-16.43</v>
       </c>
       <c r="M39" t="n">
-        <v>-16.25</v>
+        <v>-8.1</v>
       </c>
       <c r="N39" t="b">
         <v>1</v>
@@ -20323,7 +20373,7 @@
         <v>19.4</v>
       </c>
       <c r="H40" t="n">
-        <v>-6.16</v>
+        <v>-7.24</v>
       </c>
       <c r="I40" t="n">
         <v>-10.01</v>
@@ -20336,7 +20386,7 @@
         <v>-15.23</v>
       </c>
       <c r="M40" t="n">
-        <v>-5.9</v>
+        <v>-7.84</v>
       </c>
       <c r="N40" t="b">
         <v>1</v>
@@ -20374,7 +20424,7 @@
         <v>-2.6</v>
       </c>
       <c r="H41" t="n">
-        <v>-8.91</v>
+        <v>-7.39</v>
       </c>
       <c r="I41" t="n">
         <v>-4.27</v>
@@ -20387,7 +20437,7 @@
         <v>-4.86</v>
       </c>
       <c r="M41" t="n">
-        <v>-8.869999999999999</v>
+        <v>-8.210000000000001</v>
       </c>
       <c r="N41" t="b">
         <v>1</v>
@@ -20425,7 +20475,7 @@
         <v>23.8</v>
       </c>
       <c r="H42" t="n">
-        <v>-3.17</v>
+        <v>3.37</v>
       </c>
       <c r="I42" t="n">
         <v>1.36</v>
@@ -20438,7 +20488,7 @@
         <v>-9.94</v>
       </c>
       <c r="M42" t="n">
-        <v>-2.17</v>
+        <v>3.52</v>
       </c>
       <c r="N42" t="b">
         <v>1</v>
@@ -20476,7 +20526,7 @@
         <v>38.9</v>
       </c>
       <c r="H43" t="n">
-        <v>-10.17</v>
+        <v>-10.18</v>
       </c>
       <c r="I43" t="n">
         <v>-9.220000000000001</v>
@@ -20489,7 +20539,7 @@
         <v>-9.83</v>
       </c>
       <c r="M43" t="n">
-        <v>-9.16</v>
+        <v>-10.03</v>
       </c>
       <c r="N43" t="b">
         <v>1</v>
@@ -20527,7 +20577,7 @@
         <v>43.2</v>
       </c>
       <c r="H44" t="n">
-        <v>-11.84</v>
+        <v>-10.98</v>
       </c>
       <c r="I44" t="n">
         <v>-3.15</v>
@@ -20578,7 +20628,7 @@
         <v>-8.199999999999999</v>
       </c>
       <c r="H45" t="n">
-        <v>4.62</v>
+        <v>6.35</v>
       </c>
       <c r="I45" t="n">
         <v>5.34</v>
@@ -20591,7 +20641,7 @@
         <v>-5.27</v>
       </c>
       <c r="M45" t="n">
-        <v>5.46</v>
+        <v>6.33</v>
       </c>
       <c r="N45" t="b">
         <v>1</v>
@@ -20629,7 +20679,7 @@
         <v>-23.9</v>
       </c>
       <c r="H46" t="n">
-        <v>-6.52</v>
+        <v>-3.94</v>
       </c>
       <c r="I46" t="n">
         <v>3.28</v>
@@ -20642,7 +20692,7 @@
         <v>-4.46</v>
       </c>
       <c r="M46" t="n">
-        <v>-5.97</v>
+        <v>-4.25</v>
       </c>
       <c r="N46" t="b">
         <v>1</v>
@@ -20680,7 +20730,7 @@
         <v>26.7</v>
       </c>
       <c r="H47" t="n">
-        <v>-0.92</v>
+        <v>-0.6</v>
       </c>
       <c r="I47" t="n">
         <v>-0.05</v>
@@ -20693,7 +20743,7 @@
         <v>-0.87</v>
       </c>
       <c r="M47" t="n">
-        <v>-0.38</v>
+        <v>-0.92</v>
       </c>
       <c r="N47" t="b">
         <v>1</v>
@@ -20731,7 +20781,7 @@
         <v>-3.5</v>
       </c>
       <c r="H48" t="n">
-        <v>-2.56</v>
+        <v>2.59</v>
       </c>
       <c r="I48" t="n">
         <v>-4.95</v>
@@ -20744,7 +20794,7 @@
         <v>-8.43</v>
       </c>
       <c r="M48" t="n">
-        <v>-2.22</v>
+        <v>2.07</v>
       </c>
       <c r="N48" t="b">
         <v>1</v>
@@ -20782,7 +20832,7 @@
         <v>-17.9</v>
       </c>
       <c r="H49" t="n">
-        <v>-1.2</v>
+        <v>6.18</v>
       </c>
       <c r="I49" t="n">
         <v>-0.5</v>
@@ -20795,7 +20845,7 @@
         <v>-3.43</v>
       </c>
       <c r="M49" t="n">
-        <v>-0.86</v>
+        <v>5.66</v>
       </c>
       <c r="N49" t="b">
         <v>1</v>
@@ -20833,7 +20883,7 @@
         <v>53.5</v>
       </c>
       <c r="H50" t="n">
-        <v>5.6</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="I50" t="n">
         <v>1.23</v>
@@ -20846,7 +20896,7 @@
         <v>-7.57</v>
       </c>
       <c r="M50" t="n">
-        <v>5.84</v>
+        <v>8.65</v>
       </c>
       <c r="N50" t="b">
         <v>1</v>
@@ -20884,7 +20934,7 @@
         <v>-1</v>
       </c>
       <c r="H51" t="n">
-        <v>-12.45</v>
+        <v>-12.52</v>
       </c>
       <c r="I51" t="n">
         <v>-6.26</v>
@@ -20897,7 +20947,7 @@
         <v>-15</v>
       </c>
       <c r="M51" t="n">
-        <v>-12.21</v>
+        <v>-13.15</v>
       </c>
       <c r="N51" t="b">
         <v>1</v>
@@ -20935,7 +20985,7 @@
         <v>29.7</v>
       </c>
       <c r="H52" t="n">
-        <v>4.8</v>
+        <v>11.14</v>
       </c>
       <c r="I52" t="n">
         <v>11.27</v>
@@ -20948,7 +20998,7 @@
         <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>5.04</v>
+        <v>10.52</v>
       </c>
       <c r="N52" t="b">
         <v>1</v>
@@ -20986,7 +21036,7 @@
         <v>15.2</v>
       </c>
       <c r="H53" t="n">
-        <v>-38.8</v>
+        <v>-31.29</v>
       </c>
       <c r="I53" t="n">
         <v>-8.77</v>
@@ -20999,7 +21049,7 @@
         <v>-24.79</v>
       </c>
       <c r="M53" t="n">
-        <v>-37.83</v>
+        <v>-31.18</v>
       </c>
       <c r="N53" t="b">
         <v>1</v>
@@ -21037,7 +21087,7 @@
         <v>22.2</v>
       </c>
       <c r="H54" t="n">
-        <v>9.92</v>
+        <v>12.66</v>
       </c>
       <c r="I54" t="n">
         <v>1.01</v>
@@ -21050,7 +21100,7 @@
         <v>-3.94</v>
       </c>
       <c r="M54" t="n">
-        <v>10.88</v>
+        <v>12.77</v>
       </c>
       <c r="N54" t="b">
         <v>1</v>
@@ -21092,7 +21142,7 @@
         <v>-0</v>
       </c>
       <c r="H55" t="n">
-        <v>50.86</v>
+        <v>52.65</v>
       </c>
       <c r="I55" t="n">
         <v>13.5</v>
@@ -21105,7 +21155,7 @@
         <v>-2.53</v>
       </c>
       <c r="M55" t="n">
-        <v>48.34</v>
+        <v>49.24</v>
       </c>
       <c r="N55" t="b">
         <v>1</v>
@@ -21143,7 +21193,7 @@
         <v>10.5</v>
       </c>
       <c r="H56" t="n">
-        <v>16.5</v>
+        <v>18.72</v>
       </c>
       <c r="I56" t="n">
         <v>1.99</v>
@@ -21156,7 +21206,7 @@
         <v>-6.27</v>
       </c>
       <c r="M56" t="n">
-        <v>13.98</v>
+        <v>15.31</v>
       </c>
       <c r="N56" t="b">
         <v>1</v>
@@ -21194,7 +21244,7 @@
         <v>-37</v>
       </c>
       <c r="H57" t="n">
-        <v>50.12</v>
+        <v>60.29</v>
       </c>
       <c r="I57" t="n">
         <v>18.38</v>
@@ -21207,7 +21257,7 @@
         <v>-5.11</v>
       </c>
       <c r="M57" t="n">
-        <v>46.94</v>
+        <v>56.21</v>
       </c>
       <c r="N57" t="b">
         <v>1</v>
@@ -21245,7 +21295,7 @@
         <v>-26.8</v>
       </c>
       <c r="H58" t="n">
-        <v>27.97</v>
+        <v>25.57</v>
       </c>
       <c r="I58" t="n">
         <v>4.56</v>
@@ -21258,7 +21308,7 @@
         <v>-4.09</v>
       </c>
       <c r="M58" t="n">
-        <v>24.79</v>
+        <v>21.5</v>
       </c>
       <c r="N58" t="b">
         <v>1</v>
@@ -21296,7 +21346,7 @@
         <v>-36.5</v>
       </c>
       <c r="H59" t="n">
-        <v>-34.33</v>
+        <v>-32.57</v>
       </c>
       <c r="I59" t="n">
         <v>-27.75</v>
@@ -21309,7 +21359,7 @@
         <v>-31.28</v>
       </c>
       <c r="M59" t="n">
-        <v>-38.17</v>
+        <v>-37.3</v>
       </c>
       <c r="N59" t="b">
         <v>1</v>
@@ -21347,7 +21397,7 @@
         <v>-38.7</v>
       </c>
       <c r="H60" t="n">
-        <v>22.21</v>
+        <v>26.39</v>
       </c>
       <c r="I60" t="n">
         <v>17.17</v>
@@ -21360,7 +21410,7 @@
         <v>-0.54</v>
       </c>
       <c r="M60" t="n">
-        <v>18.37</v>
+        <v>21.66</v>
       </c>
       <c r="N60" t="b">
         <v>1</v>
@@ -21398,7 +21448,7 @@
         <v>-34.6</v>
       </c>
       <c r="H61" t="n">
-        <v>19.64</v>
+        <v>20.12</v>
       </c>
       <c r="I61" t="n">
         <v>6.67</v>
@@ -21411,7 +21461,7 @@
         <v>-3.06</v>
       </c>
       <c r="M61" t="n">
-        <v>15.8</v>
+        <v>15.38</v>
       </c>
       <c r="N61" t="b">
         <v>1</v>
@@ -21449,7 +21499,7 @@
         <v>-11.8</v>
       </c>
       <c r="H62" t="n">
-        <v>4.3</v>
+        <v>5.1</v>
       </c>
       <c r="I62" t="n">
         <v>9.76</v>
@@ -21457,12 +21507,14 @@
       <c r="J62" t="n">
         <v>10.33</v>
       </c>
-      <c r="K62" t="inlineStr"/>
+      <c r="K62" t="n">
+        <v>5.1</v>
+      </c>
       <c r="L62" t="n">
         <v>-1.63</v>
       </c>
       <c r="M62" t="n">
-        <v>0.35</v>
+        <v>0.25</v>
       </c>
       <c r="N62" t="b">
         <v>1</v>
@@ -21500,7 +21552,7 @@
         <v>0.1</v>
       </c>
       <c r="H63" t="n">
-        <v>-6.05</v>
+        <v>-2.62</v>
       </c>
       <c r="I63" t="n">
         <v>-2.83</v>
@@ -21508,12 +21560,14 @@
       <c r="J63" t="n">
         <v>1.23</v>
       </c>
-      <c r="K63" t="inlineStr"/>
+      <c r="K63" t="n">
+        <v>-2.62</v>
+      </c>
       <c r="L63" t="n">
         <v>-5.45</v>
       </c>
       <c r="M63" t="n">
-        <v>-10</v>
+        <v>-7.47</v>
       </c>
       <c r="N63" t="b">
         <v>1</v>
@@ -21551,7 +21605,7 @@
         <v>24.1</v>
       </c>
       <c r="H64" t="n">
-        <v>2.5</v>
+        <v>2.89</v>
       </c>
       <c r="I64" t="n">
         <v>-8.31</v>
@@ -21559,12 +21613,14 @@
       <c r="J64" t="n">
         <v>-17.97</v>
       </c>
-      <c r="K64" t="inlineStr"/>
+      <c r="K64" t="n">
+        <v>2.87</v>
+      </c>
       <c r="L64" t="n">
         <v>-18.31</v>
       </c>
       <c r="M64" t="n">
-        <v>-0.66</v>
+        <v>-1.15</v>
       </c>
       <c r="N64" t="b">
         <v>1</v>
@@ -21602,7 +21658,7 @@
         <v>-15.9</v>
       </c>
       <c r="H65" t="n">
-        <v>15.14</v>
+        <v>20.25</v>
       </c>
       <c r="I65" t="n">
         <v>10.45</v>
@@ -21610,12 +21666,14 @@
       <c r="J65" t="n">
         <v>17.86</v>
       </c>
-      <c r="K65" t="inlineStr"/>
+      <c r="K65" t="n">
+        <v>19.53</v>
+      </c>
       <c r="L65" t="n">
         <v>-0.31</v>
       </c>
       <c r="M65" t="n">
-        <v>11.99</v>
+        <v>16.21</v>
       </c>
       <c r="N65" t="b">
         <v>1</v>
@@ -21653,7 +21711,7 @@
         <v>-21.8</v>
       </c>
       <c r="H66" t="n">
-        <v>-35.04</v>
+        <v>-35.33</v>
       </c>
       <c r="I66" t="n">
         <v>-18.97</v>
@@ -21668,7 +21726,7 @@
         <v>-26.82</v>
       </c>
       <c r="M66" t="n">
-        <v>-38.96</v>
+        <v>-40.15</v>
       </c>
       <c r="N66" t="b">
         <v>1</v>
@@ -21706,7 +21764,7 @@
         <v>57</v>
       </c>
       <c r="H67" t="n">
-        <v>33.95</v>
+        <v>35.19</v>
       </c>
       <c r="I67" t="n">
         <v>-11.21</v>
@@ -21721,7 +21779,7 @@
         <v>-13.87</v>
       </c>
       <c r="M67" t="n">
-        <v>31.04</v>
+        <v>31.39</v>
       </c>
       <c r="N67" t="b">
         <v>1</v>
@@ -21759,7 +21817,7 @@
         <v>-21.8</v>
       </c>
       <c r="H68" t="n">
-        <v>19.46</v>
+        <v>24.65</v>
       </c>
       <c r="I68" t="n">
         <v>1.71</v>
@@ -21774,7 +21832,7 @@
         <v>-6.18</v>
       </c>
       <c r="M68" t="n">
-        <v>16.54</v>
+        <v>20.85</v>
       </c>
       <c r="N68" t="b">
         <v>1</v>
@@ -21812,7 +21870,7 @@
         <v>1</v>
       </c>
       <c r="H69" t="n">
-        <v>-35.81</v>
+        <v>-38.31</v>
       </c>
       <c r="I69" t="n">
         <v>-11.52</v>
@@ -21827,7 +21885,7 @@
         <v>-16.26</v>
       </c>
       <c r="M69" t="n">
-        <v>-38.77</v>
+        <v>-42.16</v>
       </c>
       <c r="N69" t="b">
         <v>1</v>
@@ -21865,7 +21923,7 @@
         <v>32.3</v>
       </c>
       <c r="H70" t="n">
-        <v>-38.04</v>
+        <v>-39.58</v>
       </c>
       <c r="I70" t="n">
         <v>-20.76</v>
@@ -21880,7 +21938,7 @@
         <v>-27.91</v>
       </c>
       <c r="M70" t="n">
-        <v>-41</v>
+        <v>-43.43</v>
       </c>
       <c r="N70" t="b">
         <v>1</v>
@@ -21918,7 +21976,7 @@
         <v>3.7</v>
       </c>
       <c r="H71" t="n">
-        <v>-13.44</v>
+        <v>-10.18</v>
       </c>
       <c r="I71" t="n">
         <v>-1.11</v>
@@ -21933,7 +21991,7 @@
         <v>-25.46</v>
       </c>
       <c r="M71" t="n">
-        <v>-16.4</v>
+        <v>-14.03</v>
       </c>
       <c r="N71" t="b">
         <v>1</v>
@@ -21971,7 +22029,7 @@
         <v>42.4</v>
       </c>
       <c r="H72" t="n">
-        <v>-20.44</v>
+        <v>-19.56</v>
       </c>
       <c r="I72" t="n">
         <v>2.16</v>
@@ -21986,7 +22044,7 @@
         <v>-15.76</v>
       </c>
       <c r="M72" t="n">
-        <v>-23.4</v>
+        <v>-23.41</v>
       </c>
       <c r="N72" t="b">
         <v>1</v>
@@ -22024,7 +22082,7 @@
         <v>28.2</v>
       </c>
       <c r="H73" t="n">
-        <v>-14.72</v>
+        <v>-13.73</v>
       </c>
       <c r="I73" t="n">
         <v>-1.71</v>
@@ -22039,7 +22097,7 @@
         <v>-23.43</v>
       </c>
       <c r="M73" t="n">
-        <v>-17.68</v>
+        <v>-17.57</v>
       </c>
       <c r="N73" t="b">
         <v>1</v>
@@ -22077,7 +22135,7 @@
         <v>28.6</v>
       </c>
       <c r="H74" t="n">
-        <v>-13.44</v>
+        <v>-3.11</v>
       </c>
       <c r="I74" t="n">
         <v>2.81</v>
@@ -22092,7 +22150,7 @@
         <v>-18.87</v>
       </c>
       <c r="M74" t="n">
-        <v>-16.4</v>
+        <v>-6.96</v>
       </c>
       <c r="N74" t="b">
         <v>1</v>
@@ -22130,7 +22188,7 @@
         <v>21.8</v>
       </c>
       <c r="H75" t="n">
-        <v>-30.1</v>
+        <v>-27.95</v>
       </c>
       <c r="I75" t="n">
         <v>-6.34</v>
@@ -22145,7 +22203,7 @@
         <v>-30.04</v>
       </c>
       <c r="M75" t="n">
-        <v>-33.06</v>
+        <v>-31.8</v>
       </c>
       <c r="N75" t="b">
         <v>1</v>
@@ -22183,7 +22241,7 @@
         <v>24.1</v>
       </c>
       <c r="H76" t="n">
-        <v>-16.34</v>
+        <v>-14.07</v>
       </c>
       <c r="I76" t="n">
         <v>-1.6</v>
@@ -22198,7 +22256,7 @@
         <v>-22.54</v>
       </c>
       <c r="M76" t="n">
-        <v>-19.3</v>
+        <v>-17.92</v>
       </c>
       <c r="N76" t="b">
         <v>1</v>
@@ -22236,7 +22294,7 @@
         <v>24.5</v>
       </c>
       <c r="H77" t="n">
-        <v>-32.65</v>
+        <v>-29.93</v>
       </c>
       <c r="I77" t="n">
         <v>-12.99</v>
@@ -22251,7 +22309,7 @@
         <v>-22.54</v>
       </c>
       <c r="M77" t="n">
-        <v>-35.61</v>
+        <v>-33.78</v>
       </c>
       <c r="N77" t="b">
         <v>1</v>
@@ -22289,7 +22347,7 @@
         <v>-8.699999999999999</v>
       </c>
       <c r="H78" t="n">
-        <v>-12.46</v>
+        <v>-10.76</v>
       </c>
       <c r="I78" t="n">
         <v>17.25</v>
@@ -22304,7 +22362,7 @@
         <v>-4.65</v>
       </c>
       <c r="M78" t="n">
-        <v>-15.42</v>
+        <v>-14.61</v>
       </c>
       <c r="N78" t="b">
         <v>1</v>
@@ -22342,7 +22400,7 @@
         <v>37.2</v>
       </c>
       <c r="H79" t="n">
-        <v>-37.91</v>
+        <v>-37.72</v>
       </c>
       <c r="I79" t="n">
         <v>-7.64</v>
@@ -22357,7 +22415,7 @@
         <v>-26.24</v>
       </c>
       <c r="M79" t="n">
-        <v>-40.87</v>
+        <v>-41.56</v>
       </c>
       <c r="N79" t="b">
         <v>1</v>
@@ -22395,7 +22453,7 @@
         <v>29.8</v>
       </c>
       <c r="H80" t="n">
-        <v>7.09</v>
+        <v>6.65</v>
       </c>
       <c r="I80" t="n">
         <v>-2.74</v>
@@ -22410,7 +22468,7 @@
         <v>-22.36</v>
       </c>
       <c r="M80" t="n">
-        <v>4.13</v>
+        <v>2.8</v>
       </c>
       <c r="N80" t="b">
         <v>1</v>
@@ -22448,7 +22506,7 @@
         <v>19.3</v>
       </c>
       <c r="H81" t="n">
-        <v>-37.42</v>
+        <v>-34.67</v>
       </c>
       <c r="I81" t="n">
         <v>-16.69</v>
@@ -22463,7 +22521,7 @@
         <v>-36.39</v>
       </c>
       <c r="M81" t="n">
-        <v>-40.38</v>
+        <v>-38.52</v>
       </c>
       <c r="N81" t="b">
         <v>1</v>
@@ -22501,7 +22559,7 @@
         <v>11.8</v>
       </c>
       <c r="H82" t="n">
-        <v>-3.91</v>
+        <v>-1.29</v>
       </c>
       <c r="I82" t="n">
         <v>-1.19</v>
@@ -22516,7 +22574,7 @@
         <v>-17.57</v>
       </c>
       <c r="M82" t="n">
-        <v>-6.87</v>
+        <v>-5.14</v>
       </c>
       <c r="N82" t="b">
         <v>1</v>
@@ -22554,7 +22612,7 @@
         <v>27.5</v>
       </c>
       <c r="H83" t="n">
-        <v>2.35</v>
+        <v>3.41</v>
       </c>
       <c r="I83" t="n">
         <v>8.42</v>
@@ -22569,7 +22627,7 @@
         <v>-2.51</v>
       </c>
       <c r="M83" t="n">
-        <v>-0.61</v>
+        <v>-0.44</v>
       </c>
       <c r="N83" t="b">
         <v>1</v>
@@ -22607,7 +22665,7 @@
         <v>-14.7</v>
       </c>
       <c r="H84" t="n">
-        <v>-20.98</v>
+        <v>-21.26</v>
       </c>
       <c r="I84" t="n">
         <v>10.3</v>
@@ -22622,7 +22680,7 @@
         <v>-2.6</v>
       </c>
       <c r="M84" t="n">
-        <v>-23.94</v>
+        <v>-25.11</v>
       </c>
       <c r="N84" t="b">
         <v>1</v>
@@ -22664,7 +22722,7 @@
         <v>-9.300000000000001</v>
       </c>
       <c r="H85" t="n">
-        <v>-21.03</v>
+        <v>-21.54</v>
       </c>
       <c r="I85" t="n">
         <v>10.42</v>
@@ -22679,7 +22737,7 @@
         <v>-21.72</v>
       </c>
       <c r="M85" t="n">
-        <v>-23.99</v>
+        <v>-25.39</v>
       </c>
       <c r="N85" t="b">
         <v>1</v>
@@ -22717,7 +22775,7 @@
         <v>5.1</v>
       </c>
       <c r="H86" t="n">
-        <v>7.54</v>
+        <v>12.95</v>
       </c>
       <c r="I86" t="n">
         <v>8.77</v>
@@ -22732,7 +22790,7 @@
         <v>-3.54</v>
       </c>
       <c r="M86" t="n">
-        <v>4.58</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="N86" t="b">
         <v>1</v>
@@ -22770,7 +22828,7 @@
         <v>34.2</v>
       </c>
       <c r="H87" t="n">
-        <v>2.73</v>
+        <v>4.09</v>
       </c>
       <c r="I87" t="n">
         <v>8.15</v>
@@ -22785,7 +22843,7 @@
         <v>-7.63</v>
       </c>
       <c r="M87" t="n">
-        <v>-0.23</v>
+        <v>0.24</v>
       </c>
       <c r="N87" t="b">
         <v>1</v>
@@ -22823,7 +22881,7 @@
         <v>42</v>
       </c>
       <c r="H88" t="n">
-        <v>-33.18</v>
+        <v>-34.98</v>
       </c>
       <c r="I88" t="n">
         <v>0.6</v>
@@ -22838,7 +22896,7 @@
         <v>-16.67</v>
       </c>
       <c r="M88" t="n">
-        <v>-36.15</v>
+        <v>-38.83</v>
       </c>
       <c r="N88" t="b">
         <v>1</v>
@@ -22876,7 +22934,7 @@
         <v>-7.7</v>
       </c>
       <c r="H89" t="n">
-        <v>-13.8</v>
+        <v>-13.67</v>
       </c>
       <c r="I89" t="n">
         <v>-6.47</v>
@@ -22891,7 +22949,7 @@
         <v>-23.05</v>
       </c>
       <c r="M89" t="n">
-        <v>-16.77</v>
+        <v>-17.52</v>
       </c>
       <c r="N89" t="b">
         <v>1</v>
@@ -22929,7 +22987,7 @@
         <v>13.7</v>
       </c>
       <c r="H90" t="n">
-        <v>2.71</v>
+        <v>4.97</v>
       </c>
       <c r="I90" t="n">
         <v>2.74</v>
@@ -22944,7 +23002,7 @@
         <v>-24.02</v>
       </c>
       <c r="M90" t="n">
-        <v>-0.25</v>
+        <v>1.12</v>
       </c>
       <c r="N90" t="b">
         <v>1</v>
@@ -22982,7 +23040,7 @@
         <v>21.8</v>
       </c>
       <c r="H91" t="n">
-        <v>-21.94</v>
+        <v>-26.36</v>
       </c>
       <c r="I91" t="n">
         <v>18.32</v>
@@ -22997,7 +23055,7 @@
         <v>-23.27</v>
       </c>
       <c r="M91" t="n">
-        <v>-24.9</v>
+        <v>-30.21</v>
       </c>
       <c r="N91" t="b">
         <v>1</v>
@@ -23035,7 +23093,7 @@
         <v>29.4</v>
       </c>
       <c r="H92" t="n">
-        <v>-23.38</v>
+        <v>-24.78</v>
       </c>
       <c r="I92" t="n">
         <v>-2.62</v>
@@ -23050,7 +23108,7 @@
         <v>-27.18</v>
       </c>
       <c r="M92" t="n">
-        <v>-26.34</v>
+        <v>-28.63</v>
       </c>
       <c r="N92" t="b">
         <v>1</v>
@@ -23088,7 +23146,7 @@
         <v>-3.7</v>
       </c>
       <c r="H93" t="n">
-        <v>-29.17</v>
+        <v>-27.66</v>
       </c>
       <c r="I93" t="n">
         <v>-8.07</v>
@@ -23103,7 +23161,7 @@
         <v>-22.12</v>
       </c>
       <c r="M93" t="n">
-        <v>-32.13</v>
+        <v>-31.5</v>
       </c>
       <c r="N93" t="b">
         <v>1</v>
@@ -23141,7 +23199,7 @@
         <v>21.3</v>
       </c>
       <c r="H94" t="n">
-        <v>1.42</v>
+        <v>1.75</v>
       </c>
       <c r="I94" t="n">
         <v>0.23</v>
@@ -23156,7 +23214,7 @@
         <v>-0.85</v>
       </c>
       <c r="M94" t="n">
-        <v>-1.54</v>
+        <v>-2.1</v>
       </c>
       <c r="N94" t="b">
         <v>1</v>
@@ -23194,7 +23252,7 @@
         <v>-21.4</v>
       </c>
       <c r="H95" t="n">
-        <v>2.26</v>
+        <v>2.87</v>
       </c>
       <c r="I95" t="n">
         <v>4.55</v>
@@ -23209,7 +23267,7 @@
         <v>-6.39</v>
       </c>
       <c r="M95" t="n">
-        <v>-0.7</v>
+        <v>-0.98</v>
       </c>
       <c r="N95" t="b">
         <v>1</v>
@@ -23247,7 +23305,7 @@
         <v>16.3</v>
       </c>
       <c r="H96" t="n">
-        <v>-15.78</v>
+        <v>-17.89</v>
       </c>
       <c r="I96" t="n">
         <v>-1</v>
@@ -23262,7 +23320,7 @@
         <v>-22.5</v>
       </c>
       <c r="M96" t="n">
-        <v>-18.74</v>
+        <v>-21.73</v>
       </c>
       <c r="N96" t="b">
         <v>1</v>
@@ -23300,7 +23358,7 @@
         <v>0.2</v>
       </c>
       <c r="H97" t="n">
-        <v>19.38</v>
+        <v>22.49</v>
       </c>
       <c r="I97" t="n">
         <v>4.35</v>
@@ -23315,7 +23373,7 @@
         <v>-2.79</v>
       </c>
       <c r="M97" t="n">
-        <v>16.42</v>
+        <v>18.64</v>
       </c>
       <c r="N97" t="b">
         <v>1</v>
@@ -23353,7 +23411,7 @@
         <v>8.4</v>
       </c>
       <c r="H98" t="n">
-        <v>-38.79</v>
+        <v>-42.87</v>
       </c>
       <c r="I98" t="n">
         <v>-0.13</v>
@@ -23368,7 +23426,7 @@
         <v>-10.87</v>
       </c>
       <c r="M98" t="n">
-        <v>-41.75</v>
+        <v>-46.72</v>
       </c>
       <c r="N98" t="b">
         <v>1</v>
@@ -23406,7 +23464,7 @@
         <v>-7.3</v>
       </c>
       <c r="H99" t="n">
-        <v>-22.37</v>
+        <v>-20.36</v>
       </c>
       <c r="I99" t="n">
         <v>-4.12</v>
@@ -23421,7 +23479,7 @@
         <v>-15.02</v>
       </c>
       <c r="M99" t="n">
-        <v>-25.33</v>
+        <v>-24.2</v>
       </c>
       <c r="N99" t="b">
         <v>1</v>
@@ -23459,7 +23517,7 @@
         <v>17.9</v>
       </c>
       <c r="H100" t="n">
-        <v>-6.79</v>
+        <v>-5.45</v>
       </c>
       <c r="I100" t="n">
         <v>12.97</v>
@@ -23474,7 +23532,7 @@
         <v>-8.130000000000001</v>
       </c>
       <c r="M100" t="n">
-        <v>-9.75</v>
+        <v>-9.300000000000001</v>
       </c>
       <c r="N100" t="b">
         <v>1</v>
@@ -23512,7 +23570,7 @@
         <v>14.8</v>
       </c>
       <c r="H101" t="n">
-        <v>-7.06</v>
+        <v>-8.31</v>
       </c>
       <c r="I101" t="n">
         <v>0.35</v>
@@ -23527,7 +23585,7 @@
         <v>-3.68</v>
       </c>
       <c r="M101" t="n">
-        <v>-10.02</v>
+        <v>-12.15</v>
       </c>
       <c r="N101" t="b">
         <v>1</v>
@@ -23565,7 +23623,7 @@
         <v>25.5</v>
       </c>
       <c r="H102" t="n">
-        <v>4.82</v>
+        <v>12.21</v>
       </c>
       <c r="I102" t="n">
         <v>-9.369999999999999</v>
@@ -23580,7 +23638,7 @@
         <v>-22.11</v>
       </c>
       <c r="M102" t="n">
-        <v>1.86</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="N102" t="b">
         <v>1</v>
@@ -23622,7 +23680,7 @@
         <v>-7.5</v>
       </c>
       <c r="H103" t="n">
-        <v>-17.07</v>
+        <v>-26.94</v>
       </c>
       <c r="I103" t="n">
         <v>4.46</v>
@@ -23637,7 +23695,7 @@
         <v>-8.52</v>
       </c>
       <c r="M103" t="n">
-        <v>-20.03</v>
+        <v>-30.79</v>
       </c>
       <c r="N103" t="b">
         <v>1</v>
@@ -23675,7 +23733,7 @@
         <v>-11</v>
       </c>
       <c r="H104" t="n">
-        <v>18.39</v>
+        <v>25.61</v>
       </c>
       <c r="I104" t="n">
         <v>10.7</v>
@@ -23690,7 +23748,7 @@
         <v>-9.43</v>
       </c>
       <c r="M104" t="n">
-        <v>15.43</v>
+        <v>21.76</v>
       </c>
       <c r="N104" t="b">
         <v>1</v>
@@ -23728,7 +23786,7 @@
         <v>-11.4</v>
       </c>
       <c r="H105" t="n">
-        <v>-18.81</v>
+        <v>-20.7</v>
       </c>
       <c r="I105" t="n">
         <v>4.36</v>
@@ -23743,7 +23801,7 @@
         <v>-11.36</v>
       </c>
       <c r="M105" t="n">
-        <v>-21.77</v>
+        <v>-24.55</v>
       </c>
       <c r="N105" t="b">
         <v>1</v>
@@ -23781,7 +23839,7 @@
         <v>27.1</v>
       </c>
       <c r="H106" t="n">
-        <v>-17.25</v>
+        <v>-17.97</v>
       </c>
       <c r="I106" t="n">
         <v>5.02</v>
@@ -23796,7 +23854,7 @@
         <v>-14.35</v>
       </c>
       <c r="M106" t="n">
-        <v>-20.21</v>
+        <v>-21.82</v>
       </c>
       <c r="N106" t="b">
         <v>1</v>
@@ -23834,7 +23892,7 @@
         <v>32.2</v>
       </c>
       <c r="H107" t="n">
-        <v>6.17</v>
+        <v>7.61</v>
       </c>
       <c r="I107" t="n">
         <v>6.49</v>
@@ -23849,7 +23907,7 @@
         <v>-3.92</v>
       </c>
       <c r="M107" t="n">
-        <v>3.21</v>
+        <v>3.76</v>
       </c>
       <c r="N107" t="b">
         <v>1</v>
@@ -23887,7 +23945,7 @@
         <v>3.2</v>
       </c>
       <c r="H108" t="n">
-        <v>-29.27</v>
+        <v>-29.37</v>
       </c>
       <c r="I108" t="n">
         <v>-10.41</v>
@@ -23902,7 +23960,7 @@
         <v>-23.7</v>
       </c>
       <c r="M108" t="n">
-        <v>-32.23</v>
+        <v>-33.22</v>
       </c>
       <c r="N108" t="b">
         <v>1</v>
@@ -23940,7 +23998,7 @@
         <v>-0.3</v>
       </c>
       <c r="H109" t="n">
-        <v>-16.89</v>
+        <v>-14.58</v>
       </c>
       <c r="I109" t="n">
         <v>17.76</v>
@@ -23955,7 +24013,7 @@
         <v>-14.18</v>
       </c>
       <c r="M109" t="n">
-        <v>-19.85</v>
+        <v>-18.43</v>
       </c>
       <c r="N109" t="b">
         <v>1</v>
@@ -23993,7 +24051,7 @@
         <v>34.6</v>
       </c>
       <c r="H110" t="n">
-        <v>-0.04</v>
+        <v>-4.57</v>
       </c>
       <c r="I110" t="n">
         <v>5.7</v>
@@ -24008,7 +24066,7 @@
         <v>-7.7</v>
       </c>
       <c r="M110" t="n">
-        <v>-3</v>
+        <v>-8.42</v>
       </c>
       <c r="N110" t="b">
         <v>1</v>
@@ -24046,7 +24104,7 @@
         <v>10.4</v>
       </c>
       <c r="H111" t="n">
-        <v>21.94</v>
+        <v>26.6</v>
       </c>
       <c r="I111" t="n">
         <v>11.05</v>
@@ -24061,7 +24119,7 @@
         <v>-5.54</v>
       </c>
       <c r="M111" t="n">
-        <v>18.98</v>
+        <v>22.75</v>
       </c>
       <c r="N111" t="b">
         <v>1</v>
@@ -24099,7 +24157,7 @@
         <v>-21.5</v>
       </c>
       <c r="H112" t="n">
-        <v>-5.74</v>
+        <v>-2.07</v>
       </c>
       <c r="I112" t="n">
         <v>10.65</v>
@@ -24114,7 +24172,7 @@
         <v>-6.89</v>
       </c>
       <c r="M112" t="n">
-        <v>-8.699999999999999</v>
+        <v>-5.91</v>
       </c>
       <c r="N112" t="b">
         <v>1</v>
@@ -24152,7 +24210,7 @@
         <v>3.5</v>
       </c>
       <c r="H113" t="n">
-        <v>58.39</v>
+        <v>67.81999999999999</v>
       </c>
       <c r="I113" t="n">
         <v>33.01</v>
@@ -24167,7 +24225,7 @@
         <v>-0.92</v>
       </c>
       <c r="M113" t="n">
-        <v>55.43</v>
+        <v>63.97</v>
       </c>
       <c r="N113" t="b">
         <v>1</v>
@@ -24205,7 +24263,7 @@
         <v>-30.5</v>
       </c>
       <c r="H114" t="n">
-        <v>3.59</v>
+        <v>-1.32</v>
       </c>
       <c r="I114" t="n">
         <v>2.96</v>
@@ -24220,7 +24278,7 @@
         <v>-17.88</v>
       </c>
       <c r="M114" t="n">
-        <v>0.63</v>
+        <v>-5.17</v>
       </c>
       <c r="N114" t="b">
         <v>1</v>
@@ -24258,7 +24316,7 @@
         <v>-6</v>
       </c>
       <c r="H115" t="n">
-        <v>-29.44</v>
+        <v>-30.73</v>
       </c>
       <c r="I115" t="n">
         <v>3.31</v>
@@ -24273,7 +24331,7 @@
         <v>-21.48</v>
       </c>
       <c r="M115" t="n">
-        <v>-32.4</v>
+        <v>-34.58</v>
       </c>
       <c r="N115" t="b">
         <v>1</v>
@@ -24311,7 +24369,7 @@
         <v>-34.6</v>
       </c>
       <c r="H116" t="n">
-        <v>11.78</v>
+        <v>20.79</v>
       </c>
       <c r="I116" t="n">
         <v>23.65</v>
@@ -24326,7 +24384,7 @@
         <v>-3.83</v>
       </c>
       <c r="M116" t="n">
-        <v>8.82</v>
+        <v>16.94</v>
       </c>
       <c r="N116" t="b">
         <v>1</v>
@@ -24364,7 +24422,7 @@
         <v>-16.2</v>
       </c>
       <c r="H117" t="n">
-        <v>2.37</v>
+        <v>6.42</v>
       </c>
       <c r="I117" t="n">
         <v>25.77</v>
@@ -24379,7 +24437,7 @@
         <v>-1.7</v>
       </c>
       <c r="M117" t="n">
-        <v>-0.6</v>
+        <v>2.58</v>
       </c>
       <c r="N117" t="b">
         <v>1</v>
@@ -24417,7 +24475,7 @@
         <v>-24.9</v>
       </c>
       <c r="H118" t="n">
-        <v>4.86</v>
+        <v>3.49</v>
       </c>
       <c r="I118" t="n">
         <v>10.88</v>
@@ -24432,7 +24490,7 @@
         <v>-4.1</v>
       </c>
       <c r="M118" t="n">
-        <v>1.9</v>
+        <v>-0.36</v>
       </c>
       <c r="N118" t="b">
         <v>1</v>
@@ -24474,7 +24532,7 @@
         <v>-8.1</v>
       </c>
       <c r="H119" t="n">
-        <v>21.35</v>
+        <v>24.38</v>
       </c>
       <c r="I119" t="n">
         <v>14.27</v>
@@ -24489,7 +24547,7 @@
         <v>-10.92</v>
       </c>
       <c r="M119" t="n">
-        <v>18.39</v>
+        <v>20.54</v>
       </c>
       <c r="N119" t="b">
         <v>1</v>
@@ -24527,7 +24585,7 @@
         <v>-10.2</v>
       </c>
       <c r="H120" t="n">
-        <v>-16.64</v>
+        <v>-14.52</v>
       </c>
       <c r="I120" t="n">
         <v>15.03</v>
@@ -24542,7 +24600,7 @@
         <v>-1.61</v>
       </c>
       <c r="M120" t="n">
-        <v>-19.6</v>
+        <v>-18.36</v>
       </c>
       <c r="N120" t="b">
         <v>1</v>
@@ -24580,7 +24638,7 @@
         <v>68.90000000000001</v>
       </c>
       <c r="H121" t="n">
-        <v>26.06</v>
+        <v>26.5</v>
       </c>
       <c r="I121" t="n">
         <v>1.84</v>
@@ -24595,7 +24653,7 @@
         <v>-10.43</v>
       </c>
       <c r="M121" t="n">
-        <v>23.1</v>
+        <v>22.65</v>
       </c>
       <c r="N121" t="b">
         <v>1</v>
@@ -24633,7 +24691,7 @@
         <v>-40.8</v>
       </c>
       <c r="H122" t="n">
-        <v>-27.82</v>
+        <v>-27.63</v>
       </c>
       <c r="I122" t="n">
         <v>21.71</v>
@@ -24648,7 +24706,7 @@
         <v>-3.3</v>
       </c>
       <c r="M122" t="n">
-        <v>-30.78</v>
+        <v>-31.48</v>
       </c>
       <c r="N122" t="b">
         <v>1</v>
@@ -24686,7 +24744,7 @@
         <v>40.7</v>
       </c>
       <c r="H123" t="n">
-        <v>27.18</v>
+        <v>31.82</v>
       </c>
       <c r="I123" t="n">
         <v>-4.08</v>
@@ -24701,7 +24759,7 @@
         <v>-11.2</v>
       </c>
       <c r="M123" t="n">
-        <v>24.22</v>
+        <v>27.98</v>
       </c>
       <c r="N123" t="b">
         <v>1</v>
@@ -24739,7 +24797,7 @@
         <v>25.7</v>
       </c>
       <c r="H124" t="n">
-        <v>-14.04</v>
+        <v>-9.539999999999999</v>
       </c>
       <c r="I124" t="n">
         <v>11.3</v>
@@ -24754,7 +24812,7 @@
         <v>-11.03</v>
       </c>
       <c r="M124" t="n">
-        <v>-17</v>
+        <v>-13.39</v>
       </c>
       <c r="N124" t="b">
         <v>1</v>

--- a/STS_holy_grail_v2.xlsx
+++ b/STS_holy_grail_v2.xlsx
@@ -464,7 +464,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6</v>
+        <v>-0.24</v>
       </c>
     </row>
     <row r="5">
@@ -474,7 +474,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-2.11</v>
+        <v>-1.75</v>
       </c>
     </row>
     <row r="6">
@@ -484,7 +484,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>48</v>
+        <v>46.8</v>
       </c>
     </row>
     <row r="8">
@@ -531,13 +531,13 @@
         <v>64</v>
       </c>
       <c r="C10" t="n">
-        <v>1.17</v>
+        <v>-0.59</v>
       </c>
       <c r="D10" t="n">
-        <v>62.5</v>
+        <v>54.69</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.26</v>
+        <v>-1.82</v>
       </c>
     </row>
     <row r="11">
@@ -550,13 +550,13 @@
         <v>79</v>
       </c>
       <c r="C11" t="n">
-        <v>-3.73</v>
+        <v>-7.6</v>
       </c>
       <c r="D11" t="n">
-        <v>30.38</v>
+        <v>29.11</v>
       </c>
       <c r="E11" t="n">
-        <v>-7.23</v>
+        <v>-9.880000000000001</v>
       </c>
     </row>
     <row r="12">
@@ -569,13 +569,13 @@
         <v>156</v>
       </c>
       <c r="C12" t="n">
-        <v>0.72</v>
+        <v>1.76</v>
       </c>
       <c r="D12" t="n">
-        <v>46.15</v>
+        <v>48.08</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.95</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="13">
@@ -588,13 +588,13 @@
         <v>34</v>
       </c>
       <c r="C13" t="n">
-        <v>9.06</v>
+        <v>8.32</v>
       </c>
       <c r="D13" t="n">
-        <v>70.59</v>
+        <v>67.65000000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>7.41</v>
+        <v>7.88</v>
       </c>
     </row>
     <row r="15">
@@ -641,13 +641,13 @@
         <v>111</v>
       </c>
       <c r="C17" t="n">
-        <v>1.26</v>
+        <v>2.5</v>
       </c>
       <c r="D17" t="n">
-        <v>45.05</v>
+        <v>48.65</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.48</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="18">
@@ -660,13 +660,13 @@
         <v>48</v>
       </c>
       <c r="C18" t="n">
-        <v>-0.39</v>
+        <v>0.34</v>
       </c>
       <c r="D18" t="n">
-        <v>50</v>
+        <v>47.92</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.69</v>
+        <v>-0.74</v>
       </c>
     </row>
     <row r="19">
@@ -679,13 +679,13 @@
         <v>45</v>
       </c>
       <c r="C19" t="n">
-        <v>0.85</v>
+        <v>2.36</v>
       </c>
       <c r="D19" t="n">
         <v>51.11</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.92</v>
+        <v>0.8100000000000001</v>
       </c>
     </row>
     <row r="20">
@@ -698,13 +698,13 @@
         <v>40</v>
       </c>
       <c r="C20" t="n">
-        <v>-6.64</v>
+        <v>-9.4</v>
       </c>
       <c r="D20" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="E20" t="n">
-        <v>-9.35</v>
+        <v>-10.9</v>
       </c>
     </row>
     <row r="21">
@@ -717,13 +717,13 @@
         <v>89</v>
       </c>
       <c r="C21" t="n">
-        <v>3.45</v>
+        <v>-1.19</v>
       </c>
       <c r="D21" t="n">
-        <v>55.06</v>
+        <v>49.44</v>
       </c>
       <c r="E21" t="n">
-        <v>0.5600000000000001</v>
+        <v>-2.86</v>
       </c>
     </row>
     <row r="23">
@@ -770,13 +770,13 @@
         <v>10</v>
       </c>
       <c r="C25" t="n">
-        <v>13.13</v>
+        <v>13.87</v>
       </c>
       <c r="D25" t="n">
         <v>80</v>
       </c>
       <c r="E25" t="n">
-        <v>9.789999999999999</v>
+        <v>11.76</v>
       </c>
     </row>
     <row r="26">
@@ -789,13 +789,13 @@
         <v>5</v>
       </c>
       <c r="C26" t="n">
-        <v>-6.49</v>
+        <v>-3.36</v>
       </c>
       <c r="D26" t="n">
         <v>40</v>
       </c>
       <c r="E26" t="n">
-        <v>-10.54</v>
+        <v>-6.18</v>
       </c>
     </row>
     <row r="27">
@@ -808,13 +808,13 @@
         <v>3</v>
       </c>
       <c r="C27" t="n">
-        <v>18.56</v>
+        <v>22.87</v>
       </c>
       <c r="D27" t="n">
         <v>66.67</v>
       </c>
       <c r="E27" t="n">
-        <v>15.54</v>
+        <v>21.08</v>
       </c>
     </row>
     <row r="29">
@@ -861,13 +861,13 @@
         <v>210</v>
       </c>
       <c r="C31" t="n">
-        <v>1.22</v>
+        <v>0.48</v>
       </c>
       <c r="D31" t="n">
-        <v>46.67</v>
+        <v>45.71</v>
       </c>
       <c r="E31" t="n">
-        <v>-1.57</v>
+        <v>-1.1</v>
       </c>
     </row>
     <row r="32">
@@ -880,13 +880,13 @@
         <v>123</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.45</v>
+        <v>-1.48</v>
       </c>
       <c r="D32" t="n">
-        <v>50.41</v>
+        <v>48.78</v>
       </c>
       <c r="E32" t="n">
-        <v>-3.04</v>
+        <v>-2.85</v>
       </c>
     </row>
   </sheetData>
@@ -999,7 +999,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Extended</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
@@ -1010,7 +1010,7 @@
         <v>-9.4</v>
       </c>
       <c r="H2" t="n">
-        <v>1.45</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
@@ -1019,7 +1019,7 @@
         <v>-1.66</v>
       </c>
       <c r="M2" t="n">
-        <v>1.68</v>
+        <v>10.3</v>
       </c>
       <c r="N2" t="b">
         <v>0</v>
@@ -1057,7 +1057,7 @@
         <v>51.4</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.34</v>
+        <v>-2.51</v>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
@@ -1066,7 +1066,7 @@
         <v>-7.85</v>
       </c>
       <c r="M3" t="n">
-        <v>0.21</v>
+        <v>-0.79</v>
       </c>
       <c r="N3" t="b">
         <v>1</v>
@@ -1104,16 +1104,18 @@
         <v>-24.3</v>
       </c>
       <c r="H4" t="n">
-        <v>-3.12</v>
-      </c>
-      <c r="I4" t="inlineStr"/>
+        <v>-1.01</v>
+      </c>
+      <c r="I4" t="n">
+        <v>-1.01</v>
+      </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="n">
         <v>-6.24</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.89</v>
+        <v>0.4</v>
       </c>
       <c r="N4" t="b">
         <v>0</v>
@@ -1151,16 +1153,18 @@
         <v>-22.1</v>
       </c>
       <c r="H5" t="n">
-        <v>-7.16</v>
-      </c>
-      <c r="I5" t="inlineStr"/>
+        <v>-12.2</v>
+      </c>
+      <c r="I5" t="n">
+        <v>-12.2</v>
+      </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="n">
-        <v>-9.27</v>
+        <v>-12.92</v>
       </c>
       <c r="M5" t="n">
-        <v>-6.93</v>
+        <v>-10.8</v>
       </c>
       <c r="N5" t="b">
         <v>0</v>
@@ -1198,7 +1202,7 @@
         <v>-16.6</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.75</v>
+        <v>0.46</v>
       </c>
       <c r="I6" t="n">
         <v>-0.75</v>
@@ -1206,10 +1210,10 @@
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="n">
-        <v>-1.39</v>
+        <v>-2.5</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.41</v>
+        <v>1.99</v>
       </c>
       <c r="N6" t="b">
         <v>1</v>
@@ -1247,7 +1251,7 @@
         <v>-7.4</v>
       </c>
       <c r="H7" t="n">
-        <v>-2.38</v>
+        <v>-2.05</v>
       </c>
       <c r="I7" t="n">
         <v>-2.38</v>
@@ -1255,10 +1259,10 @@
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="n">
-        <v>-3.12</v>
+        <v>-3.32</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.03</v>
+        <v>-0.53</v>
       </c>
       <c r="N7" t="b">
         <v>0</v>
@@ -1296,7 +1300,7 @@
         <v>-5</v>
       </c>
       <c r="H8" t="n">
-        <v>12.26</v>
+        <v>16.42</v>
       </c>
       <c r="I8" t="n">
         <v>12.26</v>
@@ -1307,7 +1311,7 @@
         <v>-1.75</v>
       </c>
       <c r="M8" t="n">
-        <v>12.61</v>
+        <v>17.94</v>
       </c>
       <c r="N8" t="b">
         <v>1</v>
@@ -1345,7 +1349,7 @@
         <v>12.5</v>
       </c>
       <c r="H9" t="n">
-        <v>7.44</v>
+        <v>7.47</v>
       </c>
       <c r="I9" t="n">
         <v>7.44</v>
@@ -1356,7 +1360,7 @@
         <v>-2.59</v>
       </c>
       <c r="M9" t="n">
-        <v>7.79</v>
+        <v>9</v>
       </c>
       <c r="N9" t="b">
         <v>1</v>
@@ -1394,7 +1398,7 @@
         <v>-1.1</v>
       </c>
       <c r="H10" t="n">
-        <v>10.88</v>
+        <v>17.1</v>
       </c>
       <c r="I10" t="n">
         <v>10.88</v>
@@ -1405,7 +1409,7 @@
         <v>-0.36</v>
       </c>
       <c r="M10" t="n">
-        <v>11.23</v>
+        <v>18.62</v>
       </c>
       <c r="N10" t="b">
         <v>0</v>
@@ -1432,7 +1436,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Extended</t>
         </is>
       </c>
       <c r="E11" t="inlineStr"/>
@@ -1443,7 +1447,7 @@
         <v>-17.3</v>
       </c>
       <c r="H11" t="n">
-        <v>0.29</v>
+        <v>5.74</v>
       </c>
       <c r="I11" t="n">
         <v>1.16</v>
@@ -1454,7 +1458,7 @@
         <v>-6.51</v>
       </c>
       <c r="M11" t="n">
-        <v>0.9399999999999999</v>
+        <v>7.57</v>
       </c>
       <c r="N11" t="b">
         <v>1</v>
@@ -1492,7 +1496,7 @@
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>7.66</v>
+        <v>8.85</v>
       </c>
       <c r="I12" t="n">
         <v>9.16</v>
@@ -1503,7 +1507,7 @@
         <v>-1.46</v>
       </c>
       <c r="M12" t="n">
-        <v>8.31</v>
+        <v>10.67</v>
       </c>
       <c r="N12" t="b">
         <v>0</v>
@@ -1541,7 +1545,7 @@
         <v>-29.3</v>
       </c>
       <c r="H13" t="n">
-        <v>10.97</v>
+        <v>13.31</v>
       </c>
       <c r="I13" t="n">
         <v>10.02</v>
@@ -1552,7 +1556,7 @@
         <v>-3.13</v>
       </c>
       <c r="M13" t="n">
-        <v>10.53</v>
+        <v>14.05</v>
       </c>
       <c r="N13" t="b">
         <v>0</v>
@@ -1590,7 +1594,7 @@
         <v>-21.8</v>
       </c>
       <c r="H14" t="n">
-        <v>0.25</v>
+        <v>3.29</v>
       </c>
       <c r="I14" t="n">
         <v>-3.37</v>
@@ -1601,7 +1605,7 @@
         <v>-5.33</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.62</v>
+        <v>3.61</v>
       </c>
       <c r="N14" t="b">
         <v>1</v>
@@ -1639,7 +1643,7 @@
         <v>-15</v>
       </c>
       <c r="H15" t="n">
-        <v>13.77</v>
+        <v>17.41</v>
       </c>
       <c r="I15" t="n">
         <v>12.31</v>
@@ -1650,7 +1654,7 @@
         <v>-4.06</v>
       </c>
       <c r="M15" t="n">
-        <v>12.96</v>
+        <v>17.78</v>
       </c>
       <c r="N15" t="b">
         <v>0</v>
@@ -1688,7 +1692,7 @@
         <v>-16.7</v>
       </c>
       <c r="H16" t="n">
-        <v>27.16</v>
+        <v>27.08</v>
       </c>
       <c r="I16" t="n">
         <v>26.03</v>
@@ -1699,7 +1703,7 @@
         <v>-6.98</v>
       </c>
       <c r="M16" t="n">
-        <v>26.34</v>
+        <v>27.46</v>
       </c>
       <c r="N16" t="b">
         <v>1</v>
@@ -1737,7 +1741,7 @@
         <v>-26.8</v>
       </c>
       <c r="H17" t="n">
-        <v>3.18</v>
+        <v>2.85</v>
       </c>
       <c r="I17" t="n">
         <v>1.39</v>
@@ -1748,7 +1752,7 @@
         <v>-5.1</v>
       </c>
       <c r="M17" t="n">
-        <v>2.36</v>
+        <v>3.22</v>
       </c>
       <c r="N17" t="b">
         <v>0</v>
@@ -1786,7 +1790,7 @@
         <v>-35.9</v>
       </c>
       <c r="H18" t="n">
-        <v>-2.77</v>
+        <v>-3.56</v>
       </c>
       <c r="I18" t="n">
         <v>-6.92</v>
@@ -1797,7 +1801,7 @@
         <v>-7.58</v>
       </c>
       <c r="M18" t="n">
-        <v>-3.58</v>
+        <v>-3.18</v>
       </c>
       <c r="N18" t="b">
         <v>0</v>
@@ -1835,7 +1839,7 @@
         <v>-7.1</v>
       </c>
       <c r="H19" t="n">
-        <v>8.16</v>
+        <v>6.41</v>
       </c>
       <c r="I19" t="n">
         <v>9.390000000000001</v>
@@ -1846,7 +1850,7 @@
         <v>-2.71</v>
       </c>
       <c r="M19" t="n">
-        <v>7.34</v>
+        <v>6.79</v>
       </c>
       <c r="N19" t="b">
         <v>0</v>
@@ -1884,7 +1888,7 @@
         <v>-11.5</v>
       </c>
       <c r="H20" t="n">
-        <v>18.34</v>
+        <v>24.98</v>
       </c>
       <c r="I20" t="n">
         <v>7.47</v>
@@ -1895,7 +1899,7 @@
         <v>-0.99</v>
       </c>
       <c r="M20" t="n">
-        <v>17.52</v>
+        <v>25.36</v>
       </c>
       <c r="N20" t="b">
         <v>1</v>
@@ -1922,7 +1926,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Extended</t>
+          <t>Retired</t>
         </is>
       </c>
       <c r="E21" t="inlineStr"/>
@@ -1933,7 +1937,7 @@
         <v>0.1</v>
       </c>
       <c r="H21" t="n">
-        <v>18.54</v>
+        <v>22.82</v>
       </c>
       <c r="I21" t="n">
         <v>6.41</v>
@@ -1944,7 +1948,7 @@
         <v>-2.51</v>
       </c>
       <c r="M21" t="n">
-        <v>17.98</v>
+        <v>23.45</v>
       </c>
       <c r="N21" t="b">
         <v>1</v>
@@ -1971,7 +1975,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Retired</t>
         </is>
       </c>
       <c r="E22" t="inlineStr"/>
@@ -1982,7 +1986,7 @@
         <v>-31.6</v>
       </c>
       <c r="H22" t="n">
-        <v>-2.84</v>
+        <v>-2.06</v>
       </c>
       <c r="I22" t="n">
         <v>-2.12</v>
@@ -1993,7 +1997,7 @@
         <v>-8.140000000000001</v>
       </c>
       <c r="M22" t="n">
-        <v>-3.4</v>
+        <v>-1.43</v>
       </c>
       <c r="N22" t="b">
         <v>1</v>
@@ -2031,18 +2035,20 @@
         <v>7.6</v>
       </c>
       <c r="H23" t="n">
-        <v>5.95</v>
+        <v>10.1</v>
       </c>
       <c r="I23" t="n">
         <v>-3.6</v>
       </c>
-      <c r="J23" t="inlineStr"/>
+      <c r="J23" t="n">
+        <v>10.1</v>
+      </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="n">
         <v>-9.359999999999999</v>
       </c>
       <c r="M23" t="n">
-        <v>4.77</v>
+        <v>10.11</v>
       </c>
       <c r="N23" t="b">
         <v>0</v>
@@ -2080,7 +2086,7 @@
         <v>-17.9</v>
       </c>
       <c r="H24" t="n">
-        <v>-10.02</v>
+        <v>-5.36</v>
       </c>
       <c r="I24" t="n">
         <v>-6.13</v>
@@ -2093,7 +2099,7 @@
         <v>-14.51</v>
       </c>
       <c r="M24" t="n">
-        <v>-9.9</v>
+        <v>-4.06</v>
       </c>
       <c r="N24" t="b">
         <v>0</v>
@@ -2131,7 +2137,7 @@
         <v>-2.7</v>
       </c>
       <c r="H25" t="n">
-        <v>-9.199999999999999</v>
+        <v>-5.75</v>
       </c>
       <c r="I25" t="n">
         <v>-3.77</v>
@@ -2144,7 +2150,7 @@
         <v>-12.44</v>
       </c>
       <c r="M25" t="n">
-        <v>-9.08</v>
+        <v>-4.45</v>
       </c>
       <c r="N25" t="b">
         <v>1</v>
@@ -2182,7 +2188,7 @@
         <v>-25.3</v>
       </c>
       <c r="H26" t="n">
-        <v>8.779999999999999</v>
+        <v>13.72</v>
       </c>
       <c r="I26" t="n">
         <v>4.1</v>
@@ -2195,7 +2201,7 @@
         <v>-0.92</v>
       </c>
       <c r="M26" t="n">
-        <v>8.9</v>
+        <v>15.03</v>
       </c>
       <c r="N26" t="b">
         <v>0</v>
@@ -2233,7 +2239,7 @@
         <v>25.6</v>
       </c>
       <c r="H27" t="n">
-        <v>8.26</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="I27" t="n">
         <v>-0.42</v>
@@ -2246,7 +2252,7 @@
         <v>-8.35</v>
       </c>
       <c r="M27" t="n">
-        <v>8.380000000000001</v>
+        <v>11.1</v>
       </c>
       <c r="N27" t="b">
         <v>0</v>
@@ -2284,7 +2290,7 @@
         <v>26.9</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.39</v>
+        <v>-1.11</v>
       </c>
       <c r="I28" t="n">
         <v>-3.24</v>
@@ -2297,7 +2303,7 @@
         <v>-12.88</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.27</v>
+        <v>0.19</v>
       </c>
       <c r="N28" t="b">
         <v>1</v>
@@ -2335,7 +2341,7 @@
         <v>-14.5</v>
       </c>
       <c r="H29" t="n">
-        <v>-9.300000000000001</v>
+        <v>-11.55</v>
       </c>
       <c r="I29" t="n">
         <v>-3.75</v>
@@ -2348,7 +2354,7 @@
         <v>-9.01</v>
       </c>
       <c r="M29" t="n">
-        <v>-10.2</v>
+        <v>-11.25</v>
       </c>
       <c r="N29" t="b">
         <v>0</v>
@@ -2386,7 +2392,7 @@
         <v>17.2</v>
       </c>
       <c r="H30" t="n">
-        <v>4.28</v>
+        <v>5.52</v>
       </c>
       <c r="I30" t="n">
         <v>-1.49</v>
@@ -2399,7 +2405,7 @@
         <v>-10.54</v>
       </c>
       <c r="M30" t="n">
-        <v>3.39</v>
+        <v>5.82</v>
       </c>
       <c r="N30" t="b">
         <v>0</v>
@@ -2437,7 +2443,7 @@
         <v>-13.2</v>
       </c>
       <c r="H31" t="n">
-        <v>14.12</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="I31" t="n">
         <v>23.71</v>
@@ -2450,7 +2456,7 @@
         <v>-0.82</v>
       </c>
       <c r="M31" t="n">
-        <v>13.23</v>
+        <v>8.67</v>
       </c>
       <c r="N31" t="b">
         <v>0</v>
@@ -2488,7 +2494,7 @@
         <v>-7.7</v>
       </c>
       <c r="H32" t="n">
-        <v>-5.21</v>
+        <v>-5.07</v>
       </c>
       <c r="I32" t="n">
         <v>-9.67</v>
@@ -2501,7 +2507,7 @@
         <v>-12.32</v>
       </c>
       <c r="M32" t="n">
-        <v>-6.11</v>
+        <v>-4.77</v>
       </c>
       <c r="N32" t="b">
         <v>0</v>
@@ -2539,7 +2545,7 @@
         <v>-18.1</v>
       </c>
       <c r="H33" t="n">
-        <v>-1.4</v>
+        <v>-0.84</v>
       </c>
       <c r="I33" t="n">
         <v>-2.43</v>
@@ -2552,7 +2558,7 @@
         <v>-6.41</v>
       </c>
       <c r="M33" t="n">
-        <v>-2.3</v>
+        <v>-0.54</v>
       </c>
       <c r="N33" t="b">
         <v>0</v>
@@ -2590,7 +2596,7 @@
         <v>-18.1</v>
       </c>
       <c r="H34" t="n">
-        <v>17.63</v>
+        <v>20.75</v>
       </c>
       <c r="I34" t="n">
         <v>4.46</v>
@@ -2603,7 +2609,7 @@
         <v>-2.69</v>
       </c>
       <c r="M34" t="n">
-        <v>16.74</v>
+        <v>21.05</v>
       </c>
       <c r="N34" t="b">
         <v>1</v>
@@ -2641,7 +2647,7 @@
         <v>7.7</v>
       </c>
       <c r="H35" t="n">
-        <v>2.27</v>
+        <v>6.87</v>
       </c>
       <c r="I35" t="n">
         <v>-6.85</v>
@@ -2654,7 +2660,7 @@
         <v>-9.359999999999999</v>
       </c>
       <c r="M35" t="n">
-        <v>1.38</v>
+        <v>7.17</v>
       </c>
       <c r="N35" t="b">
         <v>0</v>
@@ -2692,7 +2698,7 @@
         <v>-21.5</v>
       </c>
       <c r="H36" t="n">
-        <v>-2.87</v>
+        <v>3.39</v>
       </c>
       <c r="I36" t="n">
         <v>-1.68</v>
@@ -2705,7 +2711,7 @@
         <v>-8.130000000000001</v>
       </c>
       <c r="M36" t="n">
-        <v>-3.76</v>
+        <v>3.69</v>
       </c>
       <c r="N36" t="b">
         <v>1</v>
@@ -2743,7 +2749,7 @@
         <v>41.6</v>
       </c>
       <c r="H37" t="n">
-        <v>6.9</v>
+        <v>7.41</v>
       </c>
       <c r="I37" t="n">
         <v>3.43</v>
@@ -2756,7 +2762,7 @@
         <v>-4.38</v>
       </c>
       <c r="M37" t="n">
-        <v>5.35</v>
+        <v>7.06</v>
       </c>
       <c r="N37" t="b">
         <v>1</v>
@@ -2794,7 +2800,7 @@
         <v>32.1</v>
       </c>
       <c r="H38" t="n">
-        <v>11.51</v>
+        <v>14.51</v>
       </c>
       <c r="I38" t="n">
         <v>-3.47</v>
@@ -2807,7 +2813,7 @@
         <v>-6.94</v>
       </c>
       <c r="M38" t="n">
-        <v>9.970000000000001</v>
+        <v>14.16</v>
       </c>
       <c r="N38" t="b">
         <v>1</v>
@@ -2845,7 +2851,7 @@
         <v>-14.4</v>
       </c>
       <c r="H39" t="n">
-        <v>3.67</v>
+        <v>10.86</v>
       </c>
       <c r="I39" t="n">
         <v>-2.38</v>
@@ -2858,7 +2864,7 @@
         <v>-6.46</v>
       </c>
       <c r="M39" t="n">
-        <v>2.12</v>
+        <v>10.51</v>
       </c>
       <c r="N39" t="b">
         <v>1</v>
@@ -2896,7 +2902,7 @@
         <v>-16.8</v>
       </c>
       <c r="H40" t="n">
-        <v>-0.06</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="I40" t="n">
         <v>1.99</v>
@@ -2909,7 +2915,7 @@
         <v>-7.67</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.6</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="N40" t="b">
         <v>0</v>
@@ -2947,7 +2953,7 @@
         <v>-10</v>
       </c>
       <c r="H41" t="n">
-        <v>-10.24</v>
+        <v>-10.95</v>
       </c>
       <c r="I41" t="n">
         <v>-3.29</v>
@@ -2960,7 +2966,7 @@
         <v>-14.66</v>
       </c>
       <c r="M41" t="n">
-        <v>-11.78</v>
+        <v>-11.3</v>
       </c>
       <c r="N41" t="b">
         <v>1</v>
@@ -2998,7 +3004,7 @@
         <v>6.4</v>
       </c>
       <c r="H42" t="n">
-        <v>16.43</v>
+        <v>21.8</v>
       </c>
       <c r="I42" t="n">
         <v>1.48</v>
@@ -3011,7 +3017,7 @@
         <v>-3.35</v>
       </c>
       <c r="M42" t="n">
-        <v>14.89</v>
+        <v>21.45</v>
       </c>
       <c r="N42" t="b">
         <v>1</v>
@@ -3049,7 +3055,7 @@
         <v>-11</v>
       </c>
       <c r="H43" t="n">
-        <v>48.2</v>
+        <v>47.91</v>
       </c>
       <c r="I43" t="n">
         <v>11.67</v>
@@ -3062,7 +3068,7 @@
         <v>-0.97</v>
       </c>
       <c r="M43" t="n">
-        <v>46.65</v>
+        <v>47.56</v>
       </c>
       <c r="N43" t="b">
         <v>0</v>
@@ -3100,7 +3106,7 @@
         <v>-23.9</v>
       </c>
       <c r="H44" t="n">
-        <v>-3.63</v>
+        <v>-2.99</v>
       </c>
       <c r="I44" t="n">
         <v>-4.98</v>
@@ -3113,7 +3119,7 @@
         <v>-7.87</v>
       </c>
       <c r="M44" t="n">
-        <v>-5.18</v>
+        <v>-3.35</v>
       </c>
       <c r="N44" t="b">
         <v>0</v>
@@ -3155,7 +3161,7 @@
         <v>-9.800000000000001</v>
       </c>
       <c r="H45" t="n">
-        <v>11.92</v>
+        <v>16.54</v>
       </c>
       <c r="I45" t="n">
         <v>-3.41</v>
@@ -3168,7 +3174,7 @@
         <v>-8.949999999999999</v>
       </c>
       <c r="M45" t="n">
-        <v>10.37</v>
+        <v>16.19</v>
       </c>
       <c r="N45" t="b">
         <v>0</v>
@@ -3206,7 +3212,7 @@
         <v>-36.1</v>
       </c>
       <c r="H46" t="n">
-        <v>-0.71</v>
+        <v>7.04</v>
       </c>
       <c r="I46" t="n">
         <v>-1.4</v>
@@ -3219,7 +3225,7 @@
         <v>-7.04</v>
       </c>
       <c r="M46" t="n">
-        <v>-2.26</v>
+        <v>6.68</v>
       </c>
       <c r="N46" t="b">
         <v>0</v>
@@ -3257,7 +3263,7 @@
         <v>-7.9</v>
       </c>
       <c r="H47" t="n">
-        <v>-8.5</v>
+        <v>-0.55</v>
       </c>
       <c r="I47" t="n">
         <v>-8.83</v>
@@ -3270,7 +3276,7 @@
         <v>-12.99</v>
       </c>
       <c r="M47" t="n">
-        <v>-10.05</v>
+        <v>-0.9</v>
       </c>
       <c r="N47" t="b">
         <v>0</v>
@@ -3308,7 +3314,7 @@
         <v>2.6</v>
       </c>
       <c r="H48" t="n">
-        <v>11.64</v>
+        <v>18.33</v>
       </c>
       <c r="I48" t="n">
         <v>-7.8</v>
@@ -3321,7 +3327,7 @@
         <v>-12.2</v>
       </c>
       <c r="M48" t="n">
-        <v>9.6</v>
+        <v>17.49</v>
       </c>
       <c r="N48" t="b">
         <v>0</v>
@@ -3359,7 +3365,7 @@
         <v>6.3</v>
       </c>
       <c r="H49" t="n">
-        <v>7.5</v>
+        <v>11.72</v>
       </c>
       <c r="I49" t="n">
         <v>0.64</v>
@@ -3372,7 +3378,7 @@
         <v>-2.13</v>
       </c>
       <c r="M49" t="n">
-        <v>5.45</v>
+        <v>10.89</v>
       </c>
       <c r="N49" t="b">
         <v>0</v>
@@ -3410,7 +3416,7 @@
         <v>20.2</v>
       </c>
       <c r="H50" t="n">
-        <v>1.2</v>
+        <v>0.21</v>
       </c>
       <c r="I50" t="n">
         <v>3.45</v>
@@ -3423,7 +3429,7 @@
         <v>-1.07</v>
       </c>
       <c r="M50" t="n">
-        <v>-0.76</v>
+        <v>-0.54</v>
       </c>
       <c r="N50" t="b">
         <v>1</v>
@@ -3461,7 +3467,7 @@
         <v>43.7</v>
       </c>
       <c r="H51" t="n">
-        <v>15.43</v>
+        <v>15.17</v>
       </c>
       <c r="I51" t="n">
         <v>3.16</v>
@@ -3474,7 +3480,7 @@
         <v>-2.44</v>
       </c>
       <c r="M51" t="n">
-        <v>13.47</v>
+        <v>14.41</v>
       </c>
       <c r="N51" t="b">
         <v>1</v>
@@ -3512,7 +3518,7 @@
         <v>1.9</v>
       </c>
       <c r="H52" t="n">
-        <v>-3.81</v>
+        <v>0.72</v>
       </c>
       <c r="I52" t="n">
         <v>-10.64</v>
@@ -3525,7 +3531,7 @@
         <v>-14.75</v>
       </c>
       <c r="M52" t="n">
-        <v>-5.77</v>
+        <v>-0.04</v>
       </c>
       <c r="N52" t="b">
         <v>1</v>
@@ -3563,7 +3569,7 @@
         <v>37.5</v>
       </c>
       <c r="H53" t="n">
-        <v>23.93</v>
+        <v>22.06</v>
       </c>
       <c r="I53" t="n">
         <v>5.86</v>
@@ -3576,7 +3582,7 @@
         <v>-3.95</v>
       </c>
       <c r="M53" t="n">
-        <v>21.82</v>
+        <v>21.16</v>
       </c>
       <c r="N53" t="b">
         <v>1</v>
@@ -3614,7 +3620,7 @@
         <v>15</v>
       </c>
       <c r="H54" t="n">
-        <v>-29.09</v>
+        <v>-29.67</v>
       </c>
       <c r="I54" t="n">
         <v>-21.11</v>
@@ -3627,7 +3633,7 @@
         <v>-28.65</v>
       </c>
       <c r="M54" t="n">
-        <v>-31.2</v>
+        <v>-30.57</v>
       </c>
       <c r="N54" t="b">
         <v>0</v>
@@ -3665,7 +3671,7 @@
         <v>40.2</v>
       </c>
       <c r="H55" t="n">
-        <v>9.470000000000001</v>
+        <v>8.58</v>
       </c>
       <c r="I55" t="n">
         <v>-1.11</v>
@@ -3678,7 +3684,7 @@
         <v>-5.29</v>
       </c>
       <c r="M55" t="n">
-        <v>7.36</v>
+        <v>7.68</v>
       </c>
       <c r="N55" t="b">
         <v>1</v>
@@ -3716,7 +3722,7 @@
         <v>10.7</v>
       </c>
       <c r="H56" t="n">
-        <v>1.06</v>
+        <v>-5.98</v>
       </c>
       <c r="I56" t="n">
         <v>7.3</v>
@@ -3729,7 +3735,7 @@
         <v>-3.78</v>
       </c>
       <c r="M56" t="n">
-        <v>-1.05</v>
+        <v>-6.88</v>
       </c>
       <c r="N56" t="b">
         <v>1</v>
@@ -3767,7 +3773,7 @@
         <v>25.6</v>
       </c>
       <c r="H57" t="n">
-        <v>19.74</v>
+        <v>20.7</v>
       </c>
       <c r="I57" t="n">
         <v>7.71</v>
@@ -3780,7 +3786,7 @@
         <v>-4.85</v>
       </c>
       <c r="M57" t="n">
-        <v>18.39</v>
+        <v>20.55</v>
       </c>
       <c r="N57" t="b">
         <v>1</v>
@@ -3818,7 +3824,7 @@
         <v>6.3</v>
       </c>
       <c r="H58" t="n">
-        <v>0.89</v>
+        <v>2.96</v>
       </c>
       <c r="I58" t="n">
         <v>7.2</v>
@@ -3831,7 +3837,7 @@
         <v>-0.4</v>
       </c>
       <c r="M58" t="n">
-        <v>-1.35</v>
+        <v>1.92</v>
       </c>
       <c r="N58" t="b">
         <v>0</v>
@@ -3869,7 +3875,7 @@
         <v>2.3</v>
       </c>
       <c r="H59" t="n">
-        <v>-11.21</v>
+        <v>-6.13</v>
       </c>
       <c r="I59" t="n">
         <v>-8.85</v>
@@ -3882,7 +3888,7 @@
         <v>-14.2</v>
       </c>
       <c r="M59" t="n">
-        <v>-13.45</v>
+        <v>-7.16</v>
       </c>
       <c r="N59" t="b">
         <v>0</v>
@@ -3920,7 +3926,7 @@
         <v>-4.3</v>
       </c>
       <c r="H60" t="n">
-        <v>5.61</v>
+        <v>2.01</v>
       </c>
       <c r="I60" t="n">
         <v>3.39</v>
@@ -3933,7 +3939,7 @@
         <v>-5.89</v>
       </c>
       <c r="M60" t="n">
-        <v>4.18</v>
+        <v>1.78</v>
       </c>
       <c r="N60" t="b">
         <v>0</v>
@@ -3971,7 +3977,7 @@
         <v>-29.4</v>
       </c>
       <c r="H61" t="n">
-        <v>-14.6</v>
+        <v>-15.42</v>
       </c>
       <c r="I61" t="n">
         <v>-5.75</v>
@@ -3984,7 +3990,7 @@
         <v>-10.11</v>
       </c>
       <c r="M61" t="n">
-        <v>-16.03</v>
+        <v>-15.65</v>
       </c>
       <c r="N61" t="b">
         <v>0</v>
@@ -4022,7 +4028,7 @@
         <v>-6.9</v>
       </c>
       <c r="H62" t="n">
-        <v>18.01</v>
+        <v>18.96</v>
       </c>
       <c r="I62" t="n">
         <v>6.44</v>
@@ -4035,7 +4041,7 @@
         <v>-4.53</v>
       </c>
       <c r="M62" t="n">
-        <v>16.58</v>
+        <v>18.73</v>
       </c>
       <c r="N62" t="b">
         <v>1</v>
@@ -4073,7 +4079,7 @@
         <v>4.2</v>
       </c>
       <c r="H63" t="n">
-        <v>-18.08</v>
+        <v>-11.21</v>
       </c>
       <c r="I63" t="n">
         <v>-10.83</v>
@@ -4086,7 +4092,7 @@
         <v>-18.5</v>
       </c>
       <c r="M63" t="n">
-        <v>-19.51</v>
+        <v>-11.45</v>
       </c>
       <c r="N63" t="b">
         <v>0</v>
@@ -4124,7 +4130,7 @@
         <v>-32.4</v>
       </c>
       <c r="H64" t="n">
-        <v>3.42</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="I64" t="n">
         <v>-2.43</v>
@@ -4137,7 +4143,7 @@
         <v>-12.47</v>
       </c>
       <c r="M64" t="n">
-        <v>2.65</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="N64" t="b">
         <v>0</v>
@@ -4175,7 +4181,7 @@
         <v>-11</v>
       </c>
       <c r="H65" t="n">
-        <v>0.64</v>
+        <v>3.6</v>
       </c>
       <c r="I65" t="n">
         <v>-8.449999999999999</v>
@@ -4188,7 +4194,7 @@
         <v>-18.92</v>
       </c>
       <c r="M65" t="n">
-        <v>-0.13</v>
+        <v>4.01</v>
       </c>
       <c r="N65" t="b">
         <v>0</v>
@@ -4226,7 +4232,7 @@
         <v>9.699999999999999</v>
       </c>
       <c r="H66" t="n">
-        <v>3.17</v>
+        <v>-4.36</v>
       </c>
       <c r="I66" t="n">
         <v>1.27</v>
@@ -4239,7 +4245,7 @@
         <v>-20.79</v>
       </c>
       <c r="M66" t="n">
-        <v>2.24</v>
+        <v>-4.1</v>
       </c>
       <c r="N66" t="b">
         <v>0</v>
@@ -4277,7 +4283,7 @@
         <v>-28.1</v>
       </c>
       <c r="H67" t="n">
-        <v>-8.380000000000001</v>
+        <v>-5.29</v>
       </c>
       <c r="I67" t="n">
         <v>-10.79</v>
@@ -4290,7 +4296,7 @@
         <v>-13.67</v>
       </c>
       <c r="M67" t="n">
-        <v>-9.300000000000001</v>
+        <v>-5.02</v>
       </c>
       <c r="N67" t="b">
         <v>0</v>
@@ -4328,7 +4334,7 @@
         <v>-17.7</v>
       </c>
       <c r="H68" t="n">
-        <v>4.32</v>
+        <v>9.4</v>
       </c>
       <c r="I68" t="n">
         <v>-0.89</v>
@@ -4341,7 +4347,7 @@
         <v>-11.37</v>
       </c>
       <c r="M68" t="n">
-        <v>3.39</v>
+        <v>9.67</v>
       </c>
       <c r="N68" t="b">
         <v>0</v>
@@ -4379,7 +4385,7 @@
         <v>-9.300000000000001</v>
       </c>
       <c r="H69" t="n">
-        <v>-20.03</v>
+        <v>-15.64</v>
       </c>
       <c r="I69" t="n">
         <v>-3.34</v>
@@ -4392,7 +4398,7 @@
         <v>-8.77</v>
       </c>
       <c r="M69" t="n">
-        <v>-20.95</v>
+        <v>-15.38</v>
       </c>
       <c r="N69" t="b">
         <v>0</v>
@@ -4430,7 +4436,7 @@
         <v>0.3</v>
       </c>
       <c r="H70" t="n">
-        <v>-15.89</v>
+        <v>-14.76</v>
       </c>
       <c r="I70" t="n">
         <v>-10.53</v>
@@ -4443,7 +4449,7 @@
         <v>-17.73</v>
       </c>
       <c r="M70" t="n">
-        <v>-16.82</v>
+        <v>-14.49</v>
       </c>
       <c r="N70" t="b">
         <v>1</v>
@@ -4481,7 +4487,7 @@
         <v>12.3</v>
       </c>
       <c r="H71" t="n">
-        <v>2.61</v>
+        <v>4.77</v>
       </c>
       <c r="I71" t="n">
         <v>6.51</v>
@@ -4494,7 +4500,7 @@
         <v>-6.01</v>
       </c>
       <c r="M71" t="n">
-        <v>0.96</v>
+        <v>4.32</v>
       </c>
       <c r="N71" t="b">
         <v>0</v>
@@ -4532,7 +4538,7 @@
         <v>2.8</v>
       </c>
       <c r="H72" t="n">
-        <v>3.27</v>
+        <v>-0.59</v>
       </c>
       <c r="I72" t="n">
         <v>3.18</v>
@@ -4545,7 +4551,7 @@
         <v>-0.88</v>
       </c>
       <c r="M72" t="n">
-        <v>1.63</v>
+        <v>-1.03</v>
       </c>
       <c r="N72" t="b">
         <v>1</v>
@@ -4583,7 +4589,7 @@
         <v>-1.4</v>
       </c>
       <c r="H73" t="n">
-        <v>4.92</v>
+        <v>-4.51</v>
       </c>
       <c r="I73" t="n">
         <v>-4.52</v>
@@ -4596,7 +4602,7 @@
         <v>-7.44</v>
       </c>
       <c r="M73" t="n">
-        <v>3.28</v>
+        <v>-4.96</v>
       </c>
       <c r="N73" t="b">
         <v>0</v>
@@ -4634,7 +4640,7 @@
         <v>34.5</v>
       </c>
       <c r="H74" t="n">
-        <v>13.16</v>
+        <v>11.18</v>
       </c>
       <c r="I74" t="n">
         <v>0.66</v>
@@ -4647,7 +4653,7 @@
         <v>-2.64</v>
       </c>
       <c r="M74" t="n">
-        <v>11.51</v>
+        <v>10.73</v>
       </c>
       <c r="N74" t="b">
         <v>1</v>
@@ -4685,7 +4691,7 @@
         <v>-22.7</v>
       </c>
       <c r="H75" t="n">
-        <v>-16.96</v>
+        <v>-17.85</v>
       </c>
       <c r="I75" t="n">
         <v>-6.71</v>
@@ -4698,7 +4704,7 @@
         <v>-9.58</v>
       </c>
       <c r="M75" t="n">
-        <v>-18.67</v>
+        <v>-18.35</v>
       </c>
       <c r="N75" t="b">
         <v>0</v>
@@ -4736,7 +4742,7 @@
         <v>24.3</v>
       </c>
       <c r="H76" t="n">
-        <v>38.45</v>
+        <v>28.16</v>
       </c>
       <c r="I76" t="n">
         <v>2.54</v>
@@ -4749,7 +4755,7 @@
         <v>-5.21</v>
       </c>
       <c r="M76" t="n">
-        <v>37.45</v>
+        <v>28.35</v>
       </c>
       <c r="N76" t="b">
         <v>1</v>
@@ -4787,7 +4793,7 @@
         <v>56.6</v>
       </c>
       <c r="H77" t="n">
-        <v>0.83</v>
+        <v>0.21</v>
       </c>
       <c r="I77" t="n">
         <v>-13.1</v>
@@ -4800,7 +4806,7 @@
         <v>-16.17</v>
       </c>
       <c r="M77" t="n">
-        <v>-0.17</v>
+        <v>0.41</v>
       </c>
       <c r="N77" t="b">
         <v>0</v>
@@ -4838,7 +4844,7 @@
         <v>2.9</v>
       </c>
       <c r="H78" t="n">
-        <v>-17.74</v>
+        <v>-14.79</v>
       </c>
       <c r="I78" t="n">
         <v>-8.470000000000001</v>
@@ -4851,7 +4857,7 @@
         <v>-15.65</v>
       </c>
       <c r="M78" t="n">
-        <v>-18.74</v>
+        <v>-14.6</v>
       </c>
       <c r="N78" t="b">
         <v>0</v>
@@ -4889,7 +4895,7 @@
         <v>-16.9</v>
       </c>
       <c r="H79" t="n">
-        <v>1.33</v>
+        <v>5.69</v>
       </c>
       <c r="I79" t="n">
         <v>-6.47</v>
@@ -4902,7 +4908,7 @@
         <v>-11.5</v>
       </c>
       <c r="M79" t="n">
-        <v>0.33</v>
+        <v>5.88</v>
       </c>
       <c r="N79" t="b">
         <v>1</v>
@@ -4940,7 +4946,7 @@
         <v>32.8</v>
       </c>
       <c r="H80" t="n">
-        <v>5.84</v>
+        <v>14.08</v>
       </c>
       <c r="I80" t="n">
         <v>14.96</v>
@@ -4953,7 +4959,7 @@
         <v>-0.9</v>
       </c>
       <c r="M80" t="n">
-        <v>5.42</v>
+        <v>14.85</v>
       </c>
       <c r="N80" t="b">
         <v>0</v>
@@ -4991,7 +4997,7 @@
         <v>0.8</v>
       </c>
       <c r="H81" t="n">
-        <v>-9.42</v>
+        <v>-13.32</v>
       </c>
       <c r="I81" t="n">
         <v>-7.73</v>
@@ -5004,7 +5010,7 @@
         <v>-10.12</v>
       </c>
       <c r="M81" t="n">
-        <v>-9.84</v>
+        <v>-12.56</v>
       </c>
       <c r="N81" t="b">
         <v>0</v>
@@ -5042,7 +5048,7 @@
         <v>-9.6</v>
       </c>
       <c r="H82" t="n">
-        <v>-16.6</v>
+        <v>-18.3</v>
       </c>
       <c r="I82" t="n">
         <v>-1.23</v>
@@ -5055,7 +5061,7 @@
         <v>-18.52</v>
       </c>
       <c r="M82" t="n">
-        <v>-17.02</v>
+        <v>-17.54</v>
       </c>
       <c r="N82" t="b">
         <v>0</v>
@@ -5093,7 +5099,7 @@
         <v>20.3</v>
       </c>
       <c r="H83" t="n">
-        <v>-26.39</v>
+        <v>-20.39</v>
       </c>
       <c r="I83" t="n">
         <v>-2.07</v>
@@ -5106,7 +5112,7 @@
         <v>-17.35</v>
       </c>
       <c r="M83" t="n">
-        <v>-27.23</v>
+        <v>-20.04</v>
       </c>
       <c r="N83" t="b">
         <v>1</v>
@@ -5144,7 +5150,7 @@
         <v>0.3</v>
       </c>
       <c r="H84" t="n">
-        <v>-21.9</v>
+        <v>-19.2</v>
       </c>
       <c r="I84" t="n">
         <v>-9.9</v>
@@ -5157,7 +5163,7 @@
         <v>-21.72</v>
       </c>
       <c r="M84" t="n">
-        <v>-23.24</v>
+        <v>-19.35</v>
       </c>
       <c r="N84" t="b">
         <v>1</v>
@@ -5195,7 +5201,7 @@
         <v>49.4</v>
       </c>
       <c r="H85" t="n">
-        <v>0.18</v>
+        <v>-2.54</v>
       </c>
       <c r="I85" t="n">
         <v>2.9</v>
@@ -5208,7 +5214,7 @@
         <v>-5.67</v>
       </c>
       <c r="M85" t="n">
-        <v>-0.97</v>
+        <v>-2.5</v>
       </c>
       <c r="N85" t="b">
         <v>1</v>
@@ -5246,7 +5252,7 @@
         <v>4.5</v>
       </c>
       <c r="H86" t="n">
-        <v>-2.01</v>
+        <v>2.29</v>
       </c>
       <c r="I86" t="n">
         <v>-7.61</v>
@@ -5259,7 +5265,7 @@
         <v>-11.06</v>
       </c>
       <c r="M86" t="n">
-        <v>-3.16</v>
+        <v>2.33</v>
       </c>
       <c r="N86" t="b">
         <v>1</v>
@@ -5297,7 +5303,7 @@
         <v>4.2</v>
       </c>
       <c r="H87" t="n">
-        <v>-18.35</v>
+        <v>-17.58</v>
       </c>
       <c r="I87" t="n">
         <v>-6.86</v>
@@ -5310,7 +5316,7 @@
         <v>-20.23</v>
       </c>
       <c r="M87" t="n">
-        <v>-19.51</v>
+        <v>-17.54</v>
       </c>
       <c r="N87" t="b">
         <v>0</v>
@@ -5348,7 +5354,7 @@
         <v>15.4</v>
       </c>
       <c r="H88" t="n">
-        <v>5.47</v>
+        <v>7.49</v>
       </c>
       <c r="I88" t="n">
         <v>-1.19</v>
@@ -5361,7 +5367,7 @@
         <v>-7.43</v>
       </c>
       <c r="M88" t="n">
-        <v>4.32</v>
+        <v>7.53</v>
       </c>
       <c r="N88" t="b">
         <v>0</v>
@@ -5399,7 +5405,7 @@
         <v>15.5</v>
       </c>
       <c r="H89" t="n">
-        <v>-0.97</v>
+        <v>3.45</v>
       </c>
       <c r="I89" t="n">
         <v>-7.36</v>
@@ -5412,7 +5418,7 @@
         <v>-12.98</v>
       </c>
       <c r="M89" t="n">
-        <v>-2.31</v>
+        <v>3.31</v>
       </c>
       <c r="N89" t="b">
         <v>0</v>
@@ -5454,7 +5460,7 @@
         <v>-8.5</v>
       </c>
       <c r="H90" t="n">
-        <v>31.17</v>
+        <v>41.26</v>
       </c>
       <c r="I90" t="n">
         <v>-3.04</v>
@@ -5467,7 +5473,7 @@
         <v>-4.96</v>
       </c>
       <c r="M90" t="n">
-        <v>29.83</v>
+        <v>41.12</v>
       </c>
       <c r="N90" t="b">
         <v>0</v>
@@ -5505,7 +5511,7 @@
         <v>1.8</v>
       </c>
       <c r="H91" t="n">
-        <v>-7.25</v>
+        <v>-1.62</v>
       </c>
       <c r="I91" t="n">
         <v>-6.45</v>
@@ -5518,7 +5524,7 @@
         <v>-13.57</v>
       </c>
       <c r="M91" t="n">
-        <v>-8.59</v>
+        <v>-1.76</v>
       </c>
       <c r="N91" t="b">
         <v>0</v>
@@ -5556,7 +5562,7 @@
         <v>33.9</v>
       </c>
       <c r="H92" t="n">
-        <v>8.119999999999999</v>
+        <v>6.84</v>
       </c>
       <c r="I92" t="n">
         <v>-7.74</v>
@@ -5569,7 +5575,7 @@
         <v>-9.449999999999999</v>
       </c>
       <c r="M92" t="n">
-        <v>6.78</v>
+        <v>6.7</v>
       </c>
       <c r="N92" t="b">
         <v>0</v>
@@ -5607,7 +5613,7 @@
         <v>-25</v>
       </c>
       <c r="H93" t="n">
-        <v>-7.93</v>
+        <v>-5.85</v>
       </c>
       <c r="I93" t="n">
         <v>2.51</v>
@@ -5620,7 +5626,7 @@
         <v>-4.88</v>
       </c>
       <c r="M93" t="n">
-        <v>-9.1</v>
+        <v>-5.83</v>
       </c>
       <c r="N93" t="b">
         <v>0</v>
@@ -5658,7 +5664,7 @@
         <v>-12.6</v>
       </c>
       <c r="H94" t="n">
-        <v>-15.82</v>
+        <v>-16.83</v>
       </c>
       <c r="I94" t="n">
         <v>-7.89</v>
@@ -5671,7 +5677,7 @@
         <v>-21.29</v>
       </c>
       <c r="M94" t="n">
-        <v>-17</v>
+        <v>-16.82</v>
       </c>
       <c r="N94" t="b">
         <v>0</v>
@@ -5709,7 +5715,7 @@
         <v>-17.9</v>
       </c>
       <c r="H95" t="n">
-        <v>6.87</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="I95" t="n">
         <v>0.6</v>
@@ -5722,7 +5728,7 @@
         <v>-4.72</v>
       </c>
       <c r="M95" t="n">
-        <v>5.69</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="N95" t="b">
         <v>1</v>
@@ -5760,7 +5766,7 @@
         <v>2.1</v>
       </c>
       <c r="H96" t="n">
-        <v>-6.92</v>
+        <v>-0.79</v>
       </c>
       <c r="I96" t="n">
         <v>0.25</v>
@@ -5773,7 +5779,7 @@
         <v>-16.43</v>
       </c>
       <c r="M96" t="n">
-        <v>-8.1</v>
+        <v>-0.77</v>
       </c>
       <c r="N96" t="b">
         <v>1</v>
@@ -5811,7 +5817,7 @@
         <v>19.4</v>
       </c>
       <c r="H97" t="n">
-        <v>-7.24</v>
+        <v>-8</v>
       </c>
       <c r="I97" t="n">
         <v>-10.01</v>
@@ -5824,7 +5830,7 @@
         <v>-15.23</v>
       </c>
       <c r="M97" t="n">
-        <v>-7.84</v>
+        <v>-7.42</v>
       </c>
       <c r="N97" t="b">
         <v>1</v>
@@ -5862,7 +5868,7 @@
         <v>-30.5</v>
       </c>
       <c r="H98" t="n">
-        <v>-4.58</v>
+        <v>-1.66</v>
       </c>
       <c r="I98" t="n">
         <v>-4.6</v>
@@ -5875,7 +5881,7 @@
         <v>-10.37</v>
       </c>
       <c r="M98" t="n">
-        <v>-5.18</v>
+        <v>-1.08</v>
       </c>
       <c r="N98" t="b">
         <v>0</v>
@@ -5913,7 +5919,7 @@
         <v>-20.5</v>
       </c>
       <c r="H99" t="n">
-        <v>-19.37</v>
+        <v>-16.07</v>
       </c>
       <c r="I99" t="n">
         <v>-4.62</v>
@@ -5926,7 +5932,7 @@
         <v>-9.92</v>
       </c>
       <c r="M99" t="n">
-        <v>-19.97</v>
+        <v>-15.49</v>
       </c>
       <c r="N99" t="b">
         <v>0</v>
@@ -5964,7 +5970,7 @@
         <v>-12.3</v>
       </c>
       <c r="H100" t="n">
-        <v>-15.36</v>
+        <v>-11.42</v>
       </c>
       <c r="I100" t="n">
         <v>-4.36</v>
@@ -5977,7 +5983,7 @@
         <v>-13.26</v>
       </c>
       <c r="M100" t="n">
-        <v>-16.18</v>
+        <v>-11.06</v>
       </c>
       <c r="N100" t="b">
         <v>0</v>
@@ -6015,7 +6021,7 @@
         <v>13.7</v>
       </c>
       <c r="H101" t="n">
-        <v>-20.25</v>
+        <v>-17.19</v>
       </c>
       <c r="I101" t="n">
         <v>-12.16</v>
@@ -6028,7 +6034,7 @@
         <v>-13.02</v>
       </c>
       <c r="M101" t="n">
-        <v>-21.07</v>
+        <v>-16.82</v>
       </c>
       <c r="N101" t="b">
         <v>0</v>
@@ -6066,7 +6072,7 @@
         <v>-2.6</v>
       </c>
       <c r="H102" t="n">
-        <v>-7.39</v>
+        <v>-5.79</v>
       </c>
       <c r="I102" t="n">
         <v>-4.27</v>
@@ -6079,7 +6085,7 @@
         <v>-4.86</v>
       </c>
       <c r="M102" t="n">
-        <v>-8.210000000000001</v>
+        <v>-5.42</v>
       </c>
       <c r="N102" t="b">
         <v>1</v>
@@ -6117,7 +6123,7 @@
         <v>25.6</v>
       </c>
       <c r="H103" t="n">
-        <v>11.25</v>
+        <v>15.83</v>
       </c>
       <c r="I103" t="n">
         <v>4.26</v>
@@ -6130,7 +6136,7 @@
         <v>-10.74</v>
       </c>
       <c r="M103" t="n">
-        <v>10.43</v>
+        <v>16.2</v>
       </c>
       <c r="N103" t="b">
         <v>0</v>
@@ -6168,7 +6174,7 @@
         <v>23.8</v>
       </c>
       <c r="H104" t="n">
-        <v>3.37</v>
+        <v>0.22</v>
       </c>
       <c r="I104" t="n">
         <v>1.36</v>
@@ -6181,7 +6187,7 @@
         <v>-9.94</v>
       </c>
       <c r="M104" t="n">
-        <v>3.52</v>
+        <v>1.55</v>
       </c>
       <c r="N104" t="b">
         <v>1</v>
@@ -6219,7 +6225,7 @@
         <v>38.9</v>
       </c>
       <c r="H105" t="n">
-        <v>-10.18</v>
+        <v>-15.33</v>
       </c>
       <c r="I105" t="n">
         <v>-9.220000000000001</v>
@@ -6232,7 +6238,7 @@
         <v>-9.83</v>
       </c>
       <c r="M105" t="n">
-        <v>-10.03</v>
+        <v>-14</v>
       </c>
       <c r="N105" t="b">
         <v>1</v>
@@ -6270,7 +6276,7 @@
         <v>32.1</v>
       </c>
       <c r="H106" t="n">
-        <v>48.09</v>
+        <v>41.04</v>
       </c>
       <c r="I106" t="n">
         <v>11.84</v>
@@ -6283,7 +6289,7 @@
         <v>-1.82</v>
       </c>
       <c r="M106" t="n">
-        <v>48.24</v>
+        <v>42.37</v>
       </c>
       <c r="N106" t="b">
         <v>0</v>
@@ -6321,7 +6327,7 @@
         <v>53.4</v>
       </c>
       <c r="H107" t="n">
-        <v>27.36</v>
+        <v>24.31</v>
       </c>
       <c r="I107" t="n">
         <v>2.75</v>
@@ -6334,7 +6340,7 @@
         <v>-2.31</v>
       </c>
       <c r="M107" t="n">
-        <v>27.82</v>
+        <v>25.94</v>
       </c>
       <c r="N107" t="b">
         <v>0</v>
@@ -6372,7 +6378,7 @@
         <v>54.1</v>
       </c>
       <c r="H108" t="n">
-        <v>35.86</v>
+        <v>33.33</v>
       </c>
       <c r="I108" t="n">
         <v>5.54</v>
@@ -6385,7 +6391,7 @@
         <v>-0.41</v>
       </c>
       <c r="M108" t="n">
-        <v>35.84</v>
+        <v>34.5</v>
       </c>
       <c r="N108" t="b">
         <v>0</v>
@@ -6423,7 +6429,7 @@
         <v>43.2</v>
       </c>
       <c r="H109" t="n">
-        <v>-10.98</v>
+        <v>-6.79</v>
       </c>
       <c r="I109" t="n">
         <v>-3.15</v>
@@ -6436,7 +6442,7 @@
         <v>-17.51</v>
       </c>
       <c r="M109" t="n">
-        <v>-11</v>
+        <v>-5.63</v>
       </c>
       <c r="N109" t="b">
         <v>1</v>
@@ -6474,7 +6480,7 @@
         <v>-8.199999999999999</v>
       </c>
       <c r="H110" t="n">
-        <v>6.35</v>
+        <v>12.43</v>
       </c>
       <c r="I110" t="n">
         <v>5.34</v>
@@ -6487,7 +6493,7 @@
         <v>-5.27</v>
       </c>
       <c r="M110" t="n">
-        <v>6.33</v>
+        <v>13.59</v>
       </c>
       <c r="N110" t="b">
         <v>1</v>
@@ -6525,7 +6531,7 @@
         <v>-1.2</v>
       </c>
       <c r="H111" t="n">
-        <v>2.94</v>
+        <v>14.37</v>
       </c>
       <c r="I111" t="n">
         <v>8.27</v>
@@ -6538,7 +6544,7 @@
         <v>-5.3</v>
       </c>
       <c r="M111" t="n">
-        <v>2.88</v>
+        <v>15.49</v>
       </c>
       <c r="N111" t="b">
         <v>0</v>
@@ -6576,7 +6582,7 @@
         <v>-23.9</v>
       </c>
       <c r="H112" t="n">
-        <v>-3.94</v>
+        <v>1.14</v>
       </c>
       <c r="I112" t="n">
         <v>3.28</v>
@@ -6589,7 +6595,7 @@
         <v>-4.46</v>
       </c>
       <c r="M112" t="n">
-        <v>-4.25</v>
+        <v>2.02</v>
       </c>
       <c r="N112" t="b">
         <v>1</v>
@@ -6631,7 +6637,7 @@
         <v>-6.1</v>
       </c>
       <c r="H113" t="n">
-        <v>-22.07</v>
+        <v>-23.88</v>
       </c>
       <c r="I113" t="n">
         <v>4.9</v>
@@ -6644,7 +6650,7 @@
         <v>-9</v>
       </c>
       <c r="M113" t="n">
-        <v>-22.39</v>
+        <v>-23.01</v>
       </c>
       <c r="N113" t="b">
         <v>0</v>
@@ -6682,7 +6688,7 @@
         <v>26.7</v>
       </c>
       <c r="H114" t="n">
-        <v>-0.6</v>
+        <v>-0.74</v>
       </c>
       <c r="I114" t="n">
         <v>-0.05</v>
@@ -6695,7 +6701,7 @@
         <v>-0.87</v>
       </c>
       <c r="M114" t="n">
-        <v>-0.92</v>
+        <v>0.13</v>
       </c>
       <c r="N114" t="b">
         <v>1</v>
@@ -6733,7 +6739,7 @@
         <v>39.5</v>
       </c>
       <c r="H115" t="n">
-        <v>3.97</v>
+        <v>2.74</v>
       </c>
       <c r="I115" t="n">
         <v>-5.13</v>
@@ -6746,7 +6752,7 @@
         <v>-8.869999999999999</v>
       </c>
       <c r="M115" t="n">
-        <v>3.65</v>
+        <v>3.62</v>
       </c>
       <c r="N115" t="b">
         <v>0</v>
@@ -6784,7 +6790,7 @@
         <v>14.3</v>
       </c>
       <c r="H116" t="n">
-        <v>15.85</v>
+        <v>12.21</v>
       </c>
       <c r="I116" t="n">
         <v>-0.43</v>
@@ -6797,7 +6803,7 @@
         <v>-11.86</v>
       </c>
       <c r="M116" t="n">
-        <v>15.54</v>
+        <v>13.08</v>
       </c>
       <c r="N116" t="b">
         <v>0</v>
@@ -6835,7 +6841,7 @@
         <v>-11.3</v>
       </c>
       <c r="H117" t="n">
-        <v>0.32</v>
+        <v>-5.44</v>
       </c>
       <c r="I117" t="n">
         <v>1.31</v>
@@ -6848,7 +6854,7 @@
         <v>-1.88</v>
       </c>
       <c r="M117" t="n">
-        <v>0</v>
+        <v>-4.56</v>
       </c>
       <c r="N117" t="b">
         <v>0</v>
@@ -6886,7 +6892,7 @@
         <v>-23.5</v>
       </c>
       <c r="H118" t="n">
-        <v>-22.77</v>
+        <v>-20.04</v>
       </c>
       <c r="I118" t="n">
         <v>13.29</v>
@@ -6899,7 +6905,7 @@
         <v>-14.04</v>
       </c>
       <c r="M118" t="n">
-        <v>-23.08</v>
+        <v>-19.17</v>
       </c>
       <c r="N118" t="b">
         <v>0</v>
@@ -6937,7 +6943,7 @@
         <v>10.5</v>
       </c>
       <c r="H119" t="n">
-        <v>-5.62</v>
+        <v>-6.67</v>
       </c>
       <c r="I119" t="n">
         <v>-0.86</v>
@@ -6950,7 +6956,7 @@
         <v>-6.11</v>
       </c>
       <c r="M119" t="n">
-        <v>-5.94</v>
+        <v>-5.79</v>
       </c>
       <c r="N119" t="b">
         <v>0</v>
@@ -6988,7 +6994,7 @@
         <v>-3.5</v>
       </c>
       <c r="H120" t="n">
-        <v>2.59</v>
+        <v>0.65</v>
       </c>
       <c r="I120" t="n">
         <v>-4.95</v>
@@ -7001,7 +7007,7 @@
         <v>-8.43</v>
       </c>
       <c r="M120" t="n">
-        <v>2.07</v>
+        <v>1.32</v>
       </c>
       <c r="N120" t="b">
         <v>1</v>
@@ -7039,7 +7045,7 @@
         <v>-12.8</v>
       </c>
       <c r="H121" t="n">
-        <v>12.83</v>
+        <v>1.76</v>
       </c>
       <c r="I121" t="n">
         <v>-1.74</v>
@@ -7052,7 +7058,7 @@
         <v>-2.97</v>
       </c>
       <c r="M121" t="n">
-        <v>12.31</v>
+        <v>2.43</v>
       </c>
       <c r="N121" t="b">
         <v>0</v>
@@ -7090,7 +7096,7 @@
         <v>2.4</v>
       </c>
       <c r="H122" t="n">
-        <v>26.02</v>
+        <v>22.57</v>
       </c>
       <c r="I122" t="n">
         <v>12.41</v>
@@ -7103,7 +7109,7 @@
         <v>-0.07000000000000001</v>
       </c>
       <c r="M122" t="n">
-        <v>25.5</v>
+        <v>23.23</v>
       </c>
       <c r="N122" t="b">
         <v>0</v>
@@ -7141,7 +7147,7 @@
         <v>-17.9</v>
       </c>
       <c r="H123" t="n">
-        <v>6.18</v>
+        <v>-1.67</v>
       </c>
       <c r="I123" t="n">
         <v>-0.5</v>
@@ -7154,7 +7160,7 @@
         <v>-3.43</v>
       </c>
       <c r="M123" t="n">
-        <v>5.66</v>
+        <v>-1</v>
       </c>
       <c r="N123" t="b">
         <v>1</v>
@@ -7192,7 +7198,7 @@
         <v>11.9</v>
       </c>
       <c r="H124" t="n">
-        <v>-1.63</v>
+        <v>-1.05</v>
       </c>
       <c r="I124" t="n">
         <v>6.88</v>
@@ -7205,7 +7211,7 @@
         <v>-10.93</v>
       </c>
       <c r="M124" t="n">
-        <v>-2.25</v>
+        <v>-0.49</v>
       </c>
       <c r="N124" t="b">
         <v>0</v>
@@ -7243,7 +7249,7 @@
         <v>53.5</v>
       </c>
       <c r="H125" t="n">
-        <v>9.279999999999999</v>
+        <v>15.67</v>
       </c>
       <c r="I125" t="n">
         <v>1.23</v>
@@ -7256,7 +7262,7 @@
         <v>-7.57</v>
       </c>
       <c r="M125" t="n">
-        <v>8.65</v>
+        <v>16.23</v>
       </c>
       <c r="N125" t="b">
         <v>1</v>
@@ -7294,7 +7300,7 @@
         <v>18.1</v>
       </c>
       <c r="H126" t="n">
-        <v>-4.15</v>
+        <v>-3.58</v>
       </c>
       <c r="I126" t="n">
         <v>-1.69</v>
@@ -7307,7 +7313,7 @@
         <v>-1.92</v>
       </c>
       <c r="M126" t="n">
-        <v>-4.77</v>
+        <v>-3.02</v>
       </c>
       <c r="N126" t="b">
         <v>0</v>
@@ -7345,7 +7351,7 @@
         <v>-1</v>
       </c>
       <c r="H127" t="n">
-        <v>-12.52</v>
+        <v>-15.23</v>
       </c>
       <c r="I127" t="n">
         <v>-6.26</v>
@@ -7358,7 +7364,7 @@
         <v>-15</v>
       </c>
       <c r="M127" t="n">
-        <v>-13.15</v>
+        <v>-14.66</v>
       </c>
       <c r="N127" t="b">
         <v>1</v>
@@ -7396,7 +7402,7 @@
         <v>29.7</v>
       </c>
       <c r="H128" t="n">
-        <v>11.14</v>
+        <v>13.11</v>
       </c>
       <c r="I128" t="n">
         <v>11.27</v>
@@ -7409,7 +7415,7 @@
         <v>0</v>
       </c>
       <c r="M128" t="n">
-        <v>10.52</v>
+        <v>13.67</v>
       </c>
       <c r="N128" t="b">
         <v>1</v>
@@ -7447,7 +7453,7 @@
         <v>15.2</v>
       </c>
       <c r="H129" t="n">
-        <v>-31.29</v>
+        <v>-24.78</v>
       </c>
       <c r="I129" t="n">
         <v>-8.77</v>
@@ -7460,7 +7466,7 @@
         <v>-24.79</v>
       </c>
       <c r="M129" t="n">
-        <v>-31.18</v>
+        <v>-23.49</v>
       </c>
       <c r="N129" t="b">
         <v>1</v>
@@ -7498,7 +7504,7 @@
         <v>22.2</v>
       </c>
       <c r="H130" t="n">
-        <v>12.66</v>
+        <v>12.82</v>
       </c>
       <c r="I130" t="n">
         <v>1.01</v>
@@ -7511,7 +7517,7 @@
         <v>-3.94</v>
       </c>
       <c r="M130" t="n">
-        <v>12.77</v>
+        <v>14.11</v>
       </c>
       <c r="N130" t="b">
         <v>1</v>
@@ -7549,7 +7555,7 @@
         <v>10.8</v>
       </c>
       <c r="H131" t="n">
-        <v>12.83</v>
+        <v>13.75</v>
       </c>
       <c r="I131" t="n">
         <v>5.62</v>
@@ -7562,7 +7568,7 @@
         <v>-1.59</v>
       </c>
       <c r="M131" t="n">
-        <v>12.94</v>
+        <v>15.03</v>
       </c>
       <c r="N131" t="b">
         <v>0</v>
@@ -7600,7 +7606,7 @@
         <v>-2.1</v>
       </c>
       <c r="H132" t="n">
-        <v>-20.26</v>
+        <v>-22.82</v>
       </c>
       <c r="I132" t="n">
         <v>0.67</v>
@@ -7613,7 +7619,7 @@
         <v>-7.84</v>
       </c>
       <c r="M132" t="n">
-        <v>-20.15</v>
+        <v>-21.53</v>
       </c>
       <c r="N132" t="b">
         <v>0</v>
@@ -7651,7 +7657,7 @@
         <v>16.7</v>
       </c>
       <c r="H133" t="n">
-        <v>-26.22</v>
+        <v>-24.05</v>
       </c>
       <c r="I133" t="n">
         <v>-15.31</v>
@@ -7664,7 +7670,7 @@
         <v>-22</v>
       </c>
       <c r="M133" t="n">
-        <v>-28.11</v>
+        <v>-24.74</v>
       </c>
       <c r="N133" t="b">
         <v>0</v>
@@ -7702,7 +7708,7 @@
         <v>0.3</v>
       </c>
       <c r="H134" t="n">
-        <v>44.39</v>
+        <v>49.58</v>
       </c>
       <c r="I134" t="n">
         <v>6.01</v>
@@ -7715,7 +7721,7 @@
         <v>-3.85</v>
       </c>
       <c r="M134" t="n">
-        <v>40.98</v>
+        <v>47.39</v>
       </c>
       <c r="N134" t="b">
         <v>0</v>
@@ -7757,7 +7763,7 @@
         <v>-0</v>
       </c>
       <c r="H135" t="n">
-        <v>52.65</v>
+        <v>53.6</v>
       </c>
       <c r="I135" t="n">
         <v>13.5</v>
@@ -7770,7 +7776,7 @@
         <v>-2.53</v>
       </c>
       <c r="M135" t="n">
-        <v>49.24</v>
+        <v>51.41</v>
       </c>
       <c r="N135" t="b">
         <v>1</v>
@@ -7808,7 +7814,7 @@
         <v>10.5</v>
       </c>
       <c r="H136" t="n">
-        <v>18.72</v>
+        <v>24.57</v>
       </c>
       <c r="I136" t="n">
         <v>1.99</v>
@@ -7821,7 +7827,7 @@
         <v>-6.27</v>
       </c>
       <c r="M136" t="n">
-        <v>15.31</v>
+        <v>22.38</v>
       </c>
       <c r="N136" t="b">
         <v>1</v>
@@ -7859,7 +7865,7 @@
         <v>30.4</v>
       </c>
       <c r="H137" t="n">
-        <v>8.18</v>
+        <v>9.74</v>
       </c>
       <c r="I137" t="n">
         <v>8.539999999999999</v>
@@ -7872,7 +7878,7 @@
         <v>-0.44</v>
       </c>
       <c r="M137" t="n">
-        <v>4.77</v>
+        <v>7.55</v>
       </c>
       <c r="N137" t="b">
         <v>0</v>
@@ -7914,7 +7920,7 @@
         <v>-3.2</v>
       </c>
       <c r="H138" t="n">
-        <v>22.38</v>
+        <v>26.62</v>
       </c>
       <c r="I138" t="n">
         <v>15.28</v>
@@ -7927,7 +7933,7 @@
         <v>-2.53</v>
       </c>
       <c r="M138" t="n">
-        <v>18.97</v>
+        <v>24.43</v>
       </c>
       <c r="N138" t="b">
         <v>0</v>
@@ -7965,7 +7971,7 @@
         <v>-23.5</v>
       </c>
       <c r="H139" t="n">
-        <v>23</v>
+        <v>20.48</v>
       </c>
       <c r="I139" t="n">
         <v>20.48</v>
@@ -7978,7 +7984,7 @@
         <v>-2.25</v>
       </c>
       <c r="M139" t="n">
-        <v>19.58</v>
+        <v>18.29</v>
       </c>
       <c r="N139" t="b">
         <v>0</v>
@@ -8016,7 +8022,7 @@
         <v>-27.3</v>
       </c>
       <c r="H140" t="n">
-        <v>23.74</v>
+        <v>28.05</v>
       </c>
       <c r="I140" t="n">
         <v>-8.83</v>
@@ -8029,7 +8035,7 @@
         <v>-19.66</v>
       </c>
       <c r="M140" t="n">
-        <v>20.33</v>
+        <v>25.86</v>
       </c>
       <c r="N140" t="b">
         <v>0</v>
@@ -8067,7 +8073,7 @@
         <v>-12.5</v>
       </c>
       <c r="H141" t="n">
-        <v>-8.789999999999999</v>
+        <v>-3.42</v>
       </c>
       <c r="I141" t="n">
         <v>21.54</v>
@@ -8080,7 +8086,7 @@
         <v>-0.95</v>
       </c>
       <c r="M141" t="n">
-        <v>-12.87</v>
+        <v>-6.27</v>
       </c>
       <c r="N141" t="b">
         <v>0</v>
@@ -8118,7 +8124,7 @@
         <v>-37</v>
       </c>
       <c r="H142" t="n">
-        <v>60.29</v>
+        <v>60.76</v>
       </c>
       <c r="I142" t="n">
         <v>18.38</v>
@@ -8131,7 +8137,7 @@
         <v>-5.11</v>
       </c>
       <c r="M142" t="n">
-        <v>56.21</v>
+        <v>57.92</v>
       </c>
       <c r="N142" t="b">
         <v>1</v>
@@ -8173,7 +8179,7 @@
         <v>-3.4</v>
       </c>
       <c r="H143" t="n">
-        <v>11.74</v>
+        <v>13.61</v>
       </c>
       <c r="I143" t="n">
         <v>30.48</v>
@@ -8186,7 +8192,7 @@
         <v>-0.9</v>
       </c>
       <c r="M143" t="n">
-        <v>7.66</v>
+        <v>10.77</v>
       </c>
       <c r="N143" t="b">
         <v>0</v>
@@ -8224,7 +8230,7 @@
         <v>-23.4</v>
       </c>
       <c r="H144" t="n">
-        <v>-1.32</v>
+        <v>2.83</v>
       </c>
       <c r="I144" t="n">
         <v>-3.58</v>
@@ -8237,7 +8243,7 @@
         <v>-17.98</v>
       </c>
       <c r="M144" t="n">
-        <v>-5.39</v>
+        <v>-0.02</v>
       </c>
       <c r="N144" t="b">
         <v>0</v>
@@ -8275,7 +8281,7 @@
         <v>-28.9</v>
       </c>
       <c r="H145" t="n">
-        <v>-13.78</v>
+        <v>-10</v>
       </c>
       <c r="I145" t="n">
         <v>-12.9</v>
@@ -8288,7 +8294,7 @@
         <v>-23.19</v>
       </c>
       <c r="M145" t="n">
-        <v>-17.85</v>
+        <v>-12.84</v>
       </c>
       <c r="N145" t="b">
         <v>0</v>
@@ -8326,7 +8332,7 @@
         <v>-26.8</v>
       </c>
       <c r="H146" t="n">
-        <v>25.57</v>
+        <v>26.62</v>
       </c>
       <c r="I146" t="n">
         <v>4.56</v>
@@ -8339,7 +8345,7 @@
         <v>-4.09</v>
       </c>
       <c r="M146" t="n">
-        <v>21.5</v>
+        <v>23.78</v>
       </c>
       <c r="N146" t="b">
         <v>1</v>
@@ -8381,7 +8387,7 @@
         <v>-9.800000000000001</v>
       </c>
       <c r="H147" t="n">
-        <v>-19.93</v>
+        <v>-15.82</v>
       </c>
       <c r="I147" t="n">
         <v>-4.09</v>
@@ -8394,7 +8400,7 @@
         <v>-15.24</v>
       </c>
       <c r="M147" t="n">
-        <v>-25.22</v>
+        <v>-19.87</v>
       </c>
       <c r="N147" t="b">
         <v>0</v>
@@ -8432,7 +8438,7 @@
         <v>21</v>
       </c>
       <c r="H148" t="n">
-        <v>3.36</v>
+        <v>1.49</v>
       </c>
       <c r="I148" t="n">
         <v>-0.72</v>
@@ -8445,7 +8451,7 @@
         <v>-7.35</v>
       </c>
       <c r="M148" t="n">
-        <v>-1.94</v>
+        <v>-2.56</v>
       </c>
       <c r="N148" t="b">
         <v>0</v>
@@ -8483,7 +8489,7 @@
         <v>13.2</v>
       </c>
       <c r="H149" t="n">
-        <v>58.62</v>
+        <v>60.46</v>
       </c>
       <c r="I149" t="n">
         <v>8.130000000000001</v>
@@ -8496,7 +8502,7 @@
         <v>-2.36</v>
       </c>
       <c r="M149" t="n">
-        <v>53.33</v>
+        <v>56.41</v>
       </c>
       <c r="N149" t="b">
         <v>0</v>
@@ -8534,7 +8540,7 @@
         <v>6.1</v>
       </c>
       <c r="H150" t="n">
-        <v>3.65</v>
+        <v>2.09</v>
       </c>
       <c r="I150" t="n">
         <v>10.43</v>
@@ -8547,7 +8553,7 @@
         <v>-1.51</v>
       </c>
       <c r="M150" t="n">
-        <v>-1.64</v>
+        <v>-1.96</v>
       </c>
       <c r="N150" t="b">
         <v>0</v>
@@ -8585,7 +8591,7 @@
         <v>6.5</v>
       </c>
       <c r="H151" t="n">
-        <v>0.23</v>
+        <v>9.98</v>
       </c>
       <c r="I151" t="n">
         <v>-0.04</v>
@@ -8598,7 +8604,7 @@
         <v>-4.12</v>
       </c>
       <c r="M151" t="n">
-        <v>-5.07</v>
+        <v>5.93</v>
       </c>
       <c r="N151" t="b">
         <v>0</v>
@@ -8636,7 +8642,7 @@
         <v>-36.5</v>
       </c>
       <c r="H152" t="n">
-        <v>-32.57</v>
+        <v>-29.51</v>
       </c>
       <c r="I152" t="n">
         <v>-27.75</v>
@@ -8644,12 +8650,14 @@
       <c r="J152" t="n">
         <v>-30.21</v>
       </c>
-      <c r="K152" t="inlineStr"/>
+      <c r="K152" t="n">
+        <v>-29.51</v>
+      </c>
       <c r="L152" t="n">
         <v>-31.28</v>
       </c>
       <c r="M152" t="n">
-        <v>-37.3</v>
+        <v>-33.01</v>
       </c>
       <c r="N152" t="b">
         <v>1</v>
@@ -8687,7 +8695,7 @@
         <v>-14.5</v>
       </c>
       <c r="H153" t="n">
-        <v>-9.06</v>
+        <v>4.01</v>
       </c>
       <c r="I153" t="n">
         <v>4.48</v>
@@ -8695,12 +8703,14 @@
       <c r="J153" t="n">
         <v>-0.65</v>
       </c>
-      <c r="K153" t="inlineStr"/>
+      <c r="K153" t="n">
+        <v>4.01</v>
+      </c>
       <c r="L153" t="n">
         <v>-3.33</v>
       </c>
       <c r="M153" t="n">
-        <v>-13.79</v>
+        <v>0.51</v>
       </c>
       <c r="N153" t="b">
         <v>0</v>
@@ -8738,7 +8748,7 @@
         <v>1.7</v>
       </c>
       <c r="H154" t="n">
-        <v>-5.51</v>
+        <v>-4.74</v>
       </c>
       <c r="I154" t="n">
         <v>8.859999999999999</v>
@@ -8746,12 +8756,14 @@
       <c r="J154" t="n">
         <v>21.38</v>
       </c>
-      <c r="K154" t="inlineStr"/>
+      <c r="K154" t="n">
+        <v>-4.74</v>
+      </c>
       <c r="L154" t="n">
         <v>-3.27</v>
       </c>
       <c r="M154" t="n">
-        <v>-10.24</v>
+        <v>-8.24</v>
       </c>
       <c r="N154" t="b">
         <v>0</v>
@@ -8789,7 +8801,7 @@
         <v>48.1</v>
       </c>
       <c r="H155" t="n">
-        <v>9.59</v>
+        <v>8.44</v>
       </c>
       <c r="I155" t="n">
         <v>0.16</v>
@@ -8797,12 +8809,14 @@
       <c r="J155" t="n">
         <v>0.74</v>
       </c>
-      <c r="K155" t="inlineStr"/>
+      <c r="K155" t="n">
+        <v>8.44</v>
+      </c>
       <c r="L155" t="n">
         <v>-8.890000000000001</v>
       </c>
       <c r="M155" t="n">
-        <v>4.85</v>
+        <v>4.94</v>
       </c>
       <c r="N155" t="b">
         <v>0</v>
@@ -8840,7 +8854,7 @@
         <v>-38.7</v>
       </c>
       <c r="H156" t="n">
-        <v>26.39</v>
+        <v>36.19</v>
       </c>
       <c r="I156" t="n">
         <v>17.17</v>
@@ -8848,12 +8862,14 @@
       <c r="J156" t="n">
         <v>23.47</v>
       </c>
-      <c r="K156" t="inlineStr"/>
+      <c r="K156" t="n">
+        <v>36.19</v>
+      </c>
       <c r="L156" t="n">
         <v>-0.54</v>
       </c>
       <c r="M156" t="n">
-        <v>21.66</v>
+        <v>32.69</v>
       </c>
       <c r="N156" t="b">
         <v>1</v>
@@ -8891,7 +8907,7 @@
         <v>24.9</v>
       </c>
       <c r="H157" t="n">
-        <v>1.27</v>
+        <v>5.16</v>
       </c>
       <c r="I157" t="n">
         <v>10.45</v>
@@ -8899,12 +8915,14 @@
       <c r="J157" t="n">
         <v>8.609999999999999</v>
       </c>
-      <c r="K157" t="inlineStr"/>
+      <c r="K157" t="n">
+        <v>5.16</v>
+      </c>
       <c r="L157" t="n">
         <v>-0.49</v>
       </c>
       <c r="M157" t="n">
-        <v>-3.47</v>
+        <v>1.67</v>
       </c>
       <c r="N157" t="b">
         <v>0</v>
@@ -8942,7 +8960,7 @@
         <v>-34.6</v>
       </c>
       <c r="H158" t="n">
-        <v>20.12</v>
+        <v>25.14</v>
       </c>
       <c r="I158" t="n">
         <v>6.67</v>
@@ -8950,12 +8968,14 @@
       <c r="J158" t="n">
         <v>15.4</v>
       </c>
-      <c r="K158" t="inlineStr"/>
+      <c r="K158" t="n">
+        <v>25.14</v>
+      </c>
       <c r="L158" t="n">
         <v>-3.06</v>
       </c>
       <c r="M158" t="n">
-        <v>15.38</v>
+        <v>21.64</v>
       </c>
       <c r="N158" t="b">
         <v>1</v>
@@ -8993,7 +9013,7 @@
         <v>-21.4</v>
       </c>
       <c r="H159" t="n">
-        <v>-9.9</v>
+        <v>-7.12</v>
       </c>
       <c r="I159" t="n">
         <v>2.8</v>
@@ -9001,12 +9021,14 @@
       <c r="J159" t="n">
         <v>12.84</v>
       </c>
-      <c r="K159" t="inlineStr"/>
+      <c r="K159" t="n">
+        <v>-7.12</v>
+      </c>
       <c r="L159" t="n">
         <v>-2.27</v>
       </c>
       <c r="M159" t="n">
-        <v>-14.64</v>
+        <v>-10.62</v>
       </c>
       <c r="N159" t="b">
         <v>0</v>
@@ -9044,7 +9066,7 @@
         <v>-11.8</v>
       </c>
       <c r="H160" t="n">
-        <v>5.1</v>
+        <v>10.56</v>
       </c>
       <c r="I160" t="n">
         <v>9.76</v>
@@ -9059,7 +9081,7 @@
         <v>-1.63</v>
       </c>
       <c r="M160" t="n">
-        <v>0.25</v>
+        <v>6.95</v>
       </c>
       <c r="N160" t="b">
         <v>1</v>
@@ -9097,7 +9119,7 @@
         <v>0.1</v>
       </c>
       <c r="H161" t="n">
-        <v>-2.62</v>
+        <v>2.52</v>
       </c>
       <c r="I161" t="n">
         <v>-2.83</v>
@@ -9112,7 +9134,7 @@
         <v>-5.45</v>
       </c>
       <c r="M161" t="n">
-        <v>-7.47</v>
+        <v>-1.09</v>
       </c>
       <c r="N161" t="b">
         <v>1</v>
@@ -9150,7 +9172,7 @@
         <v>-13.8</v>
       </c>
       <c r="H162" t="n">
-        <v>14.93</v>
+        <v>7.62</v>
       </c>
       <c r="I162" t="n">
         <v>4.67</v>
@@ -9165,7 +9187,7 @@
         <v>-5.7</v>
       </c>
       <c r="M162" t="n">
-        <v>10.08</v>
+        <v>4.01</v>
       </c>
       <c r="N162" t="b">
         <v>0</v>
@@ -9207,7 +9229,7 @@
         <v>-8.800000000000001</v>
       </c>
       <c r="H163" t="n">
-        <v>11.01</v>
+        <v>15.24</v>
       </c>
       <c r="I163" t="n">
         <v>15.97</v>
@@ -9222,7 +9244,7 @@
         <v>-0.79</v>
       </c>
       <c r="M163" t="n">
-        <v>6.16</v>
+        <v>11.63</v>
       </c>
       <c r="N163" t="b">
         <v>0</v>
@@ -9260,7 +9282,7 @@
         <v>24.1</v>
       </c>
       <c r="H164" t="n">
-        <v>2.89</v>
+        <v>2.49</v>
       </c>
       <c r="I164" t="n">
         <v>-8.31</v>
@@ -9275,7 +9297,7 @@
         <v>-18.31</v>
       </c>
       <c r="M164" t="n">
-        <v>-1.15</v>
+        <v>-0.33</v>
       </c>
       <c r="N164" t="b">
         <v>1</v>
@@ -9313,7 +9335,7 @@
         <v>-15.9</v>
       </c>
       <c r="H165" t="n">
-        <v>20.25</v>
+        <v>23.54</v>
       </c>
       <c r="I165" t="n">
         <v>10.45</v>
@@ -9328,7 +9350,7 @@
         <v>-0.31</v>
       </c>
       <c r="M165" t="n">
-        <v>16.21</v>
+        <v>20.73</v>
       </c>
       <c r="N165" t="b">
         <v>1</v>
@@ -9366,7 +9388,7 @@
         <v>-23.3</v>
       </c>
       <c r="H166" t="n">
-        <v>-17.44</v>
+        <v>-16.64</v>
       </c>
       <c r="I166" t="n">
         <v>-20.42</v>
@@ -9381,7 +9403,7 @@
         <v>-27.45</v>
       </c>
       <c r="M166" t="n">
-        <v>-21.48</v>
+        <v>-19.46</v>
       </c>
       <c r="N166" t="b">
         <v>0</v>
@@ -9419,7 +9441,7 @@
         <v>28.9</v>
       </c>
       <c r="H167" t="n">
-        <v>-4.18</v>
+        <v>-6.29</v>
       </c>
       <c r="I167" t="n">
         <v>8.06</v>
@@ -9434,7 +9456,7 @@
         <v>-2.79</v>
       </c>
       <c r="M167" t="n">
-        <v>-9.119999999999999</v>
+        <v>-10</v>
       </c>
       <c r="N167" t="b">
         <v>0</v>
@@ -9472,7 +9494,7 @@
         <v>40.1</v>
       </c>
       <c r="H168" t="n">
-        <v>29.37</v>
+        <v>28.62</v>
       </c>
       <c r="I168" t="n">
         <v>15.9</v>
@@ -9487,7 +9509,7 @@
         <v>-5.87</v>
       </c>
       <c r="M168" t="n">
-        <v>24.43</v>
+        <v>24.91</v>
       </c>
       <c r="N168" t="b">
         <v>0</v>
@@ -9525,7 +9547,7 @@
         <v>-27.3</v>
       </c>
       <c r="H169" t="n">
-        <v>1.24</v>
+        <v>-4.65</v>
       </c>
       <c r="I169" t="n">
         <v>0.75</v>
@@ -9540,7 +9562,7 @@
         <v>-5.46</v>
       </c>
       <c r="M169" t="n">
-        <v>-3.58</v>
+        <v>-8.23</v>
       </c>
       <c r="N169" t="b">
         <v>0</v>
@@ -9578,7 +9600,7 @@
         <v>19.7</v>
       </c>
       <c r="H170" t="n">
-        <v>-27.27</v>
+        <v>-26.58</v>
       </c>
       <c r="I170" t="n">
         <v>-4.49</v>
@@ -9593,7 +9615,7 @@
         <v>-13.7</v>
       </c>
       <c r="M170" t="n">
-        <v>-32.09</v>
+        <v>-30.16</v>
       </c>
       <c r="N170" t="b">
         <v>0</v>
@@ -9631,7 +9653,7 @@
         <v>-21.3</v>
       </c>
       <c r="H171" t="n">
-        <v>-11.78</v>
+        <v>-12.55</v>
       </c>
       <c r="I171" t="n">
         <v>7.16</v>
@@ -9646,7 +9668,7 @@
         <v>-11.9</v>
       </c>
       <c r="M171" t="n">
-        <v>-16.6</v>
+        <v>-16.13</v>
       </c>
       <c r="N171" t="b">
         <v>0</v>
@@ -9684,7 +9706,7 @@
         <v>-21.8</v>
       </c>
       <c r="H172" t="n">
-        <v>-35.33</v>
+        <v>-36.2</v>
       </c>
       <c r="I172" t="n">
         <v>-18.97</v>
@@ -9699,7 +9721,7 @@
         <v>-26.82</v>
       </c>
       <c r="M172" t="n">
-        <v>-40.15</v>
+        <v>-39.79</v>
       </c>
       <c r="N172" t="b">
         <v>1</v>
@@ -9737,7 +9759,7 @@
         <v>-37.6</v>
       </c>
       <c r="H173" t="n">
-        <v>-19.36</v>
+        <v>-20.34</v>
       </c>
       <c r="I173" t="n">
         <v>15.2</v>
@@ -9752,7 +9774,7 @@
         <v>-10.3</v>
       </c>
       <c r="M173" t="n">
-        <v>-23.16</v>
+        <v>-22.91</v>
       </c>
       <c r="N173" t="b">
         <v>0</v>
@@ -9790,7 +9812,7 @@
         <v>53.8</v>
       </c>
       <c r="H174" t="n">
-        <v>47.7</v>
+        <v>42.52</v>
       </c>
       <c r="I174" t="n">
         <v>4.09</v>
@@ -9805,7 +9827,7 @@
         <v>-8.66</v>
       </c>
       <c r="M174" t="n">
-        <v>43.9</v>
+        <v>39.95</v>
       </c>
       <c r="N174" t="b">
         <v>0</v>
@@ -9847,7 +9869,7 @@
         <v>-5.7</v>
       </c>
       <c r="H175" t="n">
-        <v>37</v>
+        <v>33.88</v>
       </c>
       <c r="I175" t="n">
         <v>17.92</v>
@@ -9862,7 +9884,7 @@
         <v>-7.48</v>
       </c>
       <c r="M175" t="n">
-        <v>33.2</v>
+        <v>31.3</v>
       </c>
       <c r="N175" t="b">
         <v>0</v>
@@ -9900,7 +9922,7 @@
         <v>-39.3</v>
       </c>
       <c r="H176" t="n">
-        <v>14.47</v>
+        <v>21.05</v>
       </c>
       <c r="I176" t="n">
         <v>11.34</v>
@@ -9915,7 +9937,7 @@
         <v>-5.3</v>
       </c>
       <c r="M176" t="n">
-        <v>10.67</v>
+        <v>18.47</v>
       </c>
       <c r="N176" t="b">
         <v>0</v>
@@ -9953,7 +9975,7 @@
         <v>57</v>
       </c>
       <c r="H177" t="n">
-        <v>35.19</v>
+        <v>31.69</v>
       </c>
       <c r="I177" t="n">
         <v>-11.21</v>
@@ -9968,7 +9990,7 @@
         <v>-13.87</v>
       </c>
       <c r="M177" t="n">
-        <v>31.39</v>
+        <v>29.11</v>
       </c>
       <c r="N177" t="b">
         <v>1</v>
@@ -10006,7 +10028,7 @@
         <v>-21.8</v>
       </c>
       <c r="H178" t="n">
-        <v>24.65</v>
+        <v>30.19</v>
       </c>
       <c r="I178" t="n">
         <v>1.71</v>
@@ -10021,7 +10043,7 @@
         <v>-6.18</v>
       </c>
       <c r="M178" t="n">
-        <v>20.85</v>
+        <v>27.62</v>
       </c>
       <c r="N178" t="b">
         <v>1</v>
@@ -10059,7 +10081,7 @@
         <v>1</v>
       </c>
       <c r="H179" t="n">
-        <v>-38.31</v>
+        <v>-36.33</v>
       </c>
       <c r="I179" t="n">
         <v>-11.52</v>
@@ -10074,7 +10096,7 @@
         <v>-16.26</v>
       </c>
       <c r="M179" t="n">
-        <v>-42.16</v>
+        <v>-38.95</v>
       </c>
       <c r="N179" t="b">
         <v>1</v>
@@ -10112,7 +10134,7 @@
         <v>45.4</v>
       </c>
       <c r="H180" t="n">
-        <v>-20.63</v>
+        <v>-26.4</v>
       </c>
       <c r="I180" t="n">
         <v>-1.72</v>
@@ -10127,7 +10149,7 @@
         <v>-23.15</v>
       </c>
       <c r="M180" t="n">
-        <v>-24.47</v>
+        <v>-29.02</v>
       </c>
       <c r="N180" t="b">
         <v>0</v>
@@ -10165,7 +10187,7 @@
         <v>49.6</v>
       </c>
       <c r="H181" t="n">
-        <v>19.1</v>
+        <v>8.74</v>
       </c>
       <c r="I181" t="n">
         <v>6.34</v>
@@ -10180,7 +10202,7 @@
         <v>-20.75</v>
       </c>
       <c r="M181" t="n">
-        <v>15.25</v>
+        <v>6.11</v>
       </c>
       <c r="N181" t="b">
         <v>0</v>
@@ -10218,7 +10240,7 @@
         <v>55.3</v>
       </c>
       <c r="H182" t="n">
-        <v>-28.4</v>
+        <v>-33</v>
       </c>
       <c r="I182" t="n">
         <v>3.73</v>
@@ -10233,7 +10255,7 @@
         <v>-22.94</v>
       </c>
       <c r="M182" t="n">
-        <v>-32.25</v>
+        <v>-35.62</v>
       </c>
       <c r="N182" t="b">
         <v>0</v>
@@ -10271,7 +10293,7 @@
         <v>76.5</v>
       </c>
       <c r="H183" t="n">
-        <v>-8.83</v>
+        <v>-16.59</v>
       </c>
       <c r="I183" t="n">
         <v>-5.56</v>
@@ -10286,7 +10308,7 @@
         <v>-33.97</v>
       </c>
       <c r="M183" t="n">
-        <v>-12.68</v>
+        <v>-19.21</v>
       </c>
       <c r="N183" t="b">
         <v>0</v>
@@ -10324,7 +10346,7 @@
         <v>77.90000000000001</v>
       </c>
       <c r="H184" t="n">
-        <v>-1.25</v>
+        <v>-7.43</v>
       </c>
       <c r="I184" t="n">
         <v>-3.53</v>
@@ -10339,7 +10361,7 @@
         <v>-20.26</v>
       </c>
       <c r="M184" t="n">
-        <v>-5.1</v>
+        <v>-10.05</v>
       </c>
       <c r="N184" t="b">
         <v>0</v>
@@ -10377,7 +10399,7 @@
         <v>57.6</v>
       </c>
       <c r="H185" t="n">
-        <v>27.8</v>
+        <v>21.87</v>
       </c>
       <c r="I185" t="n">
         <v>14.81</v>
@@ -10392,7 +10414,7 @@
         <v>-5.11</v>
       </c>
       <c r="M185" t="n">
-        <v>23.96</v>
+        <v>19.25</v>
       </c>
       <c r="N185" t="b">
         <v>0</v>
@@ -10430,7 +10452,7 @@
         <v>32.1</v>
       </c>
       <c r="H186" t="n">
-        <v>-11.13</v>
+        <v>-17.55</v>
       </c>
       <c r="I186" t="n">
         <v>16.93</v>
@@ -10445,7 +10467,7 @@
         <v>-24.48</v>
       </c>
       <c r="M186" t="n">
-        <v>-14.97</v>
+        <v>-20.17</v>
       </c>
       <c r="N186" t="b">
         <v>0</v>
@@ -10483,7 +10505,7 @@
         <v>51.8</v>
       </c>
       <c r="H187" t="n">
-        <v>-11.18</v>
+        <v>-21.05</v>
       </c>
       <c r="I187" t="n">
         <v>10.75</v>
@@ -10498,7 +10520,7 @@
         <v>-25.09</v>
       </c>
       <c r="M187" t="n">
-        <v>-15.02</v>
+        <v>-23.67</v>
       </c>
       <c r="N187" t="b">
         <v>0</v>
@@ -10536,7 +10558,7 @@
         <v>32.3</v>
       </c>
       <c r="H188" t="n">
-        <v>-39.58</v>
+        <v>-45.45</v>
       </c>
       <c r="I188" t="n">
         <v>-20.76</v>
@@ -10551,7 +10573,7 @@
         <v>-27.91</v>
       </c>
       <c r="M188" t="n">
-        <v>-43.43</v>
+        <v>-48.07</v>
       </c>
       <c r="N188" t="b">
         <v>1</v>
@@ -10589,7 +10611,7 @@
         <v>15.7</v>
       </c>
       <c r="H189" t="n">
-        <v>-16.2</v>
+        <v>-22.99</v>
       </c>
       <c r="I189" t="n">
         <v>-0.87</v>
@@ -10604,7 +10626,7 @@
         <v>-29.01</v>
       </c>
       <c r="M189" t="n">
-        <v>-20.05</v>
+        <v>-25.61</v>
       </c>
       <c r="N189" t="b">
         <v>0</v>
@@ -10642,7 +10664,7 @@
         <v>63.7</v>
       </c>
       <c r="H190" t="n">
-        <v>-19.28</v>
+        <v>-25.62</v>
       </c>
       <c r="I190" t="n">
         <v>-2.16</v>
@@ -10657,7 +10679,7 @@
         <v>-19.1</v>
       </c>
       <c r="M190" t="n">
-        <v>-23.13</v>
+        <v>-28.24</v>
       </c>
       <c r="N190" t="b">
         <v>0</v>
@@ -10695,7 +10717,7 @@
         <v>3.7</v>
       </c>
       <c r="H191" t="n">
-        <v>-10.18</v>
+        <v>-10.42</v>
       </c>
       <c r="I191" t="n">
         <v>-1.11</v>
@@ -10710,7 +10732,7 @@
         <v>-25.46</v>
       </c>
       <c r="M191" t="n">
-        <v>-14.03</v>
+        <v>-13.05</v>
       </c>
       <c r="N191" t="b">
         <v>1</v>
@@ -10748,7 +10770,7 @@
         <v>42.4</v>
       </c>
       <c r="H192" t="n">
-        <v>-19.56</v>
+        <v>-27.08</v>
       </c>
       <c r="I192" t="n">
         <v>2.16</v>
@@ -10763,7 +10785,7 @@
         <v>-15.76</v>
       </c>
       <c r="M192" t="n">
-        <v>-23.41</v>
+        <v>-29.7</v>
       </c>
       <c r="N192" t="b">
         <v>1</v>
@@ -10801,7 +10823,7 @@
         <v>28.2</v>
       </c>
       <c r="H193" t="n">
-        <v>-13.73</v>
+        <v>-26.13</v>
       </c>
       <c r="I193" t="n">
         <v>-1.71</v>
@@ -10816,7 +10838,7 @@
         <v>-23.43</v>
       </c>
       <c r="M193" t="n">
-        <v>-17.57</v>
+        <v>-28.76</v>
       </c>
       <c r="N193" t="b">
         <v>1</v>
@@ -10854,7 +10876,7 @@
         <v>28.6</v>
       </c>
       <c r="H194" t="n">
-        <v>-3.11</v>
+        <v>-18.29</v>
       </c>
       <c r="I194" t="n">
         <v>2.81</v>
@@ -10869,7 +10891,7 @@
         <v>-18.87</v>
       </c>
       <c r="M194" t="n">
-        <v>-6.96</v>
+        <v>-20.91</v>
       </c>
       <c r="N194" t="b">
         <v>1</v>
@@ -10907,7 +10929,7 @@
         <v>89.09999999999999</v>
       </c>
       <c r="H195" t="n">
-        <v>23.33</v>
+        <v>14.98</v>
       </c>
       <c r="I195" t="n">
         <v>18.45</v>
@@ -10922,7 +10944,7 @@
         <v>-9.029999999999999</v>
       </c>
       <c r="M195" t="n">
-        <v>19.49</v>
+        <v>12.35</v>
       </c>
       <c r="N195" t="b">
         <v>0</v>
@@ -10960,7 +10982,7 @@
         <v>50.5</v>
       </c>
       <c r="H196" t="n">
-        <v>-9.91</v>
+        <v>-17.15</v>
       </c>
       <c r="I196" t="n">
         <v>-2.26</v>
@@ -10975,7 +10997,7 @@
         <v>-20.74</v>
       </c>
       <c r="M196" t="n">
-        <v>-13.76</v>
+        <v>-19.77</v>
       </c>
       <c r="N196" t="b">
         <v>0</v>
@@ -11013,7 +11035,7 @@
         <v>33.1</v>
       </c>
       <c r="H197" t="n">
-        <v>4.83</v>
+        <v>-7.27</v>
       </c>
       <c r="I197" t="n">
         <v>4.68</v>
@@ -11028,7 +11050,7 @@
         <v>-26.7</v>
       </c>
       <c r="M197" t="n">
-        <v>0.98</v>
+        <v>-9.890000000000001</v>
       </c>
       <c r="N197" t="b">
         <v>0</v>
@@ -11066,7 +11088,7 @@
         <v>46.3</v>
       </c>
       <c r="H198" t="n">
-        <v>-27.54</v>
+        <v>-33.45</v>
       </c>
       <c r="I198" t="n">
         <v>-3.24</v>
@@ -11081,7 +11103,7 @@
         <v>-22.77</v>
       </c>
       <c r="M198" t="n">
-        <v>-31.39</v>
+        <v>-36.07</v>
       </c>
       <c r="N198" t="b">
         <v>0</v>
@@ -11119,7 +11141,7 @@
         <v>-13.8</v>
       </c>
       <c r="H199" t="n">
-        <v>5.7</v>
+        <v>8.84</v>
       </c>
       <c r="I199" t="n">
         <v>6.03</v>
@@ -11134,7 +11156,7 @@
         <v>-13.77</v>
       </c>
       <c r="M199" t="n">
-        <v>1.86</v>
+        <v>6.21</v>
       </c>
       <c r="N199" t="b">
         <v>0</v>
@@ -11172,7 +11194,7 @@
         <v>21.8</v>
       </c>
       <c r="H200" t="n">
-        <v>-27.95</v>
+        <v>-47.88</v>
       </c>
       <c r="I200" t="n">
         <v>-6.34</v>
@@ -11187,7 +11209,7 @@
         <v>-30.04</v>
       </c>
       <c r="M200" t="n">
-        <v>-31.8</v>
+        <v>-50.51</v>
       </c>
       <c r="N200" t="b">
         <v>1</v>
@@ -11225,7 +11247,7 @@
         <v>40.3</v>
       </c>
       <c r="H201" t="n">
-        <v>-31.09</v>
+        <v>-38.73</v>
       </c>
       <c r="I201" t="n">
         <v>1.24</v>
@@ -11240,7 +11262,7 @@
         <v>-20.5</v>
       </c>
       <c r="M201" t="n">
-        <v>-34.94</v>
+        <v>-41.35</v>
       </c>
       <c r="N201" t="b">
         <v>0</v>
@@ -11278,7 +11300,7 @@
         <v>36.6</v>
       </c>
       <c r="H202" t="n">
-        <v>313.06</v>
+        <v>240.5</v>
       </c>
       <c r="I202" t="n">
         <v>-4.23</v>
@@ -11293,7 +11315,7 @@
         <v>-11.51</v>
       </c>
       <c r="M202" t="n">
-        <v>309.21</v>
+        <v>237.88</v>
       </c>
       <c r="N202" t="b">
         <v>0</v>
@@ -11331,7 +11353,7 @@
         <v>24.1</v>
       </c>
       <c r="H203" t="n">
-        <v>-14.07</v>
+        <v>-21.91</v>
       </c>
       <c r="I203" t="n">
         <v>-1.6</v>
@@ -11346,7 +11368,7 @@
         <v>-22.54</v>
       </c>
       <c r="M203" t="n">
-        <v>-17.92</v>
+        <v>-24.53</v>
       </c>
       <c r="N203" t="b">
         <v>1</v>
@@ -11384,7 +11406,7 @@
         <v>50.3</v>
       </c>
       <c r="H204" t="n">
-        <v>-31.61</v>
+        <v>-38.88</v>
       </c>
       <c r="I204" t="n">
         <v>-3.34</v>
@@ -11399,7 +11421,7 @@
         <v>-23.32</v>
       </c>
       <c r="M204" t="n">
-        <v>-35.46</v>
+        <v>-41.5</v>
       </c>
       <c r="N204" t="b">
         <v>0</v>
@@ -11437,7 +11459,7 @@
         <v>24.5</v>
       </c>
       <c r="H205" t="n">
-        <v>-29.93</v>
+        <v>-35.65</v>
       </c>
       <c r="I205" t="n">
         <v>-12.99</v>
@@ -11452,7 +11474,7 @@
         <v>-22.54</v>
       </c>
       <c r="M205" t="n">
-        <v>-33.78</v>
+        <v>-38.28</v>
       </c>
       <c r="N205" t="b">
         <v>1</v>
@@ -11490,7 +11512,7 @@
         <v>-4</v>
       </c>
       <c r="H206" t="n">
-        <v>-34.76</v>
+        <v>-39.28</v>
       </c>
       <c r="I206" t="n">
         <v>-1.59</v>
@@ -11505,7 +11527,7 @@
         <v>-25.38</v>
       </c>
       <c r="M206" t="n">
-        <v>-38.61</v>
+        <v>-41.9</v>
       </c>
       <c r="N206" t="b">
         <v>0</v>
@@ -11543,7 +11565,7 @@
         <v>14.8</v>
       </c>
       <c r="H207" t="n">
-        <v>-33.62</v>
+        <v>-34.12</v>
       </c>
       <c r="I207" t="n">
         <v>-2.48</v>
@@ -11558,7 +11580,7 @@
         <v>-40.98</v>
       </c>
       <c r="M207" t="n">
-        <v>-37.47</v>
+        <v>-36.74</v>
       </c>
       <c r="N207" t="b">
         <v>0</v>
@@ -11596,7 +11618,7 @@
         <v>-27.6</v>
       </c>
       <c r="H208" t="n">
-        <v>-22.13</v>
+        <v>-25.41</v>
       </c>
       <c r="I208" t="n">
         <v>-0.36</v>
@@ -11611,7 +11633,7 @@
         <v>-19.41</v>
       </c>
       <c r="M208" t="n">
-        <v>-25.98</v>
+        <v>-28.03</v>
       </c>
       <c r="N208" t="b">
         <v>0</v>
@@ -11649,7 +11671,7 @@
         <v>9.1</v>
       </c>
       <c r="H209" t="n">
-        <v>-34.33</v>
+        <v>-41.74</v>
       </c>
       <c r="I209" t="n">
         <v>-2.83</v>
@@ -11664,7 +11686,7 @@
         <v>-23.78</v>
       </c>
       <c r="M209" t="n">
-        <v>-38.18</v>
+        <v>-44.36</v>
       </c>
       <c r="N209" t="b">
         <v>0</v>
@@ -11702,7 +11724,7 @@
         <v>11</v>
       </c>
       <c r="H210" t="n">
-        <v>-9.140000000000001</v>
+        <v>-18.87</v>
       </c>
       <c r="I210" t="n">
         <v>3.38</v>
@@ -11717,7 +11739,7 @@
         <v>-18.71</v>
       </c>
       <c r="M210" t="n">
-        <v>-12.99</v>
+        <v>-21.5</v>
       </c>
       <c r="N210" t="b">
         <v>0</v>
@@ -11755,7 +11777,7 @@
         <v>31.2</v>
       </c>
       <c r="H211" t="n">
-        <v>-25.71</v>
+        <v>-32.8</v>
       </c>
       <c r="I211" t="n">
         <v>-11.26</v>
@@ -11770,7 +11792,7 @@
         <v>-22.9</v>
       </c>
       <c r="M211" t="n">
-        <v>-29.56</v>
+        <v>-35.43</v>
       </c>
       <c r="N211" t="b">
         <v>0</v>
@@ -11808,7 +11830,7 @@
         <v>19.3</v>
       </c>
       <c r="H212" t="n">
-        <v>-4.26</v>
+        <v>-14.44</v>
       </c>
       <c r="I212" t="n">
         <v>11.79</v>
@@ -11823,7 +11845,7 @@
         <v>-16.62</v>
       </c>
       <c r="M212" t="n">
-        <v>-8.109999999999999</v>
+        <v>-17.06</v>
       </c>
       <c r="N212" t="b">
         <v>0</v>
@@ -11861,7 +11883,7 @@
         <v>-8.699999999999999</v>
       </c>
       <c r="H213" t="n">
-        <v>-10.76</v>
+        <v>-6.2</v>
       </c>
       <c r="I213" t="n">
         <v>17.25</v>
@@ -11876,7 +11898,7 @@
         <v>-4.65</v>
       </c>
       <c r="M213" t="n">
-        <v>-14.61</v>
+        <v>-8.82</v>
       </c>
       <c r="N213" t="b">
         <v>1</v>
@@ -11914,7 +11936,7 @@
         <v>15.2</v>
       </c>
       <c r="H214" t="n">
-        <v>-22.69</v>
+        <v>-32.36</v>
       </c>
       <c r="I214" t="n">
         <v>5.36</v>
@@ -11929,7 +11951,7 @@
         <v>-28.18</v>
       </c>
       <c r="M214" t="n">
-        <v>-26.54</v>
+        <v>-34.99</v>
       </c>
       <c r="N214" t="b">
         <v>0</v>
@@ -11967,7 +11989,7 @@
         <v>37.2</v>
       </c>
       <c r="H215" t="n">
-        <v>-37.72</v>
+        <v>-43.48</v>
       </c>
       <c r="I215" t="n">
         <v>-7.64</v>
@@ -11982,7 +12004,7 @@
         <v>-26.24</v>
       </c>
       <c r="M215" t="n">
-        <v>-41.56</v>
+        <v>-46.1</v>
       </c>
       <c r="N215" t="b">
         <v>1</v>
@@ -12024,7 +12046,7 @@
         <v>-0.5</v>
       </c>
       <c r="H216" t="n">
-        <v>46.04</v>
+        <v>47.59</v>
       </c>
       <c r="I216" t="n">
         <v>12.75</v>
@@ -12039,7 +12061,7 @@
         <v>-4.72</v>
       </c>
       <c r="M216" t="n">
-        <v>42.19</v>
+        <v>44.97</v>
       </c>
       <c r="N216" t="b">
         <v>0</v>
@@ -12077,7 +12099,7 @@
         <v>-27.9</v>
       </c>
       <c r="H217" t="n">
-        <v>-54.65</v>
+        <v>-54.74</v>
       </c>
       <c r="I217" t="n">
         <v>-5.72</v>
@@ -12092,7 +12114,7 @@
         <v>-11.08</v>
       </c>
       <c r="M217" t="n">
-        <v>-58.5</v>
+        <v>-57.36</v>
       </c>
       <c r="N217" t="b">
         <v>0</v>
@@ -12130,7 +12152,7 @@
         <v>29.8</v>
       </c>
       <c r="H218" t="n">
-        <v>6.65</v>
+        <v>-5.78</v>
       </c>
       <c r="I218" t="n">
         <v>-2.74</v>
@@ -12145,7 +12167,7 @@
         <v>-22.36</v>
       </c>
       <c r="M218" t="n">
-        <v>2.8</v>
+        <v>-8.41</v>
       </c>
       <c r="N218" t="b">
         <v>1</v>
@@ -12183,7 +12205,7 @@
         <v>60.9</v>
       </c>
       <c r="H219" t="n">
-        <v>-4.51</v>
+        <v>-5.5</v>
       </c>
       <c r="I219" t="n">
         <v>6.71</v>
@@ -12198,7 +12220,7 @@
         <v>-4.9</v>
       </c>
       <c r="M219" t="n">
-        <v>-8.359999999999999</v>
+        <v>-8.119999999999999</v>
       </c>
       <c r="N219" t="b">
         <v>0</v>
@@ -12236,7 +12258,7 @@
         <v>-13.4</v>
       </c>
       <c r="H220" t="n">
-        <v>-39.47</v>
+        <v>-42.25</v>
       </c>
       <c r="I220" t="n">
         <v>0.79</v>
@@ -12251,7 +12273,7 @@
         <v>-15.41</v>
       </c>
       <c r="M220" t="n">
-        <v>-43.32</v>
+        <v>-44.87</v>
       </c>
       <c r="N220" t="b">
         <v>0</v>
@@ -12289,7 +12311,7 @@
         <v>18.2</v>
       </c>
       <c r="H221" t="n">
-        <v>-15.5</v>
+        <v>-19.57</v>
       </c>
       <c r="I221" t="n">
         <v>-11.28</v>
@@ -12304,7 +12326,7 @@
         <v>-16.87</v>
       </c>
       <c r="M221" t="n">
-        <v>-19.35</v>
+        <v>-22.19</v>
       </c>
       <c r="N221" t="b">
         <v>0</v>
@@ -12342,7 +12364,7 @@
         <v>31.2</v>
       </c>
       <c r="H222" t="n">
-        <v>-20.43</v>
+        <v>-29.79</v>
       </c>
       <c r="I222" t="n">
         <v>-3.17</v>
@@ -12357,7 +12379,7 @@
         <v>-23.66</v>
       </c>
       <c r="M222" t="n">
-        <v>-24.28</v>
+        <v>-32.41</v>
       </c>
       <c r="N222" t="b">
         <v>0</v>
@@ -12395,7 +12417,7 @@
         <v>-1.3</v>
       </c>
       <c r="H223" t="n">
-        <v>-19.36</v>
+        <v>-20.97</v>
       </c>
       <c r="I223" t="n">
         <v>5.29</v>
@@ -12410,7 +12432,7 @@
         <v>-11.87</v>
       </c>
       <c r="M223" t="n">
-        <v>-23.21</v>
+        <v>-23.59</v>
       </c>
       <c r="N223" t="b">
         <v>0</v>
@@ -12448,7 +12470,7 @@
         <v>-29.8</v>
       </c>
       <c r="H224" t="n">
-        <v>45.78</v>
+        <v>38.2</v>
       </c>
       <c r="I224" t="n">
         <v>29.88</v>
@@ -12463,7 +12485,7 @@
         <v>-0.29</v>
       </c>
       <c r="M224" t="n">
-        <v>41.93</v>
+        <v>35.57</v>
       </c>
       <c r="N224" t="b">
         <v>0</v>
@@ -12501,7 +12523,7 @@
         <v>-22.4</v>
       </c>
       <c r="H225" t="n">
-        <v>-17.45</v>
+        <v>-16.78</v>
       </c>
       <c r="I225" t="n">
         <v>5.79</v>
@@ -12516,7 +12538,7 @@
         <v>-9.67</v>
       </c>
       <c r="M225" t="n">
-        <v>-21.29</v>
+        <v>-19.4</v>
       </c>
       <c r="N225" t="b">
         <v>0</v>
@@ -12554,7 +12576,7 @@
         <v>19.3</v>
       </c>
       <c r="H226" t="n">
-        <v>-34.67</v>
+        <v>-41.66</v>
       </c>
       <c r="I226" t="n">
         <v>-16.69</v>
@@ -12569,7 +12591,7 @@
         <v>-36.39</v>
       </c>
       <c r="M226" t="n">
-        <v>-38.52</v>
+        <v>-44.28</v>
       </c>
       <c r="N226" t="b">
         <v>1</v>
@@ -12607,7 +12629,7 @@
         <v>7.6</v>
       </c>
       <c r="H227" t="n">
-        <v>-30.93</v>
+        <v>-36.5</v>
       </c>
       <c r="I227" t="n">
         <v>6.22</v>
@@ -12622,7 +12644,7 @@
         <v>-10.68</v>
       </c>
       <c r="M227" t="n">
-        <v>-34.78</v>
+        <v>-39.12</v>
       </c>
       <c r="N227" t="b">
         <v>0</v>
@@ -12660,7 +12682,7 @@
         <v>68.8</v>
       </c>
       <c r="H228" t="n">
-        <v>5.08</v>
+        <v>-3.44</v>
       </c>
       <c r="I228" t="n">
         <v>-1.41</v>
@@ -12675,7 +12697,7 @@
         <v>-19.39</v>
       </c>
       <c r="M228" t="n">
-        <v>1.23</v>
+        <v>-6.06</v>
       </c>
       <c r="N228" t="b">
         <v>0</v>
@@ -12713,7 +12735,7 @@
         <v>8.5</v>
       </c>
       <c r="H229" t="n">
-        <v>-40.88</v>
+        <v>-44.93</v>
       </c>
       <c r="I229" t="n">
         <v>-4.26</v>
@@ -12728,7 +12750,7 @@
         <v>-23.85</v>
       </c>
       <c r="M229" t="n">
-        <v>-44.73</v>
+        <v>-47.55</v>
       </c>
       <c r="N229" t="b">
         <v>0</v>
@@ -12766,7 +12788,7 @@
         <v>-15.2</v>
       </c>
       <c r="H230" t="n">
-        <v>-19.1</v>
+        <v>-22.79</v>
       </c>
       <c r="I230" t="n">
         <v>12.27</v>
@@ -12781,7 +12803,7 @@
         <v>-12.27</v>
       </c>
       <c r="M230" t="n">
-        <v>-22.95</v>
+        <v>-25.41</v>
       </c>
       <c r="N230" t="b">
         <v>0</v>
@@ -12819,7 +12841,7 @@
         <v>-33.1</v>
       </c>
       <c r="H231" t="n">
-        <v>-13.99</v>
+        <v>-13.33</v>
       </c>
       <c r="I231" t="n">
         <v>-13.13</v>
@@ -12834,7 +12856,7 @@
         <v>-21.04</v>
       </c>
       <c r="M231" t="n">
-        <v>-17.84</v>
+        <v>-15.95</v>
       </c>
       <c r="N231" t="b">
         <v>0</v>
@@ -12872,7 +12894,7 @@
         <v>11.8</v>
       </c>
       <c r="H232" t="n">
-        <v>-1.29</v>
+        <v>-16.95</v>
       </c>
       <c r="I232" t="n">
         <v>-1.19</v>
@@ -12887,7 +12909,7 @@
         <v>-17.57</v>
       </c>
       <c r="M232" t="n">
-        <v>-5.14</v>
+        <v>-19.57</v>
       </c>
       <c r="N232" t="b">
         <v>1</v>
@@ -12925,7 +12947,7 @@
         <v>27.5</v>
       </c>
       <c r="H233" t="n">
-        <v>3.41</v>
+        <v>1.74</v>
       </c>
       <c r="I233" t="n">
         <v>8.42</v>
@@ -12940,7 +12962,7 @@
         <v>-2.51</v>
       </c>
       <c r="M233" t="n">
-        <v>-0.44</v>
+        <v>-0.88</v>
       </c>
       <c r="N233" t="b">
         <v>1</v>
@@ -12978,7 +13000,7 @@
         <v>-22.4</v>
       </c>
       <c r="H234" t="n">
-        <v>-5.43</v>
+        <v>-0.31</v>
       </c>
       <c r="I234" t="n">
         <v>9.42</v>
@@ -12993,7 +13015,7 @@
         <v>-2.79</v>
       </c>
       <c r="M234" t="n">
-        <v>-9.279999999999999</v>
+        <v>-2.94</v>
       </c>
       <c r="N234" t="b">
         <v>0</v>
@@ -13031,7 +13053,7 @@
         <v>-14.7</v>
       </c>
       <c r="H235" t="n">
-        <v>-21.26</v>
+        <v>-15.16</v>
       </c>
       <c r="I235" t="n">
         <v>10.3</v>
@@ -13046,7 +13068,7 @@
         <v>-2.6</v>
       </c>
       <c r="M235" t="n">
-        <v>-25.11</v>
+        <v>-17.78</v>
       </c>
       <c r="N235" t="b">
         <v>1</v>
@@ -13088,7 +13110,7 @@
         <v>-9.300000000000001</v>
       </c>
       <c r="H236" t="n">
-        <v>-21.54</v>
+        <v>-20.23</v>
       </c>
       <c r="I236" t="n">
         <v>10.42</v>
@@ -13103,7 +13125,7 @@
         <v>-21.72</v>
       </c>
       <c r="M236" t="n">
-        <v>-25.39</v>
+        <v>-22.86</v>
       </c>
       <c r="N236" t="b">
         <v>1</v>
@@ -13141,7 +13163,7 @@
         <v>-13.5</v>
       </c>
       <c r="H237" t="n">
-        <v>141.42</v>
+        <v>138.91</v>
       </c>
       <c r="I237" t="n">
         <v>18.09</v>
@@ -13156,7 +13178,7 @@
         <v>-14.35</v>
       </c>
       <c r="M237" t="n">
-        <v>137.57</v>
+        <v>136.29</v>
       </c>
       <c r="N237" t="b">
         <v>0</v>
@@ -13194,7 +13216,7 @@
         <v>-27.5</v>
       </c>
       <c r="H238" t="n">
-        <v>-0.51</v>
+        <v>2.16</v>
       </c>
       <c r="I238" t="n">
         <v>-29.95</v>
@@ -13209,7 +13231,7 @@
         <v>-35.86</v>
       </c>
       <c r="M238" t="n">
-        <v>-4.36</v>
+        <v>-0.46</v>
       </c>
       <c r="N238" t="b">
         <v>0</v>
@@ -13247,7 +13269,7 @@
         <v>11.9</v>
       </c>
       <c r="H239" t="n">
-        <v>-56.55</v>
+        <v>-60.41</v>
       </c>
       <c r="I239" t="n">
         <v>-3.02</v>
@@ -13262,7 +13284,7 @@
         <v>-24.96</v>
       </c>
       <c r="M239" t="n">
-        <v>-60.4</v>
+        <v>-63.03</v>
       </c>
       <c r="N239" t="b">
         <v>0</v>
@@ -13300,7 +13322,7 @@
         <v>5</v>
       </c>
       <c r="H240" t="n">
-        <v>-6.71</v>
+        <v>-13.65</v>
       </c>
       <c r="I240" t="n">
         <v>0.41</v>
@@ -13315,7 +13337,7 @@
         <v>-13.87</v>
       </c>
       <c r="M240" t="n">
-        <v>-10.55</v>
+        <v>-16.27</v>
       </c>
       <c r="N240" t="b">
         <v>0</v>
@@ -13353,7 +13375,7 @@
         <v>-35.9</v>
       </c>
       <c r="H241" t="n">
-        <v>5.54</v>
+        <v>2.6</v>
       </c>
       <c r="I241" t="n">
         <v>18.67</v>
@@ -13368,7 +13390,7 @@
         <v>-6.77</v>
       </c>
       <c r="M241" t="n">
-        <v>1.69</v>
+        <v>-0.02</v>
       </c>
       <c r="N241" t="b">
         <v>0</v>
@@ -13406,7 +13428,7 @@
         <v>-25.2</v>
       </c>
       <c r="H242" t="n">
-        <v>-17.58</v>
+        <v>-25.87</v>
       </c>
       <c r="I242" t="n">
         <v>22.53</v>
@@ -13421,7 +13443,7 @@
         <v>-19.27</v>
       </c>
       <c r="M242" t="n">
-        <v>-21.42</v>
+        <v>-28.49</v>
       </c>
       <c r="N242" t="b">
         <v>0</v>
@@ -13459,7 +13481,7 @@
         <v>5.1</v>
       </c>
       <c r="H243" t="n">
-        <v>12.95</v>
+        <v>18.14</v>
       </c>
       <c r="I243" t="n">
         <v>8.77</v>
@@ -13474,7 +13496,7 @@
         <v>-3.54</v>
       </c>
       <c r="M243" t="n">
-        <v>9.109999999999999</v>
+        <v>15.51</v>
       </c>
       <c r="N243" t="b">
         <v>1</v>
@@ -13512,7 +13534,7 @@
         <v>20.8</v>
       </c>
       <c r="H244" t="n">
-        <v>-29.98</v>
+        <v>-35.44</v>
       </c>
       <c r="I244" t="n">
         <v>-10.93</v>
@@ -13527,7 +13549,7 @@
         <v>-27.1</v>
       </c>
       <c r="M244" t="n">
-        <v>-33.83</v>
+        <v>-38.07</v>
       </c>
       <c r="N244" t="b">
         <v>0</v>
@@ -13565,7 +13587,7 @@
         <v>-27.7</v>
       </c>
       <c r="H245" t="n">
-        <v>5.47</v>
+        <v>0.71</v>
       </c>
       <c r="I245" t="n">
         <v>-10.22</v>
@@ -13580,7 +13602,7 @@
         <v>-17.14</v>
       </c>
       <c r="M245" t="n">
-        <v>1.63</v>
+        <v>-1.91</v>
       </c>
       <c r="N245" t="b">
         <v>0</v>
@@ -13618,7 +13640,7 @@
         <v>-24.7</v>
       </c>
       <c r="H246" t="n">
-        <v>-15.42</v>
+        <v>-17.43</v>
       </c>
       <c r="I246" t="n">
         <v>1.65</v>
@@ -13633,7 +13655,7 @@
         <v>-19.04</v>
       </c>
       <c r="M246" t="n">
-        <v>-19.27</v>
+        <v>-20.05</v>
       </c>
       <c r="N246" t="b">
         <v>0</v>
@@ -13671,7 +13693,7 @@
         <v>-34.9</v>
       </c>
       <c r="H247" t="n">
-        <v>-15.98</v>
+        <v>-12.45</v>
       </c>
       <c r="I247" t="n">
         <v>19.9</v>
@@ -13686,7 +13708,7 @@
         <v>-12.62</v>
       </c>
       <c r="M247" t="n">
-        <v>-19.83</v>
+        <v>-15.07</v>
       </c>
       <c r="N247" t="b">
         <v>0</v>
@@ -13724,7 +13746,7 @@
         <v>-29.5</v>
       </c>
       <c r="H248" t="n">
-        <v>-6.96</v>
+        <v>-7.2</v>
       </c>
       <c r="I248" t="n">
         <v>4.05</v>
@@ -13739,7 +13761,7 @@
         <v>-2.43</v>
       </c>
       <c r="M248" t="n">
-        <v>-10.81</v>
+        <v>-9.82</v>
       </c>
       <c r="N248" t="b">
         <v>0</v>
@@ -13777,7 +13799,7 @@
         <v>34.2</v>
       </c>
       <c r="H249" t="n">
-        <v>4.09</v>
+        <v>-0.53</v>
       </c>
       <c r="I249" t="n">
         <v>8.15</v>
@@ -13792,7 +13814,7 @@
         <v>-7.63</v>
       </c>
       <c r="M249" t="n">
-        <v>0.24</v>
+        <v>-3.15</v>
       </c>
       <c r="N249" t="b">
         <v>1</v>
@@ -13830,7 +13852,7 @@
         <v>42</v>
       </c>
       <c r="H250" t="n">
-        <v>-34.98</v>
+        <v>-48.38</v>
       </c>
       <c r="I250" t="n">
         <v>0.6</v>
@@ -13845,7 +13867,7 @@
         <v>-16.67</v>
       </c>
       <c r="M250" t="n">
-        <v>-38.83</v>
+        <v>-51</v>
       </c>
       <c r="N250" t="b">
         <v>1</v>
@@ -13887,7 +13909,7 @@
         <v>-0.4</v>
       </c>
       <c r="H251" t="n">
-        <v>2.69</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="I251" t="n">
         <v>4.83</v>
@@ -13902,7 +13924,7 @@
         <v>-10.75</v>
       </c>
       <c r="M251" t="n">
-        <v>-1.16</v>
+        <v>6</v>
       </c>
       <c r="N251" t="b">
         <v>0</v>
@@ -13940,7 +13962,7 @@
         <v>64.59999999999999</v>
       </c>
       <c r="H252" t="n">
-        <v>6.53</v>
+        <v>5.88</v>
       </c>
       <c r="I252" t="n">
         <v>3.01</v>
@@ -13955,7 +13977,7 @@
         <v>-12</v>
       </c>
       <c r="M252" t="n">
-        <v>2.68</v>
+        <v>3.25</v>
       </c>
       <c r="N252" t="b">
         <v>0</v>
@@ -13993,7 +14015,7 @@
         <v>-25.3</v>
       </c>
       <c r="H253" t="n">
-        <v>60.85</v>
+        <v>71.73999999999999</v>
       </c>
       <c r="I253" t="n">
         <v>36.1</v>
@@ -14008,7 +14030,7 @@
         <v>-5.66</v>
       </c>
       <c r="M253" t="n">
-        <v>57</v>
+        <v>69.12</v>
       </c>
       <c r="N253" t="b">
         <v>0</v>
@@ -14046,7 +14068,7 @@
         <v>-7.7</v>
       </c>
       <c r="H254" t="n">
-        <v>-13.67</v>
+        <v>-20.25</v>
       </c>
       <c r="I254" t="n">
         <v>-6.47</v>
@@ -14061,7 +14083,7 @@
         <v>-23.05</v>
       </c>
       <c r="M254" t="n">
-        <v>-17.52</v>
+        <v>-22.87</v>
       </c>
       <c r="N254" t="b">
         <v>1</v>
@@ -14099,7 +14121,7 @@
         <v>-2.9</v>
       </c>
       <c r="H255" t="n">
-        <v>-13.51</v>
+        <v>-11.32</v>
       </c>
       <c r="I255" t="n">
         <v>-1.47</v>
@@ -14114,7 +14136,7 @@
         <v>-7.7</v>
       </c>
       <c r="M255" t="n">
-        <v>-17.36</v>
+        <v>-13.95</v>
       </c>
       <c r="N255" t="b">
         <v>0</v>
@@ -14152,7 +14174,7 @@
         <v>13.7</v>
       </c>
       <c r="H256" t="n">
-        <v>4.97</v>
+        <v>-8.81</v>
       </c>
       <c r="I256" t="n">
         <v>2.74</v>
@@ -14167,7 +14189,7 @@
         <v>-24.02</v>
       </c>
       <c r="M256" t="n">
-        <v>1.12</v>
+        <v>-11.43</v>
       </c>
       <c r="N256" t="b">
         <v>1</v>
@@ -14205,7 +14227,7 @@
         <v>21.8</v>
       </c>
       <c r="H257" t="n">
-        <v>-26.36</v>
+        <v>-31.3</v>
       </c>
       <c r="I257" t="n">
         <v>18.32</v>
@@ -14220,7 +14242,7 @@
         <v>-23.27</v>
       </c>
       <c r="M257" t="n">
-        <v>-30.21</v>
+        <v>-33.92</v>
       </c>
       <c r="N257" t="b">
         <v>1</v>
@@ -14258,7 +14280,7 @@
         <v>29.4</v>
       </c>
       <c r="H258" t="n">
-        <v>-24.78</v>
+        <v>-32.73</v>
       </c>
       <c r="I258" t="n">
         <v>-2.62</v>
@@ -14273,7 +14295,7 @@
         <v>-27.18</v>
       </c>
       <c r="M258" t="n">
-        <v>-28.63</v>
+        <v>-35.35</v>
       </c>
       <c r="N258" t="b">
         <v>1</v>
@@ -14311,7 +14333,7 @@
         <v>-3.7</v>
       </c>
       <c r="H259" t="n">
-        <v>-27.66</v>
+        <v>-32.17</v>
       </c>
       <c r="I259" t="n">
         <v>-8.07</v>
@@ -14326,7 +14348,7 @@
         <v>-22.12</v>
       </c>
       <c r="M259" t="n">
-        <v>-31.5</v>
+        <v>-34.79</v>
       </c>
       <c r="N259" t="b">
         <v>1</v>
@@ -14364,7 +14386,7 @@
         <v>21.3</v>
       </c>
       <c r="H260" t="n">
-        <v>1.75</v>
+        <v>1.48</v>
       </c>
       <c r="I260" t="n">
         <v>0.23</v>
@@ -14379,7 +14401,7 @@
         <v>-0.85</v>
       </c>
       <c r="M260" t="n">
-        <v>-2.1</v>
+        <v>-1.14</v>
       </c>
       <c r="N260" t="b">
         <v>1</v>
@@ -14417,7 +14439,7 @@
         <v>-21.4</v>
       </c>
       <c r="H261" t="n">
-        <v>2.87</v>
+        <v>-4.13</v>
       </c>
       <c r="I261" t="n">
         <v>4.55</v>
@@ -14432,7 +14454,7 @@
         <v>-6.39</v>
       </c>
       <c r="M261" t="n">
-        <v>-0.98</v>
+        <v>-6.75</v>
       </c>
       <c r="N261" t="b">
         <v>1</v>
@@ -14470,7 +14492,7 @@
         <v>16.3</v>
       </c>
       <c r="H262" t="n">
-        <v>-17.89</v>
+        <v>-26.28</v>
       </c>
       <c r="I262" t="n">
         <v>-1</v>
@@ -14485,7 +14507,7 @@
         <v>-22.5</v>
       </c>
       <c r="M262" t="n">
-        <v>-21.73</v>
+        <v>-28.91</v>
       </c>
       <c r="N262" t="b">
         <v>1</v>
@@ -14523,7 +14545,7 @@
         <v>11.9</v>
       </c>
       <c r="H263" t="n">
-        <v>-10.94</v>
+        <v>-15.24</v>
       </c>
       <c r="I263" t="n">
         <v>7.74</v>
@@ -14538,7 +14560,7 @@
         <v>-9.43</v>
       </c>
       <c r="M263" t="n">
-        <v>-14.78</v>
+        <v>-17.86</v>
       </c>
       <c r="N263" t="b">
         <v>0</v>
@@ -14576,7 +14598,7 @@
         <v>19.4</v>
       </c>
       <c r="H264" t="n">
-        <v>3.97</v>
+        <v>0.59</v>
       </c>
       <c r="I264" t="n">
         <v>10.89</v>
@@ -14591,7 +14613,7 @@
         <v>-2.97</v>
       </c>
       <c r="M264" t="n">
-        <v>0.12</v>
+        <v>-2.03</v>
       </c>
       <c r="N264" t="b">
         <v>0</v>
@@ -14629,7 +14651,7 @@
         <v>66.7</v>
       </c>
       <c r="H265" t="n">
-        <v>-0.63</v>
+        <v>1.57</v>
       </c>
       <c r="I265" t="n">
         <v>4.84</v>
@@ -14644,7 +14666,7 @@
         <v>-11.7</v>
       </c>
       <c r="M265" t="n">
-        <v>-4.48</v>
+        <v>-1.05</v>
       </c>
       <c r="N265" t="b">
         <v>0</v>
@@ -14682,7 +14704,7 @@
         <v>3.7</v>
       </c>
       <c r="H266" t="n">
-        <v>30</v>
+        <v>36.32</v>
       </c>
       <c r="I266" t="n">
         <v>11.13</v>
@@ -14697,7 +14719,7 @@
         <v>-2.79</v>
       </c>
       <c r="M266" t="n">
-        <v>26.15</v>
+        <v>33.69</v>
       </c>
       <c r="N266" t="b">
         <v>0</v>
@@ -14735,7 +14757,7 @@
         <v>36.8</v>
       </c>
       <c r="H267" t="n">
-        <v>31.98</v>
+        <v>29.12</v>
       </c>
       <c r="I267" t="n">
         <v>15.47</v>
@@ -14750,7 +14772,7 @@
         <v>-0.96</v>
       </c>
       <c r="M267" t="n">
-        <v>28.13</v>
+        <v>26.5</v>
       </c>
       <c r="N267" t="b">
         <v>0</v>
@@ -14788,7 +14810,7 @@
         <v>0.2</v>
       </c>
       <c r="H268" t="n">
-        <v>22.49</v>
+        <v>23.12</v>
       </c>
       <c r="I268" t="n">
         <v>4.35</v>
@@ -14803,7 +14825,7 @@
         <v>-2.79</v>
       </c>
       <c r="M268" t="n">
-        <v>18.64</v>
+        <v>20.5</v>
       </c>
       <c r="N268" t="b">
         <v>1</v>
@@ -14841,7 +14863,7 @@
         <v>-31</v>
       </c>
       <c r="H269" t="n">
-        <v>-30.54</v>
+        <v>-34.15</v>
       </c>
       <c r="I269" t="n">
         <v>19.41</v>
@@ -14856,7 +14878,7 @@
         <v>-10.33</v>
       </c>
       <c r="M269" t="n">
-        <v>-34.39</v>
+        <v>-36.78</v>
       </c>
       <c r="N269" t="b">
         <v>0</v>
@@ -14898,7 +14920,7 @@
         <v>-2</v>
       </c>
       <c r="H270" t="n">
-        <v>2.82</v>
+        <v>2.73</v>
       </c>
       <c r="I270" t="n">
         <v>14.61</v>
@@ -14913,7 +14935,7 @@
         <v>-3.45</v>
       </c>
       <c r="M270" t="n">
-        <v>-1.03</v>
+        <v>0.11</v>
       </c>
       <c r="N270" t="b">
         <v>0</v>
@@ -14951,7 +14973,7 @@
         <v>12.2</v>
       </c>
       <c r="H271" t="n">
-        <v>-31.84</v>
+        <v>-30.18</v>
       </c>
       <c r="I271" t="n">
         <v>3.47</v>
@@ -14966,7 +14988,7 @@
         <v>-27.15</v>
       </c>
       <c r="M271" t="n">
-        <v>-35.69</v>
+        <v>-32.8</v>
       </c>
       <c r="N271" t="b">
         <v>0</v>
@@ -15004,7 +15026,7 @@
         <v>8.4</v>
       </c>
       <c r="H272" t="n">
-        <v>-42.87</v>
+        <v>-45.82</v>
       </c>
       <c r="I272" t="n">
         <v>-0.13</v>
@@ -15019,7 +15041,7 @@
         <v>-10.87</v>
       </c>
       <c r="M272" t="n">
-        <v>-46.72</v>
+        <v>-48.45</v>
       </c>
       <c r="N272" t="b">
         <v>1</v>
@@ -15057,7 +15079,7 @@
         <v>-21.7</v>
       </c>
       <c r="H273" t="n">
-        <v>-8.07</v>
+        <v>-12.65</v>
       </c>
       <c r="I273" t="n">
         <v>5.5</v>
@@ -15072,7 +15094,7 @@
         <v>-4.3</v>
       </c>
       <c r="M273" t="n">
-        <v>-11.92</v>
+        <v>-15.27</v>
       </c>
       <c r="N273" t="b">
         <v>0</v>
@@ -15110,7 +15132,7 @@
         <v>-7.3</v>
       </c>
       <c r="H274" t="n">
-        <v>-20.36</v>
+        <v>-24.39</v>
       </c>
       <c r="I274" t="n">
         <v>-4.12</v>
@@ -15125,7 +15147,7 @@
         <v>-15.02</v>
       </c>
       <c r="M274" t="n">
-        <v>-24.2</v>
+        <v>-27.01</v>
       </c>
       <c r="N274" t="b">
         <v>1</v>
@@ -15163,7 +15185,7 @@
         <v>-26.1</v>
       </c>
       <c r="H275" t="n">
-        <v>-25.42</v>
+        <v>-19.8</v>
       </c>
       <c r="I275" t="n">
         <v>5.05</v>
@@ -15178,7 +15200,7 @@
         <v>-9.27</v>
       </c>
       <c r="M275" t="n">
-        <v>-29.27</v>
+        <v>-22.43</v>
       </c>
       <c r="N275" t="b">
         <v>0</v>
@@ -15216,7 +15238,7 @@
         <v>-18.5</v>
       </c>
       <c r="H276" t="n">
-        <v>50.63</v>
+        <v>54.45</v>
       </c>
       <c r="I276" t="n">
         <v>16.22</v>
@@ -15231,7 +15253,7 @@
         <v>-9.960000000000001</v>
       </c>
       <c r="M276" t="n">
-        <v>46.79</v>
+        <v>51.83</v>
       </c>
       <c r="N276" t="b">
         <v>0</v>
@@ -15269,7 +15291,7 @@
         <v>15.3</v>
       </c>
       <c r="H277" t="n">
-        <v>-47.65</v>
+        <v>-50.38</v>
       </c>
       <c r="I277" t="n">
         <v>-21.4</v>
@@ -15284,7 +15306,7 @@
         <v>-26.97</v>
       </c>
       <c r="M277" t="n">
-        <v>-51.5</v>
+        <v>-53</v>
       </c>
       <c r="N277" t="b">
         <v>0</v>
@@ -15322,7 +15344,7 @@
         <v>26.1</v>
       </c>
       <c r="H278" t="n">
-        <v>-21.45</v>
+        <v>-28.29</v>
       </c>
       <c r="I278" t="n">
         <v>-0.51</v>
@@ -15337,7 +15359,7 @@
         <v>-16.45</v>
       </c>
       <c r="M278" t="n">
-        <v>-25.3</v>
+        <v>-30.91</v>
       </c>
       <c r="N278" t="b">
         <v>0</v>
@@ -15379,7 +15401,7 @@
         <v>-8.199999999999999</v>
       </c>
       <c r="H279" t="n">
-        <v>-24.76</v>
+        <v>-22.38</v>
       </c>
       <c r="I279" t="n">
         <v>17.48</v>
@@ -15394,7 +15416,7 @@
         <v>-10.68</v>
       </c>
       <c r="M279" t="n">
-        <v>-28.61</v>
+        <v>-25</v>
       </c>
       <c r="N279" t="b">
         <v>0</v>
@@ -15432,7 +15454,7 @@
         <v>17.9</v>
       </c>
       <c r="H280" t="n">
-        <v>-5.45</v>
+        <v>-15.01</v>
       </c>
       <c r="I280" t="n">
         <v>12.97</v>
@@ -15447,7 +15469,7 @@
         <v>-8.130000000000001</v>
       </c>
       <c r="M280" t="n">
-        <v>-9.300000000000001</v>
+        <v>-17.63</v>
       </c>
       <c r="N280" t="b">
         <v>1</v>
@@ -15485,7 +15507,7 @@
         <v>0.7</v>
       </c>
       <c r="H281" t="n">
-        <v>-23.78</v>
+        <v>-21.51</v>
       </c>
       <c r="I281" t="n">
         <v>14.96</v>
@@ -15500,7 +15522,7 @@
         <v>-8.039999999999999</v>
       </c>
       <c r="M281" t="n">
-        <v>-27.63</v>
+        <v>-24.13</v>
       </c>
       <c r="N281" t="b">
         <v>0</v>
@@ -15538,7 +15560,7 @@
         <v>61.6</v>
       </c>
       <c r="H282" t="n">
-        <v>5.64</v>
+        <v>-0.29</v>
       </c>
       <c r="I282" t="n">
         <v>11.47</v>
@@ -15553,7 +15575,7 @@
         <v>-12.86</v>
       </c>
       <c r="M282" t="n">
-        <v>1.8</v>
+        <v>-2.91</v>
       </c>
       <c r="N282" t="b">
         <v>0</v>
@@ -15591,7 +15613,7 @@
         <v>54.3</v>
       </c>
       <c r="H283" t="n">
-        <v>-24.67</v>
+        <v>-20.71</v>
       </c>
       <c r="I283" t="n">
         <v>-2.86</v>
@@ -15606,7 +15628,7 @@
         <v>-24.93</v>
       </c>
       <c r="M283" t="n">
-        <v>-28.51</v>
+        <v>-23.33</v>
       </c>
       <c r="N283" t="b">
         <v>0</v>
@@ -15644,7 +15666,7 @@
         <v>14.8</v>
       </c>
       <c r="H284" t="n">
-        <v>-8.31</v>
+        <v>-11.48</v>
       </c>
       <c r="I284" t="n">
         <v>0.35</v>
@@ -15659,7 +15681,7 @@
         <v>-3.68</v>
       </c>
       <c r="M284" t="n">
-        <v>-12.15</v>
+        <v>-14.1</v>
       </c>
       <c r="N284" t="b">
         <v>1</v>
@@ -15697,7 +15719,7 @@
         <v>-13.5</v>
       </c>
       <c r="H285" t="n">
-        <v>-14.68</v>
+        <v>-12.97</v>
       </c>
       <c r="I285" t="n">
         <v>-1.88</v>
@@ -15712,7 +15734,7 @@
         <v>-11.4</v>
       </c>
       <c r="M285" t="n">
-        <v>-18.53</v>
+        <v>-15.6</v>
       </c>
       <c r="N285" t="b">
         <v>0</v>
@@ -15750,7 +15772,7 @@
         <v>25.5</v>
       </c>
       <c r="H286" t="n">
-        <v>12.21</v>
+        <v>15.13</v>
       </c>
       <c r="I286" t="n">
         <v>-9.369999999999999</v>
@@ -15765,7 +15787,7 @@
         <v>-22.11</v>
       </c>
       <c r="M286" t="n">
-        <v>8.359999999999999</v>
+        <v>12.51</v>
       </c>
       <c r="N286" t="b">
         <v>1</v>
@@ -15807,7 +15829,7 @@
         <v>-7.5</v>
       </c>
       <c r="H287" t="n">
-        <v>-26.94</v>
+        <v>-29.05</v>
       </c>
       <c r="I287" t="n">
         <v>4.46</v>
@@ -15822,7 +15844,7 @@
         <v>-8.52</v>
       </c>
       <c r="M287" t="n">
-        <v>-30.79</v>
+        <v>-31.67</v>
       </c>
       <c r="N287" t="b">
         <v>1</v>
@@ -15860,7 +15882,7 @@
         <v>1.5</v>
       </c>
       <c r="H288" t="n">
-        <v>1.96</v>
+        <v>-0.98</v>
       </c>
       <c r="I288" t="n">
         <v>-7.31</v>
@@ -15875,7 +15897,7 @@
         <v>-18.58</v>
       </c>
       <c r="M288" t="n">
-        <v>-1.89</v>
+        <v>-3.6</v>
       </c>
       <c r="N288" t="b">
         <v>0</v>
@@ -15913,7 +15935,7 @@
         <v>-11</v>
       </c>
       <c r="H289" t="n">
-        <v>25.61</v>
+        <v>30.96</v>
       </c>
       <c r="I289" t="n">
         <v>10.7</v>
@@ -15928,7 +15950,7 @@
         <v>-9.43</v>
       </c>
       <c r="M289" t="n">
-        <v>21.76</v>
+        <v>28.34</v>
       </c>
       <c r="N289" t="b">
         <v>1</v>
@@ -15966,7 +15988,7 @@
         <v>-11.4</v>
       </c>
       <c r="H290" t="n">
-        <v>-20.7</v>
+        <v>-16.4</v>
       </c>
       <c r="I290" t="n">
         <v>4.36</v>
@@ -15981,7 +16003,7 @@
         <v>-11.36</v>
       </c>
       <c r="M290" t="n">
-        <v>-24.55</v>
+        <v>-19.02</v>
       </c>
       <c r="N290" t="b">
         <v>1</v>
@@ -16019,7 +16041,7 @@
         <v>2.1</v>
       </c>
       <c r="H291" t="n">
-        <v>80.04000000000001</v>
+        <v>88.04000000000001</v>
       </c>
       <c r="I291" t="n">
         <v>20.72</v>
@@ -16034,7 +16056,7 @@
         <v>-5.79</v>
       </c>
       <c r="M291" t="n">
-        <v>76.19</v>
+        <v>85.42</v>
       </c>
       <c r="N291" t="b">
         <v>0</v>
@@ -16072,7 +16094,7 @@
         <v>27.1</v>
       </c>
       <c r="H292" t="n">
-        <v>-17.97</v>
+        <v>-26.64</v>
       </c>
       <c r="I292" t="n">
         <v>5.02</v>
@@ -16087,7 +16109,7 @@
         <v>-14.35</v>
       </c>
       <c r="M292" t="n">
-        <v>-21.82</v>
+        <v>-29.26</v>
       </c>
       <c r="N292" t="b">
         <v>1</v>
@@ -16125,7 +16147,7 @@
         <v>-21.6</v>
       </c>
       <c r="H293" t="n">
-        <v>-20.59</v>
+        <v>-22.21</v>
       </c>
       <c r="I293" t="n">
         <v>1.22</v>
@@ -16140,7 +16162,7 @@
         <v>-6.54</v>
       </c>
       <c r="M293" t="n">
-        <v>-24.43</v>
+        <v>-24.83</v>
       </c>
       <c r="N293" t="b">
         <v>0</v>
@@ -16182,7 +16204,7 @@
         <v>-2.2</v>
       </c>
       <c r="H294" t="n">
-        <v>-0.86</v>
+        <v>-6.06</v>
       </c>
       <c r="I294" t="n">
         <v>-9.050000000000001</v>
@@ -16197,7 +16219,7 @@
         <v>-18.61</v>
       </c>
       <c r="M294" t="n">
-        <v>-4.71</v>
+        <v>-8.69</v>
       </c>
       <c r="N294" t="b">
         <v>0</v>
@@ -16235,7 +16257,7 @@
         <v>0.7</v>
       </c>
       <c r="H295" t="n">
-        <v>7.22</v>
+        <v>10.12</v>
       </c>
       <c r="I295" t="n">
         <v>11.4</v>
@@ -16250,7 +16272,7 @@
         <v>-7.28</v>
       </c>
       <c r="M295" t="n">
-        <v>3.37</v>
+        <v>7.49</v>
       </c>
       <c r="N295" t="b">
         <v>0</v>
@@ -16288,7 +16310,7 @@
         <v>-31.7</v>
       </c>
       <c r="H296" t="n">
-        <v>19.9</v>
+        <v>19.97</v>
       </c>
       <c r="I296" t="n">
         <v>17.04</v>
@@ -16303,7 +16325,7 @@
         <v>-4.05</v>
       </c>
       <c r="M296" t="n">
-        <v>16.05</v>
+        <v>17.35</v>
       </c>
       <c r="N296" t="b">
         <v>0</v>
@@ -16341,7 +16363,7 @@
         <v>32.2</v>
       </c>
       <c r="H297" t="n">
-        <v>7.61</v>
+        <v>2.42</v>
       </c>
       <c r="I297" t="n">
         <v>6.49</v>
@@ -16356,7 +16378,7 @@
         <v>-3.92</v>
       </c>
       <c r="M297" t="n">
-        <v>3.76</v>
+        <v>-0.2</v>
       </c>
       <c r="N297" t="b">
         <v>1</v>
@@ -16394,7 +16416,7 @@
         <v>3.2</v>
       </c>
       <c r="H298" t="n">
-        <v>-29.37</v>
+        <v>-34.64</v>
       </c>
       <c r="I298" t="n">
         <v>-10.41</v>
@@ -16409,7 +16431,7 @@
         <v>-23.7</v>
       </c>
       <c r="M298" t="n">
-        <v>-33.22</v>
+        <v>-37.26</v>
       </c>
       <c r="N298" t="b">
         <v>1</v>
@@ -16447,7 +16469,7 @@
         <v>7.3</v>
       </c>
       <c r="H299" t="n">
-        <v>4.01</v>
+        <v>7.46</v>
       </c>
       <c r="I299" t="n">
         <v>-0.57</v>
@@ -16462,7 +16484,7 @@
         <v>-5.89</v>
       </c>
       <c r="M299" t="n">
-        <v>0.16</v>
+        <v>4.84</v>
       </c>
       <c r="N299" t="b">
         <v>0</v>
@@ -16500,7 +16522,7 @@
         <v>24.5</v>
       </c>
       <c r="H300" t="n">
-        <v>13.44</v>
+        <v>10.66</v>
       </c>
       <c r="I300" t="n">
         <v>17.24</v>
@@ -16515,7 +16537,7 @@
         <v>-0.47</v>
       </c>
       <c r="M300" t="n">
-        <v>9.59</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="N300" t="b">
         <v>0</v>
@@ -16553,7 +16575,7 @@
         <v>-0.3</v>
       </c>
       <c r="H301" t="n">
-        <v>-14.58</v>
+        <v>-25.24</v>
       </c>
       <c r="I301" t="n">
         <v>17.76</v>
@@ -16568,7 +16590,7 @@
         <v>-14.18</v>
       </c>
       <c r="M301" t="n">
-        <v>-18.43</v>
+        <v>-27.87</v>
       </c>
       <c r="N301" t="b">
         <v>1</v>
@@ -16606,7 +16628,7 @@
         <v>4</v>
       </c>
       <c r="H302" t="n">
-        <v>65.3</v>
+        <v>62.56</v>
       </c>
       <c r="I302" t="n">
         <v>8.75</v>
@@ -16621,7 +16643,7 @@
         <v>-11.02</v>
       </c>
       <c r="M302" t="n">
-        <v>61.45</v>
+        <v>59.94</v>
       </c>
       <c r="N302" t="b">
         <v>0</v>
@@ -16659,7 +16681,7 @@
         <v>-6.8</v>
       </c>
       <c r="H303" t="n">
-        <v>33.3</v>
+        <v>33.58</v>
       </c>
       <c r="I303" t="n">
         <v>8.279999999999999</v>
@@ -16674,7 +16696,7 @@
         <v>-6.78</v>
       </c>
       <c r="M303" t="n">
-        <v>29.45</v>
+        <v>30.95</v>
       </c>
       <c r="N303" t="b">
         <v>0</v>
@@ -16712,7 +16734,7 @@
         <v>-42</v>
       </c>
       <c r="H304" t="n">
-        <v>51.5</v>
+        <v>43.91</v>
       </c>
       <c r="I304" t="n">
         <v>-3.61</v>
@@ -16727,7 +16749,7 @@
         <v>-11.94</v>
       </c>
       <c r="M304" t="n">
-        <v>47.65</v>
+        <v>41.29</v>
       </c>
       <c r="N304" t="b">
         <v>0</v>
@@ -16765,7 +16787,7 @@
         <v>14.6</v>
       </c>
       <c r="H305" t="n">
-        <v>-5.83</v>
+        <v>-13.46</v>
       </c>
       <c r="I305" t="n">
         <v>8.539999999999999</v>
@@ -16780,7 +16802,7 @@
         <v>-13.21</v>
       </c>
       <c r="M305" t="n">
-        <v>-9.68</v>
+        <v>-16.08</v>
       </c>
       <c r="N305" t="b">
         <v>0</v>
@@ -16818,7 +16840,7 @@
         <v>34.6</v>
       </c>
       <c r="H306" t="n">
-        <v>-4.57</v>
+        <v>-14.53</v>
       </c>
       <c r="I306" t="n">
         <v>5.7</v>
@@ -16833,7 +16855,7 @@
         <v>-7.7</v>
       </c>
       <c r="M306" t="n">
-        <v>-8.42</v>
+        <v>-17.15</v>
       </c>
       <c r="N306" t="b">
         <v>1</v>
@@ -16871,7 +16893,7 @@
         <v>-37.2</v>
       </c>
       <c r="H307" t="n">
-        <v>37.84</v>
+        <v>46.08</v>
       </c>
       <c r="I307" t="n">
         <v>21.67</v>
@@ -16886,7 +16908,7 @@
         <v>-6.64</v>
       </c>
       <c r="M307" t="n">
-        <v>33.99</v>
+        <v>43.45</v>
       </c>
       <c r="N307" t="b">
         <v>0</v>
@@ -16924,7 +16946,7 @@
         <v>-31.2</v>
       </c>
       <c r="H308" t="n">
-        <v>-24.67</v>
+        <v>-21.37</v>
       </c>
       <c r="I308" t="n">
         <v>1.03</v>
@@ -16939,7 +16961,7 @@
         <v>-13.65</v>
       </c>
       <c r="M308" t="n">
-        <v>-28.52</v>
+        <v>-23.99</v>
       </c>
       <c r="N308" t="b">
         <v>0</v>
@@ -16977,7 +16999,7 @@
         <v>10.4</v>
       </c>
       <c r="H309" t="n">
-        <v>26.6</v>
+        <v>25.59</v>
       </c>
       <c r="I309" t="n">
         <v>11.05</v>
@@ -16992,7 +17014,7 @@
         <v>-5.54</v>
       </c>
       <c r="M309" t="n">
-        <v>22.75</v>
+        <v>22.96</v>
       </c>
       <c r="N309" t="b">
         <v>1</v>
@@ -17030,7 +17052,7 @@
         <v>-14.7</v>
       </c>
       <c r="H310" t="n">
-        <v>7.47</v>
+        <v>6.38</v>
       </c>
       <c r="I310" t="n">
         <v>12.94</v>
@@ -17045,7 +17067,7 @@
         <v>-2.34</v>
       </c>
       <c r="M310" t="n">
-        <v>3.62</v>
+        <v>3.76</v>
       </c>
       <c r="N310" t="b">
         <v>0</v>
@@ -17083,7 +17105,7 @@
         <v>-21.5</v>
       </c>
       <c r="H311" t="n">
-        <v>-2.07</v>
+        <v>2.53</v>
       </c>
       <c r="I311" t="n">
         <v>10.65</v>
@@ -17098,7 +17120,7 @@
         <v>-6.89</v>
       </c>
       <c r="M311" t="n">
-        <v>-5.91</v>
+        <v>-0.1</v>
       </c>
       <c r="N311" t="b">
         <v>1</v>
@@ -17136,7 +17158,7 @@
         <v>20.2</v>
       </c>
       <c r="H312" t="n">
-        <v>-16.6</v>
+        <v>-20.67</v>
       </c>
       <c r="I312" t="n">
         <v>-1.23</v>
@@ -17151,7 +17173,7 @@
         <v>-12.56</v>
       </c>
       <c r="M312" t="n">
-        <v>-20.44</v>
+        <v>-23.29</v>
       </c>
       <c r="N312" t="b">
         <v>0</v>
@@ -17189,7 +17211,7 @@
         <v>3.5</v>
       </c>
       <c r="H313" t="n">
-        <v>67.81999999999999</v>
+        <v>66.75</v>
       </c>
       <c r="I313" t="n">
         <v>33.01</v>
@@ -17204,7 +17226,7 @@
         <v>-0.92</v>
       </c>
       <c r="M313" t="n">
-        <v>63.97</v>
+        <v>64.13</v>
       </c>
       <c r="N313" t="b">
         <v>1</v>
@@ -17242,7 +17264,7 @@
         <v>14</v>
       </c>
       <c r="H314" t="n">
-        <v>42.64</v>
+        <v>42.09</v>
       </c>
       <c r="I314" t="n">
         <v>2.89</v>
@@ -17257,7 +17279,7 @@
         <v>-1.94</v>
       </c>
       <c r="M314" t="n">
-        <v>38.79</v>
+        <v>39.47</v>
       </c>
       <c r="N314" t="b">
         <v>0</v>
@@ -17295,7 +17317,7 @@
         <v>19.8</v>
       </c>
       <c r="H315" t="n">
-        <v>4.77</v>
+        <v>-4.38</v>
       </c>
       <c r="I315" t="n">
         <v>4.74</v>
@@ -17310,7 +17332,7 @@
         <v>-9.9</v>
       </c>
       <c r="M315" t="n">
-        <v>0.92</v>
+        <v>-7</v>
       </c>
       <c r="N315" t="b">
         <v>0</v>
@@ -17352,7 +17374,7 @@
         <v>-7.4</v>
       </c>
       <c r="H316" t="n">
-        <v>16.79</v>
+        <v>23.82</v>
       </c>
       <c r="I316" t="n">
         <v>-3.85</v>
@@ -17367,7 +17389,7 @@
         <v>-21.11</v>
       </c>
       <c r="M316" t="n">
-        <v>12.94</v>
+        <v>21.2</v>
       </c>
       <c r="N316" t="b">
         <v>0</v>
@@ -17405,7 +17427,7 @@
         <v>-10.8</v>
       </c>
       <c r="H317" t="n">
-        <v>6.34</v>
+        <v>6.23</v>
       </c>
       <c r="I317" t="n">
         <v>1.78</v>
@@ -17420,7 +17442,7 @@
         <v>-7.51</v>
       </c>
       <c r="M317" t="n">
-        <v>2.5</v>
+        <v>3.61</v>
       </c>
       <c r="N317" t="b">
         <v>0</v>
@@ -17458,7 +17480,7 @@
         <v>-24</v>
       </c>
       <c r="H318" t="n">
-        <v>57.11</v>
+        <v>61.48</v>
       </c>
       <c r="I318" t="n">
         <v>10.85</v>
@@ -17473,7 +17495,7 @@
         <v>-5.43</v>
       </c>
       <c r="M318" t="n">
-        <v>53.26</v>
+        <v>58.86</v>
       </c>
       <c r="N318" t="b">
         <v>0</v>
@@ -17511,7 +17533,7 @@
         <v>-28.3</v>
       </c>
       <c r="H319" t="n">
-        <v>-29.28</v>
+        <v>-31.47</v>
       </c>
       <c r="I319" t="n">
         <v>-8.949999999999999</v>
@@ -17526,7 +17548,7 @@
         <v>-13.18</v>
       </c>
       <c r="M319" t="n">
-        <v>-33.13</v>
+        <v>-34.09</v>
       </c>
       <c r="N319" t="b">
         <v>0</v>
@@ -17564,7 +17586,7 @@
         <v>-30.5</v>
       </c>
       <c r="H320" t="n">
-        <v>-1.32</v>
+        <v>-1.15</v>
       </c>
       <c r="I320" t="n">
         <v>2.96</v>
@@ -17579,7 +17601,7 @@
         <v>-17.88</v>
       </c>
       <c r="M320" t="n">
-        <v>-5.17</v>
+        <v>-3.77</v>
       </c>
       <c r="N320" t="b">
         <v>1</v>
@@ -17617,7 +17639,7 @@
         <v>-6</v>
       </c>
       <c r="H321" t="n">
-        <v>-30.73</v>
+        <v>-38.2</v>
       </c>
       <c r="I321" t="n">
         <v>3.31</v>
@@ -17632,7 +17654,7 @@
         <v>-21.48</v>
       </c>
       <c r="M321" t="n">
-        <v>-34.58</v>
+        <v>-40.82</v>
       </c>
       <c r="N321" t="b">
         <v>1</v>
@@ -17670,7 +17692,7 @@
         <v>-42.2</v>
       </c>
       <c r="H322" t="n">
-        <v>-17.1</v>
+        <v>-16.97</v>
       </c>
       <c r="I322" t="n">
         <v>19.24</v>
@@ -17685,7 +17707,7 @@
         <v>-0.93</v>
       </c>
       <c r="M322" t="n">
-        <v>-20.95</v>
+        <v>-19.59</v>
       </c>
       <c r="N322" t="b">
         <v>0</v>
@@ -17723,7 +17745,7 @@
         <v>-34.6</v>
       </c>
       <c r="H323" t="n">
-        <v>20.79</v>
+        <v>27.95</v>
       </c>
       <c r="I323" t="n">
         <v>23.65</v>
@@ -17738,7 +17760,7 @@
         <v>-3.83</v>
       </c>
       <c r="M323" t="n">
-        <v>16.94</v>
+        <v>25.32</v>
       </c>
       <c r="N323" t="b">
         <v>1</v>
@@ -17776,7 +17798,7 @@
         <v>-48.1</v>
       </c>
       <c r="H324" t="n">
-        <v>-34.6</v>
+        <v>-36.3</v>
       </c>
       <c r="I324" t="n">
         <v>2.19</v>
@@ -17791,7 +17813,7 @@
         <v>-13.66</v>
       </c>
       <c r="M324" t="n">
-        <v>-38.45</v>
+        <v>-38.92</v>
       </c>
       <c r="N324" t="b">
         <v>0</v>
@@ -17829,7 +17851,7 @@
         <v>-16.2</v>
       </c>
       <c r="H325" t="n">
-        <v>6.42</v>
+        <v>2.16</v>
       </c>
       <c r="I325" t="n">
         <v>25.77</v>
@@ -17844,7 +17866,7 @@
         <v>-1.7</v>
       </c>
       <c r="M325" t="n">
-        <v>2.58</v>
+        <v>-0.46</v>
       </c>
       <c r="N325" t="b">
         <v>1</v>
@@ -17882,7 +17904,7 @@
         <v>-24.9</v>
       </c>
       <c r="H326" t="n">
-        <v>3.49</v>
+        <v>-5.06</v>
       </c>
       <c r="I326" t="n">
         <v>10.88</v>
@@ -17897,7 +17919,7 @@
         <v>-4.1</v>
       </c>
       <c r="M326" t="n">
-        <v>-0.36</v>
+        <v>-7.68</v>
       </c>
       <c r="N326" t="b">
         <v>1</v>
@@ -17939,7 +17961,7 @@
         <v>-8.1</v>
       </c>
       <c r="H327" t="n">
-        <v>24.38</v>
+        <v>24.46</v>
       </c>
       <c r="I327" t="n">
         <v>14.27</v>
@@ -17954,7 +17976,7 @@
         <v>-10.92</v>
       </c>
       <c r="M327" t="n">
-        <v>20.54</v>
+        <v>21.84</v>
       </c>
       <c r="N327" t="b">
         <v>1</v>
@@ -17992,7 +18014,7 @@
         <v>-10.2</v>
       </c>
       <c r="H328" t="n">
-        <v>-14.52</v>
+        <v>-8.720000000000001</v>
       </c>
       <c r="I328" t="n">
         <v>15.03</v>
@@ -18007,7 +18029,7 @@
         <v>-1.61</v>
       </c>
       <c r="M328" t="n">
-        <v>-18.36</v>
+        <v>-11.34</v>
       </c>
       <c r="N328" t="b">
         <v>1</v>
@@ -18045,7 +18067,7 @@
         <v>68.90000000000001</v>
       </c>
       <c r="H329" t="n">
-        <v>26.5</v>
+        <v>22.94</v>
       </c>
       <c r="I329" t="n">
         <v>1.84</v>
@@ -18060,7 +18082,7 @@
         <v>-10.43</v>
       </c>
       <c r="M329" t="n">
-        <v>22.65</v>
+        <v>20.32</v>
       </c>
       <c r="N329" t="b">
         <v>1</v>
@@ -18098,7 +18120,7 @@
         <v>-40.8</v>
       </c>
       <c r="H330" t="n">
-        <v>-27.63</v>
+        <v>-21.44</v>
       </c>
       <c r="I330" t="n">
         <v>21.71</v>
@@ -18113,7 +18135,7 @@
         <v>-3.3</v>
       </c>
       <c r="M330" t="n">
-        <v>-31.48</v>
+        <v>-24.06</v>
       </c>
       <c r="N330" t="b">
         <v>1</v>
@@ -18151,7 +18173,7 @@
         <v>-10.1</v>
       </c>
       <c r="H331" t="n">
-        <v>-11.72</v>
+        <v>-12.23</v>
       </c>
       <c r="I331" t="n">
         <v>1.83</v>
@@ -18166,7 +18188,7 @@
         <v>-3.45</v>
       </c>
       <c r="M331" t="n">
-        <v>-15.57</v>
+        <v>-14.85</v>
       </c>
       <c r="N331" t="b">
         <v>0</v>
@@ -18204,7 +18226,7 @@
         <v>40.7</v>
       </c>
       <c r="H332" t="n">
-        <v>31.82</v>
+        <v>25.37</v>
       </c>
       <c r="I332" t="n">
         <v>-4.08</v>
@@ -18219,7 +18241,7 @@
         <v>-11.2</v>
       </c>
       <c r="M332" t="n">
-        <v>27.98</v>
+        <v>22.75</v>
       </c>
       <c r="N332" t="b">
         <v>1</v>
@@ -18257,7 +18279,7 @@
         <v>25.7</v>
       </c>
       <c r="H333" t="n">
-        <v>-9.539999999999999</v>
+        <v>-14.91</v>
       </c>
       <c r="I333" t="n">
         <v>11.3</v>
@@ -18272,7 +18294,7 @@
         <v>-11.03</v>
       </c>
       <c r="M333" t="n">
-        <v>-13.39</v>
+        <v>-17.54</v>
       </c>
       <c r="N333" t="b">
         <v>1</v>
@@ -18310,7 +18332,7 @@
         <v>2.3</v>
       </c>
       <c r="H334" t="n">
-        <v>0.37</v>
+        <v>5.09</v>
       </c>
       <c r="I334" t="n">
         <v>-0.95</v>
@@ -18325,7 +18347,7 @@
         <v>-7.81</v>
       </c>
       <c r="M334" t="n">
-        <v>-3.48</v>
+        <v>2.47</v>
       </c>
       <c r="N334" t="b">
         <v>0</v>
@@ -18457,7 +18479,7 @@
         <v>51.4</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.34</v>
+        <v>-2.51</v>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
@@ -18466,7 +18488,7 @@
         <v>-7.85</v>
       </c>
       <c r="M2" t="n">
-        <v>0.21</v>
+        <v>-0.79</v>
       </c>
       <c r="N2" t="b">
         <v>1</v>
@@ -18504,7 +18526,7 @@
         <v>-16.6</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.75</v>
+        <v>0.46</v>
       </c>
       <c r="I3" t="n">
         <v>-0.75</v>
@@ -18512,10 +18534,10 @@
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="n">
-        <v>-1.39</v>
+        <v>-2.5</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.41</v>
+        <v>1.99</v>
       </c>
       <c r="N3" t="b">
         <v>1</v>
@@ -18553,7 +18575,7 @@
         <v>-5</v>
       </c>
       <c r="H4" t="n">
-        <v>12.26</v>
+        <v>16.42</v>
       </c>
       <c r="I4" t="n">
         <v>12.26</v>
@@ -18564,7 +18586,7 @@
         <v>-1.75</v>
       </c>
       <c r="M4" t="n">
-        <v>12.61</v>
+        <v>17.94</v>
       </c>
       <c r="N4" t="b">
         <v>1</v>
@@ -18602,7 +18624,7 @@
         <v>12.5</v>
       </c>
       <c r="H5" t="n">
-        <v>7.44</v>
+        <v>7.47</v>
       </c>
       <c r="I5" t="n">
         <v>7.44</v>
@@ -18613,7 +18635,7 @@
         <v>-2.59</v>
       </c>
       <c r="M5" t="n">
-        <v>7.79</v>
+        <v>9</v>
       </c>
       <c r="N5" t="b">
         <v>1</v>
@@ -18640,7 +18662,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Extended</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
@@ -18651,7 +18673,7 @@
         <v>-17.3</v>
       </c>
       <c r="H6" t="n">
-        <v>0.29</v>
+        <v>5.74</v>
       </c>
       <c r="I6" t="n">
         <v>1.16</v>
@@ -18662,7 +18684,7 @@
         <v>-6.51</v>
       </c>
       <c r="M6" t="n">
-        <v>0.9399999999999999</v>
+        <v>7.57</v>
       </c>
       <c r="N6" t="b">
         <v>1</v>
@@ -18700,7 +18722,7 @@
         <v>-21.8</v>
       </c>
       <c r="H7" t="n">
-        <v>0.25</v>
+        <v>3.29</v>
       </c>
       <c r="I7" t="n">
         <v>-3.37</v>
@@ -18711,7 +18733,7 @@
         <v>-5.33</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.62</v>
+        <v>3.61</v>
       </c>
       <c r="N7" t="b">
         <v>1</v>
@@ -18749,7 +18771,7 @@
         <v>-16.7</v>
       </c>
       <c r="H8" t="n">
-        <v>27.16</v>
+        <v>27.08</v>
       </c>
       <c r="I8" t="n">
         <v>26.03</v>
@@ -18760,7 +18782,7 @@
         <v>-6.98</v>
       </c>
       <c r="M8" t="n">
-        <v>26.34</v>
+        <v>27.46</v>
       </c>
       <c r="N8" t="b">
         <v>1</v>
@@ -18798,7 +18820,7 @@
         <v>-11.5</v>
       </c>
       <c r="H9" t="n">
-        <v>18.34</v>
+        <v>24.98</v>
       </c>
       <c r="I9" t="n">
         <v>7.47</v>
@@ -18809,7 +18831,7 @@
         <v>-0.99</v>
       </c>
       <c r="M9" t="n">
-        <v>17.52</v>
+        <v>25.36</v>
       </c>
       <c r="N9" t="b">
         <v>1</v>
@@ -18836,7 +18858,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Extended</t>
+          <t>Retired</t>
         </is>
       </c>
       <c r="E10" t="inlineStr"/>
@@ -18847,7 +18869,7 @@
         <v>0.1</v>
       </c>
       <c r="H10" t="n">
-        <v>18.54</v>
+        <v>22.82</v>
       </c>
       <c r="I10" t="n">
         <v>6.41</v>
@@ -18858,7 +18880,7 @@
         <v>-2.51</v>
       </c>
       <c r="M10" t="n">
-        <v>17.98</v>
+        <v>23.45</v>
       </c>
       <c r="N10" t="b">
         <v>1</v>
@@ -18885,7 +18907,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Retired</t>
         </is>
       </c>
       <c r="E11" t="inlineStr"/>
@@ -18896,7 +18918,7 @@
         <v>-31.6</v>
       </c>
       <c r="H11" t="n">
-        <v>-2.84</v>
+        <v>-2.06</v>
       </c>
       <c r="I11" t="n">
         <v>-2.12</v>
@@ -18907,7 +18929,7 @@
         <v>-8.140000000000001</v>
       </c>
       <c r="M11" t="n">
-        <v>-3.4</v>
+        <v>-1.43</v>
       </c>
       <c r="N11" t="b">
         <v>1</v>
@@ -18945,7 +18967,7 @@
         <v>-2.7</v>
       </c>
       <c r="H12" t="n">
-        <v>-9.199999999999999</v>
+        <v>-5.75</v>
       </c>
       <c r="I12" t="n">
         <v>-3.77</v>
@@ -18958,7 +18980,7 @@
         <v>-12.44</v>
       </c>
       <c r="M12" t="n">
-        <v>-9.08</v>
+        <v>-4.45</v>
       </c>
       <c r="N12" t="b">
         <v>1</v>
@@ -18996,7 +19018,7 @@
         <v>26.9</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.39</v>
+        <v>-1.11</v>
       </c>
       <c r="I13" t="n">
         <v>-3.24</v>
@@ -19009,7 +19031,7 @@
         <v>-12.88</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.27</v>
+        <v>0.19</v>
       </c>
       <c r="N13" t="b">
         <v>1</v>
@@ -19047,7 +19069,7 @@
         <v>-18.1</v>
       </c>
       <c r="H14" t="n">
-        <v>17.63</v>
+        <v>20.75</v>
       </c>
       <c r="I14" t="n">
         <v>4.46</v>
@@ -19060,7 +19082,7 @@
         <v>-2.69</v>
       </c>
       <c r="M14" t="n">
-        <v>16.74</v>
+        <v>21.05</v>
       </c>
       <c r="N14" t="b">
         <v>1</v>
@@ -19098,7 +19120,7 @@
         <v>-21.5</v>
       </c>
       <c r="H15" t="n">
-        <v>-2.87</v>
+        <v>3.39</v>
       </c>
       <c r="I15" t="n">
         <v>-1.68</v>
@@ -19111,7 +19133,7 @@
         <v>-8.130000000000001</v>
       </c>
       <c r="M15" t="n">
-        <v>-3.76</v>
+        <v>3.69</v>
       </c>
       <c r="N15" t="b">
         <v>1</v>
@@ -19149,7 +19171,7 @@
         <v>41.6</v>
       </c>
       <c r="H16" t="n">
-        <v>6.9</v>
+        <v>7.41</v>
       </c>
       <c r="I16" t="n">
         <v>3.43</v>
@@ -19162,7 +19184,7 @@
         <v>-4.38</v>
       </c>
       <c r="M16" t="n">
-        <v>5.35</v>
+        <v>7.06</v>
       </c>
       <c r="N16" t="b">
         <v>1</v>
@@ -19200,7 +19222,7 @@
         <v>32.1</v>
       </c>
       <c r="H17" t="n">
-        <v>11.51</v>
+        <v>14.51</v>
       </c>
       <c r="I17" t="n">
         <v>-3.47</v>
@@ -19213,7 +19235,7 @@
         <v>-6.94</v>
       </c>
       <c r="M17" t="n">
-        <v>9.970000000000001</v>
+        <v>14.16</v>
       </c>
       <c r="N17" t="b">
         <v>1</v>
@@ -19251,7 +19273,7 @@
         <v>-14.4</v>
       </c>
       <c r="H18" t="n">
-        <v>3.67</v>
+        <v>10.86</v>
       </c>
       <c r="I18" t="n">
         <v>-2.38</v>
@@ -19264,7 +19286,7 @@
         <v>-6.46</v>
       </c>
       <c r="M18" t="n">
-        <v>2.12</v>
+        <v>10.51</v>
       </c>
       <c r="N18" t="b">
         <v>1</v>
@@ -19302,7 +19324,7 @@
         <v>-10</v>
       </c>
       <c r="H19" t="n">
-        <v>-10.24</v>
+        <v>-10.95</v>
       </c>
       <c r="I19" t="n">
         <v>-3.29</v>
@@ -19315,7 +19337,7 @@
         <v>-14.66</v>
       </c>
       <c r="M19" t="n">
-        <v>-11.78</v>
+        <v>-11.3</v>
       </c>
       <c r="N19" t="b">
         <v>1</v>
@@ -19353,7 +19375,7 @@
         <v>6.4</v>
       </c>
       <c r="H20" t="n">
-        <v>16.43</v>
+        <v>21.8</v>
       </c>
       <c r="I20" t="n">
         <v>1.48</v>
@@ -19366,7 +19388,7 @@
         <v>-3.35</v>
       </c>
       <c r="M20" t="n">
-        <v>14.89</v>
+        <v>21.45</v>
       </c>
       <c r="N20" t="b">
         <v>1</v>
@@ -19404,7 +19426,7 @@
         <v>20.2</v>
       </c>
       <c r="H21" t="n">
-        <v>1.2</v>
+        <v>0.21</v>
       </c>
       <c r="I21" t="n">
         <v>3.45</v>
@@ -19417,7 +19439,7 @@
         <v>-1.07</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.76</v>
+        <v>-0.54</v>
       </c>
       <c r="N21" t="b">
         <v>1</v>
@@ -19455,7 +19477,7 @@
         <v>43.7</v>
       </c>
       <c r="H22" t="n">
-        <v>15.43</v>
+        <v>15.17</v>
       </c>
       <c r="I22" t="n">
         <v>3.16</v>
@@ -19468,7 +19490,7 @@
         <v>-2.44</v>
       </c>
       <c r="M22" t="n">
-        <v>13.47</v>
+        <v>14.41</v>
       </c>
       <c r="N22" t="b">
         <v>1</v>
@@ -19506,7 +19528,7 @@
         <v>1.9</v>
       </c>
       <c r="H23" t="n">
-        <v>-3.81</v>
+        <v>0.72</v>
       </c>
       <c r="I23" t="n">
         <v>-10.64</v>
@@ -19519,7 +19541,7 @@
         <v>-14.75</v>
       </c>
       <c r="M23" t="n">
-        <v>-5.77</v>
+        <v>-0.04</v>
       </c>
       <c r="N23" t="b">
         <v>1</v>
@@ -19557,7 +19579,7 @@
         <v>37.5</v>
       </c>
       <c r="H24" t="n">
-        <v>23.93</v>
+        <v>22.06</v>
       </c>
       <c r="I24" t="n">
         <v>5.86</v>
@@ -19570,7 +19592,7 @@
         <v>-3.95</v>
       </c>
       <c r="M24" t="n">
-        <v>21.82</v>
+        <v>21.16</v>
       </c>
       <c r="N24" t="b">
         <v>1</v>
@@ -19608,7 +19630,7 @@
         <v>40.2</v>
       </c>
       <c r="H25" t="n">
-        <v>9.470000000000001</v>
+        <v>8.58</v>
       </c>
       <c r="I25" t="n">
         <v>-1.11</v>
@@ -19621,7 +19643,7 @@
         <v>-5.29</v>
       </c>
       <c r="M25" t="n">
-        <v>7.36</v>
+        <v>7.68</v>
       </c>
       <c r="N25" t="b">
         <v>1</v>
@@ -19659,7 +19681,7 @@
         <v>10.7</v>
       </c>
       <c r="H26" t="n">
-        <v>1.06</v>
+        <v>-5.98</v>
       </c>
       <c r="I26" t="n">
         <v>7.3</v>
@@ -19672,7 +19694,7 @@
         <v>-3.78</v>
       </c>
       <c r="M26" t="n">
-        <v>-1.05</v>
+        <v>-6.88</v>
       </c>
       <c r="N26" t="b">
         <v>1</v>
@@ -19710,7 +19732,7 @@
         <v>25.6</v>
       </c>
       <c r="H27" t="n">
-        <v>19.74</v>
+        <v>20.7</v>
       </c>
       <c r="I27" t="n">
         <v>7.71</v>
@@ -19723,7 +19745,7 @@
         <v>-4.85</v>
       </c>
       <c r="M27" t="n">
-        <v>18.39</v>
+        <v>20.55</v>
       </c>
       <c r="N27" t="b">
         <v>1</v>
@@ -19761,7 +19783,7 @@
         <v>-6.9</v>
       </c>
       <c r="H28" t="n">
-        <v>18.01</v>
+        <v>18.96</v>
       </c>
       <c r="I28" t="n">
         <v>6.44</v>
@@ -19774,7 +19796,7 @@
         <v>-4.53</v>
       </c>
       <c r="M28" t="n">
-        <v>16.58</v>
+        <v>18.73</v>
       </c>
       <c r="N28" t="b">
         <v>1</v>
@@ -19812,7 +19834,7 @@
         <v>0.3</v>
       </c>
       <c r="H29" t="n">
-        <v>-15.89</v>
+        <v>-14.76</v>
       </c>
       <c r="I29" t="n">
         <v>-10.53</v>
@@ -19825,7 +19847,7 @@
         <v>-17.73</v>
       </c>
       <c r="M29" t="n">
-        <v>-16.82</v>
+        <v>-14.49</v>
       </c>
       <c r="N29" t="b">
         <v>1</v>
@@ -19863,7 +19885,7 @@
         <v>2.8</v>
       </c>
       <c r="H30" t="n">
-        <v>3.27</v>
+        <v>-0.59</v>
       </c>
       <c r="I30" t="n">
         <v>3.18</v>
@@ -19876,7 +19898,7 @@
         <v>-0.88</v>
       </c>
       <c r="M30" t="n">
-        <v>1.63</v>
+        <v>-1.03</v>
       </c>
       <c r="N30" t="b">
         <v>1</v>
@@ -19914,7 +19936,7 @@
         <v>34.5</v>
       </c>
       <c r="H31" t="n">
-        <v>13.16</v>
+        <v>11.18</v>
       </c>
       <c r="I31" t="n">
         <v>0.66</v>
@@ -19927,7 +19949,7 @@
         <v>-2.64</v>
       </c>
       <c r="M31" t="n">
-        <v>11.51</v>
+        <v>10.73</v>
       </c>
       <c r="N31" t="b">
         <v>1</v>
@@ -19965,7 +19987,7 @@
         <v>24.3</v>
       </c>
       <c r="H32" t="n">
-        <v>38.45</v>
+        <v>28.16</v>
       </c>
       <c r="I32" t="n">
         <v>2.54</v>
@@ -19978,7 +20000,7 @@
         <v>-5.21</v>
       </c>
       <c r="M32" t="n">
-        <v>37.45</v>
+        <v>28.35</v>
       </c>
       <c r="N32" t="b">
         <v>1</v>
@@ -20016,7 +20038,7 @@
         <v>-16.9</v>
       </c>
       <c r="H33" t="n">
-        <v>1.33</v>
+        <v>5.69</v>
       </c>
       <c r="I33" t="n">
         <v>-6.47</v>
@@ -20029,7 +20051,7 @@
         <v>-11.5</v>
       </c>
       <c r="M33" t="n">
-        <v>0.33</v>
+        <v>5.88</v>
       </c>
       <c r="N33" t="b">
         <v>1</v>
@@ -20067,7 +20089,7 @@
         <v>20.3</v>
       </c>
       <c r="H34" t="n">
-        <v>-26.39</v>
+        <v>-20.39</v>
       </c>
       <c r="I34" t="n">
         <v>-2.07</v>
@@ -20080,7 +20102,7 @@
         <v>-17.35</v>
       </c>
       <c r="M34" t="n">
-        <v>-27.23</v>
+        <v>-20.04</v>
       </c>
       <c r="N34" t="b">
         <v>1</v>
@@ -20118,7 +20140,7 @@
         <v>0.3</v>
       </c>
       <c r="H35" t="n">
-        <v>-21.9</v>
+        <v>-19.2</v>
       </c>
       <c r="I35" t="n">
         <v>-9.9</v>
@@ -20131,7 +20153,7 @@
         <v>-21.72</v>
       </c>
       <c r="M35" t="n">
-        <v>-23.24</v>
+        <v>-19.35</v>
       </c>
       <c r="N35" t="b">
         <v>1</v>
@@ -20169,7 +20191,7 @@
         <v>49.4</v>
       </c>
       <c r="H36" t="n">
-        <v>0.18</v>
+        <v>-2.54</v>
       </c>
       <c r="I36" t="n">
         <v>2.9</v>
@@ -20182,7 +20204,7 @@
         <v>-5.67</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.97</v>
+        <v>-2.5</v>
       </c>
       <c r="N36" t="b">
         <v>1</v>
@@ -20220,7 +20242,7 @@
         <v>4.5</v>
       </c>
       <c r="H37" t="n">
-        <v>-2.01</v>
+        <v>2.29</v>
       </c>
       <c r="I37" t="n">
         <v>-7.61</v>
@@ -20233,7 +20255,7 @@
         <v>-11.06</v>
       </c>
       <c r="M37" t="n">
-        <v>-3.16</v>
+        <v>2.33</v>
       </c>
       <c r="N37" t="b">
         <v>1</v>
@@ -20271,7 +20293,7 @@
         <v>-17.9</v>
       </c>
       <c r="H38" t="n">
-        <v>6.87</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="I38" t="n">
         <v>0.6</v>
@@ -20284,7 +20306,7 @@
         <v>-4.72</v>
       </c>
       <c r="M38" t="n">
-        <v>5.69</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="N38" t="b">
         <v>1</v>
@@ -20322,7 +20344,7 @@
         <v>2.1</v>
       </c>
       <c r="H39" t="n">
-        <v>-6.92</v>
+        <v>-0.79</v>
       </c>
       <c r="I39" t="n">
         <v>0.25</v>
@@ -20335,7 +20357,7 @@
         <v>-16.43</v>
       </c>
       <c r="M39" t="n">
-        <v>-8.1</v>
+        <v>-0.77</v>
       </c>
       <c r="N39" t="b">
         <v>1</v>
@@ -20373,7 +20395,7 @@
         <v>19.4</v>
       </c>
       <c r="H40" t="n">
-        <v>-7.24</v>
+        <v>-8</v>
       </c>
       <c r="I40" t="n">
         <v>-10.01</v>
@@ -20386,7 +20408,7 @@
         <v>-15.23</v>
       </c>
       <c r="M40" t="n">
-        <v>-7.84</v>
+        <v>-7.42</v>
       </c>
       <c r="N40" t="b">
         <v>1</v>
@@ -20424,7 +20446,7 @@
         <v>-2.6</v>
       </c>
       <c r="H41" t="n">
-        <v>-7.39</v>
+        <v>-5.79</v>
       </c>
       <c r="I41" t="n">
         <v>-4.27</v>
@@ -20437,7 +20459,7 @@
         <v>-4.86</v>
       </c>
       <c r="M41" t="n">
-        <v>-8.210000000000001</v>
+        <v>-5.42</v>
       </c>
       <c r="N41" t="b">
         <v>1</v>
@@ -20475,7 +20497,7 @@
         <v>23.8</v>
       </c>
       <c r="H42" t="n">
-        <v>3.37</v>
+        <v>0.22</v>
       </c>
       <c r="I42" t="n">
         <v>1.36</v>
@@ -20488,7 +20510,7 @@
         <v>-9.94</v>
       </c>
       <c r="M42" t="n">
-        <v>3.52</v>
+        <v>1.55</v>
       </c>
       <c r="N42" t="b">
         <v>1</v>
@@ -20526,7 +20548,7 @@
         <v>38.9</v>
       </c>
       <c r="H43" t="n">
-        <v>-10.18</v>
+        <v>-15.33</v>
       </c>
       <c r="I43" t="n">
         <v>-9.220000000000001</v>
@@ -20539,7 +20561,7 @@
         <v>-9.83</v>
       </c>
       <c r="M43" t="n">
-        <v>-10.03</v>
+        <v>-14</v>
       </c>
       <c r="N43" t="b">
         <v>1</v>
@@ -20577,7 +20599,7 @@
         <v>43.2</v>
       </c>
       <c r="H44" t="n">
-        <v>-10.98</v>
+        <v>-6.79</v>
       </c>
       <c r="I44" t="n">
         <v>-3.15</v>
@@ -20590,7 +20612,7 @@
         <v>-17.51</v>
       </c>
       <c r="M44" t="n">
-        <v>-11</v>
+        <v>-5.63</v>
       </c>
       <c r="N44" t="b">
         <v>1</v>
@@ -20628,7 +20650,7 @@
         <v>-8.199999999999999</v>
       </c>
       <c r="H45" t="n">
-        <v>6.35</v>
+        <v>12.43</v>
       </c>
       <c r="I45" t="n">
         <v>5.34</v>
@@ -20641,7 +20663,7 @@
         <v>-5.27</v>
       </c>
       <c r="M45" t="n">
-        <v>6.33</v>
+        <v>13.59</v>
       </c>
       <c r="N45" t="b">
         <v>1</v>
@@ -20679,7 +20701,7 @@
         <v>-23.9</v>
       </c>
       <c r="H46" t="n">
-        <v>-3.94</v>
+        <v>1.14</v>
       </c>
       <c r="I46" t="n">
         <v>3.28</v>
@@ -20692,7 +20714,7 @@
         <v>-4.46</v>
       </c>
       <c r="M46" t="n">
-        <v>-4.25</v>
+        <v>2.02</v>
       </c>
       <c r="N46" t="b">
         <v>1</v>
@@ -20730,7 +20752,7 @@
         <v>26.7</v>
       </c>
       <c r="H47" t="n">
-        <v>-0.6</v>
+        <v>-0.74</v>
       </c>
       <c r="I47" t="n">
         <v>-0.05</v>
@@ -20743,7 +20765,7 @@
         <v>-0.87</v>
       </c>
       <c r="M47" t="n">
-        <v>-0.92</v>
+        <v>0.13</v>
       </c>
       <c r="N47" t="b">
         <v>1</v>
@@ -20781,7 +20803,7 @@
         <v>-3.5</v>
       </c>
       <c r="H48" t="n">
-        <v>2.59</v>
+        <v>0.65</v>
       </c>
       <c r="I48" t="n">
         <v>-4.95</v>
@@ -20794,7 +20816,7 @@
         <v>-8.43</v>
       </c>
       <c r="M48" t="n">
-        <v>2.07</v>
+        <v>1.32</v>
       </c>
       <c r="N48" t="b">
         <v>1</v>
@@ -20832,7 +20854,7 @@
         <v>-17.9</v>
       </c>
       <c r="H49" t="n">
-        <v>6.18</v>
+        <v>-1.67</v>
       </c>
       <c r="I49" t="n">
         <v>-0.5</v>
@@ -20845,7 +20867,7 @@
         <v>-3.43</v>
       </c>
       <c r="M49" t="n">
-        <v>5.66</v>
+        <v>-1</v>
       </c>
       <c r="N49" t="b">
         <v>1</v>
@@ -20883,7 +20905,7 @@
         <v>53.5</v>
       </c>
       <c r="H50" t="n">
-        <v>9.279999999999999</v>
+        <v>15.67</v>
       </c>
       <c r="I50" t="n">
         <v>1.23</v>
@@ -20896,7 +20918,7 @@
         <v>-7.57</v>
       </c>
       <c r="M50" t="n">
-        <v>8.65</v>
+        <v>16.23</v>
       </c>
       <c r="N50" t="b">
         <v>1</v>
@@ -20934,7 +20956,7 @@
         <v>-1</v>
       </c>
       <c r="H51" t="n">
-        <v>-12.52</v>
+        <v>-15.23</v>
       </c>
       <c r="I51" t="n">
         <v>-6.26</v>
@@ -20947,7 +20969,7 @@
         <v>-15</v>
       </c>
       <c r="M51" t="n">
-        <v>-13.15</v>
+        <v>-14.66</v>
       </c>
       <c r="N51" t="b">
         <v>1</v>
@@ -20985,7 +21007,7 @@
         <v>29.7</v>
       </c>
       <c r="H52" t="n">
-        <v>11.14</v>
+        <v>13.11</v>
       </c>
       <c r="I52" t="n">
         <v>11.27</v>
@@ -20998,7 +21020,7 @@
         <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>10.52</v>
+        <v>13.67</v>
       </c>
       <c r="N52" t="b">
         <v>1</v>
@@ -21036,7 +21058,7 @@
         <v>15.2</v>
       </c>
       <c r="H53" t="n">
-        <v>-31.29</v>
+        <v>-24.78</v>
       </c>
       <c r="I53" t="n">
         <v>-8.77</v>
@@ -21049,7 +21071,7 @@
         <v>-24.79</v>
       </c>
       <c r="M53" t="n">
-        <v>-31.18</v>
+        <v>-23.49</v>
       </c>
       <c r="N53" t="b">
         <v>1</v>
@@ -21087,7 +21109,7 @@
         <v>22.2</v>
       </c>
       <c r="H54" t="n">
-        <v>12.66</v>
+        <v>12.82</v>
       </c>
       <c r="I54" t="n">
         <v>1.01</v>
@@ -21100,7 +21122,7 @@
         <v>-3.94</v>
       </c>
       <c r="M54" t="n">
-        <v>12.77</v>
+        <v>14.11</v>
       </c>
       <c r="N54" t="b">
         <v>1</v>
@@ -21142,7 +21164,7 @@
         <v>-0</v>
       </c>
       <c r="H55" t="n">
-        <v>52.65</v>
+        <v>53.6</v>
       </c>
       <c r="I55" t="n">
         <v>13.5</v>
@@ -21155,7 +21177,7 @@
         <v>-2.53</v>
       </c>
       <c r="M55" t="n">
-        <v>49.24</v>
+        <v>51.41</v>
       </c>
       <c r="N55" t="b">
         <v>1</v>
@@ -21193,7 +21215,7 @@
         <v>10.5</v>
       </c>
       <c r="H56" t="n">
-        <v>18.72</v>
+        <v>24.57</v>
       </c>
       <c r="I56" t="n">
         <v>1.99</v>
@@ -21206,7 +21228,7 @@
         <v>-6.27</v>
       </c>
       <c r="M56" t="n">
-        <v>15.31</v>
+        <v>22.38</v>
       </c>
       <c r="N56" t="b">
         <v>1</v>
@@ -21244,7 +21266,7 @@
         <v>-37</v>
       </c>
       <c r="H57" t="n">
-        <v>60.29</v>
+        <v>60.76</v>
       </c>
       <c r="I57" t="n">
         <v>18.38</v>
@@ -21257,7 +21279,7 @@
         <v>-5.11</v>
       </c>
       <c r="M57" t="n">
-        <v>56.21</v>
+        <v>57.92</v>
       </c>
       <c r="N57" t="b">
         <v>1</v>
@@ -21295,7 +21317,7 @@
         <v>-26.8</v>
       </c>
       <c r="H58" t="n">
-        <v>25.57</v>
+        <v>26.62</v>
       </c>
       <c r="I58" t="n">
         <v>4.56</v>
@@ -21308,7 +21330,7 @@
         <v>-4.09</v>
       </c>
       <c r="M58" t="n">
-        <v>21.5</v>
+        <v>23.78</v>
       </c>
       <c r="N58" t="b">
         <v>1</v>
@@ -21346,7 +21368,7 @@
         <v>-36.5</v>
       </c>
       <c r="H59" t="n">
-        <v>-32.57</v>
+        <v>-29.51</v>
       </c>
       <c r="I59" t="n">
         <v>-27.75</v>
@@ -21354,12 +21376,14 @@
       <c r="J59" t="n">
         <v>-30.21</v>
       </c>
-      <c r="K59" t="inlineStr"/>
+      <c r="K59" t="n">
+        <v>-29.51</v>
+      </c>
       <c r="L59" t="n">
         <v>-31.28</v>
       </c>
       <c r="M59" t="n">
-        <v>-37.3</v>
+        <v>-33.01</v>
       </c>
       <c r="N59" t="b">
         <v>1</v>
@@ -21397,7 +21421,7 @@
         <v>-38.7</v>
       </c>
       <c r="H60" t="n">
-        <v>26.39</v>
+        <v>36.19</v>
       </c>
       <c r="I60" t="n">
         <v>17.17</v>
@@ -21405,12 +21429,14 @@
       <c r="J60" t="n">
         <v>23.47</v>
       </c>
-      <c r="K60" t="inlineStr"/>
+      <c r="K60" t="n">
+        <v>36.19</v>
+      </c>
       <c r="L60" t="n">
         <v>-0.54</v>
       </c>
       <c r="M60" t="n">
-        <v>21.66</v>
+        <v>32.69</v>
       </c>
       <c r="N60" t="b">
         <v>1</v>
@@ -21448,7 +21474,7 @@
         <v>-34.6</v>
       </c>
       <c r="H61" t="n">
-        <v>20.12</v>
+        <v>25.14</v>
       </c>
       <c r="I61" t="n">
         <v>6.67</v>
@@ -21456,12 +21482,14 @@
       <c r="J61" t="n">
         <v>15.4</v>
       </c>
-      <c r="K61" t="inlineStr"/>
+      <c r="K61" t="n">
+        <v>25.14</v>
+      </c>
       <c r="L61" t="n">
         <v>-3.06</v>
       </c>
       <c r="M61" t="n">
-        <v>15.38</v>
+        <v>21.64</v>
       </c>
       <c r="N61" t="b">
         <v>1</v>
@@ -21499,7 +21527,7 @@
         <v>-11.8</v>
       </c>
       <c r="H62" t="n">
-        <v>5.1</v>
+        <v>10.56</v>
       </c>
       <c r="I62" t="n">
         <v>9.76</v>
@@ -21514,7 +21542,7 @@
         <v>-1.63</v>
       </c>
       <c r="M62" t="n">
-        <v>0.25</v>
+        <v>6.95</v>
       </c>
       <c r="N62" t="b">
         <v>1</v>
@@ -21552,7 +21580,7 @@
         <v>0.1</v>
       </c>
       <c r="H63" t="n">
-        <v>-2.62</v>
+        <v>2.52</v>
       </c>
       <c r="I63" t="n">
         <v>-2.83</v>
@@ -21567,7 +21595,7 @@
         <v>-5.45</v>
       </c>
       <c r="M63" t="n">
-        <v>-7.47</v>
+        <v>-1.09</v>
       </c>
       <c r="N63" t="b">
         <v>1</v>
@@ -21605,7 +21633,7 @@
         <v>24.1</v>
       </c>
       <c r="H64" t="n">
-        <v>2.89</v>
+        <v>2.49</v>
       </c>
       <c r="I64" t="n">
         <v>-8.31</v>
@@ -21620,7 +21648,7 @@
         <v>-18.31</v>
       </c>
       <c r="M64" t="n">
-        <v>-1.15</v>
+        <v>-0.33</v>
       </c>
       <c r="N64" t="b">
         <v>1</v>
@@ -21658,7 +21686,7 @@
         <v>-15.9</v>
       </c>
       <c r="H65" t="n">
-        <v>20.25</v>
+        <v>23.54</v>
       </c>
       <c r="I65" t="n">
         <v>10.45</v>
@@ -21673,7 +21701,7 @@
         <v>-0.31</v>
       </c>
       <c r="M65" t="n">
-        <v>16.21</v>
+        <v>20.73</v>
       </c>
       <c r="N65" t="b">
         <v>1</v>
@@ -21711,7 +21739,7 @@
         <v>-21.8</v>
       </c>
       <c r="H66" t="n">
-        <v>-35.33</v>
+        <v>-36.2</v>
       </c>
       <c r="I66" t="n">
         <v>-18.97</v>
@@ -21726,7 +21754,7 @@
         <v>-26.82</v>
       </c>
       <c r="M66" t="n">
-        <v>-40.15</v>
+        <v>-39.79</v>
       </c>
       <c r="N66" t="b">
         <v>1</v>
@@ -21764,7 +21792,7 @@
         <v>57</v>
       </c>
       <c r="H67" t="n">
-        <v>35.19</v>
+        <v>31.69</v>
       </c>
       <c r="I67" t="n">
         <v>-11.21</v>
@@ -21779,7 +21807,7 @@
         <v>-13.87</v>
       </c>
       <c r="M67" t="n">
-        <v>31.39</v>
+        <v>29.11</v>
       </c>
       <c r="N67" t="b">
         <v>1</v>
@@ -21817,7 +21845,7 @@
         <v>-21.8</v>
       </c>
       <c r="H68" t="n">
-        <v>24.65</v>
+        <v>30.19</v>
       </c>
       <c r="I68" t="n">
         <v>1.71</v>
@@ -21832,7 +21860,7 @@
         <v>-6.18</v>
       </c>
       <c r="M68" t="n">
-        <v>20.85</v>
+        <v>27.62</v>
       </c>
       <c r="N68" t="b">
         <v>1</v>
@@ -21870,7 +21898,7 @@
         <v>1</v>
       </c>
       <c r="H69" t="n">
-        <v>-38.31</v>
+        <v>-36.33</v>
       </c>
       <c r="I69" t="n">
         <v>-11.52</v>
@@ -21885,7 +21913,7 @@
         <v>-16.26</v>
       </c>
       <c r="M69" t="n">
-        <v>-42.16</v>
+        <v>-38.95</v>
       </c>
       <c r="N69" t="b">
         <v>1</v>
@@ -21923,7 +21951,7 @@
         <v>32.3</v>
       </c>
       <c r="H70" t="n">
-        <v>-39.58</v>
+        <v>-45.45</v>
       </c>
       <c r="I70" t="n">
         <v>-20.76</v>
@@ -21938,7 +21966,7 @@
         <v>-27.91</v>
       </c>
       <c r="M70" t="n">
-        <v>-43.43</v>
+        <v>-48.07</v>
       </c>
       <c r="N70" t="b">
         <v>1</v>
@@ -21976,7 +22004,7 @@
         <v>3.7</v>
       </c>
       <c r="H71" t="n">
-        <v>-10.18</v>
+        <v>-10.42</v>
       </c>
       <c r="I71" t="n">
         <v>-1.11</v>
@@ -21991,7 +22019,7 @@
         <v>-25.46</v>
       </c>
       <c r="M71" t="n">
-        <v>-14.03</v>
+        <v>-13.05</v>
       </c>
       <c r="N71" t="b">
         <v>1</v>
@@ -22029,7 +22057,7 @@
         <v>42.4</v>
       </c>
       <c r="H72" t="n">
-        <v>-19.56</v>
+        <v>-27.08</v>
       </c>
       <c r="I72" t="n">
         <v>2.16</v>
@@ -22044,7 +22072,7 @@
         <v>-15.76</v>
       </c>
       <c r="M72" t="n">
-        <v>-23.41</v>
+        <v>-29.7</v>
       </c>
       <c r="N72" t="b">
         <v>1</v>
@@ -22082,7 +22110,7 @@
         <v>28.2</v>
       </c>
       <c r="H73" t="n">
-        <v>-13.73</v>
+        <v>-26.13</v>
       </c>
       <c r="I73" t="n">
         <v>-1.71</v>
@@ -22097,7 +22125,7 @@
         <v>-23.43</v>
       </c>
       <c r="M73" t="n">
-        <v>-17.57</v>
+        <v>-28.76</v>
       </c>
       <c r="N73" t="b">
         <v>1</v>
@@ -22135,7 +22163,7 @@
         <v>28.6</v>
       </c>
       <c r="H74" t="n">
-        <v>-3.11</v>
+        <v>-18.29</v>
       </c>
       <c r="I74" t="n">
         <v>2.81</v>
@@ -22150,7 +22178,7 @@
         <v>-18.87</v>
       </c>
       <c r="M74" t="n">
-        <v>-6.96</v>
+        <v>-20.91</v>
       </c>
       <c r="N74" t="b">
         <v>1</v>
@@ -22188,7 +22216,7 @@
         <v>21.8</v>
       </c>
       <c r="H75" t="n">
-        <v>-27.95</v>
+        <v>-47.88</v>
       </c>
       <c r="I75" t="n">
         <v>-6.34</v>
@@ -22203,7 +22231,7 @@
         <v>-30.04</v>
       </c>
       <c r="M75" t="n">
-        <v>-31.8</v>
+        <v>-50.51</v>
       </c>
       <c r="N75" t="b">
         <v>1</v>
@@ -22241,7 +22269,7 @@
         <v>24.1</v>
       </c>
       <c r="H76" t="n">
-        <v>-14.07</v>
+        <v>-21.91</v>
       </c>
       <c r="I76" t="n">
         <v>-1.6</v>
@@ -22256,7 +22284,7 @@
         <v>-22.54</v>
       </c>
       <c r="M76" t="n">
-        <v>-17.92</v>
+        <v>-24.53</v>
       </c>
       <c r="N76" t="b">
         <v>1</v>
@@ -22294,7 +22322,7 @@
         <v>24.5</v>
       </c>
       <c r="H77" t="n">
-        <v>-29.93</v>
+        <v>-35.65</v>
       </c>
       <c r="I77" t="n">
         <v>-12.99</v>
@@ -22309,7 +22337,7 @@
         <v>-22.54</v>
       </c>
       <c r="M77" t="n">
-        <v>-33.78</v>
+        <v>-38.28</v>
       </c>
       <c r="N77" t="b">
         <v>1</v>
@@ -22347,7 +22375,7 @@
         <v>-8.699999999999999</v>
       </c>
       <c r="H78" t="n">
-        <v>-10.76</v>
+        <v>-6.2</v>
       </c>
       <c r="I78" t="n">
         <v>17.25</v>
@@ -22362,7 +22390,7 @@
         <v>-4.65</v>
       </c>
       <c r="M78" t="n">
-        <v>-14.61</v>
+        <v>-8.82</v>
       </c>
       <c r="N78" t="b">
         <v>1</v>
@@ -22400,7 +22428,7 @@
         <v>37.2</v>
       </c>
       <c r="H79" t="n">
-        <v>-37.72</v>
+        <v>-43.48</v>
       </c>
       <c r="I79" t="n">
         <v>-7.64</v>
@@ -22415,7 +22443,7 @@
         <v>-26.24</v>
       </c>
       <c r="M79" t="n">
-        <v>-41.56</v>
+        <v>-46.1</v>
       </c>
       <c r="N79" t="b">
         <v>1</v>
@@ -22453,7 +22481,7 @@
         <v>29.8</v>
       </c>
       <c r="H80" t="n">
-        <v>6.65</v>
+        <v>-5.78</v>
       </c>
       <c r="I80" t="n">
         <v>-2.74</v>
@@ -22468,7 +22496,7 @@
         <v>-22.36</v>
       </c>
       <c r="M80" t="n">
-        <v>2.8</v>
+        <v>-8.41</v>
       </c>
       <c r="N80" t="b">
         <v>1</v>
@@ -22506,7 +22534,7 @@
         <v>19.3</v>
       </c>
       <c r="H81" t="n">
-        <v>-34.67</v>
+        <v>-41.66</v>
       </c>
       <c r="I81" t="n">
         <v>-16.69</v>
@@ -22521,7 +22549,7 @@
         <v>-36.39</v>
       </c>
       <c r="M81" t="n">
-        <v>-38.52</v>
+        <v>-44.28</v>
       </c>
       <c r="N81" t="b">
         <v>1</v>
@@ -22559,7 +22587,7 @@
         <v>11.8</v>
       </c>
       <c r="H82" t="n">
-        <v>-1.29</v>
+        <v>-16.95</v>
       </c>
       <c r="I82" t="n">
         <v>-1.19</v>
@@ -22574,7 +22602,7 @@
         <v>-17.57</v>
       </c>
       <c r="M82" t="n">
-        <v>-5.14</v>
+        <v>-19.57</v>
       </c>
       <c r="N82" t="b">
         <v>1</v>
@@ -22612,7 +22640,7 @@
         <v>27.5</v>
       </c>
       <c r="H83" t="n">
-        <v>3.41</v>
+        <v>1.74</v>
       </c>
       <c r="I83" t="n">
         <v>8.42</v>
@@ -22627,7 +22655,7 @@
         <v>-2.51</v>
       </c>
       <c r="M83" t="n">
-        <v>-0.44</v>
+        <v>-0.88</v>
       </c>
       <c r="N83" t="b">
         <v>1</v>
@@ -22665,7 +22693,7 @@
         <v>-14.7</v>
       </c>
       <c r="H84" t="n">
-        <v>-21.26</v>
+        <v>-15.16</v>
       </c>
       <c r="I84" t="n">
         <v>10.3</v>
@@ -22680,7 +22708,7 @@
         <v>-2.6</v>
       </c>
       <c r="M84" t="n">
-        <v>-25.11</v>
+        <v>-17.78</v>
       </c>
       <c r="N84" t="b">
         <v>1</v>
@@ -22722,7 +22750,7 @@
         <v>-9.300000000000001</v>
       </c>
       <c r="H85" t="n">
-        <v>-21.54</v>
+        <v>-20.23</v>
       </c>
       <c r="I85" t="n">
         <v>10.42</v>
@@ -22737,7 +22765,7 @@
         <v>-21.72</v>
       </c>
       <c r="M85" t="n">
-        <v>-25.39</v>
+        <v>-22.86</v>
       </c>
       <c r="N85" t="b">
         <v>1</v>
@@ -22775,7 +22803,7 @@
         <v>5.1</v>
       </c>
       <c r="H86" t="n">
-        <v>12.95</v>
+        <v>18.14</v>
       </c>
       <c r="I86" t="n">
         <v>8.77</v>
@@ -22790,7 +22818,7 @@
         <v>-3.54</v>
       </c>
       <c r="M86" t="n">
-        <v>9.109999999999999</v>
+        <v>15.51</v>
       </c>
       <c r="N86" t="b">
         <v>1</v>
@@ -22828,7 +22856,7 @@
         <v>34.2</v>
       </c>
       <c r="H87" t="n">
-        <v>4.09</v>
+        <v>-0.53</v>
       </c>
       <c r="I87" t="n">
         <v>8.15</v>
@@ -22843,7 +22871,7 @@
         <v>-7.63</v>
       </c>
       <c r="M87" t="n">
-        <v>0.24</v>
+        <v>-3.15</v>
       </c>
       <c r="N87" t="b">
         <v>1</v>
@@ -22881,7 +22909,7 @@
         <v>42</v>
       </c>
       <c r="H88" t="n">
-        <v>-34.98</v>
+        <v>-48.38</v>
       </c>
       <c r="I88" t="n">
         <v>0.6</v>
@@ -22896,7 +22924,7 @@
         <v>-16.67</v>
       </c>
       <c r="M88" t="n">
-        <v>-38.83</v>
+        <v>-51</v>
       </c>
       <c r="N88" t="b">
         <v>1</v>
@@ -22934,7 +22962,7 @@
         <v>-7.7</v>
       </c>
       <c r="H89" t="n">
-        <v>-13.67</v>
+        <v>-20.25</v>
       </c>
       <c r="I89" t="n">
         <v>-6.47</v>
@@ -22949,7 +22977,7 @@
         <v>-23.05</v>
       </c>
       <c r="M89" t="n">
-        <v>-17.52</v>
+        <v>-22.87</v>
       </c>
       <c r="N89" t="b">
         <v>1</v>
@@ -22987,7 +23015,7 @@
         <v>13.7</v>
       </c>
       <c r="H90" t="n">
-        <v>4.97</v>
+        <v>-8.81</v>
       </c>
       <c r="I90" t="n">
         <v>2.74</v>
@@ -23002,7 +23030,7 @@
         <v>-24.02</v>
       </c>
       <c r="M90" t="n">
-        <v>1.12</v>
+        <v>-11.43</v>
       </c>
       <c r="N90" t="b">
         <v>1</v>
@@ -23040,7 +23068,7 @@
         <v>21.8</v>
       </c>
       <c r="H91" t="n">
-        <v>-26.36</v>
+        <v>-31.3</v>
       </c>
       <c r="I91" t="n">
         <v>18.32</v>
@@ -23055,7 +23083,7 @@
         <v>-23.27</v>
       </c>
       <c r="M91" t="n">
-        <v>-30.21</v>
+        <v>-33.92</v>
       </c>
       <c r="N91" t="b">
         <v>1</v>
@@ -23093,7 +23121,7 @@
         <v>29.4</v>
       </c>
       <c r="H92" t="n">
-        <v>-24.78</v>
+        <v>-32.73</v>
       </c>
       <c r="I92" t="n">
         <v>-2.62</v>
@@ -23108,7 +23136,7 @@
         <v>-27.18</v>
       </c>
       <c r="M92" t="n">
-        <v>-28.63</v>
+        <v>-35.35</v>
       </c>
       <c r="N92" t="b">
         <v>1</v>
@@ -23146,7 +23174,7 @@
         <v>-3.7</v>
       </c>
       <c r="H93" t="n">
-        <v>-27.66</v>
+        <v>-32.17</v>
       </c>
       <c r="I93" t="n">
         <v>-8.07</v>
@@ -23161,7 +23189,7 @@
         <v>-22.12</v>
       </c>
       <c r="M93" t="n">
-        <v>-31.5</v>
+        <v>-34.79</v>
       </c>
       <c r="N93" t="b">
         <v>1</v>
@@ -23199,7 +23227,7 @@
         <v>21.3</v>
       </c>
       <c r="H94" t="n">
-        <v>1.75</v>
+        <v>1.48</v>
       </c>
       <c r="I94" t="n">
         <v>0.23</v>
@@ -23214,7 +23242,7 @@
         <v>-0.85</v>
       </c>
       <c r="M94" t="n">
-        <v>-2.1</v>
+        <v>-1.14</v>
       </c>
       <c r="N94" t="b">
         <v>1</v>
@@ -23252,7 +23280,7 @@
         <v>-21.4</v>
       </c>
       <c r="H95" t="n">
-        <v>2.87</v>
+        <v>-4.13</v>
       </c>
       <c r="I95" t="n">
         <v>4.55</v>
@@ -23267,7 +23295,7 @@
         <v>-6.39</v>
       </c>
       <c r="M95" t="n">
-        <v>-0.98</v>
+        <v>-6.75</v>
       </c>
       <c r="N95" t="b">
         <v>1</v>
@@ -23305,7 +23333,7 @@
         <v>16.3</v>
       </c>
       <c r="H96" t="n">
-        <v>-17.89</v>
+        <v>-26.28</v>
       </c>
       <c r="I96" t="n">
         <v>-1</v>
@@ -23320,7 +23348,7 @@
         <v>-22.5</v>
       </c>
       <c r="M96" t="n">
-        <v>-21.73</v>
+        <v>-28.91</v>
       </c>
       <c r="N96" t="b">
         <v>1</v>
@@ -23358,7 +23386,7 @@
         <v>0.2</v>
       </c>
       <c r="H97" t="n">
-        <v>22.49</v>
+        <v>23.12</v>
       </c>
       <c r="I97" t="n">
         <v>4.35</v>
@@ -23373,7 +23401,7 @@
         <v>-2.79</v>
       </c>
       <c r="M97" t="n">
-        <v>18.64</v>
+        <v>20.5</v>
       </c>
       <c r="N97" t="b">
         <v>1</v>
@@ -23411,7 +23439,7 @@
         <v>8.4</v>
       </c>
       <c r="H98" t="n">
-        <v>-42.87</v>
+        <v>-45.82</v>
       </c>
       <c r="I98" t="n">
         <v>-0.13</v>
@@ -23426,7 +23454,7 @@
         <v>-10.87</v>
       </c>
       <c r="M98" t="n">
-        <v>-46.72</v>
+        <v>-48.45</v>
       </c>
       <c r="N98" t="b">
         <v>1</v>
@@ -23464,7 +23492,7 @@
         <v>-7.3</v>
       </c>
       <c r="H99" t="n">
-        <v>-20.36</v>
+        <v>-24.39</v>
       </c>
       <c r="I99" t="n">
         <v>-4.12</v>
@@ -23479,7 +23507,7 @@
         <v>-15.02</v>
       </c>
       <c r="M99" t="n">
-        <v>-24.2</v>
+        <v>-27.01</v>
       </c>
       <c r="N99" t="b">
         <v>1</v>
@@ -23517,7 +23545,7 @@
         <v>17.9</v>
       </c>
       <c r="H100" t="n">
-        <v>-5.45</v>
+        <v>-15.01</v>
       </c>
       <c r="I100" t="n">
         <v>12.97</v>
@@ -23532,7 +23560,7 @@
         <v>-8.130000000000001</v>
       </c>
       <c r="M100" t="n">
-        <v>-9.300000000000001</v>
+        <v>-17.63</v>
       </c>
       <c r="N100" t="b">
         <v>1</v>
@@ -23570,7 +23598,7 @@
         <v>14.8</v>
       </c>
       <c r="H101" t="n">
-        <v>-8.31</v>
+        <v>-11.48</v>
       </c>
       <c r="I101" t="n">
         <v>0.35</v>
@@ -23585,7 +23613,7 @@
         <v>-3.68</v>
       </c>
       <c r="M101" t="n">
-        <v>-12.15</v>
+        <v>-14.1</v>
       </c>
       <c r="N101" t="b">
         <v>1</v>
@@ -23623,7 +23651,7 @@
         <v>25.5</v>
       </c>
       <c r="H102" t="n">
-        <v>12.21</v>
+        <v>15.13</v>
       </c>
       <c r="I102" t="n">
         <v>-9.369999999999999</v>
@@ -23638,7 +23666,7 @@
         <v>-22.11</v>
       </c>
       <c r="M102" t="n">
-        <v>8.359999999999999</v>
+        <v>12.51</v>
       </c>
       <c r="N102" t="b">
         <v>1</v>
@@ -23680,7 +23708,7 @@
         <v>-7.5</v>
       </c>
       <c r="H103" t="n">
-        <v>-26.94</v>
+        <v>-29.05</v>
       </c>
       <c r="I103" t="n">
         <v>4.46</v>
@@ -23695,7 +23723,7 @@
         <v>-8.52</v>
       </c>
       <c r="M103" t="n">
-        <v>-30.79</v>
+        <v>-31.67</v>
       </c>
       <c r="N103" t="b">
         <v>1</v>
@@ -23733,7 +23761,7 @@
         <v>-11</v>
       </c>
       <c r="H104" t="n">
-        <v>25.61</v>
+        <v>30.96</v>
       </c>
       <c r="I104" t="n">
         <v>10.7</v>
@@ -23748,7 +23776,7 @@
         <v>-9.43</v>
       </c>
       <c r="M104" t="n">
-        <v>21.76</v>
+        <v>28.34</v>
       </c>
       <c r="N104" t="b">
         <v>1</v>
@@ -23786,7 +23814,7 @@
         <v>-11.4</v>
       </c>
       <c r="H105" t="n">
-        <v>-20.7</v>
+        <v>-16.4</v>
       </c>
       <c r="I105" t="n">
         <v>4.36</v>
@@ -23801,7 +23829,7 @@
         <v>-11.36</v>
       </c>
       <c r="M105" t="n">
-        <v>-24.55</v>
+        <v>-19.02</v>
       </c>
       <c r="N105" t="b">
         <v>1</v>
@@ -23839,7 +23867,7 @@
         <v>27.1</v>
       </c>
       <c r="H106" t="n">
-        <v>-17.97</v>
+        <v>-26.64</v>
       </c>
       <c r="I106" t="n">
         <v>5.02</v>
@@ -23854,7 +23882,7 @@
         <v>-14.35</v>
       </c>
       <c r="M106" t="n">
-        <v>-21.82</v>
+        <v>-29.26</v>
       </c>
       <c r="N106" t="b">
         <v>1</v>
@@ -23892,7 +23920,7 @@
         <v>32.2</v>
       </c>
       <c r="H107" t="n">
-        <v>7.61</v>
+        <v>2.42</v>
       </c>
       <c r="I107" t="n">
         <v>6.49</v>
@@ -23907,7 +23935,7 @@
         <v>-3.92</v>
       </c>
       <c r="M107" t="n">
-        <v>3.76</v>
+        <v>-0.2</v>
       </c>
       <c r="N107" t="b">
         <v>1</v>
@@ -23945,7 +23973,7 @@
         <v>3.2</v>
       </c>
       <c r="H108" t="n">
-        <v>-29.37</v>
+        <v>-34.64</v>
       </c>
       <c r="I108" t="n">
         <v>-10.41</v>
@@ -23960,7 +23988,7 @@
         <v>-23.7</v>
       </c>
       <c r="M108" t="n">
-        <v>-33.22</v>
+        <v>-37.26</v>
       </c>
       <c r="N108" t="b">
         <v>1</v>
@@ -23998,7 +24026,7 @@
         <v>-0.3</v>
       </c>
       <c r="H109" t="n">
-        <v>-14.58</v>
+        <v>-25.24</v>
       </c>
       <c r="I109" t="n">
         <v>17.76</v>
@@ -24013,7 +24041,7 @@
         <v>-14.18</v>
       </c>
       <c r="M109" t="n">
-        <v>-18.43</v>
+        <v>-27.87</v>
       </c>
       <c r="N109" t="b">
         <v>1</v>
@@ -24051,7 +24079,7 @@
         <v>34.6</v>
       </c>
       <c r="H110" t="n">
-        <v>-4.57</v>
+        <v>-14.53</v>
       </c>
       <c r="I110" t="n">
         <v>5.7</v>
@@ -24066,7 +24094,7 @@
         <v>-7.7</v>
       </c>
       <c r="M110" t="n">
-        <v>-8.42</v>
+        <v>-17.15</v>
       </c>
       <c r="N110" t="b">
         <v>1</v>
@@ -24104,7 +24132,7 @@
         <v>10.4</v>
       </c>
       <c r="H111" t="n">
-        <v>26.6</v>
+        <v>25.59</v>
       </c>
       <c r="I111" t="n">
         <v>11.05</v>
@@ -24119,7 +24147,7 @@
         <v>-5.54</v>
       </c>
       <c r="M111" t="n">
-        <v>22.75</v>
+        <v>22.96</v>
       </c>
       <c r="N111" t="b">
         <v>1</v>
@@ -24157,7 +24185,7 @@
         <v>-21.5</v>
       </c>
       <c r="H112" t="n">
-        <v>-2.07</v>
+        <v>2.53</v>
       </c>
       <c r="I112" t="n">
         <v>10.65</v>
@@ -24172,7 +24200,7 @@
         <v>-6.89</v>
       </c>
       <c r="M112" t="n">
-        <v>-5.91</v>
+        <v>-0.1</v>
       </c>
       <c r="N112" t="b">
         <v>1</v>
@@ -24210,7 +24238,7 @@
         <v>3.5</v>
       </c>
       <c r="H113" t="n">
-        <v>67.81999999999999</v>
+        <v>66.75</v>
       </c>
       <c r="I113" t="n">
         <v>33.01</v>
@@ -24225,7 +24253,7 @@
         <v>-0.92</v>
       </c>
       <c r="M113" t="n">
-        <v>63.97</v>
+        <v>64.13</v>
       </c>
       <c r="N113" t="b">
         <v>1</v>
@@ -24263,7 +24291,7 @@
         <v>-30.5</v>
       </c>
       <c r="H114" t="n">
-        <v>-1.32</v>
+        <v>-1.15</v>
       </c>
       <c r="I114" t="n">
         <v>2.96</v>
@@ -24278,7 +24306,7 @@
         <v>-17.88</v>
       </c>
       <c r="M114" t="n">
-        <v>-5.17</v>
+        <v>-3.77</v>
       </c>
       <c r="N114" t="b">
         <v>1</v>
@@ -24316,7 +24344,7 @@
         <v>-6</v>
       </c>
       <c r="H115" t="n">
-        <v>-30.73</v>
+        <v>-38.2</v>
       </c>
       <c r="I115" t="n">
         <v>3.31</v>
@@ -24331,7 +24359,7 @@
         <v>-21.48</v>
       </c>
       <c r="M115" t="n">
-        <v>-34.58</v>
+        <v>-40.82</v>
       </c>
       <c r="N115" t="b">
         <v>1</v>
@@ -24369,7 +24397,7 @@
         <v>-34.6</v>
       </c>
       <c r="H116" t="n">
-        <v>20.79</v>
+        <v>27.95</v>
       </c>
       <c r="I116" t="n">
         <v>23.65</v>
@@ -24384,7 +24412,7 @@
         <v>-3.83</v>
       </c>
       <c r="M116" t="n">
-        <v>16.94</v>
+        <v>25.32</v>
       </c>
       <c r="N116" t="b">
         <v>1</v>
@@ -24422,7 +24450,7 @@
         <v>-16.2</v>
       </c>
       <c r="H117" t="n">
-        <v>6.42</v>
+        <v>2.16</v>
       </c>
       <c r="I117" t="n">
         <v>25.77</v>
@@ -24437,7 +24465,7 @@
         <v>-1.7</v>
       </c>
       <c r="M117" t="n">
-        <v>2.58</v>
+        <v>-0.46</v>
       </c>
       <c r="N117" t="b">
         <v>1</v>
@@ -24475,7 +24503,7 @@
         <v>-24.9</v>
       </c>
       <c r="H118" t="n">
-        <v>3.49</v>
+        <v>-5.06</v>
       </c>
       <c r="I118" t="n">
         <v>10.88</v>
@@ -24490,7 +24518,7 @@
         <v>-4.1</v>
       </c>
       <c r="M118" t="n">
-        <v>-0.36</v>
+        <v>-7.68</v>
       </c>
       <c r="N118" t="b">
         <v>1</v>
@@ -24532,7 +24560,7 @@
         <v>-8.1</v>
       </c>
       <c r="H119" t="n">
-        <v>24.38</v>
+        <v>24.46</v>
       </c>
       <c r="I119" t="n">
         <v>14.27</v>
@@ -24547,7 +24575,7 @@
         <v>-10.92</v>
       </c>
       <c r="M119" t="n">
-        <v>20.54</v>
+        <v>21.84</v>
       </c>
       <c r="N119" t="b">
         <v>1</v>
@@ -24585,7 +24613,7 @@
         <v>-10.2</v>
       </c>
       <c r="H120" t="n">
-        <v>-14.52</v>
+        <v>-8.720000000000001</v>
       </c>
       <c r="I120" t="n">
         <v>15.03</v>
@@ -24600,7 +24628,7 @@
         <v>-1.61</v>
       </c>
       <c r="M120" t="n">
-        <v>-18.36</v>
+        <v>-11.34</v>
       </c>
       <c r="N120" t="b">
         <v>1</v>
@@ -24638,7 +24666,7 @@
         <v>68.90000000000001</v>
       </c>
       <c r="H121" t="n">
-        <v>26.5</v>
+        <v>22.94</v>
       </c>
       <c r="I121" t="n">
         <v>1.84</v>
@@ -24653,7 +24681,7 @@
         <v>-10.43</v>
       </c>
       <c r="M121" t="n">
-        <v>22.65</v>
+        <v>20.32</v>
       </c>
       <c r="N121" t="b">
         <v>1</v>
@@ -24691,7 +24719,7 @@
         <v>-40.8</v>
       </c>
       <c r="H122" t="n">
-        <v>-27.63</v>
+        <v>-21.44</v>
       </c>
       <c r="I122" t="n">
         <v>21.71</v>
@@ -24706,7 +24734,7 @@
         <v>-3.3</v>
       </c>
       <c r="M122" t="n">
-        <v>-31.48</v>
+        <v>-24.06</v>
       </c>
       <c r="N122" t="b">
         <v>1</v>
@@ -24744,7 +24772,7 @@
         <v>40.7</v>
       </c>
       <c r="H123" t="n">
-        <v>31.82</v>
+        <v>25.37</v>
       </c>
       <c r="I123" t="n">
         <v>-4.08</v>
@@ -24759,7 +24787,7 @@
         <v>-11.2</v>
       </c>
       <c r="M123" t="n">
-        <v>27.98</v>
+        <v>22.75</v>
       </c>
       <c r="N123" t="b">
         <v>1</v>
@@ -24797,7 +24825,7 @@
         <v>25.7</v>
       </c>
       <c r="H124" t="n">
-        <v>-9.539999999999999</v>
+        <v>-14.91</v>
       </c>
       <c r="I124" t="n">
         <v>11.3</v>
@@ -24812,7 +24840,7 @@
         <v>-11.03</v>
       </c>
       <c r="M124" t="n">
-        <v>-13.39</v>
+        <v>-17.54</v>
       </c>
       <c r="N124" t="b">
         <v>1</v>

--- a/STS_holy_grail_v2.xlsx
+++ b/STS_holy_grail_v2.xlsx
@@ -476,7 +476,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.67</v>
+        <v>0.57</v>
       </c>
     </row>
     <row r="5">
@@ -486,7 +486,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-1.64</v>
+        <v>-1.68</v>
       </c>
     </row>
     <row r="6">
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>45.2</v>
+        <v>47.6</v>
       </c>
     </row>
     <row r="8">
@@ -543,13 +543,13 @@
         <v>64</v>
       </c>
       <c r="C10" t="n">
-        <v>-0.79</v>
+        <v>1.83</v>
       </c>
       <c r="D10" t="n">
-        <v>51.56</v>
+        <v>59.38</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.48</v>
+        <v>-0.15</v>
       </c>
     </row>
     <row r="11">
@@ -562,13 +562,13 @@
         <v>79</v>
       </c>
       <c r="C11" t="n">
-        <v>-7.76</v>
+        <v>-4.79</v>
       </c>
       <c r="D11" t="n">
-        <v>29.11</v>
+        <v>32.91</v>
       </c>
       <c r="E11" t="n">
-        <v>-9.5</v>
+        <v>-7.83</v>
       </c>
     </row>
     <row r="12">
@@ -581,13 +581,13 @@
         <v>156</v>
       </c>
       <c r="C12" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.74</v>
       </c>
       <c r="D12" t="n">
         <v>44.87</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.12</v>
+        <v>-1.47</v>
       </c>
     </row>
     <row r="13">
@@ -600,13 +600,13 @@
         <v>35</v>
       </c>
       <c r="C13" t="n">
-        <v>8.93</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="D13" t="n">
         <v>71.43000000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>9.01</v>
+        <v>8.43</v>
       </c>
     </row>
     <row r="15">
@@ -653,13 +653,13 @@
         <v>111</v>
       </c>
       <c r="C17" t="n">
-        <v>1.67</v>
+        <v>1.9</v>
       </c>
       <c r="D17" t="n">
         <v>45.95</v>
       </c>
       <c r="E17" t="n">
-        <v>0.67</v>
+        <v>-0.39</v>
       </c>
     </row>
     <row r="18">
@@ -672,13 +672,13 @@
         <v>48</v>
       </c>
       <c r="C18" t="n">
-        <v>-0.88</v>
+        <v>-1.8</v>
       </c>
       <c r="D18" t="n">
         <v>43.75</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.44</v>
+        <v>-3.65</v>
       </c>
     </row>
     <row r="19">
@@ -691,13 +691,13 @@
         <v>45</v>
       </c>
       <c r="C19" t="n">
-        <v>1.69</v>
+        <v>2.09</v>
       </c>
       <c r="D19" t="n">
-        <v>48.89</v>
+        <v>51.11</v>
       </c>
       <c r="E19" t="n">
-        <v>0.67</v>
+        <v>-0.22</v>
       </c>
     </row>
     <row r="20">
@@ -710,13 +710,13 @@
         <v>41</v>
       </c>
       <c r="C20" t="n">
-        <v>-9.44</v>
+        <v>-7.36</v>
       </c>
       <c r="D20" t="n">
-        <v>29.27</v>
+        <v>31.71</v>
       </c>
       <c r="E20" t="n">
-        <v>-10.38</v>
+        <v>-9.59</v>
       </c>
     </row>
     <row r="21">
@@ -729,13 +729,13 @@
         <v>89</v>
       </c>
       <c r="C21" t="n">
-        <v>-0.64</v>
+        <v>3.08</v>
       </c>
       <c r="D21" t="n">
-        <v>50.56</v>
+        <v>57.3</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.78</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="23">
@@ -782,13 +782,13 @@
         <v>10</v>
       </c>
       <c r="C25" t="n">
-        <v>12.9</v>
+        <v>11.16</v>
       </c>
       <c r="D25" t="n">
         <v>70</v>
       </c>
       <c r="E25" t="n">
-        <v>11.31</v>
+        <v>8.279999999999999</v>
       </c>
     </row>
     <row r="26">
@@ -801,13 +801,13 @@
         <v>5</v>
       </c>
       <c r="C26" t="n">
-        <v>-4.83</v>
+        <v>-7.3</v>
       </c>
       <c r="D26" t="n">
         <v>40</v>
       </c>
       <c r="E26" t="n">
-        <v>-7.11</v>
+        <v>-10.88</v>
       </c>
     </row>
     <row r="27">
@@ -820,13 +820,13 @@
         <v>3</v>
       </c>
       <c r="C27" t="n">
-        <v>19.93</v>
+        <v>16.18</v>
       </c>
       <c r="D27" t="n">
         <v>66.67</v>
       </c>
       <c r="E27" t="n">
-        <v>18.67</v>
+        <v>13.63</v>
       </c>
     </row>
     <row r="29">
@@ -873,13 +873,13 @@
         <v>211</v>
       </c>
       <c r="C31" t="n">
-        <v>0.1</v>
+        <v>1.42</v>
       </c>
       <c r="D31" t="n">
-        <v>43.6</v>
+        <v>45.97</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.95</v>
+        <v>-0.91</v>
       </c>
     </row>
     <row r="32">
@@ -892,13 +892,13 @@
         <v>123</v>
       </c>
       <c r="C32" t="n">
-        <v>-1.99</v>
+        <v>-0.87</v>
       </c>
       <c r="D32" t="n">
-        <v>47.97</v>
+        <v>50.41</v>
       </c>
       <c r="E32" t="n">
-        <v>-2.84</v>
+        <v>-3.01</v>
       </c>
     </row>
   </sheetData>
@@ -1022,7 +1022,7 @@
         <v>15.5</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0</v>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
@@ -1031,7 +1031,7 @@
         <v>-0.07000000000000001</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.08</v>
+        <v>-1.28</v>
       </c>
       <c r="N2" t="b">
         <v>0</v>
@@ -1058,7 +1058,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Extended</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="E3" t="inlineStr"/>
@@ -1069,7 +1069,7 @@
         <v>-9.4</v>
       </c>
       <c r="H3" t="n">
-        <v>7.37</v>
+        <v>2.89</v>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
@@ -1078,7 +1078,7 @@
         <v>-1.66</v>
       </c>
       <c r="M3" t="n">
-        <v>9.300000000000001</v>
+        <v>3.57</v>
       </c>
       <c r="N3" t="b">
         <v>0</v>
@@ -1116,16 +1116,18 @@
         <v>51.4</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.46</v>
-      </c>
-      <c r="I4" t="inlineStr"/>
+        <v>-1.92</v>
+      </c>
+      <c r="I4" t="n">
+        <v>-1.92</v>
+      </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="n">
         <v>-7.85</v>
       </c>
       <c r="M4" t="n">
-        <v>0.77</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="N4" t="b">
         <v>1</v>
@@ -1163,7 +1165,7 @@
         <v>-24.3</v>
       </c>
       <c r="H5" t="n">
-        <v>-5.84</v>
+        <v>-6.07</v>
       </c>
       <c r="I5" t="n">
         <v>-1.01</v>
@@ -1174,7 +1176,7 @@
         <v>-7.08</v>
       </c>
       <c r="M5" t="n">
-        <v>-3.92</v>
+        <v>-5.4</v>
       </c>
       <c r="N5" t="b">
         <v>0</v>
@@ -1212,7 +1214,7 @@
         <v>-22.1</v>
       </c>
       <c r="H6" t="n">
-        <v>-14.13</v>
+        <v>-11.38</v>
       </c>
       <c r="I6" t="n">
         <v>-12.2</v>
@@ -1223,7 +1225,7 @@
         <v>-15.53</v>
       </c>
       <c r="M6" t="n">
-        <v>-12.21</v>
+        <v>-10.71</v>
       </c>
       <c r="N6" t="b">
         <v>0</v>
@@ -1261,7 +1263,7 @@
         <v>-16.6</v>
       </c>
       <c r="H7" t="n">
-        <v>0.61</v>
+        <v>-3.11</v>
       </c>
       <c r="I7" t="n">
         <v>-0.75</v>
@@ -1269,10 +1271,10 @@
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="n">
-        <v>-2.5</v>
+        <v>-3.97</v>
       </c>
       <c r="M7" t="n">
-        <v>2.64</v>
+        <v>-2.32</v>
       </c>
       <c r="N7" t="b">
         <v>1</v>
@@ -1310,7 +1312,7 @@
         <v>-5</v>
       </c>
       <c r="H8" t="n">
-        <v>8.619999999999999</v>
+        <v>7.48</v>
       </c>
       <c r="I8" t="n">
         <v>12.26</v>
@@ -1321,7 +1323,7 @@
         <v>-1.75</v>
       </c>
       <c r="M8" t="n">
-        <v>10.66</v>
+        <v>8.27</v>
       </c>
       <c r="N8" t="b">
         <v>1</v>
@@ -1359,7 +1361,7 @@
         <v>-7.4</v>
       </c>
       <c r="H9" t="n">
-        <v>-4.84</v>
+        <v>-3.94</v>
       </c>
       <c r="I9" t="n">
         <v>-2.38</v>
@@ -1370,7 +1372,7 @@
         <v>-6.15</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.8</v>
+        <v>-3.15</v>
       </c>
       <c r="N9" t="b">
         <v>0</v>
@@ -1408,7 +1410,7 @@
         <v>-1.1</v>
       </c>
       <c r="H10" t="n">
-        <v>16.34</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="I10" t="n">
         <v>10.88</v>
@@ -1419,7 +1421,7 @@
         <v>-0.36</v>
       </c>
       <c r="M10" t="n">
-        <v>18.38</v>
+        <v>9.57</v>
       </c>
       <c r="N10" t="b">
         <v>0</v>
@@ -1457,7 +1459,7 @@
         <v>12.5</v>
       </c>
       <c r="H11" t="n">
-        <v>7.59</v>
+        <v>7.49</v>
       </c>
       <c r="I11" t="n">
         <v>7.44</v>
@@ -1468,7 +1470,7 @@
         <v>-2.59</v>
       </c>
       <c r="M11" t="n">
-        <v>9.619999999999999</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="N11" t="b">
         <v>1</v>
@@ -1506,7 +1508,7 @@
         <v>-17.3</v>
       </c>
       <c r="H12" t="n">
-        <v>5.42</v>
+        <v>5.13</v>
       </c>
       <c r="I12" t="n">
         <v>1.16</v>
@@ -1517,7 +1519,7 @@
         <v>-6.51</v>
       </c>
       <c r="M12" t="n">
-        <v>7.75</v>
+        <v>6.22</v>
       </c>
       <c r="N12" t="b">
         <v>1</v>
@@ -1555,7 +1557,7 @@
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>8.460000000000001</v>
+        <v>5.74</v>
       </c>
       <c r="I13" t="n">
         <v>9.16</v>
@@ -1566,7 +1568,7 @@
         <v>-1.46</v>
       </c>
       <c r="M13" t="n">
-        <v>10.79</v>
+        <v>6.83</v>
       </c>
       <c r="N13" t="b">
         <v>0</v>
@@ -1604,7 +1606,7 @@
         <v>-29.3</v>
       </c>
       <c r="H14" t="n">
-        <v>10.29</v>
+        <v>11.06</v>
       </c>
       <c r="I14" t="n">
         <v>10.02</v>
@@ -1615,7 +1617,7 @@
         <v>-3.13</v>
       </c>
       <c r="M14" t="n">
-        <v>11.55</v>
+        <v>11.06</v>
       </c>
       <c r="N14" t="b">
         <v>0</v>
@@ -1642,7 +1644,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Retired</t>
         </is>
       </c>
       <c r="E15" t="inlineStr"/>
@@ -1653,7 +1655,7 @@
         <v>-21.8</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.03</v>
+        <v>-0.47</v>
       </c>
       <c r="I15" t="n">
         <v>-3.37</v>
@@ -1664,7 +1666,7 @@
         <v>-5.33</v>
       </c>
       <c r="M15" t="n">
-        <v>0.82</v>
+        <v>-0.89</v>
       </c>
       <c r="N15" t="b">
         <v>1</v>
@@ -1691,7 +1693,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Extended</t>
+          <t>Retired</t>
         </is>
       </c>
       <c r="E16" t="inlineStr"/>
@@ -1702,18 +1704,20 @@
         <v>-15</v>
       </c>
       <c r="H16" t="n">
-        <v>17.36</v>
+        <v>14.39</v>
       </c>
       <c r="I16" t="n">
         <v>12.31</v>
       </c>
-      <c r="J16" t="inlineStr"/>
+      <c r="J16" t="n">
+        <v>14.39</v>
+      </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="n">
         <v>-4.06</v>
       </c>
       <c r="M16" t="n">
-        <v>18.25</v>
+        <v>14.02</v>
       </c>
       <c r="N16" t="b">
         <v>0</v>
@@ -1740,7 +1744,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Extended</t>
+          <t>Retired</t>
         </is>
       </c>
       <c r="E17" t="inlineStr"/>
@@ -1751,18 +1755,20 @@
         <v>-16.7</v>
       </c>
       <c r="H17" t="n">
-        <v>23.11</v>
+        <v>15.75</v>
       </c>
       <c r="I17" t="n">
         <v>26.03</v>
       </c>
-      <c r="J17" t="inlineStr"/>
+      <c r="J17" t="n">
+        <v>15.75</v>
+      </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="n">
         <v>-6.98</v>
       </c>
       <c r="M17" t="n">
-        <v>24</v>
+        <v>15.38</v>
       </c>
       <c r="N17" t="b">
         <v>1</v>
@@ -1789,7 +1795,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Retired</t>
         </is>
       </c>
       <c r="E18" t="inlineStr"/>
@@ -1800,18 +1806,20 @@
         <v>-35.9</v>
       </c>
       <c r="H18" t="n">
-        <v>-5.71</v>
+        <v>-3.45</v>
       </c>
       <c r="I18" t="n">
         <v>-6.92</v>
       </c>
-      <c r="J18" t="inlineStr"/>
+      <c r="J18" t="n">
+        <v>-3.45</v>
+      </c>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="n">
         <v>-7.58</v>
       </c>
       <c r="M18" t="n">
-        <v>-4.82</v>
+        <v>-3.82</v>
       </c>
       <c r="N18" t="b">
         <v>0</v>
@@ -1838,7 +1846,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Retired</t>
         </is>
       </c>
       <c r="E19" t="inlineStr"/>
@@ -1849,18 +1857,20 @@
         <v>-26.8</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.07000000000000001</v>
+        <v>4.24</v>
       </c>
       <c r="I19" t="n">
         <v>1.39</v>
       </c>
-      <c r="J19" t="inlineStr"/>
+      <c r="J19" t="n">
+        <v>4.24</v>
+      </c>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="n">
         <v>-5.1</v>
       </c>
       <c r="M19" t="n">
-        <v>0.83</v>
+        <v>3.87</v>
       </c>
       <c r="N19" t="b">
         <v>0</v>
@@ -1887,7 +1897,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Extended</t>
+          <t>Retired</t>
         </is>
       </c>
       <c r="E20" t="inlineStr"/>
@@ -1898,18 +1908,20 @@
         <v>-7.1</v>
       </c>
       <c r="H20" t="n">
-        <v>5.55</v>
+        <v>-2.01</v>
       </c>
       <c r="I20" t="n">
         <v>9.390000000000001</v>
       </c>
-      <c r="J20" t="inlineStr"/>
+      <c r="J20" t="n">
+        <v>-2.01</v>
+      </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="n">
-        <v>-2.71</v>
+        <v>-8.41</v>
       </c>
       <c r="M20" t="n">
-        <v>6.44</v>
+        <v>-2.38</v>
       </c>
       <c r="N20" t="b">
         <v>0</v>
@@ -1936,7 +1948,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Extended</t>
+          <t>Retired</t>
         </is>
       </c>
       <c r="E21" t="inlineStr"/>
@@ -1947,18 +1959,20 @@
         <v>-11.5</v>
       </c>
       <c r="H21" t="n">
-        <v>22.43</v>
+        <v>13.34</v>
       </c>
       <c r="I21" t="n">
         <v>7.47</v>
       </c>
-      <c r="J21" t="inlineStr"/>
+      <c r="J21" t="n">
+        <v>13.34</v>
+      </c>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="n">
         <v>-0.99</v>
       </c>
       <c r="M21" t="n">
-        <v>23.33</v>
+        <v>12.97</v>
       </c>
       <c r="N21" t="b">
         <v>1</v>
@@ -1996,7 +2010,7 @@
         <v>0.1</v>
       </c>
       <c r="H22" t="n">
-        <v>19.97</v>
+        <v>23.27</v>
       </c>
       <c r="I22" t="n">
         <v>6.41</v>
@@ -2009,7 +2023,7 @@
         <v>-2.51</v>
       </c>
       <c r="M22" t="n">
-        <v>21.12</v>
+        <v>23.15</v>
       </c>
       <c r="N22" t="b">
         <v>1</v>
@@ -2047,7 +2061,7 @@
         <v>-31.6</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.97</v>
+        <v>1.45</v>
       </c>
       <c r="I23" t="n">
         <v>-2.12</v>
@@ -2060,7 +2074,7 @@
         <v>-8.140000000000001</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.83</v>
+        <v>1.34</v>
       </c>
       <c r="N23" t="b">
         <v>1</v>
@@ -2098,7 +2112,7 @@
         <v>7.6</v>
       </c>
       <c r="H24" t="n">
-        <v>11.07</v>
+        <v>10.74</v>
       </c>
       <c r="I24" t="n">
         <v>-3.6</v>
@@ -2111,7 +2125,7 @@
         <v>-9.359999999999999</v>
       </c>
       <c r="M24" t="n">
-        <v>11.61</v>
+        <v>10.01</v>
       </c>
       <c r="N24" t="b">
         <v>0</v>
@@ -2149,7 +2163,7 @@
         <v>-17.9</v>
       </c>
       <c r="H25" t="n">
-        <v>-6.83</v>
+        <v>-6.98</v>
       </c>
       <c r="I25" t="n">
         <v>-6.13</v>
@@ -2162,7 +2176,7 @@
         <v>-14.51</v>
       </c>
       <c r="M25" t="n">
-        <v>-5.02</v>
+        <v>-6.41</v>
       </c>
       <c r="N25" t="b">
         <v>0</v>
@@ -2200,7 +2214,7 @@
         <v>-25.3</v>
       </c>
       <c r="H26" t="n">
-        <v>12.91</v>
+        <v>10.46</v>
       </c>
       <c r="I26" t="n">
         <v>4.1</v>
@@ -2213,7 +2227,7 @@
         <v>-0.92</v>
       </c>
       <c r="M26" t="n">
-        <v>14.73</v>
+        <v>11.02</v>
       </c>
       <c r="N26" t="b">
         <v>0</v>
@@ -2251,7 +2265,7 @@
         <v>-2.7</v>
       </c>
       <c r="H27" t="n">
-        <v>-7.58</v>
+        <v>-5.9</v>
       </c>
       <c r="I27" t="n">
         <v>-3.77</v>
@@ -2264,7 +2278,7 @@
         <v>-12.44</v>
       </c>
       <c r="M27" t="n">
-        <v>-5.76</v>
+        <v>-5.33</v>
       </c>
       <c r="N27" t="b">
         <v>1</v>
@@ -2302,7 +2316,7 @@
         <v>25.6</v>
       </c>
       <c r="H28" t="n">
-        <v>8.15</v>
+        <v>5.9</v>
       </c>
       <c r="I28" t="n">
         <v>-0.42</v>
@@ -2315,7 +2329,7 @@
         <v>-8.35</v>
       </c>
       <c r="M28" t="n">
-        <v>9.970000000000001</v>
+        <v>6.47</v>
       </c>
       <c r="N28" t="b">
         <v>0</v>
@@ -2353,7 +2367,7 @@
         <v>26.9</v>
       </c>
       <c r="H29" t="n">
-        <v>-2.1</v>
+        <v>-2.72</v>
       </c>
       <c r="I29" t="n">
         <v>-3.24</v>
@@ -2366,7 +2380,7 @@
         <v>-12.88</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.28</v>
+        <v>-2.16</v>
       </c>
       <c r="N29" t="b">
         <v>1</v>
@@ -2404,7 +2418,7 @@
         <v>-14.5</v>
       </c>
       <c r="H30" t="n">
-        <v>-13.45</v>
+        <v>-12.93</v>
       </c>
       <c r="I30" t="n">
         <v>-3.75</v>
@@ -2417,7 +2431,7 @@
         <v>-9.01</v>
       </c>
       <c r="M30" t="n">
-        <v>-12.63</v>
+        <v>-13.37</v>
       </c>
       <c r="N30" t="b">
         <v>0</v>
@@ -2455,7 +2469,7 @@
         <v>17.2</v>
       </c>
       <c r="H31" t="n">
-        <v>3.27</v>
+        <v>1.36</v>
       </c>
       <c r="I31" t="n">
         <v>-1.49</v>
@@ -2468,7 +2482,7 @@
         <v>-10.54</v>
       </c>
       <c r="M31" t="n">
-        <v>4.09</v>
+        <v>0.91</v>
       </c>
       <c r="N31" t="b">
         <v>0</v>
@@ -2506,7 +2520,7 @@
         <v>-13.2</v>
       </c>
       <c r="H32" t="n">
-        <v>10.77</v>
+        <v>20.07</v>
       </c>
       <c r="I32" t="n">
         <v>23.71</v>
@@ -2519,7 +2533,7 @@
         <v>-0.82</v>
       </c>
       <c r="M32" t="n">
-        <v>11.58</v>
+        <v>19.63</v>
       </c>
       <c r="N32" t="b">
         <v>0</v>
@@ -2557,7 +2571,7 @@
         <v>-7.7</v>
       </c>
       <c r="H33" t="n">
-        <v>-6.45</v>
+        <v>-5.92</v>
       </c>
       <c r="I33" t="n">
         <v>-9.67</v>
@@ -2570,7 +2584,7 @@
         <v>-12.32</v>
       </c>
       <c r="M33" t="n">
-        <v>-5.63</v>
+        <v>-6.36</v>
       </c>
       <c r="N33" t="b">
         <v>0</v>
@@ -2608,7 +2622,7 @@
         <v>-21.5</v>
       </c>
       <c r="H34" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="I34" t="n">
         <v>-1.68</v>
@@ -2621,7 +2635,7 @@
         <v>-8.130000000000001</v>
       </c>
       <c r="M34" t="n">
-        <v>3.32</v>
+        <v>2.55</v>
       </c>
       <c r="N34" t="b">
         <v>1</v>
@@ -2659,7 +2673,7 @@
         <v>-18.1</v>
       </c>
       <c r="H35" t="n">
-        <v>18.32</v>
+        <v>18.03</v>
       </c>
       <c r="I35" t="n">
         <v>4.46</v>
@@ -2672,7 +2686,7 @@
         <v>-2.69</v>
       </c>
       <c r="M35" t="n">
-        <v>19.14</v>
+        <v>17.58</v>
       </c>
       <c r="N35" t="b">
         <v>1</v>
@@ -2710,7 +2724,7 @@
         <v>-18.1</v>
       </c>
       <c r="H36" t="n">
-        <v>-1</v>
+        <v>-1.8</v>
       </c>
       <c r="I36" t="n">
         <v>-2.43</v>
@@ -2723,7 +2737,7 @@
         <v>-6.41</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.18</v>
+        <v>-2.25</v>
       </c>
       <c r="N36" t="b">
         <v>0</v>
@@ -2761,7 +2775,7 @@
         <v>7.7</v>
       </c>
       <c r="H37" t="n">
-        <v>3.48</v>
+        <v>-0.43</v>
       </c>
       <c r="I37" t="n">
         <v>-6.85</v>
@@ -2774,7 +2788,7 @@
         <v>-9.359999999999999</v>
       </c>
       <c r="M37" t="n">
-        <v>4.3</v>
+        <v>-0.88</v>
       </c>
       <c r="N37" t="b">
         <v>0</v>
@@ -2812,7 +2826,7 @@
         <v>32.1</v>
       </c>
       <c r="H38" t="n">
-        <v>12.63</v>
+        <v>10.64</v>
       </c>
       <c r="I38" t="n">
         <v>-3.47</v>
@@ -2825,7 +2839,7 @@
         <v>-6.94</v>
       </c>
       <c r="M38" t="n">
-        <v>12.81</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="N38" t="b">
         <v>1</v>
@@ -2863,7 +2877,7 @@
         <v>41.6</v>
       </c>
       <c r="H39" t="n">
-        <v>8.42</v>
+        <v>10.53</v>
       </c>
       <c r="I39" t="n">
         <v>3.43</v>
@@ -2876,7 +2890,7 @@
         <v>-4.38</v>
       </c>
       <c r="M39" t="n">
-        <v>8.6</v>
+        <v>9.44</v>
       </c>
       <c r="N39" t="b">
         <v>1</v>
@@ -2914,7 +2928,7 @@
         <v>-14.4</v>
       </c>
       <c r="H40" t="n">
-        <v>8.81</v>
+        <v>9.09</v>
       </c>
       <c r="I40" t="n">
         <v>-2.38</v>
@@ -2927,7 +2941,7 @@
         <v>-6.46</v>
       </c>
       <c r="M40" t="n">
-        <v>8.99</v>
+        <v>7.99</v>
       </c>
       <c r="N40" t="b">
         <v>1</v>
@@ -2965,7 +2979,7 @@
         <v>-16.8</v>
       </c>
       <c r="H41" t="n">
-        <v>9.23</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="I41" t="n">
         <v>1.99</v>
@@ -2978,7 +2992,7 @@
         <v>-7.67</v>
       </c>
       <c r="M41" t="n">
-        <v>9.41</v>
+        <v>7.7</v>
       </c>
       <c r="N41" t="b">
         <v>0</v>
@@ -3016,7 +3030,7 @@
         <v>6.4</v>
       </c>
       <c r="H42" t="n">
-        <v>20.07</v>
+        <v>16.18</v>
       </c>
       <c r="I42" t="n">
         <v>1.48</v>
@@ -3029,7 +3043,7 @@
         <v>-3.35</v>
       </c>
       <c r="M42" t="n">
-        <v>20.24</v>
+        <v>15.08</v>
       </c>
       <c r="N42" t="b">
         <v>1</v>
@@ -3067,7 +3081,7 @@
         <v>-10</v>
       </c>
       <c r="H43" t="n">
-        <v>-12.33</v>
+        <v>-10.18</v>
       </c>
       <c r="I43" t="n">
         <v>-3.29</v>
@@ -3080,7 +3094,7 @@
         <v>-14.66</v>
       </c>
       <c r="M43" t="n">
-        <v>-12.15</v>
+        <v>-11.27</v>
       </c>
       <c r="N43" t="b">
         <v>1</v>
@@ -3118,7 +3132,7 @@
         <v>-11</v>
       </c>
       <c r="H44" t="n">
-        <v>47.76</v>
+        <v>48.38</v>
       </c>
       <c r="I44" t="n">
         <v>11.67</v>
@@ -3131,7 +3145,7 @@
         <v>-0.97</v>
       </c>
       <c r="M44" t="n">
-        <v>47.93</v>
+        <v>47.28</v>
       </c>
       <c r="N44" t="b">
         <v>0</v>
@@ -3169,7 +3183,7 @@
         <v>-23.9</v>
       </c>
       <c r="H45" t="n">
-        <v>-2.48</v>
+        <v>-2.94</v>
       </c>
       <c r="I45" t="n">
         <v>-4.98</v>
@@ -3182,7 +3196,7 @@
         <v>-7.87</v>
       </c>
       <c r="M45" t="n">
-        <v>-2.31</v>
+        <v>-4.05</v>
       </c>
       <c r="N45" t="b">
         <v>0</v>
@@ -3224,7 +3238,7 @@
         <v>-9.800000000000001</v>
       </c>
       <c r="H46" t="n">
-        <v>15.29</v>
+        <v>10.67</v>
       </c>
       <c r="I46" t="n">
         <v>-3.41</v>
@@ -3237,7 +3251,7 @@
         <v>-8.949999999999999</v>
       </c>
       <c r="M46" t="n">
-        <v>15.46</v>
+        <v>9.57</v>
       </c>
       <c r="N46" t="b">
         <v>0</v>
@@ -3275,7 +3289,7 @@
         <v>-7.9</v>
       </c>
       <c r="H47" t="n">
-        <v>-3.03</v>
+        <v>-3.26</v>
       </c>
       <c r="I47" t="n">
         <v>-8.83</v>
@@ -3288,7 +3302,7 @@
         <v>-12.99</v>
       </c>
       <c r="M47" t="n">
-        <v>-2.86</v>
+        <v>-4.36</v>
       </c>
       <c r="N47" t="b">
         <v>0</v>
@@ -3326,7 +3340,7 @@
         <v>-36.1</v>
       </c>
       <c r="H48" t="n">
-        <v>1.84</v>
+        <v>7.58</v>
       </c>
       <c r="I48" t="n">
         <v>-1.4</v>
@@ -3339,7 +3353,7 @@
         <v>-7.04</v>
       </c>
       <c r="M48" t="n">
-        <v>2.01</v>
+        <v>6.48</v>
       </c>
       <c r="N48" t="b">
         <v>0</v>
@@ -3377,7 +3391,7 @@
         <v>2.6</v>
       </c>
       <c r="H49" t="n">
-        <v>13.23</v>
+        <v>6.29</v>
       </c>
       <c r="I49" t="n">
         <v>-7.8</v>
@@ -3390,7 +3404,7 @@
         <v>-12.2</v>
       </c>
       <c r="M49" t="n">
-        <v>12.92</v>
+        <v>4.7</v>
       </c>
       <c r="N49" t="b">
         <v>0</v>
@@ -3428,7 +3442,7 @@
         <v>6.3</v>
       </c>
       <c r="H50" t="n">
-        <v>10.5</v>
+        <v>16.85</v>
       </c>
       <c r="I50" t="n">
         <v>0.64</v>
@@ -3441,7 +3455,7 @@
         <v>-2.13</v>
       </c>
       <c r="M50" t="n">
-        <v>10.19</v>
+        <v>15.26</v>
       </c>
       <c r="N50" t="b">
         <v>0</v>
@@ -3479,7 +3493,7 @@
         <v>20.2</v>
       </c>
       <c r="H51" t="n">
-        <v>-0.44</v>
+        <v>0.11</v>
       </c>
       <c r="I51" t="n">
         <v>3.45</v>
@@ -3492,7 +3506,7 @@
         <v>-1.07</v>
       </c>
       <c r="M51" t="n">
-        <v>-0.67</v>
+        <v>-1.4</v>
       </c>
       <c r="N51" t="b">
         <v>1</v>
@@ -3530,7 +3544,7 @@
         <v>1.9</v>
       </c>
       <c r="H52" t="n">
-        <v>0.4</v>
+        <v>6.91</v>
       </c>
       <c r="I52" t="n">
         <v>-10.64</v>
@@ -3543,7 +3557,7 @@
         <v>-14.75</v>
       </c>
       <c r="M52" t="n">
-        <v>0.17</v>
+        <v>5.4</v>
       </c>
       <c r="N52" t="b">
         <v>1</v>
@@ -3581,7 +3595,7 @@
         <v>43.7</v>
       </c>
       <c r="H53" t="n">
-        <v>16.17</v>
+        <v>18.83</v>
       </c>
       <c r="I53" t="n">
         <v>3.16</v>
@@ -3594,7 +3608,7 @@
         <v>-2.44</v>
       </c>
       <c r="M53" t="n">
-        <v>15.94</v>
+        <v>17.32</v>
       </c>
       <c r="N53" t="b">
         <v>1</v>
@@ -3632,7 +3646,7 @@
         <v>37.5</v>
       </c>
       <c r="H54" t="n">
-        <v>24.11</v>
+        <v>28.95</v>
       </c>
       <c r="I54" t="n">
         <v>5.86</v>
@@ -3645,7 +3659,7 @@
         <v>-3.95</v>
       </c>
       <c r="M54" t="n">
-        <v>23.74</v>
+        <v>27.3</v>
       </c>
       <c r="N54" t="b">
         <v>1</v>
@@ -3683,7 +3697,7 @@
         <v>15</v>
       </c>
       <c r="H55" t="n">
-        <v>-30.08</v>
+        <v>-28.86</v>
       </c>
       <c r="I55" t="n">
         <v>-21.11</v>
@@ -3696,7 +3710,7 @@
         <v>-28.65</v>
       </c>
       <c r="M55" t="n">
-        <v>-30.46</v>
+        <v>-30.52</v>
       </c>
       <c r="N55" t="b">
         <v>0</v>
@@ -3734,7 +3748,7 @@
         <v>40.2</v>
       </c>
       <c r="H56" t="n">
-        <v>10.78</v>
+        <v>12.14</v>
       </c>
       <c r="I56" t="n">
         <v>-1.11</v>
@@ -3747,7 +3761,7 @@
         <v>-5.29</v>
       </c>
       <c r="M56" t="n">
-        <v>10.4</v>
+        <v>10.49</v>
       </c>
       <c r="N56" t="b">
         <v>1</v>
@@ -3785,7 +3799,7 @@
         <v>10.7</v>
       </c>
       <c r="H57" t="n">
-        <v>-6.08</v>
+        <v>-2.73</v>
       </c>
       <c r="I57" t="n">
         <v>7.3</v>
@@ -3798,7 +3812,7 @@
         <v>-3.78</v>
       </c>
       <c r="M57" t="n">
-        <v>-6.45</v>
+        <v>-4.39</v>
       </c>
       <c r="N57" t="b">
         <v>1</v>
@@ -3836,7 +3850,7 @@
         <v>25.6</v>
       </c>
       <c r="H58" t="n">
-        <v>19.01</v>
+        <v>19.71</v>
       </c>
       <c r="I58" t="n">
         <v>7.71</v>
@@ -3849,7 +3863,7 @@
         <v>-4.85</v>
       </c>
       <c r="M58" t="n">
-        <v>19.39</v>
+        <v>18.81</v>
       </c>
       <c r="N58" t="b">
         <v>1</v>
@@ -3887,7 +3901,7 @@
         <v>6.3</v>
       </c>
       <c r="H59" t="n">
-        <v>-0.26</v>
+        <v>5.8</v>
       </c>
       <c r="I59" t="n">
         <v>7.2</v>
@@ -3900,7 +3914,7 @@
         <v>-0.4</v>
       </c>
       <c r="M59" t="n">
-        <v>-0.77</v>
+        <v>4.02</v>
       </c>
       <c r="N59" t="b">
         <v>0</v>
@@ -3938,7 +3952,7 @@
         <v>2.3</v>
       </c>
       <c r="H60" t="n">
-        <v>-7.36</v>
+        <v>-7.28</v>
       </c>
       <c r="I60" t="n">
         <v>-8.85</v>
@@ -3951,7 +3965,7 @@
         <v>-14.2</v>
       </c>
       <c r="M60" t="n">
-        <v>-7.86</v>
+        <v>-9.06</v>
       </c>
       <c r="N60" t="b">
         <v>0</v>
@@ -3989,7 +4003,7 @@
         <v>-29.4</v>
       </c>
       <c r="H61" t="n">
-        <v>-15.35</v>
+        <v>-17.68</v>
       </c>
       <c r="I61" t="n">
         <v>-5.75</v>
@@ -4002,7 +4016,7 @@
         <v>-10.11</v>
       </c>
       <c r="M61" t="n">
-        <v>-15.06</v>
+        <v>-18.66</v>
       </c>
       <c r="N61" t="b">
         <v>0</v>
@@ -4040,7 +4054,7 @@
         <v>-6.9</v>
       </c>
       <c r="H62" t="n">
-        <v>19.98</v>
+        <v>20.87</v>
       </c>
       <c r="I62" t="n">
         <v>6.44</v>
@@ -4053,7 +4067,7 @@
         <v>-4.53</v>
       </c>
       <c r="M62" t="n">
-        <v>20.27</v>
+        <v>19.89</v>
       </c>
       <c r="N62" t="b">
         <v>1</v>
@@ -4091,7 +4105,7 @@
         <v>-4.3</v>
       </c>
       <c r="H63" t="n">
-        <v>1.37</v>
+        <v>9.75</v>
       </c>
       <c r="I63" t="n">
         <v>3.39</v>
@@ -4104,7 +4118,7 @@
         <v>-5.89</v>
       </c>
       <c r="M63" t="n">
-        <v>1.66</v>
+        <v>8.77</v>
       </c>
       <c r="N63" t="b">
         <v>0</v>
@@ -4142,7 +4156,7 @@
         <v>4.2</v>
       </c>
       <c r="H64" t="n">
-        <v>-11.8</v>
+        <v>-12.75</v>
       </c>
       <c r="I64" t="n">
         <v>-10.83</v>
@@ -4155,7 +4169,7 @@
         <v>-18.5</v>
       </c>
       <c r="M64" t="n">
-        <v>-11.51</v>
+        <v>-13.73</v>
       </c>
       <c r="N64" t="b">
         <v>0</v>
@@ -4193,7 +4207,7 @@
         <v>-32.4</v>
       </c>
       <c r="H65" t="n">
-        <v>5.39</v>
+        <v>3.08</v>
       </c>
       <c r="I65" t="n">
         <v>-2.43</v>
@@ -4206,7 +4220,7 @@
         <v>-12.47</v>
       </c>
       <c r="M65" t="n">
-        <v>6.33</v>
+        <v>2.76</v>
       </c>
       <c r="N65" t="b">
         <v>0</v>
@@ -4244,7 +4258,7 @@
         <v>-11</v>
       </c>
       <c r="H66" t="n">
-        <v>3.71</v>
+        <v>12.46</v>
       </c>
       <c r="I66" t="n">
         <v>-8.449999999999999</v>
@@ -4257,7 +4271,7 @@
         <v>-18.92</v>
       </c>
       <c r="M66" t="n">
-        <v>4.65</v>
+        <v>12.13</v>
       </c>
       <c r="N66" t="b">
         <v>0</v>
@@ -4295,7 +4309,7 @@
         <v>-28.1</v>
       </c>
       <c r="H67" t="n">
-        <v>-5.95</v>
+        <v>-7.25</v>
       </c>
       <c r="I67" t="n">
         <v>-10.79</v>
@@ -4308,7 +4322,7 @@
         <v>-13.67</v>
       </c>
       <c r="M67" t="n">
-        <v>-5.16</v>
+        <v>-7.72</v>
       </c>
       <c r="N67" t="b">
         <v>0</v>
@@ -4346,7 +4360,7 @@
         <v>9.699999999999999</v>
       </c>
       <c r="H68" t="n">
-        <v>-2.03</v>
+        <v>2.93</v>
       </c>
       <c r="I68" t="n">
         <v>1.27</v>
@@ -4359,7 +4373,7 @@
         <v>-20.79</v>
       </c>
       <c r="M68" t="n">
-        <v>-1.24</v>
+        <v>2.45</v>
       </c>
       <c r="N68" t="b">
         <v>0</v>
@@ -4397,7 +4411,7 @@
         <v>-17.7</v>
       </c>
       <c r="H69" t="n">
-        <v>9.94</v>
+        <v>7.39</v>
       </c>
       <c r="I69" t="n">
         <v>-0.89</v>
@@ -4410,7 +4424,7 @@
         <v>-11.37</v>
       </c>
       <c r="M69" t="n">
-        <v>10.73</v>
+        <v>6.91</v>
       </c>
       <c r="N69" t="b">
         <v>0</v>
@@ -4448,7 +4462,7 @@
         <v>-9.300000000000001</v>
       </c>
       <c r="H70" t="n">
-        <v>-17.98</v>
+        <v>-14.38</v>
       </c>
       <c r="I70" t="n">
         <v>-3.34</v>
@@ -4461,7 +4475,7 @@
         <v>-8.77</v>
       </c>
       <c r="M70" t="n">
-        <v>-17.19</v>
+        <v>-14.86</v>
       </c>
       <c r="N70" t="b">
         <v>0</v>
@@ -4499,7 +4513,7 @@
         <v>0.3</v>
       </c>
       <c r="H71" t="n">
-        <v>-16.34</v>
+        <v>-13.73</v>
       </c>
       <c r="I71" t="n">
         <v>-10.53</v>
@@ -4512,7 +4526,7 @@
         <v>-17.73</v>
       </c>
       <c r="M71" t="n">
-        <v>-15.56</v>
+        <v>-14.21</v>
       </c>
       <c r="N71" t="b">
         <v>1</v>
@@ -4550,7 +4564,7 @@
         <v>-1.4</v>
       </c>
       <c r="H72" t="n">
-        <v>-6.79</v>
+        <v>-0.92</v>
       </c>
       <c r="I72" t="n">
         <v>-4.52</v>
@@ -4563,7 +4577,7 @@
         <v>-7.44</v>
       </c>
       <c r="M72" t="n">
-        <v>-6.71</v>
+        <v>-2.11</v>
       </c>
       <c r="N72" t="b">
         <v>0</v>
@@ -4601,7 +4615,7 @@
         <v>2.8</v>
       </c>
       <c r="H73" t="n">
-        <v>-1.37</v>
+        <v>3.37</v>
       </c>
       <c r="I73" t="n">
         <v>3.18</v>
@@ -4614,7 +4628,7 @@
         <v>-0.88</v>
       </c>
       <c r="M73" t="n">
-        <v>-1.29</v>
+        <v>2.17</v>
       </c>
       <c r="N73" t="b">
         <v>1</v>
@@ -4652,7 +4666,7 @@
         <v>12.3</v>
       </c>
       <c r="H74" t="n">
-        <v>3.25</v>
+        <v>3.48</v>
       </c>
       <c r="I74" t="n">
         <v>6.51</v>
@@ -4665,7 +4679,7 @@
         <v>-6.01</v>
       </c>
       <c r="M74" t="n">
-        <v>3.33</v>
+        <v>2.28</v>
       </c>
       <c r="N74" t="b">
         <v>0</v>
@@ -4703,7 +4717,7 @@
         <v>34.5</v>
       </c>
       <c r="H75" t="n">
-        <v>11.84</v>
+        <v>10.46</v>
       </c>
       <c r="I75" t="n">
         <v>0.66</v>
@@ -4716,7 +4730,7 @@
         <v>-2.64</v>
       </c>
       <c r="M75" t="n">
-        <v>11.92</v>
+        <v>9.26</v>
       </c>
       <c r="N75" t="b">
         <v>1</v>
@@ -4754,7 +4768,7 @@
         <v>-22.7</v>
       </c>
       <c r="H76" t="n">
-        <v>-18.67</v>
+        <v>-17.54</v>
       </c>
       <c r="I76" t="n">
         <v>-6.71</v>
@@ -4767,7 +4781,7 @@
         <v>-9.58</v>
       </c>
       <c r="M76" t="n">
-        <v>-18.65</v>
+        <v>-18.8</v>
       </c>
       <c r="N76" t="b">
         <v>0</v>
@@ -4805,7 +4819,7 @@
         <v>24.3</v>
       </c>
       <c r="H77" t="n">
-        <v>30.41</v>
+        <v>46.7</v>
       </c>
       <c r="I77" t="n">
         <v>2.54</v>
@@ -4818,7 +4832,7 @@
         <v>-5.21</v>
       </c>
       <c r="M77" t="n">
-        <v>31.12</v>
+        <v>46.14</v>
       </c>
       <c r="N77" t="b">
         <v>1</v>
@@ -4856,7 +4870,7 @@
         <v>56.6</v>
       </c>
       <c r="H78" t="n">
-        <v>4.52</v>
+        <v>7.67</v>
       </c>
       <c r="I78" t="n">
         <v>-13.1</v>
@@ -4869,7 +4883,7 @@
         <v>-16.17</v>
       </c>
       <c r="M78" t="n">
-        <v>5.23</v>
+        <v>7.12</v>
       </c>
       <c r="N78" t="b">
         <v>0</v>
@@ -4907,7 +4921,7 @@
         <v>2.9</v>
       </c>
       <c r="H79" t="n">
-        <v>-16.39</v>
+        <v>-15.86</v>
       </c>
       <c r="I79" t="n">
         <v>-8.470000000000001</v>
@@ -4920,7 +4934,7 @@
         <v>-15.65</v>
       </c>
       <c r="M79" t="n">
-        <v>-15.68</v>
+        <v>-16.42</v>
       </c>
       <c r="N79" t="b">
         <v>0</v>
@@ -4958,7 +4972,7 @@
         <v>-16.9</v>
       </c>
       <c r="H80" t="n">
-        <v>5.12</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I80" t="n">
         <v>-6.47</v>
@@ -4971,7 +4985,7 @@
         <v>-11.5</v>
       </c>
       <c r="M80" t="n">
-        <v>5.83</v>
+        <v>8.65</v>
       </c>
       <c r="N80" t="b">
         <v>1</v>
@@ -5009,7 +5023,7 @@
         <v>32.8</v>
       </c>
       <c r="H81" t="n">
-        <v>13.68</v>
+        <v>13.48</v>
       </c>
       <c r="I81" t="n">
         <v>14.96</v>
@@ -5022,7 +5036,7 @@
         <v>-0.9</v>
       </c>
       <c r="M81" t="n">
-        <v>14.96</v>
+        <v>13.5</v>
       </c>
       <c r="N81" t="b">
         <v>0</v>
@@ -5060,7 +5074,7 @@
         <v>0.8</v>
       </c>
       <c r="H82" t="n">
-        <v>-13.74</v>
+        <v>-8.199999999999999</v>
       </c>
       <c r="I82" t="n">
         <v>-7.73</v>
@@ -5073,7 +5087,7 @@
         <v>-10.12</v>
       </c>
       <c r="M82" t="n">
-        <v>-12.46</v>
+        <v>-8.18</v>
       </c>
       <c r="N82" t="b">
         <v>0</v>
@@ -5111,7 +5125,7 @@
         <v>-9.6</v>
       </c>
       <c r="H83" t="n">
-        <v>-17.95</v>
+        <v>-16.11</v>
       </c>
       <c r="I83" t="n">
         <v>-1.23</v>
@@ -5124,7 +5138,7 @@
         <v>-18.52</v>
       </c>
       <c r="M83" t="n">
-        <v>-16.67</v>
+        <v>-16.09</v>
       </c>
       <c r="N83" t="b">
         <v>0</v>
@@ -5162,7 +5176,7 @@
         <v>20.3</v>
       </c>
       <c r="H84" t="n">
-        <v>-19.15</v>
+        <v>-20.48</v>
       </c>
       <c r="I84" t="n">
         <v>-2.07</v>
@@ -5175,7 +5189,7 @@
         <v>-17.35</v>
       </c>
       <c r="M84" t="n">
-        <v>-18.29</v>
+        <v>-20.88</v>
       </c>
       <c r="N84" t="b">
         <v>1</v>
@@ -5213,7 +5227,7 @@
         <v>0.3</v>
       </c>
       <c r="H85" t="n">
-        <v>-22.08</v>
+        <v>-22.98</v>
       </c>
       <c r="I85" t="n">
         <v>-9.9</v>
@@ -5226,7 +5240,7 @@
         <v>-21.72</v>
       </c>
       <c r="M85" t="n">
-        <v>-21.7</v>
+        <v>-23.87</v>
       </c>
       <c r="N85" t="b">
         <v>1</v>
@@ -5264,7 +5278,7 @@
         <v>49.4</v>
       </c>
       <c r="H86" t="n">
-        <v>1.02</v>
+        <v>4.74</v>
       </c>
       <c r="I86" t="n">
         <v>2.9</v>
@@ -5277,7 +5291,7 @@
         <v>-5.67</v>
       </c>
       <c r="M86" t="n">
-        <v>1.58</v>
+        <v>4.04</v>
       </c>
       <c r="N86" t="b">
         <v>1</v>
@@ -5315,7 +5329,7 @@
         <v>4.5</v>
       </c>
       <c r="H87" t="n">
-        <v>0.73</v>
+        <v>-2.67</v>
       </c>
       <c r="I87" t="n">
         <v>-7.61</v>
@@ -5328,7 +5342,7 @@
         <v>-11.06</v>
       </c>
       <c r="M87" t="n">
-        <v>1.29</v>
+        <v>-3.38</v>
       </c>
       <c r="N87" t="b">
         <v>1</v>
@@ -5366,7 +5380,7 @@
         <v>4.2</v>
       </c>
       <c r="H88" t="n">
-        <v>-18.37</v>
+        <v>-19.17</v>
       </c>
       <c r="I88" t="n">
         <v>-6.86</v>
@@ -5379,7 +5393,7 @@
         <v>-20.23</v>
       </c>
       <c r="M88" t="n">
-        <v>-17.81</v>
+        <v>-19.87</v>
       </c>
       <c r="N88" t="b">
         <v>0</v>
@@ -5417,7 +5431,7 @@
         <v>15.4</v>
       </c>
       <c r="H89" t="n">
-        <v>5.75</v>
+        <v>3.8</v>
       </c>
       <c r="I89" t="n">
         <v>-1.19</v>
@@ -5430,7 +5444,7 @@
         <v>-7.43</v>
       </c>
       <c r="M89" t="n">
-        <v>6.31</v>
+        <v>3.09</v>
       </c>
       <c r="N89" t="b">
         <v>0</v>
@@ -5468,7 +5482,7 @@
         <v>15.5</v>
       </c>
       <c r="H90" t="n">
-        <v>4.17</v>
+        <v>-0.05</v>
       </c>
       <c r="I90" t="n">
         <v>-7.36</v>
@@ -5481,7 +5495,7 @@
         <v>-12.98</v>
       </c>
       <c r="M90" t="n">
-        <v>4.55</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="N90" t="b">
         <v>0</v>
@@ -5523,7 +5537,7 @@
         <v>-8.5</v>
       </c>
       <c r="H91" t="n">
-        <v>36.14</v>
+        <v>28.38</v>
       </c>
       <c r="I91" t="n">
         <v>-3.04</v>
@@ -5536,7 +5550,7 @@
         <v>-4.96</v>
       </c>
       <c r="M91" t="n">
-        <v>36.52</v>
+        <v>27.5</v>
       </c>
       <c r="N91" t="b">
         <v>0</v>
@@ -5574,7 +5588,7 @@
         <v>1.8</v>
       </c>
       <c r="H92" t="n">
-        <v>-4.07</v>
+        <v>-9.69</v>
       </c>
       <c r="I92" t="n">
         <v>-6.45</v>
@@ -5587,7 +5601,7 @@
         <v>-13.57</v>
       </c>
       <c r="M92" t="n">
-        <v>-3.68</v>
+        <v>-10.58</v>
       </c>
       <c r="N92" t="b">
         <v>0</v>
@@ -5625,7 +5639,7 @@
         <v>33.9</v>
       </c>
       <c r="H93" t="n">
-        <v>13.96</v>
+        <v>21.79</v>
       </c>
       <c r="I93" t="n">
         <v>-7.74</v>
@@ -5638,7 +5652,7 @@
         <v>-9.449999999999999</v>
       </c>
       <c r="M93" t="n">
-        <v>14.34</v>
+        <v>20.91</v>
       </c>
       <c r="N93" t="b">
         <v>0</v>
@@ -5676,7 +5690,7 @@
         <v>-25</v>
       </c>
       <c r="H94" t="n">
-        <v>-6.38</v>
+        <v>-4.77</v>
       </c>
       <c r="I94" t="n">
         <v>2.51</v>
@@ -5689,7 +5703,7 @@
         <v>-4.88</v>
       </c>
       <c r="M94" t="n">
-        <v>-5.83</v>
+        <v>-5.49</v>
       </c>
       <c r="N94" t="b">
         <v>0</v>
@@ -5727,7 +5741,7 @@
         <v>-12.6</v>
       </c>
       <c r="H95" t="n">
-        <v>-17.35</v>
+        <v>-17.05</v>
       </c>
       <c r="I95" t="n">
         <v>-7.89</v>
@@ -5740,7 +5754,7 @@
         <v>-21.29</v>
       </c>
       <c r="M95" t="n">
-        <v>-16.81</v>
+        <v>-17.78</v>
       </c>
       <c r="N95" t="b">
         <v>0</v>
@@ -5778,7 +5792,7 @@
         <v>2.1</v>
       </c>
       <c r="H96" t="n">
-        <v>-3.32</v>
+        <v>-6.85</v>
       </c>
       <c r="I96" t="n">
         <v>0.25</v>
@@ -5791,7 +5805,7 @@
         <v>-16.43</v>
       </c>
       <c r="M96" t="n">
-        <v>-2.79</v>
+        <v>-7.58</v>
       </c>
       <c r="N96" t="b">
         <v>1</v>
@@ -5829,7 +5843,7 @@
         <v>-17.9</v>
       </c>
       <c r="H97" t="n">
-        <v>8.51</v>
+        <v>7.56</v>
       </c>
       <c r="I97" t="n">
         <v>0.6</v>
@@ -5842,7 +5856,7 @@
         <v>-4.72</v>
       </c>
       <c r="M97" t="n">
-        <v>9.039999999999999</v>
+        <v>6.83</v>
       </c>
       <c r="N97" t="b">
         <v>1</v>
@@ -5880,7 +5894,7 @@
         <v>19.4</v>
       </c>
       <c r="H98" t="n">
-        <v>-7.56</v>
+        <v>-8.17</v>
       </c>
       <c r="I98" t="n">
         <v>-10.01</v>
@@ -5893,7 +5907,7 @@
         <v>-15.23</v>
       </c>
       <c r="M98" t="n">
-        <v>-6.46</v>
+        <v>-8.33</v>
       </c>
       <c r="N98" t="b">
         <v>1</v>
@@ -5931,7 +5945,7 @@
         <v>-20.5</v>
       </c>
       <c r="H99" t="n">
-        <v>-15.43</v>
+        <v>-10.56</v>
       </c>
       <c r="I99" t="n">
         <v>-4.62</v>
@@ -5944,7 +5958,7 @@
         <v>-9.92</v>
       </c>
       <c r="M99" t="n">
-        <v>-14.32</v>
+        <v>-10.72</v>
       </c>
       <c r="N99" t="b">
         <v>0</v>
@@ -5982,7 +5996,7 @@
         <v>-30.5</v>
       </c>
       <c r="H100" t="n">
-        <v>-3.05</v>
+        <v>-3.53</v>
       </c>
       <c r="I100" t="n">
         <v>-4.6</v>
@@ -5995,7 +6009,7 @@
         <v>-10.37</v>
       </c>
       <c r="M100" t="n">
-        <v>-1.94</v>
+        <v>-3.68</v>
       </c>
       <c r="N100" t="b">
         <v>0</v>
@@ -6033,7 +6047,7 @@
         <v>-12.3</v>
       </c>
       <c r="H101" t="n">
-        <v>-14.46</v>
+        <v>-19.77</v>
       </c>
       <c r="I101" t="n">
         <v>-4.36</v>
@@ -6046,7 +6060,7 @@
         <v>-13.26</v>
       </c>
       <c r="M101" t="n">
-        <v>-13.57</v>
+        <v>-20.14</v>
       </c>
       <c r="N101" t="b">
         <v>0</v>
@@ -6084,7 +6098,7 @@
         <v>13.7</v>
       </c>
       <c r="H102" t="n">
-        <v>-22.34</v>
+        <v>-20.57</v>
       </c>
       <c r="I102" t="n">
         <v>-12.16</v>
@@ -6097,7 +6111,7 @@
         <v>-13.02</v>
       </c>
       <c r="M102" t="n">
-        <v>-21.45</v>
+        <v>-20.94</v>
       </c>
       <c r="N102" t="b">
         <v>0</v>
@@ -6135,7 +6149,7 @@
         <v>-2.6</v>
       </c>
       <c r="H103" t="n">
-        <v>-7.85</v>
+        <v>-17.1</v>
       </c>
       <c r="I103" t="n">
         <v>-4.27</v>
@@ -6148,7 +6162,7 @@
         <v>-4.86</v>
       </c>
       <c r="M103" t="n">
-        <v>-6.96</v>
+        <v>-17.47</v>
       </c>
       <c r="N103" t="b">
         <v>1</v>
@@ -6186,7 +6200,7 @@
         <v>25.6</v>
       </c>
       <c r="H104" t="n">
-        <v>10.87</v>
+        <v>11.8</v>
       </c>
       <c r="I104" t="n">
         <v>4.26</v>
@@ -6199,7 +6213,7 @@
         <v>-10.74</v>
       </c>
       <c r="M104" t="n">
-        <v>11.76</v>
+        <v>11.42</v>
       </c>
       <c r="N104" t="b">
         <v>0</v>
@@ -6237,7 +6251,7 @@
         <v>23.8</v>
       </c>
       <c r="H105" t="n">
-        <v>0.71</v>
+        <v>6.22</v>
       </c>
       <c r="I105" t="n">
         <v>1.36</v>
@@ -6250,7 +6264,7 @@
         <v>-9.94</v>
       </c>
       <c r="M105" t="n">
-        <v>2.56</v>
+        <v>6.81</v>
       </c>
       <c r="N105" t="b">
         <v>1</v>
@@ -6288,7 +6302,7 @@
         <v>32.1</v>
       </c>
       <c r="H106" t="n">
-        <v>41.05</v>
+        <v>46.31</v>
       </c>
       <c r="I106" t="n">
         <v>11.84</v>
@@ -6301,7 +6315,7 @@
         <v>-1.82</v>
       </c>
       <c r="M106" t="n">
-        <v>42.9</v>
+        <v>46.91</v>
       </c>
       <c r="N106" t="b">
         <v>0</v>
@@ -6339,7 +6353,7 @@
         <v>38.9</v>
       </c>
       <c r="H107" t="n">
-        <v>-15.26</v>
+        <v>-10.49</v>
       </c>
       <c r="I107" t="n">
         <v>-9.220000000000001</v>
@@ -6352,7 +6366,7 @@
         <v>-9.83</v>
       </c>
       <c r="M107" t="n">
-        <v>-13.42</v>
+        <v>-9.9</v>
       </c>
       <c r="N107" t="b">
         <v>1</v>
@@ -6390,7 +6404,7 @@
         <v>53.4</v>
       </c>
       <c r="H108" t="n">
-        <v>22.27</v>
+        <v>12.95</v>
       </c>
       <c r="I108" t="n">
         <v>2.75</v>
@@ -6403,7 +6417,7 @@
         <v>-2.31</v>
       </c>
       <c r="M108" t="n">
-        <v>24.41</v>
+        <v>13.85</v>
       </c>
       <c r="N108" t="b">
         <v>0</v>
@@ -6441,7 +6455,7 @@
         <v>54.1</v>
       </c>
       <c r="H109" t="n">
-        <v>32.74</v>
+        <v>26.57</v>
       </c>
       <c r="I109" t="n">
         <v>5.54</v>
@@ -6454,7 +6468,7 @@
         <v>-0.41</v>
       </c>
       <c r="M109" t="n">
-        <v>34.42</v>
+        <v>27</v>
       </c>
       <c r="N109" t="b">
         <v>0</v>
@@ -6492,7 +6506,7 @@
         <v>43.2</v>
       </c>
       <c r="H110" t="n">
-        <v>-7.52</v>
+        <v>-10.7</v>
       </c>
       <c r="I110" t="n">
         <v>-3.15</v>
@@ -6505,7 +6519,7 @@
         <v>-17.51</v>
       </c>
       <c r="M110" t="n">
-        <v>-5.84</v>
+        <v>-10.28</v>
       </c>
       <c r="N110" t="b">
         <v>1</v>
@@ -6543,7 +6557,7 @@
         <v>-8.199999999999999</v>
       </c>
       <c r="H111" t="n">
-        <v>8.31</v>
+        <v>3.8</v>
       </c>
       <c r="I111" t="n">
         <v>5.34</v>
@@ -6556,7 +6570,7 @@
         <v>-5.27</v>
       </c>
       <c r="M111" t="n">
-        <v>9.99</v>
+        <v>4.23</v>
       </c>
       <c r="N111" t="b">
         <v>1</v>
@@ -6594,7 +6608,7 @@
         <v>-1.2</v>
       </c>
       <c r="H112" t="n">
-        <v>14.48</v>
+        <v>8.84</v>
       </c>
       <c r="I112" t="n">
         <v>8.27</v>
@@ -6607,7 +6621,7 @@
         <v>-5.3</v>
       </c>
       <c r="M112" t="n">
-        <v>16.11</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="N112" t="b">
         <v>0</v>
@@ -6645,7 +6659,7 @@
         <v>-23.9</v>
       </c>
       <c r="H113" t="n">
-        <v>3.77</v>
+        <v>7.34</v>
       </c>
       <c r="I113" t="n">
         <v>3.28</v>
@@ -6658,7 +6672,7 @@
         <v>-4.46</v>
       </c>
       <c r="M113" t="n">
-        <v>5.16</v>
+        <v>7.48</v>
       </c>
       <c r="N113" t="b">
         <v>1</v>
@@ -6700,7 +6714,7 @@
         <v>-6.1</v>
       </c>
       <c r="H114" t="n">
-        <v>-21.37</v>
+        <v>-17.18</v>
       </c>
       <c r="I114" t="n">
         <v>4.9</v>
@@ -6713,7 +6727,7 @@
         <v>-9</v>
       </c>
       <c r="M114" t="n">
-        <v>-19.98</v>
+        <v>-17.05</v>
       </c>
       <c r="N114" t="b">
         <v>0</v>
@@ -6751,7 +6765,7 @@
         <v>39.5</v>
       </c>
       <c r="H115" t="n">
-        <v>10.23</v>
+        <v>10.93</v>
       </c>
       <c r="I115" t="n">
         <v>-5.13</v>
@@ -6764,7 +6778,7 @@
         <v>-8.869999999999999</v>
       </c>
       <c r="M115" t="n">
-        <v>11.62</v>
+        <v>11.06</v>
       </c>
       <c r="N115" t="b">
         <v>0</v>
@@ -6802,7 +6816,7 @@
         <v>14.3</v>
       </c>
       <c r="H116" t="n">
-        <v>12.12</v>
+        <v>10.22</v>
       </c>
       <c r="I116" t="n">
         <v>-0.43</v>
@@ -6815,7 +6829,7 @@
         <v>-11.86</v>
       </c>
       <c r="M116" t="n">
-        <v>13.51</v>
+        <v>10.35</v>
       </c>
       <c r="N116" t="b">
         <v>0</v>
@@ -6853,7 +6867,7 @@
         <v>26.7</v>
       </c>
       <c r="H117" t="n">
-        <v>-1.04</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="I117" t="n">
         <v>-0.05</v>
@@ -6866,7 +6880,7 @@
         <v>-0.87</v>
       </c>
       <c r="M117" t="n">
-        <v>0.35</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="N117" t="b">
         <v>1</v>
@@ -6904,7 +6918,7 @@
         <v>-11.3</v>
       </c>
       <c r="H118" t="n">
-        <v>-6.09</v>
+        <v>-4.04</v>
       </c>
       <c r="I118" t="n">
         <v>1.31</v>
@@ -6917,7 +6931,7 @@
         <v>-1.88</v>
       </c>
       <c r="M118" t="n">
-        <v>-4.7</v>
+        <v>-3.91</v>
       </c>
       <c r="N118" t="b">
         <v>0</v>
@@ -6955,7 +6969,7 @@
         <v>-23.5</v>
       </c>
       <c r="H119" t="n">
-        <v>-20.81</v>
+        <v>-32.81</v>
       </c>
       <c r="I119" t="n">
         <v>13.29</v>
@@ -6968,7 +6982,7 @@
         <v>-14.04</v>
       </c>
       <c r="M119" t="n">
-        <v>-19.42</v>
+        <v>-32.68</v>
       </c>
       <c r="N119" t="b">
         <v>0</v>
@@ -7006,7 +7020,7 @@
         <v>10.5</v>
       </c>
       <c r="H120" t="n">
-        <v>-8.65</v>
+        <v>-7</v>
       </c>
       <c r="I120" t="n">
         <v>-0.86</v>
@@ -7019,7 +7033,7 @@
         <v>-6.11</v>
       </c>
       <c r="M120" t="n">
-        <v>-7.26</v>
+        <v>-6.87</v>
       </c>
       <c r="N120" t="b">
         <v>0</v>
@@ -7057,7 +7071,7 @@
         <v>2.4</v>
       </c>
       <c r="H121" t="n">
-        <v>22.91</v>
+        <v>24.15</v>
       </c>
       <c r="I121" t="n">
         <v>12.41</v>
@@ -7070,7 +7084,7 @@
         <v>-0.07000000000000001</v>
       </c>
       <c r="M121" t="n">
-        <v>24.1</v>
+        <v>24.08</v>
       </c>
       <c r="N121" t="b">
         <v>0</v>
@@ -7108,7 +7122,7 @@
         <v>-3.5</v>
       </c>
       <c r="H122" t="n">
-        <v>-0.5600000000000001</v>
+        <v>7.3</v>
       </c>
       <c r="I122" t="n">
         <v>-4.95</v>
@@ -7121,7 +7135,7 @@
         <v>-8.43</v>
       </c>
       <c r="M122" t="n">
-        <v>0.63</v>
+        <v>7.23</v>
       </c>
       <c r="N122" t="b">
         <v>1</v>
@@ -7159,7 +7173,7 @@
         <v>-12.8</v>
       </c>
       <c r="H123" t="n">
-        <v>1.28</v>
+        <v>5.98</v>
       </c>
       <c r="I123" t="n">
         <v>-1.74</v>
@@ -7172,7 +7186,7 @@
         <v>-2.97</v>
       </c>
       <c r="M123" t="n">
-        <v>2.47</v>
+        <v>5.91</v>
       </c>
       <c r="N123" t="b">
         <v>0</v>
@@ -7210,7 +7224,7 @@
         <v>-17.9</v>
       </c>
       <c r="H124" t="n">
-        <v>2.1</v>
+        <v>3.6</v>
       </c>
       <c r="I124" t="n">
         <v>-0.5</v>
@@ -7223,7 +7237,7 @@
         <v>-3.43</v>
       </c>
       <c r="M124" t="n">
-        <v>3.29</v>
+        <v>3.53</v>
       </c>
       <c r="N124" t="b">
         <v>1</v>
@@ -7261,7 +7275,7 @@
         <v>11.9</v>
       </c>
       <c r="H125" t="n">
-        <v>-1.94</v>
+        <v>-3.54</v>
       </c>
       <c r="I125" t="n">
         <v>6.88</v>
@@ -7274,7 +7288,7 @@
         <v>-10.93</v>
       </c>
       <c r="M125" t="n">
-        <v>-0.85</v>
+        <v>-3.71</v>
       </c>
       <c r="N125" t="b">
         <v>0</v>
@@ -7312,7 +7326,7 @@
         <v>53.5</v>
       </c>
       <c r="H126" t="n">
-        <v>20.39</v>
+        <v>26.61</v>
       </c>
       <c r="I126" t="n">
         <v>1.23</v>
@@ -7325,7 +7339,7 @@
         <v>-7.57</v>
       </c>
       <c r="M126" t="n">
-        <v>21.47</v>
+        <v>26.43</v>
       </c>
       <c r="N126" t="b">
         <v>1</v>
@@ -7363,7 +7377,7 @@
         <v>18.1</v>
       </c>
       <c r="H127" t="n">
-        <v>-4.48</v>
+        <v>-4.31</v>
       </c>
       <c r="I127" t="n">
         <v>-1.69</v>
@@ -7376,7 +7390,7 @@
         <v>-1.92</v>
       </c>
       <c r="M127" t="n">
-        <v>-3.39</v>
+        <v>-4.49</v>
       </c>
       <c r="N127" t="b">
         <v>0</v>
@@ -7414,7 +7428,7 @@
         <v>-1</v>
       </c>
       <c r="H128" t="n">
-        <v>-14.06</v>
+        <v>-16.05</v>
       </c>
       <c r="I128" t="n">
         <v>-6.26</v>
@@ -7427,7 +7441,7 @@
         <v>-15</v>
       </c>
       <c r="M128" t="n">
-        <v>-12.98</v>
+        <v>-16.23</v>
       </c>
       <c r="N128" t="b">
         <v>1</v>
@@ -7465,7 +7479,7 @@
         <v>29.7</v>
       </c>
       <c r="H129" t="n">
-        <v>10.21</v>
+        <v>10.36</v>
       </c>
       <c r="I129" t="n">
         <v>11.27</v>
@@ -7478,7 +7492,7 @@
         <v>0</v>
       </c>
       <c r="M129" t="n">
-        <v>11.29</v>
+        <v>10.18</v>
       </c>
       <c r="N129" t="b">
         <v>1</v>
@@ -7516,7 +7530,7 @@
         <v>-2.1</v>
       </c>
       <c r="H130" t="n">
-        <v>-24.29</v>
+        <v>-24.35</v>
       </c>
       <c r="I130" t="n">
         <v>0.67</v>
@@ -7529,7 +7543,7 @@
         <v>-7.84</v>
       </c>
       <c r="M130" t="n">
-        <v>-22.48</v>
+        <v>-23.8</v>
       </c>
       <c r="N130" t="b">
         <v>0</v>
@@ -7567,7 +7581,7 @@
         <v>10.8</v>
       </c>
       <c r="H131" t="n">
-        <v>9.81</v>
+        <v>4.73</v>
       </c>
       <c r="I131" t="n">
         <v>5.62</v>
@@ -7580,7 +7594,7 @@
         <v>-1.59</v>
       </c>
       <c r="M131" t="n">
-        <v>11.62</v>
+        <v>5.28</v>
       </c>
       <c r="N131" t="b">
         <v>0</v>
@@ -7618,7 +7632,7 @@
         <v>15.2</v>
       </c>
       <c r="H132" t="n">
-        <v>-26.24</v>
+        <v>-24.45</v>
       </c>
       <c r="I132" t="n">
         <v>-8.77</v>
@@ -7631,7 +7645,7 @@
         <v>-24.79</v>
       </c>
       <c r="M132" t="n">
-        <v>-24.43</v>
+        <v>-23.9</v>
       </c>
       <c r="N132" t="b">
         <v>1</v>
@@ -7669,7 +7683,7 @@
         <v>22.2</v>
       </c>
       <c r="H133" t="n">
-        <v>12.28</v>
+        <v>14.04</v>
       </c>
       <c r="I133" t="n">
         <v>1.01</v>
@@ -7682,7 +7696,7 @@
         <v>-3.94</v>
       </c>
       <c r="M133" t="n">
-        <v>14.08</v>
+        <v>14.59</v>
       </c>
       <c r="N133" t="b">
         <v>1</v>
@@ -7720,7 +7734,7 @@
         <v>16.7</v>
       </c>
       <c r="H134" t="n">
-        <v>-27</v>
+        <v>-23.99</v>
       </c>
       <c r="I134" t="n">
         <v>-15.31</v>
@@ -7733,7 +7747,7 @@
         <v>-22</v>
       </c>
       <c r="M134" t="n">
-        <v>-27.17</v>
+        <v>-25.43</v>
       </c>
       <c r="N134" t="b">
         <v>0</v>
@@ -7771,7 +7785,7 @@
         <v>0.3</v>
       </c>
       <c r="H135" t="n">
-        <v>51.11</v>
+        <v>45.38</v>
       </c>
       <c r="I135" t="n">
         <v>6.01</v>
@@ -7779,12 +7793,14 @@
       <c r="J135" t="n">
         <v>17.44</v>
       </c>
-      <c r="K135" t="inlineStr"/>
+      <c r="K135" t="n">
+        <v>45.38</v>
+      </c>
       <c r="L135" t="n">
         <v>-3.85</v>
       </c>
       <c r="M135" t="n">
-        <v>49.45</v>
+        <v>42.43</v>
       </c>
       <c r="N135" t="b">
         <v>0</v>
@@ -7826,7 +7842,7 @@
         <v>-0</v>
       </c>
       <c r="H136" t="n">
-        <v>53.84</v>
+        <v>49.27</v>
       </c>
       <c r="I136" t="n">
         <v>13.5</v>
@@ -7834,12 +7850,14 @@
       <c r="J136" t="n">
         <v>36.05</v>
       </c>
-      <c r="K136" t="inlineStr"/>
+      <c r="K136" t="n">
+        <v>49.27</v>
+      </c>
       <c r="L136" t="n">
         <v>-2.53</v>
       </c>
       <c r="M136" t="n">
-        <v>52.18</v>
+        <v>46.32</v>
       </c>
       <c r="N136" t="b">
         <v>1</v>
@@ -7877,7 +7895,7 @@
         <v>30.4</v>
       </c>
       <c r="H137" t="n">
-        <v>8.73</v>
+        <v>7.41</v>
       </c>
       <c r="I137" t="n">
         <v>8.539999999999999</v>
@@ -7885,12 +7903,14 @@
       <c r="J137" t="n">
         <v>7.6</v>
       </c>
-      <c r="K137" t="inlineStr"/>
+      <c r="K137" t="n">
+        <v>7.41</v>
+      </c>
       <c r="L137" t="n">
         <v>-0.44</v>
       </c>
       <c r="M137" t="n">
-        <v>7.07</v>
+        <v>4.46</v>
       </c>
       <c r="N137" t="b">
         <v>0</v>
@@ -7928,7 +7948,7 @@
         <v>10.5</v>
       </c>
       <c r="H138" t="n">
-        <v>24.23</v>
+        <v>19.24</v>
       </c>
       <c r="I138" t="n">
         <v>1.99</v>
@@ -7936,12 +7956,14 @@
       <c r="J138" t="n">
         <v>12.33</v>
       </c>
-      <c r="K138" t="inlineStr"/>
+      <c r="K138" t="n">
+        <v>19.24</v>
+      </c>
       <c r="L138" t="n">
         <v>-6.27</v>
       </c>
       <c r="M138" t="n">
-        <v>22.57</v>
+        <v>16.29</v>
       </c>
       <c r="N138" t="b">
         <v>1</v>
@@ -7979,7 +8001,7 @@
         <v>-27.3</v>
       </c>
       <c r="H139" t="n">
-        <v>25.82</v>
+        <v>23.18</v>
       </c>
       <c r="I139" t="n">
         <v>-8.83</v>
@@ -7987,12 +8009,14 @@
       <c r="J139" t="n">
         <v>8.81</v>
       </c>
-      <c r="K139" t="inlineStr"/>
+      <c r="K139" t="n">
+        <v>23.18</v>
+      </c>
       <c r="L139" t="n">
         <v>-19.66</v>
       </c>
       <c r="M139" t="n">
-        <v>24.16</v>
+        <v>20.23</v>
       </c>
       <c r="N139" t="b">
         <v>0</v>
@@ -8034,7 +8058,7 @@
         <v>-3.2</v>
       </c>
       <c r="H140" t="n">
-        <v>26.62</v>
+        <v>23.89</v>
       </c>
       <c r="I140" t="n">
         <v>15.28</v>
@@ -8042,12 +8066,14 @@
       <c r="J140" t="n">
         <v>19.06</v>
       </c>
-      <c r="K140" t="inlineStr"/>
+      <c r="K140" t="n">
+        <v>23.89</v>
+      </c>
       <c r="L140" t="n">
         <v>-2.53</v>
       </c>
       <c r="M140" t="n">
-        <v>24.97</v>
+        <v>20.94</v>
       </c>
       <c r="N140" t="b">
         <v>0</v>
@@ -8085,7 +8111,7 @@
         <v>-23.5</v>
       </c>
       <c r="H141" t="n">
-        <v>17.5</v>
+        <v>25.18</v>
       </c>
       <c r="I141" t="n">
         <v>20.48</v>
@@ -8093,12 +8119,14 @@
       <c r="J141" t="n">
         <v>39.36</v>
       </c>
-      <c r="K141" t="inlineStr"/>
+      <c r="K141" t="n">
+        <v>25.18</v>
+      </c>
       <c r="L141" t="n">
         <v>-2.25</v>
       </c>
       <c r="M141" t="n">
-        <v>15.84</v>
+        <v>22.23</v>
       </c>
       <c r="N141" t="b">
         <v>0</v>
@@ -8136,7 +8164,7 @@
         <v>-12.5</v>
       </c>
       <c r="H142" t="n">
-        <v>-6.9</v>
+        <v>-7.4</v>
       </c>
       <c r="I142" t="n">
         <v>21.54</v>
@@ -8144,12 +8172,14 @@
       <c r="J142" t="n">
         <v>19.55</v>
       </c>
-      <c r="K142" t="inlineStr"/>
+      <c r="K142" t="n">
+        <v>-7.1</v>
+      </c>
       <c r="L142" t="n">
         <v>-0.95</v>
       </c>
       <c r="M142" t="n">
-        <v>-9.210000000000001</v>
+        <v>-11.01</v>
       </c>
       <c r="N142" t="b">
         <v>0</v>
@@ -8187,7 +8217,7 @@
         <v>-23.4</v>
       </c>
       <c r="H143" t="n">
-        <v>-0.25</v>
+        <v>-3.08</v>
       </c>
       <c r="I143" t="n">
         <v>-3.58</v>
@@ -8195,12 +8225,14 @@
       <c r="J143" t="n">
         <v>-15.15</v>
       </c>
-      <c r="K143" t="inlineStr"/>
+      <c r="K143" t="n">
+        <v>-2.14</v>
+      </c>
       <c r="L143" t="n">
         <v>-17.98</v>
       </c>
       <c r="M143" t="n">
-        <v>-2.56</v>
+        <v>-6.69</v>
       </c>
       <c r="N143" t="b">
         <v>0</v>
@@ -8238,7 +8270,7 @@
         <v>-37</v>
       </c>
       <c r="H144" t="n">
-        <v>59.38</v>
+        <v>58.66</v>
       </c>
       <c r="I144" t="n">
         <v>18.38</v>
@@ -8246,12 +8278,14 @@
       <c r="J144" t="n">
         <v>27.59</v>
       </c>
-      <c r="K144" t="inlineStr"/>
+      <c r="K144" t="n">
+        <v>57.9</v>
+      </c>
       <c r="L144" t="n">
         <v>-5.11</v>
       </c>
       <c r="M144" t="n">
-        <v>57.07</v>
+        <v>55.05</v>
       </c>
       <c r="N144" t="b">
         <v>1</v>
@@ -8293,7 +8327,7 @@
         <v>-3.4</v>
       </c>
       <c r="H145" t="n">
-        <v>15.16</v>
+        <v>14.59</v>
       </c>
       <c r="I145" t="n">
         <v>30.48</v>
@@ -8301,12 +8335,14 @@
       <c r="J145" t="n">
         <v>47.92</v>
       </c>
-      <c r="K145" t="inlineStr"/>
+      <c r="K145" t="n">
+        <v>16.54</v>
+      </c>
       <c r="L145" t="n">
         <v>-0.9</v>
       </c>
       <c r="M145" t="n">
-        <v>12.85</v>
+        <v>10.98</v>
       </c>
       <c r="N145" t="b">
         <v>0</v>
@@ -8344,7 +8380,7 @@
         <v>-26.8</v>
       </c>
       <c r="H146" t="n">
-        <v>19.91</v>
+        <v>15.81</v>
       </c>
       <c r="I146" t="n">
         <v>4.56</v>
@@ -8352,12 +8388,14 @@
       <c r="J146" t="n">
         <v>-1</v>
       </c>
-      <c r="K146" t="inlineStr"/>
+      <c r="K146" t="n">
+        <v>15.15</v>
+      </c>
       <c r="L146" t="n">
         <v>-4.09</v>
       </c>
       <c r="M146" t="n">
-        <v>17.6</v>
+        <v>12.2</v>
       </c>
       <c r="N146" t="b">
         <v>1</v>
@@ -8395,7 +8433,7 @@
         <v>-28.9</v>
       </c>
       <c r="H147" t="n">
-        <v>-9.449999999999999</v>
+        <v>-8.960000000000001</v>
       </c>
       <c r="I147" t="n">
         <v>-12.9</v>
@@ -8403,12 +8441,14 @@
       <c r="J147" t="n">
         <v>-11.81</v>
       </c>
-      <c r="K147" t="inlineStr"/>
+      <c r="K147" t="n">
+        <v>-9.300000000000001</v>
+      </c>
       <c r="L147" t="n">
         <v>-23.19</v>
       </c>
       <c r="M147" t="n">
-        <v>-11.76</v>
+        <v>-12.57</v>
       </c>
       <c r="N147" t="b">
         <v>0</v>
@@ -8450,7 +8490,7 @@
         <v>-9.800000000000001</v>
       </c>
       <c r="H148" t="n">
-        <v>-17.49</v>
+        <v>-21.71</v>
       </c>
       <c r="I148" t="n">
         <v>-4.09</v>
@@ -8465,7 +8505,7 @@
         <v>-15.24</v>
       </c>
       <c r="M148" t="n">
-        <v>-20.99</v>
+        <v>-26.54</v>
       </c>
       <c r="N148" t="b">
         <v>0</v>
@@ -8503,7 +8543,7 @@
         <v>21</v>
       </c>
       <c r="H149" t="n">
-        <v>3.37</v>
+        <v>12.16</v>
       </c>
       <c r="I149" t="n">
         <v>-0.72</v>
@@ -8518,7 +8558,7 @@
         <v>-7.35</v>
       </c>
       <c r="M149" t="n">
-        <v>-0.14</v>
+        <v>7.34</v>
       </c>
       <c r="N149" t="b">
         <v>0</v>
@@ -8556,7 +8596,7 @@
         <v>13.2</v>
       </c>
       <c r="H150" t="n">
-        <v>54.83</v>
+        <v>64.33</v>
       </c>
       <c r="I150" t="n">
         <v>8.130000000000001</v>
@@ -8571,7 +8611,7 @@
         <v>-2.36</v>
       </c>
       <c r="M150" t="n">
-        <v>51.32</v>
+        <v>59.5</v>
       </c>
       <c r="N150" t="b">
         <v>0</v>
@@ -8609,7 +8649,7 @@
         <v>6.1</v>
       </c>
       <c r="H151" t="n">
-        <v>-1.18</v>
+        <v>2.48</v>
       </c>
       <c r="I151" t="n">
         <v>10.43</v>
@@ -8624,7 +8664,7 @@
         <v>-1.51</v>
       </c>
       <c r="M151" t="n">
-        <v>-4.69</v>
+        <v>-2.34</v>
       </c>
       <c r="N151" t="b">
         <v>0</v>
@@ -8662,7 +8702,7 @@
         <v>6.5</v>
       </c>
       <c r="H152" t="n">
-        <v>10.46</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="I152" t="n">
         <v>-0.04</v>
@@ -8677,7 +8717,7 @@
         <v>-4.12</v>
       </c>
       <c r="M152" t="n">
-        <v>6.95</v>
+        <v>4.71</v>
       </c>
       <c r="N152" t="b">
         <v>0</v>
@@ -8715,7 +8755,7 @@
         <v>-36.5</v>
       </c>
       <c r="H153" t="n">
-        <v>-30.37</v>
+        <v>-31.98</v>
       </c>
       <c r="I153" t="n">
         <v>-27.75</v>
@@ -8730,7 +8770,7 @@
         <v>-31.28</v>
       </c>
       <c r="M153" t="n">
-        <v>-33.33</v>
+        <v>-36.25</v>
       </c>
       <c r="N153" t="b">
         <v>1</v>
@@ -8768,7 +8808,7 @@
         <v>-14.5</v>
       </c>
       <c r="H154" t="n">
-        <v>4.99</v>
+        <v>2.79</v>
       </c>
       <c r="I154" t="n">
         <v>4.48</v>
@@ -8783,7 +8823,7 @@
         <v>-3.33</v>
       </c>
       <c r="M154" t="n">
-        <v>2.03</v>
+        <v>-1.48</v>
       </c>
       <c r="N154" t="b">
         <v>0</v>
@@ -8821,7 +8861,7 @@
         <v>1.7</v>
       </c>
       <c r="H155" t="n">
-        <v>-8.1</v>
+        <v>-12.62</v>
       </c>
       <c r="I155" t="n">
         <v>8.859999999999999</v>
@@ -8836,7 +8876,7 @@
         <v>-3.27</v>
       </c>
       <c r="M155" t="n">
-        <v>-11.06</v>
+        <v>-16.89</v>
       </c>
       <c r="N155" t="b">
         <v>0</v>
@@ -8874,7 +8914,7 @@
         <v>24.9</v>
       </c>
       <c r="H156" t="n">
-        <v>3.73</v>
+        <v>2.17</v>
       </c>
       <c r="I156" t="n">
         <v>10.45</v>
@@ -8889,7 +8929,7 @@
         <v>-0.49</v>
       </c>
       <c r="M156" t="n">
-        <v>0.77</v>
+        <v>-2.1</v>
       </c>
       <c r="N156" t="b">
         <v>0</v>
@@ -8927,7 +8967,7 @@
         <v>48.1</v>
       </c>
       <c r="H157" t="n">
-        <v>8.720000000000001</v>
+        <v>6.87</v>
       </c>
       <c r="I157" t="n">
         <v>0.16</v>
@@ -8942,7 +8982,7 @@
         <v>-8.890000000000001</v>
       </c>
       <c r="M157" t="n">
-        <v>5.77</v>
+        <v>2.59</v>
       </c>
       <c r="N157" t="b">
         <v>0</v>
@@ -8980,7 +9020,7 @@
         <v>-38.7</v>
       </c>
       <c r="H158" t="n">
-        <v>30.31</v>
+        <v>22.97</v>
       </c>
       <c r="I158" t="n">
         <v>17.17</v>
@@ -8995,7 +9035,7 @@
         <v>-0.54</v>
       </c>
       <c r="M158" t="n">
-        <v>27.35</v>
+        <v>18.7</v>
       </c>
       <c r="N158" t="b">
         <v>1</v>
@@ -9033,7 +9073,7 @@
         <v>-21.4</v>
       </c>
       <c r="H159" t="n">
-        <v>-8.779999999999999</v>
+        <v>-13.4</v>
       </c>
       <c r="I159" t="n">
         <v>2.8</v>
@@ -9048,7 +9088,7 @@
         <v>-2.27</v>
       </c>
       <c r="M159" t="n">
-        <v>-11.74</v>
+        <v>-17.67</v>
       </c>
       <c r="N159" t="b">
         <v>0</v>
@@ -9086,7 +9126,7 @@
         <v>-34.6</v>
       </c>
       <c r="H160" t="n">
-        <v>24.35</v>
+        <v>20.6</v>
       </c>
       <c r="I160" t="n">
         <v>6.67</v>
@@ -9101,7 +9141,7 @@
         <v>-3.06</v>
       </c>
       <c r="M160" t="n">
-        <v>21.39</v>
+        <v>16.32</v>
       </c>
       <c r="N160" t="b">
         <v>1</v>
@@ -9139,7 +9179,7 @@
         <v>-11.8</v>
       </c>
       <c r="H161" t="n">
-        <v>9.15</v>
+        <v>6.29</v>
       </c>
       <c r="I161" t="n">
         <v>9.76</v>
@@ -9154,7 +9194,7 @@
         <v>-1.63</v>
       </c>
       <c r="M161" t="n">
-        <v>6.08</v>
+        <v>1.91</v>
       </c>
       <c r="N161" t="b">
         <v>1</v>
@@ -9192,7 +9232,7 @@
         <v>0.1</v>
       </c>
       <c r="H162" t="n">
-        <v>0.65</v>
+        <v>-2.34</v>
       </c>
       <c r="I162" t="n">
         <v>-2.83</v>
@@ -9207,7 +9247,7 @@
         <v>-5.45</v>
       </c>
       <c r="M162" t="n">
-        <v>-2.41</v>
+        <v>-6.72</v>
       </c>
       <c r="N162" t="b">
         <v>1</v>
@@ -9245,7 +9285,7 @@
         <v>-13.8</v>
       </c>
       <c r="H163" t="n">
-        <v>9.57</v>
+        <v>20.85</v>
       </c>
       <c r="I163" t="n">
         <v>4.67</v>
@@ -9260,7 +9300,7 @@
         <v>-5.7</v>
       </c>
       <c r="M163" t="n">
-        <v>6.5</v>
+        <v>16.47</v>
       </c>
       <c r="N163" t="b">
         <v>0</v>
@@ -9302,7 +9342,7 @@
         <v>-8.800000000000001</v>
       </c>
       <c r="H164" t="n">
-        <v>12</v>
+        <v>11.01</v>
       </c>
       <c r="I164" t="n">
         <v>15.97</v>
@@ -9317,7 +9357,7 @@
         <v>-0.79</v>
       </c>
       <c r="M164" t="n">
-        <v>8.93</v>
+        <v>6.63</v>
       </c>
       <c r="N164" t="b">
         <v>0</v>
@@ -9355,7 +9395,7 @@
         <v>24.1</v>
       </c>
       <c r="H165" t="n">
-        <v>2.68</v>
+        <v>3.42</v>
       </c>
       <c r="I165" t="n">
         <v>-8.31</v>
@@ -9370,7 +9410,7 @@
         <v>-18.31</v>
       </c>
       <c r="M165" t="n">
-        <v>0.4</v>
+        <v>-0.16</v>
       </c>
       <c r="N165" t="b">
         <v>1</v>
@@ -9408,7 +9448,7 @@
         <v>-15.9</v>
       </c>
       <c r="H166" t="n">
-        <v>24.45</v>
+        <v>23.26</v>
       </c>
       <c r="I166" t="n">
         <v>10.45</v>
@@ -9423,7 +9463,7 @@
         <v>-0.31</v>
       </c>
       <c r="M166" t="n">
-        <v>22.18</v>
+        <v>19.68</v>
       </c>
       <c r="N166" t="b">
         <v>1</v>
@@ -9461,7 +9501,7 @@
         <v>-23.3</v>
       </c>
       <c r="H167" t="n">
-        <v>-17.84</v>
+        <v>-16.82</v>
       </c>
       <c r="I167" t="n">
         <v>-20.42</v>
@@ -9476,7 +9516,7 @@
         <v>-27.45</v>
       </c>
       <c r="M167" t="n">
-        <v>-20.11</v>
+        <v>-20.4</v>
       </c>
       <c r="N167" t="b">
         <v>0</v>
@@ -9514,7 +9554,7 @@
         <v>28.9</v>
       </c>
       <c r="H168" t="n">
-        <v>-4.86</v>
+        <v>-0.5</v>
       </c>
       <c r="I168" t="n">
         <v>8.06</v>
@@ -9529,7 +9569,7 @@
         <v>-2.79</v>
       </c>
       <c r="M168" t="n">
-        <v>-8.02</v>
+        <v>-4.97</v>
       </c>
       <c r="N168" t="b">
         <v>0</v>
@@ -9567,7 +9607,7 @@
         <v>40.1</v>
       </c>
       <c r="H169" t="n">
-        <v>39.23</v>
+        <v>44.88</v>
       </c>
       <c r="I169" t="n">
         <v>15.9</v>
@@ -9582,7 +9622,7 @@
         <v>-5.87</v>
       </c>
       <c r="M169" t="n">
-        <v>36.07</v>
+        <v>40.4</v>
       </c>
       <c r="N169" t="b">
         <v>0</v>
@@ -9620,7 +9660,7 @@
         <v>-27.3</v>
       </c>
       <c r="H170" t="n">
-        <v>-4.39</v>
+        <v>-1.34</v>
       </c>
       <c r="I170" t="n">
         <v>0.75</v>
@@ -9635,7 +9675,7 @@
         <v>-5.46</v>
       </c>
       <c r="M170" t="n">
-        <v>-7.43</v>
+        <v>-5.69</v>
       </c>
       <c r="N170" t="b">
         <v>0</v>
@@ -9673,7 +9713,7 @@
         <v>19.7</v>
       </c>
       <c r="H171" t="n">
-        <v>-24.65</v>
+        <v>-19.76</v>
       </c>
       <c r="I171" t="n">
         <v>-4.49</v>
@@ -9688,7 +9728,7 @@
         <v>-13.7</v>
       </c>
       <c r="M171" t="n">
-        <v>-27.69</v>
+        <v>-24.12</v>
       </c>
       <c r="N171" t="b">
         <v>0</v>
@@ -9726,7 +9766,7 @@
         <v>-21.8</v>
       </c>
       <c r="H172" t="n">
-        <v>-37.18</v>
+        <v>-36.56</v>
       </c>
       <c r="I172" t="n">
         <v>-18.97</v>
@@ -9741,7 +9781,7 @@
         <v>-26.82</v>
       </c>
       <c r="M172" t="n">
-        <v>-40.22</v>
+        <v>-40.91</v>
       </c>
       <c r="N172" t="b">
         <v>1</v>
@@ -9779,7 +9819,7 @@
         <v>-21.3</v>
       </c>
       <c r="H173" t="n">
-        <v>-13.47</v>
+        <v>-2.9</v>
       </c>
       <c r="I173" t="n">
         <v>7.16</v>
@@ -9794,7 +9834,7 @@
         <v>-11.9</v>
       </c>
       <c r="M173" t="n">
-        <v>-16.51</v>
+        <v>-7.26</v>
       </c>
       <c r="N173" t="b">
         <v>0</v>
@@ -9832,7 +9872,7 @@
         <v>-37.6</v>
       </c>
       <c r="H174" t="n">
-        <v>-19.48</v>
+        <v>-14</v>
       </c>
       <c r="I174" t="n">
         <v>15.2</v>
@@ -9847,7 +9887,7 @@
         <v>-10.3</v>
       </c>
       <c r="M174" t="n">
-        <v>-21.52</v>
+        <v>-17.34</v>
       </c>
       <c r="N174" t="b">
         <v>0</v>
@@ -9885,7 +9925,7 @@
         <v>53.8</v>
       </c>
       <c r="H175" t="n">
-        <v>50.82</v>
+        <v>60.04</v>
       </c>
       <c r="I175" t="n">
         <v>4.09</v>
@@ -9900,7 +9940,7 @@
         <v>-8.66</v>
       </c>
       <c r="M175" t="n">
-        <v>48.78</v>
+        <v>56.7</v>
       </c>
       <c r="N175" t="b">
         <v>0</v>
@@ -9938,7 +9978,7 @@
         <v>-39.3</v>
       </c>
       <c r="H176" t="n">
-        <v>17.13</v>
+        <v>12.03</v>
       </c>
       <c r="I176" t="n">
         <v>11.34</v>
@@ -9953,7 +9993,7 @@
         <v>-5.3</v>
       </c>
       <c r="M176" t="n">
-        <v>15.08</v>
+        <v>8.69</v>
       </c>
       <c r="N176" t="b">
         <v>0</v>
@@ -9995,7 +10035,7 @@
         <v>-5.7</v>
       </c>
       <c r="H177" t="n">
-        <v>35.61</v>
+        <v>33.31</v>
       </c>
       <c r="I177" t="n">
         <v>17.92</v>
@@ -10010,7 +10050,7 @@
         <v>-7.48</v>
       </c>
       <c r="M177" t="n">
-        <v>33.56</v>
+        <v>29.97</v>
       </c>
       <c r="N177" t="b">
         <v>0</v>
@@ -10048,7 +10088,7 @@
         <v>57</v>
       </c>
       <c r="H178" t="n">
-        <v>30.98</v>
+        <v>22.96</v>
       </c>
       <c r="I178" t="n">
         <v>-11.21</v>
@@ -10063,7 +10103,7 @@
         <v>-13.87</v>
       </c>
       <c r="M178" t="n">
-        <v>28.94</v>
+        <v>19.62</v>
       </c>
       <c r="N178" t="b">
         <v>1</v>
@@ -10101,7 +10141,7 @@
         <v>-21.8</v>
       </c>
       <c r="H179" t="n">
-        <v>29.43</v>
+        <v>25.6</v>
       </c>
       <c r="I179" t="n">
         <v>1.71</v>
@@ -10116,7 +10156,7 @@
         <v>-6.18</v>
       </c>
       <c r="M179" t="n">
-        <v>27.38</v>
+        <v>22.26</v>
       </c>
       <c r="N179" t="b">
         <v>1</v>
@@ -10154,7 +10194,7 @@
         <v>1</v>
       </c>
       <c r="H180" t="n">
-        <v>-36.46</v>
+        <v>-35.92</v>
       </c>
       <c r="I180" t="n">
         <v>-11.52</v>
@@ -10169,7 +10209,7 @@
         <v>-16.26</v>
       </c>
       <c r="M180" t="n">
-        <v>-38.55</v>
+        <v>-39.31</v>
       </c>
       <c r="N180" t="b">
         <v>1</v>
@@ -10207,7 +10247,7 @@
         <v>45.4</v>
       </c>
       <c r="H181" t="n">
-        <v>-26.32</v>
+        <v>-20.62</v>
       </c>
       <c r="I181" t="n">
         <v>-1.72</v>
@@ -10222,7 +10262,7 @@
         <v>-23.15</v>
       </c>
       <c r="M181" t="n">
-        <v>-28.41</v>
+        <v>-24.01</v>
       </c>
       <c r="N181" t="b">
         <v>0</v>
@@ -10260,7 +10300,7 @@
         <v>49.6</v>
       </c>
       <c r="H182" t="n">
-        <v>11.19</v>
+        <v>18.52</v>
       </c>
       <c r="I182" t="n">
         <v>6.34</v>
@@ -10275,7 +10315,7 @@
         <v>-20.75</v>
       </c>
       <c r="M182" t="n">
-        <v>9.1</v>
+        <v>15.13</v>
       </c>
       <c r="N182" t="b">
         <v>0</v>
@@ -10313,7 +10353,7 @@
         <v>55.3</v>
       </c>
       <c r="H183" t="n">
-        <v>-34.99</v>
+        <v>-27.95</v>
       </c>
       <c r="I183" t="n">
         <v>3.73</v>
@@ -10328,7 +10368,7 @@
         <v>-22.94</v>
       </c>
       <c r="M183" t="n">
-        <v>-37.08</v>
+        <v>-31.34</v>
       </c>
       <c r="N183" t="b">
         <v>0</v>
@@ -10366,7 +10406,7 @@
         <v>76.5</v>
       </c>
       <c r="H184" t="n">
-        <v>-18.1</v>
+        <v>-13.68</v>
       </c>
       <c r="I184" t="n">
         <v>-5.56</v>
@@ -10381,7 +10421,7 @@
         <v>-33.97</v>
       </c>
       <c r="M184" t="n">
-        <v>-20.19</v>
+        <v>-17.07</v>
       </c>
       <c r="N184" t="b">
         <v>0</v>
@@ -10419,7 +10459,7 @@
         <v>77.90000000000001</v>
       </c>
       <c r="H185" t="n">
-        <v>-5.15</v>
+        <v>0.38</v>
       </c>
       <c r="I185" t="n">
         <v>-3.53</v>
@@ -10434,7 +10474,7 @@
         <v>-20.26</v>
       </c>
       <c r="M185" t="n">
-        <v>-7.24</v>
+        <v>-3</v>
       </c>
       <c r="N185" t="b">
         <v>0</v>
@@ -10472,7 +10512,7 @@
         <v>32.1</v>
       </c>
       <c r="H186" t="n">
-        <v>-17.77</v>
+        <v>-11.7</v>
       </c>
       <c r="I186" t="n">
         <v>16.93</v>
@@ -10487,7 +10527,7 @@
         <v>-24.48</v>
       </c>
       <c r="M186" t="n">
-        <v>-19.86</v>
+        <v>-15.08</v>
       </c>
       <c r="N186" t="b">
         <v>0</v>
@@ -10525,7 +10565,7 @@
         <v>57.6</v>
       </c>
       <c r="H187" t="n">
-        <v>24.55</v>
+        <v>33.67</v>
       </c>
       <c r="I187" t="n">
         <v>14.81</v>
@@ -10540,7 +10580,7 @@
         <v>-5.11</v>
       </c>
       <c r="M187" t="n">
-        <v>22.47</v>
+        <v>30.28</v>
       </c>
       <c r="N187" t="b">
         <v>0</v>
@@ -10578,7 +10618,7 @@
         <v>51.8</v>
       </c>
       <c r="H188" t="n">
-        <v>-21.25</v>
+        <v>-12.21</v>
       </c>
       <c r="I188" t="n">
         <v>10.75</v>
@@ -10593,7 +10633,7 @@
         <v>-25.09</v>
       </c>
       <c r="M188" t="n">
-        <v>-23.34</v>
+        <v>-15.6</v>
       </c>
       <c r="N188" t="b">
         <v>0</v>
@@ -10631,7 +10671,7 @@
         <v>32.3</v>
       </c>
       <c r="H189" t="n">
-        <v>-48.02</v>
+        <v>-46.23</v>
       </c>
       <c r="I189" t="n">
         <v>-20.76</v>
@@ -10646,7 +10686,7 @@
         <v>-27.91</v>
       </c>
       <c r="M189" t="n">
-        <v>-50.1</v>
+        <v>-49.62</v>
       </c>
       <c r="N189" t="b">
         <v>1</v>
@@ -10684,7 +10724,7 @@
         <v>15.7</v>
       </c>
       <c r="H190" t="n">
-        <v>-23.17</v>
+        <v>-21.55</v>
       </c>
       <c r="I190" t="n">
         <v>-0.87</v>
@@ -10699,7 +10739,7 @@
         <v>-29.01</v>
       </c>
       <c r="M190" t="n">
-        <v>-25.26</v>
+        <v>-24.94</v>
       </c>
       <c r="N190" t="b">
         <v>0</v>
@@ -10737,7 +10777,7 @@
         <v>3.7</v>
       </c>
       <c r="H191" t="n">
-        <v>-14.79</v>
+        <v>-14.15</v>
       </c>
       <c r="I191" t="n">
         <v>-1.11</v>
@@ -10752,7 +10792,7 @@
         <v>-25.46</v>
       </c>
       <c r="M191" t="n">
-        <v>-16.88</v>
+        <v>-17.53</v>
       </c>
       <c r="N191" t="b">
         <v>1</v>
@@ -10790,7 +10830,7 @@
         <v>63.7</v>
       </c>
       <c r="H192" t="n">
-        <v>-26.97</v>
+        <v>-22.64</v>
       </c>
       <c r="I192" t="n">
         <v>-2.16</v>
@@ -10805,7 +10845,7 @@
         <v>-19.1</v>
       </c>
       <c r="M192" t="n">
-        <v>-29.05</v>
+        <v>-26.03</v>
       </c>
       <c r="N192" t="b">
         <v>0</v>
@@ -10843,7 +10883,7 @@
         <v>42.4</v>
       </c>
       <c r="H193" t="n">
-        <v>-26.11</v>
+        <v>-15.67</v>
       </c>
       <c r="I193" t="n">
         <v>2.16</v>
@@ -10858,7 +10898,7 @@
         <v>-15.76</v>
       </c>
       <c r="M193" t="n">
-        <v>-28.2</v>
+        <v>-19.06</v>
       </c>
       <c r="N193" t="b">
         <v>1</v>
@@ -10896,7 +10936,7 @@
         <v>28.2</v>
       </c>
       <c r="H194" t="n">
-        <v>-25.77</v>
+        <v>-18.82</v>
       </c>
       <c r="I194" t="n">
         <v>-1.71</v>
@@ -10911,7 +10951,7 @@
         <v>-23.43</v>
       </c>
       <c r="M194" t="n">
-        <v>-27.85</v>
+        <v>-22.21</v>
       </c>
       <c r="N194" t="b">
         <v>1</v>
@@ -10949,7 +10989,7 @@
         <v>28.6</v>
       </c>
       <c r="H195" t="n">
-        <v>-20.08</v>
+        <v>-3.76</v>
       </c>
       <c r="I195" t="n">
         <v>2.81</v>
@@ -10964,7 +11004,7 @@
         <v>-18.87</v>
       </c>
       <c r="M195" t="n">
-        <v>-22.17</v>
+        <v>-7.15</v>
       </c>
       <c r="N195" t="b">
         <v>1</v>
@@ -11002,7 +11042,7 @@
         <v>89.09999999999999</v>
       </c>
       <c r="H196" t="n">
-        <v>15.86</v>
+        <v>27.42</v>
       </c>
       <c r="I196" t="n">
         <v>18.45</v>
@@ -11017,7 +11057,7 @@
         <v>-9.029999999999999</v>
       </c>
       <c r="M196" t="n">
-        <v>13.78</v>
+        <v>24.03</v>
       </c>
       <c r="N196" t="b">
         <v>0</v>
@@ -11055,7 +11095,7 @@
         <v>33.1</v>
       </c>
       <c r="H197" t="n">
-        <v>-6.82</v>
+        <v>6.74</v>
       </c>
       <c r="I197" t="n">
         <v>4.68</v>
@@ -11070,7 +11110,7 @@
         <v>-26.7</v>
       </c>
       <c r="M197" t="n">
-        <v>-8.9</v>
+        <v>3.35</v>
       </c>
       <c r="N197" t="b">
         <v>0</v>
@@ -11108,7 +11148,7 @@
         <v>50.5</v>
       </c>
       <c r="H198" t="n">
-        <v>-15.73</v>
+        <v>-9.16</v>
       </c>
       <c r="I198" t="n">
         <v>-2.26</v>
@@ -11123,7 +11163,7 @@
         <v>-20.74</v>
       </c>
       <c r="M198" t="n">
-        <v>-17.81</v>
+        <v>-12.55</v>
       </c>
       <c r="N198" t="b">
         <v>0</v>
@@ -11161,7 +11201,7 @@
         <v>-13.8</v>
       </c>
       <c r="H199" t="n">
-        <v>10.11</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="I199" t="n">
         <v>6.03</v>
@@ -11176,7 +11216,7 @@
         <v>-13.77</v>
       </c>
       <c r="M199" t="n">
-        <v>8.02</v>
+        <v>5.39</v>
       </c>
       <c r="N199" t="b">
         <v>0</v>
@@ -11214,7 +11254,7 @@
         <v>46.3</v>
       </c>
       <c r="H200" t="n">
-        <v>-33.15</v>
+        <v>-29.84</v>
       </c>
       <c r="I200" t="n">
         <v>-3.24</v>
@@ -11229,7 +11269,7 @@
         <v>-22.77</v>
       </c>
       <c r="M200" t="n">
-        <v>-35.24</v>
+        <v>-33.23</v>
       </c>
       <c r="N200" t="b">
         <v>0</v>
@@ -11267,7 +11307,7 @@
         <v>21.8</v>
       </c>
       <c r="H201" t="n">
-        <v>-43.5</v>
+        <v>-38.79</v>
       </c>
       <c r="I201" t="n">
         <v>-6.34</v>
@@ -11282,7 +11322,7 @@
         <v>-30.04</v>
       </c>
       <c r="M201" t="n">
-        <v>-45.58</v>
+        <v>-42.18</v>
       </c>
       <c r="N201" t="b">
         <v>1</v>
@@ -11320,7 +11360,7 @@
         <v>40.3</v>
       </c>
       <c r="H202" t="n">
-        <v>-38.84</v>
+        <v>-33.41</v>
       </c>
       <c r="I202" t="n">
         <v>1.24</v>
@@ -11335,7 +11375,7 @@
         <v>-20.5</v>
       </c>
       <c r="M202" t="n">
-        <v>-40.92</v>
+        <v>-36.79</v>
       </c>
       <c r="N202" t="b">
         <v>0</v>
@@ -11373,7 +11413,7 @@
         <v>24.1</v>
       </c>
       <c r="H203" t="n">
-        <v>-22.33</v>
+        <v>-17.15</v>
       </c>
       <c r="I203" t="n">
         <v>-1.6</v>
@@ -11388,7 +11428,7 @@
         <v>-22.54</v>
       </c>
       <c r="M203" t="n">
-        <v>-24.42</v>
+        <v>-20.54</v>
       </c>
       <c r="N203" t="b">
         <v>1</v>
@@ -11426,7 +11466,7 @@
         <v>36.6</v>
       </c>
       <c r="H204" t="n">
-        <v>236.25</v>
+        <v>249.47</v>
       </c>
       <c r="I204" t="n">
         <v>-4.23</v>
@@ -11441,7 +11481,7 @@
         <v>-11.51</v>
       </c>
       <c r="M204" t="n">
-        <v>234.16</v>
+        <v>246.08</v>
       </c>
       <c r="N204" t="b">
         <v>0</v>
@@ -11479,7 +11519,7 @@
         <v>50.3</v>
       </c>
       <c r="H205" t="n">
-        <v>-41.5</v>
+        <v>-35.66</v>
       </c>
       <c r="I205" t="n">
         <v>-3.34</v>
@@ -11494,7 +11534,7 @@
         <v>-23.32</v>
       </c>
       <c r="M205" t="n">
-        <v>-43.58</v>
+        <v>-39.05</v>
       </c>
       <c r="N205" t="b">
         <v>0</v>
@@ -11532,7 +11572,7 @@
         <v>-4</v>
       </c>
       <c r="H206" t="n">
-        <v>-41.21</v>
+        <v>-40.62</v>
       </c>
       <c r="I206" t="n">
         <v>-1.59</v>
@@ -11547,7 +11587,7 @@
         <v>-25.38</v>
       </c>
       <c r="M206" t="n">
-        <v>-43.29</v>
+        <v>-44.01</v>
       </c>
       <c r="N206" t="b">
         <v>0</v>
@@ -11585,7 +11625,7 @@
         <v>24.5</v>
       </c>
       <c r="H207" t="n">
-        <v>-36.08</v>
+        <v>-31.01</v>
       </c>
       <c r="I207" t="n">
         <v>-12.99</v>
@@ -11600,7 +11640,7 @@
         <v>-22.54</v>
       </c>
       <c r="M207" t="n">
-        <v>-38.17</v>
+        <v>-34.39</v>
       </c>
       <c r="N207" t="b">
         <v>1</v>
@@ -11638,7 +11678,7 @@
         <v>-27.6</v>
       </c>
       <c r="H208" t="n">
-        <v>-24.91</v>
+        <v>-17.49</v>
       </c>
       <c r="I208" t="n">
         <v>-0.36</v>
@@ -11653,7 +11693,7 @@
         <v>-19.41</v>
       </c>
       <c r="M208" t="n">
-        <v>-27</v>
+        <v>-20.88</v>
       </c>
       <c r="N208" t="b">
         <v>0</v>
@@ -11691,7 +11731,7 @@
         <v>14.8</v>
       </c>
       <c r="H209" t="n">
-        <v>-33.36</v>
+        <v>-35.68</v>
       </c>
       <c r="I209" t="n">
         <v>-2.48</v>
@@ -11706,7 +11746,7 @@
         <v>-40.98</v>
       </c>
       <c r="M209" t="n">
-        <v>-35.45</v>
+        <v>-39.07</v>
       </c>
       <c r="N209" t="b">
         <v>0</v>
@@ -11744,7 +11784,7 @@
         <v>9.1</v>
       </c>
       <c r="H210" t="n">
-        <v>-41.74</v>
+        <v>-34.84</v>
       </c>
       <c r="I210" t="n">
         <v>-2.83</v>
@@ -11759,7 +11799,7 @@
         <v>-23.78</v>
       </c>
       <c r="M210" t="n">
-        <v>-43.83</v>
+        <v>-38.23</v>
       </c>
       <c r="N210" t="b">
         <v>0</v>
@@ -11797,7 +11837,7 @@
         <v>11</v>
       </c>
       <c r="H211" t="n">
-        <v>-19.47</v>
+        <v>-11.7</v>
       </c>
       <c r="I211" t="n">
         <v>3.38</v>
@@ -11812,7 +11852,7 @@
         <v>-18.71</v>
       </c>
       <c r="M211" t="n">
-        <v>-21.56</v>
+        <v>-15.09</v>
       </c>
       <c r="N211" t="b">
         <v>0</v>
@@ -11850,7 +11890,7 @@
         <v>31.2</v>
       </c>
       <c r="H212" t="n">
-        <v>-33.81</v>
+        <v>-30.15</v>
       </c>
       <c r="I212" t="n">
         <v>-11.26</v>
@@ -11865,7 +11905,7 @@
         <v>-22.9</v>
       </c>
       <c r="M212" t="n">
-        <v>-35.9</v>
+        <v>-33.54</v>
       </c>
       <c r="N212" t="b">
         <v>0</v>
@@ -11903,7 +11943,7 @@
         <v>19.3</v>
       </c>
       <c r="H213" t="n">
-        <v>-14.41</v>
+        <v>-10.3</v>
       </c>
       <c r="I213" t="n">
         <v>11.79</v>
@@ -11918,7 +11958,7 @@
         <v>-16.62</v>
       </c>
       <c r="M213" t="n">
-        <v>-16.5</v>
+        <v>-13.69</v>
       </c>
       <c r="N213" t="b">
         <v>0</v>
@@ -11956,7 +11996,7 @@
         <v>15.2</v>
       </c>
       <c r="H214" t="n">
-        <v>-31.89</v>
+        <v>-23.26</v>
       </c>
       <c r="I214" t="n">
         <v>5.36</v>
@@ -11971,7 +12011,7 @@
         <v>-28.18</v>
       </c>
       <c r="M214" t="n">
-        <v>-33.97</v>
+        <v>-26.65</v>
       </c>
       <c r="N214" t="b">
         <v>0</v>
@@ -12009,7 +12049,7 @@
         <v>-8.699999999999999</v>
       </c>
       <c r="H215" t="n">
-        <v>-9.74</v>
+        <v>-12.26</v>
       </c>
       <c r="I215" t="n">
         <v>17.25</v>
@@ -12024,7 +12064,7 @@
         <v>-4.65</v>
       </c>
       <c r="M215" t="n">
-        <v>-11.83</v>
+        <v>-15.65</v>
       </c>
       <c r="N215" t="b">
         <v>1</v>
@@ -12062,7 +12102,7 @@
         <v>37.2</v>
       </c>
       <c r="H216" t="n">
-        <v>-43.35</v>
+        <v>-38.85</v>
       </c>
       <c r="I216" t="n">
         <v>-7.64</v>
@@ -12077,7 +12117,7 @@
         <v>-26.24</v>
       </c>
       <c r="M216" t="n">
-        <v>-45.44</v>
+        <v>-42.24</v>
       </c>
       <c r="N216" t="b">
         <v>1</v>
@@ -12119,7 +12159,7 @@
         <v>-0.5</v>
       </c>
       <c r="H217" t="n">
-        <v>46.63</v>
+        <v>45.26</v>
       </c>
       <c r="I217" t="n">
         <v>12.75</v>
@@ -12134,7 +12174,7 @@
         <v>-4.72</v>
       </c>
       <c r="M217" t="n">
-        <v>44.54</v>
+        <v>41.87</v>
       </c>
       <c r="N217" t="b">
         <v>0</v>
@@ -12172,7 +12212,7 @@
         <v>18.2</v>
       </c>
       <c r="H218" t="n">
-        <v>-20.65</v>
+        <v>-13.6</v>
       </c>
       <c r="I218" t="n">
         <v>-11.28</v>
@@ -12187,7 +12227,7 @@
         <v>-16.87</v>
       </c>
       <c r="M218" t="n">
-        <v>-22.73</v>
+        <v>-16.98</v>
       </c>
       <c r="N218" t="b">
         <v>0</v>
@@ -12225,7 +12265,7 @@
         <v>-13.4</v>
       </c>
       <c r="H219" t="n">
-        <v>-40.79</v>
+        <v>-36.03</v>
       </c>
       <c r="I219" t="n">
         <v>0.79</v>
@@ -12240,7 +12280,7 @@
         <v>-15.41</v>
       </c>
       <c r="M219" t="n">
-        <v>-42.88</v>
+        <v>-39.41</v>
       </c>
       <c r="N219" t="b">
         <v>0</v>
@@ -12278,7 +12318,7 @@
         <v>29.8</v>
       </c>
       <c r="H220" t="n">
-        <v>-0.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I220" t="n">
         <v>-2.74</v>
@@ -12293,7 +12333,7 @@
         <v>-22.36</v>
       </c>
       <c r="M220" t="n">
-        <v>-2.69</v>
+        <v>5.31</v>
       </c>
       <c r="N220" t="b">
         <v>1</v>
@@ -12331,7 +12371,7 @@
         <v>-27.9</v>
       </c>
       <c r="H221" t="n">
-        <v>-54.47</v>
+        <v>-57.54</v>
       </c>
       <c r="I221" t="n">
         <v>-5.72</v>
@@ -12346,7 +12386,7 @@
         <v>-11.08</v>
       </c>
       <c r="M221" t="n">
-        <v>-56.56</v>
+        <v>-60.92</v>
       </c>
       <c r="N221" t="b">
         <v>0</v>
@@ -12384,7 +12424,7 @@
         <v>60.9</v>
       </c>
       <c r="H222" t="n">
-        <v>-4.18</v>
+        <v>-1.49</v>
       </c>
       <c r="I222" t="n">
         <v>6.71</v>
@@ -12399,7 +12439,7 @@
         <v>-4.9</v>
       </c>
       <c r="M222" t="n">
-        <v>-6.27</v>
+        <v>-4.87</v>
       </c>
       <c r="N222" t="b">
         <v>0</v>
@@ -12437,7 +12477,7 @@
         <v>31.2</v>
       </c>
       <c r="H223" t="n">
-        <v>-29.8</v>
+        <v>-26.52</v>
       </c>
       <c r="I223" t="n">
         <v>-3.17</v>
@@ -12452,7 +12492,7 @@
         <v>-23.66</v>
       </c>
       <c r="M223" t="n">
-        <v>-31.89</v>
+        <v>-29.91</v>
       </c>
       <c r="N223" t="b">
         <v>0</v>
@@ -12490,7 +12530,7 @@
         <v>-22.4</v>
       </c>
       <c r="H224" t="n">
-        <v>-17.03</v>
+        <v>-17.27</v>
       </c>
       <c r="I224" t="n">
         <v>5.79</v>
@@ -12505,7 +12545,7 @@
         <v>-9.67</v>
       </c>
       <c r="M224" t="n">
-        <v>-19.11</v>
+        <v>-20.66</v>
       </c>
       <c r="N224" t="b">
         <v>0</v>
@@ -12543,7 +12583,7 @@
         <v>-1.3</v>
       </c>
       <c r="H225" t="n">
-        <v>-20.34</v>
+        <v>-24.98</v>
       </c>
       <c r="I225" t="n">
         <v>5.29</v>
@@ -12558,7 +12598,7 @@
         <v>-11.87</v>
       </c>
       <c r="M225" t="n">
-        <v>-22.43</v>
+        <v>-28.37</v>
       </c>
       <c r="N225" t="b">
         <v>0</v>
@@ -12596,7 +12636,7 @@
         <v>-29.8</v>
       </c>
       <c r="H226" t="n">
-        <v>35</v>
+        <v>43.81</v>
       </c>
       <c r="I226" t="n">
         <v>29.88</v>
@@ -12611,7 +12651,7 @@
         <v>-0.29</v>
       </c>
       <c r="M226" t="n">
-        <v>32.91</v>
+        <v>40.42</v>
       </c>
       <c r="N226" t="b">
         <v>0</v>
@@ -12649,7 +12689,7 @@
         <v>19.3</v>
       </c>
       <c r="H227" t="n">
-        <v>-41.29</v>
+        <v>-40.33</v>
       </c>
       <c r="I227" t="n">
         <v>-16.69</v>
@@ -12664,7 +12704,7 @@
         <v>-36.39</v>
       </c>
       <c r="M227" t="n">
-        <v>-43.37</v>
+        <v>-43.72</v>
       </c>
       <c r="N227" t="b">
         <v>1</v>
@@ -12702,7 +12742,7 @@
         <v>7.6</v>
       </c>
       <c r="H228" t="n">
-        <v>-38.27</v>
+        <v>-33.2</v>
       </c>
       <c r="I228" t="n">
         <v>6.22</v>
@@ -12717,7 +12757,7 @@
         <v>-10.68</v>
       </c>
       <c r="M228" t="n">
-        <v>-40.36</v>
+        <v>-36.58</v>
       </c>
       <c r="N228" t="b">
         <v>0</v>
@@ -12755,7 +12795,7 @@
         <v>68.8</v>
       </c>
       <c r="H229" t="n">
-        <v>-1.75</v>
+        <v>6.51</v>
       </c>
       <c r="I229" t="n">
         <v>-1.41</v>
@@ -12770,7 +12810,7 @@
         <v>-19.39</v>
       </c>
       <c r="M229" t="n">
-        <v>-3.84</v>
+        <v>3.13</v>
       </c>
       <c r="N229" t="b">
         <v>0</v>
@@ -12808,7 +12848,7 @@
         <v>8.5</v>
       </c>
       <c r="H230" t="n">
-        <v>-46.76</v>
+        <v>-44.66</v>
       </c>
       <c r="I230" t="n">
         <v>-4.26</v>
@@ -12823,7 +12863,7 @@
         <v>-23.85</v>
       </c>
       <c r="M230" t="n">
-        <v>-48.84</v>
+        <v>-48.05</v>
       </c>
       <c r="N230" t="b">
         <v>0</v>
@@ -12861,7 +12901,7 @@
         <v>11.8</v>
       </c>
       <c r="H231" t="n">
-        <v>-14.59</v>
+        <v>-7.57</v>
       </c>
       <c r="I231" t="n">
         <v>-1.19</v>
@@ -12876,7 +12916,7 @@
         <v>-17.57</v>
       </c>
       <c r="M231" t="n">
-        <v>-16.68</v>
+        <v>-10.95</v>
       </c>
       <c r="N231" t="b">
         <v>1</v>
@@ -12914,7 +12954,7 @@
         <v>27.5</v>
       </c>
       <c r="H232" t="n">
-        <v>1.85</v>
+        <v>4.89</v>
       </c>
       <c r="I232" t="n">
         <v>8.42</v>
@@ -12929,7 +12969,7 @@
         <v>-2.51</v>
       </c>
       <c r="M232" t="n">
-        <v>-0.24</v>
+        <v>1.5</v>
       </c>
       <c r="N232" t="b">
         <v>1</v>
@@ -12967,7 +13007,7 @@
         <v>-33.1</v>
       </c>
       <c r="H233" t="n">
-        <v>-14.29</v>
+        <v>-11.43</v>
       </c>
       <c r="I233" t="n">
         <v>-13.13</v>
@@ -12982,7 +13022,7 @@
         <v>-21.04</v>
       </c>
       <c r="M233" t="n">
-        <v>-16.37</v>
+        <v>-14.82</v>
       </c>
       <c r="N233" t="b">
         <v>0</v>
@@ -13020,7 +13060,7 @@
         <v>-15.2</v>
       </c>
       <c r="H234" t="n">
-        <v>-20.71</v>
+        <v>-12.1</v>
       </c>
       <c r="I234" t="n">
         <v>12.27</v>
@@ -13035,7 +13075,7 @@
         <v>-12.27</v>
       </c>
       <c r="M234" t="n">
-        <v>-22.8</v>
+        <v>-15.49</v>
       </c>
       <c r="N234" t="b">
         <v>0</v>
@@ -13073,7 +13113,7 @@
         <v>-22.4</v>
       </c>
       <c r="H235" t="n">
-        <v>-2.2</v>
+        <v>-7.02</v>
       </c>
       <c r="I235" t="n">
         <v>9.42</v>
@@ -13088,7 +13128,7 @@
         <v>-2.79</v>
       </c>
       <c r="M235" t="n">
-        <v>-4.28</v>
+        <v>-10.41</v>
       </c>
       <c r="N235" t="b">
         <v>0</v>
@@ -13126,7 +13166,7 @@
         <v>-13.5</v>
       </c>
       <c r="H236" t="n">
-        <v>143.67</v>
+        <v>134.89</v>
       </c>
       <c r="I236" t="n">
         <v>18.09</v>
@@ -13141,7 +13181,7 @@
         <v>-14.35</v>
       </c>
       <c r="M236" t="n">
-        <v>141.59</v>
+        <v>131.51</v>
       </c>
       <c r="N236" t="b">
         <v>0</v>
@@ -13179,7 +13219,7 @@
         <v>-14.7</v>
       </c>
       <c r="H237" t="n">
-        <v>-17.69</v>
+        <v>-18.45</v>
       </c>
       <c r="I237" t="n">
         <v>10.3</v>
@@ -13194,7 +13234,7 @@
         <v>-2.6</v>
       </c>
       <c r="M237" t="n">
-        <v>-19.78</v>
+        <v>-21.83</v>
       </c>
       <c r="N237" t="b">
         <v>1</v>
@@ -13236,7 +13276,7 @@
         <v>-9.300000000000001</v>
       </c>
       <c r="H238" t="n">
-        <v>-22.97</v>
+        <v>-25.1</v>
       </c>
       <c r="I238" t="n">
         <v>10.42</v>
@@ -13251,7 +13291,7 @@
         <v>-21.72</v>
       </c>
       <c r="M238" t="n">
-        <v>-25.06</v>
+        <v>-28.49</v>
       </c>
       <c r="N238" t="b">
         <v>1</v>
@@ -13289,7 +13329,7 @@
         <v>-27.5</v>
       </c>
       <c r="H239" t="n">
-        <v>0.13</v>
+        <v>3.12</v>
       </c>
       <c r="I239" t="n">
         <v>-29.95</v>
@@ -13304,7 +13344,7 @@
         <v>-35.86</v>
       </c>
       <c r="M239" t="n">
-        <v>-1.95</v>
+        <v>-0.26</v>
       </c>
       <c r="N239" t="b">
         <v>0</v>
@@ -13342,7 +13382,7 @@
         <v>20.8</v>
       </c>
       <c r="H240" t="n">
-        <v>-35.86</v>
+        <v>-31.16</v>
       </c>
       <c r="I240" t="n">
         <v>-10.93</v>
@@ -13357,7 +13397,7 @@
         <v>-27.1</v>
       </c>
       <c r="M240" t="n">
-        <v>-37.95</v>
+        <v>-34.55</v>
       </c>
       <c r="N240" t="b">
         <v>0</v>
@@ -13395,7 +13435,7 @@
         <v>11.9</v>
       </c>
       <c r="H241" t="n">
-        <v>-62.22</v>
+        <v>-59.65</v>
       </c>
       <c r="I241" t="n">
         <v>-3.02</v>
@@ -13410,7 +13450,7 @@
         <v>-24.96</v>
       </c>
       <c r="M241" t="n">
-        <v>-64.3</v>
+        <v>-63.04</v>
       </c>
       <c r="N241" t="b">
         <v>0</v>
@@ -13448,7 +13488,7 @@
         <v>-35.9</v>
       </c>
       <c r="H242" t="n">
-        <v>3.11</v>
+        <v>6.68</v>
       </c>
       <c r="I242" t="n">
         <v>18.67</v>
@@ -13463,7 +13503,7 @@
         <v>-6.77</v>
       </c>
       <c r="M242" t="n">
-        <v>1.02</v>
+        <v>3.29</v>
       </c>
       <c r="N242" t="b">
         <v>0</v>
@@ -13501,7 +13541,7 @@
         <v>5</v>
       </c>
       <c r="H243" t="n">
-        <v>-14.15</v>
+        <v>-11.04</v>
       </c>
       <c r="I243" t="n">
         <v>0.41</v>
@@ -13516,7 +13556,7 @@
         <v>-13.87</v>
       </c>
       <c r="M243" t="n">
-        <v>-16.24</v>
+        <v>-14.42</v>
       </c>
       <c r="N243" t="b">
         <v>0</v>
@@ -13554,7 +13594,7 @@
         <v>5.1</v>
       </c>
       <c r="H244" t="n">
-        <v>16.54</v>
+        <v>15.31</v>
       </c>
       <c r="I244" t="n">
         <v>8.77</v>
@@ -13569,7 +13609,7 @@
         <v>-3.54</v>
       </c>
       <c r="M244" t="n">
-        <v>14.45</v>
+        <v>11.93</v>
       </c>
       <c r="N244" t="b">
         <v>1</v>
@@ -13607,7 +13647,7 @@
         <v>-25.2</v>
       </c>
       <c r="H245" t="n">
-        <v>-27.69</v>
+        <v>-20.58</v>
       </c>
       <c r="I245" t="n">
         <v>22.53</v>
@@ -13622,7 +13662,7 @@
         <v>-19.27</v>
       </c>
       <c r="M245" t="n">
-        <v>-29.77</v>
+        <v>-23.96</v>
       </c>
       <c r="N245" t="b">
         <v>0</v>
@@ -13660,7 +13700,7 @@
         <v>-27.7</v>
       </c>
       <c r="H246" t="n">
-        <v>-2.05</v>
+        <v>-4.05</v>
       </c>
       <c r="I246" t="n">
         <v>-10.22</v>
@@ -13675,7 +13715,7 @@
         <v>-17.14</v>
       </c>
       <c r="M246" t="n">
-        <v>-4.13</v>
+        <v>-7.44</v>
       </c>
       <c r="N246" t="b">
         <v>0</v>
@@ -13713,7 +13753,7 @@
         <v>-24.7</v>
       </c>
       <c r="H247" t="n">
-        <v>-17.99</v>
+        <v>-12.48</v>
       </c>
       <c r="I247" t="n">
         <v>1.65</v>
@@ -13728,7 +13768,7 @@
         <v>-19.04</v>
       </c>
       <c r="M247" t="n">
-        <v>-20.07</v>
+        <v>-15.87</v>
       </c>
       <c r="N247" t="b">
         <v>0</v>
@@ -13766,7 +13806,7 @@
         <v>-25.3</v>
       </c>
       <c r="H248" t="n">
-        <v>68.69</v>
+        <v>61.84</v>
       </c>
       <c r="I248" t="n">
         <v>36.1</v>
@@ -13781,7 +13821,7 @@
         <v>-5.66</v>
       </c>
       <c r="M248" t="n">
-        <v>66.61</v>
+        <v>58.45</v>
       </c>
       <c r="N248" t="b">
         <v>0</v>
@@ -13819,7 +13859,7 @@
         <v>64.59999999999999</v>
       </c>
       <c r="H249" t="n">
-        <v>10.17</v>
+        <v>13.23</v>
       </c>
       <c r="I249" t="n">
         <v>3.01</v>
@@ -13834,7 +13874,7 @@
         <v>-12</v>
       </c>
       <c r="M249" t="n">
-        <v>8.08</v>
+        <v>9.85</v>
       </c>
       <c r="N249" t="b">
         <v>0</v>
@@ -13872,7 +13912,7 @@
         <v>34.2</v>
       </c>
       <c r="H250" t="n">
-        <v>-0.36</v>
+        <v>4.34</v>
       </c>
       <c r="I250" t="n">
         <v>8.15</v>
@@ -13887,7 +13927,7 @@
         <v>-7.63</v>
       </c>
       <c r="M250" t="n">
-        <v>-2.45</v>
+        <v>0.95</v>
       </c>
       <c r="N250" t="b">
         <v>1</v>
@@ -13925,7 +13965,7 @@
         <v>42</v>
       </c>
       <c r="H251" t="n">
-        <v>-49.72</v>
+        <v>-49.05</v>
       </c>
       <c r="I251" t="n">
         <v>0.6</v>
@@ -13940,7 +13980,7 @@
         <v>-16.67</v>
       </c>
       <c r="M251" t="n">
-        <v>-51.81</v>
+        <v>-52.44</v>
       </c>
       <c r="N251" t="b">
         <v>1</v>
@@ -13978,7 +14018,7 @@
         <v>-34.9</v>
       </c>
       <c r="H252" t="n">
-        <v>-14.92</v>
+        <v>-17.81</v>
       </c>
       <c r="I252" t="n">
         <v>19.9</v>
@@ -13993,7 +14033,7 @@
         <v>-12.62</v>
       </c>
       <c r="M252" t="n">
-        <v>-17.01</v>
+        <v>-21.19</v>
       </c>
       <c r="N252" t="b">
         <v>0</v>
@@ -14035,7 +14075,7 @@
         <v>-0.4</v>
       </c>
       <c r="H253" t="n">
-        <v>5.35</v>
+        <v>10.38</v>
       </c>
       <c r="I253" t="n">
         <v>4.83</v>
@@ -14050,7 +14090,7 @@
         <v>-10.75</v>
       </c>
       <c r="M253" t="n">
-        <v>3.27</v>
+        <v>6.99</v>
       </c>
       <c r="N253" t="b">
         <v>0</v>
@@ -14088,7 +14128,7 @@
         <v>-7.7</v>
       </c>
       <c r="H254" t="n">
-        <v>-20.33</v>
+        <v>-17.29</v>
       </c>
       <c r="I254" t="n">
         <v>-6.47</v>
@@ -14103,7 +14143,7 @@
         <v>-23.05</v>
       </c>
       <c r="M254" t="n">
-        <v>-22.41</v>
+        <v>-20.68</v>
       </c>
       <c r="N254" t="b">
         <v>1</v>
@@ -14141,7 +14181,7 @@
         <v>-29.5</v>
       </c>
       <c r="H255" t="n">
-        <v>-7.85</v>
+        <v>-8.9</v>
       </c>
       <c r="I255" t="n">
         <v>4.05</v>
@@ -14156,7 +14196,7 @@
         <v>-2.43</v>
       </c>
       <c r="M255" t="n">
-        <v>-9.93</v>
+        <v>-12.29</v>
       </c>
       <c r="N255" t="b">
         <v>0</v>
@@ -14194,7 +14234,7 @@
         <v>29.4</v>
       </c>
       <c r="H256" t="n">
-        <v>-32.73</v>
+        <v>-27.48</v>
       </c>
       <c r="I256" t="n">
         <v>-2.62</v>
@@ -14209,7 +14249,7 @@
         <v>-27.18</v>
       </c>
       <c r="M256" t="n">
-        <v>-34.81</v>
+        <v>-30.87</v>
       </c>
       <c r="N256" t="b">
         <v>1</v>
@@ -14247,7 +14287,7 @@
         <v>13.7</v>
       </c>
       <c r="H257" t="n">
-        <v>-4.39</v>
+        <v>6.68</v>
       </c>
       <c r="I257" t="n">
         <v>2.74</v>
@@ -14262,7 +14302,7 @@
         <v>-24.02</v>
       </c>
       <c r="M257" t="n">
-        <v>-6.48</v>
+        <v>3.29</v>
       </c>
       <c r="N257" t="b">
         <v>1</v>
@@ -14300,7 +14340,7 @@
         <v>21.8</v>
       </c>
       <c r="H258" t="n">
-        <v>-33.54</v>
+        <v>-29.23</v>
       </c>
       <c r="I258" t="n">
         <v>18.32</v>
@@ -14315,7 +14355,7 @@
         <v>-23.27</v>
       </c>
       <c r="M258" t="n">
-        <v>-35.63</v>
+        <v>-32.61</v>
       </c>
       <c r="N258" t="b">
         <v>1</v>
@@ -14353,7 +14393,7 @@
         <v>-2.9</v>
       </c>
       <c r="H259" t="n">
-        <v>-11.96</v>
+        <v>-16.38</v>
       </c>
       <c r="I259" t="n">
         <v>-1.47</v>
@@ -14368,7 +14408,7 @@
         <v>-7.7</v>
       </c>
       <c r="M259" t="n">
-        <v>-14.04</v>
+        <v>-19.77</v>
       </c>
       <c r="N259" t="b">
         <v>0</v>
@@ -14406,7 +14446,7 @@
         <v>-3.7</v>
       </c>
       <c r="H260" t="n">
-        <v>-30.55</v>
+        <v>-27.35</v>
       </c>
       <c r="I260" t="n">
         <v>-8.07</v>
@@ -14421,7 +14461,7 @@
         <v>-22.12</v>
       </c>
       <c r="M260" t="n">
-        <v>-32.63</v>
+        <v>-30.74</v>
       </c>
       <c r="N260" t="b">
         <v>1</v>
@@ -14459,7 +14499,7 @@
         <v>-21.4</v>
       </c>
       <c r="H261" t="n">
-        <v>-5.89</v>
+        <v>-0.66</v>
       </c>
       <c r="I261" t="n">
         <v>4.55</v>
@@ -14474,7 +14514,7 @@
         <v>-6.39</v>
       </c>
       <c r="M261" t="n">
-        <v>-7.98</v>
+        <v>-4.05</v>
       </c>
       <c r="N261" t="b">
         <v>1</v>
@@ -14512,7 +14552,7 @@
         <v>21.3</v>
       </c>
       <c r="H262" t="n">
-        <v>1.55</v>
+        <v>1.77</v>
       </c>
       <c r="I262" t="n">
         <v>0.23</v>
@@ -14527,7 +14567,7 @@
         <v>-0.85</v>
       </c>
       <c r="M262" t="n">
-        <v>-0.53</v>
+        <v>-1.62</v>
       </c>
       <c r="N262" t="b">
         <v>1</v>
@@ -14565,7 +14605,7 @@
         <v>16.3</v>
       </c>
       <c r="H263" t="n">
-        <v>-25.69</v>
+        <v>-19.11</v>
       </c>
       <c r="I263" t="n">
         <v>-1</v>
@@ -14580,7 +14620,7 @@
         <v>-22.5</v>
       </c>
       <c r="M263" t="n">
-        <v>-27.78</v>
+        <v>-22.5</v>
       </c>
       <c r="N263" t="b">
         <v>1</v>
@@ -14618,7 +14658,7 @@
         <v>11.9</v>
       </c>
       <c r="H264" t="n">
-        <v>-13.16</v>
+        <v>-10.21</v>
       </c>
       <c r="I264" t="n">
         <v>7.74</v>
@@ -14633,7 +14673,7 @@
         <v>-9.43</v>
       </c>
       <c r="M264" t="n">
-        <v>-15.25</v>
+        <v>-13.59</v>
       </c>
       <c r="N264" t="b">
         <v>0</v>
@@ -14671,7 +14711,7 @@
         <v>66.7</v>
       </c>
       <c r="H265" t="n">
-        <v>8.9</v>
+        <v>14.96</v>
       </c>
       <c r="I265" t="n">
         <v>4.84</v>
@@ -14686,7 +14726,7 @@
         <v>-11.7</v>
       </c>
       <c r="M265" t="n">
-        <v>6.82</v>
+        <v>11.57</v>
       </c>
       <c r="N265" t="b">
         <v>0</v>
@@ -14724,7 +14764,7 @@
         <v>3.7</v>
       </c>
       <c r="H266" t="n">
-        <v>34.64</v>
+        <v>25.79</v>
       </c>
       <c r="I266" t="n">
         <v>11.13</v>
@@ -14739,7 +14779,7 @@
         <v>-2.79</v>
       </c>
       <c r="M266" t="n">
-        <v>32.55</v>
+        <v>22.4</v>
       </c>
       <c r="N266" t="b">
         <v>0</v>
@@ -14777,7 +14817,7 @@
         <v>19.4</v>
       </c>
       <c r="H267" t="n">
-        <v>1.27</v>
+        <v>3.48</v>
       </c>
       <c r="I267" t="n">
         <v>10.89</v>
@@ -14792,7 +14832,7 @@
         <v>-2.97</v>
       </c>
       <c r="M267" t="n">
-        <v>-0.82</v>
+        <v>0.09</v>
       </c>
       <c r="N267" t="b">
         <v>0</v>
@@ -14830,7 +14870,7 @@
         <v>36.8</v>
       </c>
       <c r="H268" t="n">
-        <v>30.93</v>
+        <v>38.28</v>
       </c>
       <c r="I268" t="n">
         <v>15.47</v>
@@ -14845,7 +14885,7 @@
         <v>-0.96</v>
       </c>
       <c r="M268" t="n">
-        <v>28.84</v>
+        <v>34.89</v>
       </c>
       <c r="N268" t="b">
         <v>0</v>
@@ -14883,7 +14923,7 @@
         <v>0.2</v>
       </c>
       <c r="H269" t="n">
-        <v>29.98</v>
+        <v>31.16</v>
       </c>
       <c r="I269" t="n">
         <v>4.35</v>
@@ -14898,7 +14938,7 @@
         <v>-2.79</v>
       </c>
       <c r="M269" t="n">
-        <v>27.9</v>
+        <v>27.77</v>
       </c>
       <c r="N269" t="b">
         <v>1</v>
@@ -14936,7 +14976,7 @@
         <v>-31</v>
       </c>
       <c r="H270" t="n">
-        <v>-32.42</v>
+        <v>-28.74</v>
       </c>
       <c r="I270" t="n">
         <v>19.41</v>
@@ -14951,7 +14991,7 @@
         <v>-10.33</v>
       </c>
       <c r="M270" t="n">
-        <v>-34.51</v>
+        <v>-32.12</v>
       </c>
       <c r="N270" t="b">
         <v>0</v>
@@ -14989,7 +15029,7 @@
         <v>-21.7</v>
       </c>
       <c r="H271" t="n">
-        <v>-14.43</v>
+        <v>-9.869999999999999</v>
       </c>
       <c r="I271" t="n">
         <v>5.5</v>
@@ -15004,7 +15044,7 @@
         <v>-4.3</v>
       </c>
       <c r="M271" t="n">
-        <v>-16.52</v>
+        <v>-13.26</v>
       </c>
       <c r="N271" t="b">
         <v>0</v>
@@ -15042,7 +15082,7 @@
         <v>-7.3</v>
       </c>
       <c r="H272" t="n">
-        <v>-23.16</v>
+        <v>-22.63</v>
       </c>
       <c r="I272" t="n">
         <v>-4.12</v>
@@ -15057,7 +15097,7 @@
         <v>-15.02</v>
       </c>
       <c r="M272" t="n">
-        <v>-25.25</v>
+        <v>-26.01</v>
       </c>
       <c r="N272" t="b">
         <v>1</v>
@@ -15095,7 +15135,7 @@
         <v>12.2</v>
       </c>
       <c r="H273" t="n">
-        <v>-32.06</v>
+        <v>-35.16</v>
       </c>
       <c r="I273" t="n">
         <v>3.47</v>
@@ -15110,7 +15150,7 @@
         <v>-27.15</v>
       </c>
       <c r="M273" t="n">
-        <v>-34.14</v>
+        <v>-38.55</v>
       </c>
       <c r="N273" t="b">
         <v>0</v>
@@ -15152,7 +15192,7 @@
         <v>-2</v>
       </c>
       <c r="H274" t="n">
-        <v>0</v>
+        <v>-7.8</v>
       </c>
       <c r="I274" t="n">
         <v>14.61</v>
@@ -15167,7 +15207,7 @@
         <v>-3.45</v>
       </c>
       <c r="M274" t="n">
-        <v>-2.09</v>
+        <v>-11.18</v>
       </c>
       <c r="N274" t="b">
         <v>0</v>
@@ -15205,7 +15245,7 @@
         <v>8.4</v>
       </c>
       <c r="H275" t="n">
-        <v>-45.97</v>
+        <v>-44.67</v>
       </c>
       <c r="I275" t="n">
         <v>-0.13</v>
@@ -15220,7 +15260,7 @@
         <v>-10.87</v>
       </c>
       <c r="M275" t="n">
-        <v>-48.05</v>
+        <v>-48.06</v>
       </c>
       <c r="N275" t="b">
         <v>1</v>
@@ -15258,7 +15298,7 @@
         <v>0.7</v>
       </c>
       <c r="H276" t="n">
-        <v>-20.41</v>
+        <v>-19.37</v>
       </c>
       <c r="I276" t="n">
         <v>14.96</v>
@@ -15273,7 +15313,7 @@
         <v>-8.039999999999999</v>
       </c>
       <c r="M276" t="n">
-        <v>-22.5</v>
+        <v>-22.76</v>
       </c>
       <c r="N276" t="b">
         <v>0</v>
@@ -15311,7 +15351,7 @@
         <v>54.3</v>
       </c>
       <c r="H277" t="n">
-        <v>-21.76</v>
+        <v>-22.59</v>
       </c>
       <c r="I277" t="n">
         <v>-2.86</v>
@@ -15326,7 +15366,7 @@
         <v>-24.93</v>
       </c>
       <c r="M277" t="n">
-        <v>-23.84</v>
+        <v>-25.97</v>
       </c>
       <c r="N277" t="b">
         <v>0</v>
@@ -15368,7 +15408,7 @@
         <v>-8.199999999999999</v>
       </c>
       <c r="H278" t="n">
-        <v>-24.97</v>
+        <v>-23.33</v>
       </c>
       <c r="I278" t="n">
         <v>17.48</v>
@@ -15383,7 +15423,7 @@
         <v>-10.68</v>
       </c>
       <c r="M278" t="n">
-        <v>-27.05</v>
+        <v>-26.72</v>
       </c>
       <c r="N278" t="b">
         <v>0</v>
@@ -15421,7 +15461,7 @@
         <v>17.9</v>
       </c>
       <c r="H279" t="n">
-        <v>-14.74</v>
+        <v>-7.07</v>
       </c>
       <c r="I279" t="n">
         <v>12.97</v>
@@ -15436,7 +15476,7 @@
         <v>-8.130000000000001</v>
       </c>
       <c r="M279" t="n">
-        <v>-16.82</v>
+        <v>-10.45</v>
       </c>
       <c r="N279" t="b">
         <v>1</v>
@@ -15474,7 +15514,7 @@
         <v>15.3</v>
       </c>
       <c r="H280" t="n">
-        <v>-50.52</v>
+        <v>-48.94</v>
       </c>
       <c r="I280" t="n">
         <v>-21.4</v>
@@ -15489,7 +15529,7 @@
         <v>-26.97</v>
       </c>
       <c r="M280" t="n">
-        <v>-52.61</v>
+        <v>-52.33</v>
       </c>
       <c r="N280" t="b">
         <v>0</v>
@@ -15527,7 +15567,7 @@
         <v>26.1</v>
       </c>
       <c r="H281" t="n">
-        <v>-34.93</v>
+        <v>-27.77</v>
       </c>
       <c r="I281" t="n">
         <v>-0.51</v>
@@ -15542,7 +15582,7 @@
         <v>-16.45</v>
       </c>
       <c r="M281" t="n">
-        <v>-37.02</v>
+        <v>-31.16</v>
       </c>
       <c r="N281" t="b">
         <v>0</v>
@@ -15580,7 +15620,7 @@
         <v>14.8</v>
       </c>
       <c r="H282" t="n">
-        <v>-12.28</v>
+        <v>-11.05</v>
       </c>
       <c r="I282" t="n">
         <v>0.35</v>
@@ -15595,7 +15635,7 @@
         <v>-3.68</v>
       </c>
       <c r="M282" t="n">
-        <v>-14.37</v>
+        <v>-14.44</v>
       </c>
       <c r="N282" t="b">
         <v>1</v>
@@ -15633,7 +15673,7 @@
         <v>61.6</v>
       </c>
       <c r="H283" t="n">
-        <v>4.31</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="I283" t="n">
         <v>11.47</v>
@@ -15648,7 +15688,7 @@
         <v>-12.86</v>
       </c>
       <c r="M283" t="n">
-        <v>2.23</v>
+        <v>5.25</v>
       </c>
       <c r="N283" t="b">
         <v>0</v>
@@ -15686,7 +15726,7 @@
         <v>-26.1</v>
       </c>
       <c r="H284" t="n">
-        <v>-20.77</v>
+        <v>-20.98</v>
       </c>
       <c r="I284" t="n">
         <v>5.05</v>
@@ -15701,7 +15741,7 @@
         <v>-9.27</v>
       </c>
       <c r="M284" t="n">
-        <v>-22.85</v>
+        <v>-24.36</v>
       </c>
       <c r="N284" t="b">
         <v>0</v>
@@ -15739,7 +15779,7 @@
         <v>-18.5</v>
       </c>
       <c r="H285" t="n">
-        <v>56.38</v>
+        <v>52.27</v>
       </c>
       <c r="I285" t="n">
         <v>16.22</v>
@@ -15754,7 +15794,7 @@
         <v>-9.960000000000001</v>
       </c>
       <c r="M285" t="n">
-        <v>54.29</v>
+        <v>48.88</v>
       </c>
       <c r="N285" t="b">
         <v>0</v>
@@ -15792,7 +15832,7 @@
         <v>1.5</v>
       </c>
       <c r="H286" t="n">
-        <v>0.78</v>
+        <v>5.52</v>
       </c>
       <c r="I286" t="n">
         <v>-7.31</v>
@@ -15807,7 +15847,7 @@
         <v>-18.58</v>
       </c>
       <c r="M286" t="n">
-        <v>-1.3</v>
+        <v>2.13</v>
       </c>
       <c r="N286" t="b">
         <v>0</v>
@@ -15845,7 +15885,7 @@
         <v>-13.5</v>
       </c>
       <c r="H287" t="n">
-        <v>-13.1</v>
+        <v>-13.64</v>
       </c>
       <c r="I287" t="n">
         <v>-1.88</v>
@@ -15860,7 +15900,7 @@
         <v>-11.4</v>
       </c>
       <c r="M287" t="n">
-        <v>-15.19</v>
+        <v>-17.03</v>
       </c>
       <c r="N287" t="b">
         <v>0</v>
@@ -15898,7 +15938,7 @@
         <v>25.5</v>
       </c>
       <c r="H288" t="n">
-        <v>16.2</v>
+        <v>18.38</v>
       </c>
       <c r="I288" t="n">
         <v>-9.369999999999999</v>
@@ -15913,7 +15953,7 @@
         <v>-22.11</v>
       </c>
       <c r="M288" t="n">
-        <v>14.11</v>
+        <v>14.99</v>
       </c>
       <c r="N288" t="b">
         <v>1</v>
@@ -15955,7 +15995,7 @@
         <v>-7.5</v>
       </c>
       <c r="H289" t="n">
-        <v>-30.04</v>
+        <v>-29.95</v>
       </c>
       <c r="I289" t="n">
         <v>4.46</v>
@@ -15970,7 +16010,7 @@
         <v>-8.52</v>
       </c>
       <c r="M289" t="n">
-        <v>-32.13</v>
+        <v>-33.34</v>
       </c>
       <c r="N289" t="b">
         <v>1</v>
@@ -16008,7 +16048,7 @@
         <v>0.7</v>
       </c>
       <c r="H290" t="n">
-        <v>7.78</v>
+        <v>4.68</v>
       </c>
       <c r="I290" t="n">
         <v>11.4</v>
@@ -16023,7 +16063,7 @@
         <v>-7.28</v>
       </c>
       <c r="M290" t="n">
-        <v>5.69</v>
+        <v>1.29</v>
       </c>
       <c r="N290" t="b">
         <v>0</v>
@@ -16061,7 +16101,7 @@
         <v>7.3</v>
       </c>
       <c r="H291" t="n">
-        <v>9.24</v>
+        <v>10.85</v>
       </c>
       <c r="I291" t="n">
         <v>-0.57</v>
@@ -16076,7 +16116,7 @@
         <v>-5.89</v>
       </c>
       <c r="M291" t="n">
-        <v>7.15</v>
+        <v>7.46</v>
       </c>
       <c r="N291" t="b">
         <v>0</v>
@@ -16114,7 +16154,7 @@
         <v>2.1</v>
       </c>
       <c r="H292" t="n">
-        <v>89.41</v>
+        <v>80.68000000000001</v>
       </c>
       <c r="I292" t="n">
         <v>20.72</v>
@@ -16129,7 +16169,7 @@
         <v>-5.79</v>
       </c>
       <c r="M292" t="n">
-        <v>87.31999999999999</v>
+        <v>77.3</v>
       </c>
       <c r="N292" t="b">
         <v>0</v>
@@ -16167,7 +16207,7 @@
         <v>32.2</v>
       </c>
       <c r="H293" t="n">
-        <v>1.78</v>
+        <v>7.4</v>
       </c>
       <c r="I293" t="n">
         <v>6.49</v>
@@ -16182,7 +16222,7 @@
         <v>-3.92</v>
       </c>
       <c r="M293" t="n">
-        <v>-0.31</v>
+        <v>4.02</v>
       </c>
       <c r="N293" t="b">
         <v>1</v>
@@ -16220,7 +16260,7 @@
         <v>-31.7</v>
       </c>
       <c r="H294" t="n">
-        <v>15.16</v>
+        <v>14.07</v>
       </c>
       <c r="I294" t="n">
         <v>17.04</v>
@@ -16235,7 +16275,7 @@
         <v>-4.05</v>
       </c>
       <c r="M294" t="n">
-        <v>13.08</v>
+        <v>10.68</v>
       </c>
       <c r="N294" t="b">
         <v>0</v>
@@ -16273,7 +16313,7 @@
         <v>-11.4</v>
       </c>
       <c r="H295" t="n">
-        <v>-15.85</v>
+        <v>-13.75</v>
       </c>
       <c r="I295" t="n">
         <v>4.36</v>
@@ -16288,7 +16328,7 @@
         <v>-11.36</v>
       </c>
       <c r="M295" t="n">
-        <v>-17.94</v>
+        <v>-17.14</v>
       </c>
       <c r="N295" t="b">
         <v>1</v>
@@ -16326,7 +16366,7 @@
         <v>27.1</v>
       </c>
       <c r="H296" t="n">
-        <v>-26.8</v>
+        <v>-21.22</v>
       </c>
       <c r="I296" t="n">
         <v>5.02</v>
@@ -16341,7 +16381,7 @@
         <v>-14.35</v>
       </c>
       <c r="M296" t="n">
-        <v>-28.88</v>
+        <v>-24.61</v>
       </c>
       <c r="N296" t="b">
         <v>1</v>
@@ -16383,7 +16423,7 @@
         <v>-2.2</v>
       </c>
       <c r="H297" t="n">
-        <v>-7.53</v>
+        <v>-8.029999999999999</v>
       </c>
       <c r="I297" t="n">
         <v>-9.050000000000001</v>
@@ -16398,7 +16438,7 @@
         <v>-18.61</v>
       </c>
       <c r="M297" t="n">
-        <v>-9.619999999999999</v>
+        <v>-11.42</v>
       </c>
       <c r="N297" t="b">
         <v>0</v>
@@ -16436,7 +16476,7 @@
         <v>-11</v>
       </c>
       <c r="H298" t="n">
-        <v>30.52</v>
+        <v>16.81</v>
       </c>
       <c r="I298" t="n">
         <v>10.7</v>
@@ -16451,7 +16491,7 @@
         <v>-9.43</v>
       </c>
       <c r="M298" t="n">
-        <v>28.43</v>
+        <v>13.42</v>
       </c>
       <c r="N298" t="b">
         <v>1</v>
@@ -16489,7 +16529,7 @@
         <v>24.5</v>
       </c>
       <c r="H299" t="n">
-        <v>10.68</v>
+        <v>16.12</v>
       </c>
       <c r="I299" t="n">
         <v>17.24</v>
@@ -16504,7 +16544,7 @@
         <v>-0.47</v>
       </c>
       <c r="M299" t="n">
-        <v>8.6</v>
+        <v>12.73</v>
       </c>
       <c r="N299" t="b">
         <v>0</v>
@@ -16542,7 +16582,7 @@
         <v>-21.6</v>
       </c>
       <c r="H300" t="n">
-        <v>-21.26</v>
+        <v>-16.81</v>
       </c>
       <c r="I300" t="n">
         <v>1.22</v>
@@ -16557,7 +16597,7 @@
         <v>-6.54</v>
       </c>
       <c r="M300" t="n">
-        <v>-23.34</v>
+        <v>-20.2</v>
       </c>
       <c r="N300" t="b">
         <v>0</v>
@@ -16595,7 +16635,7 @@
         <v>3.2</v>
       </c>
       <c r="H301" t="n">
-        <v>-35.36</v>
+        <v>-28.81</v>
       </c>
       <c r="I301" t="n">
         <v>-10.41</v>
@@ -16610,7 +16650,7 @@
         <v>-23.7</v>
       </c>
       <c r="M301" t="n">
-        <v>-37.45</v>
+        <v>-32.19</v>
       </c>
       <c r="N301" t="b">
         <v>1</v>
@@ -16648,7 +16688,7 @@
         <v>14.6</v>
       </c>
       <c r="H302" t="n">
-        <v>-14.4</v>
+        <v>-9.33</v>
       </c>
       <c r="I302" t="n">
         <v>8.539999999999999</v>
@@ -16663,7 +16703,7 @@
         <v>-13.21</v>
       </c>
       <c r="M302" t="n">
-        <v>-16.49</v>
+        <v>-12.71</v>
       </c>
       <c r="N302" t="b">
         <v>0</v>
@@ -16701,7 +16741,7 @@
         <v>-0.3</v>
       </c>
       <c r="H303" t="n">
-        <v>-25.25</v>
+        <v>-19.63</v>
       </c>
       <c r="I303" t="n">
         <v>17.76</v>
@@ -16716,7 +16756,7 @@
         <v>-14.18</v>
       </c>
       <c r="M303" t="n">
-        <v>-27.33</v>
+        <v>-23.02</v>
       </c>
       <c r="N303" t="b">
         <v>1</v>
@@ -16754,7 +16794,7 @@
         <v>-37.2</v>
       </c>
       <c r="H304" t="n">
-        <v>43.68</v>
+        <v>37.11</v>
       </c>
       <c r="I304" t="n">
         <v>21.67</v>
@@ -16769,7 +16809,7 @@
         <v>-6.64</v>
       </c>
       <c r="M304" t="n">
-        <v>41.6</v>
+        <v>33.72</v>
       </c>
       <c r="N304" t="b">
         <v>0</v>
@@ -16807,7 +16847,7 @@
         <v>-6.8</v>
       </c>
       <c r="H305" t="n">
-        <v>35.26</v>
+        <v>38.59</v>
       </c>
       <c r="I305" t="n">
         <v>8.279999999999999</v>
@@ -16822,7 +16862,7 @@
         <v>-6.78</v>
       </c>
       <c r="M305" t="n">
-        <v>33.18</v>
+        <v>35.2</v>
       </c>
       <c r="N305" t="b">
         <v>0</v>
@@ -16860,7 +16900,7 @@
         <v>10.4</v>
       </c>
       <c r="H306" t="n">
-        <v>27.45</v>
+        <v>31.35</v>
       </c>
       <c r="I306" t="n">
         <v>11.05</v>
@@ -16875,7 +16915,7 @@
         <v>-5.54</v>
       </c>
       <c r="M306" t="n">
-        <v>25.36</v>
+        <v>27.96</v>
       </c>
       <c r="N306" t="b">
         <v>1</v>
@@ -16913,7 +16953,7 @@
         <v>34.6</v>
       </c>
       <c r="H307" t="n">
-        <v>-17.15</v>
+        <v>-12.26</v>
       </c>
       <c r="I307" t="n">
         <v>5.7</v>
@@ -16928,7 +16968,7 @@
         <v>-7.7</v>
       </c>
       <c r="M307" t="n">
-        <v>-19.23</v>
+        <v>-15.65</v>
       </c>
       <c r="N307" t="b">
         <v>1</v>
@@ -16966,7 +17006,7 @@
         <v>-31.2</v>
       </c>
       <c r="H308" t="n">
-        <v>-22.91</v>
+        <v>-24.67</v>
       </c>
       <c r="I308" t="n">
         <v>1.03</v>
@@ -16981,7 +17021,7 @@
         <v>-13.65</v>
       </c>
       <c r="M308" t="n">
-        <v>-24.99</v>
+        <v>-28.06</v>
       </c>
       <c r="N308" t="b">
         <v>0</v>
@@ -17019,7 +17059,7 @@
         <v>4</v>
       </c>
       <c r="H309" t="n">
-        <v>67.77</v>
+        <v>69.38</v>
       </c>
       <c r="I309" t="n">
         <v>8.75</v>
@@ -17034,7 +17074,7 @@
         <v>-11.02</v>
       </c>
       <c r="M309" t="n">
-        <v>65.69</v>
+        <v>66</v>
       </c>
       <c r="N309" t="b">
         <v>0</v>
@@ -17072,7 +17112,7 @@
         <v>-42</v>
       </c>
       <c r="H310" t="n">
-        <v>44.12</v>
+        <v>39.57</v>
       </c>
       <c r="I310" t="n">
         <v>-3.61</v>
@@ -17087,7 +17127,7 @@
         <v>-11.94</v>
       </c>
       <c r="M310" t="n">
-        <v>42.04</v>
+        <v>36.18</v>
       </c>
       <c r="N310" t="b">
         <v>0</v>
@@ -17125,7 +17165,7 @@
         <v>-14.7</v>
       </c>
       <c r="H311" t="n">
-        <v>5.11</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="I311" t="n">
         <v>12.94</v>
@@ -17140,7 +17180,7 @@
         <v>-2.34</v>
       </c>
       <c r="M311" t="n">
-        <v>3.02</v>
+        <v>6.15</v>
       </c>
       <c r="N311" t="b">
         <v>0</v>
@@ -17178,7 +17218,7 @@
         <v>-21.5</v>
       </c>
       <c r="H312" t="n">
-        <v>0.6899999999999999</v>
+        <v>-1.19</v>
       </c>
       <c r="I312" t="n">
         <v>10.65</v>
@@ -17193,7 +17233,7 @@
         <v>-6.89</v>
       </c>
       <c r="M312" t="n">
-        <v>-1.4</v>
+        <v>-4.58</v>
       </c>
       <c r="N312" t="b">
         <v>1</v>
@@ -17231,7 +17271,7 @@
         <v>3.5</v>
       </c>
       <c r="H313" t="n">
-        <v>68.11</v>
+        <v>66.55</v>
       </c>
       <c r="I313" t="n">
         <v>33.01</v>
@@ -17246,7 +17286,7 @@
         <v>-0.92</v>
       </c>
       <c r="M313" t="n">
-        <v>66.02</v>
+        <v>63.17</v>
       </c>
       <c r="N313" t="b">
         <v>1</v>
@@ -17284,7 +17324,7 @@
         <v>19.8</v>
       </c>
       <c r="H314" t="n">
-        <v>-3.39</v>
+        <v>3.16</v>
       </c>
       <c r="I314" t="n">
         <v>4.74</v>
@@ -17299,7 +17339,7 @@
         <v>-9.9</v>
       </c>
       <c r="M314" t="n">
-        <v>-5.47</v>
+        <v>-0.23</v>
       </c>
       <c r="N314" t="b">
         <v>0</v>
@@ -17337,7 +17377,7 @@
         <v>14</v>
       </c>
       <c r="H315" t="n">
-        <v>49.91</v>
+        <v>46.71</v>
       </c>
       <c r="I315" t="n">
         <v>2.89</v>
@@ -17352,7 +17392,7 @@
         <v>-1.94</v>
       </c>
       <c r="M315" t="n">
-        <v>47.83</v>
+        <v>43.32</v>
       </c>
       <c r="N315" t="b">
         <v>0</v>
@@ -17394,7 +17434,7 @@
         <v>-7.4</v>
       </c>
       <c r="H316" t="n">
-        <v>21.72</v>
+        <v>14.62</v>
       </c>
       <c r="I316" t="n">
         <v>-3.85</v>
@@ -17409,7 +17449,7 @@
         <v>-21.11</v>
       </c>
       <c r="M316" t="n">
-        <v>19.64</v>
+        <v>11.24</v>
       </c>
       <c r="N316" t="b">
         <v>0</v>
@@ -17447,7 +17487,7 @@
         <v>20.2</v>
       </c>
       <c r="H317" t="n">
-        <v>-22.59</v>
+        <v>-19.43</v>
       </c>
       <c r="I317" t="n">
         <v>-1.23</v>
@@ -17462,7 +17502,7 @@
         <v>-12.56</v>
       </c>
       <c r="M317" t="n">
-        <v>-24.68</v>
+        <v>-22.82</v>
       </c>
       <c r="N317" t="b">
         <v>0</v>
@@ -17500,7 +17540,7 @@
         <v>-16.2</v>
       </c>
       <c r="H318" t="n">
-        <v>2.84</v>
+        <v>6.13</v>
       </c>
       <c r="I318" t="n">
         <v>25.77</v>
@@ -17515,7 +17555,7 @@
         <v>-1.7</v>
       </c>
       <c r="M318" t="n">
-        <v>0.75</v>
+        <v>2.74</v>
       </c>
       <c r="N318" t="b">
         <v>1</v>
@@ -17553,7 +17593,7 @@
         <v>-34.6</v>
       </c>
       <c r="H319" t="n">
-        <v>24.24</v>
+        <v>19.19</v>
       </c>
       <c r="I319" t="n">
         <v>23.65</v>
@@ -17568,7 +17608,7 @@
         <v>-3.83</v>
       </c>
       <c r="M319" t="n">
-        <v>22.16</v>
+        <v>15.8</v>
       </c>
       <c r="N319" t="b">
         <v>1</v>
@@ -17606,7 +17646,7 @@
         <v>-24</v>
       </c>
       <c r="H320" t="n">
-        <v>73.29000000000001</v>
+        <v>76.68000000000001</v>
       </c>
       <c r="I320" t="n">
         <v>10.85</v>
@@ -17621,7 +17661,7 @@
         <v>-5.43</v>
       </c>
       <c r="M320" t="n">
-        <v>71.2</v>
+        <v>73.3</v>
       </c>
       <c r="N320" t="b">
         <v>0</v>
@@ -17659,7 +17699,7 @@
         <v>-48.1</v>
       </c>
       <c r="H321" t="n">
-        <v>-37.85</v>
+        <v>-35.54</v>
       </c>
       <c r="I321" t="n">
         <v>2.19</v>
@@ -17674,7 +17714,7 @@
         <v>-13.66</v>
       </c>
       <c r="M321" t="n">
-        <v>-39.94</v>
+        <v>-38.93</v>
       </c>
       <c r="N321" t="b">
         <v>0</v>
@@ -17712,7 +17752,7 @@
         <v>-42.2</v>
       </c>
       <c r="H322" t="n">
-        <v>-13.05</v>
+        <v>-10.6</v>
       </c>
       <c r="I322" t="n">
         <v>19.24</v>
@@ -17727,7 +17767,7 @@
         <v>-0.93</v>
       </c>
       <c r="M322" t="n">
-        <v>-15.14</v>
+        <v>-13.98</v>
       </c>
       <c r="N322" t="b">
         <v>0</v>
@@ -17765,7 +17805,7 @@
         <v>-24.9</v>
       </c>
       <c r="H323" t="n">
-        <v>-8</v>
+        <v>-2.8</v>
       </c>
       <c r="I323" t="n">
         <v>10.88</v>
@@ -17780,7 +17820,7 @@
         <v>-4.1</v>
       </c>
       <c r="M323" t="n">
-        <v>-10.09</v>
+        <v>-6.19</v>
       </c>
       <c r="N323" t="b">
         <v>1</v>
@@ -17822,7 +17862,7 @@
         <v>-8.1</v>
       </c>
       <c r="H324" t="n">
-        <v>20.62</v>
+        <v>15.36</v>
       </c>
       <c r="I324" t="n">
         <v>14.27</v>
@@ -17837,7 +17877,7 @@
         <v>-10.92</v>
       </c>
       <c r="M324" t="n">
-        <v>18.53</v>
+        <v>11.97</v>
       </c>
       <c r="N324" t="b">
         <v>1</v>
@@ -17875,7 +17915,7 @@
         <v>-28.3</v>
       </c>
       <c r="H325" t="n">
-        <v>-30.41</v>
+        <v>-29.81</v>
       </c>
       <c r="I325" t="n">
         <v>-8.949999999999999</v>
@@ -17890,7 +17930,7 @@
         <v>-13.18</v>
       </c>
       <c r="M325" t="n">
-        <v>-32.5</v>
+        <v>-33.19</v>
       </c>
       <c r="N325" t="b">
         <v>0</v>
@@ -17928,7 +17968,7 @@
         <v>-10.8</v>
       </c>
       <c r="H326" t="n">
-        <v>7.33</v>
+        <v>9.4</v>
       </c>
       <c r="I326" t="n">
         <v>1.78</v>
@@ -17943,7 +17983,7 @@
         <v>-7.51</v>
       </c>
       <c r="M326" t="n">
-        <v>5.25</v>
+        <v>6.02</v>
       </c>
       <c r="N326" t="b">
         <v>0</v>
@@ -17981,7 +18021,7 @@
         <v>-6</v>
       </c>
       <c r="H327" t="n">
-        <v>-38.73</v>
+        <v>-33.23</v>
       </c>
       <c r="I327" t="n">
         <v>3.31</v>
@@ -17996,7 +18036,7 @@
         <v>-21.48</v>
       </c>
       <c r="M327" t="n">
-        <v>-40.82</v>
+        <v>-36.62</v>
       </c>
       <c r="N327" t="b">
         <v>1</v>
@@ -18034,7 +18074,7 @@
         <v>-10.2</v>
       </c>
       <c r="H328" t="n">
-        <v>-9.359999999999999</v>
+        <v>-8.32</v>
       </c>
       <c r="I328" t="n">
         <v>15.03</v>
@@ -18049,7 +18089,7 @@
         <v>-1.61</v>
       </c>
       <c r="M328" t="n">
-        <v>-11.45</v>
+        <v>-11.71</v>
       </c>
       <c r="N328" t="b">
         <v>1</v>
@@ -18087,7 +18127,7 @@
         <v>-30.5</v>
       </c>
       <c r="H329" t="n">
-        <v>-0.77</v>
+        <v>-2.41</v>
       </c>
       <c r="I329" t="n">
         <v>2.96</v>
@@ -18102,7 +18142,7 @@
         <v>-17.88</v>
       </c>
       <c r="M329" t="n">
-        <v>-2.85</v>
+        <v>-5.79</v>
       </c>
       <c r="N329" t="b">
         <v>1</v>
@@ -18140,7 +18180,7 @@
         <v>2.3</v>
       </c>
       <c r="H330" t="n">
-        <v>7.73</v>
+        <v>11.6</v>
       </c>
       <c r="I330" t="n">
         <v>-0.95</v>
@@ -18155,7 +18195,7 @@
         <v>-7.81</v>
       </c>
       <c r="M330" t="n">
-        <v>5.65</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="N330" t="b">
         <v>0</v>
@@ -18193,7 +18233,7 @@
         <v>25.7</v>
       </c>
       <c r="H331" t="n">
-        <v>-13.43</v>
+        <v>-9.27</v>
       </c>
       <c r="I331" t="n">
         <v>11.3</v>
@@ -18208,7 +18248,7 @@
         <v>-11.03</v>
       </c>
       <c r="M331" t="n">
-        <v>-15.52</v>
+        <v>-12.66</v>
       </c>
       <c r="N331" t="b">
         <v>1</v>
@@ -18246,7 +18286,7 @@
         <v>40.7</v>
       </c>
       <c r="H332" t="n">
-        <v>29.41</v>
+        <v>25.83</v>
       </c>
       <c r="I332" t="n">
         <v>-4.08</v>
@@ -18261,7 +18301,7 @@
         <v>-11.2</v>
       </c>
       <c r="M332" t="n">
-        <v>27.32</v>
+        <v>22.45</v>
       </c>
       <c r="N332" t="b">
         <v>1</v>
@@ -18299,7 +18339,7 @@
         <v>68.90000000000001</v>
       </c>
       <c r="H333" t="n">
-        <v>18.16</v>
+        <v>14.22</v>
       </c>
       <c r="I333" t="n">
         <v>1.84</v>
@@ -18314,7 +18354,7 @@
         <v>-10.43</v>
       </c>
       <c r="M333" t="n">
-        <v>16.08</v>
+        <v>10.84</v>
       </c>
       <c r="N333" t="b">
         <v>1</v>
@@ -18352,7 +18392,7 @@
         <v>-40.8</v>
       </c>
       <c r="H334" t="n">
-        <v>-23.32</v>
+        <v>-25.2</v>
       </c>
       <c r="I334" t="n">
         <v>21.71</v>
@@ -18367,7 +18407,7 @@
         <v>-3.3</v>
       </c>
       <c r="M334" t="n">
-        <v>-25.41</v>
+        <v>-28.59</v>
       </c>
       <c r="N334" t="b">
         <v>1</v>
@@ -18405,7 +18445,7 @@
         <v>-10.1</v>
       </c>
       <c r="H335" t="n">
-        <v>-14.16</v>
+        <v>-16.76</v>
       </c>
       <c r="I335" t="n">
         <v>1.83</v>
@@ -18420,7 +18460,7 @@
         <v>-3.45</v>
       </c>
       <c r="M335" t="n">
-        <v>-16.24</v>
+        <v>-20.15</v>
       </c>
       <c r="N335" t="b">
         <v>0</v>
@@ -18552,16 +18592,18 @@
         <v>51.4</v>
       </c>
       <c r="H2" t="n">
-        <v>-1.46</v>
-      </c>
-      <c r="I2" t="inlineStr"/>
+        <v>-1.92</v>
+      </c>
+      <c r="I2" t="n">
+        <v>-1.92</v>
+      </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="n">
         <v>-7.85</v>
       </c>
       <c r="M2" t="n">
-        <v>0.77</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="N2" t="b">
         <v>1</v>
@@ -18599,7 +18641,7 @@
         <v>-16.6</v>
       </c>
       <c r="H3" t="n">
-        <v>0.61</v>
+        <v>-3.11</v>
       </c>
       <c r="I3" t="n">
         <v>-0.75</v>
@@ -18607,10 +18649,10 @@
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="n">
-        <v>-2.5</v>
+        <v>-3.97</v>
       </c>
       <c r="M3" t="n">
-        <v>2.64</v>
+        <v>-2.32</v>
       </c>
       <c r="N3" t="b">
         <v>1</v>
@@ -18648,7 +18690,7 @@
         <v>-5</v>
       </c>
       <c r="H4" t="n">
-        <v>8.619999999999999</v>
+        <v>7.48</v>
       </c>
       <c r="I4" t="n">
         <v>12.26</v>
@@ -18659,7 +18701,7 @@
         <v>-1.75</v>
       </c>
       <c r="M4" t="n">
-        <v>10.66</v>
+        <v>8.27</v>
       </c>
       <c r="N4" t="b">
         <v>1</v>
@@ -18697,7 +18739,7 @@
         <v>12.5</v>
       </c>
       <c r="H5" t="n">
-        <v>7.59</v>
+        <v>7.49</v>
       </c>
       <c r="I5" t="n">
         <v>7.44</v>
@@ -18708,7 +18750,7 @@
         <v>-2.59</v>
       </c>
       <c r="M5" t="n">
-        <v>9.619999999999999</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="N5" t="b">
         <v>1</v>
@@ -18746,7 +18788,7 @@
         <v>-17.3</v>
       </c>
       <c r="H6" t="n">
-        <v>5.42</v>
+        <v>5.13</v>
       </c>
       <c r="I6" t="n">
         <v>1.16</v>
@@ -18757,7 +18799,7 @@
         <v>-6.51</v>
       </c>
       <c r="M6" t="n">
-        <v>7.75</v>
+        <v>6.22</v>
       </c>
       <c r="N6" t="b">
         <v>1</v>
@@ -18784,7 +18826,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Retired</t>
         </is>
       </c>
       <c r="E7" t="inlineStr"/>
@@ -18795,7 +18837,7 @@
         <v>-21.8</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.03</v>
+        <v>-0.47</v>
       </c>
       <c r="I7" t="n">
         <v>-3.37</v>
@@ -18806,7 +18848,7 @@
         <v>-5.33</v>
       </c>
       <c r="M7" t="n">
-        <v>0.82</v>
+        <v>-0.89</v>
       </c>
       <c r="N7" t="b">
         <v>1</v>
@@ -18833,7 +18875,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Extended</t>
+          <t>Retired</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
@@ -18844,18 +18886,20 @@
         <v>-16.7</v>
       </c>
       <c r="H8" t="n">
-        <v>23.11</v>
+        <v>15.75</v>
       </c>
       <c r="I8" t="n">
         <v>26.03</v>
       </c>
-      <c r="J8" t="inlineStr"/>
+      <c r="J8" t="n">
+        <v>15.75</v>
+      </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="n">
         <v>-6.98</v>
       </c>
       <c r="M8" t="n">
-        <v>24</v>
+        <v>15.38</v>
       </c>
       <c r="N8" t="b">
         <v>1</v>
@@ -18882,7 +18926,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Extended</t>
+          <t>Retired</t>
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
@@ -18893,18 +18937,20 @@
         <v>-11.5</v>
       </c>
       <c r="H9" t="n">
-        <v>22.43</v>
+        <v>13.34</v>
       </c>
       <c r="I9" t="n">
         <v>7.47</v>
       </c>
-      <c r="J9" t="inlineStr"/>
+      <c r="J9" t="n">
+        <v>13.34</v>
+      </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="n">
         <v>-0.99</v>
       </c>
       <c r="M9" t="n">
-        <v>23.33</v>
+        <v>12.97</v>
       </c>
       <c r="N9" t="b">
         <v>1</v>
@@ -18942,7 +18988,7 @@
         <v>0.1</v>
       </c>
       <c r="H10" t="n">
-        <v>19.97</v>
+        <v>23.27</v>
       </c>
       <c r="I10" t="n">
         <v>6.41</v>
@@ -18955,7 +19001,7 @@
         <v>-2.51</v>
       </c>
       <c r="M10" t="n">
-        <v>21.12</v>
+        <v>23.15</v>
       </c>
       <c r="N10" t="b">
         <v>1</v>
@@ -18993,7 +19039,7 @@
         <v>-31.6</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.97</v>
+        <v>1.45</v>
       </c>
       <c r="I11" t="n">
         <v>-2.12</v>
@@ -19006,7 +19052,7 @@
         <v>-8.140000000000001</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.83</v>
+        <v>1.34</v>
       </c>
       <c r="N11" t="b">
         <v>1</v>
@@ -19044,7 +19090,7 @@
         <v>-2.7</v>
       </c>
       <c r="H12" t="n">
-        <v>-7.58</v>
+        <v>-5.9</v>
       </c>
       <c r="I12" t="n">
         <v>-3.77</v>
@@ -19057,7 +19103,7 @@
         <v>-12.44</v>
       </c>
       <c r="M12" t="n">
-        <v>-5.76</v>
+        <v>-5.33</v>
       </c>
       <c r="N12" t="b">
         <v>1</v>
@@ -19095,7 +19141,7 @@
         <v>26.9</v>
       </c>
       <c r="H13" t="n">
-        <v>-2.1</v>
+        <v>-2.72</v>
       </c>
       <c r="I13" t="n">
         <v>-3.24</v>
@@ -19108,7 +19154,7 @@
         <v>-12.88</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.28</v>
+        <v>-2.16</v>
       </c>
       <c r="N13" t="b">
         <v>1</v>
@@ -19146,7 +19192,7 @@
         <v>-21.5</v>
       </c>
       <c r="H14" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="I14" t="n">
         <v>-1.68</v>
@@ -19159,7 +19205,7 @@
         <v>-8.130000000000001</v>
       </c>
       <c r="M14" t="n">
-        <v>3.32</v>
+        <v>2.55</v>
       </c>
       <c r="N14" t="b">
         <v>1</v>
@@ -19197,7 +19243,7 @@
         <v>-18.1</v>
       </c>
       <c r="H15" t="n">
-        <v>18.32</v>
+        <v>18.03</v>
       </c>
       <c r="I15" t="n">
         <v>4.46</v>
@@ -19210,7 +19256,7 @@
         <v>-2.69</v>
       </c>
       <c r="M15" t="n">
-        <v>19.14</v>
+        <v>17.58</v>
       </c>
       <c r="N15" t="b">
         <v>1</v>
@@ -19248,7 +19294,7 @@
         <v>32.1</v>
       </c>
       <c r="H16" t="n">
-        <v>12.63</v>
+        <v>10.64</v>
       </c>
       <c r="I16" t="n">
         <v>-3.47</v>
@@ -19261,7 +19307,7 @@
         <v>-6.94</v>
       </c>
       <c r="M16" t="n">
-        <v>12.81</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="N16" t="b">
         <v>1</v>
@@ -19299,7 +19345,7 @@
         <v>41.6</v>
       </c>
       <c r="H17" t="n">
-        <v>8.42</v>
+        <v>10.53</v>
       </c>
       <c r="I17" t="n">
         <v>3.43</v>
@@ -19312,7 +19358,7 @@
         <v>-4.38</v>
       </c>
       <c r="M17" t="n">
-        <v>8.6</v>
+        <v>9.44</v>
       </c>
       <c r="N17" t="b">
         <v>1</v>
@@ -19350,7 +19396,7 @@
         <v>-14.4</v>
       </c>
       <c r="H18" t="n">
-        <v>8.81</v>
+        <v>9.09</v>
       </c>
       <c r="I18" t="n">
         <v>-2.38</v>
@@ -19363,7 +19409,7 @@
         <v>-6.46</v>
       </c>
       <c r="M18" t="n">
-        <v>8.99</v>
+        <v>7.99</v>
       </c>
       <c r="N18" t="b">
         <v>1</v>
@@ -19401,7 +19447,7 @@
         <v>6.4</v>
       </c>
       <c r="H19" t="n">
-        <v>20.07</v>
+        <v>16.18</v>
       </c>
       <c r="I19" t="n">
         <v>1.48</v>
@@ -19414,7 +19460,7 @@
         <v>-3.35</v>
       </c>
       <c r="M19" t="n">
-        <v>20.24</v>
+        <v>15.08</v>
       </c>
       <c r="N19" t="b">
         <v>1</v>
@@ -19452,7 +19498,7 @@
         <v>-10</v>
       </c>
       <c r="H20" t="n">
-        <v>-12.33</v>
+        <v>-10.18</v>
       </c>
       <c r="I20" t="n">
         <v>-3.29</v>
@@ -19465,7 +19511,7 @@
         <v>-14.66</v>
       </c>
       <c r="M20" t="n">
-        <v>-12.15</v>
+        <v>-11.27</v>
       </c>
       <c r="N20" t="b">
         <v>1</v>
@@ -19503,7 +19549,7 @@
         <v>20.2</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.44</v>
+        <v>0.11</v>
       </c>
       <c r="I21" t="n">
         <v>3.45</v>
@@ -19516,7 +19562,7 @@
         <v>-1.07</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.67</v>
+        <v>-1.4</v>
       </c>
       <c r="N21" t="b">
         <v>1</v>
@@ -19554,7 +19600,7 @@
         <v>1.9</v>
       </c>
       <c r="H22" t="n">
-        <v>0.4</v>
+        <v>6.91</v>
       </c>
       <c r="I22" t="n">
         <v>-10.64</v>
@@ -19567,7 +19613,7 @@
         <v>-14.75</v>
       </c>
       <c r="M22" t="n">
-        <v>0.17</v>
+        <v>5.4</v>
       </c>
       <c r="N22" t="b">
         <v>1</v>
@@ -19605,7 +19651,7 @@
         <v>43.7</v>
       </c>
       <c r="H23" t="n">
-        <v>16.17</v>
+        <v>18.83</v>
       </c>
       <c r="I23" t="n">
         <v>3.16</v>
@@ -19618,7 +19664,7 @@
         <v>-2.44</v>
       </c>
       <c r="M23" t="n">
-        <v>15.94</v>
+        <v>17.32</v>
       </c>
       <c r="N23" t="b">
         <v>1</v>
@@ -19656,7 +19702,7 @@
         <v>37.5</v>
       </c>
       <c r="H24" t="n">
-        <v>24.11</v>
+        <v>28.95</v>
       </c>
       <c r="I24" t="n">
         <v>5.86</v>
@@ -19669,7 +19715,7 @@
         <v>-3.95</v>
       </c>
       <c r="M24" t="n">
-        <v>23.74</v>
+        <v>27.3</v>
       </c>
       <c r="N24" t="b">
         <v>1</v>
@@ -19707,7 +19753,7 @@
         <v>40.2</v>
       </c>
       <c r="H25" t="n">
-        <v>10.78</v>
+        <v>12.14</v>
       </c>
       <c r="I25" t="n">
         <v>-1.11</v>
@@ -19720,7 +19766,7 @@
         <v>-5.29</v>
       </c>
       <c r="M25" t="n">
-        <v>10.4</v>
+        <v>10.49</v>
       </c>
       <c r="N25" t="b">
         <v>1</v>
@@ -19758,7 +19804,7 @@
         <v>10.7</v>
       </c>
       <c r="H26" t="n">
-        <v>-6.08</v>
+        <v>-2.73</v>
       </c>
       <c r="I26" t="n">
         <v>7.3</v>
@@ -19771,7 +19817,7 @@
         <v>-3.78</v>
       </c>
       <c r="M26" t="n">
-        <v>-6.45</v>
+        <v>-4.39</v>
       </c>
       <c r="N26" t="b">
         <v>1</v>
@@ -19809,7 +19855,7 @@
         <v>25.6</v>
       </c>
       <c r="H27" t="n">
-        <v>19.01</v>
+        <v>19.71</v>
       </c>
       <c r="I27" t="n">
         <v>7.71</v>
@@ -19822,7 +19868,7 @@
         <v>-4.85</v>
       </c>
       <c r="M27" t="n">
-        <v>19.39</v>
+        <v>18.81</v>
       </c>
       <c r="N27" t="b">
         <v>1</v>
@@ -19860,7 +19906,7 @@
         <v>-6.9</v>
       </c>
       <c r="H28" t="n">
-        <v>19.98</v>
+        <v>20.87</v>
       </c>
       <c r="I28" t="n">
         <v>6.44</v>
@@ -19873,7 +19919,7 @@
         <v>-4.53</v>
       </c>
       <c r="M28" t="n">
-        <v>20.27</v>
+        <v>19.89</v>
       </c>
       <c r="N28" t="b">
         <v>1</v>
@@ -19911,7 +19957,7 @@
         <v>0.3</v>
       </c>
       <c r="H29" t="n">
-        <v>-16.34</v>
+        <v>-13.73</v>
       </c>
       <c r="I29" t="n">
         <v>-10.53</v>
@@ -19924,7 +19970,7 @@
         <v>-17.73</v>
       </c>
       <c r="M29" t="n">
-        <v>-15.56</v>
+        <v>-14.21</v>
       </c>
       <c r="N29" t="b">
         <v>1</v>
@@ -19962,7 +20008,7 @@
         <v>2.8</v>
       </c>
       <c r="H30" t="n">
-        <v>-1.37</v>
+        <v>3.37</v>
       </c>
       <c r="I30" t="n">
         <v>3.18</v>
@@ -19975,7 +20021,7 @@
         <v>-0.88</v>
       </c>
       <c r="M30" t="n">
-        <v>-1.29</v>
+        <v>2.17</v>
       </c>
       <c r="N30" t="b">
         <v>1</v>
@@ -20013,7 +20059,7 @@
         <v>34.5</v>
       </c>
       <c r="H31" t="n">
-        <v>11.84</v>
+        <v>10.46</v>
       </c>
       <c r="I31" t="n">
         <v>0.66</v>
@@ -20026,7 +20072,7 @@
         <v>-2.64</v>
       </c>
       <c r="M31" t="n">
-        <v>11.92</v>
+        <v>9.26</v>
       </c>
       <c r="N31" t="b">
         <v>1</v>
@@ -20064,7 +20110,7 @@
         <v>24.3</v>
       </c>
       <c r="H32" t="n">
-        <v>30.41</v>
+        <v>46.7</v>
       </c>
       <c r="I32" t="n">
         <v>2.54</v>
@@ -20077,7 +20123,7 @@
         <v>-5.21</v>
       </c>
       <c r="M32" t="n">
-        <v>31.12</v>
+        <v>46.14</v>
       </c>
       <c r="N32" t="b">
         <v>1</v>
@@ -20115,7 +20161,7 @@
         <v>-16.9</v>
       </c>
       <c r="H33" t="n">
-        <v>5.12</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I33" t="n">
         <v>-6.47</v>
@@ -20128,7 +20174,7 @@
         <v>-11.5</v>
       </c>
       <c r="M33" t="n">
-        <v>5.83</v>
+        <v>8.65</v>
       </c>
       <c r="N33" t="b">
         <v>1</v>
@@ -20166,7 +20212,7 @@
         <v>20.3</v>
       </c>
       <c r="H34" t="n">
-        <v>-19.15</v>
+        <v>-20.48</v>
       </c>
       <c r="I34" t="n">
         <v>-2.07</v>
@@ -20179,7 +20225,7 @@
         <v>-17.35</v>
       </c>
       <c r="M34" t="n">
-        <v>-18.29</v>
+        <v>-20.88</v>
       </c>
       <c r="N34" t="b">
         <v>1</v>
@@ -20217,7 +20263,7 @@
         <v>0.3</v>
       </c>
       <c r="H35" t="n">
-        <v>-22.08</v>
+        <v>-22.98</v>
       </c>
       <c r="I35" t="n">
         <v>-9.9</v>
@@ -20230,7 +20276,7 @@
         <v>-21.72</v>
       </c>
       <c r="M35" t="n">
-        <v>-21.7</v>
+        <v>-23.87</v>
       </c>
       <c r="N35" t="b">
         <v>1</v>
@@ -20268,7 +20314,7 @@
         <v>49.4</v>
       </c>
       <c r="H36" t="n">
-        <v>1.02</v>
+        <v>4.74</v>
       </c>
       <c r="I36" t="n">
         <v>2.9</v>
@@ -20281,7 +20327,7 @@
         <v>-5.67</v>
       </c>
       <c r="M36" t="n">
-        <v>1.58</v>
+        <v>4.04</v>
       </c>
       <c r="N36" t="b">
         <v>1</v>
@@ -20319,7 +20365,7 @@
         <v>4.5</v>
       </c>
       <c r="H37" t="n">
-        <v>0.73</v>
+        <v>-2.67</v>
       </c>
       <c r="I37" t="n">
         <v>-7.61</v>
@@ -20332,7 +20378,7 @@
         <v>-11.06</v>
       </c>
       <c r="M37" t="n">
-        <v>1.29</v>
+        <v>-3.38</v>
       </c>
       <c r="N37" t="b">
         <v>1</v>
@@ -20370,7 +20416,7 @@
         <v>2.1</v>
       </c>
       <c r="H38" t="n">
-        <v>-3.32</v>
+        <v>-6.85</v>
       </c>
       <c r="I38" t="n">
         <v>0.25</v>
@@ -20383,7 +20429,7 @@
         <v>-16.43</v>
       </c>
       <c r="M38" t="n">
-        <v>-2.79</v>
+        <v>-7.58</v>
       </c>
       <c r="N38" t="b">
         <v>1</v>
@@ -20421,7 +20467,7 @@
         <v>-17.9</v>
       </c>
       <c r="H39" t="n">
-        <v>8.51</v>
+        <v>7.56</v>
       </c>
       <c r="I39" t="n">
         <v>0.6</v>
@@ -20434,7 +20480,7 @@
         <v>-4.72</v>
       </c>
       <c r="M39" t="n">
-        <v>9.039999999999999</v>
+        <v>6.83</v>
       </c>
       <c r="N39" t="b">
         <v>1</v>
@@ -20472,7 +20518,7 @@
         <v>19.4</v>
       </c>
       <c r="H40" t="n">
-        <v>-7.56</v>
+        <v>-8.17</v>
       </c>
       <c r="I40" t="n">
         <v>-10.01</v>
@@ -20485,7 +20531,7 @@
         <v>-15.23</v>
       </c>
       <c r="M40" t="n">
-        <v>-6.46</v>
+        <v>-8.33</v>
       </c>
       <c r="N40" t="b">
         <v>1</v>
@@ -20523,7 +20569,7 @@
         <v>-2.6</v>
       </c>
       <c r="H41" t="n">
-        <v>-7.85</v>
+        <v>-17.1</v>
       </c>
       <c r="I41" t="n">
         <v>-4.27</v>
@@ -20536,7 +20582,7 @@
         <v>-4.86</v>
       </c>
       <c r="M41" t="n">
-        <v>-6.96</v>
+        <v>-17.47</v>
       </c>
       <c r="N41" t="b">
         <v>1</v>
@@ -20574,7 +20620,7 @@
         <v>23.8</v>
       </c>
       <c r="H42" t="n">
-        <v>0.71</v>
+        <v>6.22</v>
       </c>
       <c r="I42" t="n">
         <v>1.36</v>
@@ -20587,7 +20633,7 @@
         <v>-9.94</v>
       </c>
       <c r="M42" t="n">
-        <v>2.56</v>
+        <v>6.81</v>
       </c>
       <c r="N42" t="b">
         <v>1</v>
@@ -20625,7 +20671,7 @@
         <v>38.9</v>
       </c>
       <c r="H43" t="n">
-        <v>-15.26</v>
+        <v>-10.49</v>
       </c>
       <c r="I43" t="n">
         <v>-9.220000000000001</v>
@@ -20638,7 +20684,7 @@
         <v>-9.83</v>
       </c>
       <c r="M43" t="n">
-        <v>-13.42</v>
+        <v>-9.9</v>
       </c>
       <c r="N43" t="b">
         <v>1</v>
@@ -20676,7 +20722,7 @@
         <v>43.2</v>
       </c>
       <c r="H44" t="n">
-        <v>-7.52</v>
+        <v>-10.7</v>
       </c>
       <c r="I44" t="n">
         <v>-3.15</v>
@@ -20689,7 +20735,7 @@
         <v>-17.51</v>
       </c>
       <c r="M44" t="n">
-        <v>-5.84</v>
+        <v>-10.28</v>
       </c>
       <c r="N44" t="b">
         <v>1</v>
@@ -20727,7 +20773,7 @@
         <v>-8.199999999999999</v>
       </c>
       <c r="H45" t="n">
-        <v>8.31</v>
+        <v>3.8</v>
       </c>
       <c r="I45" t="n">
         <v>5.34</v>
@@ -20740,7 +20786,7 @@
         <v>-5.27</v>
       </c>
       <c r="M45" t="n">
-        <v>9.99</v>
+        <v>4.23</v>
       </c>
       <c r="N45" t="b">
         <v>1</v>
@@ -20778,7 +20824,7 @@
         <v>-23.9</v>
       </c>
       <c r="H46" t="n">
-        <v>3.77</v>
+        <v>7.34</v>
       </c>
       <c r="I46" t="n">
         <v>3.28</v>
@@ -20791,7 +20837,7 @@
         <v>-4.46</v>
       </c>
       <c r="M46" t="n">
-        <v>5.16</v>
+        <v>7.48</v>
       </c>
       <c r="N46" t="b">
         <v>1</v>
@@ -20829,7 +20875,7 @@
         <v>26.7</v>
       </c>
       <c r="H47" t="n">
-        <v>-1.04</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="I47" t="n">
         <v>-0.05</v>
@@ -20842,7 +20888,7 @@
         <v>-0.87</v>
       </c>
       <c r="M47" t="n">
-        <v>0.35</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="N47" t="b">
         <v>1</v>
@@ -20880,7 +20926,7 @@
         <v>-3.5</v>
       </c>
       <c r="H48" t="n">
-        <v>-0.5600000000000001</v>
+        <v>7.3</v>
       </c>
       <c r="I48" t="n">
         <v>-4.95</v>
@@ -20893,7 +20939,7 @@
         <v>-8.43</v>
       </c>
       <c r="M48" t="n">
-        <v>0.63</v>
+        <v>7.23</v>
       </c>
       <c r="N48" t="b">
         <v>1</v>
@@ -20931,7 +20977,7 @@
         <v>-17.9</v>
       </c>
       <c r="H49" t="n">
-        <v>2.1</v>
+        <v>3.6</v>
       </c>
       <c r="I49" t="n">
         <v>-0.5</v>
@@ -20944,7 +20990,7 @@
         <v>-3.43</v>
       </c>
       <c r="M49" t="n">
-        <v>3.29</v>
+        <v>3.53</v>
       </c>
       <c r="N49" t="b">
         <v>1</v>
@@ -20982,7 +21028,7 @@
         <v>53.5</v>
       </c>
       <c r="H50" t="n">
-        <v>20.39</v>
+        <v>26.61</v>
       </c>
       <c r="I50" t="n">
         <v>1.23</v>
@@ -20995,7 +21041,7 @@
         <v>-7.57</v>
       </c>
       <c r="M50" t="n">
-        <v>21.47</v>
+        <v>26.43</v>
       </c>
       <c r="N50" t="b">
         <v>1</v>
@@ -21033,7 +21079,7 @@
         <v>-1</v>
       </c>
       <c r="H51" t="n">
-        <v>-14.06</v>
+        <v>-16.05</v>
       </c>
       <c r="I51" t="n">
         <v>-6.26</v>
@@ -21046,7 +21092,7 @@
         <v>-15</v>
       </c>
       <c r="M51" t="n">
-        <v>-12.98</v>
+        <v>-16.23</v>
       </c>
       <c r="N51" t="b">
         <v>1</v>
@@ -21084,7 +21130,7 @@
         <v>29.7</v>
       </c>
       <c r="H52" t="n">
-        <v>10.21</v>
+        <v>10.36</v>
       </c>
       <c r="I52" t="n">
         <v>11.27</v>
@@ -21097,7 +21143,7 @@
         <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>11.29</v>
+        <v>10.18</v>
       </c>
       <c r="N52" t="b">
         <v>1</v>
@@ -21135,7 +21181,7 @@
         <v>15.2</v>
       </c>
       <c r="H53" t="n">
-        <v>-26.24</v>
+        <v>-24.45</v>
       </c>
       <c r="I53" t="n">
         <v>-8.77</v>
@@ -21148,7 +21194,7 @@
         <v>-24.79</v>
       </c>
       <c r="M53" t="n">
-        <v>-24.43</v>
+        <v>-23.9</v>
       </c>
       <c r="N53" t="b">
         <v>1</v>
@@ -21186,7 +21232,7 @@
         <v>22.2</v>
       </c>
       <c r="H54" t="n">
-        <v>12.28</v>
+        <v>14.04</v>
       </c>
       <c r="I54" t="n">
         <v>1.01</v>
@@ -21199,7 +21245,7 @@
         <v>-3.94</v>
       </c>
       <c r="M54" t="n">
-        <v>14.08</v>
+        <v>14.59</v>
       </c>
       <c r="N54" t="b">
         <v>1</v>
@@ -21241,7 +21287,7 @@
         <v>-0</v>
       </c>
       <c r="H55" t="n">
-        <v>53.84</v>
+        <v>49.27</v>
       </c>
       <c r="I55" t="n">
         <v>13.5</v>
@@ -21249,12 +21295,14 @@
       <c r="J55" t="n">
         <v>36.05</v>
       </c>
-      <c r="K55" t="inlineStr"/>
+      <c r="K55" t="n">
+        <v>49.27</v>
+      </c>
       <c r="L55" t="n">
         <v>-2.53</v>
       </c>
       <c r="M55" t="n">
-        <v>52.18</v>
+        <v>46.32</v>
       </c>
       <c r="N55" t="b">
         <v>1</v>
@@ -21292,7 +21340,7 @@
         <v>10.5</v>
       </c>
       <c r="H56" t="n">
-        <v>24.23</v>
+        <v>19.24</v>
       </c>
       <c r="I56" t="n">
         <v>1.99</v>
@@ -21300,12 +21348,14 @@
       <c r="J56" t="n">
         <v>12.33</v>
       </c>
-      <c r="K56" t="inlineStr"/>
+      <c r="K56" t="n">
+        <v>19.24</v>
+      </c>
       <c r="L56" t="n">
         <v>-6.27</v>
       </c>
       <c r="M56" t="n">
-        <v>22.57</v>
+        <v>16.29</v>
       </c>
       <c r="N56" t="b">
         <v>1</v>
@@ -21343,7 +21393,7 @@
         <v>-37</v>
       </c>
       <c r="H57" t="n">
-        <v>59.38</v>
+        <v>58.66</v>
       </c>
       <c r="I57" t="n">
         <v>18.38</v>
@@ -21351,12 +21401,14 @@
       <c r="J57" t="n">
         <v>27.59</v>
       </c>
-      <c r="K57" t="inlineStr"/>
+      <c r="K57" t="n">
+        <v>57.9</v>
+      </c>
       <c r="L57" t="n">
         <v>-5.11</v>
       </c>
       <c r="M57" t="n">
-        <v>57.07</v>
+        <v>55.05</v>
       </c>
       <c r="N57" t="b">
         <v>1</v>
@@ -21394,7 +21446,7 @@
         <v>-26.8</v>
       </c>
       <c r="H58" t="n">
-        <v>19.91</v>
+        <v>15.81</v>
       </c>
       <c r="I58" t="n">
         <v>4.56</v>
@@ -21402,12 +21454,14 @@
       <c r="J58" t="n">
         <v>-1</v>
       </c>
-      <c r="K58" t="inlineStr"/>
+      <c r="K58" t="n">
+        <v>15.15</v>
+      </c>
       <c r="L58" t="n">
         <v>-4.09</v>
       </c>
       <c r="M58" t="n">
-        <v>17.6</v>
+        <v>12.2</v>
       </c>
       <c r="N58" t="b">
         <v>1</v>
@@ -21445,7 +21499,7 @@
         <v>-36.5</v>
       </c>
       <c r="H59" t="n">
-        <v>-30.37</v>
+        <v>-31.98</v>
       </c>
       <c r="I59" t="n">
         <v>-27.75</v>
@@ -21460,7 +21514,7 @@
         <v>-31.28</v>
       </c>
       <c r="M59" t="n">
-        <v>-33.33</v>
+        <v>-36.25</v>
       </c>
       <c r="N59" t="b">
         <v>1</v>
@@ -21498,7 +21552,7 @@
         <v>-38.7</v>
       </c>
       <c r="H60" t="n">
-        <v>30.31</v>
+        <v>22.97</v>
       </c>
       <c r="I60" t="n">
         <v>17.17</v>
@@ -21513,7 +21567,7 @@
         <v>-0.54</v>
       </c>
       <c r="M60" t="n">
-        <v>27.35</v>
+        <v>18.7</v>
       </c>
       <c r="N60" t="b">
         <v>1</v>
@@ -21551,7 +21605,7 @@
         <v>-34.6</v>
       </c>
       <c r="H61" t="n">
-        <v>24.35</v>
+        <v>20.6</v>
       </c>
       <c r="I61" t="n">
         <v>6.67</v>
@@ -21566,7 +21620,7 @@
         <v>-3.06</v>
       </c>
       <c r="M61" t="n">
-        <v>21.39</v>
+        <v>16.32</v>
       </c>
       <c r="N61" t="b">
         <v>1</v>
@@ -21604,7 +21658,7 @@
         <v>-11.8</v>
       </c>
       <c r="H62" t="n">
-        <v>9.15</v>
+        <v>6.29</v>
       </c>
       <c r="I62" t="n">
         <v>9.76</v>
@@ -21619,7 +21673,7 @@
         <v>-1.63</v>
       </c>
       <c r="M62" t="n">
-        <v>6.08</v>
+        <v>1.91</v>
       </c>
       <c r="N62" t="b">
         <v>1</v>
@@ -21657,7 +21711,7 @@
         <v>0.1</v>
       </c>
       <c r="H63" t="n">
-        <v>0.65</v>
+        <v>-2.34</v>
       </c>
       <c r="I63" t="n">
         <v>-2.83</v>
@@ -21672,7 +21726,7 @@
         <v>-5.45</v>
       </c>
       <c r="M63" t="n">
-        <v>-2.41</v>
+        <v>-6.72</v>
       </c>
       <c r="N63" t="b">
         <v>1</v>
@@ -21710,7 +21764,7 @@
         <v>24.1</v>
       </c>
       <c r="H64" t="n">
-        <v>2.68</v>
+        <v>3.42</v>
       </c>
       <c r="I64" t="n">
         <v>-8.31</v>
@@ -21725,7 +21779,7 @@
         <v>-18.31</v>
       </c>
       <c r="M64" t="n">
-        <v>0.4</v>
+        <v>-0.16</v>
       </c>
       <c r="N64" t="b">
         <v>1</v>
@@ -21763,7 +21817,7 @@
         <v>-15.9</v>
       </c>
       <c r="H65" t="n">
-        <v>24.45</v>
+        <v>23.26</v>
       </c>
       <c r="I65" t="n">
         <v>10.45</v>
@@ -21778,7 +21832,7 @@
         <v>-0.31</v>
       </c>
       <c r="M65" t="n">
-        <v>22.18</v>
+        <v>19.68</v>
       </c>
       <c r="N65" t="b">
         <v>1</v>
@@ -21816,7 +21870,7 @@
         <v>-21.8</v>
       </c>
       <c r="H66" t="n">
-        <v>-37.18</v>
+        <v>-36.56</v>
       </c>
       <c r="I66" t="n">
         <v>-18.97</v>
@@ -21831,7 +21885,7 @@
         <v>-26.82</v>
       </c>
       <c r="M66" t="n">
-        <v>-40.22</v>
+        <v>-40.91</v>
       </c>
       <c r="N66" t="b">
         <v>1</v>
@@ -21869,7 +21923,7 @@
         <v>57</v>
       </c>
       <c r="H67" t="n">
-        <v>30.98</v>
+        <v>22.96</v>
       </c>
       <c r="I67" t="n">
         <v>-11.21</v>
@@ -21884,7 +21938,7 @@
         <v>-13.87</v>
       </c>
       <c r="M67" t="n">
-        <v>28.94</v>
+        <v>19.62</v>
       </c>
       <c r="N67" t="b">
         <v>1</v>
@@ -21922,7 +21976,7 @@
         <v>-21.8</v>
       </c>
       <c r="H68" t="n">
-        <v>29.43</v>
+        <v>25.6</v>
       </c>
       <c r="I68" t="n">
         <v>1.71</v>
@@ -21937,7 +21991,7 @@
         <v>-6.18</v>
       </c>
       <c r="M68" t="n">
-        <v>27.38</v>
+        <v>22.26</v>
       </c>
       <c r="N68" t="b">
         <v>1</v>
@@ -21975,7 +22029,7 @@
         <v>1</v>
       </c>
       <c r="H69" t="n">
-        <v>-36.46</v>
+        <v>-35.92</v>
       </c>
       <c r="I69" t="n">
         <v>-11.52</v>
@@ -21990,7 +22044,7 @@
         <v>-16.26</v>
       </c>
       <c r="M69" t="n">
-        <v>-38.55</v>
+        <v>-39.31</v>
       </c>
       <c r="N69" t="b">
         <v>1</v>
@@ -22028,7 +22082,7 @@
         <v>32.3</v>
       </c>
       <c r="H70" t="n">
-        <v>-48.02</v>
+        <v>-46.23</v>
       </c>
       <c r="I70" t="n">
         <v>-20.76</v>
@@ -22043,7 +22097,7 @@
         <v>-27.91</v>
       </c>
       <c r="M70" t="n">
-        <v>-50.1</v>
+        <v>-49.62</v>
       </c>
       <c r="N70" t="b">
         <v>1</v>
@@ -22081,7 +22135,7 @@
         <v>3.7</v>
       </c>
       <c r="H71" t="n">
-        <v>-14.79</v>
+        <v>-14.15</v>
       </c>
       <c r="I71" t="n">
         <v>-1.11</v>
@@ -22096,7 +22150,7 @@
         <v>-25.46</v>
       </c>
       <c r="M71" t="n">
-        <v>-16.88</v>
+        <v>-17.53</v>
       </c>
       <c r="N71" t="b">
         <v>1</v>
@@ -22134,7 +22188,7 @@
         <v>42.4</v>
       </c>
       <c r="H72" t="n">
-        <v>-26.11</v>
+        <v>-15.67</v>
       </c>
       <c r="I72" t="n">
         <v>2.16</v>
@@ -22149,7 +22203,7 @@
         <v>-15.76</v>
       </c>
       <c r="M72" t="n">
-        <v>-28.2</v>
+        <v>-19.06</v>
       </c>
       <c r="N72" t="b">
         <v>1</v>
@@ -22187,7 +22241,7 @@
         <v>28.2</v>
       </c>
       <c r="H73" t="n">
-        <v>-25.77</v>
+        <v>-18.82</v>
       </c>
       <c r="I73" t="n">
         <v>-1.71</v>
@@ -22202,7 +22256,7 @@
         <v>-23.43</v>
       </c>
       <c r="M73" t="n">
-        <v>-27.85</v>
+        <v>-22.21</v>
       </c>
       <c r="N73" t="b">
         <v>1</v>
@@ -22240,7 +22294,7 @@
         <v>28.6</v>
       </c>
       <c r="H74" t="n">
-        <v>-20.08</v>
+        <v>-3.76</v>
       </c>
       <c r="I74" t="n">
         <v>2.81</v>
@@ -22255,7 +22309,7 @@
         <v>-18.87</v>
       </c>
       <c r="M74" t="n">
-        <v>-22.17</v>
+        <v>-7.15</v>
       </c>
       <c r="N74" t="b">
         <v>1</v>
@@ -22293,7 +22347,7 @@
         <v>21.8</v>
       </c>
       <c r="H75" t="n">
-        <v>-43.5</v>
+        <v>-38.79</v>
       </c>
       <c r="I75" t="n">
         <v>-6.34</v>
@@ -22308,7 +22362,7 @@
         <v>-30.04</v>
       </c>
       <c r="M75" t="n">
-        <v>-45.58</v>
+        <v>-42.18</v>
       </c>
       <c r="N75" t="b">
         <v>1</v>
@@ -22346,7 +22400,7 @@
         <v>24.1</v>
       </c>
       <c r="H76" t="n">
-        <v>-22.33</v>
+        <v>-17.15</v>
       </c>
       <c r="I76" t="n">
         <v>-1.6</v>
@@ -22361,7 +22415,7 @@
         <v>-22.54</v>
       </c>
       <c r="M76" t="n">
-        <v>-24.42</v>
+        <v>-20.54</v>
       </c>
       <c r="N76" t="b">
         <v>1</v>
@@ -22399,7 +22453,7 @@
         <v>24.5</v>
       </c>
       <c r="H77" t="n">
-        <v>-36.08</v>
+        <v>-31.01</v>
       </c>
       <c r="I77" t="n">
         <v>-12.99</v>
@@ -22414,7 +22468,7 @@
         <v>-22.54</v>
       </c>
       <c r="M77" t="n">
-        <v>-38.17</v>
+        <v>-34.39</v>
       </c>
       <c r="N77" t="b">
         <v>1</v>
@@ -22452,7 +22506,7 @@
         <v>-8.699999999999999</v>
       </c>
       <c r="H78" t="n">
-        <v>-9.74</v>
+        <v>-12.26</v>
       </c>
       <c r="I78" t="n">
         <v>17.25</v>
@@ -22467,7 +22521,7 @@
         <v>-4.65</v>
       </c>
       <c r="M78" t="n">
-        <v>-11.83</v>
+        <v>-15.65</v>
       </c>
       <c r="N78" t="b">
         <v>1</v>
@@ -22505,7 +22559,7 @@
         <v>37.2</v>
       </c>
       <c r="H79" t="n">
-        <v>-43.35</v>
+        <v>-38.85</v>
       </c>
       <c r="I79" t="n">
         <v>-7.64</v>
@@ -22520,7 +22574,7 @@
         <v>-26.24</v>
       </c>
       <c r="M79" t="n">
-        <v>-45.44</v>
+        <v>-42.24</v>
       </c>
       <c r="N79" t="b">
         <v>1</v>
@@ -22558,7 +22612,7 @@
         <v>29.8</v>
       </c>
       <c r="H80" t="n">
-        <v>-0.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I80" t="n">
         <v>-2.74</v>
@@ -22573,7 +22627,7 @@
         <v>-22.36</v>
       </c>
       <c r="M80" t="n">
-        <v>-2.69</v>
+        <v>5.31</v>
       </c>
       <c r="N80" t="b">
         <v>1</v>
@@ -22611,7 +22665,7 @@
         <v>19.3</v>
       </c>
       <c r="H81" t="n">
-        <v>-41.29</v>
+        <v>-40.33</v>
       </c>
       <c r="I81" t="n">
         <v>-16.69</v>
@@ -22626,7 +22680,7 @@
         <v>-36.39</v>
       </c>
       <c r="M81" t="n">
-        <v>-43.37</v>
+        <v>-43.72</v>
       </c>
       <c r="N81" t="b">
         <v>1</v>
@@ -22664,7 +22718,7 @@
         <v>11.8</v>
       </c>
       <c r="H82" t="n">
-        <v>-14.59</v>
+        <v>-7.57</v>
       </c>
       <c r="I82" t="n">
         <v>-1.19</v>
@@ -22679,7 +22733,7 @@
         <v>-17.57</v>
       </c>
       <c r="M82" t="n">
-        <v>-16.68</v>
+        <v>-10.95</v>
       </c>
       <c r="N82" t="b">
         <v>1</v>
@@ -22717,7 +22771,7 @@
         <v>27.5</v>
       </c>
       <c r="H83" t="n">
-        <v>1.85</v>
+        <v>4.89</v>
       </c>
       <c r="I83" t="n">
         <v>8.42</v>
@@ -22732,7 +22786,7 @@
         <v>-2.51</v>
       </c>
       <c r="M83" t="n">
-        <v>-0.24</v>
+        <v>1.5</v>
       </c>
       <c r="N83" t="b">
         <v>1</v>
@@ -22770,7 +22824,7 @@
         <v>-14.7</v>
       </c>
       <c r="H84" t="n">
-        <v>-17.69</v>
+        <v>-18.45</v>
       </c>
       <c r="I84" t="n">
         <v>10.3</v>
@@ -22785,7 +22839,7 @@
         <v>-2.6</v>
       </c>
       <c r="M84" t="n">
-        <v>-19.78</v>
+        <v>-21.83</v>
       </c>
       <c r="N84" t="b">
         <v>1</v>
@@ -22827,7 +22881,7 @@
         <v>-9.300000000000001</v>
       </c>
       <c r="H85" t="n">
-        <v>-22.97</v>
+        <v>-25.1</v>
       </c>
       <c r="I85" t="n">
         <v>10.42</v>
@@ -22842,7 +22896,7 @@
         <v>-21.72</v>
       </c>
       <c r="M85" t="n">
-        <v>-25.06</v>
+        <v>-28.49</v>
       </c>
       <c r="N85" t="b">
         <v>1</v>
@@ -22880,7 +22934,7 @@
         <v>5.1</v>
       </c>
       <c r="H86" t="n">
-        <v>16.54</v>
+        <v>15.31</v>
       </c>
       <c r="I86" t="n">
         <v>8.77</v>
@@ -22895,7 +22949,7 @@
         <v>-3.54</v>
       </c>
       <c r="M86" t="n">
-        <v>14.45</v>
+        <v>11.93</v>
       </c>
       <c r="N86" t="b">
         <v>1</v>
@@ -22933,7 +22987,7 @@
         <v>34.2</v>
       </c>
       <c r="H87" t="n">
-        <v>-0.36</v>
+        <v>4.34</v>
       </c>
       <c r="I87" t="n">
         <v>8.15</v>
@@ -22948,7 +23002,7 @@
         <v>-7.63</v>
       </c>
       <c r="M87" t="n">
-        <v>-2.45</v>
+        <v>0.95</v>
       </c>
       <c r="N87" t="b">
         <v>1</v>
@@ -22986,7 +23040,7 @@
         <v>42</v>
       </c>
       <c r="H88" t="n">
-        <v>-49.72</v>
+        <v>-49.05</v>
       </c>
       <c r="I88" t="n">
         <v>0.6</v>
@@ -23001,7 +23055,7 @@
         <v>-16.67</v>
       </c>
       <c r="M88" t="n">
-        <v>-51.81</v>
+        <v>-52.44</v>
       </c>
       <c r="N88" t="b">
         <v>1</v>
@@ -23039,7 +23093,7 @@
         <v>-7.7</v>
       </c>
       <c r="H89" t="n">
-        <v>-20.33</v>
+        <v>-17.29</v>
       </c>
       <c r="I89" t="n">
         <v>-6.47</v>
@@ -23054,7 +23108,7 @@
         <v>-23.05</v>
       </c>
       <c r="M89" t="n">
-        <v>-22.41</v>
+        <v>-20.68</v>
       </c>
       <c r="N89" t="b">
         <v>1</v>
@@ -23092,7 +23146,7 @@
         <v>29.4</v>
       </c>
       <c r="H90" t="n">
-        <v>-32.73</v>
+        <v>-27.48</v>
       </c>
       <c r="I90" t="n">
         <v>-2.62</v>
@@ -23107,7 +23161,7 @@
         <v>-27.18</v>
       </c>
       <c r="M90" t="n">
-        <v>-34.81</v>
+        <v>-30.87</v>
       </c>
       <c r="N90" t="b">
         <v>1</v>
@@ -23145,7 +23199,7 @@
         <v>13.7</v>
       </c>
       <c r="H91" t="n">
-        <v>-4.39</v>
+        <v>6.68</v>
       </c>
       <c r="I91" t="n">
         <v>2.74</v>
@@ -23160,7 +23214,7 @@
         <v>-24.02</v>
       </c>
       <c r="M91" t="n">
-        <v>-6.48</v>
+        <v>3.29</v>
       </c>
       <c r="N91" t="b">
         <v>1</v>
@@ -23198,7 +23252,7 @@
         <v>21.8</v>
       </c>
       <c r="H92" t="n">
-        <v>-33.54</v>
+        <v>-29.23</v>
       </c>
       <c r="I92" t="n">
         <v>18.32</v>
@@ -23213,7 +23267,7 @@
         <v>-23.27</v>
       </c>
       <c r="M92" t="n">
-        <v>-35.63</v>
+        <v>-32.61</v>
       </c>
       <c r="N92" t="b">
         <v>1</v>
@@ -23251,7 +23305,7 @@
         <v>-3.7</v>
       </c>
       <c r="H93" t="n">
-        <v>-30.55</v>
+        <v>-27.35</v>
       </c>
       <c r="I93" t="n">
         <v>-8.07</v>
@@ -23266,7 +23320,7 @@
         <v>-22.12</v>
       </c>
       <c r="M93" t="n">
-        <v>-32.63</v>
+        <v>-30.74</v>
       </c>
       <c r="N93" t="b">
         <v>1</v>
@@ -23304,7 +23358,7 @@
         <v>-21.4</v>
       </c>
       <c r="H94" t="n">
-        <v>-5.89</v>
+        <v>-0.66</v>
       </c>
       <c r="I94" t="n">
         <v>4.55</v>
@@ -23319,7 +23373,7 @@
         <v>-6.39</v>
       </c>
       <c r="M94" t="n">
-        <v>-7.98</v>
+        <v>-4.05</v>
       </c>
       <c r="N94" t="b">
         <v>1</v>
@@ -23357,7 +23411,7 @@
         <v>21.3</v>
       </c>
       <c r="H95" t="n">
-        <v>1.55</v>
+        <v>1.77</v>
       </c>
       <c r="I95" t="n">
         <v>0.23</v>
@@ -23372,7 +23426,7 @@
         <v>-0.85</v>
       </c>
       <c r="M95" t="n">
-        <v>-0.53</v>
+        <v>-1.62</v>
       </c>
       <c r="N95" t="b">
         <v>1</v>
@@ -23410,7 +23464,7 @@
         <v>16.3</v>
       </c>
       <c r="H96" t="n">
-        <v>-25.69</v>
+        <v>-19.11</v>
       </c>
       <c r="I96" t="n">
         <v>-1</v>
@@ -23425,7 +23479,7 @@
         <v>-22.5</v>
       </c>
       <c r="M96" t="n">
-        <v>-27.78</v>
+        <v>-22.5</v>
       </c>
       <c r="N96" t="b">
         <v>1</v>
@@ -23463,7 +23517,7 @@
         <v>0.2</v>
       </c>
       <c r="H97" t="n">
-        <v>29.98</v>
+        <v>31.16</v>
       </c>
       <c r="I97" t="n">
         <v>4.35</v>
@@ -23478,7 +23532,7 @@
         <v>-2.79</v>
       </c>
       <c r="M97" t="n">
-        <v>27.9</v>
+        <v>27.77</v>
       </c>
       <c r="N97" t="b">
         <v>1</v>
@@ -23516,7 +23570,7 @@
         <v>-7.3</v>
       </c>
       <c r="H98" t="n">
-        <v>-23.16</v>
+        <v>-22.63</v>
       </c>
       <c r="I98" t="n">
         <v>-4.12</v>
@@ -23531,7 +23585,7 @@
         <v>-15.02</v>
       </c>
       <c r="M98" t="n">
-        <v>-25.25</v>
+        <v>-26.01</v>
       </c>
       <c r="N98" t="b">
         <v>1</v>
@@ -23569,7 +23623,7 @@
         <v>8.4</v>
       </c>
       <c r="H99" t="n">
-        <v>-45.97</v>
+        <v>-44.67</v>
       </c>
       <c r="I99" t="n">
         <v>-0.13</v>
@@ -23584,7 +23638,7 @@
         <v>-10.87</v>
       </c>
       <c r="M99" t="n">
-        <v>-48.05</v>
+        <v>-48.06</v>
       </c>
       <c r="N99" t="b">
         <v>1</v>
@@ -23622,7 +23676,7 @@
         <v>17.9</v>
       </c>
       <c r="H100" t="n">
-        <v>-14.74</v>
+        <v>-7.07</v>
       </c>
       <c r="I100" t="n">
         <v>12.97</v>
@@ -23637,7 +23691,7 @@
         <v>-8.130000000000001</v>
       </c>
       <c r="M100" t="n">
-        <v>-16.82</v>
+        <v>-10.45</v>
       </c>
       <c r="N100" t="b">
         <v>1</v>
@@ -23675,7 +23729,7 @@
         <v>14.8</v>
       </c>
       <c r="H101" t="n">
-        <v>-12.28</v>
+        <v>-11.05</v>
       </c>
       <c r="I101" t="n">
         <v>0.35</v>
@@ -23690,7 +23744,7 @@
         <v>-3.68</v>
       </c>
       <c r="M101" t="n">
-        <v>-14.37</v>
+        <v>-14.44</v>
       </c>
       <c r="N101" t="b">
         <v>1</v>
@@ -23728,7 +23782,7 @@
         <v>25.5</v>
       </c>
       <c r="H102" t="n">
-        <v>16.2</v>
+        <v>18.38</v>
       </c>
       <c r="I102" t="n">
         <v>-9.369999999999999</v>
@@ -23743,7 +23797,7 @@
         <v>-22.11</v>
       </c>
       <c r="M102" t="n">
-        <v>14.11</v>
+        <v>14.99</v>
       </c>
       <c r="N102" t="b">
         <v>1</v>
@@ -23785,7 +23839,7 @@
         <v>-7.5</v>
       </c>
       <c r="H103" t="n">
-        <v>-30.04</v>
+        <v>-29.95</v>
       </c>
       <c r="I103" t="n">
         <v>4.46</v>
@@ -23800,7 +23854,7 @@
         <v>-8.52</v>
       </c>
       <c r="M103" t="n">
-        <v>-32.13</v>
+        <v>-33.34</v>
       </c>
       <c r="N103" t="b">
         <v>1</v>
@@ -23838,7 +23892,7 @@
         <v>32.2</v>
       </c>
       <c r="H104" t="n">
-        <v>1.78</v>
+        <v>7.4</v>
       </c>
       <c r="I104" t="n">
         <v>6.49</v>
@@ -23853,7 +23907,7 @@
         <v>-3.92</v>
       </c>
       <c r="M104" t="n">
-        <v>-0.31</v>
+        <v>4.02</v>
       </c>
       <c r="N104" t="b">
         <v>1</v>
@@ -23891,7 +23945,7 @@
         <v>-11.4</v>
       </c>
       <c r="H105" t="n">
-        <v>-15.85</v>
+        <v>-13.75</v>
       </c>
       <c r="I105" t="n">
         <v>4.36</v>
@@ -23906,7 +23960,7 @@
         <v>-11.36</v>
       </c>
       <c r="M105" t="n">
-        <v>-17.94</v>
+        <v>-17.14</v>
       </c>
       <c r="N105" t="b">
         <v>1</v>
@@ -23944,7 +23998,7 @@
         <v>27.1</v>
       </c>
       <c r="H106" t="n">
-        <v>-26.8</v>
+        <v>-21.22</v>
       </c>
       <c r="I106" t="n">
         <v>5.02</v>
@@ -23959,7 +24013,7 @@
         <v>-14.35</v>
       </c>
       <c r="M106" t="n">
-        <v>-28.88</v>
+        <v>-24.61</v>
       </c>
       <c r="N106" t="b">
         <v>1</v>
@@ -23997,7 +24051,7 @@
         <v>-11</v>
       </c>
       <c r="H107" t="n">
-        <v>30.52</v>
+        <v>16.81</v>
       </c>
       <c r="I107" t="n">
         <v>10.7</v>
@@ -24012,7 +24066,7 @@
         <v>-9.43</v>
       </c>
       <c r="M107" t="n">
-        <v>28.43</v>
+        <v>13.42</v>
       </c>
       <c r="N107" t="b">
         <v>1</v>
@@ -24050,7 +24104,7 @@
         <v>3.2</v>
       </c>
       <c r="H108" t="n">
-        <v>-35.36</v>
+        <v>-28.81</v>
       </c>
       <c r="I108" t="n">
         <v>-10.41</v>
@@ -24065,7 +24119,7 @@
         <v>-23.7</v>
       </c>
       <c r="M108" t="n">
-        <v>-37.45</v>
+        <v>-32.19</v>
       </c>
       <c r="N108" t="b">
         <v>1</v>
@@ -24103,7 +24157,7 @@
         <v>-0.3</v>
       </c>
       <c r="H109" t="n">
-        <v>-25.25</v>
+        <v>-19.63</v>
       </c>
       <c r="I109" t="n">
         <v>17.76</v>
@@ -24118,7 +24172,7 @@
         <v>-14.18</v>
       </c>
       <c r="M109" t="n">
-        <v>-27.33</v>
+        <v>-23.02</v>
       </c>
       <c r="N109" t="b">
         <v>1</v>
@@ -24156,7 +24210,7 @@
         <v>10.4</v>
       </c>
       <c r="H110" t="n">
-        <v>27.45</v>
+        <v>31.35</v>
       </c>
       <c r="I110" t="n">
         <v>11.05</v>
@@ -24171,7 +24225,7 @@
         <v>-5.54</v>
       </c>
       <c r="M110" t="n">
-        <v>25.36</v>
+        <v>27.96</v>
       </c>
       <c r="N110" t="b">
         <v>1</v>
@@ -24209,7 +24263,7 @@
         <v>34.6</v>
       </c>
       <c r="H111" t="n">
-        <v>-17.15</v>
+        <v>-12.26</v>
       </c>
       <c r="I111" t="n">
         <v>5.7</v>
@@ -24224,7 +24278,7 @@
         <v>-7.7</v>
       </c>
       <c r="M111" t="n">
-        <v>-19.23</v>
+        <v>-15.65</v>
       </c>
       <c r="N111" t="b">
         <v>1</v>
@@ -24262,7 +24316,7 @@
         <v>-21.5</v>
       </c>
       <c r="H112" t="n">
-        <v>0.6899999999999999</v>
+        <v>-1.19</v>
       </c>
       <c r="I112" t="n">
         <v>10.65</v>
@@ -24277,7 +24331,7 @@
         <v>-6.89</v>
       </c>
       <c r="M112" t="n">
-        <v>-1.4</v>
+        <v>-4.58</v>
       </c>
       <c r="N112" t="b">
         <v>1</v>
@@ -24315,7 +24369,7 @@
         <v>3.5</v>
       </c>
       <c r="H113" t="n">
-        <v>68.11</v>
+        <v>66.55</v>
       </c>
       <c r="I113" t="n">
         <v>33.01</v>
@@ -24330,7 +24384,7 @@
         <v>-0.92</v>
       </c>
       <c r="M113" t="n">
-        <v>66.02</v>
+        <v>63.17</v>
       </c>
       <c r="N113" t="b">
         <v>1</v>
@@ -24368,7 +24422,7 @@
         <v>-16.2</v>
       </c>
       <c r="H114" t="n">
-        <v>2.84</v>
+        <v>6.13</v>
       </c>
       <c r="I114" t="n">
         <v>25.77</v>
@@ -24383,7 +24437,7 @@
         <v>-1.7</v>
       </c>
       <c r="M114" t="n">
-        <v>0.75</v>
+        <v>2.74</v>
       </c>
       <c r="N114" t="b">
         <v>1</v>
@@ -24421,7 +24475,7 @@
         <v>-34.6</v>
       </c>
       <c r="H115" t="n">
-        <v>24.24</v>
+        <v>19.19</v>
       </c>
       <c r="I115" t="n">
         <v>23.65</v>
@@ -24436,7 +24490,7 @@
         <v>-3.83</v>
       </c>
       <c r="M115" t="n">
-        <v>22.16</v>
+        <v>15.8</v>
       </c>
       <c r="N115" t="b">
         <v>1</v>
@@ -24474,7 +24528,7 @@
         <v>-24.9</v>
       </c>
       <c r="H116" t="n">
-        <v>-8</v>
+        <v>-2.8</v>
       </c>
       <c r="I116" t="n">
         <v>10.88</v>
@@ -24489,7 +24543,7 @@
         <v>-4.1</v>
       </c>
       <c r="M116" t="n">
-        <v>-10.09</v>
+        <v>-6.19</v>
       </c>
       <c r="N116" t="b">
         <v>1</v>
@@ -24531,7 +24585,7 @@
         <v>-8.1</v>
       </c>
       <c r="H117" t="n">
-        <v>20.62</v>
+        <v>15.36</v>
       </c>
       <c r="I117" t="n">
         <v>14.27</v>
@@ -24546,7 +24600,7 @@
         <v>-10.92</v>
       </c>
       <c r="M117" t="n">
-        <v>18.53</v>
+        <v>11.97</v>
       </c>
       <c r="N117" t="b">
         <v>1</v>
@@ -24584,7 +24638,7 @@
         <v>-6</v>
       </c>
       <c r="H118" t="n">
-        <v>-38.73</v>
+        <v>-33.23</v>
       </c>
       <c r="I118" t="n">
         <v>3.31</v>
@@ -24599,7 +24653,7 @@
         <v>-21.48</v>
       </c>
       <c r="M118" t="n">
-        <v>-40.82</v>
+        <v>-36.62</v>
       </c>
       <c r="N118" t="b">
         <v>1</v>
@@ -24637,7 +24691,7 @@
         <v>-10.2</v>
       </c>
       <c r="H119" t="n">
-        <v>-9.359999999999999</v>
+        <v>-8.32</v>
       </c>
       <c r="I119" t="n">
         <v>15.03</v>
@@ -24652,7 +24706,7 @@
         <v>-1.61</v>
       </c>
       <c r="M119" t="n">
-        <v>-11.45</v>
+        <v>-11.71</v>
       </c>
       <c r="N119" t="b">
         <v>1</v>
@@ -24690,7 +24744,7 @@
         <v>-30.5</v>
       </c>
       <c r="H120" t="n">
-        <v>-0.77</v>
+        <v>-2.41</v>
       </c>
       <c r="I120" t="n">
         <v>2.96</v>
@@ -24705,7 +24759,7 @@
         <v>-17.88</v>
       </c>
       <c r="M120" t="n">
-        <v>-2.85</v>
+        <v>-5.79</v>
       </c>
       <c r="N120" t="b">
         <v>1</v>
@@ -24743,7 +24797,7 @@
         <v>25.7</v>
       </c>
       <c r="H121" t="n">
-        <v>-13.43</v>
+        <v>-9.27</v>
       </c>
       <c r="I121" t="n">
         <v>11.3</v>
@@ -24758,7 +24812,7 @@
         <v>-11.03</v>
       </c>
       <c r="M121" t="n">
-        <v>-15.52</v>
+        <v>-12.66</v>
       </c>
       <c r="N121" t="b">
         <v>1</v>
@@ -24796,7 +24850,7 @@
         <v>40.7</v>
       </c>
       <c r="H122" t="n">
-        <v>29.41</v>
+        <v>25.83</v>
       </c>
       <c r="I122" t="n">
         <v>-4.08</v>
@@ -24811,7 +24865,7 @@
         <v>-11.2</v>
       </c>
       <c r="M122" t="n">
-        <v>27.32</v>
+        <v>22.45</v>
       </c>
       <c r="N122" t="b">
         <v>1</v>
@@ -24849,7 +24903,7 @@
         <v>68.90000000000001</v>
       </c>
       <c r="H123" t="n">
-        <v>18.16</v>
+        <v>14.22</v>
       </c>
       <c r="I123" t="n">
         <v>1.84</v>
@@ -24864,7 +24918,7 @@
         <v>-10.43</v>
       </c>
       <c r="M123" t="n">
-        <v>16.08</v>
+        <v>10.84</v>
       </c>
       <c r="N123" t="b">
         <v>1</v>
@@ -24902,7 +24956,7 @@
         <v>-40.8</v>
       </c>
       <c r="H124" t="n">
-        <v>-23.32</v>
+        <v>-25.2</v>
       </c>
       <c r="I124" t="n">
         <v>21.71</v>
@@ -24917,7 +24971,7 @@
         <v>-3.3</v>
       </c>
       <c r="M124" t="n">
-        <v>-25.41</v>
+        <v>-28.59</v>
       </c>
       <c r="N124" t="b">
         <v>1</v>

--- a/STS_holy_grail_v2.xlsx
+++ b/STS_holy_grail_v2.xlsx
@@ -476,7 +476,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.04</v>
+        <v>1.27</v>
       </c>
     </row>
     <row r="5">
@@ -486,7 +486,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-1.56</v>
+        <v>-0.9399999999999999</v>
       </c>
     </row>
     <row r="6">
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>47.5</v>
+        <v>49.6</v>
       </c>
     </row>
     <row r="8">
@@ -543,13 +543,13 @@
         <v>65</v>
       </c>
       <c r="C10" t="n">
-        <v>1.89</v>
+        <v>2.37</v>
       </c>
       <c r="D10" t="n">
-        <v>53.85</v>
+        <v>58.46</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.4</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="11">
@@ -562,13 +562,13 @@
         <v>79</v>
       </c>
       <c r="C11" t="n">
-        <v>-3.03</v>
+        <v>-3.69</v>
       </c>
       <c r="D11" t="n">
         <v>32.91</v>
       </c>
       <c r="E11" t="n">
-        <v>-6.42</v>
+        <v>-6.69</v>
       </c>
     </row>
     <row r="12">
@@ -581,13 +581,13 @@
         <v>156</v>
       </c>
       <c r="C12" t="n">
-        <v>0.86</v>
+        <v>1.52</v>
       </c>
       <c r="D12" t="n">
-        <v>45.51</v>
+        <v>48.72</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.71</v>
+        <v>-0.66</v>
       </c>
     </row>
     <row r="13">
@@ -600,13 +600,13 @@
         <v>35</v>
       </c>
       <c r="C13" t="n">
-        <v>9.44</v>
+        <v>9.31</v>
       </c>
       <c r="D13" t="n">
-        <v>77.14</v>
+        <v>74.29000000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>7.9</v>
+        <v>8.15</v>
       </c>
     </row>
     <row r="15">
@@ -653,13 +653,13 @@
         <v>111</v>
       </c>
       <c r="C17" t="n">
-        <v>1.97</v>
+        <v>2.82</v>
       </c>
       <c r="D17" t="n">
-        <v>46.85</v>
+        <v>49.55</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.67</v>
+        <v>0.57</v>
       </c>
     </row>
     <row r="18">
@@ -672,13 +672,13 @@
         <v>49</v>
       </c>
       <c r="C18" t="n">
-        <v>-1.64</v>
+        <v>-1.31</v>
       </c>
       <c r="D18" t="n">
-        <v>42.86</v>
+        <v>48.98</v>
       </c>
       <c r="E18" t="n">
-        <v>-3.79</v>
+        <v>-3.07</v>
       </c>
     </row>
     <row r="19">
@@ -691,13 +691,13 @@
         <v>45</v>
       </c>
       <c r="C19" t="n">
-        <v>2.84</v>
+        <v>3.37</v>
       </c>
       <c r="D19" t="n">
-        <v>48.89</v>
+        <v>53.33</v>
       </c>
       <c r="E19" t="n">
-        <v>0.18</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="20">
@@ -710,13 +710,13 @@
         <v>41</v>
       </c>
       <c r="C20" t="n">
-        <v>-7.43</v>
+        <v>-6.43</v>
       </c>
       <c r="D20" t="n">
-        <v>31.71</v>
+        <v>34.15</v>
       </c>
       <c r="E20" t="n">
-        <v>-10.01</v>
+        <v>-8.619999999999999</v>
       </c>
     </row>
     <row r="21">
@@ -729,13 +729,13 @@
         <v>89</v>
       </c>
       <c r="C21" t="n">
-        <v>4.34</v>
+        <v>3.23</v>
       </c>
       <c r="D21" t="n">
-        <v>57.3</v>
+        <v>55.06</v>
       </c>
       <c r="E21" t="n">
-        <v>1.56</v>
+        <v>0.84</v>
       </c>
     </row>
     <row r="23">
@@ -782,13 +782,13 @@
         <v>10</v>
       </c>
       <c r="C25" t="n">
-        <v>10.68</v>
+        <v>10.15</v>
       </c>
       <c r="D25" t="n">
         <v>70</v>
       </c>
       <c r="E25" t="n">
-        <v>7.44</v>
+        <v>7.31</v>
       </c>
     </row>
     <row r="26">
@@ -801,13 +801,13 @@
         <v>5</v>
       </c>
       <c r="C26" t="n">
-        <v>-6.02</v>
+        <v>-5.1</v>
       </c>
       <c r="D26" t="n">
         <v>40</v>
       </c>
       <c r="E26" t="n">
-        <v>-9.960000000000001</v>
+        <v>-8.65</v>
       </c>
     </row>
     <row r="27">
@@ -820,13 +820,13 @@
         <v>3</v>
       </c>
       <c r="C27" t="n">
-        <v>18.9</v>
+        <v>19.29</v>
       </c>
       <c r="D27" t="n">
         <v>66.67</v>
       </c>
       <c r="E27" t="n">
-        <v>16</v>
+        <v>16.78</v>
       </c>
     </row>
     <row r="29">
@@ -873,13 +873,13 @@
         <v>212</v>
       </c>
       <c r="C31" t="n">
-        <v>1.97</v>
+        <v>2.04</v>
       </c>
       <c r="D31" t="n">
-        <v>45.75</v>
+        <v>48.58</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.7</v>
+        <v>-0.24</v>
       </c>
     </row>
     <row r="32">
@@ -892,13 +892,13 @@
         <v>123</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.57</v>
+        <v>-0.06</v>
       </c>
       <c r="D32" t="n">
-        <v>50.41</v>
+        <v>51.22</v>
       </c>
       <c r="E32" t="n">
-        <v>-3.05</v>
+        <v>-2.15</v>
       </c>
     </row>
   </sheetData>
@@ -1022,7 +1022,7 @@
         <v>-3.2</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.85</v>
+        <v>0.85</v>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
@@ -1031,7 +1031,7 @@
         <v>-1.55</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.97</v>
+        <v>1.12</v>
       </c>
       <c r="N2" t="b">
         <v>0</v>
@@ -1069,7 +1069,7 @@
         <v>15.5</v>
       </c>
       <c r="H3" t="n">
-        <v>0.12</v>
+        <v>0.15</v>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
@@ -1078,7 +1078,7 @@
         <v>-0.07000000000000001</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.51</v>
+        <v>-1.09</v>
       </c>
       <c r="N3" t="b">
         <v>0</v>
@@ -1116,7 +1116,7 @@
         <v>-9.4</v>
       </c>
       <c r="H4" t="n">
-        <v>0.58</v>
+        <v>1.81</v>
       </c>
       <c r="I4" t="n">
         <v>0.58</v>
@@ -1127,7 +1127,7 @@
         <v>-1.66</v>
       </c>
       <c r="M4" t="n">
-        <v>0.91</v>
+        <v>2.52</v>
       </c>
       <c r="N4" t="b">
         <v>0</v>
@@ -1165,7 +1165,7 @@
         <v>51.4</v>
       </c>
       <c r="H5" t="n">
-        <v>-3.37</v>
+        <v>-6.18</v>
       </c>
       <c r="I5" t="n">
         <v>-1.92</v>
@@ -1176,7 +1176,7 @@
         <v>-7.85</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.72</v>
+        <v>-5.16</v>
       </c>
       <c r="N5" t="b">
         <v>1</v>
@@ -1214,7 +1214,7 @@
         <v>-24.3</v>
       </c>
       <c r="H6" t="n">
-        <v>-8.49</v>
+        <v>-3.26</v>
       </c>
       <c r="I6" t="n">
         <v>-1.01</v>
@@ -1222,10 +1222,10 @@
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="n">
-        <v>-8.720000000000001</v>
+        <v>-10.37</v>
       </c>
       <c r="M6" t="n">
-        <v>-8.16</v>
+        <v>-2.55</v>
       </c>
       <c r="N6" t="b">
         <v>0</v>
@@ -1263,7 +1263,7 @@
         <v>-22.1</v>
       </c>
       <c r="H7" t="n">
-        <v>-9.800000000000001</v>
+        <v>-9.27</v>
       </c>
       <c r="I7" t="n">
         <v>-12.2</v>
@@ -1274,7 +1274,7 @@
         <v>-15.53</v>
       </c>
       <c r="M7" t="n">
-        <v>-9.470000000000001</v>
+        <v>-8.56</v>
       </c>
       <c r="N7" t="b">
         <v>0</v>
@@ -1312,7 +1312,7 @@
         <v>-5</v>
       </c>
       <c r="H8" t="n">
-        <v>6.82</v>
+        <v>8.16</v>
       </c>
       <c r="I8" t="n">
         <v>12.26</v>
@@ -1323,7 +1323,7 @@
         <v>-1.75</v>
       </c>
       <c r="M8" t="n">
-        <v>7.26</v>
+        <v>8.99</v>
       </c>
       <c r="N8" t="b">
         <v>1</v>
@@ -1361,7 +1361,7 @@
         <v>-16.6</v>
       </c>
       <c r="H9" t="n">
-        <v>-5.65</v>
+        <v>-1.25</v>
       </c>
       <c r="I9" t="n">
         <v>-0.75</v>
@@ -1372,7 +1372,7 @@
         <v>-7.55</v>
       </c>
       <c r="M9" t="n">
-        <v>-5.2</v>
+        <v>-0.43</v>
       </c>
       <c r="N9" t="b">
         <v>1</v>
@@ -1410,7 +1410,7 @@
         <v>-7.4</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.97</v>
+        <v>1.39</v>
       </c>
       <c r="I10" t="n">
         <v>-2.38</v>
@@ -1421,7 +1421,7 @@
         <v>-6.15</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.52</v>
+        <v>2.22</v>
       </c>
       <c r="N10" t="b">
         <v>0</v>
@@ -1459,7 +1459,7 @@
         <v>-1.1</v>
       </c>
       <c r="H11" t="n">
-        <v>7.74</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="I11" t="n">
         <v>10.88</v>
@@ -1470,7 +1470,7 @@
         <v>-0.36</v>
       </c>
       <c r="M11" t="n">
-        <v>8.19</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="N11" t="b">
         <v>0</v>
@@ -1508,7 +1508,7 @@
         <v>12.5</v>
       </c>
       <c r="H12" t="n">
-        <v>7.39</v>
+        <v>7.59</v>
       </c>
       <c r="I12" t="n">
         <v>7.44</v>
@@ -1519,7 +1519,7 @@
         <v>-2.59</v>
       </c>
       <c r="M12" t="n">
-        <v>7.84</v>
+        <v>8.42</v>
       </c>
       <c r="N12" t="b">
         <v>1</v>
@@ -1557,7 +1557,7 @@
         <v>-17.3</v>
       </c>
       <c r="H13" t="n">
-        <v>5.27</v>
+        <v>7.42</v>
       </c>
       <c r="I13" t="n">
         <v>1.16</v>
@@ -1568,7 +1568,7 @@
         <v>-6.51</v>
       </c>
       <c r="M13" t="n">
-        <v>6.02</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="N13" t="b">
         <v>1</v>
@@ -1606,7 +1606,7 @@
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>4.37</v>
+        <v>4.81</v>
       </c>
       <c r="I14" t="n">
         <v>9.16</v>
@@ -1617,7 +1617,7 @@
         <v>-1.46</v>
       </c>
       <c r="M14" t="n">
-        <v>5.12</v>
+        <v>5.94</v>
       </c>
       <c r="N14" t="b">
         <v>0</v>
@@ -1655,7 +1655,7 @@
         <v>-29.3</v>
       </c>
       <c r="H15" t="n">
-        <v>9.85</v>
+        <v>13.6</v>
       </c>
       <c r="I15" t="n">
         <v>10.02</v>
@@ -1666,7 +1666,7 @@
         <v>-3.13</v>
       </c>
       <c r="M15" t="n">
-        <v>9.51</v>
+        <v>13.64</v>
       </c>
       <c r="N15" t="b">
         <v>0</v>
@@ -1704,7 +1704,7 @@
         <v>-21.8</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.03</v>
+        <v>-0.53</v>
       </c>
       <c r="I16" t="n">
         <v>-3.37</v>
@@ -1717,7 +1717,7 @@
         <v>-5.33</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.8</v>
+        <v>-0.91</v>
       </c>
       <c r="N16" t="b">
         <v>1</v>
@@ -1755,7 +1755,7 @@
         <v>-15</v>
       </c>
       <c r="H17" t="n">
-        <v>14.86</v>
+        <v>33.02</v>
       </c>
       <c r="I17" t="n">
         <v>12.31</v>
@@ -1768,7 +1768,7 @@
         <v>-4.06</v>
       </c>
       <c r="M17" t="n">
-        <v>14.14</v>
+        <v>32.69</v>
       </c>
       <c r="N17" t="b">
         <v>0</v>
@@ -1806,7 +1806,7 @@
         <v>-16.7</v>
       </c>
       <c r="H18" t="n">
-        <v>14.63</v>
+        <v>16.13</v>
       </c>
       <c r="I18" t="n">
         <v>26.03</v>
@@ -1819,7 +1819,7 @@
         <v>-6.98</v>
       </c>
       <c r="M18" t="n">
-        <v>13.91</v>
+        <v>15.8</v>
       </c>
       <c r="N18" t="b">
         <v>1</v>
@@ -1857,7 +1857,7 @@
         <v>-26.8</v>
       </c>
       <c r="H19" t="n">
-        <v>6.29</v>
+        <v>20.58</v>
       </c>
       <c r="I19" t="n">
         <v>1.39</v>
@@ -1870,7 +1870,7 @@
         <v>-5.1</v>
       </c>
       <c r="M19" t="n">
-        <v>5.57</v>
+        <v>20.25</v>
       </c>
       <c r="N19" t="b">
         <v>0</v>
@@ -1908,7 +1908,7 @@
         <v>-35.9</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.38</v>
+        <v>-2.5</v>
       </c>
       <c r="I20" t="n">
         <v>-6.92</v>
@@ -1921,7 +1921,7 @@
         <v>-7.58</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.1</v>
+        <v>-2.83</v>
       </c>
       <c r="N20" t="b">
         <v>0</v>
@@ -1959,7 +1959,7 @@
         <v>-7.1</v>
       </c>
       <c r="H21" t="n">
-        <v>-2.44</v>
+        <v>-3.2</v>
       </c>
       <c r="I21" t="n">
         <v>9.390000000000001</v>
@@ -1972,7 +1972,7 @@
         <v>-8.41</v>
       </c>
       <c r="M21" t="n">
-        <v>-3.16</v>
+        <v>-3.53</v>
       </c>
       <c r="N21" t="b">
         <v>0</v>
@@ -2010,7 +2010,7 @@
         <v>-11.5</v>
       </c>
       <c r="H22" t="n">
-        <v>10.54</v>
+        <v>13.83</v>
       </c>
       <c r="I22" t="n">
         <v>7.47</v>
@@ -2023,7 +2023,7 @@
         <v>-0.99</v>
       </c>
       <c r="M22" t="n">
-        <v>9.82</v>
+        <v>13.5</v>
       </c>
       <c r="N22" t="b">
         <v>1</v>
@@ -2061,7 +2061,7 @@
         <v>0.1</v>
       </c>
       <c r="H23" t="n">
-        <v>22.95</v>
+        <v>27.02</v>
       </c>
       <c r="I23" t="n">
         <v>6.41</v>
@@ -2074,7 +2074,7 @@
         <v>-2.51</v>
       </c>
       <c r="M23" t="n">
-        <v>22.49</v>
+        <v>26.94</v>
       </c>
       <c r="N23" t="b">
         <v>1</v>
@@ -2112,7 +2112,7 @@
         <v>-31.6</v>
       </c>
       <c r="H24" t="n">
-        <v>3.82</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="I24" t="n">
         <v>-2.12</v>
@@ -2125,7 +2125,7 @@
         <v>-8.140000000000001</v>
       </c>
       <c r="M24" t="n">
-        <v>3.37</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="N24" t="b">
         <v>1</v>
@@ -2163,7 +2163,7 @@
         <v>7.6</v>
       </c>
       <c r="H25" t="n">
-        <v>11.72</v>
+        <v>11.21</v>
       </c>
       <c r="I25" t="n">
         <v>-3.6</v>
@@ -2176,7 +2176,7 @@
         <v>-9.359999999999999</v>
       </c>
       <c r="M25" t="n">
-        <v>10.64</v>
+        <v>10.52</v>
       </c>
       <c r="N25" t="b">
         <v>0</v>
@@ -2214,7 +2214,7 @@
         <v>-17.9</v>
       </c>
       <c r="H26" t="n">
-        <v>-5.7</v>
+        <v>-2.05</v>
       </c>
       <c r="I26" t="n">
         <v>-6.13</v>
@@ -2227,7 +2227,7 @@
         <v>-14.51</v>
       </c>
       <c r="M26" t="n">
-        <v>-5.48</v>
+        <v>-1.45</v>
       </c>
       <c r="N26" t="b">
         <v>0</v>
@@ -2265,7 +2265,7 @@
         <v>-25.3</v>
       </c>
       <c r="H27" t="n">
-        <v>9.59</v>
+        <v>11.31</v>
       </c>
       <c r="I27" t="n">
         <v>4.1</v>
@@ -2278,7 +2278,7 @@
         <v>-0.92</v>
       </c>
       <c r="M27" t="n">
-        <v>9.81</v>
+        <v>11.91</v>
       </c>
       <c r="N27" t="b">
         <v>0</v>
@@ -2316,7 +2316,7 @@
         <v>25.6</v>
       </c>
       <c r="H28" t="n">
-        <v>3.34</v>
+        <v>5.76</v>
       </c>
       <c r="I28" t="n">
         <v>-0.42</v>
@@ -2329,7 +2329,7 @@
         <v>-8.35</v>
       </c>
       <c r="M28" t="n">
-        <v>3.57</v>
+        <v>6.37</v>
       </c>
       <c r="N28" t="b">
         <v>0</v>
@@ -2367,7 +2367,7 @@
         <v>-2.7</v>
       </c>
       <c r="H29" t="n">
-        <v>-6.19</v>
+        <v>-1.62</v>
       </c>
       <c r="I29" t="n">
         <v>-3.77</v>
@@ -2380,7 +2380,7 @@
         <v>-12.44</v>
       </c>
       <c r="M29" t="n">
-        <v>-5.97</v>
+        <v>-1.01</v>
       </c>
       <c r="N29" t="b">
         <v>1</v>
@@ -2418,7 +2418,7 @@
         <v>26.9</v>
       </c>
       <c r="H30" t="n">
-        <v>2.2</v>
+        <v>4.38</v>
       </c>
       <c r="I30" t="n">
         <v>-3.24</v>
@@ -2431,7 +2431,7 @@
         <v>-12.88</v>
       </c>
       <c r="M30" t="n">
-        <v>2.42</v>
+        <v>4.99</v>
       </c>
       <c r="N30" t="b">
         <v>1</v>
@@ -2469,7 +2469,7 @@
         <v>-14.5</v>
       </c>
       <c r="H31" t="n">
-        <v>-12.3</v>
+        <v>-13.53</v>
       </c>
       <c r="I31" t="n">
         <v>-3.75</v>
@@ -2482,7 +2482,7 @@
         <v>-9.01</v>
       </c>
       <c r="M31" t="n">
-        <v>-13.09</v>
+        <v>-13.94</v>
       </c>
       <c r="N31" t="b">
         <v>0</v>
@@ -2520,7 +2520,7 @@
         <v>17.2</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.31</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="I32" t="n">
         <v>-1.49</v>
@@ -2533,7 +2533,7 @@
         <v>-10.54</v>
       </c>
       <c r="M32" t="n">
-        <v>-1.1</v>
+        <v>-0.47</v>
       </c>
       <c r="N32" t="b">
         <v>0</v>
@@ -2571,7 +2571,7 @@
         <v>-13.2</v>
       </c>
       <c r="H33" t="n">
-        <v>19.85</v>
+        <v>19.96</v>
       </c>
       <c r="I33" t="n">
         <v>23.71</v>
@@ -2584,7 +2584,7 @@
         <v>-0.82</v>
       </c>
       <c r="M33" t="n">
-        <v>19.06</v>
+        <v>19.55</v>
       </c>
       <c r="N33" t="b">
         <v>0</v>
@@ -2622,7 +2622,7 @@
         <v>-7.7</v>
       </c>
       <c r="H34" t="n">
-        <v>-2.82</v>
+        <v>1.55</v>
       </c>
       <c r="I34" t="n">
         <v>-9.67</v>
@@ -2635,7 +2635,7 @@
         <v>-12.32</v>
       </c>
       <c r="M34" t="n">
-        <v>-3.61</v>
+        <v>1.14</v>
       </c>
       <c r="N34" t="b">
         <v>0</v>
@@ -2673,7 +2673,7 @@
         <v>-18.1</v>
       </c>
       <c r="H35" t="n">
-        <v>-2.97</v>
+        <v>-0.7</v>
       </c>
       <c r="I35" t="n">
         <v>-2.43</v>
@@ -2686,7 +2686,7 @@
         <v>-6.41</v>
       </c>
       <c r="M35" t="n">
-        <v>-3.77</v>
+        <v>-1.11</v>
       </c>
       <c r="N35" t="b">
         <v>0</v>
@@ -2724,7 +2724,7 @@
         <v>-21.5</v>
       </c>
       <c r="H36" t="n">
-        <v>4.71</v>
+        <v>8.48</v>
       </c>
       <c r="I36" t="n">
         <v>-1.68</v>
@@ -2737,7 +2737,7 @@
         <v>-8.130000000000001</v>
       </c>
       <c r="M36" t="n">
-        <v>3.92</v>
+        <v>8.08</v>
       </c>
       <c r="N36" t="b">
         <v>1</v>
@@ -2775,7 +2775,7 @@
         <v>7.7</v>
       </c>
       <c r="H37" t="n">
-        <v>-1.35</v>
+        <v>1.23</v>
       </c>
       <c r="I37" t="n">
         <v>-6.85</v>
@@ -2788,7 +2788,7 @@
         <v>-9.359999999999999</v>
       </c>
       <c r="M37" t="n">
-        <v>-2.14</v>
+        <v>0.83</v>
       </c>
       <c r="N37" t="b">
         <v>0</v>
@@ -2826,7 +2826,7 @@
         <v>-18.1</v>
       </c>
       <c r="H38" t="n">
-        <v>13.37</v>
+        <v>14.68</v>
       </c>
       <c r="I38" t="n">
         <v>4.46</v>
@@ -2839,7 +2839,7 @@
         <v>-2.69</v>
       </c>
       <c r="M38" t="n">
-        <v>12.58</v>
+        <v>14.27</v>
       </c>
       <c r="N38" t="b">
         <v>1</v>
@@ -2877,7 +2877,7 @@
         <v>32.1</v>
       </c>
       <c r="H39" t="n">
-        <v>13.36</v>
+        <v>13.88</v>
       </c>
       <c r="I39" t="n">
         <v>-3.47</v>
@@ -2890,7 +2890,7 @@
         <v>-6.94</v>
       </c>
       <c r="M39" t="n">
-        <v>11.91</v>
+        <v>12.83</v>
       </c>
       <c r="N39" t="b">
         <v>1</v>
@@ -2928,7 +2928,7 @@
         <v>41.6</v>
       </c>
       <c r="H40" t="n">
-        <v>12.9</v>
+        <v>13.21</v>
       </c>
       <c r="I40" t="n">
         <v>3.43</v>
@@ -2941,7 +2941,7 @@
         <v>-4.38</v>
       </c>
       <c r="M40" t="n">
-        <v>11.46</v>
+        <v>12.15</v>
       </c>
       <c r="N40" t="b">
         <v>1</v>
@@ -2979,7 +2979,7 @@
         <v>-14.4</v>
       </c>
       <c r="H41" t="n">
-        <v>6.66</v>
+        <v>11.72</v>
       </c>
       <c r="I41" t="n">
         <v>-2.38</v>
@@ -2992,7 +2992,7 @@
         <v>-6.46</v>
       </c>
       <c r="M41" t="n">
-        <v>5.21</v>
+        <v>10.66</v>
       </c>
       <c r="N41" t="b">
         <v>1</v>
@@ -3030,7 +3030,7 @@
         <v>-16.8</v>
       </c>
       <c r="H42" t="n">
-        <v>7.34</v>
+        <v>9.92</v>
       </c>
       <c r="I42" t="n">
         <v>1.99</v>
@@ -3043,7 +3043,7 @@
         <v>-7.67</v>
       </c>
       <c r="M42" t="n">
-        <v>5.89</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="N42" t="b">
         <v>0</v>
@@ -3081,7 +3081,7 @@
         <v>6.4</v>
       </c>
       <c r="H43" t="n">
-        <v>15.58</v>
+        <v>16.72</v>
       </c>
       <c r="I43" t="n">
         <v>1.48</v>
@@ -3094,7 +3094,7 @@
         <v>-3.35</v>
       </c>
       <c r="M43" t="n">
-        <v>14.14</v>
+        <v>15.66</v>
       </c>
       <c r="N43" t="b">
         <v>1</v>
@@ -3132,7 +3132,7 @@
         <v>-10</v>
       </c>
       <c r="H44" t="n">
-        <v>-10.45</v>
+        <v>3.59</v>
       </c>
       <c r="I44" t="n">
         <v>-3.29</v>
@@ -3145,7 +3145,7 @@
         <v>-14.66</v>
       </c>
       <c r="M44" t="n">
-        <v>-11.89</v>
+        <v>2.54</v>
       </c>
       <c r="N44" t="b">
         <v>1</v>
@@ -3183,7 +3183,7 @@
         <v>-11</v>
       </c>
       <c r="H45" t="n">
-        <v>48.65</v>
+        <v>48.52</v>
       </c>
       <c r="I45" t="n">
         <v>11.67</v>
@@ -3196,7 +3196,7 @@
         <v>-0.97</v>
       </c>
       <c r="M45" t="n">
-        <v>47.2</v>
+        <v>47.46</v>
       </c>
       <c r="N45" t="b">
         <v>0</v>
@@ -3234,7 +3234,7 @@
         <v>-23.9</v>
       </c>
       <c r="H46" t="n">
-        <v>-5.44</v>
+        <v>-5.47</v>
       </c>
       <c r="I46" t="n">
         <v>-4.98</v>
@@ -3247,7 +3247,7 @@
         <v>-7.87</v>
       </c>
       <c r="M46" t="n">
-        <v>-6.89</v>
+        <v>-6.53</v>
       </c>
       <c r="N46" t="b">
         <v>0</v>
@@ -3285,7 +3285,7 @@
         <v>-36.1</v>
       </c>
       <c r="H47" t="n">
-        <v>8.23</v>
+        <v>12.96</v>
       </c>
       <c r="I47" t="n">
         <v>-1.4</v>
@@ -3298,7 +3298,7 @@
         <v>-7.04</v>
       </c>
       <c r="M47" t="n">
-        <v>6.78</v>
+        <v>11.9</v>
       </c>
       <c r="N47" t="b">
         <v>0</v>
@@ -3336,7 +3336,7 @@
         <v>-7.9</v>
       </c>
       <c r="H48" t="n">
-        <v>-3.68</v>
+        <v>-1.76</v>
       </c>
       <c r="I48" t="n">
         <v>-8.83</v>
@@ -3349,7 +3349,7 @@
         <v>-12.99</v>
       </c>
       <c r="M48" t="n">
-        <v>-5.13</v>
+        <v>-2.83</v>
       </c>
       <c r="N48" t="b">
         <v>0</v>
@@ -3391,7 +3391,7 @@
         <v>-9.800000000000001</v>
       </c>
       <c r="H49" t="n">
-        <v>10.8</v>
+        <v>10.5</v>
       </c>
       <c r="I49" t="n">
         <v>-3.41</v>
@@ -3404,7 +3404,7 @@
         <v>-8.949999999999999</v>
       </c>
       <c r="M49" t="n">
-        <v>9.35</v>
+        <v>9.44</v>
       </c>
       <c r="N49" t="b">
         <v>0</v>
@@ -3442,7 +3442,7 @@
         <v>2.6</v>
       </c>
       <c r="H50" t="n">
-        <v>6.52</v>
+        <v>0.35</v>
       </c>
       <c r="I50" t="n">
         <v>-7.8</v>
@@ -3455,7 +3455,7 @@
         <v>-12.2</v>
       </c>
       <c r="M50" t="n">
-        <v>4.58</v>
+        <v>-1.2</v>
       </c>
       <c r="N50" t="b">
         <v>0</v>
@@ -3493,7 +3493,7 @@
         <v>6.3</v>
       </c>
       <c r="H51" t="n">
-        <v>18.12</v>
+        <v>20.54</v>
       </c>
       <c r="I51" t="n">
         <v>0.64</v>
@@ -3506,7 +3506,7 @@
         <v>-2.13</v>
       </c>
       <c r="M51" t="n">
-        <v>16.18</v>
+        <v>18.99</v>
       </c>
       <c r="N51" t="b">
         <v>0</v>
@@ -3544,7 +3544,7 @@
         <v>20.2</v>
       </c>
       <c r="H52" t="n">
-        <v>-0.14</v>
+        <v>-8.17</v>
       </c>
       <c r="I52" t="n">
         <v>3.45</v>
@@ -3557,7 +3557,7 @@
         <v>-1.07</v>
       </c>
       <c r="M52" t="n">
-        <v>-1.99</v>
+        <v>-9.630000000000001</v>
       </c>
       <c r="N52" t="b">
         <v>1</v>
@@ -3595,7 +3595,7 @@
         <v>43.7</v>
       </c>
       <c r="H53" t="n">
-        <v>20.24</v>
+        <v>21.31</v>
       </c>
       <c r="I53" t="n">
         <v>3.16</v>
@@ -3608,7 +3608,7 @@
         <v>-2.44</v>
       </c>
       <c r="M53" t="n">
-        <v>18.39</v>
+        <v>19.84</v>
       </c>
       <c r="N53" t="b">
         <v>1</v>
@@ -3646,7 +3646,7 @@
         <v>1.9</v>
       </c>
       <c r="H54" t="n">
-        <v>7.01</v>
+        <v>7.97</v>
       </c>
       <c r="I54" t="n">
         <v>-10.64</v>
@@ -3659,7 +3659,7 @@
         <v>-14.75</v>
       </c>
       <c r="M54" t="n">
-        <v>5.16</v>
+        <v>6.51</v>
       </c>
       <c r="N54" t="b">
         <v>1</v>
@@ -3697,7 +3697,7 @@
         <v>37.5</v>
       </c>
       <c r="H55" t="n">
-        <v>34.39</v>
+        <v>35.16</v>
       </c>
       <c r="I55" t="n">
         <v>5.86</v>
@@ -3710,7 +3710,7 @@
         <v>-3.95</v>
       </c>
       <c r="M55" t="n">
-        <v>32.39</v>
+        <v>33.54</v>
       </c>
       <c r="N55" t="b">
         <v>1</v>
@@ -3748,7 +3748,7 @@
         <v>15</v>
       </c>
       <c r="H56" t="n">
-        <v>-27.44</v>
+        <v>-27.1</v>
       </c>
       <c r="I56" t="n">
         <v>-21.11</v>
@@ -3761,7 +3761,7 @@
         <v>-28.65</v>
       </c>
       <c r="M56" t="n">
-        <v>-29.45</v>
+        <v>-28.72</v>
       </c>
       <c r="N56" t="b">
         <v>0</v>
@@ -3799,7 +3799,7 @@
         <v>40.2</v>
       </c>
       <c r="H57" t="n">
-        <v>10.6</v>
+        <v>11.97</v>
       </c>
       <c r="I57" t="n">
         <v>-1.11</v>
@@ -3812,7 +3812,7 @@
         <v>-5.29</v>
       </c>
       <c r="M57" t="n">
-        <v>8.59</v>
+        <v>10.36</v>
       </c>
       <c r="N57" t="b">
         <v>1</v>
@@ -3850,7 +3850,7 @@
         <v>10.7</v>
       </c>
       <c r="H58" t="n">
-        <v>-4.39</v>
+        <v>-0.17</v>
       </c>
       <c r="I58" t="n">
         <v>7.3</v>
@@ -3863,7 +3863,7 @@
         <v>-3.78</v>
       </c>
       <c r="M58" t="n">
-        <v>-6.4</v>
+        <v>-1.79</v>
       </c>
       <c r="N58" t="b">
         <v>1</v>
@@ -3901,7 +3901,7 @@
         <v>25.6</v>
       </c>
       <c r="H59" t="n">
-        <v>20.1</v>
+        <v>26.73</v>
       </c>
       <c r="I59" t="n">
         <v>7.71</v>
@@ -3914,7 +3914,7 @@
         <v>-4.85</v>
       </c>
       <c r="M59" t="n">
-        <v>18.85</v>
+        <v>25.88</v>
       </c>
       <c r="N59" t="b">
         <v>1</v>
@@ -3952,7 +3952,7 @@
         <v>6.3</v>
       </c>
       <c r="H60" t="n">
-        <v>4.37</v>
+        <v>6.05</v>
       </c>
       <c r="I60" t="n">
         <v>7.2</v>
@@ -3965,7 +3965,7 @@
         <v>-0.4</v>
       </c>
       <c r="M60" t="n">
-        <v>2.24</v>
+        <v>4.3</v>
       </c>
       <c r="N60" t="b">
         <v>0</v>
@@ -4003,7 +4003,7 @@
         <v>2.3</v>
       </c>
       <c r="H61" t="n">
-        <v>-6.04</v>
+        <v>-3.27</v>
       </c>
       <c r="I61" t="n">
         <v>-8.85</v>
@@ -4016,7 +4016,7 @@
         <v>-14.2</v>
       </c>
       <c r="M61" t="n">
-        <v>-8.18</v>
+        <v>-5.02</v>
       </c>
       <c r="N61" t="b">
         <v>0</v>
@@ -4054,7 +4054,7 @@
         <v>-4.3</v>
       </c>
       <c r="H62" t="n">
-        <v>9.01</v>
+        <v>11.05</v>
       </c>
       <c r="I62" t="n">
         <v>3.39</v>
@@ -4067,7 +4067,7 @@
         <v>-5.89</v>
       </c>
       <c r="M62" t="n">
-        <v>7.68</v>
+        <v>10.11</v>
       </c>
       <c r="N62" t="b">
         <v>0</v>
@@ -4105,7 +4105,7 @@
         <v>-6.9</v>
       </c>
       <c r="H63" t="n">
-        <v>20.36</v>
+        <v>24.62</v>
       </c>
       <c r="I63" t="n">
         <v>6.44</v>
@@ -4118,7 +4118,7 @@
         <v>-4.53</v>
       </c>
       <c r="M63" t="n">
-        <v>19.03</v>
+        <v>23.68</v>
       </c>
       <c r="N63" t="b">
         <v>1</v>
@@ -4156,7 +4156,7 @@
         <v>-29.4</v>
       </c>
       <c r="H64" t="n">
-        <v>-19</v>
+        <v>-19.18</v>
       </c>
       <c r="I64" t="n">
         <v>-5.75</v>
@@ -4169,7 +4169,7 @@
         <v>-10.11</v>
       </c>
       <c r="M64" t="n">
-        <v>-20.32</v>
+        <v>-20.12</v>
       </c>
       <c r="N64" t="b">
         <v>0</v>
@@ -4207,7 +4207,7 @@
         <v>4.2</v>
       </c>
       <c r="H65" t="n">
-        <v>-12.48</v>
+        <v>-9.83</v>
       </c>
       <c r="I65" t="n">
         <v>-10.83</v>
@@ -4220,7 +4220,7 @@
         <v>-18.5</v>
       </c>
       <c r="M65" t="n">
-        <v>-13.81</v>
+        <v>-10.77</v>
       </c>
       <c r="N65" t="b">
         <v>0</v>
@@ -4258,7 +4258,7 @@
         <v>-32.4</v>
       </c>
       <c r="H66" t="n">
-        <v>-0.8</v>
+        <v>3.45</v>
       </c>
       <c r="I66" t="n">
         <v>-2.43</v>
@@ -4271,7 +4271,7 @@
         <v>-12.47</v>
       </c>
       <c r="M66" t="n">
-        <v>-1.47</v>
+        <v>3.16</v>
       </c>
       <c r="N66" t="b">
         <v>0</v>
@@ -4309,7 +4309,7 @@
         <v>-11</v>
       </c>
       <c r="H67" t="n">
-        <v>12.69</v>
+        <v>16.51</v>
       </c>
       <c r="I67" t="n">
         <v>-8.449999999999999</v>
@@ -4322,7 +4322,7 @@
         <v>-18.92</v>
       </c>
       <c r="M67" t="n">
-        <v>12.02</v>
+        <v>16.22</v>
       </c>
       <c r="N67" t="b">
         <v>0</v>
@@ -4360,7 +4360,7 @@
         <v>-28.1</v>
       </c>
       <c r="H68" t="n">
-        <v>-12.66</v>
+        <v>-12.12</v>
       </c>
       <c r="I68" t="n">
         <v>-10.79</v>
@@ -4373,7 +4373,7 @@
         <v>-13.67</v>
       </c>
       <c r="M68" t="n">
-        <v>-13.48</v>
+        <v>-12.56</v>
       </c>
       <c r="N68" t="b">
         <v>0</v>
@@ -4411,7 +4411,7 @@
         <v>9.699999999999999</v>
       </c>
       <c r="H69" t="n">
-        <v>3.88</v>
+        <v>1.63</v>
       </c>
       <c r="I69" t="n">
         <v>1.27</v>
@@ -4424,7 +4424,7 @@
         <v>-20.79</v>
       </c>
       <c r="M69" t="n">
-        <v>3.05</v>
+        <v>1.2</v>
       </c>
       <c r="N69" t="b">
         <v>0</v>
@@ -4462,7 +4462,7 @@
         <v>-9.300000000000001</v>
       </c>
       <c r="H70" t="n">
-        <v>-15.16</v>
+        <v>-13.81</v>
       </c>
       <c r="I70" t="n">
         <v>-3.34</v>
@@ -4475,7 +4475,7 @@
         <v>-8.77</v>
       </c>
       <c r="M70" t="n">
-        <v>-15.99</v>
+        <v>-14.24</v>
       </c>
       <c r="N70" t="b">
         <v>0</v>
@@ -4513,7 +4513,7 @@
         <v>-17.7</v>
       </c>
       <c r="H71" t="n">
-        <v>6.83</v>
+        <v>7.15</v>
       </c>
       <c r="I71" t="n">
         <v>-0.89</v>
@@ -4526,7 +4526,7 @@
         <v>-11.37</v>
       </c>
       <c r="M71" t="n">
-        <v>6</v>
+        <v>6.72</v>
       </c>
       <c r="N71" t="b">
         <v>0</v>
@@ -4564,7 +4564,7 @@
         <v>0.3</v>
       </c>
       <c r="H72" t="n">
-        <v>-11.26</v>
+        <v>-8.199999999999999</v>
       </c>
       <c r="I72" t="n">
         <v>-10.53</v>
@@ -4577,7 +4577,7 @@
         <v>-17.73</v>
       </c>
       <c r="M72" t="n">
-        <v>-12.09</v>
+        <v>-8.640000000000001</v>
       </c>
       <c r="N72" t="b">
         <v>1</v>
@@ -4615,7 +4615,7 @@
         <v>12.3</v>
       </c>
       <c r="H73" t="n">
-        <v>3.65</v>
+        <v>30.12</v>
       </c>
       <c r="I73" t="n">
         <v>6.51</v>
@@ -4628,7 +4628,7 @@
         <v>-6.01</v>
       </c>
       <c r="M73" t="n">
-        <v>2.1</v>
+        <v>28.96</v>
       </c>
       <c r="N73" t="b">
         <v>0</v>
@@ -4666,7 +4666,7 @@
         <v>-1.4</v>
       </c>
       <c r="H74" t="n">
-        <v>-0.97</v>
+        <v>-1.99</v>
       </c>
       <c r="I74" t="n">
         <v>-4.52</v>
@@ -4679,7 +4679,7 @@
         <v>-7.44</v>
       </c>
       <c r="M74" t="n">
-        <v>-2.52</v>
+        <v>-3.14</v>
       </c>
       <c r="N74" t="b">
         <v>0</v>
@@ -4717,7 +4717,7 @@
         <v>2.8</v>
       </c>
       <c r="H75" t="n">
-        <v>-0.15</v>
+        <v>0.88</v>
       </c>
       <c r="I75" t="n">
         <v>3.18</v>
@@ -4730,7 +4730,7 @@
         <v>-0.88</v>
       </c>
       <c r="M75" t="n">
-        <v>-1.69</v>
+        <v>-0.28</v>
       </c>
       <c r="N75" t="b">
         <v>1</v>
@@ -4768,7 +4768,7 @@
         <v>34.5</v>
       </c>
       <c r="H76" t="n">
-        <v>11.34</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="I76" t="n">
         <v>0.66</v>
@@ -4781,7 +4781,7 @@
         <v>-2.64</v>
       </c>
       <c r="M76" t="n">
-        <v>9.789999999999999</v>
+        <v>8.06</v>
       </c>
       <c r="N76" t="b">
         <v>1</v>
@@ -4819,7 +4819,7 @@
         <v>-22.7</v>
       </c>
       <c r="H77" t="n">
-        <v>-16.25</v>
+        <v>-17.14</v>
       </c>
       <c r="I77" t="n">
         <v>-6.71</v>
@@ -4832,7 +4832,7 @@
         <v>-9.58</v>
       </c>
       <c r="M77" t="n">
-        <v>-17.85</v>
+        <v>-18.36</v>
       </c>
       <c r="N77" t="b">
         <v>0</v>
@@ -4870,7 +4870,7 @@
         <v>24.3</v>
       </c>
       <c r="H78" t="n">
-        <v>46.56</v>
+        <v>45.08</v>
       </c>
       <c r="I78" t="n">
         <v>2.54</v>
@@ -4883,7 +4883,7 @@
         <v>-5.21</v>
       </c>
       <c r="M78" t="n">
-        <v>45.66</v>
+        <v>44.56</v>
       </c>
       <c r="N78" t="b">
         <v>1</v>
@@ -4921,7 +4921,7 @@
         <v>56.6</v>
       </c>
       <c r="H79" t="n">
-        <v>8.76</v>
+        <v>5.41</v>
       </c>
       <c r="I79" t="n">
         <v>-13.1</v>
@@ -4934,7 +4934,7 @@
         <v>-16.17</v>
       </c>
       <c r="M79" t="n">
-        <v>7.86</v>
+        <v>4.89</v>
       </c>
       <c r="N79" t="b">
         <v>0</v>
@@ -4972,7 +4972,7 @@
         <v>2.9</v>
       </c>
       <c r="H80" t="n">
-        <v>-14.84</v>
+        <v>-12.29</v>
       </c>
       <c r="I80" t="n">
         <v>-8.470000000000001</v>
@@ -4985,7 +4985,7 @@
         <v>-15.65</v>
       </c>
       <c r="M80" t="n">
-        <v>-15.74</v>
+        <v>-12.81</v>
       </c>
       <c r="N80" t="b">
         <v>0</v>
@@ -5023,7 +5023,7 @@
         <v>-16.9</v>
       </c>
       <c r="H81" t="n">
-        <v>9.26</v>
+        <v>2.6</v>
       </c>
       <c r="I81" t="n">
         <v>-6.47</v>
@@ -5036,7 +5036,7 @@
         <v>-11.5</v>
       </c>
       <c r="M81" t="n">
-        <v>8.359999999999999</v>
+        <v>2.09</v>
       </c>
       <c r="N81" t="b">
         <v>1</v>
@@ -5074,7 +5074,7 @@
         <v>0.8</v>
       </c>
       <c r="H82" t="n">
-        <v>-5.66</v>
+        <v>-7.49</v>
       </c>
       <c r="I82" t="n">
         <v>-7.73</v>
@@ -5087,7 +5087,7 @@
         <v>-10.12</v>
       </c>
       <c r="M82" t="n">
-        <v>-5.98</v>
+        <v>-7.42</v>
       </c>
       <c r="N82" t="b">
         <v>0</v>
@@ -5125,7 +5125,7 @@
         <v>32.8</v>
       </c>
       <c r="H83" t="n">
-        <v>9.66</v>
+        <v>7.56</v>
       </c>
       <c r="I83" t="n">
         <v>14.96</v>
@@ -5138,7 +5138,7 @@
         <v>-0.9</v>
       </c>
       <c r="M83" t="n">
-        <v>9.34</v>
+        <v>7.62</v>
       </c>
       <c r="N83" t="b">
         <v>0</v>
@@ -5176,7 +5176,7 @@
         <v>-9.6</v>
       </c>
       <c r="H84" t="n">
-        <v>-15.9</v>
+        <v>-15.61</v>
       </c>
       <c r="I84" t="n">
         <v>-1.23</v>
@@ -5189,7 +5189,7 @@
         <v>-18.52</v>
       </c>
       <c r="M84" t="n">
-        <v>-16.22</v>
+        <v>-15.55</v>
       </c>
       <c r="N84" t="b">
         <v>0</v>
@@ -5227,7 +5227,7 @@
         <v>20.3</v>
       </c>
       <c r="H85" t="n">
-        <v>-21.04</v>
+        <v>-18.75</v>
       </c>
       <c r="I85" t="n">
         <v>-2.07</v>
@@ -5240,7 +5240,7 @@
         <v>-17.35</v>
       </c>
       <c r="M85" t="n">
-        <v>-21.78</v>
+        <v>-19.11</v>
       </c>
       <c r="N85" t="b">
         <v>1</v>
@@ -5278,7 +5278,7 @@
         <v>0.3</v>
       </c>
       <c r="H86" t="n">
-        <v>-21.65</v>
+        <v>-18.87</v>
       </c>
       <c r="I86" t="n">
         <v>-9.9</v>
@@ -5291,7 +5291,7 @@
         <v>-21.72</v>
       </c>
       <c r="M86" t="n">
-        <v>-22.9</v>
+        <v>-19.72</v>
       </c>
       <c r="N86" t="b">
         <v>1</v>
@@ -5329,7 +5329,7 @@
         <v>49.4</v>
       </c>
       <c r="H87" t="n">
-        <v>5.52</v>
+        <v>2.52</v>
       </c>
       <c r="I87" t="n">
         <v>2.9</v>
@@ -5342,7 +5342,7 @@
         <v>-5.67</v>
       </c>
       <c r="M87" t="n">
-        <v>4.46</v>
+        <v>1.86</v>
       </c>
       <c r="N87" t="b">
         <v>1</v>
@@ -5380,7 +5380,7 @@
         <v>4.5</v>
       </c>
       <c r="H88" t="n">
-        <v>-2.74</v>
+        <v>-2.09</v>
       </c>
       <c r="I88" t="n">
         <v>-7.61</v>
@@ -5393,7 +5393,7 @@
         <v>-11.06</v>
       </c>
       <c r="M88" t="n">
-        <v>-3.79</v>
+        <v>-2.76</v>
       </c>
       <c r="N88" t="b">
         <v>1</v>
@@ -5431,7 +5431,7 @@
         <v>15.4</v>
       </c>
       <c r="H89" t="n">
-        <v>2.97</v>
+        <v>3.93</v>
       </c>
       <c r="I89" t="n">
         <v>-1.19</v>
@@ -5444,7 +5444,7 @@
         <v>-7.43</v>
       </c>
       <c r="M89" t="n">
-        <v>1.91</v>
+        <v>3.26</v>
       </c>
       <c r="N89" t="b">
         <v>0</v>
@@ -5482,7 +5482,7 @@
         <v>4.2</v>
       </c>
       <c r="H90" t="n">
-        <v>-19.96</v>
+        <v>-18.19</v>
       </c>
       <c r="I90" t="n">
         <v>-6.86</v>
@@ -5495,7 +5495,7 @@
         <v>-20.23</v>
       </c>
       <c r="M90" t="n">
-        <v>-21.02</v>
+        <v>-18.85</v>
       </c>
       <c r="N90" t="b">
         <v>0</v>
@@ -5533,7 +5533,7 @@
         <v>15.5</v>
       </c>
       <c r="H91" t="n">
-        <v>-0.47</v>
+        <v>3.08</v>
       </c>
       <c r="I91" t="n">
         <v>-7.36</v>
@@ -5546,7 +5546,7 @@
         <v>-12.98</v>
       </c>
       <c r="M91" t="n">
-        <v>-1.71</v>
+        <v>2.23</v>
       </c>
       <c r="N91" t="b">
         <v>0</v>
@@ -5588,7 +5588,7 @@
         <v>-8.5</v>
       </c>
       <c r="H92" t="n">
-        <v>32.88</v>
+        <v>34.97</v>
       </c>
       <c r="I92" t="n">
         <v>-3.04</v>
@@ -5601,7 +5601,7 @@
         <v>-4.96</v>
       </c>
       <c r="M92" t="n">
-        <v>31.65</v>
+        <v>34.12</v>
       </c>
       <c r="N92" t="b">
         <v>0</v>
@@ -5639,7 +5639,7 @@
         <v>1.8</v>
       </c>
       <c r="H93" t="n">
-        <v>-9.18</v>
+        <v>-9.77</v>
       </c>
       <c r="I93" t="n">
         <v>-6.45</v>
@@ -5652,7 +5652,7 @@
         <v>-13.57</v>
       </c>
       <c r="M93" t="n">
-        <v>-10.41</v>
+        <v>-10.62</v>
       </c>
       <c r="N93" t="b">
         <v>0</v>
@@ -5690,7 +5690,7 @@
         <v>33.9</v>
       </c>
       <c r="H94" t="n">
-        <v>21.51</v>
+        <v>22.08</v>
       </c>
       <c r="I94" t="n">
         <v>-7.74</v>
@@ -5703,7 +5703,7 @@
         <v>-9.449999999999999</v>
       </c>
       <c r="M94" t="n">
-        <v>20.27</v>
+        <v>21.23</v>
       </c>
       <c r="N94" t="b">
         <v>0</v>
@@ -5741,7 +5741,7 @@
         <v>-25</v>
       </c>
       <c r="H95" t="n">
-        <v>-3.62</v>
+        <v>-1.7</v>
       </c>
       <c r="I95" t="n">
         <v>2.51</v>
@@ -5754,7 +5754,7 @@
         <v>-4.88</v>
       </c>
       <c r="M95" t="n">
-        <v>-4.69</v>
+        <v>-2.39</v>
       </c>
       <c r="N95" t="b">
         <v>0</v>
@@ -5792,7 +5792,7 @@
         <v>-12.6</v>
       </c>
       <c r="H96" t="n">
-        <v>-14.48</v>
+        <v>-12.39</v>
       </c>
       <c r="I96" t="n">
         <v>-7.89</v>
@@ -5805,7 +5805,7 @@
         <v>-21.29</v>
       </c>
       <c r="M96" t="n">
-        <v>-15.56</v>
+        <v>-13.08</v>
       </c>
       <c r="N96" t="b">
         <v>0</v>
@@ -5843,7 +5843,7 @@
         <v>2.1</v>
       </c>
       <c r="H97" t="n">
-        <v>-6.68</v>
+        <v>-4.9</v>
       </c>
       <c r="I97" t="n">
         <v>0.25</v>
@@ -5856,7 +5856,7 @@
         <v>-16.43</v>
       </c>
       <c r="M97" t="n">
-        <v>-7.76</v>
+        <v>-5.59</v>
       </c>
       <c r="N97" t="b">
         <v>1</v>
@@ -5894,7 +5894,7 @@
         <v>-17.9</v>
       </c>
       <c r="H98" t="n">
-        <v>6.42</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I98" t="n">
         <v>0.6</v>
@@ -5907,7 +5907,7 @@
         <v>-4.72</v>
       </c>
       <c r="M98" t="n">
-        <v>5.34</v>
+        <v>7.5</v>
       </c>
       <c r="N98" t="b">
         <v>1</v>
@@ -5945,7 +5945,7 @@
         <v>19.4</v>
       </c>
       <c r="H99" t="n">
-        <v>-10.91</v>
+        <v>-6.63</v>
       </c>
       <c r="I99" t="n">
         <v>-10.01</v>
@@ -5958,7 +5958,7 @@
         <v>-15.23</v>
       </c>
       <c r="M99" t="n">
-        <v>-11.41</v>
+        <v>-6.75</v>
       </c>
       <c r="N99" t="b">
         <v>1</v>
@@ -5996,7 +5996,7 @@
         <v>-20.5</v>
       </c>
       <c r="H100" t="n">
-        <v>-11.05</v>
+        <v>-13.32</v>
       </c>
       <c r="I100" t="n">
         <v>-4.62</v>
@@ -6009,7 +6009,7 @@
         <v>-9.92</v>
       </c>
       <c r="M100" t="n">
-        <v>-11.55</v>
+        <v>-13.44</v>
       </c>
       <c r="N100" t="b">
         <v>0</v>
@@ -6047,7 +6047,7 @@
         <v>-30.5</v>
       </c>
       <c r="H101" t="n">
-        <v>-2.84</v>
+        <v>-0.83</v>
       </c>
       <c r="I101" t="n">
         <v>-4.6</v>
@@ -6060,7 +6060,7 @@
         <v>-10.37</v>
       </c>
       <c r="M101" t="n">
-        <v>-3.34</v>
+        <v>-0.95</v>
       </c>
       <c r="N101" t="b">
         <v>0</v>
@@ -6098,7 +6098,7 @@
         <v>-12.3</v>
       </c>
       <c r="H102" t="n">
-        <v>-21.18</v>
+        <v>-18.87</v>
       </c>
       <c r="I102" t="n">
         <v>-4.36</v>
@@ -6111,7 +6111,7 @@
         <v>-13.26</v>
       </c>
       <c r="M102" t="n">
-        <v>-21.9</v>
+        <v>-19.2</v>
       </c>
       <c r="N102" t="b">
         <v>0</v>
@@ -6149,7 +6149,7 @@
         <v>13.7</v>
       </c>
       <c r="H103" t="n">
-        <v>-21.16</v>
+        <v>-17.89</v>
       </c>
       <c r="I103" t="n">
         <v>-12.16</v>
@@ -6162,7 +6162,7 @@
         <v>-13.02</v>
       </c>
       <c r="M103" t="n">
-        <v>-21.88</v>
+        <v>-18.22</v>
       </c>
       <c r="N103" t="b">
         <v>0</v>
@@ -6200,7 +6200,7 @@
         <v>-2.6</v>
       </c>
       <c r="H104" t="n">
-        <v>-14.09</v>
+        <v>-12.42</v>
       </c>
       <c r="I104" t="n">
         <v>-4.27</v>
@@ -6213,7 +6213,7 @@
         <v>-4.86</v>
       </c>
       <c r="M104" t="n">
-        <v>-14.81</v>
+        <v>-12.75</v>
       </c>
       <c r="N104" t="b">
         <v>1</v>
@@ -6251,7 +6251,7 @@
         <v>25.6</v>
       </c>
       <c r="H105" t="n">
-        <v>17.78</v>
+        <v>16.81</v>
       </c>
       <c r="I105" t="n">
         <v>4.26</v>
@@ -6264,7 +6264,7 @@
         <v>-10.74</v>
       </c>
       <c r="M105" t="n">
-        <v>17.06</v>
+        <v>16.47</v>
       </c>
       <c r="N105" t="b">
         <v>0</v>
@@ -6315,7 +6315,7 @@
         <v>-9.94</v>
       </c>
       <c r="M106" t="n">
-        <v>8.67</v>
+        <v>9.06</v>
       </c>
       <c r="N106" t="b">
         <v>1</v>
@@ -6353,7 +6353,7 @@
         <v>38.9</v>
       </c>
       <c r="H107" t="n">
-        <v>-10.43</v>
+        <v>-9.68</v>
       </c>
       <c r="I107" t="n">
         <v>-9.220000000000001</v>
@@ -6366,7 +6366,7 @@
         <v>-9.83</v>
       </c>
       <c r="M107" t="n">
-        <v>-10.17</v>
+        <v>-9.050000000000001</v>
       </c>
       <c r="N107" t="b">
         <v>1</v>
@@ -6404,7 +6404,7 @@
         <v>32.1</v>
       </c>
       <c r="H108" t="n">
-        <v>51.19</v>
+        <v>51.86</v>
       </c>
       <c r="I108" t="n">
         <v>11.84</v>
@@ -6417,7 +6417,7 @@
         <v>-1.82</v>
       </c>
       <c r="M108" t="n">
-        <v>51.44</v>
+        <v>52.49</v>
       </c>
       <c r="N108" t="b">
         <v>0</v>
@@ -6455,7 +6455,7 @@
         <v>53.4</v>
       </c>
       <c r="H109" t="n">
-        <v>13.29</v>
+        <v>12.15</v>
       </c>
       <c r="I109" t="n">
         <v>2.75</v>
@@ -6468,7 +6468,7 @@
         <v>-2.31</v>
       </c>
       <c r="M109" t="n">
-        <v>13.84</v>
+        <v>13.08</v>
       </c>
       <c r="N109" t="b">
         <v>0</v>
@@ -6506,7 +6506,7 @@
         <v>54.1</v>
       </c>
       <c r="H110" t="n">
-        <v>27.96</v>
+        <v>25.56</v>
       </c>
       <c r="I110" t="n">
         <v>5.54</v>
@@ -6519,7 +6519,7 @@
         <v>-0.41</v>
       </c>
       <c r="M110" t="n">
-        <v>28.04</v>
+        <v>26.03</v>
       </c>
       <c r="N110" t="b">
         <v>0</v>
@@ -6557,7 +6557,7 @@
         <v>43.2</v>
       </c>
       <c r="H111" t="n">
-        <v>-11.04</v>
+        <v>-7.54</v>
       </c>
       <c r="I111" t="n">
         <v>-3.15</v>
@@ -6570,7 +6570,7 @@
         <v>-17.51</v>
       </c>
       <c r="M111" t="n">
-        <v>-10.95</v>
+        <v>-7.07</v>
       </c>
       <c r="N111" t="b">
         <v>1</v>
@@ -6608,7 +6608,7 @@
         <v>-8.199999999999999</v>
       </c>
       <c r="H112" t="n">
-        <v>4.95</v>
+        <v>5.45</v>
       </c>
       <c r="I112" t="n">
         <v>5.34</v>
@@ -6621,7 +6621,7 @@
         <v>-5.27</v>
       </c>
       <c r="M112" t="n">
-        <v>5.03</v>
+        <v>5.91</v>
       </c>
       <c r="N112" t="b">
         <v>1</v>
@@ -6659,7 +6659,7 @@
         <v>-1.2</v>
       </c>
       <c r="H113" t="n">
-        <v>5.5</v>
+        <v>9.19</v>
       </c>
       <c r="I113" t="n">
         <v>8.27</v>
@@ -6672,7 +6672,7 @@
         <v>-5.3</v>
       </c>
       <c r="M113" t="n">
-        <v>5.54</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="N113" t="b">
         <v>0</v>
@@ -6710,7 +6710,7 @@
         <v>-23.9</v>
       </c>
       <c r="H114" t="n">
-        <v>6.9</v>
+        <v>4.38</v>
       </c>
       <c r="I114" t="n">
         <v>3.28</v>
@@ -6723,7 +6723,7 @@
         <v>-4.46</v>
       </c>
       <c r="M114" t="n">
-        <v>6.69</v>
+        <v>4.55</v>
       </c>
       <c r="N114" t="b">
         <v>1</v>
@@ -6761,7 +6761,7 @@
         <v>26.7</v>
       </c>
       <c r="H115" t="n">
-        <v>-0.74</v>
+        <v>-0.53</v>
       </c>
       <c r="I115" t="n">
         <v>-0.05</v>
@@ -6774,7 +6774,7 @@
         <v>-0.87</v>
       </c>
       <c r="M115" t="n">
-        <v>-0.95</v>
+        <v>-0.35</v>
       </c>
       <c r="N115" t="b">
         <v>1</v>
@@ -6812,7 +6812,7 @@
         <v>39.5</v>
       </c>
       <c r="H116" t="n">
-        <v>7.86</v>
+        <v>5.01</v>
       </c>
       <c r="I116" t="n">
         <v>-5.13</v>
@@ -6825,7 +6825,7 @@
         <v>-8.869999999999999</v>
       </c>
       <c r="M116" t="n">
-        <v>7.65</v>
+        <v>5.18</v>
       </c>
       <c r="N116" t="b">
         <v>0</v>
@@ -6867,7 +6867,7 @@
         <v>-6.1</v>
       </c>
       <c r="H117" t="n">
-        <v>-19.21</v>
+        <v>-19.65</v>
       </c>
       <c r="I117" t="n">
         <v>4.9</v>
@@ -6880,7 +6880,7 @@
         <v>-9</v>
       </c>
       <c r="M117" t="n">
-        <v>-19.42</v>
+        <v>-19.48</v>
       </c>
       <c r="N117" t="b">
         <v>0</v>
@@ -6918,7 +6918,7 @@
         <v>14.3</v>
       </c>
       <c r="H118" t="n">
-        <v>11.82</v>
+        <v>10.93</v>
       </c>
       <c r="I118" t="n">
         <v>-0.43</v>
@@ -6931,7 +6931,7 @@
         <v>-11.86</v>
       </c>
       <c r="M118" t="n">
-        <v>11.61</v>
+        <v>11.11</v>
       </c>
       <c r="N118" t="b">
         <v>0</v>
@@ -6969,7 +6969,7 @@
         <v>-11.3</v>
       </c>
       <c r="H119" t="n">
-        <v>-4.37</v>
+        <v>-1.97</v>
       </c>
       <c r="I119" t="n">
         <v>1.31</v>
@@ -6982,7 +6982,7 @@
         <v>-1.88</v>
       </c>
       <c r="M119" t="n">
-        <v>-4.58</v>
+        <v>-1.79</v>
       </c>
       <c r="N119" t="b">
         <v>0</v>
@@ -7020,7 +7020,7 @@
         <v>10.5</v>
       </c>
       <c r="H120" t="n">
-        <v>-23.52</v>
+        <v>-22.1</v>
       </c>
       <c r="I120" t="n">
         <v>-0.86</v>
@@ -7033,7 +7033,7 @@
         <v>-6.11</v>
       </c>
       <c r="M120" t="n">
-        <v>-23.73</v>
+        <v>-21.93</v>
       </c>
       <c r="N120" t="b">
         <v>0</v>
@@ -7071,7 +7071,7 @@
         <v>-23.5</v>
       </c>
       <c r="H121" t="n">
-        <v>-32.19</v>
+        <v>-31.12</v>
       </c>
       <c r="I121" t="n">
         <v>13.29</v>
@@ -7084,7 +7084,7 @@
         <v>-14.04</v>
       </c>
       <c r="M121" t="n">
-        <v>-32.4</v>
+        <v>-30.95</v>
       </c>
       <c r="N121" t="b">
         <v>0</v>
@@ -7122,7 +7122,7 @@
         <v>2.4</v>
       </c>
       <c r="H122" t="n">
-        <v>22.95</v>
+        <v>22.71</v>
       </c>
       <c r="I122" t="n">
         <v>12.41</v>
@@ -7135,7 +7135,7 @@
         <v>-0.07000000000000001</v>
       </c>
       <c r="M122" t="n">
-        <v>22.54</v>
+        <v>22.68</v>
       </c>
       <c r="N122" t="b">
         <v>0</v>
@@ -7173,7 +7173,7 @@
         <v>-12.8</v>
       </c>
       <c r="H123" t="n">
-        <v>3.13</v>
+        <v>1.85</v>
       </c>
       <c r="I123" t="n">
         <v>-1.74</v>
@@ -7186,7 +7186,7 @@
         <v>-2.97</v>
       </c>
       <c r="M123" t="n">
-        <v>2.71</v>
+        <v>1.82</v>
       </c>
       <c r="N123" t="b">
         <v>0</v>
@@ -7224,7 +7224,7 @@
         <v>-3.5</v>
       </c>
       <c r="H124" t="n">
-        <v>6.54</v>
+        <v>12.59</v>
       </c>
       <c r="I124" t="n">
         <v>-4.95</v>
@@ -7237,7 +7237,7 @@
         <v>-8.43</v>
       </c>
       <c r="M124" t="n">
-        <v>6.12</v>
+        <v>12.56</v>
       </c>
       <c r="N124" t="b">
         <v>1</v>
@@ -7275,7 +7275,7 @@
         <v>-17.9</v>
       </c>
       <c r="H125" t="n">
-        <v>8.08</v>
+        <v>11.93</v>
       </c>
       <c r="I125" t="n">
         <v>-0.5</v>
@@ -7288,7 +7288,7 @@
         <v>-3.43</v>
       </c>
       <c r="M125" t="n">
-        <v>7.66</v>
+        <v>11.9</v>
       </c>
       <c r="N125" t="b">
         <v>1</v>
@@ -7326,7 +7326,7 @@
         <v>11.9</v>
       </c>
       <c r="H126" t="n">
-        <v>-2.75</v>
+        <v>-2.06</v>
       </c>
       <c r="I126" t="n">
         <v>6.88</v>
@@ -7339,7 +7339,7 @@
         <v>-10.93</v>
       </c>
       <c r="M126" t="n">
-        <v>-3.27</v>
+        <v>-2.2</v>
       </c>
       <c r="N126" t="b">
         <v>0</v>
@@ -7377,7 +7377,7 @@
         <v>53.5</v>
       </c>
       <c r="H127" t="n">
-        <v>24.18</v>
+        <v>27.94</v>
       </c>
       <c r="I127" t="n">
         <v>1.23</v>
@@ -7390,7 +7390,7 @@
         <v>-7.57</v>
       </c>
       <c r="M127" t="n">
-        <v>23.66</v>
+        <v>27.8</v>
       </c>
       <c r="N127" t="b">
         <v>1</v>
@@ -7428,7 +7428,7 @@
         <v>-1</v>
       </c>
       <c r="H128" t="n">
-        <v>-15.67</v>
+        <v>-16.68</v>
       </c>
       <c r="I128" t="n">
         <v>-6.26</v>
@@ -7441,7 +7441,7 @@
         <v>-15</v>
       </c>
       <c r="M128" t="n">
-        <v>-16.19</v>
+        <v>-16.81</v>
       </c>
       <c r="N128" t="b">
         <v>1</v>
@@ -7479,7 +7479,7 @@
         <v>18.1</v>
       </c>
       <c r="H129" t="n">
-        <v>-5.24</v>
+        <v>-3.38</v>
       </c>
       <c r="I129" t="n">
         <v>-1.69</v>
@@ -7492,7 +7492,7 @@
         <v>-1.92</v>
       </c>
       <c r="M129" t="n">
-        <v>-5.76</v>
+        <v>-3.52</v>
       </c>
       <c r="N129" t="b">
         <v>0</v>
@@ -7530,7 +7530,7 @@
         <v>29.7</v>
       </c>
       <c r="H130" t="n">
-        <v>12.08</v>
+        <v>13.32</v>
       </c>
       <c r="I130" t="n">
         <v>11.27</v>
@@ -7543,7 +7543,7 @@
         <v>0</v>
       </c>
       <c r="M130" t="n">
-        <v>11.56</v>
+        <v>13.18</v>
       </c>
       <c r="N130" t="b">
         <v>1</v>
@@ -7581,7 +7581,7 @@
         <v>-2.1</v>
       </c>
       <c r="H131" t="n">
-        <v>-25.31</v>
+        <v>-26.72</v>
       </c>
       <c r="I131" t="n">
         <v>0.67</v>
@@ -7589,12 +7589,14 @@
       <c r="J131" t="n">
         <v>-0.1</v>
       </c>
-      <c r="K131" t="inlineStr"/>
+      <c r="K131" t="n">
+        <v>-26.72</v>
+      </c>
       <c r="L131" t="n">
         <v>-7.84</v>
       </c>
       <c r="M131" t="n">
-        <v>-25.1</v>
+        <v>-26.13</v>
       </c>
       <c r="N131" t="b">
         <v>0</v>
@@ -7632,7 +7634,7 @@
         <v>22.2</v>
       </c>
       <c r="H132" t="n">
-        <v>15.57</v>
+        <v>19.3</v>
       </c>
       <c r="I132" t="n">
         <v>1.01</v>
@@ -7640,12 +7642,14 @@
       <c r="J132" t="n">
         <v>-1.9</v>
       </c>
-      <c r="K132" t="inlineStr"/>
+      <c r="K132" t="n">
+        <v>19.3</v>
+      </c>
       <c r="L132" t="n">
         <v>-3.94</v>
       </c>
       <c r="M132" t="n">
-        <v>15.78</v>
+        <v>19.89</v>
       </c>
       <c r="N132" t="b">
         <v>1</v>
@@ -7683,7 +7687,7 @@
         <v>10.8</v>
       </c>
       <c r="H133" t="n">
-        <v>4.01</v>
+        <v>4.46</v>
       </c>
       <c r="I133" t="n">
         <v>5.62</v>
@@ -7691,12 +7695,14 @@
       <c r="J133" t="n">
         <v>6.38</v>
       </c>
-      <c r="K133" t="inlineStr"/>
+      <c r="K133" t="n">
+        <v>4.46</v>
+      </c>
       <c r="L133" t="n">
         <v>-1.59</v>
       </c>
       <c r="M133" t="n">
-        <v>4.22</v>
+        <v>5.05</v>
       </c>
       <c r="N133" t="b">
         <v>0</v>
@@ -7734,7 +7740,7 @@
         <v>15.2</v>
       </c>
       <c r="H134" t="n">
-        <v>-22.14</v>
+        <v>-19.07</v>
       </c>
       <c r="I134" t="n">
         <v>-8.77</v>
@@ -7742,12 +7748,14 @@
       <c r="J134" t="n">
         <v>-20.73</v>
       </c>
-      <c r="K134" t="inlineStr"/>
+      <c r="K134" t="n">
+        <v>-19.07</v>
+      </c>
       <c r="L134" t="n">
         <v>-24.79</v>
       </c>
       <c r="M134" t="n">
-        <v>-21.93</v>
+        <v>-18.47</v>
       </c>
       <c r="N134" t="b">
         <v>1</v>
@@ -7785,7 +7793,7 @@
         <v>16.7</v>
       </c>
       <c r="H135" t="n">
-        <v>-24.17</v>
+        <v>-22.97</v>
       </c>
       <c r="I135" t="n">
         <v>-15.31</v>
@@ -7800,7 +7808,7 @@
         <v>-22</v>
       </c>
       <c r="M135" t="n">
-        <v>-25.96</v>
+        <v>-24.36</v>
       </c>
       <c r="N135" t="b">
         <v>0</v>
@@ -7838,7 +7846,7 @@
         <v>0.3</v>
       </c>
       <c r="H136" t="n">
-        <v>48.15</v>
+        <v>44.5</v>
       </c>
       <c r="I136" t="n">
         <v>6.01</v>
@@ -7853,7 +7861,7 @@
         <v>-3.85</v>
       </c>
       <c r="M136" t="n">
-        <v>44.84</v>
+        <v>41.58</v>
       </c>
       <c r="N136" t="b">
         <v>0</v>
@@ -7895,7 +7903,7 @@
         <v>-0</v>
       </c>
       <c r="H137" t="n">
-        <v>51.35</v>
+        <v>47.79</v>
       </c>
       <c r="I137" t="n">
         <v>13.5</v>
@@ -7910,7 +7918,7 @@
         <v>-2.53</v>
       </c>
       <c r="M137" t="n">
-        <v>48.04</v>
+        <v>44.88</v>
       </c>
       <c r="N137" t="b">
         <v>1</v>
@@ -7948,7 +7956,7 @@
         <v>30.4</v>
       </c>
       <c r="H138" t="n">
-        <v>6.5</v>
+        <v>7.19</v>
       </c>
       <c r="I138" t="n">
         <v>8.539999999999999</v>
@@ -7963,7 +7971,7 @@
         <v>-0.44</v>
       </c>
       <c r="M138" t="n">
-        <v>3.19</v>
+        <v>4.27</v>
       </c>
       <c r="N138" t="b">
         <v>0</v>
@@ -8001,7 +8009,7 @@
         <v>10.5</v>
       </c>
       <c r="H139" t="n">
-        <v>18.14</v>
+        <v>18.07</v>
       </c>
       <c r="I139" t="n">
         <v>1.99</v>
@@ -8016,7 +8024,7 @@
         <v>-6.27</v>
       </c>
       <c r="M139" t="n">
-        <v>14.83</v>
+        <v>15.15</v>
       </c>
       <c r="N139" t="b">
         <v>1</v>
@@ -8054,7 +8062,7 @@
         <v>-27.3</v>
       </c>
       <c r="H140" t="n">
-        <v>25.8</v>
+        <v>24.39</v>
       </c>
       <c r="I140" t="n">
         <v>-8.83</v>
@@ -8069,7 +8077,7 @@
         <v>-19.66</v>
       </c>
       <c r="M140" t="n">
-        <v>22.49</v>
+        <v>21.48</v>
       </c>
       <c r="N140" t="b">
         <v>0</v>
@@ -8107,7 +8115,7 @@
         <v>-23.5</v>
       </c>
       <c r="H141" t="n">
-        <v>28.03</v>
+        <v>27.44</v>
       </c>
       <c r="I141" t="n">
         <v>20.48</v>
@@ -8122,7 +8130,7 @@
         <v>-2.25</v>
       </c>
       <c r="M141" t="n">
-        <v>24.72</v>
+        <v>24.52</v>
       </c>
       <c r="N141" t="b">
         <v>0</v>
@@ -8164,7 +8172,7 @@
         <v>-3.2</v>
       </c>
       <c r="H142" t="n">
-        <v>23.23</v>
+        <v>17.86</v>
       </c>
       <c r="I142" t="n">
         <v>15.28</v>
@@ -8179,7 +8187,7 @@
         <v>-2.53</v>
       </c>
       <c r="M142" t="n">
-        <v>19.92</v>
+        <v>14.95</v>
       </c>
       <c r="N142" t="b">
         <v>0</v>
@@ -8217,7 +8225,7 @@
         <v>-12.5</v>
       </c>
       <c r="H143" t="n">
-        <v>-3.82</v>
+        <v>3.54</v>
       </c>
       <c r="I143" t="n">
         <v>21.54</v>
@@ -8232,7 +8240,7 @@
         <v>-0.95</v>
       </c>
       <c r="M143" t="n">
-        <v>-7.79</v>
+        <v>-0.03</v>
       </c>
       <c r="N143" t="b">
         <v>0</v>
@@ -8270,7 +8278,7 @@
         <v>-23.4</v>
       </c>
       <c r="H144" t="n">
-        <v>-3.9</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="I144" t="n">
         <v>-3.58</v>
@@ -8285,7 +8293,7 @@
         <v>-17.98</v>
       </c>
       <c r="M144" t="n">
-        <v>-7.86</v>
+        <v>-2.63</v>
       </c>
       <c r="N144" t="b">
         <v>0</v>
@@ -8327,7 +8335,7 @@
         <v>-3.4</v>
       </c>
       <c r="H145" t="n">
-        <v>15.65</v>
+        <v>12.31</v>
       </c>
       <c r="I145" t="n">
         <v>30.48</v>
@@ -8342,7 +8350,7 @@
         <v>-0.9</v>
       </c>
       <c r="M145" t="n">
-        <v>11.68</v>
+        <v>8.74</v>
       </c>
       <c r="N145" t="b">
         <v>0</v>
@@ -8380,7 +8388,7 @@
         <v>-37</v>
       </c>
       <c r="H146" t="n">
-        <v>63.48</v>
+        <v>60.53</v>
       </c>
       <c r="I146" t="n">
         <v>18.38</v>
@@ -8395,7 +8403,7 @@
         <v>-5.11</v>
       </c>
       <c r="M146" t="n">
-        <v>59.52</v>
+        <v>56.95</v>
       </c>
       <c r="N146" t="b">
         <v>1</v>
@@ -8433,7 +8441,7 @@
         <v>-28.9</v>
       </c>
       <c r="H147" t="n">
-        <v>-9.5</v>
+        <v>-7.33</v>
       </c>
       <c r="I147" t="n">
         <v>-12.9</v>
@@ -8448,7 +8456,7 @@
         <v>-23.19</v>
       </c>
       <c r="M147" t="n">
-        <v>-13.47</v>
+        <v>-10.9</v>
       </c>
       <c r="N147" t="b">
         <v>0</v>
@@ -8486,7 +8494,7 @@
         <v>-26.8</v>
       </c>
       <c r="H148" t="n">
-        <v>17.89</v>
+        <v>26.33</v>
       </c>
       <c r="I148" t="n">
         <v>4.56</v>
@@ -8501,7 +8509,7 @@
         <v>-4.09</v>
       </c>
       <c r="M148" t="n">
-        <v>13.92</v>
+        <v>22.76</v>
       </c>
       <c r="N148" t="b">
         <v>1</v>
@@ -8543,7 +8551,7 @@
         <v>-9.800000000000001</v>
       </c>
       <c r="H149" t="n">
-        <v>-19.8</v>
+        <v>-18.04</v>
       </c>
       <c r="I149" t="n">
         <v>-4.09</v>
@@ -8558,7 +8566,7 @@
         <v>-15.24</v>
       </c>
       <c r="M149" t="n">
-        <v>-24.98</v>
+        <v>-22.82</v>
       </c>
       <c r="N149" t="b">
         <v>0</v>
@@ -8596,7 +8604,7 @@
         <v>13.2</v>
       </c>
       <c r="H150" t="n">
-        <v>60.21</v>
+        <v>64.72</v>
       </c>
       <c r="I150" t="n">
         <v>8.130000000000001</v>
@@ -8611,7 +8619,7 @@
         <v>-2.36</v>
       </c>
       <c r="M150" t="n">
-        <v>55.03</v>
+        <v>59.93</v>
       </c>
       <c r="N150" t="b">
         <v>0</v>
@@ -8649,7 +8657,7 @@
         <v>21</v>
       </c>
       <c r="H151" t="n">
-        <v>12.5</v>
+        <v>13.63</v>
       </c>
       <c r="I151" t="n">
         <v>-0.72</v>
@@ -8664,7 +8672,7 @@
         <v>-7.35</v>
       </c>
       <c r="M151" t="n">
-        <v>7.31</v>
+        <v>8.84</v>
       </c>
       <c r="N151" t="b">
         <v>0</v>
@@ -8702,7 +8710,7 @@
         <v>6.1</v>
       </c>
       <c r="H152" t="n">
-        <v>3.38</v>
+        <v>5.53</v>
       </c>
       <c r="I152" t="n">
         <v>10.43</v>
@@ -8717,7 +8725,7 @@
         <v>-1.51</v>
       </c>
       <c r="M152" t="n">
-        <v>-1.8</v>
+        <v>0.74</v>
       </c>
       <c r="N152" t="b">
         <v>0</v>
@@ -8755,7 +8763,7 @@
         <v>6.5</v>
       </c>
       <c r="H153" t="n">
-        <v>11.09</v>
+        <v>13.36</v>
       </c>
       <c r="I153" t="n">
         <v>-0.04</v>
@@ -8770,7 +8778,7 @@
         <v>-4.12</v>
       </c>
       <c r="M153" t="n">
-        <v>5.91</v>
+        <v>8.57</v>
       </c>
       <c r="N153" t="b">
         <v>0</v>
@@ -8808,7 +8816,7 @@
         <v>-36.5</v>
       </c>
       <c r="H154" t="n">
-        <v>-31.66</v>
+        <v>-30.05</v>
       </c>
       <c r="I154" t="n">
         <v>-27.75</v>
@@ -8823,7 +8831,7 @@
         <v>-31.28</v>
       </c>
       <c r="M154" t="n">
-        <v>-36.28</v>
+        <v>-34.28</v>
       </c>
       <c r="N154" t="b">
         <v>1</v>
@@ -8861,7 +8869,7 @@
         <v>1.7</v>
       </c>
       <c r="H155" t="n">
-        <v>-13.17</v>
+        <v>-8.300000000000001</v>
       </c>
       <c r="I155" t="n">
         <v>8.859999999999999</v>
@@ -8876,7 +8884,7 @@
         <v>-3.27</v>
       </c>
       <c r="M155" t="n">
-        <v>-17.8</v>
+        <v>-12.53</v>
       </c>
       <c r="N155" t="b">
         <v>0</v>
@@ -8914,7 +8922,7 @@
         <v>-14.5</v>
       </c>
       <c r="H156" t="n">
-        <v>3.15</v>
+        <v>7.65</v>
       </c>
       <c r="I156" t="n">
         <v>4.48</v>
@@ -8929,7 +8937,7 @@
         <v>-3.33</v>
       </c>
       <c r="M156" t="n">
-        <v>-1.48</v>
+        <v>3.42</v>
       </c>
       <c r="N156" t="b">
         <v>0</v>
@@ -8967,7 +8975,7 @@
         <v>48.1</v>
       </c>
       <c r="H157" t="n">
-        <v>6.1</v>
+        <v>7.56</v>
       </c>
       <c r="I157" t="n">
         <v>0.16</v>
@@ -8982,7 +8990,7 @@
         <v>-8.890000000000001</v>
       </c>
       <c r="M157" t="n">
-        <v>1.47</v>
+        <v>3.33</v>
       </c>
       <c r="N157" t="b">
         <v>0</v>
@@ -9020,7 +9028,7 @@
         <v>24.9</v>
       </c>
       <c r="H158" t="n">
-        <v>4.38</v>
+        <v>-3.65</v>
       </c>
       <c r="I158" t="n">
         <v>10.45</v>
@@ -9035,7 +9043,7 @@
         <v>-0.49</v>
       </c>
       <c r="M158" t="n">
-        <v>-0.25</v>
+        <v>-7.88</v>
       </c>
       <c r="N158" t="b">
         <v>0</v>
@@ -9073,7 +9081,7 @@
         <v>-38.7</v>
       </c>
       <c r="H159" t="n">
-        <v>5.8</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="I159" t="n">
         <v>17.17</v>
@@ -9088,7 +9096,7 @@
         <v>-0.54</v>
       </c>
       <c r="M159" t="n">
-        <v>1.17</v>
+        <v>3.88</v>
       </c>
       <c r="N159" t="b">
         <v>1</v>
@@ -9126,7 +9134,7 @@
         <v>-34.6</v>
       </c>
       <c r="H160" t="n">
-        <v>20.77</v>
+        <v>16.46</v>
       </c>
       <c r="I160" t="n">
         <v>6.67</v>
@@ -9141,7 +9149,7 @@
         <v>-3.06</v>
       </c>
       <c r="M160" t="n">
-        <v>16.14</v>
+        <v>12.23</v>
       </c>
       <c r="N160" t="b">
         <v>1</v>
@@ -9179,7 +9187,7 @@
         <v>-21.4</v>
       </c>
       <c r="H161" t="n">
-        <v>-14.13</v>
+        <v>-14.05</v>
       </c>
       <c r="I161" t="n">
         <v>2.8</v>
@@ -9194,7 +9202,7 @@
         <v>-2.27</v>
       </c>
       <c r="M161" t="n">
-        <v>-18.76</v>
+        <v>-18.28</v>
       </c>
       <c r="N161" t="b">
         <v>0</v>
@@ -9232,7 +9240,7 @@
         <v>0.1</v>
       </c>
       <c r="H162" t="n">
-        <v>-1.79</v>
+        <v>-0.27</v>
       </c>
       <c r="I162" t="n">
         <v>-2.83</v>
@@ -9247,7 +9255,7 @@
         <v>-5.45</v>
       </c>
       <c r="M162" t="n">
-        <v>-6.53</v>
+        <v>-4.61</v>
       </c>
       <c r="N162" t="b">
         <v>1</v>
@@ -9285,7 +9293,7 @@
         <v>-11.8</v>
       </c>
       <c r="H163" t="n">
-        <v>6.08</v>
+        <v>7.97</v>
       </c>
       <c r="I163" t="n">
         <v>9.76</v>
@@ -9300,7 +9308,7 @@
         <v>-1.63</v>
       </c>
       <c r="M163" t="n">
-        <v>1.34</v>
+        <v>3.63</v>
       </c>
       <c r="N163" t="b">
         <v>1</v>
@@ -9338,7 +9346,7 @@
         <v>-13.8</v>
       </c>
       <c r="H164" t="n">
-        <v>22.75</v>
+        <v>24.86</v>
       </c>
       <c r="I164" t="n">
         <v>4.67</v>
@@ -9353,7 +9361,7 @@
         <v>-5.7</v>
       </c>
       <c r="M164" t="n">
-        <v>18.01</v>
+        <v>20.52</v>
       </c>
       <c r="N164" t="b">
         <v>0</v>
@@ -9395,7 +9403,7 @@
         <v>-8.800000000000001</v>
       </c>
       <c r="H165" t="n">
-        <v>8.029999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="I165" t="n">
         <v>15.97</v>
@@ -9410,7 +9418,7 @@
         <v>-0.79</v>
       </c>
       <c r="M165" t="n">
-        <v>3.29</v>
+        <v>4.16</v>
       </c>
       <c r="N165" t="b">
         <v>0</v>
@@ -9448,7 +9456,7 @@
         <v>-15.9</v>
       </c>
       <c r="H166" t="n">
-        <v>23.61</v>
+        <v>24.31</v>
       </c>
       <c r="I166" t="n">
         <v>10.45</v>
@@ -9463,7 +9471,7 @@
         <v>-0.31</v>
       </c>
       <c r="M166" t="n">
-        <v>19.67</v>
+        <v>20.77</v>
       </c>
       <c r="N166" t="b">
         <v>1</v>
@@ -9501,7 +9509,7 @@
         <v>24.1</v>
       </c>
       <c r="H167" t="n">
-        <v>3.77</v>
+        <v>3.25</v>
       </c>
       <c r="I167" t="n">
         <v>-8.31</v>
@@ -9516,7 +9524,7 @@
         <v>-18.31</v>
       </c>
       <c r="M167" t="n">
-        <v>-0.17</v>
+        <v>-0.29</v>
       </c>
       <c r="N167" t="b">
         <v>1</v>
@@ -9554,7 +9562,7 @@
         <v>-23.3</v>
       </c>
       <c r="H168" t="n">
-        <v>-14.77</v>
+        <v>-36.18</v>
       </c>
       <c r="I168" t="n">
         <v>-20.42</v>
@@ -9569,7 +9577,7 @@
         <v>-27.45</v>
       </c>
       <c r="M168" t="n">
-        <v>-18.7</v>
+        <v>-39.72</v>
       </c>
       <c r="N168" t="b">
         <v>0</v>
@@ -9607,7 +9615,7 @@
         <v>28.9</v>
       </c>
       <c r="H169" t="n">
-        <v>-1.47</v>
+        <v>-2.99</v>
       </c>
       <c r="I169" t="n">
         <v>8.06</v>
@@ -9622,7 +9630,7 @@
         <v>-2.79</v>
       </c>
       <c r="M169" t="n">
-        <v>-6.31</v>
+        <v>-7.43</v>
       </c>
       <c r="N169" t="b">
         <v>0</v>
@@ -9660,7 +9668,7 @@
         <v>40.1</v>
       </c>
       <c r="H170" t="n">
-        <v>44.14</v>
+        <v>41.16</v>
       </c>
       <c r="I170" t="n">
         <v>15.9</v>
@@ -9675,7 +9683,7 @@
         <v>-5.87</v>
       </c>
       <c r="M170" t="n">
-        <v>39.3</v>
+        <v>36.73</v>
       </c>
       <c r="N170" t="b">
         <v>0</v>
@@ -9713,7 +9721,7 @@
         <v>-27.3</v>
       </c>
       <c r="H171" t="n">
-        <v>-1.85</v>
+        <v>-2.19</v>
       </c>
       <c r="I171" t="n">
         <v>0.75</v>
@@ -9728,7 +9736,7 @@
         <v>-5.46</v>
       </c>
       <c r="M171" t="n">
-        <v>-6.56</v>
+        <v>-6.51</v>
       </c>
       <c r="N171" t="b">
         <v>0</v>
@@ -9766,7 +9774,7 @@
         <v>19.7</v>
       </c>
       <c r="H172" t="n">
-        <v>-20.96</v>
+        <v>-19.93</v>
       </c>
       <c r="I172" t="n">
         <v>-4.49</v>
@@ -9781,7 +9789,7 @@
         <v>-13.7</v>
       </c>
       <c r="M172" t="n">
-        <v>-25.68</v>
+        <v>-24.25</v>
       </c>
       <c r="N172" t="b">
         <v>0</v>
@@ -9819,7 +9827,7 @@
         <v>-21.3</v>
       </c>
       <c r="H173" t="n">
-        <v>1.48</v>
+        <v>4.26</v>
       </c>
       <c r="I173" t="n">
         <v>7.16</v>
@@ -9834,7 +9842,7 @@
         <v>-11.9</v>
       </c>
       <c r="M173" t="n">
-        <v>-3.23</v>
+        <v>-0.05</v>
       </c>
       <c r="N173" t="b">
         <v>0</v>
@@ -9872,7 +9880,7 @@
         <v>-21.8</v>
       </c>
       <c r="H174" t="n">
-        <v>-37.24</v>
+        <v>-38.47</v>
       </c>
       <c r="I174" t="n">
         <v>-18.97</v>
@@ -9887,7 +9895,7 @@
         <v>-26.82</v>
       </c>
       <c r="M174" t="n">
-        <v>-41.96</v>
+        <v>-42.78</v>
       </c>
       <c r="N174" t="b">
         <v>1</v>
@@ -9925,7 +9933,7 @@
         <v>-37.6</v>
       </c>
       <c r="H175" t="n">
-        <v>-14.3</v>
+        <v>-9.26</v>
       </c>
       <c r="I175" t="n">
         <v>15.2</v>
@@ -9940,7 +9948,7 @@
         <v>-10.3</v>
       </c>
       <c r="M175" t="n">
-        <v>-18</v>
+        <v>-12.56</v>
       </c>
       <c r="N175" t="b">
         <v>0</v>
@@ -9978,7 +9986,7 @@
         <v>53.8</v>
       </c>
       <c r="H176" t="n">
-        <v>57.62</v>
+        <v>57.06</v>
       </c>
       <c r="I176" t="n">
         <v>4.09</v>
@@ -9993,7 +10001,7 @@
         <v>-8.66</v>
       </c>
       <c r="M176" t="n">
-        <v>53.93</v>
+        <v>53.76</v>
       </c>
       <c r="N176" t="b">
         <v>0</v>
@@ -10035,7 +10043,7 @@
         <v>-5.7</v>
       </c>
       <c r="H177" t="n">
-        <v>31.32</v>
+        <v>30.55</v>
       </c>
       <c r="I177" t="n">
         <v>17.92</v>
@@ -10050,7 +10058,7 @@
         <v>-7.48</v>
       </c>
       <c r="M177" t="n">
-        <v>27.62</v>
+        <v>27.25</v>
       </c>
       <c r="N177" t="b">
         <v>0</v>
@@ -10088,7 +10096,7 @@
         <v>-39.3</v>
       </c>
       <c r="H178" t="n">
-        <v>11.94</v>
+        <v>12.96</v>
       </c>
       <c r="I178" t="n">
         <v>11.34</v>
@@ -10103,7 +10111,7 @@
         <v>-5.3</v>
       </c>
       <c r="M178" t="n">
-        <v>8.24</v>
+        <v>9.66</v>
       </c>
       <c r="N178" t="b">
         <v>0</v>
@@ -10141,7 +10149,7 @@
         <v>57</v>
       </c>
       <c r="H179" t="n">
-        <v>20.54</v>
+        <v>20.46</v>
       </c>
       <c r="I179" t="n">
         <v>-11.21</v>
@@ -10156,7 +10164,7 @@
         <v>-13.87</v>
       </c>
       <c r="M179" t="n">
-        <v>16.84</v>
+        <v>17.16</v>
       </c>
       <c r="N179" t="b">
         <v>1</v>
@@ -10194,7 +10202,7 @@
         <v>-21.8</v>
       </c>
       <c r="H180" t="n">
-        <v>19.73</v>
+        <v>24.05</v>
       </c>
       <c r="I180" t="n">
         <v>1.71</v>
@@ -10209,7 +10217,7 @@
         <v>-6.18</v>
       </c>
       <c r="M180" t="n">
-        <v>16.03</v>
+        <v>2